--- a/PIRNN/01-Pwm-XYTheta/Ts-03/resultados.xlsx
+++ b/PIRNN/01-Pwm-XYTheta/Ts-03/resultados.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AN10"/>
+  <dimension ref="A1:AN46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -633,1219 +633,1219 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>model_5_0</t>
+          <t>model_5_2_0</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>[5]</t>
+          <t>[5, 2]</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>[[[-0.04259999841451645, 0.029600000008940697, -0.07779999822378159, -0.005100000184029341, -0.04410000145435333], [-0.04879999905824661, 0.02410000003874302, -0.08290000259876251, -0.048500001430511475, -0.09309999644756317]], [[0.13539999723434448, -0.4584999978542328, -0.477400004863739, -0.1550000011920929, -0.72079998254776], [0.5835999846458435, -0.4325999915599823, 0.2556000053882599, 0.6330000162124634, 0.07940000295639038], [0.19769999384880066, -0.5473999977111816, 0.16369999945163727, -0.6754999756813049, 0.4221000075340271], [0.7177000045776367, 0.4742000102996826, -0.4474000036716461, -0.17790000140666962, 0.16779999434947968], [0.29490000009536743, 0.2793999910354614, 0.6926000118255615, -0.2955999970436096, -0.5174999833106995]], [0.0, 0.0, 0.0, 0.0, 0.0], [[-0.04259999841451645, 0.029600000008940697, -0.07779999822378159], [-0.005100000184029341, -0.04410000145435333, -0.04879999905824661], [0.02410000003874302, -0.08290000259876251, -0.048500001430511475], [-0.09309999644756317, -0.053599998354911804, 0.0340999998152256], [0.01899999938905239, -0.04569999873638153, 0.06360000371932983]], [0.0, 0.0, 0.0]]</t>
+          <t>[[[0.03319999948143959, 0.0027000000700354576, -0.016699999570846558, -0.0017999999690800905, 0.12229999899864197], [-0.014700000174343586, -0.04670000076293945, -0.05999999865889549, -0.0005000000237487257, -0.16120000183582306]], [[0.2806999981403351, 0.7276999950408936, -0.33489999175071716, 0.40529999136924744, -0.3395000100135803], [-0.4000999927520752, 0.1981000006198883, 0.6194999814033508, 0.6101999878883362, 0.210999995470047], [0.23909999430179596, -0.1762000024318695, -0.4426000118255615, 0.4065999984741211, 0.7419999837875366], [0.7856000065803528, 0.12690000236034393, 0.5533999800682068, -0.15410000085830688, 0.1914999932050705], [-0.2944999933242798, 0.6197999715805054, -0.04390000179409981, -0.5236999988555908, 0.5029000043869019]], [0.0, 0.0, 0.0, 0.0, 0.0], [[0.03319999948143959, 0.0027000000700354576], [-0.016699999570846558, -0.0017999999690800905], [0.12229999899864197, -0.014700000174343586], [-0.04670000076293945, -0.05999999865889549], [-0.0005000000237487257, -0.16120000183582306]], [[-0.9934999942779541, -0.11349999904632568], [-0.11349999904632568, 0.9934999942779541]], [0.0, 0.0], [[0.03319999948143959, 0.0027000000700354576, -0.016699999570846558], [-0.0017999999690800905, 0.12229999899864197, -0.014700000174343586]], [0.0, 0.0, 0.0]]</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>[[[0.006599999964237213, 0.6840000152587891, -0.24199999868869781, 0.31850001215934753, 0.42910000681877136], [0.2994999885559082, -0.4717999994754791, 0.21529999375343323, -0.19609999656677246, -0.6122999787330627]], [[0.6715999841690063, -0.40700000524520874, -0.2872999906539917, -0.4715999960899353, 0.0340999998152256], [1.038599967956543, -0.11980000138282776, 0.8726000189781189, 0.9269000291824341, 0.631600022315979], [0.5659000277519226, -1.0200999975204468, 0.1987999975681305, -1.3314000368118286, 0.9229999780654907], [0.8022000193595886, 0.5716999769210815, -0.3522999882698059, -0.259799987077713, 0.15379999577999115], [0.2831999957561493, 1.020799994468689, 1.3509000539779663, 0.0034000000450760126, -0.11509999632835388]], [0.21979999542236328, 0.09160000085830688, 0.2687999904155731, 0.2345999926328659, -0.16349999606609344], [[1.0348000526428223, 0.42160001397132874, -0.014000000432133675], [-0.8202000260353088, 0.25429999828338623, -0.057999998331069946], [0.11550000309944153, -0.36570000648498535, 0.14059999585151672], [-0.8858000040054321, 0.15629999339580536, 0.22210000455379486], [0.29030001163482666, -0.3384999930858612, -0.09610000252723694]], [-0.2793999910354614, 0.0034000000450760126, 0.0203000009059906]]</t>
+          <t>[[[0.6812000274658203, -0.039000000804662704, 0.3359000086784363, -0.21619999408721924, 0.23929999768733978], [-0.6258999705314636, 0.14810000360012054, 0.36469998955726624, 0.08049999922513962, -0.46790000796318054]], [[0.7383000254631042, 1.1612000465393066, -1.0961999893188477, 0.043699998408555984, -0.3831000030040741], [-0.8338000178337097, 0.8133999705314636, 1.3062000274658203, 1.3357000350952148, 0.4415000081062317], [0.6097999811172485, -0.32679998874664307, -0.949400007724762, -0.03849999979138374, 0.3208000063896179], [0.7853999733924866, 0.15199999511241913, 1.0077999830245972, -0.37860000133514404, -0.44839999079704285], [0.05559999868273735, 1.180299997329712, -0.5346999764442444, -0.6244000196456909, 0.5123000144958496]], [0.18140000104904175, -0.18299999833106995, 0.2888999879360199, -0.7340999841690063, -0.0478999987244606], [[-0.8977000117301941, 0.32359999418258667], [0.4212999939918518, 0.08460000157356262], [0.998199999332428, 0.06989999860525131], [0.9358999729156494, 0.010900000110268593], [-0.12229999899864197, -0.490200012922287]], [[-1.0424000024795532, -0.4237000048160553], [-0.25060001015663147, 1.3947999477386475]], [-0.15919999778270721, -0.06289999932050705], [[1.3350000381469727, -0.13670000433921814, 0.19900000095367432], [0.1996999979019165, 0.35249999165534973, -0.5544000267982483]], [0.004399999976158142, -0.01720000058412552, 0.0877000018954277]]</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>[0.95345422290353]</t>
+          <t>[0.6511766035568695]</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>[0.010624847602176132]</t>
+          <t>[0.07962474059892329]</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>[0.3825173674879414]</t>
+          <t>[0.16861388879957195]</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>[0.14097330475521797]</t>
+          <t>[0.18980816860662822]</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>[0.859923561488802]</t>
+          <t>[0.6817531126244752]</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>[0.045844174008711644]</t>
+          <t>[0.10415574408973913]</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>[0.718411401092936]</t>
+          <t>[0.6670786729872502]</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>[0.06468627195378163]</t>
+          <t>[0.07647837867707205]</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>[-0.31219740850772393]</t>
+          <t>[-0.3876603594078345]</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>[0.3112020851942182]</t>
+          <t>[0.3290989561396733]</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>[-0.4279768921534204]</t>
+          <t>[0.5803565110344266]</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>[0.46944375282771267]</t>
+          <t>[0.1379567242244619]</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>[0.7980647717831609]</t>
+          <t>[-0.08155643136541335]</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>[0.021773813195300955]</t>
+          <t>[0.1166196106775345]</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>[-0.5479522285622318]</t>
+          <t>[-0.08107721898495668]</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>[0.13043098070984815]</t>
+          <t>[0.0910919337777318]</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>[-1.0419928174283983]</t>
+          <t>[-0.973804054242323]</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>[0.19526174582227224]</t>
+          <t>[0.18874132281611175]</t>
         </is>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>[0.6949368029479321]</t>
+          <t>[-0.22341470890075787]</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>[0.03195861074664075]</t>
+          <t>[0.1281656877699371]</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>[-0.5772660000508636]</t>
+          <t>[-0.1500386412557384]</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>[0.12979828169802934]</t>
+          <t>[0.09464037107026813]</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>[-1.531710344924643]</t>
+          <t>[-1.4423936831997608]</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>[0.23292842630855493]</t>
+          <t>[0.2247109027279379]</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>[-1.9725706627095168]</t>
+          <t>[-0.8534662757753562]</t>
         </is>
       </c>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>[0.24908944621317822]</t>
+          <t>[0.1553130070209541]</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>[-2.7162414676261357]</t>
+          <t>[-0.7352855915969194]</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>[0.4001577240671559]</t>
+          <t>[0.18685221048984021]</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>[-2.5506048202302285]</t>
+          <t>[-3.7264947543485034]</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>[0.2643423813497446]</t>
+          <t>[0.351887338090344]</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>[-2.2111182642387277]</t>
+          <t>[-1.1510038810379646]</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>[0.26314756709235326]</t>
+          <t>[0.17627237352329078]</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>[-2.6830816482026956]</t>
+          <t>[-0.8032322657876954]</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>[0.3909321323517216]</t>
+          <t>[0.1913998933837956]</t>
         </is>
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>[-2.6043100453375683]</t>
+          <t>[-4.9071711106351765]</t>
         </is>
       </c>
       <c r="AN2" t="inlineStr">
         <is>
-          <t>[0.2768371413022212]</t>
+          <t>[0.4537135659477236]</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>model_10_0</t>
+          <t>model_5_2_1</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>[10]</t>
+          <t>[5, 2]</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>[[[-0.04259999841451645, 0.029600000008940697, -0.07779999822378159, -0.005100000184029341, -0.04410000145435333, -0.04879999905824661, 0.02410000003874302, -0.08290000259876251, -0.048500001430511475, -0.09309999644756317], [-0.053599998354911804, 0.0340999998152256, 0.01899999938905239, -0.04569999873638153, 0.06360000371932983, 0.0364999994635582, 0.09669999778270721, -0.010900000110268593, -0.0017000000225380063, 0.053700000047683716]], [[0.07959999889135361, -0.534500002861023, 0.2207999974489212, -0.08789999783039093, 0.051600001752376556, -0.1599999964237213, 0.3001999855041504, 0.6685000061988831, -0.10980000346899033, -0.27239999175071716], [0.41990000009536743, -0.20909999310970306, -0.13349999487400055, -0.056699998676776886, -0.2906999886035919, -0.6370999813079834, -0.07919999957084656, -0.2800999879837036, 0.39309999346733093, -0.17090000212192535], [0.4894999861717224, 0.19269999861717224, 0.1931000053882599, 0.08820000290870667, 0.5702000260353088, -0.2630999982357025, 0.3181999921798706, -0.1882999986410141, -0.3384000062942505, 0.18050000071525574], [-0.1273999959230423, 0.2160000056028366, -0.1565999984741211, 0.2485000044107437, 0.5432999730110168, 0.026399999856948853, 0.07079999893903732, 0.10819999873638153, 0.5669999718666077, -0.46560001373291016], [0.15559999644756317, 0.11699999868869781, -0.7394000291824341, -0.44850000739097595, 0.1298999935388565, -0.0038999998942017555, -0.11420000344514847, 0.15690000355243683, -0.33559998869895935, -0.21719999611377716], [-0.6704000234603882, 0.2159000039100647, 0.05429999902844429, -0.15809999406337738, -0.029600000008940697, -0.5680000185966492, 0.2678000032901764, -0.13030000030994415, -0.2134000062942505, -0.13519999384880066], [-0.1324000060558319, -0.41659998893737793, 0.2858999967575073, -0.5162000060081482, 0.39809998869895935, 0.13079999387264252, -0.30000001192092896, -0.4081999957561493, 0.02500000037252903, -0.16680000722408295], [-0.003100000089034438, -0.28769999742507935, -0.24199999868869781, 0.0997999981045723, -0.15610000491142273, 0.34549999237060547, 0.6714000105857849, -0.4456999897956848, -0.054999999701976776, -0.2290000021457672], [0.15919999778270721, 0.2084999978542328, 0.28220000863075256, 0.2551000118255615, -0.20839999616146088, 0.07100000232458115, -0.27390000224113464, -0.10700000077486038, -0.40139999985694885, -0.7002000212669373], [-0.2117999941110611, -0.47609999775886536, -0.31940001249313354, 0.5932000279426575, 0.22020000219345093, -0.18569999933242798, -0.31119999289512634, -0.09529999643564224, -0.2728999853134155, 0.10570000112056732]], [0.0, 0.0, 0.0, 0.0, 0.0, 0.0, 0.0, 0.0, 0.0, 0.0], [[-0.04259999841451645, 0.029600000008940697, -0.07779999822378159], [-0.005100000184029341, -0.04410000145435333, -0.04879999905824661], [0.02410000003874302, -0.08290000259876251, -0.048500001430511475], [-0.09309999644756317, -0.053599998354911804, 0.0340999998152256], [0.01899999938905239, -0.04569999873638153, 0.06360000371932983], [0.0364999994635582, 0.09669999778270721, -0.010900000110268593], [-0.0017000000225380063, 0.053700000047683716, 0.0625], [0.025100000202655792, -0.013000000268220901, -0.017400000244379044], [-0.05829999968409538, 0.017000000923871994, -0.08060000091791153], [0.013899999670684338, 0.06469999998807907, -0.007400000002235174]], [0.0, 0.0, 0.0]]</t>
+          <t>[[[0.01979999989271164, -0.020899999886751175, 0.04690000042319298, 0.05649999901652336, 0.05119999870657921], [-0.12319999933242798, 0.017400000244379044, 0.01510000042617321, -0.01759999990463257, 0.030300000682473183]], [[0.7200999855995178, -0.5178999900817871, 0.26930001378059387, -0.2728999853134155, -0.2574000060558319], [0.6653000116348267, 0.35120001435279846, -0.44269999861717224, 0.2660999894142151, 0.4090000092983246], [-0.032499998807907104, -0.15330000221729279, 0.5831000208854675, 0.029200000688433647, 0.7965999841690063], [-0.0019000000320374966, 0.323199987411499, -0.12549999356269836, -0.9190000295639038, 0.18770000338554382], [0.19460000097751617, 0.6931999921798706, 0.6129999756813049, 0.09619999676942825, -0.3109000027179718]], [0.0, 0.0, 0.0, 0.0, 0.0], [[0.01979999989271164, -0.020899999886751175], [0.04690000042319298, 0.05649999901652336], [0.05119999870657921, -0.12319999933242798], [0.017400000244379044, 0.01510000042617321], [-0.01759999990463257, 0.030300000682473183]], [[0.9728000164031982, -0.23160000145435333], [-0.23160000145435333, -0.9728000164031982]], [0.0, 0.0], [[0.01979999989271164, -0.020899999886751175, 0.04690000042319298], [0.05649999901652336, 0.05119999870657921, -0.12319999933242798]], [0.0, 0.0, 0.0]]</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>[[[0.28380000591278076, -0.18889999389648438, -0.670799970626831, -0.22050000727176666, -0.1331000030040741, 0.10360000282526016, -0.18619999289512634, 0.014999999664723873, -0.1290999948978424, -0.40070000290870667], [-0.37540000677108765, 0.11699999868869781, 0.2386000007390976, -0.2134999930858612, 0.14030000567436218, 0.3068999946117401, 0.5278000235557556, -0.17440000176429749, -0.2705000042915344, 0.5182999968528748]], [[-0.2623000144958496, -0.5128999948501587, 0.20260000228881836, -0.17239999771118164, 0.033799998462200165, -0.02160000056028366, 0.1412999927997589, 1.0078999996185303, 0.03460000082850456, -0.8870000243186951], [0.4025999903678894, -0.40790000557899475, -0.163100004196167, -0.05979999899864197, -0.23649999499320984, -0.774399995803833, 0.2547999918460846, -0.5619999766349792, 0.2563000023365021, -0.3849000036716461], [0.7613000273704529, 0.016100000590085983, 0.36730000376701355, 0.2782000005245209, 0.9200999736785889, -0.4844000041484833, 0.7276999950408936, -0.890999972820282, -0.6786999702453613, -0.011500000022351742], [0.024700000882148743, 0.19779999554157257, -0.11860000342130661, 0.3086000084877014, 0.9545999765396118, 0.01640000008046627, -0.11219999939203262, 0.19249999523162842, 0.4659999907016754, -0.7305999994277954], [0.05790000036358833, -0.05510000139474869, -0.8780999779701233, -0.3483999967575073, 0.7538999915122986, -0.6614000201225281, -0.6205999851226807, 0.2937000095844269, -0.8345999717712402, 0.21629999577999115], [-0.9922000169754028, 0.06800000369548798, 0.1932000070810318, -0.11259999871253967, -0.5072000026702881, -1.0498000383377075, 0.5992000102996826, -0.6212999820709229, -0.2815999984741211, -0.07440000027418137], [-0.4401000142097473, -0.5662000179290771, 0.5206999778747559, -0.6316999793052673, 0.186599999666214, -0.11710000038146973, -0.14300000667572021, -0.5509999990463257, -0.45730000734329224, -0.5030999779701233], [0.32989999651908875, -0.6033999919891357, -0.32839998602867126, 0.4657999873161316, -0.7735999822616577, 0.3052999973297119, 1.0362999439239502, -1.2283999919891357, 0.24060000479221344, -0.7328000068664551], [0.3894999921321869, 0.2709999978542328, 0.31189998984336853, 0.3571999967098236, -0.3393000066280365, 0.4198000133037567, -0.07569999992847443, -0.6510000228881836, -0.38119998574256897, -1.0877000093460083], [0.09570000320672989, -0.6263999938964844, -0.44440001249313354, 0.8122000098228455, 0.5799999833106995, -0.6370999813079834, -0.48100000619888306, -0.6604999899864197, -0.47429999709129333, 0.7468000054359436]], [-0.2280000001192093, -0.2248000055551529, -0.16859999299049377, -0.36250001192092896, 0.013100000098347664, 0.02329999953508377, 0.14890000224113464, -0.4593999981880188, 0.022099999710917473, 0.05829999968409538], [[-0.30169999599456787, -0.05460000038146973, -0.11110000312328339], [0.04490000009536743, -0.03290000185370445, -0.002400000113993883], [0.5278000235557556, -0.17720000445842743, -0.03590000048279762], [-0.04019999876618385, -0.24320000410079956, 0.050200000405311584], [-0.3199000060558319, -0.1485999971628189, 0.057999998331069946], [-0.4359000027179718, 0.16339999437332153, 0.0949999988079071], [0.617900013923645, -0.03700000047683716, -0.007000000216066837], [-0.6539999842643738, -0.14890000224113464, 0.09350000321865082], [-0.39320001006126404, -0.10580000281333923, -0.008700000122189522], [-0.28999999165534973, 0.13449999690055847, -0.06069999933242798]], [-0.065700002014637, -0.11840000003576279, 0.07580000162124634]]</t>
+          <t>[[[0.1688999980688095, -0.7548999786376953, -0.148499995470047, 0.17810000479221344, 0.07460000365972519], [-0.3578000068664551, 0.6554999947547913, 0.044599998742341995, -0.05719999969005585, 0.05909999832510948]], [[0.8925999999046326, -0.5579000115394592, 0.763700008392334, -0.6492999792098999, -0.5519000291824341], [0.5501999855041504, 0.9467999935150146, -0.9524000287055969, 0.784600019454956, 0.9501000046730042], [-0.10329999774694443, -0.11029999703168869, 0.007699999958276749, 0.3650999963283539, 0.9445000290870667], [-0.04520000144839287, 0.19900000095367432, 0.6227999925613403, -1.2905000448226929, -0.11620000004768372], [0.2029999941587448, 0.7838000059127808, 1.157099962234497, -0.1679999977350235, -0.5967000126838684]], [0.3264999985694885, 0.03500000014901161, 0.006399999838322401, -0.28040000796318054, 0.16899999976158142], [[0.17389999330043793, -0.27549999952316284], [-0.5521000027656555, 0.0997999981045723], [0.19840000569820404, -0.4074000120162964], [-0.12630000710487366, 0.42080000042915344], [-0.21289999783039093, 0.3986999988555908]], [[1.4703999757766724, -0.2070000022649765], [-0.7319999933242798, -1.1538000106811523]], [-0.2328999936580658, -0.0681999996304512], [[0.6315000057220459, -0.1145000010728836, 0.17949999868869781], [0.26089999079704285, 0.27790001034736633, -0.4251999855041504]], [0.08370000123977661, 0.09910000115633011, -0.093299999833107]]</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>[0.9377007449431272]</t>
+          <t>[0.8992823869060289]</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>[0.0142208409011303]</t>
+          <t>[0.02299046995736028]</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>[0.6455226999742752]</t>
+          <t>[0.34546036087925114]</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>[0.08092832707219089]</t>
+          <t>[0.14943354057547156]</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>[0.3644639374618752]</t>
+          <t>[-3.3301171910413414]</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>[0.2079980484189715]</t>
+          <t>[1.417159431622354]</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>[0.7844363757818309]</t>
+          <t>[0.6819471131650812]</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>[0.0495190759627359]</t>
+          <t>[0.07306281438006323]</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>[0.4163867258957319]</t>
+          <t>[0.7115015152829108]</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>[0.13841032353113658]</t>
+          <t>[0.06842059695989863]</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>[-2.4186010323453737]</t>
+          <t>[0.09926665789780953]</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>[1.123856350101555]</t>
+          <t>[0.29611378358920276]</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>[0.8145965372307196]</t>
+          <t>[-0.08407822636260631]</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>[0.019991263534094025]</t>
+          <t>[0.11689152506152084]</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>[-0.5936773589821236]</t>
+          <t>[0.07144699639557861]</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>[0.1342837957345674]</t>
+          <t>[0.0782401915682444]</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>[-0.37297940208082614]</t>
+          <t>[-0.24732223744303328]</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>[0.1312885886474094]</t>
+          <t>[0.11927285718506675]</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>[0.7488954564383499]</t>
+          <t>[-0.17278358238464864]</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>[0.026305868560834562]</t>
+          <t>[0.12286153938485321]</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>[-0.6140649166169041]</t>
+          <t>[0.08070891343488151]</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>[0.13282658265580513]</t>
+          <t>[0.07565141416388792]</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>[-1.9098645443477866]</t>
+          <t>[-0.7484985795137227]</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>[0.26772026683256483]</t>
+          <t>[0.16086951785197123]</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>[-2.021302285068814]</t>
+          <t>[-0.614198135648161]</t>
         </is>
       </c>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>[0.25317295984628485]</t>
+          <t>[0.1352633007958327]</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>[-2.852499740483261]</t>
+          <t>[-0.6288560814544373]</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>[0.4148297524664994]</t>
+          <t>[0.17539208581193474]</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>[-2.681125222568567]</t>
+          <t>[-1.5783769279246331]</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>[0.27405961988112415]</t>
+          <t>[0.19196005516058573]</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>[-2.2665949031351014]</t>
+          <t>[-0.8010924581900982]</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>[0.26769381589253655]</t>
+          <t>[0.14759752194722492]</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>[-2.8364199988877914]</t>
+          <t>[-0.5560861573325775]</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>[0.40720787482239773]</t>
+          <t>[0.16516714472128974]</t>
         </is>
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>[-2.484377281258029]</t>
+          <t>[-3.0334999641705327]</t>
         </is>
       </c>
       <c r="AN3" t="inlineStr">
         <is>
-          <t>[0.2676254355558739]</t>
+          <t>[0.30980203852551835]</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>model_15_0</t>
+          <t>model_5_2_2</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>[15]</t>
+          <t>[5, 2]</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>[[[-0.04259999841451645, 0.029600000008940697, -0.07779999822378159, -0.005100000184029341, -0.04410000145435333, -0.04879999905824661, 0.02410000003874302, -0.08290000259876251, -0.048500001430511475, -0.09309999644756317, -0.053599998354911804, 0.0340999998152256, 0.01899999938905239, -0.04569999873638153, 0.06360000371932983], [0.0364999994635582, 0.09669999778270721, -0.010900000110268593, -0.0017000000225380063, 0.053700000047683716, 0.0625, 0.025100000202655792, -0.013000000268220901, -0.017400000244379044, -0.05829999968409538, 0.017000000923871994, -0.08060000091791153, 0.013899999670684338, 0.06469999998807907, -0.007400000002235174]], [[0.22280000150203705, 0.13210000097751617, 0.06539999693632126, 0.1509999930858612, -0.16040000319480896, -0.14830000698566437, 0.06360000371932983, -0.027899999171495438, 0.287200003862381, -0.5, 0.38269999623298645, 0.07249999791383743, 0.40369999408721924, -0.29260000586509705, -0.34700000286102295], [-0.05119999870657921, 0.15240000188350677, -0.32600000500679016, 0.01600000075995922, -0.04479999840259552, -0.14509999752044678, 0.08370000123977661, 0.4902999997138977, 0.39730000495910645, -0.11079999804496765, 0.029500000178813934, -0.39640000462532043, 0.018300000578165054, -0.03370000049471855, 0.5171999931335449], [0.16099999845027924, -0.4544000029563904, -0.16060000658035278, 0.1720999926328659, 0.21160000562667847, 0.3885999917984009, -0.3601999878883362, 0.3889999985694885, 0.08919999748468399, 0.17550000548362732, 0.10700000077486038, -0.22290000319480896, 0.06859999895095825, -0.07020000368356705, -0.3547999858856201], [-0.03799999877810478, -0.3871999979019165, -0.06589999794960022, 0.04170000180602074, -0.031199999153614044, 0.0015999999595806003, 0.588699996471405, -0.04430000111460686, -0.09920000284910202, -0.37689998745918274, -0.30239999294281006, -0.38040000200271606, -0.0892999991774559, 0.18369999527931213, -0.2517000138759613], [0.33230000734329224, 0.15600000321865082, 0.12070000171661377, -0.2563999891281128, -0.07180000096559525, -0.08079999685287476, -0.2615000009536743, 0.1835000067949295, -0.6535000205039978, -0.21240000426769257, -0.11259999871253967, -0.35339999198913574, 0.19920000433921814, -0.11840000003576279, 0.08789999783039093], [0.07280000299215317, -0.04479999840259552, -0.3977999985218048, -0.29980000853538513, 0.009200000204145908, 0.021199999377131462, 0.22849999368190765, 0.3822999894618988, -0.28349998593330383, -0.12960000336170197, 0.3684000074863434, 0.47999998927116394, -0.09870000183582306, 0.2635999917984009, -0.05620000138878822], [-0.05689999833703041, 0.23389999568462372, -0.23180000483989716, -0.5274999737739563, -0.10920000076293945, 0.07580000162124634, -0.24539999663829803, -0.28360000252723694, 0.22210000455379486, -0.07840000092983246, 0.17020000517368317, -0.3465999960899353, -0.35580000281333923, 0.11829999834299088, -0.3264000117778778], [0.6141999959945679, 0.08760000020265579, -0.10980000346899033, 0.08100000023841858, 0.39430001378059387, -0.5041999816894531, -0.01640000008046627, -0.04989999905228615, 0.16449999809265137, 0.14270000159740448, -0.18549999594688416, 0.03009999915957451, -0.09929999709129333, 0.2705000042915344, -0.13519999384880066], [0.14319999516010284, -0.18359999358654022, 0.35030001401901245, -0.16279999911785126, 0.4740000069141388, 0.06949999928474426, 0.11900000274181366, -0.026200000196695328, 0.035999998450279236, -0.22609999775886536, 0.2856000065803528, -0.012199999764561653, -0.4578999876976013, -0.3822000026702881, 0.24979999661445618], [-0.1120000034570694, -0.009100000374019146, 0.6061999797821045, -0.25130000710487366, 0.08269999921321869, -0.057100001722574234, 0.11490000039339066, 0.22110000252723694, 0.14139999449253082, 0.17180000245571136, 0.2754000127315521, -0.1768999993801117, 0.2689000070095062, 0.5023999810218811, -0.05550000071525574], [0.14920000731945038, -0.5425999760627747, -0.13750000298023224, -0.39809998869895935, -0.03819999843835831, -0.002300000051036477, -0.1754000037908554, -0.33629998564720154, 0.19200000166893005, -0.12080000340938568, -0.07010000199079514, 0.12520000338554382, 0.3871000111103058, 0.08709999918937683, 0.362199991941452], [-0.3346000015735626, -0.12540000677108765, -0.2467000037431717, -0.13600000739097595, 0.2671000063419342, -0.44839999079704285, 0.17100000381469727, -0.11980000138282776, -0.1987999975681305, 0.3644999861717224, 0.24660000205039978, -0.20149999856948853, 0.24879999458789825, -0.35120001435279846, -0.13349999487400055], [-0.07280000299215317, -0.2928999960422516, 0.004000000189989805, 0.4189999997615814, -0.2513999938964844, -0.3456000089645386, -0.2962999939918518, -0.15049999952316284, -0.19349999725818634, -0.12200000137090683, 0.4336000084877014, -0.1453000009059906, -0.2685000002384186, 0.2874999940395355, 0.1551000028848648], [-0.20010000467300415, 0.2734000086784363, -0.1988999992609024, 0.22339999675750732, 0.5893999934196472, 0.2800000011920929, -0.08330000191926956, -0.2515000104904175, -0.12849999964237213, -0.30250000953674316, 0.10289999842643738, -0.08860000222921371, 0.259799987077713, 0.3027999997138977, 0.11949999630451202], [-0.46000000834465027, -0.09870000183582306, 0.10559999942779541, -0.11429999768733978, 0.19760000705718994, -0.36340001225471497, -0.3865000009536743, 0.2825999855995178, 0.07970000058412552, -0.3767000138759613, -0.3409000039100647, 0.22439999878406525, -0.06939999759197235, -0.009800000116229057, -0.18520000576972961]], [0.0, 0.0, 0.0, 0.0, 0.0, 0.0, 0.0, 0.0, 0.0, 0.0, 0.0, 0.0, 0.0, 0.0, 0.0], [[-0.04259999841451645, 0.029600000008940697, -0.07779999822378159], [-0.005100000184029341, -0.04410000145435333, -0.04879999905824661], [0.02410000003874302, -0.08290000259876251, -0.048500001430511475], [-0.09309999644756317, -0.053599998354911804, 0.0340999998152256], [0.01899999938905239, -0.04569999873638153, 0.06360000371932983], [0.0364999994635582, 0.09669999778270721, -0.010900000110268593], [-0.0017000000225380063, 0.053700000047683716, 0.0625], [0.025100000202655792, -0.013000000268220901, -0.017400000244379044], [-0.05829999968409538, 0.017000000923871994, -0.08060000091791153], [0.013899999670684338, 0.06469999998807907, -0.007400000002235174], [-0.00019999999494757503, 0.02930000051856041, 0.08919999748468399], [-0.005499999970197678, 0.018200000748038292, -0.07169999927282333], [0.0017999999690800905, 0.020500000566244125, -0.03720000013709068], [0.05310000106692314, 0.08250000327825546, -0.11060000211000443], [-0.053199999034404755, 0.0940999984741211, -0.09839999675750732]], [0.0, 0.0, 0.0]]</t>
+          <t>[[[-0.05169999971985817, 0.011599999852478504, 0.05860000103712082, 0.015599999576807022, -0.0568000003695488], [0.0071000000461936, -0.04830000177025795, 0.012000000104308128, 0.012199999764561653, 0.0006000000284984708]], [[0.06539999693632126, 0.3950999975204468, 0.25870001316070557, 0.6608999967575073, 0.5795000195503235], [0.2709999978542328, -0.6230999827384949, 0.6399000287055969, 0.2856999933719635, -0.21709999442100525], [-0.5199000239372253, -0.4839000105857849, -0.47760000824928284, 0.5170000195503235, 0.012199999764561653], [0.6899999976158142, -0.3490999937057495, -0.4555000066757202, -0.06400000303983688, 0.43639999628067017], [-0.41940000653266907, -0.3156000077724457, 0.29660001397132874, -0.4584999978542328, 0.652999997138977]], [0.0, 0.0, 0.0, 0.0, 0.0], [[-0.05169999971985817, 0.011599999852478504], [0.05860000103712082, 0.015599999576807022], [-0.0568000003695488, 0.0071000000461936], [-0.04830000177025795, 0.012000000104308128], [0.012199999764561653, 0.0006000000284984708]], [[-0.9868999719619751, 0.16130000352859497], [0.16130000352859497, 0.9868999719619751]], [0.0, 0.0], [[-0.05169999971985817, 0.011599999852478504, 0.05860000103712082], [0.015599999576807022, -0.0568000003695488, 0.0071000000461936]], [0.0, 0.0, 0.0]]</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>[[[-0.33090001344680786, -0.11299999803304672, -0.3249000012874603, -0.17579999566078186, -0.36970001459121704, -0.02459999918937683, 0.08780000358819962, -0.3481999933719635, 0.06319999694824219, -0.2734000086784363, -0.00430000014603138, 0.3953000009059906, 0.048900000751018524, -0.11490000039339066, 0.2590000033378601], [0.2809000015258789, 0.1071000024676323, 0.11029999703168869, -0.050200000405311584, 0.06610000133514404, 0.2632000148296356, 0.25110000371932983, -0.05050000175833702, -0.193900004029274, 0.21150000393390656, 0.0957999974489212, -0.383899986743927, 0.13099999725818634, 0.26660001277923584, -0.48510000109672546]], [[0.7504000067710876, 0.3853999972343445, 0.12160000205039978, 0.5976999998092651, -0.04039999842643738, -0.4196000099182129, -0.2667999863624573, 0.37860000133514404, 0.4740000069141388, -1.0085999965667725, 0.4749000072479248, -0.25290000438690186, 0.7350000143051147, -0.04639999940991402, -0.3662000000476837], [0.22169999778270721, 0.23360000550746918, -0.38339999318122864, 0.20730000734329224, -0.050599999725818634, -0.11069999635219574, 0.03449999913573265, 0.5412999987602234, 0.4966000020503998, -0.37630000710487366, 0.2818000018596649, -0.6157000064849854, 0.5501999855041504, 0.1923000067472458, 0.6565999984741211], [0.388700008392334, -0.33709999918937683, -0.1404999941587448, 0.2946999967098236, 0.30959999561309814, 0.26899999380111694, -0.45350000262260437, 0.6137999892234802, -0.10080000013113022, 0.027300000190734863, -0.12880000472068787, -0.3644999861717224, 0.1598999947309494, -0.010700000450015068, -0.4348999857902527], [0.37790000438690186, -0.4101000130176544, -0.17739999294281006, 0.4478999972343445, 0.029400000348687172, -0.5232999920845032, 0.4643000066280365, 0.28700000047683716, 0.012400000356137753, -0.704800009727478, -0.5210000276565552, -0.5453000068664551, 0.28290000557899475, 0.3837999999523163, 0.09849999845027924], [0.616100013256073, 0.3553999960422516, 0.1096000000834465, -0.08470000326633453, -0.03620000183582306, -0.22709999978542328, -0.3443000018596649, 0.4846999943256378, -0.9063000082969666, -0.33149999380111694, -0.4440999925136566, -0.5030999779701233, 0.33009999990463257, 0.046300001442432404, -0.02879999950528145], [0.3109999895095825, 0.15209999680519104, -0.33629998564720154, -0.1460999995470047, 0.0406000018119812, 0.0957999974489212, 0.030799999833106995, 0.5490000247955322, 0.09960000216960907, -0.3684999942779541, 0.8641999959945679, 0.27720001339912415, 0.3521000146865845, 0.5060999989509583, -0.17419999837875366], [-0.05139999836683273, 0.36320000886917114, -0.14030000567436218, -0.7886999845504761, -0.20990000665187836, 0.3865000009536743, -0.24690000712871552, -0.5573999881744385, 0.32249999046325684, 0.05950000137090683, 0.4876999855041504, -0.5778999924659729, -0.5392000079154968, 0.2529999911785126, -0.5552999973297119], [0.951200008392334, 0.09350000321865082, -0.2126999944448471, 0.5813000202178955, 0.4544000029563904, -0.8356000185012817, -0.10339999943971634, 0.057100001722574234, 0.10180000215768814, -0.10050000250339508, -0.5090000033378601, -0.06360000371932983, 0.22290000319480896, 0.3050000071525574, 0.12250000238418579], [0.3224000036716461, -0.2354000061750412, 0.28369998931884766, 0.23479999601840973, 0.5976999998092651, -0.0843999981880188, 0.12449999898672104, 0.13570000231266022, 0.2003999948501587, -0.5493999719619751, 0.383899986743927, -0.13619999587535858, -0.20489999651908875, -0.5214999914169312, 0.5242999792098999], [-0.3508000075817108, 0.3686999976634979, 0.9322999715805054, -0.6578999757766724, 0.1615000069141388, 0.04179999977350235, 0.013100000098347664, 0.7027000188827515, -0.011900000274181366, 0.3546999990940094, 0.14730000495910645, 0.10369999706745148, -0.04349999874830246, 0.7120000123977661, -0.932699978351593], [0.3978999853134155, -0.32260000705718994, 0.06729999929666519, -0.4546000063419342, 0.16220000386238098, -0.03709999844431877, -0.23929999768733978, -0.08969999849796295, 0.742900013923645, -0.47760000824928284, 0.6449999809265137, -0.26409998536109924, 0.7594000101089478, 0.10429999977350235, 0.27239999175071716], [-0.8050000071525574, -0.45210000872612, -0.4749999940395355, -0.42080000042915344, 0.19830000400543213, -0.6298999786376953, 0.5825999975204468, -0.800000011920929, -0.3440000116825104, 0.8783000111579895, -0.015200000256299973, 0.18719999492168427, -0.16339999437332153, -0.9057000279426575, 0.5855000019073486], [0.23739999532699585, -0.21359999477863312, -0.029200000688433647, 0.7795000076293945, -0.30090001225471497, -0.35440000891685486, -0.3571000099182129, -0.3792000114917755, -0.1006999984383583, -0.4803999960422516, 0.7548999786376953, -0.5587999820709229, 0.010099999606609344, 0.3813000023365021, 0.4278999865055084], [0.12489999830722809, 0.436599999666214, -0.12919999659061432, 0.4327000081539154, 0.6087999939918518, 0.26170000433921814, -0.23929999768733978, -0.20020000636577606, 0.1736000031232834, -0.6518999934196472, 0.6079000234603882, -0.4341999888420105, 0.8184000253677368, 0.48429998755455017, 0.07109999656677246], [-1.1424000263214111, -0.40369999408721924, -0.13910000026226044, -0.3165000081062317, 0.052299998700618744, -0.4431000053882599, -0.09839999675750732, 0.4408999979496002, -0.006800000090152025, -0.09929999709129333, -0.39329999685287476, 0.7267000079154968, -0.42289999127388, -0.3140000104904175, -0.22190000116825104]], [-0.13050000369548798, 0.03229999914765358, -0.07500000298023224, -0.12060000002384186, -0.1704999953508377, -0.09030000120401382, 0.2883000075817108, -0.21739999949932098, 0.07519999891519547, -0.025499999523162842, 0.3021000027656555, -0.044599998742341995, 0.08609999716281891, 0.07100000232458115, -0.24130000174045563], [[-0.1737000048160553, -0.09350000321865082, -0.00019999999494757503], [0.15929999947547913, 0.09849999845027924, -0.003700000001117587], [0.3815000057220459, -0.16130000352859497, -0.19760000705718994], [-0.30820000171661377, -0.14730000495910645, 0.11309999972581863], [0.07329999655485153, -0.13199999928474426, 0.25940001010894775], [0.42750000953674316, 0.08980000019073486, 0.12290000170469284], [0.003800000064074993, 0.15469999611377716, 0.22519999742507935], [0.25220000743865967, -0.07419999688863754, -0.093299999833107], [-0.33320000767707825, -0.027799999341368675, -0.08749999850988388], [0.3434999883174896, -0.0812000036239624, -0.25130000710487366], [-0.2897000014781952, -0.04989999905228615, 0.03290000185370445], [-0.048500001430511475, 0.008500000461935997, -0.022600000724196434], [-0.11890000104904175, 0.17919999361038208, -0.13169999420642853], [0.3276999890804291, 0.16699999570846558, -0.16329999268054962], [-0.8234999775886536, 0.11999999731779099, 0.022600000724196434]], [-0.05790000036358833, -0.03500000014901161, 0.05660000070929527]]</t>
+          <t>[[[0.6607999801635742, -0.0406000018119812, 0.07970000058412552, 0.11909999698400497, -0.3352999985218048], [-0.7709000110626221, 0.1145000010728836, 0.025800000876188278, -0.3504999876022339, 0.26989999413490295]], [[0.8737999796867371, 1.0607000589370728, -0.47859999537467957, 1.2316999435424805, 1.1399999856948853], [0.45500001311302185, -0.3743000030517578, 0.16529999673366547, 0.7937999963760376, -0.1005999967455864], [-0.7652000188827515, -0.4023999869823456, -0.6312000155448914, 0.3296000063419342, 0.03700000047683716], [1.6229000091552734, -0.03959999978542328, -0.8295000195503235, 0.820900022983551, 0.40720000863075256], [-0.20649999380111694, -0.23600000143051147, 0.299699991941452, -0.6144000291824341, 0.6837000250816345]], [0.11749999970197678, 0.2117999941110611, 0.3334999978542328, 0.24699999392032623, -0.49810001254081726], [[-0.5999000072479248, 0.4316999912261963], [0.5027999877929688, 0.15189999341964722], [-0.2874999940395355, 0.017999999225139618], [0.2971999943256378, 0.296099990606308], [0.45820000767707825, 0.20970000326633453]], [[-1.6797000169754028, 1.4160000085830688], [0.2928999960422516, 1.3602999448776245]], [0.044199999421834946, -0.43790000677108765], [[-0.8203999996185303, -0.32249999046325684, 0.5138000249862671], [0.8086000084877014, -0.24500000476837158, 0.37549999356269836]], [0.07769999653100967, -0.09790000319480896, 0.21240000426769257]]</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>[0.8457956589417058]</t>
+          <t>[0.8809761026920397]</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>[0.035199705011748995]</t>
+          <t>[0.027169183732675208]</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>[0.20874885202450943]</t>
+          <t>[0.823344838620904]</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>[0.18064522522305365]</t>
+          <t>[0.040330951172446415]</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>[0.6185000413171089]</t>
+          <t>[-8.008871418049985]</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>[0.12485718994616367]</t>
+          <t>[2.948420685882701]</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>[0.7660728172700525]</t>
+          <t>[0.543990359195202]</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>[0.05373753560400898]</t>
+          <t>[0.10475411203839566]</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>[-0.1186283899097178]</t>
+          <t>[0.7805132162363481]</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>[0.26529505792367675]</t>
+          <t>[0.0520537110780454]</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>[-0.9029233733988724]</t>
+          <t>[-0.4799264349392336]</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>[0.6255811943880956]</t>
+          <t>[0.48652203221518875]</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>[0.8316341343496756]</t>
+          <t>[-0.21800046398780504]</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>[0.01815417220416226]</t>
+          <t>[0.13133178796412132]</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>[-0.6398441032189848]</t>
+          <t>[-0.16487855087929026]</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>[0.1381738212895469]</t>
+          <t>[0.09815306247543176]</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>[-1.3940537810655194]</t>
+          <t>[-1.268185442438344]</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>[0.22892691731990225]</t>
+          <t>[0.21689099273959797]</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>[0.7202970106981916]</t>
+          <t>[-0.4162454535191289]</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>[0.029301859569257162]</t>
+          <t>[0.14836675681659625]</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>[-0.6441294905955035]</t>
+          <t>[-0.22924722481956739]</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>[0.13530069294682748]</t>
+          <t>[0.10115869964768515]</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>[-1.1187094774920632]</t>
+          <t>[-1.4151773093095934]</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>[0.19493053989631517]</t>
+          <t>[0.2222068772762227]</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>[-2.125325327962769]</t>
+          <t>[-1.0786665448767847]</t>
         </is>
       </c>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>[0.2618896717727381]</t>
+          <t>[0.17418388232805365]</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>[-2.9917755219564715]</t>
+          <t>[-0.8513516783856185]</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>[0.4298267003821566]</t>
+          <t>[0.19934998318177857]</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>[-2.583522680816024]</t>
+          <t>[-3.9088802210276183]</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>[0.2667931147027241]</t>
+          <t>[0.36546592850706505]</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>[-2.4432396414249453]</t>
+          <t>[-1.4735389047867375]</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>[0.28216965555198237]</t>
+          <t>[0.20270375966897838]</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>[-2.950585966879667]</t>
+          <t>[-0.875301324636041]</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>[0.41932575587204585]</t>
+          <t>[0.1990494959566612]</t>
         </is>
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>[-2.671743793768626]</t>
+          <t>[-4.650998653742313]</t>
         </is>
       </c>
       <c r="AN4" t="inlineStr">
         <is>
-          <t>[0.2820165420496946]</t>
+          <t>[0.43403766410949957]</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>model_20_0</t>
+          <t>model_5_2_3</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>[20]</t>
+          <t>[5, 2]</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>[[[-0.04259999841451645, 0.029600000008940697, -0.07779999822378159, -0.005100000184029341, -0.04410000145435333, -0.04879999905824661, 0.02410000003874302, -0.08290000259876251, -0.048500001430511475, -0.09309999644756317, -0.053599998354911804, 0.0340999998152256, 0.01899999938905239, -0.04569999873638153, 0.06360000371932983, 0.0364999994635582, 0.09669999778270721, -0.010900000110268593, -0.0017000000225380063, 0.053700000047683716], [0.0625, 0.025100000202655792, -0.013000000268220901, -0.017400000244379044, -0.05829999968409538, 0.017000000923871994, -0.08060000091791153, 0.013899999670684338, 0.06469999998807907, -0.007400000002235174, -0.00019999999494757503, 0.02930000051856041, 0.08919999748468399, -0.005499999970197678, 0.018200000748038292, -0.07169999927282333, 0.0017999999690800905, 0.020500000566244125, -0.03720000013709068, 0.05310000106692314]], [[0.19169999659061432, 0.05350000038743019, -0.3098999857902527, -0.18700000643730164, -0.45239999890327454, 0.10419999808073044, -0.1673000007867813, 0.12729999423027039, -0.07829999923706055, -0.15080000460147858, 0.04490000009536743, 0.49480000138282776, 0.33219999074935913, 0.1964000016450882, 0.3089999854564667, 0.17149999737739563, 0.035999998450279236, 0.014399999752640724, 0.13259999454021454, 0.03229999914765358], [-0.24130000174045563, -0.0877000018954277, 0.188400000333786, -0.2612999975681305, -0.057500001043081284, -0.03359999880194664, 0.16539999842643738, 0.21060000360012054, 0.4129999876022339, -0.11680000275373459, 0.37450000643730164, -0.1265999972820282, 0.1143999993801117, 0.5072000026702881, -0.1412999927997589, 0.17499999701976776, -0.10760000348091125, -0.25099998712539673, -0.13330000638961792, 0.016699999570846558], [0.10080000013113022, -0.005400000140070915, -0.19269999861717224, -0.24969999492168427, 0.07440000027418137, -0.10750000178813934, 0.06279999762773514, 0.0949999988079071, 0.06040000170469284, 0.011300000362098217, 0.19779999554157257, 0.002300000051036477, 0.06759999692440033, -0.24570000171661377, -0.11190000176429749, -0.27160000801086426, -0.4943999946117401, -0.10999999940395355, 0.42320001125335693, -0.48010000586509705], [0.42329999804496765, -0.05849999934434891, -0.3587000072002411, -0.06340000033378601, 0.04670000076293945, -0.3831000030040741, 0.3393000066280365, -0.007300000172108412, 0.028699999675154686, 0.15049999952316284, -0.21170000731945038, 0.07050000131130219, -0.24609999358654022, 0.27559998631477356, -0.19099999964237213, 0.0940999984741211, -0.2531000077724457, 0.09449999779462814, -0.10379999876022339, 0.2858000099658966], [-0.1808999925851822, 0.25540000200271606, -0.014999999664723873, 0.3230000138282776, -0.38960000872612, -0.3197000026702881, 0.2897000014781952, 0.09570000320672989, 0.02290000021457672, -0.1274999976158142, -0.2775999903678894, -0.3073999881744385, 0.30399999022483826, -0.11990000307559967, 0.21739999949932098, -0.11219999939203262, -0.1695999950170517, -0.24250000715255737, -0.00989999994635582, 0.0877000018954277], [-0.016599999740719795, 0.13529999554157257, 0.07769999653100967, -0.4041000008583069, -0.016200000420212746, -0.6075000166893005, -0.186599999666214, -0.219200000166893, 0.02590000070631504, -0.06759999692440033, -0.09390000253915787, -0.01489999983459711, 0.06199999898672104, -0.19900000095367432, -0.030700000002980232, 0.3239000141620636, 0.2533999979496002, 0.013899999670684338, -0.19990000128746033, -0.30309998989105225], [-0.04610000178217888, 0.3260999917984009, -0.033799998462200165, -0.035100001841783524, 0.23000000417232513, -0.16820000112056732, 0.004699999932199717, 0.1776999980211258, -0.09549999982118607, -0.3959999978542328, 0.13439999520778656, -0.11079999804496765, -0.193900004029274, 0.02630000002682209, -0.0272000003606081, 0.14270000159740448, 0.2353000044822693, 0.029100000858306885, 0.5990999937057495, 0.3249000012874603], [0.11879999935626984, 0.017400000244379044, 0.0471000000834465, 0.18549999594688416, -0.1145000010728836, 0.011800000444054604, 0.5105000138282776, -0.272599995136261, 0.2939000129699707, 0.19339999556541443, 0.061000000685453415, 0.2126999944448471, -0.007799999788403511, 0.050700001418590546, -0.032099999487400055, -0.04659999907016754, 0.5073999762535095, -0.07519999891519547, 0.29350000619888306, -0.2702000141143799], [-0.12039999663829803, -0.2718999981880188, -0.05299999937415123, 0.4627000093460083, 0.03220000118017197, -0.12060000002384186, -0.3075000047683716, 0.15049999952316284, 0.40959998965263367, -0.2362000048160553, -0.32600000500679016, 0.1639000028371811, -0.1145000010728836, 0.0869000032544136, -0.11460000276565552, 0.23180000483989716, -0.10660000145435333, 0.13079999387264252, 0.15860000252723694, -0.2529999911785126], [-0.38269999623298645, -0.04839999973773956, 0.22349999845027924, 0.055399999022483826, 0.054099999368190765, -0.026799999177455902, 0.41190001368522644, -0.18000000715255737, -0.4505000114440918, -0.20970000326633453, 0.00839999970048666, 0.3849000036716461, 0.009499999694526196, 0.05000000074505806, -0.07800000160932541, 0.22849999368190765, -0.28610000014305115, 0.20569999516010284, -0.0010999999940395355, -0.11079999804496765], [-0.09260000288486481, 0.71670001745224, -0.026399999856948853, -0.04430000111460686, 0.06109999865293503, 0.21969999372959137, -0.05849999934434891, 0.1225999966263771, 0.06610000133514404, 0.03359999880194664, -0.27959999442100525, 0.2694999873638153, -0.21490000188350677, 0.1428000032901764, -0.23569999635219574, -0.09589999914169312, -0.04490000009536743, -0.21130000054836273, -0.18799999356269836, -0.18700000643730164], [-0.3165000081062317, 0.03460000082850456, -0.07639999687671661, 0.07329999655485153, -0.2921000123023987, -0.23190000653266907, -0.23399999737739563, -0.2298000007867813, -0.08009999990463257, 0.271699994802475, 0.2320999950170517, 0.0038999998942017555, -0.5457000136375427, 0.24699999392032623, 0.32199999690055847, -0.13210000097751617, -0.10090000182390213, -0.04670000076293945, 0.11240000277757645, -0.04170000180602074], [-0.08299999684095383, 0.03700000047683716, -0.13590000569820404, -0.021299999207258224, 0.11969999969005585, -0.17110000550746918, 0.15139999985694885, 0.2955999970436096, 0.0737999975681305, -0.25920000672340393, 0.11180000007152557, 0.04399999976158142, -0.02879999950528145, 0.11379999667406082, 0.22390000522136688, -0.49729999899864197, 0.2029000073671341, 0.51419997215271, -0.2870999872684479, -0.18070000410079956], [0.1265999972820282, 0.36660000681877136, -0.23180000483989716, 0.2800000011920929, 0.11569999903440475, 0.11500000208616257, -0.02280000038444996, -0.42969998717308044, 0.2632000148296356, -0.13910000026226044, 0.414900004863739, -0.11620000004768372, 0.11420000344514847, -0.0812000036239624, 0.09539999812841415, 0.24719999730587006, -0.2329999953508377, 0.24060000479221344, -0.17149999737739563, 0.0034000000450760126], [-0.41609999537467957, -0.1088000014424324, -0.3946000039577484, -0.0851999968290329, 0.2619999945163727, -0.0020000000949949026, 0.1581999957561493, 0.14429999887943268, 0.23890000581741333, 0.15600000321865082, 0.042100001126527786, 0.2870999872684479, -0.06300000101327896, -0.42750000953674316, 0.20880000293254852, 0.1324000060558319, 0.05290000140666962, -0.225600004196167, -0.1216999962925911, 0.23569999635219574], [0.2648000121116638, 0.07890000194311142, 0.42179998755455017, 0.304500013589859, 0.23499999940395355, -0.3698999881744385, -0.15620000660419464, 0.14020000398159027, 0.00139999995008111, 0.11710000038146973, 0.28360000252723694, 0.4287000000476837, 0.13449999690055847, -0.043800000101327896, 0.09260000288486481, -0.15710000693798065, -0.08730000257492065, -0.218299999833107, -0.0754999965429306, 0.1573999971151352], [0.17299999296665192, 0.010599999688565731, -0.13750000298023224, 0.26759999990463257, -0.03099999949336052, 0.026599999517202377, 0.11890000104904175, 0.4851999878883362, -0.3391999900341034, 0.12860000133514404, 0.25679999589920044, -0.18310000002384186, -0.17910000681877136, -0.04809999838471413, 0.0544000007212162, 0.4081999957561493, 0.12359999865293503, -0.12070000171661377, -0.16339999437332153, -0.36959999799728394], [0.16259999573230743, -0.00930000003427267, 0.27149999141693115, -0.09539999812841415, -0.5063999891281128, 0.08579999953508377, 0.10339999943971634, 0.12919999659061432, 0.21480000019073486, -0.23810000717639923, 0.1370999962091446, 0.11379999667406082, -0.423799991607666, -0.4551999866962433, -0.1429000049829483, 0.011900000274181366, -0.0820000022649765, 0.12189999967813492, -0.10999999940395355, 0.1542000025510788], [0.27079999446868896, -0.0828000009059906, 0.18889999389648438, -0.14589999616146088, 0.25049999356269836, 0.1518000066280365, 0.1453000009059906, -0.12409999966621399, 0.0771000012755394, -0.3255000114440918, -0.22849999368190765, -0.04740000143647194, -0.2583000063896179, 0.07129999995231628, 0.6204000115394592, 0.06499999761581421, -0.11640000343322754, -0.2757999897003174, -0.04560000076889992, -0.14669999480247498], [-0.029200000688433647, 0.20919999480247498, 0.3154999911785126, -0.14740000665187836, 0.039400000125169754, 0.04650000110268593, 0.07100000232458115, 0.25380000472068787, 0.20399999618530273, 0.49729999899864197, -0.15479999780654907, -0.06279999762773514, 0.0771000012755394, -0.01590000092983246, 0.2955999970436096, 0.25099998712539673, -0.16140000522136688, 0.4666000008583069, 0.20819999277591705, 0.020999999716877937]], [0.0, 0.0, 0.0, 0.0, 0.0, 0.0, 0.0, 0.0, 0.0, 0.0, 0.0, 0.0, 0.0, 0.0, 0.0, 0.0, 0.0, 0.0, 0.0, 0.0], [[-0.04259999841451645, 0.029600000008940697, -0.07779999822378159], [-0.005100000184029341, -0.04410000145435333, -0.04879999905824661], [0.02410000003874302, -0.08290000259876251, -0.048500001430511475], [-0.09309999644756317, -0.053599998354911804, 0.0340999998152256], [0.01899999938905239, -0.04569999873638153, 0.06360000371932983], [0.0364999994635582, 0.09669999778270721, -0.010900000110268593], [-0.0017000000225380063, 0.053700000047683716, 0.0625], [0.025100000202655792, -0.013000000268220901, -0.017400000244379044], [-0.05829999968409538, 0.017000000923871994, -0.08060000091791153], [0.013899999670684338, 0.06469999998807907, -0.007400000002235174], [-0.00019999999494757503, 0.02930000051856041, 0.08919999748468399], [-0.005499999970197678, 0.018200000748038292, -0.07169999927282333], [0.0017999999690800905, 0.020500000566244125, -0.03720000013709068], [0.05310000106692314, 0.08250000327825546, -0.11060000211000443], [-0.053199999034404755, 0.0940999984741211, -0.09839999675750732], [-0.0729999989271164, 0.10050000250339508, -0.1046999990940094], [0.008999999612569809, -0.027699999511241913, 0.05829999968409538], [0.022199999541044235, -0.0681999996304512, -0.01940000057220459], [-0.03229999914765358, 0.015799999237060547, 0.05689999833703041], [-0.10809999704360962, 0.0026000000070780516, -0.10679999738931656]], [0.0, 0.0, 0.0]]</t>
+          <t>[[[0.025800000876188278, -0.06419999897480011, -0.005400000140070915, 0.029899999499320984, 0.02449999935925007], [-0.04399999976158142, -0.07069999724626541, 0.009800000116229057, -0.008299999870359898, -0.02370000071823597]], [[0.6628000140190125, 0.6535000205039978, -0.05570000037550926, 0.23430000245571136, 0.2750999927520752], [0.4512999951839447, -0.5479999780654907, -0.6963000297546387, 0.1046999990940094, -0.015599999576807022], [-0.1281999945640564, -0.3384000062942505, 0.26669999957084656, 0.6470000147819519, 0.6158999800682068], [0.5778999924659729, -0.38019999861717224, 0.6636999845504761, -0.10679999738931656, -0.2639000117778778], [-0.08150000125169754, 0.11630000174045563, -0.022199999541044235, 0.7099999785423279, -0.689300000667572]], [0.0, 0.0, 0.0, 0.0, 0.0], [[0.025800000876188278, -0.06419999897480011], [-0.005400000140070915, 0.029899999499320984], [0.02449999935925007, -0.04399999976158142], [-0.07069999724626541, 0.009800000116229057], [-0.008299999870359898, -0.02370000071823597]], [[0.21359999477863312, -0.9768999814987183], [-0.9768999814987183, -0.21359999477863312]], [0.0, 0.0], [[0.025800000876188278, -0.06419999897480011, -0.005400000140070915], [0.029899999499320984, 0.02449999935925007, -0.04399999976158142]], [0.0, 0.0, 0.0]]</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>[[[-0.015799999237060547, -0.2549999952316284, -0.1565999984741211, -0.23090000450611115, -0.13019999861717224, 0.0430000014603138, 0.23190000653266907, -0.34220001101493835, -0.3149000108242035, -0.16949999332427979, -0.21539999544620514, 0.10570000112056732, -0.3594000041484833, -0.22519999742507935, 0.22380000352859497, 0.21050000190734863, 0.3052999973297119, -0.19529999792575836, 0.18930000066757202, -0.19509999454021454], [0.15530000627040863, 0.17430000007152557, -0.0706000030040741, 0.2313999980688095, -0.07289999723434448, 0.24879999458789825, -0.05139999836683273, 0.6039000153541565, 0.26600000262260437, 0.038600001484155655, 0.3528999984264374, 0.012199999764561653, 0.46560001373291016, 0.20630000531673431, -0.021700000390410423, -0.1454000025987625, 0.021400000900030136, -0.002899999963119626, -0.05339999869465828, 0.16120000183582306]], [[0.427700012922287, 0.04149999842047691, -0.30160000920295715, 0.12800000607967377, -0.5529000163078308, 0.05310000106692314, -0.3427000045776367, 0.13030000030994415, 0.289000004529953, -0.18000000715255737, -0.17649999260902405, 0.6062999963760376, 0.2531999945640564, 0.3946000039577484, 0.24950000643730164, 0.09950000047683716, 0.08070000261068344, 0.227400004863739, 0.2199999988079071, 0.03550000116229057], [-0.14219999313354492, 0.02459999918937683, 0.24369999766349792, -0.09300000220537186, -0.13439999520778656, -0.07500000298023224, 0.10279999673366547, 0.2856000065803528, 0.41370001435279846, 0.027000000700354576, 0.18369999527931213, 0.03720000013709068, 0.17059999704360962, 0.5860000252723694, -0.06800000369548798, 0.12890000641345978, -0.08229999989271164, -0.2053000032901764, -0.032099999487400055, 0.18310000002384186], [-0.06539999693632126, 0.09350000321865082, -0.17080000042915344, -0.2930000126361847, 0.18230000138282776, -0.14059999585151672, 0.11230000108480453, 0.16060000658035278, 0.06539999693632126, -0.00139999995008111, 0.1459999978542328, -0.008299999870359898, 0.3280999958515167, -0.27869999408721924, -0.17249999940395355, -0.2856999933719635, -0.6462000012397766, -0.04170000180602074, 0.2897999882698059, -0.5263000130653381], [0.4871000051498413, 0.07240000367164612, -0.2994000017642975, 0.2858999967575073, 0.007899999618530273, -0.39430001378059387, 0.11249999701976776, -0.03590000048279762, 0.40939998626708984, 0.11810000240802765, -0.8044000267982483, 0.16179999709129333, -0.11670000106096268, 0.43650001287460327, -0.4896000027656555, -0.11110000312328339, -0.5257999897003174, 0.4772999882698059, -0.2554999887943268, 0.11379999667406082], [-0.3328000009059906, 0.27869999408721924, 0.03819999843835831, 0.19200000166893005, -0.273499995470047, -0.24070000648498535, 0.39890000224113464, 0.1282999962568283, -0.2175000011920929, -0.12530000507831573, -0.21410000324249268, -0.37779998779296875, 0.44850000739097595, -0.22949999570846558, 0.21320000290870667, -0.06419999897480011, -0.2418999969959259, -0.27489998936653137, -0.14030000567436218, 0.08299999684095383], [-0.06120000034570694, 0.17309999465942383, -0.006099999882280827, -0.39010000228881836, -0.01679999940097332, -0.5899999737739563, -0.03629999980330467, -0.1720000058412552, 0.22280000150203705, -0.04540000110864639, -0.26820001006126404, -0.0502999983727932, 0.32670000195503235, -0.003599999938160181, -0.06769999861717224, 0.44449999928474426, 0.1988999992609024, 0.1673000007867813, -0.20759999752044678, -0.4097999930381775], [-0.16030000150203705, 0.21539999544620514, 0.0658000037074089, -0.11649999767541885, 0.30630001425743103, -0.3215999901294708, -0.02889999933540821, -0.08259999752044678, -0.4779999852180481, -0.536899983882904, 0.3686000108718872, -0.24959999322891235, -0.40529999136924744, -0.2705000042915344, -0.06650000065565109, 0.10589999705553055, 0.6215999722480774, -0.04580000042915344, 0.6021000146865845, 0.42419999837875366], [0.11249999701976776, 0.07980000227689743, -0.0066999997943639755, 0.34619998931884766, -0.2037000060081482, 0.06390000134706497, 0.7730000019073486, -0.16850000619888306, 0.736299991607666, 0.3050999939441681, -0.23739999532699585, 0.36640000343322754, 0.42719998955726624, 0.5300999879837036, -0.19130000472068787, 0.030799999833106995, 0.52920001745224, 0.1551000028848648, 0.12460000067949295, -0.4715999960899353], [0.16220000386238098, -0.414900004863739, -0.0012000000569969416, 0.9052000045776367, -0.22869999706745148, -0.18649999797344208, -0.5605000257492065, -0.06040000170469284, 0.9283999800682068, -0.3287999927997589, -0.6617000102996826, 0.46389999985694885, -0.23909999430179596, 0.39419999718666077, -0.3328000009059906, 0.2257000058889389, -0.49630001187324524, 0.4860000014305115, 0.15950000286102295, -0.07859999686479568], [-0.4675999879837036, -0.053199999034404755, 0.23479999601840973, 0.048700001090765, 0.1662999987602234, 0.10649999976158142, 0.43630000948905945, -0.16760000586509705, -0.2770000100135803, -0.16030000150203705, 0.14229999482631683, 0.34689998626708984, 0.13989999890327454, 0.11089999973773956, -0.0722000002861023, 0.3140000104904175, -0.5626000165939331, 0.3912000060081482, -0.12600000202655792, -0.0877000018954277], [-0.2800000011920929, 0.9308000206947327, -0.11020000278949738, -0.35510000586509705, 0.14159999787807465, 0.2833000123500824, 0.46860000491142273, 0.5741000175476074, 0.15279999375343323, 0.1386999934911728, -0.6639000177383423, 0.2029000073671341, 0.37529999017715454, 0.48019999265670776, -0.4235000014305115, -0.04740000143647194, -0.027400000020861626, -0.14390000700950623, -0.4000999927520752, -0.5396000146865845], [-0.11190000176429749, -0.029500000178813934, -0.1005999967455864, 0.33799999952316284, -0.41679999232292175, -0.23729999363422394, -0.4587000012397766, -0.31520000100135803, 0.17640000581741333, 0.28949999809265137, 0.22849999368190765, 0.06300000101327896, -0.7617999911308289, 0.3303999900817871, 0.337799996137619, -0.1647000014781952, -0.030400000512599945, 0.009399999864399433, 0.2231999933719635, 0.01979999989271164], [-0.04919999837875366, 0.44359999895095825, -0.3612000048160553, 0.24089999496936798, 0.12020000070333481, -0.2924000024795532, 0.15449999272823334, 0.7455000281333923, 0.4577000141143799, -0.15160000324249268, -0.3614000082015991, 0.20440000295639038, 0.2004999965429306, 0.583899974822998, 0.03819999843835831, -0.5609999895095825, 0.12680000066757202, 0.8482999801635742, -0.2662000060081482, -0.2345999926328659], [0.2653000056743622, 0.3262999951839447, -0.1817999929189682, 0.7245000004768372, 0.02290000021457672, 0.21619999408721924, -0.16120000183582306, -0.5479000210762024, 0.7925999760627747, -0.06710000336170197, 0.16979999840259552, -0.01549999974668026, 0.2750999927520752, 0.14300000667572021, -0.10779999941587448, 0.21140000224113464, -0.4984000027179718, 0.607200026512146, -0.2337999939918518, 0.004800000227987766], [-0.3248000144958496, -0.2387000024318695, -0.4449000060558319, -0.18440000712871552, 0.16840000450611115, 0.06970000267028809, 0.2542000114917755, 0.11739999800920486, 0.08879999816417694, 0.18490000069141388, 0.12890000641345978, 0.2809000015258789, -0.16439999639987946, -0.37619999051094055, 0.30320000648498535, 0.21860000491142273, 0.15049999952316284, -0.34950000047683716, -0.03830000013113022, 0.25099998712539673], [0.20559999346733093, -0.1745000034570694, 0.46619999408721924, 0.2222999930381775, 0.17679999768733978, -0.33309999108314514, -0.09480000287294388, -0.08320000022649765, -0.26570001244544983, 0.09679999947547913, 0.47620001435279846, 0.33649998903274536, -0.053300000727176666, -0.20160000026226044, 0.13269999623298645, -0.12759999930858612, 0.03359999880194664, -0.4074000120162964, -0.06469999998807907, 0.11810000240802765], [0.22339999675750732, 0.030899999663233757, -0.1453000009059906, 0.07429999858140945, -0.07010000199079514, 0.02449999935925007, 0.4178999960422516, 0.5539000034332275, -0.6762999892234802, 0.16369999945163727, 0.19920000433921814, -0.23309999704360962, -0.11089999973773956, -0.07419999688863754, 0.06849999725818634, 0.3831000030040741, 0.5372999906539917, -0.38659998774528503, -0.07259999960660934, -0.44670000672340393], [0.34290000796318054, -0.1834000051021576, 0.19949999451637268, 0.17759999632835388, -0.6362000107765198, 0.17419999837875366, -0.1688999980688095, -0.047200001776218414, 0.6704000234603882, -0.26980000734329224, 0.34369999170303345, 0.3102000057697296, -0.5356000065803528, -0.25270000100135803, -0.08789999783039093, 0.09309999644756317, -0.4885999858379364, 0.3499999940395355, -0.03440000116825104, 0.3330000042915344], [0.17299999296665192, -0.035999998450279236, 0.2563999891281128, -0.10090000182390213, 0.2574000060558319, 0.06939999759197235, 0.10930000245571136, -0.22429999709129333, -0.16060000658035278, -0.4124000072479248, -0.24379999935626984, -0.16580000519752502, -0.3750999867916107, -0.10459999740123749, 0.5076000094413757, -0.024299999698996544, 0.09939999878406525, -0.27549999952316284, -0.15309999883174896, -0.22130000591278076], [-0.050700001418590546, 0.5254999995231628, 0.19349999725818634, -0.29980000853538513, 0.06930000334978104, 0.14830000698566437, 0.1120000034570694, 0.593999981880188, 0.29170000553131104, 0.6284999847412109, -0.3433000147342682, -0.09839999675750732, 0.304500013589859, 0.21209999918937683, 0.351500004529953, 0.28780001401901245, -0.3222000002861023, 0.4959000051021576, 0.19619999825954437, -0.11209999769926071]], [0.11990000307559967, 0.00019999999494757503, 0.008299999870359898, 0.00559999980032444, -0.07440000027418137, 0.04610000178217888, 0.06849999725818634, 0.2703000009059906, 0.0071000000461936, -0.19920000433921814, 0.11169999837875366, 0.06289999932050705, 0.0575999990105629, -0.020999999716877937, -0.06520000100135803, 0.047200001776218414, 0.2865999937057495, -0.1412999927997589, 0.02319999970495701, -0.20960000157356262], [[-0.11789999902248383, 0.014399999752640724, -0.03460000082850456], [0.39320001006126404, -0.0348999984562397, -0.03269999846816063], [-0.018400000408291817, -0.1736000031232834, -0.034299999475479126], [-0.17599999904632568, 0.21960000693798065, 0.2304999977350235], [0.1266999989748001, -0.14790000021457672, 0.10999999940395355], [0.17880000174045563, 0.17239999771118164, 0.13330000638961792], [0.1875, 0.1462000012397766, -0.1446000039577484], [0.5134000182151794, 0.011900000274181366, 0.0357000008225441], [-0.2125999927520752, 0.00570000009611249, 0.08649999648332596], [0.17960000038146973, 0.1145000010728836, -0.03790000081062317], [-0.19290000200271606, 0.05009999871253967, 0.2224999964237213], [-0.07010000199079514, 0.12939999997615814, -0.10109999775886536], [0.4672999978065491, 0.14579999446868896, 0.04769999906420708], [0.1256999969482422, 0.03460000082850456, -0.18539999425411224], [-0.22290000319480896, 0.20430000126361847, -0.05139999836683273], [-0.15080000460147858, 0.17020000517368317, -0.163100004196167], [0.20970000326633453, 0.057500001043081284, 0.06300000101327896], [-0.08699999749660492, -0.1298999935388565, -0.021700000390410423], [-0.329800009727478, -0.03180000185966492, 0.06530000269412994], [-0.1388999968767166, 0.10700000077486038, 0.1234000027179718]], [-0.12330000102519989, -0.06310000270605087, 0.05530000105500221]]</t>
+          <t>[[[0.1898999959230423, 0.2540999948978424, -0.3901999890804291, 0.11270000040531158, 0.6280999779701233], [-0.4262999892234802, -0.2743000090122223, 0.07129999995231628, 0.012500000186264515, 0.07129999995231628]], [[1.559000015258789, 1.315600037574768, -0.4318999946117401, 0.12409999966621399, 0.3582000136375427], [0.9901999831199646, -0.2305999994277954, -0.9319999814033508, -0.14249999821186066, -0.4499000012874603], [-0.37470000982284546, -0.38679999113082886, 0.35749998688697815, 1.0855000019073486, 1.114400029182434], [0.5443999767303467, -0.26829999685287476, 0.6517000198364258, 0.03869999945163727, -0.1956000030040741], [0.1298999935388565, 0.1873999983072281, -0.07440000027418137, 0.26840001344680786, -1.5622999668121338]], [-0.10209999978542328, 0.050200000405311584, -0.2750000059604645, -0.26089999079704285, 0.45899999141693115], [[0.3531000018119812, -0.3504999876022339], [0.21860000491142273, -0.1428000032901764], [-0.20679999887943268, 0.11429999768733978], [-0.20509999990463257, 0.09690000116825104], [0.3206999897956848, 0.5152999758720398]], [[0.48660001158714294, -1.5094000101089478], [-1.610700011253357, -0.17489999532699585]], [-0.12290000170469284, 0.1923000067472458], [[0.9046000242233276, 0.17440000176429749, -0.20810000598430634], [-0.2476000040769577, 0.23399999737739563, -0.3801000118255615]], [-0.016200000420212746, -0.03530000150203705, 0.11729999631643295]]</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>[0.4184152540990914]</t>
+          <t>[0.9068442380091424]</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>[0.132756389052018]</t>
+          <t>[0.02126435170189729]</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>[-1.3192992489948558]</t>
+          <t>[0.7221169009415401]</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>[0.5295036048495094]</t>
+          <t>[0.06344162045582337]</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>[0.8544080154483484]</t>
+          <t>[-0.5428614320325118]</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>[0.04764930023207291]</t>
+          <t>[0.5049472181988274]</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>[0.0383508359835264]</t>
+          <t>[0.7382657119534732]</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>[0.22090915466441444]</t>
+          <t>[0.06012535806463834]</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>[-2.556169904945079]</t>
+          <t>[0.7338793283305979]</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>[0.843384907292567]</t>
+          <t>[0.06311345183266788]</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>[-0.5991260466757393]</t>
+          <t>[0.600280036467392]</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>[0.5257085998527129]</t>
+          <t>[0.13140691617070188]</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>[0.8175063913848378]</t>
+          <t>[-0.20872668955454698]</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>[0.019677506388613153]</t>
+          <t>[0.1303318364751801]</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>[-0.5890653005837532]</t>
+          <t>[-0.144376671774477]</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>[0.13389518212693088]</t>
+          <t>[0.09642556717635573]</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>[-1.2801396903475033]</t>
+          <t>[-0.5361407122286064]</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>[0.21803409534838886]</t>
+          <t>[0.14689058391310622]</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>[0.7233833969674319]</t>
+          <t>[-0.3359697488309954]</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>[0.028978527819162124]</t>
+          <t>[0.1399570239372071]</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>[-0.6130157951901387]</t>
+          <t>[-0.2794756453334486]</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>[0.13274024708622947]</t>
+          <t>[0.10529215759003449]</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>[-1.734848122106695]</t>
+          <t>[-1.0260305895662158]</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>[0.2516179904041038]</t>
+          <t>[0.18640367679767067]</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>[-1.9586280204982538]</t>
+          <t>[-1.0703886923419232]</t>
         </is>
       </c>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>[0.247921108965314]</t>
+          <t>[0.17349023163385502]</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>[-2.782872162526182]</t>
+          <t>[-0.9870251621813608]</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>[0.4073323889689087]</t>
+          <t>[0.21395904262124668]</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>[-2.439998853866379]</t>
+          <t>[-2.8264089840624673]</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>[0.25610777174928395]</t>
+          <t>[0.2848759898882644]</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>[-2.1803505935579017]</t>
+          <t>[-1.4278288133144832]</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>[0.2606261907310633]</t>
+          <t>[0.1989578685579438]</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>[-2.7339197725052764]</t>
+          <t>[-1.0990123806994379]</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>[0.3963282267739205]</t>
+          <t>[0.2227947855079251]</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>[-3.00572034135105]</t>
+          <t>[-3.801873148169741]</t>
         </is>
       </c>
       <c r="AN5" t="inlineStr">
         <is>
-          <t>[0.30766836210171905]</t>
+          <t>[0.3688186694579176]</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>model_25_0</t>
+          <t>model_5_2_4</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>[25]</t>
+          <t>[5, 2]</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>[[[-0.04259999841451645, 0.029600000008940697, -0.07779999822378159, -0.005100000184029341, -0.04410000145435333, -0.04879999905824661, 0.02410000003874302, -0.08290000259876251, -0.048500001430511475, -0.09309999644756317, -0.053599998354911804, 0.0340999998152256, 0.01899999938905239, -0.04569999873638153, 0.06360000371932983, 0.0364999994635582, 0.09669999778270721, -0.010900000110268593, -0.0017000000225380063, 0.053700000047683716, 0.0625, 0.025100000202655792, -0.013000000268220901, -0.017400000244379044, -0.05829999968409538], [0.017000000923871994, -0.08060000091791153, 0.013899999670684338, 0.06469999998807907, -0.007400000002235174, -0.00019999999494757503, 0.02930000051856041, 0.08919999748468399, -0.005499999970197678, 0.018200000748038292, -0.07169999927282333, 0.0017999999690800905, 0.020500000566244125, -0.03720000013709068, 0.05310000106692314, 0.08250000327825546, -0.11060000211000443, -0.053199999034404755, 0.0940999984741211, -0.09839999675750732, -0.0729999989271164, 0.10050000250339508, -0.1046999990940094, 0.008999999612569809, -0.027699999511241913]], [[-0.3027999997138977, -0.27959999442100525, 0.19349999725818634, 0.09470000118017197, -0.06480000168085098, 0.029500000178813934, 0.023399999365210533, -0.0031999999191612005, -0.3160000145435333, -0.1932000070810318, -0.296099990606308, -0.0007999999797903001, -0.11869999766349792, 0.3515999913215637, -0.17800000309944153, -0.3765999972820282, 0.21690000593662262, -0.18860000371932983, 0.05950000137090683, 0.07999999821186066, -0.021700000390410423, 0.12189999967813492, -0.27869999408721924, 0.048900000751018524, -0.23250000178813934], [0.04340000078082085, -0.1160999983549118, 0.12690000236034393, 0.49230000376701355, 0.11389999836683273, 0.13330000638961792, -0.12960000336170197, 0.10729999840259552, -0.04390000179409981, 0.22179999947547913, 0.05920000001788139, 0.4034999907016754, -0.2353000044822693, -0.1842000037431717, 0.02199999988079071, -0.07150000333786011, -0.3361999988555908, -0.005499999970197678, -0.16840000450611115, -0.17720000445842743, 0.02539999969303608, 0.08789999783039093, 0.026200000196695328, -0.22579999268054962, -0.34929999709129333], [0.24490000307559967, 0.28859999775886536, -0.19099999964237213, 0.26030001044273376, -0.47540000081062317, 0.13429999351501465, 0.02800000086426735, 0.035100001841783524, -0.24279999732971191, 0.07519999891519547, -0.23810000717639923, 0.0502999983727932, -0.10369999706745148, 0.15919999778270721, 0.11490000039339066, -0.07620000094175339, 0.1915999948978424, 0.07029999792575836, 0.2944999933242798, -0.32749998569488525, 0.16200000047683716, -0.13989999890327454, 0.18389999866485596, -0.05310000106692314, 0.09669999778270721], [0.19779999554157257, 0.11429999768733978, 0.45350000262260437, 0.05270000174641609, -0.06289999932050705, 0.15080000460147858, 0.10559999942779541, -0.10509999841451645, 0.3589000105857849, -0.16519999504089355, 0.08910000324249268, 0.05689999833703041, 0.2847999930381775, 0.25600001215934753, -0.04500000178813934, -0.36169999837875366, -0.10419999808073044, -0.24709999561309814, -0.21330000460147858, -0.21089999377727509, -0.009200000204145908, -0.07660000026226044, 0.11289999634027481, -0.09690000116825104, 0.23170000314712524], [-0.042899999767541885, -0.25440001487731934, -0.08299999684095383, 0.008799999952316284, -0.14329999685287476, -0.020600000396370888, -0.4519999921321869, 0.04190000146627426, 0.11270000040531158, -0.4702000021934509, 0.30630001425743103, -0.13510000705718994, 0.04989999905228615, -0.03370000049471855, 0.057999998331069946, -0.11779999732971191, -0.18629999458789825, 0.1623000055551529, 0.40220001339912415, -0.16179999709129333, 0.10580000281333923, 0.14669999480247498, -0.050599999725818634, -0.21819999814033508, 0.02930000051856041], [-0.19499999284744263, -0.16329999268054962, 0.07119999825954437, -0.3312999904155731, -0.25049999356269836, 0.10429999977350235, 0.04780000075697899, -0.07900000363588333, 0.03449999913573265, -0.04259999841451645, 0.01600000075995922, -0.032499998807907104, -0.08009999990463257, -0.20999999344348907, -0.007600000128149986, 0.05739999935030937, -0.02319999970495701, -0.07320000231266022, -0.14790000021457672, -0.19460000097751617, 0.28450000286102295, -0.6543999910354614, -0.08889999985694885, -0.12070000171661377, -0.28780001401901245], [-0.11860000342130661, 0.10679999738931656, 0.1899999976158142, -0.1673000007867813, 0.11919999867677689, -0.2459000051021576, 0.33959999680519104, 0.3474999964237213, -0.02019999921321869, -0.17180000245571136, -0.1307000070810318, 0.24089999496936798, -0.019999999552965164, -0.019600000232458115, 0.44620001316070557, 0.1177000030875206, -0.039500001817941666, -0.14749999344348907, 0.15360000729560852, -0.010300000198185444, 0.3488999903202057, 0.1784999966621399, -0.08089999854564667, -0.25690001249313354, 0.08799999952316284], [0.2451999932527542, -0.07249999791383743, 0.15279999375343323, -0.12020000070333481, 0.2824000120162964, 0.08649999648332596, 0.11810000240802765, -0.03830000013113022, 0.05139999836683273, 0.06400000303983688, 0.15399999916553497, -0.32739999890327454, -0.37770000100135803, 0.08030000329017639, 0.37049999833106995, -0.20669999718666077, 0.19089999794960022, 0.31119999289512634, -0.06790000200271606, -0.3183000087738037, 0.046799998730421066, 0.08640000224113464, -0.1103999987244606, 0.21289999783039093, -0.14509999752044678], [0.013700000010430813, 0.09319999814033508, -0.1200999990105629, 0.2425999939441681, 0.04729999974370003, 0.14749999344348907, 0.1437000036239624, 0.2240000069141388, -0.3443000018596649, -0.07519999891519547, 0.23160000145435333, -0.1679999977350235, 0.4490000009536743, -0.21119999885559082, 0.24660000205039978, -0.11469999700784683, -0.1395999938249588, -0.1768999993801117, -0.0008999999845400453, -0.06700000166893005, -0.12189999967813492, -0.16769999265670776, -0.3582000136375427, 0.2632000148296356, -0.031700000166893005], [-0.21209999918937683, -0.03370000049471855, 0.08640000224113464, 0.1875, -0.12950000166893005, -0.44940000772476196, 0.05469999834895134, 0.07339999824762344, 0.044599998742341995, 0.058400001376867294, 0.03880000114440918, 0.1216999962925911, -0.0035000001080334187, -0.1363999992609024, 0.1500999927520752, -0.4481000006198883, 0.04749999940395355, 0.45890000462532043, -0.06019999831914902, 0.22660000622272491, -0.12770000100135803, -0.3052000105381012, 0.08169999718666077, 0.023099999874830246, 0.18950000405311584], [-0.1956000030040741, 0.09000000357627869, 0.43880000710487366, -0.006800000090152025, -0.04919999837875366, -0.18850000202655792, -0.029100000858306885, -0.16660000383853912, -0.39809998869895935, 0.10740000009536743, 0.20419999957084656, 0.020800000056624413, 0.09719999879598618, 0.26750001311302185, -0.15039999783039093, 0.3605000078678131, -0.2402999997138977, 0.28790000081062317, 0.02329999953508377, -0.25949999690055847, 0.06719999760389328, 0.012000000104308128, -0.03830000013113022, 0.14720000326633453, 0.11140000075101852], [-0.04969999939203262, -0.01209999993443489, -0.36149999499320984, 0.2094999998807907, 0.45660001039505005, -0.17949999868869781, -0.14300000667572021, -0.13779999315738678, -0.056699998676776886, -0.2361000031232834, -0.07720000296831131, 0.09309999644756317, -0.015799999237060547, 0.287200003862381, 0.04230000078678131, 0.1266999989748001, 0.14329999685287476, -0.015599999576807022, -0.2750000059604645, -0.25440001487731934, 0.008200000040233135, -0.2992999851703644, -0.13519999384880066, -0.22269999980926514, 0.22339999675750732], [0.09809999912977219, 0.017799999564886093, -0.2011999934911728, -0.3481000065803528, 0.1454000025987625, -0.3962000012397766, 0.09880000352859497, -0.22750000655651093, -0.21940000355243683, 0.048900000751018524, 0.037700001150369644, 0.17499999701976776, 0.1023000031709671, -0.09669999778270721, -0.07850000262260437, -0.32179999351501465, -0.13490000367164612, -0.2110999971628189, 0.1761000007390976, -0.33739998936653137, -0.2078000009059906, 0.06509999930858612, 0.2632000148296356, 0.01730000041425228, -0.2281000018119812], [-0.019500000402331352, -0.03319999948143959, 0.2612999975681305, 0.012799999676644802, 0.4375999867916107, 0.28360000252723694, 0.0478999987244606, -0.059300001710653305, -0.18320000171661377, 0.07739999890327454, -0.1354999989271164, -0.08269999921321869, -0.05260000005364418, -0.3630000054836273, -0.23970000445842743, -0.10379999876022339, 0.08340000361204147, 0.031099999323487282, 0.41990000009536743, -0.011599999852478504, -0.011300000362098217, -0.19269999861717224, 0.05609999969601631, -0.21320000290870667, 0.3386000096797943], [-0.3118000030517578, 0.29429998993873596, -0.05939999967813492, 0.14480000734329224, 0.07769999653100967, -0.02449999935925007, 0.06419999897480011, 0.1851000040769577, 0.16689999401569366, -0.2401999980211258, 0.30469998717308044, 0.1298999935388565, -0.32409998774528503, -0.12929999828338623, -0.30970001220703125, -0.0364999994635582, 0.15230000019073486, -0.17839999496936798, 0.05119999870657921, -0.15940000116825104, 0.17509999871253967, 0.000699999975040555, 0.13930000364780426, 0.4438000023365021, 0.04639999940991402], [0.06350000202655792, 0.265500009059906, 0.2110999971628189, 0.1680999994277954, -0.03610000014305115, -0.2623000144958496, -0.25049999356269836, -0.43700000643730164, 0.23309999704360962, -0.03400000184774399, -0.2757999897003174, 0.05130000039935112, 0.08489999920129776, -0.33980000019073486, 0.0934000015258789, 0.07729999721050262, 0.17219999432563782, -0.07519999891519547, 0.1193000003695488, -0.0786999985575676, 0.05050000175833702, 0.07320000231266022, -0.39660000801086426, 0.14159999787807465, -0.12759999930858612], [-0.16060000658035278, -0.26589998602867126, -0.0142000000923872, 0.06019999831914902, 0.18610000610351562, 0.07919999957084656, -0.29739999771118164, -0.1347000002861023, 0.01549999974668026, 0.25679999589920044, -0.0649000033736229, 0.06970000267028809, 0.24959999322891235, 0.11699999868869781, 0.31470000743865967, -0.07079999893903732, 0.026200000196695328, -0.15610000491142273, 0.09690000116825104, 0.09319999814033508, 0.44040000438690186, -0.053300000727176666, 0.3517000079154968, 0.36320000886917114, 0.03669999912381172], [0.09059999883174896, 0.05339999869465828, -0.11680000275373459, -0.11640000343322754, 0.01549999974668026, -0.2361000031232834, -0.19820000231266022, 0.3422999978065491, 0.10540000349283218, 0.4575999975204468, -0.07580000162124634, -0.20309999585151672, -0.007000000216066837, 0.0706000030040741, -0.31619998812675476, -0.23409999907016754, -0.17479999363422394, -0.07859999686479568, -0.034299999475479126, -0.12389999628067017, 0.3253999948501587, 0.02889999933540821, -0.3596000075340271, -0.030500000342726707, 0.17839999496936798], [-0.4677000045776367, 0.28940001130104065, -0.21539999544620514, -0.041600000113248825, 0.09799999743700027, 0.2825999855995178, 0.15240000188350677, -0.09709999710321426, 0.1632000058889389, -0.017100000753998756, -0.2922999858856201, -0.10920000076293945, 0.2547999918460846, -0.012600000016391277, -0.033799998462200165, -0.15790000557899475, -0.19840000569820404, 0.38580000400543213, -0.08079999685287476, -0.17820000648498535, 0.09399999678134918, 0.2142000049352646, 0.03970000147819519, -0.0763000026345253, -0.15240000188350677], [0.20069999992847443, -0.1298999935388565, -0.08150000125169754, 0.20430000126361847, -0.07029999792575836, -0.14800000190734863, 0.2766999900341034, -0.3028999865055084, -0.24699999392032623, -0.19449999928474426, 0.06199999898672104, -0.2498999983072281, 0.0034000000450760126, -0.25119999051094055, -0.179299995303154, -0.07739999890327454, -0.03709999844431877, 0.01510000042617321, -0.2930000126361847, 0.14169999957084656, 0.5009999871253967, 0.21709999442100525, 0.12080000340938568, -0.08429999649524689, 0.07490000128746033], [-0.1656000018119812, -0.21359999477863312, -0.21289999783039093, 0.12839999794960022, -0.09889999777078629, 0.06390000134706497, 0.41819998621940613, -0.3603000044822693, 0.23360000550746918, 0.31929999589920044, 0.36010000109672546, 0.1639000028371811, -0.016899999231100082, 0.13840000331401825, 0.020099999383091927, 0.009200000204145908, 0.06549999862909317, -0.06270000338554382, 0.290800005197525, -0.015399999916553497, 0.027300000190734863, 0.05350000038743019, -0.29910001158714294, -0.11789999902248383, 0.11649999767541885], [0.2517000138759613, 0.06679999828338623, -0.125900000333786, -0.29679998755455017, 0.01810000091791153, 0.2612000107765198, -0.054999999701976776, -0.14880000054836273, -0.1281999945640564, -0.18549999594688416, -0.04309999942779541, 0.5246000289916992, -0.12610000371932983, 0.028200000524520874, -0.020600000396370888, -0.16680000722408295, -0.2533000111579895, 0.21160000562667847, -0.030500000342726707, 0.2037999927997589, 0.14970000088214874, -0.032099999487400055, -0.28540000319480896, 0.2655999958515167, 0.1867000013589859], [0.17090000212192535, 0.2888000011444092, 0.010099999606609344, 0.16189999878406525, 0.22499999403953552, -0.11670000106096268, 0.11240000277757645, -0.07190000265836716, 0.10369999706745148, -0.08420000225305557, 0.034299999475479126, -0.1898999959230423, -0.0689999982714653, 0.3246999979019165, -0.06650000065565109, -0.009499999694526196, -0.305400013923645, 0.012799999676644802, 0.33070001006126404, 0.37229999899864197, 0.1363999992609024, -0.31220000982284546, 0.03350000083446503, -0.02850000001490116, -0.3871000111103058], [0.2777999937534332, -0.21410000324249268, 0.02979999966919422, 0.03139999881386757, 0.1168999969959259, -0.03959999978542328, 0.14059999585151672, 0.2556999921798706, 0.12389999628067017, -0.05730000138282776, 0.01489999983459711, 0.2660999894142151, 0.43779999017715454, 0.017000000923871994, -0.31189998984336853, 0.10689999908208847, 0.382099986076355, 0.33390000462532043, 0.09380000084638596, -0.09709999710321426, 0.15459999442100525, -0.023099999874830246, -0.01730000041425228, 0.06270000338554382, -0.28290000557899475], [0.07760000228881836, -0.41690000891685486, -0.0430000014603138, 0.1581999957561493, -0.044599998742341995, -0.10869999974966049, 0.2705000042915344, 0.0649000033736229, 0.226500004529953, -0.14239999651908875, -0.43070000410079956, -0.09139999747276306, -0.0997999981045723, -0.03620000183582306, -0.04450000077486038, 0.17560000717639923, -0.4016999900341034, 0.0035000001080334187, 0.11599999666213989, -0.21410000324249268, -0.13750000298023224, -0.08089999854564667, 0.02280000038444996, 0.34950000047683716, 0.15399999916553497]], [0.0, 0.0, 0.0, 0.0, 0.0, 0.0, 0.0, 0.0, 0.0, 0.0, 0.0, 0.0, 0.0, 0.0, 0.0, 0.0, 0.0, 0.0, 0.0, 0.0, 0.0, 0.0, 0.0, 0.0, 0.0], [[-0.04259999841451645, 0.029600000008940697, -0.07779999822378159], [-0.005100000184029341, -0.04410000145435333, -0.04879999905824661], [0.02410000003874302, -0.08290000259876251, -0.048500001430511475], [-0.09309999644756317, -0.053599998354911804, 0.0340999998152256], [0.01899999938905239, -0.04569999873638153, 0.06360000371932983], [0.0364999994635582, 0.09669999778270721, -0.010900000110268593], [-0.0017000000225380063, 0.053700000047683716, 0.0625], [0.025100000202655792, -0.013000000268220901, -0.017400000244379044], [-0.05829999968409538, 0.017000000923871994, -0.08060000091791153], [0.013899999670684338, 0.06469999998807907, -0.007400000002235174], [-0.00019999999494757503, 0.02930000051856041, 0.08919999748468399], [-0.005499999970197678, 0.018200000748038292, -0.07169999927282333], [0.0017999999690800905, 0.020500000566244125, -0.03720000013709068], [0.05310000106692314, 0.08250000327825546, -0.11060000211000443], [-0.053199999034404755, 0.0940999984741211, -0.09839999675750732], [-0.0729999989271164, 0.10050000250339508, -0.1046999990940094], [0.008999999612569809, -0.027699999511241913, 0.05829999968409538], [0.022199999541044235, -0.0681999996304512, -0.01940000057220459], [-0.03229999914765358, 0.015799999237060547, 0.05689999833703041], [-0.10809999704360962, 0.0026000000070780516, -0.10679999738931656], [0.03830000013113022, -0.10700000077486038, -0.01209999993443489], [-0.016100000590085983, -0.03929999843239784, -0.10050000250339508], [-0.024800000712275505, -0.023900000378489494, 0.01140000019222498], [-0.04430000111460686, 0.04039999842643738, 0.01549999974668026], [-0.025800000876188278, 0.06639999896287918, 0.06449999660253525]], [0.0, 0.0, 0.0]]</t>
+          <t>[[[0.07999999821186066, 0.005799999926239252, -0.07419999688863754, 0.015799999237060547, 0.03500000014901161], [-0.018699999898672104, -0.015799999237060547, -0.043299999088048935, 0.013000000268220901, 0.042500000447034836]], [[-0.19740000367164612, -0.25, -0.29330000281333923, -0.7731999754905701, 0.4634000062942505], [-0.37070000171661377, -0.28619998693466187, 0.5268999934196472, -0.37389999628067017, -0.6026999950408936], [0.5274999737739563, 0.2084999978542328, -0.44679999351501465, -0.37940001487731934, -0.5785999894142151], [0.25099998712539673, -0.899399995803833, -0.2290000021457672, 0.26030001044273376, -0.08900000154972076], [-0.6945000290870667, 0.057100001722574234, -0.6200000047683716, 0.22529999911785126, -0.2815999984741211]], [0.0, 0.0, 0.0, 0.0, 0.0], [[0.07999999821186066, 0.005799999926239252], [-0.07419999688863754, 0.015799999237060547], [0.03500000014901161, -0.018699999898672104], [-0.015799999237060547, -0.043299999088048935], [0.013000000268220901, 0.042500000447034836]], [[0.08590000122785568, 0.9962999820709229], [0.9962999820709229, -0.08590000122785568]], [0.0, 0.0], [[0.07999999821186066, 0.005799999926239252, -0.07419999688863754], [0.015799999237060547, 0.03500000014901161, -0.018699999898672104]], [0.0, 0.0, 0.0]]</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>[[[0.06430000066757202, 0.05999999865889549, -0.1527000069618225, -0.06780000030994415, 0.1185000017285347, 0.11379999667406082, 0.1152999997138977, -0.2126999944448471, 0.10080000013113022, -0.1266999989748001, -0.08760000020265579, 0.08990000188350677, 0.17159999907016754, -0.009999999776482582, 0.21209999918937683, 0.03799999877810478, 0.29440000653266907, -0.13670000433921814, 0.03539999946951866, 0.12790000438690186, 0.2678000032901764, -0.024800000712275505, 0.020999999716877937, 0.4562999904155731, -0.15929999947547913], [0.03880000114440918, -0.13130000233650208, -0.01679999940097332, 0.1881999969482422, -0.10530000180006027, -0.005200000014156103, -0.02410000003874302, 0.0778999999165535, -0.16439999639987946, -0.02280000038444996, -0.08380000293254852, 0.10859999805688858, -0.093299999833107, 0.08460000157356262, 0.04800000041723251, 0.20649999380111694, -0.3610000014305115, -0.016300000250339508, 0.03620000183582306, -0.27390000224113464, -0.21299999952316284, 0.15459999442100525, -0.23409999907016754, -0.4429999887943268, 0.15070000290870667]], [[-0.14710000157356262, -0.21209999918937683, 0.24979999661445618, 0.012500000186264515, -0.07729999721050262, -0.03480000048875809, -0.1665000021457672, 0.07599999755620956, -0.2615000009536743, -0.2160000056028366, -0.49619999527931213, -0.04430000111460686, -0.20669999718666077, 0.2680000066757202, -0.4932999908924103, -0.35589998960494995, 0.2766000032424927, -0.23250000178813934, -0.040699999779462814, 0.10790000110864639, -0.03519999980926514, 0.03240000084042549, -0.12120000272989273, 0.15850000083446503, -0.1851000040769577], [0.1753000020980835, -0.49480000138282776, 0.10130000114440918, 0.6427000164985657, 0.019600000232458115, 0.33399999141693115, 0.04809999838471413, 0.19189999997615814, 0.11029999703168869, 0.34290000796318054, 0.10499999672174454, 0.35269999504089355, -0.11969999969005585, -0.16290000081062317, 0.41769999265670776, -0.0005000000237487257, 0.07339999824762344, 0.027699999511241913, 0.026499999687075615, 0.06109999865293503, -0.013799999840557575, -0.020600000396370888, 0.05460000038146973, -0.03310000151395798, -0.6717000007629395], [0.4253999888896942, 0.24809999763965607, -0.09179999679327011, 0.40290001034736633, -0.5659999847412109, 0.08720000088214874, -0.15860000252723694, 0.19539999961853027, -0.16920000314712524, 0.04490000009536743, -0.4090000092983246, -0.1842000037431717, -0.32679998874664307, 0.00039999998989515007, 0.03440000116825104, -0.014800000004470348, 0.22370000183582306, 0.156700000166893, 0.24549999833106995, -0.28369998931884766, 0.03579999879002571, -0.13680000603199005, 0.15320000052452087, 0.017999999225139618, 0.16439999639987946], [0.31790000200271606, 0.3203999996185303, 0.49880000948905945, -0.2971000075340271, -0.13699999451637268, -0.08240000158548355, -0.12449999898672104, -0.1339000016450882, 0.3328999876976013, -0.29580000042915344, -0.04610000178217888, 0.03590000048279762, 0.10119999945163727, 0.1867000013589859, -0.5295000076293945, -0.35100001096725464, -0.3544999957084656, -0.48260000348091125, -0.44290000200271606, -0.44830000400543213, -0.04170000180602074, -0.04129999876022339, 0.05000000074505806, -0.052299998700618744, 0.5899999737739563], [-0.21809999644756317, -0.30329999327659607, -0.26910001039505005, -0.06109999865293503, 0.06729999929666519, 0.07280000299215317, -0.21559999883174896, -0.08879999816417694, 0.014000000432133675, -0.39340001344680786, 0.49149999022483826, 0.049800001084804535, 0.3037000000476837, 0.1039000004529953, 0.5026000142097473, -0.21819999814033508, 0.04560000076889992, 0.11389999836683273, 0.5385000109672546, 0.026200000196695328, 0.2922999858856201, 0.18790000677108765, 0.0794999971985817, -0.26570001244544983, -0.4203999936580658], [-0.10740000009536743, -0.02329999953508377, 0.04309999942779541, -0.26420000195503235, -0.2160000056028366, 0.032499998807907104, -0.020999999716877937, -0.06589999794960022, -0.00800000037997961, 0.11959999799728394, 0.039799999445676804, -0.11640000343322754, -0.10760000348091125, -0.18060000240802765, 0.10740000009536743, 0.17970000207424164, -0.2168000042438507, -0.09709999710321426, -0.06480000168085098, -0.20090000331401825, 0.21279999613761902, -0.6970999836921692, -0.08829999715089798, -0.12639999389648438, -0.26930001378059387], [-0.25999999046325684, 0.1428000032901764, 0.08070000261068344, -0.24220000207424164, 0.19429999589920044, -0.1834000051021576, 0.43950000405311584, 0.19519999623298645, -0.05660000070929527, -0.19269999861717224, 0.015599999576807022, 0.3995000123977661, 0.12290000170469284, 0.1378999948501587, 0.6236000061035156, 0.05079999938607216, -0.1818999946117401, -0.26669999957084656, 0.14910000562667847, -0.10930000245571136, 0.5805000066757202, 0.22190000116825104, -0.1096000000834465, -0.32170000672340393, 0.15080000460147858], [0.32170000672340393, 0.006200000178068876, 0.2703000009059906, -0.02930000051856041, 0.1469999998807907, -0.010200000368058681, -0.12549999356269836, 0.0957999974489212, 0.1956000030040741, -0.028200000524520874, -0.04170000180602074, -0.682200014591217, -0.6744999885559082, -0.09390000253915787, 0.1776999980211258, -0.049400001764297485, 0.03629999980330467, 0.3359000086784363, -0.2809999883174896, -0.49639999866485596, -0.09769999980926514, 0.08510000258684158, -0.23399999737739563, 0.24879999458789825, 0.28130000829696655], [0.20160000026226044, 0.04439999908208847, -0.12460000067949295, 0.3885999917984009, -0.1492999941110611, 0.16019999980926514, 0.09780000150203705, 0.36079999804496765, -0.3021000027656555, 0.08070000261068344, 0.14810000360012054, -0.263700008392334, 0.38040000200271606, -0.13189999759197235, 0.36419999599456787, -0.06689999997615814, -0.09430000185966492, -0.10970000177621841, 0.16539999842643738, 0.1979999989271164, -0.26660001277923584, -0.2176000028848648, -0.31769999861717224, 0.28870001435279846, -0.17749999463558197], [-0.33880001306533813, 0.049400001764297485, 0.11289999634027481, 0.20160000026226044, -0.0982000008225441, -0.507099986076355, -0.026000000536441803, 0.10570000112056732, -0.042899999767541885, -0.11180000007152557, -0.03610000014305115, 0.04569999873638153, -0.1080000028014183, -0.23019999265670776, 0.014600000344216824, -0.47600001096725464, -0.09799999743700027, 0.4959999918937683, -0.19470000267028809, 0.1339000016450882, -0.08410000056028366, -0.2184000015258789, 0.07169999927282333, -0.02160000056028366, 0.4577000141143799], [-0.44190001487731934, 0.20489999651908875, 0.3725999891757965, -0.004699999932199717, 0.13760000467300415, -0.21279999613761902, 0.11209999769926071, -0.2946000099182129, -0.5759999752044678, -0.012400000356137753, 0.35510000586509705, 0.05530000105500221, 0.21089999377727509, 0.29280000925064087, -0.011800000444054604, 0.257099986076355, -0.41200000047683716, 0.2865000069141388, 0.07450000196695328, -0.3149000108242035, 0.40549999475479126, 0.19349999725818634, -0.08720000088214874, 0.004000000189989805, 0.2303999960422516], [-0.09719999879598618, 0.09589999914169312, -0.44369998574256897, 0.02239999920129776, 0.558899998664856, -0.18279999494552612, -0.01979999989271164, -0.3321000039577484, -0.17069999873638153, -0.15870000422000885, 0.02879999950528145, 0.3824000060558319, 0.1770000010728836, 0.45559999346733093, 0.03500000014901161, 0.08030000329017639, -0.061900001019239426, -0.03009999915957451, -0.28049999475479126, -0.3285999894142151, 0.000699999975040555, -0.2953999936580658, -0.10429999977350235, -0.2727000117301941, 0.26440000534057617], [-0.2231999933719635, 0.07840000092983246, -0.4025000035762787, -0.5038999915122986, 0.3278000056743622, -0.3659000098705292, 0.38659998774528503, -0.5149999856948853, -0.36000001430511475, -0.09290000051259995, 0.3366999924182892, 0.5525000095367432, 0.4207000136375427, 0.11249999701976776, 0.019899999722838402, -0.608299970626831, -0.14810000360012054, -0.32679998874664307, 0.23510000109672546, -0.3474999964237213, 0.12630000710487366, 0.1826999932527542, 0.32089999318122864, -0.16359999775886536, -0.2676999866962433], [-0.14509999752044678, 0.12680000066757202, 0.27410000562667847, -0.09939999878406525, 0.6808000206947327, 0.24869999289512634, 0.049400001764297485, -0.20409999787807465, -0.3695000112056732, 0.034699998795986176, -0.11800000071525574, 0.06019999831914902, 0.06989999860525131, -0.40779998898506165, -0.2874000072479248, -0.13420000672340393, 0.025699999183416367, 0.05990000069141388, 0.38920000195503235, -0.03269999846816063, 0.12960000336170197, -0.1103999987244606, 0.10639999806880951, -0.3698999881744385, 0.30880001187324524], [-0.29030001163482666, 0.30640000104904175, -0.12460000067949295, 0.10530000180006027, 0.020600000396370888, -0.00430000014603138, 0.04650000110268593, 0.15649999678134918, 0.22679999470710754, -0.18610000610351562, 0.37549999356269836, 0.15839999914169312, -0.29409998655319214, -0.0869000032544136, -0.24860000610351562, 0.03929999843239784, 0.05590000003576279, -0.3107999861240387, 0.0421999990940094, -0.2637999951839447, 0.16009999811649323, -0.05469999834895134, 0.07940000295639038, 0.4449000060558319, 0.09730000048875809], [-0.012600000016391277, 0.33239999413490295, 0.2198999971151352, 0.023900000378489494, -0.06300000101327896, -0.28630000352859497, -0.3336000144481659, -0.4359000027179718, 0.2476000040769577, 0.008999999612569809, -0.2930000126361847, 0.07620000094175339, 0.065700002014637, -0.29339998960494995, -0.08699999749660492, 0.15399999916553497, 0.18279999494552612, -0.1429000049829483, -0.0017000000225380063, -0.17800000309944153, 0.04969999939203262, 0.007199999876320362, -0.40049999952316284, 0.03240000084042549, -0.09030000120401382], [-0.12489999830722809, -0.6439999938011169, -0.2630000114440918, 0.3057999908924103, 0.20090000331401825, 0.2720000147819519, -0.007199999876320362, -0.27410000562667847, -0.06949999928474426, 0.3617999851703644, 0.1670999974012375, 0.4803999960422516, 0.5683000087738037, 0.26159998774528503, 0.8317999839782715, -0.423799991607666, 0.04129999876022339, -0.24950000643730164, 0.3700000047683716, 0.2768999934196472, 0.6948999762535095, 0.04960000142455101, 0.373199999332428, 0.3953000009059906, -0.23479999601840973], [0.20960000157356262, 0.04019999876618385, -0.09449999779462814, -0.04580000042915344, 0.0015999999595806003, -0.2644999921321869, -0.2092999964952469, 0.3847000002861023, 0.09470000118017197, 0.30309998989105225, -0.12330000102519989, -0.2856000065803528, -0.08020000159740448, -0.03420000150799751, -0.43470001220703125, -0.2662999927997589, -0.1745000034570694, -0.05550000071525574, 0.02319999970495701, -0.09319999814033508, 0.3824999928474426, 0.06809999793767929, -0.3596000075340271, 0.005799999926239252, 0.2856999933719635], [-0.6593000292778015, 0.37059998512268066, -0.3528999984264374, -0.2370000034570694, 0.21160000562667847, 0.1973000019788742, 0.1762000024318695, -0.5099999904632568, 0.0835999995470047, -0.10949999839067459, -0.06800000369548798, 0.07519999891519547, 0.3603000044822693, -0.0722000002861023, -0.05040000006556511, -0.2874999940395355, -0.5475000143051147, 0.10930000245571136, -0.24950000643730164, -0.46299999952316284, 0.42010000348091125, 0.3172999918460846, -0.06589999794960022, -0.15240000188350677, 0.23430000245571136], [0.08100000023841858, -0.23399999737739563, -0.16030000150203705, 0.27320000529289246, 0.0575999990105629, -0.07769999653100967, 0.44130000472068787, -0.35010001063346863, -0.3230000138282776, -0.31130000948905945, 0.24330000579357147, -0.17069999873638153, 0.19249999523162842, -0.15399999916553497, -0.07419999688863754, -0.25110000371932983, 0.10750000178813934, 0.00279999990016222, -0.13930000364780426, 0.24789999425411224, 0.8281999826431274, 0.3131999969482422, 0.15850000083446503, -0.13529999554157257, -0.053199999034404755], [-0.42559999227523804, -0.15940000116825104, -0.4041999876499176, 0.008999999612569809, 0.15710000693798065, 0.20990000665187836, 0.6419000029563904, -0.5627999901771545, 0.05510000139474869, 0.23010000586509705, 0.6607999801635742, 0.5306000113487244, 0.3334999978542328, 0.30410000681877136, 0.2387000024318695, -0.5026000142097473, 0.28279998898506165, -0.26499998569488525, 0.426800012588501, 0.07760000228881836, 0.4408000111579895, 0.22869999706745148, -0.14149999618530273, -0.27379998564720154, -0.211899995803833], [0.21709999442100525, 0.027000000700354576, -0.1720000058412552, -0.4401000142097473, -0.014299999922513962, 0.3425999879837036, -0.044599998742341995, -0.23319999873638153, -0.10209999978542328, -0.048900000751018524, -0.030500000342726707, 0.6272000074386597, -0.06750000268220901, 0.12070000171661377, -0.02290000021457672, -0.15469999611377716, -0.2761000096797943, 0.15049999952316284, -0.15870000422000885, 0.1712999939918518, 0.045099999755620956, -0.1282999962568283, -0.25189998745918274, 0.31869998574256897, 0.21860000491142273], [0.11630000174045563, 0.24539999663829803, 0.012400000356137753, 0.258899986743927, 0.29649999737739563, -0.09799999743700027, 0.2110999971628189, -0.05979999899864197, 0.04540000110864639, -0.15559999644756317, 0.09759999811649323, -0.2231999933719635, -0.043699998408555984, 0.29249998927116394, 0.0017999999690800905, -0.0966000035405159, -0.26460000872612, 0.05290000140666962, 0.426800012588501, 0.43309998512268066, 0.3188999891281128, -0.23929999768733978, 0.03550000116229057, -0.04910000041127205, -0.39739999175071716], [0.5180000066757202, -0.7975999712944031, -0.0917000025510788, 0.45500001311302185, -0.1151999980211258, 0.1542000025510788, 0.35409998893737793, 0.3050000071525574, 0.37610000371932983, 0.18520000576972961, 0.15109999477863312, 0.4336000084877014, 0.6053000092506409, 0.052799999713897705, 0.09300000220537186, -0.13109999895095825, 0.6995000243186951, 0.3292999863624573, 0.4794999957084656, 0.3037000000476837, 0.36000001430511475, -0.08860000222921371, 0.2558000087738037, 0.24480000138282776, -0.659500002861023], [0.4535999894142151, -0.3206000030040741, 0.22439999878406525, 0.20000000298023224, -0.13699999451637268, -0.2558000087738037, -0.02199999988079071, 0.3296999931335449, 0.2517000138759613, 0.029400000348687172, -0.8077999949455261, -0.3050999939441681, -0.3765999972820282, -0.09359999746084213, -0.2296999990940094, 0.27230000495910645, -0.32109999656677246, 0.32190001010894775, 0.06210000067949295, -0.04809999838471413, -0.5814999938011169, -0.25600001215934753, 0.20600000023841858, 0.4763999879360199, -0.08070000261068344]], [0.09520000219345093, -0.06700000166893005, -0.05290000140666962, 0.08110000193119049, -0.0640999972820282, -0.08089999854564667, -0.010700000450015068, -0.1316000074148178, -0.05869999900460243, 0.020999999716877937, -0.07039999961853027, 0.23070000112056732, 0.0568000003695488, -0.019700000062584877, -0.18150000274181366, 0.026399999856948853, 0.049400001764297485, -0.005400000140070915, 0.02630000002682209, -0.02419999986886978, 0.0032999999821186066, 0.27219998836517334, -0.05180000141263008, 0.10869999974966049, 0.09319999814033508], [[-0.23819999396800995, 0.00419999985024333, 0.09399999678134918], [0.21699999272823334, -0.04839999973773956, -0.15299999713897705], [-0.031300000846385956, -0.1257999986410141, -0.09619999676942825], [-0.08839999884366989, -0.04529999941587448, 0.16140000522136688], [0.14319999516010284, 0.026100000366568565, -0.01640000008046627], [-0.20919999480247498, 0.14910000562667847, 0.05310000106692314], [0.04089999943971634, 0.037300001829862595, 0.0723000019788742], [-0.14589999616146088, -0.07840000092983246, 0.10729999840259552], [-0.2815000116825104, -0.012500000186264515, -0.08780000358819962], [-0.09849999845027924, -0.0210999995470047, 0.03150000050663948], [0.10819999873638153, -0.1281999945640564, -0.06790000200271606], [0.18629999458789825, 0.06790000200271606, -0.023399999365210533], [0.10419999808073044, 0.0020000000949949026, 0.050700001418590546], [0.13660000264644623, 0.019700000062584877, -0.13339999318122864], [-0.23499999940395355, 0.16779999434947968, -0.08340000361204147], [0.1451999992132187, 0.1535000056028366, -0.07270000129938126], [-0.6514000296592712, -0.11949999630451202, -0.00039999998989515007], [0.04340000078082085, -0.12129999697208405, -0.043800000101327896], [-0.11879999935626984, -0.012799999676644802, 0.15489999949932098], [-0.40860000252723694, -0.0658000037074089, -0.14920000731945038], [0.10429999977350235, -0.20419999957084656, 0.1014999970793724], [0.1598999947309494, 0.06759999692440033, 0.014600000344216824], [-0.2037000060081482, -0.11460000276565552, -0.08030000329017639], [-0.5063999891281128, 0.03920000046491623, -0.015399999916553497], [0.4595000147819519, 0.061900001019239426, -0.07159999758005142]], [-0.06159999966621399, -0.025299999862909317, -0.02019999921321869]]</t>
+          <t>[[[0.6294999718666077, 0.19589999318122864, 0.35100001096725464, -0.17309999465942383, -0.08720000088214874], [0.24120000004768372, -0.18799999356269836, -0.17560000717639923, 0.3018999993801117, 0.21490000188350677]], [[-0.2207999974489212, -0.08630000054836273, -0.04769999906420708, -0.849399983882904, -0.15800000727176666], [-0.5935999751091003, -0.10499999672174454, 0.6065000295639038, -0.8287000060081482, -0.8130999803543091], [0.15399999916553497, 0.3871000111103058, -0.44279998540878296, -0.9106000065803528, -0.9886999726295471], [-0.21930000185966492, -1.6263999938964844, -1.228600025177002, 1.152899980545044, 0.3659000098705292], [-0.6297000050544739, -0.08919999748468399, -0.7132999897003174, 0.5098999738693237, -0.1834000051021576]], [0.38269999623298645, 0.11129999905824661, 0.12759999930858612, 0.015200000256299973, -0.09809999912977219], [[0.5105999708175659, -0.09650000184774399], [0.039900001138448715, -0.49140000343322754], [0.18880000710487366, -0.4925000071525574], [0.19009999930858612, 0.25850000977516174], [0.19349999725818634, 0.12449999898672104]], [[0.33570000529289246, 1.5866999626159668], [1.62909996509552, 0.08869999647140503]], [0.16060000658035278, 0.20739999413490295], [[-0.24779999256134033, 0.26100000739097595, -0.40310001373291016], [-1.0205999612808228, -0.1606999933719635, 0.1882999986410141]], [0.09629999846220016, -0.050700001418590546, 0.11590000241994858]]</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>[0.8974495524929746]</t>
+          <t>[0.9394912019193224]</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>[0.02340884488916913]</t>
+          <t>[0.01381213932395177]</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>[-0.07727346265575852]</t>
+          <t>[0.7194121108534848]</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>[0.24594505522827545]</t>
+          <t>[0.06405913288015035]</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>[0.6077239339888088]</t>
+          <t>[-2.661116478838173]</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>[0.12838399106093967]</t>
+          <t>[1.1982090828829957]</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>[0.6184507848076475]</t>
+          <t>[0.6677845565739613]</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>[0.08764913207949243]</t>
+          <t>[0.07631622375377285]</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>[-0.9637755126642278]</t>
+          <t>[0.3400151178911357]</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>[0.4657310176290104]</t>
+          <t>[0.1565226925287971]</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>[-0.9082534244145306]</t>
+          <t>[0.021909605851393787]</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>[0.6273334350337971]</t>
+          <t>[0.32154471669456597]</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>[0.8120273064234088]</t>
+          <t>[-0.5558327553564202]</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>[0.020268292718887505]</t>
+          <t>[0.16775880106409372]</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>[-0.5908421785877884]</t>
+          <t>[-0.4029073931999503]</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>[0.13404490247126177]</t>
+          <t>[0.11820945360188786]</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>[-1.0482939531216942]</t>
+          <t>[-1.0868969411406946]</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>[0.19586428014346802]</t>
+          <t>[0.19955561870754732]</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>[0.6843691908548768]</t>
+          <t>[-0.7146756704384578]</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>[0.033065680378989104]</t>
+          <t>[0.17963049242850804]</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>[-0.622070277176809]</t>
+          <t>[-0.5682046578959739]</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>[0.13348536947110154]</t>
+          <t>[0.12905259476789538]</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>[-1.6490676315748019]</t>
+          <t>[-1.8342853445870362]</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>[0.2437258100416759]</t>
+          <t>[0.2607666498450514]</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>[-1.9766867924512819]</t>
+          <t>[-1.1277323404288389]</t>
         </is>
       </c>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>[0.24943436130326505]</t>
+          <t>[0.1782953983284605]</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>[-2.800034539584052]</t>
+          <t>[-1.0076613792251892]</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>[0.4091804006772131]</t>
+          <t>[0.21618111072891705]</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>[-1.6454684046389096]</t>
+          <t>[-2.8322102282518293]</t>
         </is>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>[0.19695501281452504]</t>
+          <t>[0.28530789227713904]</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>[-2.184479710594939]</t>
+          <t>[-1.4485778097325301]</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>[0.26096456727565737]</t>
+          <t>[0.20065822571632816]</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>[-2.717476254080248]</t>
+          <t>[-1.1083771112926066]</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>[0.39458286776880636]</t>
+          <t>[0.22378878304840139]</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>[-1.9801357504904407]</t>
+          <t>[-3.916196569951861]</t>
         </is>
       </c>
       <c r="AN6" t="inlineStr">
         <is>
-          <t>[0.2288960304415363]</t>
+          <t>[0.37759953705031307]</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>model_5_2_0</t>
+          <t>model_10_5_0</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>[5, 2]</t>
+          <t>[10, 5]</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>[[[-0.04259999841451645, 0.029600000008940697, -0.07779999822378159, -0.005100000184029341, -0.04410000145435333], [-0.04879999905824661, 0.02410000003874302, -0.08290000259876251, -0.048500001430511475, -0.09309999644756317]], [[-0.06080000102519989, 0.017000000923871994, -0.5347999930381775, -0.23589999973773956, 0.808899998664856], [0.5494999885559082, -0.2662000060081482, 0.5062000155448914, 0.3644999861717224, 0.4878999888896942], [0.8001999855041504, 0.38359999656677246, -0.22300000488758087, -0.3515999913215637, -0.19779999554157257], [-0.17569999396800995, 0.15489999949932098, 0.6201000213623047, -0.7264000177383423, 0.18170000612735748], [0.15219999849796295, -0.8704000115394592, -0.15330000221729279, -0.400299996137619, -0.1882999986410141]], [0.0, 0.0, 0.0, 0.0, 0.0], [[-0.04259999841451645, 0.029600000008940697], [-0.07779999822378159, -0.005100000184029341], [-0.04410000145435333, -0.04879999905824661], [0.02410000003874302, -0.08290000259876251], [-0.048500001430511475, -0.09309999644756317]], [[0.8902000188827515, -0.4555000066757202], [0.4555000066757202, 0.8902000188827515]], [0.0, 0.0], [[-0.04259999841451645, 0.029600000008940697, -0.07779999822378159], [-0.005100000184029341, -0.04410000145435333, -0.04879999905824661]], [0.0, 0.0, 0.0]]</t>
+          <t>[[[0.03319999948143959, 0.0027000000700354576, -0.016699999570846558, -0.0017999999690800905, 0.12229999899864197, -0.014700000174343586, -0.04670000076293945, -0.05999999865889549, -0.0005000000237487257, -0.16120000183582306], [-0.057500001043081284, -0.03150000050663948, 0.04129999876022339, 0.027000000700354576, -0.054999999701976776, 0.0066999997943639755, 0.0007999999797903001, 0.059300001710653305, 0.00139999995008111, -0.021199999377131462]], [[-0.28209999203681946, 0.3644999861717224, 0.031700000166893005, 0.7330999970436096, 0.31929999589920044, -0.061900001019239426, -0.3179999887943268, -0.11209999769926071, -0.1517000049352646, 0.08190000057220459], [-0.18209999799728394, -0.4537999927997589, -0.5788000226020813, 0.33880001306533813, -0.30630001425743103, 0.2071000039577484, -0.19529999792575836, 0.188400000333786, 0.31679999828338623, 0.0210999995470047], [-0.3212999999523163, -0.22220000624656677, 0.014399999752640724, -0.2653999924659729, 0.5875999927520752, -0.25220000743865967, -0.24889999628067017, 0.08250000327825546, 0.36489999294281006, -0.4074000120162964], [0.274399995803833, 0.007499999832361937, -0.026200000196695328, 0.0674000009894371, -0.38029998540878296, -0.3181999921798706, -0.41119998693466187, -0.03530000150203705, -0.3010999858379364, -0.6424000263214111], [0.5289999842643738, 0.010499999858438969, -0.07079999893903732, 0.20999999344348907, 0.39489999413490295, 0.2563999891281128, 0.14100000262260437, 0.6200000047683716, -0.08959999680519104, -0.19220000505447388], [-0.05310000106692314, 0.671500027179718, -0.4221999943256378, -0.041099999099969864, -0.13189999759197235, -0.22190000116825104, 0.32409998774528503, 0.09309999644756317, 0.37959998846054077, -0.2045000046491623], [0.5260999798774719, -0.026399999856948853, 0.27379998564720154, 0.2370000034570694, -0.002099999925121665, 0.028999999165534973, -0.10540000349283218, -0.38749998807907104, 0.6552000045776367, 0.006599999964237213], [-0.20739999413490295, -0.26750001311302185, 0.4309000074863434, 0.3774999976158142, -0.20730000734329224, -0.4187000095844269, 0.48969998955726624, 0.27559998631477356, 0.09989999979734421, -0.11500000208616257], [-0.1046999990940094, 0.2736000120639801, 0.38019999861717224, -0.1639000028371811, -0.28540000319480896, 0.05779999867081642, -0.4837999939918518, 0.5583000183105469, 0.24210000038146973, 0.23160000145435333], [0.30880001187324524, -0.1168999969959259, -0.2732999920845032, -0.03909999877214432, 0.12860000133514404, -0.7027999758720398, -0.14079999923706055, 0.11429999768733978, -0.05299999937415123, 0.5182999968528748]], [0.0, 0.0, 0.0, 0.0, 0.0, 0.0, 0.0, 0.0, 0.0, 0.0], [[0.03319999948143959, 0.0027000000700354576, -0.016699999570846558, -0.0017999999690800905, 0.12229999899864197], [-0.014700000174343586, -0.04670000076293945, -0.05999999865889549, -0.0005000000237487257, -0.16120000183582306], [-0.057500001043081284, -0.03150000050663948, 0.04129999876022339, 0.027000000700354576, -0.054999999701976776], [0.0066999997943639755, 0.0007999999797903001, 0.059300001710653305, 0.00139999995008111, -0.021199999377131462], [0.06199999898672104, 0.042500000447034836, 0.11349999904632568, 0.019600000232458115, 0.05620000138878822], [-0.0026000000070780516, -0.029600000008940697, 0.05090000107884407, -0.008500000461935997, 0.039400000125169754], [0.014999999664723873, 0.01720000058412552, 0.03959999978542328, 0.014700000174343586, 0.010400000028312206], [0.060499999672174454, -0.015599999576807022, -0.013299999758601189, 0.07540000230073929, -0.02539999969303608], [0.0722000002861023, -0.014800000004470348, -0.05270000174641609, 0.08399999886751175, -0.05649999901652336], [0.015200000256299973, -0.012799999676644802, -0.015799999237060547, 0.018699999898672104, 0.006300000008195639]], [[0.7603999972343445, -0.4284000098705292, -0.2085999995470047, -0.4345000088214874, -0.07699999958276749], [0.4487999975681305, 0.16140000522136688, -0.2842999994754791, 0.677299976348877, 0.482699990272522], [0.4074000120162964, 0.47350001335144043, 0.7613999843597412, -0.1379999965429306, 0.10499999672174454], [-0.20149999856948853, -0.5788999795913696, 0.3573000133037567, -0.07760000228881836, 0.7003999948501587], [0.11710000038146973, -0.48069998621940613, 0.41019999980926514, 0.5722000002861023, -0.5094000101089478]], [0.0, 0.0, 0.0, 0.0, 0.0], [[0.03319999948143959, 0.0027000000700354576, -0.016699999570846558], [-0.0017999999690800905, 0.12229999899864197, -0.014700000174343586], [-0.04670000076293945, -0.05999999865889549, -0.0005000000237487257], [-0.16120000183582306, -0.057500001043081284, -0.03150000050663948], [0.04129999876022339, 0.027000000700354576, -0.054999999701976776]], [0.0, 0.0, 0.0]]</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>[[[-0.45249998569488525, 0.21459999680519104, -0.06849999725818634, 0.6783999800682068, -0.46380001306533813], [-0.01899999938905239, -0.37950000166893005, -0.357699990272522, -0.4607999920845032, 0.027699999511241913]], [[0.011699999682605267, -0.010700000450015068, -0.5005999803543091, -0.27390000224113464, 0.79830002784729], [0.3174999952316284, 0.33180001378059387, 1.0716999769210815, 0.8389999866485596, 0.22830000519752502], [0.8518999814987183, 0.9316999912261963, 0.20759999752044678, -0.17990000545978546, -0.2671999931335449], [-0.47429999709129333, 0.9951000213623047, 1.3166999816894531, 0.09390000253915787, -0.2924000024795532], [0.22920000553131104, -0.8697999715805054, -0.11810000240802765, -0.43799999356269836, -0.17560000717639923]], [0.13699999451637268, 0.08219999819993973, 0.13169999420642853, -0.07069999724626541, 0.11140000075101852], [[-0.20600000023841858, 0.1492999941110611], [-0.30309998989105225, -0.585099995136261], [-0.3492000102996826, -0.566100001335144], [0.17090000212192535, -0.3889999985694885], [-0.2167000025510788, 0.02800000086426735]], [[1.073699951171875, -0.6110000014305115], [0.8338000178337097, 1.5658999681472778]], [0.44200000166893005, -0.04820000007748604], [[-0.6061999797821045, 0.48899999260902405, 0.01119999960064888], [-0.42260000109672546, -0.4066999852657318, 0.020800000056624413]], [0.060499999672174454, -0.14560000598430634, 0.02160000056028366]]</t>
+          <t>[[[0.193900004029274, -0.04749999940395355, -0.07410000264644623, -0.01899999938905239, 0.37790000438690186, 0.14749999344348907, -0.06159999966621399, -0.33889999985694885, -0.22859999537467957, -0.3084999918937683], [-0.3111000061035156, -0.1379999965429306, 0.25040000677108765, -0.1265999972820282, -0.1386999934911728, -0.22339999675750732, -0.16040000319480896, 0.18770000338554382, -0.02979999966919422, -0.030799999833106995]], [[-0.026599999517202377, 0.6495000123977661, -0.25099998712539673, 1.0641000270843506, 0.40689998865127563, 0.1720000058412552, -0.29280000925064087, -0.3982999920845032, -0.4708999991416931, 0.013299999758601189], [0.06790000200271606, -0.3544999957084656, -0.7817999720573425, 0.4894999861717224, -0.3375000059604645, 0.2766999900341034, -0.32019999623298645, 0.013000000268220901, 0.2815999984741211, -0.04690000042319298], [-0.567799985408783, -0.4474000036716461, 0.23680000007152557, -0.531499981880188, 0.5688999891281128, -0.39160001277923584, -0.18729999661445618, 0.29910001158714294, 0.47530001401901245, -0.34389999508857727], [0.4203999936580658, 0.13519999384880066, -0.11940000206232071, 0.15559999644756317, -0.383899986743927, -0.30469998717308044, -0.47870001196861267, -0.19169999659061432, -0.47360000014305115, -0.7034000158309937], [0.6305999755859375, 0.10329999774694443, -0.34049999713897705, 0.33320000767707825, 0.6025000214576721, 0.41749998927116394, 0.3228999972343445, 0.39649999141693115, -0.2775000035762787, -0.19509999454021454], [0.2766999900341034, 0.7641000151634216, -0.7268999814987183, 0.17430000007152557, 0.1468999981880188, 0.05139999836683273, 0.44760000705718994, -0.22609999775886536, 0.31450000405311584, -0.4052000045776367], [0.5579000115394592, -0.21549999713897705, 0.3034000098705292, 0.1923999935388565, -0.14000000059604645, -0.06390000134706497, -0.42179998755455017, -0.22509999573230743, 0.7451000213623047, 0.05920000001788139], [-0.3059999942779541, -0.4523000121116638, 0.5674999952316284, 0.18279999494552612, -0.5382999777793884, -0.7041000127792358, 0.13809999823570251, 0.6183000206947327, 0.3610000014305115, -0.019700000062584877], [-0.19939999282360077, 0.29179999232292175, 0.5284000039100647, -0.12639999389648438, -0.3953000009059906, -0.0020000000949949026, -0.6385999917984009, 0.6647999882698059, 0.2621000111103058, 0.28610000014305115], [0.3255999982357025, -0.11410000175237656, -0.1673000007867813, -0.04910000041127205, -0.02630000002682209, -0.781499981880188, -0.3580000102519989, 0.24819999933242798, 0.023000000044703484, 0.5127000212669373]], [-0.03189999982714653, -0.06729999929666519, 0.04259999841451645, -0.08410000056028366, 0.06960000097751617, 0.03689999878406525, 0.023800000548362732, -0.061500001698732376, -0.04490000009536743, -0.011699999682605267], [[0.3504999876022339, -0.14149999618530273, -0.08760000020265579, -0.24690000712871552, 0.4472000002861023], [0.26600000262260437, -0.14980000257492065, -0.1753000020980835, -0.25110000371932983, -0.048500001430511475], [-0.37779998779296875, 0.15219999849796295, 0.17470000684261322, 0.3034999966621399, -0.45590001344680786], [0.22830000519752502, -0.14820000529289246, -0.056699998676776886, -0.2345000058412552, -0.1005999967455864], [0.2892000079154968, 0.16359999775886536, 0.21320000290870667, -0.07259999960660934, 0.12449999898672104], [0.3075000047683716, 0.08470000326633453, 0.07970000058412552, -0.08799999952316284, 0.09059999883174896], [0.06260000169277191, 0.13179999589920044, -0.2094999998807907, 0.2160000056028366, 0.21199999749660492], [-0.24799999594688416, -0.08150000125169754, -0.14920000731945038, 0.3321000039577484, -0.36489999294281006], [0.012900000438094139, -0.09149999916553497, -0.1306000053882599, 0.32190001010894775, 0.03929999843239784], [-0.12540000677108765, -0.15870000422000885, -0.11140000075101852, 0.193900004029274, -0.14000000059604645]], [[1.113800048828125, -0.7544999718666077, -0.5263000130653381, -0.7397000193595886, 0.13449999690055847], [0.5526999831199646, 0.2538999915122986, -0.29089999198913574, 0.7946000099182129, 0.5162000060081482], [0.5414999723434448, 0.5716000199317932, 0.7494000196456909, -0.1151999980211258, 0.19930000603199005], [-0.5389999747276306, -0.5145999789237976, 0.4812999963760376, 0.18400000035762787, 0.5914999842643738], [0.30480000376701355, -0.45989999175071716, 0.46709999442100525, 0.8274000287055969, -0.8450999855995178]], [0.0406000018119812, -0.002300000051036477, 0.16179999709129333, 0.016899999231100082, -0.08380000293254852], [[0.3346000015735626, 0.11029999703168869, -0.20229999721050262], [-0.12189999967813492, 0.22840000689029694, -0.15219999849796295], [-0.21080000698566437, 0.047600001096725464, -0.1251000016927719], [-0.47049999237060547, -0.027300000190734863, -0.09600000083446503], [-0.044199999421834946, 0.09629999846220016, -0.13249999284744263]], [0.02539999969303608, 0.016100000590085983, 0.08889999985694885]]</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>[0.7268502082588842]</t>
+          <t>[0.901165000367952]</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>[0.06235098199779763]</t>
+          <t>[0.02256073212990322]</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>[0.4666655358994509]</t>
+          <t>[0.7706696440111604]</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>[0.1217620026627053]</t>
+          <t>[0.052356870399599395]</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>[0.6446133441971286]</t>
+          <t>[-2.5702629869159823]</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>[0.1163108361560642]</t>
+          <t>[1.1684745797984744]</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>[0.4499382439631714]</t>
+          <t>[0.7294176997432379]</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>[0.12635967677837817]</t>
+          <t>[0.0621579152288954]</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>[0.12162930438739417]</t>
+          <t>[0.6349411998309793]</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>[0.2083152963691666]</t>
+          <t>[0.0865777200095956]</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>[0.49033666619803395]</t>
+          <t>[0.17679856773744052]</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>[0.16755051808847654]</t>
+          <t>[0.27062536643132495]</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>[0.7688681267059336]</t>
+          <t>[0.07058947980849728]</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>[0.02492196273540205]</t>
+          <t>[0.10021436688930214]</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>[-0.5183806697475049]</t>
+          <t>[0.06689911809506521]</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>[0.1279392711169066]</t>
+          <t>[0.07862339733902968]</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>[-1.1235824260094094]</t>
+          <t>[-0.6264881495380554]</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>[0.20306359961750117]</t>
+          <t>[0.15552988870842285]</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>[0.5424857679467856]</t>
+          <t>[-0.0924877271174569]</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>[0.047929476234858194]</t>
+          <t>[0.11444969551823694]</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>[-0.5506264722898879]</t>
+          <t>[0.020383965450814223]</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>[0.127606029453633]</t>
+          <t>[0.08061574775860335]</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>[-1.4723072484525828]</t>
+          <t>[-0.6634597887088123]</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>[0.22746308158346393]</t>
+          <t>[0.15304557710887656]</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>[-1.9644867718108965]</t>
+          <t>[-1.1969420899931125]</t>
         </is>
       </c>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>[0.2484120487227012]</t>
+          <t>[0.18409489652299757]</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>[-2.6778981928661425]</t>
+          <t>[-0.8854836210266508]</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>[0.39602899408690473]</t>
+          <t>[0.20302524503012956]</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>[-2.5473320199370493]</t>
+          <t>[-4.416476701193587]</t>
         </is>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>[0.2640987215038919]</t>
+          <t>[0.4032564653663937]</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>[-2.169519504577355]</t>
+          <t>[-1.6574573237814492]</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>[0.2597385950464281]</t>
+          <t>[0.2177756693650245]</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>[-2.631087032139101]</t>
+          <t>[-0.9612144723018614]</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>[0.3854132848022872]</t>
+          <t>[0.20816854712687818]</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>[-2.875705816140451]</t>
+          <t>[-4.520976562760358]</t>
         </is>
       </c>
       <c r="AN7" t="inlineStr">
         <is>
-          <t>[0.29768230401173124]</t>
+          <t>[0.4240510249134228]</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>model_10_5_0</t>
+          <t>model_10_5_1</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1855,596 +1855,7868 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>[[[-0.04259999841451645, 0.029600000008940697, -0.07779999822378159, -0.005100000184029341, -0.04410000145435333, -0.04879999905824661, 0.02410000003874302, -0.08290000259876251, -0.048500001430511475, -0.09309999644756317], [-0.053599998354911804, 0.0340999998152256, 0.01899999938905239, -0.04569999873638153, 0.06360000371932983, 0.0364999994635582, 0.09669999778270721, -0.010900000110268593, -0.0017000000225380063, 0.053700000047683716]], [[-0.5573999881744385, -0.3352999985218048, 0.08869999647140503, -0.1080000028014183, -0.4390999972820282, 0.13600000739097595, 0.3569999933242798, -0.02410000003874302, -0.09319999814033508, 0.4575999975204468], [0.051600001752376556, -0.04100000113248825, -0.23559999465942383, -0.28459998965263367, -0.45809999108314514, -0.5289999842643738, 0.11389999836683273, -0.12399999797344208, -0.3797999918460846, -0.44369998574256897], [0.3734000027179718, -0.5784000158309937, 0.19269999861717224, -0.535099983215332, 0.03359999880194664, 0.06080000102519989, 0.10580000281333923, 0.1728000044822693, 0.37880000472068787, -0.11479999870061874], [0.42829999327659607, 0.44699999690055847, 0.48579999804496765, -0.13760000467300415, -0.16429999470710754, -0.06360000371932983, 0.295199990272522, 0.27149999141693115, -0.2678000032901764, 0.313400000333786], [0.1996999979019165, 0.0035000001080334187, -0.18449999392032623, 0.17249999940395355, 0.26260000467300415, 0.05389999970793724, 0.788100004196167, -0.4399999976158142, 0.07530000060796738, -0.06430000066757202], [-0.3546999990940094, 0.4521999955177307, -0.22280000150203705, -0.6007000207901001, 0.2955000102519989, -0.22390000522136688, 0.10180000215768814, 0.06300000101327896, 0.2985000014305115, 0.1354999989271164], [-0.2295999974012375, -0.22269999980926514, 0.20970000326633453, 0.35839998722076416, 0.3009999990463257, -0.5945000052452087, 0.22300000488758087, 0.47269999980926514, 0.054999999701976776, -0.0714000016450882], [-0.21459999680519104, 0.3075999915599823, 0.31380000710487366, 0.14309999346733093, -0.3986999988555908, 0.18070000410079956, 0.16030000150203705, 0.06199999898672104, 0.49950000643730164, -0.5194000005722046], [0.31459999084472656, 0.04670000076293945, -0.48649999499320984, 0.24879999458789825, -0.4027999937534332, -0.2298000007867813, -0.014100000262260437, 0.17730000615119934, 0.4672999978065491, 0.3677999973297119], [0.01769999973475933, -0.025200000032782555, 0.4480000138282776, 0.025599999353289604, -0.0340999998152256, -0.4494999945163727, -0.2329999953508377, -0.6513000130653381, 0.2574000060558319, 0.22310000658035278]], [0.0, 0.0, 0.0, 0.0, 0.0, 0.0, 0.0, 0.0, 0.0, 0.0], [[-0.04259999841451645, 0.029600000008940697, -0.07779999822378159, -0.005100000184029341, -0.04410000145435333], [-0.04879999905824661, 0.02410000003874302, -0.08290000259876251, -0.048500001430511475, -0.09309999644756317], [-0.053599998354911804, 0.0340999998152256, 0.01899999938905239, -0.04569999873638153, 0.06360000371932983], [0.0364999994635582, 0.09669999778270721, -0.010900000110268593, -0.0017000000225380063, 0.053700000047683716], [0.0625, 0.025100000202655792, -0.013000000268220901, -0.017400000244379044, -0.05829999968409538], [0.017000000923871994, -0.08060000091791153, 0.013899999670684338, 0.06469999998807907, -0.007400000002235174], [-0.00019999999494757503, 0.02930000051856041, 0.08919999748468399, -0.005499999970197678, 0.018200000748038292], [-0.07169999927282333, 0.0017999999690800905, 0.020500000566244125, -0.03720000013709068, 0.05310000106692314], [0.08250000327825546, -0.11060000211000443, -0.053199999034404755, 0.0940999984741211, -0.09839999675750732], [-0.0729999989271164, 0.10050000250339508, -0.1046999990940094, 0.008999999612569809, -0.027699999511241913]], [[-0.40549999475479126, -0.5008999705314636, 0.14069999754428864, -0.004100000020116568, 0.7516000270843506], [0.4000999927520752, 0.07890000194311142, 0.08810000121593475, 0.8718000054359436, 0.2565999925136566], [-0.16220000386238098, 0.02759999968111515, 0.9535999894142151, 0.04830000177025795, -0.24740000069141388], [0.6514999866485596, 0.24719999730587006, 0.2493000030517578, -0.48399999737739563, 0.4668999910354614], [0.4740999937057495, -0.8252000212669373, 0.029600000008940697, -0.0575999990105629, -0.3000999987125397]], [0.0, 0.0, 0.0, 0.0, 0.0], [[-0.04259999841451645, 0.029600000008940697, -0.07779999822378159], [-0.005100000184029341, -0.04410000145435333, -0.04879999905824661], [0.02410000003874302, -0.08290000259876251, -0.048500001430511475], [-0.09309999644756317, -0.053599998354911804, 0.0340999998152256], [0.01899999938905239, -0.04569999873638153, 0.06360000371932983]], [0.0, 0.0, 0.0]]</t>
+          <t>[[[0.01979999989271164, -0.020899999886751175, 0.04690000042319298, 0.05649999901652336, 0.05119999870657921, -0.12319999933242798, 0.017400000244379044, 0.01510000042617321, -0.01759999990463257, 0.030300000682473183], [-0.039000000804662704, -0.014499999582767487, 0.03610000014305115, 0.09679999947547913, -0.0632999986410141, 0.003100000089034438, -0.010999999940395355, -0.0006000000284984708, 0.009399999864399433, 0.00570000009611249]], [[0.36730000376701355, 0.2628999948501587, -0.5149000287055969, -0.012500000186264515, -0.22499999403953552, -0.0024999999441206455, 0.3880999982357025, 0.19949999451637268, -0.34139999747276306, -0.41609999537467957], [0.3569999933242798, 0.28679999709129333, 0.5807999968528748, 0.08389999717473984, -0.4490000009536743, 0.26339998841285706, -0.3018999993801117, 0.22120000422000885, -0.18639999628067017, -0.006200000178068876], [-0.0575999990105629, -0.025200000032782555, 0.0071000000461936, -0.19709999859333038, -0.037700001150369644, -0.6995999813079834, -0.43220001459121704, -0.08919999748468399, -0.5167999863624573, -0.06689999997615814], [-0.024399999529123306, 0.0038999998942017555, -0.125, -0.02889999933540821, 0.37220001220703125, 0.5889000296592712, -0.31940001249313354, -0.3953000009059906, -0.45329999923706055, -0.18379999697208405], [-0.19979999959468842, 0.08959999680519104, -0.4828000068664551, 0.257099986076355, -0.14910000562667847, 0.08309999853372574, -0.6320000290870667, 0.3562000095844269, 0.29260000586509705, -0.10859999805688858], [0.3495999872684479, -0.36719998717308044, 0.1468999981880188, 0.11640000343322754, -0.032099999487400055, -0.13199999928474426, -0.13030000030994415, -0.31349998712539673, 0.36649999022483826, -0.6632000207901001], [0.3693999946117401, -0.3797999918460846, -0.23739999532699585, 0.5424000024795532, -0.20919999480247498, -0.031700000166893005, -0.023499999195337296, -0.23970000445842743, -0.17630000412464142, 0.4846000075340271], [-0.1784999966621399, -0.36550000309944153, -0.163100004196167, -0.5601000189781189, -0.6353999972343445, 0.23510000109672546, -0.01940000057220459, -0.17759999632835388, 0.017000000923871994, 0.05510000139474869], [0.45019999146461487, -0.43689998984336853, -0.039400000125169754, -0.3785000145435333, 0.3634999990463257, 0.07989999651908875, -0.13279999792575836, 0.5360999703407288, -0.01860000006854534, 0.13289999961853027], [0.4478999972343445, 0.4862000048160553, -0.20640000700950623, -0.349700003862381, 0.07039999961853027, -0.08630000054836273, -0.1858000010251999, -0.3813000023365021, 0.35280001163482666, 0.28529998660087585]], [0.0, 0.0, 0.0, 0.0, 0.0, 0.0, 0.0, 0.0, 0.0, 0.0], [[0.01979999989271164, -0.020899999886751175, 0.04690000042319298, 0.05649999901652336, 0.05119999870657921], [-0.12319999933242798, 0.017400000244379044, 0.01510000042617321, -0.01759999990463257, 0.030300000682473183], [-0.039000000804662704, -0.014499999582767487, 0.03610000014305115, 0.09679999947547913, -0.0632999986410141], [0.003100000089034438, -0.010999999940395355, -0.0006000000284984708, 0.009399999864399433, 0.00570000009611249], [-0.03370000049471855, -0.07819999754428864, -0.08079999685287476, 0.07209999859333038, 0.03180000185966492], [-0.039500001817941666, 0.04800000041723251, -0.0617000013589859, 0.14569999277591705, -0.03849999979138374], [-0.019700000062584877, 0.003700000001117587, -0.012799999676644802, 0.02979999966919422, -0.010999999940395355], [-0.023900000378489494, -0.02449999935925007, 0.014000000432133675, -0.05990000069141388, -0.028300000354647636], [0.032099999487400055, -0.0835999995470047, -0.06310000270605087, -0.0348999984562397, 0.05040000006556511], [-0.029600000008940697, 0.026799999177455902, -0.005100000184029341, -0.12250000238418579, 0.03200000151991844]], [[-0.03750000149011612, 0.0803999975323677, 0.2093999981880188, 0.5163000226020813, -0.8256999850273132], [-0.5005999803543091, 0.8294000029563904, 0.1573999971151352, -0.1898999959230423, 0.02459999918937683], [0.8547000288963318, 0.44279998540878296, 0.1453000009059906, -0.20999999344348907, -0.09019999951124191], [-0.045499999076128006, -0.2337000072002411, 0.9528999924659729, -0.08959999680519104, 0.164900004863739], [-0.1242000013589859, -0.23420000076293945, -0.04699999839067459, -0.8032000064849854, -0.5314000248908997]], [0.0, 0.0, 0.0, 0.0, 0.0], [[0.01979999989271164, -0.020899999886751175, 0.04690000042319298], [0.05649999901652336, 0.05119999870657921, -0.12319999933242798], [0.017400000244379044, 0.01510000042617321, -0.01759999990463257], [0.030300000682473183, -0.039000000804662704, -0.014499999582767487], [0.03610000014305115, 0.09679999947547913, -0.0632999986410141]], [0.0, 0.0, 0.0]]</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>[[[-0.28439998626708984, -0.009999999776482582, -0.29019999504089355, -0.15150000154972076, -0.09440000355243683, -0.18529999256134033, -0.3783999979496002, -0.05689999833703041, -0.23000000417232513, -0.3596000075340271], [0.13519999384880066, 0.18050000071525574, 0.11640000343322754, -0.060100000351667404, 0.3215000033378601, 0.41019999980926514, 0.3418000042438507, -0.24709999561309814, 0.12950000166893005, 0.3190999925136566]], [[-0.39070001244544983, -0.51910001039505, 0.22460000216960907, -0.03180000185966492, -0.5257999897003174, -0.11429999768733978, 0.43970000743865967, 0.1543000042438507, -0.07569999992847443, 0.5972999930381775], [0.01269999984651804, -0.10080000013113022, -0.15029999613761902, -0.37290000915527344, -0.3634999990463257, -0.5809999704360962, -0.2379000037908554, 0.08309999853372574, -0.37720000743865967, -0.4456999897956848], [0.47760000824928284, -0.7049999833106995, 0.2928999960422516, -0.4706000089645386, -0.09759999811649323, -0.12630000710487366, 0.1542000025510788, 0.28940001130104065, 0.37119999527931213, 0.008299999870359898], [0.4787999987602234, 0.5421000123023987, 0.42170000076293945, -0.09880000352859497, -0.31380000710487366, -0.20630000531673431, 0.3720000088214874, 0.23280000686645508, -0.3465999960899353, 0.2777999937534332], [0.44110000133514404, -0.12290000170469284, -0.013399999588727951, 0.19779999554157257, 0.4262000024318695, -0.09759999811649323, 0.6746000051498413, -0.23360000550746918, 0.36079999804496765, 0.13369999825954437], [-0.3041999936103821, -0.014600000344216824, 0.1703999936580658, -0.6693000197410583, 0.21649999916553497, -0.621999979019165, -0.24549999833106995, 0.7016000151634216, 0.12849999964237213, 0.25690001249313354], [-0.07410000264644623, -0.5601999759674072, 0.4726000130176544, 0.2948000133037567, 0.41749998927116394, -0.75, 0.11569999903440475, 0.7943999767303467, 0.31049999594688416, 0.3294000029563904], [-0.1428000032901764, 0.3107999861240387, 0.275299996137619, 0.21449999511241913, -0.544700026512146, 0.1080000028014183, 0.29339998960494995, 0.003700000001117587, 0.4440999925136566, -0.491100013256073], [0.40529999136924744, -0.23810000717639923, -0.388700008392334, 0.3321000039577484, -0.2985999882221222, -0.32749998569488525, 0.1348000019788742, 0.16529999673366547, 0.6385999917984009, 0.6164000034332275], [0.2897000014781952, -0.49480000138282776, 0.792900025844574, 0.13449999690055847, 0.1145000010728836, -0.7716000080108643, -0.16189999878406525, -0.27559998631477356, 0.492000013589859, 0.597100019454956]], [0.09589999914169312, 0.02329999953508377, 0.16300000250339508, 0.17739999294281006, -0.04430000111460686, 0.11890000104904175, 0.05570000037550926, 0.030700000002980232, -0.14560000598430634, -0.041099999099969864], [[0.019500000402331352, 0.18629999458789825, 0.14710000157356262, 0.11940000206232071, -0.3698999881744385], [0.0723000019788742, -0.19789999723434448, -0.3156000077724457, -0.23999999463558197, -0.3416000008583069], [-0.16609999537467957, 0.1662999987602234, 0.26899999380111694, 0.0010000000474974513, -0.24240000545978546], [0.16220000386238098, 0.11460000276565552, 0.16429999470710754, 0.16910000145435333, -0.020400000736117363], [0.06480000168085098, -0.0032999999821186066, -0.2554999887943268, -0.1080000028014183, -0.4480000138282776], [0.289000004529953, -0.30169999599456787, -0.019300000742077827, -0.2727999985218048, -0.43970000743865967], [-0.0019000000320374966, 0.1290999948978424, 0.0681999996304512, -0.20880000293254852, -0.5541999936103821], [-0.2468000054359436, 0.09160000085830688, 0.26750001311302185, 0.023900000378489494, 0.18629999458789825], [0.049800001084804535, 0.22920000553131104, 0.050999999046325684, 0.3598000109195709, -0.15569999814033508], [-0.1039000004529953, 0.49959999322891235, -0.09860000014305115, 0.289000004529953, -0.4871000051498413]], [[-1.0259000062942505, -0.6902999877929688, 0.03519999980926514, -0.17730000615119934, 0.9430999755859375], [0.6507999897003174, 0.3792000114917755, 0.12549999356269836, 1.15910005569458, 0.2718000113964081], [-0.0934000015258789, -0.033900000154972076, 1.1730999946594238, -0.06120000034570694, -0.15850000083446503], [0.8043000102043152, 0.5457000136375427, 0.3336000144481659, -0.14339999854564667, 0.628600001335144], [1.1441999673843384, -1.311900019645691, 0.2362000048160553, -0.07259999960660934, -0.6517000198364258]], [0.22419999539852142, -0.08720000088214874, 0.1662999987602234, -0.20419999957084656, -0.010900000110268593], [[-0.6055999994277954, 0.271699994802475, 0.04670000076293945], [-0.181099995970726, -0.09430000185966492, -0.05490000173449516], [0.20739999413490295, -0.1768999993801117, 0.0013000000035390258], [-0.35989999771118164, -0.1525000035762787, 0.06069999933242798], [-0.06949999928474426, -0.19599999487400055, 0.028599999845027924]], [-0.02889999933540821, -0.10239999741315842, 0.03440000116825104]]</t>
+          <t>[[[0.11879999935626984, 0.16189999878406525, 0.01720000058412552, -0.19349999725818634, 0.3046000003814697, -0.37209999561309814, 0.211899995803833, 0.027300000190734863, -0.026200000196695328, 0.42820000648498535], [-0.15719999372959137, -0.08240000158548355, -0.07109999656677246, 0.34549999237060547, -0.4526999890804291, 0.12770000100135803, -0.23250000178813934, -0.0215000007301569, -0.01360000018030405, -0.06469999998807907]], [[0.27239999175071716, 0.3292999863624573, -0.6396999955177307, 0.17790000140666962, -0.5281999707221985, -0.3093999922275543, -0.06769999861717224, 0.4050000011920929, -0.25619998574256897, -0.2605000138282776], [0.3986999988555908, 0.28189998865127563, 0.26739999651908875, -0.009600000455975533, -0.5489000082015991, 0.4471000134944916, -0.2802000045776367, 0.3797000050544739, 0.03610000014305115, 0.18140000104904175], [-0.08820000290870667, 0.031700000166893005, 0.029899999499320984, -0.03180000185966492, 0.16619999706745148, -0.8492000102996826, -0.5626000165939331, -0.1388999968767166, -0.6207000017166138, -0.048700001090765], [0.0010000000474974513, 0.026599999517202377, 0.0778999999165535, -0.2847000062465668, 0.6572999954223633, 0.8234999775886536, 0.18389999866485596, -0.5551000237464905, -0.5554999709129333, -0.262800008058548], [-0.30570000410079956, 0.2687000036239624, -0.8367000222206116, 0.666100025177002, -0.6729999780654907, -0.34060001373291016, -1.284500002861023, 0.6545000076293945, 0.37139999866485596, 0.1868000030517578], [0.421099990606308, -0.47699999809265137, 0.39649999141693115, 0.10530000180006027, 0.2653999924659729, -0.09520000219345093, 0.12489999830722809, -0.5788000226020813, 0.28630000352859497, -0.9815000295639038], [0.1315000057220459, -0.11649999767541885, -0.1889999955892563, 1.0439000129699707, 0.014399999752640724, -0.598800003528595, -0.37400001287460327, -0.47859999537467957, -0.5698000192642212, 0.5604000091552734], [-0.20499999821186066, -0.4032999873161316, -0.1363999992609024, -0.6725999712944031, -0.7876999974250793, 0.32499998807907104, 0.1362999975681305, -0.08089999854564667, 0.07530000060796738, 0.08479999750852585], [0.4083000123500824, -0.4864000082015991, 0.1039000004529953, -0.3736000061035156, 0.30820000171661377, 0.05979999899864197, -0.06960000097751617, 0.5235999822616577, -0.03959999978542328, 0.029600000008940697], [0.4246000051498413, 0.6266999840736389, -0.5460000038146973, -0.3249000012874603, -0.1606999933719635, -0.004900000058114529, -0.35659998655319214, -0.1647000014781952, 0.48559999465942383, 0.6315000057220459]], [-0.053300000727176666, -0.03880000114440918, -0.20110000669956207, -0.02199999988079071, -0.029999999329447746, -0.04659999907016754, -0.12849999964237213, 0.12770000100135803, -0.07680000364780426, -0.021400000900030136], [[0.06300000101327896, -0.06689999997615814, -0.1599999964237213, 0.009600000455975533, 0.1573999971151352], [-0.18649999797344208, 0.10140000283718109, -0.12049999833106995, -0.26589998602867126, 0.15860000252723694], [-0.15160000324249268, 0.13249999284744263, -0.26030001044273376, 0.3815999925136566, -0.0681999996304512], [-0.04149999842047691, 0.10660000145435333, 0.42260000109672546, -0.19200000166893005, 0.23729999363422394], [-0.5235000252723694, -0.09139999747276306, 0.1550000011920929, 0.48809999227523804, 0.2029000073671341], [0.17990000545978546, -0.01489999983459711, -0.482699990272522, 0.4602000117301941, -0.478300005197525], [-0.030500000342726707, 0.17329999804496765, -0.28519999980926514, 0.5182999968528748, -0.3310999870300293], [0.14429999887943268, -0.15240000188350677, 0.014100000262260437, -0.3052000105381012, -0.08370000123977661], [0.19949999451637268, -0.1776999980211258, -0.19869999587535858, -0.13189999759197235, 0.005799999926239252], [-0.13689999282360077, 0.11469999700784683, -0.13040000200271606, -0.43720000982284546, 0.2410999983549118]], [[-0.1128000020980835, 0.09319999814033508, 0.30709999799728394, 0.7583000063896179, -0.8611999750137329], [-0.5726000070571899, 0.8723999857902527, 0.1597999930381775, -0.17399999499320984, 0.15369999408721924], [0.6934000253677368, 0.5612000226974487, 0.20559999346733093, -0.211899995803833, -0.22210000455379486], [-0.0551999993622303, -0.3653999865055084, 1.2652000188827515, -0.0560000017285347, 0.24320000410079956], [0.05920000001788139, -0.2069000005722046, -0.33730000257492065, -1.045199990272522, -0.7350000143051147]], [-0.0430000014603138, -0.07720000296831131, 0.05640000104904175, -0.33629998564720154, 0.10360000282526016], [[0.2653999924659729, -0.09969999641180038, 0.1842000037431717], [-0.05860000103712082, 0.1356000006198883, -0.2671999931335449], [-0.6308000087738037, -0.15119999647140503, 0.21279999613761902], [0.2648000121116638, -0.08869999647140503, 0.12060000002384186], [-0.460999995470047, 0.148499995470047, -0.18469999730587006]], [-0.07999999821186066, 0.029600000008940697, 0.007799999788403511]]</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>[0.9551146856072423]</t>
+          <t>[0.8326605866193261]</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>[0.010245819379283299]</t>
+          <t>[0.038198003684034566]</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>[0.6833144387541357]</t>
+          <t>[0.8243359313101821]</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>[0.07230034949398942]</t>
+          <t>[0.04010468146967297]</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>[-1.1185744676098928]</t>
+          <t>[-2.5826413736205485]</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>[0.6933664046274082]</t>
+          <t>[1.1725257744180884]</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>[0.8419957048066884]</t>
+          <t>[0.6786508701194667]</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>[0.0362966002473467]</t>
+          <t>[0.07382002427741688]</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>[0.5515217168035712]</t>
+          <t>[0.5784182900992232]</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>[0.1063615702867243]</t>
+          <t>[0.09998275133774848]</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>[-3.225961935605765]</t>
+          <t>[-1.5010056648506627]</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>[1.3892741831180082]</t>
+          <t>[0.8221992187704964]</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>[0.7048695205806416]</t>
+          <t>[-0.23711662423847102]</t>
         </is>
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>[0.03182265909649172]</t>
+          <t>[0.13339300187902323]</t>
         </is>
       </c>
       <c r="S8" t="inlineStr">
         <is>
-          <t>[-0.46233934413797995]</t>
+          <t>[-0.2315826834729846]</t>
         </is>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>[0.12321720998048542]</t>
+          <t>[0.1037735753511271]</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>[-2.3352296339990537]</t>
+          <t>[-1.3182780003227395]</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>[0.31892509880273795]</t>
+          <t>[0.22168099994321205]</t>
         </is>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>[0.552596636353532]</t>
+          <t>[-0.42504834890033893]</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>[0.04687025535589204]</t>
+          <t>[0.149288953625815]</t>
         </is>
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>[-0.5068480544975267]</t>
+          <t>[-0.30562445720239384]</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>[0.1240033629378242]</t>
+          <t>[0.10744402724862388]</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>[-5.145027876915122]</t>
+          <t>[-1.6790910778818482]</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>[0.5653694451505843]</t>
+          <t>[0.24648809843484826]</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>[-2.0723496569131834]</t>
+          <t>[-1.0763687860771807]</t>
         </is>
       </c>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>[0.25745052395699364]</t>
+          <t>[0.17399133939741623]</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>[-2.7784861136164105]</t>
+          <t>[-0.918075881107181]</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>[0.40686010766946384]</t>
+          <t>[0.2065347168256641]</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>[-2.7913403524237883]</t>
+          <t>[-4.0020386048296785]</t>
         </is>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>[0.2822651317197555]</t>
+          <t>[0.3724015663106923]</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>[-2.2969308513581153]</t>
+          <t>[-1.439945241435736]</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>[0.2701798130790083]</t>
+          <t>[0.1999507963543023]</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>[-2.740883326303727]</t>
+          <t>[-0.975600556513756]</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>[0.3970673569901899]</t>
+          <t>[0.20969552456434332]</t>
         </is>
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>[-3.1153968873631976]</t>
+          <t>[-4.92283835925433]</t>
         </is>
       </c>
       <c r="AN8" t="inlineStr">
         <is>
-          <t>[0.31609231594697185]</t>
+          <t>[0.4549169242230219]</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>model_15_5_0</t>
+          <t>model_10_5_2</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>[15, 5]</t>
+          <t>[10, 5]</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>[[[-0.04259999841451645, 0.029600000008940697, -0.07779999822378159, -0.005100000184029341, -0.04410000145435333, -0.04879999905824661, 0.02410000003874302, -0.08290000259876251, -0.048500001430511475, -0.09309999644756317, -0.053599998354911804, 0.0340999998152256, 0.01899999938905239, -0.04569999873638153, 0.06360000371932983], [0.0364999994635582, 0.09669999778270721, -0.010900000110268593, -0.0017000000225380063, 0.053700000047683716, 0.0625, 0.025100000202655792, -0.013000000268220901, -0.017400000244379044, -0.05829999968409538, 0.017000000923871994, -0.08060000091791153, 0.013899999670684338, 0.06469999998807907, -0.007400000002235174]], [[0.23980000615119934, 0.35989999771118164, 0.2939999997615814, 0.46700000762939453, -0.30320000648498535, -0.03220000118017197, 0.1889999955892563, 0.12620000541210175, 0.19519999623298645, -0.11379999667406082, 0.1704999953508377, 0.12540000677108765, 0.5145000219345093, -0.033799998462200165, 0.04639999940991402], [-0.358599990606308, 0.2655999958515167, -0.09880000352859497, 0.09640000015497208, 0.019899999722838402, -0.33480000495910645, -0.04650000110268593, -0.23800000548362732, -0.22429999709129333, 0.29330000281333923, -0.421099990606308, 0.08009999990463257, 0.3337000012397766, 0.26269999146461487, -0.33180001378059387], [0.2393999993801117, 0.2578999996185303, -0.13300000131130219, -0.2045000046491623, 0.10970000177621841, -0.26330000162124634, 0.0568000003695488, 0.15479999780654907, 0.5220999717712402, -0.2896000146865845, -0.251800000667572, -0.22579999268054962, -0.12880000472068787, -0.08749999850988388, -0.46160000562667847], [0.2913999855518341, 0.0722000002861023, -0.05810000002384186, 0.18050000071525574, 0.21060000360012054, 0.07440000027418137, 0.3853999972343445, -0.23770000040531158, -0.0015999999595806003, 0.41839998960494995, 0.3630000054836273, -0.3465999960899353, -0.17260000109672546, 0.3456999957561493, -0.20659999549388885], [0.04010000079870224, -0.2621999979019165, -0.2574000060558319, -0.15399999916553497, 0.462799996137619, 0.10599999874830246, 0.2865999937057495, 0.16249999403953552, -0.21060000360012054, -0.3301999866962433, 0.13650000095367432, 0.08879999816417694, 0.5443999767303467, 0.06750000268220901, -0.15770000219345093], [-0.05820000171661377, 0.3190000057220459, -0.060600001364946365, -0.1543000042438507, -0.016200000420212746, 0.29159998893737793, 0.4496000111103058, 0.22849999368190765, -0.19300000369548798, 0.3230000138282776, -0.1151999980211258, 0.2535000145435333, -0.1331000030040741, -0.517799973487854, -0.15119999647140503], [0.002199999988079071, 0.17829999327659607, 0.13009999692440033, -0.03779999911785126, 0.251800000667572, -0.0640999972820282, 0.3400999903678894, 0.26820001006126404, 0.07970000058412552, -0.06759999692440033, -0.3319999873638153, 0.22310000658035278, -0.21170000731945038, 0.501800000667572, 0.4765999913215637], [0.29089999198913574, -0.2533999979496002, -0.43950000405311584, 0.3221000134944916, -0.2858000099658966, 0.40549999475479126, -0.0729999989271164, 0.20970000326633453, 0.008799999952316284, 0.09759999811649323, -0.4629000127315521, -0.07779999822378159, 0.03790000081062317, 0.15940000116825104, -0.04600000008940697], [-0.009200000204145908, -0.11980000138282776, 0.10429999977350235, -0.060600001364946365, -0.42730000615119934, -0.26409998536109924, 0.42800000309944153, 0.004900000058114529, -0.4602999985218048, -0.3165999948978424, -0.13420000672340393, -0.4424000084400177, -0.09040000289678574, -0.025699999183416367, 0.02630000002682209], [-0.16339999437332153, 0.3224000036716461, -0.06199999898672104, 0.545799970626831, 0.30410000681877136, 0.1615999937057495, -0.1777999997138977, 0.039500001817941666, -0.3140999972820282, -0.4253999888896942, 0.04129999876022339, -0.054099999368190765, -0.33070001006126404, -0.05220000073313713, -0.13950000703334808], [0.32499998807907104, 0.18860000371932983, 0.3628000020980835, -0.2599000036716461, 0.09350000321865082, 0.06679999828338623, -0.412200003862381, 0.45249998569488525, -0.37940001487731934, 0.17990000545978546, -0.016200000420212746, -0.22660000622272491, 0.10840000212192535, 0.14159999787807465, -0.10970000177621841], [-0.09849999845027924, 0.41589999198913574, -0.589900016784668, -0.11249999701976776, -0.03519999980926514, -0.120899997651577, -0.10819999873638153, 0.12970000505447388, -0.004999999888241291, 0.0771000012755394, 0.19939999282360077, -0.3431999981403351, 0.16329999268054962, -0.07410000264644623, 0.46540001034736633], [0.3109999895095825, -0.24639999866485596, -0.17710000276565552, 0.2912999987602234, 0.1306000053882599, -0.6563000082969666, -0.03700000047683716, 0.25459998846054077, -0.16410000622272491, 0.2004999965429306, 0.07029999792575836, 0.2623000144958496, -0.14710000157356262, -0.22020000219345093, 0.03669999912381172], [-0.459199994802475, -0.2702000141143799, 0.2337000072002411, 0.275299996137619, 0.23330000042915344, -0.01080000028014183, 0.08460000157356262, 0.3797999918460846, 0.2574000060558319, 0.23389999568462372, -0.09510000050067902, -0.4487000107765198, 0.1111999973654747, -0.18559999763965607, 0.04100000113248825], [0.36390000581741333, 0.0340999998152256, 0.14970000088214874, 0.05609999969601631, 0.3675999939441681, 0.03680000081658363, -0.011599999852478504, -0.4691999852657318, -0.05719999969005585, 0.014800000004470348, -0.41029998660087585, -0.20229999721050262, 0.16509999334812164, -0.37540000677108765, 0.32120001316070557]], [0.0, 0.0, 0.0, 0.0, 0.0, 0.0, 0.0, 0.0, 0.0, 0.0, 0.0, 0.0, 0.0, 0.0, 0.0], [[-0.04259999841451645, 0.029600000008940697, -0.07779999822378159, -0.005100000184029341, -0.04410000145435333], [-0.04879999905824661, 0.02410000003874302, -0.08290000259876251, -0.048500001430511475, -0.09309999644756317], [-0.053599998354911804, 0.0340999998152256, 0.01899999938905239, -0.04569999873638153, 0.06360000371932983], [0.0364999994635582, 0.09669999778270721, -0.010900000110268593, -0.0017000000225380063, 0.053700000047683716], [0.0625, 0.025100000202655792, -0.013000000268220901, -0.017400000244379044, -0.05829999968409538], [0.017000000923871994, -0.08060000091791153, 0.013899999670684338, 0.06469999998807907, -0.007400000002235174], [-0.00019999999494757503, 0.02930000051856041, 0.08919999748468399, -0.005499999970197678, 0.018200000748038292], [-0.07169999927282333, 0.0017999999690800905, 0.020500000566244125, -0.03720000013709068, 0.05310000106692314], [0.08250000327825546, -0.11060000211000443, -0.053199999034404755, 0.0940999984741211, -0.09839999675750732], [-0.0729999989271164, 0.10050000250339508, -0.1046999990940094, 0.008999999612569809, -0.027699999511241913], [0.05829999968409538, 0.022199999541044235, -0.0681999996304512, -0.01940000057220459, -0.03229999914765358], [0.015799999237060547, 0.05689999833703041, -0.10809999704360962, 0.0026000000070780516, -0.10679999738931656], [0.03830000013113022, -0.10700000077486038, -0.01209999993443489, -0.016100000590085983, -0.03929999843239784], [-0.10050000250339508, -0.024800000712275505, -0.023900000378489494, 0.01140000019222498, -0.04430000111460686], [0.04039999842643738, 0.01549999974668026, -0.025800000876188278, 0.06639999896287918, 0.06449999660253525]], [[0.9355999827384949, 0.04430000111460686, -0.21040000021457672, 0.25110000371932983, 0.12409999966621399], [-0.03889999911189079, 0.06449999660253525, -0.04650000110268593, 0.5159000158309937, -0.8521000146865845], [0.09539999812841415, -0.9254999756813049, -0.1809999942779541, -0.24009999632835388, -0.20990000665187836], [-0.29750001430511475, 0.032600000500679016, -0.8970000147819519, 0.24539999663829803, 0.21359999477863312], [0.1598999947309494, 0.3693000078201294, -0.3409000039100647, -0.7436000108718872, -0.41100001335144043]], [0.0, 0.0, 0.0, 0.0, 0.0], [[-0.04259999841451645, 0.029600000008940697, -0.07779999822378159], [-0.005100000184029341, -0.04410000145435333, -0.04879999905824661], [0.02410000003874302, -0.08290000259876251, -0.048500001430511475], [-0.09309999644756317, -0.053599998354911804, 0.0340999998152256], [0.01899999938905239, -0.04569999873638153, 0.06360000371932983]], [0.0, 0.0, 0.0]]</t>
+          <t>[[[-0.05169999971985817, 0.011599999852478504, 0.05860000103712082, 0.015599999576807022, -0.0568000003695488, 0.0071000000461936, -0.04830000177025795, 0.012000000104308128, 0.012199999764561653, 0.0006000000284984708], [-0.012400000356137753, 0.032099999487400055, 0.012500000186264515, -0.06700000166893005, -9.999999747378752e-05, 0.053700000047683716, -0.13729999959468842, 0.050999999046325684, -0.026900000870227814, 0.04170000180602074]], [[0.2639999985694885, -0.16670000553131104, -0.6772000193595886, 0.051600001752376556, -0.36959999799728394, 0.0071000000461936, 0.38350000977516174, 0.14229999482631683, 0.35370001196861267, 0.11069999635219574], [0.21629999577999115, 0.16439999639987946, 0.5253000259399414, -0.45210000872612, -0.18619999289512634, -0.35089999437332153, 0.2992999851703644, 0.21780000627040863, 0.3885999917984009, -0.0017000000225380063], [-0.32919999957084656, -0.3488999903202057, 0.18790000677108765, -0.3353999853134155, -0.4020000100135803, 0.3700999915599823, 0.30550000071525574, -0.25099998712539673, -0.26510000228881836, 0.31130000948905945], [-0.2815000116825104, 0.5259000062942505, -0.2214999943971634, -0.2280000001192093, -0.43470001220703125, -0.08299999684095383, -0.5091999769210815, 0.011300000362098217, 0.0722000002861023, 0.28760001063346863], [-0.20730000734329224, -0.4885999858379364, 0.17440000176429749, 0.1655000001192093, -0.40799999237060547, 0.035999998450279236, -0.39079999923706055, 0.3521000146865845, 0.21780000627040863, -0.4104999899864197], [0.054099999368190765, -0.06159999966621399, 0.29499998688697815, 0.6603000164031982, -0.23980000615119934, -0.3197000026702881, 0.006200000178068876, -0.2996000051498413, 0.12700000405311584, 0.4523000121116638], [-0.4846999943256378, 0.18780000507831573, -0.03420000150799751, 0.24629999697208405, -0.0203000009059906, -0.2502000033855438, 0.40369999408721924, 0.5692999958992004, -0.3424000144004822, 0.026399999856948853], [0.2906999886035919, -0.43320000171661377, -0.11649999767541885, -0.26249998807907104, 0.06639999896287918, -0.46299999952316284, -0.28119999170303345, 0.22589999437332153, -0.4212999939918518, 0.3449000120162964], [-0.5537999868392944, -0.2540000081062317, -0.20659999549388885, -0.18850000202655792, 0.2768999934196472, -0.47839999198913574, 0.05469999834895134, -0.35409998893737793, 0.33239999413490295, -0.07840000092983246], [0.15449999272823334, 0.12960000336170197, -0.07930000126361847, -0.003599999938160181, -0.4156000018119812, -0.3515999913215637, 0.11379999667406082, -0.3937000036239624, -0.4239000082015991, -0.5559999942779541]], [0.0, 0.0, 0.0, 0.0, 0.0, 0.0, 0.0, 0.0, 0.0, 0.0], [[-0.05169999971985817, 0.011599999852478504, 0.05860000103712082, 0.015599999576807022, -0.0568000003695488], [0.0071000000461936, -0.04830000177025795, 0.012000000104308128, 0.012199999764561653, 0.0006000000284984708], [-0.012400000356137753, 0.032099999487400055, 0.012500000186264515, -0.06700000166893005, -9.999999747378752e-05], [0.053700000047683716, -0.13729999959468842, 0.050999999046325684, -0.026900000870227814, 0.04170000180602074], [-0.0071000000461936, 0.04320000112056732, 0.0003000000142492354, 0.015699999406933784, -0.0632999986410141], [0.04490000009536743, -0.0071000000461936, 0.08869999647140503, 0.030500000342726707, -0.001500000013038516], [0.05389999970793724, -0.05169999971985817, -0.02070000022649765, 0.0020000000949949026, 0.01140000019222498], [0.009800000116229057, 0.01940000057220459, -0.03799999877810478, -0.01640000008046627, 0.01549999974668026], [-0.024399999529123306, 0.09529999643564224, -0.006300000008195639, -0.015699999406933784, -0.07580000162124634], [-0.03310000151395798, -0.020099999383091927, 0.032099999487400055, 0.10859999805688858, 0.09799999743700027]], [[-0.8956999778747559, 0.09929999709129333, -0.24940000474452972, 0.0625, 0.3488999903202057], [0.3716999888420105, 0.4537000060081482, -0.5692999958992004, -0.32420000433921814, 0.4763000011444092], [-0.1354999989271164, -0.12849999964237213, -0.6226999759674072, -0.2799000144004822, -0.7063999772071838], [-0.20069999992847443, 0.3693999946117401, 0.4742000102996826, -0.7597000002861023, -0.14560000598430634], [0.02889999933540821, -0.7946000099182129, -0.03500000014901161, -0.4851999878883362, 0.3621000051498413]], [0.0, 0.0, 0.0, 0.0, 0.0], [[-0.05169999971985817, 0.011599999852478504, 0.05860000103712082], [0.015599999576807022, -0.0568000003695488, 0.0071000000461936], [-0.04830000177025795, 0.012000000104308128, 0.012199999764561653], [0.0006000000284984708, -0.012400000356137753, 0.032099999487400055], [0.012500000186264515, -0.06700000166893005, -9.999999747378752e-05]], [0.0, 0.0, 0.0]]</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>[[[-0.4165000021457672, -0.0010000000474974513, -0.07440000027418137, -0.11909999698400497, 0.020600000396370888, -0.1868000030517578, 0.23989999294281006, -0.1412000060081482, -0.2126999944448471, -0.034699998795986176, -0.4772999882698059, 0.49160000681877136, 0.05820000171661377, -0.33219999074935913, 0.04500000178813934], [0.0908999964594841, 0.2581999897956848, -0.20110000669956207, -0.04610000178217888, 0.09160000085830688, 0.4325999915599823, -0.10329999774694443, -0.010099999606609344, 0.3269999921321869, -0.179299995303154, 0.2370000034570694, -0.29019999504089355, 0.07959999889135361, 0.10050000250339508, -0.0017999999690800905]], [[0.4934999942779541, 0.11649999767541885, 0.8550000190734863, 0.894599974155426, -0.36010000109672546, -0.02239999920129776, 0.5985000133514404, 0.3928999900817871, -0.12680000066757202, 0.2223999947309494, -0.16859999299049377, 0.1096000000834465, 0.39419999718666077, -0.14800000190734863, -0.08449999988079071], [-0.5769000053405762, -0.05299999937415123, 0.06729999929666519, 0.11320000141859055, -0.020899999886751175, -0.5005000233650208, 0.16259999573230743, -0.28110000491142273, -0.3571000099182129, 0.3474000096321106, -0.6366000175476074, 0.20280000567436218, 0.3037000000476837, 0.1703999936580658, -0.38040000200271606], [0.8151000142097473, 0.6230000257492065, -0.19480000436306, -0.061900001019239426, 0.22210000455379486, -0.10830000042915344, -0.017899999395012856, 0.3001999855041504, 0.7475000023841858, -0.2264000028371811, -0.0771000012755394, -0.25619998574256897, -0.16419999301433563, 0.08550000190734863, -0.5163999795913696], [0.5857999920845032, 0.13289999961853027, 0.017100000753998756, 0.23199999332427979, 0.2143000066280365, 0.1509999930858612, 0.4927000105381012, -0.17710000276565552, -0.04010000079870224, 0.4115999937057495, 0.2540999948978424, -0.3910999894142151, -0.2029999941587448, 0.3305000066757202, -0.17069999873638153], [0.0348999984562397, -0.4242999851703644, -0.12349999696016312, -0.050999999046325684, 0.413100004196167, 0.034699998795986176, 0.4413999915122986, 0.1906999945640564, -0.33070001006126404, -0.1728000044822693, -0.01510000042617321, 0.147599995136261, 0.4875999987125397, 0.09709999710321426, -0.2329999953508377], [-0.1703999936580658, 0.24539999663829803, -0.006899999920278788, 0.0007999999797903001, -0.3628999888896942, 0.31049999594688416, 0.7652000188827515, 0.30970001220703125, -0.2939000129699707, 0.4374000132083893, -0.4074000120162964, 0.6171000003814697, -0.5655999779701233, -0.7294999957084656, -0.30709999799728394], [0.4966999888420105, 0.6614999771118164, -0.1973000019788742, -0.20059999823570251, 0.6682999730110168, 0.032600000500679016, 0.11129999905824661, 0.09860000014305115, 0.3635999858379364, -0.4154999852180481, 0.06360000371932983, 0.30090001225471497, 0.03629999980330467, 0.6021000146865845, 0.6604999899864197], [0.5059999823570251, -0.2224999964237213, -0.3984000086784363, 0.3424000144004822, -0.3240000009536743, 0.5027999877929688, 0.10119999945163727, 0.27869999408721924, -0.03680000081658363, 0.1898999959230423, -0.6848000288009644, -0.10729999840259552, -0.04019999876618385, 0.16619999706745148, -0.0731000006198883], [-0.17329999804496765, -0.326200008392334, 0.2540000081062317, 0.25859999656677246, -0.6769999861717224, -0.43529999256134033, 0.7419999837875366, 0.2728999853134155, -0.6870999932289124, -0.07289999723434448, -0.4302000105381012, -0.33730000257492065, -0.2996000051498413, -0.0723000019788742, -0.26109999418258667], [0.03689999878406525, 0.6859999895095825, -0.2069000005722046, 0.44130000472068787, 0.42419999837875366, 0.21160000562667847, -0.3684999942779541, 0.06310000270605087, -0.24379999935626984, -0.4271000027656555, 0.12890000641345978, 0.006200000178068876, -0.27570000290870667, -0.045099999755620956, -0.16009999811649323], [-0.1006999984383583, -0.31949999928474426, 0.8539000153541565, 0.29589998722076416, -0.34529998898506165, -0.2345999926328659, 0.061400000005960464, 0.907800018787384, -0.8378000259399414, 0.6575999855995178, -0.4634000062942505, -0.1639000028371811, -0.11739999800920486, -0.1347000002861023, -0.41760000586509705], [-0.2797999978065491, 0.6800000071525574, -1.0550999641418457, -0.5066999793052673, 0.17810000479221344, -0.14589999616146088, -0.504800021648407, -0.17270000278949738, 0.41679999232292175, -0.21719999611377716, 0.5015000104904175, -0.36579999327659607, 0.3723999857902527, 0.12370000034570694, 0.6596999764442444], [0.4050999879837036, -0.2849999964237213, -0.1754000037908554, 0.36250001192092896, 0.16990000009536743, -0.7312999963760376, -0.07859999686479568, 0.23510000109672546, -0.041099999099969864, 0.18940000236034393, 0.25540000200271606, 0.28130000829696655, -0.08269999921321869, -0.17010000348091125, 0.029999999329447746], [-0.3041999936103821, -0.36800000071525574, 0.5479000210762024, 0.4812999963760376, 0.21729999780654907, 0.025699999183416367, 0.3424000144004822, 0.48969998955726624, -0.004699999932199717, 0.429500013589859, -0.3190000057220459, -0.40689998865127563, 0.07479999959468842, -0.30730000138282776, -0.02239999920129776], [0.1137000024318695, -0.061500001698732376, 0.21899999678134918, 0.09009999781847, 0.37779998779296875, -0.04450000077486038, -0.1891999989748001, -0.4952000081539154, -0.10140000283718109, -0.026100000366568565, -0.20160000026226044, -0.21729999780654907, 0.2290000021457672, -0.38119998574256897, 0.31220000982284546]], [-0.1941000074148178, 0.09969999641180038, -0.2483000010251999, -0.179299995303154, -0.05640000104904175, 0.1615999937057495, -0.13349999487400055, 0.09210000187158585, -0.042500000447034836, 0.09790000319480896, -0.09809999912977219, 0.08730000257492065, -0.350600004196167, -0.07509999722242355, -0.1111999973654747], [[-0.13809999823570251, 0.11999999731779099, -0.6115000247955322, 0.002400000113993883, -0.44040000438690186], [0.08449999988079071, -0.14489999413490295, -0.32339999079704285, -0.19259999692440033, -0.3953999876976013], [-0.16050000488758087, 0.3774999976158142, 0.19429999589920044, 0.011099999770522118, 0.272599995136261], [-0.019300000742077827, 0.30820000171661377, -0.023900000378489494, 0.013100000098347664, -0.15189999341964722], [0.1632000058889389, -0.07859999686479568, -0.21930000185966492, -0.13750000298023224, -0.10209999978542328], [-0.16599999368190765, 0.05810000002384186, 0.1915999948978424, 0.09619999676942825, -0.1729000061750412], [0.0892999991774559, 0.3027999997138977, 0.27639999985694885, 0.03189999982714653, -0.028999999165534973], [-0.1923000067472458, 0.1762000024318695, 0.06430000066757202, 0.03959999978542328, -0.10379999876022339], [-0.05180000141263008, -0.1860000044107437, -0.40869998931884766, 0.30219998955726624, -0.4814000129699707], [-0.22300000488758087, 0.22660000622272491, 0.07039999961853027, 0.11020000278949738, 0.04879999905824661], [-0.08020000159740448, -0.31790000200271606, -0.42320001125335693, -0.009999999776482582, 0.04259999841451645], [0.12300000339746475, -0.14300000667572021, 0.017899999395012856, 0.012799999676644802, -0.09849999845027924], [0.18649999797344208, -0.15029999613761902, -0.08139999955892563, -0.12680000066757202, 0.1274999976158142], [-0.1607999950647354, 0.06560000032186508, -0.1517000049352646, 0.10540000349283218, -0.1973000019788742], [0.17350000143051147, -0.17000000178813934, -0.18520000576972961, -0.017999999225139618, 0.11299999803304672]], [[1.1026999950408936, -0.025100000202655792, -0.42910000681877136, 0.19169999659061432, 0.25], [-0.11649999767541885, 0.1500999927520752, -0.16979999840259552, 0.6212000250816345, -1.1634999513626099], [0.035100001841783524, -1.0898000001907349, -0.42289999127388, -0.017799999564886093, -0.628000020980835], [-0.38510000705718994, 0.03020000085234642, -0.7095000147819519, 0.23499999940395355, 0.04270000010728836], [-0.0471000000834465, -0.017000000923871994, -0.6065999865531921, -0.6279000043869019, -0.44929999113082886]], [-0.3831999897956848, -0.33000001311302185, 0.23909999430179596, 0.1145000010728836, -0.09430000185966492], [[-0.13189999759197235, 0.20409999787807465, 0.049400001764297485], [0.2944999933242798, -0.09350000321865082, -0.048900000751018524], [0.3257000148296356, -0.19040000438690186, 0.11420000344514847], [0.023600000888109207, -0.21140000224113464, -0.09520000219345093], [0.5667999982833862, 0.16449999809265137, -0.14010000228881836]], [0.019999999552965164, 0.01679999940097332, -0.03790000081062317]]</t>
+          <t>[[[-0.40220001339912415, -0.38350000977516174, 0.10050000250339508, 0.07429999858140945, -0.016599999740719795, -0.09489999711513519, 0.1177000030875206, 0.3483999967575073, 0.05169999971985817, -0.1826000064611435], [0.16990000009536743, 0.15889999270439148, -0.0008999999845400453, 0.03500000014901161, -0.23659999668598175, 0.24580000340938568, -0.30090001225471497, -0.34610000252723694, -0.1657000035047531, 0.2702000141143799]], [[0.7027999758720398, 0.0010000000474974513, -0.9412999749183655, -0.03500000014901161, -0.6621000170707703, 0.029100000858306885, 0.63919997215271, -0.07209999859333038, 0.6254000067710876, -0.09570000320672989], [0.5146999955177307, 0.4036000072956085, 0.3312000036239624, -0.4839000105857849, -0.5909000039100647, -0.24740000069141388, 0.3961000144481659, -0.10769999772310257, 0.5357000231742859, -0.05700000002980232], [-0.27480000257492065, -0.322299987077713, 0.18359999358654022, -0.27000001072883606, -0.3384999930858612, 0.4189000129699707, 0.29910001158714294, -0.23029999434947968, -0.27390000224113464, 0.31690001487731934], [-0.3944000005722046, 0.4334000051021576, -0.3118000030517578, -0.314300000667572, -0.21279999613761902, -0.15970000624656677, -0.35830000042915344, 0.19580000638961792, 0.2232999950647354, 0.2232999950647354], [-0.38690000772476196, -0.5871000289916992, 0.31790000200271606, 0.1581999957561493, -0.516700029373169, -0.004100000020116568, -0.47780001163482666, 0.3799999952316284, 0.15240000188350677, -0.40709999203681946], [0.2939999997615814, 0.09279999881982803, 0.18529999256134033, 0.7139999866485596, -0.32359999418258667, -0.2624000012874603, 0.04050000011920929, -0.3953000009059906, 0.17890000343322754, 0.4496999979019165], [-0.739799976348877, 0.010900000110268593, 0.019600000232458115, 0.15410000085830688, 0.1242000013589859, -0.32510000467300415, 0.4327999949455261, 0.6840000152587891, -0.34769999980926514, 0.009700000286102295], [-0.03620000183582306, -0.5827999711036682, -0.026499999687075615, -0.2815999984741211, 0.299699991941452, -0.4812999963760376, -0.3792000114917755, 0.4666999876499176, -0.8317000269889832, 0.699400007724762], [-0.6876000165939331, -0.3587999939918518, -0.29649999737739563, -0.29339998960494995, 0.43050000071525574, -0.5231999754905701, 0.1396999955177307, -0.31380000710487366, 0.33480000495910645, -0.0794999971985817], [0.4036000072956085, 0.31299999356269836, -0.07760000228881836, 0.10050000250339508, -0.6233999729156494, -0.2838999927043915, 0.04899999871850014, -0.5364999771118164, -0.3840999901294708, -0.5776000022888184]], [-0.011800000444054604, 0.01590000092983246, 0.004699999932199717, 0.07509999722242355, 0.05909999832510948, -0.013399999588727951, -0.006099999882280827, -0.036400001496076584, 0.00039999998989515007, 0.04170000180602074], [[-0.26980000734329224, -0.40689998865127563, 0.31439998745918274, 0.11270000040531158, -0.34950000047683716], [-0.06849999725818634, -0.336899995803833, 0.1745000034570694, 0.06260000169277191, -0.18039999902248383], [-0.18870000541210175, -0.05310000106692314, 0.003100000089034438, -0.27239999175071716, 0.21960000693798065], [-0.05889999866485596, -0.09870000183582306, -0.0019000000320374966, -0.13619999587535858, -0.1412000060081482], [0.17870000004768372, 0.1868000030517578, -0.08160000294446945, 0.1347000002861023, 0.1468999981880188], [-0.1152999997138977, -0.14980000257492065, 0.2320999950170517, -0.10660000145435333, -0.125], [0.2223999947309494, 0.08959999680519104, -0.029899999499320984, 0.22089999914169312, -0.26969999074935913], [0.18379999697208405, 0.24779999256134033, -0.2538999915122986, 0.0017999999690800905, 0.2524000108242035], [0.07909999787807465, 0.1647000014781952, -0.026200000196695328, 0.21619999408721924, -0.4374000132083893], [-0.037700001150369644, -0.1362999975681305, 0.22550000250339508, 0.18199999630451202, 0.21080000698566437]], [[-0.8180999755859375, 0.23389999568462372, -0.4023999869823456, 0.019500000402331352, 0.6101999878883362], [0.43160000443458557, 0.5342000126838684, -0.6837000250816345, -0.3549000024795532, 0.6805999875068665], [-0.21860000491142273, -0.2768000066280365, -0.4521999955177307, -0.2402999997138977, -0.974399983882904], [-0.2298000007867813, 0.40450000762939453, 0.3905999958515167, -0.7494000196456909, -0.011599999852478504], [-0.24320000410079956, -0.888700008392334, -0.1444000005722046, -0.6820999979972839, 0.7573000192642212]], [0.03669999912381172, -0.06019999831914902, 0.030300000682473183, -0.09139999747276306, 0.09870000183582306], [[-0.04259999841451645, -0.04560000076889992, 0.16380000114440918], [-0.030500000342726707, -0.15279999375343323, 0.14499999582767487], [-0.2003999948501587, 0.11559999734163284, -0.13689999282360077], [-0.2978000044822693, -0.10740000009536743, 0.19089999794960022], [0.4117000102996826, -0.03880000114440918, 0.08079999685287476]], [0.01730000041425228, 0.011300000362098217, 0.03680000081658363]]</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>[0.9349398483105437]</t>
+          <t>[0.9223278627100218]</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>[0.014851061466698755]</t>
+          <t>[0.017729956896646318]</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>[0.47337192608536693]</t>
+          <t>[0.34452693882876384]</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>[0.12023091184701652]</t>
+          <t>[0.14964664388277152]</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>[-0.7664657600655453]</t>
+          <t>[-3.48540768240066]</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>[0.5781283743761237]</t>
+          <t>[1.4679828561999702]</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>[0.7440094403771687]</t>
+          <t>[0.5882031676535595]</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>[0.05880591409465553]</t>
+          <t>[0.09459758665747398]</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>[0.29405271484528983]</t>
+          <t>[0.693541904617011]</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>[0.1674231832443449]</t>
+          <t>[0.07267991667221267]</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>[-0.7988241516737717]</t>
+          <t>[0.5561014033525649]</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>[0.5913588413643149]</t>
+          <t>[0.14593052886932736]</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>[0.7825490637514224]</t>
+          <t>[-0.1197221805754467]</t>
         </is>
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>[0.023446805724930974]</t>
+          <t>[0.12073486040932287]</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>[-0.5004895941772476]</t>
+          <t>[-0.01971002244033304]</t>
         </is>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>[0.12643176301069706]</t>
+          <t>[0.08592111294680492]</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>[-0.47762711747997355]</t>
+          <t>[-1.5167397271841407]</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>[0.14129533080181284]</t>
+          <t>[0.2406585315658075]</t>
         </is>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>[0.6404307475812416]</t>
+          <t>[-0.29090260884970887]</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>[0.03766869909434006]</t>
+          <t>[0.13523576225095893]</t>
         </is>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>[-0.5357035531196177]</t>
+          <t>[-0.05295776654134032]</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>[0.12637797453698787]</t>
+          <t>[0.08665127428934202]</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>[-1.9332203089981261]</t>
+          <t>[-1.4856649948977192]</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>[0.2698690993465776]</t>
+          <t>[0.22869205268781312]</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>[-1.8727138839348334]</t>
+          <t>[-1.0161508439678526]</t>
         </is>
       </c>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>[0.24072185043567512]</t>
+          <t>[0.1689453184431364]</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>[-2.6372911638317764]</t>
+          <t>[-0.801485027370108]</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>[0.39165650740618846]</t>
+          <t>[0.1939804382393816]</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>[-1.8830695573115204]</t>
+          <t>[-4.153781858521746]</t>
         </is>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>[0.2146444087594248]</t>
+          <t>[0.38369884524361464]</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>[-2.131983615816994]</t>
+          <t>[-1.3437554774475853]</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>[0.2566625707479957]</t>
+          <t>[0.19206815227527138]</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>[-2.530416739402514]</t>
+          <t>[-0.8221342654168382]</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>[0.37472787080306436]</t>
+          <t>[0.1934062021563253]</t>
         </is>
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>[-1.6981796061589844]</t>
+          <t>[-4.57635684045756]</t>
         </is>
       </c>
       <c r="AN9" t="inlineStr">
         <is>
-          <t>[0.20723975448650642]</t>
+          <t>[0.4283046317256471]</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
+          <t>model_10_5_3</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>[10, 5]</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>[[[0.025800000876188278, -0.06419999897480011, -0.005400000140070915, 0.029899999499320984, 0.02449999935925007, -0.04399999976158142, -0.07069999724626541, 0.009800000116229057, -0.008299999870359898, -0.02370000071823597], [0.05350000038743019, 0.012000000104308128, 0.05649999901652336, -0.08569999784231186, -0.01899999938905239, 0.1006999984383583, 0.043699998408555984, 0.05550000071525574, -0.012400000356137753, 0.024900000542402267]], [[0.031300000846385956, 0.3357999920845032, 0.4797999858856201, -0.49399998784065247, -0.06939999759197235, -0.16019999980926514, -0.30970001220703125, -0.0421999990940094, 0.5099999904632568, -0.15440000593662262], [-0.3921999931335449, -0.29789999127388, -0.04450000077486038, -0.15600000321865082, 0.0502999983727932, -0.8209999799728394, 0.2013999968767166, 0.11089999973773956, 0.0038999998942017555, 0.0414000004529953], [0.6065000295639038, -0.007300000172108412, -0.06270000338554382, -0.37470000982284546, -0.09239999949932098, -0.06440000236034393, 0.3431999981403351, 0.5654000043869019, -0.15109999477863312, -0.12219999730587006], [0.3296999931335449, 0.06989999860525131, -0.18690000474452972, 0.11990000307559967, 0.13850000500679016, -0.10679999738931656, 0.2842999994754791, -0.17299999296665192, 0.5573999881744385, 0.6205999851226807], [0.19760000705718994, -0.4584999978542328, 0.628600001335144, -0.13259999454021454, 0.27059999108314514, 0.062300000339746475, -0.05820000171661377, -0.15119999647140503, -0.3084000051021576, 0.3734999895095825], [-0.2513999938964844, -0.016599999740719795, 0.4837999939918518, 0.43950000405311584, -0.3303000032901764, 0.13510000705718994, 0.2671999931335449, 0.49720001220703125, 0.22920000553131104, 0.10350000113248825], [-0.0697999969124794, -0.6065000295639038, -0.21619999408721924, -0.31949999928474426, -0.5698000192642212, 0.25859999656677246, -0.10320000350475311, -0.08699999749660492, 0.2524999976158142, 0.07000000029802322], [0.49000000953674316, -0.303600013256073, 0.09799999743700027, 0.499099999666214, -0.11460000276565552, -0.32420000433921814, -0.19979999959468842, -0.1696999967098236, 0.17599999904632568, -0.43709999322891235], [-0.015200000256299973, 0.10999999940395355, 0.20600000023841858, -0.09950000047683716, -0.2282000035047531, 0.04280000180006027, 0.6984999775886536, -0.5615000128746033, -0.08240000158548355, -0.267300009727478], [-0.14589999616146088, -0.33320000767707825, -0.03139999881386757, -0.07050000131130219, 0.6266000270843506, 0.2980000078678131, 0.2273000031709671, 0.12070000171661377, 0.39649999141693115, -0.3959999978542328]], [0.0, 0.0, 0.0, 0.0, 0.0, 0.0, 0.0, 0.0, 0.0, 0.0], [[0.025800000876188278, -0.06419999897480011, -0.005400000140070915, 0.029899999499320984, 0.02449999935925007], [-0.04399999976158142, -0.07069999724626541, 0.009800000116229057, -0.008299999870359898, -0.02370000071823597], [0.05350000038743019, 0.012000000104308128, 0.05649999901652336, -0.08569999784231186, -0.01899999938905239], [0.1006999984383583, 0.043699998408555984, 0.05550000071525574, -0.012400000356137753, 0.024900000542402267], [-0.02850000001490116, 0.019300000742077827, -0.030400000512599945, -0.006000000052154064, 0.017100000753998756], [0.026000000536441803, 0.024000000208616257, -0.00559999980032444, 0.03750000149011612, 0.023600000888109207], [0.04470000043511391, -0.11550000309944153, -0.05739999935030937, -0.038600001484155655, 0.09920000284910202], [-0.01850000023841858, 0.06840000301599503, 0.01769999973475933, 0.0771000012755394, -9.999999747378752e-05], [-0.06710000336170197, 0.0414000004529953, 0.03220000118017197, 0.006500000134110451, 9.999999747378752e-05], [0.05260000005364418, -0.08470000326633453, -0.0406000018119812, -0.024700000882148743, 0.05829999968409538]], [[-0.21889999508857727, -0.4456000030040741, -0.6011000275611877, -0.5575000047683716, 0.28529998660087585], [0.3546000123023987, -0.5291000008583069, -0.219200000166893, 0.6746000051498413, 0.3018999993801117], [-0.35749998688697815, 0.5516999959945679, -0.6373999714851379, 0.4009999930858612, 0.02810000069439411], [0.0722000002861023, 0.34299999475479126, 0.23589999973773956, -0.09560000151395798, 0.9013000130653381], [-0.8325999975204468, -0.31529998779296875, 0.3587999939918518, 0.2533999979496002, 0.11969999969005585]], [0.0, 0.0, 0.0, 0.0, 0.0], [[0.025800000876188278, -0.06419999897480011, -0.005400000140070915], [0.029899999499320984, 0.02449999935925007, -0.04399999976158142], [-0.07069999724626541, 0.009800000116229057, -0.008299999870359898], [-0.02370000071823597, 0.05350000038743019, 0.012000000104308128], [0.05649999901652336, -0.08569999784231186, -0.01899999938905239]], [0.0, 0.0, 0.0]]</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>[[[-0.03849999979138374, 0.07989999651908875, -0.09319999814033508, 0.025299999862909317, 0.2515999972820282, -0.37790000438690186, -0.5092999935150146, 0.022600000724196434, -0.365200012922287, -0.2653000056743622], [0.1754000037908554, -0.542900025844574, 0.19529999792575836, -0.19660000503063202, -0.09359999746084213, 0.45899999141693115, 0.5128999948501587, 0.000699999975040555, -0.21410000324249268, 0.12319999933242798]], [[0.07750000059604645, 0.2727000117301941, 0.8075000047683716, -0.5540000200271606, -0.20479999482631683, -0.07800000160932541, -0.3197000026702881, -0.014700000174343586, 0.4706000089645386, -0.21930000185966492], [-0.31630000472068787, -0.6384000182151794, -0.6614999771118164, -0.2021999955177307, 0.13500000536441803, -0.8895000219345093, 0.18799999356269836, 0.2522999942302704, 0.10459999740123749, 0.07180000096559525], [0.6394000053405762, -0.1111999973654747, 0.31610000133514404, -0.46059998869895935, -0.2535000145435333, 0.25839999318122864, 0.44440001249313354, 0.5896000266075134, -0.2621999979019165, -0.20579999685287476], [0.2865000069141388, -0.22310000658035278, -0.4943999946117401, 0.219200000166893, 0.4853000044822693, 0.09560000151395798, 0.5199999809265137, -0.20819999277591705, 0.498199999332428, 0.8634999990463257], [0.07819999754428864, -0.7508000135421753, 0.9194999933242798, 0.02239999920129776, 0.5706999897956848, 0.3276999890804291, 0.13050000369548798, -0.37770000100135803, -0.6312999725341797, 0.6686999797821045], [0.14319999516010284, 0.2904999852180481, 0.8011999726295471, 0.2720000147819519, -0.7312999963760376, 0.2037999927997589, 0.23440000414848328, 0.8913000226020813, 0.32089999318122864, -0.3926999866962433], [0.4018000066280365, -0.743399977684021, -0.33889999985694885, -0.7064999938011169, -0.9068999886512756, 0.5889000296592712, 0.05310000106692314, 0.19589999318122864, 0.4627000093460083, -0.27140000462532043], [0.5978999733924866, -0.08250000327825546, 0.3244999945163727, 0.5024999976158142, -0.2879999876022339, -0.8503999710083008, -0.32260000705718994, -0.09109999984502792, 0.2734000086784363, -0.5224999785423279], [0.027300000190734863, 0.36649999022483826, -0.40630000829696655, -0.121799997985363, -0.37459999322891235, -0.3698999881744385, 0.5271000266075134, -0.4499000012874603, 0.3668000102043152, -0.46239998936653137], [0.008700000122189522, -0.1835000067949295, -0.22910000383853912, -0.120899997651577, 0.6880999803543091, 0.8533999919891357, 0.8069999814033508, 0.21240000426769257, 0.227400004863739, -0.423799991607666]], [0.02710000053048134, -0.10159999877214432, 0.08510000258684158, 0.03500000014901161, 0.06880000233650208, 0.04320000112056732, -0.01720000058412552, 0.06350000202655792, -0.12700000405311584, 0.12790000438690186], [[-0.026900000870227814, 0.03519999980926514, 0.052400000393390656, 0.13050000369548798, 0.3012000024318695], [-0.20329999923706055, 0.23819999396800995, 0.3856000006198883, 0.5370000004768372, -0.36239999532699585], [0.03539999946951866, 0.1128000020980835, 0.01860000006854534, -0.030700000002980232, 0.4742000102996826], [0.21619999408721924, 0.2312999963760376, 0.03359999880194664, 0.051100000739097595, -0.2320999950170517], [0.19499999284744263, 0.1889999955892563, -0.3255000114440918, 0.19110000133514404, 0.34950000047683716], [0.3610000014305115, -0.5146999955177307, -0.19699999690055847, -0.6258000135421753, 0.4205000102519989], [0.3093000054359436, -0.8353000283241272, -0.2648000121116638, -0.6680999994277954, 0.302700012922287], [-0.179299995303154, 0.13619999587535858, 0.16189999878406525, 0.07020000368356705, 0.2222999930381775], [-0.22630000114440918, -0.4341999888420105, 0.18479999899864197, -0.48660001158714294, -0.1890999972820282], [0.26109999418258667, -0.24969999492168427, -0.2890999913215637, -0.1606999933719635, 0.2759999930858612]], [[-0.09939999878406525, -0.7384999990463257, -0.5874000191688538, -1.3590999841690063, 0.6015999913215637], [0.3912000060081482, -0.325300008058548, -0.21060000360012054, 0.9241999983787537, 0.3310000002384186], [-0.47909998893737793, 0.6195999979972839, -0.5687999725341797, 0.6901999711990356, -0.257999986410141], [0.055399999022483826, 0.5189999938011169, 0.329800009727478, -0.053599998354911804, 1.0634000301361084], [-1.0823999643325806, -0.22990000247955322, 0.25949999690055847, -0.035999998450279236, 0.7573999762535095]], [0.08720000088214874, -0.10189999639987946, -0.05249999836087227, 0.23749999701976776, 0.14259999990463257], [[0.273499995470047, -0.12479999661445618, 0.12250000238418579], [-0.39010000228881836, 0.09719999879598618, -0.14219999313354492], [-0.3871999979019165, -0.0006000000284984708, -0.1289999932050705], [-0.5206000208854675, 0.09210000187158585, -0.08380000293254852], [0.5752999782562256, 0.1599999964237213, -0.303600013256073]], [-0.3131999969482422, 0.04859999939799309, -0.008100000210106373]]</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>[0.8435007990325277]</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>[0.03572354494577407]</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>[0.6286166583996571]</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>[0.08478803166243537]</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>[-0.4694922066229421]</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>[0.4809349605178769]</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>[0.7690164137168687]</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>[0.053061335356484815]</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>[0.3454418839807315]</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>[0.15523567510901418]</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>[-0.42920956661445153]</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>[0.4698489914055784]</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>[-0.12700420286975778]</t>
+        </is>
+      </c>
+      <c r="R10" t="inlineStr">
+        <is>
+          <t>[0.12152004977187476]</t>
+        </is>
+      </c>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>[-0.10466404262150375]</t>
+        </is>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>[0.09307936755119038]</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>[-0.9388039482835027]</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>[0.18539450311373373]</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>[-0.3199484364844074]</t>
+        </is>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>[0.13827862126562046]</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>[-0.1728550749499842]</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>[0.0965180086329206]</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>[-0.8390352203055682]</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>[0.16919928484335872]</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>[-0.9102871409369147]</t>
+        </is>
+      </c>
+      <c r="AD10" t="inlineStr">
+        <is>
+          <t>[0.16007436661250213]</t>
+        </is>
+      </c>
+      <c r="AE10" t="inlineStr">
+        <is>
+          <t>[-0.7049691941818621]</t>
+        </is>
+      </c>
+      <c r="AF10" t="inlineStr">
+        <is>
+          <t>[0.18358779920300475]</t>
+        </is>
+      </c>
+      <c r="AG10" t="inlineStr">
+        <is>
+          <t>[-3.449578991529342]</t>
+        </is>
+      </c>
+      <c r="AH10" t="inlineStr">
+        <is>
+          <t>[0.33127097105343123]</t>
+        </is>
+      </c>
+      <c r="AI10" t="inlineStr">
+        <is>
+          <t>[-1.3831674151830629]</t>
+        </is>
+      </c>
+      <c r="AJ10" t="inlineStr">
+        <is>
+          <t>[0.1952979166987704]</t>
+        </is>
+      </c>
+      <c r="AK10" t="inlineStr">
+        <is>
+          <t>[-0.7776256958201802]</t>
+        </is>
+      </c>
+      <c r="AL10" t="inlineStr">
+        <is>
+          <t>[0.1886819435918057]</t>
+        </is>
+      </c>
+      <c r="AM10" t="inlineStr">
+        <is>
+          <t>[-3.2851330807952213]</t>
+        </is>
+      </c>
+      <c r="AN10" t="inlineStr">
+        <is>
+          <t>[0.32912928612272746]</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>model_10_5_4</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>[10, 5]</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>[[[0.07999999821186066, 0.005799999926239252, -0.07419999688863754, 0.015799999237060547, 0.03500000014901161, -0.018699999898672104, -0.015799999237060547, -0.043299999088048935, 0.013000000268220901, 0.042500000447034836], [-0.10080000013113022, 0.057500001043081284, -0.02810000069439411, 0.10559999942779541, -0.01590000092983246, -0.015799999237060547, 0.06909999996423721, 0.006899999920278788, 0.009600000455975533, -0.08489999920129776]], [[0.298799991607666, 0.24729999899864197, 0.272599995136261, -0.4778999984264374, 0.4528999924659729, -0.07349999994039536, 0.24130000174045563, 0.2896000146865845, -0.21660000085830688, -0.3837999999523163], [-0.21619999408721924, 0.2833000123500824, 0.07880000025033951, -0.4219000041484833, 0.05559999868273735, 0.4284999966621399, -0.3433000147342682, -0.5918999910354614, -0.18299999833106995, 0.019999999552965164], [-0.19709999859333038, 0.026499999687075615, 0.08720000088214874, 0.24369999766349792, 0.5224999785423279, -0.513700008392334, -0.1826000064611435, -0.15150000154972076, -0.423799991607666, 0.3472000062465668], [-0.0851999968290329, -0.7297999858856201, 0.011300000362098217, -0.11180000007152557, 0.08649999648332596, -0.0966000035405159, -0.3880000114440918, -0.06700000166893005, -0.07840000092983246, -0.5192000269889832], [-0.1193000003695488, 0.26269999146461487, 0.3653999865055084, 0.3310999870300293, 0.33629998564720154, 0.06199999898672104, -0.33889999985694885, 0.054099999368190765, 0.6259999871253967, -0.2168000042438507], [-0.023600000888109207, -0.19619999825954437, 0.5788000226020813, 0.4207000136375427, -0.03680000081658363, 0.32829999923706055, 0.43459999561309814, -0.2434999942779541, -0.2793999910354614, -0.11670000106096268], [0.7480999827384949, 0.009999999776482582, -0.35040000081062317, 0.326200008392334, 0.25699999928474426, 0.21860000491142273, -0.15109999477863312, -0.2583000063896179, -0.06830000132322311, -0.05590000003576279], [-0.1445000022649765, 0.428600013256073, -0.21960000693798065, 0.24809999763965607, -0.28769999742507935, -0.36079999804496765, 0.07249999791383743, -0.2459000051021576, -0.17239999771118164, -0.6141999959945679], [0.06610000133514404, -0.17739999294281006, -0.030799999833106995, -0.23270000517368317, 0.16949999332427979, -0.33219999074935913, 0.45019999146461487, -0.5795000195503235, 0.4790000021457672, 0.04410000145435333], [0.46709999442100525, 0.049800001084804535, 0.5209000110626221, -0.11389999836683273, -0.4681999981403351, -0.37119999527931213, -0.32499998807907104, -0.11420000344514847, -0.0052999998442828655, 0.1386999934911728]], [0.0, 0.0, 0.0, 0.0, 0.0, 0.0, 0.0, 0.0, 0.0, 0.0], [[0.07999999821186066, 0.005799999926239252, -0.07419999688863754, 0.015799999237060547, 0.03500000014901161], [-0.018699999898672104, -0.015799999237060547, -0.043299999088048935, 0.013000000268220901, 0.042500000447034836], [-0.10080000013113022, 0.057500001043081284, -0.02810000069439411, 0.10559999942779541, -0.01590000092983246], [-0.015799999237060547, 0.06909999996423721, 0.006899999920278788, 0.009600000455975533, -0.08489999920129776], [-0.06239999830722809, -0.00860000029206276, -0.0658000037074089, 0.037300001829862595, -0.05820000171661377], [-0.061500001698732376, 0.04960000142455101, 0.0917000025510788, -0.01510000042617321, -0.06719999760389328], [-0.00279999990016222, 0.1103999987244606, 0.04879999905824661, 0.0210999995470047, 0.03229999914765358], [0.1177000030875206, -0.002199999988079071, -0.013399999588727951, 0.054999999701976776, 0.02410000003874302], [-0.03189999982714653, -0.027000000700354576, -0.03830000013113022, 0.014999999664723873, -0.030500000342726707], [0.1274999976158142, 0.06849999725818634, -0.05130000039935112, 0.08389999717473984, -0.042500000447034836]], [[-0.05480000004172325, -0.6467000246047974, 0.6072999835014343, 0.2295999974012375, 0.39660000801086426], [-0.4702000021934509, 0.10540000349283218, -0.28220000863075256, 0.8274000287055969, 0.05999999865889549], [0.30149999260902405, -0.43639999628067017, -0.7146999835968018, -0.04969999939203262, 0.45329999923706055], [-0.44369998574256897, 0.40450000762939453, 0.047600001096725464, -0.33980000019073486, 0.7222999930381775], [-0.6987000107765198, -0.46540001034736633, -0.19629999995231628, -0.38040000200271606, -0.33469998836517334]], [0.0, 0.0, 0.0, 0.0, 0.0], [[0.07999999821186066, 0.005799999926239252, -0.07419999688863754], [0.015799999237060547, 0.03500000014901161, -0.018699999898672104], [-0.015799999237060547, -0.043299999088048935, 0.013000000268220901], [0.042500000447034836, -0.10080000013113022, 0.057500001043081284], [-0.02810000069439411, 0.10559999942779541, -0.01590000092983246]], [0.0, 0.0, 0.0]]</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>[[[0.38670000433921814, -0.1574999988079071, -0.13510000705718994, -0.019600000232458115, 0.01489999983459711, -0.3100999891757965, -0.3619999885559082, -0.07180000096559525, 0.33559998869895935, 0.23469999432563782], [-0.2207999974489212, 0.1387999951839447, 0.07339999824762344, 0.12290000170469284, 0.028200000524520874, -0.21199999749660492, 0.43380001187324524, 0.39419999718666077, -0.3156000077724457, -0.2791000008583069]], [[0.7638999819755554, 0.04129999876022339, 0.5396999716758728, -0.8485000133514404, 0.06679999828338623, -0.3089999854564667, 0.6988000273704529, 0.48840001225471497, 0.5116999745368958, 0.02449999935925007], [-0.15539999306201935, 0.2718999981880188, -0.0012000000569969416, -0.5230000019073486, -0.023900000378489494, 0.23190000653266907, -0.6571999788284302, -0.6304000020027161, 0.1889999955892563, -0.08209999650716782], [-0.11140000075101852, 0.07249999791383743, 0.03830000013113022, 0.43630000948905945, 0.5766000151634216, -0.5511999726295471, -0.012000000104308128, -0.2651999890804291, -0.7001000046730042, 0.5842000246047974], [-0.3589000105857849, -0.9898999929428101, -0.014499999582767487, -0.3050999939441681, 0.13300000131130219, 0.1509000062942505, -0.8938000202178955, -0.11720000207424164, 0.25119999051094055, -0.9973000288009644], [-0.06449999660253525, 0.07249999791383743, 0.26030001044273376, 0.093299999833107, 0.2287999987602234, 0.03849999979138374, -0.41940000653266907, -0.07180000096559525, 0.9642999768257141, -0.1265999972820282], [-0.4198000133037567, -0.6308000087738037, 0.2574000060558319, 0.4932999908924103, -0.10729999840259552, 1.1243000030517578, 0.3278999924659729, -0.5192000269889832, -0.24269999563694, -0.05570000037550926], [0.8450000286102295, 0.37529999017715454, -0.4999000132083893, 0.7968000173568726, 0.6733999848365784, -0.41920000314712524, -0.5615000128746033, -0.2906999886035919, -0.6952000260353088, -0.1615000069141388], [-0.05249999836087227, 0.8733000159263611, -0.08100000023841858, 0.5372999906539917, -0.1103999987244606, -0.8054999709129333, 0.07509999722242355, -0.10490000247955322, -0.4503999948501587, -0.8282999992370605], [0.5805000066757202, -0.13210000097751617, 0.30410000681877136, -0.49790000915527344, -0.26759999990463257, -0.48910000920295715, 0.8648999929428101, -0.24560000002384186, 0.7297000288963318, 0.6395000219345093], [0.7325000166893005, -0.24269999563694, 0.8008999824523926, -0.43290001153945923, -0.5636000037193298, -0.28060001134872437, -0.24040000140666962, -0.11219999939203262, 0.44119998812675476, 0.6137999892234802]], [0.030899999663233757, -0.25, 0.12020000070333481, -0.12489999830722809, -0.02070000022649765, -0.2587999999523163, -0.04100000113248825, 0.0714000016450882, 0.04560000076889992, -0.05559999868273735], [[0.3328000009059906, 0.017999999225139618, -0.30070000886917114, 0.24570000171661377, 0.07479999959468842], [0.22689999639987946, 0.1745000034570694, -0.359499990940094, 0.2522999942302704, 0.4675000011920929], [-0.28999999165534973, 0.1738000065088272, 0.05900000035762787, 0.25029999017715454, -0.33980000019073486], [-0.05260000005364418, 0.04690000042319298, -0.4099000096321106, -0.17270000278949738, 0.5291000008583069], [-0.15839999914169312, 0.07400000095367432, -0.27720001339912415, 0.15729999542236328, 0.0215000007301569], [-0.4081999957561493, -0.05790000036358833, 0.24879999458789825, -0.16689999401569366, -0.23970000445842743], [0.19130000472068787, 0.5437999963760376, 0.3878999948501587, 0.11890000104904175, 0.36309999227523804], [0.23350000381469727, 0.03889999911189079, 0.03959999978542328, -0.007199999876320362, 0.06379999965429306], [-0.05860000103712082, -0.22849999368190765, 0.6492000222206116, -0.492900013923645, -0.7294999957084656], [0.04540000110864639, 0.2070000022649765, -0.25189998745918274, 0.31139999628067017, -0.3154999911785126]], [[0.18610000610351562, -0.7093999981880188, 0.5425000190734863, 0.060100000351667404, 0.2799000144004822], [-0.5306000113487244, 0.15690000355243683, -0.4449999928474426, 1.1374000310897827, 0.13330000638961792], [0.4480000138282776, -0.3407000005245209, -0.8985999822616577, -0.29429998993873596, 0.7019000053405762], [-0.4902999997138977, 0.6251000165939331, 0.0714000016450882, -0.01679999940097332, 0.649399995803833], [-0.5228000283241272, -0.6226000189781189, -0.4560000002384186, -0.39660000801086426, -0.1688999980688095]], [-0.04439999908208847, -0.10329999774694443, 0.1088000014424324, -0.10869999974966049, -0.01080000028014183], [[0.15109999477863312, 0.16110000014305115, -0.2858000099658966], [0.20360000431537628, -0.10130000114440918, 0.10540000349283218], [-0.5346999764442444, 0.023499999195337296, -0.1679999977350235], [0.41350001096725464, -0.21220000088214874, 0.2750999927520752], [0.5547000169754028, 0.17970000207424164, -0.23330000042915344]], [-0.09960000216960907, -0.049300000071525574, 0.09719999879598618]]</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>[0.8481676879185744]</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>[0.03465824995482856]</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>[0.7522568627123379]</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>[0.05656056859734487]</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>[-2.8330047025305176]</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>[1.2544646082286823]</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>[0.6758363895003798]</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>[0.0744665641566646]</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>[0.5395267679455336]</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>[0.10920630467822448]</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>[-0.5313001965921795]</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>[0.5034110250271567]</t>
+        </is>
+      </c>
+      <c r="Q11" t="inlineStr">
+        <is>
+          <t>[-0.15694883699558404]</t>
+        </is>
+      </c>
+      <c r="R11" t="inlineStr">
+        <is>
+          <t>[0.12474885177643259]</t>
+        </is>
+      </c>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>[-0.13418793111033334]</t>
+        </is>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>[0.09556706042627539]</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>[-1.1519019120944436]</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>[0.20577159753333968]</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>[-0.2956177097002115]</t>
+        </is>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>[0.13572971915617896]</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>[-0.2123969294046959]</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>[0.09977203475356836]</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>[-1.125007204611446]</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>[0.195509958339732]</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>[-0.9255698698256707]</t>
+        </is>
+      </c>
+      <c r="AD11" t="inlineStr">
+        <is>
+          <t>[0.1613549977252564]</t>
+        </is>
+      </c>
+      <c r="AE11" t="inlineStr">
+        <is>
+          <t>[-0.7175159694485931]</t>
+        </is>
+      </c>
+      <c r="AF11" t="inlineStr">
+        <is>
+          <t>[0.18493881179969812]</t>
+        </is>
+      </c>
+      <c r="AG11" t="inlineStr">
+        <is>
+          <t>[-3.3444119344140635]</t>
+        </is>
+      </c>
+      <c r="AH11" t="inlineStr">
+        <is>
+          <t>[0.3234412880205572]</t>
+        </is>
+      </c>
+      <c r="AI11" t="inlineStr">
+        <is>
+          <t>[-1.2559124043512622]</t>
+        </is>
+      </c>
+      <c r="AJ11" t="inlineStr">
+        <is>
+          <t>[0.18486951022317202]</t>
+        </is>
+      </c>
+      <c r="AK11" t="inlineStr">
+        <is>
+          <t>[-0.7855309107884734]</t>
+        </is>
+      </c>
+      <c r="AL11" t="inlineStr">
+        <is>
+          <t>[0.18952102424204373]</t>
+        </is>
+      </c>
+      <c r="AM11" t="inlineStr">
+        <is>
+          <t>[-3.717651329221842]</t>
+        </is>
+      </c>
+      <c r="AN11" t="inlineStr">
+        <is>
+          <t>[0.36234982318788866]</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>model_15_5_0</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>[15, 5]</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>[[[0.03319999948143959, 0.0027000000700354576, -0.016699999570846558, -0.0017999999690800905, 0.12229999899864197, -0.014700000174343586, -0.04670000076293945, -0.05999999865889549, -0.0005000000237487257, -0.16120000183582306, -0.057500001043081284, -0.03150000050663948, 0.04129999876022339, 0.027000000700354576, -0.054999999701976776], [0.0066999997943639755, 0.0007999999797903001, 0.059300001710653305, 0.00139999995008111, -0.021199999377131462, 0.06199999898672104, 0.042500000447034836, 0.11349999904632568, 0.019600000232458115, 0.05620000138878822, -0.0026000000070780516, -0.029600000008940697, 0.05090000107884407, -0.008500000461935997, 0.039400000125169754]], [[-0.1598999947309494, -0.05429999902844429, -0.2671000063419342, -0.21379999816417694, -0.3978999853134155, -0.23280000686645508, 0.6503000259399414, 0.05739999935030937, -0.09780000150203705, 0.13580000400543213, 0.23479999601840973, 0.30880001187324524, -0.08579999953508377, -0.12800000607967377, 0.1160999983549118], [0.5145999789237976, -0.534600019454956, 0.11150000244379044, -0.23579999804496765, 0.23240000009536743, -0.1559000015258789, 0.14900000393390656, -0.35850000381469727, -0.10480000078678131, -0.24220000207424164, 0.1882999986410141, 0.07930000126361847, 0.0714000016450882, 0.18719999492168427, -0.029999999329447746], [-0.38589999079704285, -0.16130000352859497, -0.03370000049471855, -0.4230000078678131, 0.04749999940395355, -0.14550000429153442, 0.10270000249147415, 0.025200000032782555, 0.11509999632835388, 0.21610000729560852, -0.0575999990105629, -0.5270000100135803, 0.08190000057220459, 0.4205000102519989, -0.2930000126361847], [0.11299999803304672, -0.19840000569820404, 0.24210000038146973, 0.06870000064373016, -0.5692999958992004, -0.032499998807907104, -0.10670000314712524, 0.20270000398159027, 0.10760000348091125, -0.21690000593662262, -0.18160000443458557, -0.06120000034570694, -0.43650001287460327, 0.40950000286102295, 0.23109999299049377], [-0.12530000507831573, -0.26829999685287476, 0.05660000070929527, 0.22789999842643738, -0.38089999556541443, 0.2888999879360199, -0.02160000056028366, -0.44029998779296875, -0.050599999725818634, 0.10740000009536743, -0.07199999690055847, 0.06390000134706497, -0.10369999706745148, -0.18250000476837158, -0.6057000160217285], [0.41749998927116394, 0.1737000048160553, -0.06369999796152115, -0.1168999969959259, -0.4350999891757965, -0.03200000151991844, -0.305400013923645, -0.13089999556541443, -0.023499999195337296, 0.5063999891281128, 0.23119999468326569, -0.11959999799728394, 0.3630000054836273, 0.0851999968290329, 0.11509999632835388], [-0.328000009059906, -0.23000000417232513, 0.22050000727176666, 0.0649000033736229, -0.15680000185966492, -0.010400000028312206, 0.0706000030040741, -0.3019999861717224, 0.19619999825954437, -0.12229999899864197, -0.27880001068115234, -0.031300000846385956, 0.5443999767303467, -0.14069999754428864, 0.46639999747276306], [-0.25949999690055847, -0.38960000872612, -0.3986999988555908, -0.08980000019073486, -0.027300000190734863, 0.47870001196861267, -0.3138999938964844, 0.19499999284744263, -0.2533999979496002, -0.12939999997615814, 0.32260000705718994, 0.07370000332593918, 0.09989999979734421, 0.10779999941587448, 0.18809999525547028], [-0.07079999893903732, 0.27230000495910645, -0.20649999380111694, 0.00570000009611249, -0.23250000178813934, -0.3758000135421753, -0.15379999577999115, -0.07909999787807465, -0.4860000014305115, -0.5289000272750854, -0.11860000342130661, -0.046799998730421066, 0.257099986076355, 0.09989999979734421, -0.21130000054836273], [-0.04639999940991402, -0.18529999256134033, 0.08550000190734863, 0.4115999937057495, -0.02070000022649765, -0.2628999948501587, 0.03830000013113022, 0.04560000076889992, -0.1363999992609024, -0.03009999915957451, 0.4528999924659729, -0.597100019454956, -0.12250000238418579, -0.3228999972343445, 0.11509999632835388], [-0.13109999895095825, -0.21469999849796295, 0.06030000001192093, 0.5358999967575073, 0.10719999670982361, -0.3384999930858612, -0.04529999941587448, 0.23319999873638153, 0.03220000118017197, 0.24220000207424164, 0.10409999638795853, 0.37540000677108765, 0.2619999945163727, 0.3955000042915344, -0.16380000114440918], [0.34040001034736633, 0.020099999383091927, -0.3553999960422516, 0.28049999475479126, -0.0908999964594841, 0.30219998955726624, 0.4049000144004822, 0.23119999468326569, 0.3154999911785126, -0.23270000517368317, -0.09200000017881393, -0.2572000026702881, 0.31279999017715454, 0.10400000214576721, -0.15690000355243683], [0.03629999980330467, 0.10000000149011612, 0.5034000277519226, 0.031199999153614044, 0.01940000057220459, 0.3643999993801117, 0.3449999988079071, 0.18520000576972961, -0.6104000210762024, 0.13279999792575836, -0.054099999368190765, -0.0812000036239624, 0.16290000081062317, 0.1453000009059906, 0.022299999371170998], [0.18569999933242798, -0.40149998664855957, 0.001500000013038516, -0.19550000131130219, -0.059300001710653305, -0.18469999730587006, -0.1412000060081482, 0.51419997215271, -0.11749999970197678, 0.12399999797344208, -0.40290001034736633, -0.003700000001117587, 0.12770000100135803, -0.45980000495910645, -0.1574999988079071], [-0.0835999995470047, 0.11330000311136246, 0.4564000070095062, -0.2500999867916107, -0.15320000052452087, 0.04910000041127205, -0.07530000060796738, 0.2671999931335449, 0.3271999955177307, -0.32089999318122864, 0.47839999198913574, 0.14020000398159027, 0.22589999437332153, -0.13459999859333038, -0.28060001134872437]], [0.0, 0.0, 0.0, 0.0, 0.0, 0.0, 0.0, 0.0, 0.0, 0.0, 0.0, 0.0, 0.0, 0.0, 0.0], [[0.03319999948143959, 0.0027000000700354576, -0.016699999570846558, -0.0017999999690800905, 0.12229999899864197], [-0.014700000174343586, -0.04670000076293945, -0.05999999865889549, -0.0005000000237487257, -0.16120000183582306], [-0.057500001043081284, -0.03150000050663948, 0.04129999876022339, 0.027000000700354576, -0.054999999701976776], [0.0066999997943639755, 0.0007999999797903001, 0.059300001710653305, 0.00139999995008111, -0.021199999377131462], [0.06199999898672104, 0.042500000447034836, 0.11349999904632568, 0.019600000232458115, 0.05620000138878822], [-0.0026000000070780516, -0.029600000008940697, 0.05090000107884407, -0.008500000461935997, 0.039400000125169754], [0.014999999664723873, 0.01720000058412552, 0.03959999978542328, 0.014700000174343586, 0.010400000028312206], [0.060499999672174454, -0.015599999576807022, -0.013299999758601189, 0.07540000230073929, -0.02539999969303608], [0.0722000002861023, -0.014800000004470348, -0.05270000174641609, 0.08399999886751175, -0.05649999901652336], [0.015200000256299973, -0.012799999676644802, -0.015799999237060547, 0.018699999898672104, 0.006300000008195639], [-0.03020000085234642, 0.09740000218153, 0.07370000332593918, 0.02070000022649765, 0.014800000004470348], [-0.029400000348687172, -0.04830000177025795, 0.004000000189989805, -0.07289999723434448, -0.042399998754262924], [0.0008999999845400453, -0.04740000143647194, -0.061400000005960464, -0.007499999832361937, 0.02319999970495701], [-0.028599999845027924, 0.02879999950528145, 0.014399999752640724, 0.1039000004529953, -0.06560000032186508], [-0.04690000042319298, -0.0005000000237487257, 0.03680000081658363, 0.04340000078082085, -0.10540000349283218]], [[0.21170000731945038, -0.791700005531311, 0.1965000033378601, -0.2752000093460083, 0.4627000093460083], [-0.045899998396635056, -0.4025999903678894, -0.8776999711990356, 0.15850000083446503, -0.20090000331401825], [0.021700000390410423, 0.035100001841783524, -0.07559999823570251, -0.8902999758720398, -0.4472000002861023], [0.6069999933242798, 0.43290001153945923, -0.382099986076355, -0.1923999935388565, 0.5109999775886536], [-0.7642999887466431, 0.14970000088214874, -0.19840000569820404, -0.2637999951839447, 0.53329998254776]], [0.0, 0.0, 0.0, 0.0, 0.0], [[0.03319999948143959, 0.0027000000700354576, -0.016699999570846558], [-0.0017999999690800905, 0.12229999899864197, -0.014700000174343586], [-0.04670000076293945, -0.05999999865889549, -0.0005000000237487257], [-0.16120000183582306, -0.057500001043081284, -0.03150000050663948], [0.04129999876022339, 0.027000000700354576, -0.054999999701976776]], [0.0, 0.0, 0.0]]</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>[[[0.263700008392334, 0.07119999825954437, -0.06729999929666519, -0.13729999959468842, 0.26179999113082886, -0.044599998742341995, -0.17870000004768372, -0.13989999890327454, 0.02199999988079071, -0.4309999942779541, -0.30230000615119934, -0.0142000000923872, 0.02969999983906746, 0.01730000041425228, -0.30169999599456787], [0.12729999423027039, -0.18520000576972961, 0.18529999256134033, -0.034299999475479126, -0.1396999955177307, 0.23829999566078186, 0.13910000026226044, 0.2667999863624573, -0.1551000028848648, 0.2003999948501587, 0.17949999868869781, -0.1850000023841858, 0.2094999998807907, 0.03880000114440918, 0.1177000030875206]], [[0.03700000047683716, -0.010599999688565731, -0.33730000257492065, -0.2849000096321106, -0.33410000801086426, -0.20409999787807465, 0.7609000205993652, 0.012299999594688416, -0.1729000061750412, 0.13279999792575836, 0.09139999747276306, 0.35339999198913574, -0.09749999642372131, -0.21570000052452087, 0.014000000432133675], [0.6301000118255615, -0.4503999948501587, -0.06400000303983688, -0.26840001344680786, 0.2980000078678131, -0.18029999732971191, 0.1151999980211258, -0.5206000208854675, -0.10570000112056732, -0.39649999141693115, 0.09539999812841415, 0.1777999997138977, -0.005100000184029341, -0.000699999975040555, -0.1298999935388565], [-0.531499981880188, -0.2856999933719635, 0.2176000028848648, -0.41499999165534973, -0.12710000574588776, -0.10409999638795853, -0.0714000016450882, 0.2824999988079071, 0.07540000230073929, 0.476500004529953, 0.10859999805688858, -0.699999988079071, 0.24449999630451202, 0.7107999920845032, -0.19750000536441803], [0.008999999612569809, -0.14239999651908875, 0.28450000286102295, 0.12049999833106995, -0.5855000019073486, -0.029999999329447746, -0.3061999976634979, 0.28299999237060547, 0.19140000641345978, -0.19120000302791595, -0.23409999907016754, -0.031099999323487282, -0.4359999895095825, 0.5544999837875366, 0.28209999203681946], [0.14249999821186066, -0.12720000743865967, -0.14149999618530273, 0.12489999830722809, -0.12720000743865967, 0.27469998598098755, 0.09350000321865082, -0.5720000267028809, -0.008100000210106373, 0.0471000000834465, -0.337799996137619, 0.15970000624656677, -0.2143000066280365, -0.28130000829696655, -0.8532999753952026], [0.4535999894142151, 0.08560000360012054, 0.019600000232458115, -0.1468999981880188, -0.5450999736785889, -0.0027000000700354576, -0.24199999868869781, -0.04340000078082085, -0.13249999284744263, 0.5918999910354614, 0.3336000144481659, -0.21490000188350677, 0.4440000057220459, 0.07509999722242355, 0.13660000264644623], [-0.3483999967575073, -0.25929999351501465, 0.31619998812675476, 0.120899997651577, -0.3589000105857849, 0.015300000086426735, 0.04650000110268593, -0.26489999890327454, 0.11060000211000443, -0.1062999963760376, -0.17309999465942383, -0.09520000219345093, 0.6323999762535095, -0.27959999442100525, 0.5859000086784363], [-0.47600001096725464, -0.4758000075817108, -0.11710000038146973, -0.06689999997615814, -0.3246999979019165, 0.5453000068664551, -0.46309998631477356, 0.47130000591278076, -0.3127000033855438, 0.12530000507831573, 0.6207000017166138, -0.12309999763965607, 0.3059999942779541, 0.39730000495910645, 0.39959999918937683], [-0.10939999669790268, 0.35269999504089355, -0.22360000014305115, 0.045099999755620956, -0.2363000065088272, -0.39239999651908875, -0.3425999879837036, -0.07029999792575836, -0.4108999967575073, -0.5385000109672546, -0.24570000171661377, 0.020400000736117363, 0.23360000550746918, 0.13760000467300415, -0.20059999823570251], [-0.37540000677108765, -0.40209999680519104, 0.4059999883174896, 0.6147000193595886, -0.353300005197525, -0.2134000062942505, 0.013399999588727951, 0.2475000023841858, -0.37779998779296875, -0.04989999905228615, 0.7631999850273132, -0.8806999921798706, 0.06430000066757202, -0.2892000079154968, 0.4595000147819519], [-0.4603999853134155, -0.2628999948501587, 0.3546000123023987, 0.6610000133514404, -0.19290000200271606, -0.31150001287460327, -0.22920000553131104, 0.5397999882698059, 0.09589999914169312, 0.38260000944137573, 0.4059000015258789, 0.26570001244544983, 0.38029998540878296, 0.7281000018119812, 0.1535000056028366], [0.42149999737739563, 0.003599999938160181, -0.5224000215530396, 0.31189998984336853, -0.07649999856948853, 0.2531999945640564, 0.44020000100135803, 0.07660000026226044, 0.29589998722076416, -0.423799991607666, -0.147599995136261, -0.18160000443458557, 0.25200000405311584, -0.10700000077486038, -0.2240000069141388], [-0.008100000210106373, 0.020999999716877937, 0.667900025844574, -0.02160000056028366, 0.01600000075995922, 0.40549999475479126, 0.31630000472068787, 0.3384999930858612, -0.6312999725341797, 0.31940001249313354, 0.018699999898672104, -0.16949999332427979, 0.23190000653266907, 0.3425999879837036, 0.043800000101327896], [0.16169999539852142, -0.453000009059906, 0.041600000113248825, -0.21549999713897705, -0.0478999987244606, -0.1754000037908554, -0.1298000067472458, 0.5856999754905701, -0.10930000245571136, 0.2410999983549118, -0.3628999888896942, -0.03889999911189079, 0.14000000059604645, -0.32910001277923584, -0.15029999613761902], [-0.3190000057220459, 0.10400000214576721, 0.6449000239372253, -0.15160000324249268, -0.3610000014305115, 0.04659999907016754, -0.22499999403953552, 0.47540000081062317, 0.3855000138282776, -0.2362000048160553, 0.6905999779701233, 0.07970000058412552, 0.2992999851703644, 0.0966000035405159, -0.06129999831318855]], [0.009999999776482582, 0.010999999940395355, 0.0034000000450760126, -0.02290000021457672, -0.029600000008940697, -0.023800000548362732, 0.010599999688565731, 0.008200000040233135, -0.016899999231100082, 0.024299999698996544, -0.019700000062584877, 0.0142000000923872, 0.004900000058114529, -0.02410000003874302, -0.03150000050663948], [[0.1665000021457672, 0.03150000050663948, -0.0421999990940094, -0.2386000007390976, 0.3538999855518341], [0.14550000429153442, -0.13950000703334808, 0.04749999940395355, -0.10109999775886536, -0.1289999932050705], [-0.38339999318122864, 0.2282000035047531, -0.18569999933242798, 0.3465000092983246, -0.2361000031232834], [0.05739999935030937, -0.030500000342726707, 0.07180000096559525, -0.00279999990016222, -0.16940000653266907], [0.2581000030040741, 0.03970000147819519, 0.07890000194311142, -0.005200000014156103, 0.21809999644756317], [-0.11010000109672546, 0.08049999922513962, 0.006000000052154064, 0.0210999995470047, 0.1729000061750412], [0.018400000408291817, 0.11640000343322754, 0.14319999516010284, -0.2752000093460083, 0.1264999955892563], [-0.21089999377727509, 0.20069999992847443, -0.16519999504089355, 0.3889999985694885, -0.13650000095367432], [0.1826999932527542, -0.1054999977350235, 0.00139999995008111, 0.0364999994635582, -0.14820000529289246], [-0.21860000491142273, 0.21310000121593475, 0.13699999451637268, 0.12330000102519989, 0.051500000059604645], [-0.3481000065803528, 0.35109999775886536, -0.05719999969005585, 0.2768999934196472, -0.29019999504089355], [0.12129999697208405, -0.19280000030994415, 0.16019999980926514, -0.031199999153614044, -0.09629999846220016], [-0.18320000171661377, 0.10119999945163727, -0.21570000052452087, 0.10520000010728836, 0.07989999651908875], [-0.12139999866485596, -0.2029000073671341, -0.04650000110268593, 0.4487999975681305, -0.29789999127388], [-0.218299999833107, 0.1469999998807907, 0.013100000098347664, 0.07329999655485153, -0.28839999437332153]], [[0.36890000104904175, -0.9606000185012817, 0.38609999418258667, -0.45080000162124634, 0.6072999835014343], [-0.21089999377727509, -0.3305000066757202, -0.927299976348877, 0.40529999136924744, -0.37119999527931213], [0.09149999916553497, -0.05950000137090683, -0.08720000088214874, -0.9610000252723694, -0.44429999589920044], [0.4449999928474426, 0.49559998512268066, -0.4268999993801117, 0.02889999933540821, 0.37720000743865967], [-0.7972000241279602, 0.26019999384880066, -0.22460000216960907, -0.3443000018596649, 0.7010999917984009]], [-0.06920000165700912, 0.04340000078082085, -0.04259999841451645, -0.05550000071525574, -0.01489999983459711], [[0.18320000171661377, -0.03700000047683716, 0.10199999809265137], [-0.18569999933242798, 0.14550000429153442, -0.0982000008225441], [0.15860000252723694, -0.0723000019788742, 0.04490000009536743], [-0.4327999949455261, -0.09359999746084213, -0.003800000064074993], [0.1582999974489212, 0.14749999344348907, -0.2540999948978424]], [0.06129999831318855, 0.025299999862909317, -0.006800000090152025]]</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>[0.34347244247659925]</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>[0.1498633319808527]</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>[0.7261060870390661]</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>[0.06253087622134353]</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>[-14.001927528885657]</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>[4.909826259220144]</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>[-1.0561169770109768]</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>[0.4723292862706271]</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>[0.6332258101367023]</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>[0.08698454359141229]</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>[-0.6948505645628313]</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>[0.5571777903987684]</t>
+        </is>
+      </c>
+      <c r="Q12" t="inlineStr">
+        <is>
+          <t>[0.11238187547743295]</t>
+        </is>
+      </c>
+      <c r="R12" t="inlineStr">
+        <is>
+          <t>[0.09570807135922074]</t>
+        </is>
+      </c>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>[-0.07855168925974088]</t>
+        </is>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>[0.09087913178501285]</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>[-0.4366999547598174]</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>[0.13738174737679665]</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>[0.03821751280350383]</t>
+        </is>
+      </c>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>[0.10075693308230364]</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>[-0.1490933243746566]</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>[0.0945625779099384]</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>[-0.7066629189243232]</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>[0.15702045407411724]</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>[-0.6591084410916159]</t>
+        </is>
+      </c>
+      <c r="AD12" t="inlineStr">
+        <is>
+          <t>[0.13902660346597956]</t>
+        </is>
+      </c>
+      <c r="AE12" t="inlineStr">
+        <is>
+          <t>[-0.6890665180198015]</t>
+        </is>
+      </c>
+      <c r="AF12" t="inlineStr">
+        <is>
+          <t>[0.18187542966108367]</t>
+        </is>
+      </c>
+      <c r="AG12" t="inlineStr">
+        <is>
+          <t>[-1.9482461688301815]</t>
+        </is>
+      </c>
+      <c r="AH12" t="inlineStr">
+        <is>
+          <t>[0.21949680477910713]</t>
+        </is>
+      </c>
+      <c r="AI12" t="inlineStr">
+        <is>
+          <t>[-0.9176534379142363]</t>
+        </is>
+      </c>
+      <c r="AJ12" t="inlineStr">
+        <is>
+          <t>[0.15714956447829617]</t>
+        </is>
+      </c>
+      <c r="AK12" t="inlineStr">
+        <is>
+          <t>[-0.7152212468384669]</t>
+        </is>
+      </c>
+      <c r="AL12" t="inlineStr">
+        <is>
+          <t>[0.18205816854718773]</t>
+        </is>
+      </c>
+      <c r="AM12" t="inlineStr">
+        <is>
+          <t>[-2.22579732887325]</t>
+        </is>
+      </c>
+      <c r="AN12" t="inlineStr">
+        <is>
+          <t>[0.247764620610482]</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>model_15_5_1</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>[15, 5]</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>[[[0.01979999989271164, -0.020899999886751175, 0.04690000042319298, 0.05649999901652336, 0.05119999870657921, -0.12319999933242798, 0.017400000244379044, 0.01510000042617321, -0.01759999990463257, 0.030300000682473183, -0.039000000804662704, -0.014499999582767487, 0.03610000014305115, 0.09679999947547913, -0.0632999986410141], [0.003100000089034438, -0.010999999940395355, -0.0006000000284984708, 0.009399999864399433, 0.00570000009611249, -0.03370000049471855, -0.07819999754428864, -0.08079999685287476, 0.07209999859333038, 0.03180000185966492, -0.039500001817941666, 0.04800000041723251, -0.0617000013589859, 0.14569999277591705, -0.03849999979138374]], [[0.04830000177025795, -0.1889999955892563, -0.03790000081062317, 0.3619000017642975, 0.4602000117301941, -0.07890000194311142, 0.11330000311136246, 0.06930000334978104, -0.164900004863739, 0.09849999845027924, 0.5565999746322632, 0.20649999380111694, 0.1436000019311905, -0.3384999930858612, -0.26330000162124634], [0.2623000144958496, -0.20499999821186066, -0.1873999983072281, 0.3188999891281128, 0.35019999742507935, -0.041200000792741776, -0.03849999979138374, -0.032099999487400055, -0.22190000116825104, -0.6129000186920166, -0.4101000130176544, -0.06689999997615814, -0.0729999989271164, 0.1492999941110611, 0.01850000023841858], [-0.0210999995470047, 0.12359999865293503, -0.2937999963760376, -0.14730000495910645, 0.05460000038146973, 0.06369999796152115, -0.11110000312328339, -0.31839999556541443, -0.24959999322891235, 0.2741999924182892, -0.48910000920295715, 0.4174000024795532, 0.07419999688863754, -0.3946000039577484, -0.20800000429153442], [0.17829999327659607, 0.2883000075817108, 0.11180000007152557, 0.1234000027179718, -0.014999999664723873, 0.2687000036239624, 0.5936999917030334, -0.5853000283241272, -0.16529999673366547, 0.017799999564886093, 0.10679999738931656, -0.16660000383853912, -0.13099999725818634, 0.0763000026345253, 0.009700000286102295], [0.5200999975204468, -0.2101999968290329, 0.014999999664723873, 0.21379999816417694, -0.25839999318122864, 0.2962999939918518, -0.48669999837875366, -0.1371999979019165, -0.008299999870359898, 0.1826000064611435, 0.14579999446868896, -0.07840000092983246, -0.34220001101493835, -0.18729999661445618, 0.1265999972820282], [-0.49399998784065247, 0.0210999995470047, -0.020800000056624413, -0.33469998836517334, 0.2547000050544739, 0.29840001463890076, -0.2872999906539917, -0.18850000202655792, -0.1850000023841858, -0.3131999969482422, 0.2345000058412552, -0.21130000054836273, -0.3034999966621399, -0.210099995136261, 0.05310000106692314], [-0.1062999963760376, -0.24060000479221344, 0.5187000036239624, 0.09529999643564224, -0.3285999894142151, 0.0860000029206276, 0.09040000289678574, -0.08749999850988388, -0.02410000003874302, -0.351500004529953, -0.10809999704360962, 0.12189999967813492, 0.3540000021457672, -0.4659999907016754, 0.16820000112056732], [0.31200000643730164, 0.17990000545978546, -0.22759999334812164, -0.3555999994277954, -0.3034999966621399, -0.24040000140666962, -0.013399999588727951, 0.09510000050067902, -0.5504000186920166, -0.24969999492168427, 0.3296999931335449, 0.08799999952316284, 0.17980000376701355, 0.00860000029206276, 0.1371999979019165], [-0.0551999993622303, -0.16169999539852142, -0.03819999843835831, -0.02500000037252903, 0.09269999712705612, -0.20900000631809235, -0.25780001282691956, -0.6050000190734863, 0.24779999256134033, -0.06129999831318855, 0.21379999816417694, 0.3596000075340271, 0.2287999987602234, 0.3529999852180481, 0.25839999318122864], [0.14499999582767487, -0.1542000025510788, 0.13609999418258667, -0.2475000023841858, -0.1071000024676323, -0.558899998664856, 0.06889999657869339, -0.22869999706745148, 0.22030000388622284, -0.16760000586509705, 0.012400000356137753, -0.09430000185966492, -0.37929999828338623, -0.1964000016450882, -0.4758000075817108], [0.17640000581741333, -0.29899999499320984, 0.11349999904632568, -0.303600013256073, 0.08569999784231186, 0.26759999990463257, -0.1307000070810318, -0.10989999771118164, -0.09600000083446503, 0.10080000013113022, -0.027799999341368675, -0.3675000071525574, 0.5033000111579895, 0.21889999508857727, -0.45820000767707825], [0.41589999198913574, 0.4368000030517578, 0.11299999803304672, -0.2727000117301941, 0.30169999599456787, 0.25450000166893005, -0.04899999871850014, 0.12929999828338623, 0.4652999937534332, -0.2694000005722046, 0.0494999997317791, 0.2167000025510788, 0.10209999978542328, -0.15700000524520874, -0.02459999918937683], [-0.09860000014305115, -0.08129999786615372, 0.1940000057220459, 0.01720000058412552, -0.22010000050067902, 0.3231000006198883, 0.019700000062584877, 0.13539999723434448, -0.14390000700950623, -0.1670999974012375, 0.07479999959468842, 0.569599986076355, -0.2678999900817871, 0.38909998536109924, -0.41519999504089355], [0.16990000009536743, -0.5390999913215637, 0.046300001442432404, -0.4562999904155731, 0.2467000037431717, 0.08990000188350677, 0.37209999561309814, 0.11640000343322754, -0.03709999844431877, 0.1785999983549118, -0.06499999761581421, 0.17970000207424164, -0.21060000360012054, -0.007400000002235174, 0.3675000071525574], [-0.08169999718666077, -0.24819999933242798, -0.6765000224113464, 0.012299999594688416, -0.3206000030040741, 0.2624000012874603, 0.25200000405311584, -0.011599999852478504, 0.3720000088214874, -0.21780000627040863, 0.1257999986410141, -0.02239999920129776, 0.09200000017881393, -0.13420000672340393, -0.09969999641180038]], [0.0, 0.0, 0.0, 0.0, 0.0, 0.0, 0.0, 0.0, 0.0, 0.0, 0.0, 0.0, 0.0, 0.0, 0.0], [[0.01979999989271164, -0.020899999886751175, 0.04690000042319298, 0.05649999901652336, 0.05119999870657921], [-0.12319999933242798, 0.017400000244379044, 0.01510000042617321, -0.01759999990463257, 0.030300000682473183], [-0.039000000804662704, -0.014499999582767487, 0.03610000014305115, 0.09679999947547913, -0.0632999986410141], [0.003100000089034438, -0.010999999940395355, -0.0006000000284984708, 0.009399999864399433, 0.00570000009611249], [-0.03370000049471855, -0.07819999754428864, -0.08079999685287476, 0.07209999859333038, 0.03180000185966492], [-0.039500001817941666, 0.04800000041723251, -0.0617000013589859, 0.14569999277591705, -0.03849999979138374], [-0.019700000062584877, 0.003700000001117587, -0.012799999676644802, 0.02979999966919422, -0.010999999940395355], [-0.023900000378489494, -0.02449999935925007, 0.014000000432133675, -0.05990000069141388, -0.028300000354647636], [0.032099999487400055, -0.0835999995470047, -0.06310000270605087, -0.0348999984562397, 0.05040000006556511], [-0.029600000008940697, 0.026799999177455902, -0.005100000184029341, -0.12250000238418579, 0.03200000151991844], [-0.028999999165534973, 0.0731000006198883, 0.017999999225139618, -0.03880000114440918, 0.07970000058412552], [-0.007000000216066837, 0.031300000846385956, -0.03139999881386757, 0.050599999725818634, 0.06360000371932983], [-0.04699999839067459, 0.028300000354647636, 0.056699998676776886, -0.07150000333786011, -0.09989999979734421], [0.006500000134110451, -0.049400001764297485, 0.02630000002682209, -0.010700000450015068, -0.07890000194311142], [0.10100000351667404, -0.03750000149011612, -0.08540000021457672, 0.07190000265836716, 0.05290000140666962]], [[0.325300008058548, 0.4648999869823456, 0.7782999873161316, 0.26820001006126404, -0.020800000056624413], [0.03759999945759773, -0.1890999972820282, 0.4059000015258789, -0.8924000263214111, 0.0414000004529953], [0.9294000267982483, -0.06620000302791595, -0.3160000145435333, -0.08320000022649765, 0.15850000083446503], [-0.13940000534057617, 0.8066999912261963, -0.3100000023841858, -0.3003000020980835, 0.37880000472068787], [-0.09809999912977219, -0.30480000376701355, 0.18320000171661377, 0.18610000610351562, 0.9106000065803528]], [0.0, 0.0, 0.0, 0.0, 0.0], [[0.01979999989271164, -0.020899999886751175, 0.04690000042319298], [0.05649999901652336, 0.05119999870657921, -0.12319999933242798], [0.017400000244379044, 0.01510000042617321, -0.01759999990463257], [0.030300000682473183, -0.039000000804662704, -0.014499999582767487], [0.03610000014305115, 0.09679999947547913, -0.0632999986410141]], [0.0, 0.0, 0.0]]</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>[[[0.299699991941452, -0.1542000025510788, 0.3264000117778778, 0.26269999146461487, 0.08429999649524689, -0.325300008058548, 0.35910001397132874, 0.033900000154972076, -0.1062999963760376, 0.028699999675154686, -0.2554999887943268, -0.06539999693632126, 0.0746999979019165, 0.18250000476837158, -0.16339999437332153], [-0.03519999980926514, 0.382099986076355, -0.08630000054836273, 0.020400000736117363, 0.08009999990463257, 0.1542000025510788, -0.21699999272823334, -0.22450000047683716, 0.29249998927116394, -0.2822999954223633, -0.061900001019239426, 0.350600004196167, -0.11720000207424164, 0.12110000103712082, 0.10499999672174454]], [[0.272599995136261, -0.3896999955177307, 0.0019000000320374966, 0.4074999988079071, 0.28209999203681946, -0.0494999997317791, 0.18389999866485596, 0.15129999816417694, -0.35600000619888306, 0.15330000221729279, 0.6489999890327454, 0.2590000033378601, 0.13779999315738678, -0.5450000166893005, -0.3790999948978424], [-0.31360000371932983, -0.027699999511241913, -0.5702999830245972, 0.10859999805688858, 0.30790001153945923, 0.1665000021457672, -0.34599998593330383, 0.18719999492168427, -0.03700000047683716, -0.7031999826431274, -0.05570000037550926, 0.2215999960899353, 0.011800000444054604, 0.3391000032424927, 0.28209999203681946], [0.2070000022649765, -0.06759999692440033, -0.0674000009894371, 0.18559999763965607, -0.13189999759197235, 0.05530000105500221, 0.16769999265670776, -0.4577000141143799, -0.4496999979019165, 0.42969998717308044, -0.42419999837875366, 0.6129999756813049, 0.16410000622272491, -0.696399986743927, -0.257999986410141], [0.4325999915599823, 0.027000000700354576, 0.2752000093460083, 0.3765000104904175, -0.1597999930381775, 0.3422999978065491, 0.7662000060081482, -0.769599974155426, -0.28040000796318054, -0.02329999953508377, 0.12540000677108765, -0.0272000003606081, -0.09709999710321426, -0.09920000284910202, -0.03200000151991844], [0.6049000024795532, -0.4968999922275543, -0.07150000333786011, 0.19939999282360077, -0.2750000059604645, 0.5049999952316284, -0.5030999779701233, -0.14730000495910645, -0.01860000006854534, 0.19629999995231628, 0.4675999879837036, 0.10999999940395355, -0.4903999865055084, -0.26429998874664307, 0.24899999797344208], [-0.5024999976158142, 0.09520000219345093, -0.2354000061750412, -0.6037999987602234, 0.46209999918937683, 0.43630000948905945, -0.6643000245094299, -0.4620000123977661, 0.1598999947309494, -0.7013999819755554, -0.015599999576807022, -0.461899995803833, -0.3919000029563904, 0.1590999960899353, -0.0031999999191612005], [0.2515000104904175, -0.6018000245094299, 0.7409999966621399, 0.41990000009536743, -0.7253000140190125, -0.11620000004768372, 0.4781000018119812, -0.2087000012397766, -0.36320000886917114, -0.08789999783039093, -0.0835999995470047, 0.1137000024318695, 0.5612999796867371, -0.9276000261306763, -0.1054999977350235], [0.22750000655651093, 0.258899986743927, -0.1492999941110611, -0.42719998955726624, -0.3075000047683716, -0.6018999814987183, 0.07259999960660934, 0.6166999936103821, -0.6973999738693237, -0.09539999812841415, 0.16539999842643738, -0.12189999967813492, 0.2538999915122986, -0.14509999752044678, 0.003000000026077032], [-0.07039999961853027, -0.36890000104904175, -0.31150001287460327, -0.07680000364780426, 0.23829999566078186, 0.26190000772476196, -0.4399000108242035, -0.9941999912261963, 0.5080999732017517, -0.17970000207424164, 0.5641000270843506, 0.7634999752044678, -0.023900000378489494, 0.5611000061035156, 0.5928999781608582], [0.27559998631477356, 0.11349999904632568, 0.40959998965263367, -0.24169999361038208, -0.12950000166893005, -0.7522000074386597, 0.2126999944448471, 0.08089999854564667, -0.08389999717473984, -0.035999998450279236, -0.18289999663829803, -0.484499990940094, -0.3402999937534332, -0.527999997138977, -0.6541000008583069], [0.11339999735355377, -0.20759999752044678, 0.03550000116229057, -0.578499972820282, 0.21250000596046448, 0.15489999949932098, -0.2612000107765198, 0.15860000252723694, 0.01720000058412552, 0.04879999905824661, -0.25380000472068787, -0.7450000047683716, 0.4796000123023987, 0.33059999346733093, -0.6013000011444092], [0.4977000057697296, 0.6884999871253967, 0.053300000727176666, -0.24549999833106995, 0.2102999985218048, 0.5396999716758728, -0.12269999831914902, -0.20509999990463257, 0.536899983882904, -0.4535999894142151, 0.1340000033378601, 0.2874000072479248, 0.1281999945640564, -0.04259999841451645, -0.08380000293254852], [-0.13940000534057617, -0.021400000900030136, 0.3741999864578247, 0.15690000355243683, -0.23180000483989716, 0.019500000402331352, 0.16529999673366547, 0.2029999941587448, -0.24490000307559967, -0.07760000228881836, -0.07829999923706055, 0.4627000093460083, -0.14090000092983246, 0.2838999927043915, -0.47620001435279846], [0.21570000052452087, -0.8118000030517578, -0.06599999964237213, -0.3675999939441681, 0.2231999933719635, 0.4020000100135803, 0.3393999934196472, 0.03319999948143959, -0.0013000000035390258, 0.09679999947547913, 0.2644999921321869, 0.6079999804496765, -0.39959999918937683, -0.05290000140666962, 0.626800000667572], [0.035999998450279236, -0.16290000081062317, -0.832099974155426, -0.2500999867916107, -0.16439999639987946, 0.6952000260353088, 0.0017999999690800905, -0.8745999932289124, 0.921500027179718, -0.7268999814987183, 0.11420000344514847, -0.2962000072002411, 0.004900000058114529, 0.20100000500679016, -0.33160001039505005]], [-0.08330000191926956, -0.04399999976158142, 0.09690000116825104, 0.1728000044822693, -0.045899998396635056, 0.026200000196695328, 0.08659999817609787, -0.1843000054359436, 0.07890000194311142, -0.10189999639987946, -0.227400004863739, 0.120899997651577, 0.05990000069141388, 0.051100000739097595, 0.0746999979019165], [[0.06629999727010727, 0.03319999948143959, 0.027000000700354576, 0.25929999351501465, 0.1777999997138977], [-0.2558000087738037, 0.459199994802475, 0.7483000159263611, -0.7656999826431274, -0.36320000886917114], [0.31869998574256897, 0.23720000684261322, 0.2768999934196472, 0.3767000138759613, -0.05000000074505806], [0.17749999463558197, 0.2815000116825104, 0.09030000120401382, 0.1331000030040741, 0.09910000115633011], [-0.11020000278949738, -0.04309999942779541, -0.08669999986886978, 0.08980000019073486, 0.15440000593662262], [-0.5674999952316284, -0.019700000062584877, -0.2515000104904175, -0.02459999918937683, -0.05620000138878822], [0.365200012922287, 0.2736999988555908, 0.10220000147819519, 0.36820000410079956, -0.03849999979138374], [0.24729999899864197, -0.17919999361038208, -0.04690000042319298, -0.2703999876976013, -0.09309999644756317], [-0.3749000132083893, -0.027499999850988388, -0.06480000168085098, -0.061799999326467514, 0.19300000369548798], [0.2167000025510788, 0.03370000049471855, -0.302700012922287, 0.061000000685453415, 0.13169999420642853], [-0.4507000148296356, -0.03579999879002571, -0.22759999334812164, 0.06430000066757202, 0.1695999950170517], [0.017100000753998756, 0.4936000108718872, -0.051899999380111694, -0.01590000092983246, 0.062199998646974564], [0.13570000231266022, -0.02539999969303608, 0.2126999944448471, -0.14219999313354492, -0.21150000393390656], [-0.11550000309944153, -0.15219999849796295, -0.04769999906420708, -0.04019999876618385, 0.07620000094175339], [-0.04399999976158142, 0.05490000173449516, -0.5217999815940857, -0.01889999955892563, 0.16290000081062317]], [[0.4844000041484833, 0.9804999828338623, 1.1109999418258667, 0.3086000084877014, -0.10540000349283218], [-0.05609999969601631, -0.27619999647140503, 0.6201000213623047, -1.0532000064849854, -0.2872999906539917], [1.4319000244140625, 0.29319998621940613, -0.24390000104904175, -0.5496000051498413, -0.10490000247955322], [-0.2854999899864197, 0.8517000079154968, -0.15469999611377716, -0.24740000069141388, 0.3596000075340271], [-0.3003000020980835, -0.362199991941452, 0.1720999926328659, 0.34610000252723694, 0.9653000235557556]], [0.09260000288486481, 0.13099999725818634, -0.005799999926239252, 0.4180999994277954, -0.15800000727176666], [[0.30250000953674316, -0.014999999664723873, 0.26010000705718994], [0.17739999294281006, 0.05640000104904175, -0.3458000123500824], [0.4115000069141388, 0.10920000076293945, -0.03180000185966492], [-0.6539000272750854, 0.10760000348091125, 0.04190000146627426], [-0.16019999980926514, 0.25380000472068787, -0.19290000200271606]], [-0.10589999705553055, 0.06419999897480011, 0.05719999969005585]]</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>[0.8190699952417819]</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>[0.041300282155195954]</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>[0.8222654411119196]</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>[0.04057738115439918]</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>[-2.2266715946259197]</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>[1.0560240938819443]</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>[0.7603538772990222]</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>[0.055051285193620424]</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>[0.5553557619945908]</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>[0.10545228419117327]</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>[-1.1286979097880407]</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>[0.6998039960579708]</t>
+        </is>
+      </c>
+      <c r="Q13" t="inlineStr">
+        <is>
+          <t>[-0.09364577381226935]</t>
+        </is>
+      </c>
+      <c r="R13" t="inlineStr">
+        <is>
+          <t>[0.11792315284011946]</t>
+        </is>
+      </c>
+      <c r="S13" t="inlineStr">
+        <is>
+          <t>[-0.08634918036797168]</t>
+        </is>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>[0.09153615103506264]</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>[-1.062424340942485]</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>[0.197215472063187]</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>[-0.26605110755778694]</t>
+        </is>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>[0.13263230347935687]</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>[-0.13502423948806652]</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>[0.09340478775705092]</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>[-1.2044776294446486]</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>[0.20282158505547354]</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>[-0.8414332472352921]</t>
+        </is>
+      </c>
+      <c r="AD13" t="inlineStr">
+        <is>
+          <t>[0.15430468770565148]</t>
+        </is>
+      </c>
+      <c r="AE13" t="inlineStr">
+        <is>
+          <t>[-0.8331641672527479]</t>
+        </is>
+      </c>
+      <c r="AF13" t="inlineStr">
+        <is>
+          <t>[0.1973915870105996]</t>
+        </is>
+      </c>
+      <c r="AG13" t="inlineStr">
+        <is>
+          <t>[-4.073288433514504]</t>
+        </is>
+      </c>
+      <c r="AH13" t="inlineStr">
+        <is>
+          <t>[0.37770611309607266]</t>
+        </is>
+      </c>
+      <c r="AI13" t="inlineStr">
+        <is>
+          <t>[-1.4536927536165178]</t>
+        </is>
+      </c>
+      <c r="AJ13" t="inlineStr">
+        <is>
+          <t>[0.20107738967359348]</t>
+        </is>
+      </c>
+      <c r="AK13" t="inlineStr">
+        <is>
+          <t>[-0.9083356024095368]</t>
+        </is>
+      </c>
+      <c r="AL13" t="inlineStr">
+        <is>
+          <t>[0.2025558425121316]</t>
+        </is>
+      </c>
+      <c r="AM13" t="inlineStr">
+        <is>
+          <t>[-2.9599024397200933]</t>
+        </is>
+      </c>
+      <c r="AN13" t="inlineStr">
+        <is>
+          <t>[0.30414921509482157]</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>model_15_5_2</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>[15, 5]</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>[[[-0.05169999971985817, 0.011599999852478504, 0.05860000103712082, 0.015599999576807022, -0.0568000003695488, 0.0071000000461936, -0.04830000177025795, 0.012000000104308128, 0.012199999764561653, 0.0006000000284984708, -0.012400000356137753, 0.032099999487400055, 0.012500000186264515, -0.06700000166893005, -9.999999747378752e-05], [0.053700000047683716, -0.13729999959468842, 0.050999999046325684, -0.026900000870227814, 0.04170000180602074, -0.0071000000461936, 0.04320000112056732, 0.0003000000142492354, 0.015699999406933784, -0.0632999986410141, 0.04490000009536743, -0.0071000000461936, 0.08869999647140503, 0.030500000342726707, -0.001500000013038516]], [[0.25699999928474426, -0.18709999322891235, 0.3253999948501587, 0.5472999811172485, 0.17839999496936798, 0.036400001496076584, 0.4124000072479248, -0.032499998807907104, 0.0674000009894371, -0.24500000476837158, -0.12080000340938568, -0.06710000336170197, 0.2596000134944916, 0.27230000495910645, -0.2531999945640564], [-0.006500000134110451, 0.6204000115394592, 0.15790000557899475, -0.01850000023841858, -0.39169999957084656, 0.0003000000142492354, -0.065700002014637, 0.2809999883174896, 0.09759999811649323, 0.17470000684261322, -0.19169999659061432, -0.15070000290870667, 0.16380000114440918, 0.47279998660087585, -0.05640000104904175], [0.4627000093460083, -0.33959999680519104, 0.012000000104308128, -0.11890000104904175, -0.20649999380111694, -0.5045999884605408, -0.13619999587535858, 0.0843999981880188, -0.07829999923706055, 0.413100004196167, -0.08489999920129776, -0.17749999463558197, 0.07530000060796738, -0.08869999647140503, -0.3228999972343445], [-0.3528999984264374, -0.36410000920295715, -0.3052999973297119, -0.12099999934434891, -0.2685999870300293, 0.07829999923706055, -0.010599999688565731, 0.35089999437332153, 0.33980000019073486, -0.25769999623298645, 0.08839999884366989, 0.10369999706745148, 0.11190000176429749, 0.13940000534057617, -0.44850000739097595], [0.311599999666214, -0.05950000137090683, -0.10700000077486038, -0.19930000603199005, 0.16859999299049377, 0.47850000858306885, -0.02630000002682209, 0.3571999967098236, -0.3303000032901764, 0.13379999995231628, 0.24120000004768372, 0.10819999873638153, 0.5103999972343445, 0.01640000008046627, 0.07029999792575836], [0.2680000066757202, -0.00839999970048666, -0.3456999957561493, -0.020500000566244125, 0.35249999165534973, 0.20350000262260437, -0.02459999918937683, 0.19789999723434448, 0.4422999918460846, 0.12250000238418579, -0.5934000015258789, -0.04670000076293945, -0.16140000522136688, -0.02319999970495701, 0.10599999874830246], [0.0038999998942017555, 0.06120000034570694, 0.26350000500679016, -0.6327999830245972, 0.22419999539852142, 0.17149999737739563, 0.050599999725818634, -0.2612999975681305, -0.17589999735355377, -0.20260000228881836, -0.2515000104904175, -0.1151999980211258, -0.09449999779462814, 0.10570000112056732, -0.4551999866962433], [-0.10199999809265137, -0.20270000398159027, -0.027400000020861626, 0.015599999576807022, -0.4438000023365021, 0.4708999991416931, 0.3255999982357025, -0.42010000348091125, 0.05420000106096268, 0.46219998598098755, -0.155799999833107, -0.002300000051036477, 0.043699998408555984, -0.058800000697374344, 0.007799999788403511], [-0.23160000145435333, -0.03139999881386757, -0.08780000358819962, 0.1396999955177307, 0.33709999918937683, -0.10920000076293945, -0.3425000011920929, -0.28929999470710754, -0.03519999980926514, 0.3626999855041504, -0.06040000170469284, 0.48489999771118164, 0.16930000483989716, 0.39980000257492065, -0.1777999997138977], [-0.3797000050544739, -0.20759999752044678, -0.1657000035047531, -0.03460000082850456, 0.2685000002384186, -0.11800000071525574, 0.3061999976634979, 0.20020000636577606, -0.296999990940094, 0.2574000060558319, 0.02459999918937683, -0.49050000309944153, -0.14259999990463257, 0.35440000891685486, 0.15060000121593475], [-0.21690000593662262, -0.2329999953508377, 0.461899995803833, -0.3319999873638153, 0.07819999754428864, -0.2085999995470047, 0.05559999868273735, 0.050200000405311584, 0.3702999949455261, 0.045899998396635056, -0.11969999969005585, 0.04969999939203262, 0.42649999260902405, -0.04490000009536743, 0.42419999837875366], [-0.36320000886917114, 0.2078000009059906, 0.19380000233650208, 0.2386000007390976, 0.23520000278949738, 0.1071000024676323, -0.11219999939203262, 0.1729000061750412, 0.04839999973773956, 0.2689000070095062, -0.030300000682473183, -0.24570000171661377, 0.17180000245571136, -0.5608999729156494, -0.37560001015663147], [-0.1404000073671341, 0.13539999723434448, -0.4246000051498413, 0.01360000018030405, -0.10890000313520432, -0.2671999931335449, 0.14820000529289246, -0.15489999949932098, -0.33379998803138733, -0.257999986410141, -0.45019999146461487, 0.008700000122189522, 0.4821999967098236, -0.19120000302791595, 0.049300000071525574], [0.04089999943971634, -0.12950000166893005, -0.10909999907016754, 0.09099999815225601, -0.016100000590085983, 0.16859999299049377, -0.5447999835014343, -0.35659998655319214, 0.1460999995470047, -0.17890000343322754, 0.09629999846220016, -0.5963000059127808, 0.24570000171661377, 0.1445000022649765, 0.09650000184774399], [0.13369999825954437, 0.3271999955177307, -0.31049999594688416, -0.18479999899864197, 0.20190000534057617, -0.1889999955892563, 0.38940000534057617, -0.2662999927997589, 0.4050999879837036, 0.11829999834299088, 0.4519999921321869, -0.09560000151395798, 0.19210000336170197, -0.007899999618530273, -0.12970000505447388]], [0.0, 0.0, 0.0, 0.0, 0.0, 0.0, 0.0, 0.0, 0.0, 0.0, 0.0, 0.0, 0.0, 0.0, 0.0], [[-0.05169999971985817, 0.011599999852478504, 0.05860000103712082, 0.015599999576807022, -0.0568000003695488], [0.0071000000461936, -0.04830000177025795, 0.012000000104308128, 0.012199999764561653, 0.0006000000284984708], [-0.012400000356137753, 0.032099999487400055, 0.012500000186264515, -0.06700000166893005, -9.999999747378752e-05], [0.053700000047683716, -0.13729999959468842, 0.050999999046325684, -0.026900000870227814, 0.04170000180602074], [-0.0071000000461936, 0.04320000112056732, 0.0003000000142492354, 0.015699999406933784, -0.0632999986410141], [0.04490000009536743, -0.0071000000461936, 0.08869999647140503, 0.030500000342726707, -0.001500000013038516], [0.05389999970793724, -0.05169999971985817, -0.02070000022649765, 0.0020000000949949026, 0.01140000019222498], [0.009800000116229057, 0.01940000057220459, -0.03799999877810478, -0.01640000008046627, 0.01549999974668026], [-0.024399999529123306, 0.09529999643564224, -0.006300000008195639, -0.015699999406933784, -0.07580000162124634], [-0.03310000151395798, -0.020099999383091927, 0.032099999487400055, 0.10859999805688858, 0.09799999743700027], [0.048700001090765, -0.03189999982714653, 0.02250000089406967, -0.05260000005364418, -0.016499999910593033], [0.02250000089406967, -0.0203000009059906, -0.004600000102072954, 0.022700000554323196, -0.01769999973475933], [-0.05779999867081642, 0.13570000231266022, -0.026399999856948853, -0.004699999932199717, 0.01940000057220459], [-0.014499999582767487, -0.07180000096559525, 0.035599999129772186, 0.02669999934732914, 0.06109999865293503], [-0.020500000566244125, 0.0340999998152256, 0.062199998646974564, 0.04610000178217888, 0.01489999983459711]], [[-0.6141999959945679, 0.6470000147819519, -0.29679998755455017, 0.25920000672340393, -0.22110000252723694], [-0.45890000462532043, -0.3319999873638153, 0.5909000039100647, -0.06849999725818634, -0.5703999996185303], [0.39750000834465027, 0.23029999434947968, 0.42879998683929443, 0.7710999846458435, -0.10220000147819519], [-0.4462999999523163, -0.5347999930381775, -0.13269999623298645, 0.5259000062942505, 0.46970000863075256], [-0.23440000414848328, 0.3635999858379364, 0.6010000109672546, -0.2387000024318695, 0.6281999945640564]], [0.0, 0.0, 0.0, 0.0, 0.0], [[-0.05169999971985817, 0.011599999852478504, 0.05860000103712082], [0.015599999576807022, -0.0568000003695488, 0.0071000000461936], [-0.04830000177025795, 0.012000000104308128, 0.012199999764561653], [0.0006000000284984708, -0.012400000356137753, 0.032099999487400055], [0.012500000186264515, -0.06700000166893005, -9.999999747378752e-05]], [0.0, 0.0, 0.0]]</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>[[[-0.1785999983549118, 0.1151999980211258, 0.16349999606609344, 0.3598000109195709, -0.3659000098705292, 0.10440000146627426, -0.06369999796152115, 0.10419999808073044, 0.16750000417232513, -0.05130000039935112, 0.050599999725818634, 0.28110000491142273, -0.009999999776482582, -0.20010000467300415, -0.17319999635219574], [0.24330000579357147, -0.3418999910354614, 0.09849999845027924, -0.2003999948501587, 0.11580000072717667, -0.18979999423027039, 0.22550000250339508, -0.20200000703334808, -0.10220000147819519, -0.10189999639987946, 0.0215000007301569, -0.14030000567436218, 0.17479999363422394, 0.0142000000923872, -0.05700000002980232]], [[0.6577000021934509, -0.527400016784668, 0.3197000026702881, 0.32600000500679016, 0.5389000177383423, 0.1348000019788742, 0.6920999884605408, -0.37400001287460327, 0.0034000000450760126, -0.546500027179718, 0.2856000065803528, -0.3070000112056732, 0.5504999756813049, 0.3675999939441681, -0.048900000751018524], [-0.2517000138759613, 0.7734000086784363, 0.186599999666214, 0.059300001710653305, -0.6401000022888184, 0.09070000052452087, -0.19619999825954437, 0.5421000123023987, 0.20229999721050262, 0.3215999901294708, -0.44130000472068787, -0.0828000009059906, 0.14959999918937683, 0.5200999975204468, -0.09489999711513519], [0.4921000003814697, -0.32429999113082886, -0.05050000175833702, -0.21799999475479126, -0.13369999825954437, -0.6190000176429749, -0.1527000069618225, 0.0778999999165535, 0.027000000700354576, 0.3808000087738037, -0.12049999833106995, -0.15070000290870667, 0.08449999988079071, -0.23270000517368317, -0.3880000114440918], [-0.590399980545044, -0.1606999933719635, -0.5260000228881836, -0.28029999136924744, -0.6337000131607056, -0.1290999948978424, -0.20409999787807465, 0.5956000089645386, 0.7150999903678894, -0.04910000041127205, -0.26840001344680786, 0.43950000405311584, 0.13570000231266022, -0.2012999951839447, -0.8040000200271606], [0.5774000287055969, -0.24140000343322754, 0.18539999425411224, -0.19429999589920044, 0.5514000058174133, 0.8715000152587891, 0.1907999962568283, 0.21770000457763672, -0.435699999332428, -0.07859999686479568, 0.6312999725341797, -0.258899986743927, 0.6693000197410583, 0.40130001306533813, 0.5123999714851379], [0.19030000269412994, -0.05909999832510948, -0.29339998960494995, -0.08449999988079071, 0.18400000035762787, 0.30730000138282776, -0.04879999905824661, 0.34940001368522644, 0.5648000240325928, 0.13269999623298645, -0.7013000249862671, -0.02410000003874302, 0.032499998807907104, -0.00839999970048666, 0.10320000350475311], [0.17630000412464142, -0.0803999975323677, 0.1177000030875206, -0.7228000164031982, 0.4399999976158142, 0.17839999496936798, 0.12880000472068787, -0.42739999294281006, -0.271699994802475, -0.3203999996185303, -0.022299999371170998, -0.24860000610351562, -0.022199999541044235, 0.1615000069141388, -0.3244999945163727], [-0.361299991607666, -0.026499999687075615, 0.027400000020861626, 0.15700000524520874, -0.7193999886512756, 0.43230000138282776, 0.13760000467300415, -0.25679999589920044, 0.05939999967813492, 0.6581000089645386, -0.4546999931335449, 0.1379999965429306, -0.15240000188350677, -0.11069999635219574, -0.11500000208616257], [-0.44279998540878296, 0.14650000631809235, -0.2904999852180481, 0.390500009059906, 0.0052999998442828655, -0.462799996137619, -0.6341999769210815, -0.24220000207424164, -0.16670000553131104, 0.58160001039505, -0.42969998717308044, 0.8023999929428101, -0.07980000227689743, 0.066600002348423, -0.5555999875068665], [-0.5288000106811523, -0.1363999992609024, -0.18479999899864197, 0.05779999867081642, 0.08320000022649765, -0.038100000470876694, 0.2290000021457672, 0.25200000405311584, -0.37540000677108765, 0.414000004529953, -0.15080000460147858, -0.4593999981880188, -0.31360000371932983, 0.5078999996185303, 0.15649999678134918], [-0.0803999975323677, -0.31850001215934753, 0.4708999991416931, -0.6359999775886536, 0.2125999927520752, -0.19550000131130219, 0.14429999887943268, 0.06930000334978104, 0.6358000040054321, -0.1678999960422516, 0.009800000116229057, -0.03909999877214432, 0.8912000060081482, -0.15160000324249268, 0.53329998254776], [-0.47119998931884766, 0.3797999918460846, 0.0714000016450882, 0.2768999934196472, 0.1956000030040741, -0.07779999822378159, -0.22869999706745148, 0.3149999976158142, 0.21359999477863312, 0.3628000020980835, -0.15970000624656677, -0.09920000284910202, 0.004900000058114529, -0.7494999766349792, -0.5709999799728394], [0.016100000590085983, 0.046799998730421066, -0.4521999955177307, -0.10559999942779541, 0.06880000233650208, -0.37400001287460327, 0.2273000031709671, -0.28519999980926514, -0.31220000982284546, -0.37860000133514404, -0.2574999928474426, -0.02290000021457672, 0.5928000211715698, -0.33899998664855957, 0.039000000804662704], [0.046300001442432404, -0.22519999742507935, -0.026100000366568565, 0.11630000174045563, -0.08709999918937683, 0.30300000309944153, -0.5178999900817871, -0.39590001106262207, 0.05609999969601631, -0.20430000126361847, 0.1256999969482422, -0.6273000240325928, 0.3450999855995178, 0.23899999260902405, 0.17229999601840973], [0.1509000062942505, 0.21610000729560852, -0.23720000684261322, -0.2639999985694885, 0.13570000231266022, -0.008500000461935997, 0.45010000467300415, -0.23810000717639923, 0.47620001435279846, 0.07199999690055847, 0.46219998598098755, -0.16820000112056732, 0.38359999656677246, 0.15780000388622284, -0.043299999088048935]], [-0.0066999997943639755, 0.03709999844431877, 0.0892999991774559, 0.12070000171661377, -0.07829999923706055, -0.02290000021457672, -0.0010000000474974513, 0.006000000052154064, -0.0017000000225380063, -0.13940000534057617, 0.12729999423027039, 0.011599999852478504, 0.1160999983549118, -0.020500000566244125, -0.09049999713897705], [[0.2304999977350235, 0.37049999833106995, 0.10610000044107437, -0.3018999993801117, -0.0551999993622303], [0.0003000000142492354, -0.226500004529953, 0.15889999270439148, 0.1445000022649765, 0.012000000104308128], [0.10480000078678131, -0.1143999993801117, -0.07129999995231628, -0.12290000170469284, -0.061000000685453415], [0.1535000056028366, -0.44940000772476196, 0.07609999924898148, 0.06700000166893005, -0.2565999925136566], [0.2078000009059906, 0.35600000619888306, 0.2948000133037567, -0.3278000056743622, -0.01590000092983246], [0.21860000491142273, 0.035599999129772186, 0.23520000278949738, 0.02930000051856041, 0.04050000011920929], [0.11640000343322754, 0.22169999778270721, -0.053199999034404755, -0.1808999925851822, 0.11100000143051147], [0.265500009059906, 0.008299999870359898, 0.021900000050663948, 0.13660000264644623, -0.13750000298023224], [0.1467999964952469, 0.4244000017642975, 0.003599999938160181, 0.23839999735355377, -0.17829999327659607], [-0.2630000114440918, -0.1477999985218048, 0.054999999701976776, 0.2808000147342682, 0.16990000009536743], [0.25600001215934753, 0.03970000147819519, 0.10450000315904617, -0.4230000078678131, -0.045499999076128006], [0.03310000151395798, -0.21699999272823334, -0.07490000128746033, 0.03539999946951866, -0.15870000422000885], [0.30550000071525574, 0.5544000267982483, -0.10260000079870224, -0.11259999871253967, -0.02410000003874302], [0.026399999856948853, 0.10580000281333923, 0.11339999735355377, 0.049400001764297485, 0.16930000483989716], [0.044599998742341995, 0.16220000386238098, 0.1851000040769577, 0.03139999881386757, 0.10170000046491623]], [[-0.44440001249313354, 0.945900022983551, -0.0738999992609024, 0.03480000048875809, -0.38199999928474426], [-0.249099999666214, -0.2540999948978424, 0.6974999904632568, -0.4284000098705292, -0.8026999831199646], [0.4237000048160553, 0.39809998869895935, 0.460999995470047, 0.7950999736785889, -0.10159999877214432], [-0.5874000191688538, -0.5228000283241272, -0.14169999957084656, 0.6729000210762024, 0.5659999847412109], [-0.4564000070095062, 0.3287000060081482, 0.5271000266075134, -0.15139999985694885, 0.8111000061035156]], [-0.1200999990105629, 0.013199999928474426, 0.06840000301599503, -0.15680000185966492, -0.029200000688433647], [[-0.4318999946117401, -0.07190000265836716, -0.10610000044107437], [-0.27630001306533813, -0.07859999686479568, 0.20319999754428864], [-0.01850000023841858, -0.08609999716281891, 0.1670999974012375], [0.09510000050067902, -0.12540000677108765, 0.17520000040531158], [0.35350000858306885, -0.133200004696846, 0.08910000324249268]], [0.037300001829862595, -0.06599999964237213, 0.08869999647140503]]</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>[0.9083723644969103]</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>[0.02091553142082792]</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>[0.7680772556214586]</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>[0.0529487211485323]</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>[-3.3188938001259816]</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>[1.4134862436718307]</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>[0.6165433667100972]</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>[0.08808730239699314]</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>[0.7549715004870836]</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>[0.05811121061971006]</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>[0.5236738367561371]</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>[0.1565910084903534]</t>
+        </is>
+      </c>
+      <c r="Q14" t="inlineStr">
+        <is>
+          <t>[-0.14860007408852383]</t>
+        </is>
+      </c>
+      <c r="R14" t="inlineStr">
+        <is>
+          <t>[0.12384864032964638]</t>
+        </is>
+      </c>
+      <c r="S14" t="inlineStr">
+        <is>
+          <t>[-0.17601081106345373]</t>
+        </is>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>[0.09909107050083853]</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>[-1.4143810661818836]</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>[0.23087067595890026]</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>[-0.32085308028864246]</t>
+        </is>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>[0.13837339231464663]</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>[-0.2603407517380545]</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>[0.10371748577876315]</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>[-1.2476345756869134]</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>[0.20679221289315092]</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>[-0.9362303964300882]</t>
+        </is>
+      </c>
+      <c r="AD14" t="inlineStr">
+        <is>
+          <t>[0.1622483069076241]</t>
+        </is>
+      </c>
+      <c r="AE14" t="inlineStr">
+        <is>
+          <t>[-0.7838534041228131]</t>
+        </is>
+      </c>
+      <c r="AF14" t="inlineStr">
+        <is>
+          <t>[0.19208189900512834]</t>
+        </is>
+      </c>
+      <c r="AG14" t="inlineStr">
+        <is>
+          <t>[-3.698396852918507]</t>
+        </is>
+      </c>
+      <c r="AH14" t="inlineStr">
+        <is>
+          <t>[0.34979545049625965]</t>
+        </is>
+      </c>
+      <c r="AI14" t="inlineStr">
+        <is>
+          <t>[-1.3998499641677373]</t>
+        </is>
+      </c>
+      <c r="AJ14" t="inlineStr">
+        <is>
+          <t>[0.19666503301681632]</t>
+        </is>
+      </c>
+      <c r="AK14" t="inlineStr">
+        <is>
+          <t>[-0.8344446668007273]</t>
+        </is>
+      </c>
+      <c r="AL14" t="inlineStr">
+        <is>
+          <t>[0.19471286106937377]</t>
+        </is>
+      </c>
+      <c r="AM14" t="inlineStr">
+        <is>
+          <t>[-3.2801232109585223]</t>
+        </is>
+      </c>
+      <c r="AN14" t="inlineStr">
+        <is>
+          <t>[0.3287444917996969]</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>model_15_5_3</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>[15, 5]</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>[[[0.025800000876188278, -0.06419999897480011, -0.005400000140070915, 0.029899999499320984, 0.02449999935925007, -0.04399999976158142, -0.07069999724626541, 0.009800000116229057, -0.008299999870359898, -0.02370000071823597, 0.05350000038743019, 0.012000000104308128, 0.05649999901652336, -0.08569999784231186, -0.01899999938905239], [0.1006999984383583, 0.043699998408555984, 0.05550000071525574, -0.012400000356137753, 0.024900000542402267, -0.02850000001490116, 0.019300000742077827, -0.030400000512599945, -0.006000000052154064, 0.017100000753998756, 0.026000000536441803, 0.024000000208616257, -0.00559999980032444, 0.03750000149011612, 0.023600000888109207]], [[-0.18960000574588776, 0.3677000105381012, 0.07050000131130219, -0.15000000596046448, 0.20029999315738678, 0.13830000162124634, -0.1551000028848648, -0.08179999887943268, 0.15559999644756317, 0.13510000705718994, 0.5455999970436096, -0.2524000108242035, -0.5429999828338623, -0.11100000143051147, 0.019300000742077827], [-0.1316000074148178, 0.23729999363422394, 0.4634999930858612, -0.04690000042319298, 0.02449999935925007, 0.1476999968290329, 0.4731000065803528, 0.07580000162124634, 0.2151000052690506, -0.2833999991416931, 0.08649999648332596, 0.20080000162124634, 0.0551999993622303, 0.5123999714851379, -0.13169999420642853], [0.2856000065803528, -0.12290000170469284, -0.06440000236034393, -0.1972000002861023, 0.2037999927997589, -0.16750000417232513, -0.14569999277591705, -0.13249999284744263, 0.32179999351501465, 0.32179999351501465, 0.32589998841285706, 0.21580000221729279, 0.30149999260902405, 0.34389999508857727, 0.4275999963283539], [-0.40630000829696655, 0.021800000220537186, -0.31060001254081726, 0.21320000290870667, -0.07240000367164612, -0.2037000060081482, -0.03720000013709068, -0.2727000117301941, 0.2651999890804291, -0.1800999939441681, -0.17949999868869781, 0.5081999897956848, -0.3547999858856201, 0.03840000182390213, 0.2222999930381775], [0.382999986410141, 0.4075999855995178, -0.43790000677108765, -0.15620000660419464, 0.3109000027179718, -0.13930000364780426, 0.10719999670982361, -0.19699999690055847, -0.014700000174343586, -0.32260000705718994, -0.26759999990463257, -0.2702000141143799, -0.06790000200271606, 0.2224999964237213, -0.04089999943971634], [0.08110000193119049, 0.027499999850988388, -0.05490000173449516, -0.1851000040769577, -0.1370999962091446, -0.14480000734329224, -0.04780000075697899, 0.7797999978065491, 0.35679998993873596, -0.20270000398159027, -0.11180000007152557, -0.07689999788999557, -0.1500999927520752, -0.1039000004529953, 0.29170000553131104], [-0.16519999504089355, -0.028999999165534973, 0.1873999983072281, -0.4832000136375427, -0.2305999994277954, -0.15399999916553497, -0.5586000084877014, -0.046300001442432404, -0.31459999084472656, -0.14920000731945038, -0.12839999794960022, 0.010499999858438969, -0.10670000314712524, 0.4002000093460083, -0.05290000140666962], [-0.051600001752376556, -0.4113999903202057, 0.33390000462532043, 0.11789999902248383, 0.5898000001907349, 0.019200000911951065, 0.03400000184774399, 0.00570000009611249, -0.10660000145435333, 0.00570000009611249, -0.3197999894618988, -0.18799999356269836, -0.3122999966144562, 0.10840000212192535, 0.30809998512268066], [0.49869999289512634, 0.11150000244379044, 0.1679999977350235, -0.026900000870227814, -0.03620000183582306, 0.3625999987125397, -0.20170000195503235, -0.00800000037997961, 0.19189999997615814, 0.27709999680519104, -0.3343000113964081, 0.3878999948501587, -0.32359999418258667, -0.041200000792741776, -0.23270000517368317], [-0.2574000060558319, -0.19499999284744263, -0.3262999951839447, 0.045899998396635056, 0.13169999420642853, -0.125, 0.023099999874830246, 0.2524999976158142, 0.20389999449253082, 0.42660000920295715, -0.08089999854564667, -0.14030000567436218, -0.07410000264644623, 0.38370001316070557, -0.5360999703407288], [0.3009999990463257, -0.43939998745918274, -0.07069999724626541, 0.33219999074935913, -0.28949999809265137, 0.1624000072479248, -0.15610000491142273, -0.1298999935388565, 0.21860000491142273, -0.39160001277923584, 0.27810001373291016, -0.25130000710487366, -0.19689999520778656, 0.24650000035762787, -0.09120000153779984], [0.03460000082850456, 0.10760000348091125, 0.23770000040531158, 0.01549999974668026, -0.4851999878883362, -0.2856999933719635, 0.23810000717639923, -0.28450000286102295, 0.21130000054836273, 0.3580000102519989, -0.272599995136261, -0.4142000079154968, -0.12559999525547028, 0.05480000004172325, 0.19599999487400055], [0.027899999171495438, 0.43650001287460327, 0.08309999853372574, 0.6771000027656555, 0.002099999925121665, -0.06830000132322311, -0.3319999873638153, 0.23360000550746918, -0.21130000054836273, 0.11860000342130661, 0.0003000000142492354, -0.03539999946951866, 0.0860000029206276, 0.28369998931884766, 0.16169999539852142], [-0.1404999941587448, -0.009499999694526196, -0.36090001463890076, -0.11429999768733978, -0.2092999964952469, 0.6644999980926514, 0.17839999496936798, 0.0706000030040741, -0.22849999368190765, 0.1695999950170517, -0.07699999958276749, -0.07000000029802322, -0.050200000405311584, 0.2630999982357025, 0.388700008392334], [0.2992999851703644, -0.10100000351667404, -0.06949999928474426, -0.002899999963119626, -0.11909999698400497, -0.35190001130104065, 0.3718000054359436, 0.15929999947547913, -0.5001000165939331, 0.12189999967813492, 0.27880001068115234, 0.2565000057220459, -0.41780000925064087, 0.10350000113248825, 0.00839999970048666]], [0.0, 0.0, 0.0, 0.0, 0.0, 0.0, 0.0, 0.0, 0.0, 0.0, 0.0, 0.0, 0.0, 0.0, 0.0], [[0.025800000876188278, -0.06419999897480011, -0.005400000140070915, 0.029899999499320984, 0.02449999935925007], [-0.04399999976158142, -0.07069999724626541, 0.009800000116229057, -0.008299999870359898, -0.02370000071823597], [0.05350000038743019, 0.012000000104308128, 0.05649999901652336, -0.08569999784231186, -0.01899999938905239], [0.1006999984383583, 0.043699998408555984, 0.05550000071525574, -0.012400000356137753, 0.024900000542402267], [-0.02850000001490116, 0.019300000742077827, -0.030400000512599945, -0.006000000052154064, 0.017100000753998756], [0.026000000536441803, 0.024000000208616257, -0.00559999980032444, 0.03750000149011612, 0.023600000888109207], [0.04470000043511391, -0.11550000309944153, -0.05739999935030937, -0.038600001484155655, 0.09920000284910202], [-0.01850000023841858, 0.06840000301599503, 0.01769999973475933, 0.0771000012755394, -9.999999747378752e-05], [-0.06710000336170197, 0.0414000004529953, 0.03220000118017197, 0.006500000134110451, 9.999999747378752e-05], [0.05260000005364418, -0.08470000326633453, -0.0406000018119812, -0.024700000882148743, 0.05829999968409538], [0.020400000736117363, 0.018699999898672104, 0.021900000050663948, -0.09279999881982803, -0.046799998730421066], [-0.05609999969601631, 0.025499999523162842, 0.016599999740719795, 0.04809999838471413, -0.06289999932050705], [0.06310000270605087, -0.032999999821186066, 0.0071000000461936, 0.06989999860525131, 0.03819999843835831], [-0.040699999779462814, 0.04129999876022339, -0.031599998474121094, 0.039400000125169754, -0.06400000303983688], [-0.03060000017285347, 0.08089999854564667, -0.13809999823570251, 0.01510000042617321, -0.051500000059604645]], [[0.39719998836517334, -0.4964999854564667, 0.5564000010490417, -0.43970000743865967, 0.30469998717308044], [-0.22759999334812164, 0.0860000029206276, -0.18639999628067017, -0.8438000082969666, -0.4404999911785126], [-0.3644999861717224, 0.33180001378059387, -0.10740000009536743, -0.2720000147819519, 0.8195000290870667], [0.15530000627040863, -0.5878000259399414, -0.7688999772071838, -0.033799998462200165, 0.19509999454021454], [-0.7958999872207642, -0.5389999747276306, 0.23010000586509705, 0.13979999721050262, -0.059300001710653305]], [0.0, 0.0, 0.0, 0.0, 0.0], [[0.025800000876188278, -0.06419999897480011, -0.005400000140070915], [0.029899999499320984, 0.02449999935925007, -0.04399999976158142], [-0.07069999724626541, 0.009800000116229057, -0.008299999870359898], [-0.02370000071823597, 0.05350000038743019, 0.012000000104308128], [0.05649999901652336, -0.08569999784231186, -0.01899999938905239]], [0.0, 0.0, 0.0]]</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>[[[-0.03480000048875809, -0.227400004863739, -0.0017999999690800905, 0.1315000057220459, -0.07050000131130219, -0.1655000001192093, -0.18639999628067017, 0.08560000360012054, -0.07360000163316727, -0.0869000032544136, 0.12280000001192093, -0.25920000672340393, 0.18440000712871552, -0.2865999937057495, -0.23549999296665192], [0.2434999942779541, 0.3416999876499176, 0.21789999306201935, 0.02419999986886978, 0.25699999928474426, -0.002400000113993883, -0.0494999997317791, -0.06239999830722809, 0.1477999985218048, -0.09449999779462814, 0.1006999984383583, 0.3174000084400177, -0.23340000212192535, 0.1501999944448471, 0.09570000320672989]], [[-0.22050000727176666, 0.5486000180244446, 0.1404000073671341, -0.15600000321865082, 0.2371000051498413, 0.2572000026702881, -0.09220000356435776, -0.1639000028371811, 0.2685999870300293, 0.11159999668598175, 0.6148999929428101, -0.3458999991416931, -0.6866999864578247, 0.03550000116229057, 0.19439999759197235], [-0.10320000350475311, 0.527899980545044, 0.38089999556541443, -0.2071000039577484, -0.06069999933242798, 0.3021000027656555, 0.607699990272522, -0.16459999978542328, 0.47699999809265137, -0.28049999475479126, 0.1307000070810318, 0.3747999966144562, -0.19130000472068787, 0.7670000195503235, 0.11479999870061874], [0.2793000042438507, 0.040300000458955765, -0.007400000002235174, -0.2232999950647354, 0.1949000060558319, -0.026499999687075615, -0.03240000084042549, -0.2345000058412552, 0.4000000059604645, 0.31940001249313354, 0.39559999108314514, 0.13570000231266022, 0.17550000548362732, 0.4803999960422516, 0.5593000054359436], [-0.4659999907016754, -0.10740000009536743, -0.14589999616146088, 0.44429999589920044, 0.12070000171661377, -0.4072999954223633, -0.1785999983549118, -0.2295999974012375, 0.262800008058548, -0.22120000422000885, -0.12839999794960022, 0.35510000586509705, -0.2745000123977661, -0.16339999437332153, 0.0803999975323677], [0.35260000824928284, 0.5199000239372253, -0.3091000020503998, -0.07289999723434448, 0.44359999895095825, -0.16500000655651093, 0.10170000046491623, -0.26980000734329224, 0.0754999965429306, -0.3553999960422516, -0.2020999938249588, -0.3725000023841858, -0.1396999955177307, 0.3098999857902527, 0.05889999866485596], [0.15520000457763672, 0.10419999808073044, -0.18039999902248383, -0.35100001096725464, -0.2517000138759613, -0.04639999940991402, -0.006599999964237213, 0.7166000008583069, 0.39579999446868896, -0.21660000085830688, -0.16060000658035278, 0.26660001277923584, -0.2671999931335449, 0.01850000023841858, 0.375900000333786], [-0.10429999977350235, 0.08889999985694885, 0.02669999934732914, -0.704200029373169, -0.40619999170303345, 0.03849999979138374, -0.4530999958515167, -0.10339999943971634, -0.29670000076293945, -0.131400004029274, -0.17149999737739563, 0.3296000063419342, -0.22110000252723694, 0.6097000241279602, 0.17350000143051147], [0.030500000342726707, -0.5360999703407288, 0.3930000066757202, 0.26080000400543213, 0.6836000084877014, -0.1590999960899353, 0.07119999825954437, -0.09489999711513519, -0.18809999525547028, 0.06549999862909317, -0.3531000018119812, -0.4027999937534332, -0.12219999730587006, -0.2483000010251999, 0.13779999315738678], [0.47269999980926514, 0.21330000460147858, 0.17829999327659607, -0.10440000146627426, -0.0820000022649765, 0.44620001316070557, -0.2206999957561493, 0.014700000174343586, 0.274399995803833, 0.2321999967098236, -0.3100000023841858, 0.5372999906539917, -0.4422000050544739, 0.17409999668598175, -0.0892999991774559], [-0.21950000524520874, -0.1420000046491623, -0.4140999913215637, -0.015399999916553497, 0.08389999717473984, -0.05810000002384186, 0.01889999955892563, 0.210999995470047, 0.2305999994277954, 0.40470001101493835, -0.10540000349283218, -0.013899999670684338, -0.12559999525547028, 0.4092000126838684, -0.520799994468689], [0.24779999256134033, -0.4027000069618225, -0.0017999999690800905, 0.35089999437332153, -0.29660001397132874, 0.1876000016927719, -0.19380000233650208, -0.07800000160932541, 0.2554999887943268, -0.4339999854564667, 0.33399999141693115, -0.21529999375343323, -0.2303999960422516, 0.33390000462532043, -0.059700001031160355], [0.10000000149011612, 0.4196000099182129, 0.25110000371932983, -0.06859999895095825, -0.3894999921321869, -0.07890000194311142, 0.6065000295639038, -0.6549000144004822, 0.5462999939918518, 0.5982999801635742, -0.22120000422000885, -0.5895000100135803, -0.35359999537467957, 0.19419999420642853, 0.4661000072956085], [0.006099999882280827, 0.23070000112056732, 0.20280000567436218, 0.8654000163078308, 0.11900000274181366, -0.20419999957084656, -0.42080000042915344, 0.38100001215934753, -0.41940000653266907, 0.11129999905824661, 0.012799999676644802, -0.22529999911785126, 0.2667999863624573, 0.00430000014603138, -0.08799999952316284], [-0.0284000001847744, 0.25619998574256897, -0.564300000667572, -0.38659998774528503, -0.37049999833106995, 0.9034000039100647, 0.36419999599456787, -0.1462000012397766, -0.0729999989271164, 0.16279999911785126, -0.07840000092983246, 0.2989000082015991, -0.24490000307559967, 0.5728999972343445, 0.6647999882698059], [0.31940001249313354, 0.09910000115633011, -0.16040000319480896, -0.13899999856948853, -0.17149999737739563, -0.20360000431537628, 0.3815999925136566, 0.04399999976158142, -0.3005000054836273, 0.023399999365210533, 0.31200000643730164, 0.5821999907493591, -0.7002999782562256, 0.305400013923645, 0.16249999403953552]], [-0.004999999888241291, 0.004100000020116568, 0.016699999570846558, 0.1289999932050705, 0.07069999724626541, -0.013899999670684338, -0.07090000063180923, -0.011599999852478504, 0.043800000101327896, -0.12809999287128448, 0.09489999711513519, 0.05270000174641609, -0.022700000554323196, -0.026799999177455902, -0.08079999685287476], [[-0.13420000672340393, 0.04910000041127205, 0.11029999703168869, -0.043800000101327896, -0.08630000054836273], [-0.31369999051094055, 0.08420000225305557, -0.016499999910593033, -0.02280000038444996, -0.08420000225305557], [-0.04619999974966049, 0.10740000009536743, 0.10980000346899033, -0.15459999442100525, -0.04470000043511391], [0.2856000065803528, 0.11460000276565552, 0.3529999852180481, -0.218299999833107, 0.2946999967098236], [0.024299999698996544, 0.12099999934434891, 0.2328999936580658, -0.17679999768733978, 0.25850000977516174], [-0.28220000863075256, -0.007000000216066837, -0.24040000140666962, 0.24500000476837158, -0.3138999938964844], [-0.11490000039339066, -0.17219999432563782, -0.3199999928474426, 0.13449999690055847, -0.013199999928474426], [0.1120000034570694, -0.03700000047683716, -0.029100000858306885, 0.18770000338554382, -0.08399999886751175], [-0.17980000376701355, 0.1386999934911728, 0.11670000106096268, -0.07490000128746033, -0.009999999776482582], [0.04010000079870224, -0.15649999678134918, -0.1965000033378601, 0.05979999899864197, 0.08139999955892563], [-0.05270000174641609, 0.10849999636411667, 0.11580000072717667, -0.19220000505447388, -0.17720000445842743], [-0.31540000438690186, 0.1785999983549118, 0.12399999797344208, 0.22859999537467957, -0.1860000044107437], [0.3027999997138977, -0.15060000121593475, 0.02759999968111515, 0.06930000334978104, 0.11599999666213989], [-0.3978999853134155, 0.05460000038146973, -0.258899986743927, 0.26739999651908875, -0.39079999923706055], [-0.2524999976158142, 0.0729999989271164, -0.3005000054836273, 0.03669999912381172, -0.022299999371170998]], [[0.5938000082969666, -0.5849000215530396, 0.6431000232696533, -0.4902999997138977, 0.4049000144004822], [-0.335099995136261, 0.1599999964237213, -0.1762000024318695, -0.8604999780654907, -0.5533999800682068], [-0.32850000262260437, 0.412200003862381, 0.0957999974489212, -0.4652000069618225, 0.9351000189781189], [0.1915999948978424, -0.6395999789237976, -0.8813999891281128, 0.0640999972820282, 0.259799987077713], [-0.5365999937057495, -0.6628999710083008, 0.4372999966144562, 0.0003000000142492354, 0.14710000157356262]], [-0.06800000369548798, 0.10040000081062317, 0.20520000159740448, -0.133200004696846, -0.018400000408291817], [[0.1818999946117401, -0.11020000278949738, 0.11079999804496765], [-0.11500000208616257, 0.0803999975323677, -0.1469999998807907], [0.1873999983072281, 0.11569999903440475, -0.14569999277591705], [-0.11550000309944153, -0.025299999862909317, 0.14180000126361847], [0.4205000102519989, -0.008100000210106373, 0.09189999848604202]], [-0.020999999716877937, -0.04280000180006027, 0.15029999613761902]]</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>[0.9007613714101985]</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>[0.02265286715119779]</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>[0.6937365117589753]</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>[0.06992095613694033]</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>[-1.2070958009315382]</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>[0.7223376395575157]</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>[0.8134112488972851]</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>[0.04286299496568114]</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>[0.7710327529785995]</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>[0.0543021074818866]</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>[0.6872003263237574]</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>[0.10283209308269584]</t>
+        </is>
+      </c>
+      <c r="Q15" t="inlineStr">
+        <is>
+          <t>[-0.20363423285073323]</t>
+        </is>
+      </c>
+      <c r="R15" t="inlineStr">
+        <is>
+          <t>[0.129782738618639]</t>
+        </is>
+      </c>
+      <c r="S15" t="inlineStr">
+        <is>
+          <t>[-0.15587971098218767]</t>
+        </is>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>[0.0973948171682622]</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>[-1.3558636454196877]</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>[0.22527505699221234]</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>[-0.417646340174489]</t>
+        </is>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>[0.14851351457614065]</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>[-0.2551398303525092]</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>[0.10328948526453882]</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>[-1.0251377647049158]</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>[0.18632153300490673]</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>[-1.0371546551889055]</t>
+        </is>
+      </c>
+      <c r="AD15" t="inlineStr">
+        <is>
+          <t>[0.17070535320733923]</t>
+        </is>
+      </c>
+      <c r="AE15" t="inlineStr">
+        <is>
+          <t>[-0.899888099685596]</t>
+        </is>
+      </c>
+      <c r="AF15" t="inlineStr">
+        <is>
+          <t>[0.2045762915503169]</t>
+        </is>
+      </c>
+      <c r="AG15" t="inlineStr">
+        <is>
+          <t>[-4.464851510685204]</t>
+        </is>
+      </c>
+      <c r="AH15" t="inlineStr">
+        <is>
+          <t>[0.4068579679232243]</t>
+        </is>
+      </c>
+      <c r="AI15" t="inlineStr">
+        <is>
+          <t>[-1.5264286506029627]</t>
+        </is>
+      </c>
+      <c r="AJ15" t="inlineStr">
+        <is>
+          <t>[0.20703801546100922]</t>
+        </is>
+      </c>
+      <c r="AK15" t="inlineStr">
+        <is>
+          <t>[-1.0043509739608045]</t>
+        </is>
+      </c>
+      <c r="AL15" t="inlineStr">
+        <is>
+          <t>[0.21274717073245408]</t>
+        </is>
+      </c>
+      <c r="AM15" t="inlineStr">
+        <is>
+          <t>[-3.948313296129821]</t>
+        </is>
+      </c>
+      <c r="AN15" t="inlineStr">
+        <is>
+          <t>[0.3800663344543249]</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>model_15_5_4</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>[15, 5]</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>[[[0.07999999821186066, 0.005799999926239252, -0.07419999688863754, 0.015799999237060547, 0.03500000014901161, -0.018699999898672104, -0.015799999237060547, -0.043299999088048935, 0.013000000268220901, 0.042500000447034836, -0.10080000013113022, 0.057500001043081284, -0.02810000069439411, 0.10559999942779541, -0.01590000092983246], [-0.015799999237060547, 0.06909999996423721, 0.006899999920278788, 0.009600000455975533, -0.08489999920129776, -0.06239999830722809, -0.00860000029206276, -0.0658000037074089, 0.037300001829862595, -0.05820000171661377, -0.061500001698732376, 0.04960000142455101, 0.0917000025510788, -0.01510000042617321, -0.06719999760389328]], [[-0.4537999927997589, -0.13989999890327454, 0.4986000061035156, 0.07569999992847443, -0.42089998722076416, 0.24549999833106995, 0.22920000553131104, 0.04540000110864639, 0.019200000911951065, -0.009999999776482582, 0.013000000268220901, 0.2856000065803528, 0.27790001034736633, -0.26159998774528503, 0.01590000092983246], [0.2646999955177307, -0.23569999635219574, 0.026100000366568565, -0.09099999815225601, -0.24210000038146973, 0.05889999866485596, -0.3822999894618988, -0.19920000433921814, -0.5608999729156494, 0.07859999686479568, -0.11069999635219574, 0.3603000044822693, 0.05820000171661377, 0.14910000562667847, -0.35929998755455017], [0.4392000138759613, -0.37439998984336853, 0.1298999935388565, 0.251800000667572, -0.031599998474121094, -0.25369998812675476, -0.013399999588727951, 0.027400000020861626, -0.14300000667572021, -0.2815999984741211, -0.15119999647140503, -0.0940999984741211, 0.07930000126361847, -0.4343999922275543, 0.44020000100135803], [0.2669999897480011, 0.26759999990463257, -0.09040000289678574, -0.21359999477863312, -0.042399998754262924, -0.19169999659061432, -0.0026000000070780516, 0.023499999195337296, 0.2572999894618988, -0.34279999136924744, 0.38600000739097595, 0.5824000239372253, 0.28119999170303345, 0.04190000146627426, 0.10689999908208847], [-0.062300000339746475, -0.1891999989748001, -0.6333000063896179, -0.010300000198185444, 0.1137000024318695, 0.37940001487731934, 0.03999999910593033, 0.048900000751018524, 0.14169999957084656, -0.0284000001847744, -0.38749998807907104, 0.14740000665187836, 0.4036000072956085, -0.20419999957084656, -0.02889999933540821], [-0.10740000009536743, 0.2745000123977661, -0.05530000105500221, -0.5472999811172485, -0.15690000355243683, -0.2451000064611435, 0.32739999890327454, 0.12690000236034393, -0.34470000863075256, -0.31380000710487366, -0.39410001039505005, -0.10610000044107437, -0.062199998646974564, -0.11079999804496765, -0.049300000071525574], [-0.1835000067949295, 0.16509999334812164, 0.021800000220537186, -0.3077000081539154, 0.3037000000476837, 0.1031000018119812, -0.23929999768733978, -0.41780000925064087, -0.2858999967575073, 0.11829999834299088, 0.32499998807907104, -0.18140000104904175, 0.260699987411499, -0.41019999980926514, 0.19679999351501465], [-0.11060000211000443, -0.30820000171661377, -0.2395000010728836, 0.015699999406933784, 0.11410000175237656, 0.03739999979734421, 0.4860999882221222, 0.10849999636411667, -0.45590001344680786, 0.09650000184774399, 0.3562999963760376, 0.12549999356269836, -0.016300000250339508, 0.3212999999523163, 0.33059999346733093], [0.18170000612735748, -0.052000001072883606, -0.032600000500679016, -0.08179999887943268, -0.1826000064611435, -0.3336000144481659, 0.39640000462532043, -0.5659000277519226, 0.22509999573230743, 0.48179998993873596, -0.16050000488758087, 0.018200000748038292, 0.15639999508857727, 0.03319999948143959, 0.007499999832361937], [0.3610999882221222, -0.1898999959230423, 0.07660000026226044, -0.5202999711036682, -0.3082999885082245, 0.5198000073432922, 0.000699999975040555, 0.03849999979138374, 0.21250000596046448, 0.03689999878406525, 0.11469999700784683, -0.22910000383853912, -0.1551000028848648, 0.07999999821186066, 0.21819999814033508], [0.025699999183416367, -0.2249000072479248, 0.3953000009059906, -0.3472999930381775, 0.5157999992370605, -0.1412000060081482, -0.0851999968290329, 0.3416000008583069, 0.09260000288486481, 0.2800000011920929, -0.25220000743865967, 0.15399999916553497, 0.23919999599456787, 0.1606999933719635, 0.06790000200271606], [0.1664000004529953, 0.45890000462532043, -0.0038999998942017555, 0.12080000340938568, 0.01600000075995922, 0.21459999680519104, 0.02070000022649765, 0.14300000667572021, -0.14550000429153442, 0.4214000105857849, -0.20250000059604645, 0.39149999618530273, -0.3434000015258789, -0.24210000038146973, 0.33219999074935913], [0.18359999358654022, -0.1615999937057495, 0.1500999927520752, -0.03689999878406525, 0.42879998683929443, 0.21050000190734863, 0.3982999920845032, -0.19460000097751617, 0.04560000076889992, -0.18889999389648438, 0.08980000019073486, 0.18979999423027039, -0.3465999960899353, -0.3066999912261963, -0.4422000050544739], [0.41339999437332153, 0.36250001192092896, 0.16940000653266907, 0.22949999570846558, 0.03830000013113022, 0.22689999639987946, 0.27399998903274536, 0.18719999492168427, -0.20489999651908875, 0.061900001019239426, 0.06379999965429306, -0.2973000109195709, 0.5045999884605408, 0.08569999784231186, -0.23019999265670776], [0.04639999940991402, -0.14920000731945038, -0.22179999947547913, -0.12540000677108765, -0.19609999656677246, -0.2752000093460083, -0.01209999993443489, 0.46950000524520874, 0.01640000008046627, 0.3813000023365021, 0.3492000102996826, -0.06889999657869339, -0.023499999195337296, -0.4472000002861023, -0.32089999318122864]], [0.0, 0.0, 0.0, 0.0, 0.0, 0.0, 0.0, 0.0, 0.0, 0.0, 0.0, 0.0, 0.0, 0.0, 0.0], [[0.07999999821186066, 0.005799999926239252, -0.07419999688863754, 0.015799999237060547, 0.03500000014901161], [-0.018699999898672104, -0.015799999237060547, -0.043299999088048935, 0.013000000268220901, 0.042500000447034836], [-0.10080000013113022, 0.057500001043081284, -0.02810000069439411, 0.10559999942779541, -0.01590000092983246], [-0.015799999237060547, 0.06909999996423721, 0.006899999920278788, 0.009600000455975533, -0.08489999920129776], [-0.06239999830722809, -0.00860000029206276, -0.0658000037074089, 0.037300001829862595, -0.05820000171661377], [-0.061500001698732376, 0.04960000142455101, 0.0917000025510788, -0.01510000042617321, -0.06719999760389328], [-0.00279999990016222, 0.1103999987244606, 0.04879999905824661, 0.0210999995470047, 0.03229999914765358], [0.1177000030875206, -0.002199999988079071, -0.013399999588727951, 0.054999999701976776, 0.02410000003874302], [-0.03189999982714653, -0.027000000700354576, -0.03830000013113022, 0.014999999664723873, -0.030500000342726707], [0.1274999976158142, 0.06849999725818634, -0.05130000039935112, 0.08389999717473984, -0.042500000447034836], [0.09709999710321426, 0.013399999588727951, -0.05310000106692314, -0.001500000013038516, 0.03840000182390213], [0.13680000603199005, -0.07649999856948853, 0.024900000542402267, 9.999999747378752e-05, -0.05130000039935112], [-0.0007999999797903001, 0.02800000086426735, 0.0038999998942017555, -0.0908999964594841, -0.07919999957084656], [0.04610000178217888, 0.03669999912381172, 0.004800000227987766, 0.03620000183582306, 0.027799999341368675], [0.05209999904036522, -0.08340000361204147, -0.03959999978542328, -0.012900000438094139, -0.02850000001490116]], [[0.03440000116825104, 0.6079000234603882, 0.004399999976158142, 0.5975000262260437, 0.5217999815940857], [0.1421000063419342, -0.642799973487854, 0.5182999968528748, 0.19760000705718994, 0.508899986743927], [-0.3400000035762787, 0.120899997651577, 0.6456999778747559, 0.3779999911785126, -0.5568000078201294], [-0.899399995803833, -0.2249000072479248, -0.2865999937057495, 0.0851999968290329, 0.22589999437332153], [0.23240000009536743, -0.39010000228881836, -0.48190000653266907, 0.6736000180244446, -0.32829999923706055]], [0.0, 0.0, 0.0, 0.0, 0.0], [[0.07999999821186066, 0.005799999926239252, -0.07419999688863754], [0.015799999237060547, 0.03500000014901161, -0.018699999898672104], [-0.015799999237060547, -0.043299999088048935, 0.013000000268220901], [0.042500000447034836, -0.10080000013113022, 0.057500001043081284], [-0.02810000069439411, 0.10559999942779541, -0.01590000092983246]], [0.0, 0.0, 0.0]]</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>[[[0.32580000162124634, 0.12020000070333481, -0.09300000220537186, 0.2687999904155731, -0.05620000138878822, -0.08980000019073486, -0.1590999960899353, 0.024000000208616257, 0.08500000089406967, 0.14589999616146088, -0.030500000342726707, 0.36800000071525574, -0.26429998874664307, 0.30399999022483826, 0.15039999783039093], [-0.1665000021457672, -0.023399999365210533, 0.41429999470710754, -0.4690000116825104, 0.05689999833703041, -0.18330000340938568, 0.14219999313354492, -0.1445000022649765, -0.17399999499320984, -0.2425999939441681, 0.13420000672340393, 0.06469999998807907, 0.296999990940094, -0.04280000180006027, -0.16339999437332153]], [[-0.061400000005960464, -0.03759999945759773, 0.3285999894142151, 0.0763000026345253, -0.7214000225067139, 0.3082999885082245, 0.18719999492168427, 0.2198999971151352, 0.04500000178813934, 0.2989000082015991, 0.2363000065088272, 0.7549999952316284, 0.22220000624656677, 0.13819999992847443, 0.3447999954223633], [0.3700999915599823, -0.24539999663829803, 0.04600000008940697, -0.13729999959468842, -0.305400013923645, 0.01209999993443489, -0.4059000015258789, -0.19769999384880066, -0.5770999789237976, 0.11479999870061874, 0.03229999914765358, 0.32749998569488525, 0.02930000051856041, 0.310699999332428, -0.2635999917984009], [0.3781999945640564, -0.3986999988555908, 0.2013999968767166, 0.2676999866962433, -0.002400000113993883, -0.28700000047683716, -0.004100000020116568, -0.060499999672174454, -0.18880000710487366, -0.5350000262260437, -0.2558000087738037, 0.03929999843239784, 0.054099999368190765, -0.4374000132083893, 0.27219998836517334], [0.47749999165534973, 0.4359000027179718, -0.6722000241279602, -0.4284999966621399, -0.3203999996185303, -0.3197000026702881, -0.15950000286102295, 0.11670000106096268, 0.32420000433921814, -0.37450000643730164, 0.5712000131607056, 0.8629999756813049, 0.7190999984741211, 0.2955000102519989, 0.48730000853538513], [-0.263700008392334, 0.030400000512599945, -0.6010000109672546, 0.17350000143051147, 0.3375000059604645, 0.24009999632835388, -0.044599998742341995, -0.0812000036239624, 0.3986999988555908, -0.20399999618530273, -0.7113999724388123, 0.09749999642372131, 0.4571000039577484, -0.44850000739097595, -0.17599999904632568], [0.008799999952316284, 0.22300000488758087, -0.6013000011444092, -0.661300003528595, -0.36340001225471497, -0.4275999963283539, 0.29600000381469727, 0.17739999294281006, -0.3725999891757965, -0.40869998931884766, -0.31929999589920044, 0.16750000417232513, 0.04879999905824661, 0.026799999177455902, -0.030799999833106995], [-0.2021999955177307, 0.13410000503063202, 0.06480000168085098, -0.31310001015663147, 0.29350000619888306, 0.15620000660419464, -0.20090000331401825, -0.4004000127315521, -0.35929998755455017, 0.1941000074148178, 0.3165000081062317, -0.02590000070631504, 0.05719999969005585, -0.4049000144004822, 0.10559999942779541], [-0.08489999920129776, -0.44859999418258667, -0.2784000039100647, -0.13779999315738678, 0.050700001418590546, 0.250900000333786, 0.6482999920845032, 0.25360000133514404, -0.5892999768257141, 0.28850001096725464, 0.4810999929904938, 0.33169999718666077, -0.17139999568462372, 0.383899986743927, 0.4056999981403351], [0.0885000005364418, -0.07500000298023224, -0.05180000141263008, -0.18199999630451202, -0.09629999846220016, -0.4404999911785126, 0.3806999921798706, -0.6409000158309937, 0.3050000071525574, 0.4438999891281128, -0.10679999738931656, -0.28519999980926514, 0.3206999897956848, -0.060499999672174454, 0.012600000016391277], [0.671500027179718, -0.1981000006198883, -0.2815999984741211, -0.7075999975204468, -0.6692000031471252, 0.4571000039577484, 0.10970000177621841, 0.2784999907016754, 0.13979999721050262, 0.16220000386238098, 0.4268999993801117, 0.15889999270439148, -0.0044999998062849045, 0.48429998755455017, 0.5976999998092651], [0.04280000180006027, -0.4066999852657318, 0.7594000101089478, -0.4366999864578247, 0.4659999907016754, 0.059300001710653305, 0.0697999969124794, 0.4180999994277954, -0.07150000333786011, 0.3707999885082245, -0.16220000386238098, 0.30889999866485596, -0.1370999962091446, 0.23800000548362732, -0.010999999940395355], [0.42399999499320984, 0.5268999934196472, 0.02539999969303608, 0.15620000660419464, -0.14650000631809235, 0.2506999969482422, -0.006800000090152025, 0.22460000216960907, -0.11620000004768372, 0.6207000017166138, -0.061900001019239426, 0.5019000172615051, -0.47049999237060547, 0.020099999383091927, 0.49900001287460327], [-0.025200000032782555, -0.4887999892234802, 0.7554000020027161, -0.12250000238418579, 0.718999981880188, 0.24050000309944153, 0.695900022983551, -0.4196000099182129, -0.06530000269412994, -0.28119999170303345, 0.03220000118017197, -0.249099999666214, -0.7404000163078308, -0.6216999888420105, -0.7372999787330627], [0.753000020980835, 0.3808000087738037, 0.1889999955892563, 0.25099998712539673, -0.16529999673366547, 0.30649998784065247, 0.2597000002861023, 0.361299991607666, -0.1738000065088272, 0.46140000224113464, 0.272599995136261, 0.027799999341368675, 0.3346000015735626, 0.39969998598098755, 0.011900000274181366], [0.1891999989748001, -0.3100000023841858, -0.18369999527931213, -0.3287000060081482, -0.32679998874664307, -0.011300000362098217, 0.16369999945163727, 0.7039999961853027, -0.13050000369548798, 0.6854000091552734, 0.51419997215271, 0.2418999969959259, -0.227400004863739, -0.24289999902248383, -0.14480000734329224]], [0.00989999994635582, 0.03180000185966492, -0.14749999344348907, 0.01850000023841858, 0.00559999980032444, -0.03009999915957451, 0.012500000186264515, -0.023000000044703484, 0.20469999313354492, -0.0013000000035390258, 0.003100000089034438, -0.02319999970495701, 0.07010000199079514, 0.008100000210106373, -0.009999999776482582], [[0.2754000127315521, 0.005900000222027302, -0.1949000060558319, -0.2896000146865845, -0.0019000000320374966], [0.07280000299215317, -0.08460000157356262, -0.15299999713897705, -0.1996999979019165, 0.16859999299049377], [0.20909999310970306, 0.4413999915122986, 0.15520000457763672, 0.5895000100135803, 0.4047999978065491], [-0.5049999952316284, 0.1940000057220459, -0.20110000669956207, -0.4837999939918518, -0.5889000296592712], [-0.24130000174045563, 0.0738999992609024, -0.07249999791383743, 0.35589998960494995, -0.17319999635219574], [-0.046799998730421066, 0.11789999902248383, 0.21580000221729279, -0.03869999945163727, -0.11550000309944153], [0.2199999988079071, 0.24770000576972961, 0.21570000052452087, 0.36329999566078186, 0.1356000006198883], [0.15600000321865082, 0.08699999749660492, 0.1599999964237213, 0.06800000369548798, -0.013399999588727951], [-0.2363000065088272, -0.2198999971151352, -0.18880000710487366, -0.27059999108314514, -0.07490000128746033], [0.29170000553131104, 0.296099990606308, -0.17569999396800995, -0.2093999981880188, -0.19280000030994415], [0.3986000120639801, 0.12409999966621399, 0.15639999508857727, 0.0284000001847744, 0.2784000039100647], [0.3319999873638153, -0.1678999960422516, -0.09969999641180038, -0.3027999997138977, -0.04650000110268593], [0.008100000210106373, -0.2827000021934509, 0.06920000165700912, -0.2232999950647354, 0.4616999924182892], [0.21289999783039093, -0.054099999368190765, -0.09160000085830688, -0.30140000581741333, 0.023600000888109207], [0.11299999803304672, -0.10869999974966049, 0.06960000097751617, -0.24940000474452972, -0.1656000018119812]], [[0.43549999594688416, 0.7437999844551086, 0.07639999687671661, 0.6276999711990356, 0.75], [0.33730000257492065, -0.7508999705314636, 0.5694000124931335, 0.32910001277923584, 0.5098999738693237], [-0.48739999532699585, 0.07699999958276749, 0.6323000192642212, 0.43070000410079956, -0.7156000137329102], [-0.991100013256073, -0.4104999899864197, -0.3386000096797943, 0.12809999287128448, 0.0026000000070780516], [0.29899999499320984, 0.07199999690055847, -0.6439999938011169, 1.4459999799728394, -0.4620000123977661]], [0.07639999687671661, -0.06210000067949295, -0.035100001841783524, -0.24150000512599945, 0.2037000060081482], [[0.3813999891281128, 0.05649999901652336, -0.19499999284744263], [0.4226999878883362, -0.03229999914765358, 0.18860000371932983], [0.16220000386238098, -0.093299999833107, 0.11909999698400497], [0.6935999989509583, -0.17219999432563782, 0.05939999967813492], [0.21570000052452087, 0.14959999918937683, -0.1500999927520752]], [-0.033900000154972076, -0.02800000086426735, 0.093299999833107]]</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>[0.42140340415518507]</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>[0.13207429411368177]</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>[0.7486331076943338]</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>[0.05738788372106437]</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>[-4.684792711137748]</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>[1.8605172220453088]</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>[0.3382337315545002]</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>[0.15202033383685756]</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>[0.9042370986143154]</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>[0.022711228053227714]</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>[-3.7092677218160546]</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>[1.5481597248159267]</t>
+        </is>
+      </c>
+      <c r="Q16" t="inlineStr">
+        <is>
+          <t>[-0.18418336339674135]</t>
+        </is>
+      </c>
+      <c r="R16" t="inlineStr">
+        <is>
+          <t>[0.12768543443988212]</t>
+        </is>
+      </c>
+      <c r="S16" t="inlineStr">
+        <is>
+          <t>[-0.19311310492165035]</t>
+        </is>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>[0.10053211559199388]</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>[-1.068981582266566]</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>[0.1978424960065574]</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>[-0.3928813545179084]</t>
+        </is>
+      </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>[0.14591911923644416]</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>[-0.2644404003357901]</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>[0.10405485902052114]</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>[-1.1643075624204573]</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>[0.19912576317150024]</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>[-1.0305852864537508]</t>
+        </is>
+      </c>
+      <c r="AD16" t="inlineStr">
+        <is>
+          <t>[0.17015486657274453]</t>
+        </is>
+      </c>
+      <c r="AE16" t="inlineStr">
+        <is>
+          <t>[-0.8142317064833662]</t>
+        </is>
+      </c>
+      <c r="AF16" t="inlineStr">
+        <is>
+          <t>[0.19535297609727112]</t>
+        </is>
+      </c>
+      <c r="AG16" t="inlineStr">
+        <is>
+          <t>[-3.6523878973632007]</t>
+        </is>
+      </c>
+      <c r="AH16" t="inlineStr">
+        <is>
+          <t>[0.3463700856666936]</t>
+        </is>
+      </c>
+      <c r="AI16" t="inlineStr">
+        <is>
+          <t>[-1.48286342399877]</t>
+        </is>
+      </c>
+      <c r="AJ16" t="inlineStr">
+        <is>
+          <t>[0.20346789363821854]</t>
+        </is>
+      </c>
+      <c r="AK16" t="inlineStr">
+        <is>
+          <t>[-0.8847347489737003]</t>
+        </is>
+      </c>
+      <c r="AL16" t="inlineStr">
+        <is>
+          <t>[0.200050784834821]</t>
+        </is>
+      </c>
+      <c r="AM16" t="inlineStr">
+        <is>
+          <t>[-3.5562602677023456]</t>
+        </is>
+      </c>
+      <c r="AN16" t="inlineStr">
+        <is>
+          <t>[0.3499538196419163]</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
           <t>model_20_5_0</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="B17" t="inlineStr">
         <is>
           <t>[20, 5]</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>[[[-0.04259999841451645, 0.029600000008940697, -0.07779999822378159, -0.005100000184029341, -0.04410000145435333, -0.04879999905824661, 0.02410000003874302, -0.08290000259876251, -0.048500001430511475, -0.09309999644756317, -0.053599998354911804, 0.0340999998152256, 0.01899999938905239, -0.04569999873638153, 0.06360000371932983, 0.0364999994635582, 0.09669999778270721, -0.010900000110268593, -0.0017000000225380063, 0.053700000047683716], [0.0625, 0.025100000202655792, -0.013000000268220901, -0.017400000244379044, -0.05829999968409538, 0.017000000923871994, -0.08060000091791153, 0.013899999670684338, 0.06469999998807907, -0.007400000002235174, -0.00019999999494757503, 0.02930000051856041, 0.08919999748468399, -0.005499999970197678, 0.018200000748038292, -0.07169999927282333, 0.0017999999690800905, 0.020500000566244125, -0.03720000013709068, 0.05310000106692314]], [[0.12449999898672104, -0.17069999873638153, 0.2513999938964844, -0.5200999975204468, 0.10419999808073044, -0.19740000367164612, 0.13899999856948853, -0.06710000336170197, 0.25200000405311584, -0.017999999225139618, 0.3012999892234802, -0.11860000342130661, 0.2249000072479248, -0.16189999878406525, -0.17730000615119934, -0.08980000019073486, 0.04859999939799309, 0.1281999945640564, -0.4478999972343445, 0.20900000631809235], [-0.2110999971628189, 0.1851000040769577, -0.10199999809265137, 0.05959999933838844, -0.4864000082015991, -0.07100000232458115, -0.01979999989271164, -0.1527000069618225, -0.06669999659061432, -0.13050000369548798, -0.31360000371932983, 0.16740000247955322, 0.5742999911308289, -0.1598999947309494, -0.0333000011742115, -0.024700000882148743, -0.09939999878406525, -0.0364999994635582, -0.10769999772310257, 0.337799996137619], [-0.18050000071525574, 0.0364999994635582, 0.17949999868869781, 0.1800999939441681, 0.20749999582767487, 0.0738999992609024, 0.03319999948143959, -0.08560000360012054, -0.18240000307559967, -0.17810000479221344, 0.16110000014305115, -0.04410000145435333, -0.03750000149011612, -0.029600000008940697, 0.1964000016450882, 0.5072000026702881, 0.4332999885082245, 0.15369999408721924, 0.02370000071823597, 0.49149999022483826], [0.09969999641180038, -0.14890000224113464, 0.053300000727176666, -0.1688999980688095, -0.11739999800920486, -0.1527000069618225, 0.23980000615119934, -0.21060000360012054, -0.38100001215934753, 0.12120000272989273, -0.28790000081062317, -0.08110000193119049, -0.2321999967098236, -0.25459998846054077, -0.5371999740600586, 0.32760000228881836, -0.02669999934732914, 0.03449999913573265, 0.16990000009536743, -0.05260000005364418], [0.2151000052690506, 0.2709999978542328, 0.11999999731779099, -0.028200000524520874, -0.4050999879837036, -0.09679999947547913, 0.02630000002682209, 0.36250001192092896, 0.03830000013113022, 0.2328999936580658, 0.27970001101493835, 0.1826999932527542, 0.1656000018119812, 0.23720000684261322, -0.19050000607967377, 0.14669999480247498, 0.3077999949455261, 0.3052999973297119, 0.21449999511241913, -0.1298000067472458], [0.11630000174045563, 0.13040000200271606, 0.18369999527931213, 0.19169999659061432, -0.2824999988079071, -0.08919999748468399, -0.22939999401569366, -0.5271000266075134, 0.1662999987602234, 0.12060000002384186, -0.07450000196695328, -0.15109999477863312, -0.13570000231266022, 0.026000000536441803, 0.17229999601840973, 0.18979999423027039, 0.1850000023841858, 0.04430000111460686, -0.3970000147819519, -0.3626999855041504], [0.32359999418258667, 0.21580000221729279, -0.2515000104904175, 0.03849999979138374, 0.1517000049352646, 0.08229999989271164, -0.02879999950528145, -0.16030000150203705, 0.6230000257492065, 0.1436000019311905, -0.19429999589920044, -0.07240000367164612, -0.05920000001788139, -0.046300001442432404, -0.10930000245571136, 0.1915999948978424, -0.15520000457763672, 0.1680999994277954, 0.24619999527931213, 0.3296999931335449], [0.15309999883174896, -0.020899999886751175, 0.06440000236034393, 0.2003999948501587, 0.1509000062942505, -0.16189999878406525, -0.11089999973773956, -0.09830000251531601, 0.003800000064074993, -0.31279999017715454, 0.15119999647140503, -0.1428000032901764, 0.31459999084472656, -0.5428000092506409, 0.053300000727176666, -0.12919999659061432, 0.06909999996423721, 0.23829999566078186, 0.38370001316070557, -0.31290000677108765], [-0.0632999986410141, 0.14380000531673431, -0.33489999175071716, -0.08250000327825546, -0.002199999988079071, 0.21209999918937683, -0.13040000200271606, -0.3102000057697296, -0.08619999885559082, 0.21140000224113464, 0.25450000166893005, -0.14169999957084656, 0.013199999928474426, -0.06949999928474426, -0.26330000162124634, -0.3490999937057495, 0.4966999888420105, -0.3046000003814697, 0.12080000340938568, 0.10480000078678131], [-0.17710000276565552, 0.12030000239610672, 0.24310000240802765, -0.17339999973773956, 0.11779999732971191, 0.05009999871253967, 0.3208000063896179, -0.26429998874664307, 0.2526000142097473, -0.16599999368190765, -0.16689999401569366, 0.6373999714851379, -0.1282999962568283, -0.01730000041425228, 0.02160000056028366, -0.15000000596046448, 0.24199999868869781, -0.026100000366568565, 0.16419999301433563, -0.15649999678134918], [0.11490000039339066, 0.16779999434947968, -0.05299999937415123, 0.059300001710653305, 0.08940000087022781, 0.30979999899864197, 0.6363999843597412, -0.05979999899864197, -0.09629999846220016, -0.08959999680519104, -0.19480000436306, -0.40230000019073486, 0.24650000035762787, 0.2556000053882599, 0.05889999866485596, -0.11670000106096268, 0.09589999914169312, 0.19040000438690186, -0.09300000220537186, -0.15929999947547913], [0.024900000542402267, -0.3443000018596649, -0.007400000002235174, 0.5950000286102295, -0.13199999928474426, 0.042100001126527786, 0.351500004529953, 0.21960000693798065, 0.2743000090122223, 0.13590000569820404, 0.0722000002861023, 0.09769999980926514, -0.05169999971985817, -0.28679999709129333, -0.1776999980211258, -0.04129999876022339, 0.1525000035762787, -0.19020000100135803, -0.21799999475479126, 0.04729999974370003], [0.6259999871253967, -0.05169999971985817, 0.12950000166893005, 0.14579999446868896, 0.26249998807907104, -0.23000000417232513, -0.13940000534057617, -9.999999747378752e-05, -0.1860000044107437, -0.1168999969959259, -0.2535000145435333, 0.17919999361038208, 0.19920000433921814, 0.260699987411499, -0.06560000032186508, -0.08190000057220459, 0.19930000603199005, -0.3215999901294708, -0.06629999727010727, 0.12349999696016312], [0.4440000057220459, -0.23309999704360962, 0.019600000232458115, -0.12049999833106995, -0.4196999967098236, 0.1988999992609024, 0.17350000143051147, -0.19020000100135803, -0.15950000286102295, -0.010700000450015068, 0.18979999423027039, 0.0908999964594841, -0.20329999923706055, -0.10459999740123749, 0.44609999656677246, -0.16339999437332153, -0.10419999808073044, 0.025699999183416367, 0.17759999632835388, 0.24650000035762787], [0.08049999922513962, 0.04439999908208847, 0.29670000076293945, -0.07180000096559525, -0.04520000144839287, 0.5095999836921692, -0.039400000125169754, -0.035599999129772186, 0.10010000318288803, -0.13660000264644623, 0.22759999334812164, -0.018300000578165054, 0.24770000576972961, -0.009600000455975533, -0.15119999647140503, 0.3727000057697296, -0.22949999570846558, -0.48989999294281006, 0.10589999705553055, -0.16089999675750732], [-0.09269999712705612, 0.028300000354647636, 0.15469999611377716, -0.07670000195503235, -0.32030001282691956, -0.28299999237060547, 0.04470000043511391, 0.15199999511241913, 0.27379998564720154, -0.46650001406669617, -0.1088000014424324, -0.4250999987125397, -0.25220000743865967, 0.14480000734329224, -0.03350000083446503, -0.094200000166893, 0.16750000417232513, -0.28929999470710754, 0.22750000655651093, 0.09870000183582306], [0.2101999968290329, 0.5633999705314636, -0.1379999965429306, 0.049400001764297485, -0.012500000186264515, 0.10260000079870224, 0.012900000438094139, 0.16699999570846558, -0.15399999916553497, -0.39649999141693115, 0.1348000019788742, 0.12479999661445618, -0.3434999883174896, -0.26840001344680786, -0.16920000314712524, -0.05139999836683273, -0.10140000283718109, 0.03180000185966492, -0.36090001463890076, 0.026900000870227814], [0.027699999511241913, 0.3483999967575073, 0.15839999914169312, -0.188400000333786, 0.0892999991774559, -0.1200999990105629, 0.12939999997615814, 0.2802000045776367, -0.02800000086426735, 0.43130001425743103, -0.20999999344348907, -0.12800000607967377, 0.02250000089406967, -0.41519999504089355, 0.39649999141693115, 0.05460000038146973, 0.10920000076293945, -0.32659998536109924, 0.01940000057220459, -0.014000000432133675], [0.07450000196695328, -0.16249999403953552, -0.6545000076293945, -0.23829999566078186, -0.028699999675154686, -0.18160000443458557, 0.15000000596046448, 0.04179999977350235, 0.0786999985575676, -0.20839999616146088, 0.07540000230073929, 0.12720000743865967, 0.10339999943971634, -0.007499999832361937, 0.20319999754428864, 0.41119998693466187, 0.17659999430179596, -0.17599999904632568, -0.08160000294446945, -0.25200000405311584], [0.07500000298023224, -0.2623000144958496, 0.009600000455975533, -0.2231999933719635, -0.08990000188350677, 0.49140000343322754, -0.3379000127315521, 0.298799991607666, 0.06970000267028809, -0.11670000106096268, -0.4359000027179718, -0.01600000075995922, -0.026499999687075615, -0.1777999997138977, -0.01979999989271164, -0.01940000057220459, 0.3452000021934509, 0.2117999941110611, -0.11420000344514847, -0.060499999672174454]], [0.0, 0.0, 0.0, 0.0, 0.0, 0.0, 0.0, 0.0, 0.0, 0.0, 0.0, 0.0, 0.0, 0.0, 0.0, 0.0, 0.0, 0.0, 0.0, 0.0], [[-0.04259999841451645, 0.029600000008940697, -0.07779999822378159, -0.005100000184029341, -0.04410000145435333], [-0.04879999905824661, 0.02410000003874302, -0.08290000259876251, -0.048500001430511475, -0.09309999644756317], [-0.053599998354911804, 0.0340999998152256, 0.01899999938905239, -0.04569999873638153, 0.06360000371932983], [0.0364999994635582, 0.09669999778270721, -0.010900000110268593, -0.0017000000225380063, 0.053700000047683716], [0.0625, 0.025100000202655792, -0.013000000268220901, -0.017400000244379044, -0.05829999968409538], [0.017000000923871994, -0.08060000091791153, 0.013899999670684338, 0.06469999998807907, -0.007400000002235174], [-0.00019999999494757503, 0.02930000051856041, 0.08919999748468399, -0.005499999970197678, 0.018200000748038292], [-0.07169999927282333, 0.0017999999690800905, 0.020500000566244125, -0.03720000013709068, 0.05310000106692314], [0.08250000327825546, -0.11060000211000443, -0.053199999034404755, 0.0940999984741211, -0.09839999675750732], [-0.0729999989271164, 0.10050000250339508, -0.1046999990940094, 0.008999999612569809, -0.027699999511241913], [0.05829999968409538, 0.022199999541044235, -0.0681999996304512, -0.01940000057220459, -0.03229999914765358], [0.015799999237060547, 0.05689999833703041, -0.10809999704360962, 0.0026000000070780516, -0.10679999738931656], [0.03830000013113022, -0.10700000077486038, -0.01209999993443489, -0.016100000590085983, -0.03929999843239784], [-0.10050000250339508, -0.024800000712275505, -0.023900000378489494, 0.01140000019222498, -0.04430000111460686], [0.04039999842643738, 0.01549999974668026, -0.025800000876188278, 0.06639999896287918, 0.06449999660253525], [-0.034299999475479126, -0.008299999870359898, -0.010900000110268593, 0.0031999999191612005, -0.03060000017285347], [-0.07109999656677246, -0.015300000086426735, 0.027300000190734863, -0.003800000064074993, -0.05510000139474869], [-0.03660000115633011, -0.08969999849796295, 0.045899998396635056, -0.014999999664723873, -0.061799999326467514], [0.012900000438094139, 0.033799998462200165, -0.09200000017881393, -0.00860000029206276, -0.014399999752640724], [-0.060499999672174454, -0.0471000000834465, 0.02539999969303608, -0.07370000332593918, 0.019999999552965164]], [[-0.15800000727176666, 0.5634999871253967, -0.3668000102043152, 0.6679999828338623, 0.27709999680519104], [-0.14239999651908875, -0.7843000292778015, 0.01510000042617321, 0.5956000089645386, 0.09809999912977219], [0.49619999527931213, 0.2084999978542328, 0.6381999850273132, 0.43290001153945923, -0.3400999903678894], [0.5102999806404114, -0.12060000002384186, -0.6754999756813049, 0.0649000033736229, -0.5142999887466431], [-0.6694999933242798, 0.09640000015497208, 0.0414000004529953, 0.08609999716281891, -0.7303000092506409]], [0.0, 0.0, 0.0, 0.0, 0.0], [[-0.04259999841451645, 0.029600000008940697, -0.07779999822378159], [-0.005100000184029341, -0.04410000145435333, -0.04879999905824661], [0.02410000003874302, -0.08290000259876251, -0.048500001430511475], [-0.09309999644756317, -0.053599998354911804, 0.0340999998152256], [0.01899999938905239, -0.04569999873638153, 0.06360000371932983]], [0.0, 0.0, 0.0]]</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>[[[-0.10729999840259552, 0.05620000138878822, -0.32420000433921814, -0.08070000261068344, 0.12630000710487366, -0.5210000276565552, -0.2054000049829483, -0.23000000417232513, -0.07020000368356705, -0.2727000117301941, 0.08320000022649765, 0.30230000615119934, 0.17749999463558197, -0.3752000033855438, 0.1784999966621399, 0.008299999870359898, 0.25839999318122864, 0.04879999905824661, 0.1005999967455864, 0.16840000450611115], [0.3111000061035156, 0.2371000051498413, 0.038100000470876694, -0.09929999709129333, -0.29319998621940613, 0.39820000529289246, -0.3287000060081482, 0.09839999675750732, 0.2903999984264374, 0.2994000017642975, 0.3700000047683716, 0.0877000018954277, 0.23409999907016754, 0.18170000612735748, -0.041200000792741776, -0.27810001373291016, -0.2434999942779541, 0.44530001282691956, 0.2847999930381775, -0.09700000286102295]], [[0.1712999939918518, -0.21220000088214874, 0.16140000522136688, -0.5680999755859375, 0.10159999877214432, -0.27160000801086426, -0.031599998474121094, -0.35120001435279846, 0.21459999680519104, -0.28949999809265137, 0.4268999993801117, 0.14740000665187836, 0.5282999873161316, -0.4715999960899353, 0.008700000122189522, -0.36090001463890076, 0.09889999777078629, 0.22470000386238098, -0.14000000059604645, 0.5503000020980835], [-0.1451999992132187, 0.18080000579357147, -0.04259999841451645, 0.1542000025510788, -0.40070000290870667, -0.11420000344514847, -0.15109999477863312, 0.049800001084804535, -0.06520000100135803, -0.2590999901294708, -0.23090000450611115, 0.33219999074935913, 0.9293000102043152, -0.13860000669956207, -0.07689999788999557, -0.2409999966621399, -0.13819999992847443, 0.09300000220537186, 0.17659999430179596, 0.40720000863075256], [-0.1753000020980835, 0.07989999651908875, 0.27549999952316284, 0.1289999932050705, 0.0860000029206276, 0.06340000033378601, 0.24169999361038208, -0.5329999923706055, -0.12349999696016312, -0.10769999772310257, 0.2159000039100647, -0.34279999136924744, -0.13670000433921814, -0.35269999504089355, 0.46059998869895935, 0.6157000064849854, 0.51910001039505, 0.20999999344348907, -0.10840000212192535, 0.6327999830245972], [0.07639999687671661, -0.18359999358654022, 0.08609999716281891, -0.27390000224113464, -0.08100000023841858, -0.14669999480247498, 0.34929999709129333, -0.3968000113964081, -0.40689998865127563, 0.2565999925136566, -0.39579999446868896, -0.33070001006126404, -0.4936999976634979, -0.3725000023841858, -0.5174000263214111, 0.5259000062942505, 0.1006999984383583, -0.061000000685453415, -0.04479999840259552, 0.00039999998989515007], [0.36730000376701355, -0.024000000208616257, 0.29760000109672546, 0.2847999930381775, -0.5996999740600586, -0.23420000076293945, -0.3458999991416931, 0.5881999731063843, -0.10719999670982361, 0.1535000056028366, 0.44609999656677246, 0.3668000102043152, 0.030500000342726707, 0.535099983215332, -0.59170001745224, 0.23229999840259552, -0.060499999672174454, 0.5368000268936157, 0.29589998722076416, -0.34130001068115234], [-0.05380000174045563, 0.4203000068664551, 0.15230000019073486, 0.15489999949932098, -0.5784000158309937, -0.34200000762939453, -0.3919000029563904, -0.9922000169754028, 0.5584999918937683, -0.3813000023365021, 0.38589999079704285, 0.46799999475479126, 0.3720000088214874, -0.29350000619888306, 0.4187999963760376, -0.42100000381469727, 0.22040000557899475, 0.5414000153541565, 0.05609999969601631, -0.09889999777078629], [0.20350000262260437, 0.310699999332428, -0.2662999927997589, 0.07670000195503235, 0.1826999932527542, 0.1851000040769577, 0.12060000002384186, -0.1446000039577484, 0.6855000257492065, 0.24089999496936798, -0.09040000289678574, -0.18729999661445618, -0.5109000205993652, 0.022199999541044235, -0.251800000667572, 0.5848000049591064, -0.09120000153779984, 0.06080000102519989, -0.2425999939441681, 0.11879999935626984], [0.1754000037908554, -0.25850000977516174, 0.4092000126838684, 0.5069000124931335, -0.3427000045776367, -0.5968000292778015, -0.6589000225067139, -0.5146999955177307, 0.001500000013038516, -0.8015000224113464, 0.6291999816894531, 0.2955999970436096, 0.20919999480247498, -0.8744999766349792, 0.08020000159740448, -0.2809999883174896, 0.057500001043081284, 0.6862000226974487, 0.7890999913215637, -0.052299998700618744], [-0.1031000018119812, 0.09109999984502792, -0.4196999967098236, -0.17100000381469727, 0.08510000258684158, 0.12639999389648438, -0.15119999647140503, -0.5336999893188477, -0.11729999631643295, -0.044599998742341995, 0.17870000004768372, -0.05860000103712082, 0.22190000116825104, -0.3531000018119812, -0.03359999880194664, -0.5440999865531921, 0.5767999887466431, -0.24809999763965607, 0.3986999988555908, 0.41499999165534973], [-0.26339998841285706, 0.17030000686645508, 0.30140000581741333, -0.15620000660419464, -0.19280000030994415, -0.1469999998807907, 0.12860000133514404, -0.6344000101089478, 0.2637999951839447, -0.5742999911308289, 0.09139999747276306, 1.170799970626831, -0.024000000208616257, -0.26739999651908875, 0.22429999709129333, -0.5846999883651733, 0.29840001463890076, 0.3043000102043152, 0.32170000672340393, 0.08380000293254852], [-0.33719998598098755, -0.009399999864399433, -0.42739999294281006, -0.30160000920295715, 0.24770000576972961, 0.328000009059906, 0.9815999865531921, -0.23350000381469727, -0.4235999882221222, -0.20319999754428864, -0.5889000296592712, -0.6013000011444092, -0.02290000021457672, -0.1559000015258789, 0.4196999967098236, 0.18930000066757202, 0.6467000246047974, -0.20399999618530273, -0.3564000129699707, 0.0885000005364418], [0.0877000018954277, -0.5134000182151794, -0.18410000205039978, 0.5496000051498413, 0.03400000184774399, 0.03629999980330467, 0.25619998574256897, 0.36730000376701355, 0.1809999942779541, 0.015599999576807022, -0.21490000188350677, 0.19110000133514404, 0.3179999887943268, -0.26010000705718994, -0.2542000114917755, -0.22750000655651093, 0.17669999599456787, -0.28130000829696655, -0.005900000222027302, 0.15770000219345093], [0.7153000235557556, -0.11479999870061874, -0.12880000472068787, 0.016300000250339508, 0.3343000113964081, -0.19709999859333038, -0.24060000479221344, -0.026100000366568565, -0.20679999887943268, -0.22769999504089355, -0.5514000058174133, 0.4406000077724457, 0.5379999876022339, 0.18209999799728394, 0.009100000374019146, -0.3264999985694885, 0.25769999623298645, -0.5285999774932861, 0.04349999874830246, 0.30649998784065247], [0.5328999757766724, -0.2476000040769577, 0.1973000019788742, -0.2152000069618225, -0.7200000286102295, -0.13009999692440033, 0.0737999975681305, -0.7092999815940857, -0.14839999377727509, -0.3596999943256378, 0.27730000019073486, 0.11879999935626984, -0.2087000012397766, -0.5543000102043152, 0.6395999789237976, -0.2215999960899353, 0.12280000001192093, 0.24050000309944153, 0.2766000032424927, 0.641700029373169], [0.07240000367164612, 0.2046000063419342, 0.11540000140666962, 0.024800000712275505, 0.15850000083446503, 0.8246999979019165, 0.1437000036239624, 0.33399999141693115, 0.22190000116825104, 0.0803999975323677, 0.289900004863739, -0.010700000450015068, 0.43299999833106995, 0.23420000076293945, -0.13840000331401825, 0.3093000054359436, -0.3700000047683716, -0.6111999750137329, -0.0038999998942017555, -0.48019999265670776], [-0.20440000295639038, 0.08869999647140503, 0.3337000012397766, 0.019200000911951065, -0.36660000681877136, -0.24330000579357147, 0.10369999706745148, 0.3874000012874603, 0.2879999876022339, -0.23240000009536743, 0.020500000566244125, -0.6062999963760376, -0.7355999946594238, 0.4327000081539154, -0.23720000684261322, 0.23240000009536743, 0.1307000070810318, -0.2621999979019165, -0.02630000002682209, -0.2085999995470047], [0.1517000049352646, 0.542900025844574, -0.09049999713897705, 0.2964000105857849, 0.10890000313520432, 0.3418999910354614, -0.025200000032782555, 0.7303000092506409, -0.14820000529289246, -0.03750000149011612, 0.030500000342726707, 0.15209999680519104, -0.3734000027179718, 0.3917999863624573, -0.6310999989509583, 0.04879999905824661, -0.5288000106811523, -0.15029999613761902, -0.3700999915599823, -0.7028999924659729], [-0.5, 0.23970000445842743, -0.16359999775886536, -0.579800009727478, 0.19830000400543213, -0.10159999877214432, 0.40939998626708984, 0.15489999949932098, -0.35589998960494995, 0.4147000014781952, -0.5526999831199646, -0.4124999940395355, -0.23659999668598175, -0.8616999983787537, 0.7680000066757202, 0.23569999635219574, 0.7416999936103821, -0.6812000274658203, -0.21379999816417694, 0.24150000512599945], [-0.2167000025510788, -0.33640000224113464, -0.7773000001907349, -0.42910000681877136, 0.030300000682473183, -0.16210000216960907, 0.39910000562667847, 0.02969999983906746, -0.17870000004768372, -0.3021000027656555, -0.1793999969959259, -0.04670000076293945, -0.016300000250339508, -0.32019999623298645, 0.4474000036716461, 0.629800021648407, 0.5516999959945679, -0.48019999265670776, -0.35569998621940613, -0.12349999696016312], [0.08630000054836273, -0.26350000500679016, -0.15080000460147858, -0.07970000058412552, 0.09059999883174896, 0.6089000105857849, -0.11670000106096268, 0.6764000058174133, 0.09430000185966492, 0.004399999976158142, -0.3328999876976013, -0.20190000534057617, 0.3476000130176544, 0.06040000170469284, -0.07500000298023224, -0.06930000334978104, 0.13449999690055847, 0.20630000531673431, 0.05299999937415123, -0.29919999837875366]], [-0.20000000298023224, -0.2506999969482422, 0.1379999965429306, 0.2939999997615814, -0.12790000438690186, -0.1306000053882599, 0.1362999975681305, -0.1006999984383583, -0.04729999974370003, -0.04280000180006027, 0.36090001463890076, -0.10949999839067459, -0.19670000672340393, 0.030300000682473183, -0.15309999883174896, 0.22300000488758087, -0.0917000025510788, 0.334199994802475, 0.20479999482631683, -0.12919999659061432], [[-0.026599999517202377, -0.12960000336170197, -0.29260000586509705, 0.2029999941587448, -0.08160000294446945], [-0.14169999957084656, -0.018699999898672104, -0.13169999420642853, 0.01140000019222498, -0.3718999922275543], [0.02710000053048134, 0.2662000060081482, 0.271699994802475, -0.17059999704360962, -0.1851000040769577], [0.20630000531673431, 0.1354999989271164, -0.025800000876188278, -0.2151000052690506, -0.0940999984741211], [-0.29829999804496765, -0.08169999718666077, -0.18569999933242798, 0.08479999750852585, -0.05810000002384186], [-0.2524000108242035, -0.3343000113964081, -0.004399999976158142, 0.32359999418258667, -0.4187999963760376], [-0.05689999833703041, 0.11240000277757645, 0.3111000061035156, 0.01889999955892563, 0.1509000062942505], [-0.3122999966144562, 0.016300000250339508, 0.3935999870300293, 0.0640999972820282, -0.2371000051498413], [0.10220000147819519, -0.16830000281333923, -0.15549999475479126, 0.10620000213384628, -0.37540000677108765], [-0.40610000491142273, -0.04919999837875366, -0.05009999871253967, 0.29989999532699585, -0.30250000953674316], [0.33489999175071716, -0.03849999979138374, -0.1137000024318695, -0.5199000239372253, -0.23350000381469727], [0.10429999977350235, -0.03709999844431877, -0.38929998874664307, 0.18930000066757202, -0.1972000002861023], [0.26269999146461487, -0.2150000035762787, -0.23759999871253967, 0.1696999967098236, -0.000699999975040555], [-0.39820000529289246, 0.02850000001490116, 0.2522999942302704, 0.07970000058412552, -0.8810999989509583], [0.3310999870300293, 0.0737999975681305, 0.13850000500679016, 0.3319000005722046, 0.32420000433921814], [-0.22669999301433563, 0.14499999582767487, 0.18790000677108765, -0.057999998331069946, 0.059700001031160355], [-0.14339999854564667, -0.14239999651908875, -0.11940000206232071, 0.3813000023365021, 0.40459999442100525], [0.2623000144958496, -0.040300000458955765, 0.14480000734329224, -0.42829999327659607, -0.035999998450279236], [0.3677999973297119, 0.09120000153779984, -0.00019999999494757503, -0.3352999985218048, 0.08649999648332596], [-0.120899997651577, -0.12020000070333481, -0.30230000615119934, 0.44769999384880066, 0.8001999855041504]], [[-0.6317999958992004, 0.38040000200271606, -0.2906000018119812, 1.0273000001907349, 0.11959999799728394], [-0.1404000073671341, -0.7364000082015991, 0.34130001068115234, 0.3716999888420105, -0.21969999372959137], [0.40689998865127563, 0.32280001044273376, 1.0943000316619873, 0.3197999894618988, -0.5519000291824341], [0.510699987411499, -0.10809999704360962, -1.0192999839782715, -0.1867000013589859, -0.6947000026702881], [-0.44670000672340393, 0.10369999706745148, 0.49000000953674316, -0.2565999925136566, -1.1019999980926514]], [0.04390000179409981, 0.1378999948501587, 0.09319999814033508, -0.21080000698566437, -0.17790000140666962], [[0.3000999987125397, 0.08309999853372574, -0.023800000548362732], [-0.030700000002980232, -0.22990000247955322, -0.04179999977350235], [0.2985999882221222, -0.26409998536109924, -0.02759999968111515], [-0.43869999051094055, -0.07880000025033951, 0.041600000113248825], [0.40869998931884766, -0.1623000055551529, 0.004699999932199717]], [-0.1136000007390976, 0.1273999959230423, 0.05649999901652336]]</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>[0.925750126022297]</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>[0.0169487683889954]</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>[0.49522986827265114]</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>[0.11524067214949796]</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>[0.7811854834954692]</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>[0.07161354812332617]</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>[0.8215541081560869]</t>
-        </is>
-      </c>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>[0.04099242488386449]</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>[0.6905779949264237]</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>[0.0733828405387421]</t>
-        </is>
-      </c>
-      <c r="O10" t="inlineStr">
-        <is>
-          <t>[-1.8867503482902044]</t>
-        </is>
-      </c>
-      <c r="P10" t="inlineStr">
-        <is>
-          <t>[0.9490117973368873]</t>
-        </is>
-      </c>
-      <c r="Q10" t="inlineStr">
-        <is>
-          <t>[0.7440617617263121]</t>
-        </is>
-      </c>
-      <c r="R10" t="inlineStr">
-        <is>
-          <t>[0.027596727123420275]</t>
-        </is>
-      </c>
-      <c r="S10" t="inlineStr">
-        <is>
-          <t>[-0.6009512118057116]</t>
-        </is>
-      </c>
-      <c r="T10" t="inlineStr">
-        <is>
-          <t>[0.1348966930448422]</t>
-        </is>
-      </c>
-      <c r="U10" t="inlineStr">
-        <is>
-          <t>[-1.4774643974451083]</t>
-        </is>
-      </c>
-      <c r="V10" t="inlineStr">
-        <is>
-          <t>[0.23690290158163993]</t>
-        </is>
-      </c>
-      <c r="W10" t="inlineStr">
-        <is>
-          <t>[0.6203647380490589]</t>
-        </is>
-      </c>
-      <c r="X10" t="inlineStr">
-        <is>
-          <t>[0.03977082676517791]</t>
-        </is>
-      </c>
-      <c r="Y10" t="inlineStr">
-        <is>
-          <t>[-0.6686689341873258]</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>[0.13732012252429984]</t>
-        </is>
-      </c>
-      <c r="AA10" t="inlineStr">
-        <is>
-          <t>[-3.070707608953862]</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>[0.3745229067048373]</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>[-2.0941735215761583]</t>
-        </is>
-      </c>
-      <c r="AD10" t="inlineStr">
-        <is>
-          <t>[0.25927927589595573]</t>
-        </is>
-      </c>
-      <c r="AE10" t="inlineStr">
-        <is>
-          <t>[-2.8925373546241366]</t>
-        </is>
-      </c>
-      <c r="AF10" t="inlineStr">
-        <is>
-          <t>[0.4191409256481296]</t>
-        </is>
-      </c>
-      <c r="AG10" t="inlineStr">
-        <is>
-          <t>[-2.4017905442629495]</t>
-        </is>
-      </c>
-      <c r="AH10" t="inlineStr">
-        <is>
-          <t>[0.253263164686743]</t>
-        </is>
-      </c>
-      <c r="AI10" t="inlineStr">
-        <is>
-          <t>[-2.3320032650283737]</t>
-        </is>
-      </c>
-      <c r="AJ10" t="inlineStr">
-        <is>
-          <t>[0.2730539583361819]</t>
-        </is>
-      </c>
-      <c r="AK10" t="inlineStr">
-        <is>
-          <t>[-2.858492820888045]</t>
-        </is>
-      </c>
-      <c r="AL10" t="inlineStr">
-        <is>
-          <t>[0.40955074315815404]</t>
-        </is>
-      </c>
-      <c r="AM10" t="inlineStr">
-        <is>
-          <t>[-2.710250420847747]</t>
-        </is>
-      </c>
-      <c r="AN10" t="inlineStr">
-        <is>
-          <t>[0.2849741301671664]</t>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>[[[0.03319999948143959, 0.0027000000700354576, -0.016699999570846558, -0.0017999999690800905, 0.12229999899864197, -0.014700000174343586, -0.04670000076293945, -0.05999999865889549, -0.0005000000237487257, -0.16120000183582306, -0.057500001043081284, -0.03150000050663948, 0.04129999876022339, 0.027000000700354576, -0.054999999701976776, 0.0066999997943639755, 0.0007999999797903001, 0.059300001710653305, 0.00139999995008111, -0.021199999377131462], [0.06199999898672104, 0.042500000447034836, 0.11349999904632568, 0.019600000232458115, 0.05620000138878822, -0.0026000000070780516, -0.029600000008940697, 0.05090000107884407, -0.008500000461935997, 0.039400000125169754, 0.014999999664723873, 0.01720000058412552, 0.03959999978542328, 0.014700000174343586, 0.010400000028312206, 0.060499999672174454, -0.015599999576807022, -0.013299999758601189, 0.07540000230073929, -0.02539999969303608]], [[-0.10119999945163727, 0.0031999999191612005, 0.19930000603199005, 0.1632000058889389, -0.12639999389648438, 0.30730000138282776, 0.14180000126361847, -0.4214000105857849, 0.07240000367164612, 0.062300000339746475, -0.5870000123977661, -0.23000000417232513, 0.12250000238418579, -0.13619999587535858, 0.009800000116229057, -0.15610000491142273, -0.01640000008046627, -0.026499999687075615, 0.28679999709129333, -0.2599000036716461], [0.2101999968290329, 0.3488999903202057, 0.148499995470047, -0.3138999938964844, -0.12129999697208405, -0.47690001130104065, -0.11550000309944153, -0.05909999832510948, -0.07050000131130219, 0.2583000063896179, -0.13089999556541443, 0.10480000078678131, 0.424699991941452, -0.17059999704360962, 0.10450000315904617, 0.23000000417232513, -0.02969999983906746, 0.030500000342726707, 0.27379998564720154, 0.06859999895095825], [0.10270000249147415, 0.21220000088214874, -0.2709999978542328, 0.20399999618530273, -0.11010000109672546, -0.047200001776218414, 0.18790000677108765, 0.1535000056028366, 0.3682999908924103, 0.2685999870300293, -0.2296999990940094, 0.013100000098347664, -0.14790000021457672, -0.11890000104904175, 0.3734999895095825, 0.06759999692440033, 0.48730000853538513, -0.07919999957084656, -0.25929999351501465, 0.06560000032186508], [0.30809998512268066, -0.15559999644756317, 0.32749998569488525, 0.04899999871850014, -0.07270000129938126, 0.014700000174343586, 0.2320999950170517, -0.06279999762773514, -0.30410000681877136, 0.05730000138282776, -0.3353999853134155, 0.3806999921798706, -0.24719999730587006, 0.12049999833106995, -0.2809999883174896, 0.15160000324249268, 0.11240000277757645, -0.12970000505447388, -0.1446000039577484, 0.3562000095844269], [-0.155799999833107, -0.2745000123977661, -0.07259999960660934, 0.03889999911189079, 0.06379999965429306, 0.1738000065088272, -0.3418000042438507, 0.40400001406669617, -0.2529999911785126, 0.02710000053048134, -0.16769999265670776, -0.0430000014603138, 0.08030000329017639, -0.45350000262260437, -0.0851999968290329, -0.004699999932199717, 0.3411000072956085, 0.1476999968290329, 0.2628999948501587, 0.24050000309944153], [0.05119999870657921, 0.05079999938607216, 0.3091000020503998, -0.32100000977516174, -0.03359999880194664, 0.3628999888896942, 0.2921999990940094, 0.29159998893737793, -0.04839999973773956, -0.32030001282691956, 0.05770000070333481, 0.2249000072479248, 0.14079999923706055, -0.1289999932050705, 0.5180000066757202, -0.1225999966263771, -0.04670000076293945, -0.10819999873638153, 0.01269999984651804, -0.016200000420212746], [0.3280999958515167, -0.18809999525547028, 0.10559999942779541, -0.3433000147342682, 0.19009999930858612, -0.04479999840259552, 0.04580000042915344, -0.23319999873638153, 0.1941000074148178, 0.07609999924898148, 0.06909999996423721, -0.3772999942302704, 0.029600000008940697, -0.1453000009059906, -0.014499999582767487, -0.4564000070095062, 0.08780000358819962, 0.155799999833107, -0.1834000051021576, 0.3828999996185303], [-0.08089999854564667, 0.13830000162124634, 0.11990000307559967, 0.062300000339746475, -0.004399999976158142, 0.23649999499320984, 0.15279999375343323, -0.026499999687075615, 0.0706000030040741, 0.6021999716758728, 0.4106999933719635, 0.1712999939918518, -0.28790000081062317, -0.1477999985218048, -0.03550000116229057, -0.1412999927997589, -0.12150000035762787, -0.04809999838471413, 0.38960000872612, 0.1251000016927719], [-0.10350000113248825, -0.13680000603199005, 0.2736999988555908, 0.0812000036239624, 0.14059999585151672, -0.12549999356269836, -0.351500004529953, 0.22110000252723694, 0.004900000058114529, 0.3253999948501587, -0.21940000355243683, -0.06430000066757202, -0.07930000126361847, -0.12120000272989273, 0.19349999725818634, -0.11100000143051147, -0.42879998683929443, -0.3594000041484833, -0.365200012922287, -0.07509999722242355], [0.0210999995470047, 0.05429999902844429, -0.14980000257492065, -0.35690000653266907, -0.07620000094175339, -0.0203000009059906, -0.23929999768733978, -0.16179999709129333, 0.028999999165534973, -0.12860000133514404, -0.21930000185966492, 0.14589999616146088, -0.649399995803833, -0.18070000410079956, 0.18619999289512634, 0.09390000253915787, -0.19580000638961792, 0.35269999504089355, 0.05469999834895134, -0.08229999989271164], [0.2750000059604645, 0.04280000180006027, -0.4293999969959259, 0.1257999986410141, 0.24940000474452972, 0.2281000018119812, -0.08089999854564667, 0.04610000178217888, -0.009200000204145908, 0.0010000000474974513, -0.21979999542236328, -0.02930000051856041, 0.10570000112056732, 0.32409998774528503, 0.23170000314712524, 0.04170000180602074, -0.3596999943256378, -0.09109999984502792, 0.28299999237060547, 0.4009000062942505], [0.03229999914765358, 0.10270000249147415, -0.1429000049829483, 0.18950000405311584, 0.2994999885559082, -0.0763000026345253, 0.5139999985694885, 0.094200000166893, -0.2912999987602234, 0.06019999831914902, -0.03920000046491623, -0.12839999794960022, 0.048500001430511475, -0.40220001339912415, -0.04399999976158142, 0.1404999941587448, -0.3197000026702881, 0.3474000096321106, -0.2076999992132187, -0.07159999758005142], [-0.10689999908208847, 0.007199999876320362, -0.37860000133514404, -0.557200014591217, 0.05779999867081642, -0.009999999776482582, 0.2623000144958496, 0.19380000233650208, -0.13850000500679016, 0.14489999413490295, -0.18389999866485596, -0.11429999768733978, -0.08799999952316284, 0.05009999871253967, -0.2915000021457672, -0.10909999907016754, 0.04639999940991402, -0.42800000309944153, 0.058400001376867294, -0.20499999821186066], [-0.18449999392032623, 0.020600000396370888, 0.00279999990016222, -0.23160000145435333, 0.5224999785423279, 0.3357999920845032, -0.1550000011920929, -0.3314000070095062, -0.08659999817609787, 0.258899986743927, 0.013000000268220901, 0.21359999477863312, 0.18490000069141388, 0.1160999983549118, 0.09030000120401382, 0.2754000127315521, 0.23669999837875366, 0.09799999743700027, -0.2549999952316284, -0.09799999743700027], [-0.555899977684021, -0.1818999946117401, 0.11410000175237656, -0.05420000106096268, 0.2671999931335449, -0.3122999966144562, 0.26030001044273376, -0.05590000003576279, 0.3792000114917755, -0.17419999837875366, -0.11129999905824661, 0.06549999862909317, -0.04490000009536743, -0.025800000876188278, 0.03759999945759773, 0.18880000710487366, -0.053199999034404755, -0.0869000032544136, 0.18569999933242798, 0.3560999929904938], [-0.03460000082850456, 0.5300999879837036, 0.21899999678134918, 0.13860000669956207, 0.40709999203681946, -0.15360000729560852, -0.08869999647140503, -0.015399999916553497, -0.31459999084472656, -0.21889999508857727, 0.00139999995008111, -0.24220000207424164, -0.30059999227523804, 0.06930000334978104, 0.08129999786615372, -0.17090000212192535, 0.2522999942302704, -0.17749999463558197, 0.14350000023841858, 0.031300000846385956], [0.33230000734329224, -0.24240000545978546, -0.05220000073313713, 0.14319999516010284, 0.429500013589859, -0.23729999363422394, 0.004100000020116568, 0.039500001817941666, 0.20399999618530273, -0.06449999660253525, -0.04580000042915344, 0.44769999384880066, 0.017999999225139618, -0.08950000256299973, -0.03830000013113022, -0.28790000081062317, 0.08540000021457672, -0.012199999764561653, 0.23729999363422394, -0.40049999952316284], [-0.06830000132322311, 0.5170999765396118, 0.02199999988079071, -0.021800000220537186, 0.04960000142455101, 0.2214999943971634, -0.13910000026226044, 0.1776999980211258, 0.36739999055862427, -0.14159999787807465, -0.1655000001192093, 0.25110000371932983, 0.12780000269412994, -0.11289999634027481, -0.47940000891685486, -0.1906999945640564, -0.1412999927997589, 0.09769999980926514, -0.18880000710487366, 0.1362999975681305], [-0.11509999632835388, -0.017400000244379044, 0.22769999504089355, -0.08299999684095383, 0.03539999946951866, -0.07249999791383743, 0.09939999878406525, 0.4090999960899353, 0.0210999995470047, 0.2526000142097473, -0.20659999549388885, -0.09099999815225601, -0.021199999377131462, 0.5476999878883362, 0.02979999966919422, -0.1509999930858612, 0.04439999908208847, 0.5336999893188477, 0.07689999788999557, -0.10899999737739563], [0.35659998655319214, -0.039400000125169754, 0.2639999985694885, -0.06849999725818634, 0.1770000010728836, 0.19290000200271606, -0.019999999552965164, 0.22529999911785126, 0.34700000286102295, -0.041999999433755875, 0.05950000137090683, -0.36149999499320984, -0.13680000603199005, -0.045099999755620956, -0.1800999939441681, 0.5608999729156494, 0.0020000000949949026, -0.07900000363588333, 0.13750000298023224, -0.16670000553131104]], [0.0, 0.0, 0.0, 0.0, 0.0, 0.0, 0.0, 0.0, 0.0, 0.0, 0.0, 0.0, 0.0, 0.0, 0.0, 0.0, 0.0, 0.0, 0.0, 0.0], [[0.03319999948143959, 0.0027000000700354576, -0.016699999570846558, -0.0017999999690800905, 0.12229999899864197], [-0.014700000174343586, -0.04670000076293945, -0.05999999865889549, -0.0005000000237487257, -0.16120000183582306], [-0.057500001043081284, -0.03150000050663948, 0.04129999876022339, 0.027000000700354576, -0.054999999701976776], [0.0066999997943639755, 0.0007999999797903001, 0.059300001710653305, 0.00139999995008111, -0.021199999377131462], [0.06199999898672104, 0.042500000447034836, 0.11349999904632568, 0.019600000232458115, 0.05620000138878822], [-0.0026000000070780516, -0.029600000008940697, 0.05090000107884407, -0.008500000461935997, 0.039400000125169754], [0.014999999664723873, 0.01720000058412552, 0.03959999978542328, 0.014700000174343586, 0.010400000028312206], [0.060499999672174454, -0.015599999576807022, -0.013299999758601189, 0.07540000230073929, -0.02539999969303608], [0.0722000002861023, -0.014800000004470348, -0.05270000174641609, 0.08399999886751175, -0.05649999901652336], [0.015200000256299973, -0.012799999676644802, -0.015799999237060547, 0.018699999898672104, 0.006300000008195639], [-0.03020000085234642, 0.09740000218153, 0.07370000332593918, 0.02070000022649765, 0.014800000004470348], [-0.029400000348687172, -0.04830000177025795, 0.004000000189989805, -0.07289999723434448, -0.042399998754262924], [0.0008999999845400453, -0.04740000143647194, -0.061400000005960464, -0.007499999832361937, 0.02319999970495701], [-0.028599999845027924, 0.02879999950528145, 0.014399999752640724, 0.1039000004529953, -0.06560000032186508], [-0.04690000042319298, -0.0005000000237487257, 0.03680000081658363, 0.04340000078082085, -0.10540000349283218], [-0.03840000182390213, 0.014999999664723873, 0.025499999523162842, 0.006800000090152025, -0.04230000078678131], [0.03500000014901161, 0.0035000001080334187, 0.019099999219179153, 0.00019999999494757503, 0.05869999900460243], [-0.0035000001080334187, -0.053300000727176666, 0.043800000101327896, 0.01119999960064888, -0.0010000000474974513], [-0.04439999908208847, -0.06549999862909317, -0.08110000193119049, 0.02759999968111515, 0.018699999898672104], [-0.0010000000474974513, 0.026200000196695328, -0.006500000134110451, 0.04010000079870224, -0.0892999991774559]], [[0.11500000208616257, -0.27559998631477356, -0.3068999946117401, 0.5770000219345093, -0.6955000162124634], [-0.41749998927116394, -0.29190000891685486, -0.5684000253677368, -0.6111000180244446, -0.20960000157356262], [-0.8388000130653381, -0.11389999836683273, 0.4677000045776367, 0.22990000247955322, -0.10920000076293945], [0.2612000107765198, -0.881600022315979, 0.3472000062465668, -0.12639999389648438, 0.13449999690055847], [0.20180000364780426, 0.22059999406337738, 0.4934000074863434, -0.4740999937057495, -0.6650999784469604]], [0.0, 0.0, 0.0, 0.0, 0.0], [[0.03319999948143959, 0.0027000000700354576, -0.016699999570846558], [-0.0017999999690800905, 0.12229999899864197, -0.014700000174343586], [-0.04670000076293945, -0.05999999865889549, -0.0005000000237487257], [-0.16120000183582306, -0.057500001043081284, -0.03150000050663948], [0.04129999876022339, 0.027000000700354576, -0.054999999701976776]], [0.0, 0.0, 0.0]]</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>[[[0.05139999836683273, 0.16140000522136688, -0.14419999718666077, 0.14030000567436218, 0.11379999667406082, -0.11810000240802765, -0.14020000398159027, -0.22040000557899475, -0.11330000311136246, -0.24899999797344208, -0.14509999752044678, -0.009800000116229057, 0.0575999990105629, 0.11219999939203262, -0.18729999661445618, 0.1404000073671341, 0.11159999668598175, 0.09950000047683716, -0.1673000007867813, -0.07800000160932541], [0.27300000190734863, -0.06430000066757202, 0.26739999651908875, -0.15330000221729279, 0.2651999890804291, 0.04179999977350235, 0.15940000116825104, 0.20819999277591705, 0.1274999976158142, 0.04580000042915344, 0.24390000104904175, -0.164000004529953, 0.1340000033378601, -0.16979999840259552, 0.22519999742507935, -0.08399999886751175, -0.17409999668598175, -0.0689999982714653, 0.1695999950170517, -0.1298000067472458]], [[-0.3116999864578247, 0.21379999816417694, 0.06419999897480011, 0.2881999909877777, -0.3783999979496002, 0.4366999864578247, 0.2599000036716461, -0.41909998655319214, 0.039500001817941666, 0.05079999938607216, -0.8069999814033508, -0.009499999694526196, 0.17810000479221344, -0.2824999988079071, 0.010999999940395355, -0.2721000015735626, 0.08609999716281891, -0.23880000412464142, 0.35760000348091125, -0.07989999651908875], [0.14560000598430634, 0.3578999936580658, 0.21150000393390656, -0.23999999463558197, -0.18240000307559967, -0.4918000102043152, -0.19580000638961792, -0.18469999730587006, -0.05050000175833702, 0.2296999990940094, -0.08500000089406967, 0.1469999998807907, 0.3224000036716461, 0.07819999754428864, 0.15530000627040863, 0.4424999952316284, -0.1371999979019165, 0.1459999978542328, 0.0917000025510788, 0.14219999313354492], [-0.1437000036239624, 0.28119999170303345, -0.17219999432563782, 0.14319999516010284, -0.3151000142097473, 0.09929999709129333, 0.49810001254081726, 0.3846000134944916, 0.6035000085830688, 0.48399999737739563, -0.30480000376701355, -0.026100000366568565, -0.28529998660087585, -0.35830000042915344, 0.6067000031471252, -0.09830000251531601, 0.5088000297546387, -0.34709998965263367, 0.02419999986886978, 0.3400000035762787], [0.6121000051498413, -0.2533999979496002, 0.15940000116825104, 0.12439999729394913, 0.16429999470710754, -0.303600013256073, 0.13429999351501465, -0.25119999051094055, -0.5777999758720398, -0.2354000061750412, -0.4205999970436096, 0.4864000082015991, -0.09070000052452087, 0.156700000166893, -0.5605000257492065, 0.1776999980211258, 0.179299995303154, -0.10199999809265137, -0.2856000065803528, 0.055399999022483826], [-0.3133000135421753, -0.20469999313354492, -0.1761000007390976, 0.0625, -0.12770000100135803, 0.2053000032901764, -0.22689999639987946, 0.3953000009059906, -0.27869999408721924, 0.004600000102072954, -0.3167000114917755, 0.1387999951839447, 0.1363999992609024, -0.5516999959945679, -0.11550000309944153, -0.09560000151395798, 0.44449999928474426, -0.0010999999940395355, 0.3001999855041504, 0.38659998774528503], [0.15610000491142273, -0.2021999955177307, 0.40369999408721924, -0.5223000049591064, 0.14959999918937683, 0.30959999561309814, 0.2930000126361847, 0.38109999895095825, 0.05090000107884407, -0.1932000070810318, 0.32100000977516174, 0.00430000014603138, 0.06930000334978104, -0.10740000009536743, 0.5776000022888184, -0.1468999981880188, -0.09619999676942825, -0.01510000042617321, 0.03840000182390213, -0.08590000122785568], [0.22380000352859497, -0.2637999951839447, 0.3239000141620636, -0.5386000275611877, 0.21209999918937683, 0.06350000202655792, 0.26190000772476196, 0.07620000094175339, 0.4659000039100647, 0.37470000982284546, 0.260699987411499, -0.6689000129699707, -0.21469999849796295, -0.1467999964952469, 0.27709999680519104, -0.5236999988555908, -0.00430000014603138, 0.17319999635219574, 0.06599999964237213, 0.6460000276565552], [-0.27709999680519104, 0.03359999880194664, 0.33640000224113464, -0.2768000066280365, -0.10540000349283218, 0.5439000129699707, 0.4650000035762787, 0.2948000133037567, 0.37950000166893005, 0.9111999869346619, 0.6711000204086304, -0.08579999953508377, -0.4968000054359436, -0.20980000495910645, 0.24070000648498535, -0.24070000648498535, -0.1720999926328659, -0.12870000302791595, 0.628600001335144, 0.41519999504089355], [-0.24500000476837158, -0.11460000276565552, 0.5356000065803528, 0.02759999968111515, 0.10980000346899033, -0.12229999899864197, -0.2913999855518341, 0.3310999870300293, 0.26420000195503235, 0.6000000238418579, -0.14550000429153442, -0.1485999971628189, -0.23499999940395355, 0.01850000023841858, 0.4489000141620636, -0.07400000095367432, -0.526199996471405, -0.16580000519752502, -0.2637999951839447, 0.195700004696846], [-0.003000000026077032, -0.13289999961853027, 0.033900000154972076, -0.5350000262260437, 0.02329999953508377, -0.035599999129772186, -0.2102999985218048, 0.021199999377131462, 0.21299999952316284, 0.058800000697374344, 0.016699999570846558, -0.09440000355243683, -0.7591999769210815, -0.10849999636411667, 0.3531000018119812, 0.125900000333786, -0.29190000891685486, 0.46639999747276306, 0.13699999451637268, 0.04399999976158142], [0.021800000220537186, 0.22190000116825104, -0.37220001220703125, 0.18559999763965607, 0.027499999850988388, 0.46369999647140503, 0.010599999688565731, 0.19349999725818634, 0.17550000548362732, 0.28690001368522644, -0.4027000069618225, -0.023000000044703484, 0.010200000368058681, 0.18719999492168427, 0.4772999882698059, 0.02319999970495701, -0.41130000352859497, -0.2069000005722046, 0.5141000151634216, 0.6887000203132629], [0.0026000000070780516, 0.243599995970726, -0.13369999825954437, 0.4043999910354614, 0.2694999873638153, 0.039900001138448715, 0.3564000129699707, 0.027300000190734863, -0.33880001306533813, 0.01640000008046627, -0.10639999806880951, -0.06239999830722809, 0.05139999836683273, -0.3783000111579895, -0.056699998676776886, 0.2215999960899353, -0.39890000224113464, 0.38280001282691956, -0.2596000134944916, -0.10040000081062317], [-0.09309999644756317, -0.026200000196695328, -0.5016000270843506, -0.5877000093460083, 0.019899999722838402, 0.021400000900030136, 0.3490999937057495, 0.18119999766349792, -0.18080000579357147, 0.10660000145435333, -0.33379998803138733, -0.08630000054836273, -0.04259999841451645, -0.07400000095367432, -0.34700000286102295, -0.18860000371932983, 0.14190000295639038, -0.5910999774932861, 0.07100000232458115, -0.19660000503063202], [-0.12809999287128448, 0.05909999832510948, -0.0020000000949949026, -0.19480000436306, 0.5314000248908997, 0.19089999794960022, -0.31529998779296875, -0.4943999946117401, -0.25929999351501465, 0.0625, -0.04439999908208847, 0.26820001006126404, 0.36559998989105225, 0.23100000619888306, -0.049400001764297485, 0.36820000410079956, 0.23729999363422394, 0.1899999976158142, -0.4250999987125397, -0.2084999978542328], [-0.7777000069618225, -0.1282999962568283, 0.3743000030517578, -0.12160000205039978, 0.19449999928474426, -0.21140000224113464, 0.412200003862381, 0.21580000221729279, 0.6779000163078308, 0.13850000500679016, 0.08839999884366989, -0.10849999636411667, -0.23919999599456787, 0.015599999576807022, 0.31299999356269836, 0.19830000400543213, -0.1476999968290329, -0.020899999886751175, 0.36320000886917114, 0.6488000154495239], [-0.13099999725818634, 0.6402999758720398, 0.2409999966621399, 0.22020000219345093, 0.2919999957084656, -0.13989999890327454, -0.22599999606609344, -0.17080000042915344, -0.40139999985694885, -0.36489999294281006, -0.11069999635219574, -0.1298999935388565, -0.1451999992132187, 0.12880000472068787, 0.06159999966621399, -0.0746999979019165, 0.17030000686645508, -0.2329999953508377, 0.03229999914765358, 0.05990000069141388], [0.5325999855995178, -0.3587000072002411, -0.17800000309944153, 0.12280000001192093, 0.5667999982833862, -0.3709999918937683, -0.0430000014603138, -0.026100000366568565, 0.07940000295639038, -0.2004999965429306, 0.03970000147819519, 0.4699999988079071, 0.030700000002980232, -0.08139999955892563, -0.22210000455379486, -0.3059000074863434, 0.15520000457763672, -0.0203000009059906, 0.10819999873638153, -0.660099983215332], [-0.10779999941587448, 0.5770000219345093, 0.05469999834895134, 0.0007999999797903001, -0.010700000450015068, 0.16599999368190765, -0.24979999661445618, 0.07119999825954437, 0.22120000422000885, -0.30070000886917114, -0.23080000281333923, 0.2802000045776367, 0.32089999318122864, 0.011300000362098217, -0.5882999897003174, -0.12939999997615814, -0.1500999927520752, 0.14249999821186066, -0.31310001015663147, 0.07609999924898148], [-0.21279999613761902, -0.21400000154972076, 0.350600004196167, -0.32409998774528503, 0.08760000020265579, -0.1436000019311905, 0.4147000014781952, 0.6509000062942505, 0.22660000622272491, 0.444599986076355, -0.013000000268220901, -0.33180001378059387, -0.18070000410079956, 0.5252000093460083, 0.23409999907016754, -0.38760000467300415, 0.12280000001192093, 0.4586000144481659, 0.3537999987602234, 0.18940000236034393], [0.5029000043869019, -0.1858000010251999, 0.49399998784065247, -0.20550000667572021, 0.3921000063419342, 0.04610000178217888, -0.06859999895095825, 0.28450000286102295, 0.47450000047683716, 0.0414000004529953, 0.32120001316070557, -0.6225000023841858, -0.21860000491142273, 0.13619999587535858, -0.10109999775886536, 0.6658999919891357, -0.1046999990940094, 0.16019999980926514, 0.12839999794960022, -0.2962000072002411]], [0.10679999738931656, -0.013399999588727951, -0.004800000227987766, -0.041600000113248825, 0.11129999905824661, -0.03530000150203705, -0.00019999999494757503, -0.0017999999690800905, -0.020400000736117363, -0.015300000086426735, 0.016200000420212746, -0.015599999576807022, 0.06849999725818634, -0.05990000069141388, -0.010900000110268593, -0.014600000344216824, -0.00430000014603138, -0.030799999833106995, 0.0012000000569969416, -0.025800000876188278], [[0.11429999768733978, 0.18520000576972961, -0.07249999791383743, 0.04309999942779541, 0.2818000018596649], [-0.1673000007867813, -0.10719999670982361, -0.04919999837875366, -0.06700000166893005, -0.28110000491142273], [0.1339000016450882, 0.09920000284910202, 0.09189999848604202, 0.31299999356269836, -0.1023000031709671], [-0.3021000027656555, -0.10209999978542328, -0.16429999470710754, -0.19979999959468842, -0.18320000171661377], [0.11860000342130661, 0.20160000026226044, 0.05779999867081642, 0.06080000102519989, 0.1860000044107437], [-0.0544000007212162, -0.2142000049352646, -0.023000000044703484, -0.07880000025033951, -0.12060000002384186], [0.23680000007152557, -0.1615999937057495, 0.04050000011920929, 0.08560000360012054, 0.10570000112056732], [0.3447999954223633, -0.18129999935626984, -0.01080000028014183, 0.33059999346733093, 0.012900000438094139], [0.18539999425411224, -0.21639999747276306, 0.0812000036239624, 0.3163999915122986, -0.2280000001192093], [0.16519999504089355, -0.21570000052452087, 0.08349999785423279, 0.2493000030517578, -0.17730000615119934], [0.26899999380111694, 0.18880000710487366, 0.21469999849796295, 0.28299999237060547, 0.16689999401569366], [-0.1460999995470047, 0.07159999758005142, -0.0544000007212162, -0.1088000014424324, 0.05609999969601631], [-0.07039999961853027, 0.06809999793767929, -0.18729999661445618, -0.1467999964952469, 0.17649999260902405], [-0.001500000013038516, 0.15639999508857727, 0.14000000059604645, 0.15049999952316284, -0.03189999982714653], [0.10740000009536743, -0.21369999647140503, 0.1273999959230423, 0.25360000133514404, -0.2800999879837036], [-0.09139999747276306, 0.06530000269412994, 0.13680000603199005, 0.10499999672174454, -0.1785999983549118], [-0.041999999433755875, 0.07199999690055847, -0.07419999688863754, -0.13930000364780426, 0.21160000562667847], [0.03139999881386757, 0.0714000016450882, 0.19009999930858612, 0.2581999897956848, -0.04769999906420708], [0.17239999771118164, -0.14509999752044678, -0.19269999861717224, 0.16369999945163727, 0.09210000187158585], [-0.016200000420212746, -0.18080000579357147, 0.06809999793767929, 0.04529999941587448, -0.25440001487731934]], [[0.2581000030040741, -0.39480000734329224, -0.1964000016450882, 0.6043000221252441, -0.6241000294685364], [-0.5181999802589417, -0.4043999910354614, -0.7505999803543091, -0.9046000242233276, -0.16220000386238098], [-0.843999981880188, -0.15880000591278076, 0.44029998779296875, 0.22630000114440918, -0.20419999957084656], [0.2892000079154968, -1.0880000591278076, 0.4456000030040741, -0.04170000180602074, -0.009600000455975533], [0.09099999815225601, 0.1446000039577484, 0.34060001373291016, -0.6959999799728394, -0.5817000269889832]], [0.015200000256299973, -0.00019999999494757503, -0.08349999785423279, 0.007799999788403511, 0.005900000222027302], [[-0.11079999804496765, 0.10080000013113022, -0.17990000545978546], [0.12120000272989273, 0.13019999861717224, -0.09870000183582306], [-0.2004999965429306, 0.0015999999595806003, 0.06350000202655792], [-0.4471000134944916, 0.032999999821186066, -0.013899999670684338], [0.1143999993801117, 0.09650000184774399, -0.17599999904632568]], [0.037700001150369644, 0.01600000075995922, 0.06120000034570694]]</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>[0.7065706650382924]</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>[0.06698012495342943]</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>[0.4821442600103344]</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>[0.11822815931811068]</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>[-6.60429784984265]</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>[2.488732277515676]</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>[0.25095049094267585]</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>[0.17207095897273977]</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>[0.819914346755789]</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>[0.04270929849411565]</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>[0.4487818392723363]</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>[0.181211561209901]</t>
+        </is>
+      </c>
+      <c r="Q17" t="inlineStr">
+        <is>
+          <t>[0.14887269717326201]</t>
+        </is>
+      </c>
+      <c r="R17" t="inlineStr">
+        <is>
+          <t>[0.09177342190769051]</t>
+        </is>
+      </c>
+      <c r="S17" t="inlineStr">
+        <is>
+          <t>[-0.030072410981189623]</t>
+        </is>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>[0.08679425132597557]</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>[-0.43538411638073815]</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>[0.13725592279165313]</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>[0.0006729240890095411]</t>
+        </is>
+      </c>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>[0.10469012760712353]</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>[-0.08118717014171861]</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>[0.0889743625195905]</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>[-0.27891694687944657]</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>[0.11766595353736574]</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>[-0.8479982414635348]</t>
+        </is>
+      </c>
+      <c r="AD17" t="inlineStr">
+        <is>
+          <t>[0.1548548077741901]</t>
+        </is>
+      </c>
+      <c r="AE17" t="inlineStr">
+        <is>
+          <t>[-0.8884343696719417]</t>
+        </is>
+      </c>
+      <c r="AF17" t="inlineStr">
+        <is>
+          <t>[0.20334297596136208]</t>
+        </is>
+      </c>
+      <c r="AG17" t="inlineStr">
+        <is>
+          <t>[-2.843650850451451]</t>
+        </is>
+      </c>
+      <c r="AH17" t="inlineStr">
+        <is>
+          <t>[0.2861596461245792]</t>
+        </is>
+      </c>
+      <c r="AI17" t="inlineStr">
+        <is>
+          <t>[-1.1606774471943675]</t>
+        </is>
+      </c>
+      <c r="AJ17" t="inlineStr">
+        <is>
+          <t>[0.1770651115010581]</t>
+        </is>
+      </c>
+      <c r="AK17" t="inlineStr">
+        <is>
+          <t>[-0.9734283742181757]</t>
+        </is>
+      </c>
+      <c r="AL17" t="inlineStr">
+        <is>
+          <t>[0.20946496332846024]</t>
+        </is>
+      </c>
+      <c r="AM17" t="inlineStr">
+        <is>
+          <t>[-3.3009808245829095]</t>
+        </is>
+      </c>
+      <c r="AN17" t="inlineStr">
+        <is>
+          <t>[0.3303465077354876]</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>model_20_5_1</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>[20, 5]</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>[[[0.01979999989271164, -0.020899999886751175, 0.04690000042319298, 0.05649999901652336, 0.05119999870657921, -0.12319999933242798, 0.017400000244379044, 0.01510000042617321, -0.01759999990463257, 0.030300000682473183, -0.039000000804662704, -0.014499999582767487, 0.03610000014305115, 0.09679999947547913, -0.0632999986410141, 0.003100000089034438, -0.010999999940395355, -0.0006000000284984708, 0.009399999864399433, 0.00570000009611249], [-0.03370000049471855, -0.07819999754428864, -0.08079999685287476, 0.07209999859333038, 0.03180000185966492, -0.039500001817941666, 0.04800000041723251, -0.0617000013589859, 0.14569999277591705, -0.03849999979138374, -0.019700000062584877, 0.003700000001117587, -0.012799999676644802, 0.02979999966919422, -0.010999999940395355, -0.023900000378489494, -0.02449999935925007, 0.014000000432133675, -0.05990000069141388, -0.028300000354647636]], [[0.4074000120162964, -0.02710000053048134, 0.06650000065565109, -0.20999999344348907, -0.22360000014305115, -0.1770000010728836, 0.13650000095367432, -0.3959999978542328, 0.024299999698996544, 0.2549000084400177, -0.17820000648498535, -0.2854999899864197, -0.27000001072883606, 0.0012000000569969416, 0.07999999821186066, -0.17499999701976776, -0.19359999895095825, 0.3467000126838684, -0.18809999525547028, 0.21480000019073486], [0.01119999960064888, 0.33239999413490295, -0.2110999971628189, -0.2596000134944916, 0.15129999816417694, 0.06700000166893005, -0.08829999715089798, -0.04470000043511391, -0.2955999970436096, 0.09189999848604202, -0.0860000029206276, 0.019600000232458115, 0.1289999932050705, -0.13030000030994415, -0.18440000712871552, -0.1256999969482422, -0.351500004529953, -0.2549000084400177, -0.5094000101089478, -0.32440000772476196], [0.14219999313354492, -0.28349998593330383, -0.07859999686479568, -0.23690000176429749, 0.15800000727176666, 0.04729999974370003, 0.4034999907016754, 0.40779998898506165, 0.041600000113248825, 0.2578999996185303, 0.39629998803138733, 0.1363999992609024, 0.03660000115633011, -0.21080000698566437, -0.1120000034570694, -0.10540000349283218, 0.18970000743865967, 0.05820000171661377, -0.28690001368522644, 0.21410000324249268], [-0.13089999556541443, 0.3089999854564667, -0.11980000138282776, -0.0471000000834465, -0.21170000731945038, -0.2897999882698059, -0.033900000154972076, 0.03610000014305115, -0.011800000444054604, 0.32710000872612, -0.03060000017285347, 0.21629999577999115, 0.1509999930858612, -0.3885999917984009, -0.4122999906539917, -0.006300000008195639, -0.0763000026345253, 0.20309999585151672, 0.42829999327659607, 0.1014999970793724], [-0.32919999957084656, 0.24899999797344208, 0.08380000293254852, 0.12630000710487366, 0.001500000013038516, 0.4787999987602234, 0.1859000027179718, 0.04740000143647194, -0.14190000295639038, 0.3068000078201294, -0.3000999987125397, -0.11760000139474869, -0.07530000060796738, -0.09369999915361404, 0.09650000184774399, 0.40619999170303345, 0.1298999935388565, 0.18880000710487366, -0.1851000040769577, 0.21639999747276306], [0.24250000715255737, -0.2296999990940094, 0.289000004529953, -0.06390000134706497, -0.07590000331401825, 0.31220000982284546, -0.17749999463558197, -0.03550000116229057, 0.1298000067472458, -0.02250000089406967, -0.15080000460147858, -0.06369999796152115, 0.6116999983787537, -0.4431000053882599, 0.1826000064611435, -0.025100000202655792, -0.1152999997138977, 0.012799999676644802, 0.05169999971985817, -0.009100000374019146], [-0.10360000282526016, 0.09839999675750732, 0.3700000047683716, 0.1940000057220459, -0.04879999905824661, 0.17409999668598175, 0.3815000057220459, -0.385699987411499, -0.19580000638961792, -0.2808000147342682, 0.47290000319480896, -0.06830000132322311, -0.04010000079870224, -0.18549999594688416, -0.24959999322891235, -0.04639999940991402, -0.1736000031232834, -0.01590000092983246, 0.039799999445676804, -0.010300000198185444], [0.0032999999821186066, -0.2775000035762787, -0.30570000410079956, 0.2971000075340271, -0.024900000542402267, -0.1459999978542328, 0.16689999401569366, 0.038100000470876694, 0.016899999231100082, -0.156700000166893, -0.04010000079870224, 0.18770000338554382, -0.14059999585151672, -0.31839999556541443, 0.1860000044107437, 0.3167000114917755, -0.301800012588501, 0.3555999994277954, -0.11940000206232071, -0.3747999966144562], [-0.017400000244379044, 0.1657000035047531, 0.27889999747276306, 0.47450000047683716, 0.20309999585151672, -0.32679998874664307, 0.26179999113082886, 0.07339999824762344, 0.011599999852478504, 0.2549999952316284, -0.19709999859333038, -0.046799998730421066, 0.10260000079870224, -0.0997999981045723, 0.21320000290870667, -0.4059999883174896, 0.1987999975681305, -0.07569999992847443, -0.08489999920129776, -0.24070000648498535], [-0.039799999445676804, -0.22709999978542328, 0.08839999884366989, -0.2087000012397766, -0.43479999899864197, -0.09269999712705612, -0.0012000000569969416, -0.17299999296665192, -0.20430000126361847, 0.040300000458955765, -0.09920000284910202, 0.021299999207258224, -0.18639999628067017, -0.2623000144958496, -0.05400000140070915, 0.13519999384880066, 0.5412999987602234, -0.2856999933719635, -0.07599999755620956, -0.3303000032901764], [-0.022700000554323196, -0.45100000500679016, -0.011599999852478504, 0.08649999648332596, 0.007300000172108412, 0.041999999433755875, 0.32030001282691956, -0.2053000032901764, -0.13930000364780426, 0.2777999937534332, -0.2851000130176544, 0.22360000014305115, 0.2621999979019165, 0.4205999970436096, -0.2973000109195709, 0.07620000094175339, -0.18889999389648438, -0.16099999845027924, 0.10570000112056732, -0.03660000115633011], [-0.520799994468689, -0.305400013923645, 0.04960000142455101, -0.08370000123977661, -0.10840000212192535, -0.19609999656677246, -0.024299999698996544, 0.18529999256134033, 0.01489999983459711, 0.1476999968290329, 0.047600001096725464, -0.4530999958515167, -0.10339999943971634, -0.14579999446868896, 0.13570000231266022, -0.06319999694824219, -0.3962000012397766, -0.288100004196167, 0.053700000047683716, 0.11840000003576279], [-0.12309999763965607, 0.015699999406933784, 0.05530000105500221, -0.12759999930858612, 0.03370000049471855, -0.1467999964952469, -0.1606999933719635, -0.15109999477863312, -0.18029999732971191, 0.35440000891685486, 0.47540000081062317, -0.15449999272823334, 0.32899999618530273, 0.27070000767707825, 0.24199999868869781, 0.2151000052690506, 0.08969999849796295, 0.3158000111579895, 0.010099999606609344, -0.3027999997138977], [0.050700001418590546, 0.26589998602867126, -0.10869999974966049, 0.03319999948143959, -0.38350000977516174, 0.07509999722242355, 0.262800008058548, -0.01269999984651804, 0.691100001335144, 0.12250000238418579, 0.1412999927997589, -0.060499999672174454, 0.10859999805688858, 0.1354999989271164, 0.012500000186264515, 0.1665000021457672, -0.07559999823570251, -0.2542000114917755, -0.10220000147819519, -0.19169999659061432], [0.18150000274181366, 0.008700000122189522, 0.3248000144958496, -0.037700001150369644, 0.424699991941452, -0.14669999480247498, -0.17299999296665192, -0.18359999358654022, 0.17229999601840973, 0.28189998865127563, 0.08789999783039093, 0.25609999895095825, -0.2809999883174896, -0.1632000058889389, 0.06809999793767929, 0.41769999265670776, -0.1378999948501587, -0.3188000023365021, 0.04830000177025795, 0.06650000065565109], [-0.07349999994039536, 0.0820000022649765, -0.3562000095844269, -0.3668999969959259, 0.3752000033855438, 0.06279999762773514, 0.40230000019073486, -0.29170000553131104, 0.045899998396635056, -0.08659999817609787, -0.10050000250339508, -0.12880000472068787, 0.04910000041127205, -0.1459999978542328, 0.2890999913215637, -0.04309999942779541, 0.12139999866485596, -0.09290000051259995, 0.39989998936653137, -0.07779999822378159], [0.5016000270843506, 0.16200000047683716, -0.10769999772310257, 0.1623000055551529, -0.18889999389648438, -0.037700001150369644, 0.16189999878406525, 0.3138999938964844, -0.4551999866962433, 0.0340999998152256, 0.07850000262260437, -0.21119999885559082, 0.032499998807907104, 0.0348999984562397, 0.17790000140666962, 0.24690000712871552, -0.11159999668598175, -0.288100004196167, 0.26010000705718994, 0.07209999859333038], [-0.10869999974966049, 0.02979999966919422, -0.25200000405311584, 0.17350000143051147, -0.06469999998807907, -0.36730000376701355, -0.00559999980032444, -0.3149000108242035, -0.05950000137090683, -0.1656000018119812, 0.0494999997317791, 0.10670000314712524, 0.3499000072479248, -0.07280000299215317, 0.16410000622272491, 0.15719999372959137, 0.13199999928474426, -0.17870000004768372, -0.3305000066757202, 0.5220999717712402], [-0.025699999183416367, -0.06939999759197235, -0.29899999499320984, 0.24860000610351562, -0.17890000343322754, 0.3824999928474426, -0.20239999890327454, -0.21240000426769257, -0.0778999999165535, 0.3375999927520752, 0.23499999940395355, 0.3041999936103821, -0.1881999969482422, -0.06710000336170197, 0.30570000410079956, -0.37540000677108765, -0.052299998700618744, -0.14270000159740448, 0.09910000115633011, 0.06300000101327896], [0.15790000557899475, -0.16120000183582306, -0.3312000036239624, 0.3596999943256378, 0.25540000200271606, 0.0934000015258789, -0.21119999885559082, -0.1535000056028366, 0.1193000003695488, 0.13860000669956207, 0.07039999961853027, -0.527899980545044, -0.00419999985024333, -0.13819999992847443, -0.42820000648498535, 0.06710000336170197, 0.20100000500679016, -0.03790000081062317, -0.004399999976158142, -0.04470000043511391]], [0.0, 0.0, 0.0, 0.0, 0.0, 0.0, 0.0, 0.0, 0.0, 0.0, 0.0, 0.0, 0.0, 0.0, 0.0, 0.0, 0.0, 0.0, 0.0, 0.0], [[0.01979999989271164, -0.020899999886751175, 0.04690000042319298, 0.05649999901652336, 0.05119999870657921], [-0.12319999933242798, 0.017400000244379044, 0.01510000042617321, -0.01759999990463257, 0.030300000682473183], [-0.039000000804662704, -0.014499999582767487, 0.03610000014305115, 0.09679999947547913, -0.0632999986410141], [0.003100000089034438, -0.010999999940395355, -0.0006000000284984708, 0.009399999864399433, 0.00570000009611249], [-0.03370000049471855, -0.07819999754428864, -0.08079999685287476, 0.07209999859333038, 0.03180000185966492], [-0.039500001817941666, 0.04800000041723251, -0.0617000013589859, 0.14569999277591705, -0.03849999979138374], [-0.019700000062584877, 0.003700000001117587, -0.012799999676644802, 0.02979999966919422, -0.010999999940395355], [-0.023900000378489494, -0.02449999935925007, 0.014000000432133675, -0.05990000069141388, -0.028300000354647636], [0.032099999487400055, -0.0835999995470047, -0.06310000270605087, -0.0348999984562397, 0.05040000006556511], [-0.029600000008940697, 0.026799999177455902, -0.005100000184029341, -0.12250000238418579, 0.03200000151991844], [-0.028999999165534973, 0.0731000006198883, 0.017999999225139618, -0.03880000114440918, 0.07970000058412552], [-0.007000000216066837, 0.031300000846385956, -0.03139999881386757, 0.050599999725818634, 0.06360000371932983], [-0.04699999839067459, 0.028300000354647636, 0.056699998676776886, -0.07150000333786011, -0.09989999979734421], [0.006500000134110451, -0.049400001764297485, 0.02630000002682209, -0.010700000450015068, -0.07890000194311142], [0.10100000351667404, -0.03750000149011612, -0.08540000021457672, 0.07190000265836716, 0.05290000140666962], [0.017999999225139618, 0.026200000196695328, 0.04619999974966049, -0.05559999868273735, 0.0210999995470047], [-0.01590000092983246, 0.07689999788999557, 0.05220000073313713, 0.025200000032782555, 0.10400000214576721], [-0.0284000001847744, 0.0005000000237487257, -0.05040000006556511, -0.094200000166893, 0.009399999864399433], [0.0364999994635582, -0.06710000336170197, 0.00559999980032444, -0.10379999876022339, 0.07909999787807465], [-0.015599999576807022, 0.09070000052452087, 0.008700000122189522, -0.023000000044703484, 0.031599998474121094]], [[-0.47690001130104065, 0.3109000027179718, -0.2011999934911728, -0.03920000046491623, 0.7961999773979187], [-0.42879998683929443, 0.039000000804662704, 0.3472999930381775, 0.8205000162124634, -0.14399999380111694], [-0.6761000156402588, -0.5958999991416931, -0.23649999499320984, -0.2678999900817871, -0.2451999932527542], [0.33320000767707825, -0.7373999953269958, 0.05920000001788139, 0.27469998598098755, 0.515999972820282], [0.14339999854564667, 0.05469999834895134, -0.8828999996185303, 0.4219000041484833, -0.13779999315738678]], [0.0, 0.0, 0.0, 0.0, 0.0], [[0.01979999989271164, -0.020899999886751175, 0.04690000042319298], [0.05649999901652336, 0.05119999870657921, -0.12319999933242798], [0.017400000244379044, 0.01510000042617321, -0.01759999990463257], [0.030300000682473183, -0.039000000804662704, -0.014499999582767487], [0.03610000014305115, 0.09679999947547913, -0.0632999986410141]], [0.0, 0.0, 0.0]]</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>[[[-0.13910000026226044, 0.09279999881982803, 0.0357000008225441, 0.15309999883174896, 0.056699998676776886, -0.20919999480247498, 0.18310000002384186, -0.125900000333786, -0.08380000293254852, 0.3806999921798706, 0.21230000257492065, -0.08079999685287476, 0.06830000132322311, -0.004100000020116568, -0.21940000355243683, 0.2858000099658966, 0.29829999804496765, -0.032600000500679016, 0.30820000171661377, -0.23389999568462372], [0.30809998512268066, -0.3260999917984009, -0.1565999984741211, -0.0012000000569969416, 0.08879999816417694, 0.0771000012755394, -0.14419999718666077, 0.20589999854564667, 0.21930000185966492, -0.14270000159740448, 0.016100000590085983, 0.2957000136375427, 0.042500000447034836, -0.06459999829530716, -0.004999999888241291, -0.25850000977516174, -0.2660999894142151, -0.023600000888109207, -0.243599995970726, -0.4456000030040741]], [[0.400299996137619, -0.14669999480247498, 0.2287999987602234, -0.10199999809265137, -0.24320000410079956, -0.0013000000035390258, 0.2754000127315521, -0.27300000190734863, 0.08780000358819962, 0.22370000183582306, -0.27219998836517334, -0.4397999942302704, -0.436599999666214, 0.07190000265836716, 0.16599999368190765, -0.09759999811649323, -0.2696000039577484, 0.2888999879360199, -0.06459999829530716, -0.10090000182390213], [0.12710000574588776, 0.48590001463890076, -0.29499998688697815, -0.40450000762939453, 0.13369999825954437, 0.22859999537467957, -0.23919999599456787, -0.018300000578165054, -0.4749999940395355, -0.003599999938160181, 0.17820000648498535, 0.03150000050663948, -0.008299999870359898, -0.2761000096797943, -0.16259999573230743, -0.10480000078678131, -0.21809999644756317, -0.4187000095844269, -0.5770000219345093, -0.21449999511241913], [0.0026000000070780516, -0.08259999752044678, -0.35040000081062317, -0.1266999989748001, 0.45969998836517334, -0.009800000116229057, 0.6590999960899353, 0.1526000052690506, 0.06560000032186508, 0.4023999869823456, 0.5649999976158142, 0.17599999904632568, 0.11289999634027481, -0.33550000190734863, -0.3409000039100647, -0.28690001368522644, 0.35370001196861267, 0.11789999902248383, -0.3107999861240387, 0.4138000011444092], [-0.23839999735355377, 0.4081999957561493, -0.2264000028371811, -0.04659999907016754, -0.3458000123500824, -0.3124000132083893, 0.07609999924898148, -0.01759999990463257, -0.0625, 0.511900007724762, -0.09099999815225601, 0.06019999831914902, 0.1729000061750412, -0.4562000036239624, -0.45239999890327454, 0.052000001072883606, 0.03550000116229057, 0.3693000078201294, 0.5016999840736389, 0.07609999924898148], [-0.4456999897956848, 0.2493000030517578, 0.031300000846385956, 0.16300000250339508, 0.020899999886751175, 0.6322000026702881, 0.45190000534057617, -0.002899999963119626, -0.023800000548362732, 0.5277000069618225, -0.4239000082015991, -0.3221000134944916, 0.013500000350177288, -0.017400000244379044, 0.14839999377727509, 0.3571000099182129, 0.11320000141859055, 0.3499000072479248, -0.04230000078678131, 0.06239999830722809], [0.34860000014305115, -0.3646000027656555, 0.4781000018119812, -0.04529999941587448, 0.10649999976158142, 0.3483999967575073, -0.27880001068115234, 0.029100000858306885, 0.2766999900341034, -0.19840000569820404, -0.1534000039100647, 0.007000000216066837, 0.6431000232696533, -0.2912999987602234, 0.21870000660419464, -0.08020000159740448, -0.2754000127315521, -0.10719999670982361, -0.009999999776482582, 0.05810000002384186], [-0.15629999339580536, 0.17880000174045563, 0.44999998807907104, 0.12950000166893005, -0.27140000462532043, 0.23309999704360962, 0.396699994802475, -0.38659998774528503, -0.3977999985218048, -0.21979999542236328, 0.5720000267028809, 0.02199999988079071, -0.07509999722242355, -0.38760000467300415, -0.3073999881744385, 0.1266999989748001, -0.04659999907016754, 0.02500000037252903, 0.12729999423027039, 0.03539999946951866], [0.04699999839067459, -0.31709998846054077, -0.3278000056743622, 0.38440001010894775, 0.06629999727010727, -0.1761000007390976, 0.1964000016450882, -0.02500000037252903, 0.13580000400543213, -0.13590000569820404, -0.0494999997317791, 0.2773999869823456, -0.15610000491142273, -0.19599999487400055, 0.16249999403953552, 0.21310000121593475, -0.2881999909877777, 0.29179999232292175, -0.20309999585151672, -0.3887999951839447], [-0.16910000145435333, 0.13030000030994415, -0.028599999845027924, 0.6827999949455261, 0.3027999997138977, -0.4375, 0.5698999762535095, 0.02280000038444996, 0.20499999821186066, 0.43779999017715454, -0.26899999380111694, -0.23170000314712524, 0.27090001106262207, 0.040699999779462814, 0.21070000529289246, -0.43939998745918274, 0.1598999947309494, 0.23980000615119934, 0.006800000090152025, -0.29010000824928284], [-0.07980000227689743, -0.03139999881386757, 0.09749999642372131, -0.3580999970436096, -0.7749999761581421, 0.03530000150203705, 0.02290000021457672, -0.18029999732971191, -0.5228000283241272, 0.20110000669956207, 0.059700001031160355, 0.11840000003576279, -0.3107999861240387, -0.5746999979019165, -0.12300000339746475, 0.33970001339912415, 0.7986999750137329, -0.3610999882221222, -0.0071000000461936, -0.38179999589920044], [0.18119999766349792, -0.510699987411499, 0.2551000118255615, -0.21209999918937683, -0.2542000114917755, 0.33230000734329224, 0.053599998354911804, 0.15919999778270721, -0.33009999990463257, 0.06889999657869339, -0.2653000056743622, 0.288100004196167, -0.0035000001080334187, 0.27649998664855957, -0.11060000211000443, 0.26109999418258667, -0.27549999952316284, -0.4097000062465668, 0.09049999713897705, -0.38909998536109924], [-0.491100013256073, -0.5120999813079834, 0.23250000178813934, 0.06989999860525131, -0.36010000109672546, -0.31869998574256897, 0.009800000116229057, 0.32440000772476196, 0.03060000017285347, 0.07199999690055847, -0.10010000318288803, -0.5127999782562256, -0.19519999623298645, -0.07540000230073929, 0.19380000233650208, 0.12240000069141388, -0.5033000111579895, -0.3149999976158142, 0.030899999663233757, -0.15940000116825104], [-0.21480000019073486, 0.050700001418590546, 0.07029999792575836, -0.20399999618530273, 0.040699999779462814, -0.07090000063180923, -0.06970000267028809, -0.05530000105500221, -0.09300000220537186, 0.4787999987602234, 0.23749999701976776, -0.329800009727478, 0.2687000036239624, 0.32850000262260437, 0.3781000077724457, 0.12929999828338623, -0.029500000178813934, 0.4194999933242798, 0.11699999868869781, -0.5289999842643738], [-0.08139999955892563, 0.5449000000953674, -0.4830999970436096, 0.15960000455379486, -0.156700000166893, -0.05530000105500221, 0.520799994468689, -0.2922999858856201, 0.6309999823570251, 0.2815999984741211, 0.17759999632835388, -0.05649999901652336, 0.24809999763965607, -0.0008999999845400453, -0.14949999749660492, -0.0494999997317791, 0.014399999752640724, -0.08980000019073486, -0.17669999599456787, -0.07289999723434448], [0.2476000040769577, -0.04309999942779541, 0.22179999947547913, 0.06629999727010727, 0.7001000046730042, -0.23309999704360962, -0.15309999883174896, -0.29820001125335693, 0.36010000109672546, 0.15189999341964722, 0.04190000146627426, 0.4587000012397766, -0.1589999943971634, -0.009200000204145908, -0.0738999992609024, 0.24629999697208405, -0.2556000053882599, -0.3434000015258789, -0.14810000360012054, 0.23260000348091125], [-0.1404999941587448, 0.3538999855518341, -0.5507000088691711, -0.6606000065803528, 0.06340000033378601, 0.30059999227523804, 0.5235000252723694, -0.4341999888420105, -0.3122999966144562, 0.16169999539852142, 0.17569999396800995, -0.004399999976158142, -0.1274999976158142, -0.49880000948905945, 0.13680000603199005, 0.008799999952316284, 0.5045999884605408, -0.3555000126361847, 0.33469998836517334, -0.13590000569820404], [0.5171999931335449, 0.3644999861717224, -0.14380000531673431, -0.13429999351501465, -0.5805000066757202, 0.14190000295639038, 0.0008999999845400453, 0.36809998750686646, -0.8461999893188477, 0.1386999934911728, 0.41909998655319214, -0.14380000531673431, -0.07769999653100967, -0.2971000075340271, 0.13779999315738678, 0.39320001006126404, 0.18310000002384186, -0.5508999824523926, 0.364300012588501, 0.1842000037431717], [-0.1784999966621399, 0.2071000039577484, -0.5202999711036682, 0.23319999873638153, 0.0010000000474974513, -0.44449999928474426, 0.19380000233650208, -0.5091000199317932, -0.065700002014637, 0.025499999523162842, -0.08789999783039093, 0.21930000185966492, 0.4081999957561493, -0.11959999799728394, 0.05220000073313713, 0.08259999752044678, 0.19169999659061432, 0.025299999862909317, -0.3659999966621399, 0.5906000137329102], [-0.04100000113248825, 0.19900000095367432, -0.44179999828338623, -0.008899999782443047, -0.5085999965667725, 0.5358999967575073, -0.24480000138282776, -0.24609999358654022, -0.4521999955177307, 0.4846000075340271, 0.45210000872612, 0.49709999561309814, -0.32850000262260437, -0.40639999508857727, 0.1973000019788742, -0.3084999918937683, 0.2752000093460083, -0.3650999963283539, 0.10729999840259552, -0.01899999938905239], [0.1543000042438507, 0.024299999698996544, -0.3409000039100647, 0.21050000190734863, 0.5992000102996826, 0.2522999942302704, -0.2069000005722046, -0.25920000672340393, 0.11509999632835388, 0.10589999705553055, 0.11079999804496765, -0.6980000138282776, 0.13249999284744263, -0.19580000638961792, -0.5566999912261963, -0.0471000000834465, 0.1039000004529953, -0.03539999946951866, 0.06390000134706497, 0.10450000315904617]], [-0.056299999356269836, 0.06449999660253525, -0.2492000013589859, 0.1388999968767166, -0.11909999698400497, -0.1688999980688095, -0.039000000804662704, -0.008200000040233135, -0.11819999665021896, 0.020800000056624413, -0.036400001496076584, 0.04190000146627426, 0.002400000113993883, -0.0714000016450882, -0.07119999825954437, -0.07620000094175339, 0.031599998474121094, 0.02850000001490116, -0.013500000350177288, -0.2223999947309494], [[-0.18320000171661377, -0.2549000084400177, 0.4456999897956848, 0.271699994802475, -0.1543000042438507], [0.04690000042319298, 0.10499999672174454, -0.1589999943971634, -0.41280001401901245, 0.524399995803833], [0.2831000089645386, -0.2531999945640564, 0.13899999856948853, 0.0640999972820282, -0.11550000309944153], [-0.040300000458955765, 0.14339999854564667, -0.3723999857902527, -0.049300000071525574, 0.008899999782443047], [-0.1137000024318695, -0.2003999948501587, -0.2167000025510788, 0.1420000046491623, -0.09390000253915787], [-0.016499999910593033, -0.19470000267028809, 0.25119999051094055, 0.2612999975681305, -0.16019999980926514], [-0.049800001084804535, 0.19110000133514404, -0.39309999346733093, -0.16979999840259552, -0.03819999843835831], [-0.013399999588727951, -0.10750000178813934, 0.06589999794960022, 0.0908999964594841, -0.07919999957084656], [0.14730000495910645, -0.1899999976158142, -0.3077000081539154, 0.03880000114440918, -0.07400000095367432], [0.010700000450015068, 0.17219999432563782, -0.2838999927043915, -0.3702000081539154, 0.0706000030040741], [-0.2467000037431717, 0.20800000429153442, 0.07280000299215317, -0.09790000319480896, 0.19370000064373016], [-0.28119999170303345, 0.3400999903678894, 0.33889999985694885, 0.36239999532699585, 0.03370000049471855], [-0.0674000009894371, -0.08060000091791153, -0.10520000010728836, -0.04529999941587448, -0.0828000009059906], [0.2606000006198883, -0.11599999666213989, 0.07150000333786011, 0.07850000262260437, -0.10530000180006027], [0.17399999499320984, -0.09470000118017197, -0.08749999850988388, 0.17900000512599945, -0.04670000076293945], [0.36970001459121704, 0.005100000184029341, 0.16779999434947968, -0.4778999984264374, 0.17260000109672546], [0.05429999902844429, 0.20469999313354492, -0.08649999648332596, -0.27489998936653137, 0.3066999912261963], [0.1451999992132187, -0.11599999666213989, -0.4643000066280365, -0.10279999673366547, -0.155799999833107], [0.1956000030040741, 0.08110000193119049, 0.14980000257492065, -0.24799999594688416, 0.13300000131130219], [0.25769999623298645, 0.007600000128149986, -0.33489999175071716, -0.21789999306201935, 0.12610000371932983]], [[-0.6545000076293945, 0.5623999834060669, -0.5389999747276306, -0.3919000029563904, 1.072700023651123], [-0.5827000141143799, -0.04910000041127205, 0.7069000005722046, 0.7712000012397766, 0.007400000002235174], [-0.7396000027656555, -0.58160001039505, -0.21870000660419464, 0.04560000076889992, -0.492000013589859], [0.37959998846054077, -0.6811000108718872, 0.023900000378489494, 0.41029998660087585, 0.3422999978065491], [0.11819999665021896, -0.07259999960660934, -0.6656000018119812, 0.323199987411499, -0.10339999943971634]], [-0.20999999344348907, 0.05090000107884407, 0.009100000374019146, 0.05739999935030937, 0.17399999499320984], [[-0.035599999129772186, -0.07020000368356705, 0.15330000221729279], [-0.155799999833107, 0.10760000348091125, -0.14480000734329224], [0.45989999175071716, 0.07240000367164612, -0.1467999964952469], [0.5684999823570251, -0.03150000050663948, 0.19789999723434448], [-0.5740000009536743, 0.19859999418258667, -0.15880000591278076]], [-0.1843000054359436, 0.00839999970048666, -0.004699999932199717]]</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>[0.8634085903277648]</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>[0.031179260548729097]</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>[0.7934992778914928]</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>[0.04714479031020628]</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>[-1.4639747947997876]</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>[0.8064089182054046]</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>[0.7646854887517875]</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>[0.05405623142539534]</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>[0.5483673977680364]</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>[0.1071096518290759]</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>[-0.4665622801964402]</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>[0.4821286005075046]</t>
+        </is>
+      </c>
+      <c r="Q18" t="inlineStr">
+        <is>
+          <t>[-0.11212978146736141]</t>
+        </is>
+      </c>
+      <c r="R18" t="inlineStr">
+        <is>
+          <t>[0.11991620444055798]</t>
+        </is>
+      </c>
+      <c r="S18" t="inlineStr">
+        <is>
+          <t>[-0.09774675753923323]</t>
+        </is>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>[0.0924965147599462]</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>[-1.039851900487295]</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>[0.19505702464205435]</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>[-0.26050174726025]</t>
+        </is>
+      </c>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>[0.13205094903425946]</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>[-0.1649670157357872]</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>[0.09586887492186484]</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>[-1.3878921785098761]</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>[0.21969652588806246]</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>[-1.0009019689104912]</t>
+        </is>
+      </c>
+      <c r="AD18" t="inlineStr">
+        <is>
+          <t>[0.1676675241450692]</t>
+        </is>
+      </c>
+      <c r="AE18" t="inlineStr">
+        <is>
+          <t>[-0.768792069040412]</t>
+        </is>
+      </c>
+      <c r="AF18" t="inlineStr">
+        <is>
+          <t>[0.1904601234503132]</t>
+        </is>
+      </c>
+      <c r="AG18" t="inlineStr">
+        <is>
+          <t>[-3.251917678277758]</t>
+        </is>
+      </c>
+      <c r="AH18" t="inlineStr">
+        <is>
+          <t>[0.31655509449405295]</t>
+        </is>
+      </c>
+      <c r="AI18" t="inlineStr">
+        <is>
+          <t>[-1.370951750124087]</t>
+        </is>
+      </c>
+      <c r="AJ18" t="inlineStr">
+        <is>
+          <t>[0.19429685654583745]</t>
+        </is>
+      </c>
+      <c r="AK18" t="inlineStr">
+        <is>
+          <t>[-0.8284083957363813]</t>
+        </is>
+      </c>
+      <c r="AL18" t="inlineStr">
+        <is>
+          <t>[0.1940721551214648]</t>
+        </is>
+      </c>
+      <c r="AM18" t="inlineStr">
+        <is>
+          <t>[-4.038967362395594]</t>
+        </is>
+      </c>
+      <c r="AN18" t="inlineStr">
+        <is>
+          <t>[0.3870292239496121]</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>model_20_5_2</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>[20, 5]</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>[[[-0.05169999971985817, 0.011599999852478504, 0.05860000103712082, 0.015599999576807022, -0.0568000003695488, 0.0071000000461936, -0.04830000177025795, 0.012000000104308128, 0.012199999764561653, 0.0006000000284984708, -0.012400000356137753, 0.032099999487400055, 0.012500000186264515, -0.06700000166893005, -9.999999747378752e-05, 0.053700000047683716, -0.13729999959468842, 0.050999999046325684, -0.026900000870227814, 0.04170000180602074], [-0.0071000000461936, 0.04320000112056732, 0.0003000000142492354, 0.015699999406933784, -0.0632999986410141, 0.04490000009536743, -0.0071000000461936, 0.08869999647140503, 0.030500000342726707, -0.001500000013038516, 0.05389999970793724, -0.05169999971985817, -0.02070000022649765, 0.0020000000949949026, 0.01140000019222498, 0.009800000116229057, 0.01940000057220459, -0.03799999877810478, -0.01640000008046627, 0.01549999974668026]], [[-0.16419999301433563, 0.04019999876618385, 0.09529999643564224, 0.2662000060081482, -0.2289000004529953, 0.2248000055551529, 0.41769999265670776, -0.11230000108480453, -0.061000000685453415, -0.13330000638961792, -0.023900000378489494, -0.26829999685287476, 0.2632000148296356, 0.3546000123023987, -0.06080000102519989, 0.20329999923706055, 0.13130000233650208, 0.23270000517368317, -0.4426000118255615, 0.007300000172108412], [0.0794999971985817, 0.21050000190734863, -0.33899998664855957, -0.10170000046491623, -0.24570000171661377, 0.257099986076355, 0.17389999330043793, 0.13650000095367432, 0.22709999978542328, -0.5825999975204468, 0.2199999988079071, 0.28189998865127563, 0.1103999987244606, -0.17020000517368317, 0.12120000272989273, -0.062300000339746475, -0.12200000137090683, 0.12349999696016312, 0.1193000003695488, 0.1607999950647354], [0.5029000043869019, 0.20329999923706055, -0.023499999195337296, -0.03220000118017197, -0.18940000236034393, 0.18970000743865967, 0.04050000011920929, 0.21850000321865082, -0.2939000129699707, 0.05869999900460243, 0.18060000240802765, -0.49399998784065247, -0.12139999866485596, -0.14710000157356262, 0.051500000059604645, -0.30469998717308044, -0.04179999977350235, -0.15940000116825104, -0.13940000534057617, -0.19499999284744263], [0.10220000147819519, 0.0658000037074089, -0.3337000012397766, 0.3637000024318695, 0.08869999647140503, -0.32820001244544983, -0.11479999870061874, 0.03200000151991844, -0.2190999984741211, -0.1551000028848648, -0.15950000286102295, -0.08669999986886978, -0.3312999904155731, -0.15459999442100525, 0.17100000381469727, 0.1851000040769577, 0.054499998688697815, 0.5467000007629395, -0.03310000151395798, -0.08190000057220459], [0.03720000013709068, -0.16210000216960907, -0.30469998717308044, -0.1899999976158142, -0.1834000051021576, -0.1316000074148178, -0.02449999935925007, -0.3750999867916107, -0.1151999980211258, -0.10090000182390213, -0.3752000033855438, 0.01360000018030405, 0.19990000128746033, -0.429500013589859, 0.011699999682605267, 0.04170000180602074, 0.11840000003576279, -0.31130000948905945, -0.38589999079704285, 0.023399999365210533], [-0.14079999923706055, 0.11710000038146973, -0.3695000112056732, -0.29089999198913574, -0.02410000003874302, -0.054999999701976776, 0.10289999842643738, -0.05220000073313713, -0.2648000121116638, -0.0763000026345253, -0.2547000050544739, -0.20720000565052032, 0.0617000013589859, 0.31790000200271606, -0.37049999833106995, -0.23280000686645508, 0.22179999947547913, 0.07010000199079514, 0.44040000438690186, 0.01759999990463257], [-0.12720000743865967, -0.11429999768733978, -0.15719999372959137, -0.03440000116825104, -0.16830000281333923, -0.08460000157356262, -0.5982000231742859, -0.06199999898672104, -0.027000000700354576, -0.16500000655651093, 0.477400004863739, -0.18289999663829803, 0.039799999445676804, 0.11089999973773956, -0.40560001134872437, 0.17139999568462372, -0.13770000636577606, 0.0035000001080334187, -0.17550000548362732, 0.029899999499320984], [0.23569999635219574, -0.03999999910593033, -0.020500000566244125, -0.19619999825954437, -0.023000000044703484, 0.052799999713897705, 0.07880000025033951, -0.04809999838471413, -0.10279999673366547, 0.05900000035762787, -0.23919999599456787, -0.17560000717639923, -0.10019999742507935, 0.1632000058889389, 0.041200000792741776, 0.4016999900341034, -0.6230000257492065, -0.01860000006854534, 0.09030000120401382, 0.4399000108242035], [0.22750000655651093, 0.4453999996185303, 0.008999999612569809, 0.16220000386238098, -0.06390000134706497, -0.07580000162124634, -0.20759999752044678, -0.48100000619888306, -0.27869999408721924, 0.11540000140666962, 0.1437000036239624, 0.2768000066280365, 0.30250000953674316, 0.26269999146461487, 0.2718000113964081, -0.026599999517202377, -0.01899999938905239, -0.050700001418590546, 0.11320000141859055, 0.007699999958276749], [0.12770000100135803, 0.18250000476837158, 0.2596000134944916, 0.14890000224113464, -0.24729999899864197, -0.5403000116348267, 0.23010000586509705, -0.23149999976158142, 0.3617999851703644, -0.23399999737739563, -0.041099999099969864, -0.12720000743865967, -0.13050000369548798, -0.010400000028312206, -0.2648000121116638, -0.06430000066757202, -0.18649999797344208, -0.14090000092983246, 0.1324000060558319, -0.18469999730587006], [0.01679999940097332, 0.08160000294446945, -0.24719999730587006, 0.16869999468326569, -0.06889999657869339, -0.05550000071525574, -0.25110000371932983, 0.44679999351501465, 0.2371000051498413, -0.05869999900460243, -0.3416999876499176, -0.03590000048279762, 0.22020000219345093, 0.3400000035762787, 0.2029000073671341, 0.17219999432563782, -0.05480000004172325, -0.3393999934196472, -0.01360000018030405, -0.3192000091075897], [0.058800000697374344, 0.3093000054359436, -0.25760000944137573, -0.06199999898672104, 0.5964999794960022, -0.10520000010728836, 0.15960000455379486, -0.032499998807907104, 0.28999999165534973, 0.16820000112056732, 0.1898999959230423, -0.2721000015735626, 0.36970001459121704, -0.19329999387264252, -0.10899999737739563, 0.1412000060081482, -0.043800000101327896, 0.04320000112056732, -0.07100000232458115, 9.999999747378752e-05], [-0.09529999643564224, 0.05009999871253967, -0.25929999351501465, -0.15309999883174896, -0.16179999709129333, -0.39329999685287476, 0.09989999979734421, 0.11580000072717667, 0.19699999690055847, 0.27730000019073486, 0.16699999570846558, 0.015300000086426735, -0.18729999661445618, 0.2773999869823456, 0.2529999911785126, -0.31859999895095825, 0.06289999932050705, -0.005499999970197678, -0.335999995470047, 0.3939000070095062], [0.3635999858379364, -0.24639999866485596, -0.13459999859333038, -0.30379998683929443, 0.17880000174045563, 0.10289999842643738, 0.04430000111460686, -0.2093999981880188, 0.16200000047683716, -0.012500000186264515, -0.03189999982714653, 0.2540999948978424, -0.11580000072717667, 0.32839998602867126, -0.09480000287294388, -0.1340000033378601, -0.16449999809265137, 0.25859999656677246, -0.2596000134944916, -0.454800009727478], [-0.29350000619888306, 0.37070000171661377, -0.08169999718666077, -0.19040000438690186, -0.39899998903274536, 0.23839999735355377, -0.10000000149011612, -0.11789999902248383, 0.2362000048160553, 0.445499986410141, -0.11230000108480453, -0.03440000116825104, -0.15530000627040863, -0.19830000400543213, -0.0020000000949949026, 0.13680000603199005, -0.11410000175237656, 0.24130000174045563, 0.033900000154972076, -0.266400009393692], [0.07959999889135361, -0.2485000044107437, 0.12280000001192093, 0.08510000258684158, -0.054999999701976776, 0.09560000151395798, -0.32010000944137573, -0.17509999871253967, 0.33730000257492065, -0.0421999990940094, -0.20499999821186066, -0.366100013256073, 0.3107999861240387, -0.03480000048875809, 0.2304999977350235, -0.39969998598098755, -0.04830000177025795, 0.3292999863624573, 0.14749999344348907, 0.17149999737739563], [-0.19200000166893005, 0.32580000162124634, 0.3206999897956848, -0.46059998869895935, 0.2387000024318695, -0.015399999916553497, -0.19329999387264252, -0.07819999754428864, -0.005400000140070915, -0.4246000051498413, -0.08229999989271164, -0.2071000039577484, -0.21699999272823334, 0.1023000031709671, 0.3125999867916107, 0.07540000230073929, 0.1446000039577484, -0.020500000566244125, -0.1664000004529953, -0.03689999878406525], [-0.4108999967575073, -0.0786999985575676, -0.27559998631477356, 0.3052000105381012, 0.2150000035762787, 0.21690000593662262, 0.09860000014305115, -0.3181999921798706, -0.03269999846816063, -0.09309999644756317, 0.08460000157356262, -0.15289999544620514, -0.2770000100135803, 0.05139999836683273, 0.18330000340938568, -0.25209999084472656, -0.35659998655319214, -0.2973000109195709, 0.03400000184774399, -0.13459999859333038], [-0.10429999977350235, 0.35109999775886536, 0.13490000367164612, 0.15539999306201935, 0.15479999780654907, 0.0544000007212162, -0.16329999268054962, 0.1932000070810318, -0.11949999630451202, -0.048900000751018524, -0.3352999985218048, 0.23499999940395355, 0.047600001096725464, -0.062199998646974564, -0.376800000667572, -0.38679999113082886, -0.311599999666214, 0.09040000289678574, -0.34529998898506165, 0.16120000183582306], [0.2971999943256378, 0.1476999968290329, -0.10220000147819519, 0.23589999973773956, 0.08389999717473984, 0.3407000005245209, -0.1500999927520752, -0.1956000030040741, 0.3416000008583069, 0.013000000268220901, -0.13050000369548798, -0.002400000113993883, -0.38670000433921814, 0.10419999808073044, -0.22280000150203705, 0.09849999845027924, 0.4016999900341034, -0.18490000069141388, -0.025599999353289604, 0.3001999855041504]], [0.0, 0.0, 0.0, 0.0, 0.0, 0.0, 0.0, 0.0, 0.0, 0.0, 0.0, 0.0, 0.0, 0.0, 0.0, 0.0, 0.0, 0.0, 0.0, 0.0], [[-0.05169999971985817, 0.011599999852478504, 0.05860000103712082, 0.015599999576807022, -0.0568000003695488], [0.0071000000461936, -0.04830000177025795, 0.012000000104308128, 0.012199999764561653, 0.0006000000284984708], [-0.012400000356137753, 0.032099999487400055, 0.012500000186264515, -0.06700000166893005, -9.999999747378752e-05], [0.053700000047683716, -0.13729999959468842, 0.050999999046325684, -0.026900000870227814, 0.04170000180602074], [-0.0071000000461936, 0.04320000112056732, 0.0003000000142492354, 0.015699999406933784, -0.0632999986410141], [0.04490000009536743, -0.0071000000461936, 0.08869999647140503, 0.030500000342726707, -0.001500000013038516], [0.05389999970793724, -0.05169999971985817, -0.02070000022649765, 0.0020000000949949026, 0.01140000019222498], [0.009800000116229057, 0.01940000057220459, -0.03799999877810478, -0.01640000008046627, 0.01549999974668026], [-0.024399999529123306, 0.09529999643564224, -0.006300000008195639, -0.015699999406933784, -0.07580000162124634], [-0.03310000151395798, -0.020099999383091927, 0.032099999487400055, 0.10859999805688858, 0.09799999743700027], [0.048700001090765, -0.03189999982714653, 0.02250000089406967, -0.05260000005364418, -0.016499999910593033], [0.02250000089406967, -0.0203000009059906, -0.004600000102072954, 0.022700000554323196, -0.01769999973475933], [-0.05779999867081642, 0.13570000231266022, -0.026399999856948853, -0.004699999932199717, 0.01940000057220459], [-0.014499999582767487, -0.07180000096559525, 0.035599999129772186, 0.02669999934732914, 0.06109999865293503], [-0.020500000566244125, 0.0340999998152256, 0.062199998646974564, 0.04610000178217888, 0.01489999983459711], [-0.07909999787807465, 0.0786999985575676, 0.016200000420212746, -0.037300001829862595, 0.04659999907016754], [-0.05420000106096268, 0.04479999840259552, -0.061400000005960464, -0.031300000846385956, 0.04540000110864639], [0.013299999758601189, -0.0006000000284984708, -0.011900000274181366, -0.09560000151395798, 0.02879999950528145], [0.07519999891519547, 0.05119999870657921, -0.01600000075995922, 0.012600000016391277, -0.00839999970048666], [-0.05860000103712082, -0.08869999647140503, 0.04019999876618385, -0.0215000007301569, -0.013799999840557575]], [[0.2678000032901764, 0.7322999835014343, -0.38749998807907104, 0.4092999994754791, -0.2727000117301941], [0.12349999696016312, 0.20579999685287476, 0.9007999897003174, 0.35429999232292175, -0.07440000027418137], [-0.7089999914169312, 0.5091000199317932, 0.051600001752376556, -0.07919999957084656, 0.47870001196861267], [0.5027999877929688, -0.039000000804662704, -0.07819999754428864, 0.2206999957561493, 0.8310999870300293], [0.3968999981880188, 0.4009000062942505, 0.17239999771118164, -0.8073999881744385, 0.009399999864399433]], [0.0, 0.0, 0.0, 0.0, 0.0], [[-0.05169999971985817, 0.011599999852478504, 0.05860000103712082], [0.015599999576807022, -0.0568000003695488, 0.0071000000461936], [-0.04830000177025795, 0.012000000104308128, 0.012199999764561653], [0.0006000000284984708, -0.012400000356137753, 0.032099999487400055], [0.012500000186264515, -0.06700000166893005, -9.999999747378752e-05]], [0.0, 0.0, 0.0]]</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>[[[-0.0917000025510788, -0.049400001764297485, 0.1467999964952469, 0.07720000296831131, -0.09549999982118607, -0.3264999985694885, -0.02500000037252903, 0.07050000131130219, -0.13269999623298645, -0.19470000267028809, -0.392300009727478, -0.00839999970048666, -0.007899999618530273, -0.15399999916553497, -0.2605000138282776, 0.10559999942779541, -0.29789999127388, 0.4115000069141388, 0.23649999499320984, 0.16689999401569366], [-0.014299999922513962, 0.1446000039577484, 0.026499999687075615, 0.08500000089406967, -0.17309999465942383, 0.14100000262260437, -0.001500000013038516, 0.1648000031709671, -0.13539999723434448, 0.26930001378059387, 0.33079999685287476, -0.1454000025987625, -0.10869999974966049, -0.07620000094175339, 0.12210000306367874, 0.09380000084638596, 0.16439999639987946, -0.4205999970436096, -0.35179999470710754, 0.03959999978542328]], [[-0.19589999318122864, 0.0617000013589859, 0.15000000596046448, 0.07540000230073929, -0.19550000131130219, 0.36809998750686646, 0.3465999960899353, -0.2176000028848648, 0.026100000366568565, -0.3382999897003174, 0.16349999606609344, -0.2321999967098236, 0.3303999900817871, 0.5802000164985657, 0.0982000008225441, 0.028200000524520874, 0.07129999995231628, 0.3409000039100647, -0.400299996137619, -0.03720000013709068], [0.14800000190734863, 0.2689000070095062, -0.25440001487731934, -0.17509999871253967, -0.28780001401901245, 0.2928999960422516, 0.2328999936580658, 0.18299999833106995, 0.35249999165534973, -0.7379999756813049, 0.4514999985694885, 0.20759999752044678, 0.09070000052452087, -0.014600000344216824, 0.34200000762939453, -0.08380000293254852, -0.10270000249147415, 0.17219999432563782, 0.08229999989271164, 0.19619999825954437], [0.5960999727249146, 0.3183000087738037, 0.07180000096559525, 0.026399999856948853, -0.19259999692440033, 0.4088999927043915, -0.10080000013113022, 0.22470000386238098, -0.39980000257492065, 0.08609999716281891, 0.3391999900341034, -0.5834000110626221, -0.3001999855041504, 0.009600000455975533, 0.09019999951124191, -0.3596000075340271, -0.26820001006126404, -0.12189999967813492, -0.2522999942302704, -0.06459999829530716], [0.015399999916553497, 0.03999999910593033, -0.362199991941452, 0.3817000091075897, 0.1412999927997589, -0.4560000002384186, -0.10320000350475311, 0.015300000086426735, -0.31380000710487366, -0.1550000011920929, -0.5910000205039978, -0.0608999989926815, -0.3750999867916107, -0.25839999318122864, -0.03620000183582306, 0.21549999713897705, 0.20309999585151672, 0.6524999737739563, 0.08250000327825546, -0.1200999990105629], [-0.1071000024676323, -0.3034999966621399, -0.45100000500679016, -0.20250000059604645, -0.1103999987244606, -0.3319000005722046, 0.07150000333786011, -0.43140000104904175, -0.15539999306201935, 0.03290000185370445, -0.608299970626831, 0.13529999554157257, 0.3589000105857849, -0.5853999853134155, -0.131400004029274, 0.053700000047683716, 0.3046000003814697, -0.383899986743927, -0.28299999237060547, -0.0892999991774559], [0.16009999811649323, 0.31130000948905945, -0.06750000268220901, -0.413100004196167, -0.3531999886035919, -0.421999990940094, 0.3443000018596649, 0.23849999904632568, 0.16859999299049377, -0.37229999899864197, -0.4528999924659729, -0.3878999948501587, 0.2337000072002411, 0.14399999380111694, -0.3294999897480011, 0.15479999780654907, 0.548799991607666, 0.3197999894618988, 0.5214999914169312, -0.04769999906420708], [-0.009700000286102295, -0.042100001126527786, -0.062199998646974564, -0.06030000001192093, -0.2750000059604645, -0.07699999958276749, -0.7325999736785889, -0.03189999982714653, 0.1451999992132187, -0.3224000036716461, 0.4359000027179718, -0.21330000460147858, 0.1145000010728836, 0.12919999659061432, -0.2621999979019165, 0.2046000063419342, -0.267300009727478, 0.02630000002682209, -0.14640000462532043, 0.08020000159740448], [0.4138999879360199, 0.10090000182390213, 0.14949999749660492, -0.26269999146461487, -0.1006999984383583, 0.21850000321865082, -0.006500000134110451, 0.008700000122189522, 0.022099999710917473, -0.16820000112056732, -0.09679999947547913, -0.2971000075340271, -0.1559000015258789, 0.3215000033378601, 0.20029999315738678, 0.4235999882221222, -0.7885000109672546, 0.11010000109672546, 0.04580000042915344, 0.505299985408783], [0.32659998536109924, 0.5196999907493591, 0.12150000035762787, -0.03460000082850456, -0.06340000033378601, -0.03500000014901161, -0.2644999921321869, -0.6098999977111816, -0.1704999953508377, 0.031700000166893005, 0.38960000872612, 0.24789999425411224, 0.4431000053882599, 0.4487000107765198, 0.4659000039100647, -0.20579999685287476, -0.1071000024676323, -0.05169999971985817, -0.23559999465942383, 0.025599999353289604], [-0.21770000457763672, -0.03610000014305115, 0.10949999839067459, -0.1745000034570694, -0.21359999477863312, -0.8543999791145325, 0.5892000198364258, -0.10700000077486038, 0.36320000886917114, -0.32030001282691956, -0.4165000021457672, -0.0215000007301569, 0.1282999962568283, -0.07079999893903732, -0.4593000113964081, 0.11680000275373459, 0.19930000603199005, -0.07450000196695328, 0.31850001215934753, -0.4551999866962433], [0.3027999997138977, 0.23729999363422394, 0.04820000007748604, -0.10450000315904617, -0.4088999927043915, -0.48559999465942383, 0.04839999973773956, 0.8356000185012817, 0.67330002784729, -0.396699994802475, -0.7203999757766724, -0.23280000686645508, 0.5688999891281128, 0.4219000041484833, 0.4237000048160553, 0.5892000198364258, 0.41130000352859497, -0.04820000007748604, 0.26589998602867126, -0.444599986076355], [-0.0778999999165535, 0.18379999697208405, -0.4255000054836273, 0.046799998730421066, 0.6739000082015991, -0.26969999074935913, 0.24250000715255737, -0.08489999920129776, 0.16290000081062317, 0.40799999237060547, 0.10809999704360962, -0.18569999933242798, 0.384799987077713, -0.37610000371932983, -0.25360000133514404, 0.12399999797344208, 0.03099999949336052, -0.0949999988079071, -0.22210000455379486, -0.021199999377131462], [-0.06830000132322311, 0.04639999940991402, -0.2892000079154968, -0.10559999942779541, -0.14259999990463257, -0.2175000011920929, 0.03180000185966492, 0.06729999929666519, 0.15880000591278076, 0.4196999967098236, 0.5264999866485596, 0.003599999938160181, -0.21060000360012054, 0.3483000099658966, 0.42910000681877136, -0.4580000042915344, -0.08630000054836273, -0.15760000050067902, -0.4765999913215637, 0.4772000014781952], [0.44850000739097595, -0.20909999310970306, -0.07090000063180923, -0.391400009393692, 0.09650000184774399, 0.20960000157356262, -0.00279999990016222, -0.19470000267028809, 0.36010000109672546, -0.22030000388622284, 0.4284999966621399, 0.23659999668598175, -0.01640000008046627, 0.430400013923645, 0.20229999721050262, -0.13850000500679016, -0.2892000079154968, 0.24729999899864197, -0.3416000008583069, -0.45840001106262207], [-0.06710000336170197, 0.5544999837875366, 0.1348000019788742, -0.5274999737739563, -0.5830000042915344, 0.2775999903678894, -0.01679999940097332, -0.0203000009059906, 0.5361999869346619, 0.02199999988079071, 0.34950000047683716, -0.14800000190734863, 0.008999999612569809, 0.07000000029802322, 0.26660001277923584, 0.21040000021457672, -0.11460000276565552, 0.43050000071525574, 0.09920000284910202, -0.2996000051498413], [0.19140000641345978, -0.14579999446868896, 0.22619999945163727, 0.058800000697374344, -0.053599998354911804, 0.31029999256134033, -0.43299999833106995, -0.1754000037908554, 0.27559998631477356, -0.09880000352859497, 0.1396999955177307, -0.4657000005245209, 0.17010000348091125, 0.14509999752044678, 0.3671000003814697, -0.4625000059604645, -0.2784999907016754, 0.38510000705718994, 0.004399999976158142, 0.2524999976158142], [-0.07689999788999557, 0.390500009059906, 0.4250999987125397, -0.7398999929428101, 0.11969999969005585, 0.09839999675750732, -0.13199999928474426, 0.014600000344216824, 0.24799999594688416, -0.6730999946594238, 0.323199987411499, -0.23999999463558197, -0.002099999925121665, 0.30869999527931213, 0.73580002784729, 0.10750000178813934, 0.06809999793767929, 0.0008999999845400453, -0.07280000299215317, -0.1379999965429306], [-0.5866000056266785, -0.25940001010894775, -0.5461000204086304, 0.7200000286102295, 0.5976999998092651, 0.5012000203132629, -0.24469999969005585, -0.7736999988555908, -0.4075999855995178, 0.08449999988079071, 0.3621000051498413, 0.16040000319480896, -0.586899995803833, -0.07500000298023224, -0.2492000013589859, -0.6798999905586243, -0.6687999963760376, -0.5110999941825867, -0.27810001373291016, 0.08699999749660492], [0.12300000339746475, 0.45890000462532043, 0.2110999971628189, 0.32280001044273376, 0.24320000410079956, 0.30649998784065247, -0.5573999881744385, -0.018699999898672104, -0.2012999951839447, -0.027499999850988388, -0.04780000075697899, 0.2644999921321869, -0.1388999968767166, -0.048900000751018524, -0.4101000130176544, -0.5857999920845032, -0.6710000038146973, 0.12030000239610672, -0.6190999746322632, 0.3172000050544739], [0.24979999661445618, 0.1551000028848648, -0.10540000349283218, 0.3010999858379364, 0.13249999284744263, 0.37209999561309814, -0.1696999967098236, -0.2257000058889389, 0.2363000065088272, 0.04749999940395355, -0.44749999046325684, -0.006300000008195639, -0.5073000192642212, 0.03779999911785126, -0.41029998660087585, 0.08139999955892563, 0.4316999912261963, -0.09650000184774399, 0.03610000014305115, 0.32760000228881836]], [0.09229999780654907, 0.033799998462200165, 0.2628999948501587, -0.14319999516010284, -0.29840001463890076, -0.08060000091791153, 0.15919999778270721, 0.1598999947309494, 0.0478999987244606, -0.0934000015258789, -0.07370000332593918, -0.12610000371932983, 0.0414000004529953, -0.04129999876022339, 0.030400000512599945, 0.20509999990463257, 0.08229999989271164, 0.015399999916553497, 0.02759999968111515, 0.07259999960660934], [[-0.03269999846816063, 0.09799999743700027, 0.06360000371932983, -0.1071000024676323, -0.12809999287128448], [0.003800000064074993, 0.031700000166893005, 0.13169999420642853, -0.12359999865293503, -0.0925000011920929], [-0.07639999687671661, 0.08529999852180481, 0.10920000076293945, -0.2671000063419342, -0.16599999368190765], [-0.08320000022649765, -0.3788999915122986, 0.019700000062584877, -0.08079999685287476, -0.0754999965429306], [0.07129999995231628, 0.0284000001847744, -0.021400000900030136, 0.17499999701976776, -0.053599998354911804], [0.13600000739097595, -0.05310000106692314, 0.45010000467300415, -0.07599999755620956, -0.3075999915599823], [0.1120000034570694, -0.10729999840259552, -0.1632000058889389, 0.15860000252723694, 0.2858000099658966], [-0.09359999746084213, 0.020999999716877937, -0.03319999948143959, -0.1469999998807907, 0.26260000467300415], [0.09700000286102295, 0.3287000060081482, -0.0284000001847744, -0.22450000047683716, 0.20080000162124634], [0.02850000001490116, -0.28450000286102295, 0.0843999981880188, 0.322299987077713, 0.08209999650716782], [0.5227000117301941, -0.0658000037074089, 0.4462999999523163, 0.13339999318122864, -0.15309999883174896], [0.08940000087022781, -0.00139999995008111, -0.03700000047683716, 0.14740000665187836, 0.008100000210106373], [0.04820000007748604, 0.3562999963760376, -0.12710000574588776, 0.03799999877810478, 0.20579999685287476], [0.24410000443458557, 0.3653999865055084, 0.2460000067949295, -0.01600000075995922, -0.2782999873161316], [0.34549999237060547, 0.3912999927997589, 0.2766999900341034, -0.016200000420212746, -0.10220000147819519], [-0.24480000138282776, 0.06120000034570694, -0.17890000343322754, -0.13269999623298645, 0.29980000853538513], [0.054999999701976776, 0.1607999950647354, -0.2994000017642975, 0.1535000056028366, 0.4237000048160553], [-0.19760000705718994, -0.002099999925121665, -0.07760000228881836, -0.32089999318122864, -0.23180000483989716], [-0.15440000593662262, 0.11949999630451202, -0.25859999656677246, -0.17000000178813934, 0.2045000046491623], [-0.17159999907016754, -0.2290000021457672, 0.14090000092983246, -0.10159999877214432, -0.23690000176429749]], [[0.3174999952316284, 0.8794000148773193, -0.46889999508857727, 0.36399999260902405, -0.13030000030994415], [0.383899986743927, 0.4724999964237213, 1.0992000102996826, 0.3846000134944916, -0.14589999616146088], [-0.8101000189781189, 0.5573999881744385, -0.1907999962568283, -0.17990000545978546, 0.6797999739646912], [0.5656999945640564, 0.06369999796152115, -0.19110000133514404, 0.3328999876976013, 1.082200050354004], [0.6583999991416931, 0.6039999723434448, 0.32350000739097595, -0.9710000157356262, -0.273499995470047]], [-0.14659999310970306, -9.999999747378752e-05, -0.06970000267028809, -0.25119999051094055, 0.019300000742077827], [[-0.21050000190734863, -0.044199999421834946, 0.20280000567436218], [0.12620000541210175, -0.1136000007390976, 0.1339000016450882], [-0.43700000643730164, -0.03819999843835831, 0.012900000438094139], [0.18410000205039978, -0.10159999877214432, 0.1581999957561493], [0.3560999929904938, -0.0674000009894371, 0.10660000145435333]], [-0.06539999693632126, -0.007699999958276749, 0.12549999356269836]]</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>[0.7527794131211136]</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>[0.0564322098278582]</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>[0.733860569117368]</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>[0.06076050259837044]</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>[-1.6270724151224587]</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>[0.8597874575654096]</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>[0.6761688961031403]</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>[0.07439018104805836]</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>[0.8617129859122938]</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>[0.03279629029927554]</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>[-0.7128820552225847]</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>[0.5631055968576162]</t>
+        </is>
+      </c>
+      <c r="Q19" t="inlineStr">
+        <is>
+          <t>[-0.042898215094111736]</t>
+        </is>
+      </c>
+      <c r="R19" t="inlineStr">
+        <is>
+          <t>[0.11245126032585143]</t>
+        </is>
+      </c>
+      <c r="S19" t="inlineStr">
+        <is>
+          <t>[-0.060376670156708334]</t>
+        </is>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>[0.08934769850025923]</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>[-0.6761437086734039]</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>[0.16027810872359402]</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>[-0.20838617060307452]</t>
+        </is>
+      </c>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>[0.1265912887267622]</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>[-0.11305086883060933]</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>[0.09159652855767692]</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>[-1.2069944063136857]</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>[0.20305313953667622]</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>[-0.6303719232621325]</t>
+        </is>
+      </c>
+      <c r="AD19" t="inlineStr">
+        <is>
+          <t>[0.13661859904003376]</t>
+        </is>
+      </c>
+      <c r="AE19" t="inlineStr">
+        <is>
+          <t>[-0.4985238360511901]</t>
+        </is>
+      </c>
+      <c r="AF19" t="inlineStr">
+        <is>
+          <t>[0.16135816063579703]</t>
+        </is>
+      </c>
+      <c r="AG19" t="inlineStr">
+        <is>
+          <t>[-2.763647869481936]</t>
+        </is>
+      </c>
+      <c r="AH19" t="inlineStr">
+        <is>
+          <t>[0.2802034275152696]</t>
+        </is>
+      </c>
+      <c r="AI19" t="inlineStr">
+        <is>
+          <t>[-0.9695850400813699]</t>
+        </is>
+      </c>
+      <c r="AJ19" t="inlineStr">
+        <is>
+          <t>[0.16140530146490292]</t>
+        </is>
+      </c>
+      <c r="AK19" t="inlineStr">
+        <is>
+          <t>[-0.5565863689205452]</t>
+        </is>
+      </c>
+      <c r="AL19" t="inlineStr">
+        <is>
+          <t>[0.16522023851648343]</t>
+        </is>
+      </c>
+      <c r="AM19" t="inlineStr">
+        <is>
+          <t>[-3.2923479665779265]</t>
+        </is>
+      </c>
+      <c r="AN19" t="inlineStr">
+        <is>
+          <t>[0.3296834416559036]</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>model_20_5_3</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>[20, 5]</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>[[[0.025800000876188278, -0.06419999897480011, -0.005400000140070915, 0.029899999499320984, 0.02449999935925007, -0.04399999976158142, -0.07069999724626541, 0.009800000116229057, -0.008299999870359898, -0.02370000071823597, 0.05350000038743019, 0.012000000104308128, 0.05649999901652336, -0.08569999784231186, -0.01899999938905239, 0.1006999984383583, 0.043699998408555984, 0.05550000071525574, -0.012400000356137753, 0.024900000542402267], [-0.02850000001490116, 0.019300000742077827, -0.030400000512599945, -0.006000000052154064, 0.017100000753998756, 0.026000000536441803, 0.024000000208616257, -0.00559999980032444, 0.03750000149011612, 0.023600000888109207, 0.04470000043511391, -0.11550000309944153, -0.05739999935030937, -0.038600001484155655, 0.09920000284910202, -0.01850000023841858, 0.06840000301599503, 0.01769999973475933, 0.0771000012755394, -9.999999747378752e-05]], [[-0.01510000042617321, -0.1469999998807907, -0.39660000801086426, -0.18140000104904175, -0.3765000104904175, 0.13760000467300415, 0.13740000128746033, 0.03180000185966492, -0.060499999672174454, 0.19740000367164612, -0.017500000074505806, -0.17270000278949738, -0.045899998396635056, 0.3382999897003174, -0.042100001126527786, 0.0414000004529953, -0.5893999934196472, 0.017400000244379044, -0.008700000122189522, -0.25850000977516174], [0.23800000548362732, -0.4147000014781952, 0.0658000037074089, 0.01889999955892563, -0.053700000047683716, -0.28119999170303345, 0.5396000146865845, -0.23399999737739563, -0.025499999523162842, 0.13410000503063202, 0.05180000141263008, -0.10480000078678131, -0.023000000044703484, -0.12860000133514404, 0.07450000196695328, 0.016200000420212746, 0.0026000000070780516, 0.39239999651908875, 0.18369999527931213, 0.30970001220703125], [0.002400000113993883, 0.2800000011920929, -0.07349999994039536, -0.24809999763965607, 0.1006999984383583, -0.002400000113993883, 0.03889999911189079, 0.13609999418258667, -0.0215000007301569, 0.11800000071525574, 0.210099995136261, -0.2840999960899353, -0.0052999998442828655, 0.15440000593662262, 0.20589999854564667, 0.5037000179290771, 0.20419999957084656, -0.09619999676942825, 0.5586000084877014, 0.04670000076293945], [0.10090000182390213, 0.06400000303983688, 0.18619999289512634, 0.6800000071525574, -0.08030000329017639, -0.028599999845027924, -0.07660000026226044, 0.20000000298023224, -0.10999999940395355, 0.2451000064611435, -0.09629999846220016, -0.32690000534057617, 0.16290000081062317, 0.30320000648498535, 0.2930999994277954, 0.03889999911189079, 0.049800001084804535, 0.1298000067472458, -0.13760000467300415, -0.05559999868273735], [-0.04100000113248825, 0.20509999990463257, -0.10830000042915344, 0.0006000000284984708, 0.09529999643564224, -0.16910000145435333, 0.0421999990940094, -0.20229999721050262, 0.3222000002861023, -0.1590999960899353, 0.18369999527931213, -0.07940000295639038, 0.42649999260902405, 0.45899999141693115, -0.2896000146865845, 0.020099999383091927, -0.07580000162124634, -0.006200000178068876, -0.19419999420642853, 0.4178999960422516], [-0.05079999938607216, -0.21449999511241913, 0.02759999968111515, 0.16130000352859497, 0.25209999084472656, 0.40139999985694885, 0.12929999828338623, 0.02879999950528145, -0.1687999963760376, -0.6015999913215637, -0.1386999934911728, 0.13809999823570251, -0.11429999768733978, 0.2533000111579895, 0.06300000101327896, 0.3431999981403351, -0.11829999834299088, 0.18880000710487366, 0.03280000016093254, 0.06340000033378601], [0.1582999974489212, 0.3578000068664551, 0.19200000166893005, 0.07729999721050262, -0.28870001435279846, -0.07699999958276749, -0.2736999988555908, -0.34459999203681946, -0.2345000058412552, -0.2029000073671341, 0.28760001063346863, -0.010099999606609344, 0.04360000044107437, -0.27730000019073486, -0.06120000034570694, 0.24549999833106995, -0.3075999915599823, 0.31290000677108765, 0.006300000008195639, -0.0820000022649765], [0.1469999998807907, 0.19979999959468842, -0.3531999886035919, 0.22179999947547913, 0.20960000157356262, 0.012199999764561653, 0.2214999943971634, 0.04320000112056732, 0.1842000037431717, -0.009700000286102295, 0.5551999807357788, 0.32839998602867126, -0.18150000274181366, 0.00570000009611249, 0.34209999442100525, -0.15690000355243683, -0.035100001841783524, 0.0714000016450882, -0.09350000321865082, -0.17219999432563782], [-0.149399995803833, -0.040699999779462814, -0.29269999265670776, -0.015799999237060547, -0.2305999994277954, 0.1949000060558319, -0.06499999761581421, -0.1501999944448471, 0.3684999942779541, -0.12929999828338623, -0.02539999969303608, -0.3377000093460083, -0.1103999987244606, -0.08749999850988388, -0.05860000103712082, 0.07850000262260437, 0.4812000095844269, 0.4083000123500824, -0.1754000037908554, -0.21539999544620514], [0.2418999969959259, 0.13590000569820404, -0.13950000703334808, 0.09149999916553497, -0.3068000078201294, 0.2142000049352646, 0.14800000190734863, 0.23190000653266907, -0.06549999862909317, -0.030700000002980232, 0.05139999836683273, -0.13609999418258667, -0.3140999972820282, -0.22380000352859497, -0.09130000323057175, 0.17630000412464142, 0.038600001484155655, -0.3125, -0.31940001249313354, 0.5135999917984009], [-0.1501999944448471, -0.14560000598430634, -0.4163999855518341, 0.28299999237060547, -0.2565999925136566, -0.541700005531311, -0.22200000286102295, 0.24500000476837158, -0.048500001430511475, -0.32580000162124634, -0.0681999996304512, 0.12950000166893005, -0.043299999088048935, -0.03720000013709068, -0.05169999971985817, 0.009700000286102295, 0.03420000150799751, -0.040699999779462814, 0.29589998722076416, 0.08860000222921371], [0.5156000256538391, -0.19140000641345978, -0.3995000123977661, 0.1193000003695488, 0.42329999804496765, 0.14409999549388885, -0.2985000014305115, -0.012799999676644802, -0.053300000727176666, 0.1444000005722046, -0.0502999983727932, -0.12710000574588776, 0.22370000183582306, -0.21729999780654907, -0.27889999747276306, 0.08470000326633453, -0.04749999940395355, 0.017100000753998756, 0.0763000026345253, -0.03929999843239784], [0.367900013923645, -0.05849999934434891, -0.0697999969124794, -0.41019999980926514, -0.20890000462532043, 0.015699999406933784, -0.2874999940395355, 0.13030000030994415, -0.009200000204145908, -0.09070000052452087, -0.1453000009059906, 0.21729999780654907, 0.2515999972820282, 0.12999999523162842, 0.5281000137329102, -0.058800000697374344, 0.10339999943971634, 0.1876000016927719, -0.15029999613761902, 0.19189999997615814], [-0.24560000002384186, 0.17260000109672546, -0.25839999318122864, 0.04600000008940697, -0.049800001084804535, 0.06520000100135803, 0.4083000123500824, -0.009999999776482582, -0.2329999953508377, -0.019899999722838402, -0.1800999939441681, 0.09139999747276306, 0.6075000166893005, -0.35089999437332153, 0.13809999823570251, 0.15389999747276306, 0.05950000137090683, -0.08550000190734863, -0.12060000002384186, -0.10830000042915344], [0.07680000364780426, -0.10050000250339508, 0.2689000070095062, 0.09889999777078629, -0.15479999780654907, 0.15600000321865082, 0.042500000447034836, 0.35030001401901245, 0.6704999804496765, -0.07750000059604645, 0.013799999840557575, 0.06019999831914902, 0.23649999499320984, -0.26919999718666077, 0.002099999925121665, 0.11789999902248383, -0.2816999852657318, -0.012000000104308128, 0.21209999918937683, -0.053700000047683716], [-0.29580000042915344, -0.5209000110626221, 0.034699998795986176, 0.07270000129938126, -0.14869999885559082, 0.2587999999523163, -0.25220000743865967, -0.13249999284744263, -0.13089999556541443, 0.09860000014305115, 0.5501999855041504, 0.008299999870359898, 0.21690000593662262, -0.03590000048279762, 0.11309999972581863, 0.02850000001490116, 0.094200000166893, -0.2046000063419342, 0.010999999940395355, 0.14820000529289246], [-0.27970001101493835, 0.09589999914169312, -0.007699999958276749, -0.10999999940395355, 0.09650000184774399, 0.09109999984502792, -0.05429999902844429, 0.5372999906539917, -0.18770000338554382, 0.25049999356269836, 0.15559999644756317, 0.13979999721050262, 0.029400000348687172, -0.0430000014603138, -0.2761000096797943, -0.041999999433755875, -0.029999999329447746, 0.5662999749183655, -0.045899998396635056, 0.21199999749660492], [0.249099999666214, -0.03579999879002571, 0.07620000094175339, 0.10369999706745148, -0.3043999969959259, 0.04989999905228615, 0.10289999842643738, -0.04769999906420708, -0.01590000092983246, 0.22360000014305115, -0.0012000000569969416, 0.5584999918937683, 0.04610000178217888, 0.2655999958515167, -0.3582000136375427, 0.3012000024318695, 0.3407999873161316, -0.03139999881386757, 0.04309999942779541, -0.1981000006198883], [-0.27810001373291016, 0.0949999988079071, -0.17270000278949738, 0.17010000348091125, 0.06469999998807907, 0.10350000113248825, -0.2102999985218048, -0.35010001063346863, 0.22920000553131104, 0.39089998602867126, -0.32199999690055847, 0.2865000069141388, -0.17980000376701355, -0.07159999758005142, 0.20880000293254852, 0.22869999706745148, -0.17309999465942383, 0.07919999957084656, 0.07259999960660934, 0.32749998569488525], [-0.07819999754428864, -0.23600000143051147, 0.07190000265836716, -0.14630000293254852, 0.21930000185966492, -0.4359000027179718, -0.05510000139474869, 0.125900000333786, 0.08640000224113464, 0.07750000059604645, 0.06920000165700912, -0.006500000134110451, -0.0877000018954277, -0.06239999830722809, 0.06840000301599503, 0.5554999709129333, -0.08299999684095383, -0.04580000042915344, -0.519599974155426, -0.18029999732971191]], [0.0, 0.0, 0.0, 0.0, 0.0, 0.0, 0.0, 0.0, 0.0, 0.0, 0.0, 0.0, 0.0, 0.0, 0.0, 0.0, 0.0, 0.0, 0.0, 0.0], [[0.025800000876188278, -0.06419999897480011, -0.005400000140070915, 0.029899999499320984, 0.02449999935925007], [-0.04399999976158142, -0.07069999724626541, 0.009800000116229057, -0.008299999870359898, -0.02370000071823597], [0.05350000038743019, 0.012000000104308128, 0.05649999901652336, -0.08569999784231186, -0.01899999938905239], [0.1006999984383583, 0.043699998408555984, 0.05550000071525574, -0.012400000356137753, 0.024900000542402267], [-0.02850000001490116, 0.019300000742077827, -0.030400000512599945, -0.006000000052154064, 0.017100000753998756], [0.026000000536441803, 0.024000000208616257, -0.00559999980032444, 0.03750000149011612, 0.023600000888109207], [0.04470000043511391, -0.11550000309944153, -0.05739999935030937, -0.038600001484155655, 0.09920000284910202], [-0.01850000023841858, 0.06840000301599503, 0.01769999973475933, 0.0771000012755394, -9.999999747378752e-05], [-0.06710000336170197, 0.0414000004529953, 0.03220000118017197, 0.006500000134110451, 9.999999747378752e-05], [0.05260000005364418, -0.08470000326633453, -0.0406000018119812, -0.024700000882148743, 0.05829999968409538], [0.020400000736117363, 0.018699999898672104, 0.021900000050663948, -0.09279999881982803, -0.046799998730421066], [-0.05609999969601631, 0.025499999523162842, 0.016599999740719795, 0.04809999838471413, -0.06289999932050705], [0.06310000270605087, -0.032999999821186066, 0.0071000000461936, 0.06989999860525131, 0.03819999843835831], [-0.040699999779462814, 0.04129999876022339, -0.031599998474121094, 0.039400000125169754, -0.06400000303983688], [-0.03060000017285347, 0.08089999854564667, -0.13809999823570251, 0.01510000042617321, -0.051500000059604645], [-0.1128000020980835, 0.018699999898672104, -0.013700000010430813, 0.04520000144839287, -0.012199999764561653], [-0.02500000037252903, 0.019500000402331352, 0.045899998396635056, 0.03240000084042549, 0.011500000022351742], [0.0210999995470047, -0.015599999576807022, -0.021199999377131462, 0.041200000792741776, -0.023000000044703484], [0.0007999999797903001, -0.02669999934732914, 0.04479999840259552, -0.058400001376867294, -0.04749999940395355], [0.03579999879002571, 0.03180000185966492, 0.07940000295639038, -0.07440000027418137, -0.11640000343322754]], [[0.8921999931335449, 0.2921999990940094, -0.03920000046491623, 0.3021000027656555, 0.16060000658035278], [0.024299999698996544, 0.1266999989748001, -0.17560000717639923, 0.2799000144004822, -0.9350000023841858], [-0.11460000276565552, 0.46709999442100525, -0.8184000253677368, -0.2872999906539917, 0.12809999287128448], [-0.33340001106262207, 0.800000011920929, 0.4381999969482422, 0.22300000488758087, 0.08420000225305557], [-0.28119999170303345, -0.20090000331401825, -0.325300008058548, 0.8356000185012817, 0.2766999900341034]], [0.0, 0.0, 0.0, 0.0, 0.0], [[0.025800000876188278, -0.06419999897480011, -0.005400000140070915], [0.029899999499320984, 0.02449999935925007, -0.04399999976158142], [-0.07069999724626541, 0.009800000116229057, -0.008299999870359898], [-0.02370000071823597, 0.05350000038743019, 0.012000000104308128], [0.05649999901652336, -0.08569999784231186, -0.01899999938905239]], [0.0, 0.0, 0.0]]</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>[[[0.09399999678134918, -0.16599999368190765, -0.15950000286102295, 0.23880000412464142, 0.25450000166893005, -0.2084999978542328, -0.13359999656677246, -0.01810000091791153, -0.053599998354911804, 0.09229999780654907, 0.02800000086426735, 0.3246999979019165, 0.31790000200271606, 0.08869999647140503, -0.14390000700950623, 0.24390000104904175, -0.025200000032782555, 0.1632000058889389, -0.17339999973773956, -0.04659999907016754], [-0.15520000457763672, -0.04899999871850014, 0.18080000579357147, -0.2079000025987625, -0.40310001373291016, 0.298799991607666, -0.026900000870227814, 0.28769999742507935, 0.227400004863739, -0.14149999618530273, 0.019300000742077827, -0.2854999899864197, -0.1835000067949295, -0.16899999976158142, 0.3626999855041504, -0.1776999980211258, 0.17970000207424164, -0.21379999816417694, 0.21490000188350677, 0.020800000056624413]], [[0.19220000505447388, -0.4494999945163727, -0.6207000017166138, 0.1428000032901764, -0.4634999930858612, 0.4332999885082245, -0.022199999541044235, 0.249099999666214, -0.3750999867916107, -0.09809999912977219, -0.1565999984741211, -0.2167000025510788, 0.3361999988555908, 0.5149000287055969, 0.03920000046491623, -0.03449999913573265, -0.727400004863739, -0.14190000295639038, -0.23000000417232513, -0.4343999922275543], [0.18860000371932983, -0.2775000035762787, 0.28450000286102295, -0.15230000019073486, 0.03579999879002571, -0.24580000340938568, 0.8467000126838684, -0.37059998512268066, -0.10830000042915344, 0.3434000015258789, 0.0284000001847744, -0.1014999970793724, -0.13300000131130219, -0.22390000522136688, 0.07069999724626541, -0.05249999836087227, 0.05249999836087227, 0.39590001106262207, 0.3034999966621399, 0.3441999852657318], [-0.11969999969005585, 0.6689000129699707, 0.1582999974489212, -0.4740000069141388, -0.0015999999595806003, -0.04430000111460686, 0.3499000072479248, -0.13130000233650208, 0.21070000529289246, 0.07519999891519547, 0.33169999718666077, -0.30570000410079956, -0.25760000944137573, 0.010300000198185444, 0.11089999973773956, 0.4056999981403351, 0.2231999933719635, 0.12970000505447388, 0.795199990272522, -0.030300000682473183], [0.32019999623298645, -0.3846000134944916, -0.15309999883174896, 1.1345000267028809, -0.18850000202655792, -0.09880000352859497, -0.6570000052452087, 0.5680000185966492, -0.21709999442100525, 0.11420000344514847, -0.07259999960660934, -0.2282000035047531, 0.4138999879360199, 0.5838000178337097, 0.14980000257492065, 0.19789999723434448, -0.0771000012755394, -0.1363999992609024, -0.3337000012397766, -0.11919999867677689], [0.012400000356137753, 0.14149999618530273, -0.04740000143647194, -0.0940999984741211, 0.18359999358654022, -0.2590999901294708, 0.060600001364946365, -0.14820000529289246, 0.23749999701976776, 0.31679999828338623, 0.1467999964952469, -0.20010000467300415, 0.447299987077713, 0.49559998512268066, -0.2996000051498413, 0.09300000220537186, 0.0860000029206276, -0.1436000019311905, -0.2612000107765198, 0.6517000198364258], [-0.17139999568462372, 0.021700000390410423, 0.17309999465942383, -0.1062999963760376, 0.1023000031709671, 0.3449000120162964, 0.22030000388622284, -0.07970000058412552, -0.03849999979138374, -0.5613999962806702, -0.1476999968290329, -0.020099999383091927, -0.47429999709129333, 0.06440000236034393, 0.14820000529289246, 0.23980000615119934, -0.18639999628067017, 0.38600000739097595, 0.1906999945640564, -0.03739999979734421], [0.12359999865293503, 0.5206000208854675, 0.3684000074863434, -0.06589999794960022, -0.28630000352859497, 0.08229999989271164, 0.05400000140070915, -0.41749998927116394, -0.29679998755455017, -0.1817999929189682, 0.3084000051021576, 0.019999999552965164, -0.05090000107884407, -0.3887999951839447, 0.02879999950528145, 0.1664000004529953, -0.27459999918937683, 0.30709999799728394, 0.10320000350475311, -0.19220000505447388], [0.1525000035762787, 0.19499999284744263, -0.4296000003814697, 0.1535000056028366, 0.1216999962925911, -0.06480000168085098, 0.010099999606609344, 0.12610000371932983, 0.35740000009536743, -0.15139999985694885, 0.453000009059906, 0.16990000009536743, -0.23880000412464142, 0.061799999326467514, 0.40720000863075256, -0.2142000049352646, -0.09589999914169312, 0.13169999420642853, -0.14800000190734863, -0.14509999752044678], [-0.2890999913215637, 0.13079999387264252, -0.1728000044822693, -0.2475000023841858, -0.2818000018596649, 0.10080000013113022, -0.056699998676776886, -0.2110999971628189, 0.616599977016449, -0.1770000010728836, 0.03750000149011612, -0.39089998602867126, -0.41280001401901245, -0.24160000681877136, -0.06379999965429306, 0.08020000159740448, 0.5633999705314636, 0.5393999814987183, -0.019500000402331352, -0.13120000064373016], [0.2685000002384186, -0.1152999997138977, -0.2867000102996826, 0.20000000298023224, -0.366100013256073, 0.4943000078201294, -0.020899999886751175, 0.48330000042915344, -0.3109000027179718, -0.4964999854564667, 0.031099999323487282, -0.017999999225139618, -0.20319999754428864, -0.09109999984502792, -0.0008999999845400453, 0.10689999908208847, -0.09390000253915787, -0.3285999894142151, -0.3822999894618988, 0.2667999863624573], [-0.1800999939441681, -0.07010000199079514, -0.3919000029563904, 0.1257999986410141, -0.24729999899864197, -0.6686000227928162, -0.2547000050544739, 0.14910000562667847, 0.2069000005722046, -0.35659998655319214, -0.08340000361204147, 0.08879999816417694, -0.1761000007390976, -0.1412000060081482, -0.12080000340938568, 0.02199999988079071, 0.04699999839067459, 0.00139999995008111, 0.33410000801086426, 0.16169999539852142], [0.8356000185012817, -0.27970001101493835, -0.47369998693466187, 0.5169000029563904, 0.6467999815940857, -0.3490999937057495, -0.5964999794960022, -0.289000004529953, -0.1615000069141388, 0.5234000086784363, -0.07349999994039536, -0.1526000052690506, 0.4293999969959259, 0.013700000010430813, -0.8270999789237976, 0.24529999494552612, -0.17110000550746918, -0.2678000032901764, -0.11800000071525574, 0.1356000006198883], [0.6327000260353088, -0.4708000123500824, -0.5116999745368958, 0.060100000351667404, -0.2517000138759613, 0.006899999920278788, -0.7924000024795532, 0.5716999769210815, -0.1736000031232834, 0.00570000009611249, -0.17820000648498535, 0.17329999804496765, 0.6218000054359436, 0.3111000061035156, 0.5825999975204468, 0.045899998396635056, -0.07429999858140945, -0.1143999993801117, -0.45260000228881836, -0.005499999970197678], [-0.0908999964594841, -0.004999999888241291, -0.3806000053882599, 0.20200000703334808, -0.02459999918937683, 0.12680000066757202, 0.32199999690055847, 0.2061000019311905, -0.4999000132083893, -0.19609999656677246, -0.3903999924659729, -0.10040000081062317, 0.8141000270843506, -0.1152999997138977, 0.32260000705718994, 0.12999999523162842, 0.0010000000474974513, -0.1256999969482422, -0.3874000012874603, -0.14800000190734863], [-0.011699999682605267, -0.008700000122189522, 0.2944999933242798, -0.1607999950647354, -0.310699999332428, 0.21580000221729279, -0.024800000712275505, 0.3684999942779541, 0.8251000046730042, -0.11949999630451202, 0.04149999842047691, 0.06289999932050705, 0.009700000286102295, -0.43529999256134033, 0.10939999669790268, 0.0885000005364418, -0.29600000381469727, 0.16200000047683716, 0.28110000491142273, -0.09589999914169312], [-0.24809999763965607, -0.5260000228881836, -0.019600000232458115, 0.16089999675750732, -0.044599998742341995, 0.13249999284744263, -0.4178999960422516, -0.11490000039339066, 0.01810000091791153, 0.05480000004172325, 0.5852000117301941, 0.04340000078082085, 0.2777999937534332, -0.016899999231100082, -0.06700000166893005, 0.08349999785423279, 0.10100000351667404, -0.260699987411499, 0.021800000220537186, 0.22789999842643738], [-0.3400999903678894, 0.13179999589920044, -0.02500000037252903, -0.2410999983549118, -0.0052999998442828655, 0.12200000137090683, -0.15780000388622284, 0.5602999925613403, -0.0026000000070780516, 0.045099999755620956, 0.1941000074148178, 0.12389999628067017, -0.10779999941587448, -0.1574999988079071, -0.225600004196167, -0.039000000804662704, -0.041999999433755875, 0.6725999712944031, 0.010599999688565731, 0.18379999697208405], [0.2168000042438507, -0.1137000024318695, 0.1906999945640564, 0.18310000002384186, 0.2476000040769577, -0.5335000157356262, 0.004600000102072954, -0.39309999346733093, 0.11779999732971191, 0.691100001335144, 0.2061000019311905, 0.5889000296592712, -0.10189999639987946, 0.30239999294281006, -0.7297000288963318, 0.7416999936103821, 0.5091999769210815, -0.33889999985694885, 0.20569999516010284, 0.2004999965429306], [-0.6471999883651733, 0.3603000044822693, 0.03229999914765358, -0.1914999932050705, 0.12849999964237213, 0.02879999950528145, -0.0544000007212162, -0.5598000288009644, 0.6826000213623047, 0.23810000717639923, -0.10419999808073044, 0.34549999237060547, -0.5720000267028809, -0.351500004529953, 0.12120000272989273, 0.27730000019073486, 0.01759999990463257, 0.38609999418258667, 0.39410001039505005, 0.477400004863739], [-0.1185000017285347, -0.027499999850988388, 0.3091000020503998, -0.5069000124931335, -0.18690000474452972, -0.17739999294281006, 0.18880000710487366, 0.13650000095367432, 0.012500000186264515, -0.1996999979019165, -0.1143999993801117, -0.27549999952316284, -0.36730000376701355, -0.13109999895095825, 0.17890000343322754, 0.3203999996185303, -0.0885000005364418, -0.04479999840259552, -0.4350999891757965, -0.3571999967098236]], [-0.013399999588727951, -0.0008999999845400453, -0.02930000051856041, -0.03869999945163727, 0.1875, 0.006399999838322401, -0.11949999630451202, 0.05849999934434891, 0.002300000051036477, -0.007499999832361937, -0.01679999940097332, 0.006099999882280827, -0.01940000057220459, 0.08250000327825546, 0.04430000111460686, -0.01979999989271164, 0.014299999922513962, -0.06970000267028809, -0.048900000751018524, 0.046799998730421066], [[0.26499998569488525, -0.13220000267028809, 0.14509999752044678, -0.10350000113248825, 0.004000000189989805], [-0.13660000264644623, -0.3248000144958496, -0.36719998717308044, -0.07959999889135361, -0.0674000009894371], [0.000699999975040555, -0.30489999055862427, -0.2766999900341034, 0.01940000057220459, 0.08250000327825546], [0.23890000581741333, 0.18709999322891235, 0.7286999821662903, -0.12520000338554382, -0.06549999862909317], [-0.22040000557899475, -0.2492000013589859, 0.8794999718666077, -0.37439998984336853, -0.09719999879598618], [0.011800000444054604, 0.6340000033378601, -1.0082000494003296, 0.4788999855518341, -0.040800001472234726], [0.01209999993443489, -0.3447999954223633, -0.3377000093460083, -0.10859999805688858, 0.07429999858140945], [-0.03150000050663948, 0.5785999894142151, 0.013100000098347664, 0.24560000002384186, 0.027000000700354576], [-0.2460000067949295, 0.20970000326633453, -0.10339999943971634, 0.17820000648498535, 0.10769999772310257], [0.09730000048875809, -0.17720000445842743, 0.5188000202178955, -0.18459999561309814, -0.13109999895095825], [-0.11999999731779099, -0.0017000000225380063, 0.10320000350475311, -0.0406000018119812, 0.11400000005960464], [-0.07810000330209732, -0.49219998717308044, 0.6973999738693237, -0.29820001125335693, -0.21240000426769257], [0.44940000772476196, 0.125900000333786, 0.011099999770522118, 0.13089999556541443, 0.0722000002861023], [0.2117999941110611, 0.14010000228881836, 0.29249998927116394, -0.14090000092983246, -0.1298999935388565], [-0.03189999982714653, 0.7146000266075134, -0.6779999732971191, 0.37299999594688416, -0.07500000298023224], [-0.16979999840259552, -0.16850000619888306, 0.5034000277519226, -0.06610000133514404, 0.0035000001080334187], [-0.10750000178813934, 0.11680000275373459, 0.10729999840259552, 0.15800000727176666, 0.1906999945640564], [-0.20419999957084656, -0.1972000002861023, -0.10189999639987946, 0.07400000095367432, -0.2531000077724457], [-0.38510000705718994, -0.1770000010728836, 0.21170000731945038, 0.005499999970197678, 0.04540000110864639], [-0.10530000180006027, -0.0502999983727932, 0.41100001335144043, -0.13840000331401825, 0.19789999723434448]], [[1.1864999532699585, 0.41620001196861267, -0.13600000739097595, 0.4442000091075897, 0.02979999966919422], [-0.042899999767541885, 0.3684000074863434, -0.27799999713897705, 0.36320000886917114, -0.9391000270843506], [-0.28630000352859497, 0.48089998960494995, -0.47760000824928284, -0.4375999867916107, 0.2409999966621399], [-0.09489999711513519, 1.1746000051498413, 0.2687999904155731, 0.313400000333786, 0.06549999862909317], [-0.0738999992609024, -0.06949999928474426, -0.5809000134468079, 0.9830999970436096, -0.07900000363588333]], [-0.15209999680519104, 0.13500000536441803, 0.0031999999191612005, -0.08399999886751175, -0.09619999676942825], [[0.30489999055862427, -0.05429999902844429, 0.19539999961853027], [0.48969998955726624, 0.0689999982714653, -0.21960000693798065], [-0.6830999851226807, 0.09130000323057175, -0.040300000458955765], [0.47999998927116394, 0.027000000700354576, 0.009499999694526196], [-0.033799998462200165, -0.12870000302791595, 0.11620000004768372]], [-0.06629999727010727, 0.028599999845027924, 0.054099999368190765]]</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>[0.9035265468521617]</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>[0.022021669876238836]</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>[0.8141289853842197]</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>[0.042434960610945226]</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>[0.759793048549942]</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>[0.0786148576978439]</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>[0.8442619894858965]</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>[0.03577599143131886]</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>[0.725237611373178]</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>[0.06516293030242472]</t>
+        </is>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>[0.6405814558802053]</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>[0.11815792756493806]</t>
+        </is>
+      </c>
+      <c r="Q20" t="inlineStr">
+        <is>
+          <t>[-0.16128084699640555]</t>
+        </is>
+      </c>
+      <c r="R20" t="inlineStr">
+        <is>
+          <t>[0.1252159539128502]</t>
+        </is>
+      </c>
+      <c r="S20" t="inlineStr">
+        <is>
+          <t>[-0.10505381193149521]</t>
+        </is>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>[0.09311220964567801]</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>[-1.158136374769236]</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>[0.2063677563717811]</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>[-0.3162444092694843]</t>
+        </is>
+      </c>
+      <c r="X20" t="inlineStr">
+        <is>
+          <t>[0.13789058506492305]</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>[-0.15478017152169965]</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>[0.09503056681475328]</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>[-1.4308177916404263]</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>[0.2236458700675312]</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>[-0.972965168036318]</t>
+        </is>
+      </c>
+      <c r="AD20" t="inlineStr">
+        <is>
+          <t>[0.16532653277823228]</t>
+        </is>
+      </c>
+      <c r="AE20" t="inlineStr">
+        <is>
+          <t>[-0.8221264973198403]</t>
+        </is>
+      </c>
+      <c r="AF20" t="inlineStr">
+        <is>
+          <t>[0.19620307196984307]</t>
+        </is>
+      </c>
+      <c r="AG20" t="inlineStr">
+        <is>
+          <t>[-3.8906045206966677]</t>
+        </is>
+      </c>
+      <c r="AH20" t="inlineStr">
+        <is>
+          <t>[0.36410530337672325]</t>
+        </is>
+      </c>
+      <c r="AI20" t="inlineStr">
+        <is>
+          <t>[-1.415083471582307]</t>
+        </is>
+      </c>
+      <c r="AJ20" t="inlineStr">
+        <is>
+          <t>[0.19791340199128563]</t>
+        </is>
+      </c>
+      <c r="AK20" t="inlineStr">
+        <is>
+          <t>[-0.8296334014305451]</t>
+        </is>
+      </c>
+      <c r="AL20" t="inlineStr">
+        <is>
+          <t>[0.19420218050072738]</t>
+        </is>
+      </c>
+      <c r="AM20" t="inlineStr">
+        <is>
+          <t>[-3.8481789659364942]</t>
+        </is>
+      </c>
+      <c r="AN20" t="inlineStr">
+        <is>
+          <t>[0.37237529196124297]</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>model_20_5_4</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>[20, 5]</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>[[[0.07999999821186066, 0.005799999926239252, -0.07419999688863754, 0.015799999237060547, 0.03500000014901161, -0.018699999898672104, -0.015799999237060547, -0.043299999088048935, 0.013000000268220901, 0.042500000447034836, -0.10080000013113022, 0.057500001043081284, -0.02810000069439411, 0.10559999942779541, -0.01590000092983246, -0.015799999237060547, 0.06909999996423721, 0.006899999920278788, 0.009600000455975533, -0.08489999920129776], [-0.06239999830722809, -0.00860000029206276, -0.0658000037074089, 0.037300001829862595, -0.05820000171661377, -0.061500001698732376, 0.04960000142455101, 0.0917000025510788, -0.01510000042617321, -0.06719999760389328, -0.00279999990016222, 0.1103999987244606, 0.04879999905824661, 0.0210999995470047, 0.03229999914765358, 0.1177000030875206, -0.002199999988079071, -0.013399999588727951, 0.054999999701976776, 0.02410000003874302]], [[-0.24650000035762787, -0.18479999899864197, -0.6194000244140625, 0.05130000039935112, 0.28040000796318054, -0.03759999945759773, -0.3797999918460846, 0.041600000113248825, 0.03660000115633011, 0.11620000004768372, -0.1500999927520752, -0.02319999970495701, 0.34380000829696655, 0.06849999725818634, -0.09740000218153, -0.06909999996423721, -0.16619999706745148, 0.05299999937415123, 0.059700001031160355, -0.28929999470710754], [-0.00860000029206276, -0.03020000085234642, -0.17749999463558197, -0.32170000672340393, -0.4180999994277954, -0.31290000677108765, 0.2402999997138977, 0.05420000106096268, -0.20489999651908875, -0.10509999841451645, -0.2524000108242035, -0.1517000049352646, 0.28529998660087585, -0.07419999688863754, -0.31850001215934753, -0.17960000038146973, 0.2554999887943268, 0.2840000092983246, -0.11569999903440475, 0.10520000010728836], [-0.047600001096725464, 0.243599995970726, -0.14560000598430634, 0.5569999814033508, -0.09369999915361404, -0.18520000576972961, 0.2401999980211258, -0.03350000083446503, 0.11779999732971191, -0.20399999618530273, -0.25220000743865967, -0.05290000140666962, 0.14869999885559082, -0.011900000274181366, 0.25, -0.2669999897480011, -0.3476000130176544, -0.10019999742507935, -0.1193000003695488, 0.2865999937057495], [0.39579999446868896, 0.3384000062942505, 0.0632999986410141, -0.023399999365210533, 0.07800000160932541, 0.023099999874830246, -0.24130000174045563, 0.22709999978542328, -0.26179999113082886, -0.09700000286102295, 0.13279999792575836, 0.09449999779462814, 0.031700000166893005, 0.11379999667406082, 0.04010000079870224, -0.15080000460147858, -0.3167000114917755, 0.5924000144004822, 0.1160999983549118, -0.017999999225139618], [-0.09099999815225601, 0.20090000331401825, -0.09369999915361404, -0.2498999983072281, 0.17309999465942383, 0.065700002014637, 0.3255999982357025, -0.38260000944137573, 0.08500000089406967, 0.06080000102519989, 0.21860000491142273, -0.17800000309944153, 0.27129998803138733, 0.5472000241279602, 0.1444000005722046, 0.045899998396635056, 0.023099999874830246, 0.0737999975681305, 0.2703999876976013, 0.16680000722408295], [-0.12999999523162842, 0.0982000008225441, -0.24809999763965607, -0.014100000262260437, -0.2655999958515167, -0.09269999712705612, -0.18780000507831573, -0.18790000677108765, -0.08860000222921371, -0.19779999554157257, 0.6233000159263611, -0.3301999866962433, -0.12790000438690186, -0.36090001463890076, 0.018799999728798866, -0.13259999454021454, -0.0835999995470047, -0.1071000024676323, 0.18479999899864197, 0.017799999564886093], [0.04729999974370003, -0.2572999894618988, 0.11890000104904175, 0.14669999480247498, -0.397599995136261, 0.028200000524520874, 0.019200000911951065, 0.0674000009894371, -0.19519999623298645, -0.05990000069141388, 0.17949999868869781, 0.4311000108718872, 0.5094000101089478, 0.04910000041127205, 0.04490000009536743, 0.2289000004529953, -0.13680000603199005, -0.1817999929189682, 0.32179999351501465, -0.026599999517202377], [-0.3248000144958496, 0.2012999951839447, -0.19830000400543213, -0.21230000257492065, 0.03099999949336052, -0.17919999361038208, -0.013199999928474426, 0.047200001776218414, -0.16779999434947968, -0.5271000266075134, -0.17249999940395355, 0.4025999903678894, -0.33730000257492065, 0.12729999423027039, 0.19850000739097595, 0.16140000522136688, 0.0925000011920929, -0.05389999970793724, 0.15600000321865082, -0.07020000368356705], [-0.045899998396635056, 0.13539999723434448, 0.020600000396370888, -0.23240000009536743, -0.14090000092983246, 0.28290000557899475, -0.09700000286102295, 0.30720001459121704, 0.527899980545044, -0.3783000111579895, -0.01940000057220459, -0.2102999985218048, 0.2029999941587448, -0.03280000016093254, -0.09229999780654907, 0.37139999866485596, -0.20280000567436218, 0.018799999728798866, -0.1388999968767166, 0.07419999688863754], [0.18240000307559967, 0.4357999861240387, -0.12620000541210175, -0.20360000431537628, -0.09860000014305115, -0.10760000348091125, -0.2678000032901764, -0.35760000348091125, -0.007400000002235174, 0.36160001158714294, -0.23970000445842743, 0.1875, 0.05719999969005585, -0.26570001244544983, -0.028699999675154686, 0.32010000944137573, -0.1120000034570694, -0.16009999811649323, -0.006599999964237213, 0.24449999630451202], [-0.2770000100135803, -0.08789999783039093, 0.19429999589920044, 0.29109999537467957, -0.20029999315738678, 0.08240000158548355, -0.4668999910354614, -0.09809999912977219, -0.2012999951839447, -0.009499999694526196, -0.219200000166893, -0.3393000066280365, -0.02759999968111515, 0.20759999752044678, 0.1467999964952469, 0.23199999332427979, 0.23759999871253967, 0.23649999499320984, 0.09640000015497208, 0.2718000113964081], [-0.3917999863624573, 0.2345000058412552, -0.05829999968409538, 0.1331000030040741, -0.35600000619888306, 0.13619999587535858, -0.01850000023841858, -0.00279999990016222, 0.30649998784065247, 0.3068999946117401, 0.24009999632835388, 0.39879998564720154, -0.06809999793767929, 0.1088000014424324, -0.029100000858306885, -0.14730000495910645, 0.13910000026226044, 0.3091999888420105, -0.24240000545978546, -0.08470000326633453], [-0.25999999046325684, 0.0640999972820282, 0.11940000206232071, 0.06639999896287918, 0.4577000141143799, 0.01489999983459711, 0.022099999710917473, -0.050999999046325684, -0.29190000891685486, -0.1673000007867813, 0.27469998598098755, 0.1542000025510788, 0.3280999958515167, -0.23800000548362732, -0.10999999940395355, 0.1476999968290329, 0.1136000007390976, 0.07989999651908875, -0.43560001254081726, 0.2777999937534332], [-0.010099999606609344, -0.09229999780654907, 0.11630000174045563, -0.23330000042915344, 0.06880000233650208, -0.10329999774694443, -0.3822999894618988, 0.19179999828338623, 0.18150000274181366, -0.020899999886751175, 0.061400000005960464, 0.18199999630451202, 0.03750000149011612, 0.18960000574588776, -0.09780000150203705, -0.4941999912261963, 0.07000000029802322, -0.28360000252723694, 0.08529999852180481, 0.5206000208854675], [0.06719999760389328, 0.17219999432563782, 0.26660001277923584, 0.14630000293254852, 0.093299999833107, 0.12839999794960022, -0.13750000298023224, -0.44119998812675476, 0.23829999566078186, -0.34880000352859497, -0.17180000245571136, 0.09929999709129333, 0.2053000032901764, -0.1753000020980835, -0.25, -0.25940001010894775, 0.25780001282691956, 0.05480000004172325, 0.2476000040769577, -0.28850001096725464], [-0.3894999921321869, 0.1655000001192093, 0.4900999963283539, -0.289900004863739, -0.032999999821186066, -0.22830000519752502, -0.0803999975323677, 0.04610000178217888, -0.10930000245571136, 0.1444000005722046, -0.08990000188350677, -0.1678999960422516, 0.1923000067472458, -0.03999999910593033, 0.24719999730587006, -0.1738000065088272, -0.29339998960494995, -0.12759999930858612, -0.08479999750852585, -0.3555000126361847], [-0.03139999881386757, 0.08410000056028366, 0.04129999876022339, 0.09520000219345093, 0.20569999516010284, -0.4171999990940094, 0.08169999718666077, 0.34119999408721924, 0.3140999972820282, 0.17149999737739563, 0.06930000334978104, -0.02160000056028366, 0.12950000166893005, -0.31040000915527344, 0.24950000643730164, 0.15029999613761902, 0.33320000767707825, 0.19480000436306, 0.397599995136261, 0.05829999968409538], [-0.014399999752640724, 0.22849999368190765, -0.16830000281333923, -0.09920000284910202, -0.02710000053048134, 0.6248999834060669, 0.0803999975323677, 0.2492000013589859, -0.24289999902248383, 0.08479999750852585, -0.1404000073671341, -0.05040000006556511, 0.1559000015258789, -0.22380000352859497, 0.3379000127315521, -0.23759999871253967, 0.2822999954223633, -0.16140000522136688, 0.1006999984383583, 0.016200000420212746], [0.13109999895095825, 0.4641000032424927, -0.023600000888109207, 0.25279998779296875, -0.02319999970495701, -0.17579999566078186, -0.08869999647140503, 0.28119999170303345, -0.1348000019788742, 0.02019999921321869, 0.13359999656677246, -0.15389999747276306, 0.07689999788999557, 0.3467999994754791, -0.29350000619888306, 0.1088000014424324, 0.2858000099658966, -0.3937999904155731, -0.09920000284910202, -0.23170000314712524], [-0.3734000027179718, 0.1379999965429306, 0.0934000015258789, 0.09380000084638596, 0.08980000019073486, 0.16750000417232513, 0.21860000491142273, 0.1688999980688095, -0.1306000053882599, 0.1550000011920929, -0.10729999840259552, -0.030300000682473183, -0.1704999953508377, -0.10040000081062317, -0.5680999755859375, 0.020500000566244125, -0.28110000491142273, 0.008500000461935997, 0.4348999857902527, 0.16590000689029694]], [0.0, 0.0, 0.0, 0.0, 0.0, 0.0, 0.0, 0.0, 0.0, 0.0, 0.0, 0.0, 0.0, 0.0, 0.0, 0.0, 0.0, 0.0, 0.0, 0.0], [[0.07999999821186066, 0.005799999926239252, -0.07419999688863754, 0.015799999237060547, 0.03500000014901161], [-0.018699999898672104, -0.015799999237060547, -0.043299999088048935, 0.013000000268220901, 0.042500000447034836], [-0.10080000013113022, 0.057500001043081284, -0.02810000069439411, 0.10559999942779541, -0.01590000092983246], [-0.015799999237060547, 0.06909999996423721, 0.006899999920278788, 0.009600000455975533, -0.08489999920129776], [-0.06239999830722809, -0.00860000029206276, -0.0658000037074089, 0.037300001829862595, -0.05820000171661377], [-0.061500001698732376, 0.04960000142455101, 0.0917000025510788, -0.01510000042617321, -0.06719999760389328], [-0.00279999990016222, 0.1103999987244606, 0.04879999905824661, 0.0210999995470047, 0.03229999914765358], [0.1177000030875206, -0.002199999988079071, -0.013399999588727951, 0.054999999701976776, 0.02410000003874302], [-0.03189999982714653, -0.027000000700354576, -0.03830000013113022, 0.014999999664723873, -0.030500000342726707], [0.1274999976158142, 0.06849999725818634, -0.05130000039935112, 0.08389999717473984, -0.042500000447034836], [0.09709999710321426, 0.013399999588727951, -0.05310000106692314, -0.001500000013038516, 0.03840000182390213], [0.13680000603199005, -0.07649999856948853, 0.024900000542402267, 9.999999747378752e-05, -0.05130000039935112], [-0.0007999999797903001, 0.02800000086426735, 0.0038999998942017555, -0.0908999964594841, -0.07919999957084656], [0.04610000178217888, 0.03669999912381172, 0.004800000227987766, 0.03620000183582306, 0.027799999341368675], [0.05209999904036522, -0.08340000361204147, -0.03959999978542328, -0.012900000438094139, -0.02850000001490116], [-0.042100001126527786, 0.05820000171661377, -0.03319999948143959, -0.026900000870227814, 0.04500000178813934], [0.06790000200271606, -0.03180000185966492, -0.009200000204145908, 0.007699999958276749, -0.039500001817941666], [-0.05990000069141388, -0.03359999880194664, -0.011699999682605267, -0.013500000350177288, 0.05959999933838844], [-0.021900000050663948, -0.013000000268220901, 0.01140000019222498, 0.02800000086426735, 0.03150000050663948], [0.020999999716877937, 0.04569999873638153, -0.006399999838322401, -0.0071000000461936, 0.037300001829862595]], [[0.11479999870061874, 0.2574999928474426, -0.3463999927043915, -0.30880001187324524, 0.8396999835968018], [0.8348000049591064, 0.37869998812675476, -0.11640000343322754, 0.3521000146865845, -0.14880000054836273], [0.08349999785423279, -0.7069000005722046, -0.4537999927997589, 0.49709999561309814, 0.20090000331401825], [0.1818999946117401, -0.1712000072002411, -0.5860999822616577, -0.6290000081062317, -0.445499986410141], [-0.4999000132083893, 0.5112000107765198, -0.5630000233650208, 0.37130001187324524, -0.18410000205039978]], [0.0, 0.0, 0.0, 0.0, 0.0], [[0.07999999821186066, 0.005799999926239252, -0.07419999688863754], [0.015799999237060547, 0.03500000014901161, -0.018699999898672104], [-0.015799999237060547, -0.043299999088048935, 0.013000000268220901], [0.042500000447034836, -0.10080000013113022, 0.057500001043081284], [-0.02810000069439411, 0.10559999942779541, -0.01590000092983246]], [0.0, 0.0, 0.0]]</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>[[[0.21610000729560852, 0.18970000743865967, 0.062300000339746475, -0.1251000016927719, 0.19349999725818634, -0.24819999933242798, -0.11599999666213989, -0.14489999413490295, -0.08940000087022781, 0.2207999974489212, -0.2547000050544739, -0.06270000338554382, -0.32120001316070557, 0.19380000233650208, -0.040800001472234726, -0.2718000113964081, 0.18459999561309814, 0.06390000134706497, -0.044599998742341995, -0.012600000016391277], [-0.06859999895095825, -0.26429998874664307, -0.10199999809265137, 0.27219998836517334, -0.26339998841285706, 0.04410000145435333, 0.12020000070333481, 0.11819999665021896, -0.035999998450279236, -0.06620000302791595, 0.1143999993801117, 0.19539999961853027, 0.3646000027656555, 0.06379999965429306, -0.14720000326633453, 0.3327000141143799, -0.0066999997943639755, -0.38420000672340393, 0.23669999837875366, -0.1462000012397766]], [[0.05000000074505806, -0.32690000534057617, -0.6870999932289124, 0.21439999341964722, 0.35429999232292175, -0.22840000689029694, -0.07519999891519547, -0.05849999934434891, 0.11590000241994858, 0.32249999046325684, -0.4408000111579895, -0.13079999387264252, 0.3197000026702881, 0.33250001072883606, -0.23579999804496765, -0.06939999759197235, -0.0008999999845400453, -0.0723000019788742, 0.27140000462532043, -0.3458000123500824], [-0.05590000003576279, -0.0778999999165535, -0.27320000529289246, -0.5059000253677368, -0.5555999875068665, -0.4359999895095825, 0.27140000462532043, -0.2167000025510788, -0.15389999747276306, -0.4196999967098236, -0.4819999933242798, -0.38769999146461487, -0.022600000724196434, -0.1477999985218048, 0.004900000058114529, -0.39489999413490295, 0.33149999380111694, 0.5412999987602234, -0.07079999893903732, 0.47189998626708984], [-0.28760001063346863, 0.2556999921798706, -0.14659999310970306, 0.34709998965263367, -0.18880000710487366, -0.13729999959468842, 0.09000000357627869, -0.13230000436306, 0.06379999965429306, -0.3831999897956848, -0.49300000071525574, -0.07069999724626541, -0.09589999914169312, -0.16820000112056732, 0.4205000102519989, -0.30469998717308044, -0.40799999237060547, 0.065700002014637, -0.1256999969482422, 0.46799999475479126], [0.2410999983549118, 0.4657000005245209, 0.4350000023841858, 0.07400000095367432, 0.164900004863739, 0.2770000100135803, -0.3190000057220459, 0.2685999870300293, -0.23430000245571136, -0.17479999363422394, 0.2076999992132187, -0.035599999129772186, -0.1298999935388565, -0.11069999635219574, 0.026000000536441803, -0.21850000321865082, -0.4832000136375427, 0.5705999732017517, -0.08100000023841858, -0.12049999833106995], [0.015300000086426735, 0.052299998700618744, -0.28049999475479126, -0.25200000405311584, 0.03999999910593033, -0.1535000056028366, 0.5217999815940857, -0.5476999878883362, 0.1459999978542328, 0.08860000222921371, -0.28540000319480896, -0.1647000014781952, -0.16930000483989716, 0.7996000051498413, 0.06390000134706497, 0.12020000070333481, 0.19850000739097595, 0.398499995470047, 0.5821999907493591, 0.33160001039505005], [-0.21660000085830688, 0.093299999833107, -0.2443999946117401, -0.0066999997943639755, -0.24330000579357147, 0.04500000178813934, -0.21889999508857727, -0.18729999661445618, -0.15760000050067902, -0.2053000032901764, 0.6043000221252441, -0.25540000200271606, 0.00039999998989515007, -0.4052000045776367, -0.1704999953508377, -0.07729999721050262, -0.15790000557899475, -0.1550000011920929, 0.263700008392334, 0.015799999237060547], [0.2732999920845032, -0.24310000240802765, 0.11699999868869781, 0.32820001244544983, 0.025100000202655792, 0.06880000233650208, 0.09260000288486481, 0.23970000445842743, -0.01979999989271164, 0.19050000607967377, 0.35350000858306885, 0.4814999997615814, 0.6736999750137329, 0.367900013923645, -0.08649999648332596, 0.3192000091075897, 0.002899999963119626, -0.24169999361038208, 0.3736000061035156, -0.18310000002384186], [-0.45910000801086426, 0.2827000021934509, -0.12439999729394913, -0.35839998722076416, -0.04800000041723251, -0.0617000013589859, -0.18700000643730164, 0.08780000358819962, -0.21529999375343323, -0.7440000176429749, 0.042500000447034836, 0.29580000042915344, -0.3206999897956848, -0.07779999822378159, 0.4684999883174896, 0.04910000041127205, -0.0714000016450882, 0.01640000008046627, -0.09040000289678574, -0.09719999879598618], [0.1647000014781952, 0.06279999762773514, -0.22660000622272491, -0.08619999885559082, -0.19280000030994415, 0.2249000072479248, -0.004699999932199717, 0.4392000138759613, 0.34119999408721924, -0.20430000126361847, 0.14319999516010284, 0.05510000139474869, 0.5807999968528748, 0.2378000020980835, -0.18400000035762787, 0.5249999761581421, -0.14650000631809235, -0.05559999868273735, -0.04670000076293945, -0.010599999688565731], [0.42910000681877136, 0.2971999943256378, -0.1573999971151352, -0.13979999721050262, -0.12269999831914902, -0.24560000002384186, -0.05299999937415123, -0.49300000071525574, 0.02930000051856041, 0.41029998660087585, -0.4950999915599823, 0.013000000268220901, 0.014800000004470348, -0.0860000029206276, -0.00419999985024333, 0.3855000138282776, -0.05380000174045563, -0.14569999277591705, 0.07729999721050262, 0.24320000410079956], [-0.5766000151634216, -0.003000000026077032, 0.38260000944137573, 0.03759999945759773, -0.4275999963283539, 0.4487999975681305, -0.7609999775886536, -0.09790000319480896, -0.36660000681877136, -0.29100000858306885, -0.20239999890327454, -0.353300005197525, -0.13099999725818634, -0.0778999999165535, 0.274399995803833, 0.23729999363422394, -0.07970000058412552, 0.3497999906539917, -0.0982000008225441, 0.29820001125335693], [-0.3959999978542328, 0.28189998865127563, -0.026599999517202377, 0.07609999924898148, -0.39160001277923584, 0.12939999997615814, -0.060100000351667404, 0.025699999183416367, 0.30640000104904175, 0.24390000104904175, 0.34459999203681946, 0.32359999418258667, -0.04619999974966049, 0.025100000202655792, 0.18870000541210175, -0.17010000348091125, 0.11010000109672546, 0.27390000224113464, -0.43639999628067017, -0.17880000174045563], [-0.4415000081062317, 0.3889999985694885, 0.3012999892234802, -0.019700000062584877, 0.34850001335144043, 0.3269999921321869, -0.37380000948905945, 0.29899999499320984, -0.4708000123500824, -0.41429999470710754, 0.5584999918937683, 0.33550000190734863, 0.6880000233650208, -0.554099977016449, -0.1282999962568283, 0.10499999672174454, -0.2948000133037567, -0.09510000050067902, -0.7235000133514404, 0.09390000253915787], [0.14880000054836273, -0.11050000041723251, 0.08839999884366989, -0.16500000655651093, 0.05420000106096268, -0.2345999926328659, -0.24469999969005585, 0.1907999962568283, 0.24560000002384186, 0.04650000110268593, 0.03959999978542328, 0.10570000112056732, -0.04690000042319298, 0.2799000144004822, -0.10170000046491623, -0.5027999877929688, 0.13429999351501465, -0.3684999942779541, 0.07209999859333038, 0.5027999877929688], [-0.1039000004529953, 0.2517000138759613, 0.19519999623298645, 0.01489999983459711, 0.08290000259876251, 0.17710000276565552, -0.3091999888420105, -0.3650999963283539, 0.27730000019073486, -0.37529999017715454, -0.05620000138878822, 0.29120001196861267, 0.2313999980688095, -0.31869998574256897, -0.22669999301433563, -0.30820000171661377, 0.3125999867916107, 0.08799999952316284, 0.21160000562667847, -0.2549000084400177], [-0.5429999828338623, 0.4661000072956085, 0.7369999885559082, -0.15539999306201935, 0.11190000176429749, 0.05909999832510948, -0.3889999985694885, 0.31610000133514404, -0.24779999256134033, 0.0812000036239624, 0.3100999891757965, -0.06909999996423721, 0.49480000138282776, -0.29249998927116394, 0.17139999568462372, -0.42579999566078186, -0.58160001039505, -0.17069999873638153, -0.4632999897003174, -0.5647000074386597], [0.11819999665021896, 0.07509999722242355, 0.009600000455975533, 0.15610000491142273, 0.17759999632835388, -0.5669999718666077, 0.21570000052452087, 0.32339999079704285, 0.36579999327659607, 0.23659999668598175, 0.07590000331401825, -0.09650000184774399, -0.013100000098347664, -0.2272000014781952, 0.3750999867916107, 0.17180000245571136, 0.4174000024795532, 0.20329999923706055, 0.3643999993801117, 0.15459999442100525], [-0.11640000343322754, 0.24009999632835388, -0.263700008392334, -0.3296999931335449, -0.058800000697374344, 0.49050000309944153, 0.025599999353289604, 0.15629999339580536, -0.2281000018119812, 0.0494999997317791, -0.2718000113964081, -0.014499999582767487, -0.023900000378489494, -0.24629999697208405, 0.40139999985694885, -0.3882000148296356, 0.41190001368522644, 0.044599998742341995, 0.2160000056028366, 0.19269999861717224], [0.3869999945163727, 0.45809999108314514, -0.02969999983906746, 0.5461000204086304, 0.11259999871253967, -0.2012999951839447, 0.04019999876618385, 0.45089998841285706, -0.06159999966621399, 0.25949999690055847, 0.48100000619888306, -0.0908999964594841, 0.3905999958515167, 0.5979999899864197, -0.4390000104904175, 0.28760001063346863, 0.3276999890804291, -0.5620999932289124, -0.14149999618530273, -0.38449999690055847], [-0.32659998536109924, 0.10830000042915344, 0.08550000190734863, 0.18410000205039978, 0.15569999814033508, 0.1500999927520752, 0.1687999963760376, 0.24889999628067017, -0.0478999987244606, 0.34929999709129333, 0.02239999920129776, 0.11980000138282776, -0.14980000257492065, 0.025100000202655792, -0.7085000276565552, 0.07639999687671661, -0.18160000443458557, -0.01140000019222498, 0.567799985408783, 0.016699999570846558]], [0.05860000103712082, 0.005499999970197678, -0.025800000876188278, 0.021400000900030136, 0.0017000000225380063, 0.08139999955892563, -0.0020000000949949026, -0.04600000008940697, 0.09759999811649323, 0.08139999955892563, 0.07039999961853027, -0.03460000082850456, 0.03669999912381172, 0.03669999912381172, -0.15690000355243683, 0.04039999842643738, -0.00989999994635582, -0.13259999454021454, 0.1160999983549118, 0.0026000000070780516], [[0.16169999539852142, 0.3560999929904938, -0.3418000042438507, 0.11299999803304672, -0.030300000682473183], [-0.0203000009059906, -0.27079999446868896, -0.2766999900341034, -0.037300001829862595, 0.23489999771118164], [-0.18019999563694, -0.1664000004529953, 0.08699999749660492, 0.19200000166893005, -0.04439999908208847], [0.1331000030040741, 0.38749998807907104, 0.25130000710487366, 0.23090000450611115, -0.28349998593330383], [-0.016100000590085983, 0.093299999833107, -0.17890000343322754, 0.15029999613761902, -0.03449999913573265], [-0.033799998462200165, -0.0031999999191612005, 0.22830000519752502, 0.12380000203847885, -0.1446000039577484], [-0.11869999766349792, 0.3831999897956848, 0.03579999879002571, -0.11400000005960464, 0.0568000003695488], [0.23569999635219574, 0.10859999805688858, 0.17229999601840973, 0.13989999890327454, -0.02449999935925007], [0.07590000331401825, 0.22630000114440918, 0.002199999988079071, -0.22460000216960907, -0.06840000301599503], [0.2556000053882599, 0.4101000130176544, -0.2612999975681305, 0.057999998331069946, -0.01269999984651804], [0.23319999873638153, -0.032600000500679016, 0.48500001430511475, 0.29159998893737793, -0.29840001463890076], [0.20909999310970306, 0.057999998331069946, 0.09669999778270721, 0.050599999725818634, -0.09929999709129333], [0.26080000400543213, 0.421999990940094, 0.34040001034736633, 0.24089999496936798, -0.3776000142097473], [0.11209999769926071, 0.23309999704360962, -0.2533000111579895, -0.06780000030994415, 0.1379999965429306], [-0.20110000669956207, -0.41690000891685486, -0.20720000565052032, -0.3481999933719635, 0.24940000474452972], [0.25870001316070557, 0.18799999356269836, 0.6775000095367432, 0.05270000174641609, -0.1168999969959259], [0.12520000338554382, 0.04879999905824661, -0.1485999971628189, -0.051100000739097595, 0.0560000017285347], [-0.30640000104904175, -0.4323999881744385, -0.3659999966621399, -0.3086000084877014, 0.40119999647140503], [0.19930000603199005, 0.33480000495910645, 0.0017000000225380063, 0.06560000032186508, -0.10509999841451645], [-0.19189999997615814, -0.26489999890327454, -0.16519999504089355, -0.313400000333786, 0.3163999915122986]], [[0.13760000467300415, 0.33889999985694885, -0.2711000144481659, -0.3100000023841858, 0.8066999912261963], [0.9175999760627747, 0.5622000098228455, 0.05939999967813492, 0.4108000099658966, -0.20890000462532043], [0.1949000060558319, -0.8460000157356262, -0.3815999925136566, 0.6700999736785889, 0.131400004029274], [-0.1459999978542328, 0.24279999732971191, -0.6629999876022339, -0.9172999858856201, -0.22920000553131104], [-0.5210000276565552, 0.2117999941110611, -0.6194999814033508, 0.22020000219345093, -0.09640000015497208]], [0.2655999958515167, 0.08590000122785568, -0.05469999834895134, -0.07050000131130219, -0.041600000113248825], [[0.31299999356269836, 0.11699999868869781, -0.23639999330043793], [0.30959999561309814, 0.08049999922513962, -0.11469999700784683], [0.4180999994277954, -0.08789999783039093, 0.08569999784231186], [0.4259999990463257, -0.08150000125169754, 0.16130000352859497], [-0.36399999260902405, 0.10029999911785126, -0.14880000054836273]], [-0.19910000264644623, 0.011900000274181366, 0.05249999836087227]]</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>[0.7931695199748807]</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>[0.047212496317275705]</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>[0.8191712577836694]</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>[0.0412837933291471]</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>[-2.9281907871155743]</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>[1.2856170809164886]</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>[0.7619630655515908]</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>[0.05468162395969795]</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>[0.7182035450339066]</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>[0.06683113670032116]</t>
+        </is>
+      </c>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>[-2.524322668298613]</t>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>[1.1586120676553107]</t>
+        </is>
+      </c>
+      <c r="Q21" t="inlineStr">
+        <is>
+          <t>[-0.11804455270236569]</t>
+        </is>
+      </c>
+      <c r="R21" t="inlineStr">
+        <is>
+          <t>[0.12055396896090026]</t>
+        </is>
+      </c>
+      <c r="S21" t="inlineStr">
+        <is>
+          <t>[-0.1268185518475058]</t>
+        </is>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>[0.09494611402577427]</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>[-0.9917125098967163]</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>[0.19045378540961946]</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>[-0.31630970609622744]</t>
+        </is>
+      </c>
+      <c r="X21" t="inlineStr">
+        <is>
+          <t>[0.13789742560120877]</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>[-0.21480595172506778]</t>
+        </is>
+      </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>[0.09997028093255554]</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>[-0.8048184091762032]</t>
+        </is>
+      </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>[0.16605118854330697]</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>[-0.8809289828176814]</t>
+        </is>
+      </c>
+      <c r="AD21" t="inlineStr">
+        <is>
+          <t>[0.15761427123462035]</t>
+        </is>
+      </c>
+      <c r="AE21" t="inlineStr">
+        <is>
+          <t>[-0.7185833708259917]</t>
+        </is>
+      </c>
+      <c r="AF21" t="inlineStr">
+        <is>
+          <t>[0.1850537475242916]</t>
+        </is>
+      </c>
+      <c r="AG21" t="inlineStr">
+        <is>
+          <t>[-3.3536611892891743]</t>
+        </is>
+      </c>
+      <c r="AH21" t="inlineStr">
+        <is>
+          <t>[0.32412989466173187]</t>
+        </is>
+      </c>
+      <c r="AI21" t="inlineStr">
+        <is>
+          <t>[-1.3215539442386612]</t>
+        </is>
+      </c>
+      <c r="AJ21" t="inlineStr">
+        <is>
+          <t>[0.190248761343859]</t>
+        </is>
+      </c>
+      <c r="AK21" t="inlineStr">
+        <is>
+          <t>[-0.8170470555578073]</t>
+        </is>
+      </c>
+      <c r="AL21" t="inlineStr">
+        <is>
+          <t>[0.1928662321019329]</t>
+        </is>
+      </c>
+      <c r="AM21" t="inlineStr">
+        <is>
+          <t>[-3.152651373276238]</t>
+        </is>
+      </c>
+      <c r="AN21" t="inlineStr">
+        <is>
+          <t>[0.3189537305453611]</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>model_64_32_0</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>[64, 32]</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>[[[0.03319999948143959, 0.0027000000700354576, -0.016699999570846558, -0.0017999999690800905, 0.12229999899864197, -0.014700000174343586, -0.04670000076293945, -0.05999999865889549, -0.0005000000237487257, -0.16120000183582306, -0.057500001043081284, -0.03150000050663948, 0.04129999876022339, 0.027000000700354576, -0.054999999701976776, 0.0066999997943639755, 0.0007999999797903001, 0.059300001710653305, 0.00139999995008111, -0.021199999377131462, 0.06199999898672104, 0.042500000447034836, 0.11349999904632568, 0.019600000232458115, 0.05620000138878822, -0.0026000000070780516, -0.029600000008940697, 0.05090000107884407, -0.008500000461935997, 0.039400000125169754, 0.014999999664723873, 0.01720000058412552, 0.03959999978542328, 0.014700000174343586, 0.010400000028312206, 0.060499999672174454, -0.015599999576807022, -0.013299999758601189, 0.07540000230073929, -0.02539999969303608, 0.0722000002861023, -0.014800000004470348, -0.05270000174641609, 0.08399999886751175, -0.05649999901652336, 0.015200000256299973, -0.012799999676644802, -0.015799999237060547, 0.018699999898672104, 0.006300000008195639, -0.03020000085234642, 0.09740000218153, 0.07370000332593918, 0.02070000022649765, 0.014800000004470348, -0.029400000348687172, -0.04830000177025795, 0.004000000189989805, -0.07289999723434448, -0.042399998754262924, 0.0008999999845400453, -0.04740000143647194, -0.061400000005960464, -0.007499999832361937], [0.02319999970495701, -0.028599999845027924, 0.02879999950528145, 0.014399999752640724, 0.1039000004529953, -0.06560000032186508, -0.04690000042319298, -0.0005000000237487257, 0.03680000081658363, 0.04340000078082085, -0.10540000349283218, -0.03840000182390213, 0.014999999664723873, 0.025499999523162842, 0.006800000090152025, -0.04230000078678131, 0.03500000014901161, 0.0035000001080334187, 0.019099999219179153, 0.00019999999494757503, 0.05869999900460243, -0.0035000001080334187, -0.053300000727176666, 0.043800000101327896, 0.01119999960064888, -0.0010000000474974513, -0.04439999908208847, -0.06549999862909317, -0.08110000193119049, 0.02759999968111515, 0.018699999898672104, -0.0010000000474974513, 0.026200000196695328, -0.006500000134110451, 0.04010000079870224, -0.0892999991774559, 0.002899999963119626, -0.04540000110864639, -0.14000000059604645, -0.05000000074505806, 0.06949999928474426, -0.03139999881386757, -0.013700000010430813, 0.04580000042915344, -0.007899999618530273, -0.011300000362098217, 0.08389999717473984, 0.03620000183582306, -0.05420000106096268, -0.022199999541044235, 0.049800001084804535, -0.024900000542402267, 0.020400000736117363, 0.026799999177455902, 0.014800000004470348, 0.08070000261068344, -0.02410000003874302, -0.044199999421834946, 0.03819999843835831, -0.003000000026077032, 0.043299999088048935, 0.05959999933838844, 0.021199999377131462, 0.024399999529123306]], [[0.12849999964237213, 0.012600000016391277, -0.0722000002861023, 0.12319999933242798, -0.026399999856948853, 0.012500000186264515, 0.007400000002235174, 0.21160000562667847, 0.093299999833107, 0.1712999939918518, 0.08250000327825546, 0.020099999383091927, -0.0828000009059906, -0.2890999913215637, -0.09529999643564224, -0.035599999129772186, 0.05510000139474869, -0.04859999939799309, 0.04839999973773956, -0.02410000003874302, 0.445499986410141, 0.02889999933540821, -0.12389999628067017, -0.1266999989748001, 0.04580000042915344, -0.027799999341368675, -0.12319999933242798, -0.01769999973475933, 0.03590000048279762, -0.01140000019222498, 0.06459999829530716, 0.1404999941587448, 0.03550000116229057, 0.04600000008940697, -0.11129999905824661, -0.09570000320672989, 0.14219999313354492, 0.10199999809265137, 0.03880000114440918, 0.2874999940395355, -0.055799998342990875, 0.2777999937534332, -0.0035000001080334187, -0.12759999930858612, -0.03759999945759773, 0.17489999532699585, 0.1340000033378601, 0.05480000004172325, -0.08510000258684158, 0.13130000233650208, 0.13680000603199005, -0.14380000531673431, 0.057100001722574234, -0.040300000458955765, -0.14429999887943268, 0.1582999974489212, -0.12280000001192093, 0.025699999183416367, 0.12300000339746475, 0.05429999902844429, 0.08240000158548355, 0.15929999947547913, -0.12160000205039978, -0.061799999326467514], [-0.0010999999940395355, 0.14079999923706055, 0.09350000321865082, -0.00570000009611249, 0.051600001752376556, 0.06279999762773514, 0.24060000479221344, -0.0020000000949949026, 0.08449999988079071, -0.0608999989926815, -0.10849999636411667, -0.17970000207424164, -0.01590000092983246, -0.0714000016450882, 0.10620000213384628, -0.023000000044703484, -0.11219999939203262, 0.32089999318122864, 0.008999999612569809, -0.08810000121593475, -0.027699999511241913, -0.09019999951124191, -0.1298999935388565, -0.05570000037550926, -0.15360000729560852, 0.04390000179409981, -0.1891999989748001, 0.09000000357627869, -0.07599999755620956, 0.05249999836087227, 0.04179999977350235, 0.06769999861717224, 0.08990000188350677, 0.004100000020116568, 0.2524000108242035, 0.24629999697208405, 0.2493000030517578, -0.06710000336170197, -0.2143000066280365, -0.06310000270605087, -0.20440000295639038, -0.018699999898672104, 0.13729999959468842, -0.06960000097751617, 0.004000000189989805, 0.1526000052690506, 0.13580000400543213, 0.09019999951124191, 0.18850000202655792, 0.027000000700354576, 0.05950000137090683, -0.06030000001192093, -0.2709999978542328, -0.06750000268220901, 0.05490000173449516, 0.020600000396370888, -0.09939999878406525, -0.17749999463558197, -0.164000004529953, -0.13249999284744263, -0.0020000000949949026, 0.12530000507831573, 0.08240000158548355, -0.01720000058412552], [0.0551999993622303, -0.021299999207258224, 0.2599000036716461, -0.1543000042438507, -0.15940000116825104, 0.02979999966919422, -0.1005999967455864, -0.12359999865293503, -0.13249999284744263, -0.09510000050067902, 0.1348000019788742, -0.1046999990940094, -0.11349999904632568, -0.04969999939203262, 0.24690000712871552, 0.20360000431537628, -0.09539999812841415, 0.07689999788999557, 0.018400000408291817, 0.026399999856948853, 0.032999999821186066, -0.05950000137090683, 0.0754999965429306, 0.16689999401569366, 0.09570000320672989, -0.20170000195503235, 0.04560000076889992, -0.17440000176429749, 0.14990000426769257, -0.05590000003576279, -0.06650000065565109, 0.07119999825954437, -0.10220000147819519, -0.07329999655485153, 0.07829999923706055, -0.1307000070810318, 0.005799999926239252, 0.07779999822378159, 0.06390000134706497, 0.219200000166893, -0.15800000727176666, -0.10119999945163727, 0.0560000017285347, 0.06080000102519989, 0.13570000231266022, 0.0625, 0.28119999170303345, -0.01899999938905239, 0.07100000232458115, -0.06889999657869339, -0.0010999999940395355, -0.06080000102519989, -0.11410000175237656, 0.10719999670982361, -0.3151000142097473, -0.011599999852478504, -0.006399999838322401, 0.08799999952316284, -0.01080000028014183, -0.20020000636577606, -0.06430000066757202, -0.20649999380111694, -0.1867000013589859, 0.01510000042617321], [-0.32820001244544983, 0.20200000703334808, 0.15719999372959137, 0.007899999618530273, 0.03440000116825104, -0.0925000011920929, -0.07999999821186066, 0.05460000038146973, 0.15639999508857727, 0.12030000239610672, 0.0885000005364418, -0.12950000166893005, -0.1264999955892563, 0.06419999897480011, 0.025299999862909317, -0.1462000012397766, 0.06300000101327896, -0.11710000038146973, -0.0071000000461936, 0.08219999819993973, -0.24060000479221344, -0.1509999930858612, 0.14390000700950623, 0.04699999839067459, 0.03739999979734421, -0.15530000627040863, 0.08789999783039093, -0.04619999974966049, -0.00019999999494757503, -0.14309999346733093, 0.023900000378489494, -0.07370000332593918, -0.11479999870061874, 0.02070000022649765, -0.05339999869465828, 0.011900000274181366, -0.06610000133514404, 0.008200000040233135, 0.09380000084638596, 0.04390000179409981, -0.07779999822378159, -0.1014999970793724, -0.12129999697208405, -0.14319999516010284, -0.16920000314712524, -0.05040000006556511, 0.12409999966621399, -0.13650000095367432, -0.11060000211000443, 0.19290000200271606, 0.09459999948740005, -0.03370000049471855, 0.019600000232458115, -0.25859999656677246, -0.02459999918937683, -0.1031000018119812, -0.2881999909877777, -0.10580000281333923, 0.002400000113993883, -0.163100004196167, 0.10100000351667404, 0.29600000381469727, 0.005900000222027302, -0.08169999718666077], [0.07020000368356705, 0.23559999465942383, -0.14800000190734863, 0.025299999862909317, 0.19120000302791595, 0.21639999747276306, 0.14069999754428864, -0.1467999964952469, -0.06780000030994415, 0.19189999997615814, -0.00019999999494757503, -0.1736000031232834, 0.0005000000237487257, 0.10029999911785126, 0.05779999867081642, 0.1972000002861023, -0.07720000296831131, 0.05009999871253967, 0.066600002348423, -0.10369999706745148, 0.08340000361204147, -0.0632999986410141, 0.23489999771118164, -0.09319999814033508, -0.09780000150203705, -0.004800000227987766, 0.2062000036239624, 0.0786999985575676, 0.02070000022649765, -0.13019999861717224, 0.015200000256299973, -0.041600000113248825, 0.13850000500679016, -0.10999999940395355, -0.05590000003576279, -0.18160000443458557, 0.047600001096725464, 0.17419999837875366, 0.10040000081062317, 0.007199999876320362, 0.01269999984651804, -0.0786999985575676, -0.17389999330043793, -0.0038999998942017555, -0.25949999690055847, 0.2320999950170517, 0.1843000054359436, 0.007499999832361937, 0.11259999871253967, -0.024000000208616257, -0.04529999941587448, 0.06750000268220901, -0.03460000082850456, 0.03449999913573265, 0.09690000116825104, -0.10119999945163727, 0.15700000524520874, 0.14390000700950623, 0.1850000023841858, 0.10270000249147415, -0.11230000108480453, 0.10830000042915344, 0.15189999341964722, 0.1046999990940094], [0.20810000598430634, 0.022600000724196434, -0.23569999635219574, -0.21160000562667847, 0.012500000186264515, 0.12229999899864197, -0.0997999981045723, -0.07069999724626541, -0.05790000036358833, -0.07209999859333038, 0.13330000638961792, 0.0625, -0.09470000118017197, 0.051100000739097595, -0.004399999976158142, 0.050999999046325684, -0.14259999990463257, -0.056299999356269836, -0.08699999749660492, 0.08749999850988388, -0.10369999706745148, -0.0, 0.1031000018119812, -0.06610000133514404, -0.019600000232458115, 0.1362999975681305, -0.23350000381469727, 0.10170000046491623, 0.09030000120401382, 0.06369999796152115, -0.07440000027418137, 0.10939999669790268, -0.1876000016927719, -0.11890000104904175, -0.035599999129772186, -0.0010999999940395355, 0.0738999992609024, 0.10930000245571136, 0.13580000400543213, -0.06780000030994415, -0.10130000114440918, 0.29100000858306885, 0.2134000062942505, 0.12099999934434891, -0.012500000186264515, -0.1664000004529953, 0.01590000092983246, 0.03959999978542328, -0.09470000118017197, 0.15610000491142273, -0.04149999842047691, 0.12449999898672104, -0.09830000251531601, 0.07930000126361847, -0.006399999838322401, -0.3034000098705292, -0.042399998754262924, 0.11289999634027481, 0.0026000000070780516, -0.18070000410079956, 0.16439999639987946, 0.23749999701976776, 0.133200004696846, -0.1429000049829483], [0.07940000295639038, 0.1362999975681305, -0.05979999899864197, 0.32030001282691956, -0.015599999576807022, -0.10660000145435333, 0.3912999927997589, -0.027899999171495438, 0.045499999076128006, -0.19290000200271606, -0.17970000207424164, -0.02370000071823597, -0.04089999943971634, 0.22390000522136688, -0.01940000057220459, -0.10849999636411667, -0.031700000166893005, 0.15690000355243683, -0.07150000333786011, 0.008899999782443047, 0.004000000189989805, -0.22100000083446503, -0.11729999631643295, 0.010300000198185444, 0.061400000005960464, 0.04580000042915344, 0.10239999741315842, -0.032999999821186066, 0.18199999630451202, 0.22910000383853912, 0.023600000888109207, 0.003000000026077032, -0.17739999294281006, -0.007899999618530273, 0.03959999978542328, -0.1834000051021576, -0.06679999828338623, 0.07970000058412552, 0.14390000700950623, 0.20180000364780426, 0.09040000289678574, 0.10080000013113022, 0.11289999634027481, 0.08669999986886978, -0.005799999926239252, -0.039799999445676804, 0.02710000053048134, -0.17739999294281006, -0.06790000200271606, -0.07129999995231628, -0.23440000414848328, 0.12540000677108765, 0.13490000367164612, -0.04129999876022339, -0.02850000001490116, 0.14830000698566437, -0.08209999650716782, 0.0348999984562397, -0.05739999935030937, -0.1306000053882599, -0.03180000185966492, 0.07039999961853027, -0.023000000044703484, 0.029999999329447746], [0.19169999659061432, 0.03920000046491623, 0.025200000032782555, 0.14810000360012054, -0.006399999838322401, 0.20250000059604645, -0.10660000145435333, -0.03610000014305115, 0.07540000230073929, -0.18479999899864197, 0.2696000039577484, -0.07639999687671661, 0.06989999860525131, -0.014600000344216824, -0.025100000202655792, -0.014700000174343586, 0.06509999930858612, -0.005100000184029341, -0.032999999821186066, 0.11089999973773956, -0.08269999921321869, 0.002300000051036477, -0.27480000257492065, -0.04580000042915344, -0.01549999974668026, 0.01209999993443489, -0.05959999933838844, 0.07940000295639038, 0.09059999883174896, 0.18539999425411224, -0.12449999898672104, -0.32030001282691956, 0.09369999915361404, 0.06440000236034393, -0.002899999963119626, -0.03020000085234642, 0.05299999937415123, 0.027899999171495438, 0.028599999845027924, 0.07940000295639038, -0.025800000876188278, -0.2142000049352646, -0.1615000069141388, -0.21160000562667847, 0.031700000166893005, 0.04619999974966049, 0.007300000172108412, -0.07829999923706055, 0.09560000151395798, -0.018799999728798866, 0.006899999920278788, 0.188400000333786, -0.01810000091791153, 0.1793999969959259, -0.0934000015258789, -0.17790000140666962, -0.2304999977350235, -0.006099999882280827, -0.017899999395012856, 0.22390000522136688, 0.2856000065803528, 0.011500000022351742, -0.014299999922513962, 0.1826000064611435], [-0.11309999972581863, -0.1665000021457672, -0.06499999761581421, 0.07900000363588333, -0.028699999675154686, 0.07569999992847443, 0.06480000168085098, -0.10779999941587448, -0.08839999884366989, -0.0038999998942017555, 0.35589998960494995, -0.02800000086426735, 0.14139999449253082, -0.2752000093460083, 0.22370000183582306, -0.09510000050067902, 0.029200000688433647, 0.05620000138878822, 0.2547999918460846, -0.1573999971151352, -0.07769999653100967, -0.029600000008940697, 0.16509999334812164, 0.08190000057220459, 0.04490000009536743, 0.11180000007152557, 0.04479999840259552, 0.09640000015497208, 0.03999999910593033, 0.2556000053882599, -0.019999999552965164, -0.01209999993443489, -0.023499999195337296, 0.13220000267028809, 0.0019000000320374966, 0.18700000643730164, -0.1949000060558319, -0.09189999848604202, 0.16329999268054962, -0.00139999995008111, 0.20669999718666077, 0.1462000012397766, 0.022600000724196434, 0.07980000227689743, 0.08540000021457672, 0.16840000450611115, 0.09799999743700027, 0.07320000231266022, 0.027000000700354576, -0.057999998331069946, -0.06319999694824219, 0.04309999942779541, 0.041600000113248825, -0.061799999326467514, 0.024900000542402267, -0.02850000001490116, -0.20499999821186066, -0.11990000307559967, 0.13689999282360077, 0.006500000134110451, -0.22089999914169312, 0.058800000697374344, 0.08049999922513962, -0.10119999945163727], [0.06620000302791595, -0.08720000088214874, 0.014700000174343586, -0.14579999446868896, 0.17520000040531158, -0.1103999987244606, 0.2711000144481659, 0.05649999901652336, -0.02370000071823597, -0.057999998331069946, -0.0917000025510788, -0.12549999356269836, -0.041200000792741776, -0.14000000059604645, -0.0017999999690800905, 0.10000000149011612, 0.10530000180006027, -0.020800000056624413, -0.11079999804496765, 0.023000000044703484, 0.11050000041723251, 0.08789999783039093, 0.05299999937415123, 0.35420000553131104, 0.33660000562667847, -0.2978000044822693, -0.12780000269412994, -0.052799999713897705, -0.06710000336170197, 0.07729999721050262, 0.10140000283718109, 0.021700000390410423, 0.06400000303983688, -0.035999998450279236, -0.028999999165534973, 0.1096000000834465, -0.10050000250339508, -0.052400000393390656, -0.020099999383091927, -0.1251000016927719, 0.008200000040233135, 0.06610000133514404, -0.1005999967455864, -0.12620000541210175, 0.019899999722838402, -0.06520000100135803, 0.07090000063180923, 0.09600000083446503, -0.08799999952316284, -0.15309999883174896, -0.20640000700950623, 0.16689999401569366, -0.14949999749660492, -0.06939999759197235, 0.09929999709129333, -0.05559999868273735, -0.008899999782443047, 0.08590000122785568, 0.1770000010728836, 0.03999999910593033, 0.22290000319480896, 0.14399999380111694, 0.014700000174343586, 0.15299999713897705], [-0.12449999898672104, -0.12389999628067017, 0.0006000000284984708, 0.1469999998807907, 0.13830000162124634, 0.014299999922513962, -0.19619999825954437, -0.05339999869465828, 0.014700000174343586, -0.02850000001490116, 0.14920000731945038, -0.1534000039100647, 0.029600000008940697, 0.08860000222921371, -0.23389999568462372, 0.17190000414848328, -0.0551999993622303, -0.07900000363588333, -0.26159998774528503, -0.09109999984502792, 0.0786999985575676, 0.08910000324249268, 0.12770000100135803, 0.004600000102072954, -0.1973000019788742, 0.03359999880194664, 0.07400000095367432, 0.07180000096559525, 0.16439999639987946, 0.11110000312328339, 0.15330000221729279, 0.15029999613761902, -0.14959999918937683, 0.11500000208616257, 0.1395999938249588, -0.04490000009536743, 0.06840000301599503, -0.2678999900817871, -0.00930000003427267, 0.03359999880194664, -0.06300000101327896, -0.20319999754428864, 0.26019999384880066, -0.02879999950528145, -0.02889999933540821, 0.07649999856948853, -0.08810000121593475, 0.1412999927997589, -0.1559000015258789, 0.022600000724196434, -0.025299999862909317, 0.17640000581741333, -0.11789999902248383, -0.08079999685287476, -0.062199998646974564, 0.14890000224113464, 0.01140000019222498, -0.038600001484155655, 0.2101999968290329, -0.03229999914765358, -0.03200000151991844, 0.10400000214576721, -0.11559999734163284, 0.1906999945640564], [-0.07720000296831131, 0.14239999651908875, -0.01889999955892563, 0.25, 0.025699999183416367, 0.006000000052154064, 0.018799999728798866, -0.004900000058114529, -0.03790000081062317, 0.018200000748038292, 0.15940000116825104, 0.48500001430511475, 0.08869999647140503, 0.0471000000834465, -0.01889999955892563, -0.03020000085234642, -0.058400001376867294, 0.015599999576807022, 0.014999999664723873, -0.10649999976158142, -0.03350000083446503, -0.020800000056624413, 0.010300000198185444, 0.15360000729560852, -0.04320000112056732, -0.017899999395012856, 0.09849999845027924, 0.17139999568462372, 0.10999999940395355, -0.18940000236034393, 0.13510000705718994, 0.07079999893903732, 0.10279999673366547, -0.21119999885559082, -0.02590000070631504, -0.04360000044107437, -0.1451999992132187, 0.10220000147819519, -0.32820001244544983, 0.03269999846816063, 0.020600000396370888, 0.09730000048875809, 0.1428000032901764, -0.18330000340938568, 0.06279999762773514, -0.16940000653266907, 0.21119999885559082, 0.0430000014603138, -0.05869999900460243, -0.19059999287128448, 0.07720000296831131, 0.019099999219179153, -0.14399999380111694, 0.10199999809265137, 0.049400001764297485, -0.13199999928474426, -0.054499998688697815, -0.13379999995231628, 0.05310000106692314, -0.03150000050663948, 0.038600001484155655, -0.0010999999940395355, -0.11069999635219574, 0.08100000023841858], [-0.06780000030994415, 0.12559999525547028, 0.06289999932050705, 0.09459999948740005, -0.09269999712705612, -0.12489999830722809, -0.0729999989271164, 0.02419999986886978, -0.16089999675750732, -0.14920000731945038, 0.0032999999821186066, -0.06350000202655792, 0.13099999725818634, 0.024299999698996544, -0.010300000198185444, -0.25040000677108765, -0.11010000109672546, -0.2745000123977661, -0.008299999870359898, -0.13019999861717224, 0.22849999368190765, -0.0027000000700354576, 0.08709999918937683, -0.12770000100135803, -0.06759999692440033, -0.061500001698732376, 0.013500000350177288, -0.0421999990940094, -0.03310000151395798, -0.1476999968290329, 0.00139999995008111, -0.0471000000834465, -0.03550000116229057, 0.041600000113248825, 0.11490000039339066, 0.05460000038146973, -0.053700000047683716, 0.12520000338554382, 0.0617000013589859, -0.13099999725818634, 0.12549999356269836, -0.0017000000225380063, -0.002099999925121665, -0.09549999982118607, 0.03759999945759773, 0.21819999814033508, -0.1907999962568283, -0.13269999623298645, 0.06830000132322311, -0.1347000002861023, -0.2547000050544739, -0.0414000004529953, -0.40209999680519104, 0.16830000281333923, -0.05900000035762787, 0.03220000118017197, -0.03280000016093254, 0.13189999759197235, 0.003800000064074993, -0.0632999986410141, 0.15000000596046448, 0.06719999760389328, 0.007600000128149986, -0.2603999972343445], [-0.10080000013113022, 0.040699999779462814, -0.08749999850988388, 0.14399999380111694, 0.06270000338554382, -0.09679999947547913, -0.12240000069141388, -0.05889999866485596, 0.125900000333786, 0.1535000056028366, -0.05460000038146973, 0.22130000591278076, -0.13179999589920044, -0.003100000089034438, -0.1023000031709671, 0.0471000000834465, 0.051600001752376556, -0.13259999454021454, 0.13779999315738678, -0.012600000016391277, -0.13580000400543213, -0.07320000231266022, -0.046799998730421066, 0.07530000060796738, -0.051600001752376556, -0.24719999730587006, -0.1257999986410141, 0.23029999434947968, 0.10729999840259552, 0.06889999657869339, -0.06239999830722809, -0.09369999915361404, 0.24699999392032623, -0.04179999977350235, 0.26100000739097595, 0.0851999968290329, -0.012400000356137753, -0.25870001316070557, 0.2282000035047531, 0.10220000147819519, -0.13899999856948853, 0.10670000314712524, -0.08709999918937683, 0.11500000208616257, 0.03739999979734421, 0.09939999878406525, 0.08659999817609787, 0.008100000210106373, 0.027799999341368675, 0.010300000198185444, -0.12790000438690186, -0.032999999821186066, 0.012400000356137753, 0.1111999973654747, -0.13490000367164612, 0.1535000056028366, 0.18719999492168427, 0.09459999948740005, -0.004399999976158142, -0.14800000190734863, 0.14419999718666077, -0.08209999650716782, 0.26429998874664307, -0.007699999958276749], [0.08349999785423279, 0.05490000173449516, 0.0142000000923872, -0.10939999669790268, -0.06449999660253525, 0.14419999718666077, 0.08049999922513962, 0.06430000066757202, 0.13670000433921814, 0.01119999960064888, -0.04019999876618385, 0.08190000057220459, -0.08630000054836273, -0.017500000074505806, 0.053300000727176666, 0.16940000653266907, 0.412200003862381, 0.15299999713897705, 0.030899999663233757, -0.043699998408555984, 0.19259999692440033, 0.08190000057220459, 0.18549999594688416, -0.005200000014156103, -0.008100000210106373, 0.14550000429153442, 0.23170000314712524, 0.04699999839067459, 0.30399999022483826, -0.10159999877214432, -0.09480000287294388, -0.04690000042319298, -0.21529999375343323, 0.12409999966621399, 0.04179999977350235, 0.2418999969959259, -0.12399999797344208, -0.14010000228881836, 0.0681999996304512, 0.04430000111460686, -0.09549999982118607, 0.023099999874830246, -0.01720000058412552, -0.17520000040531158, 0.00139999995008111, -0.11659999936819077, -0.14350000023841858, -0.20440000295639038, -0.020999999716877937, -0.0957999974489212, 0.11029999703168869, -0.1046999990940094, -0.1348000019788742, 0.16930000483989716, 0.06509999930858612, 0.06210000067949295, 0.03660000115633011, 0.03370000049471855, -0.11429999768733978, -0.04769999906420708, 0.03319999948143959, 0.08810000121593475, 0.120899997651577, 0.03269999846816063], [0.14959999918937683, 0.014700000174343586, -0.302700012922287, 0.054999999701976776, -0.1858000010251999, -0.03779999911785126, 0.01979999989271164, -0.15399999916553497, 0.09849999845027924, 0.0940999984741211, 0.021199999377131462, -0.03970000147819519, -0.15449999272823334, 0.05869999900460243, 0.04580000042915344, -0.018300000578165054, -0.01360000018030405, -0.12960000336170197, 0.05900000035762787, -0.09560000151395798, 0.0738999992609024, 0.08110000193119049, 0.12770000100135803, -0.050200000405311584, 0.04270000010728836, -0.16509999334812164, -0.01810000091791153, 0.08470000326633453, -0.05090000107884407, -0.07280000299215317, -0.032499998807907104, 0.06669999659061432, -0.1687999963760376, -0.022199999541044235, 0.0940999984741211, 0.014000000432133675, 0.03319999948143959, 0.2345999926328659, 0.002099999925121665, -0.1362999975681305, -0.26249998807907104, -0.13079999387264252, -0.08129999786615372, -0.24699999392032623, 0.34299999475479126, -0.0035000001080334187, -0.06509999930858612, 0.0272000003606081, 0.06199999898672104, -0.057999998331069946, -0.04039999842643738, 0.266400009393692, 0.18809999525547028, -0.1451999992132187, -0.002300000051036477, 0.13030000030994415, -0.026499999687075615, -0.3125999867916107, -0.007699999958276749, 0.0019000000320374966, -0.06319999694824219, -0.09239999949932098, 0.06499999761581421, -0.06679999828338623], [0.28189998865127563, 0.13429999351501465, 0.14309999346733093, 0.1387999951839447, -0.125900000333786, -0.14259999990463257, -0.10649999976158142, 0.09610000252723694, 0.18729999661445618, 0.008200000040233135, 0.008799999952316284, -0.21070000529289246, -0.03180000185966492, 0.03400000184774399, 0.2371000051498413, -0.11299999803304672, 0.015300000086426735, -0.04919999837875366, -0.15950000286102295, 0.20649999380111694, 0.10289999842643738, 0.04309999942779541, 0.1388999968767166, -0.09549999982118607, 0.07909999787807465, 0.20350000262260437, 0.08619999885559082, 0.10509999841451645, -0.0851999968290329, 0.029600000008940697, -0.0649000033736229, 0.032499998807907104, 0.2574999928474426, 0.02160000056028366, 0.14550000429153442, -0.07680000364780426, -0.2800999879837036, -0.05490000173449516, -0.2175000011920929, -0.019300000742077827, 0.014999999664723873, 0.02239999920129776, -0.07559999823570251, 0.10939999669790268, 0.09120000153779984, -0.08290000259876251, -0.009399999864399433, 0.16300000250339508, -0.12049999833106995, 0.0786999985575676, -0.05389999970793724, -0.08160000294446945, 0.013899999670684338, 0.07000000029802322, -0.11270000040531158, -0.08070000261068344, 0.06300000101327896, -0.10050000250339508, 0.18129999935626984, -0.16269999742507935, -0.0786999985575676, 0.06880000233650208, 0.16779999434947968, 0.11720000207424164], [-0.09049999713897705, 0.032099999487400055, -0.14110000431537628, -0.20600000023841858, 0.14710000157356262, -0.03240000084042549, -0.10610000044107437, 0.1265999972820282, 0.2791000008583069, -0.22210000455379486, -0.04190000146627426, 0.08839999884366989, 0.08229999989271164, 0.027699999511241913, 0.0421999990940094, -0.04820000007748604, -0.07010000199079514, -0.010700000450015068, -0.1680999994277954, 0.03400000184774399, 0.062199998646974564, -0.01889999955892563, -0.08829999715089798, 0.10029999911785126, -0.1599999964237213, -0.019899999722838402, 0.3246000111103058, -0.10580000281333923, 0.13189999759197235, 0.1785999983549118, -0.13979999721050262, 0.09160000085830688, 0.21469999849796295, 0.10080000013113022, 0.0997999981045723, 0.10029999911785126, 0.05180000141263008, 0.17720000445842743, 0.10520000010728836, -0.016699999570846558, 0.07819999754428864, -0.03819999843835831, 0.03799999877810478, -0.14489999413490295, 0.24469999969005585, -0.018400000408291817, 0.16009999811649323, 0.08079999685287476, 0.15639999508857727, -0.05719999969005585, 0.08959999680519104, -0.05299999937415123, 0.11999999731779099, -0.17190000414848328, 0.05009999871253967, -0.08150000125169754, 0.13660000264644623, 0.17299999296665192, 0.1256999969482422, -0.01489999983459711, 0.0032999999821186066, 0.08919999748468399, -0.04320000112056732, -0.20839999616146088], [0.066600002348423, -0.11020000278949738, -0.029600000008940697, -0.0005000000237487257, -0.10639999806880951, -0.1712000072002411, 0.0414000004529953, 0.17020000517368317, 0.0640999972820282, -0.0364999994635582, 0.22779999673366547, 0.2924000024795532, -0.15049999952316284, -0.0052999998442828655, 0.09610000252723694, -0.017000000923871994, 0.003000000026077032, 0.1193000003695488, -0.19629999995231628, 0.1996999979019165, 0.14550000429153442, -0.14069999754428864, 0.19130000472068787, 0.031599998474121094, -0.017100000753998756, 0.13590000569820404, 0.04230000078678131, 0.10559999942779541, -0.2680000066757202, -0.004699999932199717, -0.02500000037252903, 0.07750000059604645, 0.061500001698732376, -0.15440000593662262, -0.11720000207424164, 0.07410000264644623, -0.01860000006854534, -0.05570000037550926, 0.25029999017715454, 0.028599999845027924, 0.018300000578165054, -0.19979999959468842, 0.008700000122189522, 0.12300000339746475, -0.18000000715255737, 0.1517000049352646, 0.01889999955892563, -0.06539999693632126, 0.24410000443458557, 0.025800000876188278, 0.008200000040233135, 0.20909999310970306, -0.13570000231266022, -0.1054999977350235, 0.0723000019788742, 0.11089999973773956, 0.08550000190734863, -0.10260000079870224, -0.11479999870061874, 0.0019000000320374966, 0.15360000729560852, -0.03139999881386757, -0.13369999825954437, 0.030899999663233757], [0.020800000056624413, -0.041600000113248825, 0.03700000047683716, 0.08410000056028366, -0.023099999874830246, 0.07249999791383743, 0.15410000085830688, 0.15839999914169312, -0.0949999988079071, -0.15790000557899475, 0.005200000014156103, -0.024800000712275505, 0.08529999852180481, -0.1793999969959259, -0.12610000371932983, 0.17730000615119934, 0.1509000062942505, -0.32899999618530273, -0.059300001710653305, 0.15489999949932098, -0.09179999679327011, -0.1808999925851822, 0.05770000070333481, 0.10090000182390213, -0.19220000505447388, -0.04010000079870224, 0.18070000410079956, 0.10949999839067459, -0.09910000115633011, 0.035599999129772186, 0.18549999594688416, 0.20260000228881836, -0.05090000107884407, -0.015200000256299973, -0.08340000361204147, 0.20479999482631683, 0.14550000429153442, 0.26969999074935913, -0.05139999836683273, -0.05119999870657921, 0.014100000262260437, -0.05290000140666962, -0.07739999890327454, 0.07069999724626541, 0.04619999974966049, 0.1234000027179718, -0.029600000008940697, 0.07270000129938126, -0.04749999940395355, 0.0406000018119812, 0.0035000001080334187, -0.09189999848604202, 0.17249999940395355, 0.16820000112056732, -0.05939999967813492, -0.022600000724196434, -0.1282999962568283, 0.05000000074505806, -0.16249999403953552, -0.21889999508857727, -0.01679999940097332, -0.07429999858140945, 0.18860000371932983, 0.18140000104904175], [0.0035000001080334187, 0.26460000872612, -0.06930000334978104, -0.14970000088214874, -0.13920000195503235, -0.23970000445842743, 0.07580000162124634, 0.04439999908208847, -0.16089999675750732, -0.01850000023841858, -0.028699999675154686, 0.2847000062465668, 0.17069999873638153, 0.14499999582767487, 0.02850000001490116, 0.09830000251531601, -0.1200999990105629, -0.022600000724196434, 0.09480000287294388, 0.04969999939203262, 0.030300000682473183, 0.061799999326467514, 0.2184000015258789, 0.07329999655485153, 0.06549999862909317, 0.12790000438690186, -0.14470000565052032, 0.07509999722242355, -0.0215000007301569, 0.15150000154972076, 0.002300000051036477, -0.0738999992609024, -0.09229999780654907, 0.2825999855995178, 0.12680000066757202, -0.0934000015258789, 0.20350000262260437, -0.12359999865293503, -0.03319999948143959, -0.05739999935030937, -0.0737999975681305, -0.005499999970197678, -0.15520000457763672, -0.10520000010728836, -0.07970000058412552, 0.06260000169277191, -0.09610000252723694, 0.07000000029802322, 0.16769999265670776, -0.10679999738931656, 0.05550000071525574, -0.16990000009536743, 0.17880000174045563, -0.06650000065565109, -0.11900000274181366, -0.06019999831914902, -0.1657000035047531, 0.11819999665021896, 0.12960000336170197, -0.08259999752044678, -0.0020000000949949026, 0.07109999656677246, -0.1136000007390976, 0.2029000073671341], [-0.10939999669790268, -0.12139999866485596, -0.15569999814033508, -0.07540000230073929, 0.0414000004529953, -0.06750000268220901, 0.0868000015616417, -0.1729000061750412, 0.155799999833107, 0.16859999299049377, 0.051600001752376556, -0.04619999974966049, 0.13729999959468842, 0.04580000042915344, -0.07760000228881836, -0.07680000364780426, -0.18410000205039978, -0.043800000101327896, -0.18559999763965607, 0.14589999616146088, 0.12600000202655792, -0.10670000314712524, 0.026599999517202377, 0.05999999865889549, 0.15399999916553497, 0.05990000069141388, 0.0035000001080334187, 0.023000000044703484, -0.02759999968111515, 0.14900000393390656, 0.041600000113248825, -0.18930000066757202, -0.027000000700354576, 0.038600001484155655, 0.02319999970495701, 0.12160000205039978, 0.181099995970726, 0.12250000238418579, 0.03929999843239784, 0.25119999051094055, 0.02019999921321869, -0.016599999740719795, -0.1987999975681305, -0.11460000276565552, -0.16300000250339508, -0.2289000004529953, -0.017000000923871994</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>[[[-0.0015999999595806003, -0.053199999034404755, -0.0421999990940094, 0.004399999976158142, 0.09880000352859497, 0.0008999999845400453, -0.06719999760389328, -0.0843999981880188, -0.036400001496076584, -0.21719999611377716, -0.08380000293254852, -0.02759999968111515, 0.04740000143647194, 0.08460000157356262, -0.12060000002384186, 0.05480000004172325, -0.033900000154972076, 0.07509999722242355, 0.024000000208616257, -0.10520000010728836, 0.010900000110268593, 0.08449999988079071, 0.155799999833107, 0.014600000344216824, 0.07569999992847443, 0.00800000037997961, 0.00800000037997961, 0.0851999968290329, 0.02930000051856041, 0.06430000066757202, -0.040699999779462814, -0.06430000066757202, 0.061400000005960464, -0.03739999979734421, 0.01720000058412552, 0.08950000256299973, 0.06199999898672104, 0.013500000350177288, 0.14830000698566437, 0.12890000641345978, 0.05730000138282776, 0.013199999928474426, 0.003100000089034438, 0.0949999988079071, -0.06419999897480011, 0.0714000016450882, -0.06279999762773514, -0.06109999865293503, 0.08290000259876251, 0.02319999970495701, -0.1031000018119812, 0.09669999778270721, 0.08579999953508377, -0.019999999552965164, 0.03629999980330467, -0.06319999694824219, 0.031300000846385956, 0.04280000180006027, -0.08510000258684158, -0.05909999832510948, -0.04639999940991402, -0.12939999997615814, -0.10740000009536743, -0.06270000338554382], [0.03269999846816063, -0.007300000172108412, 0.062300000339746475, 0.03909999877214432, 0.05009999871253967, -0.10300000011920929, -0.08020000159740448, 0.05920000001788139, 0.08579999953508377, 0.0949999988079071, 0.010999999940395355, -0.03590000048279762, -0.009999999776482582, -0.02850000001490116, 0.08349999785423279, -0.06019999831914902, 0.08669999986886978, -0.0674000009894371, -0.05290000140666962, 0.1615000069141388, 0.026000000536441803, -0.1306000053882599, -0.12219999730587006, 0.0746999979019165, -0.09160000085830688, -0.030899999663233757, -0.06790000200271606, -0.09600000083446503, -0.07970000058412552, -0.04879999905824661, 0.09430000185966492, 0.06260000169277191, 0.0333000011742115, -0.0010000000474974513, 0.027300000190734863, -0.1598999947309494, -0.05550000071525574, -0.06930000334978104, -0.15530000627040863, -0.23579999804496765, -0.03319999948143959, -0.05000000074505806, 0.03180000185966492, -0.01769999973475933, 0.07609999924898148, -0.033399999141693115, 0.08789999783039093, 0.10260000079870224, -0.0568000003695488, -0.008700000122189522, 0.10670000314712524, -0.10140000283718109, -0.11620000004768372, 0.00419999985024333, -0.11309999972581863, 0.1412999927997589, 0.0010999999940395355, -0.05820000171661377, 0.12520000338554382, 0.07100000232458115, 0.03739999979734421, 0.08479999750852585, 0.10270000249147415, 0.01720000058412552]], [[0.08299999684095383, 0.047200001776218414, -0.060499999672174454, 0.11479999870061874, -0.06939999759197235, 0.033399999141693115, 0.005900000222027302, 0.24279999732971191, 0.06289999932050705, 0.16439999639987946, 0.08139999955892563, 0.0015999999595806003, -0.09309999644756317, -0.2784999907016754, -0.09459999948740005, 0.0203000009059906, 0.027799999341368675, -0.0406000018119812, 0.057500001043081284, -0.058400001376867294, 0.4122999906539917, 0.07410000264644623, -0.11559999734163284, -0.1216999962925911, 0.09059999883174896, -0.011099999770522118, -0.11010000109672546, -0.026900000870227814, 0.02800000086426735, 0.015599999576807022, 0.013100000098347664, 0.11680000275373459, 0.03660000115633011, 0.03739999979734421, -0.10890000313520432, -0.046300001442432404, 0.10679999738931656, 0.10769999772310257, 0.10329999774694443, 0.2736000120639801, -0.09650000184774399, 0.29510000348091125, 0.015300000086426735, -0.1687999963760376, -0.05959999933838844, 0.15449999272823334, 0.09969999641180038, 0.031199999153614044, -0.050200000405311584, 0.1289999932050705, 0.14190000295639038, -0.11969999969005585, 0.05649999901652336, -0.035999998450279236, -0.12240000069141388, 0.13860000669956207, -0.15610000491142273, 0.05700000002980232, 0.09390000253915787, 0.024800000712275505, 0.060600001364946365, 0.10660000145435333, -0.10989999771118164, -0.0763000026345253], [0.009600000455975533, 0.03350000083446503, 0.12080000340938568, -0.011699999682605267, 0.05299999937415123, 0.14239999651908875, 0.24459999799728394, -0.05660000070929527, 0.10320000350475311, -0.06480000168085098, -0.10339999943971634, -0.1965000033378601, 0.03530000150203705, -0.06780000030994415, 0.1551000028848648, -0.06310000270605087, -0.18559999763965607, 0.3361000120639801, 0.06040000170469284, -0.11010000109672546, 0.02199999988079071, -0.11029999703168869, -0.09749999642372131, -0.022600000724196434, -0.14350000023841858, 0.0005000000237487257, -0.18559999763965607, 0.13259999454021454, -0.09870000183582306, 0.056299999356269836, 0.009700000286102295, 0.06930000334978104, 0.06960000097751617, 0.029999999329447746, 0.3158000111579895, 0.2678000032901764, 0.36489999294281006, -0.10719999670982361, -0.2093999981880188, -0.03790000081062317, -0.19460000097751617, 0.026499999687075615, 0.1031000018119812, 0.012500000186264515, 0.03269999846816063, 0.24050000309944153, 0.20200000703334808, 0.06650000065565109, 0.16979999840259552, 0.0674000009894371, -0.05420000106096268, -0.0071000000461936, -0.24969999492168427, -0.03790000081062317, 0.029999999329447746, -0.02070000022649765, -0.01640000008046627, -0.23389999568462372, -0.18649999797344208, -0.14920000731945038, -0.02250000089406967, 0.10100000351667404, -0.05790000036358833, 0.018200000748038292], [0.00860000029206276, 0.05209999904036522, 0.30070000886917114, -0.20909999310970306, -0.16850000619888306, -0.009600000455975533, -0.13819999992847443, -0.08320000022649765, -0.10369999706745148, -0.10840000212192535, 0.12200000137090683, -0.14949999749660492, -0.09319999814033508, -0.08720000088214874, 0.2515999972820282, 0.23100000619888306, -0.05310000106692314, 0.04639999940991402, -0.023900000378489494, 0.028699999675154686, 0.08250000327825546, -0.018400000408291817, 0.09539999812841415, 0.18529999256134033, 0.08479999750852585, -0.20069999992847443, -0.00800000037997961, -0.19689999520778656, 0.11079999804496765, -0.0215000007301569, -0.06790000200271606, 0.10939999669790268, -0.11089999973773956, -0.016499999910593033, 0.07419999688863754, -0.14579999446868896, 0.010599999688565731, 0.05620000138878822, 0.016300000250339508, 0.25619998574256897, -0.10279999673366547, -0.08299999684095383, 0.07199999690055847, 0.033799998462200165, 0.15800000727176666, 0.08330000191926956, 0.32919999957084656, -0.019600000232458115, 0.05959999933838844, -0.09690000116825104, 0.017500000074505806, -0.0778999999165535, -0.07460000365972519, 0.12030000239610672, -0.29660001397132874, -0.007899999618530273, 0.004699999932199717, 0.029400000348687172, -0.006000000052154064, -0.2565999925136566, -0.012000000104308128, -0.17249999940395355, -0.19020000100135803, 0.08079999685287476], [-0.3544999957084656, 0.2924000024795532, 0.14509999752044678, -0.012299999594688416, 0.007000000216066837, -0.09260000288486481, -0.08869999647140503, 0.09290000051259995, 0.1371999979019165, 0.10170000046491623, 0.0763000026345253, -0.11760000139474869, -0.18219999969005585, 0.05829999968409538, -0.014600000344216824, -0.08619999885559082, 0.09369999915361404, -0.10930000245571136, -0.041200000792741776, 0.07540000230073929, -0.262800008058548, -0.12890000641345978, 0.14810000360012054, 0.027799999341368675, 0.06729999929666519, -0.12039999663829803, 0.093299999833107, -0.06279999762773514, 0.016499999910593033, -0.10899999737739563, -0.028999999165534973, -0.07599999755620956, -0.11389999836683273, 0.0035000001080334187, -0.0989999994635582, 0.023499999195337296, -0.05420000106096268, 0.03449999913573265, 0.1446000039577484, 0.02800000086426735, -0.08659999817609787, -0.09059999883174896, -0.08259999752044678, -0.21320000290870667, -0.22269999980926514, -0.10320000350475311, 0.07800000160932541, -0.11729999631643295, -0.0892999991774559, 0.15780000388622284, 0.13850000500679016, -0.02759999968111515, 0.024399999529123306, -0.2531000077724457, 0.024399999529123306, -0.10100000351667404, -0.37040001153945923, -0.06400000303983688, -0.04129999876022339, -0.16830000281333923, 0.11100000143051147, 0.30709999799728394, 0.042899999767541885, -0.09380000084638596], [0.07859999686479568, 0.2596000134944916, -0.13030000030994415, 0.04430000111460686, 0.14509999752044678, 0.22120000422000885, 0.0925000011920929, -0.10369999706745148, -0.10790000110864639, 0.22089999914169312, -0.020999999716877937, -0.20090000331401825, -0.03610000014305115, 0.10580000281333923, 0.0731000006198883, 0.2296999990940094, -0.09130000323057175, 0.020800000056624413, 0.06629999727010727, -0.10750000178813934, 0.05739999935030937, -0.07750000059604645, 0.21739999949932098, -0.06870000064373016, -0.08479999750852585, -0.01549999974668026, 0.2011999934911728, 0.051100000739097595, 0.008700000122189522, -0.1469999998807907, -0.021900000050663948, -0.08640000224113464, 0.18549999594688416, -0.13429999351501465, -0.046300001442432404, -0.14830000698566437, -0.018300000578165054, 0.15639999508857727, 0.1492999941110611, -0.035100001841783524, -0.046799998730421066, -0.06840000301599503, -0.1858000010251999, -0.0421999990940094, -0.2565999925136566, 0.18019999563694, 0.14920000731945038, 0.025100000202655792, 0.15960000455379486, 9.999999747378752e-05, 0.002199999988079071, 0.044199999421834946, -0.05869999900460243, 0.0038999998942017555, 0.08720000088214874, -0.06870000064373016, 0.12479999661445618, 0.17739999294281006, 0.2021999955177307, 0.14489999413490295, -0.1451999992132187, 0.06530000269412994, 0.21549999713897705, 0.06430000066757202], [0.23280000686645508, -0.026000000536441803, -0.2639000117778778, -0.1964000016450882, 0.08179999887943268, 0.08829999715089798, -0.06120000034570694, -0.0997999981045723, -0.035100001841783524, -0.06830000132322311, 0.13289999961853027, 0.10790000110864639, -0.022600000724196434, 0.03790000081062317, -0.014700000174343586, -0.01209999993443489, -0.12939999997615814, -0.05009999871253967, -0.09220000356435776, 0.11590000241994858, -0.07660000026226044, 0.03579999879002571, 0.08129999786615372, -0.1088000014424324, -0.0868000015616417, 0.09430000185966492, -0.21040000021457672, 0.13519999384880066, 0.11110000312328339, 0.07339999824762344, -0.07050000131130219, 0.14169999957084656, -0.20100000500679016, -0.11259999871253967, -0.05389999970793724, -0.035100001841783524, 0.17499999701976776, 0.12080000340938568, 0.06909999996423721, -0.04639999940991402, -0.07020000368356705, 0.2533000111579895, 0.18520000576972961, 0.18080000579357147, 0.013100000098347664, -0.13979999721050262, 0.025499999523162842, 0.013899999670684338, -0.14309999346733093, 0.15690000355243683, -0.06930000334978104, 0.07670000195503235, -0.07819999754428864, 0.0778999999165535, -0.010200000368058681, -0.3003999888896942, 0.026000000536441803, 0.08129999786615372, 0.025599999353289604, -0.1915999948978424, 0.17800000309944153, 0.2849000096321106, 0.049300000071525574, -0.12839999794960022], [0.08780000358819962, 0.07800000160932541, -0.0778999999165535, 0.3109999895095825, 0.04390000179409981, -0.12200000137090683, 0.42660000920295715, -0.053300000727176666, 0.08290000259876251, -0.21050000190734863, -0.16449999809265137, 0.0010000000474974513, -0.00139999995008111, 0.20239999890327454, -0.023499999195337296, -0.15080000460147858, -0.009200000204145908, 0.16979999840259552, -0.08699999749660492, 0.0013000000035390258, 0.028599999845027924, -0.19130000472068787, -0.10670000314712524, -0.019700000062584877, 0.026799999177455902, 0.052299998700618744, 0.10790000110864639, -0.015300000086426735, 0.19660000503063202, 0.21400000154972076, 0.041600000113248825, 0.03970000147819519, -0.20280000567436218, 0.00860000029206276, 0.0284000001847744, -0.22220000624656677, -0.013199999928474426, 0.0997999981045723, 0.08089999854564667, 0.24040000140666962, 0.14569999277591705, 0.08110000193119049, 0.11980000138282776, 0.09369999915361404, -0.003599999938160181, 0.002400000113993883, 0.05040000006556511, -0.1850000023841858, -0.11159999668598175, -0.08789999783039093, -0.2535000145435333, 0.1264999955892563, 0.14980000257492065, -0.0333000011742115, -0.024000000208616257, 0.14229999482631683, -0.06069999933242798, 0.006000000052154064, -0.04800000041723251, -0.1388999968767166, 0.0024999999441206455, 0.10580000281333923, -0.05869999900460243, 0.054499998688697815], [0.1875, 0.04390000179409981, 0.09860000014305115, 0.06689999997615814, -0.0333000011742115, 0.20469999313354492, -0.18160000443458557, -0.09200000017881393, 0.18310000002384186, -0.1996999979019165, 0.2720000147819519, -0.14720000326633453, 0.039400000125169754, -0.09149999916553497, 0.02850000001490116, -0.04610000178217888, 0.14239999651908875, -0.012400000356137753, -0.05810000002384186, 0.14339999854564667, 0.022600000724196434, -0.012600000016391277, -0.22220000624656677, 0.03700000047683716, -0.004900000058114529, 0.05849999934434891, -0.15049999952316284, 0.04749999940395355, -0.009499999694526196, 0.1582999974489212, -0.10419999808073044, -0.2612000107765198, 0.04740000143647194, 0.11550000309944153, 0.03920000046491623, -0.1014999970793724, 0.10649999976158142, -0.08659999817609787, 0.03739999979734421, 0.1103999987244606, 0.06350000202655792, -0.13760000467300415, -0.16410000622272491, -0.17960000038146973, 0.007899999618530273, 0.11890000104904175, 0.14790000021457672, -0.020099999383091927, 0.041600000113248825, -0.08900000154972076, -0.0017999999690800905, 0.2980000078678131, 0.03689999878406525, 0.27239999175071716, -0.09380000084638596, -0.20069999992847443, -0.21660000085830688, -0.09120000153779984, -0.11180000007152557, 0.18029999732971191, 0.352400004863739, 0.08659999817609787, -0.07519999891519547, 0.323199987411499], [-0.20069999992847443, -0.11420000344514847, -0.0737999975681305, 0.005799999926239252, 0.004100000020116568, 0.0044999998062849045, 0.0885000005364418, -0.05900000035762787, -0.08269999921321869, -0.036400001496076584, 0.3353999853134155, -0.03280000016093254, 0.1485999971628189, -0.31540000438690186, 0.2175000011920929, -0.05700000002980232, 0.08219999819993973, 0.03620000183582306, 0.20260000228881836, -0.18860000371932983, -0.05119999870657921, -0.025499999523162842, 0.15320000052452087, 0.07199999690055847, 0.03709999844431877, 0.13660000264644623, 0.0052999998442828655, 0.07400000095367432, 0.003100000089034438, 0.28110000491142273, -0.03290000185370445, 0.038600001484155655, -0.05559999868273735, 0.1468999981880188, -0.05510000139474869, 0.17509999871253967, -0.23759999871253967, -0.121799997985363, 0.10339999943971634, 0.03180000185966492, 0.25209999084472656, 0.09600000083446503, 0.07150000333786011, 0.01769999973475933, 0.03610000014305115, 0.23360000550746918, 0.1234000027179718, 0.06440000236034393, -0.017000000923871994, -0.12710000574588776, -0.033399999141693115, 0.00570000009611249, 0.05640000104904175, -0.06419999897480011, 0.0649000033736229, -0.005499999970197678, -0.2168000042438507, -0.14550000429153442, 0.15970000624656677, -0.06080000102519989, -0.1492999941110611, 0.11020000278949738, 0.14149999618530273, -0.03440000116825104], [0.13210000097751617, -0.07410000264644623, 0.06759999692440033, -0.2110999971628189, 0.10580000281333923, -0.09799999743700027, 0.259799987077713, 0.043800000101327896, 0.08269999921321869, -0.08150000125169754, -0.020999999716877937, -0.211899995803833, -0.11599999666213989, -0.2142000049352646, 0.06719999760389328, 0.10589999705553055, 0.15780000388622284, -0.05719999969005585, -0.1574999988079071, 0.006300000008195639, 0.15459999442100525, 0.0044999998062849045, 0.120899997651577, 0.4309000074863434, 0.3970000147819519, -0.22300000488758087, -0.1923000067472458, -0.13950000703334808, -0.13439999520778656, -0.017400000244379044, 0.20479999482631683, 0.050700001418590546, 0.07100000232458115, 0.014999999664723873, 0.03420000150799751, 0.006099999882280827, -0.08030000329017639, -0.06549999862909317, -0.08129999786615372, -0.133200004696846, 0.043800000101327896, 0.1362999975681305, -0.05169999971985817, -0.13729999959468842, 0.08340000361204147, -0.0568000003695488, 0.16619999706745148, 0.17820000648498535, -0.16089999675750732, -0.1745000034570694, -0.20100000500679016, 0.210099995136261, -0.15719999372959137, -0.03020000085234642, 0.07029999792575836, -0.05620000138878822, -0.09880000352859497, 0.010999999940395355, 0.15240000188350677, 0.10769999772310257, 0.2937000095844269, 0.2345999926328659, 0.019500000402331352, 0.24889999628067017], [-0.1281999945640564, -0.15209999680519104, -0.024700000882148743, 0.14030000567436218, 0.1956000030040741, -0.004100000020116568, -0.1606999933719635, -0.09300000220537186, 0.04450000077486038, -0.04610000178217888, 0.14920000731945038, -0.12060000002384186, 0.05739999935030937, 0.09809999912977219, -0.2547000050544739, 0.1404000073671341, -0.04089999943971634, -0.052000001072883606, -0.26429998874664307, -0.0729999989271164, 0.09759999811649323, 0.09730000048875809, 0.12030000239610672, -0.01759999990463257, -0.21449999511241913, 0.03500000014901161, 0.09189999848604202, 0.10480000078678131, 0.18080000579357147, 0.11800000071525574, 0.20160000026226044, 0.17649999260902405, -0.17339999973773956, 0.11900000274181366, 0.12600000202655792, -0.07450000196695328, 0.10279999673366547, -0.2524999976158142, -0.053300000727176666, 0.07159999758005142, -0.013500000350177288, -0.2386000007390976, 0.2554999887943268, 0.007300000172108412, -0.040800001472234726, 0.1289999932050705, -0.08540000021457672, 0.12549999356269836, -0.1881999969482422, 0.007799999788403511, -0.08169999718666077, 0.1873999983072281, -0.0949999988079071, -0.06859999895095825, -0.0560000017285347, 0.12929999828338623, 0.043800000101327896, -0.057100001722574234, 0.20160000026226044, -0.060499999672174454, -0.004000000189989805, 0.14090000092983246, -0.1606999933719635, 0.21549999713897705], [-0.07970000058412552, 0.125900000333786, -0.05220000073313713, 0.23960000276565552, 0.056699998676776886, 0.003800000064074993, 0.0674000009894371, -0.04390000179409981, -0.013899999670684338, 0.0035000001080334187, 0.17520000040531158, 0.5156999826431274, 0.04960000142455101, 0.05130000039935112, -0.045899998396635056, -0.03849999979138374, -0.04540000110864639, 0.04969999939203262, -0.015399999916553497, -0.1216999962925911, -0.03350000083446503, -0.050599999725818634, 0.01080000028014183, 0.12349999696016312, -0.03929999843239784, -0.004100000020116568, 0.1242000013589859, 0.18310000002384186, 0.1371999979019165, -0.20329999923706055, 0.16179999709129333, 0.0835999995470047, 0.07129999995231628, -0.22460000216960907, -0.04650000110268593, -0.06949999928474426, -0.10220000147819519, 0.1348000019788742, -0.35760000348091125, 0.07240000367164612, 0.057100001722574234, 0.08659999817609787, 0.1664000004529953, -0.18060000240802765, 0.027899999171495438, -0.1420000046491623, 0.18459999561309814, 0.042899999767541885, -0.08129999786615372, -0.21119999885559082, 0.03999999910593033, 0.04639999940991402, -0.13269999623298645, 0.1014999970793724, 0.06469999998807907, -0.1500999927520752, -0.06539999693632126, -0.12720000743865967, 0.03139999881386757, -0.04780000075697899, 0.06790000200271606, 0.017000000923871994, -0.13249999284744263, 0.09309999644756317], [-0.0868000015616417, 0.17749999463558197, 0.05480000004172325, 0.10040000081062317, -0.10599999874830246, -0.16920000314712524, -0.062199998646974564, 0.09719999879598618, -0.1768999993801117, -0.11550000309944153, -0.004999999888241291, -0.05469999834895134, 0.08699999749660492, 0.01549999974668026, -0.04520000144839287, -0.2003999948501587, -0.06239999830722809, -0.3328999876976013, -0.06279999762773514, -0.16110000014305115, 0.17499999701976776, 0.05000000074505806, 0.06790000200271606, -0.17479999363422394, -0.09210000187158585, -0.052400000393390656, 0.014000000432133675, -0.07559999823570251, -0.0032999999821186066, -0.1518000066280365, 0.029999999329447746, -0.0348999984562397, -0.037300001829862595, 0.014299999922513962, 0.07339999824762344, 0.04089999943971634, -0.1469999998807907, 0.1331000030040741, 0.06549999862909317, -0.15800000727176666, 0.08110000193119049, -0.019500000402331352, 0.004600000102072954, -0.17980000376701355, 0.03319999948143959, 0.10360000282526016, -0.2517000138759613, -0.1128000020980835, 0.07890000194311142, -0.1720000058412552, -0.19370000064373016, -0.1071000024676323, -0.39070001244544983, 0.147599995136261, -0.03359999880194664, 0.09449999779462814, -0.10360000282526016, 0.16169999539852142, 0.032999999821186066, -0.00930000003427267, 0.14229999482631683, 0.07320000231266022, 0.12020000070333481, -0.28769999742507935], [-0.06610000133514404, 0.10719999670982361, -0.11649999767541885, 0.20909999310970306, 0.009499999694526196, -0.08829999715089798, -0.14740000665187836, -0.026599999517202377, 0.049800001084804535, 0.18019999563694, -0.06769999861717224, 0.23800000548362732, -0.2151000052690506, 0.033900000154972076, -0.13269999623298645, 0.10760000348091125, 0.03060000017285347, -0.1420000046491623, 0.11420000344514847, 0.03669999912381172, -0.1981000006198883, -0.13179999589920044, -0.09549999982118607, 0.0632999986410141, -0.03220000118017197, -0.2660999894142151, -0.08739999681711197, 0.23250000178813934, 0.13500000536441803, 0.032099999487400055, -0.07490000128746033, -0.18469999730587006, 0.30970001220703125, -0.11020000278949738, 0.2117999941110611, 0.11909999698400497, -0.05869999900460243, -0.23929999768733978, 0.29350000619888306, 0.03579999879002571, -0.2354000061750412, 0.08370000123977661, -0.10790000110864639, 0.08510000258684158, -0.007000000216066837, -0.0020000000949949026, -0.00279999990016222, 0.04340000078082085, 0.09759999811649323, 0.055399999022483826, -0.05829999968409538, -0.03280000016093254, -0.05609999969601631, 0.03840000182390213, -0.15449999272823334, 0.1915999948978424, 0.1444000005722046, 0.19050000607967377, -0.02199999988079071, -0.07750000059604645, 0.08560000360012054, -0.12489999830722809, 0.3431999981403351, -0.09309999644756317], [0.08569999784231186, 0.05400000140070915, 0.12729999423027039, -0.21160000562667847, -0.15960000455379486, 0.17499999701976776, 0.014499999582767487, 0.05570000037550926, 0.28139999508857727, -0.008500000461935997, 0.037300001829862595, -0.05640000104904175, -0.1607999950647354, -0.11720000207424164, 0.14830000698566437, 0.16539999842643738, 0.46650001406669617, 0.08619999885559082, -0.01360000018030405, -0.06769999861717224, 0.2962000072002411, 0.0560000017285347, 0.27959999442100525, 0.08990000188350677, 0.06289999932050705, 0.24070000648498535, 0.14259999990463257, -0.03840000182390213, 0.18160000443458557, -0.1738000065088272, -0.03700000047683716, 0.01510000042617321, -0.2483000010251999, 0.20319999754428864, 0.19439999759197235, 0.13850000500679016, -0.09359999746084213, -0.20819999277591705, 0.015399999916553497, 0.0737999975681305, -0.019200000911951065, 0.18790000677108765, 0.05339999869465828, -0.18709999322891235, 0.058800000697374344, -0.08640000224113464, 0.010200000368058681, -0.11270000040531158, -0.11620000004768372, -0.1429000049829483, 0.0843999981880188, -0.027899999171495438, -0.1103999987244606, 0.26100000739097595, 0.05260000005364418, 0.050200000405311584, -0.04619999974966049, -0.07850000262260437, -0.15569999814033508, -0.006399999838322401, 0.11729999631643295, 0.14429999887943268, 0.08829999715089798, 0.17589999735355377], [0.16220000386238098, 0.002300000051036477, -0.35040000081062317, 0.043299999088048935, -0.09200000017881393, -0.05730000138282776, 0.04149999842047691, -0.2071000039577484, 0.01119999960064888, 0.09489999711513519, -0.039500001817941666, 0.014499999582767487, -0.020800000056624413, 0.09769999980926514, 0.00860000029206276, -0.06390000134706497, -0.0568000003695488, -0.04780000075697899, 0.1266999989748001, -0.012199999764561653, 0.13429999351501465, 0.1356000006198883, 0.07859999686479568, -0.10320000350475311, -0.022199999541044235, -0.20499999821186066, 0.04780000075697899, 0.17749999463558197, -0.019099999219179153, 0.08179999887943268, -0.13030000030994415, 0.0786999985575676, -0.16779999434947968, -0.04179999977350235, 0.045899998396635056, 0.0632999986410141, 0.1527000069618225, 0.2685999870300293, -0.02630000002682209, -0.11289999634027481, -0.24860000610351562, -0.1965000033378601, -0.1362999975681305, -0.2117999941110611, 0.3043000102043152, 0.07900000363588333, -0.09950000047683716, -0.07440000027418137, 0.03629999980330467, -0.06390000134706497, 0.035999998450279236, 0.19820000231266022, 0.2134999930858612, -0.12610000371932983, 0.04349999874830246, 0.050999999046325684, 0.10700000077486038, -0.3449999988079071, -0.053700000047683716, -0.08269999921321869, -0.04639999940991402, -0.07069999724626541, -0.066600002348423, -0.04839999973773956], [0.1598999947309494, 0.1525000035762787, 0.20509999990463257, 0.03449999913573265, -0.1200999990105629, -0.1485999971628189, -0.13449999690055847, 0.1307000070810318, 0.1835000067949295, -0.03229999914765358, 0.002400000113993883, -0.2825999855995178, -0.01979999989271164, -0.0017000000225380063, 0.23819999396800995, -0.07150000333786011, 0.05139999836683273, -0.07090000063180923, -0.14110000431537628, 0.12370000034570694, 0.1436000019311905, 0.12020000070333481, 0.17100000381469727, -0.10450000315904617, 0.08619999885559082, 0.25679999589920044, 0.03970000147819519, 0.10429999977350235, -0.1396999955177307, 0.1046999990940094, -0.09939999878406525, 0.09830000251531601, 0.19050000607967377, 0.07129999995231628, 0.15070000290870667, -0.05169999971985817, -0.29750001430511475, -0.08869999647140503, -0.22370000183582306, 0.048700001090765, 0.07729999721050262, 0.0754999965429306, -0.047600001096725464, 0.04340000078082085, 0.07739999890327454, -0.0430000014603138, 0.033799998462200165, 0.1290999948978424, -0.11209999769926071, 0.0020000000949949026, -0.05660000070929527, -0.07620000094175339, 0.05570000037550926, 0.10740000009536743, -0.0617000013589859, -0.09210000187158585, 0.03620000183582306, -0.12770000100135803, 0.17249999940395355, -0.2298000007867813, -0.04910000041127205, 0.04320000112056732, 0.17270000278949738, 0.1485999971628189], [0.01549999974668026, -0.03790000081062317, -0.13410000503063202, -0.11900000274181366, 0.11540000140666962, 0.018400000408291817, -0.09839999675750732, 0.20520000159740448, 0.17030000686645508, -0.17270000278949738, -0.050599999725818634, 0.08129999786615372, 0.04780000075697899, 0.07760000228881836, 0.09910000115633011, -0.043699998408555984, -0.15950000286102295, -0.056699998676776886, -0.11720000207424164, -0.014499999582767487, -0.015200000256299973, -0.02850000001490116, -0.1111999973654747, 0.05460000038146973, -0.1835000067949295, -0.06469999998807907, 0.38029998540878296, -0.08640000224113464, 0.15440000593662262, 0.12880000472068787, -0.20759999752044678, 0.012299999594688416, 0.25189998745918274, 0.08889999985694885, 0.11710000038146973, 0.18410000205039978, 0.019200000911951065, 0.2264000028371811, 0.10679999738931656, -0.06199999898672104, -0.004800000227987766, -0.02419999986886978, -0.008100000210106373, -0.10639999806880951, 0.3443000018596649, -0.11249999701976776, 0.07649999856948853, 0.04569999873638153, 0.20440000295639038, 0.0017000000225380063, 0.07859999686479568, -0.1543000042438507, 0.0771000012755394, -0.2619999945163727, 0.043699998408555984, -0.030400000512599945, 0.14259999990463257, 0.2517000138759613, 0.23119999468326569, 0.05950000137090683, -0.0723000019788742, 0.0012000000569969416, -0.014100000262260437, -0.31869998574256897], [0.13449999690055847, -0.1453000009059906, 0.07159999758005142, 0.049800001084804535, -0.19779999554157257, -0.13210000097751617, -0.001500000013038516, 0.14800000190734863, 0.11659999936819077, 0.03869999945163727, 0.26429998874664307, 0.23839999735355377, -0.1809999942779541, -0.0024999999441206455, 0.10239999741315842, -0.04490000009536743, 0.013700000010430813, 0.03970000147819519, -0.16760000586509705, 0.2337000072002411, 0.11469999700784683, -0.16869999468326569, 0.19470000267028809, 0.07779999822378159, -0.01549999974668026, 0.14270000159740448, -0.06080000102519989, 0.050200000405311584, -0.27489998936653137, -0.04529999941587448, -0.039400000125169754, 0.07119999825954437, 0.07349999994039536, -0.1527000069618225, -0.07090000063180923, 0.029899999499320984, -0.04619999974966049, -0.12479999661445618, 0.26350000500679016, -0.02280000038444996, -0.04989999905228615, -0.13269999623298645, -0.02410000003874302, 0.16200000047683716, -0.08290000259876251, 0.06520000100135803, 0.10360000282526016, -0.009999999776482582, 0.20479999482631683, 0.054999999701976776, 0.0007999999797903001, 0.20489999651908875, -0.1599999964237213, -0.08489999920129776, 0.007199999876320362, 0.1996999979019165, 0.06669999659061432, -0.1265999972820282, -0.09399999678134918, 0.09730000048875809, 0.10419999808073044, -0.027799999341368675, -0.10989999771118164, 0.030899999663233757], [0.02979999966919422, 0.04960000142455101, 0.016899999231100082, 0.08950000256299973, -0.0940999984741211, 0.07259999960660934, 0.0746999979019165, 0.1362999975681305, -0.03790000081062317, -0.1867000013589859, 0.04520000144839287, -0.05000000074505806, -0.025499999523162842, -0.16850000619888306, -0.1467999964952469, 0.20550000667572021, 0.18850000202655792, -0.33869999647140503, -0.15649999678134918, 0.1306000053882599, -0.06920000165700912, -0.23399999737739563, 0.0674000009894371, 0.17800000309944153, -0.12210000306367874, -0.043699998408555984, 0.13500000536441803, 0.045499999076128006, -0.08579999953508377, -0.06539999693632126, 0.2872999906539917, 0.15729999542236328, -0.008999999612569809, -0.03139999881386757, -0.07100000232458115, 0.1500999927520752, 0.11620000004768372, 0.26269999146461487, -0.006500000134110451, -0.046799998730421066, 0.006800000090152025, -0.014999999664723873, -0.01850000023841858, 0.09309999644756317, 0.009999999776482582, 0.13269999623298645, -0.050599999725818634, 0.19429999589920044, -0.011900000274181366, 0.06669999659061432, -0.12479999661445618, -0.023499999195337296, 0.14270000159740448, 0.17010000348091125, -0.10180000215768814, 0.0066999997943639755, -0.26899999380111694, 0.07689999788999557, -0.2215999960899353, -0.13989999890327454, -0.0032999999821186066, -0.08489999920129776, 0.23510000109672546, 0.1964000016450882], [-0.0017999999690800905, 0.2418999969959259, -0.05130000039935112, -0.1281999945640564, -0.18970000743865967, -0.23180000483989716, 0.033799998462200165, 0.07980000227689743, -0.1882999986410141, 0.01269999984651804, -0.014399999752640724, 0.2669999897480011, 0.12330000102519989, 0.1738000065088272, 0.06069999933242798, 0.12080000340938568, -0.14409999549388885, -0.05090000107884407, 0.10459999740123749, 0.011699999682605267, -0.013399999588727951, 0.0017000000225380063, 0.1776999980211258, 0.09109999984502792, 0.0820000022649765, 0.12319999933242798, -0.155799999833107, 0.035599999129772186, -0.02449999935925007, 0.11010000109672546, -0.009200000204145908, -0.10159999877214432, -0.05400000140070915, 0.2587999999523163, 0.1459999978542328, -0.061900001019239426, 0.09449999779462814, -0.12849999964237213, 0.006500000134110451, -0.11400000005960464, -0.14159999787807465, 0.010900000110268593, -0.1445000022649765, -0.1378999948501587, -0.05640000104904175, 0.01510000042617321, -0.11890000104904175, 0.0803999975323677, 0.20329999923706055, -0.07689999788999557, 0.051600001752376556, -0.15760000050067902, 0.11659999936819077, -0.08869999647140503, -0.149399995803833, -0.03519999980926514, -0.19660000503063202, 0.12960000336170197, 0.17069999873638153, -0.0414000004529953, -0.04039999842643738, 0.03290000185370445, -0.0035000001080334187, 0.16459999978542328], [-0.011099999770522118, -0.22599999606609344, -0.10440000146627426, 0.03779999911785126, 0.11630000174045563, -0.04490000009536743, 0.08370000123977661, -0.13009999692440033, 0.05999999865889549, 0.24709999561309814, 0.02290000021457672, -0.03229999914765358, 0.2709999978542328, 0.09570000320672989, -0.02250000089406967, -0.11379999667406082, -0.25619998574256897, -0.13650000095367432, -0.052400000393390656, 0.14159999787807465, 0.09470000118017197, -0.008700000122189522, -0.04430000111460686, -0.006599999964237213, 0.023600000888109207, -0.019500000402331352, 0.022299999371170998, 0.09730000048875809, -0.016699999570846558, 0.20669999718666077, -0.06719999760389328, -0.1973000019788742, -0.08089999854564667, 0.02759999968111515, 0.11490000039339066, 0.17299999296665192, 0.188400000333786, 0.10869999974966049, 0.04270000010728836, 0.17100000381469727, -0.10010000318288803, 0.023099999874830246, -0.33970001339912415, -0.04749999940395355, 0.03189999982714653, -0.32190001010894775, 0.013199999928474426, -0.03009999915957451, -0.14890000224113464, 0.053899999707</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>[0.8532836933465264]</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>[0.03349043664512195]</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>[0.7608939015884699]</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>[0.054588704370631014]</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>[-4.178939574254611]</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>[1.6949617619222326]</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>[0.7298500386981837]</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>[0.062058598724873626]</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>[0.7777931811238157]</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>[0.0526987973991533]</t>
+        </is>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>[-0.8894012115641308]</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>[0.6211358182528612]</t>
+        </is>
+      </c>
+      <c r="Q22" t="inlineStr">
+        <is>
+          <t>[-0.09068662944283101]</t>
+        </is>
+      </c>
+      <c r="R22" t="inlineStr">
+        <is>
+          <t>[0.11760408094123866]</t>
+        </is>
+      </c>
+      <c r="S22" t="inlineStr">
+        <is>
+          <t>[-0.04790686975572034]</t>
+        </is>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>[0.08829698888174108]</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>[-1.119256662250622]</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>[0.20264995654474086]</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>[-0.13754140040491447]</t>
+        </is>
+      </c>
+      <c r="X22" t="inlineStr">
+        <is>
+          <t>[0.11916954642524237]</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>[-0.10920745184252945]</t>
+        </is>
+      </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>[0.0912802414375046]</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>[-1.8296440717650229]</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>[0.26033963244289576]</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>[-0.8049581686995335]</t>
+        </is>
+      </c>
+      <c r="AD22" t="inlineStr">
+        <is>
+          <t>[0.1512482230681472]</t>
+        </is>
+      </c>
+      <c r="AE22" t="inlineStr">
+        <is>
+          <t>[-0.6899308285248094]</t>
+        </is>
+      </c>
+      <c r="AF22" t="inlineStr">
+        <is>
+          <t>[0.18196849695167397]</t>
+        </is>
+      </c>
+      <c r="AG22" t="inlineStr">
+        <is>
+          <t>[-1.963268338538776]</t>
+        </is>
+      </c>
+      <c r="AH22" t="inlineStr">
+        <is>
+          <t>[0.22061520468978837]</t>
+        </is>
+      </c>
+      <c r="AI22" t="inlineStr">
+        <is>
+          <t>[-1.2143637894291]</t>
+        </is>
+      </c>
+      <c r="AJ22" t="inlineStr">
+        <is>
+          <t>[0.18146464748280325]</t>
+        </is>
+      </c>
+      <c r="AK22" t="inlineStr">
+        <is>
+          <t>[-0.6567373935621756]</t>
+        </is>
+      </c>
+      <c r="AL22" t="inlineStr">
+        <is>
+          <t>[0.1758505360119159]</t>
+        </is>
+      </c>
+      <c r="AM22" t="inlineStr">
+        <is>
+          <t>[-2.001963740145309]</t>
+        </is>
+      </c>
+      <c r="AN22" t="inlineStr">
+        <is>
+          <t>[0.23057257829130998]</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>model_64_32_1</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>[64, 32]</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>[[[0.01979999989271164, -0.020899999886751175, 0.04690000042319298, 0.05649999901652336, 0.05119999870657921, -0.12319999933242798, 0.017400000244379044, 0.01510000042617321, -0.01759999990463257, 0.030300000682473183, -0.039000000804662704, -0.014499999582767487, 0.03610000014305115, 0.09679999947547913, -0.0632999986410141, 0.003100000089034438, -0.010999999940395355, -0.0006000000284984708, 0.009399999864399433, 0.00570000009611249, -0.03370000049471855, -0.07819999754428864, -0.08079999685287476, 0.07209999859333038, 0.03180000185966492, -0.039500001817941666, 0.04800000041723251, -0.0617000013589859, 0.14569999277591705, -0.03849999979138374, -0.019700000062584877, 0.003700000001117587, -0.012799999676644802, 0.02979999966919422, -0.010999999940395355, -0.023900000378489494, -0.02449999935925007, 0.014000000432133675, -0.05990000069141388, -0.028300000354647636, 0.032099999487400055, -0.0835999995470047, -0.06310000270605087, -0.0348999984562397, 0.05040000006556511, -0.029600000008940697, 0.026799999177455902, -0.005100000184029341, -0.12250000238418579, 0.03200000151991844, -0.028999999165534973, 0.0731000006198883, 0.017999999225139618, -0.03880000114440918, 0.07970000058412552, -0.007000000216066837, 0.031300000846385956, -0.03139999881386757, 0.050599999725818634, 0.06360000371932983, -0.04699999839067459, 0.028300000354647636, 0.056699998676776886, -0.07150000333786011], [-0.09989999979734421, 0.006500000134110451, -0.049400001764297485, 0.02630000002682209, -0.010700000450015068, -0.07890000194311142, 0.10100000351667404, -0.03750000149011612, -0.08540000021457672, 0.07190000265836716, 0.05290000140666962, 0.017999999225139618, 0.026200000196695328, 0.04619999974966049, -0.05559999868273735, 0.0210999995470047, -0.01590000092983246, 0.07689999788999557, 0.05220000073313713, 0.025200000032782555, 0.10400000214576721, -0.0284000001847744, 0.0005000000237487257, -0.05040000006556511, -0.094200000166893, 0.009399999864399433, 0.0364999994635582, -0.06710000336170197, 0.00559999980032444, -0.10379999876022339, 0.07909999787807465, -0.015599999576807022, 0.09070000052452087, 0.008700000122189522, -0.023000000044703484, 0.031599998474121094, 0.04809999838471413, 0.0835999995470047, 0.01640000008046627, 0.043800000101327896, -0.02879999950528145, -0.014600000344216824, 0.023600000888109207, 0.002899999963119626, -0.05040000006556511, 0.05000000074505806, -0.03449999913573265, -0.019500000402331352, -0.01889999955892563, -0.009499999694526196, 0.03790000081062317, -0.004800000227987766, -0.06629999727010727, -0.05990000069141388, 0.019500000402331352, 0.0771000012755394, -0.051899999380111694, 0.08720000088214874, -0.03909999877214432, -0.049300000071525574, 0.008500000461935997, -0.0737999975681305, -0.01730000041425228, -0.04349999874830246]], [[-0.03240000084042549, 0.10350000113248825, -0.24079999327659607, 0.02889999933540821, -0.07999999821186066, -0.09260000288486481, 0.11919999867677689, -0.016200000420212746, -0.2685000002384186, -0.20839999616146088, 0.04410000145435333, -0.03189999982714653, -0.17020000517368317, -0.0860000029206276, 0.14839999377727509, -0.1054999977350235, -0.03370000049471855, 0.08370000123977661, 0.22220000624656677, 0.13019999861717224, 0.16120000183582306, 0.05820000171661377, 0.07190000265836716, 0.09839999675750732, -0.049800001084804535, 0.00279999990016222, -0.09629999846220016, -0.10980000346899033, -0.039500001817941666, 0.011500000022351742, -0.09790000319480896, 0.07959999889135361, 0.10570000112056732, 0.016300000250339508, -0.05040000006556511, -0.033900000154972076, -0.16220000386238098, -0.051600001752376556, -0.03229999914765358, -0.0729999989271164, 0.04989999905228615, 0.0917000025510788, -0.1565999984741211, -0.19750000536441803, -0.09019999951124191, -0.08959999680519104, 0.06859999895095825, -0.28119999170303345, 0.0357000008225441, -0.11460000276565552, 0.09080000221729279, -0.18790000677108765, 0.24570000171661377, 0.2110999971628189, 0.03590000048279762, -0.004399999976158142, 0.034299999475479126, -0.0786999985575676, 0.01679999940097332, 0.33230000734329224, 0.06360000371932983, 0.1396999955177307, 0.14489999413490295, 0.014399999752640724], [-0.21480000019073486, 0.0940999984741211, -0.03500000014901161, -0.007899999618530273, -0.03579999879002571, -0.10029999911785126, 0.04899999871850014, 0.14020000398159027, -0.08370000123977661, 0.002899999963119626, 0.11980000138282776, 0.019999999552965164, 0.04670000076293945, -0.10490000247955322, 0.3357999920845032, 0.07020000368356705, 0.08160000294446945, -0.04349999874830246, -0.09570000320672989, 0.06319999694824219, 0.06700000166893005, 0.12610000371932983, -0.06809999793767929, 0.014700000174343586, 0.14219999313354492, -0.13809999823570251, -0.014299999922513962, -0.09700000286102295, -0.14090000092983246, 0.066600002348423, -0.037300001829862595, -0.1712000072002411, 0.05299999937415123, 0.06700000166893005, 0.0017999999690800905, -0.28200000524520874, 0.399399995803833, -0.1412000060081482, 0.12139999866485596, 0.06539999693632126, 0.014999999664723873, -0.13179999589920044, -0.11949999630451202, 0.06289999932050705, 0.11980000138282776, 0.057999998331069946, -0.11129999905824661, -0.12389999628067017, -0.0035000001080334187, 0.07880000025033951, 0.06920000165700912, 0.35109999775886536, 0.11860000342130661, 0.04910000041127205, 0.18950000405311584, -0.009800000116229057, -0.1145000010728836, 0.0340999998152256, -0.1348000019788742, -0.024299999698996544, -0.04650000110268593, -0.1298000067472458, -0.012799999676644802, -0.03579999879002571], [0.2021999955177307, 0.051899999380111694, -0.04520000144839287, 0.04280000180006027, -0.08160000294446945, -0.06960000097751617, 0.10830000042915344, 0.07479999959468842, -0.10980000346899033, -0.0982000008225441, 0.2053000032901764, 0.08560000360012054, -0.24650000035762787, 0.05350000038743019, 0.020800000056624413, -0.08569999784231186, 0.23890000581741333, -0.10040000081062317, -0.15860000252723694, -0.1185000017285347, -0.08460000157356262, -0.4165000021457672, -0.008999999612569809, -0.07850000262260437, -0.06759999692440033, -0.05689999833703041, 0.09749999642372131, -0.03610000014305115, 0.009100000374019146, -0.03020000085234642, 0.016200000420212746, 0.06419999897480011, 0.24330000579357147, 0.04050000011920929, -0.08070000261068344, 0.0430000014603138, 0.11749999970197678, 0.034299999475479126, 0.05779999867081642, -0.02459999918937683, -0.19140000641345978, -0.11400000005960464, 0.1264999955892563, 0.008200000040233135, -0.0008999999845400453, -0.24050000309944153, 0.07559999823570251, 0.13220000267028809, -0.039500001817941666, 0.12349999696016312, 0.1657000035047531, -0.2159000039100647, 0.06859999895095825, 0.1339000016450882, 0.033399999141693115, 0.03009999915957451, -0.13089999556541443, 0.07859999686479568, -0.12800000607967377, -0.06199999898672104, -0.17249999940395355, -0.05460000038146973, -0.11710000038146973, -0.15320000052452087], [0.1014999970793724, 0.03400000184774399, 0.13510000705718994, 0.019200000911951065, -0.03220000118017197, -0.0560000017285347, -0.015799999237060547, 0.06840000301599503, -0.0737999975681305, -0.07410000264644623, 0.05739999935030937, -0.01489999983459711, -0.15559999644756317, -0.12530000507831573, -0.08410000056028366, 0.1281999945640564, -0.05260000005364418, -0.18940000236034393, 0.04820000007748604, -0.16830000281333923, 0.1509000062942505, -0.06650000065565109, 0.0966000035405159, -0.007799999788403511, 0.1225999966263771, -0.10300000011920929, 0.12729999423027039, -0.022299999371170998, 0.004399999976158142, -0.013299999758601189, 0.01889999955892563, 0.31690001487731934, -0.19609999656677246, 0.02410000003874302, 0.10490000247955322, -0.060600001364946365, 0.13289999961853027, 0.13830000162124634, -0.03350000083446503, -0.04690000042319298, -0.10620000213384628, 0.2662000060081482, -0.13840000331401825, -0.010099999606609344, -0.0658000037074089, 0.038100000470876694, -0.16210000216960907, -0.04039999842643738, -0.06790000200271606, -0.08609999716281891, 0.030500000342726707, 0.0044999998062849045, 0.18520000576972961, -0.04410000145435333, -0.047600001096725464, -0.11230000108480453, 0.19930000603199005, 0.2759999930858612, -0.010200000368058681, -0.05990000069141388, 0.03359999880194664, -0.26170000433921814, -0.06260000169277191, 0.38429999351501465], [-0.02590000070631504, 0.11909999698400497, 0.22589999437332153, 0.05530000105500221, -0.1315000057220459, 0.20200000703334808, 0.041200000792741776, -0.13670000433921814, -0.003700000001117587, -0.04349999874830246, -0.20900000631809235, 0.0284000001847744, -0.23800000548362732, -0.028599999845027924, -0.2434999942779541, -0.09319999814033508, 0.08889999985694885, -0.00559999980032444, -0.11050000041723251, 0.05900000035762787, 0.11620000004768372, 0.30140000581741333, 0.008899999782443047, -0.07989999651908875, -0.042100001126527786, -0.11649999767541885, -0.002400000113993883, 0.13740000128746033, -0.11670000106096268, 0.13650000095367432, 0.11800000071525574, -0.003100000089034438, 0.16750000417232513, -0.14669999480247498, -0.09480000287294388, -0.11299999803304672, 0.13609999418258667, -0.03350000083446503, 0.05590000003576279, 0.08799999952316284, -0.27140000462532043, -0.07119999825954437, -0.07020000368356705, -0.17560000717639923, -0.15189999341964722, -0.07249999791383743, -0.12330000102519989, 0.0885000005364418, -0.06719999760389328, 0.02250000089406967, 0.11309999972581863, 0.09780000150203705, -0.006300000008195639, 0.12280000001192093, -0.05139999836683273, 0.01080000028014183, 0.09359999746084213, -0.06270000338554382, 0.06080000102519989, -0.0820000022649765, 0.1656000018119812, 0.29660001397132874, -0.11919999867677689, 0.01600000075995922], [-0.06650000065565109, -0.15680000185966492, -0.2777000069618225, -0.1582999974489212, -0.17190000414848328, -0.17800000309944153, -0.027300000190734863, -0.18019999563694, -0.027300000190734863, -0.0024999999441206455, -0.06129999831318855, -0.07559999823570251, -0.12970000505447388, -0.16920000314712524, -0.164900004863739, 0.050700001418590546, 0.1257999986410141, 0.11169999837875366, 0.10610000044107437, -0.015599999576807022, -0.06120000034570694, 0.12960000336170197, 0.040699999779462814, -0.040300000458955765, -0.07349999994039536, -0.01810000091791153, -0.19869999587535858, 0.13249999284744263, 0.2702000141143799, -0.008299999870359898, -0.03440000116825104, 0.17030000686645508, 0.14650000631809235, -0.021400000900030136, 0.14010000228881836, -0.11309999972581863, 0.07569999992847443, 0.04560000076889992, -0.011800000444054604, 0.1088000014424324, -0.00839999970048666, 0.00559999980032444, 0.14910000562667847, 0.15559999644756317, 0.0632999986410141, 0.22789999842643738, -0.18230000138282776, 0.13289999961853027, -0.17710000276565552, 0.17970000207424164, -0.05009999871253967, -0.03759999945759773, -0.05590000003576279, 0.1290999948978424, 0.1509000062942505, 0.11810000240802765, -0.008700000122189522, 0.18369999527931213, 0.10329999774694443, 0.13040000200271606, 0.06769999861717224, -0.15369999408721924, 0.03350000083446503, -0.12960000336170197], [-0.04129999876022339, 0.29030001163482666, -0.12380000203847885, 0.05009999871253967, -0.09600000083446503, -0.2393999993801117, -0.11400000005960464, -0.009800000116229057, 0.14229999482631683, -0.19539999961853027, -0.15710000693798065, -0.1151999980211258, 0.10270000249147415, 0.07829999923706055, -0.04899999871850014, 0.1509000062942505, -0.12380000203847885, -0.09369999915361404, 0.02250000089406967, -0.008100000210106373, -0.13410000503063202, -0.0997999981045723, 0.0019000000320374966, -0.09149999916553497, 0.1437000036239624, -0.1467999964952469, -0.17800000309944153, 0.021800000220537186, -0.2597000002861023, -0.23029999434947968, -0.07429999858140945, -0.06279999762773514, 0.15839999914169312, -0.049300000071525574, -0.07810000330209732, 0.07069999724626541, -0.027699999511241913, -0.09269999712705612, -0.18709999322891235, -0.12729999423027039, -0.26109999418258667, 0.10040000081062317, -0.0738999992609024, -0.07599999755620956, -0.1128000020980835, 0.06419999897480011, 0.03920000046491623, 0.008899999782443047, 0.1177000030875206, 0.13950000703334808, -0.13359999656677246, 0.11840000003576279, -0.030700000002980232, -0.042500000447034836, -0.09709999710321426, -0.0640999972820282, -0.029999999329447746, 0.09860000014305115, 0.250900000333786, 0.07429999858140945, -0.10450000315904617, -0.07029999792575836, -0.12070000171661377, -0.12189999967813492], [-0.22849999368190765, 0.08829999715089798, 0.06480000168085098, -0.1712999939918518, -0.03200000151991844, 0.07980000227689743, 0.038600001484155655, 0.10320000350475311, 0.10459999740123749, 0.17100000381469727, -0.027699999511241913, 0.027499999850988388, 0.11919999867677689, 0.09099999815225601, 0.10270000249147415, -0.044599998742341995, -0.03060000017285347, 0.16050000488758087, 0.21709999442100525, 0.10000000149011612, -0.19470000267028809, -0.12600000202655792, 0.16850000619888306, 0.030799999833106995, 0.0203000009059906, -0.2451999932527542, 0.16459999978542328, 0.2743000090122223, -0.164900004863739, 0.019500000402331352, 0.11110000312328339, -0.006399999838322401, -0.08429999649524689, 0.14159999787807465, -0.08470000326633453, -0.12929999828338623, 0.024800000712275505, -0.035999998450279236, 0.042899999767541885, -0.0020000000949949026, -0.13519999384880066, 0.07249999791383743, 0.003700000001117587, 0.20309999585151672, -0.030799999833106995, -0.164000004529953, -0.10080000013113022, 0.19589999318122864, -0.031300000846385956, -0.1446000039577484, 0.1080000028014183, -0.22190000116825104, 0.07689999788999557, 0.17409999668598175, -0.002899999963119626, -0.004399999976158142, 0.07050000131130219, -0.1054999977350235, 0.1720000058412552, 0.07209999859333038, 0.10050000250339508, -0.17739999294281006, 0.17659999430179596, -0.04149999842047691], [-0.25949999690055847, -0.19290000200271606, 0.03460000082850456, 0.26820001006126404, 0.15839999914169312, -0.19189999997615814, -0.12520000338554382, -0.02250000089406967, 0.034699998795986176, -0.0982000008225441, 0.032499998807907104, 0.1136000007390976, -0.03629999980330467, -0.053300000727176666, -0.10920000076293945, -0.1054999977350235, -0.10480000078678131, -0.07079999893903732, 0.20200000703334808, -0.018200000748038292, 0.03779999911785126, -0.014800000004470348, 0.05869999900460243, 0.1891999989748001, -0.03229999914765358, -0.04500000178813934, 0.28369998931884766, 0.01889999955892563, -0.007600000128149986, -0.03269999846816063, -0.043699998408555984, 0.08910000324249268, 0.011599999852478504, -0.11810000240802765, -0.059700001031160355, -0.030300000682473183, 0.09179999679327011, -0.034299999475479126, -0.05570000037550926, -9.999999747378752e-05, -0.08940000087022781, 0.02459999918937683, -0.07919999957084656, 0.27149999141693115, -0.010599999688565731, -0.026499999687075615, -0.0333000011742115, 0.02630000002682209, 0.0892999991774559, 0.004100000020116568, -0.16050000488758087, -0.041099999099969864, -0.08489999920129776, 0.05559999868273735, 0.28999999165534973, 0.04560000076889992, 0.024399999529123306, 0.04670000076293945, -0.003599999938160181, -0.01769999973475933, -0.3230000138282776, 0.3682999908924103, -0.041999999433755875, 0.009499999694526196], [-0.12720000743865967, 0.1379999965429306, 0.05640000104904175, -0.14730000495910645, -0.11289999634027481, 0.19140000641345978, -0.188400000333786, -0.10610000044107437, -0.22529999911785126, 0.061799999326467514, -0.017999999225139618, -0.08209999650716782, 0.09549999982118607, -0.15150000154972076, 0.04610000178217888, 0.05260000005364418, -0.035599999129772186, 0.09560000151395798, 0.08659999817609787, -0.18060000240802765, -0.023900000378489494, 0.12150000035762787, 0.03240000084042549, -0.07569999992847443, -0.1428000032901764, -0.11249999701976776, 0.11680000275373459, -0.2827000021934509, 0.10509999841451645, -0.0843999981880188, -0.026799999177455902, 0.17810000479221344, -0.09870000183582306, 0.09459999948740005, -0.18330000340938568, -0.09070000052452087, -0.27250000834465027, -0.011699999682605267, 0.04039999842643738, -0.09019999951124191, -0.1251000016927719, 0.009600000455975533, 0.13130000233650208, -0.08190000057220459, 0.12790000438690186, -0.08020000159740448, -0.09390000253915787, -0.08030000329017639, 0.1648000031709671, -0.11789999902248383, 0.1647000014781952, 0.09300000220537186, -0.09920000284910202, -0.03480000048875809, 0.09839999675750732, 0.10369999706745148, 0.03449999913573265, 0.07540000230073929, 0.004600000102072954, -0.14000000059604645, -0.16930000483989716, -0.04560000076889992, -0.2199999988079071, -0.24279999732971191], [0.1298999935388565, -0.061500001698732376, -0.1459999978542328, 0.10660000145435333, -0.058800000697374344, 0.051500000059604645, 0.027000000700354576, -0.12729999423027039, 0.09130000323057175, 0.0892999991774559, 0.03909999877214432, -0.07750000059604645, -0.09939999878406525, 0.008299999870359898, 0.03669999912381172, -0.15360000729560852, -0.08330000191926956, -0.23960000276565552, 0.04670000076293945, -0.0005000000237487257, -0.047600001096725464, 0.10010000318288803, -0.11129999905824661, 0.039400000125169754, 0.1200999990105629, 0.040800001472234726, 0.03370000049471855, 0.14059999585151672, -0.10010000318288803, 0.025100000202655792, 0.12870000302791595, 0.10750000178813934, 0.16830000281333923, -0.1729000061750412, 0.2037000060081482, -0.18199999630451202, -0.250900000333786, -0.20659999549388885, 0.22200000286102295, -0.257099986076355, -0.08340000361204147, -0.23160000145435333, -0.08380000293254852, 0.14300000667572021, 0.10429999977350235, 0.026599999517202377, 0.10670000314712524, -0.00989999994635582, -0.0015999999595806003, -0.19949999451637268, 0.08869999647140503, 0.06759999692440033, -0.15459999442100525, -0.006800000090152025, -0.025699999183416367, -0.02979999966919422, 0.17870000004768372, -0.09200000017881393, -0.0551999993622303, 0.11739999800920486, -0.1518000066280365, -0.2533999979496002, -0.0778999999165535, 0.055799998342990875], [0.11490000039339066, 0.10010000318288803, 0.025499999523162842, 0.08410000056028366, -0.22619999945163727, 0.06679999828338623, -0.2029999941587448, -0.12300000339746475, -0.056699998676776886, -0.19550000131130219, -0.11659999936819077, -0.1729000061750412, 0.11840000003576279, 0.011099999770522118, 0.1817999929189682, -0.15870000422000885, -0.27790001034736633, 0.13189999759197235, 0.2021999955177307, -0.2289000004529953, 0.027000000700354576, -0.14869999885559082, -0.05990000069141388, 0.023600000888109207, 0.056299999356269836, 0.2721000015735626, 0.00559999980032444, 0.11240000277757645, 0.027899999171495438, 0.262800008058548, 0.05000000074505806, -0.06400000303983688, -0.0333000011742115, -0.07530000060796738, -0.0024999999441206455, -0.026499999687075615, 0.12389999628067017, -0.053700000047683716, -0.03480000048875809, 0.06610000133514404, 0.015399999916553497, 0.04600000008940697, 0.014600000344216824, 0.008500000461935997, 0.014000000432133675, -0.1665000021457672, 0.17900000512599945, 0.12460000067949295, -0.2976999878883362, -0.010099999606609344, 0.11259999871253967, 0.15549999475479126, 0.01810000091791153, -0.021900000050663948, 0.08240000158548355, 0.004100000020116568, -0.06960000097751617, 0.20430000126361847, 0.024299999698996544, -0.0803999975323677, -0.006800000090152025, 0.0430000014603138, 0.14030000567436218, -0.026599999517202377], [-0.15710000693798065, -0.06629999727010727, 0.11219999939203262, -0.1826999932527542, 0.09459999948740005, 0.16609999537467957, 0.060499999672174454, 0.009600000455975533, -0.23019999265670776, -0.3140999972820282, -0.06970000267028809, 0.125900000333786, -0.17229999601840973, -0.04569999873638153, 0.014100000262260437, -0.026900000870227814, -0.0044999998062849045, -0.12399999797344208, 0.03759999945759773, 0.1550000011920929, 0.04439999908208847, 0.033900000154972076, -0.17260000109672546, 0.093299999833107, -0.08940000087022781, -0.07670000195503235, -0.04410000145435333, 0.1266999989748001, 0.09350000321865082, 0.06440000236034393, -0.053700000047683716, 0.033799998462200165, -0.14149999618530273, -0.00559999980032444, 0.1738000065088272, 0.21539999544620514, 0.018400000408291817, -0.32839998602867126, -0.11550000309944153, 0.1378999948501587, -0.11479999870061874, -0.05079999938607216, 0.09669999778270721, 0.1898999959230423, 0.09929999709129333, -0.1704999953508377, 0.06589999794960022, 0.05260000005364418, 0.14079999923706055, 0.006599999964237213, -0.02459999918937683, 0.06759999692440033, 0.07119999825954437, -0.24959999322891235, -0.20110000669956207, -0.07720000296831131, -0.10289999842643738, 0.08569999784231186, 0.09570000320672989, 0.1264999955892563, -0.020600000396370888, -0.12150000035762787, -0.02019999921321869, -0.0803999975323677], [0.17749999463558197, -0.17389999330043793, 0.021299999207258224, 0.29280000925064087, -0.014499999582767487, 0.24279999732971191, 0.10189999639987946, 0.12960000336170197, -0.057500001043081284, -0.03669999912381172, 0.07590000331401825, -0.019600000232458115, 0.17470000684261322, -0.19949999451637268, 0.13510000705718994, -0.0026000000070780516, -0.09269999712705612, 0.02199999988079071, 0.004800000227987766, 0.25529998540878296, -0.06499999761581421, 0.03280000016093254, -0.11949999630451202, -0.16110000014305115, -0.094200000166893, -0.10050000250339508, -0.034299999475479126, 0.0010999999940395355, -0.16850000619888306, -0.20430000126361847, -0.16329999268054962, -0.06800000369548798, 0.15790000557899475, -0.04899999871850014, -0.07919999957084656, 0.06069999933242798, -0.009100000374019146, 0.08389999717473984, 0.03620000183582306, 0.011599999852478504, -0.1071000024676323, 0.07819999754428864, 0.15119999647140503, 0.10400000214576721, 0.1251000016927719, -0.07890000194311142, -0.19519999623298645, -0.1005999967455864, -0.2337000072002411, -0.12060000002384186, -0.039000000804662704, -0.0934000015258789, -0.16419999301433563, -0.11050000041723251, 0.09049999713897705, -0.08060000091791153, 0.033900000154972076, 0.2793999910354614, 0.0406000018119812, 0.094200000166893, 0.17389999330043793, 0.059700001031160355, -0.023099999874830246, 0.01979999989271164], [-0.0835999995470047, 0.13750000298023224, -0.033799998462200165, -0.05299999937415123, 0.15379999577999115, 0.06809999793767929, 0.005100000184029341, -0.07760000228881836, -0.09139999747276306, -0.0272000003606081, -0.09009999781847, -0.12189999967813492, -0.20739999413490295, 0.09049999713897705, 0.0934000015258789, 0.14180000126361847, 0.10360000282526016, 0.11949999630451202, 0.03440000116825104, 0.0052999998442828655, -0.01899999938905239, 0.03189999982714653, -0.03610000014305115, 0.1860000044107437, -0.164000004529953, -0.0575999990105629, 0.17219999432563782, 0.19550000131130219, -0.0877000018954277, -0.017500000074505806, -0.0421999990940094, -0.24050000309944153, 0.026100000366568565, -0.18940000236034393, 0.04320000112056732, 0.09619999676942825, -0.07680000364780426, 0.09950000047683716, -0.005799999926239252, -0.04479999840259552, -0.08089999854564667, 0.20550000667572021, -0.0812000036239624, -0.1444000005722046, 0.2199999988079071, 0.08089999854564667, 0.05119999870657921, -0.09300000220537186, -0.30820000171661377, 0.1873999983072281, -0.10740000009536743, -0.1331000030040741, 0.03999999910593033, -0.18790000677108765, 0.20170000195503235, -0.027799999341368675, 0.17569999396800995, -0.14820000529289246, -0.16699999570846558, -0.1395999938249588, -0.09109999984502792, -0.1745000034570694, -0.08560000360012054, -0.050200000405311584], [-0.14810000360012054, 0.008899999782443047, -0.026599999517202377, -0.28949999809265137, 0.20200000703334808, -0.029200000688433647, 0.08500000089406967, 0.009100000374019146, -0.09619999676942825, 0.05209999904036522, 0.12530000507831573, -0.011300000362098217, 0.012299999594688416, -0.05380000174045563, -0.004800000227987766, -0.1281999945640564, -0.09369999915361404, 0.10809999704360962, -0.1995999962091446, -0.1746000051498413, 0.1607999950647354, -0.033799998462200165, -0.06539999693632126, -0.06939999759197235, -0.07039999961853027, 0.04960000142455101, -0.15410000085830688, 0.10610000044107437, -0.0925000011920929, -0.1776999980211258, -0.1096000000834465, 0.066600002348423, 0.13899999856948853, -0.03579999879002571, -0.13210000097751617, 0.13699999451637268, 0.04360000044107437, -0.14399999380111694, 0.2071000039577484, -0.26669999957084656, 0.2574999928474426, 0.09070000052452087, -0.07599999755620956, 0.01600000075995922, -0.13600000739097595, -0.08190000057220459, -0.055399999022483826, 0.3163999915122986, -0.18709999322891235, -0.13989999890327454, -0.06069999933242798, 0.11100000143051147, 0.10440000146627426, -0.08489999920129776, 0.09059999883174896, 0.05079999938607216, 0.08879999816417694, 0.026499999687075615, 0.13670000433921814, 0.030400000512599945, -0.05079999938607216, 0.09449999779462814, -0.15639999508857727, 0.07259999960660934], [-0.10419999808073044, 0.03269999846816063, -0.13740000128746033, -0.0681999996304512, 0.061900001019239426, 0.19439999759197235, -0.08470000326633453, 0.24889999628067017, -0.0746999979019165, 0.04560000076889992, 0.0003000000142492354, -0.13989999890327454, -0.10170000046491623, -0.09799999743700027, -0.12250000238418579, 0.06939999759197235, 0.05620000138878822, 0.06790000200271606, -0.11320000141859055, -0.04439999908208847, -0.11259999871253967, 0.13830000162124634, -0.0917000025510788, -0.13490000367164612, 0.11209999769926071, 0.043699998408555984, -0.09109999984502792, -0.016899999231100082, 0.028200000524520874, 0.002199999988079071, 0.2037000060081482, -0.01209999993443489, -0.17020000517368317, 0.021700000390410423, -0.009100000374019146, 0.17900000512599945, -0.05490000173449516, 0.1517000049352646, -0.06629999727010727, -0.1907999962568283, -0.15060000121593475, -0.22460000216960907, -0.17890000343322754, 0.1671999990940094, -0.08150000125169754, -0.04780000075697899, 0.1354999989271164, -0.02590000070631504, -0.08649999648332596, -0.032999999821186066, -0.19840000569820404, 0.018699999898672104, 0.10010000318288803, 0.21690000593662262, 0.08569999784231186, -0.29589998722076416, 0.05719999969005585, 0.20080000162124634, -0.15029999613761902, -0.0203000009059906, -0.07199999690055847, 0.09200000017881393, 0.2199999988079071, -0.14830000698566437], [0.06769999861717224, 0.23260000348091125, 0.054999999701976776, 0.11420000344514847, 0.16740000247955322, 0.07329999655485153, -0.10719999670982361, -0.1468999981880188, -0.019300000742077827, -0.07020000368356705, -0.10599999874830246, -0.06459999829530716, 0.025800000876188278, 0.026900000870227814, 0.16060000658035278, 0.0035000001080334187, 0.02329999953508377, -0.10899999737739563, -0.06599999964237213, 0.002099999925121665, 0.13600000739097595, 0.053300000727176666, 0.08739999681711197, -0.050700001418590546, 0.005900000222027302, -0.058400001376867294, -0.10369999706745148, -0.007899999618530273, 0.03200000151991844, 0.010099999606609344, -0.09139999747276306, 0.30239999294281006, -0.016599999740719795, -0.2632000148296356, -0.18780000507831573, -0.04100000113248825, 0.05079999938607216, 0.07360000163316727, -0.019600000232458115, 0.03759999945759773, 0.1437000036239624, -0.08429999649524689, 0.031199999153614044, 0.18240000307559967, 0.0763000026345253, -0.15389999747276306, -0.15700000524520874, -0.03709999844431877, -0.12269999831914902, -0.0729999989271164, -0.38339999318122864, -0.09210000187158585, -0.008899999782443047, 0.21410000324249268, -0.15839999914169312, 0.03139999881386757, -0.2554999887943268, -0.22789999842643738, -0.02329999953508377, -0.08699999749660492, -0.026000000536441803, -0.18469999730587006, 0.0625, -0.04039999842643738], [-0.1388999968767166, -0.14740000665187836, 0.17239999771118164, -0.07940000295639038, 0.0957999974489212, 0.006200000178068876, 0.12359999865293503, 0.027000000700354576, 0.1460999995470047, -0.09269999712705612, -0.011900000274181366, 0.08410000056028366, 0.024700000882148743, -0.027699999511241913, 0.10360000282526016, 0.24690000712871552, 0.14110000431537628, 0.2011999934911728, 0.1940000057220459, -0.0982000008225441, -0.013899999670684338, -0.053599998354911804, 0.05000000074505806, -0.3075999915599823, 0.11429999768733978, 0.10980000346899033, 0.033399999141693115, 0.10400000214576721, -0.11349999904632568, 0.07410000264644623, -0.22840000689029694, 0.1451999992132187, 0.012799999676644802, -0.39989998936653137, 0.0044999998062849045, 0.05040000006556511, -0.04580000042915344, -0.07750000059604645, 0.030300000682473183, -0.07349999994039536, -0.03929999843239784, -0.09220000356435776, 0.18490000069141388, -0.2517000138759613, 0.06589999794960022, 0.015300000086426735, 0.08190000057220459, 0.060499999672174454, 0.20229999721050262, 0.021199999377131462, 0.04580000042915344, 0.05990000069141388, -0.03020000085234642, 0.1526000052690506, 0.06790000200271606, -0.04019999876618385, 0.012799999676644802, 0.09799999743700027, -0.18359999358654022, 0.0746999979019165, 0.0031999999191612005, -0.026399999856948853, 0.1145000010728836, 0.10490000247955322], [-0.17229999601840973, 0.11569999903440475, 0.06449999660253525, -0.050599999725818634, -0.0925000011920929, 0.12950000166893005, 0.04529999941587448, 0.050200000405311584, -0.006200000178068876, -0.10199999809265137, 0.0697999969124794, 0.0017000000225380063, -0.05959999933838844, -0.2281000018119812, -0.010999999940395355, -0.10920000076293945, -0.20000000298023224, 0.07429999858140945, -0.05779999867081642, 0.1446000039577484, 0.07680000364780426, -0.14980000257492065, 0.03500000014901161, -0.11760000139474869, -0.13860000669956207, 0.1444000005722046, 0.1234000027179718, -0.0006000000284984708, 0.038600001484155655, -0.03629999980330467, -0.08100000023841858, -0.10899999737739563, 0.12479999661445618, 0.07000000029802322, 0.0017999999690800905, 0.09700000286102295, -0.18930000066757202, 0.04540000110864639, -0.2134999930858612, -0.02710000053048134, 0.0210999995470047, -0.09910000115633011, -0.2046000063419342, 0.08869999647140503, -0.009999999776482582, 0.17720000445842743, -0.21160000562667847, 0.06769999861717224, -0.04619999974966049, 0.24950000643730164, 0.17170000076293945, 0.08139999955892563, -0.2393999993801117, 0.1987999975681305, -0.13930000364780426, -0.009700000286102295, -0.1046999990940094, -0.11909999698400497, -0.045499999076128006, -0.05939999967813492, -0.17970000207424164, -0.13030000030994415, 0.09109999984502792, 0.29589998722076416], [-0.0031999999191612005, 0.052799999713897705, -0.003599999938160181, 0.10459999740123749, -0.2540000081062317, 0.07829999923706055, -0.058400001376867294, -0.030400000512599945, 0.1160999983549118, 0.11800000071525574, -0.03849999979138374, 0.15039999783039093, 0.0997999981045723, 0.11959999799728394, 0.12280000001192093, -0.26809999346733093, 0.13590000569820404, 0.21439999341964722, -0.07760000228881836, 0.16850000619888306, 0.00139999995008111, 0.1264999955892563, -0.1160999983549118, 0.16189999878406525, -0.09179999679327011, 0.1469999998807907, -0.1704999953508377, -0.004900000058114529, -0.008899999782443047, -0.12250000238418579, -0.007699999958276749, 0.15399999916553497, 0.00570000009611249, -0.04309999942779541, 0.1412000060081482, 0.18279999494552612, 0.05180000141263008, 0.11219999939203262, 0.05959999933838844, 0.013700000010430813, -0.065700002014637, 0.3142000138759613, -0.13220000267028809, 0.03099999949336052, 0.044199999421834946, -0.20440000295639038, -0.008700000122189522, 0.121799997985363, 0.31529998779296875, 0.11840000003576279, -0.09099999815225601, 0.09629999846220016, 0.054999999701976776, 0.13760000467300415, 0.07079999893903732, 0.014299999922513962, 0.08590000122785568, 0.09179999679327011, -0.17630000412464142, -0.010300000198185444, -0.07829999923706055, -0.14550000429153442, -0.07289999723434448, 0.061799999326467514], [-0.061900001019239426, -0.0032999999821186066, 0.10790000110864639, -0.053599998354911804, -0.164000004529953, -0.026900000870227814, -0.08209999650716782, -0.03020000085234642, 0.06620000302791595, -0.06279999762773514, 0.08730000257492065, -0.09600000083446503, 0.15289999544620514, 0.22089999914169312, -0.09489999711513519, 0.19169999659061432, 0.21950000524520874, 0.1290999948978424, -0.012799999676644802, -0.06210000067949295, 0.26919999718666077, -0.06909999996423721, -0.2379000037908554, -0.04670000076293945, -0.1736000031232834, 0.0746999979019165, 0.1445000022649765, 0.14499999582767487, 0.15649999678134918, -0.22179999947547913, -0.04969999939203262, -0.029200000688433647, 0.05990000069141388, -0.0608999989926815, -0.0560000017285347, 0.04910000041127205, 0.12430000305175781, 0.10909999907016754, 0.08540000021457672, 0.028599999845027924, -0.1444000005722046, -0.15189999341964722, -0.23409999907016754, 0.18080000579357147, -0.0439999997615814</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>[[[0.09279999881982803, 0.004800000227987766, 0.08429999649524689, 0.05169999971985817, 0.05220000073313713, -0.1882999986410141, -0.04520000144839287, 0.06270000338554382, 0.05570000037550926, 0.02459999918937683, -0.094200000166893, -0.042100001126527786, 0.020099999383091927, 0.11100000143051147, -0.02500000037252903, -0.05810000002384186, -0.040300000458955765, -0.07150000333786011, -0.05119999870657921, -0.006599999964237213, -0.09839999675750732, -0.10859999805688858, -0.12999999523162842, 0.12080000340938568, 0.11620000004768372, -0.05950000137090683, 0.08659999817609787, -0.060499999672174454, 0.20350000262260437, -0.07020000368356705, -0.07010000199079514, 0.05590000003576279, -0.05719999969005585, 0.0877000018954277, 0.03669999912381172, -0.06199999898672104, -0.0737999975681305, -0.03790000081062317, -0.05889999866485596, -0.06390000134706497, 0.07289999723434448, -0.05689999833703041, -0.08649999648332596, -0.024900000542402267, 0.11330000311136246, -0.09619999676942825, 0.05559999868273735, -0.0421999990940094, -0.16920000314712524, 0.0640999972820282, -0.10700000077486038, 0.08619999885559082, 0.034699998795986176, 0.022099999710917473, 0.08489999920129776, -0.03539999946951866, 0.09139999747276306, -0.08150000125169754, 0.06710000336170197, 0.0885000005364418, -0.09189999848604202, 0.04830000177025795, 0.04879999905824661, -0.09610000252723694], [-0.10369999706745148, 0.11339999735355377, -0.047600001096725464, -0.04879999905824661, -0.06069999933242798, -0.04580000042915344, 0.17180000245571136, -0.047200001776218414, -0.07859999686479568, 0.0997999981045723, 0.13510000705718994, 0.05719999969005585, 0.10700000077486038, 0.04490000009536743, -0.1581999957561493, 0.05810000002384186, -0.08889999985694885, 0.08460000157356262, 0.08129999786615372, 0.066600002348423, 0.1200999990105629, 0.0714000016450882, 0.21170000731945038, -0.10740000009536743, -0.14830000698566437, 0.03819999843835831, 0.03539999946951866, -0.057500001043081284, -0.026799999177455902, -0.12620000541210175, 0.10580000281333923, -0.08919999748468399, 0.15189999341964722, -0.13490000367164612, -0.07930000126361847, 0.0625, 0.043800000101327896, 0.06449999660253525, 0.053199999034404755, 0.09849999845027924, -0.06889999657869339, -0.01600000075995922, 0.07859999686479568, 0.0674000009894371, -0.09769999980926514, 0.03819999843835831, -0.06300000101327896, 0.017400000244379044, 0.02250000089406967, -0.0868000015616417, 0.08399999886751175, -0.05570000037550926, -0.1242000013589859, -0.06459999829530716, 0.001500000013038516, 0.08900000154972076, -0.09640000015497208, 0.11680000275373459, -0.06319999694824219, -0.10599999874830246, 0.0738999992609024, -0.11640000343322754, -0.010200000368058681, -0.03220000118017197]], [[-0.029500000178813934, 0.11860000342130661, -0.2531999945640564, 0.11479999870061874, -0.00570000009611249, -0.30970001220703125, 0.2777999937534332, 0.027899999171495438, -0.3208000063896179, -0.22509999573230743, 0.1379999965429306, 0.14010000228881836, -0.19850000739097595, -0.07129999995231628, 0.02449999935925007, -0.15279999375343323, -0.008299999870359898, -0.0032999999821186066, 0.15919999778270721, 0.19140000641345978, 0.08839999884366989, 0.1151999980211258, 0.16619999706745148, 0.28290000557899475, 0.057999998331069946, -0.1428000032901764, 0.03590000048279762, -0.24629999697208405, 0.12800000607967377, 0.04450000077486038, -0.17550000548362732, 0.15639999508857727, 0.19349999725818634, -0.1005999967455864, -0.012199999764561653, -0.05550000071525574, -0.13220000267028809, 0.003800000064074993, -0.12919999659061432, 0.007000000216066837, 0.1615000069141388, 0.04879999905824661, -0.24169999361038208, -0.3368000090122223, -0.09070000052452087, -0.17659999430179596, 0.1307000070810318, -0.3637999892234802, -0.10580000281333923, -0.08579999953508377, 0.12479999661445618, -0.2700999975204468, 0.3027999997138977, 0.11779999732971191, -0.08370000123977661, -0.13860000669956207, 0.1492999941110611, -0.0778999999165535, -0.01600000075995922, 0.42080000042915344, 0.11219999939203262, 0.056699998676776886, 0.2727000117301941, -0.15070000290870667], [-0.14880000054836273, 0.0024999999441206455, 0.02979999966919422, -0.017500000074505806, -0.08879999816417694, -0.1476999968290329, 0.07159999758005142, 0.1039000004529953, -0.0746999979019165, -0.03280000016093254, 0.12700000405311584, -0.0471000000834465, 0.07349999994039536, -0.16290000081062317, 0.3276999890804291, 0.04280000180006027, 0.034299999475479126, -0.014700000174343586, -0.10260000079870224, 0.07280000299215317, 0.038100000470876694, 0.02280000038444996, -0.11990000307559967, 0.07909999787807465, 0.11890000104904175, -0.18700000643730164, -0.003700000001117587, -0.16019999980926514, -0.10339999943971634, 0.028200000524520874, -0.07930000126361847, -0.14489999413490295, 0.09549999982118607, 0.13199999928474426, -0.05169999971985817, -0.2637999951839447, 0.3337000012397766, -0.15230000019073486, 0.10719999670982361, 0.07720000296831131, 0.10620000213384628, -0.1876000016927719, -0.093299999833107, 0.11410000175237656, 0.10140000283718109, 0.046799998730421066, -0.14309999346733093, -0.08179999887943268, -0.020600000396370888, 0.01899999938905239, 0.0210999995470047, 0.3154999911785126, 0.05860000103712082, 0.07169999927282333, 0.26809999346733093, -0.004000000189989805, -0.1298000067472458, 0.09489999711513519, -0.22360000014305115, -0.019500000402331352, -0.03779999911785126, -0.1703999936580658, 0.02669999934732914, -0.10769999772310257], [0.2337999939918518, 0.01769999973475933, -0.044599998742341995, 0.16060000658035278, -0.03999999910593033, -0.23499999940395355, 0.17880000174045563, 0.05550000071525574, -0.07970000058412552, -0.16089999675750732, 0.19670000672340393, 0.21410000324249268, -0.27320000529289246, 0.025499999523162842, -0.017400000244379044, -0.17059999704360962, 0.2971999943256378, -0.14720000326633453, -0.22200000286102295, -0.11779999732971191, -0.1979999989271164, -0.4000000059604645, 0.06549999862909317, 0.08429999649524689, 0.032099999487400055, -0.17739999294281006, 0.16590000689029694, -0.11940000206232071, 0.09279999881982803, -0.0012000000569969416, -0.125, 0.13449999690055847, 0.25440001487731934, 0.0052999998442828655, -0.01899999938905239, 0.004600000102072954, 0.07720000296831131, 0.10849999636411667, -0.052400000393390656, -0.015200000256299973, -0.033799998462200165, -0.14259999990463257, 0.08330000191926956, -0.05009999871253967, -0.0024999999441206455, -0.3447999954223633, 0.1388999968767166, 0.09640000015497208, -0.16539999842643738, 0.16019999980926514, 0.17839999496936798, -0.26649999618530273, 0.0738999992609024, 0.13750000298023224, -0.08240000158548355, -0.06350000202655792, -0.059300001710653305, 0.06719999760389328, -0.16339999437332153, -0.002300000051036477, -0.15729999542236328, -0.08340000361204147, -0.04270000010728836, -0.3003000020980835], [0.17170000076293945, 0.007600000128149986, 0.19709999859333038, -0.09809999912977219, -0.06270000338554382, -0.03880000114440918, -0.061799999326467514, 0.06400000303983688, -0.05260000005364418, -0.054099999368190765, 0.023000000044703484, -0.066600002348423, -0.10400000214576721, -0.10509999841451645, -0.12300000339746475, 0.09700000286102295, -0.07440000027418137, -0.16930000483989716, -0.01860000006854534, -0.11580000072717667, 0.12950000166893005, -0.04769999906420708, 0.12960000336170197, 0.022600000724196434, 0.07500000298023224, -0.09300000220537186, 0.18119999766349792, 0.05290000140666962, -0.026100000366568565, -0.019099999219179153, 0.01979999989271164, 0.2964000105857849, -0.1923999935388565, -0.018799999728798866, 0.16030000150203705, -0.08150000125169754, 0.08500000089406967, 0.11420000344514847, 0.02979999966919422, -0.03849999979138374, -0.10000000149011612, 0.357699990272522, -0.131400004029274, 0.12269999831914902, -0.07100000232458115, -0.010999999940395355, -0.13519999384880066, -0.06809999793767929, -0.007600000128149986, -0.11580000072717667, 0.09269999712705612, -0.09880000352859497, 0.15539999306201935, -0.02250000089406967, -0.05739999935030937, -0.14740000665187836, 0.14640000462532043, 0.31139999628067017, -0.027300000190734863, -0.0885000005364418, 0.042100001126527786, -0.27140000462532043, -0.031700000166893005, 0.3695000112056732], [0.021400000900030136, 0.14259999990463257, 0.27799999713897705, -0.00860000029206276, -0.12770000100135803, 0.15809999406337738, 0.01850000023841858, -0.07159999758005142, 0.009600000455975533, 0.029999999329447746, -0.21070000529289246, -0.038100000470876694, -0.17520000040531158, -0.0013000000035390258, -0.3257000148296356, -0.12389999628067017, 0.01889999955892563, -0.016499999910593033, -0.19480000436306, 0.1914999932050705, 0.09459999948740005, 0.3725999891757965, 0.0746999979019165, -0.03999999910593033, -0.07169999927282333, -0.0908999964594841, 0.0989999994635582, 0.12800000607967377, -0.020600000396370888, 0.1500999927520752, 0.12290000170469284, 0.0215000007301569, 0.13459999859333038, -0.2143000066280365, -0.066600002348423, -0.18639999628067017, 0.07349999994039536, -0.09229999780654907, 0.1005999967455864, 0.06809999793767929, -0.296099990606308, 0.0010999999940395355, -0.14669999480247498, -0.09139999747276306, -0.07829999923706055, -0.1615999937057495, -0.07890000194311142, 0.009600000455975533, -0.028599999845027924, 0.05119999870657921, 0.2087000012397766, -0.0210999995470047, -0.007699999958276749, 0.08500000089406967, 0.020800000056624413, -0.07880000025033951, 0.057999998331069946, -0.02979999966919422, 0.01850000023841858, -0.0284000001847744, 0.14830000698566437, 0.3149000108242035, -0.06199999898672104, -0.07819999754428864], [-0.06870000064373016, -0.25679999589920044, -0.2782000005245209, -0.12790000438690186, -0.20569999516010284, -0.1882999986410141, -0.033399999141693115, -0.17180000245571136, -0.06040000170469284, 0.00279999990016222, -0.04050000011920929, -0.0625, -0.19850000739097595, -0.14169999957084656, -0.13199999928474426, 0.11940000206232071, 0.17679999768733978, 0.12700000405311584, 0.13429999351501465, -0.008999999612569809, -0.019099999219179153, 0.06260000169277191, -0.01140000019222498, -0.06920000165700912, -0.06120000034570694, -0.04690000042319298, -0.23180000483989716, 0.06700000166893005, 0.24490000307559967, 0.05090000107884407, -0.04190000146627426, 0.11259999871253967, 0.17000000178813934, 0.022600000724196434, 0.11129999905824661, -0.052000001072883606, 0.11309999972581863, 0.02459999918937683, -0.01730000041425228, 0.15719999372959137, -0.0071000000461936, -0.08269999921321869, 0.15770000219345093, 0.10209999978542328, 0.02199999988079071, 0.29840001463890076, -0.20730000734329224, 0.17059999704360962, -0.21709999442100525, 0.19679999351501465, -0.08699999749660492, 0.024800000712275505, -0.03350000083446503, 0.11379999667406082, 0.1679999977350235, 0.14720000326633453, 0.05640000104904175, 0.20280000567436218, 0.13289999961853027, 0.11829999834299088, 0.07559999823570251, -0.19300000369548798, -0.01940000057220459, -0.11330000311136246], [0.000699999975040555, 0.29980000853538513, -0.07900000363588333, -0.02800000086426735, -0.13840000331401825, -0.19679999351501465, -0.1071000024676323, -0.053700000047683716, 0.15230000019073486, -0.1890999972820282, -0.17880000174045563, -0.18880000710487366, 0.1784999966621399, 0.02759999968111515, -0.06610000133514404, 0.19949999451637268, -0.13609999418258667, -0.032999999821186066, -0.03779999911785126, -0.008299999870359898, -0.131400004029274, -0.11479999870061874, 0.005400000140070915, -0.022299999371170998, 0.10869999974966049, -0.04839999973773956, -0.17990000545978546, 0.11490000039339066, -0.2578999996185303, -0.1907999962568283, 0.0560000017285347, -0.14949999749660492, 0.15299999713897705, -0.06859999895095825, -0.059700001031160355, 0.06360000371932983, -0.07240000367164612, -0.21299999952316284, -0.1445000022649765, -0.13369999825954437, -0.33009999990463257, 0.09130000323057175, -0.03500000014901161, 0.01940000057220459, -0.2615000009536743, 0.03480000048875809, 0.012799999676644802, 0.030400000512599945, 0.218299999833107, 0.07109999656677246, -0.12409999966621399, 0.11469999700784683, -0.09640000015497208, -0.025499999523162842, -0.013899999670684338, -0.049800001084804535, -0.09070000052452087, 0.156700000166893, 0.22689999639987946, 0.08169999718666077, -0.0908999964594841, -0.07689999788999557, -0.08550000190734863, -0.04800000041723251], [-0.14180000126361847, 0.10050000250339508, 0.13750000298023224, -0.17149999737739563, -0.06469999998807907, -0.12210000306367874, 0.07090000063180923, 0.1378999948501587, 0.05000000074505806, 0.13819999992847443, 0.023600000888109207, 0.1143999993801117, 0.14509999752044678, -0.0012000000569969416, 0.03869999945163727, 0.013799999840557575, 0.004100000020116568, 0.1476999968290329, 0.0966000035405159, 0.12710000574588776, -0.18150000274181366, -0.09510000050067902, 0.23690000176429749, 0.21570000052452087, 0.08569999784231186, -0.30480000376701355, 0.2757999897003174, 0.21080000698566437, 0.015599999576807022, 0.09139999747276306, 0.10239999741315842, 0.09149999916553497, -0.1103999987244606, 0.11219999939203262, -0.10199999809265137, -0.1941000074148178, -0.03739999979734421, -0.08980000019073486, -0.014399999752640724, 0.04500000178813934, -0.08560000360012054, 0.04280000180006027, -0.04520000144839287, 0.3377000093460083, -0.05939999967813492, -0.2614000141620636, -0.1624000072479248, 0.13770000636577606, -0.03869999945163727, -0.2037000060081482, 0.16940000653266907, -0.3287999927997589, 0.04100000113248825, 0.1251000016927719, -0.03610000014305115, -0.1200999990105629, 0.0934000015258789, -0.06790000200271606, 0.14229999482631683, 0.22599999606609344, 0.1784999966621399, -0.19599999487400055, 0.2540999948978424, -0.19789999723434448], [-0.326200008392334, -0.14429999887943268, -0.025299999862909317, 0.30410000681877136, 0.20649999380111694, -0.3456000089645386, -0.08950000256299973, 0.05649999901652336, -0.0722000002861023, -0.04830000177025795, 0.09880000352859497, 0.2222999930381775, -0.08269999921321869, -0.04390000179409981, -0.11879999935626984, -0.06120000034570694, -0.08799999952316284, -0.14180000126361847, 0.19589999318122864, -0.023800000548362732, 0.06939999759197235, 0.05860000103712082, 0.14329999685287476, 0.21979999542236328, -0.016300000250339508, -0.11339999735355377, 0.31200000643730164, -0.12070000171661377, 0.08569999784231186, -0.041200000792741776, -0.059700001031160355, 0.1842000037431717, 0.0544000007212162, -0.16380000114440918, -0.11140000075101852, -0.03709999844431877, 0.19200000166893005, -0.02449999935925007, -0.09759999811649323, 0.0575999990105629, -0.08079999685287476, 0.030799999833106995, -0.10379999876022339, 0.19509999454021454, 0.03189999982714653, -0.025299999862909317, -0.040699999779462814, -0.05460000038146973, -0.010499999858438969, 0.016100000590085983, -0.12710000574588776, -0.03869999945163727, -0.052000001072883606, -0.0421999990940094, 0.2281000018119812, -0.007799999788403511, 0.06920000165700912, 0.01940000057220459, -0.010200000368058681, 0.03750000149011612, -0.2619999945163727, 0.30230000615119934, -0.0763000026345253, -0.07620000094175339], [-0.11089999973773956, 0.1266999989748001, 0.07649999856948853, -0.15489999949932098, -0.13019999861717224, 0.23649999499320984, -0.16429999470710754, -0.15629999339580536, -0.19349999725818634, 0.03689999878406525, -0.05939999967813492, -0.08720000088214874, 0.13510000705718994, -0.15060000121593475, 0.04520000144839287, -0.0071000000461936, -0.04659999907016754, 0.11890000104904175, 0.07029999792575836, -0.218299999833107, -0.06800000369548798, 0.08190000057220459, -0.00419999985024333, -0.01979999989271164, -0.14579999446868896, -0.13040000200271606, 0.11550000309944153, -0.26429998874664307, 0.08780000358819962, -0.11779999732971191, -0.05730000138282776, 0.16329999268054962, -0.10100000351667404, 0.10440000146627426, -0.1306000053882599, -0.08340000361204147, -0.31209999322891235, 0.029200000688433647, 0.04479999840259552, -0.09359999746084213, -0.09989999979734421, 0.005799999926239252, 0.14499999582767487, -0.05490000173449516, 0.0892999991774559, -0.11010000109672546, -0.08020000159740448, -0.039500001817941666, 0.20440000295639038, -0.11060000211000443, 0.15440000593662262, 0.10130000114440918, -0.12479999661445618, -0.004000000189989805, 0.07519999891519547, 0.10769999772310257, -0.0019000000320374966, 0.0982000008225441, -0.010200000368058681, -0.17059999704360962, -0.15479999780654907, -0.048900000751018524, -0.20160000026226044, -0.23250000178813934], [0.1363999992609024, 0.019600000232458115, -0.06759999692440033, 0.000699999975040555, -0.09239999949932098, 0.12780000269412994, 0.022099999710917473, -0.1005999967455864, -0.028599999845027924, 0.11100000143051147, -0.0013000000035390258, -0.12759999930858612, -0.0142000000923872, -0.050999999046325684, 0.0738999992609024, -0.026399999856948853, -0.07429999858140945, -0.21140000224113464, 0.0868000015616417, -0.06310000270605087, 0.032499998807907104, 0.14079999923706055, -0.15330000221729279, -0.022600000724196434, 0.04879999905824661, 0.1428000032901764, -0.03610000014305115, 0.23759999871253967, -0.0632999986410141, 0.11129999905824661, 0.20550000667572021, 0.037700001150369644, 0.13809999823570251, -0.16019999980926514, 0.13009999692440033, -0.22450000047683716, -0.17839999496936798, -0.28139999508857727, 0.2599000036716461, -0.26100000739097595, -0.19210000336170197, -0.20149999856948853, -0.06159999966621399, 0.18330000340938568, 0.0917000025510788, 0.04809999838471413, 0.016599999740719795, 0.004999999888241291, 0.10010000318288803, -0.2498999983072281, 0.11869999766349792, 0.12229999899864197, -0.19120000302791595, -0.09149999916553497, 0.08179999887943268, 0.04540000110864639, 0.03700000047683716, -0.07999999821186066, -0.0035000001080334187, 0.2134000062942505, -0.10000000149011612, -0.19130000472068787, -0.14509999752044678, 0.17739999294281006], [0.15479999780654907, 0.020400000736117363, 0.06449999660253525, 0.04879999905824661, -0.267300009727478, 0.06159999966621399, -0.1923999935388565, -0.1469999998807907, -0.04129999876022339, -0.1981000006198883, -0.1054999977350235, -0.25429999828338623, 0.13539999723434448, -0.023600000888109207, 0.149399995803833, -0.16500000655651093, -0.3375000059604645, 0.1785999983549118, 0.20319999754428864, -0.14329999685287476, 0.019500000402331352, -0.18559999763965607, -0.0778999999165535, 0.03240000084042549, -0.011500000022351742, 0.25850000977516174, 0.038100000470876694, 0.08389999717473984, -0.008500000461935997, 0.27799999713897705, 0.06809999793767929, -0.07320000231266022, 0.015599999576807022, -0.0729999989271164, -0.05939999967813492, 0.015699999406933784, 0.08129999786615372, -0.09610000252723694, 0.04270000010728836, 0.11500000208616257, 0.05290000140666962, -0.006099999882280827, 0.0674000009894371, 0.08609999716281891, -0.05860000103712082, -0.18209999799728394, 0.18279999494552612, 0.15039999783039093, -0.28220000863075256, -0.08049999922513962, 0.11230000108480453, 0.09380000084638596, -0.0364999994635582, 0.00930000003427267, 0.09560000151395798, 0.052000001072883606, -0.09610000252723694, 0.25440001487731934, -0.03020000085234642, -0.11400000005960464, -0.05900000035762787, 0.0006000000284984708, 0.18479999899864197, -0.07169999927282333], [-0.13770000636577606, -0.09749999642372131, 0.09709999710321426, -0.1753000020980835, 0.10050000250339508, 0.0575999990105629, 0.11400000005960464, -0.05009999871253967, -0.18310000002384186, -0.3386000096797943, -0.09040000289678574, 0.13099999725818634, -0.15530000627040863, -0.03370000049471855, -0.012600000016391277, -0.07919999957084656, -0.016499999910593033, -0.13179999589920044, -0.011599999852478504, 0.13899999856948853, -0.02410000003874302, 0.01720000058412552, -0.16689999401569366, 0.2198999971151352, -0.06199999898672104, -0.13189999759197235, -0.022600000724196434, 0.1062999963760376, 0.09780000150203705, 0.05420000106096268, -0.10899999737739563, -0.009399999864399433, -0.12950000166893005, -0.03460000082850456, 0.2630999982357025, 0.2078000009059906, -0.03830000013113022, -0.21729999780654907, -0.11110000312328339, 0.15520000457763672, -0.07010000199079514, -0.07970000058412552, 0.10599999874830246, 0.1889999955892563, 0.048700001090765, -0.25529998540878296, 0.0966000035405159, 0.06780000030994415, 0.14219999313354492, 0.021800000220537186, -0.018799999728798866, 0.04500000178813934, 0.04019999876618385, -0.2078000009059906, -0.2312999963760376, -0.07890000194311142, -0.11309999972581863, 0.10320000350475311, 0.07119999825954437, 0.11739999800920486, -0.04050000011920929, -0.1444000005722046, 0.04129999876022339, -0.13099999725818634], [0.19670000672340393, -0.15919999778270721, 0.039000000804662704, 0.29429998993873596, -0.014999999664723873, 0.2522999942302704, 0.11969999969005585, 0.1014999970793724, -0.01360000018030405, -0.056699998676776886, 0.039400000125169754, -0.013000000268220901, 0.20180000364780426, -0.1964000016450882, 0.12700000405311584, -0.08269999921321869, -0.09769999980926514, 0.010400000028312206, -0.0215000007301569, 0.21449999511241913, -0.1193000003695488, 0.03009999915957451, -0.09839999675750732, -0.09809999912977219, -0.08250000327825546, -0.08829999715089798, -0.016899999231100082, 0.04349999874830246, -0.1688999980688095, -0.23649999499320984, -0.19689999520778656, -0.061799999326467514, 0.13580000400543213, -0.06459999829530716, -0.017000000923871994, 0.033399999141693115, -0.05249999836087227, 0.12999999523162842, 0.029999999329447746, -0.04430000111460686, -0.07810000330209732, 0.15440000593662262, 0.13910000026226044, 0.12269999831914902, 0.17800000309944153, -0.12790000438690186, -0.1647000014781952, -0.12759999930858612, -0.21279999613761902, -0.09189999848604202, -0.031599998474121094, -0.08950000256299973, -0.17149999737739563, -0.07609999924898148, 0.04690000042319298, -0.09989999979734421, 0.008100000210106373, 0.2831999957561493, 0.030700000002980232, 0.07999999821186066, 0.16249999403953552, 0.06960000097751617, 0.007000000216066837, 0.011699999682605267], [-0.12330000102519989, 0.14820000529289246, -0.06040000170469284, -0.013799999840557575, 0.18639999628067017, 0.06459999829530716, 0.00039999998989515007, -0.03590000048279762, -0.11500000208616257, -0.03150000050663948, -0.049800001084804535, -0.07729999721050262, -0.2572999894618988, 0.10019999742507935, 0.1005999967455864, 0.14489999413490295, 0.11060000211000443, 0.09470000118017197, 0.09870000183582306, 0.02419999986886978, 0.007300000172108412, 0.05700000002980232, -0.05609999969601631, 0.09260000288486481, -0.1590999960899353, -0.10010000318288803, 0.1656000018119812, 0.15209999680519104, -0.1128000020980835, 0.003000000026077032, -0.1266999989748001, -0.21969999372959137, 0.03449999913573265, -0.18209999799728394, -0.0019000000320374966, 0.12559999525547028, -0.029600000008940697, 0.10050000250339508, -0.023900000378489494, -0.00839999970048666, -0.04600000008940697, 0.2013999968767166, -0.08500000089406967, -0.20960000157356262, 0.2312999963760376, 0.14020000398159027, 0.05209999904036522, -0.07209999859333038, -0.37940001487731934, 0.19539999961853027, -0.1088000014424324, -0.12600000202655792, 0.08919999748468399, -0.2070000022649765, 0.14839999377727509, -0.009399999864399433, 0.22290000319480896, -0.19009999930858612, -0.13760000467300415, -0.15569999814033508, -0.08590000122785568, -0.16429999470710754, -0.11490000039339066, -0.08560000360012054], [-0.13760000467300415, -0.05939999967813492, -0.023399999365210533, -0.2761000096797943, 0.19040000438690186, 0.04089999943971634, 0.0763000026345253, -0.0348999984562397, -0.04619999974966049, 0.0658000037074089, 0.08079999685287476, -0.12210000306367874, 0.06310000270605087, 0.006399999838322401, -0.030400000512599945, -0.1776999980211258, -0.1477999985218048, 0.1459999978542328, -0.13850000500679016, -0.08730000257492065, 0.12160000205039978, -0.07590000331401825, -0.10719999670982361, -0.14990000426769257, -0.11460000276565552, 0.06260000169277191, -0.13300000131130219, 0.10920000076293945, -0.16680000722408295, -0.19629999995231628, -0.10559999942779541, 0.012299999594688416, 0.15710000693798065, -0.03680000081658363, -0.10570000112056732, 0.1931000053882599, -0.007300000172108412, -0.11050000041723251, 0.25929999351501465, -0.3172000050544739, 0.3578999936580658, 0.09539999812841415, -0.02979999966919422, 0.04259999841451645, -0.1071000024676323, -0.09210000187158585, -0.008100000210106373, 0.353300005197525, -0.1527000069618225, -0.06520000100135803, -0.03440000116825104, 0.09549999982118607, 0.09600000083446503, -0.03700000047683716, 0.20250000059604645, 0.11680000275373459, 0.08560000360012054, 0.018799999728798866, 0.12250000238418579, -0.043299999088048935, -0.1446000039577484, 0.09269999712705612, -0.11590000241994858, 0.07779999822378159], [-0.14399999380111694, 0.04540000110864639, -0.17339999973773956, -0.11320000141859055, 0.08179999887943268, 0.26030001044273376, -0.11349999904632568, 0.28519999980926514, -0.09860000014305115, 0.09610000252723694, 0.027799999341368675, -0.14149999618530273, -0.12160000205039978, -0.04089999943971634, -0.11710000038146973, 0.09059999883174896, 0.046300001442432404, 0.057999998331069946, -0.05209999904036522, 0.006300000008195639, -0.06920000165700912, 0.1768999993801117, -0.0794999971985817, -0.24480000138282776, 0.09019999951124191, 0.06689999997615814, -0.10000000149011612, -0.011500000022351742, -0.006399999838322401, -0.005200000014156103, 0.2159000039100647, -0.03280000016093254, -0.16419999301433563, -0.0032999999821186066, -0.045899998396635056, 0.19120000302791595, -0.0044999998062849045, 0.15530000627040863, -0.059300001710653305, -0.20669999718666077, -0.1454000025987625, -0.2011999934911728, -0.17630000412464142, 0.14949999749660492, -0.037700001150369644, -0.00570000009611249, 0.13269999623298645, -0.045899998396635056, -0.057999998331069946, -0.006399999838322401, -0.18469999730587006, 0.006899999920278788, 0.1339000016450882, 0.1867000013589859, 0.10989999771118164, -0.24160000681877136, 0.07079999893903732, 0.17749999463558197, -0.12120000272989273, -0.04039999842643738, -0.09920000284910202, 0.10350000113248825, 0.19529999792575836, -0.11500000208616257], [-0.0038999998942017555, 0.1745000034570694, -0.02419999986886978, 0.09009999781847, 0.11010000109672546, 0.3091999888420105, -0.20800000429153442, -0.26019999384880066, 0.0771000012755394, -0.10109999775886536, -0.21130000054836273, -0.16099999845027924, -0.017000000923871994, 0.07429999858140945, 0.26589998602867126, -0.061799999326467514, 0.010200000368058681, -0.0723000019788742, 0.050200000405311584, -0.0478999987244606, 0.0997999981045723, -0.05990000069141388, -0.014399999752640724, -0.2298000007867813, -0.019200000911951065, 0.03359999880194664, -0.19900000095367432, 0.12099999934434891, -0.16140000522136688, -0.04879999905824661, -0.04540000110864639, 0.2257000058889389, -0.027000000700354576, -0.16830000281333923, -0.15000000596046448, 0.035100001841783524, 0.008500000461935997, 0.1071000024676323, 0.029100000858306885, -0.06300000101327896, 0.11980000138282776, -0.05979999899864197, 0.09390000253915787, 0.2328999936580658, 0.09459999948740005, -0.08380000293254852, -0.14010000228881836, 0.08089999854564667, -0.027899999171495438, -0.041999999433755875, -0.44119998812675476, -0.0348999984562397, -0.06080000102519989, 0.3190999925136566, -0.10540000349283218, 0.15929999947547913, -0.32010000944137573, -0.27970001101493835, 0.03669999912381172, -0.2207999974489212, -0.1128000020980835, -0.1623000055551529, 0.021700000390410423, 0.09489999711513519], [-0.13670000433921814, -0.17319999635219574, 0.17990000545978546, -0.02850000001490116, 0.08100000023841858, 0.08269999921321869, 0.14110000431537628, -0.04529999941587448, 0.17820000648498535, -0.12319999933242798, -0.07020000368356705, 0.07580000162124634, 0.07370000332593918, -0.01209999993443489, 0.11069999635219574, 0.20890000462532043, 0.14869999885559082, 0.24560000002384186, 0.20170000195503235, -0.12970000505447388, -0.04830000177025795, -0.11209999769926071, -0.014999999664723873, -0.28529998660087585, 0.1080000028014183, 0.10369999706745148, 0.009200000204145908, 0.12380000203847885, -0.1656000018119812, 0.05559999868273735, -0.23149999976158142, 0.11659999936819077, 0.012000000104308128, -0.36320000886917114, 0.05730000138282776, 0.08449999988079071, -0.07900000363588333, -0.03269999846816063, 0.043699998408555984, -0.07720000296831131, -0.05310000106692314, -0.1185000017285347, 0.21060000360012054, -0.23819999396800995, 0.019700000062584877, 0.017000000923871994, 0.09210000187158585, 0.12690000236034393, 0.2524000108242035, 0.026100000366568565, 0.019200000911951065, 0.09600000083446503, -0.0544000007212162, 0.1800999939441681, 0.06809999793767929, -0.005799999926239252, -0.01269999984651804, 0.12080000340938568, -0.18649999797344208, 0.020099999383091927, 0.011599999852478504, -0.02710000053048134, 0.11749999970197678, 0.16099999845027924], [-0.15600000321865082, 0.10760000348091125, 0.08749999850988388, -0.08290000259876251, -0.11010000109672546, 0.16259999573230743, 0.04729999974370003, 0.0203000009059906, 0.020999999716877937, -0.12389999628067017, 0.03720000013709068, -0.006200000178068876, -0.05869999900460243, -0.24449999630451202, -0.003000000026077032, -0.14350000023841858, -0.1835000067949295, 0.08940000087022781, -0.08389999717473984, 0.07440000027418137, 0.049800001084804535, -0.17870000004768372, 0.012199999764561653, -0.07970000058412552, -0.13109999895095825, 0.1768999993801117, 0.120899997651577, 0.06599999964237213, 0.04309999942779541, -0.05380000174045563, -0.0632999986410141, -0.13050000369548798, 0.10019999742507935, 0.07670000195503235, 0.04520000144839287, 0.08389999717473984, -0.23010000586509705, 0.0494999997317791, -0.21070000529289246, -0.06560000032186508, -0.019899999722838402, -0.05510000139474869, -0.20659999549388885, 0.12160000205039978, -0.004600000102072954, 0.15199999511241913, -0.2071000039577484, 0.059700001031160355, -0.0035000001080334187, 0.24240000545978546, 0.16130000352859497, 0.12120000272989273, -0.2540999948978424, 0.2281000018119812, -0.14640000462532043, -0.014600000344216824, -0.1281999945640564, -0.11379999667406082, -0.04320000112056732, -0.06710000336170197, -0.15960000455379486, -0.11479999870061874, 0.09459999948740005, 0.3183000087738037], [-0.06369999796152115, -0.023399999365210533, -0.05900000035762787, 0.07419999688863754, -0.3109999895095825, 0.2612000107765198, -0.13850000500679016, -0.15219999849796295, 0.18569999933242798, 0.0835999995470047, -0.16529999673366547, 0.028200000524520874, 0.06759999692440033, 0.16019999980926514, 0.24369999766349792, -0.31060001254081726, 0.12449999898672104, 0.28040000796318054, 0.03280000016093254, 0.11720000207424164, -0.03970000147819519, 0.0005000000237487257, -0.2402999997138977, 0.043699998408555984, -0.11739999800920486, 0.24199999868869781, -0.2791999876499176, 0.12399999797344208, -0.15080000460147858, -0.18150000274181366, -0.011300000362098217, 0.09549999982118607, 0.006099999882280827, 0.06679999828338623, 0.15279999375343323, 0.25519999861717224, 0.006200000178068876, 0.1143999993801117, 0.09849999845027924, -0.011599999852478504, -0.06599999964237213, 0.3018999993801117, -0.05490000173449516, 0.0746999979019165, 0.061000000685453415, -0.1257999986410141, -0.011900000274181366, 0.24959999322891235, 0.42320001125335693, 0.12409999966621399, -0.19169999659061432, 0.15700000524520874, -0.01889999955892563, 0.2460000067949295, 0.193900004029274, 0.14249999821186066, 0.02160000056028366, 0.07670000195503235, -0.1436000019311905, -0.10899999737739563, -0.1542000025510788, -0.15940000116825104, -0.11720000207424164, 0.22949999570846558], [-0.039500001817941666, -0.06669999659061432, 0.1354999989271164, -0.08879999816417694, -0.17980000376701355, -0.04670000076293945, -0.14720000326633453, -0.0034000000450760126, 0.04039999842643738, -0.0674000009894371, 0.08579999953508377, -0.1876000016927719, 0.12120000272989273, 0.1793999969959259, -0.065700002014637, 0.24860000610351562, 0.2312999963760376, 0.14169999957084656, -0.008100000210106373, -0.06939999759197235, 0.31630000472068787, -0.11649999767541885, -0.2865000069141388, -0.08649999648332596, -0.16359999775886536, 0.07859999686479568, 0.12229999899864197, 0.14059999585151672, 0.19349999725818634, -0.19949999451637268, -0.03460000082850456, -0.01549999974668026, 0.03970000147819519, 0.004600000102072954, -0.1120000034570694, 0.05050000175833702, 0.12729999423027039, -0.06949999928474426, 0.08269999921321869, 0.04839999973773956, -0.18119999766349792, -0.2282000035047531, -0.2401999980211258, 0.1703999936580658, -0.06159999966621399, 0.049400001764297485, 0.0551999993622303, -0.2703999876976013, -0.03400000184774399, -0.246399998664855</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>[0.5515157110422664]</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>[0.1023739965125133]</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>[0.04547848085249262]</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>[0.21792038501028993]</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>[-1.5994487737470564]</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>[0.8507468006538839]</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>[0.5829489879232685]</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>[0.09580457195534048]</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>[-0.15795387911002057]</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>[0.2746215313346665]</t>
+        </is>
+      </c>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>[0.4425671266170915]</t>
+        </is>
+      </c>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>[0.1832546321080753]</t>
+        </is>
+      </c>
+      <c r="Q23" t="inlineStr">
+        <is>
+          <t>[-0.2963687570423996]</t>
+        </is>
+      </c>
+      <c r="R23" t="inlineStr">
+        <is>
+          <t>[0.13978190629400988]</t>
+        </is>
+      </c>
+      <c r="S23" t="inlineStr">
+        <is>
+          <t>[-0.12783662629670545]</t>
+        </is>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>[0.09503189732476411]</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>[-1.3324740314660102]</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>[0.22303846888292814]</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>[-0.45480530011901155]</t>
+        </is>
+      </c>
+      <c r="X23" t="inlineStr">
+        <is>
+          <t>[0.15240631039055783]</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>[-0.20778102798206444]</t>
+        </is>
+      </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>[0.09939217740983197]</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>[-1.9593573404579283]</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>[0.27227382057328264]</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>[-1.3690076766287063]</t>
+        </is>
+      </c>
+      <c r="AD23" t="inlineStr">
+        <is>
+          <t>[0.1985132994982657]</t>
+        </is>
+      </c>
+      <c r="AE23" t="inlineStr">
+        <is>
+          <t>[-1.2559885370432848]</t>
+        </is>
+      </c>
+      <c r="AF23" t="inlineStr">
+        <is>
+          <t>[0.24292050082566186]</t>
+        </is>
+      </c>
+      <c r="AG23" t="inlineStr">
+        <is>
+          <t>[-3.0777003098436593]</t>
+        </is>
+      </c>
+      <c r="AH23" t="inlineStr">
+        <is>
+          <t>[0.3035846186523147]</t>
+        </is>
+      </c>
+      <c r="AI23" t="inlineStr">
+        <is>
+          <t>[-1.7909755633816982]</t>
+        </is>
+      </c>
+      <c r="AJ23" t="inlineStr">
+        <is>
+          <t>[0.22871734046588288]</t>
+        </is>
+      </c>
+      <c r="AK23" t="inlineStr">
+        <is>
+          <t>[-1.1732454339489724]</t>
+        </is>
+      </c>
+      <c r="AL23" t="inlineStr">
+        <is>
+          <t>[0.23067408023167385]</t>
+        </is>
+      </c>
+      <c r="AM23" t="inlineStr">
+        <is>
+          <t>[-3.9262451009985977]</t>
+        </is>
+      </c>
+      <c r="AN23" t="inlineStr">
+        <is>
+          <t>[0.3783713370825727]</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>model_64_32_2</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>[64, 32]</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>[[[-0.05169999971985817, 0.011599999852478504, 0.05860000103712082, 0.015599999576807022, -0.0568000003695488, 0.0071000000461936, -0.04830000177025795, 0.012000000104308128, 0.012199999764561653, 0.0006000000284984708, -0.012400000356137753, 0.032099999487400055, 0.012500000186264515, -0.06700000166893005, -9.999999747378752e-05, 0.053700000047683716, -0.13729999959468842, 0.050999999046325684, -0.026900000870227814, 0.04170000180602074, -0.0071000000461936, 0.04320000112056732, 0.0003000000142492354, 0.015699999406933784, -0.0632999986410141, 0.04490000009536743, -0.0071000000461936, 0.08869999647140503, 0.030500000342726707, -0.001500000013038516, 0.05389999970793724, -0.05169999971985817, -0.02070000022649765, 0.0020000000949949026, 0.01140000019222498, 0.009800000116229057, 0.01940000057220459, -0.03799999877810478, -0.01640000008046627, 0.01549999974668026, -0.024399999529123306, 0.09529999643564224, -0.006300000008195639, -0.015699999406933784, -0.07580000162124634, -0.03310000151395798, -0.020099999383091927, 0.032099999487400055, 0.10859999805688858, 0.09799999743700027, 0.048700001090765, -0.03189999982714653, 0.02250000089406967, -0.05260000005364418, -0.016499999910593033, 0.02250000089406967, -0.0203000009059906, -0.004600000102072954, 0.022700000554323196, -0.01769999973475933, -0.05779999867081642, 0.13570000231266022, -0.026399999856948853, -0.004699999932199717], [0.01940000057220459, -0.014499999582767487, -0.07180000096559525, 0.035599999129772186, 0.02669999934732914, 0.06109999865293503, -0.020500000566244125, 0.0340999998152256, 0.062199998646974564, 0.04610000178217888, 0.01489999983459711, -0.07909999787807465, 0.0786999985575676, 0.016200000420212746, -0.037300001829862595, 0.04659999907016754, -0.05420000106096268, 0.04479999840259552, -0.061400000005960464, -0.031300000846385956, 0.04540000110864639, 0.013299999758601189, -0.0006000000284984708, -0.011900000274181366, -0.09560000151395798, 0.02879999950528145, 0.07519999891519547, 0.05119999870657921, -0.01600000075995922, 0.012600000016391277, -0.00839999970048666, -0.05860000103712082, -0.08869999647140503, 0.04019999876618385, -0.0215000007301569, -0.013799999840557575, 0.053300000727176666, -0.08959999680519104, 0.052000001072883606, 0.007300000172108412, 0.026100000366568565, -0.016300000250339508, -0.020899999886751175, -0.03929999843239784, -0.11860000342130661, 0.030500000342726707, 0.029400000348687172, 0.039500001817941666, -0.031300000846385956, 0.027499999850988388, -0.030500000342726707, -0.05730000138282776, 0.013399999588727951, -0.0215000007301569, -0.061000000685453415, 0.016899999231100082, -0.026000000536441803, -0.03720000013709068, -0.05510000139474869, 0.015200000256299973, -0.015300000086426735, 0.0551999993622303, -0.017400000244379044, -0.033799998462200165]], [[-0.07400000095367432, 0.04430000111460686, 0.17270000278949738, 0.17309999465942383, 0.043299999088048935, -0.11240000277757645, 0.16820000112056732, -0.08860000222921371, 0.08219999819993973, -0.02710000053048134, -0.07880000025033951, -0.06930000334978104, -0.027899999171495438, -0.14560000598430634, 0.21080000698566437, 0.19280000030994415, 0.08290000259876251, -0.0786999985575676, -0.11460000276565552, 0.0625, -0.2290000021457672, 0.08640000224113464, 0.004399999976158142, 0.001500000013038516, 0.15760000050067902, 0.012299999594688416, 0.08709999918937683, 0.1695999950170517, -0.026399999856948853, 0.05939999967813492, 0.227400004863739, 0.11569999903440475, -0.1678999960422516, 0.057999998331069946, 0.09790000319480896, 0.2085999995470047, 0.16060000658035278, 0.06379999965429306, -0.11919999867677689, -0.07410000264644623, 0.181099995970726, 0.050200000405311584, -0.024800000712275505, -0.2628999948501587, -0.016300000250339508, -0.1981000006198883, -0.01759999990463257, 0.12860000133514404, -0.03790000081062317, 0.13819999992847443, -0.09269999712705612, 0.09600000083446503, 0.05950000137090683, -0.11159999668598175, 0.21559999883174896, -0.1890999972820282, -0.051899999380111694, 0.00800000037997961, -0.04190000146627426, -0.1615000069141388, 0.08160000294446945, 0.00419999985024333, -0.24449999630451202, 0.10050000250339508], [-0.3027999997138977, 0.0052999998442828655, 0.012400000356137753, 0.19679999351501465, -0.046799998730421066, 0.23980000615119934, -0.11219999939203262, 0.2085999995470047, -0.12520000338554382, -0.031099999323487282, 0.05620000138878822, 0.24220000207424164, 0.14659999310970306, -0.028699999675154686, -0.0142000000923872, 0.06019999831914902, -0.15880000591278076, -0.07360000163316727, -0.2705000042915344, 0.18440000712871552, -0.07079999893903732, 0.06729999929666519, 0.20469999313354492, -0.10189999639987946, -0.00800000037997961, 0.0071000000461936, 0.026100000366568565, -0.0406000018119812, -0.025800000876188278, -0.08349999785423279, -0.30630001425743103, 0.003800000064074993, 0.00430000014603138, -0.05469999834895134, 0.05620000138878822, -0.059300001710653305, 0.08829999715089798, 0.006300000008195639, 0.1200999990105629, -0.11649999767541885, 0.15049999952316284, 0.11909999698400497, -0.19179999828338623, 0.07829999923706055, -0.0031999999191612005, 0.03269999846816063, 0.14409999549388885, -0.22769999504089355, 0.005499999970197678, -0.07639999687671661, 0.08630000054836273, 0.08100000023841858, 0.10890000313520432, 0.019999999552965164, 0.0007999999797903001, -0.08810000121593475, 0.010599999688565731, 0.12559999525547028, -0.07699999958276749, -0.11999999731779099, 0.02239999920129776, -0.11800000071525574, -0.2070000022649765, -0.1145000010728836], [0.11140000075101852, -0.12849999964237213, 0.19429999589920044, 0.1054999977350235, -0.00139999995008111, -0.05810000002384186, -0.01940000057220459, -0.13609999418258667, -0.06499999761581421, -0.05730000138282776, 0.26010000705718994, 0.04670000076293945, -0.16429999470710754, 0.09009999781847, 0.11129999905824661, 0.039000000804662704, 0.10159999877214432, -0.0982000008225441, -0.17520000040531158, 0.05889999866485596, -0.04820000007748604, 0.23399999737739563, -0.17069999873638153, 0.04179999977350235, -0.0284000001847744, -0.09749999642372131, 0.019200000911951065, 0.11209999769926071, 0.16369999945163727, -0.030700000002980232, -0.06369999796152115, 0.04399999976158142, -0.06210000067949295, -0.17139999568462372, 0.0012000000569969416, -0.09849999845027924, 0.006399999838322401, 0.04899999871850014, 0.0020000000949949026, 0.2551000118255615, -0.03449999913573265, -0.04100000113248825, -0.022299999371170998, 0.08720000088214874, -0.18719999492168427, 0.17010000348091125, -0.3619999885559082, 0.019899999722838402, 0.19110000133514404, -0.07289999723434448, 0.02810000069439411, -0.10379999876022339, -0.18709999322891235, 0.20819999277591705, -0.10320000350475311, -0.06430000066757202, -0.22059999406337738, 0.12540000677108765, -0.045099999755620956, -0.02979999966919422, 0.032099999487400055, -0.1565999984741211, -0.11860000342130661, -0.06449999660253525], [-0.10939999669790268, 0.12399999797344208, 0.23090000450611115, -0.0340999998152256, 0.08950000256299973, 0.05530000105500221, -0.08160000294446945, -0.1469999998807907, -0.05310000106692314, 0.04050000011920929, 0.09759999811649323, -0.2143000066280365, 0.03709999844431877, 0.08370000123977661, -0.045499999076128006, 0.0494999997317791, 0.29840001463890076, 0.012000000104308128, 0.007400000002235174, -0.09520000219345093, -0.22370000183582306, -0.06360000371932983, 0.05869999900460243, 0.12530000507831573, -0.09030000120401382, -0.17970000207424164, -0.003700000001117587, -0.040300000458955765, 0.21979999542236328, 0.16850000619888306, -0.03819999843835831, -0.0885000005364418, 0.004999999888241291, 0.17790000140666962, -0.16979999840259552, -0.024299999698996544, -0.13600000739097595, 0.04809999838471413, 0.2581000030040741, -0.15160000324249268, -0.04639999940991402, -0.04600000008940697, -0.048700001090765, 0.10499999672174454, 0.06379999965429306, 0.07779999822378159, 0.09939999878406525, -0.1728000044822693, -0.12359999865293503, -0.09019999951124191, -0.1501999944448471, 0.08309999853372574, -0.13249999284744263, 0.0210999995470047, -0.048500001430511475, 0.032099999487400055, 0.12950000166893005, -0.10530000180006027, 0.07320000231266022, -0.1881999969482422, 0.23019999265670776, -0.11760000139474869, -0.09260000288486481, 0.22139999270439148], [-0.0038999998942017555, 0.09969999641180038, -0.09539999812841415, -0.07109999656677246, 0.04740000143647194, 0.03590000048279762, -0.010400000028312206, -0.05460000038146973, -0.014700000174343586, 0.025499999523162842, 0.14069999754428864, 0.026599999517202377, 0.10329999774694443, -0.16519999504089355, -0.15489999949932098, 0.1370999962091446, -0.16680000722408295, -0.04600000008940697, -0.15919999778270721, -0.1941000074148178, -0.23070000112056732, -0.19210000336170197, -0.04320000112056732, 0.016899999231100082, -0.08780000358819962, 0.02449999935925007, -0.010499999858438969, -0.15150000154972076, -0.09309999644756317, 0.06769999861717224, -0.0786999985575676, 0.05429999902844429, 0.017100000753998756, 0.23989999294281006, 0.054099999368190765, 0.02459999918937683, 0.2953999936580658, -0.07530000060796738, -0.17560000717639923, 0.013299999758601189, -0.05350000038743019, -0.28769999742507935, 0.06199999898672104, -0.20149999856948853, 0.013100000098347664, 0.08399999886751175, 0.02759999968111515, 0.06989999860525131, 0.24480000138282776, 0.0697999969124794, 0.2337999939918518, -0.024000000208616257, -0.094200000166893, 0.17579999566078186, -0.06239999830722809, 0.08009999990463257, -0.055399999022483826, 0.04600000008940697, 0.16910000145435333, 0.020099999383091927, 0.30079999566078186, -0.0674000009894371, 0.022099999710917473, -0.010700000450015068], [-0.006200000178068876, 0.04989999905228615, 0.10050000250339508, -0.09910000115633011, -0.08009999990463257, -0.04190000146627426, -0.15209999680519104, -0.19300000369548798, 0.06440000236034393, -0.06880000233650208, 0.0502999983727932, 0.0649000033736229, 0.1387999951839447, -0.13779999315738678, -0.03319999948143959, 0.2930999994277954, -0.0210999995470047, -0.028699999675154686, -0.3402000069618225, 0.042899999767541885, 0.10660000145435333, -0.09570000320672989, 0.08869999647140503, 0.07670000195503235, 0.010700000450015068, 0.004000000189989805, -0.21480000019073486, 0.17030000686645508, 0.02800000086426735, 0.00860000029206276, -0.022700000554323196, -0.13979999721050262, -0.09040000289678574, -0.15330000221729279, -0.13210000097751617, 0.02889999933540821, -0.0617000013589859, 0.1688999980688095, -0.121799997985363, -0.12549999356269836, -0.16619999706745148, 0.14740000665187836, 0.14959999918937683, 0.05490000173449516, -0.02810000069439411, 0.006800000090152025, 0.1446000039577484, -0.01269999984651804, -0.14579999446868896, 0.13019999861717224, 0.16840000450611115, -0.09070000052452087, -0.14390000700950623, -0.013199999928474426, -0.06639999896287918, 0.05040000006556511, -0.21299999952316284, -0.08479999750852585, -0.18310000002384186, -0.06400000303983688, -0.041999999433755875, 0.29350000619888306, 0.15880000591278076, 0.058400001376867294], [-0.08229999989271164, 0.22990000247955322, -0.19040000438690186, 0.12600000202655792, -0.04899999871850014, 0.012500000186264515, 0.06499999761581421, 0.07479999959468842, -0.16419999301433563, -0.031099999323487282, -0.06030000001192093, 0.10379999876022339, -0.11469999700784683, -0.004100000020116568, 0.08510000258684158, 0.24120000004768372, -0.12210000306367874, -0.06610000133514404, 0.026599999517202377, -0.05640000104904175, 0.10339999943971634, -0.0778999999165535, -0.065700002014637, -0.0406000018119812, -0.07999999821186066, -0.14569999277591705, 0.044199999421834946, 0.24079999327659607, -0.016499999910593033, 0.04270000010728836, -0.09480000287294388, 0.19629999995231628, 0.2093999981880188, 0.07410000264644623, -0.05209999904036522, -0.09549999982118607, -0.2662000060081482, -0.04969999939203262, 0.041999999433755875, 0.2476000040769577, -0.010599999688565731, 0.23160000145435333, -0.07509999722242355, -0.02280000038444996, -0.06589999794960022, 0.11140000075101852, 0.04230000078678131, 0.24300000071525574, 0.04179999977350235, 0.039900001138448715, -0.020800000056624413, 0.09950000047683716, 0.06530000269412994, 0.03909999877214432, 0.002300000051036477, -0.04969999939203262, -0.054499998688697815, -0.03620000183582306, 0.24660000205039978, -0.21799999475479126, 0.0714000016450882, 0.05510000139474869, 0.155799999833107, 0.26440000534057617], [0.059700001031160355, -0.0908999964594841, -0.06040000170469284, 0.16439999639987946, 0.06210000067949295, 0.11760000139474869, -0.22759999334812164, -0.08330000191926956, -0.09440000355243683, 0.23739999532699585, -0.057100001722574234, -0.12359999865293503, -0.11710000038146973, -0.07180000096559525, -0.10970000177621841, 0.14890000224113464, 0.04270000010728836, 0.10729999840259552, -0.10830000042915344, -0.08969999849796295, 0.14980000257492065, 0.33869999647140503, -0.14180000126361847, -0.11129999905824661, 0.026100000366568565, -0.04050000011920929, 0.10740000009536743, -0.0778999999165535, -0.1160999983549118, -0.0640999972820282, 0.00570000009611249, -0.08259999752044678, 0.13279999792575836, 0.12720000743865967, -0.32260000705718994, 0.10260000079870224, 0.0414000004529953, -0.05849999934434891, 0.02459999918937683, -0.14820000529289246, -0.22339999675750732, 0.022199999541044235, -0.13289999961853027, 0.023099999874830246, -0.02879999950528145, -0.15139999985694885, 0.07289999723434448, 0.1665000021457672, 0.027799999341368675, 0.01549999974668026, 0.059300001710653305, 0.09870000183582306, 0.08370000123977661, -0.03180000185966492, -0.09160000085830688, -0.18410000205039978, -0.09189999848604202, 0.05559999868273735, -0.05310000106692314, 0.2921000123023987, 0.0357000008225441, -0.030400000512599945, -0.11490000039339066, 0.12630000710487366], [0.11010000109672546, 0.0843999981880188, 0.08799999952316284, -0.18709999322891235, 0.019300000742077827, 0.14259999990463257, -0.24160000681877136, 0.24369999766349792, 0.30239999294281006, 0.14990000426769257, 0.0203000009059906, 0.10949999839067459, -0.03779999911785126, -0.13230000436306, 0.11620000004768372, 0.16599999368190765, -0.0032999999821186066, -0.02199999988079071, -0.049400001764297485, 0.13019999861717224, -0.1860000044107437, 0.1062999963760376, 0.06889999657869339, -0.11909999698400497, -0.012299999594688416, -0.0877000018954277, 0.10180000215768814, -0.19920000433921814, -0.04230000078678131, 0.018200000748038292, 0.13079999387264252, 0.13040000200271606, 0.006200000178068876, -0.12080000340938568, -0.0738999992609024, 0.06239999830722809, -0.17949999868869781, -0.10830000042915344, -0.060499999672174454, 0.16539999842643738, -0.0284000001847744, -0.03500000014901161, -0.038100000470876694, -0.08860000222921371, -0.048700001090765, 0.28200000524520874, -0.10180000215768814, -0.009100000374019146, 0.03779999911785126, 0.009200000204145908, -0.07779999822378159, 0.17260000109672546, -0.1137000024318695, -0.15780000388622284, -0.06970000267028809, 0.07450000196695328, 0.2257000058889389, -0.10700000077486038, -0.039799999445676804, 0.0649000033736229, 0.03220000118017197, 0.2556000053882599, -0.09220000356435776, -0.056299999356269836], [-0.06800000369548798, -0.36489999294281006, -0.13040000200271606, 0.18330000340938568, 0.13449999690055847, -0.25369998812675476, 0.047600001096725464, -0.053300000727176666, 0.1257999986410141, 0.01759999990463257, -0.05420000106096268, 0.2150000035762787, -0.008700000122189522, -0.15000000596046448, -0.14499999582767487, 0.05810000002384186, 0.04820000007748604, -0.1809999942779541, 0.04500000178813934, 0.019300000742077827, -0.15049999952316284, 0.017999999225139618, -0.054499998688697815, -0.1160999983549118, 0.32249999046325684, -0.10379999876022339, -0.10080000013113022, -0.2029999941587448, -0.04280000180006027, 0.1914999932050705, 0.06970000267028809, 0.034299999475479126, 0.039900001138448715, -0.07400000095367432, 0.023499999195337296, -0.049800001084804535, -0.11500000208616257, 0.042399998754262924, 0.17810000479221344, 0.09650000184774399, -0.14429999887943268, 0.06800000369548798, -0.0012000000569969416, 0.06279999762773514, 0.007300000172108412, -0.12160000205039978, 0.028300000354647636, -0.08320000022649765, -0.09459999948740005, -0.032600000500679016, 0.11289999634027481, 0.09030000120401382, -0.01850000023841858, 0.027699999511241913, -0.03310000151395798, -0.08900000154972076, -0.0005000000237487257, -0.17880000174045563, 0.06790000200271606, -0.06520000100135803, 0.19930000603199005, -0.08399999886751175, 0.21969999372959137, -0.17110000550746918], [0.11720000207424164, -0.019899999722838402, -0.029600000008940697, -0.07500000298023224, -0.18150000274181366, 0.039400000125169754, -0.14339999854564667, -0.044199999421834946, -0.1941000074148178, 0.11050000041723251, -0.16740000247955322, -0.11980000138282776, 0.09099999815225601, -0.10700000077486038, -0.05310000106692314, -0.0560000017285347, -0.20319999754428864, -0.15940000116825104, -0.0617000013589859, -0.08100000023841858, -0.09740000218153, -0.09080000221729279, -0.04919999837875366, 0.060600001364946365, 0.19259999692440033, -0.08959999680519104, 0.09149999916553497, 0.06930000334978104, 0.03849999979138374, -0.24889999628067017, 0.18469999730587006, -0.07400000095367432, -0.1623000055551529, -0.019999999552965164, -0.11420000344514847, -0.000699999975040555, 0.21240000426769257, -0.009800000116229057, 0.24480000138282776, 0.35659998655319214, -0.11349999904632568, -0.23350000381469727, -0.07289999723434448, 0.033900000154972076, -0.1527000069618225, -0.017100000753998756, 0.1378999948501587, -0.12229999899864197, -0.05469999834895134, -0.006800000090152025, -0.10450000315904617, 0.055799998342990875, 0.025599999353289604, 0.0203000009059906, 0.02319999970495701, -0.09049999713897705, 0.06469999998807907, 0.07490000128746033, -0.01720000058412552, -0.24009999632835388, -0.18860000371932983, 0.05550000071525574, 0.06430000066757202, 0.0348999984562397], [0.148499995470047, 0.17299999296665192, 0.1103999987244606, 0.031700000166893005, 0.2689000070095062, 0.07370000332593918, -0.16019999980926514, 0.11779999732971191, -0.025800000876188278, -0.1728000044822693, -0.19740000367164612, 0.15770000219345093, 0.07329999655485153, -0.16220000386238098, -0.03849999979138374, -0.25459998846054077, 0.03840000182390213, 0.09059999883174896, 0.03759999945759773, 0.08889999985694885, -0.1251000016927719, -0.020400000736117363, -0.14949999749660492, -0.1501999944448471, -0.10080000013113022, 0.04430000111460686, -0.10559999942779541, 0.12319999933242798, 0.2632000148296356, -0.1348000019788742, -0.09780000150203705, 0.10429999977350235, -0.02630000002682209, 0.1120000034570694, 0.07519999891519547, 0.06870000064373016, -0.009100000374019146, -0.265500009059906, 0.012299999594688416, 0.10499999672174454, -0.000699999975040555, -0.026399999856948853, 0.057100001722574234, 0.11720000207424164, -0.05590000003576279, -0.23469999432563782, -0.06830000132322311, 0.05649999901652336, -0.20759999752044678, 0.09510000050067902, 0.18369999527931213, -0.06530000269412994, -0.12039999663829803, -0.13120000064373016, -0.11959999799728394, -0.12549999356269836, -0.03680000081658363, 0.004900000058114529, -0.13439999520778656, -0.007400000002235174, 0.15520000457763672, -0.03610000014305115, 0.05950000137090683, 0.09669999778270721], [-0.08799999952316284, -0.08330000191926956, -0.10350000113248825, -0.06390000134706497, -0.07680000364780426, 0.049400001764297485, 0.07020000368356705, 0.20309999585151672, -0.08370000123977661, -0.06599999964237213, 0.02810000069439411, 0.24009999632835388, 0.1834000051021576, -0.02850000001490116, -0.05909999832510948, 0.017100000753998756, 0.0729999989271164, 0.08919999748468399, 0.1251000016927719, 0.06419999897480011, 0.28459998965263367, 0.09520000219345093, -0.13379999995231628, 0.14010000228881836, 0.019099999219179153, -0.06030000001192093, 0.06199999898672104, -0.10459999740123749, 0.0860000029206276, 0.11259999871253967, 0.13770000636577606, -0.16449999809265137, -0.08320000022649765, 0.008500000461935997, 0.02290000021457672, 0.45730000734329224, 0.056299999356269836, 0.17190000414848328, 0.1647000014781952, -0.09679999947547913, 0.06859999895095825, -0.1128000020980835, 0.044199999421834946, 0.065700002014637, 0.012199999764561653, 0.17389999330043793, -0.13539999723434448, 0.12240000069141388, 0.10819999873638153, 0.13449999690055847, 0.12039999663829803, -0.03150000050663948, -0.07490000128746033, -0.06440000236034393, -0.17800000309944153, -0.14659999310970306, 0.06509999930858612, 0.04439999908208847, 0.061400000005960464, -0.2272000014781952, 0.0333000011742115, 0.027699999511241913, -0.026200000196695328, 0.1298000067472458], [0.05820000171661377, -0.002300000051036477, -0.1062999963760376, 0.03370000049471855, -0.07410000264644623, -0.04390000179409981, -0.021800000220537186, -0.13940000534057617, 0.008899999782443047, -0.17520000040531158, 0.07530000060796738, -0.18240000307559967, -0.10000000149011612, -0.1597999930381775, -0.04309999942779541, -0.2913999855518341, -0.19859999418258667, 0.010999999940395355, -0.1492999941110611, 0.019500000402331352, 0.011699999682605267, 0.012900000438094139, -0.20759999752044678, 0.0982000008225441, 0.10440000146627426, -0.2540999948978424, 0.3041999936103821, -0.12690000236034393, 0.014600000344216824, -0.04050000011920929, -0.009600000455975533, -0.07240000367164612, 0.17679999768733978, -0.02070000022649765, 0.011500000022351742, 0.024000000208616257, -0.1915999948978424, -0.01769999973475933, -0.20229999721050262, -0.08309999853372574, 0.18240000307559967, 0.025599999353289604, -0.040800001472234726, 0.12020000070333481, 0.07050000131130219, 0.1598999947309494, 0.0828000009059906, -0.057100001722574234, -0.054999999701976776, 0.2623000144958496, 0.10809999704360962, 0.15279999375343323, -0.07410000264644623, -0.17640000581741333, 0.12729999423027039, 0.15760000050067902, -0.09640000015497208, -0.04859999939799309, -0.12409999966621399, -0.1234000027179718, 0.039400000125169754, -0.1371999979019165, -0.04050000011920929, -0.03909999877214432], [-0.18459999561309814, 0.11309999972581863, 0.017100000753998756, -0.25529998540878296, -0.06889999657869339, -0.17550000548362732, 0.0917000025510788, 0.1289999932050705, 0.02370000071823597, 0.05849999934434891, -0.19750000536441803, -0.0869000032544136, -0.05119999870657921, 0.04879999905824661, -0.09480000287294388, -0.16380000114440918, 0.1492999941110611, 0.05860000103712082, -0.18369999527931213, 0.11699999868869781, 0.15639999508857727, 0.10100000351667404, -0.09399999678134918, -0.19329999387264252, -0.045899998396635056, -0.10379999876022339, -0.08250000327825546, 0.025499999523162842, -0.20829999446868896, 0.11949999630451202, -0.0722000002861023, -0.003100000089034438, -0.14579999446868896, 0.3012999892234802, 0.03180000185966492, -0.10750000178813934, -0.024000000208616257, 0.11569999903440475, 0.04540000110864639, 0.15189999341964722, -0.04360000044107437, -0.03799999877810478, -0.10260000079870224, -0.0007999999797903001, -0.25679999589920044, 0.02419999986886978, -0.03350000083446503, -0.22130000591278076, 0.07639999687671661, 0.1914999932050705, 0.11620000004768372, -0.09019999951124191, 0.03060000017285347, 0.03220000118017197, 0.10559999942779541, -0.03970000147819519, -0.10119999945163727, -0.2847999930381775, 0.02290000021457672, 0.03229999914765358, 0.00989999994635582, 0.058800000697374344, -0.16940000653266907, -0.014800000004470348], [0.14239999651908875, -0.04360000044107437, -0.055399999022483826, -0.05779999867081642, 0.32710000872612, 0.05389999970793724, -0.08560000360012054, -0.10869999974966049, 9.999999747378752e-05, -0.1712999939918518, -0.1290999948978424, -0.13109999895095825, -0.02930000051856041, -0.02630000002682209, 0.14800000190734863, -0.046799998730421066, -0.13269999623298645, -0.19130000472068787, 0.11050000041723251, 0.3635999858379364, 0.02239999920129776, 0.0333000011742115, 0.015300000086426735, 0.15620000660419464, 0.08529999852180481, 0.0502999983727932, -0.03689999878406525, 0.12240000069141388, -0.2777000069618225, 0.004399999976158142, -0.04800000041723251, 0.025699999183416367, 0.09059999883174896, 0.20800000429153442, 0.09849999845027924, 0.13660000264644623, -0.0019000000320374966, 0.0203000009059906, 0.0568000003695488, -0.13940000534057617, -0.18219999969005585, 0.02850000001490116, -0.05609999969601631, 0.03200000151991844, 0.004100000020116568, 0.13429999351501465, 0.11249999701976776, -0.01140000019222498, 0.10180000215768814, -0.29190000891685486, 0.08139999955892563, -0.010200000368058681, -0.2906000018119812, 0.053700000047683716, 0.02810000069439411, -0.03150000050663948, -0.029999999329447746, -0.015399999916553497, 0.13109999895095825, -0.0828000009059906, -0.12470000237226486, 0.05959999933838844, -0.12099999934434891, -0.013000000268220901], [-0.08060000091791153, 0.060600001364946365, 0.07509999722242355, -0.11469999700784683, -0.10819999873638153, -0.08529999852180481, -0.11729999631643295, 0.053700000047683716, 0.015200000256299973, -0.08070000261068344, -0.10830000042915344, -0.2159000039100647, -0.08810000121593475, -0.13359999656677246, -0.1550000011920929, -0.0835999995470047, 0.05620000138878822, -0.26759999990463257, -0.1445000022649765, -0.005900000222027302, 0.03759999945759773, 0.022099999710917473, -0.05380000174045563, 0.030300000682473183, -0.04360000044107437, -0.04309999942779541, -0.3481999933719635, -0.030500000342726707, 0.14569999277591705, -0.1193000003695488, 0.07000000029802322, 0.21799999475479126, -0.010999999940395355, -0.24420000612735748, 0.18700000643730164, 0.18719999492168427, 0.0019000000320374966, 0.03689999878406525, 0.1940000057220459, -0.06840000301599503, 0.036400001496076584, 0.10649999976158142, -0.14730000495910645, -0.03680000081658363, 0.07490000128746033, 0.07500000298023224, 0.1898999959230423, 0.2328999936580658, 0.12300000339746475, 0.0658000037074089, -0.07039999961853027, -0.026499999687075615, 0.06549999862909317, -0.03689999878406525, -0.13570000231266022, 0.11789999902248383, 0.00139999995008111, 0.0066999997943639755, 0.19529999792575836, 0.21559999883174896, 0.0020000000949949026, -0.18729999661445618, -0.0544000007212162, -0.04470000043511391], [0.03150000050663948, -0.038600001484155655, -0.031599998474121094, -0.004699999932199717, -0.03620000183582306, -0.01640000008046627, -0.14569999277591705, -0.11209999769926071, -0.1906999945640564, -0.2102999985218048, -0.0868000015616417, 0.04740000143647194, 0.17970000207424164, 0.04129999876022339, 0.026799999177455902, -0.07729999721050262, -0.04670000076293945, 0.04830000177025795, 0.01940000057220459, -0.37400001287460327, -0.11379999667406082, 0.2037000060081482, 0.0934000015258789, -0.04439999908208847, -0.02329999953508377, -0.05739999935030937, -0.19210000336170197, -0.07270000129938126, -0.09380000084638596, -0.02329999953508377, 0.012500000186264515, 0.09740000218153, 0.2175000011920929, -0.0608999989926815, 0.18250000476837158, 0.13359999656677246, -0.07909999787807465, 0.09220000356435776, -0.03460000082850456, -0.08370000123977661, -0.12790000438690186, 0.120899997651577, 0.1168999969959259, -0.11620000004768372, -0.2517000138759613, -0.15549999475479126, -0.23639999330043793, -0.2500999867916107, 0.20479999482631683, -0.01889999955892563, -0.024299999698996544, 0.18549999594688416, 0.019899999722838402, -0.06400000303983688, 0.01600000075995922, 0.1527000069618225, 0.07829999923706055, -0.013500000350177288, -0.04320000112056732, -0.07850000262260437, -0.0835999995470047, 0.06449999660253525, -0.07580000162124634, 0.1712000072002411], [-0.1679999977350235, 0.04039999842643738, -0.13359999656677246, -0.04740000143647194, -0.20509999990463257, -0.005200000014156103, -0.10159999877214432, -0.05979999899864197, 0.027400000020861626, -0.07580000162124634, 0.17960000038146973, 0.11540000140666962, -0.1378999948501587, -0.07079999893903732, -0.04780000075697899, -0.14249999821186066, 0.16349999606609344, 0.04340000078082085, -0.004100000020116568, 0.004399999976158142, 0.019999999552965164, -0.08579999953508377, 0.14270000159740448, -0.07419999688863754, -0.023000000044703484, -0.20579999685287476, 0.04690000042319298, 0.046799998730421066, -0.013700000010430813, -0.03060000017285347, 0.003700000001117587, 0.008999999612569809, 0.07569999992847443, -0.18129999935626984, 0.06319999694824219, 0.035999998450279236, 0.1761000007390976, -0.16930000483989716, 0.0737999975681305, -0.08449999988079071, -0.19779999554157257, -0.02539999969303608, -0.014600000344216824, 0.05260000005364418, -0.04899999871850014, -0.05209999904036522, -0.051600001752376556, 0.22089999914169312, -0.052799999713897705, -0.08950000256299973, 0.11400000005960464, -0.0658000037074089, -0.23890000581741333, 0.13099999725818634, 0.5157999992370605, -0.1460999995470047, 0.23929999768733978, -0.06549999862909317, -0.030300000682473183, 0.06530000269412994, -0.0142000000923872, 0.045899998396635056, -0.03310000151395798, 0.09629999846220016], [-0.11550000309944153, 0.027499999850988388, 0.06319999694824219, -0.10159999877214432, -0.06319999694824219, -0.1534000039100647, 0.17569999396800995, 0.06019999831914902, -0.0697999969124794, 0.22010000050067902, -0.06040000170469284, -0.19099999964237213, 0.06239999830722809, -0.23880000412464142, -0.13030000030994415, -0.10840000212192535, -0.003100000089034438, 0.04659999907016754, 0.07959999889135361, 0.08489999920129776, -0.1111999973654747, 0.18930000066757202, 0.2289000004529953, 0.07460000365972519, -0.14059999585151672, 0.14470000565052032, -0.05570000037550926, -0.11900000274181366, -0.12330000102519989, 0.06729999929666519, -0.04969999939203262, 0.20229999721050262, 0.03240000084042549, -0.10649999976158142, -0.16030000150203705, 0.06449999660253525, 0.06970000267028809, -0.08980000019073486, -0.012000000104308128, 0.015599999576807022, 0.014299999922513962, 0.04650000110268593, -0.1404999941587448, 0.08789999783039093, 0.1467999964952469, 0.07410000264644623, -0.26829999685287476, -0.047600001096725464, -0.13439999520778656, -0.04479999840259552, 0.10540000349283218, 0.14990000426769257, -0.13210000097751617, 0.010900000110268593, 0.06949999928474426, -0.0024999999441206455, -0.2849999964237213, 0.20880000293254852, 0.004900000058114529, -0.12309999763965607, -0.08579999953508377, 0.014100000262260437, 0.22460000216960907, 0.1509999930858612], [0.14069999754428864, -0.11590000241994858, -0.026799999177455902, 0.13660000264644623, -0.094200000166893, -0.09099999815225601, 0.055399999022483826, -0.033399999141693115, 0.041099999099969864, 0.03660000115633011, -0.10729999840259552, -0.02319999970495701, 0.06669999659061432, -0.044599998742341995, -0.05510000139474869, -0.13189999759197235, 0.05389999970793724, -0.0617000013589859, -0.11990000307559967, 0.16859999299049377, 0.0478999987244606, -0.18299999833106995, 0.05990000069141388, 0.2628999948501587, -0.30649998784065247, -0.1768999993801117, 0.19930000603199005, -0.10429999977350235, -0.00039999998989515007, -0.07450000196695328, -0.1412999927997589, 0.2946999967098236, 0.01360000018030405, 0.11590000241994858, -0.13779999315738678, 0.1606999933719635, 0.09690000116825104, 0.27129998803138733, -0.07680000364780426, 0.11620000004768372, -0.13109999895095825, 0.23980000615119934, 0.09269999712705612, 0.014299999922513962, -0.04360000044107437, -0.13449999690055847, -0.08460000157356262, 0.0012000000569969416, -0.06109999865293503, -0.05609999969601631, -0.06210000067949295, -0.062300000339746475, 0.12610000371932983, 0.07840000092983246, -0.08829999715089798, 0.008500000461935997, 0.24060000479221344, 0.054999999701976776, -0.0658000037074089, 0.03779999911785126, 0.1670999974012375, 0.11659999936819077, -0.05649999901652336, -0.10239999741315842], [-0.0003000000142492354, 0.021199999377131462, -0.004699999932199717, -0.08380000293254852, 0.11649999767541885, 0.0010999999940395355, -0.00800000037997961, 0.05510000139474869, 0.06599999964237213, -0.04360000044107437, 0.017000000923871994, 0.009999999776482582, -0.11259999871253967, -0.3310000002384186, 0.15080000460147858, 0.029600000008940697, -0.06769999861717224, 0.2451000064611435, 0.08020000159740448, 0.07859999686479568, -0.13300000131130219, 0.04149999842047691, -0.051600001752376556, -0.05429999902844429, -0.1420000046491623, -0.22419999539852142, 0.005200000014156103, 0.13910000026226044, 0.06939999759197235, -0.10080000013113022, -0.11010000109672546, -0.20000000298023224, -0.0723000019788742, 0.06549999862909317, 0.0617000013589859, 0.06400000303983688, -0.09719999879598618, 0.25760000944137573, 0.2101999968290329, -0.1509000062942505, -0.03929999843239784, -0.03280000016093254, 0.05939999967813492, -0.18379999697208405, -0.089800000190</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>[[[-0.06319999694824219, -0.02239999920129776, 0.0786999985575676, 0.08429999649524689, -0.12700000405311584, -0.06889999657869339, -0.10840000212192535, -0.06989999860525131, -0.003000000026077032, -0.03849999979138374, -0.10429999977350235, 0.11949999630451202, -0.03400000184774399, -0.10909999907016754, 0.053199999034404755, 0.010099999606609344, -0.10289999842643738, 0.08089999854564667, 0.07020000368356705, 0.07909999787807465, -0.07699999958276749, 0.10649999976158142, 0.01940000057220459, 0.031099999323487282, -0.09179999679327011, -0.0471000000834465, -0.05079999938607216, 0.09449999779462814, 0.1080000028014183, 0.005400000140070915, 0.07129999995231628, -0.02239999920129776, 0.026599999517202377, -0.04569999873638153, -0.003100000089034438, 0.1062999963760376, -0.022700000554323196, 0.022099999710917473, -0.07100000232458115, 0.07760000228881836, -0.07119999825954437, 0.09600000083446503, 0.061799999326467514, -0.006399999838322401, -0.0868000015616417, -0.0940999984741211, -0.05299999937415123, -0.012600000016391277, 0.12880000472068787, 0.15960000455379486, 0.0640999972820282, 0.023399999365210533, 0.06080000102519989, -0.12349999696016312, 0.04179999977350235, -0.015399999916553497, 0.027000000700354576, 0.061900001019239426, 0.04479999840259552, 0.0406000018119812, -0.032499998807907104, 0.1136000007390976, -0.014000000432133675, 0.020999999716877937], [0.10029999911785126, 0.032099999487400055, -0.11869999766349792, -0.14319999516010284, 0.04560000076889992, 0.0544000007212162, 0.05079999938607216, 0.03629999980330467, -0.006599999964237213, 0.06379999965429306, 0.06459999829530716, -0.07919999957084656, 0.10040000081062317, 0.0934000015258789, -0.08320000022649765, 0.019899999722838402, 0.07169999927282333, -0.049300000071525574, -0.04520000144839287, -0.09910000115633011, 0.08550000190734863, -0.021299999207258224, 0.005200000014156103, -0.0421999990940094, -0.04600000008940697, 0.050700001418590546, 0.10419999808073044, 0.012900000438094139, -0.08349999785423279, -0.007300000172108412, -0.023900000378489494, -0.07620000094175339, -0.10509999841451645, 0.08980000019073486, 0.011300000362098217, -0.13930000364780426, -0.0471000000834465, -0.19820000231266022, 0.09870000183582306, -0.05900000035762787, 0.09709999710321426, -0.10819999873638153, -0.05889999866485596, -0.05310000106692314, -0.10270000249147415, 0.06469999998807907, 0.066600002348423, 0.05180000141263008, -0.11259999871253967, -0.00419999985024333, -0.04360000044107437, -0.02979999966919422, -0.12300000339746475, 0.030500000342726707, -0.07289999723434448, 0.015300000086426735, -0.03889999911189079, -0.061500001698732376, -0.09369999915361404, 0.04910000041127205, 0.0471000000834465, -0.11569999903440475, 0.00839999970048666, -0.06390000134706497]], [[-0.22460000216960907, 0.16699999570846558, 0.15369999408721924, 0.19509999454021454, 0.10649999976158142, -0.023399999365210533, 0.27129998803138733, -0.022700000554323196, 0.06080000102519989, -0.08070000261068344, 0.09920000284910202, -0.10840000212192535, -0.0754999965429306, 0.028699999675154686, -0.004800000227987766, 0.32670000195503235, 0.009999999776482582, -0.23489999771118164, -0.1940000057220459, 0.03929999843239784, -0.1655000001192093, 0.007600000128149986, 0.02250000089406967, 0.09449999779462814, 0.23559999465942383, -0.016499999910593033, 0.06710000336170197, 0.18960000574588776, -0.2062000036239624, -0.02930000051856041, 0.21279999613761902, 0.1347000002861023, -0.020999999716877937, 0.09849999845027924, 0.15960000455379486, 0.2685999870300293, 0.2037000060081482, 0.17080000042915344, -0.06689999997615814, 0.02160000056028366, 0.25220000743865967, 0.039500001817941666, -0.13199999928474426, -0.27129998803138733, 0.03440000116825104, -0.12489999830722809, -0.003800000064074993, 0.1891999989748001, -0.10249999910593033, 0.06679999828338623, -0.012600000016391277, 0.2750999927520752, 0.03590000048279762, 0.07209999859333038, 0.18459999561309814, -0.1527000069618225, -0.14399999380111694, -0.05900000035762787, -0.179299995303154, -0.2248000055551529, 0.10760000348091125, 0.08009999990463257, -0.3190000057220459, 0.06520000100135803], [-0.27799999713897705, -0.023000000044703484, 0.032600000500679016, 0.18860000371932983, -0.02250000089406967, 0.25270000100135803, -0.0966000035405159, 0.23770000040531158, -0.11909999698400497, 0.03709999844431877, 0.02419999986886978, 0.2378000020980835, 0.1738000065088272, -0.06809999793767929, 0.006200000178068876, -0.0617000013589859, -0.1696999967098236, 0.007799999788403511, -0.26969999074935913, 0.20319999754428864, -0.09709999710321426, 0.06499999761581421, 0.20190000534057617, -0.1395999938249588, -0.050999999046325684, 0.05000000074505806, 0.04800000041723251, -0.0210999995470047, -0.0575999990105629, -0.08169999718666077, -0.2791999876499176, 0.0007999999797903001, -0.048700001090765, -0.03539999946951866, 0.05719999969005585, -0.07159999758005142, 0.05849999934434891, -0.08299999684095383, 0.1362999975681305, -0.11289999634027481, 0.16529999673366547, 0.11620000004768372, -0.1678999960422516, 0.0835999995470047, -0.051600001752376556, 0.04490000009536743, 0.16930000483989716, -0.25780001282691956, 0.07590000331401825, -0.09769999980926514, 0.05169999971985817, 0.027000000700354576, 0.11640000343322754, -0.04969999939203262, 0.0006000000284984708, -0.08609999716281891, 0.017100000753998756, 0.13220000267028809, -0.1143999993801117, -0.10649999976158142, 0.008799999952316284, -0.11670000106096268, -0.16619999706745148, -0.08959999680519104], [0.22130000591278076, -0.15299999713897705, 0.2718000113964081, -0.02850000001490116, 0.011800000444054604, -0.12060000002384186, -0.034699998795986176, -0.21250000596046448, -0.08420000225305557, -0.02850000001490116, 0.24549999833106995, 0.06679999828338623, -0.23520000278949738, 0.04670000076293945, 0.21639999747276306, -0.03420000150799751, 0.2142000049352646, -0.0007999999797903001, -0.09960000216960907, 0.13750000298023224, -0.16369999945163727, 0.21209999918937683, -0.03319999948143959, -0.06260000169277191, -0.15389999747276306, -0.1890999972820282, -0.03060000017285347, 0.20239999890327454, 0.1858000010251999, -0.05420000106096268, -0.06440000236034393, 0.09130000323057175, -0.19460000097751617, -0.2639000117778778, 0.06669999659061432, -0.219200000166893, -0.09319999814033508, -0.05590000003576279, -0.049300000071525574, 0.21819999814033508, -0.002400000113993883, -0.0019000000320374966, -0.010499999858438969, 0.147599995136261, -0.23960000276565552, 0.20430000126361847, -0.44940000772476196, -0.07980000227689743, 0.24330000579357147, -0.05909999832510948, 0.11029999703168869, -0.250900000333786, -0.26919999718666077, 0.09070000052452087, -0.023099999874830246, -0.11829999834299088, -0.12370000034570694, 0.12460000067949295, -0.048900000751018524, 0.09120000153779984, -0.0471000000834465, -0.2328999936580658, -0.10660000145435333, 0.03819999843835831], [-0.015300000086426735, 0.05290000140666962, 0.2418999969959259, -0.04569999873638153, 0.032099999487400055, -0.007899999618530273, -0.16040000319480896, -0.2605000138282776, -0.08429999649524689, 0.04450000077486038, -0.09220000356435776, -0.17560000717639923, 0.07159999758005142, 0.003599999938160181, 0.061500001698732376, -0.04690000042319298, 0.35679998993873596, 0.14890000224113464, 0.07159999758005142, -0.07940000295639038, -0.28049999475479126, -0.005100000184029341, 0.09470000118017197, 0.03799999877810478, -0.1550000011920929, -0.12300000339746475, 0.0, -0.03400000184774399, 0.3449999988079071, 0.25529998540878296, -0.07360000163316727, -0.08869999647140503, -0.02290000021457672, 0.14419999718666077, -0.22179999947547913, -0.07800000160932541, -0.14079999923706055, 0.08330000191926956, 0.19990000128746033, -0.21539999544620514, -0.11060000211000443, 0.03420000150799751, -0.037300001829862595, 0.14890000224113464, 0.1290999948978424, 0.09939999878406525, 0.125, -0.28519999980926514, -0.050599999725818634, -0.07639999687671661, -0.18129999935626984, 0.03629999980330467, -0.10840000212192535, -0.08179999887943268, -0.05660000070929527, -0.00039999998989515007, 0.2282000035047531, -0.024299999698996544, 0.11150000244379044, -0.1664000004529953, 0.17339999973773956, -0.1535000056028366, -0.06560000032186508, 0.26010000705718994], [-0.07440000027418137, 0.1340000033378601, -0.17730000615119934, -0.03799999877810478, -0.020099999383091927, 0.0502999983727932, -0.03099999949336052, -0.04170000180602074, 0.04149999842047691, -0.012500000186264515, 0.12880000472068787, 0.03319999948143959, 0.10209999978542328, -0.09239999949932098, -0.121799997985363, 0.2206999957561493, -0.16459999978542328, -0.12520000338554382, -0.2004999965429306, -0.2630000114440918, -0.15379999577999115, -0.15800000727176666, -0.10790000110864639, 0.10540000349283218, 0.0071000000461936, -0.004900000058114529, -0.007799999788403511, -0.22509999573230743, -0.10450000315904617, -0.0544000007212162, -0.0066999997943639755, 0.04830000177025795, 0.06080000102519989, 0.25760000944137573, -0.03280000016093254, 0.07930000126361847, 0.32179999351501465, -0.0608999989926815, -0.15790000557899475, 0.13750000298023224, -0.10920000076293945, -0.3361999988555908, 0.0982000008225441, -0.25859999656677246, 0.0008999999845400453, -0.07660000026226044, 0.04879999905824661, 0.16949999332427979, 0.16680000722408295, 0.10689999908208847, 0.21690000593662262, -0.05939999967813492, -0.031599998474121094, 0.2003999948501587, -0.05389999970793724, 0.06930000334978104, -0.1379999965429306, 0.0658000037074089, 0.2395000010728836, -0.03200000151991844, 0.37130001187324524, -0.005400000140070915, 0.00570000009611249, -0.060600001364946365], [0.005799999926239252, -0.009399999864399433, -0.020500000566244125, 0.018699999898672104, -0.10899999737739563, -0.007699999958276749, -0.18639999628067017, -0.10029999911785126, 0.1412000060081482, -0.06729999929666519, -0.008700000122189522, 0.003700000001117587, 0.26919999718666077, -0.12409999966621399, 0.009100000374019146, 0.27459999918937683, -0.055799998342990875, -0.10249999910593033, -0.40529999136924744, -0.07429999858140945, 0.24009999632835388, -0.06920000165700912, -0.049300000071525574, 0.1396999955177307, 0.14710000157356262, 0.1371999979019165, -0.12710000574588776, 0.057500001043081284, 0.06599999964237213, 0.05510000139474869, -0.0035000001080334187, -0.18310000002384186, -0.011599999852478504, 0.0006000000284984708, -0.2076999992132187, 0.11259999871253967, 0.0640999972820282, 0.1469999998807907, -0.05429999902844429, -0.1469999998807907, -0.2289000004529953, 0.08910000324249268, 0.15489999949932098, 0.011699999682605267, -0.0640999972820282, -0.0877000018954277, 0.31189998984336853, 0.12939999997615814, -0.21979999542236328, 0.13500000536441803, 0.04659999907016754, -0.13359999656677246, -0.06069999933242798, -0.018699999898672104, -0.1615000069141388, 0.11490000039339066, -0.22669999301433563, -0.05739999935030937, -0.08389999717473984, -0.16200000047683716, 0.012900000438094139, 0.30390000343322754, 0.2160000056028366, -0.08649999648332596], [-0.12020000070333481, 0.2198999971151352, -0.19949999451637268, 0.13379999995231628, -0.03629999980330467, 0.07440000027418137, -0.006899999920278788, 0.08630000054836273, -0.15000000596046448, 0.032099999487400055, -0.012199999764561653, 0.05719999969005585, -0.08070000261068344, -0.02329999953508377, 0.07810000330209732, 0.2946000099182129, -0.16359999775886536, -0.06870000064373016, -0.04899999871850014, -0.05979999899864197, 0.15039999783039093, -0.120899997651577, -0.06360000371932983, -0.047200001776218414, -0.09520000219345093, -0.10700000077486038, 0.07119999825954437, 0.26269999146461487, -0.06509999930858612, 0.01979999989271164, -0.1136000007390976, 0.23819999396800995, 0.19949999451637268, 0.1467999964952469, -0.06729999929666519, -0.07240000367164612, -0.19339999556541443, -0.023099999874830246, 0.11100000143051147, 0.3034000098705292, -0.07090000063180923, 0.24860000610351562, -0.09229999780654907, -0.004100000020116568, -0.03480000048875809, 0.10029999911785126, 0.06669999659061432, 0.26350000500679016, 0.048700001090765, -0.014800000004470348, -0.017899999395012856, 0.10719999670982361, 0.066600002348423, 0.09239999949932098, -0.05169999971985817, -0.010599999688565731, -0.04439999908208847, -0.06970000267028809, 0.23919999599456787, -0.27149999141693115, 0.052299998700618744, 0.10419999808073044, 0.14839999377727509, 0.2630000114440918], [0.05400000140070915, -0.1371999979019165, -0.10170000046491623, 0.24899999797344208, 0.10849999636411667, 0.10450000315904617, -0.23000000417232513, 0.012299999594688416, -0.04360000044107437, 0.2531999945640564, 0.00279999990016222, -0.2718999981880188, -0.030700000002980232, -0.06080000102519989, -0.12929999828338623, 0.12409999966621399, -0.01889999955892563, 0.13349999487400055, -0.24799999594688416, -0.07109999656677246, 0.19750000536441803, 0.24410000443458557, -0.13330000638961792, -0.06830000132322311, 0.1590999960899353, 0.04580000042915344, 0.19519999623298645, -0.10949999839067459, -0.0340999998152256, -0.13199999928474426, -0.03350000083446503, -0.00139999995008111, 0.16380000114440918, 0.2345999926328659, -0.38449999690055847, 0.11909999698400497, 0.14110000431537628, -0.11100000143051147, 0.04879999905824661, -0.20239999890327454, -0.17599999904632568, 0.05810000002384186, -0.13330000638961792, 0.066600002348423, -0.04919999837875366, -0.2791999876499176, 0.18960000574588776, 0.14550000429153442, -0.055399999022483826, -0.08309999853372574, -0.035599999129772186, 0.06360000371932983, 0.1445000022649765, 0.06610000133514404, -0.19509999454021454, -0.07100000232458115, -0.01850000023841858, -0.008899999782443047, -0.04729999974370003, 0.17589999735355377, -0.01080000028014183, -0.023900000378489494, -0.06780000030994415, -0.007899999618530273], [0.1437000036239624, 0.06520000100135803, 0.06360000371932983, -0.1818999946117401, -0.0364999994635582, 0.11680000275373459, -0.2222999930381775, 0.23520000278949738, 0.2824999988079071, 0.155799999833107, -0.00430000014603138, 0.0885000005364418, -0.03370000049471855, -0.06480000168085098, 0.10980000346899033, 0.1266999989748001, 0.04360000044107437, -0.06369999796152115, -0.03420000150799751, 0.0843999981880188, -0.17970000207424164, 0.12219999730587006, 0.050700001418590546, -0.11050000041723251, 0.027699999511241913, -0.04340000078082085, 0.0982000008225441, -0.2345999926328659, -0.026000000536441803, 0.04910000041127205, 0.12849999964237213, 0.1242000013589859, 0.024800000712275505, -0.11490000039339066, -0.09650000184774399, 0.04659999907016754, -0.17479999363422394, -0.12530000507831573, -0.07720000296831131, 0.148499995470047, -0.02800000086426735, -0.05660000070929527, -0.05959999933838844, -0.08709999918937683, -0.017899999395012856, 0.27889999747276306, -0.0722000002861023, -0.007699999958276749, -0.013700000010430813, -0.005499999970197678, -0.09160000085830688, 0.18310000002384186, -0.10209999978542328, -0.1339000016450882, -0.066600002348423, 0.05590000003576279, 0.24719999730587006, -0.08910000324249268, -0.050999999046325684, 0.07270000129938126, 0.05000000074505806, 0.22550000250339508, -0.09369999915361404, -0.08380000293254852], [-0.07819999754428864, -0.33899998664855957, -0.17100000381469727, 0.22460000216960907, 0.11150000244379044, -0.29989999532699585, 0.11140000075101852, -0.03150000050663948, 0.11330000311136246, -0.06669999659061432, -0.05849999934434891, 0.18799999356269836, -0.0430000014603138, -0.08420000225305557, -0.16519999504089355, 0.0364999994635582, 0.07699999958276749, -0.24629999697208405, 0.03720000013709068, -0.02070000022649765, -0.0786999985575676, 0.039799999445676804, -0.11230000108480453, -0.06390000134706497, 0.41780000925064087, -0.15760000050067902, -0.1404000073671341, -0.25220000743865967, -0.021900000050663948, 0.1753000020980835, 0.13289999961853027, -0.01640000008046627, 0.10670000314712524, -0.08349999785423279, 0.04039999842643738, 0.0010999999940395355, -0.14419999718666077, -0.007799999788403511, 0.16680000722408295, 0.12839999794960022, -0.09009999781847, 0.02319999970495701, 0.00279999990016222, 0.010099999606609344, -0.0471000000834465, -0.16419999301433563, 0.03060000017285347, -0.04610000178217888, -0.15330000221729279, -0.010499999858438969, 0.09989999979734421, 0.11670000106096268, -0.008999999612569809, 0.031300000846385956, -0.012199999764561653, -0.1005999967455864, -0.03440000116825104, -0.17419999837875366, 0.07890000194311142, -0.06780000030994415, 0.24240000545978546, -0.10459999740123749, 0.20260000228881836, -0.2282000035047531], [0.06639999896287918, -0.05220000073313713, -0.0608999989926815, 0.02800000086426735, -0.1436000019311905, 0.06289999932050705, -0.19099999964237213, 0.0658000037074089, -0.16169999539852142, 0.12240000069141388, -0.11749999970197678, -0.19059999287128448, 0.1712000072002411, -0.11349999904632568, -0.05480000004172325, -0.014700000174343586, -0.27869999408721924, -0.2248000055551529, -0.18400000035762787, -0.08569999784231186, 0.0034000000450760126, -0.1356000006198883, -0.08370000123977661, 0.10010000318288803, 0.31220000982284546, -0.01850000023841858, 0.16179999709129333, 0.05640000104904175, 0.06340000033378601, -0.26669999957084656, 0.19359999895095825, -0.0430000014603138, -0.10760000348091125, 0.06430000066757202, -0.1623000055551529, 0.02979999966919422, 0.3003999888896942, -0.0908999964594841, 0.30979999899864197, 0.39430001378059387, -0.11580000072717667, -0.22859999537467957, -0.0786999985575676, 0.02590000070631504, -0.16769999265670776, -0.15080000460147858, 0.22089999914169312, -0.09220000356435776, -0.08990000188350677, -0.024800000712275505, -0.1662999987602234, 0.04529999941587448, 0.0746999979019165, 0.09679999947547913, -0.04820000007748604, -0.017500000074505806, -0.03920000046491623, 0.07090000063180923, 0.03350000083446503, -0.3353999853134155, -0.2078000009059906, 0.0868000015616417, 0.14139999449253082, -0.06300000101327896], [0.26109999418258667, 0.1923999935388565, 0.1972000002861023, -0.0860000029206276, 0.21480000019073486, 0.06830000132322311, -0.17739999294281006, -0.0340999998152256, -0.10409999638795853, -0.18940000236034393, -0.3353999853134155, 0.2296999990940094, -0.007600000128149986, -0.1964000016450882, 0.010300000198185444, -0.26969999074935913, 0.12700000405311584, 0.20479999482631683, 0.20229999721050262, 0.10610000044107437, -0.22689999639987946, -0.006000000052154064, -0.10639999806880951, -0.25699999928474426, -0.33379998803138733, -0.013299999758601189, -0.18209999799728394, 0.16339999437332153, 0.2948000133037567, -0.10589999705553055, -0.1655000001192093, 0.0877000018954277, -0.15809999406337738, 0.01759999990463257, 0.1501999944448471, 0.007000000216066837, -0.09480000287294388, -0.1818999946117401, -0.03460000082850456, 0.041600000113248825, -0.03500000014901161, -0.008299999870359898, 0.034299999475479126, 0.17990000545978546, 0.010099999606609344, -0.020600000396370888, -0.18529999256134033, -0.01889999955892563, -0.06930000334978104, 0.11400000005960464, 0.2766000032424927, -0.02410000003874302, -0.2069000005722046, -0.2687000036239624, -0.04039999842643738, -0.2076999992132187, 0.023399999365210533, 0.050599999725818634, -0.11150000244379044, 0.10819999873638153, 0.09809999912977219, -0.07859999686479568, 0.006000000052154064, 0.2395000010728836], [-0.1054999977350235, -0.0714000016450882, -0.1404999941587448, -0.032499998807907104, -0.11860000342130661, 0.05380000174045563, 0.1446000039577484, 0.19359999895095825, -0.07729999721050262, -0.1281999945640564, 0.0203000009059906, 0.26989999413490295, 0.1882999986410141, 0.03689999878406525, -0.11410000175237656, 0.02239999920129776, 0.09120000153779984, 0.016100000590085983, 0.14730000495910645, 0.010300000198185444, 0.3098999857902527, 0.1251000016927719, -0.18799999356269836, 0.20200000703334808, 0.05290000140666962, -0.07249999791383743, 0.051500000059604645, -0.15649999678134918, 0.056699998676776886, 0.1265999972820282, 0.1574999988079071, -0.19609999656677246, -0.011599999852478504, 0.00430000014603138, 0.0006000000284984708, 0.5120999813079834, 0.04749999940395355, 0.20190000534057617, 0.1525000035762787, -0.0737999975681305, 0.06469999998807907, -0.15690000355243683, 0.04919999837875366, 0.03150000050663948, 0.011099999770522118, 0.15360000729560852, -0.12290000170469284, 0.17640000581741333, 0.059300001710653305, 0.14000000059604645, 0.1128000020980835, 0.023000000044703484, -0.05739999935030937, -0.04270000010728836, -0.15889999270439148, -0.15530000627040863, -0.011800000444054604, 0.06549999862909317, 0.0421999990940094, -0.2304999977350235, 0.09380000084638596, 0.02319999970495701, -0.045499999076128006, 0.08889999985694885], [-0.041099999099969864, 0.03799999877810478, -0.14390000700950623, 0.08449999988079071, -0.05779999867081642, 0.0272000003606081, -0.058400001376867294, -0.0697999969124794, 0.04179999977350235, -0.14880000054836273, 0.16099999845027924, -0.25429999828338623, -0.07699999958276749, -0.15700000524520874, -0.08789999783039093, -0.20059999823570251, -0.2696000039577484, -0.035599999129772186, -0.2676999866962433, 0.001500000013038516, 0.09539999812841415, -0.02160000056028366, -0.23090000450611115, 0.1535000056028366, 0.18549999594688416, -0.2515999972820282, 0.3273000121116638, -0.12680000066757202, -0.06859999895095825, -0.1354999989271164, 0.024000000208616257, -0.039000000804662704, 0.21649999916553497, 0.07039999961853027, 0.007199999876320362, 0.1111999973654747, -0.11460000276565552, 0.020099999383091927, -0.12950000166893005, 0.10649999976158142, 0.1949000060558319, 0.03759999945759773, -0.05889999866485596, 0.11599999666213989, 0.0551999993622303, 0.1088000014424324, 0.1316000074148178, 0.01209999993443489, -0.09399999678134918, 0.2102999985218048, 0.09749999642372131, 0.17329999804496765, -0.04879999905824661, -0.07270000129938126, 0.0729999989271164, 0.20890000462532043, -0.15639999508857727, -0.0908999964594841, -0.14419999718666077, -0.2092999964952469, 0.03819999843835831, -0.06019999831914902, -0.04899999871850014, -0.08630000054836273], [-0.16019999980926514, 0.1120000034570694, 0.10409999638795853, -0.3296999931335449, -0.04740000143647194, -0.2160000056028366, 0.04390000179409981, 0.023499999195337296, -0.052299998700618744, 0.14820000529289246, -0.17560000717639923, -0.0966000035405159, -0.12430000305175781, 0.011300000362098217, -0.11640000343322754, -0.14560000598430634, 0.17749999463558197, 0.12129999697208405, -0.15399999916553497, 0.19030000269412994, 0.13840000331401825, 0.08429999649524689, -0.022299999371170998, -0.24809999763965607, -0.07509999722242355, -0.13529999554157257, -0.12489999830722809, 0.0934000015258789, -0.18520000576972961, 0.12880000472068787, -0.17569999396800995, 0.00419999985024333, -0.2827000021934509, 0.24220000207424164, 0.08529999852180481, -0.15800000727176666, -0.07649999856948853, 0.1451999992132187, 0.029899999499320984, 0.10890000313520432, -0.08179999887943268, 0.025100000202655792, -0.11749999970197678, 0.04019999876618385, -0.19660000503063202, 0.13519999384880066, -0.16130000352859497, -0.3179999887943268, 0.1527000069618225, 0.20749999582767487, 0.16529999673366547, -0.02879999950528145, -0.05050000175833702, 0.02199999988079071, 0.09449999779462814, -0.05570000037550926, -0.04740000143647194, -0.30570000410079956, 0.00989999994635582, 0.10350000113248825, -0.06549999862909317, 0.041099999099969864, -0.21130000054836273, 0.0997999981045723], [0.21610000729560852, -0.07930000126361847, -0.05260000005364418, -0.025699999183416367, 0.41350001096725464, -0.07970000058412552, -0.06629999727010727, -0.04690000042319298, 0.04089999943971634, -0.17630000412464142, -0.17110000550746918, -0.1378999948501587, 0.024800000712275505, -0.04340000078082085, 0.1931000053882599, -0.08619999885559082, -0.1128000020980835, -0.14190000295639038, 0.1680999994277954, 0.3912000060081482, -0.007699999958276749, 0.049300000071525574, 0.04639999940991402, 0.14180000126361847, 0.14229999482631683, 0.0892999991774559, -0.018799999728798866, 0.09390000253915787, -0.23989999294281006, 0.019300000742077827, 0.007799999788403511, 0.04569999873638153, 0.06930000334978104, 0.21950000524520874, 0.06859999895095825, 0.08100000023841858, 0.032099999487400055, -0.07670000195503235, 0.011599999852478504, -0.18709999322891235, -0.1388999968767166, 0.008200000040233135, -0.013000000268220901, -0.004900000058114529, -0.07660000026226044, 0.050700001418590546, 0.15080000460147858, -0.06469999998807907, 0.07680000364780426, -0.25110000371932983, 0.004600000102072954, -0.10779999941587448, -0.271699994802475, -0.024700000882148743, 0.012600000016391277, -0.003599999938160181, -0.05730000138282776, -0.00839999970048666, 0.12210000306367874, -0.05180000141263008, -0.12030000239610672, -0.03750000149011612, -0.053199999034404755, -0.03709999844431877], [-0.11940000206232071, 0.08780000358819962, 0.07599999755620956, -0.12290000170469284, -0.08560000360012054, -0.03480000048875809, -0.16210000216960907, 0.05790000036358833, 0.01679999940097332, -0.03400000184774399, -0.03370000049471855, -0.2554999887943268, -0.0982000008225441, -0.1160999983549118, -0.19589999318122864, -0.03150000050663948, 0.016300000250339508, -0.2971000075340271, -0.20909999310970306, 0.0017999999690800905, 0.08489999920129776, -0.02329999953508377, -0.04699999839067459, 0.02979999966919422, -0.05909999832510948, -0.0697999969124794, -0.3504999876022339, 0.007400000002235174, 0.0868000015616417, -0.1746000051498413, 0.0722000002861023, 0.21699999272823334, -0.02449999935925007, -0.1931000053882599, 0.2092999964952469, 0.20360000431537628, 0.03310000151395798, 0.05009999871253967, 0.25450000166893005, 0.019700000062584877, 0.04520000144839287, 0.11180000007152557, -0.15929999947547913, -0.028599999845027924, 0.09040000289678574, 0.09889999777078629, 0.1738000065088272, 0.25049999356269836, 0.12439999729394913, 0.03009999915957451, -0.04089999943971634, 0.006899999920278788, 0.05130000039935112, 0.030500000342726707, -0.1615999937057495, 0.13529999554157257, -0.005499999970197678, -0.035100001841783524, 0.16369999945163727, 0.18709999322891235, -0.013000000268220901, -0.1395999938249588, -0.07519999891519547, -0.03739999979734421], [0.10239999741315842, -0.05920000001788139, -0.03020000085234642, -0.04179999977350235, -0.07689999788999557, -0.04969999939203262, -0.03750000149011612, -0.14180000126361847, -0.18870000541210175, -0.2791999876499176, -0.09610000252723694, 0.14010000228881836, 0.1624000072479248, 0.11069999635219574, 0.028699999675154686, -0.14949999749660492, 0.023399999365210533, 0.0038999998942017555, 0.1266999989748001, -0.41620001196861267, -0.20819999277591705, 0.24609999358654022, 0.13030000030994415, -0.002899999963119626, -0.06870000064373016, -0.1062999963760376, -0.21729999780654907, -0.08789999783039093, -0.10339999943971634, 0.001500000013038516, 0.030500000342726707, 0.05609999969601631, 0.18690000474452972, -0.13379999995231628, 0.15770000219345093, 0.07329999655485153, -0.16850000619888306, 0.036400001496076584, -0.09220000356435776, -0.08739999681711197, -0.1137000024318695, 0.06120000034570694, 0.13850000500679016, -0.14980000257492065, -0.2782999873161316, -0.15639999508857727, -0.2678999900817871, -0.2363000065088272, 0.16120000183582306, 0.02969999983906746, -0.007300000172108412, 0.17100000381469727, 0.0024999999441206455, -0.10750000178813934, 0.0820000022649765, 0.07039999961853027, 0.053599998354911804, 0.006599999964237213, -0.08009999990463257, 0.01140000019222498, -0.0017999999690800905, 0.0052999998442828655, -0.0406000018119812, 0.2046000063419342], [-0.17100000381469727, 0.08500000089406967, -0.023600000888109207, -0.14509999752044678, -0.2393999993801117, 0.047600001096725464, -0.11400000005960464, -0.2045000046491623, -0.042899999767541885, -0.11710000038146973, 0.22630000114440918, 0.21570000052452087, -0.22920000553131104, -0.07400000095367432, -0.08799999952316284, -0.1242000013589859, 0.1873999983072281, 0.04580000042915344, 0.09570000320672989, 0.06400000303983688, -0.07769999653100967, -0.10700000077486038, 0.20559999346733093, -0.1039000004529953, -0.26420000195503235, -0.28940001130104065, -0.033799998462200165, 0.16030000150203705, -0.07460000365972519, -0.05469999834895134, -0.03660000115633011, 0.04610000178217888, 0.041999999433755875, -0.2863999903202057, 0.11869999766349792, 0.0012000000569969416, 0.08100000023841858, -0.10300000011920929, 0.039400000125169754, -0.06289999932050705, -0.218299999833107, 0.03799999877810478, -0.04650000110268593, 0.1339000016450882, 0.01860000006854534, 0.07169999927282333, -0.18569999933242798, 0.15060000121593475, 0.04610000178217888, -0.11309999972581863, 0.23520000278949738, 0.03709999844431877, -0.31279999017715454, 0.1800999939441681, 0.6043999791145325, -0.22259999811649323, 0.2606000006198883, -0.062199998646974564, -0.08070000261068344, 0.13220000267028809, -0.034299999475479126, 0.05829999968409538, -0.07479999959468842, 0.26910001039505005], [0.10369999706745148, -0.05939999967813492, 0.14300000667572021, -0.28690001368522644, -0.12099999934434891, -0.2603999972343445, 0.15049999952316284, -0.1193000003695488, -0.08020000159740448, 0.28679999709129333, -0.1843000054359436, -0.026200000196695328, 0.002300000051036477, -0.29350000619888306, 0.004999999888241291, -0.2653999924659729, 0.13030000030994415, 0.12160000205039978, 0.2727000117301941, 0.09290000051259995, -0.2994999885559082, 0.271699994802475, 0.33730000257492065, -0.06129999831318855, -0.35179999470710754, 0.08609999716281891, -0.14010000228881836, -0.054499998688697815, -0.03060000017285347, 0.20409999787807465, -0.051100000739097595, 0.1386999934911728, -0.1445000022649765, -0.2547000050544739, -0.20029999315738678, -0.06769999861717224, -0.05480000004172325, -0.2224999964237213, -0.12950000166893005, -0.04320000112056732, -0.08609999716281891, 0.01860000006854534, -0.05829999968409538, 0.12280000001192093, 0.11219999939203262, 0.10409999638795853, -0.4309999942779541, -0.09870000183582306, -0.07989999651908875, 0.0738999992609024, 0.12939999997615814, -0.03200000151991844, -0.2021999955177307, -0.14350000023841858, 0.1673000007867813, -0.16509999334812164, -0.25540000200271606, 0.2808000147342682, 0.05130000039935112, 0.04439999908208847, -0.09730000048875809, -0.14890000224113464, 0.2687999904155731, 0.31470000743865967], [0.05400000140070915, -0.12449999898672104, -0.15700000524520874, 0.26330000162124634, -0.014600000344216824, -0.054499998688697815, 0.0754999965429306, 0.11389999836683273, 0.11020000278949738, 0.05139999836683273, -0.09059999883174896, -0.12399999797344208, 0.17730000615119934, -0.01979999989271164, -0.06289999932050705, -0.10209999978542328, -0.06030000001192093, -0.0934000015258789, -0.2475000023841858, 0.09860000014305115, 0.16179999709129333, -0.186599999666214, -0.030300000682473183, 0.3483999967575073, -0.1599999964237213, -0.06509999930858612, 0.3098999857902527, -0.21119999885559082, -0.007499999832361937, -0.07190000265836716, -0.12099999934434891, 0.2493000030517578, 0.12099999934434891, 0.26969999074935913, -0.18000000715255737, 0.2500999867916107, 0.2337999939918518, 0.2678999900817871, 0.02850000001490116, 0.11169999837875366, -0.0908999964594841, 0.1860000044107437, 0.08110000193119049, -0.08420000225305557, -0.09130000323057175, -0.22110000252723694, 0.09459999948740005, 0.039000000804662704, -0.12470000237226486, -0.07280000299215317, -0.17569999396800995, -0.050200000405311584, 0.2142000049352646, 0.10819999873638153, -0.22040000557899475, 0.12559999525547028, 0.25290000438690186, 0.019300000742077827, -0.08560000360012054, -0.10930000245571136, 0.2498999983072281, 0.19789999723434448, -0.0430000014603138, -0.2522999942302704], [0.037300001829862595, 0.021800000220537186, -0.01140000019222498, -0.10090000182390213, 0.08269999921321869, -0.014100000262260437, 0.05640000104904175, -0.010099999606609344, 0.05380000174045563, -0.0885000005364418, -0.02199999988079071, 0.0617000013589859, -0.14710000157356262, -0.29409998655319214, 0.15029999613761902, -0.007600000128149986, -0.021900000050663948, 0.22010000050067902, 0.15230000019073486, 0.04690000042319298, -0.17030000686645508, 0.0763000026345253, -0.07190000265836716, -0.04149999842047691, -0.1696999967098236, -0.2540000081062317, -0.026499999687075615, 0.11420000344514847, 0.0812000036239624, -0.06379999965429306, -0.10570000112056732, -0.23909999430179596, -0.06210000067949295, 0.024399999529123306, 0.05260000005364418, 0.06880000233650208, -0.1388999968767166, 0.2743000090122223, 0.17520000040531158, -0.17890000343322754, -0.04740000143647194, -0.06480000168085098, 0.06459999829530716, -0.2079000025987625, -0.08669999986886978, 0.06700000166893005, -0.07159999758005142, -0.06599999964237213, -0.045899998396635056, 0.12449999898672104, -0.0869999974966</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>[0.5454343890264206]</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>[0.10376215938503779]</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>[0.2877313278871422]</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>[0.16261326763615402]</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>[-5.224187420949524]</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>[2.0370501579109845]</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>[0.6410231793445451]</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>[0.08246382252744014]</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>[-0.007724913909059383]</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>[0.23899307564347883]</t>
+        </is>
+      </c>
+      <c r="O24" t="inlineStr">
+        <is>
+          <t>[-1.1066488565998922]</t>
+        </is>
+      </c>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>[0.6925554261883751]</t>
+        </is>
+      </c>
+      <c r="Q24" t="inlineStr">
+        <is>
+          <t>[-0.12434770037993514]</t>
+        </is>
+      </c>
+      <c r="R24" t="inlineStr">
+        <is>
+          <t>[0.1212336104542925]</t>
+        </is>
+      </c>
+      <c r="S24" t="inlineStr">
+        <is>
+          <t>[-0.08983098332977746]</t>
+        </is>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>[0.09182952893559941]</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>[-1.0459794347519722]</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>[0.19564295865117268]</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>[-0.23001768079368778]</t>
+        </is>
+      </c>
+      <c r="X24" t="inlineStr">
+        <is>
+          <t>[0.1288574192227519]</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>[-0.12630413799629858]</t>
+        </is>
+      </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>[0.0926871826163661]</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>[-1.5431599742162905]</t>
+        </is>
+      </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>[0.23398184228801966]</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>[-0.9285718765806514]</t>
+        </is>
+      </c>
+      <c r="AD24" t="inlineStr">
+        <is>
+          <t>[0.16160655379741545]</t>
+        </is>
+      </c>
+      <c r="AE24" t="inlineStr">
+        <is>
+          <t>[-0.686707313692321]</t>
+        </is>
+      </c>
+      <c r="AF24" t="inlineStr">
+        <is>
+          <t>[0.1816213950827286]</t>
+        </is>
+      </c>
+      <c r="AG24" t="inlineStr">
+        <is>
+          <t>[-2.6447557583341923]</t>
+        </is>
+      </c>
+      <c r="AH24" t="inlineStr">
+        <is>
+          <t>[0.2713519147799111]</t>
+        </is>
+      </c>
+      <c r="AI24" t="inlineStr">
+        <is>
+          <t>[-1.404426905040013]</t>
+        </is>
+      </c>
+      <c r="AJ24" t="inlineStr">
+        <is>
+          <t>[0.19704010822618437]</t>
+        </is>
+      </c>
+      <c r="AK24" t="inlineStr">
+        <is>
+          <t>[-0.6619323490328934]</t>
+        </is>
+      </c>
+      <c r="AL24" t="inlineStr">
+        <is>
+          <t>[0.17640194247357577]</t>
+        </is>
+      </c>
+      <c r="AM24" t="inlineStr">
+        <is>
+          <t>[-2.80267806140394]</t>
+        </is>
+      </c>
+      <c r="AN24" t="inlineStr">
+        <is>
+          <t>[0.2920732430256689]</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>model_64_32_3</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>[64, 32]</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>[[[0.025800000876188278, -0.06419999897480011, -0.005400000140070915, 0.029899999499320984, 0.02449999935925007, -0.04399999976158142, -0.07069999724626541, 0.009800000116229057, -0.008299999870359898, -0.02370000071823597, 0.05350000038743019, 0.012000000104308128, 0.05649999901652336, -0.08569999784231186, -0.01899999938905239, 0.1006999984383583, 0.043699998408555984, 0.05550000071525574, -0.012400000356137753, 0.024900000542402267, -0.02850000001490116, 0.019300000742077827, -0.030400000512599945, -0.006000000052154064, 0.017100000753998756, 0.026000000536441803, 0.024000000208616257, -0.00559999980032444, 0.03750000149011612, 0.023600000888109207, 0.04470000043511391, -0.11550000309944153, -0.05739999935030937, -0.038600001484155655, 0.09920000284910202, -0.01850000023841858, 0.06840000301599503, 0.01769999973475933, 0.0771000012755394, -9.999999747378752e-05, -0.06710000336170197, 0.0414000004529953, 0.03220000118017197, 0.006500000134110451, 9.999999747378752e-05, 0.05260000005364418, -0.08470000326633453, -0.0406000018119812, -0.024700000882148743, 0.05829999968409538, 0.020400000736117363, 0.018699999898672104, 0.021900000050663948, -0.09279999881982803, -0.046799998730421066, -0.05609999969601631, 0.025499999523162842, 0.016599999740719795, 0.04809999838471413, -0.06289999932050705, 0.06310000270605087, -0.032999999821186066, 0.0071000000461936, 0.06989999860525131], [0.03819999843835831, -0.040699999779462814, 0.04129999876022339, -0.031599998474121094, 0.039400000125169754, -0.06400000303983688, -0.03060000017285347, 0.08089999854564667, -0.13809999823570251, 0.01510000042617321, -0.051500000059604645, -0.1128000020980835, 0.018699999898672104, -0.013700000010430813, 0.04520000144839287, -0.012199999764561653, -0.02500000037252903, 0.019500000402331352, 0.045899998396635056, 0.03240000084042549, 0.011500000022351742, 0.0210999995470047, -0.015599999576807022, -0.021199999377131462, 0.041200000792741776, -0.023000000044703484, 0.0007999999797903001, -0.02669999934732914, 0.04479999840259552, -0.058400001376867294, -0.04749999940395355, 0.03579999879002571, 0.03180000185966492, 0.07940000295639038, -0.07440000027418137, -0.11640000343322754, 0.11949999630451202, 0.03220000118017197, 0.015200000256299973, 0.04619999974966049, -0.008299999870359898, -0.04989999905228615, 0.002899999963119626, 0.01940000057220459, 0.011099999770522118, 0.06419999897480011, -0.0649000033736229, -0.05299999937415123, -0.009700000286102295, -0.039400000125169754, 0.012799999676644802, 0.03830000013113022, -0.018300000578165054, -0.007300000172108412, -0.023900000378489494, -0.06970000267028809, 0.039799999445676804, 0.019999999552965164, 0.025699999183416367, 0.03280000016093254, -0.013299999758601189, -0.05979999899864197, 0.08389999717473984, -0.048700001090765]], [[0.15070000290870667, -0.18950000405311584, -0.07180000096559525, 0.15700000524520874, 0.009200000204145908, 0.09769999980926514, -0.19359999895095825, -0.05790000036358833, -0.08410000056028366, 0.10329999774694443, -0.09749999642372131, 0.27970001101493835, 0.11219999939203262, -0.10620000213384628, -0.026599999517202377, 0.08489999920129776, -0.12999999523162842, -0.11020000278949738, -0.2345999926328659, -0.09749999642372131, -0.025599999353289604, 0.10209999978542328, 0.03280000016093254, -0.05590000003576279, -0.01209999993443489, -0.05050000175833702, -0.05350000038743019, -0.08250000327825546, 0.4259999990463257, 0.012900000438094139, 0.06120000034570694, -0.28209999203681946, -0.10740000009536743, 0.006899999920278788, -0.10080000013113022, 0.22529999911785126, 0.07349999994039536, -0.1371999979019165, -0.06310000270605087, -0.034299999475479126, 0.09790000319480896, -0.019500000402331352, 0.11159999668598175, 0.08780000358819962, -0.006399999838322401, -0.08969999849796295, -0.00039999998989515007, -0.017799999564886093, -0.16009999811649323, 0.1307000070810318, 0.02969999983906746, 0.04830000177025795, -0.043800000101327896, -0.025200000032782555, 0.043299999088048935, -0.03200000151991844, 0.06440000236034393, -0.1678999960422516, -0.1264999955892563, -0.10989999771118164, 0.2775000035762787, 0.03669999912381172, 0.030400000512599945, 0.07850000262260437], [0.15729999542236328, 0.1657000035047531, -0.08709999918937683, -0.07959999889135361, 0.26030001044273376, -0.04100000113248825, -0.04809999838471413, -0.0658000037074089, -0.0917000025510788, 0.10249999910593033, -0.19480000436306, 0.08760000020265579, -0.12729999423027039, -0.0203000009059906, 0.1453000009059906, -0.09070000052452087, -0.24979999661445618, 0.10570000112056732, -0.02630000002682209, 0.09309999644756317, -0.16120000183582306, -0.06800000369548798, -0.056299999356269836, 0.10090000182390213, -0.12439999729394913, -0.06909999996423721, -0.16580000519752502, -0.21379999816417694, -0.16979999840259552, 0.0625, -0.22130000591278076, -0.06679999828338623, 0.06469999998807907, 0.09759999811649323, 0.09889999777078629, 0.02410000003874302, 0.023499999195337296, -0.04439999908208847, -0.08749999850988388, 0.053199999034404755, 0.026399999856948853, 0.1703999936580658, -0.017500000074505806, -0.009100000374019146, 0.04619999974966049, 0.26820001006126404, -0.05180000141263008, -0.01940000057220459, -0.09780000150203705, 0.30869999527931213, 0.13779999315738678, -0.14830000698566437, -0.03840000182390213, 0.05719999969005585, 0.06019999831914902, 0.1559000015258789, 0.028999999165534973, -0.21050000190734863, -0.03220000118017197, -0.00279999990016222, -0.2224999964237213, -0.10970000177621841, -0.022700000554323196, -0.09839999675750732], [-0.06440000236034393, -0.094200000166893, 0.05310000106692314, 0.09059999883174896, 0.0949999988079071, -0.031300000846385956, -0.030899999663233757, -0.23190000653266907, 0.14300000667572021, -0.16410000622272491, -0.10819999873638153, -0.09759999811649323, 0.2567000091075897, 0.07720000296831131, 0.38850000500679016, -0.07109999656677246, 0.10540000349283218, -0.08590000122785568, -0.13539999723434448, -0.018200000748038292, -0.12300000339746475, 0.04659999907016754, 0.11670000106096268, 0.07360000163316727, 0.014999999664723873, 0.09229999780654907, -0.07159999758005142, -0.020099999383091927, 0.032999999821186066, -0.02500000037252903, -0.04439999908208847, -0.16760000586509705, 0.029400000348687172, -0.13510000705718994, -0.039500001817941666, -0.027400000020861626, 0.05510000139474869, 0.15629999339580536, 0.05810000002384186, 0.08889999985694885, -0.003100000089034438, -0.06830000132322311, -0.03889999911189079, 0.07919999957084656, -0.21549999713897705, 0.11680000275373459, -0.06520000100135803, -0.008200000040233135, -0.06109999865293503, -0.04479999840259552, 0.07020000368356705, 0.14219999313354492, 0.2962999939918518, 0.07680000364780426, 0.04809999838471413, -0.03880000114440918, -0.08250000327825546, 0.13850000500679016, -0.18400000035762787, 0.03709999844431877, -0.12080000340938568, -0.07209999859333038, -0.38530001044273376, 0.01940000057220459], [-0.2522999942302704, -0.16779999434947968, 0.0284000001847744, -0.08739999681711197, -0.06430000066757202, 0.05339999869465828, -0.043800000101327896, -0.20880000293254852, 0.289000004529953, 0.11029999703168869, 0.11630000174045563, -0.011699999682605267, -0.17139999568462372, -0.03420000150799751, 0.01850000023841858, -0.1200999990105629, -0.07639999687671661, 0.17419999837875366, -0.012900000438094139, -0.08290000259876251, -0.12370000034570694, 0.08330000191926956, -0.0142000000923872, -0.31470000743865967, 0.003700000001117587, -0.010400000028312206, 0.1168999969959259, -0.048500001430511475, -0.02500000037252903, -0.20640000700950623, 0.05050000175833702, -0.16449999809265137, 0.007499999832361937, 0.1216999962925911, -0.06369999796152115, 0.05640000104904175, -0.2685000002384186, -0.04259999841451645, 0.06289999932050705, -0.10369999706745148, 0.10109999775886536, -0.019700000062584877, -0.015300000086426735, 0.19769999384880066, 0.0949999988079071, 0.04490000009536743, 0.059700001031160355, -0.1746000051498413, 0.13009999692440033, 0.1412999927997589, -0.032600000500679016, 0.07159999758005142, -0.045499999076128006, 0.013700000010430813, -0.23829999566078186, -0.11379999667406082, 0.0010999999940395355, -0.10599999874830246, -0.10899999737739563, 0.026900000870227814, -0.1914999932050705, 0.09260000288486481, -0.014600000344216824, -0.2206999957561493], [0.2101999968290329, -0.11559999734163284, 0.2750999927520752, -0.033900000154972076, -0.1404000073671341, 0.15780000388622284, -0.05909999832510948, -0.08399999886751175, -0.05220000073313713, 0.03889999911189079, 0.09759999811649323, 0.1527000069618225, -0.07150000333786011, 0.10019999742507935, -0.013899999670684338, 0.1386999934911728, 0.09109999984502792, 0.08900000154972076, -0.22089999914169312, 0.1324000060558319, 0.07519999891519547, 0.10270000249147415, -0.11270000040531158, -0.09399999678134918, 0.050599999725818634, -0.11309999972581863, -0.22120000422000885, 0.05990000069141388, 0.10170000046491623, 0.03449999913573265, -0.14810000360012054, 0.16189999878406525, 0.050999999046325684, -0.057500001043081284, 0.20739999413490295, 0.11840000003576279, 0.0786999985575676, -0.04360000044107437, 0.12030000239610672, -0.0560000017285347, 0.2678999900817871, 0.06080000102519989, -0.02710000053048134, -0.010999999940395355, 0.04089999943971634, 0.05130000039935112, -0.09870000183582306, -0.15479999780654907, 0.13249999284744263, -0.09269999712705612, -0.10520000010728836, -0.05810000002384186, 0.025800000876188278, 0.29899999499320984, 0.022299999371170998, -0.14429999887943268, -0.05739999935030937, 0.12060000002384186, 0.20090000331401825, -0.025100000202655792, -0.16699999570846558, -0.20730000734329224, -0.07339999824762344, -0.02979999966919422], [0.057500001043081284, -0.10530000180006027, 0.1436000019311905, -0.012799999676644802, 0.22769999504089355, -0.07079999893903732, 0.11900000274181366, -0.22550000250339508, -0.06539999693632126, -0.1379999965429306, 0.1517000049352646, -0.14800000190734863, 0.12030000239610672, -0.07360000163316727, -0.14309999346733093, 0.04230000078678131, 0.028200000524520874, 0.19189999997615814, 0.2150000035762787, -0.13609999418258667, 0.06469999998807907, -0.032999999821186066, -0.019200000911951065, 0.16760000586509705, 0.08860000222921371, -0.11150000244379044, -0.13989999890327454, -0.03539999946951866, -0.10750000178813934, 0.044199999421834946, -0.007899999618530273, -0.19480000436306, -0.24310000240802765, 0.16210000216960907, 0.08190000057220459, -0.13300000131130219, 0.05530000105500221, -0.16089999675750732, 0.10289999842643738, -0.05959999933838844, 0.1712000072002411, -0.023399999365210533, 0.2540000081062317, 0.1835000067949295, -0.03539999946951866, -0.0364999994635582, -0.02850000001490116, -0.03290000185370445, 0.00430000014603138, -0.06870000064373016, -0.030500000342726707, -0.19859999418258667, 0.15039999783039093, 0.0038999998942017555, 0.08290000259876251, 0.004600000102072954, 0.241799995303154, 0.093299999833107, -0.09600000083446503, 0.03709999844431877, 0.1468999981880188, -0.04560000076889992, 0.0771000012755394, -0.19089999794960022], [0.05939999967813492, -0.061000000685453415, 0.05090000107884407, -0.07490000128746033, -0.05810000002384186, 0.053599998354911804, 0.04820000007748604, -0.055799998342990875, 0.00279999990016222, 0.04230000078678131, -0.020899999886751175, 0.038600001484155655, -0.09809999912977219, -0.015200000256299973, -0.21809999644756317, -0.04529999941587448, -0.17219999432563782, -0.31630000472068787, 0.01080000028014183, -0.14730000495910645, -0.18119999766349792, -0.021800000220537186, 0.09049999713897705, 0.1973000019788742, 0.03189999982714653, 0.19609999656677246, 0.22589999437332153, 0.15060000121593475, 0.06310000270605087, -0.05640000104904175, -0.11140000075101852, -0.011500000022351742, 0.2021999955177307, -0.02630000002682209, 0.11949999630451202, -0.19550000131130219, 0.16680000722408295, 0.0689999982714653, -0.11159999668598175, 0.01549999974668026, 0.25360000133514404, -0.07620000094175339, 0.2912999987602234, 0.11050000041723251, -0.031099999323487282, 0.0502999983727932, -0.05649999901652336, -0.12210000306367874, -0.21070000529289246, -0.18310000002384186, -0.000699999975040555, -0.11029999703168869, -0.050999999046325684, -0.003599999938160181, -0.12070000171661377, 0.01899999938905239, -0.21539999544620514, -0.07410000264644623, -0.004000000189989805, 0.17090000212192535, -0.15230000019073486, 0.0471000000834465, 0.02250000089406967, -0.04439999908208847], [-0.15489999949932098, 0.10239999741315842, 0.07639999687671661, -0.009700000286102295, 0.1598999947309494, 0.1103999987244606, 0.05990000069141388, 0.2890999913215637, 0.15399999916553497, -0.054499998688697815, -0.0551999993622303, 0.023900000378489494, 0.10949999839067459, -0.05869999900460243, -0.009499999694526196, 0.16760000586509705, -0.031300000846385956, -0.039000000804662704, 0.1543000042438507, 0.012400000356137753, 0.008299999870359898, 0.1023000031709671, -0.14730000495910645, -0.17059999704360962, -0.13130000233650208, 0.10729999840259552, 0.016599999740719795, -0.19349999725818634, 0.06210000067949295, 0.08649999648332596, -0.07069999724626541, -0.13439999520778656, 0.07320000231266022, -0.11389999836683273, 0.051500000059604645, 0.08699999749660492, 0.3474999964237213, -0.19030000269412994, 0.16599999368190765, 0.21950000524520874, -0.040300000458955765, 0.19099999964237213, 0.08789999783039093, 0.09449999779462814, -0.07429999858140945, 0.12380000203847885, 0.08760000020265579, -0.03720000013709068, 0.031099999323487282, 0.03269999846816063, 0.12720000743865967, 0.045899998396635056, 0.038100000470876694, -0.032499998807907104, -0.1762000024318695, -0.21240000426769257, -0.006599999964237213, 0.1695999950170517, 0.18790000677108765, 0.12319999933242798, 0.009700000286102295, 0.18569999933242798, 0.06270000338554382, -0.09690000116825104], [0.08089999854564667, 0.018300000578165054, -0.08810000121593475, -0.03290000185370445, -0.03680000081658363, 0.11789999902248383, -0.12309999763965607, -0.03449999913573265, -0.35589998960494995, -0.1446000039577484, -0.10989999771118164, 0.00800000037997961, -0.1265999972820282, -0.35280001163482666, -0.07880000025033951, 0.009700000286102295, -0.004699999932199717, 0.022199999541044235, 0.1573999971151352, 0.11779999732971191, -0.009600000455975533, 0.04670000076293945, -0.06780000030994415, -0.023600000888109207, 0.08829999715089798, 0.07680000364780426, 0.08370000123977661, -0.093299999833107, -0.09470000118017197, -0.3407000005245209, 0.09210000187158585, -0.07739999890327454, 0.20340000092983246, -0.025200000032782555, -0.07079999893903732, 0.05860000103712082, 0.12780000269412994, 0.09059999883174896, 0.09139999747276306, 0.01979999989271164, -0.0430000014603138, -0.008299999870359898, 0.011699999682605267, 0.10360000282526016, 0.10180000215768814, 0.13950000703334808, -0.1404000073671341, 0.011099999770522118, 0.10459999740123749, -0.13699999451637268, -0.09239999949932098, 0.12880000472068787, 0.06509999930858612, -0.17509999871253967, -0.08579999953508377, -0.0010999999940395355, 0.03539999946951866, 0.08009999990463257, 0.009800000116229057, -0.2825999855995178, 0.0714000016450882, -0.22660000622272491, -0.1695999950170517, -0.12070000171661377], [-0.09239999949932098, -0.02889999933540821, -0.057500001043081284, 0.016899999231100082, 0.09960000216960907, 0.0203000009059906, -0.025299999862909317, -0.031300000846385956, -0.10670000314712524, -0.09690000116825104, 0.020500000566244125, 0.2345999926328659, -0.14329999685287476, -0.05480000004172325, 0.2214999943971634, -0.022700000554323196, 0.09109999984502792, -0.07429999858140945, 0.014399999752640724, -0.007300000172108412, -0.05829999968409538, 0.025599999353289604, -0.10369999706745148, 0.15160000324249268, -0.25999999046325684, -0.1136000007390976, 0.12200000137090683, 0.337799996137619, -0.15780000388622284, 0.004600000102072954, 0.12280000001192093, -0.15139999985694885, 0.039400000125169754, -0.019500000402331352, 0.023600000888109207, -0.017899999395012856, -0.025200000032782555, -0.15680000185966492, 0.02669999934732914, -0.15719999372959137, 0.15639999508857727, 0.060100000351667404, -0.0877000018954277, -0.031599998474121094, -0.008899999782443047, 0.08290000259876251, -0.11209999769926071, -0.023800000548362732, 0.09889999777078629, -0.11800000071525574, 0.23520000278949738, 0.019600000232458115, -0.14350000023841858, 0.02800000086426735, -0.16920000314712524, -0.09399999678134918, 0.304500013589859, 0.11410000175237656, -0.058800000697374344, 0.14239999651908875, -0.005799999926239252, -0.017999999225139618, 0.05730000138282776, 0.34619998931884766], [0.11800000071525574, 0.007699999958276749, -0.06669999659061432, 0.027300000190734863, 0.07670000195503235, -0.06030000001192093, -0.027400000020861626, 0.1876000016927719, -0.03020000085234642, -0.298799991607666, -0.08429999649524689, -0.0835999995470047, -0.026000000536441803, 0.14480000734329224, 0.03500000014901161, 0.21960000693798065, 0.02250000089406967, 0.00039999998989515007, 0.09350000321865082, 0.03889999911189079, -0.421099990606308, -0.07720000296831131, 0.0024999999441206455, -0.14589999616146088, 0.2500999867916107, -0.1695999950170517, 0.09440000355243683, 0.007000000216066837, 0.021900000050663948, 0.07859999686479568, 0.22210000455379486, -0.07349999994039536, 0.021900000050663948, -0.14139999449253082, 0.11219999939203262, 0.1914999932050705, -0.24979999661445618, 0.0012000000569969416, -0.11270000040531158, 0.017899999395012856, 0.15330000221729279, -0.22110000252723694, 0.09520000219345093, -0.02370000071823597, 0.13940000534057617, 0.11490000039339066, 0.08900000154972076, 0.15189999341964722, -0.08100000023841858, 0.04179999977350235, 0.02930000051856041, -0.1289999932050705, -0.12080000340938568, 0.07490000128746033, 0.03959999978542328, -0.08169999718666077, -0.0210999995470047, 0.15970000624656677, 0.03959999978542328, 0.007899999618530273, -0.025200000032782555, 0.011699999682605267, -0.03449999913573265, -0.09189999848604202], [0.010999999940395355, -0.2752000093460083, -0.2646999955177307, -0.028599999845027924, 0.11490000039339066, -0.147599995136261, -0.07050000131130219, -0.21979999542236328, 0.028699999675154686, -0.001500000013038516, -0.07840000092983246, 0.12370000034570694, 0.10859999805688858, -0.1688999980688095, -0.08139999955892563, 0.14749999344348907, -0.012900000438094139, -0.19910000264644623, -0.058400001376867294, 0.06390000134706497, 0.13089999556541443, 0.11919999867677689, -0.06679999828338623, 0.03790000081062317, -0.08420000225305557, 0.09589999914169312, 0.0210999995470047, 0.058800000697374344, -0.08569999784231186, -0.006599999964237213, 0.14499999582767487, 0.056699998676776886, -0.03680000081658363, -0.10930000245571136, 0.24250000715255737, -0.10289999842643738, -0.05770000070333481, -0.03739999979734421, 0.16670000553131104, 0.210999995470047, -0.11020000278949738, -0.12720000743865967, -0.321399986743927, 0.08160000294446945, -0.08699999749660492, 0.002899999963119626, 0.041200000792741776, 0.20679999887943268, -0.032600000500679016, 0.08810000121593475, -0.19370000064373016, -0.21619999408721924, -0.08699999749660492, 0.10419999808073044, -0.048900000751018524, -0.06689999997615814, -0.035100001841783524, 0.006300000008195639, 0.022199999541044235, 0.03440000116825104, -0.10239999741315842, -0.013199999928474426, 0.15600000321865082, -0.17659999430179596], [-0.19329999387264252, 0.0008999999845400453, 0.12070000171661377, -0.15449999272823334, -0.009700000286102295, 0.11590000241994858, -0.04879999905824661, 0.05979999899864197, 0.0406000018119812, 0.039500001817941666, 0.03440000116825104, -0.26429998874664307, -0.11670000106096268, 0.09059999883174896, -0.06159999966621399, -0.19429999589920044, 0.0940999984741211, -0.2071000039577484, -0.21170000731945038, 0.27320000529289246, -0.03779999911785126, 0.062199998646974564, -0.364300012588501, 0.23829999566078186, 0.03460000082850456, 0.08669999986886978, -0.0729999989271164, 0.026200000196695328, -0.12409999966621399, -0.02889999933540821, 0.09369999915361404, -0.1451999992132187, -0.035100001841783524, -0.13289999961853027, 0.10320000350475311, 0.08619999885559082, 0.025699999183416367, 0.042100001126527786, -0.07599999755620956, -0.013500000350177288, 0.18690000474452972, -0.027300000190734863, 0.003000000026077032, 0.07419999688863754, -0.1492999941110611, -0.016699999570846558, 0.1850000023841858, 0.04690000042319298, 0.01889999955892563, 0.17520000040531158, -0.0843999981880188, 0.04050000011920929, -0.09939999878406525, -0.09960000216960907, 0.12970000505447388, -0.010099999606609344, 0.10289999842643738, -0.15469999611377716, 0.09000000357627869, -0.006399999838322401, 0.24539999663829803, -0.029600000008940697, -0.09700000286102295, -0.07039999961853027], [-0.1889999955892563, -0.04399999976158142, -0.22660000622272491, 0.20319999754428864, 0.0203000009059906, 0.024299999698996544, -0.13279999792575836, 0.0357000008225441, 0.02889999933540821, 0.10830000042915344, 0.260699987411499, -0.0272000003606081, 0.0892999991774559, 0.15330000221729279, -0.059300001710653305, 0.041200000792741776, 0.02319999970495701, 0.012900000438094139, -0.04399999976158142, 0.07900000363588333, 0.029400000348687172, -0.042899999767541885, 0.03909999877214432, -0.04830000177025795, 0.03440000116825104, 0.03539999946951866, 0.1696999967098236, -0.23000000417232513, -0.11270000040531158, -0.07360000163316727, -0.22699999809265137, -0.20020000636577606, 0.024700000882148743, 0.07989999651908875, -0.18479999899864197, 0.02459999918937683, 0.17069999873638153, -0.10119999945163727, -0.28839999437332153, 0.04600000008940697, 0.164000004529953, -0.14239999651908875, -0.26759999990463257, -0.09740000218153, 0.10100000351667404, 0.015300000086426735, -0.07959999889135361, 0.05079999938607216, -0.09539999812841415, -0.25429999828338623, -0.04039999842643738, -0.1509000062942505, 0.01759999990463257, 0.03819999843835831, 0.10499999672174454, -0.04560000076889992, 0.16930000483989716, 0.0, 0.17010000348091125, 0.08470000326633453, -0.06199999898672104, -0.1526000052690506, -0.036400001496076584, -0.04769999906420708], [0.0812000036239624, 0.01810000091791153, -0.13500000536441803, 0.18809999525547028, -0.07970000058412552, -0.12049999833106995, -0.052400000393390656, 0.008700000122189522, 0.15230000019073486, 0.05810000002384186, 0.1273999959230423, -0.005799999926239252, -0.06440000236034393, 0.11230000108480453, 0.007899999618530273, 0.1590999960899353, 0.16590000689029694, -0.04969999939203262, 0.17000000178813934, 0.17489999532699585, -0.018799999728798866, -0.09440000355243683, -0.03460000082850456, 0.13609999418258667, -0.10750000178813934, 0.18410000205039978, 0.0010999999940395355, 0.005400000140070915, 0.08030000329017639, -0.12540000677108765, -0.06689999997615814, 0.16089999675750732, -0.2240000069141388, 0.0544000007212162, -0.03819999843835831, 0.25949999690055847, 0.0215000007301569, 0.22450000047683716, 0.1876000016927719, 0.04270000010728836, 0.21459999680519104, 0.1143999993801117, 0.07800000160932541, 0.07930000126361847, 0.1062999963760376, 0.05550000071525574, 0.01549999974668026, 0.1200999990105629, -0.05209999904036522, 0.08910000324249268, 0.14480000734329224, 0.1395999938249588, 0.053199999034404755, -0.06400000303983688, -0.15440000593662262, 0.059700001031160355, -0.04879999905824661, -0.004600000102072954, -0.2110999971628189, 0.164900004863739, 0.03669999912381172, -0.3050000071525574, 0.20890000462532043, -0.07940000295639038], [-0.16830000281333923, -0.04769999906420708, 0.125900000333786, 0.11420000344514847, 0.30149999260902405, 0.042899999767541885, 0.1103999987244606, 0.002199999988079071, -0.007000000216066837, 0.05380000174045563, 0.03370000049471855, 0.05810000002384186, -0.04270000010728836, 0.2029000073671341, 0.05180000141263008, 0.18870000541210175, -0.06830000132322311, 0.21459999680519104, -0.035599999129772186, 0.013899999670684338, 0.1598999947309494, 0.12060000002384186, -0.10450000315904617, -0.08229999989271164, -0.18549999594688416, 0.0471000000834465, 0.03889999911189079, -0.06310000270605087, 0.11699999868869781, -0.2190999984741211, 0.15700000524520874, 0.0957999974489212, 0.02419999986886978, -0.15150000154972076, 0.04809999838471413, -0.15189999341964722, 0.04170000180602074, 0.24210000038146973, -0.19449999928474426, 0.04619999974966049, 0.048700001090765, -0.1354999989271164, 0.20309999585151672, -0.03550000116229057, 0.026599999517202377, 0.09809999912977219, -0.323199987411499, 0.059700001031160355, 0.121799997985363, 0.14900000393390656, -0.14309999346733093, -0.13609999418258667, -0.10729999840259552, -0.17890000343322754, 0.1111999973654747, -0.002400000113993883, -0.07039999961853027, 0.01899999938905239, -0.11219999939203262, 0.011500000022351742, 0.020500000566244125, 0.00860000029206276, 0.01940000057220459, 0.1324000060558319], [0.06989999860525131, -0.1492999941110611, 0.04690000042319298, -0.027300000190734863, 0.035100001841783524, 0.18369999527931213, -0.2632000148296356, 0.05920000001788139, 0.12399999797344208, 0.015699999406933784, 0.14159999787807465, 0.11249999701976776, -0.04690000042319298, 0.18700000643730164, 0.09560000151395798, 0.22200000286102295, -0.0812000036239624, -0.06880000233650208, 0.10740000009536743, 0.12780000269412994, 0.07400000095367432, -0.2061000019311905, 0.13899999856948853, 0.16990000009536743, -0.10379999876022339, 0.0729999989271164, 0.11150000244379044, 0.05920000001788139, 0.07989999651908875, 0.035599999129772186, -0.12430000305175781, -0.00930000003427267, 0.06300000101327896, 0.19990000128746033, 0.0843999981880188, -0.09629999846220016, -0.09200000017881393, 0.10010000318288803, 0.04019999876618385, -0.22349999845027924, -0.14569999277591705, 0.04670000076293945, -0.020600000396370888, 0.17509999871253967, -0.052799999713897705, 0.3084000051021576, 0.1800999939441681, 0.06520000100135803, 0.09059999883174896, -0.042399998754262924, -0.04729999974370003, -0.02199999988079071, -0.014100000262260437, -0.05620000138878822, 0.13779999315738678, 0.05290000140666962, 0.08330000191926956, 0.11129999905824661, 0.052000001072883606, -0.2493000030517578, 0.08780000358819962, 0.25369998812675476, -0.08070000261068344, -0.0868000015616417], [-0.012199999764561653, 0.1412999927997589, -0.023600000888109207, -0.1152999997138977, 0.06120000034570694, 0.27090001106262207, 0.1265999972820282, -0.03020000085234642, 0.03889999911189079, -0.188400000333786, 0.05609999969601631, 0.006599999964237213, 0.022199999541044235, -0.07050000131130219, 0.11540000140666962, -0.03420000150799751, 0.01810000091791153, -0.024299999698996544, -0.12880000472068787, 0.015300000086426735, 0.1111999973654747, 0.17110000550746918, 0.14790000021457672, -0.08820000290870667, -0.09809999912977219, -0.03819999843835831, 0.21729999780654907, 0.26739999651908875, -0.04450000077486038, -0.009600000455975533, -0.25679999589920044, -0.15109999477863312, -0.026799999177455902, 0.11150000244379044, -0.07429999858140945, -0.003599999938160181, -0.07490000128746033, -0.07779999822378159, 0.0015999999595806003, -0.05620000138878822, -0.06809999793767929, -0.0003000000142492354, 0.12439999729394913, 0.14429999887943268, 0.10499999672174454, -0.14869999885559082, -0.056699998676776886, 0.3003999888896942, -0.08619999885559082, 0.23929999768733978, 0.01080000028014183, 0.0406000018119812, -0.04500000178813934, 0.007899999618530273, 0.17350000143051147, 0.0215000007301569, -0.23010000586509705, 0.1428000032901764, 0.18930000066757202, 0.026900000870227814, 0.044199999421834946, -0.2678999900817871, 0.09380000084638596, -0.09809999912977219], [0.0697999969124794, 0.09939999878406525, -0.06790000200271606, 0.04619999974966049, -0.0649000033736229, 0.18449999392032623, 0.07039999961853027, 0.07259999960660934, -0.09910000115633011, 0.09130000323057175, -0.2053000032901764, -0.15160000324249268, -0.006300000008195639, -0.032099999487400055, 0.08760000020265579, 0.1761000007390976, 0.22859999537467957, 0.1103999987244606, -0.04259999841451645, 0.01640000008046627, 0.10499999672174454, -0.16740000247955322, 0.11569999903440475, 0.06239999830722809, -0.12790000438690186, 0.1340000033378601, 0.07109999656677246, -0.022199999541044235, -0.07810000330209732, -0.022299999371170998, -0.19290000200271606, -0.0729999989271164, 0.10400000214576721, -0.019099999219179153, 0.12269999831914902, 0.1445000022649765, -0.25200000405311584, -0.2809999883174896, 0.09189999848604202, -0.02969999983906746, 0.131400004029274, -0.19859999418258667, -0.0034000000450760126, -0.1875, -0.21330000460147858, 0.02879999950528145, -0.22200000286102295, -0.1306000053882599, -0.050999999046325684, 0.047600001096725464, -0.2632000148296356, 0.04410000145435333, 0.041999999433755875, -0.04360000044107437, -0.11819999665021896, 0.02710000053048134, -0.02969999983906746, -0.05660000070929527, -0.12800000607967377, 0.12139999866485596, 0.12720000743865967, 0.17470000684261322, 0.030400000512599945, -0.11969999969005585], [0.04010000079870224, -0.013299999758601189, 0.09070000052452087, 0.04230000078678131, -0.03400000184774399, 0.03869999945163727, 0.1535000056028366, 0.07410000264644623, -0.1598999947309494, 0.07289999723434448, 0.24969999492168427, -0.09160000085830688, 0.22220000624656677, 0.09109999984502792, -0.02759999968111515, -0.23499999940395355, -0.33799999952316284, -0.024299999698996544, 0.07490000128746033, -0.07320000231266022, 0.10350000113248825, -0.19020000100135803, -0.1168999969959259, 0.0966000035405159, 0.02290000021457672, 0.13199999928474426, -0.06679999828338623, 0.10270000249147415, 0.13330000638961792, -0.17970000207424164, 0.08829999715089798, -0.121799997985363, 0.057999998331069946, -0.04470000043511391, 0.03229999914765358, 0.1324000060558319, -0.12139999866485596, -0.08669999986886978, 0.12330000102519989, -0.13230000436306, -0.011300000362098217, -0.010200000368058681, -0.16089999675750732, -0.24199999868869781, -0.07769999653100967, 0.09679999947547913, -0.10029999911785126, 0.1251000016927719, -0.07100000232458115, 0.093299999833107, 0.22010000050067902, -0.08780000358819962, 0.010499999858438969, -0.026799999177455902, -0.019200000911951065, -0.29120001196861267, -0.1451999992132187, 0.09520000219345093, -0.053599998354911804, -0.14730000495910645, -0.09600000083446503, -0.04190000146627426, 0.06360000371932983, -0.09719999879598618], [-0.016499999910593033, 0.2029000073671341, 0.24500000476837158, 0.24169999361038208, -0.03739999979734421, -0.0008999999845400453, 0.031099999323487282, 0.06750000268220901, 0.1624000072479248, 0.019999999552965164, -0.1581999957561493, 0.19179999828338623, -0.024800000712275505, -0.1460999995470047, -0.007300000172108412, 0.020800000056624413, 0.07450000196695328, 0.007300000172108412, 0.05139999836683273, -0.37709999084472656, -0.041200000792741776, 0.21879999339580536, -0.10090000182390213, 0.15209999680519104, -0.005400000140070915, 0.16769999265670776, 0.10620000213384628, -0.008999999612569809, -0.15839999914169312, -0.10260000079870224, -0.15369999408721924, -0.003000000026077032, 0.001500000013038516, 0.06530000269412994, 0.05689999833703041, 0.13539999723434448, -0.00430000014603138, 0.09279999881982803, 0.11699999868869781, -0.012400000356137753, 0.025699999183416367, -0.21960000693798065, -0.061799999326467514, -0.13920000195503235, 0.13449999690055847, 0.044199999421834946, 0.27900001406669617, 0.048900000751018524, 0.11879999935626984, -0.00419999985024333, -0.017899999395012856, -0.1615999937057495, 0.011300000362098217, 0.08590000122785568, 0.24079999327659607, -0.12950000166893005, 0.046300001442432404, -0.10159999877214432, -0.11410000175237656, -0.1347000002861023, 0.007199999876320362, -0.028200000524520874, -0.0210999995470047, 0.040300000458955765], [-0.05689999833703041, -0.015799999237060547, 0.024900000542402267, -0.03099999949336052, 0.11909999698400497, -0.22669999301433563, -0.055799998342990875, 0.13760000467300415, -0.05739999935030937, 0.0034000000450760126, -0.0421999990940094, -0.11089999973773956, -0.030500000342726707, -0.0142000000923872, 0.09799999743700027, -0.0, 0.14480000734329224, 0.04919999837875366, -0.07129999995231628, 0.05820000171661377, -0.028999999165534973, 0.27160000801086426, 0.03350000083446503, 0.01769999973475933, 0.0803999975323677, -0.18629999458789825, -0.09889999777078629, 0.09510000050067902, 0.17870000004768372, -0.20749999582767487, -0.027300000190734863, -0.1476999968290329, 0.12150000035762787, 0.010499999858438969, 0.024800000712275505, 0.03909999877214432, 0.2222999930381775, -0.025299999862909317, 0.045899998396635056, -0.38839998841285706, -0.03689999878406525, -0.04170000180602074, -0.18060000240802765, -0.05779999867081642, -0.03739999979734421, 0.11649999767541885, 0.14059999585151672, -0.065999999</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>[[[0.05400000140070915, -0.08529999852180481, -0.10509999841451645, 0.08399999886751175, 0.07159999758005142, 0.039400000125169754, -0.07670000195503235, -0.05299999937415123, 0.07729999721050262, -0.09080000221729279, 0.10029999911785126, 0.0966000035405159, 0.08479999750852585, -0.10289999842643738, -0.0860000029206276, 0.16349999606609344, 0.11249999701976776, 0.06199999898672104, -0.02250000089406967, -0.01759999990463257, -0.05209999904036522, 0.01640000008046627, -0.052799999713897705, 0.051500000059604645, 0.06480000168085098, 0.019700000062584877, -0.00559999980032444, 0.0608999989926815, -0.013100000098347664, 0.014800000004470348, 0.11320000141859055, -0.1656000018119812, -0.0551999993622303, -0.12939999997615814, 0.13030000030994415, -0.03020000085234642, 0.012000000104308128, -0.03579999879002571, 0.1362999975681305, -0.021800000220537186, -0.1428000032901764, 0.09589999914169312, 0.06239999830722809, 0.02459999918937683, 0.0625, 0.09690000116825104, -0.11659999936819077, 0.003599999938160181, -0.011099999770522118, 0.1005999967455864, -0.040699999779462814, -0.05209999904036522, 0.05180000141263008, -0.09179999679327011, -0.032999999821186066, -0.06629999727010727, -0.04740000143647194, 0.019300000742077827, 0.05849999934434891, -0.10000000149011612, 0.08209999650716782, -0.037300001829862595, -0.045899998396635056, 0.09449999779462814], [0.042399998754262924, -0.034299999475479126, 0.08129999786615372, -0.039500001817941666, 0.03220000118017197, -0.043800000101327896, 0.03440000116825104, 0.08590000122785568, -0.20909999310970306, 0.05350000038743019, -0.12559999525547028, -0.14270000159740448, -0.08560000360012054, 0.025699999183416367, 0.04749999940395355, -0.016300000250339508, -0.06459999829530716, -0.022099999710917473, 0.06620000302791595, -0.04019999876618385, 0.12729999423027039, 0.08950000256299973, 0.008100000210106373, -0.07639999687671661, 0.042500000447034836, -0.1251000016927719, -0.1324000060558319, -0.06620000302791595, 0.08070000261068344, -0.16899999976158142, -0.051100000739097595, 0.08049999922513962, 0.1412000060081482, 0.1307000070810318, -0.12770000100135803, -0.20819999277591705, 0.10540000349283218, 0.13420000672340393, 0.04149999842047691, 0.17679999768733978, 0.056299999356269836, -0.10040000081062317, -0.03370000049471855, -0.02199999988079071, -0.008100000210106373, 0.04600000008940697, 0.029100000858306885, -0.07750000059604645, -0.030700000002980232, -0.09300000220537186, -0.028599999845027924, 0.050700001418590546, -0.12080000340938568, 0.09740000218153, 0.05849999934434891, -0.10080000013113022, 0.16200000047683716, 0.0568000003695488, 0.02329999953508377, 0.0869000032544136, -0.08980000019073486, -0.0697999969124794, 0.057999998331069946, -0.16940000653266907]], [[0.18569999933242798, -0.23160000145435333, -0.06610000133514404, 0.1867000013589859, -0.028999999165534973, 0.13259999454021454, -0.08730000257492065, -0.048700001090765, -0.12919999659061432, 0.14949999749660492, -0.12680000066757202, 0.28600001335144043, 0.07039999961853027, -0.011900000274181366, -0.05909999832510948, 0.11800000071525574, -0.17730000615119934, -0.10090000182390213, -0.25459998846054077, -0.19110000133514404, -0.008100000210106373, 0.14149999618530273, 0.014499999582767487, -0.01730000041425228, 0.017799999564886093, -0.11630000174045563, -0.0722000002861023, -0.21119999885559082, 0.4099000096321106, 0.006099999882280827, 0.09629999846220016, -0.19280000030994415, -0.11879999935626984, -0.02759999968111515, -0.09809999912977219, 0.15489999949932098, 0.062199998646974564, -0.14419999718666077, -0.0364999994635582, -0.006200000178068876, 0.13729999959468842, 0.011800000444054604, 0.131400004029274, 0.0414000004529953, -0.043800000101327896, -0.0868000015616417, 0.055799998342990875, 0.003000000026077032, -0.14740000665187836, 0.1014999970793724, 0.016699999570846558, 0.05079999938607216, -0.044599998742341995, -0.034299999475479126, 0.05180000141263008, -0.04410000145435333, 0.07429999858140945, -0.13500000536441803, -0.12870000302791595, -0.1151999980211258, 0.23980000615119934, 0.019700000062584877, 0.050200000405311584, 0.10540000349283218], [0.11469999700784683, 0.19020000100135803, -0.003100000089034438, -0.1128000020980835, 0.24529999494552612, -0.09099999815225601, -0.05270000174641609, -0.05730000138282776, -0.06040000170469284, 0.12200000137090683, -0.17329999804496765, 0.052000001072883606, -0.09629999846220016, -0.10379999876022339, 0.20110000669956207, -0.1143999993801117, -0.29490000009536743, 0.07010000199079514, -0.03920000046491623, 0.22010000050067902, -0.15610000491142273, -0.11479999870061874, -0.03959999978542328, 0.03310000151395798, -0.1460999995470047, -0.035599999129772186, -0.2515000104904175, -0.19599999487400055, -0.2206999957561493, 0.07429999858140945, -0.2727999985218048, -0.06960000097751617, 0.01810000091791153, 0.09220000356435776, 0.07999999821186066, 0.08879999816417694, 0.03790000081062317, -0.07100000232458115, -0.11460000276565552, 0.0035000001080334187, 0.03189999982714653, 0.1356000006198883, -0.050700001418590546, -0.04560000076889992, -0.006899999920278788, 0.21209999918937683, -0.013199999928474426, -0.0982000008225441, -0.07240000367164612, 0.27399998903274536, 0.2071000039577484, -0.09269999712705612, -0.05469999834895134, 0.10989999771118164, -0.002099999925121665, 0.20270000398159027, 0.015399999916553497, -0.24330000579357147, -0.045899998396635056, 0.0010999999940395355, -0.25099998712539673, -0.0697999969124794, -0.0430000014603138, -0.06279999762773514], [-0.15690000355243683, 0.045899998396635056, 0.2962000072002411, 0.009100000374019146, -0.10589999705553055, -0.24330000579357147, -0.07419999688863754, -0.24969999492168427, 0.052799999713897705, -0.12700000405311584, -0.10140000283718109, -0.14470000565052032, 0.13989999890327454, 0.08399999886751175, 0.5946000218391418, -0.19850000739097595, -0.010999999940395355, 0.007899999618530273, -0.1143999993801117, 0.18029999732971191, -0.08410000056028366, 0.14890000224113464, 0.29030001163482666, -0.11490000039339066, -0.07890000194311142, -0.028699999675154686, 0.026799999177455902, 0.009700000286102295, 0.11710000038146973, 0.09099999815225601, -0.1476999968290329, -0.1624000072479248, -0.08049999922513962, -0.03060000017285347, -0.21050000190734863, -0.12549999356269836, 0.15549999475479126, -0.004000000189989805, -0.08860000222921371, -0.05660000070929527, 0.14419999718666077, -0.12790000438690186, -0.2459000051021576, 0.01769999973475933, -0.35910001397132874, 0.04340000078082085, -0.13259999454021454, -0.1460999995470047, -0.09390000253915787, -0.13169999420642853, 0.24160000681877136, 0.38029998540878296, 0.3093999922275543, -0.08219999819993973, -0.1264999955892563, -0.1324000060558319, -0.23430000245571136, 0.23960000276565552, -0.36309999227523804, 0.1979999989271164, -0.20810000598430634, -0.20749999582767487, -0.39910000562667847, 0.13369999825954437], [-0.19939999282360077, -0.20440000295639038, -0.07180000096559525, -0.07569999992847443, -0.022600000724196434, 0.11389999836683273, -0.04540000110864639, -0.19419999420642853, 0.3531999886035919, 0.05299999937415123, 0.13809999823570251, 0.05090000107884407, -0.0031999999191612005, 0.07530000060796738, -0.05350000038743019, -0.07450000196695328, -0.017999999225139618, 0.1298999935388565, 0.011699999682605267, -0.20029999315738678, -0.1606999933719635, 0.05290000140666962, -0.08709999918937683, -0.2224999964237213, -0.019500000402331352, 0.026000000536441803, 0.08219999819993973, 0.031199999153614044, -0.04129999876022339, -0.2662999927997589, 0.07370000332593918, -0.1987999975681305, 0.03449999913573265, 0.11999999731779099, 0.013399999588727951, 0.0989999994635582, -0.30320000648498535, 0.07090000063180923, 0.09109999984502792, -0.054499998688697815, 0.031099999323487282, -0.04670000076293945, 0.07840000092983246, 0.23399999737739563, 0.18219999969005585, 0.08410000056028366, -0.0008999999845400453, -0.10459999740123749, 0.12049999833106995, 0.2054000049829483, -0.10790000110864639, -0.00430000014603138, 0.05119999870657921, 0.03550000116229057, -0.19850000739097595, -0.15710000693798065, 0.09570000320672989, -0.12849999964237213, 0.008700000122189522, -0.04639999940991402, -0.14079999923706055, 0.08320000022649765, 0.022600000724196434, -0.2531000077724457], [0.24250000715255737, -0.16439999639987946, 0.2678000032901764, 0.03440000116825104, -0.19449999928474426, 0.23309999704360962, 0.05139999836683273, -0.09610000252723694, -0.08309999853372574, 0.09019999951124191, 0.07020000368356705, 0.1656000018119812, -0.0934000015258789, 0.1859000027179718, -0.06120000034570694, 0.19040000438690186, 0.042899999767541885, 0.12559999525547028, -0.2957000136375427, 0.013899999670684338, 0.10760000348091125, 0.12839999794960022, -0.1386999934911728, -0.026499999687075615, 0.08299999684095383, -0.18709999322891235, -0.2069000005722046, 0.013199999928474426, 0.05719999969005585, 0.012500000186264515, -0.09839999675750732, 0.22460000216960907, 0.031199999153614044, -0.11050000041723251, 0.23399999737739563, 0.08250000327825546, 0.03720000013709068, -0.07360000163316727, 0.17299999296665192, -0.04470000043511391, 0.3165999948978424, 0.11299999803304672, -0.012600000016391277, -0.03610000014305115, 0.0012000000569969416, 0.05530000105500221, -0.041200000792741776, -0.06120000034570694, 0.16249999403953552, -0.12349999696016312, -0.13729999959468842, -0.051899999380111694, 0.019700000062584877, 0.2662000060081482, 0.12610000371932983, -0.1386999934911728, -0.10000000149011612, 0.12309999763965607, 0.17080000042915344, -0.04690000042319298, -0.18469999730587006, -0.2084999978542328, -0.08560000360012054, 0.024900000542402267], [0.03539999946951866, -0.14880000054836273, 0.02160000056028366, -0.0020000000949949026, 0.2919999957084656, -0.059300001710653305, 0.12200000137090683, -0.1395999938249588, -0.04320000112056732, -0.08940000087022781, 0.1251000016927719, -0.19220000505447388, 0.17759999632835388, -0.11649999767541885, -0.24869999289512634, 0.10450000315904617, 0.09120000153779984, 0.16099999845027924, 0.16529999673366547, -0.13529999554157257, -0.011900000274181366, -0.15060000121593475, -0.10019999742507935, 0.21389999985694885, 0.014600000344216824, -0.014399999752640724, -0.11540000140666962, -0.028300000354647636, -0.12150000035762787, 0.026799999177455902, -0.01269999984651804, -0.1696999967098236, -0.32269999384880066, 0.1761000007390976, 0.18140000104904175, -0.10369999706745148, 0.17190000414848328, -0.1808999925851822, 0.07450000196695328, -0.06199999898672104, 0.10520000010728836, -0.04820000007748604, 0.36230000853538513, 0.15139999985694885, 0.0681999996304512, -0.07069999724626541, 0.03319999948143959, -0.014100000262260437, -0.04580000042915344, -0.042500000447034836, -0.10320000350475311, -0.2962999939918518, 0.18150000274181366, -0.007199999876320362, 0.09650000184774399, 0.039400000125169754, 0.2750000059604645, 0.031700000166893005, -0.01080000028014183, -0.05389999970793724, 0.24789999425411224, -0.05700000002980232, 0.19589999318122864, -0.15230000019073486], [0.026499999687075615, -0.06949999928474426, 0.07739999890327454, -0.08250000327825546, -0.050599999725818634, 0.02459999918937683, -0.07729999721050262, -0.032499998807907104, 0.02019999921321869, 0.07639999687671661, -0.01269999984651804, 0.011599999852478504, -0.07159999758005142, -0.12319999933242798, -0.18649999797344208, -0.06530000269412994, -0.16269999742507935, -0.3000999987125397, -0.02419999986886978, -0.08990000188350677, -0.21389999985694885, -0.06120000034570694, 0.08579999953508377, 0.15199999511241913, -0.009499999694526196, 0.2635999917984009, 0.23569999635219574, 0.12960000336170197, 0.10620000213384628, -0.050200000405311584, -0.14429999887943268, -0.004399999976158142, 0.15440000593662262, -0.054099999368190765, 0.1256999969482422, -0.18119999766349792, 0.2282000035047531, 0.06440000236034393, -0.12939999997615814, -0.01590000092983246, 0.24500000476837158, -0.08449999988079071, 0.299699991941452, 0.13699999451637268, -0.0632999986410141, 0.01730000041425228, -0.04659999907016754, -0.17739999294281006, -0.25279998779296875, -0.1973000019788742, 0.03669999912381172, -0.08479999750852585, -0.043800000101327896, -0.017100000753998756, -0.18369999527931213, 0.04520000144839287, -0.1996999979019165, -0.10140000283718109, 0.004399999976158142, 0.1597999930381775, -0.12549999356269836, 0.05260000005364418, 0.03370000049471855, -0.020899999886751175], [-0.1266999989748001, 0.19120000302791595, 0.10329999774694443, -0.06679999828338623, 0.13500000536441803, -0.021800000220537186, 0.02710000053048134, 0.21359999477863312, 0.08229999989271164, -0.09350000321865082, -0.03709999844431877, 0.05119999870657921, 0.06369999796152115, -0.14249999821186066, 0.05730000138282776, 0.07609999924898148, 0.01140000019222498, 0.019500000402331352, 0.07100000232458115, 0.024299999698996544, 0.027300000190734863, 0.16449999809265137, -0.06459999829530716, -0.2321999967098236, -0.14149999618530273, 0.053599998354911804, 0.125, -0.16220000386238098, 0.13770000636577606, 0.15620000660419464, -0.07240000367164612, -0.16019999980926514, 0.09220000356435776, -0.07840000092983246, -0.02459999918937683, -0.013299999758601189, 0.34450000524520874, -0.2782999873161316, 0.13330000638961792, 0.17739999294281006, 0.008700000122189522, 0.21809999644756317, 0.05770000070333481, 0.14069999754428864, -0.08500000089406967, 0.11389999836683273, 0.014800000004470348, 0.02239999920129776, -0.018799999728798866, 0.059300001710653305, 0.14869999885559082, 0.08179999887943268, -0.0003000000142492354, -0.10920000076293945, -0.1315000057220459, -0.22779999673366547, -0.10740000009536743, 0.17560000717639923, 0.1168999969959259, 0.20739999413490295, 0.050599999725818634, 0.13729999959468842, -0.0006000000284984708, -0.052799999713897705], [0.09430000185966492, -0.03799999877810478, -0.1534000039100647, -0.019600000232458115, 0.05869999900460243, 0.13770000636577606, -0.18070000410079956, -0.04019999876618385, -0.2818000018596649, -0.19300000369548798, -0.09120000153779984, 0.03999999910593033, 0.01269999984651804, -0.3666999936103821, -0.10869999974966049, 0.0333000011742115, 0.006200000178068876, -0.0284000001847744, 0.18250000476837158, 0.1906999945640564, -0.029500000178813934, -0.011900000274181366, -0.1145000010728836, 0.029100000858306885, 0.11060000211000443, 0.1826000064611435, -0.03440000116825104, 0.054499998688697815, -0.20600000023841858, -0.3921000063419342, 0.09549999982118607, -0.13050000369548798, 0.18299999833106995, -0.03739999979734421, -0.014600000344216824, 0.1720999926328659, 0.12780000269412994, 0.18320000171661377, 0.11509999632835388, 0.06289999932050705, -0.13359999656677246, -0.06129999831318855, 0.04989999905228615, 0.17759999632835388, 0.18299999833106995, 0.1648000031709671, -0.20260000228881836, -0.020800000056624413, 0.1647000014781952, -0.10159999877214432, -0.12600000202655792, 0.09080000221729279, 0.07039999961853027, -0.09229999780654907, -0.10570000112056732, 0.07320000231266022, 0.10909999907016754, 0.04839999973773956, 0.07190000265836716, -0.3490000069141388, 0.10000000149011612, -0.19349999725818634, -0.186599999666214, -0.1467999964952469], [-0.11720000207424164, 0.0560000017285347, -0.006500000134110451, -0.054999999701976776, 0.11949999630451202, -0.09210000187158585, -0.17820000648498535, -0.04479999840259552, -0.16619999706745148, -0.11140000075101852, 0.03920000046491623, 0.19789999723434448, -0.20489999651908875, -0.17960000038146973, 0.31139999628067017, -0.11760000139474869, 0.11540000140666962, -0.06599999964237213, 0.05180000141263008, 0.1151999980211258, -0.02250000089406967, 0.08309999853372574, -0.005200000014156103, 0.05350000038743019, -0.2856000065803528, -0.12319999933242798, 0.17080000042915344, 0.3474999964237213, -0.07209999859333038, 0.08959999680519104, 0.03449999913573265, -0.20000000298023224, 0.05180000141263008, 0.0568000003695488, -0.07559999823570251, -0.09380000084638596, 0.012900000438094139, -0.2110999971628189, -0.049400001764297485, -0.19679999351501465, 0.17820000648498535, -0.00570000009611249, -0.16670000553131104, -0.009399999864399433, -0.009600000455975533, 0.05139999836683273, -0.18469999730587006, -0.1006999984383583, 0.041600000113248825, -0.11670000106096268, 0.2928999960422516, 0.061500001698732376, -0.2126999944448471, -9.999999747378752e-05, -0.22030000388622284, -0.12489999830722809, 0.2922999858856201, 0.16210000216960907, -0.14429999887943268, 0.23350000381469727, -0.0032999999821186066, -0.0640999972820282, 0.08139999955892563, 0.31630000472068787], [0.2459000051021576, -0.12880000472068787, -0.1898999959230423, 0.10419999808073044, 0.22679999470710754, 0.12489999830722809, -0.06790000200271606, 0.1429000049829483, 0.07410000264644623, -0.3882000148296356, -0.0689999982714653, 0.003599999938160181, 0.17219999432563782, 0.32760000228881836, -0.12530000507831573, 0.3887999951839447, 0.049300000071525574, -0.09070000052452087, 0.28139999508857727, -0.03449999913573265, -0.38510000705718994, -0.11320000141859055, -0.12189999967813492, -0.02759999968111515, 0.3955000042915344, -0.052799999713897705, -0.18780000507831573, 0.20430000126361847, -0.17239999771118164, -0.03480000048875809, 0.3021000027656555, -0.1656000018119812, 0.14100000262260437, -0.20880000293254852, 0.23499999940395355, 0.3610999882221222, -0.41769999265670776, 0.3172000050544739, 0.027699999511241913, 0.2506999969482422, 0.019700000062584877, -0.24379999935626984, 0.17790000140666962, 0.14229999482631683, 0.2784000039100647, 0.30550000071525574, -0.030500000342726707, 0.20469999313354492, 0.09239999949932098, 0.10909999907016754, -0.07840000092983246, -0.2727000117301941, -0.10939999669790268, 0.259799987077713, 0.07090000063180923, -0.030899999663233757, 0.1665000021457672, 0.14419999718666077, 0.16349999606609344, -0.1145000010728836, -0.022600000724196434, 0.0892999991774559, -0.08060000091791153, -0.24459999799728394], [0.07959999889135361, -0.43720000982284546, -0.3968999981880188, 0.060100000351667404, 0.2563000023365021, 0.05869999900460243, -0.038600001484155655, -0.19210000336170197, 0.1509999930858612, -0.0551999993622303, -0.050700001418590546, 0.16300000250339508, 0.18539999425411224, -0.05050000175833702, -0.258899986743927, 0.29440000653266907, -0.0142000000923872, -0.2985000014305115, 0.05490000173449516, 0.022700000554323196, 0.11159999668598175, 0.05460000038146973, -0.22550000250339508, 0.16840000450611115, 0.031700000166893005, 0.188400000333786, -0.15760000050067902, 0.06019999831914902, -0.22020000219345093, -0.14509999752044678, 0.23559999465942383, 0.03290000185370445, -0.03290000185370445, -0.1873999983072281, 0.3896999955177307, 0.05570000037550926, -0.1688999980688095, 0.12070000171661377, 0.29100000858306885, 0.320499986410141, -0.25029999017715454, -0.20509999990463257, -0.1995999962091446, 0.06030000001192093, 0.033399999141693115, 0.07370000332593918, 0.05660000070929527, 0.17579999566078186, 0.08460000157356262, 0.13850000500679016, -0.3276999890804291, -0.36160001158714294, -0.05810000002384186, 0.2632000148296356, -0.04349999874830246, -0.012199999764561653, 0.10119999945163727, -0.016599999740719795, 0.16329999268054962, -0.11320000141859055, -0.07159999758005142, 0.09989999979734421, 0.20280000567436218, -0.26739999651908875], [-0.12860000133514404, -0.00800000037997961, 0.07760000228881836, -0.17180000245571136, 0.008100000210106373, 0.27390000224113464, -0.04670000076293945, 0.03500000014901161, 0.008700000122189522, -9.999999747378752e-05, 0.01730000041425228, -0.2468000054359436, -0.18310000002384186, 0.13609999418258667, -0.13609999418258667, -0.04690000042319298, 0.10689999908208847, -0.14319999516010284, -0.09749999642372131, 0.17329999804496765, 0.08669999986886978, 0.13940000534057617, -0.34790000319480896, 0.30300000309944153, 0.15870000422000885, -0.013799999840557575, -0.06530000269412994, 0.09679999947547913, -0.09399999678134918, -0.007000000216066837, 0.17319999635219574, -0.20190000534057617, 0.05920000001788139, -0.09449999779462814, 0.10369999706745148, 0.08449999988079071, -0.07940000295639038, 0.09210000187158585, -0.008999999612569809, 0.12470000237226486, 0.1534000039100647, 0.011599999852478504, -0.0502999983727932, 0.09690000116825104, -0.06040000170469284, 0.13779999315738678, 0.13490000367164612, 0.11500000208616257, 0.006599999964237213, 0.18610000610351562, -0.1526000052690506, -0.026499999687075615, -0.18150000274181366, -0.06199999898672104, 0.20640000700950623, -0.05389999970793724, 0.04520000144839287, -0.10620000213384628, 0.03290000185370445, -0.007000000216066837, 0.28439998626708984, -0.03689999878406525, -0.1120000034570694, -0.1867000013589859], [-0.21559999883174896, -0.04430000111460686, -0.2289000004529953, 0.2071000039577484, 0.05689999833703041, -0.009399999864399433, -0.2535000145435333, 0.08449999988079071, 0.030899999663233757, 0.1656000018119812, 0.2459000051021576, -0.07249999791383743, 0.08470000326633453, 0.016300000250339508, -0.04129999876022339, 0.026000000536441803, 0.07329999655485153, 0.04100000113248825, -0.09319999814033508, 0.11879999935626984, 0.0017000000225380063, -0.07050000131130219, 0.03189999982714653, -0.1128000020980835, 0.0005000000237487257, 0.11079999804496765, 0.24410000443458557, -0.22120000422000885, -0.02459999918937683, -0.06729999929666519, -0.2639999985694885, -0.24289999902248383, -0.013700000010430813, 0.10429999977350235, -0.1809999942779541, 0.04520000144839287, 0.22830000519752502, -0.14560000598430634, -0.3025999963283539, 0.020899999886751175, 0.16740000247955322, -0.12430000305175781, -0.272599995136261, -0.11349999904632568, 0.11879999935626984, 0.014000000432133675, -0.05050000175833702, 0.02160000056028366, -0.17010000348091125, -0.2581000030040741, -0.03420000150799751, -0.11500000208616257, 0.009999999776482582, -0.02879999950528145, 0.09179999679327011, -0.032499998807907104, 0.19679999351501465, -0.03660000115633011, 0.1597999930381775, 0.08579999953508377, -0.0010000000474974513, -0.15770000219345093, -0.023900000378489494, -0.07500000298023224], [0.07940000295639038, 0.11699999868869781, -0.014499999582767487, 0.11699999868869781, -0.09759999811649323, -0.4083999991416931, -0.15289999544620514, -0.03759999945759773, 0.06440000236034393, 0.06369999796152115, 0.16599999368190765, 0.001500000013038516, -0.12759999930858612, 0.04479999840259552, 0.133200004696846, -0.03269999846816063, 0.1720000058412552, 0.009499999694526196, 0.1793999969959259, 0.24300000071525574, -0.01899999938905239, -0.04050000011920929, 0.07599999755620956, -0.04190000146627426, -0.16179999709129333, 0.1688999980688095, 0.08659999817609787, 0.019300000742077827, 0.15610000491142273, -0.054499998688697815, -0.21950000524520874, 0.13120000064373016, -0.179299995303154, 0.13210000097751617, -0.20360000431537628, 0.16920000314712524, 0.031199999153614044, 0.193900004029274, 0.08110000193119049, 0.03530000150203705, 0.24250000715255737, 0.054499998688697815, -0.05640000104904175, 0.09740000218153, 0.07919999957084656, 0.050700001418590546, -0.023900000378489494, 0.09070000052452087, -0.1251000016927719, 0.08829999715089798, 0.22439999878406525, 0.19200000166893005, 0.020899999886751175, -0.13379999995231628, -0.17890000343322754, 0.03009999915957451, -0.007300000172108412, 0.03889999911189079, -0.3434999883174896, 0.33799999952316284, 0.05040000006556511, -0.42010000348091125, 0.15160000324249268, -0.10999999940395355], [-0.1151999980211258, -0.07760000228881836, 0.02879999950528145, 0.13420000672340393, 0.329800009727478, 0.10570000112056732, 0.12120000272989273, -0.024399999529123306, -0.0015999999595806003, 0.00559999980032444, 0.03610000014305115, 0.11620000004768372, -0.007400000002235174, 0.314300000667572, -0.014700000174343586, 0.21879999339580536, -0.016699999570846558, 0.20990000665187836, -0.012600000016391277, -0.11559999734163284, 0.13760000467300415, 0.14169999957084656, -0.13580000400543213, 0.00570000009611249, -0.15199999511241913, 0.05009999871253967, 0.04390000179409981, -0.02160000056028366, 0.11890000104904175, -0.24809999763965607, 0.22179999947547913, 0.07349999994039536, 0.06449999660253525, -0.14980000257492065, 0.0877000018954277, -0.17990000545978546, 0.0032999999821186066, 0.31450000405311584, -0.1574999988079071, 0.10209999978542328, -0.006500000134110451, -0.11289999634027481, 0.2529999911785126, 0.01899999938905239, 0.10589999705553055, 0.14710000157356262, -0.3824000060558319, 0.14550000429153442, 0.1256999969482422, 0.2037000060081482, -0.22269999980926514, -0.20589999854564667, -0.06360000371932983, -0.1881999969482422, 0.1656000018119812, -0.041200000792741776, -0.05570000037550926, 0.04019999876618385, -0.07249999791383743, -0.017999999225139618, 0.06069999933242798, -0.012500000186264515, 0.03060000017285347, 0.10180000215768814], [0.13269999623298645, -0.21559999883174896, -0.0414000004529953, 0.010300000198185444, 0.06469999998807907, 0.2547999918460846, -0.1606999933719635, 0.04039999842643738, 0.17759999632835388, -0.03610000014305115, 0.13590000569820404, 0.1599999964237213, 0.08590000122785568, 0.32170000672340393, 0.019300000742077827, 0.28040000796318054, -0.08569999784231186, -0.11479999870061874, 0.1492999941110611, -0.011500000022351742, 0.08299999684095383, -0.2312999963760376, 0.06610000133514404, 0.26019999384880066, -0.04820000007748604, 0.08749999850988388, -0.027699999511241913, 0.08789999783039093, 0.006000000052154064, -0.04039999842643738, -0.053300000727176666, 0.03290000185370445, 0.09920000284910202, 0.1476999968290329, 0.14949999749660492, -0.09449999779462814, -0.149399995803833, 0.18459999561309814, 0.0949999988079071, -0.1648000031709671, -0.19709999859333038, 0.05739999935030937, 0.05609999969601631, 0.15459999442100525, 0.00019999999494757503, 0.3481000065803528, 0.17020000517368317, 0.13740000128746033, 0.1446000039577484, -0.00800000037997961, -0.12449999898672104, -0.09679999947547913, 0.01489999983459711, 0.011800000444054604, 0.16220000386238098, 0.04960000142455101, 0.09679999947547913, 0.12399999797344208, 0.13689999282360077, -0.323199987411499, 0.07100000232458115, 0.2590999901294708, -0.06909999996423721, -0.11060000211000443], [0.019999999552965164, 0.17900000512599945, -0.05480000004172325, -0.15710000693798065, 0.07959999889135361, 0.24629999697208405, 0.13760000467300415, -0.04639999940991402, 0.012400000356137753, -0.22579999268054962, 0.062199998646974564, 0.04129999876022339, 0.07490000128746033, -0.0006000000284984708, 0.09279999881982803, -0.04780000075697899, 0.03840000182390213, -0.04479999840259552, -0.09920000284910202, -0.009399999864399433, 0.10700000077486038, 0.19769999384880066, 0.15770000219345093, -0.0551999993622303, -0.08030000329017639, 0.008799999952316284, 0.18479999899864197, 0.2793000042438507, -0.060100000351667404, -0.00989999994635582, -0.2363000065088272, -0.16949999332427979, -0.012400000356137753, 0.16169999539852142, -0.08869999647140503, -0.04569999873638153, -0.09510000050067902, 0.01640000008046627, -0.006899999920278788, -0.01140000019222498, -0.09860000014305115, -0.05790000036358833, 0.12890000641345978, 0.15809999406337738, 0.14300000667572021, -0.1331000030040741, -0.11169999837875366, 0.32179999351501465, -0.09019999951124191, 0.265500009059906, -0.017899999395012856, 0.016100000590085983, -0.028300000354647636, 0.016200000420212746, 0.20319999754428864, -0.007699999958276749, -0.2076999992132187, 0.17710000276565552, 0.19900000095367432, 0.050999999046325684, 0.04830000177025795, -0.3005000054836273, 0.11559999734163284, -0.12549999356269836], [0.07660000026226044, 0.14180000126361847, -0.036400001496076584, 0.006899999920278788, -0.12210000306367874, 0.15850000083446503, 0.15680000185966492, 0.07199999690055847, -0.14509999752044678, 0.11879999935626984, -0.210099995136261, -0.18119999766349792, -0.15539999306201935, -0.013299999758601189, 0.08079999685287476, 0.1648000031709671, 0.22630000114440918, 0.11540000140666962, -0.06239999830722809, -0.04450000077486038, 0.11969999969005585, -0.14229999482631683, 0.13490000367164612, 0.032499998807907104, -0.11069999635219574, 0.05660000070929527, 0.16040000319480896, -0.1362999975681305, -0.05719999969005585, -0.0010000000474974513, -0.17399999499320984, -0.04280000180006027, 0.0982000008225441, 0.008299999870359898, 0.094200000166893, 0.08889999985694885, -0.2840000092983246, -0.3677000105381012, 0.07109999656677246, -0.04230000078678131, 0.18960000574588776, -0.15780000388622284, -0.01979999989271164, -0.29649999737739563, -0.2524000108242035, 0.03929999843239784, -0.15569999814033508, -0.09769999980926514, -0.0625, 0.01860000006854534, -0.2637999951839447, 0.06199999898672104, 0.041099999099969864, -0.08669999986886978, -0.07410000264644623, 0.0, -0.05849999934434891, -0.050700001418590546, -0.16619999706745148, 0.15970000624656677, 0.12300000339746475, 0.1712999939918518, 0.03420000150799751, -0.07540000230073929], [0.08240000158548355, -0.05050000175833702, 0.17149999737739563, 0.09149999916553497, -0.0737999975681305, 0.10830000042915344, 0.16769999265670776, 0.01549999974668026, -0.16830000281333923, 0.025100000202655792, 0.2824999988079071, -0.05000000074505806, 0.17829999327659607, 0.09380000084638596, -0.020899999886751175, -0.17710000276565552, -0.38089999556541443, -0.028200000524520874, 0.14219999313354492, -0.09109999984502792, 0.1898999959230423, -0.1459999978542328, -0.08959999680519104, 0.10819999873638153, 0.11420000344514847, 0.05429999902844429, -0.1340000033378601, 0.09120000153779984, 0.09179999679327011, -0.17649999260902405, 0.12070000171661377, -0.120899997651577, 0.0689999982714653, -0.05770000070333481, 0.004800000227987766, 0.14409999549388885, -0.21539999544620514, -0.032099999487400055, 0.19120000302791595, -0.05310000106692314, 0.012199999764561653, 0.012000000104308128, -0.26899999380111694, -0.20239999890327454, -0.16760000586509705, 0.16940000653266907, -0.15109999477863312, 0.10809999704360962, -0.006500000134110451, 0.07509999722242355, 0.2395000010728836, -0.05660000070929527, -0.032600000500679016, -0.005400000140070915, -0.021900000050663948, -0.2540000081062317, -0.17910000681877136, 0.1421000063419342, -0.21610000729560852, -0.12219999730587006, -0.14409999549388885, -0.04450000077486038, -0.0010999999940395355, -0.09610000252723694], [-0.06809999793767929, 0.22130000591278076, 0.2460000067949295, 0.22269999980926514, -0.09719999879598618, -0.04769999906420708, 0.05609999969601631, 0.12189999967813492, 0.1534000039100647, 0.07559999823570251, -0.1462000012397766, 0.14470000565052032, -0.024700000882148743, -0.1266999989748001, 0.02590000070631504, 0.013700000010430813, 0.07400000095367432, -0.032499998807907104, -0.004100000020116568, -0.37439998984336853, -0.12950000166893005, 0.19619999825954437, -0.13199999928474426, 0.12200000137090683, -0.06390000134706497, 0.1761000007390976, 0.13539999723434448, -0.07460000365972519, -0.14429999887943268, -0.13259999454021454, -0.17080000042915344, 0.08160000294446945, -0.10989999771118164, 0.06289999932050705, 0.06599999964237213, 0.10090000182390213, 0.05339999869465828, 0.08110000193119049, 0.052400000393390656, -0.05000000074505806, 0.05860000103712082, -0.21279999613761902, -0.012000000104308128, -0.1889999955892563, 0.0989999994635582, -0.01209999993443489, 0.3671000003814697, 0.048500001430511475, 0.05530000105500221, -0.012500000186264515, -0.013700000010430813, -0.12229999899864197, 0.08089999854564667, 0.05609999969601631, 0.21199999749660492, -0.13920000195503235, 0.09870000183582306, -0.12380000203847885, -0.06889999657869339, -0.13510000705718994, 0.0007999999797903001, -0.0008999999845400453, 0.04039999842643738, 0.0737999975681305], [-0.027899999171495438, 0.0032999999821186066, -0.027499999850988388, -0.033900000154972076, 0.1145000010728836, -0.21070000529289246, -0.054499998688697815, 0.13089999556541443, -0.08060000091791153, -0.009399999864399433, -0.05550000071525574, -0.07079999893903732, -0.048500001430511475, -0.0024999999441206455, 0.051600001752376556, -0.014800000004470348, 0.19670000672340393, 0.08489999920129776, -0.0957999974489212, 0.016699999570846558, -0.05139999836683273, 0.26820001006126404, 0.03480000048875809, 0.06880000233650208, 0.07989999651908875, -0.1665000021457672, 0.0027000000700354576, 0.07240000367164612, 0.2151000052690506, -0.20280000567436218, -0.04690000042319298, -0.13030000030994415, 0.10939999669790268, 0.011300000362098217, 0.0340999998152256, -0.015599999576807022, 0.19580000638961792, -0.07199999690055847, 0.05510000139474869, -0.39629998803138733, -0.04610000178217888, -0.026100000366568565, -0.15530000627040863, -0.0812000036239624, 0.0003000000142492354, 0.10320000350475311, 0.186599999666214, -0.011800000444054604, -0.06989999860525131, -0.08640000224113464, -0.0449000000</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>[0.6889732831173325]</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>[0.0709970199924784]</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>[0.45783464064273105]</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>[0.12377812493520124]</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>[-1.1215865997483299]</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>[0.6943522143136011]</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>[0.7685322473328272]</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>[0.053172557609482786]</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>[0.16458053081301016]</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>[0.19812893939373136]</t>
+        </is>
+      </c>
+      <c r="O25" t="inlineStr">
+        <is>
+          <t>[-3.398861500382785]</t>
+        </is>
+      </c>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>[1.4461144730395077]</t>
+        </is>
+      </c>
+      <c r="Q25" t="inlineStr">
+        <is>
+          <t>[-0.25121929636490203]</t>
+        </is>
+      </c>
+      <c r="R25" t="inlineStr">
+        <is>
+          <t>[0.13491363278204602]</t>
+        </is>
+      </c>
+      <c r="S25" t="inlineStr">
+        <is>
+          <t>[-0.027230638475336688]</t>
+        </is>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>[0.0865548026091137]</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>[-0.9670173832059747]</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>[0.1880923600854065]</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>[-0.2772611026324583]</t>
+        </is>
+      </c>
+      <c r="X25" t="inlineStr">
+        <is>
+          <t>[0.13380666955342]</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>[-0.07902127648746848]</t>
+        </is>
+      </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>[0.08879612417890906]</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>[-1.8403293291895748]</t>
+        </is>
+      </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>[0.2613227228669612]</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>[-0.8191269932198981]</t>
+        </is>
+      </c>
+      <c r="AD25" t="inlineStr">
+        <is>
+          <t>[0.1524355134823143]</t>
+        </is>
+      </c>
+      <c r="AE25" t="inlineStr">
+        <is>
+          <t>[-1.0098151040656793]</t>
+        </is>
+      </c>
+      <c r="AF25" t="inlineStr">
+        <is>
+          <t>[0.2164130196718491]</t>
+        </is>
+      </c>
+      <c r="AG25" t="inlineStr">
+        <is>
+          <t>[-2.9149687691299477]</t>
+        </is>
+      </c>
+      <c r="AH25" t="inlineStr">
+        <is>
+          <t>[0.29146926220715946]</t>
+        </is>
+      </c>
+      <c r="AI25" t="inlineStr">
+        <is>
+          <t>[-1.2040149832585505]</t>
+        </is>
+      </c>
+      <c r="AJ25" t="inlineStr">
+        <is>
+          <t>[0.18061657433756328]</t>
+        </is>
+      </c>
+      <c r="AK25" t="inlineStr">
+        <is>
+          <t>[-0.918062975563243]</t>
+        </is>
+      </c>
+      <c r="AL25" t="inlineStr">
+        <is>
+          <t>[0.2035883319034583]</t>
+        </is>
+      </c>
+      <c r="AM25" t="inlineStr">
+        <is>
+          <t>[-2.6953073229464573]</t>
+        </is>
+      </c>
+      <c r="AN25" t="inlineStr">
+        <is>
+          <t>[0.283826391916806]</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>model_64_32_4</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>[64, 32]</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>[[[0.07999999821186066, 0.005799999926239252, -0.07419999688863754, 0.015799999237060547, 0.03500000014901161, -0.018699999898672104, -0.015799999237060547, -0.043299999088048935, 0.013000000268220901, 0.042500000447034836, -0.10080000013113022, 0.057500001043081284, -0.02810000069439411, 0.10559999942779541, -0.01590000092983246, -0.015799999237060547, 0.06909999996423721, 0.006899999920278788, 0.009600000455975533, -0.08489999920129776, -0.06239999830722809, -0.00860000029206276, -0.0658000037074089, 0.037300001829862595, -0.05820000171661377, -0.061500001698732376, 0.04960000142455101, 0.0917000025510788, -0.01510000042617321, -0.06719999760389328, -0.00279999990016222, 0.1103999987244606, 0.04879999905824661, 0.0210999995470047, 0.03229999914765358, 0.1177000030875206, -0.002199999988079071, -0.013399999588727951, 0.054999999701976776, 0.02410000003874302, -0.03189999982714653, -0.027000000700354576, -0.03830000013113022, 0.014999999664723873, -0.030500000342726707, 0.1274999976158142, 0.06849999725818634, -0.05130000039935112, 0.08389999717473984, -0.042500000447034836, 0.09709999710321426, 0.013399999588727951, -0.05310000106692314, -0.001500000013038516, 0.03840000182390213, 0.13680000603199005, -0.07649999856948853, 0.024900000542402267, 9.999999747378752e-05, -0.05130000039935112, -0.0007999999797903001, 0.02800000086426735, 0.0038999998942017555, -0.0908999964594841], [-0.07919999957084656, 0.04610000178217888, 0.03669999912381172, 0.004800000227987766, 0.03620000183582306, 0.027799999341368675, 0.05209999904036522, -0.08340000361204147, -0.03959999978542328, -0.012900000438094139, -0.02850000001490116, -0.042100001126527786, 0.05820000171661377, -0.03319999948143959, -0.026900000870227814, 0.04500000178813934, 0.06790000200271606, -0.03180000185966492, -0.009200000204145908, 0.007699999958276749, -0.039500001817941666, -0.05990000069141388, -0.03359999880194664, -0.011699999682605267, -0.013500000350177288, 0.05959999933838844, -0.021900000050663948, -0.013000000268220901, 0.01140000019222498, 0.02800000086426735, 0.03150000050663948, 0.020999999716877937, 0.04569999873638153, -0.006399999838322401, -0.0071000000461936, 0.037300001829862595, 0.01590000092983246, 0.02329999953508377, -0.04969999939203262, -0.04019999876618385, 0.021400000900030136, 0.0689999982714653, -0.015399999916553497, 0.031599998474121094, -0.003599999938160181, -0.07039999961853027, -0.022099999710917473, -0.007899999618530273, 0.01860000006854534, 0.05869999900460243, 0.03709999844431877, -0.014700000174343586, -0.04170000180602074, 0.009999999776482582, 0.017899999395012856, -0.07649999856948853, 0.14429999887943268, -0.003599999938160181, -0.04270000010728836, 0.0284000001847744, -0.10570000112056732, 0.010300000198185444, 0.0272000003606081, -0.049300000071525574]], [[0.056699998676776886, -0.10660000145435333, -0.13770000636577606, 0.006800000090152025, 0.013500000350177288, -0.07559999823570251, 0.014299999922513962, -0.06889999657869339, 0.14880000054836273, -0.1274999976158142, 0.003599999938160181, -0.16019999980926514, 0.04439999908208847, 0.11060000211000443, -0.010499999858438969, 0.006899999920278788, 0.02370000071823597, 0.21960000693798065, -0.08730000257492065, -0.16680000722408295, 0.03139999881386757, 0.041099999099969864, 0.06560000032186508, 0.1242000013589859, -0.12200000137090683, 0.0544000007212162, -0.19779999554157257, 0.1143999993801117, -0.02250000089406967, -0.18019999563694, -0.028300000354647636, 0.0877000018954277, -0.05299999937415123, 0.09799999743700027, -0.03709999844431877, -0.3199999928474426, -0.12540000677108765, -0.17509999871253967, -0.06669999659061432, -0.450300008058548, -0.164000004529953, -0.002300000051036477, -0.03449999913573265, 0.06589999794960022, -0.1784999966621399, 0.05620000138878822, 0.17110000550746918, 0.031300000846385956, -0.04769999906420708, -0.010400000028312206, 0.1931000053882599, 0.14229999482631683, 0.025100000202655792, -0.16910000145435333, -0.125, -0.002400000113993883, -0.22419999539852142, 0.03220000118017197, -0.0917000025510788, 0.01899999938905239, 0.033399999141693115, 0.15610000491142273, -0.026900000870227814, 0.02160000056028366], [0.043699998408555984, 0.27059999108314514, 0.21279999613761902, -0.34040001034736633, 0.11840000003576279, -0.08089999854564667, -0.12960000336170197, -0.051600001752376556, -0.08780000358819962, 0.04050000011920929, -0.0738999992609024, -0.016100000590085983, 0.13259999454021454, -0.2078000009059906, -0.040300000458955765, 0.024800000712275505, 0.08139999955892563, 0.004699999932199717, 0.1590999960899353, 0.2425999939441681, -0.24160000681877136, 0.07190000265836716, -0.046300001442432404, -0.024700000882148743, 0.04439999908208847, -0.12860000133514404, -0.07970000058412552, 0.1177000030875206, -0.02239999920129776, -0.16030000150203705, -0.1818999946117401, 0.09239999949932098, 0.2215999960899353, 0.03220000118017197, -0.04899999871850014, -0.007699999958276749, -0.22460000216960907, -0.08479999750852585, -0.2540000081062317, -0.02879999950528145, -0.09200000017881393, 0.05389999970793724, -0.1257999986410141, 0.06769999861717224, 0.04600000008940697, -0.12470000237226486, 0.060600001364946365, -0.05090000107884407, 0.04259999841451645, -0.07890000194311142, -0.09669999778270721, 0.2117999941110611, 0.045499999076128006, 0.04569999873638153, 0.0674000009894371, 0.042399998754262924, -0.01860000006854534, -0.009700000286102295, -0.03099999949336052, -0.011099999770522118, 0.26420000195503235, -0.07699999958276749, 0.02630000002682209, -0.0003000000142492354], [0.1185000017285347, 0.2362000048160553, -0.1623000055551529, -0.07999999821186066, 0.006300000008195639, 0.04190000146627426, 0.2084999978542328, 0.13120000064373016, -0.09459999948740005, 0.12860000133514404, -0.4115999937057495, -0.000699999975040555, 0.09290000051259995, -0.07010000199079514, 0.07670000195503235, -0.05510000139474869, 0.10869999974966049, -0.07490000128746033, 0.06530000269412994, -0.08910000324249268, 0.1720999926328659, -0.08739999681711197, -0.05400000140070915, 0.06340000033378601, -0.12210000306367874, 0.17790000140666962, -0.1777999997138977, -0.15530000627040863, -0.04729999974370003, -0.07400000095367432, 0.1624000072479248, 0.1695999950170517, -0.025299999862909317, 0.01510000042617321, -0.1137000024318695, 0.1168999969959259, 0.08659999817609787, -0.041999999433755875, -0.12330000102519989, -0.03359999880194664, -0.12129999697208405, 0.1356000006198883, 0.06509999930858612, 0.0649000033736229, -0.09610000252723694, -0.1582999974489212, -0.06300000101327896, 0.00419999985024333, -0.08420000225305557, 0.3395000100135803, 0.0052999998442828655, -0.18459999561309814, -0.13840000331401825, 0.13339999318122864, -0.061000000685453415, -0.06889999657869339, 0.005900000222027302, 0.13819999992847443, 0.04650000110268593, -0.05609999969601631, 0.11840000003576279, 0.04190000146627426, 0.02969999983906746, 0.052799999713897705], [0.03799999877810478, 0.01549999974668026, 0.12600000202655792, 0.10490000247955322, 0.05860000103712082, 0.17059999704360962, -0.14270000159740448, -0.017899999395012856, -0.12309999763965607, -0.11140000075101852, -0.10300000011920929, 0.09489999711513519, 0.07569999992847443, -0.14810000360012054, 0.21899999678134918, 0.005499999970197678, -0.025499999523162842, 0.05460000038146973, -0.01209999993443489, -0.3319999873638153, 0.049300000071525574, -0.13289999961853027, 0.16930000483989716, -0.30709999799728394, -0.023800000548362732, -0.01360000018030405, -0.04360000044107437, 0.0957999974489212, 0.09239999949932098, 0.04050000011920929, -0.0551999993622303, -0.16259999573230743, -0.014100000262260437, -0.03920000046491623, -0.21770000457763672, 0.08619999885559082, -0.0414000004529953, -0.22429999709129333, -0.026399999856948853, -0.03449999913573265, 0.08250000327825546, 0.12370000034570694, -0.09989999979734421, 0.010900000110268593, 0.1664000004529953, -0.12319999933242798, 0.060100000351667404, -0.19840000569820404, 0.04399999976158142, -0.08839999884366989, -0.07840000092983246, 0.06849999725818634, 0.08309999853372574, -0.04340000078082085, -0.08619999885559082, 0.07460000365972519, -0.017100000753998756, 0.1680999994277954, 0.19679999351501465, 0.0869000032544136, -0.19290000200271606, 0.17679999768733978, 0.08869999647140503, 0.25459998846054077], [-0.11919999867677689, -0.13740000128746033, -0.01850000023841858, 0.042500000447034836, -0.18279999494552612, 0.03739999979734421, 0.01810000091791153, 0.07119999825954437, -0.12710000574588776, -0.2298000007867813, 0.1712999939918518, -0.009800000116229057, 0.11150000244379044, 0.14560000598430634, 0.005900000222027302, 0.043800000101327896, 0.08060000091791153, 0.055799998342990875, -0.015599999576807022, 0.27390000224113464, -0.10809999704360962, -0.3050000071525574, -0.11209999769926071, 0.0421999990940094, -0.03669999912381172, -0.00839999970048666, -0.04650000110268593, -0.05719999969005585, -0.0005000000237487257, -0.3849000036716461, 0.0071000000461936, 0.19130000472068787, 0.09139999747276306, -0.038100000470876694, -0.14630000293254852, -0.002400000113993883, 0.133200004696846, -0.1606999933719635, -0.02539999969303608, -0.004900000058114529, -0.01140000019222498, -0.08709999918937683, 0.0551999993622303, -0.00039999998989515007, 0.2460000067949295, 0.01899999938905239, -0.2551000118255615, 0.0066999997943639755, -0.1362999975681305, 0.037700001150369644, 0.02800000086426735, 0.06780000030994415, 0.053199999034404755, 0.21649999916553497, -0.12489999830722809, 0.0729999989271164, 0.13519999384880066, -0.05900000035762787, -0.042100001126527786, -0.02710000053048134, -0.13169999420642853, 0.16670000553131104, 0.0835999995470047, 0.10209999978542328], [0.3253999948501587, -0.039799999445676804, -0.04839999973773956, -0.10130000114440918, 0.05999999865889549, 0.13899999856948853, 0.07039999961853027, -0.1445000022649765, -0.19840000569820404, 0.06729999929666519, 0.03550000116229057, -0.010400000028312206, -0.03840000182390213, 0.020600000396370888, -0.27559998631477356, -0.06759999692440033, 0.014600000344216824, -0.048500001430511475, 0.08879999816417694, -0.044599998742341995, -0.007400000002235174, 0.07999999821186066, 0.14399999380111694, 0.012900000438094139, -0.030899999663233757, 0.0957999974489212, 0.07360000163316727, 0.1996999979019165, -0.009200000204145908, 0.09740000218153, -0.053300000727176666, -0.13819999992847443, 0.09070000052452087, -0.24240000545978546, -0.05290000140666962, 0.0015999999595806003, 0.1362999975681305, 0.0544000007212162, -0.039000000804662704, -0.11050000041723251, -0.24140000343322754, 0.09000000357627869, -0.1436000019311905, 0.17630000412464142, 0.027699999511241913, 0.03229999914765358, -0.08089999854564667, 0.2069000005722046, 0.02070000022649765, -0.06679999828338623, 0.07039999961853027, -0.01510000042617321, 0.053300000727176666, 0.17170000076293945, 0.07599999755620956, -0.14300000667572021, 0.10019999742507935, -0.18389999866485596, -0.1573999971151352, -0.24690000712871552, -0.2529999911785126, 0.10109999775886536, 0.010499999858438969, 0.17270000278949738], [0.24770000576972961, 0.03849999979138374, 0.09929999709129333, 0.13580000400543213, 0.09749999642372131, -0.1777999997138977, -0.10849999636411667, -0.04670000076293945, -0.0877000018954277, 0.10419999808073044, 0.11630000174045563, 0.002099999925121665, 0.03660000115633011, 0.02019999921321869, -0.00019999999494757503, -0.0771000012755394, 0.1826999932527542, 0.2994000017642975, 0.16200000047683716, -0.03889999911189079, 0.19789999723434448, 0.06700000166893005, 0.08349999785423279, -0.0786999985575676, 0.012199999764561653, -0.0032999999821186066, 0.08320000022649765, 0.18629999458789825, 0.052400000393390656, -0.17090000212192535, -0.057100001722574234, 0.0925000011920929, -0.05590000003576279, 0.19619999825954437, 0.07400000095367432, -0.04600000008940697, 0.0689999982714653, 0.19169999659061432, -0.14630000293254852, 0.01850000023841858, 0.05429999902844429, 0.15459999442100525, 0.25999999046325684, -0.10180000215768814, -0.0608999989926815, 0.19329999387264252, -0.024000000208616257, 0.07159999758005142, -0.07670000195503235, 0.09650000184774399, -0.051899999380111694, 0.06469999998807907, -0.2029999941587448, 0.04430000111460686, 0.035100001841783524, 0.1695999950170517, 0.2904999852180481, 0.04039999842643738, 0.02800000086426735, 0.22529999911785126, -0.0869000032544136, -0.06809999793767929, -0.009700000286102295, 0.1080000028014183], [-0.04309999942779541, 0.03610000014305115, -0.1454000025987625, 0.03200000151991844, -0.11999999731779099, -0.15129999816417694, 0.06639999896287918, 0.011500000022351742, -0.09600000083446503, 0.0575999990105629, 0.06419999897480011, -0.013199999928474426, -0.13300000131130219, 0.13269999623298645, 0.3476000130176544, -0.19140000641345978, 0.14180000126361847, -0.04749999940395355, 0.17069999873638153, -0.01730000041425228, -0.15520000457763672, -0.01730000041425228, 0.011300000362098217, -0.03519999980926514, -0.06560000032186508, 0.18930000066757202, 0.03220000118017197, 0.035599999129772186, -0.02160000056028366, 0.10140000283718109, 0.09049999713897705, 0.11209999769926071, -0.06469999998807907, -0.04619999974966049, 0.00279999990016222, 0.04969999939203262, -0.048900000751018524, -0.15559999644756317, -0.24250000715255737, 0.1046999990940094, 0.026499999687075615, 0.2223999947309494, -0.052400000393390656, -0.13369999825954437, 0.055799998342990875, 0.11829999834299088, -0.02280000038444996, 0.13529999554157257, 0.010499999858438969, -0.16169999539852142, -0.1860000044107437, 0.06849999725818634, 0.04100000113248825, -0.29499998688697815, -0.03759999945759773, -0.16179999709129333, 0.03819999843835831, -0.30300000309944153, 0.050200000405311584, -0.06340000033378601, 0.0763000026345253, 0.19869999587535858, -0.17219999432563782, -0.057100001722574234], [-0.0421999990940094, -0.22470000386238098, -0.013899999670684338, -0.17080000042915344, 0.10679999738931656, -0.07699999958276749, -0.1315000057220459, -0.02800000086426735, 0.02710000053048134, 0.1518000066280365, 0.017500000074505806, 0.030899999663233757, -0.053599998354911804, -0.1526000052690506, -0.10189999639987946, 0.09070000052452087, 0.022299999371170998, -0.1543000042438507, -0.033900000154972076, -0.14949999749660492, 0.07159999758005142, 0.07840000092983246, 0.10790000110864639, -0.17329999804496765, 0.05079999938607216, 0.023499999195337296, -0.1290999948978424, -0.23980000615119934, -0.040300000458955765, -0.1754000037908554, -0.0024999999441206455, 0.148499995470047, -0.004699999932199717, -0.33640000224113464, -0.06710000336170197, 0.07959999889135361, 0.17239999771118164, 0.21729999780654907, -0.22920000553131104, 0.014000000432133675, -0.08160000294446945, -0.057100001722574234, 0.03150000050663948, -0.19429999589920044, 0.10260000079870224, 0.15039999783039093, 0.12120000272989273, -0.23010000586509705, 0.05590000003576279, 0.12210000306367874, 0.14949999749660492, 0.06549999862909317, 0.08320000022649765, -0.15379999577999115, -0.10930000245571136, 0.05050000175833702, 0.03620000183582306, -0.15889999270439148, -0.10180000215768814, 0.08940000087022781, 0.00559999980032444, 0.11900000274181366, 0.10109999775886536, -0.13590000569820404], [0.17839999496936798, 0.0925000011920929, 0.21080000698566437, -0.08910000324249268, 0.10970000177621841, -0.10999999940395355, -0.055799998342990875, 0.062199998646974564, 0.12950000166893005, 0.15320000052452087, 0.04280000180006027, -0.019099999219179153, -0.11270000040531158, 0.16220000386238098, -0.08910000324249268, 0.11540000140666962, 0.11259999871253967, 0.10419999808073044, 0.1348000019788742, -0.14059999585151672, 0.042399998754262924, -0.147599995136261, -0.09950000047683716, -0.22460000216960907, -0.05909999832510948, 0.05590000003576279, 0.1388999968767166, -0.13770000636577606, -0.038600001484155655, -0.05730000138282776, -0.015399999916553497, 0.1266999989748001, 0.07029999792575836, 0.18970000743865967, 0.02419999986886978, 0.04490000009536743, -0.01140000019222498, -0.15719999372959137, 0.030500000342726707, -0.003100000089034438, 0.15770000219345093, -0.3587000072002411, -0.029200000688433647, -0.025299999862909317, 0.17239999771118164, 0.04360000044107437, 0.07440000027418137, 0.0024999999441206455, 0.14339999854564667, -0.024399999529123306, 0.028200000524520874, -0.20730000734329224, -0.12929999828338623, 0.016300000250339508, -0.06019999831914902, -0.3131999969482422, -0.2117999941110611, -0.09290000051259995, -0.12929999828338623, -0.09350000321865082, -0.028699999675154686, 0.01360000018030405, -0.03709999844431877, 0.18870000541210175], [-0.050700001418590546, -0.027300000190734863, 0.06769999861717224, 0.12729999423027039, 0.20110000669956207, 0.09040000289678574, 0.05169999971985817, -0.14149999618530273, -0.13490000367164612, -0.02930000051856041, -0.08959999680519104, -0.10480000078678131, -0.35429999232292175, -0.11389999836683273, 0.012199999764561653, 0.16410000622272491, -0.03750000149011612, 0.09260000288486481, -0.14010000228881836, 0.10779999941587448, -0.06939999759197235, 0.07720000296831131, 0.03889999911189079, -0.18379999697208405, -0.04600000008940697, 0.14159999787807465, -0.006399999838322401, 0.04349999874830246, -0.02979999966919422, 0.020800000056624413, 0.0877000018954277, 0.18440000712871552, 0.08449999988079071, 0.1120000034570694, -0.2962999939918518, -0.09380000084638596, 0.053599998354911804, -0.13249999284744263, 0.03610000014305115, -0.12189999967813492, -0.01810000091791153, 0.12530000507831573, 0.1451999992132187, 0.0272000003606081, 0.026599999517202377, 0.009399999864399433, -0.15620000660419464, -0.1785999983549118, 0.043800000101327896, -0.11540000140666962, 0.19760000705718994, -0.08820000290870667, -0.03739999979734421, 0.09130000323057175, 0.08399999886751175, -0.060499999672174454, 0.06480000168085098, -0.148499995470047, 0.1388999968767166, -0.00570000009611249, -0.0005000000237487257, -0.2624000012874603, -0.2101999968290329, -0.24009999632835388], [-0.060100000351667404, 0.0026000000070780516, -0.07180000096559525, -0.08309999853372574, -0.013100000098347664, 0.10939999669790268, -0.11010000109672546, 0.06909999996423721, -0.2069000005722046, 0.09350000321865082, -0.0071000000461936, -0.23890000581741333, -0.03139999881386757, 0.03629999980330467, 0.048700001090765, -0.0917000025510788, -0.10329999774694443, -0.09120000153779984, -0.13130000233650208, -0.1265999972820282, -0.04699999839067459, -0.06549999862909317, -0.11949999630451202, -0.12809999287128448, 0.08940000087022781, 0.1347000002861023, 0.06040000170469284, 0.14180000126361847, -0.1242000013589859, -0.18019999563694, 0.155799999833107, 0.03180000185966492, 0.3253999948501587, 0.2757999897003174, 0.14839999377727509, -0.06679999828338623, 0.125, 0.2531999945640564, 0.08229999989271164, 0.10180000215768814, -0.12309999763965607, 0.0026000000070780516, -0.11060000211000443, -0.07100000232458115, -0.1712999939918518, -0.010900000110268593, -0.10409999638795853, 0.041099999099969864, 0.26980000734329224, 0.056299999356269836, -0.07810000330209732, 0.11630000174045563, 0.13770000636577606, 0.053199999034404755, -0.0027000000700354576, 0.0272000003606081, -0.2287999987602234, 0.008999999612569809, 0.0925000011920929, 0.17960000038146973, -0.09279999881982803, 0.12939999997615814, -0.06270000338554382, 0.02459999918937683], [0.029500000178813934, 0.06769999861717224, 0.08810000121593475, 0.11249999701976776, 0.17440000176429749, -0.2175000011920929, 0.03350000083446503, -0.020999999716877937, -0.2087000012397766, -0.0478999987244606, 0.12720000743865967, -0.03200000151991844, -0.0071000000461936, 0.15219999849796295, 0.03629999980330467, 0.16940000653266907, -0.19359999895095825, -0.004100000020116568, -0.11990000307559967, 0.027000000700354576, 0.1914999932050705, 0.014800000004470348, 0.051100000739097595, 0.2533000111579895, -0.025800000876188278, 0.09430000185966492, 0.048700001090765, -0.18559999763965607, 0.0737999975681305, 0.155799999833107, -0.031700000166893005, 0.10570000112056732, 0.20730000734329224, -0.045499999076128006, -0.13750000298023224, -0.01119999960064888, -0.08420000225305557, 0.15970000624656677, -0.019999999552965164, -0.07590000331401825, -0.004900000058114529, 0.002300000051036477, -0.21359999477863312, 0.08420000225305557, 0.2085999995470047, 0.043299999088048935, 0.027499999850988388, 0.05389999970793724, 0.1842000037431717, 0.1168999969959259, -0.19910000264644623, 0.21379999816417694, -0.1915999948978424, -0.07050000131130219, -0.24120000004768372, -0.010700000450015068, 0.07989999651908875, 0.22120000422000885, 0.07850000262260437, -0.13359999656677246, -0.025699999183416367, 0.0284000001847744, -0.06599999964237213, -0.10649999976158142], [-0.11309999972581863, 0.08529999852180481, 0.11630000174045563, -0.257999986410141, -0.1363999992609024, -0.11169999837875366, 0.02539999969303608, -0.11559999734163284, -0.08049999922513962, -0.11949999630451202, -0.1225999966263771, 0.03400000184774399, -0.02070000022649765, 0.09019999951124191, 0.05550000071525574, -0.17520000040531158, 0.005200000014156103, 0.07109999656677246, -0.24560000002384186, 0.003800000064074993, 0.02669999934732914, -0.11640000343322754, 0.3546000123023987, -0.03280000016093254, -0.11620000004768372, 0.004399999976158142, -0.19539999961853027, -0.04399999976158142, -0.035100001841783524, 0.03660000115633011, -0.2865000069141388, 0.026900000870227814, -0.16040000319480896, -0.0066999997943639755, -0.05900000035762787, -0.020999999716877937, 0.0957999974489212, 0.12700000405311584, 0.2061000019311905, 0.0142000000923872, -0.02930000051856041, -0.12300000339746475, 0.020400000736117363, 0.030400000512599945, 0.04439999908208847, -0.010099999606609344, -0.04580000042915344, 0.09009999781847, 0.018400000408291817, 0.163100004196167, -0.16850000619888306, 0.0828000009059906, -0.16030000150203705, -0.009700000286102295, 0.12110000103712082, 0.014700000174343586, -0.15549999475479126, -0.34369999170303345, 0.09889999777078629, 0.09780000150203705, -0.018300000578165054, -0.15690000355243683, -0.03889999911189079, 0.10809999704360962], [-0.11590000241994858, 0.0820000022649765, -0.21930000185966492, -0.06509999930858612, 0.10809999704360962, -0.04430000111460686, -0.22669999301433563, 0.13910000026226044, 0.14390000700950623, -0.054999999701976776, 0.04149999842047691, 0.1216999962925911, -0.2370000034570694, 0.0010999999940395355, 0.05959999933838844, -0.01769999973475933, -0.031700000166893005, -0.1688999980688095, -0.08959999680519104, 0.09950000047683716, -0.12809999287128448, -0.26660001277923584, 0.09769999980926514, -0.12890000641345978, 0.05959999933838844, -0.05249999836087227, -0.12309999763965607, 0.1396999955177307, 0.10859999805688858, -0.06530000269412994, 0.2337999939918518, 0.001500000013038516, 0.155799999833107, -0.0949999988079071, 0.12530000507831573, -0.0414000004529953, -0.04989999905228615, -0.04740000143647194, -0.05350000038743019, -0.05249999836087227, -0.07940000295639038, -0.05040000006556511, -0.015799999237060547, 0.08150000125169754, -0.06610000133514404, -0.05130000039935112, 0.2168000042438507, 0.14319999516010284, 0.04320000112056732, 0.11020000278949738, 0.08699999749660492, -0.007400000002235174, -0.28380000591278076, -0.15379999577999115, 0.04259999841451645, -0.0008999999845400453, 0.2669000029563904, 0.062300000339746475, 0.00989999994635582, -0.07779999822378159, -0.18410000205039978, -0.21080000698566437, -0.03290000185370445, 0.17430000007152557], [-0.05220000073313713, 0.0731000006198883, 0.07909999787807465, 0.11460000276565552, -0.13840000331401825, -0.1680999994277954, -0.043800000101327896, 0.09549999982118607, -0.10220000147819519, -0.0697999969124794, 0.14110000431537628, -0.08150000125169754, -0.2045000046491623, -0.07500000298023224, 0.05620000138878822, 0.08950000256299973, -0.36309999227523804, 0.00419999985024333, 0.13600000739097595, -0.17110000550746918, 0.04450000077486038, 0.10080000013113022, -0.037700001150369644, -0.1371999979019165, -0.16349999606609344, -0.08900000154972076, -0.3630000054836273, -0.10729999840259552, 0.01679999940097332, 0.09480000287294388, -0.00430000014603138, -0.08079999685287476, 0.09520000219345093, 0.029500000178813934, 0.11100000143051147, -0.13699999451637268, 0.07779999822378159, -0.05810000002384186, -0.08079999685287476, 0.05829999968409538, -0.04479999840259552, 0.04879999905824661, 0.14419999718666077, 0.1386999934911728, 0.13429999351501465, -0.04800000041723251, -0.09830000251531601, 0.2295999974012375, 0.02290000021457672, 0.0010999999940395355, 0.06120000034570694, -0.029400000348687172, 0.014999999664723873, 0.10289999842643738, 0.2093999981880188, -0.08370000123977661, 0.05550000071525574, 0.01140000019222498, -0.1842000037431717, 0.13500000536441803, 0.18870000541210175, 0.11819999665021896, 0.22010000050067902, 0.004800000227987766], [-0.16680000722408295, 0.04670000076293945, 0.13269999623298645, -0.15629999339580536, -0.09130000323057175, 0.08889999985694885, 0.09480000287294388, 0.04830000177025795, -0.05350000038743019, 0.06889999657869339, 0.10689999908208847, 0.042899999767541885, 0.01979999989271164, -0.23420000076293945, 0.057500001043081284, -0.006800000090152025, 0.08730000257492065, 0.16009999811649323, -0.10719999670982361, -0.14190000295639038, 0.20579999685287476, 0.06909999996423721, -0.11649999767541885, -0.010300000198185444, 0.10909999907016754, 0.04610000178217888, 0.050999999046325684, -0.010499999858438969, -0.029200000688433647, -0.022299999371170998, 0.14659999310970306, -0.1738000065088272, 0.10930000245571136, -0.05079999938607216, -0.05829999968409538, -0.1348000019788742, 0.02930000051856041, -0.16220000386238098, 0.20600000023841858, -0.1347000002861023, -0.1216999962925911, -0.07169999927282333, -0.13289999961853027, -0.1809999942779541, -0.0940999984741211, 0.1096000000834465, -0.09149999916553497, 0.13539999723434448, -0.023099999874830246, -0.021800000220537186, -0.12520000338554382, -0.022199999541044235, 0.039500001817941666, -0.06989999860525131, -0.3073999881744385, -0.09640000015497208, 0.3222000002861023, -0.13979999721050262, -0.06560000032186508, 0.03099999949336052, 0.22859999537467957, -0.21549999713897705, 0.12929999828338623, 0.11029999703168869], [0.00019999999494757503, -0.04650000110268593, -0.039000000804662704, -0.05380000174045563, -0.033799998462200165, -0.0066999997943639755, -0.05590000003576279, 0.09449999779462814, -0.039400000125169754, -0.23070000112056732, -0.06109999865293503, 0.2705000042915344, -0.1973000019788742, 0.06069999933242798, -0.10920000076293945, 0.15809999406337738, -0.10949999839067459, -0.04320000112056732, 0.032099999487400055, 0.1615999937057495, 0.25110000371932983, 0.062300000339746475, -0.10570000112056732, 0.1525000035762787, 0.12439999729394913, 0.3479999899864197, 0.11020000278949738, 0.20329999923706055, 0.12630000710487366, 0.005900000222027302, -0.06279999762773514, -0.19619999825954437, 0.07280000299215317, -0.044199999421834946, -0.04149999842047691, -0.07240000367164612, -0.07000000029802322, -0.12319999933242798, -0.19599999487400055, 0.11739999800920486, 0.07429999858140945, 0.10450000315904617, 0.11069999635219574, -0.16380000114440918, 0.010300000198185444, -0.035999998450279236, 0.12120000272989273, -0.0414000004529953, 0.011699999682605267, 0.18490000069141388, 0.019600000232458115, 0.02449999935925007, 0.0006000000284984708, 0.09740000218153, -0.05739999935030937, -0.008999999612569809, -0.27790001034736633, -0.18979999423027039, -0.020500000566244125, 0.16869999468326569, 0.06390000134706497, -0.03669999912381172, 0.04780000075697899, 0.14229999482631683], [0.06449999660253525, -0.014399999752640724, -0.15710000693798065, -0.12309999763965607, -0.20559999346733093, -0.049800001084804535, 0.09149999916553497, -0.12690000236034393, -0.08229999989271164, 0.08320000022649765, 0.10719999670982361, -0.0052999998442828655, -0.1648000031709671, -0.12860000133514404, -0.16699999570846558, 0.053700000047683716, -0.028300000354647636, 0.05869999900460243, 0.1379999965429306, -0.12319999933242798, -0.06440000236034393, -0.2401999980211258, 0.02590000070631504, 0.2538999915122986, 0.02250000089406967, -0.22920000553131104, -0.0421999990940094, 0.1826000064611435, -0.08219999819993973, 0.25130000710487366, 0.09749999642372131, -0.14579999446868896, -0.016499999910593033, 0.25609999895095825, -0.12030000239610672, 0.09989999979734421, 0.02449999935925007, -0.01979999989271164, -0.06859999895095825, -0.003000000026077032, -0.04390000179409981, -0.21699999272823334, 0.04450000077486038, -0.14489999413490295, 0.07919999957084656, -0.07190000265836716, -0.0689999982714653, -0.2732999920845032, 0.0835999995470047, 0.1581999957561493, 0.1444000005722046, 0.13429999351501465, -0.09520000219345093, -0.05889999866485596, -0.00860000029206276, 0.05790000036358833, 0.1316000074148178, -0.044599998742341995, 0.08709999918937683, 0.0015999999595806003, 0.12600000202655792, 0.15649999678134918, -0.13519999384880066, 0.035100001841783524], [-0.06480000168085098, 0.00989999994635582, -0.010599999688565731, -0.01889999955892563, -0.04670000076293945, -0.27810001373291016, -0.04830000177025795, 0.10279999673366547, 0.04439999908208847, 0.10050000250339508, 0.08550000190734863, -0.10360000282526016, 0.011300000362098217, -0.10209999978542328, -0.18240000307559967, -0.13199999928474426, -0.038100000470876694, -0.06350000202655792, -0.0008999999845400453, 0.11429999768733978, 0.2937000095844269, -0.04580000042915344, -0.044199999421834946, -0.05420000106096268, -0.14710000157356262, 0.20200000703334808, 0.11739999800920486, 0.06560000032186508, 0.03310000151395798, -0.15469999611377716, 0.1193000003695488, -0.06780000030994415, -0.08540000021457672, -0.10819999873638153, 0.0357000008225441, 0.065700002014637, 0.08129999786615372, -0.12139999866485596, 0.2313999980688095, -0.03999999910593033, -0.0869000032544136, 0.12139999866485596, -0.16599999368190765, 0.16359999775886536, 0.0731000006198883, -0.11240000277757645, -0.11670000106096268, -0.3310000002384186, -0.02199999988079071, -0.20960000157356262, -0.06949999928474426, 0.039000000804662704, -0.20739999413490295, -0.1331000030040741, 0.23109999299049377, 0.14180000126361847, -0.03009999915957451, 0.031599998474121094, -0.1501999944448471, 0.06509999930858612, 0.10249999910593033, 0.09139999747276306, -0.1436000019311905, 0.05660000070929527], [0.2190999984741211, 0.1420000046491623, -0.042500000447034836, -0.045899998396635056, -0.10540000349283218, -0.053700000047683716, -0.10660000145435333, 0.07069999724626541, -0.08839999884366989, -0.15449999272823334, 0.06710000336170197, -0.04729999974370003, 0.02329999953508377, 0.06750000268220901, -0.1460999995470047, -0.029500000178813934, -0.15850000083446503, -0.051600001752376556, -0.11640000343322754, 0.05920000001788139, -0.15889999270439148, 0.2937999963760376, 0.08420000225305557, -0.16419999301433563, 0.27219998836517334, -0.09889999777078629, -0.06159999966621399, -0.008299999870359898, 0.19009999930858612, -0.0869000032544136, 0.12460000067949295, 0.005900000222027302, -0.2597000002861023, 0.05350000038743019, 0.20909999310970306, 0.25060001015663147, -0.07639999687671661, -0.10140000283718109, 0.06350000202655792, -0.23499999940395355, -0.04010000079870224, 0.10989999771118164, 0.026900000870227814, -0.15320000052452087, 0.08709999918937683, -0.03709999844431877, -0.2809000015258789, -0.05950000137090683, 0.061000000685453415, 0.12380000203847885, -0.014299999922513962, -0.04769999906420708, -0.08579999953508377, -0.044199999421834946, -0.22859999537467957, -0.14409999549388885, -0.06700000166893005, 0.0005000000237487257, 0.04439999908208847, -0.007899999618530273, -0.0071000000461936, 0.0017000000225380063, -0.012500000186264515, -0.04749999940395355], [-0.14229999482631683, -0.14069999754428864, -0.12999999523162842, 0.13779999315738678, 0.23520000278949738, 0.015300000086426735, -0.051600001752376556, -0.020800000056624413, -0.1964000016450882, 0.08449999988079071, -0.12300000339746475, 0.2921999990940094, 0.10620000213384628, -0.20000000298023224, -0.2363000065088272, 0.05249999836087227, 0.07699999958276749, -0.10939999669790268, 0.07400000095367432, 0.08290000259876251, -0.16769999265670776, 0.11500000208616257, -0.1923000067472458, -0.12160000205039978, -0.1754000037908554, 0.03060000017285347, -0.06449999660253525, -0.09369999915361404, -0.008999999612569809, 0.10480000078678131, 0.06809999793767929, 0.0026000000070780516, -0.17970000207424164, 0.1988999992609024, -0.031300000846385956, -0.008100000210106373, -0.09570000320672989, -0.05590000003576279, 0.16369999945163727, -0.07079999893903732, 0.045099999755620956, -0.1136000007390976, -0.00019999999494757503, 0.12860000133514404, -0.013100000098347664, 0.004000000189989805, 0.02700000</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>[[[0.17430000007152557, -0.0024999999441206455, -0.10170000046491623, 0.021299999207258224, 0.01850000023841858, -0.023800000548362732, -0.027000000700354576, -0.011800000444054604, 0.06109999865293503, 0.057999998331069946, -0.10180000215768814, 0.09390000253915787, -0.08609999716281891, 0.15520000457763672, -0.16990000009536743, -0.07129999995231628, 0.005900000222027302, 0.02800000086426735, 0.03579999879002571, -0.11540000140666962, 0.03180000185966492, -0.05429999902844429, -0.024000000208616257, 0.065700002014637, -0.0722000002861023, -0.11990000307559967, 0.06239999830722809, 0.11190000176429749, 0.00930000003427267, -0.06109999865293503, -0.07039999961853027, 0.10989999771118164, -0.009200000204145908, 0.07569999992847443, 0.02419999986886978, 0.1371999979019165, -0.01720000058412552, -0.040800001472234726, 0.12430000305175781, 0.0575999990105629, 0.0003000000142492354, -0.0632999986410141, -0.020600000396370888, 0.012000000104308128, 0.01119999960064888, 0.14949999749660492, 0.11079999804496765, -0.12049999833106995, 0.11680000275373459, -0.12439999729394913, 0.1152999997138977, 0.05920000001788139, 0.03739999979734421, -0.020099999383091927, -0.02850000001490116, 0.15469999611377716, -0.14630000293254852, 0.03819999843835831, 0.07249999791383743, -0.06379999965429306, 0.07450000196695328, 0.0414000004529953, -0.05550000071525574, -0.029400000348687172], [-0.16859999299049377, 0.08250000327825546, 0.1266999989748001, -0.06939999759197235, -0.01640000008046627, 0.08760000020265579, 0.11069999635219574, -0.10909999907016754, -0.07840000092983246, -0.04129999876022339, 0.03449999913573265, -0.07930000126361847, 0.07029999792575836, -0.10429999977350235, 0.04360000044107437, 0.0608999989926815, 0.1704999953508377, -0.08420000225305557, -0.025599999353289604, -0.017899999395012856, -0.055399999022483826, -0.016300000250339508, -0.03840000182390213, 0.0013000000035390258, 0.03819999843835831, 0.06849999725818634, -0.08879999816417694, -0.04439999908208847, 0.002099999925121665, 0.03920000046491623, 0.06719999760389328, 0.007799999788403511, -0.013799999840557575, -0.06800000369548798, -0.14419999718666077, -0.01940000057220459, 0.042100001126527786, 0.12099999934434891, -0.10140000283718109, -0.07159999758005142, 0.03790000081062317, 0.12189999967813492, -0.003100000089034438, 0.03849999979138374, 0.0771000012755394, -0.16740000247955322, -0.11339999735355377, 0.10279999673366547, -0.0478999987244606, 0.14890000224113464, 0.01209999993443489, -0.06909999996423721, -0.027699999511241913, 0.06459999829530716, 0.006200000178068876, -0.13899999856948853, 0.17630000412464142, -0.025599999353289604, -0.12939999997615814, 0.09610000252723694, -0.1768999993801117, 0.03400000184774399, 0.042899999767541885, -0.09929999709129333]], [[0.042500000447034836, -0.21459999680519104, -0.1006999984383583, 0.0017000000225380063, 0.22130000591278076, -0.10279999673366547, -0.08560000360012054, -0.0052999998442828655, 0.1973000019788742, -0.2612999975681305, -0.12470000237226486, -0.1598999947309494, 0.17870000004768372, 0.1632000058889389, -0.24629999697208405, -0.07050000131130219, -0.050200000405311584, 0.14329999685287476, -0.1670999974012375, -0.2624000012874603, 0.25279998779296875, -0.1898999959230423, 0.18449999392032623, 0.20600000023841858, -0.14249999821186066, 0.05220000073313713, -0.16500000655651093, 0.1354999989271164, 0.10949999839067459, -0.33219999074935913, -0.09920000284910202, -0.1103999987244606, 0.025299999862909317, 0.5044999718666077, -0.14139999449253082, -0.20960000157356262, -0.1996999979019165, -0.2004999965429306, -0.04410000145435333, -0.4839000105857849, -0.11140000075101852, -0.03840000182390213, -0.09070000052452087, -0.0272000003606081, -0.23729999363422394, 0.031599998474121094, 0.20469999313354492, -0.09390000253915787, -0.016599999740719795, -0.24940000474452972, 0.28839999437332153, 0.32710000872612, 0.057100001722574234, -0.2386000007390976, -0.13819999992847443, -0.1282999962568283, -0.23440000414848328, -0.05849999934434891, -0.18729999661445618, 0.08309999853372574, 0.20669999718666077, 0.15860000252723694, -0.16979999840259552, -0.009200000204145908], [0.04560000076889992, 0.20250000059604645, 0.19249999523162842, -0.4171999990940094, 0.1518000066280365, -0.10559999942779541, -0.18539999425411224, -0.04280000180006027, -0.10660000145435333, 0.05889999866485596, -0.11909999698400497, -0.07590000331401825, 0.08839999884366989, -0.2224999964237213, -0.09369999915361404, 0.07769999653100967, 0.0820000022649765, 0.007799999788403511, 0.1987999975681305, 0.3253999948501587, -0.19130000472068787, 0.08500000089406967, -0.052400000393390656, -0.058400001376867294, 0.05719999969005585, -0.14820000529289246, -0.03359999880194664, 0.11349999904632568, -0.041200000792741776, -0.19439999759197235, -0.13249999284744263, 0.024299999698996544, 0.16060000658035278, 0.016599999740719795, -0.03790000081062317, -0.024900000542402267, -0.2443999946117401, -0.07940000295639038, -0.2854999899864197, -0.02019999921321869, -0.011800000444054604, 0.03449999913573265, -0.07119999825954437, 0.10050000250339508, 0.06769999861717224, -0.08320000022649765, 0.08540000021457672, -0.007799999788403511, -0.029999999329447746, -0.07599999755620956, -0.08860000222921371, 0.20160000026226044, 0.02669999934732914, 0.08810000121593475, 0.028699999675154686, 0.062300000339746475, 0.01720000058412552, -0.008999999612569809, -0.06700000166893005, -0.03269999846816063, 0.2750000059604645, -0.16699999570846558, 0.013199999928474426, -0.010400000028312206], [0.15039999783039093, 0.2630999982357025, -0.2054000049829483, -0.22579999268054962, -0.036400001496076584, -0.06030000001192093, 0.22380000352859497, 0.15119999647140503, -0.13269999623298645, 0.1988999992609024, -0.4221000075340271, -0.02800000086426735, -0.014499999582767487, -0.042899999767541885, 0.15189999341964722, 0.024700000882148743, 0.19269999861717224, -0.05810000002384186, 0.11919999867677689, -0.02889999933540821, 0.23880000412464142, 0.05249999836087227, -0.19169999659061432, 0.016899999231100082, -0.17910000681877136, 0.1834000051021576, -0.08150000125169754, -0.1898999959230423, -0.11540000140666962, 0.02070000022649765, 0.13349999487400055, 0.24779999256134033, -0.09690000116825104, -0.09589999914169312, -0.08389999717473984, 0.2087000012397766, 0.007600000128149986, -0.12359999865293503, -0.05869999900460243, -0.0560000017285347, -0.060600001364946365, 0.17949999868869781, 0.1607999950647354, 0.17470000684261322, -0.03909999877214432, -0.12359999865293503, -0.1551000028848648, 0.09359999746084213, -0.21199999749660492, 0.3684999942779541, 0.005100000184029341, -0.2401999980211258, -0.14830000698566437, 0.30149999260902405, -0.07649999856948853, -0.0034000000450760126, -0.01860000006854534, 0.16169999539852142, 0.12030000239610672, -0.18029999732971191, 0.11079999804496765, 0.028699999675154686, 0.22830000519752502, 0.12020000070333481], [0.0714000016450882, -0.00930000003427267, 0.1518000066280365, 0.17000000178813934, 0.03929999843239784, 0.24860000610351562, -0.13650000095367432, -0.01140000019222498, -0.13680000603199005, -0.09189999848604202, -0.07100000232458115, 0.09399999678134918, 0.07289999723434448, -0.15889999270439148, 0.188400000333786, -0.06589999794960022, -0.06970000267028809, 0.02290000021457672, -0.055399999022483826, -0.35830000042915344, -0.0544000007212162, -0.14380000531673431, 0.17980000376701355, -0.27070000767707825, 0.042899999767541885, -0.0771000012755394, -0.09520000219345093, 0.15410000085830688, 0.054499998688697815, 0.04129999876022339, -0.046799998730421066, -0.13619999587535858, 0.003800000064074993, -0.09600000083446503, -0.17820000648498535, 0.029999999329447746, 0.03929999843239784, -0.17069999873638153, -0.05249999836087227, 0.012600000016391277, 0.04019999876618385, 0.12770000100135803, -0.10289999842643738, -0.037300001829862595, 0.10599999874830246, -0.08649999648332596, 0.09220000356435776, -0.23190000653266907, 0.06700000166893005, -0.04919999837875366, -0.10270000249147415, 0.07129999995231628, 0.07519999891519547, -0.11649999767541885, -0.10790000110864639, 0.019700000062584877, -0.03280000016093254, 0.10270000249147415, 0.2476000040769577, 0.13850000500679016, -0.19509999454021454, 0.18379999697208405, 0.006800000090152025, 0.20080000162124634], [0.03869999945163727, -0.131400004029274, -0.05139999836683273, -0.029600000008940697, -0.2727999985218048, 0.0364999994635582, -0.05820000171661377, 0.16380000114440918, -0.14090000092983246, -0.21199999749660492, 0.12950000166893005, -0.06920000165700912, -0.0008999999845400453, 0.19099999964237213, -0.03310000151395798, 0.06469999998807907, 0.0778999999165535, -0.01640000008046627, -0.03579999879002571, 0.3027999997138977, -0.11869999766349792, -0.25110000371932983, -0.12919999659061432, 0.10859999805688858, -0.01640000008046627, -0.08510000258684158, 0.07119999825954437, -0.003800000064074993, -0.03099999949336052, -0.423799991607666, 0.03849999979138374, 0.24369999766349792, 0.024399999529123306, -0.07010000199079514, -0.10419999808073044, 0.04610000178217888, 0.11540000140666962, -0.13609999418258667, -0.011800000444054604, 0.06080000102519989, -0.01140000019222498, -0.1080000028014183, 0.08160000294446945, 0.05339999869465828, 0.20180000364780426, 0.11749999970197678, -0.22280000150203705, 0.049400001764297485, -0.20999999344348907, 0.00570000009611249, 0.07970000058412552, 0.08959999680519104, 0.07930000126361847, 0.2298000007867813, -0.20029999315738678, 0.034699998795986176, 0.08399999886751175, -0.14800000190734863, 0.07689999788999557, 0.04470000043511391, 0.01140000019222498, 0.10859999805688858, 0.01489999983459711, 0.014499999582767487], [0.33629998564720154, -0.02160000056028366, -0.057500001043081284, -0.1882999986410141, 0.08540000021457672, 0.10719999670982361, 0.04520000144839287, -0.1404999941587448, -0.2224999964237213, 0.10779999941587448, -0.0027000000700354576, -0.057999998331069946, -0.08100000023841858, 0.03060000017285347, -0.27390000224113464, -0.003800000064074993, 0.03139999881386757, -0.028699999675154686, 0.1128000020980835, 0.028999999165534973, 0.09290000051259995, 0.16509999334812164, 0.09510000050067902, -0.02329999953508377, -0.07450000196695328, 0.08900000154972076, 0.14000000059604645, 0.18289999663829803, -0.050599999725818634, 0.09239999949932098, -0.05920000001788139, -0.13109999895095825, 0.042100001126527786, -0.3050000071525574, -0.041600000113248825, 0.0632999986410141, 0.045899998396635056, 0.02969999983906746, -0.01640000008046627, -0.11969999969005585, -0.19020000100135803, 0.09880000352859497, -0.08020000159740448, 0.22939999401569366, 0.07900000363588333, 0.040800001472234726, -0.11469999700784683, 0.26579999923706055, -0.051600001752376556, -0.0649000033736229, 0.08299999684095383, -0.03799999877810478, 0.0340999998152256, 0.259799987077713, 0.061400000005960464, -0.11810000240802765, 0.10840000212192535, -0.16609999537467957, -0.14380000531673431, -0.3018999993801117, -0.2630999982357025, 0.07720000296831131, 0.08889999985694885, 0.23469999432563782], [0.2468000054359436, 0.1477999985218048, 0.10970000177621841, 0.05700000002980232, 0.03970000147819519, -0.17960000038146973, -0.1225999966263771, -0.0575999990105629, -0.1363999992609024, 0.13940000534057617, 0.0957999974489212, -0.0812000036239624, -0.007400000002235174, 0.006899999920278788, 0.12970000505447388, -0.011900000274181366, 0.20960000157356262, 0.2870999872684479, 0.19189999997615814, 0.051500000059604645, 0.20509999990463257, 0.10949999839067459, 0.05829999968409538, -0.13189999759197235, 0.028599999845027924, -0.01590000092983246, 0.1445000022649765, 0.18160000443458557, 0.003000000026077032, -0.16699999570846558, -0.04800000041723251, 0.10350000113248825, -0.1251000016927719, 0.12020000070333481, 0.07289999723434448, -0.0681999996304512, 0.0284000001847744, 0.2304999977350235, -0.1298000067472458, 0.025699999183416367, 0.10279999673366547, 0.1720999926328659, 0.3215000033378601, -0.055799998342990875, 0.1062999963760376, 0.20260000228881836, -0.0640999972820282, 0.16009999811649323, -0.15629999339580536, 0.16419999301433563, -0.053599998354911804, -0.010499999858438969, -0.22669999301433563, 0.12870000302791595, 0.003599999938160181, 0.16060000658035278, 0.31299999356269836, 0.03500000014901161, 0.06509999930858612, 0.18960000574588776, -0.15970000624656677, -0.09000000357627869, 0.01889999955892563, 0.15530000627040863], [-0.0640999972820282, -0.00039999998989515007, -0.16099999845027924, 0.12770000100135803, -0.1265999972820282, -0.16449999809265137, 0.11079999804496765, 0.02160000056028366, -0.04800000041723251, 0.013000000268220901, 0.1128000020980835, 0.061400000005960464, -0.08990000188350677, 0.14630000293254852, 0.3617999851703644, -0.2433999925851822, 0.13660000264644623, -0.054999999701976776, 0.15219999849796295, -0.11020000278949738, -0.18729999661445618, -0.06509999930858612, 0.031599998474121094, -0.0031999999191612005, -0.10260000079870224, 0.21040000021457672, -0.01850000023841858, 0.0348999984562397, 0.01720000058412552, 0.1316000074148178, 0.025299999862909317, 0.25099998712539673, 0.02319999970495701, -0.00860000029206276, 0.0038999998942017555, 0.10779999941587448, -0.054499998688697815, -0.19910000264644623, -0.18440000712871552, 0.0885000005364418, -0.07440000027418137, 0.22220000624656677, -0.10379999876022339, -0.16300000250339508, -0.010099999606609344, 0.08980000019073486, -0.0340999998152256, 0.06430000066757202, 0.09350000321865082, -0.20739999413490295, -0.19599999487400055, 0.13539999723434448, 0.06509999930858612, -0.33629998564720154, 0.008799999952316284, -0.14100000262260437, 0.0031999999191612005, -0.29269999265670776, 0.05050000175833702, -0.061400000005960464, 0.0803999975323677, 0.28369998931884766, -0.1647000014781952, -0.032600000500679016], [-0.004800000227987766, -0.19179999828338623, 0.07100000232458115, -0.039900001138448715, 0.1120000034570694, -0.02590000070631504, -0.0957999974489212, 0.018300000578165054, -0.011099999770522118, 0.14020000398159027, -0.030700000002980232, 0.1234000027179718, -0.06509999930858612, -0.08309999853372574, -0.08290000259876251, 0.022299999371170998, -0.07980000227689743, -0.22269999980926514, -0.13009999692440033, -0.22669999301433563, 0.022700000554323196, -0.02930000051856041, 0.13189999759197235, -0.09880000352859497, 0.01549999974668026, -0.048900000751018524, -0.11890000104904175, -0.1720999926328659, -0.010900000110268593, -0.17389999330043793, -0.07720000296831131, 0.13940000534057617, -0.006599999964237213, -0.3034999966621399, -0.05790000036358833, 0.10209999978542328, 0.16830000281333923, 0.1881999969482422, -0.1868000030517578, 0.047600001096725464, -0.1143999993801117, -0.0478999987244606, -0.05420000106096268, -0.24609999358654022, 0.14880000054836273, 0.12300000339746475, 0.1145000010728836, -0.24469999969005585, 0.13580000400543213, 0.0723000019788742, 0.2287999987602234, 0.0333000011742115, 0.1615000069141388, -0.22499999403953552, -0.09960000216960907, -0.08240000158548355, -0.05719999969005585, -0.2583000063896179, -0.021299999207258224, 0.12219999730587006, -9.999999747378752e-05, 0.21549999713897705, 0.07410000264644623, -0.10620000213384628], [0.14329999685287476, 0.06350000202655792, 0.22859999537467957, -0.12060000002384186, 0.163100004196167, -0.0934000015258789, -0.10450000315904617, 0.08410000056028366, 0.11919999867677689, 0.10769999772310257, 9.999999747378752e-05, -0.05260000005364418, -0.10589999705553055, 0.17720000445842743, -0.15950000286102295, 0.14980000257492065, 0.07509999722242355, 0.05559999868273735, 0.12229999899864197, -0.11829999834299088, 0.08980000019073486, -0.19089999794960022, -0.09220000356435776, -0.2249000072479248, -0.05469999834895134, 0.05889999866485596, 0.14270000159740448, -0.14419999718666077, -0.020099999383091927, -0.10130000114440918, -0.028599999845027924, 0.04619999974966049, 0.04019999876618385, 0.2312999963760376, -0.01810000091791153, 0.06849999725818634, -0.03280000016093254, -0.1648000031709671, 0.015300000086426735, -0.01600000075995922, 0.22349999845027924, -0.34459999203681946, -0.007600000128149986, -0.018699999898672104, 0.16099999845027924, -0.027300000190734863, 0.05040000006556511, -0.061900001019239426, 0.0860000029206276, -0.05389999970793724, 0.044599998742341995, -0.1890999972820282, -0.14149999618530273, -0.0026000000070780516, -0.05900000035762787, -0.3874000012874603, -0.23430000245571136, -0.1324000060558319, -0.1785999983549118, -0.07050000131130219, -0.026900000870227814, 0.0019000000320374966, -0.08810000121593475, 0.17159999907016754], [-0.07000000029802322, -0.02710000053048134, 0.015300000086426735, 0.17980000376701355, 0.07720000296831131, 0.03480000048875809, 0.09560000151395798, -0.13809999823570251, -0.09749999642372131, -0.03460000082850456, -0.02459999918937683, -0.04619999974966049, -0.3463999927043915, -0.15360000729560852, 0.19130000472068787, 0.19689999520778656, -0.01720000058412552, 0.1265999972820282, -0.09229999780654907, 0.12030000239610672, -0.18410000205039978, 0.06669999659061432, 0.032999999821186066, -0.23909999430179596, -0.08269999921321869, 0.1899999976158142, -0.03880000114440918, 0.006300000008195639, -0.01810000091791153, 0.07039999961853027, 0.08959999680519104, 0.31520000100135803, 0.133200004696846, 0.06509999930858612, -0.27649998664855957, -0.11060000211000443, 0.06960000097751617, -0.1777999997138977, 0.09920000284910202, -0.1500999927520752, -0.12449999898672104, 0.1315000057220459, 0.1453000009059906, 0.04859999939799309, 0.018699999898672104, -0.005900000222027302, -0.1551000028848648, -0.16410000622272491, 0.11699999868869781, -0.11209999769926071, 0.14409999549388885, -0.06069999933242798, -0.06040000170469284, 0.11630000174045563, 0.15649999678134918, 0.01590000092983246, 0.08250000327825546, -0.11559999734163284, 0.13670000433921814, -0.08160000294446945, -0.05620000138878822, -0.21619999408721924, -0.164000004529953, -0.20260000228881836], [-0.10729999840259552, 0.02199999988079071, -0.009800000116229057, 0.06270000338554382, -0.008899999782443047, 0.18379999697208405, -0.1858000010251999, 0.09510000050067902, -0.22669999301433563, 0.03709999844431877, -0.05999999865889549, -0.20319999754428864, 0.029899999499320984, 0.033900000154972076, 0.039900001138448715, -0.2223999947309494, -0.21629999577999115, -0.16419999301433563, -0.24490000307559967, -0.1754000037908554, -0.015200000256299973, -0.13120000064373016, 0.0044999998062849045, -0.0885000005364418, 0.14180000126361847, 0.1014999970793724, 0.0608999989926815, 0.23680000007152557, -0.041099999099969864, -0.22020000219345093, 0.09130000323057175, -0.06849999725818634, 0.3147999942302704, 0.26249998807907104, 0.13860000669956207, -0.1436000019311905, 0.13500000536441803, 0.27880001068115234, 0.06629999727010727, 0.10530000180006027, -0.0737999975681305, -0.00039999998989515007, -0.16940000653266907, -0.15680000185966492, -0.18930000066757202, -0.007400000002235174, -0.10689999908208847, 0.004600000102072954, 0.31540000438690186, 0.0019000000320374966, -0.02759999968111515, 0.16220000386238098, 0.23810000717639923, -0.06809999793767929, -0.0024999999441206455, -0.09629999846220016, -0.2702000141143799, -0.04230000078678131, 0.12530000507831573, 0.31060001254081726, -0.05009999871253967, 0.13420000672340393, -0.13979999721050262, 0.012400000356137753], [0.00800000037997961, 0.07109999656677246, 0.08219999819993973, 0.06960000097751617, -0.04259999841451645, -0.1940000057220459, 0.0215000007301569, -0.0008999999845400453, -0.24959999322891235, 0.014499999582767487, 0.15569999814033508, -0.11089999973773956, -0.11110000312328339, 0.1421000063419342, 0.29409998655319214, 0.24879999458789825, -0.16380000114440918, -0.08760000020265579, -0.06310000270605087, 0.10580000281333923, 0.08900000154972076, 0.08089999854564667, -0.026200000196695328, 0.17430000007152557, 0.054999999701976776, 0.07900000363588333, 0.0869000032544136, -0.17649999260902405, -0.011800000444054604, 0.21639999747276306, -0.03440000116825104, 0.30469998717308044, 0.1412000060081482, -0.13590000569820404, -0.0364999994635582, -0.025200000032782555, -0.10130000114440918, 0.1768999993801117, 0.040300000458955765, -0.12710000574588776, -0.062199998646974564, 0.04910000041127205, -0.13670000433921814, 0.1665000021457672, 0.14180000126361847, 0.1160999983549118, -0.055799998342990875, 0.1339000016450882, 0.13009999692440033, 0.14380000531673431, -0.19900000095367432, 0.17020000517368317, -0.2599000036716461, 0.001500000013038516, -0.26269999146461487, -0.025299999862909317, 0.06880000233650208, 0.16179999709129333, 0.13699999451637268, -0.18160000443458557, -0.045499999076128006, 0.04179999977350235, -0.048500001430511475, -0.07370000332593918], [-0.08889999985694885, 0.10899999737739563, 0.17980000376701355, -0.18140000104904175, -0.032499998807907104, -0.032999999821186066, -0.026399999856948853, -0.0934000015258789, -0.08179999887943268, -0.16680000722408295, -0.2134999930858612, 0.029899999499320984, 0.010300000198185444, 0.15139999985694885, -0.0478999987244606, -0.2957000136375427, -0.07660000026226044, 0.1274999976158142, -0.36010000109672546, -0.09510000050067902, 0.11540000140666962, -0.14640000462532043, 0.4528999924659729, 0.07840000092983246, -0.09870000183582306, -0.08569999784231186, -0.21850000321865082, 0.05050000175833702, 0.004100000020116568, -0.04019999876618385, -0.334199994802475, -0.16509999334812164, -0.18029999732971191, -0.0019000000320374966, -0.13230000436306, -0.0034000000450760126, 0.08569999784231186, 0.2102999985218048, 0.15150000154972076, 0.065700002014637, 0.05530000105500221, -0.16369999945163727, -0.044599998742341995, -0.07989999651908875, 0.0877000018954277, -0.0019000000320374966, -0.01119999960064888, 0.03660000115633011, 0.032499998807907104, 0.14319999516010284, -0.11909999698400497, 0.1388999968767166, -0.07599999755620956, -0.1103999987244606, 0.05649999901652336, -0.08229999989271164, -0.15240000188350677, -0.40560001134872437, 0.06440000236034393, 0.250900000333786, 0.060600001364946365, -0.15240000188350677, -0.1264999955892563, 0.05990000069141388], [-0.14100000262260437, 0.04740000143647194, -0.2685000002384186, -0.030799999833106995, 0.15800000727176666, -0.13779999315738678, -0.1987999975681305, 0.15410000085830688, 0.22120000422000885, -0.0997999981045723, 0.038600001484155655, 0.23729999363422394, -0.149399995803833, 0.023099999874830246, -0.04619999974966049, 0.050999999046325684, -0.0812000036239624, -0.22429999709129333, -0.05040000006556511, 0.05700000002980232, -0.0560000017285347, -0.40049999952316284, 0.12929999828338623, -0.16670000553131104, -0.013899999670684338, -0.0031999999191612005, -0.05860000103712082, 0.1014999970793724, 0.20200000703334808, -0.09399999678134918, 0.19120000302791595, -0.022199999541044235, 0.2752000093460083, 0.0778999999165535, 0.15219999849796295, 0.04569999873638153, -0.08630000054836273, -0.11339999735355377, 0.06909999996423721, -0.09619999676942825, -0.2513999938964844, -0.032600000500679016, -0.02319999970495701, 0.07930000126361847, -0.14219999313354492, -0.026399999856948853, 0.288100004196167, 0.015399999916553497, 0.16380000114440918, -0.03720000013709068, 0.08889999985694885, 0.07509999722242355, -0.3276999890804291, -0.14990000426769257, 0.14730000495910645, 0.08739999681711197, 0.22830000519752502, 0.12439999729394913, -0.08489999920129776, -0.22450000047683716, -0.12479999661445618, -0.11720000207424164, -0.04600000008940697, 0.19609999656677246], [-0.09650000184774399, 0.03579999879002571, 0.016899999231100082, 0.05530000105500221, -0.20190000534057617, -0.1793999969959259, -0.07029999792575836, 0.038100000470876694, -0.07760000228881836, 0.06759999692440033, 0.1981000006198883, -0.1257999986410141, -0.18850000202655792, -0.14180000126361847, 0.1264999955892563, 0.1704999953508377, -0.3384000062942505, 0.10689999908208847, 0.2556999921798706, -0.05570000037550926, -0.013000000268220901, 0.07959999889135361, -0.056699998676776886, -0.28360000252723694, -0.10409999638795853, 0.0, -0.35280001163482666, -0.16599999368190765, -0.0017000000225380063, 0.08190000057220459, 0.1023000031709671, -0.10840000212192535, 0.09969999641180038, 0.045499999076128006, 0.19949999451637268, -0.25600001215934753, 0.1526000052690506, 0.008200000040233135, -0.06960000097751617, 0.011900000274181366, -0.10530000180006027, 0.015200000256299973, 0.2597000002861023, 0.19140000641345978, 0.07180000096559525, 0.03830000013113022, -0.018799999728798866, 0.19519999623298645, 0.03700000047683716, 0.05849999934434891, -0.0885000005364418, 0.005400000140070915, -0.10320000350475311, 0.07779999822378159, 0.2249000072479248, 0.07000000029802322, 0.11630000174045563, 0.08749999850988388, -0.22460000216960907, 0.02160000056028366, 0.18320000171661377, -0.007300000172108412, 0.20739999413490295, -0.014499999582767487], [-0.15029999613761902, 0.06620000302791595, 0.1518000066280365, -0.26100000739097595, -0.09929999709129333, 0.09700000286102295, 0.05810000002384186, 0.02239999920129776, -0.11580000072717667, 0.13339999318122864, 0.07249999791383743, -0.042500000447034836, -0.009999999776482582, -0.2802000045776367, 0.0754999965429306, 0.052799999713897705, 0.09560000151395798, 0.17229999601840973, -0.0617000013589859, -0.03150000050663948, 0.23929999768733978, 0.0869000032544136, -0.14319999516010284, -0.0560000017285347, 0.16380000114440918, 0.04050000011920929, 0.0892999991774559, -0.025499999523162842, -0.08240000158548355, -0.04490000009536743, 0.22930000722408295, -0.31380000710487366, 0.022700000554323196, -0.09480000287294388, -0.0348999984562397, -0.20759999752044678, 0.05290000140666962, -0.11159999668598175, 0.1459999978542328, -0.13189999759197235, -0.01979999989271164, -0.051100000739097595, -0.05950000137090683, -0.14720000326633453, 0.028599999845027924, 0.1421000063419342, -0.07540000230073929, 0.17499999701976776, -0.10920000076293945, 0.026499999687075615, -0.13770000636577606, -0.10599999874830246, -0.005900000222027302, -0.01769999973475933, -0.33889999985694885, -0.10980000346899033, 0.38769999146461487, -0.13429999351501465, -0.08139999955892563, -0.0017000000225380063, 0.23309999704360962, -0.3296999931335449, 0.13279999792575836, 0.10019999742507935], [-0.041600000113248825, -0.1151999980211258, -0.03280000016093254, -0.04439999908208847, 0.05220000073313713, -0.007199999876320362, -0.07850000262260437, 0.14990000426769257, -0.03290000185370445, -0.27000001072883606, -0.1624000072479248, 0.3361999988555908, -0.2110999971628189, 0.13600000739097595, -0.21140000224113464, 0.18880000710487366, -0.16539999842643738, -0.14900000393390656, -0.023900000378489494, 0.07100000232458115, 0.24979999661445618, -0.03999999910593033, -0.11110000312328339, 0.18889999389648438, 0.10180000215768814, 0.37950000166893005, 0.12349999696016312, 0.20180000364780426, 0.2101999968290329, -0.03909999877214432, -0.12250000238418579, -0.20800000429153442, 0.07609999924898148, 0.0044999998062849045, 0.04430000111460686, 0.009600000455975533, -0.07900000363588333, -0.2623000144958496, -0.13840000331401825, 0.06040000170469284, 0.05820000171661377, 0.1371999979019165, 0.08730000257492065, -0.1274999976158142, -0.14880000054836273, -0.022299999371170998, 0.11060000211000443, -0.10350000113248825, 0.049400001764297485, 0.06289999932050705, 0.10660000145435333, 0.07609999924898148, 0.0006000000284984708, 0.09080000221729279, -0.027499999850988388, -0.09040000289678574, -0.3499000072479248, -0.22769999504089355, -0.1428000032901764, 0.11949999630451202, 0.12559999525547028, 0.02459999918937683, 0.03180000185966492, 0.16200000047683716], [0.02759999968111515, -0.040300000458955765, -0.18539999425411224, -0.08269999921321869, -0.13199999928474426, -0.0714000016450882, 0.0689999982714653, -0.16269999742507935, -0.0406000018119812, 0.033399999141693115, 0.12099999934434891, -0.011699999682605267, -0.10540000349283218, -0.1720000058412552, -0.20180000364780426, 0.04450000077486038, -0.04190000146627426, 0.14149999618530273, 0.19259999692440033, -0.062199998646974564, -0.05040000006556511, -0.2632000148296356, 0.09839999675750732, 0.22660000622272491, 0.04149999842047691, -0.1664000004529953, -0.058800000697374344, 0.1023000031709671, -0.03060000017285347, 0.1988999992609024, 0.15150000154972076, -0.28139999508857727, 0.003800000064074993, 0.30410000681877136, -0.19599999487400055, 0.049400001764297485, 0.039000000804662704, 0.02810000069439411, -0.10859999805688858, -0.027499999850988388, 0.002300000051036477, -0.2498999983072281, 0.03970000147819519, -0.19249999523162842, 0.12489999830722809, -0.12300000339746475, 0.0007999999797903001, -0.3163999915122986, 0.12870000302791595, 0.16750000417232513, 0.09529999643564224, 0.17170000076293945, -0.12700000405311584, -0.09769999980926514, 0.01679999940097332, 0.10260000079870224, 0.17910000681877136, 0.010300000198185444, 0.00930000003427267, 0.0142000000923872, 0.12849999964237213, 0.09449999779462814, -0.1453000009059906, -0.00419999985024333], [-0.10159999877214432, -0.07240000367164612, -0.042500000447034836, -0.027499999850988388, -0.08590000122785568, -0.29820001125335693, -0.009499999694526196, 0.10890000313520432, 0.07970000058412552, 0.08150000125169754, 0.13670000433921814, -0.08100000023841858, 0.010599999688565731, -0.16609999537467957, -0.1688999980688095, -0.05640000104904175, 0.020600000396370888, -0.1460999995470047, 0.0551999993622303, 0.17579999566078186, 0.2087000012397766, -0.0869000032544136, -0.09149999916553497, -0.12290000170469284, -0.18029999732971191, 0.26759999990463257, 0.10840000212192535, 0.012500000186264515, 0.03229999914765358, -0.12530000507831573, 0.12780000269412994, 0.030700000002980232, -0.046799998730421066, -0.07090000063180923, 0.07039999961853027, 0.0746999979019165, 0.0763000026345253, -0.2070000022649765, 0.2727999985218048, -0.08540000021457672, -0.16619999706745148, 0.1589999943971634, -0.14259999990463257, 0.22360000014305115, -0.026900000870227814, -0.11800000071525574, -0.14300000667572021, -0.3068000078201294, 0.00419999985024333, -0.23639999330043793, -0.05640000104904175, 0.07000000029802322, -0.24719999730587006, -0.06939999759197235, 0.3206000030040741, 0.17870000004768372, -0.03280000016093254, 0.041200000792741776, -0.2176000028848648, -0.004600000102072954, 0.06499999761581421, 0.13989999890327454, -0.10350000113248825, 0.06650000065565109], [0.2160000056028366, 0.0925000011920929, -0.059300001710653305, -0.04129999876022339, -0.06679999828338623, -0.059700001031160355, -0.07919999957084656, 0.06480000168085098, -0.05469999834895134, -0.16769999265670776, 0.07540000230073929, 0.00139999995008111, 0.04010000079870224, 0.07410000264644623, -0.17730000615119934, -0.01549999974668026, -0.11580000072717667, -0.09749999642372131, -0.11630000174045563, -0.01140000019222498, -0.1574999988079071, 0.25099998712539673, 0.07329999655485153, -0.15680000185966492, 0.2460000067949295, -0.07540000230073929, -0.025699999183416367, -0.01810000091791153, 0.2125999927520752, -0.07360000163316727, 0.07280000299215317, 0.10199999809265137, -0.22339999675750732, 0.1136000007390976, 0.210999995470047, 0.32249999046325684, -0.08510000258684158, -0.16590000689029694, 0.1264999955892563, -0.25290000438690186, -0.08500000089406967, 0.13210000097751617, -0.006099999882280827, -0.14630000293254852, 0.05779999867081642, -0.03669999912381172, -0.2962999939918518, -0.06700000166893005, 0.10379999876022339, 0.062300000339746475, 0.024000000208616257, -0.022199999541044235, -0.07540000230073929, -0.008999999612569809, -0.2071000039577484, -0.12269999831914902, -0.1128000020980835, 0.021199999377131462, 0.02710000053048134, -0.05119999870657921, -0.0012000000569969416, 0.06700000166893005, 0.01889999955892563, -0.008899999782443047], [-0.10570000112056732, -0.23350000381469727, -0.1745000034570694, 0.16329999268054962, 0.2572000026702881, -0.029400000348687172, -0.06589999794960022, 0.004699999932199717, -0.1420000046491623, 0.06620000302791595, -0.13249999284744263, 0.3653999865055084, 0.1168999969959259, -0.19539999961853027, -0.2815999984741211, 0.023499999195337296, 0.0625, -0.0729999989271164, 0.08089999854564667, 0.029600000008940697, -0.18310000002384186, 0.01759999990463257, -0.1655000001192093, -0.0957999974489212, -0.20059999823570251, 0.053300000727176666, -0.06369999796152115, -0.0982000008225441, 0.04470000043511391, 0.0851999968290329, 0.06930000334978104, -0.03150000050663948, -0.14810000360012054, 0.2969000041484833, -0.025800000876188278, 0.026399999856948853, -0.08510000258684158, -0.14499999582767487, 0.20409999787807465, -0.08879999816417694, -0.01850000023841858, -0.1582999974489212, -0.023499999195337296, 0.11540000140666962, -0.0803999975323677, 0.03849999979138374, 0.06970000267028809, 0.09960000216960907, 0.06719999760389328, -0.0</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>[0.7915349716612479]</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>[0.047585609149719106]</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>[0.7571588478364288]</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>[0.055441429359383364]</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>[-3.90814648641859]</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>[1.6063366828507195]</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>[0.8311136506311797]</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>[0.038796415646637994]</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>[0.8987837534784306]</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>[0.02400454898692861]</t>
+        </is>
+      </c>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>[-1.9502894458689761]</t>
+        </is>
+      </c>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>[0.9699001132351115]</t>
+        </is>
+      </c>
+      <c r="Q26" t="inlineStr">
+        <is>
+          <t>[-0.2443436740732714]</t>
+        </is>
+      </c>
+      <c r="R26" t="inlineStr">
+        <is>
+          <t>[0.13417226379605288]</t>
+        </is>
+      </c>
+      <c r="S26" t="inlineStr">
+        <is>
+          <t>[-0.06731477369886929]</t>
+        </is>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>[0.08993230546200703]</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>[-1.7194300041421697]</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>[0.2600404103864525]</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>[-0.3608918759511308]</t>
+        </is>
+      </c>
+      <c r="X26" t="inlineStr">
+        <is>
+          <t>[0.14256788151461186]</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>[-0.11479782537148853]</t>
+        </is>
+      </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>[0.09174029121863578]</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>[-2.1450599975207374]</t>
+        </is>
+      </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>[0.2893592773506237]</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>[-1.0162215327068616]</t>
+        </is>
+      </c>
+      <c r="AD26" t="inlineStr">
+        <is>
+          <t>[0.16895124187468813]</t>
+        </is>
+      </c>
+      <c r="AE26" t="inlineStr">
+        <is>
+          <t>[-1.1244507064484135]</t>
+        </is>
+      </c>
+      <c r="AF26" t="inlineStr">
+        <is>
+          <t>[0.22875676055794517]</t>
+        </is>
+      </c>
+      <c r="AG26" t="inlineStr">
+        <is>
+          <t>[-4.095366172824167]</t>
+        </is>
+      </c>
+      <c r="AH26" t="inlineStr">
+        <is>
+          <t>[0.37934979987041684]</t>
+        </is>
+      </c>
+      <c r="AI26" t="inlineStr">
+        <is>
+          <t>[-1.696071689135454]</t>
+        </is>
+      </c>
+      <c r="AJ26" t="inlineStr">
+        <is>
+          <t>[0.22094007361973061]</t>
+        </is>
+      </c>
+      <c r="AK26" t="inlineStr">
+        <is>
+          <t>[-0.9733310211888433]</t>
+        </is>
+      </c>
+      <c r="AL26" t="inlineStr">
+        <is>
+          <t>[0.209454630017667]</t>
+        </is>
+      </c>
+      <c r="AM26" t="inlineStr">
+        <is>
+          <t>[-3.6451842898458517]</t>
+        </is>
+      </c>
+      <c r="AN26" t="inlineStr">
+        <is>
+          <t>[0.35678382920647866]</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>model_128_64_0</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>[128, 64]</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>[[[0.03319999948143959, 0.0027000000700354576, -0.016699999570846558, -0.0017999999690800905, 0.12229999899864197, -0.014700000174343586, -0.04670000076293945, -0.05999999865889549, -0.0005000000237487257, -0.16120000183582306, -0.057500001043081284, -0.03150000050663948, 0.04129999876022339, 0.027000000700354576, -0.054999999701976776, 0.0066999997943639755, 0.0007999999797903001, 0.059300001710653305, 0.00139999995008111, -0.021199999377131462, 0.06199999898672104, 0.042500000447034836, 0.11349999904632568, 0.019600000232458115, 0.05620000138878822, -0.0026000000070780516, -0.029600000008940697, 0.05090000107884407, -0.008500000461935997, 0.039400000125169754, 0.014999999664723873, 0.01720000058412552, 0.03959999978542328, 0.014700000174343586, 0.010400000028312206, 0.060499999672174454, -0.015599999576807022, -0.013299999758601189, 0.07540000230073929, -0.02539999969303608, 0.0722000002861023, -0.014800000004470348, -0.05270000174641609, 0.08399999886751175, -0.05649999901652336, 0.015200000256299973, -0.012799999676644802, -0.015799999237060547, 0.018699999898672104, 0.006300000008195639, -0.03020000085234642, 0.09740000218153, 0.07370000332593918, 0.02070000022649765, 0.014800000004470348, -0.029400000348687172, -0.04830000177025795, 0.004000000189989805, -0.07289999723434448, -0.042399998754262924, 0.0008999999845400453, -0.04740000143647194, -0.061400000005960464, -0.007499999832361937, 0.02319999970495701, -0.028599999845027924, 0.02879999950528145, 0.014399999752640724, 0.1039000004529953, -0.06560000032186508, -0.04690000042319298, -0.0005000000237487257, 0.03680000081658363, 0.04340000078082085, -0.10540000349283218, -0.03840000182390213, 0.014999999664723873, 0.025499999523162842, 0.006800000090152025, -0.04230000078678131, 0.03500000014901161, 0.0035000001080334187, 0.019099999219179153, 0.00019999999494757503, 0.05869999900460243, -0.0035000001080334187, -0.053300000727176666, 0.043800000101327896, 0.01119999960064888, -0.0010000000474974513, -0.04439999908208847, -0.06549999862909317, -0.08110000193119049, 0.02759999968111515, 0.018699999898672104, -0.0010000000474974513, 0.026200000196695328, -0.006500000134110451, 0.04010000079870224, -0.0892999991774559, 0.002899999963119626, -0.04540000110864639, -0.14000000059604645, -0.05000000074505806, 0.06949999928474426, -0.03139999881386757, -0.013700000010430813, 0.04580000042915344, -0.007899999618530273, -0.011300000362098217, 0.08389999717473984, 0.03620000183582306, -0.05420000106096268, -0.022199999541044235, 0.049800001084804535, -0.024900000542402267, 0.020400000736117363, 0.026799999177455902, 0.014800000004470348, 0.08070000261068344, -0.02410000003874302, -0.044199999421834946, 0.03819999843835831, -0.003000000026077032, 0.043299999088048935, 0.05959999933838844, 0.021199999377131462, 0.024399999529123306], [0.0357000008225441, -0.05339999869465828, -0.034299999475479126, 0.01360000018030405, -0.08009999990463257, -0.0008999999845400453, 0.02239999920129776, 0.03480000048875809, -0.005799999926239252, -0.03189999982714653, 0.019099999219179153, -0.014800000004470348, -0.019500000402331352, -0.07180000096559525, -0.01759999990463257, -0.07119999825954437, -0.01979999989271164, -0.029600000008940697, -0.07909999787807465, -0.01360000018030405, 0.005400000140070915, -0.03790000081062317, 0.042899999767541885, -0.039799999445676804, -0.1054999977350235, -0.052000001072883606, 0.06800000369548798, -0.05739999935030937, 0.04529999941587448, -0.02500000037252903, 0.01940000057220459, -0.011699999682605267, -0.09629999846220016, -0.03460000082850456, 0.05469999834895134, 0.002400000113993883, 0.007600000128149986, -0.04659999907016754, 0.0038999998942017555, 0.01899999938905239, 0.052400000393390656, -0.0010000000474974513, 0.06689999997615814, -0.014499999582767487, -0.10840000212192535, -0.05849999934434891, 0.09889999777078629, -0.04019999876618385, 0.06459999829530716, -0.047200001776218414, -0.042100001126527786, 0.09960000216960907, -0.04879999905824661, 0.062199998646974564, -0.0142000000923872, -0.029100000858306885, 0.007499999832361937, -0.029999999329447746, 0.06840000301599503, 0.028300000354647636, 0.042500000447034836, -0.03099999949336052, 0.009100000374019146, 0.030899999663233757, 0.02329999953508377, 0.03020000085234642, 0.021199999377131462, 0.015599999576807022, 0.05490000173449516, -0.0215000007301569, 0.016899999231100082, -0.005799999926239252, -0.025299999862909317, 0.05999999865889549, -0.01979999989271164, -0.015300000086426735, -0.0494999997317791, -0.12300000339746475, -0.042500000447034836, 0.048900000751018524, 0.048700001090765, -0.04639999940991402, 0.010999999940395355, -0.08259999752044678, 0.03849999979138374, -0.04430000111460686, -0.007300000172108412, 0.056299999356269836, -0.057999998331069946, -0.07970000058412552, 0.005200000014156103, -0.01979999989271164, -0.049300000071525574, 0.04690000042319298, -0.10719999670982361, -0.04580000042915344, -0.0003000000142492354, -0.09889999777078629, -0.0333000011742115, -0.04740000143647194, 0.02019999921321869, 0.04360000044107437, -0.009200000204145908, -0.05260000005364418, -0.03550000116229057, -0.011099999770522118, 0.007499999832361937, -0.014100000262260437, 0.04490000009536743, 0.042399998754262924, -0.01510000042617321, -0.06759999692440033, -0.02370000071823597, -0.08839999884366989, 0.010200000368058681, -0.04010000079870224, 0.0008999999845400453, 0.04859999939799309, -0.057100001722574234, 0.005499999970197678, 0.03629999980330467, -0.09080000221729279, 0.032099999487400055, -0.02019999921321869, 0.002099999925121665, 0.0031999999191612005, -0.08340000361204147, -0.07880000025033951]], [[0.0203000009059906, 0.002400000113993883, 0.06430000066757202, 0.019999999552965164, -0.041999999433755875, 0.01759999990463257, 0.0820000022649765, 0.11829999834299088, -0.07270000129938126, 0.17430000007152557, 0.1298000067472458, -0.11659999936819077, 0.08900000154972076, 0.08470000326633453, 0.08259999752044678, 0.04500000178813934, 0.051600001752376556, -0.05810000002384186, 0.03779999911785126, 0.028200000524520874, -0.01360000018030405, 0.0003000000142492354, -0.04830000177025795, -0.03750000149011612, 0.10769999772310257, 0.1770000010728836, 0.09830000251531601, -0.0885000005364418, -0.08100000023841858, 0.15369999408721924, 0.0925000011920929, 0.08030000329017639, -0.06650000065565109, -0.1266999989748001, 0.13199999928474426, -0.040800001472234726, -0.03189999982714653, -0.056699998676776886, 0.01269999984651804, -0.1559000015258789, -0.03660000115633011, 0.06679999828338623, 0.026799999177455902, -0.08190000057220459, 0.015300000086426735, 0.09319999814033508, -0.09480000287294388, 0.01549999974668026, 0.013899999670684338, -0.06080000102519989, 0.05310000106692314, 0.10859999805688858, 0.03370000049471855, 0.05220000073313713, -0.1388999968767166, 0.029200000688433647, -0.050999999046325684, 0.03869999945163727, 0.0034000000450760126, -0.032600000500679016, -0.24469999969005585, 0.14020000398159027, 0.04399999976158142, -0.14669999480247498, 0.03610000014305115, -0.13670000433921814, 0.20839999616146088, -0.1324000060558319, -0.025299999862909317, 0.00989999994635582, 9.999999747378752e-05, -0.07509999722242355, 0.0034000000450760126, -0.07349999994039536, 0.013899999670684338, 0.08510000258684158, -0.006000000052154064, 0.00039999998989515007, -0.05689999833703041, -0.06750000268220901, -0.05920000001788139, 0.16030000150203705, -0.04490000009536743, -0.01080000028014183, -0.09920000284910202, -0.14740000665187836, -0.1200999990105629, 0.0348999984562397, -0.07109999656677246, 0.03799999877810478, -0.0032999999821186066, 0.15760000050067902, -0.12380000203847885, -0.10649999976158142, -0.025800000876188278, -0.029600000008940697, 0.0044999998062849045, 0.09390000253915787, 0.03530000150203705, -0.06159999966621399, -0.18880000710487366, -0.14219999313354492, -0.15809999406337738, 0.06270000338554382, 0.19380000233650208, 0.015300000086426735, 0.0828000009059906, 0.08470000326633453, -0.027300000190734863, 0.012400000356137753, -0.006000000052154064, 0.07270000129938126, -0.11339999735355377, 0.006200000178068876, 0.07980000227689743, -0.024700000882148743, 0.07680000364780426, 0.03139999881386757, 0.002899999963119626, 0.08209999650716782, -0.07509999722242355, 0.08209999650716782, 0.034299999475479126, -0.10199999809265137, -0.11869999766349792, -0.07169999927282333, 0.149399995803833, -0.11079999804496765], [-0.01899999938905239, 0.010999999940395355, 0.0625, 0.003100000089034438, 0.24729999899864197, -0.07880000025033951, 0.16609999537467957, -0.02199999988079071, 0.02319999970495701, -0.04050000011920929, 0.062300000339746475, 0.16220000386238098, 0.09160000085830688, -0.07370000332593918, -0.027000000700354576, 0.09070000052452087, 0.05620000138878822, 0.04580000042915344, -0.05040000006556511, 0.01269999984651804, 0.04439999908208847, 0.14499999582767487, 0.1590999960899353, 0.11110000312328339, 0.041099999099969864, 0.09390000253915787, 0.006500000134110451, -0.1842000037431717, -0.05649999901652336, -0.08889999985694885, -0.04610000178217888, -0.03669999912381172, -0.06849999725818634, -0.053199999034404755, -0.1298000067472458, -0.004100000020116568, 0.07079999893903732, -0.11020000278949738, 0.0017000000225380063, 0.004900000058114529, 0.16910000145435333, 0.07649999856948853, -0.008100000210106373, 0.09189999848604202, 0.027799999341368675, 0.026399999856948853, -0.2053000032901764, 0.01720000058412552, -0.03920000046491623, -0.13660000264644623, -0.003100000089034438, 0.01769999973475933, 0.09229999780654907, 0.053300000727176666, -0.09120000153779984, -0.05689999833703041, 0.1459999978542328, -0.0034000000450760126, -0.1527000069618225, -0.04910000041127205, -0.07349999994039536, -0.03590000048279762, 0.011900000274181366, 0.1551000028848648, -0.013899999670684338, -0.11410000175237656, -0.041200000792741776, 0.047600001096725464, 0.013799999840557575, 0.06260000169277191, -0.019300000742077827, 0.0674000009894371, -0.09849999845027924, -0.03819999843835831, 0.09179999679327011, 0.027899999171495438, -0.017799999564886093, -0.14059999585151672, -0.07419999688863754, -0.10400000214576721, 0.01979999989271164, -0.12890000641345978, -0.12919999659061432, 0.10040000081062317, -0.032600000500679016, -0.09210000187158585, -0.03610000014305115, -0.24719999730587006, 0.033900000154972076, -0.11840000003576279, -0.018200000748038292, -0.035100001841783524, -0.11999999731779099, 0.00839999970048666, -0.037700001150369644, 0.08089999854564667, -0.00860000029206276, -0.12439999729394913, -0.15369999408721924, -0.0966000035405159, -0.06589999794960022, -0.11890000104904175, 0.07240000367164612, -0.08619999885559082, 0.04450000077486038, 0.20399999618530273, -9.999999747378752e-05, 0.04600000008940697, -0.060600001364946365, -0.00860000029206276, -0.03189999982714653, 0.0, 0.061500001698732376, -0.04690000042319298, -0.07639999687671661, 0.12919999659061432, -0.019099999219179153, -0.0746999979019165, -0.12710000574588776, -0.010400000028312206, -0.041200000792741776, -0.15860000252723694, -0.0031999999191612005, -0.033900000154972076, -0.06909999996423721, 0.05979999899864197, -0.10450000315904617, 0.03920000046491623], [0.014700000174343586, -0.10440000146627426, -0.023399999365210533, 0.15459999442100525, -0.006300000008195639, -0.010700000450015068, -0.0885000005364418, -0.07819999754428864, -0.027000000700354576, 0.035599999129772186, -0.1754000037908554, -0.11670000106096268, 0.031199999153614044, -0.010300000198185444, -0.16040000319480896, 0.03440000116825104, -0.08500000089406967, -0.08169999718666077, 0.09229999780654907, 0.0714000016450882, -0.03669999912381172, -0.04039999842643738, -0.07109999656677246, 0.06129999831318855, -0.14139999449253082, 0.05660000070929527, 0.13079999387264252, -0.04149999842047691, 0.013000000268220901, -0.02879999950528145, -0.08269999921321869, -0.08699999749660492, 0.053700000047683716, -0.06920000165700912, 0.011099999770522118, -0.0071000000461936, 0.008899999782443047, 0.03400000184774399, 0.04740000143647194, 0.06809999793767929, -0.14890000224113464, 0.031199999153614044, -0.019200000911951065, 0.05829999968409538, 0.009399999864399433, 0.013299999758601189, -0.03310000151395798, -0.0008999999845400453, -0.1688999980688095, -0.19990000128746033, -0.05920000001788139, -0.08060000091791153, -0.07530000060796738, -0.003800000064074993, 0.03680000081658363, -0.0333000011742115, 0.149399995803833, -0.07880000025033951, 0.02669999934732914, 0.07010000199079514, 0.025599999353289604, 0.1843000054359436, 0.02160000056028366, 0.030500000342726707, 0.07249999791383743, -0.12790000438690186, -0.16910000145435333, 0.05469999834895134, -0.10090000182390213, -0.003100000089034438, 0.0640999972820282, -0.1395999938249588, 0.07370000332593918, 0.00839999970048666, 0.01860000006854534, 0.0697999969124794, -0.13330000638961792, -0.032999999821186066, -0.010700000450015068, 0.05389999970793724, -0.004399999976158142, 0.11699999868869781, -0.0828000009059906, -0.0066999997943639755, 0.003100000089034438, 0.0038999998942017555, -0.08799999952316284, -0.13429999351501465, 0.035100001841783524, 0.010200000368058681, -0.01759999990463257, -0.13600000739097595, -0.048900000751018524, 0.1339000016450882, 0.08290000259876251, -0.1282999962568283, 0.09000000357627869, -0.03660000115633011, 0.10610000044107437, -0.042399998754262924, -0.0794999971985817, 0.147599995136261, -0.1290999948978424, 0.07370000332593918, 0.1331000030040741, -0.025100000202655792, 0.1671999990940094, -0.04580000042915344, 0.06920000165700912, -0.2134999930858612, -0.1451999992132187, 0.1273999959230423, 0.06539999693632126, -0.03460000082850456, 0.15889999270439148, 0.04969999939203262, -0.060600001364946365, -0.05469999834895134, -0.16179999709129333, -0.08709999918937683, 0.10350000113248825, 0.04170000180602074, 0.06120000034570694, -0.05299999937415123, 0.03689999878406525, -0.16169999539852142, -0.1388999968767166, 0.015200000256299973], [0.04089999943971634, 0.026499999687075615, -0.09880000352859497, -0.07999999821186066, 0.2667999863624573, 0.09719999879598618, 0.05169999971985817, 0.09560000151395798, 0.10509999841451645, 0.11259999871253967, -0.038100000470876694, 0.11869999766349792, -0.012400000356137753, 0.05550000071525574, -0.03959999978542328, -0.18870000541210175, 0.026100000366568565, -0.12269999831914902, 0.025100000202655792, 0.11320000141859055, -0.09799999743700027, 0.06549999862909317, 0.007899999618530273, -0.02459999918937683, 0.056299999356269836, 0.0478999987244606, -0.02410000003874302, -0.014100000262260437, -0.011800000444054604, 0.05400000140070915, 0.08630000054836273, 0.10360000282526016, -0.08869999647140503, 0.10270000249147415, 0.05590000003576279, -0.029100000858306885, -0.07039999961853027, -0.05400000140070915, 0.12729999423027039, 0.19359999895095825, -0.012400000356137753, 0.09780000150203705, 0.06989999860525131, 0.11259999871253967, 0.10140000283718109, 0.014499999582767487, 0.059300001710653305, -0.03099999949336052, 0.1964000016450882, -0.08219999819993973, -0.1500999927520752, 0.0632999986410141, -0.08269999921321869, -0.042399998754262924, 0.020099999383091927, -0.0027000000700354576, -0.038600001484155655, -0.017799999564886093, -0.01889999955892563, 0.03889999911189079, -0.12049999833106995, 0.12030000239610672, 0.19210000336170197, -0.1679999977350235, -0.07440000027418137, 0.01360000018030405, -0.0934000015258789, -0.03539999946951866, -0.0885000005364418, 0.05649999901652336, 0.05889999866485596, 0.007400000002235174, -0.01899999938905239, -0.09920000284910202, -0.02459999918937683, -0.01889999955892563, -0.010900000110268593, -0.15729999542236328, 0.029200000688433647, -0.044199999421834946, -0.06539999693632126, -0.04670000076293945, 0.02280000038444996, 0.13600000739097595, 0.020800000056624413, 0.03550000116229057, -0.047200001776218414, 0.16339999437332153, 0.006500000134110451, -0.026200000196695328, 0.16500000655651093, -0.15839999914169312, 0.022700000554323196, 0.23070000112056732, -0.07419999688863754, 0.09309999644756317, -0.125900000333786, 0.037700001150369644, 0.12540000677108765, 0.051500000059604645, -0.003700000001117587, 0.04309999942779541, -0.03920000046491623, -0.09179999679327011, -0.13580000400543213, 0.07339999824762344, -0.02410000003874302, -0.09350000321865082, 0.0210999995470047, 0.12120000272989273, -0.03350000083446503, -0.03350000083446503, -0.09109999984502792, -0.05860000103712082, 0.1501999944448471, -0.10580000281333923, -0.11789999902248383, -0.06350000202655792, -0.08860000222921371, 0.01810000091791153, 0.059700001031160355, -0.03539999946951866, 0.0723000019788742, -0.011099999770522118, 0.04230000078678131, 0.03849999979138374, 0.05810000002384186, -0.02500000037252903], [0.0471000000834465, 0.0008999999845400453, -0.03590000048279762, -0.0723000019788742, -0.03310000151395798, -0.026000000536441803, -0.04019999876618385, 0.04050000011920929, 0.19539999961853027, -0.026799999177455902, 0.03020000085234642, -0.13429999351501465, -0.12880000472068787, -0.08879999816417694, 0.02759999968111515, -0.11089999973773956, 0.0272000003606081, 0.048900000751018524, 0.14740000665187836, 0.13899999856948853, 0.1160999983549118, 0.04769999906420708, 0.06679999828338623, 0.08330000191926956, -0.05260000005364418, 0.03350000083446503, 0.1177000030875206, 0.03359999880194664, -0.043299999088048935, -0.08579999953508377, 0.12200000137090683, -0.08479999750852585, -0.020400000736117363, -0.00419999985024333, -0.10199999809265137, 0.006300000008195639, 0.021299999207258224, 0.0917000025510788, 0.01080000028014183, -0.031599998474121094, -0.029999999329447746, -0.06040000170469284, 0.09719999879598618, -0.07580000162124634, 0.13050000369548798, -0.05719999969005585, -0.019300000742077827, -0.22210000455379486, -0.07739999890327454, -0.12700000405311584, 0.057100001722574234, 0.1932000070810318, -0.07930000126361847, -0.01889999955892563, 0.10199999809265137, 0.001500000013038516, -0.1850000023841858, 0.10050000250339508, -0.11720000207424164, -0.10440000146627426, -0.04529999941587448, -0.13539999723434448, -0.10249999910593033, -0.023499999195337296, 0.047600001096725464, -0.039000000804662704, 0.08179999887943268, -0.03290000185370445, -0.15049999952316284, 0.04340000078082085, -0.04569999873638153, 0.011300000362098217, 0.010900000110268593, 0.05469999834895134, -0.010200000368058681, 0.03739999979734421, 0.03739999979734421, -0.04619999974966049, 0.12380000203847885, 0.10490000247955322, 0.03689999878406525, 0.02410000003874302, 0.029500000178813934, -0.029200000688433647, -0.1648000031709671, 0.06430000066757202, -0.00430000014603138, -0.15940000116825104, 0.07020000368356705, 0.042899999767541885, 0.07590000331401825, -0.14900000393390656, 0.10830000042915344, 0.029600000008940697, -0.06199999898672104, 0.05790000036358833, 0.03229999914765358, 0.012199999764561653, 0.05469999834895134, -0.04270000010728836, 0.014999999664723873, -0.011900000274181366, 0.11590000241994858, 0.14659999310970306, -0.01850000023841858, 0.08309999853372574, -0.10949999839067459, 0.031300000846385956, -0.21649999916553497, 0.16269999742507935, -0.08990000188350677, 0.03370000049471855, 0.09390000253915787, -0.06440000236034393, 0.05979999899864197, 0.021400000900030136, 0.12710000574588776, 0.021400000900030136, 0.028699999675154686, -0.17069999873638153, -0.08179999887943268, 0.06930000334978104, 0.031300000846385956, -0.19519999623298645, -0.0012000000569969416, -0.16249999403953552, 0.05380000174045563, 0.05739999935030937], [-0.07029999792575836, -0.004100000020116568, 0.1315000057220459, 0.06369999796152115, 0.10140000283718109, -0.01360000018030405, 0.019600000232458115, -0.013100000098347664, 0.13670000433921814, 0.18529999256134033, -0.0052999998442828655, -0.033900000154972076, -0.14079999923706055, 0.09629999846220016, -0.13210000097751617, -0.018400000408291817, 0.11909999698400497, 0.08250000327825546, -0.07029999792575836, 0.0835999995470047, 0.05829999968409538, -0.018400000408291817, 0.04960000142455101, 0.0640999972820282, 0.03929999843239784, 0.09860000014305115, -0.1088000014424324, -0.12380000203847885, -0.0502999983727932, 0.09809999912977219, 0.16369999945163727, -0.09989999979734421, 0.024900000542402267, 0.08789999783039093, -0.02329999953508377, 0.11720000207424164, 0.10520000010728836, 0.05609999969601631, 0.006099999882280827, 0.027400000020861626, 0.04839999973773956, 0.0026000000070780516, 0.07540000230073929, -0.017500000074505806, -0.0010999999940395355, -0.066600002348423, 0.034299999475479126, 0.11580000072717667, -0.020999999716877937, 0.023900000378489494, 0.13539999723434448, -0.01209999993443489, 0.08470000326633453, -0.0421999990940094, 0.15299999713897705, 0.03929999843239784, -0.016300000250339508, -0.04270000010728836, -0.09430000185966492, 0.04529999941587448, 0.08089999854564667, -0.0737999975681305, -0.020400000736117363, -0.10570000112056732, 0.023399999365210533, -0.023399999365210533, -0.06880000233650208, 0.05339999869465828, 0.11559999734163284, -0.05169999971985817, -0.05640000104904175, 0.0763000026345253, 0.07739999890327454, 0.1882999986410141, 0.008200000040233135, 0.11919999867677689, -0.0478999987244606, -0.10980000346899033, 0.08129999786615372, -0.04899999871850014, 0.1315000057220459, -0.08429999649524689, 0.03500000014901161, -0.0035000001080334187, -0.04800000041723251, 0.001500000013038516, 0.034699998795986176, 0.1680999994277954, -0.03590000048279762, -0.03739999979734421, 0.05590000003576279, -0.0052999998442828655, -0.15240000188350677, -0.015399999916553497, 0.16369999945163727, 0.11559999734163284, -0.059700001031160355, -0.07769999653100967, -0.022199999541044235, 0.08630000054836273, -0.1860000044107437, 0.026200000196695328, -0.08219999819993973, -0.05620000138878822, -0.010400000028312206, -0.05950000137090683, -0.03799999877810478, -0.13379999995231628, 0.05249999836087227, -0.3059000074863434, 0.14970000088214874, -0.094200000166893, 0.04500000178813934, 0.05420000106096268, 0.041999999433755875, -0.005799999926239252, 0.11680000275373459, 0.09200000017881393, 0.08829999715089798, 0.06589999794960022, 0.044599998742341995, 0.1298999935388565, 0.057500001043081284, -0.19670000672340393, -0.09019999951124191, -0.08529999852180481, -0.01940000057220459, 0.07349999994039536], [-0.16259999573230743, 0.09309999644756317, -0.004600000102072954, -0.04520000144839287, 0.016300000250339508, 0.02160000056028366, -0.01730000041425228, 0.06729999929666519, -0.012199999764561653, -0.05620000138878822, -0.18240000307559967, -0.03099999949336052, 0.11699999868869781, -0.10459999740123749, 0.0421999990940094, -0.06499999761581421, -0.022700000554323196, 0.04410000145435333, -0.10840000212192535, 0.13989999890327454, 0.013100000098347664, -0.10729999840259552, 0.031700000166893005, 0.07400000095367432, 0.3009999990463257, -0.002199999988079071, -0.16019999980926514, -0.04270000010728836, 0.021900000050663948, -0.04170000180602074, 0.05590000003576279, -0.08380000293254852, 0.08129999786615372, 0.08240000158548355, -0.06750000268220901, 0.019899999722838402, -0.006099999882280827, 0.062199998646974564, -0.029600000008940697, -0.1412000060081482, 0.04309999942779541, -0.1225999966263771, 0.10779999941587448, -0.07039999961853027, -0.10729999840259552, 0.11259999871253967, 0.1451999992132187, -0.09309999644756317, -0.027400000020861626, 0.00930000003427267, -0.09040000289678574, 0.023600000888109207, -0.09189999848604202, -0.03240000084042549, -0.03680000081658363, 0.024800000712275505, -0.022299999371170998, -0.007699999958276749, -0.1014999970793724, 0.08569999784231186, -0.010599999688565731, -0.008899999782443047, -0.05889999866485596, 0.004800000227987766, -0.07270000129938126, -0.05810000002384186, -0.04809999838471413, 0.03519999980926514, -0.15600000321865082, -0.05820000171661377, -0.01209999993443489, -0.06669999659061432, 0.023000000044703484, 0.021299999207258224, 0.002899999963119626, 0.22380000352859497, -0.1242000013589859, -0.07500000298023224, -0.08190000057220459, -0.019700000062584877, 0.01119999960064888, 0.04729999974370003, 0.060600001364946365, -0.09059999883174896, -0.09549999982118607, 0.05290000140666962, -0.07509999722242355, 0.18700000643730164, 0.08569999784231186, 0.0746999979019165, -0.0, 0.12039999663829803, -0.051899999380111694, 0.002099999925121665, -0.0722000002861023, -0.09650000184774399, 0.1679999977350235, -0.09769999980926514, 0.05339999869465828, 0.012600000016391277, 0.05310000106692314, 0.013100000098347664, -0.029400000348687172, -0.0957999974489212, 0.021700000390410423, 0.03819999843835831, 0.04340000078082085, 0.03099999949336052, -0.028999999165534973, 0.00430000014603138, 0.14640000462532043, 0.09149999916553497, 0.11140000075101852, -0.15950000286102295, 0.023399999365210533, 0.001500000013038516, 0.042500000447034836, -0.16750000417232513, -0.1736000031232834, 0.10670000314712524, -0.2508000135421753, -0.07739999890327454, -0.03790000081062317, 0.09459999948740005, 0.1160999983549118, 0.0649000033736229, -0.03840000182390213, -0.025299999862909317], [0.010999999940395355, -0.09749999642372131, 0.05609999969601631, -0.0843999981880188, -0.2777000069618225, -0.07029999792575836, -0.065700002014637, -0.05730000138282776, -0.019700000062584877, 0.010599999688565731, -0.15700000524520874, 0.07670000195503235, 0.1843000054359436, -0.02930000051856041, -0.19990000128746033, -0.06239999830722809, 0.07500000298023224, 0.027000000700354576, -0.01119999960064888, -0.04410000145435333, 0.20890000462532043, 0.11540000140666962, -0.03550000116229057, -0.13830000162124634, 0.14890000224113464, -0.07590000331401825, -0.13429999351501465, -0.10459999740123749, -0.066600002348423, 0.03359999880194664, -0.020400000736117363, 0.06639999896287918, 0.12610000371932983, 0.042899999767541885, -0.026499999687075615, 0.028999999165534973, 0.09719999879598618, 0.04960000142455101, 0.052000001072883606, 0.08190000057220459, 0.15240000188350677, 0.011099999770522118, -0.03610000014305115, 0.06589999794960022, -0.029500000178813934, -0.025599999353289604, -0.012000000104308128, -0.07609999924898148, -0.12309999763965607, -0.03660000115633011, -0.014100000262260437, -0.04769999906420708, -0.03220000118017197, 0.07909999787807465, -0.052000001072883606, 0.10329999774694443, -0.0689999982714653, 0.06239999830722809, 0.03669999912381172, -0.10320000350475311, -0.14100000262260437, 0.12970000505447388, -0.017999999225139618, -0.03269999846816063, -0.017899999395012856, -0.18410000205039978, 0.09889999777078629, 0.017000000923871994, -0.03350000083446503, -0.11349999904632568, 0.05790000036358833, 0.00019999999494757503, -0.09700000286102295, -0.010900000110268593, 0.14869999885559082, 0.042899999767541885, 0.1137000024318695, -0.05849999934434891, 0.08609999716281891, -0.00570000009611249, -0.16300000250339508, -0.11779999732971191, -0.07460000365972519, 0.03350000083446503, -0.003700000001117587, -0.09790000319480896, 0.09130000323057175, 0.0038999998942017555, 0.10159999877214432, -0.03909999877214432, 0.14350000023841858, -0.08980000019073486, 0.14090000092983246, -0.0024999999441206455, 0.06870000064373016, -0.09589999914169312, -0.05249999836087227, -0.08500000089406967, 0.0035000001080334187, 0.05640000104904175, 0.01850000023841858, -0.022199999541044235, 0.08810000121593475, 0.07940000295639038, -0.024900000542402267, -0.15479999780654907, 0.01640000008046627, -0.10580000281333923, -0.1023000031709671, -0.051899999380111694, 0.03610000014305115, 0.0284000001847744, -0.018799999728798866, 0.020600000396370888, -0.055399999022483826, 0.010599999688565731, -0.016499999910593033, 0.005400000140070915, 0.04749999940395355, 0.04809999838471413, 0.13249999284744263, 0.0007999999797903001, 0.13269999623298645, -0.07850000262260437, 0.0851999968290329, 0.06939999759197235, 0.04969999939203262, -0.2231999933719635], [0.06719999760389328, 0.07069999724626541, 0.13420000672340393, -0.06419999897480011, 0.04149999842047691, 0.1664000004529953, 0.011599999852478504, 0.020999999716877937, -0.13910000026226044, -0.01209999993443489, 0.018799999728798866, -0.12790000438690186, 0.09780000150203705, -0.06210000067949295, -0.060100000351667404, 0.1467999964952469, 0.04960000142455101, -0.020899999886751175, -0.01549999974668026, 0.13840000331401825, -0.0729999989271164, 0.0272000003606081, -0.17630000412464142, 0.1111999973654747, -0.03310000151395798, 0.08030000329017639, -0.030799999833106995, -0.021900000050663948, 0.02250000089406967, 0.04149999842047691, -0.11240000277757645, 0.1573999971151352, -0.06260000169277191, 0.009700000286102295, -0.014399999752640724, -0.12720000743865967, -0.06210000067949295, -0.08100000023841858, -0.07039999961853027, -0.018799999728798866, -0.03500000014901161, 0.027400000020861626, 0.0868000015616417, -0.047600001096725464, -0.10260000079870224, 0.04699999839067459, -0.014100000262260437, 0.016499999910593033, -0.11980000138282776, 0.1356000006198883, -0.14180000126361847, 0.1005999967455864, 0.07980000227689743, -0.030799999833106995, 0.09830000251531601, 0.05119999870657921, -0.07919999957084656, -0.15700000524520874, -0.035999998450279236, -0.0017000000225380063, 0.0364999994635582, 0.0052999998442828655, 0.19779999554157257, -0.03420000150799751, 0.030899999663233757, -0.004600000102072954, 0.0031999999191612005, -0.10999999940395355, 0.07599999755620956, 0.1526000052690506, 0.032999999821186066, 0.09759999811649323, -0.025699999183416367, 0.020500000566244125, 0.05139999836683273, -0.05209999904036522, 0.012000000104308128, -0.2110999971628189, 0.06849999725818634, 0.211899995803833, 0.08479999750852585, -0.07850000262260437, -0.039900001138448715, -0.12540000677108765, -0.0017999999690800905, 0.1860000044107437, 0.04969999939203262, -0.10360000282526016, 0.11940000206232071, 0.060100000351667404, -0.003800000064074993, 0.011800000444054604, 0.06109999865293503, -0.017000000923871994, 0.0723000019788742, -0.03629999980330467, 0.07819999754428864, -0.08990000188350677, -0.10589999705553055, 0.06319999694824219, -0.050700001418590546, -0.10329999774694443, 0.006300000008195639, 0.21369999647140503, -0.14489999413490295, 0.017100000753998756, 0.037700001150369644, -0.08349999785423279, -0.1451999992132187, 0.008899999782443047, 0.053300000727176666, 0.06700000166893005, 0.13729999959468842, 0.06270000338554382, 0.03889999911189079, -0.06599999964237213, -0.15000000596046448, 0.06809999793767929, 0.04580000042915344, 0.17960000038146973, -0.030700000002980232, 0.017899999395012856, 0.11729999631643295, 0.08950000256299973, -0.05380000174045563, -0.006099999882280827, -0.043800000101327896, 0.0210999995470047], [0.031099999323487282, 0.0982000008225441, 0.029899999499320984, 0.0357000008225441, 0.093299999833107, 0.09740000218153, 0.1972000002861023, -0.06719999760389328, 0.0625, -0.17910000681877136, -0.06319999694824219, -0.10419999808073044, 0.17659999430179596, -0.033900000154972076, 0.045499999076128006, -0.04749999940395355, 0.20720000565052032, -0.09139999747276306, -0.13850000500679016, 0.1412999927997589, 0.06310000270605087, -0.020600000396370888, 0.0494999997317791, 0.02710000053048134, -0.011300000362098217, -0.03220000118017197, 0.11779999732971191, -0.0471000000834465, -0.022600000724196434, -0.09109999984502792, -0.06859999895095825, -0.014399999752640724, -0.02160000056028366, -0.023399999365210533, -0.01810000091791153, -0.050200000405311584, 0.007300000172108412, 0.1111999973654747, -0.03880000114440918, 0.1867000013589859, -0.09839999675750732, -0.14090000092983246, -0.053199999034404755, 0.08579999953508377, -0.018400000408291817, 0.08699999749660492, 0.02850000001490116, 0.010400000028312206, -0.005100000184029341, 0.0035000001080334187, 0.18039999902248383, 0.09179999679327011, 0.013100000098347664, 0.010099999606609344, -0.10329999774694443, 0.08320000022649765, 0.030899999663233757, 0.061500001698732376, 0.007199999876320362, -0.08749999850988388, -0.017100000753998756, -0.0364999994635582, -0.01600000075995922, -0.028300000354647636, 0.07119999825954437, 0.05649999901652336, 0.02879999950528145, 0.09549999982118607, 0.11349999904632568, 0.03959999978542328, -0.0005000000237487257, -0.2126999944448471, 0.11339999735355377, 0.10559999942779541, -0.07119999825954437, -0.017100000753998756, 0.10189999639987946, 0.011300000362098217, -0.22630000114440918, 0.12790000438690186, 0.04280000180006027, -0.049300000071525574, 0.034699998795986176, -0.06650000065565109, -0.014999999664723873, 0.03840000182390213, 0.11469999700784683, 0.16459999978542328, -0.06849999725818634, -0.10270000249147415, 0.05130000039935112, 0.12219999730587006, -0.0142000000923872, 0.07559999823570251, 0.020600000396370888, -0.12870000302791595, -0.065700002014637, -0.06549999862909317, -0.048900000751018524, 0.02419999986886978, 0.06679999828338623, 0</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>[[[0.025200000032782555, 0.03909999877214432, 0.04050000011920929, -0.06459999829530716, 0.12809999287128448, -0.04089999943971634, -0.1080000028014183, -0.07400000095367432, 0.026000000536441803, -0.14810000360012054, -0.06430000066757202, -0.0031999999191612005, 0.0052999998442828655, 0.08730000257492065, -0.0340999998152256, 0.04320000112056732, 0.033399999141693115, 0.07569999992847443, 0.06019999831914902, -0.026499999687075615, 0.034699998795986176, 0.06970000267028809, 0.06210000067949295, 0.05139999836683273, 0.11400000005960464, 0.014600000344216824, -0.08110000193119049, 0.05689999833703041, -0.027899999171495438, 0.06459999829530716, -0.017000000923871994, 0.042500000447034836, 0.08259999752044678, 0.0722000002861023, -0.03590000048279762, 0.08139999955892563, 0.04050000011920929, 0.023600000888109207, 0.0723000019788742, -0.023399999365210533, 0.009499999694526196, -0.01940000057220459, -0.08869999647140503, 0.09730000048875809, 0.02370000071823597, 0.07479999959468842, -0.07829999923706055, -0.028300000354647636, -0.07460000365972519, 0.03519999980926514, 0.0035000001080334187, -0.0024999999441206455, 0.09130000323057175, -0.04089999943971634, -0.0019000000320374966, 0.042100001126527786, -0.04639999940991402, 0.021700000390410423, -0.0737999975681305, -0.05040000006556511, 0.004000000189989805, -0.02290000021457672, -0.06729999929666519, -0.04050000011920929, 0.01730000041425228, -0.046300001442432404, 0.01889999955892563, -0.027499999850988388, 0.06930000334978104, -0.026499999687075615, -0.04600000008940697, 0.03909999877214432, 0.01730000041425228, -0.05270000174641609, -0.07750000059604645, -0.02969999983906746, 0.06260000169277191, 0.07930000126361847, 0.0478999987244606, -0.0868000015616417, 0.00139999995008111, 0.0681999996304512, -0.05820000171661377, 0.06499999761581421, 0.039799999445676804, 0.03280000016093254, -0.018699999898672104, -0.006899999920278788, 0.04780000075697899, 0.061900001019239426, -0.042500000447034836, -0.048900000751018524, -0.05299999937415123, -0.008299999870359898, 0.07559999823570251, 0.05570000037550926, 0.015300000086426735, 0.04100000113248825, 0.029400000348687172, -0.039799999445676804, -0.021900000050663948, -0.08669999986886978, -0.15790000557899475, 0.02710000053048134, 0.08550000190734863, 0.0038999998942017555, -0.03350000083446503, 0.08020000159740448, -0.03440000116825104, -0.042899999767541885, 0.07169999927282333, 0.0877000018954277, -0.014600000344216824, 0.027000000700354576, -0.028200000524520874, 0.02669999934732914, -0.0215000007301569, -0.029200000688433647, 0.04580000042915344, 0.06689999997615814, -0.05660000070929527, 0.007899999618530273, 0.004900000058114529, 0.03790000081062317, 0.05920000001788139, 0.04800000041723251, 0.07779999822378159, 0.06560000032186508], [0.004600000102072954, -0.04910000041127205, -0.05469999834895134, 0.05559999868273735, -0.1500999927520752, 0.031300000846385956, 0.03869999945163727, 0.07599999755620956, -0.02930000051856041, 0.04490000009536743, 0.06719999760389328, 0.003800000064074993, -0.02329999953508377, -0.08209999650716782, 0.016100000590085983, -0.06480000168085098, -0.025699999183416367, -0.06889999657869339, -0.06909999996423721, -0.065700002014637, -0.051899999380111694, -0.09589999914169312, -0.00139999995008111, -0.0908999964594841, -0.11879999935626984, -0.11249999701976776, 0.09070000052452087, -0.10289999842643738, 0.022299999371170998, -0.05860000103712082, -0.012900000438094139, -0.0430000014603138, -0.11100000143051147, -0.0828000009059906, 0.052400000393390656, -0.07779999822378159, -0.017999999225139618, -0.030500000342726707, -0.026799999177455902, 0.04149999842047691, -0.02449999935925007, 0.04479999840259552, 0.0835999995470047, -0.0908999964594841, -0.06920000165700912, -0.04450000077486038, 0.0778999999165535, 0.005400000140070915, 0.08950000256299973, -0.053300000727176666, -0.007400000002235174, 0.05559999868273735, -0.0794999971985817, 0.04470000043511391, 0.002899999963119626, -0.009600000455975533, 0.08399999886751175, -0.015799999237060547, 0.09139999747276306, 0.04800000041723251, 0.016699999570846558, -0.0005000000237487257, 0.06650000065565109, 0.05559999868273735, -0.009999999776482582, 0.05480000004172325, -0.023900000378489494, 0.014499999582767487, 0.020500000566244125, 0.04129999876022339, 0.08190000057220459, -0.013799999840557575, -0.030400000512599945, 0.03319999948143959, 0.04879999905824661, 0.06939999759197235, -0.09319999814033508, -0.13770000636577606, -0.027000000700354576, 0.09780000150203705, 0.0142000000923872, -0.01940000057220459, 0.000699999975040555, -0.08079999685287476, -0.042100001126527786, -0.024399999529123306, 0.03200000151991844, 0.00860000029206276, -0.10379999876022339, -0.06970000267028809, 0.11299999803304672, 0.04270000010728836, 0.004600000102072954, 0.017500000074505806, -0.10530000180006027, -0.04100000113248825, -0.009800000116229057, -0.08219999819993973, -0.07559999823570251, 0.021700000390410423, 0.02280000038444996, 0.07970000058412552, 0.031300000846385956, -0.051600001752376556, -0.09600000083446503, 0.03680000081658363, 0.030400000512599945, -0.03480000048875809, 0.04839999973773956, 0.06530000269412994, -0.06480000168085098, -0.06759999692440033, 0.04540000110864639, -0.09669999778270721, 0.00019999999494757503, -0.028699999675154686, 0.03620000183582306, 0.03020000085234642, -0.03400000184774399, -0.06949999928474426, 0.05180000141263008, -0.07670000195503235, 0.013799999840557575, -0.043800000101327896, -0.10459999740123749, -0.04010000079870224, -0.10639999806880951, -0.08659999817609787]], [[0.0038999998942017555, -0.011599999852478504, 0.0738999992609024, 0.0632999986410141, -0.05909999832510948, 0.0357000008225441, 0.06889999657869339, 0.1436000019311905, -0.07109999656677246, 0.25040000677108765, 0.16410000622272491, -0.11230000108480453, 0.08910000324249268, 0.07010000199079514, 0.12809999287128448, 0.01759999990463257, 0.05400000140070915, -0.07259999960660934, 0.0364999994635582, 0.05829999968409538, -0.04360000044107437, -0.0005000000237487257, -0.10599999874830246, -0.02199999988079071, 0.08479999750852585, 0.15209999680519104, 0.10740000009536743, -0.10980000346899033, -0.10599999874830246, 0.1257999986410141, 0.07500000298023224, 0.07919999957084656, -0.057100001722574234, -0.1160999983549118, 0.13300000131130219, -0.09560000151395798, -0.03849999979138374, -0.03539999946951866, -0.004900000058114529, -0.1477999985218048, -0.051100000739097595, 0.05900000035762787, 0.028699999675154686, -0.07760000228881836, 0.012400000356137753, 0.09350000321865082, -0.10109999775886536, 0.01730000041425228, -0.013299999758601189, -0.0763000026345253, 0.05939999967813492, 0.05649999901652336, 0.031700000166893005, 0.01810000091791153, -0.11749999970197678, 0.016899999231100082, -0.04800000041723251, 0.031599998474121094, 0.04479999840259552, -0.026900000870227814, -0.28279998898506165, 0.14390000700950623, 0.07970000058412552, -0.1257999986410141, 0.03720000013709068, -0.12489999830722809, 0.1949000060558319, -0.12250000238418579, -0.06369999796152115, 0.07169999927282333, 0.017899999395012856, -0.08619999885559082, 0.011300000362098217, -0.0697999969124794, 0.04280000180006027, 0.11869999766349792, -0.013500000350177288, 0.029899999499320984, -0.04960000142455101, -0.017799999564886093, -0.066600002348423, 0.17249999940395355, -0.02930000051856041, 0.01600000075995922, -0.12129999697208405, -0.13339999318122864, -0.12880000472068787, 0.016100000590085983, -0.09269999712705612, 0.04280000180006027, 0.032499998807907104, 0.17810000479221344, -0.05649999901652336, -0.11659999936819077, -0.015200000256299973, -0.014299999922513962, 0.033399999141693115, 0.1289999932050705, 0.033900000154972076, -0.032600000500679016, -0.15029999613761902, -0.11949999630451202, -0.13729999959468842, 0.06780000030994415, 0.19930000603199005, 0.016499999910593033, 0.0917000025510788, 0.07959999889135361, -0.02979999966919422, 0.031099999323487282, -0.042500000447034836, 0.04089999943971634, -0.09160000085830688, 0.027699999511241913, 0.12250000238418579, -0.02290000021457672, 0.09309999644756317, 0.04839999973773956, 0.006200000178068876, 0.06310000270605087, -0.066600002348423, 0.08420000225305557, -0.007000000216066837, -0.13339999318122864, -0.12060000002384186, -0.08179999887943268, 0.15629999339580536, -0.1177000030875206], [-0.0414000004529953, -0.07429999858140945, 0.12330000102519989, -0.05900000035762787, 0.2630999982357025, -0.10100000351667404, 0.14399999380111694, -0.07989999651908875, -0.00139999995008111, -0.028699999675154686, 0.08510000258684158, 0.16840000450611115, -0.00989999994635582, -0.0502999983727932, -0.04450000077486038, 0.09480000287294388, -0.008999999612569809, 0.04019999876618385, -0.09149999916553497, -0.032999999821186066, 0.026599999517202377, 0.11670000106096268, 0.12939999997615814, 0.10239999741315842, -0.032499998807907104, 0.062300000339746475, 0.052299998700618744, -0.14149999618530273, -0.05429999902844429, -0.03240000084042549, 0.03099999949336052, 0.027000000700354576, -0.10140000283718109, -0.05550000071525574, -0.07689999788999557, 0.05290000140666962, 0.08309999853372574, -0.16930000483989716, 0.022600000724196434, 0.030400000512599945, 0.22939999401569366, 0.1168999969959259, 0.06199999898672104, 0.10329999774694443, -0.05620000138878822, 0.08699999749660492, -0.12710000574588776, -0.00559999980032444, -0.007000000216066837, -0.10740000009536743, -0.09510000050067902, 0.045499999076128006, 0.027400000020861626, 0.07509999722242355, -0.10639999806880951, -0.08879999816417694, 0.11420000344514847, 0.04699999839067459, -0.17679999768733978, -0.04839999973773956, -0.019600000232458115, -0.040699999779462814, 0.0723000019788742, 0.1776999980211258, 0.05209999904036522, -0.08649999648332596, -0.009499999694526196, 0.04690000042319298, -0.036400001496076584, 0.10199999809265137, -0.061400000005960464, 0.08940000087022781, -0.0966000035405159, -0.02630000002682209, 0.03620000183582306, 0.07930000126361847, 0.015799999237060547, -0.16419999301433563, -0.12070000171661377, -0.10339999943971634, -0.022700000554323196, -0.16200000047683716, -0.07490000128746033, 0.02449999935925007, -0.025299999862909317, -0.13099999725818634, -0.0966000035405159, -0.1673000007867813, 0.10019999742507935, -0.16110000014305115, -0.011599999852478504, -0.07370000332593918, -0.18649999797344208, -0.03060000017285347, -0.02630000002682209, 0.08919999748468399, -0.002199999988079071, -0.18709999322891235, -0.13369999825954437, -0.1655000001192093, -0.062199998646974564, -0.1712000072002411, 0.019700000062584877, -0.0868000015616417, 0.012000000104308128, 0.18809999525547028, 0.0066999997943639755, 0.050599999725818634, -0.05660000070929527, -0.06340000033378601, 0.0003000000142492354, -0.07329999655485153, 0.10689999908208847, -0.07410000264644623, -0.13030000030994415, 0.1526000052690506, -0.04960000142455101, -0.007400000002235174, -0.11869999766349792, -0.022199999541044235, -0.060499999672174454, -0.10320000350475311, 0.041600000113248825, -0.055399999022483826, 0.014399999752640724, 0.0215000007301569, -0.13420000672340393, 0.03280000016093254], [0.019999999552965164, -0.08349999785423279, -0.04190000146627426, 0.11219999939203262, 0.023099999874830246, -0.048700001090765, -0.1014999970793724, -0.08810000121593475, -0.03500000014901161, -0.08990000188350677, -0.2053000032901764, -0.1080000028014183, 0.03350000083446503, 0.0052999998442828655, -0.19329999387264252, 0.050700001418590546, -0.08100000023841858, -0.0625, 0.121799997985363, 0.024000000208616257, -0.010700000450015068, -0.03460000082850456, -0.010700000450015068, 0.04010000079870224, -0.11630000174045563, 0.07029999792575836, 0.11089999973773956, 0.006399999838322401, 0.0340999998152256, 0.017000000923871994, -0.08760000020265579, -0.05939999967813492, 0.04170000180602074, -0.09139999747276306, -0.005400000140070915, 0.06369999796152115, 0.003800000064074993, 0.003800000064074993, 0.060100000351667404, 0.058400001376867294, -0.11779999732971191, 0.02850000001490116, -0.012900000438094139, 0.08789999783039093, 0.007600000128149986, 0.00860000029206276, -0.04879999905824661, -0.01860000006854534, -0.15240000188350677, -0.18850000202655792, -0.08020000159740448, -0.03020000085234642, -0.0674000009894371, 0.00839999970048666, 0.02710000053048134, -0.015799999237060547, 0.14079999923706055, -0.0674000009894371, -0.005900000222027302, 0.05559999868273735, 0.06549999862909317, 0.17479999363422394, -0.0019000000320374966, 0.023600000888109207, 0.053599998354911804, -0.13030000030994415, -0.12269999831914902, 0.04500000178813934, -0.061900001019239426, -0.05469999834895134, 0.0406000018119812, -0.13500000536441803, 0.07199999690055847, 0.010900000110268593, -0.012900000438094139, 0.049400001764297485, -0.12120000272989273, -0.06340000033378601, -0.028200000524520874, -0.0005000000237487257, 0.02459999918937683, 0.11180000007152557, -0.08839999884366989, -0.013299999758601189, 0.032499998807907104, -0.0035000001080334187, -0.07810000330209732, -0.11479999870061874, 0.04280000180006027, 0.02419999986886978, -0.05270000174641609, -0.13950000703334808, -0.1088000014424324, 0.15489999949932098, 0.10140000283718109, -0.13770000636577606, 0.05889999866485596, -0.05860000103712082, 0.057100001722574234, -0.04610000178217888, -0.13979999721050262, 0.1136000007390976, -0.15389999747276306, 0.06930000334978104, 0.13079999387264252, -0.029899999499320984, 0.14270000159740448, -0.03999999910593033, 0.06840000301599503, -0.20839999616146088, -0.11270000040531158, 0.16210000216960907, -0.008700000122189522, -0.039400000125169754, 0.12309999763965607, 0.03099999949336052, -0.05590000003576279, -0.04179999977350235, -0.1712999939918518, -0.07829999923706055, 0.08609999716281891, 0.0478999987244606, 0.08320000022649765, -0.027799999341368675, 0.03889999911189079, -0.10679999738931656, -0.1451999992132187, 0.007699999958276749], [0.0723000019788742, -0.00019999999494757503, -0.11680000275373459, -0.10130000114440918, 0.32179999351501465, 0.03929999843239784, 0.09369999915361404, 0.08969999849796295, 0.10100000351667404, 0.11020000278949738, -0.09279999881982803, 0.08579999953508377, -0.06030000001192093, 0.03970000147819519, -0.01640000008046627, -0.1817999929189682, 0.0502999983727932, -0.06430000066757202, 0.038100000470876694, 0.03060000017285347, -0.011800000444054604, 0.12549999356269836, 0.011500000022351742, -0.09130000323057175, 0.02669999934732914, 0.004600000102072954, -0.050599999725818634, 0.032499998807907104, 0.049400001764297485, 0.11460000276565552, 0.13220000267028809, 0.12800000607967377, -0.09459999948740005, 0.1534000039100647, 0.04989999905228615, -0.006599999964237213, -0.1152999997138977, -0.0406000018119812, 0.20749999582767487, 0.10379999876022339, -0.11410000175237656, 0.09939999878406525, 0.05959999933838844, 0.10840000212192535, 0.12489999830722809, -0.015699999406933784, 0.060499999672174454, 0.002099999925121665, 0.22779999673366547, -0.09939999878406525, -0.15889999270439148, -0.00989999994635582, -0.06930000334978104, -0.013500000350177288, -0.010300000198185444, -0.031300000846385956, -0.06620000302791595, 0.02250000089406967, -0.0714000016450882, 0.09950000047683716, -0.09889999777078629, 0.11720000207424164, 0.08389999717473984, -0.13570000231266022, -0.06530000269412994, 0.012199999764561653, -9.999999747378752e-05, -0.04749999940395355, -0.05849999934434891, 0.016200000420212746, 0.034299999475479126, -0.016100000590085983, -0.045099999755620956, -0.03009999915957451, -0.04809999838471413, 0.024399999529123306, -0.0044999998062849045, -0.13819999992847443, 0.011599999852478504, -0.17139999568462372, -0.06430000066757202, -0.11429999768733978, 0.04039999842643738, 0.12129999697208405, 0.10090000182390213, -0.012600000016391277, 0.011699999682605267, 0.15710000693798065, 0.0010000000474974513, -0.07100000232458115, 0.1395999938249588, -0.11559999734163284, 0.019700000062584877, 0.25600001215934753, -0.03200000151991844, 0.05220000073313713, -0.14180000126361847, 0.1151999980211258, 0.15139999985694885, 0.022299999371170998, -0.0, 0.0625, -0.03689999878406525, -0.07339999824762344, -0.10180000215768814, 0.048900000751018524, -0.02410000003874302, -0.09009999781847, 0.019600000232458115, 0.0949999988079071, 0.009499999694526196, 0.07509999722242355, -0.09000000357627869, -0.07249999791383743, 0.1265999972820282, -0.13750000298023224, -0.10119999945163727, -0.03909999877214432, -0.0851999968290329, 0.06350000202655792, 0.08579999953508377, -0.07819999754428864, 0.09200000017881393, -0.00989999994635582, 0.05350000038743019, 0.08089999854564667, 0.07169999927282333, -0.0478999987244606], [0.1657000035047531, -0.008999999612569809, -0.024700000882148743, -0.1898999959230423, -0.20810000598430634, -0.18170000612735748, -0.12520000338554382, -0.04320000112056732, 0.08900000154972076, 0.09070000052452087, 0.05400000140070915, -0.013500000350177288, -0.1818999946117401, -0.12479999661445618, -0.12479999661445618, -0.1251000016927719, 0.11630000174045563, 0.14710000157356262, 0.27000001072883606, 0.22050000727176666, 0.08560000360012054, -0.05550000071525574, -0.10029999911785126, 0.1915999948978424, 0.007699999958276749, -0.020899999886751175, -0.003800000064074993, -0.1080000028014183, -0.19140000641345978, -0.003000000026077032, 0.05570000037550926, -0.1005999967455864, 0.010900000110268593, -0.1177000030875206, -0.15160000324249268, 0.15330000221729279, 0.19439999759197235, 0.2492000013589859, 0.11999999731779099, 0.13249999284744263, -0.11800000071525574, -0.03790000081062317, 0.0754999965429306, -0.07940000295639038, 0.16220000386238098, 0.10520000010728836, -0.0471000000834465, -0.3634999990463257, -0.1388999968767166, -0.29679998755455017, -0.07980000227689743, 0.25130000710487366, -0.11180000007152557, 0.0722000002861023, -0.007199999876320362, 0.10620000213384628, -0.08129999786615372, -0.0019000000320374966, -0.04899999871850014, -0.2159000039100647, 0.017799999564886093, -0.2667999863624573, 0.011599999852478504, -0.12150000035762787, 0.10090000182390213, -0.027799999341368675, -0.07850000262260437, -0.1858000010251999, -0.10849999636411667, 0.17649999260902405, -0.19050000607967377, 0.0989999994635582, 0.023000000044703484, -0.12120000272989273, -0.031599998474121094, -0.007000000216066837, -0.011300000362098217, -0.10700000077486038, 0.13940000534057617, 0.15700000524520874, 0.09860000014305115, 0.14000000059604645, 0.02850000001490116, 0.042899999767541885, -0.04879999905824661, 0.1762000024318695, 0.07509999722242355, -0.09200000017881393, -0.004600000102072954, 0.21789999306201935, 0.17589999735355377, -0.2175000011920929, -0.07609999924898148, 0.03579999879002571, -0.2653999924659729, 0.218299999833107, -0.0421999990940094, -0.1501999944448471, -0.02630000002682209, -0.1251000016927719, -0.0617000013589859, -0.14229999482631683, -0.01979999989271164, 0.17270000278949738, 0.0038999998942017555, 0.2662999927997589, -0.12630000710487366, 0.13019999861717224, -0.1128000020980835, -0.0032999999821186066, -0.20640000700950623, -0.029899999499320984, 0.03929999843239784, 0.026100000366568565, -0.1624000072479248, 0.17499999701976776, 0.12110000103712082, -0.032499998807907104, 0.11749999970197678, -0.17949999868869781, -0.1467999964952469, 0.2037999927997589, 0.13330000638961792, -0.16259999573230743, -0.11469999700784683, -0.23589999973773956, 0.03449999913573265, -0.032499998807907104], [-0.058800000697374344, -0.033799998462200165, 0.11180000007152557, 0.012900000438094139, 0.09109999984502792, -0.11339999735355377, 0.010999999940395355, -0.01730000041425228, 0.08659999817609787, 0.15379999577999115, -0.03519999980926514, -0.0803999975323677, -0.1386999934911728, 0.10490000247955322, -0.18889999389648438, -0.03280000016093254, 0.09730000048875809, 0.1152999997138977, -0.10429999977350235, -0.06270000338554382, 0.11590000241994858, -0.011900000274181366, 0.08900000154972076, -0.0035000001080334187, 0.029899999499320984, 0.045899998396635056, -0.0966000035405159, -0.08460000157356262, -0.026000000536441803, 0.16359999775886536, 0.16279999911785126, -0.0812000036239624, -0.019300000742077827, 0.08169999718666077, -0.06920000165700912, 0.12139999866485596, 0.11259999871253967, 0.006099999882280827, 0.03999999910593033, 0.04560000076889992, 0.03009999915957451, 0.019999999552965164, 0.07649999856948853, -0.018699999898672104, -0.000699999975040555, -0.06199999898672104, 0.02850000001490116, 0.09189999848604202, 0.026900000870227814, 0.0010000000474974513, 0.10700000077486038, 0.02590000070631504, 0.09030000120401382, 0.008500000461935997, 0.1257999986410141, 0.06400000303983688, 0.014600000344216824, -0.05350000038743019, -0.09130000323057175, 0.07150000333786011, 0.14239999651908875, -0.11500000208616257, -0.11110000312328339, -0.014800000004470348, -0.007699999958276749, 0.0035000001080334187, -0.014399999752640724, 0.03669999912381172, 0.15649999678134918, -0.094200000166893, -0.0794999971985817, 0.07739999890327454, 0.05889999866485596, 0.2687999904155731, -0.0560000017285347, 0.1143999993801117, -0.05400000140070915, -0.12890000641345978, 0.08799999952316284, -0.12240000069141388, 0.17520000040531158, -0.10199999809265137, 0.03840000182390213, -0.043699998408555984, -0.009399999864399433, 0.00930000003427267, 0.08049999922513962, 0.15379999577999115, -0.08049999922513962, -0.046300001442432404, 0.0272000003606081, -0.017500000074505806, -0.15929999947547913, -0.01360000018030405, 0.15950000286102295, 0.10809999704360962, -0.1777999997138977, -0.06129999831318855, -0.05050000175833702, 0.08829999715089798, -0.3310000002384186, -0.00839999970048666, -0.10740000009536743, -0.05169999971985817, -0.020099999383091927, -0.016699999570846558, -0.06889999657869339, -0.12060000002384186, 0.03579999879002571, -0.3343999981880188, 0.18549999594688416, -0.0544000007212162, 0.021900000050663948, 0.0471000000834465, -0.09040000289678574, -0.042399998754262924, 0.13289999961853027, 0.10409999638795853, 0.10639999806880951, 0.08250000327825546, 0.04659999907016754, 0.12210000306367874, 0.09769999980926514, -0.1867000013589859, -0.12080000340938568, -0.03539999946951866, -0.08569999784231186, 0.06109999865293503], [-0.16449999809265137, 0.13850000500679016, -0.046300001442432404, -0.056699998676776886, 0.013700000010430813, 0.05139999836683273, 0.10189999639987946, 0.10689999908208847, -0.00989999994635582, -0.07020000368356705, -0.19130000472068787, -0.06419999897480011, 0.12860000133514404, -0.09399999678134918, 0.0697999969124794, -0.06830000132322311, 0.0008999999845400453, 0.04280000180006027, -0.0722000002861023, 0.18790000677108765, 0.02630000002682209, -0.053599998354911804, 0.03579999879002571, 0.05790000036358833, 0.275299996137619, 0.01640000008046627, -0.09470000118017197, -0.06620000302791595, 0.0689999982714653, -0.07800000160932541, 0.027400000020861626, -0.12470000237226486, 0.04179999977350235, 0.10080000013113022, -0.10249999910593033, 0.034699998795986176, -0.029200000688433647, 0.04470000043511391, -0.03909999877214432, -0.14730000495910645, 0.0731000006198883, -0.1817999929189682, 0.08550000190734863, -0.14650000631809235, -0.04960000142455101, 0.05220000073313713, 0.15760000050067902, -0.03229999914765358, -0.05130000039935112, 0.04580000042915344, -0.0803999975323677, -0.03629999980330467, -0.11299999803304672, -0.09189999848604202, -0.06499999761581421, -0.004399999976158142, -0.03849999979138374, -0.047600001096725464, -0.09749999642372131, 0.1080000028014183, -0.04439999908208847, 0.012799999676644802, -0.14219999313354492, -0.0551999993622303, -0.09260000288486481, -0.06120000034570694, -0.05169999971985817, 0.07580000162124634, -0.13510000705718994, -0.08550000190734863, -0.032999999821186066, -0.11739999800920486, 0.019300000742077827, -0.019600000232458115, 0.05620000138878822, 0.21979999542236328, -0.13950000703334808, -0.08590000122785568, -0.13030000030994415, -0.0005000000237487257, 0.014700000174343586, -0.04179999977350235, 0.09120000153779984, -0.07599999755620956, -0.10109999775886536, -0.005900000222027302, -0.07109999656677246, 0.18039999902248383, 0.07109999656677246, 0.08340000361204147, -0.050999999046325684, 0.12559999525547028, -0.07320000231266022, 0.024299999698996544, -0.12610000371932983, -0.18379999697208405, 0.1477999985218048, -0.05009999871253967, 0.0551999993622303, -0.028699999675154686, 0.042899999767541885, 0.07779999822378159, 0.03909999877214432, -0.04230000078678131, 0.005200000014156103, 0.0026000000070780516, 0.016100000590085983, -0.05649999901652336, -0.051100000739097595, 0.03830000013113022, 0.08410000056028366, 0.13570000231266022, 0.09960000216960907, -0.1914999932050705, 0.06109999865293503, -0.024900000542402267, -0.016699999570846558, -0.18479999899864197, -0.24560000002384186, 0.18029999732971191, -0.218299999833107, -0.13189999759197235, -0.05050000175833702, 0.09510000050067902, 0.09889999777078629, 0.09700000286102295, -0.034699998795986176, 0.0340999998152256], [-0.03869999945163727, -0.15309999883174896, 0.09480000287294388, -0.11429999768733978, -0.19050000607967377, -0.002300000051036477, 0.020400000736117363, -0.07819999754428864, -0.003000000026077032, -0.017400000244379044, -0.11060000211000443, 0.03319999948143959, 0.09969999641180038, 0.01730000041425228, -0.1282999962568283, -0.09130000323057175, 0.03280000016093254, -0.004600000102072954, -0.044199999421834946, -0.1460999995470047, 0.2831999957561493, 0.1964000016450882, 0.02019999921321869, -0.1720999926328659, 0.07569999992847443, -0.09160000085830688, -0.05469999834895134, -0.01600000075995922, 0.010900000110268593, 0.05909999832510948, 0.042899999767541885, 0.0689999982714653, 0.08150000125169754, 0.1088000014424324, -9.999999747378752e-05, -0.019200000911951065, 0.06350000202655792, -0.028999999165534973, 0.05169999971985817, 0.06520000100135803, 0.16619999706745148, 0.00860000029206276, -0.05290000140666962, 0.019500000402331352, 0.015599999576807022, -0.06610000133514404, 0.0020000000949949026, 0.015699999406933784, -0.09529999643564224, 0.03400000184774399, 0.01730000041425228, -0.11410000175237656, -0.06970000267028809, 0.012199999764561653, -0.07159999758005142, 0.011599999852478504, -0.1378999948501587, 0.12080000340938568, -0.02969999983906746, -0.07689999788999557, -0.11010000109672546, 0.16279999911785126, -0.08060000091791153, 0.049400001764297485, 0.06859999895095825, -0.23340000212192535, 0.11389999836683273, 0.09120000153779984, -0.033900000154972076, -0.1851000040769577, 0.08399999886751175, -0.0203000009059906, -0.14300000667572021, 0.12430000305175781, 0.08990000188350677, 0.06650000065565109, 0.15289999544620514, -0.0348999984562397, 0.06870000064373016, -0.018400000408291817, -0.19120000302791595, -0.20509999990463257, -0.009700000286102295, 0.02239999920129776, -0.02290000021457672, -0.16259999573230743, 0.03420000150799751, 0.03319999948143959, 0.13570000231266022, -0.13259999454021454, 0.07509999722242355, -0.11649999767541885, 0.1738000065088272, -0.06539999693632126, 0.16840000450611115, -0.18700000643730164, 0.0015999999595806003, 0.011599999852478504, 0.08240000158548355, 0.08659999817609787, 0.09189999848604202, 0.038100000470876694, 0.17069999873638153, 0.08820000290870667, -0.015599999576807022, -0.20829999446868896, 0.048900000751018524, -0.19300000369548798, -0.148499995470047, -0.005499999970197678, 0.06379999965429306, 0.05260000005364418, -0.02449999935925007, 0.013299999758601189, 0.05380000174045563, -0.055399999022483826, -0.03519999980926514, 0.0414000004529953, 0.03790000081062317, 0.06650000065565109, 0.14390000700950623, -0.04390000179409981, 0.13040000200271606, -0.05990000069141388, 0.13539999723434448, 0.12929999828338623, 0.05939999967813492, -0.10920000076293945], [0.13770000636577606, 0.12250000238418579, 0.04100000113248825, -0.1453000009059906, 0.00930000003427267, 0.10589999705553055, 9.999999747378752e-05, 0.021299999207258224, -0.26510000228881836, -0.018300000578165054, -0.01140000019222498, -0.21559999883174896, 0.12280000001192093, 0.009499999694526196, -0.12370000034570694, 0.14059999585151672, 0.055399999022483826, 0.07559999823570251, 0.051500000059604645, 0.0892999991774559, -0.041200000792741776, 0.017400000244379044, -0.09260000288486481, 0.0868000015616417, -0.009700000286102295, -0.03720000013709068, -0.06769999861717224, -0.002099999925121665, 0.008999999612569809, 0.04439999908208847, -0.09839999675750732, 0.17560000717639923, -0.08179999887943268, -0.05770000070333481, -0.07850000262260437, -0.06759999692440033, -0.014299999922513962, -0.05590000003576279, -0.002199999988079071, 0.07150000333786011, -0.09019999951124191, 0.01899999938905239, 0.04390000179409981, 0.010999999940395355, -0.042100001126527786, -0.020999999716877937, -0.018400000408291817, 0.0005000000237487257, -0.10010000318288803, 0.11800000071525574, -0.2160000056028366, 0.10890000313520432, 0.13199999928474426, -0.04500000178813934, 0.0997999981045723, 0.08299999684095383, -0.01360000018030405, -0.28529998660087585, -0.03359999880194664, -0.04039999842643738, 0.07270000129938126, -0.05000000074505806, 0.1542000025510788, 0.033900000154972076, -0.008299999870359898, 0.04699999839067459, 0.022099999710917473, -0.12219999730587006, 0.16609999537467957, 0.0722000002861023, -0.006500000134110451, 0.10869999974966049, -0.06610000133514404, 0.061900001019239426, 0.030700000002980232, -0.022299999371170998, 0.012799999676644802, -0.22550000250339508, 0.06800000369548798, 0.18440000712871552, 0.17759999632835388, -0.060600001364946365, -0.03700000047683716, -0.06790000200271606, 0.10369999706745148, 0.22529999911785126, 0.10429999977350235, -0.10220000147819519, 0.04639999940991402, 0.08129999786615372, 0.0044999998062849045, 0.01810000091791153, 0.06909999996423721, -0.022700000554323196, 0.05260000005364418, 0.015599999576807022, 0.0869000032544136, -0.08799999952316284, -0.14630000293254852, 0.09700000286102295, -0.12540000677108765, -0.1234000027179718, -0.01899999938905239, 0.20440000295639038, -0.09929999709129333, 0.09279999881982803, -0.050999999046325684, -0.11990000307559967, -0.18219999969005585, 0.009499999694526196, 0.042399998754262924, 0.12080000340938568, 0.10040000081062317, 0.10260000079870224, 0.07829999923706055, -0.06669999659061432, -0.09759999811649323, 0.10670000314712524, 0.045899998396635056, 0.1995999962091446, -0.10610000044107437, 0.0658000037074089, 0.15330000221729279, 0.1356000006198883, -0.10220000147819519, 0.054999999701976776, -0.024800000712275505, 0.03610000014305115], [0.0215000007301569, 0.09600000083446503, 0.019899999722838402, 0.01140000019222498, 0.11800000071525574, 0.10180000215768814, 0.25220000743865967, -0.08349999785423279, 0.08760000020265579, -0.20960000157356262, -0.06700000166893005, -0.179299995303154, 0.17100000381469727, -0.02630000002682209, 0.027400000020861626, -0.023099999874830246, 0.1632000058889389, -0.09179999679327011, -0.14920000731945038, 0.18410000205039978, 0.08860000222921371, -0.019999999552965164, 0.07259999960660934, 0.023499999195337296, -0.03189999982714653, 0.023600000888109207, 0.15549999475479126, -0.03620000183582306, 0.011900000274181366, -0.10300000011920929, -0.02669999934732914, -0.03240000084042549, -0.051500000059604645, -0.002099999925121665, -0.01769999973475933, -0.026200000196695328, 0.006099999882280827, 0.0860000029206276, -0.04390000179409981, 0.14030000567436218, -0.052299998700618744, -0.12700000405311584, -0.05570000037550926, 0.04479999840259552, -0.04490000009536743, 0.06599999964237213, 0.06239999830722809, 0.027799999341368675, 0.036400001496076584, 0.03620000183582306, 0.16130000352859497, 0.1151999980211258, -0.0071000000461936, 0.01720000058412552, -0.0608999989926815, 0.05999999865889549, -0.010400000028312206, 0.10540000349283218, -0.0333000011742115, -0.07800000160932541, -0.021800000220537186, 0.0005000000237487257, -0.048500001430511475, -0.066600002348423, 0.0843999981880188, 0.04479999840259552, 0.05299999937415123, 0.11540000140666962, 0.09570000320672989, -0.0031999999191612005, -0.013399999588727951, -0.2572999894618988, 0.09910000115633011, 0.1509999930858612, -0.07289999723434448, -0.048900000751018524, 0.11100000143051147, -0.017899999395012856, -0.265500009059906, 0.12250000238418579, 0.014399999752640724, -0.10530000180006027, -0.003599999938160181, -0.10580000281333923, -0.0203000009059906, -0.003700000001117587, 0.08780000358819962, 0.16850000619888306, -0.02710000053048134, -0.1307000070810318, 0.012900000438094139, 0.10760000348091125, -0.06599999964237213, 0.0835999995470047, 0.026499999687075615, -0.1736000031232834, -0.06469999998807907, -0.06289999932050705, -0.02759999968111515, -0.017899999395012856, 0.04910000041127205, 0.03579999879002571, -0.030899999663233757, -0.09929999709129333, 0.11289999634027481, 0.0458999</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>[0.5300873462477564]</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>[0.10726537709540986]</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>[-0.026411600052050677]</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>[0.23433312562941258]</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>[-1.9825885778569128]</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>[0.9761406787104836]</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>[0.4511176119953938]</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>[0.12608875344709972]</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>[-0.37644306942063244]</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>[0.3264386521247344]</t>
+        </is>
+      </c>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>[0.5876748091628767]</t>
+        </is>
+      </c>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>[0.13555085242316772]</t>
+        </is>
+      </c>
+      <c r="Q27" t="inlineStr">
+        <is>
+          <t>[0.1389191068225072]</t>
+        </is>
+      </c>
+      <c r="R27" t="inlineStr">
+        <is>
+          <t>[0.09284667504352852]</t>
+        </is>
+      </c>
+      <c r="S27" t="inlineStr">
+        <is>
+          <t>[0.11997751250966837]</t>
+        </is>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>[0.0741509937917761]</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>[-0.6813383032390321]</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>[0.16077483211804788]</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>[0.15067931306756033]</t>
+        </is>
+      </c>
+      <c r="X27" t="inlineStr">
+        <is>
+          <t>[0.08897536476060275]</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>[0.05152448859477288]</t>
+        </is>
+      </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>[0.07805309415728741]</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>[-1.4668529824239367]</t>
+        </is>
+      </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>[0.226961265249985]</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>[-0.5823513455699401]</t>
+        </is>
+      </c>
+      <c r="AD27" t="inlineStr">
+        <is>
+          <t>[0.1325946680855103]</t>
+        </is>
+      </c>
+      <c r="AE27" t="inlineStr">
+        <is>
+          <t>[-0.46588565781130264]</t>
+        </is>
+      </c>
+      <c r="AF27" t="inlineStr">
+        <is>
+          <t>[0.1578437444612974]</t>
+        </is>
+      </c>
+      <c r="AG27" t="inlineStr">
+        <is>
+          <t>[-2.6587544433084718]</t>
+        </is>
+      </c>
+      <c r="AH27" t="inlineStr">
+        <is>
+          <t>[0.27239411629464516]</t>
+        </is>
+      </c>
+      <c r="AI27" t="inlineStr">
+        <is>
+          <t>[-0.845102599035749]</t>
+        </is>
+      </c>
+      <c r="AJ27" t="inlineStr">
+        <is>
+          <t>[0.1512041039968183]</t>
+        </is>
+      </c>
+      <c r="AK27" t="inlineStr">
+        <is>
+          <t>[-0.4693997565352177]</t>
+        </is>
+      </c>
+      <c r="AL27" t="inlineStr">
+        <is>
+          <t>[0.15596601839650542]</t>
+        </is>
+      </c>
+      <c r="AM27" t="inlineStr">
+        <is>
+          <t>[-2.776493430661176]</t>
+        </is>
+      </c>
+      <c r="AN27" t="inlineStr">
+        <is>
+          <t>[0.2900620735564225]</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>model_128_64_1</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>[128, 64]</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>[[[0.01979999989271164, -0.020899999886751175, 0.04690000042319298, 0.05649999901652336, 0.05119999870657921, -0.12319999933242798, 0.017400000244379044, 0.01510000042617321, -0.01759999990463257, 0.030300000682473183, -0.039000000804662704, -0.014499999582767487, 0.03610000014305115, 0.09679999947547913, -0.0632999986410141, 0.003100000089034438, -0.010999999940395355, -0.0006000000284984708, 0.009399999864399433, 0.00570000009611249, -0.03370000049471855, -0.07819999754428864, -0.08079999685287476, 0.07209999859333038, 0.03180000185966492, -0.039500001817941666, 0.04800000041723251, -0.0617000013589859, 0.14569999277591705, -0.03849999979138374, -0.019700000062584877, 0.003700000001117587, -0.012799999676644802, 0.02979999966919422, -0.010999999940395355, -0.023900000378489494, -0.02449999935925007, 0.014000000432133675, -0.05990000069141388, -0.028300000354647636, 0.032099999487400055, -0.0835999995470047, -0.06310000270605087, -0.0348999984562397, 0.05040000006556511, -0.029600000008940697, 0.026799999177455902, -0.005100000184029341, -0.12250000238418579, 0.03200000151991844, -0.028999999165534973, 0.0731000006198883, 0.017999999225139618, -0.03880000114440918, 0.07970000058412552, -0.007000000216066837, 0.031300000846385956, -0.03139999881386757, 0.050599999725818634, 0.06360000371932983, -0.04699999839067459, 0.028300000354647636, 0.056699998676776886, -0.07150000333786011, -0.09989999979734421, 0.006500000134110451, -0.049400001764297485, 0.02630000002682209, -0.010700000450015068, -0.07890000194311142, 0.10100000351667404, -0.03750000149011612, -0.08540000021457672, 0.07190000265836716, 0.05290000140666962, 0.017999999225139618, 0.026200000196695328, 0.04619999974966049, -0.05559999868273735, 0.0210999995470047, -0.01590000092983246, 0.07689999788999557, 0.05220000073313713, 0.025200000032782555, 0.10400000214576721, -0.0284000001847744, 0.0005000000237487257, -0.05040000006556511, -0.094200000166893, 0.009399999864399433, 0.0364999994635582, -0.06710000336170197, 0.00559999980032444, -0.10379999876022339, 0.07909999787807465, -0.015599999576807022, 0.09070000052452087, 0.008700000122189522, -0.023000000044703484, 0.031599998474121094, 0.04809999838471413, 0.0835999995470047, 0.01640000008046627, 0.043800000101327896, -0.02879999950528145, -0.014600000344216824, 0.023600000888109207, 0.002899999963119626, -0.05040000006556511, 0.05000000074505806, -0.03449999913573265, -0.019500000402331352, -0.01889999955892563, -0.009499999694526196, 0.03790000081062317, -0.004800000227987766, -0.06629999727010727, -0.05990000069141388, 0.019500000402331352, 0.0771000012755394, -0.051899999380111694, 0.08720000088214874, -0.03909999877214432, -0.049300000071525574, 0.008500000461935997, -0.0737999975681305, -0.01730000041425228, -0.04349999874830246], [0.08550000190734863, 0.06120000034570694, 0.04780000075697899, 0.006500000134110451, -0.028300000354647636, -0.08110000193119049, -0.052299998700618744, -0.0640999972820282, 0.020800000056624413, -0.007799999788403511, 0.02199999988079071, -0.0071000000461936, -0.0284000001847744, -0.08789999783039093, 0.0017999999690800905, -0.016699999570846558, -0.0284000001847744, -0.07460000365972519, -0.05310000106692314, -0.028699999675154686, 0.0544000007212162, 0.041600000113248825, 0.019600000232458115, 0.021800000220537186, -0.05310000106692314, 0.02810000069439411, -0.013899999670684338, -0.02070000022649765, 0.0031999999191612005, -0.06729999929666519, 0.03150000050663948, -0.0008999999845400453, -0.03610000014305115, -0.005100000184029341, 0.03750000149011612, -0.00430000014603138, -0.0689999982714653, -0.05299999937415123, 0.09290000051259995, 0.017799999564886093, -0.054499998688697815, 0.007899999618530273, 0.05350000038743019, 0.01889999955892563, 0.01269999984651804, 0.014399999752640724, -0.008999999612569809, 0.03590000048279762, -0.04910000041127205, -0.061900001019239426, -0.006200000178068876, -0.0284000001847744, -0.005799999926239252, -0.09480000287294388, -0.06880000233650208, -0.09839999675750732, 0.014700000174343586, 0.08150000125169754, 0.06889999657869339, -0.07959999889135361, 0.05299999937415123, -0.013299999758601189, 0.03750000149011612, 0.04399999976158142, 0.08150000125169754, 0.06270000338554382, -0.008299999870359898, 0.01549999974668026, 0.0017000000225380063, -0.02239999920129776, -0.04050000011920929, -0.027000000700354576, -0.08240000158548355, -0.05040000006556511, 0.03139999881386757, 0.05719999969005585, 0.04309999942779541, 0.04479999840259552, -0.01850000023841858, 0.0738999992609024, -0.04479999840259552, 0.03269999846816063, -0.03959999978542328, -0.07020000368356705, 0.04129999876022339, 0.10819999873638153, -0.0272000003606081, -0.06279999762773514, -0.03889999911189079, 0.0828000009059906, 0.05270000174641609, 0.024900000542402267, -0.05079999938607216, -0.07769999653100967, -0.07289999723434448, 0.017000000923871994, -0.08510000258684158, -0.04960000142455101, -0.011800000444054604, 0.08110000193119049, 0.027300000190734863, 0.030700000002980232, -0.011300000362098217, 0.01549999974668026, 0.007400000002235174, -0.044599998742341995, 0.07500000298023224, -0.01889999955892563, -0.05590000003576279, 0.03240000084042549, 0.05079999938607216, 0.08720000088214874, -0.07329999655485153, 0.030300000682473183, 0.03959999978542328, 0.0013000000035390258, 0.02810000069439411, -0.030899999663233757, -0.10530000180006027, -0.03350000083446503, 0.0421999990940094, -0.08380000293254852, -0.03229999914765358, -0.007899999618530273, -0.04320000112056732, 0.039400000125169754, 0.010900000110268593, -0.07999999821186066]], [[-0.16009999811649323, 0.05350000038743019, 0.016300000250339508, 0.012799999676644802, -0.10279999673366547, 0.09309999644756317, 0.042500000447034836, 0.0038999998942017555, 0.020999999716877937, -0.013199999928474426, 0.18539999425411224, 0.028699999675154686, -0.12540000677108765, 0.023399999365210533, 0.08780000358819962, -0.09549999982118607, 0.07190000265836716, -0.09009999781847, -0.019500000402331352, 0.0617000013589859, -0.0681999996304512, -0.04320000112056732, -0.03400000184774399, -0.06719999760389328, -0.07699999958276749, 0.048700001090765, -0.11050000041723251, -0.08479999750852585, -0.10689999908208847, 0.06270000338554382, 0.03500000014901161, 0.09989999979734421, -0.0737999975681305, -0.0027000000700354576, -0.25999999046325684, -0.053599998354911804, 0.10890000313520432, -0.13330000638961792, 0.12280000001192093, -0.002099999925121665, 0.027799999341368675, 0.008299999870359898, -0.010099999606609344, -0.012299999594688416, -0.058400001376867294, 0.033399999141693115, -0.054999999701976776, 0.19359999895095825, 0.0575999990105629, 0.03920000046491623, -0.1551000028848648, -0.04899999871850014, -0.060600001364946365, 0.13729999959468842, -0.05649999901652336, 0.03840000182390213, -0.03449999913573265, -0.15520000457763672, -0.13169999420642853, -0.0820000022649765, 0.15889999270439148, -0.07540000230073929, -0.07460000365972519, 0.06040000170469284, 0.09769999980926514, 0.001500000013038516, 0.03590000048279762, 0.19699999690055847, 0.012600000016391277, 0.03500000014901161, 0.07320000231266022, 0.016699999570846558, 0.0568000003695488, -0.1145000010728836, 0.09380000084638596, 0.11659999936819077, -0.04749999940395355, 0.10660000145435333, -0.08789999783039093, -0.01889999955892563, -0.029999999329447746, -0.020600000396370888, -0.12520000338554382, 0.1273999959230423, -0.0754999965429306, 0.010900000110268593, -0.15189999341964722, -0.020999999716877937, 0.01590000092983246, -0.007799999788403511, 0.01600000075995922, 0.015399999916553497, -0.10000000149011612, 0.040800001472234726, 0.04129999876022339, -0.10360000282526016, -0.03970000147819519, -0.0746999979019165, 0.04580000042915344, -0.0015999999595806003, 0.04769999906420708, 0.12330000102519989, 0.008299999870359898, -0.09120000153779984, -0.1451999992132187, 0.056299999356269836, -0.0038999998942017555, 0.12150000035762787, 0.11949999630451202, 0.002400000113993883, 0.03099999949336052, 0.00019999999494757503, -0.07029999792575836, 0.17919999361038208, 0.06719999760389328, -0.09560000151395798, 0.03579999879002571, 0.02630000002682209, -0.10819999873638153, -0.1371999979019165, 0.009200000204145908, -0.024000000208616257, -0.024900000542402267, 0.06159999966621399, 0.03959999978542328, -0.013700000010430813, -0.26809999346733093, -0.16279999911785126], [0.01489999983459711, 0.015799999237060547, -0.08470000326633453, 0.0625, 0.13809999823570251, 0.19539999961853027, 0.05389999970793724, 0.1348000019788742, -0.0026000000070780516, 0.1257999986410141, -0.05889999866485596, -0.09000000357627869, -0.07339999824762344, 0.018699999898672104, -0.03739999979734421, -0.08009999990463257, 0.03929999843239784, 0.05310000106692314, -0.07079999893903732, 0.12430000305175781, -0.1460999995470047, 0.031199999153614044, 0.022700000554323196, -0.04340000078082085, 0.029100000858306885, 0.022299999371170998, 0.0568000003695488, -0.07020000368356705, 0.0203000009059906, -0.041099999099969864, 0.04050000011920929, -0.03700000047683716, 0.06930000334978104, -0.014700000174343586, -0.21060000360012054, 0.11649999767541885, -0.1468999981880188, -0.019600000232458115, 0.10740000009536743, 9.999999747378752e-05, -0.06270000338554382, 0.1542000025510788, -0.14069999754428864, 0.11389999836683273, 0.11259999871253967, 0.00419999985024333, -0.20669999718666077, 0.03880000114440918, 0.03970000147819519, 0.0885000005364418, 0.09369999915361404, -0.1517000049352646, 0.013399999588727951, 0.1103999987244606, -0.08190000057220459, -0.17820000648498535, -0.053599998354911804, -0.04650000110268593, 0.03660000115633011, 0.06379999965429306, 0.012000000104308128, -0.04190000146627426, -0.07450000196695328, 0.09880000352859497, -0.044199999421834946, 0.05590000003576279, 0.06729999929666519, -0.11299999803304672, -0.05169999971985817, 0.024000000208616257, 0.07180000096559525, 0.013700000010430813, 0.1266999989748001, 0.004000000189989805, -0.1145000010728836, -0.0632999986410141, -0.02160000056028366, -0.04729999974370003, -0.04430000111460686, -0.11180000007152557, -0.018200000748038292, 0.02500000037252903, 0.14229999482631683, -0.07590000331401825, 0.10849999636411667, -0.00039999998989515007, 0.13089999556541443, 0.05730000138282776, -0.021900000050663948, 0.01119999960064888, 0.08889999985694885, -0.014800000004470348, -0.03220000118017197, 0.030500000342726707, 0.09849999845027924, 0.12919999659061432, 0.026000000536441803, 0.07090000063180923, 0.1014999970793724, 0.2915000021457672, 0.03060000017285347, -0.00279999990016222, -0.11909999698400497, -0.12870000302791595, 0.009499999694526196, -0.033399999141693115, -0.03440000116825104, 0.0820000022649765, -0.23839999735355377, 0.00430000014603138, -0.013399999588727951, -0.09629999846220016, -0.056699998676776886, 0.040800001472234726, 0.04919999837875366, 0.09040000289678574, -0.00419999985024333, 0.02590000070631504, 0.038600001484155655, 0.04470000043511391, 0.06700000166893005, 0.21729999780654907, 0.006200000178068876, -0.04230000078678131, -0.05310000106692314, 0.006599999964237213, -0.093299999833107, 0.031599998474121094], [0.06260000169277191, -0.09049999713897705, -0.19709999859333038, -0.10949999839067459, -0.020800000056624413, 0.14399999380111694, 0.07240000367164612, -0.10530000180006027, 0.10700000077486038, -0.007199999876320362, 0.0406000018119812, 0.03739999979734421, -0.12330000102519989, 0.10980000346899033, 0.11089999973773956, 0.022600000724196434, -0.06509999930858612, -0.1501999944448471, 0.0794999971985817, 0.0414000004529953, 0.12460000067949295, 0.004000000189989805, -0.04340000078082085, -0.14990000426769257, -0.0714000016450882, -0.024700000882148743, 0.04479999840259552, 0.1251000016927719, 0.2070000022649765, -0.021700000390410423, 0.059300001710653305, -0.05090000107884407, -0.10589999705553055, 0.061500001698732376, -0.20640000700950623, -0.024000000208616257, -0.0689999982714653, 0.007699999958276749, -0.12219999730587006, -0.024000000208616257, -0.06069999933242798, 0.00559999980032444, -0.05849999934434891, -0.04179999977350235, 0.04690000042319298, -0.09600000083446503, -0.08100000023841858, -0.08399999886751175, 0.07599999755620956, -0.10869999974966049, -0.15479999780654907, -0.035100001841783524, -0.018400000408291817, -0.002099999925121665, 0.09220000356435776, -0.00570000009611249, 0.027000000700354576, 0.0203000009059906, 0.028200000524520874, -0.006099999882280827, -0.08950000256299973, -0.0066999997943639755, -0.07150000333786011, 0.028599999845027924, -0.02280000038444996, -0.05530000105500221, -0.06279999762773514, -0.0142000000923872, -0.09399999678134918, 0.1136000007390976, 0.09399999678134918, 0.11289999634027481, -0.22380000352859497, 0.007199999876320362, -0.024399999529123306, -0.06120000034570694, -0.0731000006198883, -0.03660000115633011, 0.01489999983459711, 0.04740000143647194, -0.004600000102072954, 0.08959999680519104, 0.08219999819993973, -0.04039999842643738, -0.06129999831318855, -0.11540000140666962, 0.11590000241994858, 0.02979999966919422, -0.10440000146627426, 0.0632999986410141, -0.06210000067949295, 0.1704999953508377, 0.06319999694824219, 0.02370000071823597, -0.04749999940395355, -0.1395999938249588, -0.06260000169277191, -0.03929999843239784, 0.16840000450611115, -0.002199999988079071, -0.15299999713897705, 0.04569999873638153, 0.03889999911189079, 0.22689999639987946, -0.08810000121593475, 0.09220000356435776, -0.06300000101327896, 0.09640000015497208, 0.017799999564886093, -0.16899999976158142, -0.0560000017285347, -0.03519999980926514, 0.07769999653100967, -0.00039999998989515007, 0.08299999684095383, -0.0008999999845400453, -0.008899999782443047, 0.09600000083446503, 0.04960000142455101, -0.06310000270605087, 0.06930000334978104, -0.07909999787807465, -0.09099999815225601, 0.07249999791383743, -0.20479999482631683, 0.004399999976158142, 0.010999999940395355, 0.10119999945163727], [-0.1996999979019165, 0.12600000202655792, -0.008500000461935997, 0.020500000566244125, 0.020899999886751175, -0.1160999983549118, 0.08980000019073486, -0.08009999990463257, 0.048700001090765, 0.007400000002235174, -0.006099999882280827, 0.1340000033378601, 0.0284000001847744, -0.08500000089406967, -0.058800000697374344, 0.05909999832510948, -0.05339999869465828, 0.05860000103712082, 0.039000000804662704, 0.05730000138282776, -0.008899999782443047, 0.03310000151395798, 0.024299999698996544, -0.06909999996423721, 0.02800000086426735, -0.03530000150203705, 0.0729999989271164, -0.09520000219345093, -0.0674000009894371, -0.003800000064074993, 0.19099999964237213, -0.004999999888241291, -0.032600000500679016, 0.053700000047683716, 0.012900000438094139, 0.004100000020116568, -0.13950000703334808, -0.012000000104308128, 0.0706000030040741, -0.05050000175833702, -0.06159999966621399, 0.08460000157356262, 0.0007999999797903001, -0.024700000882148743, 0.13930000364780426, -0.027899999171495438, -0.021400000900030136, -0.06849999725818634, -0.11309999972581863, -0.014800000004470348, 0.031199999153614044, 0.026799999177455902, -0.05909999832510948, -0.08330000191926956, 0.15109999477863312, -0.1784999966621399, 0.1265999972820282, 0.02630000002682209, -0.0052999998442828655, 0.061900001019239426, 0.04089999943971634, -0.0017000000225380063, -0.07500000298023224, -0.03750000149011612, -0.10830000042915344, 0.28519999980926514, 0.17990000545978546, -0.2087000012397766, 0.09960000216960907, 0.2054000049829483, -0.15649999678134918, -0.032600000500679016, 0.07670000195503235, 0.030400000512599945, -0.05649999901652336, 0.0625, 0.0044999998062849045, 0.05869999900460243, 0.09529999643564224, -0.07339999824762344, 0.013199999928474426, -0.01489999983459711, 0.052799999713897705, 0.08259999752044678, -0.020999999716877937, 0.1808999925851822, -0.16099999845027924, -0.023800000548362732, -0.18410000205039978, 0.09640000015497208, 0.10520000010728836, 0.09920000284910202, 0.09000000357627869, -0.018300000578165054, -0.016200000420212746, -0.07079999893903732, -0.02630000002682209, -0.1031000018119812, -0.05640000104904175, 0.004900000058114529, 0.010099999606609344, 0.0210999995470047, 0.0982000008225441, 0.04670000076293945, -0.08609999716281891, -0.01730000041425228, -0.03290000185370445, -0.014499999582767487, 0.1315000057220459, -0.00989999994635582, -0.10180000215768814, 0.06390000134706497, -0.08009999990463257, 0.10199999809265137, 0.042399998754262924, -0.0006000000284984708, 0.012299999594688416, -0.053300000727176666, 0.22529999911785126, -0.11949999630451202, -0.01889999955892563, -0.06920000165700912, -0.03550000116229057, 0.15049999952316284, 0.09719999879598618, -0.010400000028312206, -0.0494999997317791, 0.07800000160932541], [-0.08560000360012054, -0.01889999955892563, 0.02250000089406967, 0.11860000342130661, 0.14159999787807465, -0.08269999921321869, -0.094200000166893, -0.065700002014637, -0.030799999833106995, -0.03889999911189079, 0.08009999990463257, 0.050599999725818634, 0.04439999908208847, 0.04089999943971634, 0.05609999969601631, 0.0017999999690800905, -0.06340000033378601, -0.05139999836683273, 0.24500000476837158, 0.0689999982714653, 0.0478999987244606, -0.00800000037997961, -0.10419999808073044, 0.07829999923706055, -0.0406000018119812, 0.0966000035405159, 0.05649999901652336, 0.020099999383091927, 0.0697999969124794, -0.09669999778270721, 0.08259999752044678, -0.006599999964237213, -0.061400000005960464, -0.02280000038444996, -0.020899999886751175, -0.18019999563694, 0.19740000367164612, 0.06800000369548798, 0.02539999969303608, -0.06599999964237213, 0.00019999999494757503, -0.03840000182390213, 0.15729999542236328, 0.07779999822378159, -0.03689999878406525, 0.038100000470876694, -0.009800000116229057, 0.06239999830722809, -0.09570000320672989, 0.052400000393390656, 0.0215000007301569, -0.1282999962568283, -0.06469999998807907, -0.10360000282526016, 0.08889999985694885, -0.25, -0.03709999844431877, -0.09839999675750732, -0.10220000147819519, -0.1136000007390976, 0.02710000053048134, -0.03720000013709068, 0.05380000174045563, -0.125, -0.002400000113993883, 0.11010000109672546, 0.033900000154972076, 0.09449999779462814, 0.000699999975040555, 0.04450000077486038, -0.039799999445676804, -0.12939999997615814, -0.06880000233650208, 0.03959999978542328, -0.010700000450015068, -0.0203000009059906, -0.0044999998062849045, -0.07090000063180923, -0.04439999908208847, 0.029100000858306885, 0.04699999839067459, 0.03689999878406525, 0.16120000183582306, -0.03970000147819519, 0.021199999377131462, -0.13429999351501465, 0.09809999912977219, 0.10029999911785126, 0.12639999389648438, 0.1492999941110611, -0.05119999870657921, 0.07649999856948853, 0.12890000641345978, -0.11230000108480453, 0.06369999796152115, -0.0828000009059906, 0.0877000018954277, -0.19599999487400055, 0.04019999876618385, 0.05090000107884407, 0.06780000030994415, 0.007799999788403511, 0.08389999717473984, -0.012400000356137753, 0.05000000074505806, -0.027400000020861626, -0.01209999993443489, 0.026499999687075615, -0.02419999986886978, -0.05849999934434891, -0.07320000231266022, -0.08479999750852585, -0.03350000083446503, -0.048700001090765, -0.025499999523162842, -0.01979999989271164, -0.041099999099969864, -0.027400000020861626, -0.16760000586509705, 0.060499999672174454, 0.12110000103712082, 0.27309998869895935, 0.025200000032782555, -0.02800000086426735, 0.11089999973773956, 0.13179999589920044, 0.10320000350475311, -0.18170000612735748], [-0.05700000002980232, 0.047600001096725464, 0.07400000095367432, 0.16449999809265137, -0.05999999865889549, 0.06289999932050705, -0.027499999850988388, 0.037300001829862595, -0.018699999898672104, 0.09399999678134918, 0.1315000057220459, 0.007000000216066837, 0.019700000062584877, -0.027000000700354576, 0.0010000000474974513, 0.03929999843239784, 0.027699999511241913, -0.012500000186264515, -0.20280000567436218, -0.05820000171661377, 0.040699999779462814, -0.03530000150203705, 0.1348000019788742, -0.04639999940991402, -0.01679999940097332, 0.06780000030994415, -0.02759999968111515, 0.20110000669956207, -0.06800000369548798, 0.07540000230073929, 0.0551999993622303, -0.061799999326467514, 0.008200000040233135, 0.006800000090152025, 0.013899999670684338, -0.12919999659061432, -0.10639999806880951, 0.11320000141859055, -0.006800000090152025, 0.024399999529123306, -0.04179999977350235, 0.20819999277591705, 0.04179999977350235, 0.08540000021457672, 0.023399999365210533, 0.002300000051036477, 0.048500001430511475, 0.06849999725818634, -0.18449999392032623, -0.022299999371170998, 0.020999999716877937, -0.10019999742507935, 0.018699999898672104, -0.04490000009536743, -0.009399999864399433, -0.0786999985575676, 0.0551999993622303, 0.14869999885559082, 0.1671999990940094, -0.2840999960899353, 0.11209999769926071, -0.17980000376701355, -0.0215000007301569, -0.032600000500679016, -0.0723000019788742, 0.11540000140666962, -0.10440000146627426, 0.14710000157356262, -0.0608999989926815, 0.015799999237060547, 0.04740000143647194, -0.020800000056624413, 0.024700000882148743, -0.00860000029206276, 0.06599999964237213, 0.14980000257492065, -0.12800000607967377, 0.031599998474121094, -0.04230000078678131, 0.045499999076128006, -0.005100000184029341, -0.007000000216066837, -0.09920000284910202, -0.060100000351667404, -0.12250000238418579, -0.017799999564886093, -0.03669999912381172, 0.002400000113993883, -0.19670000672340393, 0.03269999846816063, 0.039400000125169754, -0.0142000000923872, -0.02459999918937683, 0.019999999552965164, -0.006599999964237213, 0.0010000000474974513, 0.002099999925121665, 0.13379999995231628, -0.00139999995008111, 0.0017000000225380063, -0.09929999709129333, -0.10189999639987946, 0.009700000286102295, 0.04619999974966049, -0.027899999171495438, 0.08290000259876251, 0.010599999688565731, -0.09380000084638596, -0.07329999655485153, 0.025200000032782555, 0.013500000350177288, 0.06440000236034393, 0.08720000088214874, -0.18979999423027039, 0.11779999732971191, -0.035999998450279236, 0.05209999904036522, 0.014600000344216824, -0.07980000227689743, 0.17090000212192535, 0.13079999387264252, -0.004399999976158142, -0.2167000025510788, -0.09529999643564224, 0.06909999996423721, 0.1420000046491623, -0.0284000001847744, 0.10440000146627426], [0.07209999859333038, -0.08380000293254852, 0.08330000191926956, -0.02759999968111515, 0.07720000296831131, -0.21289999783039093, 0.093299999833107, 0.022199999541044235, 0.13809999823570251, -0.10109999775886536, 0.11270000040531158, -0.05079999938607216, -0.010499999858438969, -0.0925000011920929, -0.06629999727010727, -0.08980000019073486, 0.15459999442100525, -0.02850000001490116, -0.12759999930858612, -0.053700000047683716, -0.00039999998989515007, 0.04820000007748604, -0.05299999937415123, -0.06440000236034393, -0.020800000056624413, 0.05999999865889549, 0.08489999920129776, -0.038600001484155655, 0.06870000064373016, -0.01850000023841858, 0.010599999688565731, 0.040800001472234726, 0.00800000037997961, 0.024399999529123306, 0.13349999487400055, 0.04100000113248825, 0.042899999767541885, 0.07079999893903732, -0.08780000358819962, 0.1517000049352646, -0.05900000035762787, 0.2825999855995178, 0.039500001817941666, 0.04839999973773956, -0.0284000001847744, 0.006800000090152025, 0.08269999921321869, 0.03400000184774399, -0.09740000218153, -0.11840000003576279, -0.14020000398159027, 0.04690000042319298, 0.10719999670982361, -0.023900000378489494, 0.006399999838322401, -0.02850000001490116, -0.08429999649524689, 0.131400004029274, 0.009499999694526196, -0.01549999974668026, 0.008999999612569809, 0.006899999920278788, -0.08110000193119049, -0.13600000739097595, 0.019200000911951065, 0.10509999841451645, 0.011099999770522118, -0.1340000033378601, -0.15360000729560852, -0.0031999999191612005, 0.08780000358819962, 0.03519999980926514, 0.019700000062584877, -0.09730000048875809, 0.06360000371932983, -0.18029999732971191, -0.062199998646974564, 0.007899999618530273, -0.007300000172108412, 0.04259999841451645, -0.019899999722838402, -0.0632999986410141, 0.03319999948143959, 0.04190000146627426, 0.1216999962925911, 0.0828000009059906, -0.011599999852478504, 0.19509999454021454, 0.16940000653266907, -0.13289999961853027, -0.0421999990940094, 0.10189999639987946, -0.10840000212192535, -0.00839999970048666, 0.04399999976158142, -0.023600000888109207, -0.039900001138448715, 0.02969999983906746, 0.20069999992847443, -0.056299999356269836, 0.07779999822378159, 0.16539999842643738, -0.03610000014305115, -0.08219999819993973, -0.186599999666214, -0.10970000177621841, -0.004900000058114529, -0.07129999995231628, 0.09369999915361404, 0.002400000113993883, -0.01759999990463257, 0.026100000366568565, -0.06710000336170197, 0.07850000262260437, -0.060499999672174454, -0.13449999690055847, -0.1242000013589859, 0.1615000069141388, 0.06589999794960022, 0.10809999704360962, 0.04340000078082085, 0.07599999755620956, -0.04569999873638153, 0.03739999979734421, -0.0869000032544136, 0.010200000368058681, 0.005900000222027302, -0.08340000361204147], [0.025100000202655792, -0.10740000009536743, 0.10029999911785126, -0.09520000219345093, -0.0722000002861023, -0.04320000112056732, 0.025599999353289604, -0.12280000001192093, -0.13169999420642853, 0.05790000036358833, 0.019600000232458115, -0.06920000165700912, 0.07699999958276749, -0.08889999985694885, 0.03999999910593033, 0.041999999433755875, -0.09989999979734421, 0.10480000078678131, 0.02800000086426735, 0.02449999935925007, 0.06589999794960022, 0.21819999814033508, 0.0494999997317791, -0.18379999697208405, -0.002899999963119626, -0.05180000141263008, -0.07159999758005142, 0.04479999840259552, 0.11469999700784683, 0.0031999999191612005, 0.13359999656677246, -0.1251000016927719, -0.0778999999165535, -0.0032999999821186066, -0.010900000110268593, -0.10819999873638153, 0.01899999938905239, 0.01810000091791153, 0.07739999890327454, 0.0544000007212162, -0.04179999977350235, -0.00419999985024333, -0.09669999778270721, -0.12849999964237213, 0.056699998676776886, 0.1436000019311905, -0.10189999639987946, 0.049300000071525574, 0.02800000086426735, 0.08399999886751175, -0.032999999821186066, -0.14790000021457672, -0.23510000109672546, -0.03700000047683716, -0.05270000174641609, 0.016200000420212746, 0.16419999301433563, -0.02810000069439411, 0.10440000146627426, 0.027899999171495438, 0.13220000267028809, -0.04050000011920929, 0.17949999868869781, -0.08160000294446945, 0.11680000275373459, 0.09910000115633011, -0.07800000160932541, -0.032499998807907104, -0.0272000003606081, -0.03359999880194664, 0.06589999794960022, 0.06390000134706497, 0.06949999928474426, 0.09839999675750732, -0.28439998626708984, -0.14910000562667847, -0.1256999969482422, 0.00039999998989515007, -0.13650000095367432, 0.0414000004529953, -0.03840000182390213, 0.004699999932199717, 0.043299999088048935, 0.031300000846385956, -0.004399999976158142, -0.09749999642372131, -0.13500000536441803, 0.05979999899864197, -0.015399999916553497, -0.04100000113248825, -0.17810000479221344, 0.013500000350177288, -0.0544000007212162, 0.0066999997943639755, 0.09889999777078629, 0.0794999971985817, -0.08110000193119049, 0.10899999737739563, -0.021700000390410423, -0.06509999930858612, 0.11999999731779099, -0.03020000085234642, -0.06589999794960022, 0.0031999999191612005, 0.009100000374019146, -0.07729999721050262, 0.03680000081658363, -0.00839999970048666, 0.019099999219179153, 0.05009999871253967, -0.05649999901652336, 0.05169999971985817, 0.13750000298023224, -0.061799999326467514, -0.07689999788999557, -0.12470000237226486, 0.061500001698732376, 0.05730000138282776, -0.03889999911189079, -0.07199999690055847, -0.09030000120401382, 0.032600000500679016, 0.07280000299215317, 0.03189999982714653, 0.04769999906420708, -0.19179999828338623, -0.030700000002980232, -0.016100000590085983], [-0.019200000911951065, 0.04490000009536743, -0.13030000030994415, 0.12070000171661377, -0.07559999823570251, -0.10189999639987946, 0.06560000032186508, 0.03359999880194664, -0.012900000438094139, -0.04500000178813934, -0.17669999599456787, -0.10559999942779541, -0.11309999972581863, 0.019700000062584877, -0.03889999911189079, 0.07559999823570251, 0.1979999989271164, -0.08299999684095383, -0.0949999988079071, -0.2304999977350235, 0.027400000020861626, -0.020800000056624413, -0.07419999688863754, -0.1412999927997589, -0.08229999989271164, -0.0210999995470047, -0.06610000133514404, 0.04619999974966049, -0.025299999862909317, 0.07490000128746033, -0.10729999840259552, -0.06080000102519989, 0.13910000026226044, -0.07150000333786011, -0.030700000002980232, 0.06809999793767929, 0.09059999883174896, 0.06960000097751617, -0.014700000174343586, 0.0697999969124794, 0.027000000700354576, 0.002199999988079071, 0.022199999541044235, 0.013399999588727951, -0.0608999989926815, -0.11190000176429749, -0.16060000658035278, 0.06480000168085098, -0.10170000046491623, -0.05849999934434891, 0.033399999141693115, -0.03269999846816063, -0.06889999657869339, 0.020600000396370888, -0.05700000002980232, -0.019899999722838402, 0.10890000313520432, 0.07259999960660934, -0.01489999983459711, 0.010900000110268593, 0.002300000051036477, 0.13420000672340393, 0.011599999852478504, 0.1387999951839447, 0.1657000035047531, -0.020899999886751175, 0.05469999834895134, -0.03889999911189079, 0.016200000420212746, 0.14429999887943268, 0.07419999688863754, 0.10580000281333923, -0.08590000122785568, -0.005200000014156103, -0.05860000103712082, 0.08399999886751175, -0.15000000596046448, 0.00839999970048666, 0.020400000736117363, -0.057100001722574234, -0.11240000277757645, 0.08060000091791153, 0.15150000154972076, 0.04089999943971634, -0.1395999938249588, -0.08619999885559082, -0.04149999842047691, -0.0722000002861023, 0.08030000329017639, 0.05510000139474869, -0.06800000369548798, -0.06539999693632126, 0.10360000282526016, -0.059300001710653305, 0.02199999988079071, -0.08950000256299973, -0.06849999725818634, -0.07349999994039536, -0.006800000090152025, 0.04360000044107437, 0.0406000018119812, 0.02669999934732914, 0.10530000180006027, -0.1446000039577484, 0.20170000195503235, 0.007499999832361937, 0.15379999577999115, 0.12839999794960022, 0.09539999812841415, 0.041200000792741776, -0.09229999780654907, 0.052299998700618744, -0.007699999958276749, -0.02850000001490116, 0.05730000138282776, 0.053700000047683716, -0.11259999871253967, 0.09690000116825104, 0.14239999651908875, 0.17560000717639923, 0.046799998730421066, -0.02160000056028366, 0.019999999552965164, 0.008500000461935997, 0.24150000512599945, -0.06350000202655792, 0.07240000367164612, -0.024299999698996544], [0.01140000019222498, -0.029999999329447746, 0.039900001138448715, -0.11479999870061874, -0.02019999921321869, 0.020500000566244125, 0.07930000126361847, 0.10189999639987946, -0.08250000327825546, 0.003700000001117587, 0.05350000038743019, 0.037300001829862595, 0.08980000019073486, 0.11869999766349792, -0.00039999998989515007, 0.13770000636577606, 0.1835000067949295, -0.09889999777078629, -0.07840000092983246, 0.13580000400543213, 0.04129999876022339, -0.0142000000923872, 0.14810000360012054, 0.21320000290870667, 0.04349999874830246, 0.07429999858140945, -0.13809999823570251, -0.041099999099969864, -0.08749999850988388, -0.11330000311136246, 0.02800000086426735, 0.09390000253915787, 0.04619999974966049, -0.13420000672340393, 0.021800000220537186, -0.10740000009536743, 0.04500000178813934, -0.18559999763965607, 0.011800000444054604, 0.1379999965429306, -0.05939999967813492, 0.03909999877214432, 0.034699998795986176, -0.12120000272989273, 0.05920000001788139, -0.02419999986886978, 0.020800000056624413, -0.023900000378489494, 0.14949999749660492, 0.18449999392032623, -0.021700000390410423, -0.03269999846816063, -0.017400000244379044, 0.010599999688565731, -0.06629999727010727, -0.14749999344348907, -0.02889999933540821, 0.09889999777078629, 0.11180000007152557, 0.04259999841451645, -0.1371999979019165, -0.05990000069141388, 0.05990000069141388, -0.03660000115633011, -0.08320000022649765, 0.009600000455975533, 0.12300000339746475, 0.10869999974966049, -0.003599999938160181, 0.05040000006556511, -0.10450000315904617, 0.03700000047683716, 0.020500000566244125, -0.0877000018954277, 0.02199999988079071, -0.06729999929666519, -0.19830000400543213, 0.03539999946951866, 0.057500001043081284, -0.12139999866485596, 0.07440000027418137, 0.06849999725818634, 0.1624000072479248, -0.14159999787807465, 0.1307000070810318, 0.016100000590085983, -0.05660000070929527, -0.009800000116229057, -0.019999999552965164, -0.10369999706745148, -0.16949999332427979, -0.003100000089034438, 0.019700000062584877, -0.16459999978542328, -0.09749999642372131, -0.09369999915361404, -0.009399999864399433, 0.020800000056624413, -0.0714000016450882, 0.08429999649524689, -0.020600000396370888, 0.04769999906420708, 0.1054999977350235, 0.01059999968856573</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>[[[-0.015300000086426735, -0.08420000225305557, 0.002300000051036477, 0.03840000182390213, 0.04969999939203262, -0.07280000299215317, 0.03750000149011612, 0.0722000002861023, -0.016699999570846558, 0.025499999523162842, -0.06759999692440033, -0.01769999973475933, 0.04989999905228615, 0.11860000342130661, -0.061000000685453415, -0.009200000204145908, 0.010599999688565731, 0.048700001090765, 0.03530000150203705, 0.03840000182390213, -0.05339999869465828, -0.043800000101327896, -0.0885000005364418, 0.07689999788999557, 0.07339999824762344, -0.0917000025510788, 0.056699998676776886, -0.05810000002384186, 0.14219999313354492, 0.008799999952316284, -0.04729999974370003, -0.01640000008046627, -0.014600000344216824, 0.0215000007301569, 0.02969999983906746, -0.04010000079870224, 0.0215000007301569, 0.04280000180006027, -0.09549999982118607, -0.043800000101327896, 0.06390000134706497, -0.06419999897480011, -0.08789999783039093, -0.06319999694824219, 0.00839999970048666, -0.05550000071525574, 0.03579999879002571, -0.053700000047683716, -0.09369999915361404, 0.052299998700618744, 0.003100000089034438, 0.09359999746084213, 0.011800000444054604, 0.001500000013038516, 0.08590000122785568, 0.05139999836683273, -0.020600000396370888, -0.08749999850988388, 0.007199999876320362, 0.09700000286102295, -0.06499999761581421, 0.06109999865293503, 0.038600001484155655, -0.05999999865889549, -0.13979999721050262, -0.045499999076128006, -0.09040000289678574, -0.017799999564886093, 0.030300000682473183, -0.05050000175833702, 0.09870000183582306, -0.0340999998152256, -0.03750000149011612, 0.05490000173449516, 0.013100000098347664, -0.02669999934732914, -0.0544000007212162, -0.01860000006854534, -0.029899999499320984, 0.00800000037997961, 0.015399999916553497, 0.06620000302791595, 0.06210000067949295, 0.08160000294446945, 0.06780000030994415, -0.07900000363588333, 0.0333000011742115, -9.999999747378752e-05, -0.06419999897480011, -0.053599998354911804, 0.017999999225139618, -0.060499999672174454, 0.04129999876022339, -0.020600000396370888, 0.12449999898672104, -0.01889999955892563, 0.10779999941587448, 0.04280000180006027, -0.031700000166893005, -0.02329999953508377, 0.0357000008225441, 0.07289999723434448, 0.037700001150369644, 0.029200000688433647, 0.004000000189989805, 0.009600000455975533, -0.025100000202655792, 0.0478999987244606, 0.0031999999191612005, 0.01640000008046627, -0.06069999933242798, -0.048900000751018524, 0.03519999980926514, -0.04100000113248825, 0.019899999722838402, 0.013399999588727951, -0.07750000059604645, -0.041099999099969864, 0.0771000012755394, 0.07069999724626541, -0.06560000032186508, 0.10920000076293945, -0.03530000150203705, -0.028699999675154686, 0.01510000042617321, -0.08709999918937683, -0.022600000724196434, -0.0003000000142492354], [0.07190000265836716, 0.06629999727010727, 0.019500000402331352, -0.031700000166893005, -0.06469999998807907, -0.0031999999191612005, -0.04360000044107437, -0.05689999833703041, 0.021900000050663948, -0.03750000149011612, 0.05770000070333481, 0.023000000044703484, -0.032600000500679016, -0.11900000274181366, 0.054499998688697815, -0.002300000051036477, -0.013399999588727951, -0.062300000339746475, -0.022700000554323196, -0.026100000366568565, 0.049300000071525574, 0.03290000185370445, 0.08789999783039093, -0.06679999828338623, -0.06449999660253525, 0.10279999673366547, -0.05420000106096268, 0.024900000542402267, -0.029999999329447746, -0.033399999141693115, 0.03920000046491623, -0.00800000037997961, -0.003100000089034438, -0.022099999710917473, -0.045899998396635056, 0.010400000028312206, -0.029999999329447746, -0.04520000144839287, 0.09759999811649323, 0.07129999995231628, -0.062199998646974564, 0.05939999967813492, 0.0763000026345253, 0.05810000002384186, -0.015200000256299973, 0.06509999930858612, -0.06669999659061432, 0.03920000046491623, 0.03290000185370445, -0.058400001376867294, -0.005900000222027302, -0.021199999377131462, -0.005799999926239252, -0.061400000005960464, -0.09449999779462814, -0.0957999974489212, 0.035100001841783524, 0.08320000022649765, 0.051500000059604645, -0.09449999779462814, 0.11110000312328339, -0.0568000003695488, -0.05090000107884407, 0.07890000194311142, 0.14970000088214874, 0.03720000013709068, 0.055399999022483826, 0.026200000196695328, -0.015399999916553497, 0.04470000043511391, -0.09139999747276306, 0.011800000444054604, -0.01759999990463257, -0.07999999821186066, 0.045099999755620956, 0.03799999877810478, 0.05119999870657921, 0.02669999934732914, 0.04769999906420708, 0.019700000062584877, -0.019899999722838402, -0.02449999935925007, -0.06809999793767929, -0.07580000162124634, -0.030799999833106995, 0.10040000081062317, -0.03480000048875809, -0.030799999833106995, 0.02449999935925007, 0.05939999967813492, -0.00019999999494757503, 0.06270000338554382, -0.03310000151395798, -0.028200000524520874, -0.08869999647140503, 0.016899999231100082, -0.11050000041723251, -0.03700000047683716, 0.05130000039935112, 0.056299999356269836, -0.020600000396370888, -0.04470000043511391, -0.03689999878406525, -0.016300000250339508, 0.01549999974668026, -0.02630000002682209, 0.04470000043511391, -0.055399999022483826, -0.024800000712275505, -0.009600000455975533, 0.06800000369548798, 0.07460000365972519, -0.04580000042915344, 0.029200000688433647, -0.01679999940097332, -0.01209999993443489, 0.06199999898672104, 0.029400000348687172, -0.08969999849796295, -0.08389999717473984, 0.10440000146627426, -0.11680000275373459, 0.007199999876320362, 0.021800000220537186, -0.02669999934732914, 0.0746999979019165, 0.017999999225139618, -0.042899999767541885]], [[-0.23309999704360962, 0.005499999970197678, -0.035599999129772186, -0.03150000050663948, -0.08240000158548355, 0.14350000023841858, 0.0843999981880188, 0.038600001484155655, -0.017400000244379044, 0.012000000104308128, 0.16779999434947968, 0.025100000202655792, -0.14350000023841858, 0.055399999022483826, 0.08129999786615372, -0.08250000327825546, 0.10419999808073044, -0.03880000114440918, -0.006599999964237213, 0.11999999731779099, -0.11020000278949738, -0.07349999994039536, -0.03530000150203705, -0.09019999951124191, -0.057100001722574234, 0.02879999950528145, -0.133200004696846, -0.023499999195337296, -0.12330000102519989, 0.09359999746084213, 0.014299999922513962, 0.05530000105500221, 0.01269999984651804, -0.012500000186264515, -0.22010000050067902, -0.05469999834895134, 0.12120000272989273, -0.09629999846220016, 0.08910000324249268, 0.025299999862909317, 0.05979999899864197, 0.012600000016391277, -0.02539999969303608, 0.013100000098347664, -0.04839999973773956, 0.04360000044107437, -0.06369999796152115, 0.14589999616146088, 0.09619999676942825, 0.10949999839067459, -0.14399999380111694, -0.026100000366568565, -0.07289999723434448, 0.2522999942302704, -0.0625, 0.13819999992847443, -0.0502999983727932, -0.1762000024318695, -0.16269999742507935, -0.09380000084638596, 0.14880000054836273, -0.10779999941587448, -0.06430000066757202, 0.08030000329017639, 0.10530000180006027, -0.0034000000450760126, 0.0034000000450760126, 0.18529999256134033, -0.019999999552965164, 0.05790000036358833, 0.059300001710653305, -0.04569999873638153, 0.07349999994039536, -0.11999999731779099, 0.11029999703168869, 0.093299999833107, -0.10530000180006027, 0.06769999861717224, -0.03959999978542328, -0.02979999966919422, -0.05389999970793724, -0.09080000221729279, -0.12729999423027039, 0.14489999413490295, -0.0908999964594841, 0.006099999882280827, -0.16519999504089355, 0.005900000222027302, 0.10559999942779541, -0.030700000002980232, -0.003000000026077032, 0.034299999475479126, -0.06449999660253525, 0.08030000329017639, 0.060100000351667404, -0.08380000293254852, -0.04670000076293945, -0.0031999999191612005, 0.04820000007748604, -0.0364999994635582, 0.028599999845027924, 0.07599999755620956, -0.010200000368058681, -0.12380000203847885, -0.1395999938249588, 0.04019999876618385, -0.03319999948143959, 0.048500001430511475, 0.17829999327659607, -0.062300000339746475, -0.026799999177455902, -0.006000000052154064, -0.02630000002682209, 0.17399999499320984, 0.030899999663233757, -0.06589999794960022, 0.06560000032186508, 0.05860000103712082, -0.07440000027418137, -0.1889999955892563, 0.00430000014603138, -0.029200000688433647, -0.07980000227689743, 0.11620000004768372, 0.08320000022649765, 0.009399999864399433, -0.2574000060558319, -0.05380000174045563], [-0.005499999970197678, -0.013100000098347664, -0.10809999704360962, -0.014600000344216824, 0.11150000244379044, 0.21490000188350677, 0.10700000077486038, 0.15489999949932098, 0.02810000069439411, 0.06939999759197235, -0.03920000046491623, 0.012799999676644802, -0.09589999914169312, 0.00989999994635582, 0.010099999606609344, 0.06080000102519989, 0.12039999663829803, 0.03020000085234642, -0.05739999935030937, 0.1080000028014183, -0.15780000388622284, 0.0031999999191612005, 0.04580000042915344, -0.09390000253915787, 0.053700000047683716, 0.00930000003427267, 0.04259999841451645, -0.04019999876618385, -0.006599999964237213, -0.02290000021457672, 0.08739999681711197, -0.07329999655485153, 0.14149999618530273, -0.07620000094175339, -0.21289999783039093, 0.10760000348091125, -0.10130000114440918, 0.0006000000284984708, 0.06849999725818634, 0.02449999935925007, -0.07450000196695328, 0.17720000445842743, -0.131400004029274, 0.13689999282360077, 0.14990000426769257, 0.07460000365972519, -0.2329999953508377, 0.013000000268220901, 0.05909999832510948, 0.13979999721050262, 0.1256999969482422, -0.1185000017285347, -0.0203000009059906, 0.18299999833106995, -0.12700000405311584, -0.10220000147819519, -0.10239999741315842, -0.06480000168085098, 0.02800000086426735, 0.023399999365210533, 0.011300000362098217, -0.08640000224113464, -0.0731000006198883, 0.12280000001192093, 0.03229999914765358, 0.02160000056028366, 0.04619999974966049, -0.14309999346733093, -0.07190000265836716, 0.08500000089406967, 0.008899999782443047, -0.07739999890327454, 0.16920000314712524, -0.026900000870227814, -0.07500000298023224, -0.07760000228881836, -0.06790000200271606, -0.10260000079870224, 0.009200000204145908, -0.11469999700784683, -0.020899999886751175, -0.02500000037252903, 0.10480000078678131, -0.07670000195503235, 0.1005999967455864, 0.03150000050663948, 0.13420000672340393, 0.08879999816417694, 0.03750000149011612, -0.005900000222027302, 0.07930000126361847, -0.013399999588727951, -0.020400000736117363, 0.06960000097751617, 0.05649999901652336, 0.020500000566244125, -0.037300001829862595, 0.13109999895095825, 0.18379999697208405, 0.25929999351501465, 0.02759999968111515, -0.048900000751018524, -0.1274999976158142, -0.1590999960899353, 0.0502999983727932, -0.06469999998807907, -0.09139999747276306, 0.049400001764297485, -0.20499999821186066, -0.029200000688433647, -0.01080000028014183, -0.09889999777078629, -0.022199999541044235, -0.006000000052154064, -0.0015999999595806003, 0.14010000228881836, 0.03720000013709068, 0.09989999979734421, 0.061799999326467514, -0.004100000020116568, 0.15379999577999115, 0.1995999962091446, -0.08919999748468399, 0.02370000071823597, -0.048900000751018524, 0.033900000154972076, -0.07090000063180923, 0.09809999912977219], [0.0020000000949949026, -0.14169999957084656, -0.28679999709129333, -0.1615000069141388, -0.012199999764561653, 0.22689999639987946, 0.1395999938249588, -0.06870000064373016, 0.08100000023841858, 0.031599998474121094, 0.05649999901652336, 0.021299999207258224, -0.13269999623298645, 0.12200000137090683, 0.10300000011920929, 0.004000000189989805, -0.04309999942779541, -0.10249999910593033, 0.11710000038146973, 0.12099999934434891, 0.0640999972820282, -0.004699999932199717, -0.011800000444054604, -0.2167000025510788, -0.07729999721050262, -0.019500000402331352, 0.027499999850988388, 0.20469999313354492, 0.16529999673366547, -0.0024999999441206455, 0.019300000742077827, -0.093299999833107, -0.023900000378489494, 0.03269999846816063, -0.14579999446868896, -0.03759999945759773, -0.04089999943971634, 0.04149999842047691, -0.14030000567436218, 0.025499999523162842, -0.005900000222027302, 0.029200000688433647, -0.05310000106692314, 0.0544000007212162, -0.002899999963119626, -0.03269999846816063, -0.1306000053882599, -0.0917000025510788, 0.15539999306201935, -0.05290000140666962, -0.1371999979019165, 0.02630000002682209, -0.034699998795986176, 0.06639999896287918, 0.07980000227689743, 0.017500000074505806, 0.04960000142455101, -0.02590000070631504, -0.007199999876320362, -0.08410000056028366, -0.07460000365972519, -0.0746999979019165, -0.08259999752044678, 0.06350000202655792, -0.025699999183416367, -0.05959999933838844, -0.07119999825954437, -0.029100000858306885, -0.08449999988079071, 0.15389999747276306, 0.053599998354911804, 0.13660000264644623, -0.21379999816417694, -0.07150000333786011, -0.010599999688565731, -0.08299999684095383, -0.15330000221729279, -0.051100000739097595, -0.014800000004470348, 0.07100000232458115, -0.06030000001192093, 0.06669999659061432, 0.050999999046325684, -0.05400000140070915, -0.1054999977350235, -0.1136000007390976, 0.01850000023841858, 0.058400001376867294, -0.019200000911951065, 0.04780000075697899, -0.12549999356269836, 0.219200000166893, 0.13379999995231628, 0.04749999940395355, -0.019500000402331352, -0.09849999845027924, -0.059300001710653305, 0.028200000524520874, 0.17749999463558197, -0.02850000001490116, -0.20909999310970306, -0.0348999984562397, -0.04960000142455101, 0.1868000030517578, -0.04129999876022339, 0.04580000042915344, -0.08959999680519104, 0.03009999915957451, 0.11159999668598175, -0.2484000027179718, -0.12189999967813492, -0.052400000393390656, 0.1225999966263771, 0.009399999864399433, 0.06159999966621399, 0.01600000075995922, 0.05480000004172325, 0.1388999968767166, 0.08269999921321869, -0.13899999856948853, 0.10649999976158142, -0.1500999927520752, -0.07909999787807465, 0.1454000025987625, -0.14659999310970306, 0.019099999219179153, 0.055799998342990875, 0.14339999854564667], [-0.2662999927997589, 0.08070000261068344, -0.06650000065565109, -0.02459999918937683, -0.01769999973475933, -0.04179999977350235, 0.15119999647140503, -0.0284000001847744, 0.061500001698732376, -0.016200000420212746, 0.04610000178217888, 0.13189999759197235, 0.01679999940097332, -0.09239999949932098, -0.04309999942779541, 0.08500000089406967, -0.002400000113993883, 0.08429999649524689, 0.08049999922513962, 0.10809999704360962, -0.04899999871850014, 0.006399999838322401, 0.04089999943971634, -0.07769999653100967, 0.054499998688697815, -0.01810000091791153, 0.08980000019073486, -0.042100001126527786, -0.09489999711513519, 0.031700000166893005, 0.18330000340938568, -0.032999999821186066, 0.01860000006854534, 0.028200000524520874, 0.0471000000834465, -0.013399999588727951, -0.10859999805688858, 0.014399999752640724, 0.012299999594688416, -0.030300000682473183, -0.010400000028312206, 0.12219999730587006, -0.01810000091791153, -0.014399999752640724, 0.12229999899864197, -0.010599999688565731, -0.05719999969005585, -0.1054999977350235, -0.05649999901652336, 0.029200000688433647, 0.05889999866485596, 0.06340000033378601, -0.10010000318288803, 0.006200000178068876, 0.10949999839067459, -0.10859999805688858, 0.0828000009059906, -0.04390000179409981, -0.04100000113248825, 0.06270000338554382, -0.0012000000569969416, -0.03020000085234642, -0.1039000004529953, -0.014499999582767487, -0.09880000352859497, 0.25600001215934753, 0.17579999566078186, -0.2280000001192093, 0.037700001150369644, 0.23190000653266907, -0.18479999899864197, -0.09809999912977219, 0.10509999841451645, -0.02019999921321869, -0.042899999767541885, 0.03579999879002571, -0.05139999836683273, 0.03579999879002571, 0.1412999927997589, -0.048700001090765, 0.04439999908208847, -0.07540000230073929, 0.024900000542402267, 0.12189999967813492, -0.06369999796152115, 0.195700004696846, -0.17229999601840973, 0.024000000208616257, -0.1128000020980835, 0.06800000369548798, 0.12129999697208405, 0.05979999899864197, 0.1379999965429306, 0.0284000001847744, 0.013299999758601189, -0.0746999979019165, -0.05339999869465828, -0.051100000739097595, -0.048700001090765, -0.03750000149011612, 0.013199999928474426, -0.017899999395012856, 0.0737999975681305, 0.01730000041425228, -0.013899999670684338, -0.055399999022483826, -0.07519999891519547, -0.07159999758005142, 0.20739999413490295, -0.05290000140666962, -0.1257999986410141, 0.05350000038743019, -0.0215000007301569, 0.09430000185966492, 0.01979999989271164, 0.025800000876188278, 0.029899999499320984, -0.016300000250339508, 0.2662000060081482, -0.14489999413490295, -0.0010999999940395355, -0.06030000001192093, -0.07370000332593918, 0.21209999918937683, 0.10779999941587448, 0.01640000008046627, -0.01720000058412552, 0.12610000371932983], [-0.13169999420642853, -0.05220000073313713, -0.03620000183582306, 0.08529999852180481, 0.04569999873638153, 0.04580000042915344, -0.03889999911189079, 0.028599999845027924, 0.022299999371170998, -0.06279999762773514, 0.16979999840259552, 0.02759999968111515, 0.039900001138448715, -0.003100000089034438, 0.09019999951124191, -0.07440000027418137, -0.05000000074505806, -0.0494999997317791, 0.3310999870300293, 0.13529999554157257, -0.0007999999797903001, -0.025800000876188278, -0.054999999701976776, 0.07010000199079514, -0.018400000408291817, 0.15629999339580536, 0.1662999987602234, 0.07349999994039536, 0.03680000081658363, -0.06199999898672104, 0.009700000286102295, -0.006800000090152025, -0.09920000284910202, -0.04919999837875366, 0.043299999088048935, -0.22020000219345093, 0.24899999797344208, 0.08089999854564667, -0.02199999988079071, -0.022700000554323196, 0.10899999737739563, 0.02879999950528145, 0.12919999659061432, -0.026200000196695328, -0.09929999709129333, 0.04390000179409981, -0.09040000289678574, 0.054099999368190765, -0.032600000500679016, 0.05130000039935112, 0.08730000257492065, -0.0737999975681305, -0.13079999387264252, -0.09049999713897705, -0.010599999688565731, -0.21899999678134918, -0.08950000256299973, -0.18140000104904175, -0.13279999792575836, -0.11779999732971191, -0.03530000150203705, -0.07169999927282333, -0.03999999910593033, -0.07980000227689743, -0.0210999995470047, 0.06199999898672104, 0.09040000289678574, 0.06030000001192093, -0.05000000074505806, 0.07750000059604645, -0.07199999690055847, -0.09149999916553497, -0.05299999937415123, -0.03460000082850456, 0.017100000753998756, -0.0551999993622303, -0.03830000013113022, -0.03500000014901161, -0.01510000042617321, 0.10499999672174454, 0.1362999975681305, 0.00800000037997961, 0.10999999940395355, 0.060100000351667404, -0.06449999660253525, -0.08340000361204147, 0.06159999966621399, 0.17030000686645508, 0.03200000151991844, 0.10670000314712524, 0.01769999973475933, 0.0406000018119812, 0.19300000369548798, -0.0738999992609024, 0.10010000318288803, -0.14910000562667847, 0.06109999865293503, -0.2071000039577484, 0.02449999935925007, -0.0038999998942017555, 0.1932000070810318, -0.00930000003427267, 0.020600000396370888, -0.04919999837875366, 0.13609999418258667, -0.07779999822378159, -0.010499999858438969, -0.03460000082850456, 0.08190000057220459, 0.024900000542402267, -0.002400000113993883, -0.0934000015258789, 0.031300000846385956, -0.0502999983727932, -0.02500000037252903, -0.04270000010728836, -0.04490000009536743, -0.009800000116229057, -0.12309999763965607, 0.05169999971985817, 0.12300000339746475, 0.2865000069141388, 0.06199999898672104, 0.03150000050663948, 0.01360000018030405, 0.17829999327659607, 0.16599999368190765, -0.19300000369548798], [0.00430000014603138, 0.06449999660253525, 0.13040000200271606, 0.1987999975681305, -0.04960000142455101, -0.03849999979138374, -0.0851999968290329, 0.028699999675154686, 0.00570000009611249, 0.05460000038146973, 0.10090000182390213, 0.01899999938905239, 0.010999999940395355, -0.041200000792741776, 0.02280000038444996, 0.07970000058412552, 0.028200000524520874, -0.005799999926239252, -0.21289999783039093, -0.10499999672174454, 0.05180000141263008, -0.03229999914765358, 0.11829999834299088, 0.005499999970197678, -0.011500000022351742, 0.054999999701976776, -0.005900000222027302, 0.14560000598430634, -0.0544000007212162, 0.0617000013589859, 0.10660000145435333, -0.06809999793767929, -0.06030000001192093, 0.024800000712275505, -0.04740000143647194, -0.1266999989748001, -0.12960000336170197, 0.1160999983549118, 0.029600000008940697, -0.024000000208616257, -0.0786999985575676, 0.17739999294281006, 0.035100001841783524, 0.03709999844431877, 0.07540000230073929, -0.007600000128149986, 0.07689999788999557, 0.06369999796152115, -0.25429999828338623, -0.044599998742341995, 0.002300000051036477, -0.13779999315738678, 0.04450000077486038, -0.1315000057220459, 0.028699999675154686, -0.12409999966621399, 0.027899999171495438, 0.15559999644756317, 0.1776999980211258, -0.24609999358654022, 0.07989999651908875, -0.1185000017285347, -0.008100000210106373, -0.07850000262260437, -0.09189999848604202, 0.11800000071525574, -0.10660000145435333, 0.15360000729560852, -0.07150000333786011, -0.026200000196695328, 0.09239999949932098, -9.999999747378752e-05, 0.02070000022649765, 0.04830000177025795, 0.05909999832510948, 0.16349999606609344, -0.09070000052452087, 0.027400000020861626, -0.07100000232458115, 0.03220000118017197, 0.0284000001847744, 0.026599999517202377, -0.07569999992847443, -0.06030000001192093, -0.08550000190734863, -0.024299999698996544, 0.02199999988079071, -0.02290000021457672, -0.2766999900341034, 0.04600000008940697, 0.07109999656677246, -0.02070000022649765, -0.06069999933242798, -0.037700001150369644, -0.03779999911785126, -0.0284000001847744, 0.021700000390410423, 0.09139999747276306, 0.002899999963119626, 0.027699999511241913, -0.051500000059604645, -0.05139999836683273, 0.0689999982714653, 0.05570000037550926, -0.05790000036358833, 0.08799999952316284, 0.014700000174343586, 0.011900000274181366, -0.1412999927997589, 0.06599999964237213, 0.04569999873638153, 0.0722000002861023, 0.03220000118017197, -0.20679999887943268, 0.12030000239610672, -0.028599999845027924, 0.020600000396370888, -0.012900000438094139, -0.11100000143051147, 0.22769999504089355, 0.12449999898672104, 0.0340999998152256, -0.20160000026226044, -0.14409999549388885, 0.03779999911785126, 0.1193000003695488, -0.05590000003576279, 0.029200000688433647], [0.10189999639987946, -0.0544000007212162, 0.14180000126361847, 0.050700001418590546, 0.10440000146627426, -0.3208000063896179, 0.032600000500679016, 0.009200000204145908, 0.1388999968767166, -0.07370000332593918, 0.11640000343322754, -0.07829999923706055, 0.026599999517202377, -0.08659999817609787, -0.15289999544620514, -0.17550000548362732, 0.10639999806880951, -0.03290000185370445, -0.14339999854564667, -0.0414000004529953, 0.026000000536441803, 0.06849999725818634, -0.07519999891519547, -0.01140000019222498, -0.033900000154972076, 0.10530000180006027, 0.11509999632835388, -0.0940999984741211, 0.10689999908208847, -0.03610000014305115, -0.014800000004470348, 0.07569999992847443, -0.0746999979019165, 0.05310000106692314, 0.10360000282526016, 0.04410000145435333, 0.004800000227987766, 0.043800000101327896, -0.06239999830722809, 0.10400000214576721, -0.045899998396635056, 0.260699987411499, 0.022199999541044235, -0.011900000274181366, -0.05869999900460243, -0.05559999868273735, 0.10930000245571136, 0.07199999690055847, -0.12110000103712082, -0.1745000034570694, -0.16940000653266907, 0.023099999874830246, 0.13220000267028809, -0.1136000007390976, 0.04540000110864639, -0.09350000321865082, -0.03449999913573265, 0.1445000022649765, 0.021299999207258224, 0.04340000078082085, 0.01640000008046627, 0.07680000364780426, -0.05700000002980232, -0.16910000145435333, -0.02500000037252903, 0.12070000171661377, 0.0917000025510788, -0.1145000010728836, -0.1282999962568283, -0.06689999997615814, 0.14239999651908875, 0.11069999635219574, -0.006000000052154064, -0.05920000001788139, 0.025699999183416367, -0.1670999974012375, 0.00559999980032444, 0.03720000013709068, -0.035999998450279236, 0.04320000112056732, 0.029999999329447746, -0.000699999975040555, 0.08209999650716782, 0.048500001430511475, 0.14300000667572021, 0.04430000111460686, 0.011500000022351742, 0.18000000715255737, 0.07000000029802322, -0.12479999661445618, -0.02669999934732914, 0.07270000129938126, -0.14069999754428864, -0.05689999833703041, 0.09300000220537186, 0.01860000006854534, 0.01850000023841858, -0.027799999341368675, 0.16040000319480896, -0.03189999982714653, 0.10409999638795853, 0.22290000319480896, -0.008299999870359898, -0.046300001442432404, -0.20090000331401825, -0.0828000009059906, 0.0608999989926815, -0.0024999999441206455, 0.030400000512599945, 0.06989999860525131, 0.016699999570846558, 0.032499998807907104, -0.11620000004768372, 0.08969999849796295, -0.014100000262260437, -0.1762000024318695, -0.1923999935388565, 0.08609999716281891, 0.05310000106692314, 0.18209999799728394, -0.0066999997943639755, 0.10610000044107437, 0.056299999356269836, -0.029500000178813934, -0.10729999840259552, -0.03240000084042549, -0.019200000911951065, -0.19609999656677246], [0.08299999684095383, -0.043299999088048935, 0.19099999964237213, -0.033799998462200165, -0.11110000312328339, -0.07940000295639038, 0.009100000374019146, -0.18050000071525574, -0.10220000147819519, 0.026799999177455902, 0.06390000134706497, -0.05779999867081642, 0.09539999812841415, -0.12250000238418579, 0.03319999948143959, 0.03400000184774399, -0.15139999985694885, 0.06260000169277191, 0.004900000058114529, -0.03610000014305115, 0.10490000247955322, 0.22439999878406525, 0.031300000846385956, -0.09300000220537186, -0.005100000184029341, 0.000699999975040555, -0.045899998396635056, -0.024000000208616257, 0.14010000228881836, -0.006399999838322401, 0.18129999935626984, -0.03669999912381172, -0.19210000336170197, 0.013899999670684338, -0.0729999989271164, -0.08789999783039093, 0.014700000174343586, -0.0494999997317791, 0.07069999724626541, -0.025299999862909317, -0.09019999951124191, -0.01269999984651804, -0.09539999812841415, -0.1981000006198883, 0.03280000016093254, 0.07540000230073929, -0.08070000261068344, 0.08179999887943268, 0.027699999511241913, -0.0015999999595806003, -0.04100000113248825, -0.1859000027179718, -0.22990000247955322, -0.09650000184774399, -0.07280000299215317, -0.04349999874830246, 0.13899999856948853, 0.007199999876320362, 0.13570000231266022, 0.08070000261068344, 0.11919999867677689, 0.03920000046491623, 0.12929999828338623, -0.10409999638795853, 0.09449999779462814, 0.10239999741315842, -0.015200000256299973, 0.012500000186264515, -0.030700000002980232, -0.07209999859333038, 0.11640000343322754, 0.09709999710321426, 0.06030000001192093, 0.11540000140666962, -0.32600000500679016, -0.13439999520778656, -0.04989999905228615, 0.05590000003576279, -0.18960000574588776, 0.05339999869465828, 0.035100001841783524, 0.11309999972581863, 0.05480000004172325, 0.05559999868273735, -0.025200000032782555, -0.10239999741315842, -0.09179999679327011, 0.06610000133514404, -0.06859999895095825, -0.04309999942779541, -0.133200004696846, -0.027899999171495438, -0.1062999963760376, 0.013700000010430813, 0.1225999966263771, 0.04100000113248825, -0.07639999687671661, 0.03480000048875809, -0.040800001472234726, -0.033900000154972076, 0.1664000004529953, 0.06700000166893005, 0.023399999365210533, 0.033399999141693115, -0.02319999970495701, -0.052799999713897705, 0.07639999687671661, 0.07490000128746033, -0.04529999941587448, 0.11550000309944153, 0.03579999879002571, 0.005200000014156103, 0.13210000097751617, -0.041099999099969864, -0.01510000042617321, -0.15549999475479126, 0.010999999940395355, 0.00800000037997961, -0.07069999724626541, -0.00559999980032444, -0.11879999935626984, 0.08290000259876251, 0.10029999911785126, -0.03970000147819519, -0.03269999846816063, -0.20509999990463257, -0.05939999967813492, -0.05689999833703041], [0.010599999688565731, 0.07419999688863754, -0.09019999951124191, 0.1298000067472458, -0.030400000512599945, -0.19439999759197235, 0.04190000146627426, -0.011900000274181366, -0.0019000000320374966, -0.06469999998807907, -0.2272000014781952, -0.0649000033736229, -0.09619999676942825, 0.04859999939799309, -0.029400000348687172, 0.18240000307559967, 0.14630000293254852, -0.048500001430511475, -0.13259999454021454, -0.2574000060558319, 0.04390000179409981, -0.018400000408291817, -0.10790000110864639, -0.08470000326633453, -0.11240000277757645, -0.027499999850988388, -0.10490000247955322, 0.01940000057220459, -0.005499999970197678, 0.05220000073313713, -0.00839999970048666, -0.03759999945759773, 0.1680999994277954, -0.018200000748038292, -0.08259999752044678, 0.15029999613761902, 0.060600001364946365, 0.04129999876022339, 0.027400000020861626, 0.03550000116229057, -0.04580000042915344, -0.032499998807907104, 0.04749999940395355, 0.03849999979138374, -0.04619999974966049, -0.13089999556541443, -0.12359999865293503, 0.07500000298023224, -0.11339999735355377, -0.06840000301599503, -0.0421999990940094, -0.07360000163316727, -0.030899999663233757, 0.06539999693632126, -0.024700000882148743, -0.04439999908208847, 0.13279999792575836, 0.11379999667406082, 0.017799999564886093, 0.05270000174641609, 0.023099999874830246, 0.15600000321865082, -0.04879999905824661, 0.12359999865293503, 0.17249999940395355, 0.07620000094175339, 0.04479999840259552, 0.028599999845027924, 0.027300000190734863, 0.12489999830722809, 0.09309999644756317, 0.11810000240802765, -0.08160000294446945, 0.032499998807907104, -0.09059999883174896, 0.11999999731779099, -0.09260000288486481, -0.003599999938160181, 0.016200000420212746, -0.12929999828338623, -0.06920000165700912, 0.0885000005364418, 0.17299999296665192, 0.016200000420212746, -0.09399999678134918, -0.1096000000834465, 0.035599999129772186, -0.09279999881982803, 0.13030000030994415, 0.06780000030994415, -0.07329999655485153, -0.06040000170469284, 0.061799999326467514, -0.008999999612569809, 0.0364999994635582, -0.060100000351667404, -0.04560000076889992, -0.11410000175237656, -0.0203000009059906, 0.1451999992132187, 0.0357000008225441, 0.0551999993622303, 0.1738000065088272, -0.13410000503063202, 0.11680000275373459, 0.026599999517202377, 0.13359999656677246, 0.16459999978542328, 0.027699999511241913, 0.039900001138448715, 0.013399999588727951, 0.042399998754262924, -0.017899999395012856, -0.014999999664723873, 0.07209999859333038, 0.07159999758005142, -0.15049999952316284, 0.09459999948740005, 0.07249999791383743, 0.1876000016927719, 0.023900000378489494, -0.013299999758601189, -0.004900000058114529, -0.048500001430511475, 0.23989999294281006, -0.07779999822378159, 0.039799999445676804, -0.007000000216066837], [-0.07429999858140945, -0.1062999963760376, 0.02199999988079071, -0.15199999511241913, -0.08990000188350677, 0.06080000102519989, 0.11640000343322754, 0.21469999849796295, -0.02410000003874302, -0.03370000049471855, 0.10130000114440918, 0.062300000339746475, 0.05590000003576279, 0.09640000015497208, 0.03229999914765358, 0.1809999942779541, 0.1979999989271164, -0.03229999914765358, 0.01360000018030405, 0.20059999823570251, -0.035599999129772186, -0.07090000063180923, 0.19499999284744263, 0.21709999442100525, 0.0746999979019165, 0.07769999653100967, -0.07090000063180923, -0.014600000344216824, -0.13650000095367432, -0.04520000144839287, 0.06499999761581421, 0.04800000041723251, 0.017500000074505806, -0.16699999570846558, -0.01640000008046627, -0.15770000219345093, 0.06549999862909317, -0.13109999895095825, -0.020899999886751175, 0.13189999759197235, 0.003700000001117587, 0.09319999814033508, -0.019099999219179153, -0.15710000693798065, 0.05990000069141388, -0.014100000262260437, -0.0697999969124794, -0.05180000141263008, 0.21379999816417694, 0.20329999923706055, 0.00839999970048666, 0.0013000000035390258, -0.09709999710321426, 0.06870000064373016, -0.1185000017285347, -0.09759999811649323, -0.0617000013589859, -0.0203000009059906, 0.05139999836683273, 0.05169999971985817, -0.2248000055551529, -0.1014999970793724, 0.005499999970197678, -0.02419999986886978, -0.031599998474121094, -0.016899999231100082, 0.11169999837875366, 0.07959999889135361, -0.06629999727010727, 0.061000000685453415, -0.09669999778270721, 0.03830000013113022, 0.042100001126527786, -0.15209999680519104, 0.05310000106692314, -0.09210000187158585, -0.20319999754428864, 0.010499999858438969, 0.1151999980211258, -0.07639999687671661, 0.20839999616146088, -0.00800000037997961, 0.14509999752044678, -0.06430000066757202, 0.05829999968409538, 0.04529999941587448, 0.014700000174343586, 0.0340999998152256, -0.01489999983459711, -0.12680000066757202, -0.149399995803833, -0.0031999999191612005, 0.05590000003576279, -0.15680000185966492, -0.09210000187158585, -0.11630000174045563, -0.021299999207258224, 0.0052999998442828655, -0.06809999793767929, 0.027000000700354576, 0.044599998742341995, 0.01940000057220459, 0.1308999955654144</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>[0.8025793870052077]</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>[0.04506453769695336]</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>[0.18591247396111188]</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>[0.1858588450315004]</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>[-3.1782474785250674]</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>[1.3674555584995913]</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>[0.6189713108275747]</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>[0.08752955732463827]</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>[-0.1275277524154057]</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>[0.26740563987629534]</t>
+        </is>
+      </c>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t>[0.569168879197826]</t>
+        </is>
+      </c>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>[0.1416346295907795]</t>
+        </is>
+      </c>
+      <c r="Q28" t="inlineStr">
+        <is>
+          <t>[-0.2709145646463824]</t>
+        </is>
+      </c>
+      <c r="R28" t="inlineStr">
+        <is>
+          <t>[0.1370372894425461]</t>
+        </is>
+      </c>
+      <c r="S28" t="inlineStr">
+        <is>
+          <t>[-0.18697854524094493]</t>
+        </is>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>[0.10001521550902381]</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>[-1.8008456114264417]</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>[0.26782562563296247]</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>[-0.30713935114137736]</t>
+        </is>
+      </c>
+      <c r="X28" t="inlineStr">
+        <is>
+          <t>[0.13693673349792448]</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>[-0.2639083730054135]</t>
+        </is>
+      </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>[0.10401107678385527]</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>[-2.3630003509239077]</t>
+        </is>
+      </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>[0.3094107432100966]</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>[-1.2519435548191877]</t>
+        </is>
+      </c>
+      <c r="AD28" t="inlineStr">
+        <is>
+          <t>[0.18870379769608278]</t>
+        </is>
+      </c>
+      <c r="AE28" t="inlineStr">
+        <is>
+          <t>[-1.122974976297948]</t>
+        </is>
+      </c>
+      <c r="AF28" t="inlineStr">
+        <is>
+          <t>[0.22859785677747452]</t>
+        </is>
+      </c>
+      <c r="AG28" t="inlineStr">
+        <is>
+          <t>[-3.653265955147962]</t>
+        </is>
+      </c>
+      <c r="AH28" t="inlineStr">
+        <is>
+          <t>[0.34643545703228856]</t>
+        </is>
+      </c>
+      <c r="AI28" t="inlineStr">
+        <is>
+          <t>[-1.6582954186882835]</t>
+        </is>
+      </c>
+      <c r="AJ28" t="inlineStr">
+        <is>
+          <t>[0.2178443503096605]</t>
+        </is>
+      </c>
+      <c r="AK28" t="inlineStr">
+        <is>
+          <t>[-1.100655359568194]</t>
+        </is>
+      </c>
+      <c r="AL28" t="inlineStr">
+        <is>
+          <t>[0.2229691756773326]</t>
+        </is>
+      </c>
+      <c r="AM28" t="inlineStr">
+        <is>
+          <t>[-3.5475357794352886]</t>
+        </is>
+      </c>
+      <c r="AN28" t="inlineStr">
+        <is>
+          <t>[0.34928371569392186]</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>model_128_64_2</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>[128, 64]</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>[[[-0.05169999971985817, 0.011599999852478504, 0.05860000103712082, 0.015599999576807022, -0.0568000003695488, 0.0071000000461936, -0.04830000177025795, 0.012000000104308128, 0.012199999764561653, 0.0006000000284984708, -0.012400000356137753, 0.032099999487400055, 0.012500000186264515, -0.06700000166893005, -9.999999747378752e-05, 0.053700000047683716, -0.13729999959468842, 0.050999999046325684, -0.026900000870227814, 0.04170000180602074, -0.0071000000461936, 0.04320000112056732, 0.0003000000142492354, 0.015699999406933784, -0.0632999986410141, 0.04490000009536743, -0.0071000000461936, 0.08869999647140503, 0.030500000342726707, -0.001500000013038516, 0.05389999970793724, -0.05169999971985817, -0.02070000022649765, 0.0020000000949949026, 0.01140000019222498, 0.009800000116229057, 0.01940000057220459, -0.03799999877810478, -0.01640000008046627, 0.01549999974668026, -0.024399999529123306, 0.09529999643564224, -0.006300000008195639, -0.015699999406933784, -0.07580000162124634, -0.03310000151395798, -0.020099999383091927, 0.032099999487400055, 0.10859999805688858, 0.09799999743700027, 0.048700001090765, -0.03189999982714653, 0.02250000089406967, -0.05260000005364418, -0.016499999910593033, 0.02250000089406967, -0.0203000009059906, -0.004600000102072954, 0.022700000554323196, -0.01769999973475933, -0.05779999867081642, 0.13570000231266022, -0.026399999856948853, -0.004699999932199717, 0.01940000057220459, -0.014499999582767487, -0.07180000096559525, 0.035599999129772186, 0.02669999934732914, 0.06109999865293503, -0.020500000566244125, 0.0340999998152256, 0.062199998646974564, 0.04610000178217888, 0.01489999983459711, -0.07909999787807465, 0.0786999985575676, 0.016200000420212746, -0.037300001829862595, 0.04659999907016754, -0.05420000106096268, 0.04479999840259552, -0.061400000005960464, -0.031300000846385956, 0.04540000110864639, 0.013299999758601189, -0.0006000000284984708, -0.011900000274181366, -0.09560000151395798, 0.02879999950528145, 0.07519999891519547, 0.05119999870657921, -0.01600000075995922, 0.012600000016391277, -0.00839999970048666, -0.05860000103712082, -0.08869999647140503, 0.04019999876618385, -0.0215000007301569, -0.013799999840557575, 0.053300000727176666, -0.08959999680519104, 0.052000001072883606, 0.007300000172108412, 0.026100000366568565, -0.016300000250339508, -0.020899999886751175, -0.03929999843239784, -0.11860000342130661, 0.030500000342726707, 0.029400000348687172, 0.039500001817941666, -0.031300000846385956, 0.027499999850988388, -0.030500000342726707, -0.05730000138282776, 0.013399999588727951, -0.0215000007301569, -0.061000000685453415, 0.016899999231100082, -0.026000000536441803, -0.03720000013709068, -0.05510000139474869, 0.015200000256299973, -0.015300000086426735, 0.0551999993622303, -0.017400000244379044, -0.033799998462200165], [0.0421999990940094, 0.009600000455975533, 0.024299999698996544, 0.07769999653100967, -0.030899999663233757, 0.01549999974668026, -0.0284000001847744, 0.08179999887943268, -0.07509999722242355, -0.07479999959468842, 0.051899999380111694, 0.04619999974966049, -0.0038999998942017555, 0.04190000146627426, -0.04690000042319298, 0.06920000165700912, -0.12280000001192093, 0.015599999576807022, 0.06719999760389328, 0.029999999329447746, 0.02850000001490116, 0.05979999899864197, -0.03370000049471855, 0.019099999219179153, 0.06639999896287918, -0.0421999990940094, -0.04450000077486038, -0.028999999165534973, -0.01119999960064888, 0.10209999978542328, 0.0414000004529953, -0.12240000069141388, -0.07519999891519547, 0.0706000030040741, 0.03319999948143959, 0.08320000022649765, 0.07699999958276749, 0.03290000185370445, -0.04969999939203262, -0.08209999650716782, 0.060499999672174454, -0.06599999964237213, 0.0010000000474974513, -0.05009999871253967, -0.028999999165534973, 0.07029999792575836, 0.0714000016450882, -0.02539999969303608, 0.05090000107884407, 0.07479999959468842, -0.035100001841783524, -0.023900000378489494, 0.007499999832361937, 0.05000000074505806, 0.09740000218153, 0.03500000014901161, 0.0017999999690800905, 0.010700000450015068, -0.039400000125169754, -0.010300000198185444, 0.04569999873638153, 0.010200000368058681, 0.027699999511241913, -0.024800000712275505, -0.03739999979734421, 0.031599998474121094, -0.04639999940991402, 0.04910000041127205, -0.07890000194311142, 0.08820000290870667, 0.01860000006854534, -0.06780000030994415, 0.01720000058412552, 0.04309999942779541, 0.008100000210106373, -0.01899999938905239, 0.0617000013589859, -0.06319999694824219, -0.040300000458955765, -0.09430000185966492, -0.030300000682473183, 0.07940000295639038, -0.017899999395012856, 0.006399999838322401, -0.016499999910593033, 0.02759999968111515, -0.014700000174343586, 0.09009999781847, 0.015300000086426735, -0.030899999663233757, 0.007799999788403511, 0.04129999876022339, -0.014000000432133675, 0.048500001430511475, 0.03669999912381172, 0.006200000178068876, 0.060600001364946365, 0.004399999976158142, 0.0625, -0.0357000008225441, 0.00860000029206276, 0.10670000314712524, -0.017799999564886093, 0.018300000578165054, -0.047600001096725464, -0.00019999999494757503, 0.02759999968111515, -0.09929999709129333, 0.09880000352859497, 0.05220000073313713, 0.005499999970197678, 0.03669999912381172, -0.031700000166893005, 0.022299999371170998, 0.04490000009536743, 0.0015999999595806003, 0.0608999989926815, 0.014399999752640724, 0.04910000041127205, 0.03579999879002571, 0.017799999564886093, -0.10750000178813934, 0.04540000110864639, 0.006800000090152025, -0.05220000073313713, -0.007600000128149986, 0.07999999821186066, 0.014399999752640724]], [[0.12309999763965607, -0.02160000056028366, -0.015699999406933784, 0.10999999940395355, -0.10830000042915344, 0.01679999940097332, -0.05719999969005585, 0.10109999775886536, 0.027300000190734863, -0.013000000268220901, -0.06689999997615814, 0.06440000236034393, -0.163100004196167, -0.0681999996304512, -0.09560000151395798, -0.04340000078082085, 0.013299999758601189, 0.042399998754262924, 0.019600000232458115, 0.009399999864399433, -0.14900000393390656, 0.12039999663829803, 0.12729999423027039, 0.08860000222921371, -0.16910000145435333, -0.05609999969601631, 0.11760000139474869, -0.018200000748038292, 0.05299999937415123, 0.1500999927520752, 0.12189999967813492, -0.05779999867081642, 0.18219999969005585, 0.053300000727176666, -0.07010000199079514, -0.1738000065088272, -0.11209999769926071, -0.19040000438690186, -0.002199999988079071, -0.06530000269412994, 0.06859999895095825, 0.05260000005364418, 0.02370000071823597, -0.05770000070333481, 0.060600001364946365, -0.04149999842047691, 0.02370000071823597, -0.032999999821186066, -0.10649999976158142, 0.02419999986886978, 0.11219999939203262, 0.061900001019239426, -0.006800000090152025, -0.09600000083446503, -0.00279999990016222, 0.0940999984741211, -0.05590000003576279, 0.0803999975323677, 0.07660000026226044, -0.08349999785423279, -0.03610000014305115, -0.009399999864399433, 0.07620000094175339, -0.06430000066757202, -0.04580000042915344, 0.005499999970197678, -0.06440000236034393, 0.17419999837875366, 0.015699999406933784, -0.010999999940395355, 0.004699999932199717, 0.019500000402331352, -0.0071000000461936, -0.032499998807907104, 0.19089999794960022, -0.11739999800920486, 0.06970000267028809, -0.011300000362098217, -0.08799999952316284, 0.08720000088214874, -0.0031999999191612005, 0.010499999858438969, 0.0421999990940094, -0.050599999725818634, -0.019200000911951065, -0.05290000140666962, 0.09910000115633011, -0.1800999939441681, -0.04749999940395355, -0.014100000262260437, -0.0794999971985817, 0.02850000001490116, -0.12759999930858612, 0.09229999780654907, -0.043299999088048935, -0.05790000036358833, 9.999999747378752e-05, 0.17579999566078186, 0.10189999639987946, -0.17299999296665192, -0.03269999846816063, 0.19750000536441803, -0.06689999997615814, -0.06700000166893005, -0.013799999840557575, -0.049400001764297485, -0.017899999395012856, 0.24699999392032623, 0.03240000084042549, -0.035100001841783524, -0.0625, -0.08560000360012054, 0.03539999946951866, 0.04430000111460686, 0.0007999999797903001, -0.06679999828338623, 0.09440000355243683, -0.08320000022649765, -0.11129999905824661, -0.1842000037431717, 0.022099999710917473, 0.09489999711513519, -0.04100000113248825, 0.08760000020265579, -0.14790000021457672, 0.07840000092983246, -0.07840000092983246, -0.007000000216066837], [0.05700000002980232, 0.09269999712705612, -0.015200000256299973, -0.08839999884366989, -0.11829999834299088, 0.007300000172108412, 0.005100000184029341, -0.09600000083446503, -0.00559999980032444, 0.1873999983072281, 0.023099999874830246, 0.02500000037252903, -0.22429999709129333, 0.0649000033736229, -0.023499999195337296, 0.1031000018119812, -0.17499999701976776, -0.019099999219179153, -0.012799999676644802, 0.03500000014901161, -0.0738999992609024, -0.03790000081062317, -0.06650000065565109, -0.08640000224113464, 0.07890000194311142, 0.014700000174343586, 0.024800000712275505, -0.014399999752640724, -0.13169999420642853, -0.11789999902248383, 0.07729999721050262, 0.03700000047683716, 0.15279999375343323, -0.10329999774694443, 0.014999999664723873, -0.05950000137090683, 0.03909999877214432, -0.052299998700618744, 0.025599999353289604, 0.006599999964237213, 0.0015999999595806003, -0.016300000250339508, -0.12020000070333481, -0.1145000010728836, -0.11729999631643295, 0.010400000028312206, -0.04879999905824661, 0.05920000001788139, 0.09950000047683716, -0.05990000069141388, 0.045899998396635056, -0.07010000199079514, 0.14990000426769257, -0.03629999980330467, -0.05889999866485596, 0.08609999716281891, 0.002400000113993883, 0.04690000042319298, 0.13609999418258667, 0.02329999953508377, 0.13120000064373016, -0.0284000001847744, 0.19089999794960022, -0.07410000264644623, -0.009499999694526196, -0.04659999907016754, -0.11569999903440475, -0.022700000554323196, -0.005200000014156103, 0.06809999793767929, 0.11500000208616257, -0.02070000022649765, -0.017899999395012856, 0.06859999895095825, -0.048900000751018524, 0.032600000500679016, 0.19210000336170197, 0.011699999682605267, -0.03530000150203705, 0.020600000396370888, -0.006899999920278788, 0.18160000443458557, 0.07530000060796738, 0.13269999623298645, 0.11599999666213989, -0.24369999766349792, -0.04600000008940697, -0.040300000458955765, 0.08659999817609787, 0.07209999859333038, 0.027799999341368675, 0.06449999660253525, -0.07039999961853027, 0.014700000174343586, -0.04670000076293945, -0.0560000017285347, 0.08079999685287476, 0.05299999937415123, -0.21950000524520874, 0.022600000724196434, 0.05730000138282776, -0.08500000089406967, -0.046799998730421066, 0.1429000049829483, 0.04899999871850014, -0.20990000665187836, 0.01850000023841858, -0.0032999999821186066, -0.036400001496076584, -0.04910000041127205, 0.05790000036358833, 0.13279999792575836, 0.0714000016450882, -0.11110000312328339, 0.050999999046325684, -0.1720999926328659, 0.016100000590085983, -0.04989999905228615, 0.12070000171661377, 0.13770000636577606, 0.1264999955892563, -0.016300000250339508, -0.09529999643564224, 0.0851999968290329, 0.04780000075697899, 0.0357000008225441, 0.05770000070333481, -0.014000000432133675], [0.17649999260902405, -0.0982000008225441, -0.13830000162124634, -0.060499999672174454, -0.06759999692440033, 0.05649999901652336, -0.025599999353289604, -0.07460000365972519, -0.10400000214576721, 0.014600000344216824, 0.13779999315738678, 0.07739999890327454, -0.04899999871850014, 0.10809999704360962, 0.06549999862909317, -0.017400000244379044, 0.14270000159740448, 0.12250000238418579, -0.023399999365210533, -0.045499999076128006, -0.02930000051856041, -0.021700000390410423, 0.006300000008195639, -0.0333000011742115, 0.09960000216960907, 0.11999999731779099, -0.07859999686479568, -0.10909999907016754, -0.03139999881386757, -0.057500001043081284, -0.10760000348091125, -0.07850000262260437, 0.09130000323057175, 0.07599999755620956, -0.10409999638795853, 0.009499999694526196, 0.08009999990463257, -0.03620000183582306, -0.015699999406933784, 0.10199999809265137, -0.12370000034570694, 0.22290000319480896, 0.01140000019222498, 0.01720000058412552, -0.07580000162124634, 0.02459999918937683, 0.10769999772310257, -0.04479999840259552, 0.14079999923706055, 0.056699998676776886, -0.007199999876320362, 0.00860000029206276, 0.006399999838322401, 0.17810000479221344, -0.018200000748038292, -0.13030000030994415, -0.0066999997943639755, -0.025699999183416367, 0.21050000190734863, -0.015599999576807022, 0.06350000202655792, 0.15469999611377716, -0.07850000262260437, 0.14390000700950623, 0.014999999664723873, -0.025699999183416367, -0.05730000138282776, 0.10639999806880951, -0.11490000039339066, -0.054099999368190765, -0.030400000512599945, -0.053599998354911804, -0.1784999966621399, 0.01209999993443489, -0.031300000846385956, -0.10989999771118164, -0.02590000070631504, 0.012000000104308128, 0.02329999953508377, -0.008200000040233135, 0.05559999868273735, 0.0957999974489212, 0.07249999791383743, 0.0568000003695488, -0.042899999767541885, -0.024399999529123306, 0.052299998700618744, -0.05559999868273735, 0.10760000348091125, 0.10999999940395355, 0.0364999994635582, -0.163100004196167, 0.05090000107884407, 0.15330000221729279, -0.16689999401569366, -0.011800000444054604, -0.07720000296831131, -0.12020000070333481, -0.10509999841451645, 0.029100000858306885, 0.07670000195503235, 0.1598999947309494, -0.06859999895095825, 0.04390000179409981, -0.11230000108480453, 0.1762000024318695, 0.08950000256299973, 0.10159999877214432, 0.0272000003606081, -0.1396999955177307, 0.05640000104904175, 0.04859999939799309, -0.0430000014603138, 0.18039999902248383, -0.04899999871850014, 0.033399999141693115, -0.021199999377131462, 0.06800000369548798, -0.16110000014305115, 0.037700001150369644, -0.07320000231266022, 0.05420000106096268, 0.019099999219179153, 0.002400000113993883, 0.03849999979138374, 0.01979999989271164, -0.07720000296831131, -0.007899999618530273], [0.04100000113248825, 0.0012000000569969416, -0.03539999946951866, -0.18440000712871552, 0.1932000070810318, -0.1867000013589859, 0.007400000002235174, -0.024900000542402267, -0.10080000013113022, 0.11230000108480453, -0.02710000053048134, 0.07339999824762344, 0.1454000025987625, 0.03909999877214432, 0.1306000053882599, 0.007300000172108412, -0.01730000041425228, -0.08619999885559082, 0.0892999991774559, 0.0723000019788742, -0.020400000736117363, -0.07620000094175339, 0.0934000015258789, -0.13940000534057617, -0.09160000085830688, 0.042899999767541885, 0.06620000302791595, -0.1688999980688095, 0.08619999885559082, 0.09950000047683716, 0.10450000315904617, -0.1868000030517578, 0.0006000000284984708, 0.1404999941587448, -0.032999999821186066, 0.01590000092983246, -0.14329999685287476, -0.010599999688565731, -0.04690000042319298, -0.13729999959468842, 0.05609999969601631, 0.0560000017285347, 0.02630000002682209, -0.026799999177455902, -0.002300000051036477, -0.0027000000700354576, 0.10419999808073044, 0.09040000289678574, -0.10790000110864639, 0.003800000064074993, -0.056699998676776886, 0.013899999670684338, 0.06629999727010727, -0.10369999706745148, -0.07810000330209732, 0.15649999678134918, 0.009499999694526196, 0.09719999879598618, -0.01269999984651804, 0.029600000008940697, 0.04600000008940697, 0.14869999885559082, 0.21040000021457672, -0.009499999694526196, 0.002400000113993883, 0.004800000227987766, -0.05590000003576279, 0.02199999988079071, -0.21649999916553497, -0.11540000140666962, -0.039900001138448715, -0.02199999988079071, 0.05220000073313713, 0.0803999975323677, -0.07660000026226044, 0.027899999171495438, -0.0966000035405159, -0.05900000035762787, -0.00559999980032444, 0.09070000052452087, 0.00860000029206276, -0.018400000408291817, 0.0843999981880188, -0.25609999895095825, -0.08749999850988388, 0.0008999999845400453, 0.11219999939203262, -0.04830000177025795, 0.12700000405311584, 0.10719999670982361, -0.005200000014156103, -0.09719999879598618, 0.05079999938607216, 0.0034000000450760126, 0.05590000003576279, -0.03269999846816063, -0.022299999371170998, 0.14090000092983246, 0.07940000295639038, 0.06080000102519989, 0.04349999874830246, -0.11640000343322754, -0.08110000193119049, 0.11230000108480453, 0.02759999968111515, 0.09229999780654907, -0.050999999046325684, -0.0632999986410141, -0.09059999883174896, 0.11749999970197678, -0.014600000344216824, 0.15369999408721924, -0.1031000018119812, -0.014600000344216824, -0.005900000222027302, 0.05550000071525574, 0.04699999839067459, 0.056299999356269836, -0.0013000000035390258, 0.1363999992609024, 0.06310000270605087, -0.12049999833106995, 0.037300001829862595, 0.024700000882148743, -0.03629999980330467, 0.03790000081062317, 0.010499999858438969, 0.0017000000225380063], [-0.14329999685287476, -0.02710000053048134, -0.05979999899864197, -0.09629999846220016, -0.1136000007390976, 0.10570000112056732, 0.1412999927997589, 0.06939999759197235, -0.07109999656677246, -0.051600001752376556, -0.03590000048279762, -0.06019999831914902, -0.051899999380111694, -0.04610000178217888, -0.003000000026077032, 0.0284000001847744, -0.16609999537467957, -0.02280000038444996, 0.1160999983549118, 0.03669999912381172, -0.04089999943971634, 0.16899999976158142, 0.04230000078678131, 0.009700000286102295, 0.033799998462200165, 0.10740000009536743, 0.04670000076293945, -0.0689999982714653, 0.11460000276565552, -0.1412000060081482, 0.11069999635219574, -0.031199999153614044, 0.010599999688565731, 0.1307000070810318, 0.03629999980330467, -0.039799999445676804, -0.016899999231100082, -0.010999999940395355, 0.09759999811649323, 0.1826999932527542, -0.07680000364780426, 0.07010000199079514, 0.09740000218153, 0.179299995303154, -0.10239999741315842, -0.00570000009611249, 0.14890000224113464, 0.053599998354911804, -0.10670000314712524, -0.08240000158548355, 0.09539999812841415, 0.15839999914169312, 0.0284000001847744, 0.01860000006854534, 0.049800001084804535, -9.999999747378752e-05, -0.0010999999940395355, 0.06710000336170197, 0.01889999955892563, -0.08649999648332596, 0.1264999955892563, 0.0013000000035390258, 0.008999999612569809, 0.08429999649524689, 0.08489999920129776, 0.0406000018119812, 0.12700000405311584, -0.06440000236034393, 0.03350000083446503, 0.050700001418590546, 0.16380000114440918, -0.1534000039100647, 0.06780000030994415, -0.03999999910593033, 0.0024999999441206455, 0.025499999523162842, -0.10360000282526016, 0.07739999890327454, 0.1574999988079071, 0.1290999948978424, -0.003700000001117587, 0.030300000682473183, -0.048700001090765, 0.06930000334978104, -0.07479999959468842, 0.016300000250339508, 0.08810000121593475, -0.06520000100135803, 0.009800000116229057, 0.030500000342726707, 0.020400000736117363, -0.02500000037252903, 0.17640000581741333, -0.13699999451637268, -0.04399999976158142, -0.12460000067949295, -0.052400000393390656, -0.12319999933242798, -0.016200000420212746, 0.012600000016391277, -0.013299999758601189, 0.03709999844431877, 0.06939999759197235, -0.019099999219179153, -0.03400000184774399, -0.08669999986886978, -0.14800000190734863, -0.03790000081062317, -0.057100001722574234, -0.05779999867081642, 0.06830000132322311, -0.1356000006198883, -0.16949999332427979, -0.17000000178813934, 0.008100000210106373, 0.04270000010728836, 0.1216999962925911, 0.1623000055551529, 0.11599999666213989, -0.0794999971985817, -0.011900000274181366, 0.030300000682473183, -0.14710000157356262, 0.1509999930858612, -0.11420000344514847, 0.011699999682605267, 0.01600000075995922, 0.07150000333786011], [0.04340000078082085, 0.024000000208616257, -0.02969999983906746, 0.029200000688433647, 0.013500000350177288, 0.03830000013113022, 0.04479999840259552, -0.00019999999494757503, 0.01269999984651804, 0.00139999995008111, 0.1005999967455864, 0.12150000035762787, 0.10869999974966049, 0.19059999287128448, 0.006500000134110451, -0.03920000046491623, -0.10670000314712524, 0.03539999946951866, -0.08780000358819962, 0.13259999454021454, -0.05220000073313713, 0.013899999670684338, 0.08560000360012054, -0.2070000022649765, 0.10010000318288803, 0.05860000103712082, -0.022600000724196434, -0.00800000037997961, 0.0763000026345253, 0.0649000033736229, 0.0697999969124794, -0.03150000050663948, -0.13410000503063202, 0.07020000368356705, -0.0024999999441206455, -0.11980000138282776, -0.026000000536441803, -0.05979999899864197, -0.1437000036239624, 0.061400000005960464, -0.11339999735355377, -0.03680000081658363, -0.1453000009059906, 0.07959999889135361, 0.09679999947547913, -0.027799999341368675, -0.04690000042319298, 0.05480000004172325, -0.05649999901652336, -0.02810000069439411, 0.01549999974668026, -0.24539999663829803, 0.007899999618530273, -0.05290000140666962, -0.06159999966621399, -0.039500001817941666, -0.11339999735355377, -0.02800000086426735, 0.043699998408555984, 0.20399999618530273, 0.03400000184774399, 0.04129999876022339, -0.0860000029206276, -0.04769999906420708, 0.02889999933540821, -0.11330000311136246, 0.04280000180006027, 0.133200004696846, 0.13819999992847443, -0.15459999442100525, -0.019200000911951065, -0.014700000174343586, -0.121799997985363, -0.05299999937415123, 0.05290000140666962, 0.07580000162124634, -0.07180000096559525, -0.00430000014603138, 0.07909999787807465, -0.10109999775886536, -0.14959999918937683, 0.15489999949932098, 0.03709999844431877, 0.18150000274181366, -0.2046000063419342, 0.05739999935030937, -0.15389999747276306, -0.13210000097751617, -0.08429999649524689, 0.031199999153614044, 0.1315000057220459, -0.019500000402331352, 0.006200000178068876, -0.010900000110268593, -0.03150000050663948, 0.0786999985575676, -0.0625, 0.08380000293254852, 0.11490000039339066, -0.13670000433921814, 0.06369999796152115, -0.2087000012397766, 0.07850000262260437, -0.032999999821186066, 0.0012000000569969416, -0.10119999945163727, 0.04639999940991402, -0.009100000374019146, -0.12139999866485596, 0.03150000050663948, -0.00839999970048666, -0.06379999965429306, 0.07270000129938126, 0.012000000104308128, 0.09920000284910202, 0.0066999997943639755, 0.055799998342990875, 0.002400000113993883, 0.10220000147819519, -0.12680000066757202, -0.07050000131130219, 0.018799999728798866, 0.05380000174045563, 0.029600000008940697, -0.035999998450279236, 0.11749999970197678, -0.08009999990463257, 0.02710000053048134], [-0.0215000007301569, 0.11169999837875366, -0.07010000199079514, -0.024299999698996544, -0.11270000040531158, 0.10989999771118164, 0.03290000185370445, 0.06599999964237213, -0.024299999698996544, -0.08030000329017639, 0.11389999836683273, -0.08150000125169754, 0.1454000025987625, 0.007899999618530273, -0.08330000191926956, 0.01140000019222498, 0.08110000193119049, -0.08460000157356262, -0.02759999968111515, -0.05480000004172325, 0.08590000122785568, -0.1143999993801117, -0.0019000000320374966, 0.01590000092983246, 0.005499999970197678, -0.03280000016093254, -0.03590000048279762, 0.07280000299215317, -0.07240000367164612, 0.15449999272823334, 0.08640000224113464, -0.14030000567436218, 0.03920000046491623, 0.00039999998989515007, 0.037700001150369644, -0.05139999836683273, 0.1264999955892563, 0.1014999970793724, 0.21729999780654907, -0.013199999928474426, 0.023600000888109207, -0.15289999544620514, -0.013399999588727951, 0.12200000137090683, -0.04529999941587448, 0.03189999982714653, -0.06239999830722809, 0.12049999833106995, -0.049800001084804535, -0.17800000309944153, 0.056699998676776886, -0.03579999879002571, -0.07519999891519547, 0.041099999099969864, -0.11779999732971191, 0.04439999908208847, -0.004100000020116568, -0.035100001841783524, 0.09269999712705612, 0.08169999718666077, 0.07450000196695328, 0.06279999762773514, 0.052799999713897705, 0.004399999976158142, 0.12870000302791595, -0.08950000256299973, 0.01850000023841858, -0.042100001126527786, -0.04830000177025795, 0.08259999752044678, 0.121799997985363, 0.18940000236034393, -0.06849999725818634, -0.18780000507831573, -0.13249999284744263, -0.2224999964237213, -0.0044999998062849045, -0.11680000275373459, -0.0803999975323677, -0.048900000751018524, 0.16060000658035278, -0.04690000042319298, -0.04170000180602074, -0.03869999945163727, -0.019500000402331352, 0.011500000022351742, 0.11010000109672546, 0.0430000014603138, 0.0052999998442828655, 0.04859999939799309, -0.057999998331069946, -0.05979999899864197, 0.0714000016450882, -0.06599999964237213, -0.15760000050067902, -0.027499999850988388, -0.1340000033378601, 0.11420000344514847, 0.04989999905228615, -0.08389999717473984, -0.04340000078082085, -0.05990000069141388, -0.07999999821186066, -0.044199999421834946, -0.06599999964237213, 0.05420000106096268, 0.04740000143647194, 0.10700000077486038, 0.07760000228881836, 0.09489999711513519, -0.0013000000035390258, 0.04360000044107437, 0.1891999989748001, -0.01759999990463257, 0.10339999943971634, 0.050999999046325684, -0.1655000001192093, -0.018799999728798866, 0.06459999829530716, 0.061400000005960464, -0.03669999912381172, 0.06159999966621399, -0.0617000013589859, 0.18240000307559967, -0.07810000330209732, 0.051600001752376556, 0.13109999895095825, 0.10989999771118164], [-0.10369999706745148, 0.09149999916553497, -0.0203000009059906, -0.07930000126361847, 0.10000000149011612, 0.007199999876320362, -0.07090000063180923, 0.027499999850988388, 0.1388999968767166, -0.003800000064074993, -0.03139999881386757, -0.038100000470876694, -0.1306000053882599, -0.012299999594688416, -0.007000000216066837, -0.01769999973475933, 0.012500000186264515, 0.04309999942779541, 0.19470000267028809, 0.12430000305175781, -0.02250000089406967, -0.028699999675154686, -0.15129999816417694, -0.04479999840259552, 0.1842000037431717, -0.18299999833106995, -0.017000000923871994, -0.03680000081658363, -0.10300000011920929, -0.008999999612569809, 0.0017000000225380063, 0.13099999725818634, -0.007799999788403511, 0.09880000352859497, -0.05950000137090683, -0.057999998331069946, -0.14569999277591705, 0.008799999952316284, -0.24770000576972961, 0.10530000180006027, 0.03590000048279762, -0.05400000140070915, 0.01209999993443489, 0.06340000033378601, -0.061900001019239426, -0.15780000388622284, 0.16200000047683716, 0.02410000003874302, 0.16869999468326569, 0.025699999183416367, 0.007199999876320362, 0.05249999836087227, -0.09849999845027924, -0.07769999653100967, -0.10409999638795853, 0.017899999395012856, 0.019700000062584877, 0.0035000001080334187, 0.07429999858140945, -0.15330000221729279, 0.019600000232458115, -0.029999999329447746, 0.0031999999191612005, -0.15870000422000885, 0.11330000311136246, 0.027000000700354576, 0.011900000274181366, 0.11640000343322754, -0.07259999960660934, 0.01510000042617321, -0.09120000153779984, 0.035100001841783524, -0.023600000888109207, -0.02539999969303608, 0.04859999939799309, -0.05389999970793724, -0.000699999975040555, 0.04690000042319298, -0.09179999679327011, -0.07329999655485153, 0.08640000224113464, -0.10750000178813934, -0.01140000019222498, -0.06549999862909317, -0.11869999766349792, 0.2134000062942505, 0.008500000461935997, 0.035100001841783524, -0.031199999153614044, 0.020500000566244125, 0.10440000146627426, -0.1746000051498413, 0.009100000374019146, 0.007899999618530273, -0.16009999811649323, 0.05739999935030937, -0.06989999860525131, 0.0869000032544136, -0.1096000000834465, 0.08129999786615372, -0.19529999792575836, -0.05040000006556511, 0.04410000145435333, -0.03189999982714653, 0.04340000078082085, -0.08869999647140503, 0.14630000293254852, 0.15060000121593475, -0.04500000178813934, 0.06859999895095825, -0.00430000014603138, -0.04769999906420708, 0.10350000113248825, -0.10660000145435333, -0.0414000004529953, -0.022600000724196434, 0.10459999740123749, 0.09059999883174896, -0.006099999882280827, 0.025599999353289604, -0.024700000882148743, -0.025499999523162842, -0.12610000371932983, -0.05950000137090683, 0.11209999769926071, -0.10440000146627426, 0.05999999865889549, 0.030899999663233757], [0.09950000047683716, -0.094200000166893, 0.09690000116825104, 0.07129999995231628, -0.06390000134706497, -0.08950000256299973, -0.032499998807907104, -0.1137000024318695, 0.013000000268220901, -0.0681999996304512, -0.00930000003427267, -0.04439999908208847, -0.07649999856948853, -0.03359999880194664, 0.03889999911189079, 0.09019999951124191, -0.037300001829862595, -0.034699998795986176, 0.1476999968290329, -0.051500000059604645, 0.07050000131130219, -0.041999999433755875, -0.11659999936819077, 0.026100000366568565, 0.062199998646974564, -0.00839999970048666, 0.09969999641180038, 0.1534000039100647, -0.08030000329017639, -0.022099999710917473, -0.10119999945163727, -0.11429999768733978, 0.02459999918937683, 0.045499999076128006, -0.09910000115633011, 0.04639999940991402, 0.08070000261068344, -0.08910000324249268, -0.01940000057220459, -0.017899999395012856, 0.0722000002861023, 0.06120000034570694, 0.03139999881386757, 0.1331000030040741, -0.0012000000569969416, 0.06419999897480011, 0.08869999647140503, -0.09279999881982803, -0.03819999843835831, -0.025299999862909317, 0.17139999568462372, -0.05649999901652336, 0.10199999809265137, 0.1906999945640564, -0.03449999913573265, 0.03189999982714653, -0.1193000003695488, 0.03579999879002571, -0.0010999999940395355, -0.09929999709129333, -0.07840000092983246, 0.09019999951124191, -0.052299998700618744, -0.06620000302791595, 0.14560000598430634, 0.021700000390410423, -0.14830000698566437, 0.1891999989748001, 0.035999998450279236, -0.05570000037550926, 0.02370000071823597, 0.12099999934434891, 0.14550000429153442, 0.06989999860525131, 0.020400000736117363, -0.0820000022649765, 0.09189999848604202, -0.06310000270605087, 0.11869999766349792, -0.00559999980032444, -0.05939999967813492, -0.12389999628067017, 0.017799999564886093, -0.02199999988079071, -0.14589999616146088, 0.08190000057220459, 0.0608999989926815, 0.0575999990105629, 0.0414000004529953, -0.164900004863739, -0.020899999886751175, 0.012400000356137753, 0.052799999713897705, 0.13130000233650208, 0.15209999680519104, 0.055799998342990875, -0.13019999861717224, 0.007300000172108412, -0.09929999709129333, 0.00860000029206276, 0.07909999787807465, -0.06620000302791595, 0.2468000054359436, 0.09030000120401382, 0.12240000069141388, -0.048500001430511475, -0.2046000063419342, -0.002300000051036477, -0.0560000017285347, 0.003700000001117587, 0.1420000046491623, 0.1145000010728836, 0.094200000166893, -0.004999999888241291, 0.09759999811649323, 0.11079999804496765, -0.0982000008225441, -0.0575999990105629, 0.14650000631809235, -0.0494999997317791, -0.00800000037997961, -0.021800000220537186, 0.07440000027418137, 0.1046999990940094, -0.028599999845027924, 0.05290000140666962, -0.09369999915361404, -0.06669999659061432], [0.03709999844431877, -0.03709999844431877, -0.08299999684095383, -0.042399998754262924, -0.0034000000450760126, 0.00039999998989515007, 0.03280000016093254, -0.05660000070929527, -0.06270000338554382, 0.03830000013113022, 0.08529999852180481, -0.23600000143051147, 0.11869999766349792, 0.08659999817609787, 0.052400000393390656, 0.03999999910593033, 0.08500000089406967, 0.05939999967813492, -0.04019999876618385, -0.0044999998062849045, 0.10080000013113022, 0.14730000495910645, -0.06780000030994415, 0.05790000036358833, 0.07100000232458115, -0.04969999939203262, -0.053599998354911804, -0.026599999517202377, 0.044599998742341995, -0.03400000184774399, -0.045499999076128006, -0.04520000144839287, 0.008999999612569809, 0.04230000078678131, -0.1324000060558319, -0.042399998754262924, -0.08229999989271164, -0.05209999904036522, -0.09120000153779984, -0.06520000100135803, 0.11500000208616257, 0.11569999903440475, -0.1868000030517578, -0.05660000070929527, 0.08699999749660492, 0.06199999898672104, 0.1746000051498413, -0.019500000402331352, 0.06939999759197235, 0.030799999833106995, -0.15070000290870667, 0.03759999945759773, 0.00559999980032444, 0.03480000048875809, 0.0803999975323677, 0.06430000066757202, -0.04830000177025795, -0.05849999934434891, -0.05380000174045563, 0.07119999825954437, -0.03909999877214432, 0.07919999957084656, 0.11949999630451202, 0.1200999990105629, 0.07270000129938126, -0.043299999088048935, -0.06719999760389328, -0.041999999433755875, -0.00139999995008111, 0.10740000009536743, 0.0828000009059906, -0.08470000326633453, 0.026200000196695328, 0.06480000168085098, 0.05719999969005585, 0.12409999966621399, 0.06069999933242798, -0.02810000069439411, 0.002899999963119626, 0.032099999487400055, -0.002300000051036477, 0.04100000113248825, 0.20010000467300415, 0.051500000059604645, 0.012299999594688416, 0.13920000195503235, -0.03420000150799751, 0.05429999902844429, 0.04170000180602074, -0.09260000288486481, -0.1428000032901764, 0.13449999690055847, -0.04280000180006027, -0.10209999978542328, -0.053199999034404755, -0.06480000168085098, -0.18289999663829803, 0.15940000116825104, -0.09969999641180038, -0.04309999942779541, -0.029100000858306885, 0.005799999926239252, -0.07729999721050262, -0.12110</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>[[[-0.09549999982118607, -0.00570000009611249, 0.037300001829862595, -0.0794999971985817, -0.04919999837875366, 0.04179999977350235, -0.013000000268220901, -0.06549999862909317, 0.08900000154972076, 0.05869999900460243, -0.05939999967813492, -0.021900000050663948, -0.03819999843835831, -0.09650000184774399, 0.05480000004172325, 0.011699999682605267, -0.08810000121593475, 0.007400000002235174, -0.07819999754428864, 0.04670000076293945, -0.08139999955892563, -0.04410000145435333, 0.08529999852180481, -0.03020000085234642, -0.10670000314712524, 0.0786999985575676, -0.005400000140070915, 0.09629999846220016, 0.054999999701976776, -0.04809999838471413, 0.011900000274181366, 0.024700000882148743, 0.065700002014637, -0.0697999969124794, -0.046799998730421066, -0.07819999754428864, -0.01899999938905239, -0.07339999824762344, -0.004399999976158142, 0.0828000009059906, -0.07259999960660934, 0.12600000202655792, -0.04349999874830246, 0.06970000267028809, -0.08959999680519104, -0.1006999984383583, -0.10100000351667404, 0.13600000739097595, 0.08100000023841858, 0.04830000177025795, 0.09719999879598618, -0.026000000536441803, -0.013700000010430813, -0.10890000313520432, -0.09969999641180038, -0.041099999099969864, 0.046300001442432404, -0.06390000134706497, 0.06419999897480011, -0.03240000084042549, -0.10419999808073044, 0.14090000092983246, -0.04670000076293945, 0.07180000096559525, 0.05959999933838844, -0.04839999973773956, -0.044199999421834946, -0.032099999487400055, 0.08900000154972076, 0.0006000000284984708, -0.05350000038743019, 0.09109999984502792, 0.055799998342990875, -0.010999999940395355, -0.0017000000225380063, -0.07460000365972519, 0.05779999867081642, 0.1005999967455864, -0.0015999999595806003, 0.10520000010728836, 0.030799999833106995, -0.0035000001080334187, -0.05959999933838844, 0.002899999963119626, 0.04129999876022339, 0.05249999836087227, -0.006800000090152025, -0.06610000133514404, -0.10180000215768814, 0.055799998342990875, 0.08500000089406967, 0.0348999984562397, 0.014700000174343586, -0.0706000030040741, -0.049300000071525574, -0.04690000042319298, -0.12800000607967377, 0.06689999997615814, -0.07819999754428864, 0.016699999570846558, -0.010599999688565731, -0.14429999887943268, 0.09459999948740005, -0.035999998450279236, 0.10830000042915344, 0.03290000185370445, -0.07490000128746033, 0.0284000001847744, -0.13179999589920044, -0.04749999940395355, 0.05590000003576279, -0.03869999945163727, 0.031300000846385956, -0.12039999663829803, -0.11389999836683273, -0.03629999980330467, -0.03530000150203705, -0.05550000071525574, -0.0966000035405159, -0.002099999925121665, 0.0008999999845400453, 0.0430000014603138, -0.09889999777078629, 0.05719999969005585, 0.05310000106692314, 0.07050000131130219, -0.061000000685453415, -0.05979999899864197], [0.059700001031160355, -0.027699999511241913, -0.10920000076293945, 0.10700000077486038, 0.06260000169277191, -0.10419999808073044, 0.01730000041425228, 0.07079999893903732, -0.05570000037550926, -0.0649000033736229, 0.08290000259876251, 0.01600000075995922, -0.001500000013038516, 0.050999999046325684, -0.08169999718666077, -0.016200000420212746, -0.08470000326633453, -0.00039999998989515007, 0.061400000005960464, -0.041200000792741776, 0.08389999717473984, 0.057100001722574234, 0.028200000524520874, 0.05939999967813492, 0.0982000008225441, -0.06880000233650208, 0.02280000038444996, -0.07109999656677246, -0.05389999970793724, 0.07199999690055847, 0.006500000134110451, -0.13619999587535858, -0.04479999840259552, 0.11249999701976776, 0.023900000378489494, 0.11749999970197678, 0.03869999945163727, 0.10750000178813934, 0.005499999970197678, -0.06800000369548798, 0.08879999816417694, -0.1006999984383583, -0.015200000256299973, -0.06379999965429306, 0.03200000151991844, 0.08590000122785568, 0.10140000283718109, -0.15449999272823334, 0.00039999998989515007, 0.065700002014637, -0.13689999282360077, 0.004999999888241291, -0.0005000000237487257, 0.10819999873638153, 0.11190000176429749, 0.024700000882148743, 0.03550000116229057, 0.05290000140666962, -0.052799999713897705, 0.05900000035762787, 0.06700000166893005, -0.022299999371170998, 0.054099999368190765, -0.019300000742077827, -0.09749999642372131, 0.034699998795986176, -0.005100000184029341, 0.007199999876320362, -0.06809999793767929, 0.024900000542402267, 0.020400000736117363, -0.07530000060796738, -0.03700000047683716, 0.030300000682473183, -0.029899999499320984, 0.048700001090765, 0.04749999940395355, -0.11320000141859055, -0.02889999933540821, -0.1046999990940094, -0.02879999950528145, 0.07940000295639038, 0.021900000050663948, 0.014399999752640724, -0.016499999910593033, -0.12439999729394913, -0.014700000174343586, 0.08259999752044678, 0.07620000094175339, -0.05429999902844429, -0.035100001841783524, -0.0015999999595806003, 0.003800000064074993, 0.07599999755620956, 0.06520000100135803, 0.09040000289678574, 0.10419999808073044, -0.05689999833703041, 0.07890000194311142, -0.0406000018119812, -0.00800000037997961, 0.13989999890327454, -0.054099999368190765, 0.0414000004529953, -0.09080000221729279, -0.010400000028312206, 0.034699998795986176, -0.06949999928474426, 0.18170000612735748, 0.006099999882280827, -0.03539999946951866, -0.000699999975040555, -0.019300000742077827, 0.08349999785423279, 0.07739999890327454, 0.094200000166893, 0.03669999912381172, 0.03280000016093254, 0.16290000081062317, -0.019999999552965164, 0.043699998408555984, -0.1500999927520752, 0.12280000001192093, -0.03849999979138374, -0.02969999983906746, -0.03920000046491623, 0.09950000047683716, 0.04320000112056732]], [[0.24639999866485596, 0.00419999985024333, -0.0027000000700354576, 0.09719999879598618, -0.04179999977350235, -0.03880000114440918, 0.0706000030040741, 0.18479999899864197, -0.08089999854564667, 0.04340000078082085, -0.04910000041127205, 0.04309999942779541, -0.10249999910593033, -0.020099999383091927, -0.1088000014424324, -0.07249999791383743, -0.04390000179409981, 0.06279999762773514, 0.1404000073671341, 0.052299998700618744, -0.12540000677108765, 0.10109999775886536, 0.1542000025510788, 0.013500000350177288, -0.06849999725818634, -0.12600000202655792, 0.11410000175237656, -0.07129999995231628, 0.08709999918937683, 0.15289999544620514, 0.06440000236034393, -0.04470000043511391, 0.1703999936580658, 0.09950000047683716, -0.07620000094175339, -0.1753000020980835, -0.09769999980926514, -0.2160000056028366, 0.026200000196695328, -0.16349999606609344, 0.1103999987244606, -0.047200001776218414, 0.09210000187158585, 0.007400000002235174, 0.14710000157356262, 0.00430000014603138, -0.11259999871253967, 0.007699999958276749, -0.17180000245571136, -0.09740000218153, 0.18310000002384186, 0.014600000344216824, 0.02590000070631504, -0.09709999710321426, -0.027899999171495438, 0.07509999722242355, -0.0794999971985817, 0.11410000175237656, 0.05939999967813492, -0.08649999648332596, 0.056299999356269836, -0.0917000025510788, 0.041999999433755875, -0.06759999692440033, 0.03460000082850456, 0.07460000365972519, -0.08129999786615372, 0.15649999678134918, -0.08429999649524689, -0.04129999876022339, 0.04529999941587448, 0.003800000064074993, 0.06469999998807907, -0.1347000002861023, 0.2409999966621399, -0.049800001084804535, 0.11420000344514847, 0.027799999341368675, 0.018400000408291817, 0.10660000145435333, -0.00860000029206276, 0.07360000163316727, 0.12690000236034393, -0.13940000534057617, -0.05460000038146973, -0.04740000143647194, 0.17970000207424164, -0.2800999879837036, -0.0421999990940094, -0.013299999758601189, -0.08510000258684158, -0.07190000265836716, -0.1712999939918518, 0.14010000228881836, 0.0017999999690800905, 0.012500000186264515, 0.031099999323487282, 0.08349999785423279, 0.1046999990940094, -0.16290000081062317, 0.07930000126361847, 0.32359999418258667, -0.13500000536441803, -0.10010000318288803, -0.07840000092983246, -0.1404000073671341, 0.037300001829862595, 0.30309998989105225, 0.06499999761581421, 0.04470000043511391, -0.17479999363422394, -0.0674000009894371, 0.03959999978542328, 0.035100001841783524, 0.02329999953508377, -0.0333000011742115, 0.1362999975681305, -0.12430000305175781, -0.08320000022649765, -0.30309998989105225, -0.06159999966621399, 0.05950000137090683, -0.09849999845027924, 0.10790000110864639, -0.0794999971985817, -0.0038999998942017555, -0.050999999046325684, 0.012400000356137753], [0.023499999195337296, -0.011599999852478504, -0.1356000006198883, -0.13689999282360077, -0.10750000178813934, -0.02889999933540821, 0.025299999862909317, -0.10890000313520432, -0.01600000075995922, 0.225600004196167, 0.16750000417232513, -0.010999999940395355, -0.27309998869895935, 0.06040000170469284, -0.10159999877214432, 0.14730000495910645, -0.13410000503063202, -0.09019999951124191, -0.03590000048279762, -0.042500000447034836, -0.06639999896287918, 0.00430000014603138, -0.16990000009536743, -0.050700001418590546, 0.04919999837875366, 0.09130000323057175, -0.042399998754262924, -0.0003000000142492354, -0.02879999950528145, -0.14169999957084656, 0.06889999657869339, 0.02250000089406967, 0.15539999306201935, -0.0714000016450882, -0.039000000804662704, -0.024399999529123306, 0.03889999911189079, 0.01600000075995922, 0.06530000269412994, 0.07029999792575836, -0.043299999088048935, -0.006099999882280827, -0.12389999628067017, -0.08470000326633453, -0.1225999966263771, -0.007899999618530273, -0.09570000320672989, 0.07280000299215317, 0.08219999819993973, -0.07530000060796738, 0.05180000141263008, -0.1534000039100647, 0.18870000541210175, -0.07339999824762344, -0.048500001430511475, 0.029999999329447746, 0.07750000059604645, -0.005200000014156103, 0.06710000336170197, 0.12809999287128448, 0.1298999935388565, -0.05040000006556511, 0.18199999630451202, -0.02290000021457672, -0.08160000294446945, -0.0272000003606081, -0.09279999881982803, -0.10719999670982361, 0.00839999970048666, 0.027899999171495438, 0.032099999487400055, 0.015300000086426735, 0.06030000001192093, 0.04010000079870224, -0.09480000287294388, 0.002300000051036477, 0.16269999742507935, -0.023099999874830246, 0.05900000035762787, 0.03750000149011612, 0.03610000014305115, 0.20509999990463257, 0.09109999984502792, 0.20669999718666077, 0.13779999315738678, -0.1695999950170517, -0.054499998688697815, -0.13930000364780426, 0.04430000111460686, 0.07169999927282333, 0.07689999788999557, 0.021400000900030136, -0.05350000038743019, -0.06780000030994415, -0.051600001752376556, -0.006300000008195639, 0.04639999940991402, 0.009700000286102295, -0.181099995970726, -0.036400001496076584, 0.03779999911785126, -0.062199998646974564, -0.05350000038743019, 0.1387999951839447, 0.1168999969959259, -0.2379000037908554, -0.07909999787807465, 0.07729999721050262, -0.03150000050663948, 0.013199999928474426, -0.00430000014603138, 0.20319999754428864, 0.06279999762773514, -0.12409999966621399, 0.031099999323487282, -0.11270000040531158, -0.013899999670684338, -0.11640000343322754, 0.08579999953508377, 0.0738999992609024, 0.17030000686645508, -0.05480000004172325, -0.07959999889135361, 0.11020000278949738, 0.10040000081062317, 0.0729999989271164, 0.12919999659061432, 0.020999999716877937], [0.17739999294281006, -0.15770000219345093, -0.22920000553131104, -0.09309999644756317, -0.10819999873638153, 0.055399999022483826, 0.03720000013709068, -0.11729999631643295, -0.06440000236034393, 0.02759999968111515, 0.17870000004768372, 0.026100000366568565, -0.11309999972581863, 0.0949999988079071, 0.0071000000461936, -0.041999999433755875, 0.21170000731945038, 0.020999999716877937, -0.041999999433755875, -0.14059999585151672, -0.052299998700618744, -0.029100000858306885, -0.10909999907016754, -0.00019999999494757503, 0.04830000177025795, 0.16779999434947968, -0.12210000306367874, -0.17520000040531158, 0.07360000163316727, -0.120899997651577, -0.14390000700950623, -0.07850000262260437, 0.12070000171661377, 0.00989999994635582, -0.1128000020980835, 0.03290000185370445, 0.041200000792741776, 0.019200000911951065, 0.037300001829862595, 0.1459999978542328, -0.16359999775886536, 0.1746000051498413, -0.0010000000474974513, 0.023399999365210533, -0.0794999971985817, -0.009200000204145908, 0.09510000050067902, -0.035999998450279236, 0.10260000079870224, 0.011599999852478504, -0.02669999934732914, -0.011599999852478504, 0.006599999964237213, 0.18389999866485596, -0.07010000199079514, -0.20270000398159027, 0.012600000016391277, -0.0989999994635582, 0.1923999935388565, 0.014100000262260437, 0.0649000033736229, 0.12210000306367874, -0.0794999971985817, 0.1987999975681305, -0.018699999898672104, -0.06780000030994415, -0.024800000712275505, -0.009600000455975533, -0.08799999952316284, -0.1282999962568283, -0.11079999804496765, -0.02850000001490116, -0.17589999735355377, -0.02329999953508377, -0.06270000338554382, -0.057999998331069946, -0.10490000247955322, 0.017500000074505806, 0.0851999968290329, 0.03280000016093254, 0.1298999935388565, 0.058800000697374344, 0.10260000079870224, 0.1509000062942505, -0.00930000003427267, 0.05310000106692314, 0.05700000002980232, -0.10830000042915344, 0.1054999977350235, 0.10220000147819519, 0.048500001430511475, -0.2563999891281128, 0.08959999680519104, 0.039799999445676804, -0.23469999432563782, 0.032600000500679016, -0.09790000319480896, -0.12470000237226486, -0.05220000073313713, -0.0210999995470047, -0.006800000090152025, 0.19789999723434448, -0.06859999895095825, -0.005900000222027302, -0.05460000038146973, 0.18019999563694, 0.037700001150369644, 0.1606999933719635, 0.050599999725818634, -0.12240000069141388, 0.031199999153614044, 0.044599998742341995, -0.002899999963119626, 0.1973000019788742, -0.0820000022649765, 0.05550000071525574, -0.027899999171495438, 0.04390000179409981, -0.19740000367164612, -0.08370000123977661, 0.013799999840557575, 0.11129999905824661, 0.01080000028014183, 0.00989999994635582, 0.07989999651908875, 0.11599999666213989, -0.020600000396370888, 0.010400000028312206], [0.015799999237060547, -0.052000001072883606, -0.060499999672174454, -0.18150000274181366, 0.21649999916553497, -0.17139999568462372, 0.066600002348423, -0.03840000182390213, -0.08619999885559082, 0.10930000245571136, -0.009600000455975533, 0.07090000063180923, 0.09390000253915787, 0.041999999433755875, 0.15049999952316284, -0.031700000166893005, -0.028999999165534973, -0.09380000084638596, 0.08399999886751175, 0.062199998646974564, 0.038100000470876694, -0.08529999852180481, 0.08560000360012054, -0.15469999611377716, -0.11309999972581863, 0.017799999564886093, 0.03830000013113022, -0.20669999718666077, 0.09480000287294388, 0.11649999767541885, 0.07339999824762344, -0.16979999840259552, 0.022199999541044235, 0.17599999904632568, -0.03220000118017197, 0.01979999989271164, -0.18449999392032623, 0.024299999698996544, -0.05469999834895134, -0.16169999539852142, 0.08190000057220459, -0.014800000004470348, -0.0008999999845400453, -0.007000000216066837, 0.01679999940097332, 0.006000000052154064, 0.08919999748468399, 0.11580000072717667, -0.14249999821186066, -0.03519999980926514, -0.039000000804662704, -0.029400000348687172, 0.0697999969124794, -0.08869999647140503, -0.07000000029802322, 0.08429999649524689, 0.05869999900460243, 0.11460000276565552, -0.03099999949336052, 0.04729999974370003, 0.031300000846385956, 0.10899999737739563, 0.21240000426769257, -0.0052999998442828655, -0.00019999999494757503, -0.026399999856948853, -0.03720000013709068, -0.0035000001080334187, -0.20360000431537628, -0.11050000041723251, -0.06830000132322311, 0.05559999868273735, 0.05770000070333481, 0.030700000002980232, -0.10320000350475311, 0.06340000033378601, -0.06019999831914902, -0.030500000342726707, 0.020099999383091927, 0.11180000007152557, 0.014999999664723873, -0.00279999990016222, 0.11180000007152557, -0.2231999933719635, -0.13249999284744263, -0.07689999788999557, 0.1485999971628189, -0.08410000056028366, 0.15520000457763672, 0.08810000121593475, -0.06289999932050705, -0.1395999938249588, 0.07989999651908875, 0.008299999870359898, 0.1298000067472458, 0.008799999952316284, -0.004399999976158142, 0.0835999995470047, 0.13429999351501465, 0.03610000014305115, 0.03660000115633011, -0.11249999701976776, -0.06560000032186508, 0.10610000044107437, 0.024399999529123306, 0.09640000015497208, -0.09109999984502792, -0.06689999997615814, -0.01510000042617321, 0.12710000574588776, -0.019300000742077827, 0.13660000264644623, -0.06549999862909317, -0.026499999687075615, -0.049300000071525574, 0.07440000027418137, 0.016100000590085983, 0.054499998688697815, 0.03999999910593033, 0.10300000011920929, 0.09769999980926514, -0.10769999772310257, -0.02979999966919422, -0.00019999999494757503, -0.011099999770522118, 0.09470000118017197, 0.04089999943971634, -0.001500000013038516], [-0.038100000470876694, 0.04259999841451645, -0.02449999935925007, -0.08229999989271164, -0.1459999978542328, 0.10890000313520432, 0.10980000346899033, 0.1256999969482422, -0.16609999537467957, -0.0794999971985817, -0.021400000900030136, -0.048500001430511475, -0.05860000103712082, -0.03359999880194664, -0.005400000140070915, 0.03830000013113022, -0.2184000015258789, -0.00039999998989515007, 0.12999999523162842, 0.11400000005960464, -0.04540000110864639, 0.11949999630451202, 0.09960000216960907, -0.010099999606609344, 0.08579999953508377, 0.11180000007152557, 0.03310000151395798, -0.014100000262260437, 0.042899999767541885, -0.09910000115633011, 0.1370999962091446, -0.042100001126527786, -0.033799998462200165, 0.1664000004529953, 0.02889999933540821, -0.05220000073313713, 0.009399999864399433, -0.061000000685453415, 0.0414000004529953, 0.13860000669956207, -0.08290000259876251, 0.10869999974966049, 0.026499999687075615, 0.12049999833106995, -0.09189999848604202, 0.007000000216066837, 0.15070000290870667, 0.08309999853372574, -0.05730000138282776, -0.07599999755620956, 0.10450000315904617, 0.013299999758601189, 0.004999999888241291, 0.013000000268220901, 0.05660000070929527, -0.008500000461935997, -0.01730000041425228, 0.13699999451637268, 0.043299999088048935, -0.10369999706745148, 0.1266999989748001, 0.05050000175833702, 0.008799999952316284, 0.09040000289678574, 0.09600000083446503, 0.05570000037550926, 0.07169999927282333, -0.012900000438094139, -0.022299999371170998, 0.08330000191926956, 0.2215999960899353, -0.15379999577999115, 0.08070000261068344, -0.03739999979734421, -0.004100000020116568, -0.07400000095367432, -0.08649999648332596, 0.06319999694824219, 0.07760000228881836, 0.16769999265670776, -0.007499999832361937, -0.008200000040233135, -0.13030000030994415, 0.00559999980032444, -0.04580000042915344, 0.024399999529123306, -0.006099999882280827, -0.07100000232458115, -0.012199999764561653, 0.07329999655485153, 0.11699999868869781, 0.03959999978542328, 0.18539999425411224, -0.09269999712705612, -0.05829999968409538, -0.1712999939918518, -0.05810000002384186, -0.06440000236034393, -0.028699999675154686, 0.03579999879002571, 0.01679999940097332, 0.09040000289678574, 0.1103999987244606, 0.0333000011742115, -0.006099999882280827, -0.044599998742341995, -0.08269999921321869, -0.04560000076889992, -0.06719999760389328, -0.08919999748468399, 0.11479999870061874, -0.1859000027179718, -0.1720999926328659, -0.15929999947547913, 0.06509999930858612, 0.02850000001490116, 0.12479999661445618, 0.1745000034570694, 0.11079999804496765, -0.015699999406933784, -0.03009999915957451, 0.014600000344216824, -0.1387999951839447, 0.14399999380111694, -0.16060000658035278, -0.020800000056624413, -0.04010000079870224, 0.04969999939203262], [0.0430000014603138, -0.023399999365210533, -0.16140000522136688, 0.06960000097751617, 0.05380000174045563, -0.06159999966621399, 0.0478999987244606, 0.029600000008940697, -0.011500000022351742, 0.046300001442432404, 0.14300000667572021, 0.11159999668598175, 0.17260000109672546, 0.17069999873638153, -0.07660000026226044, -0.006200000178068876, -0.14489999413490295, 0.008100000210106373, -0.060499999672174454, 0.007899999618530273, -0.022700000554323196, 0.09839999675750732, 0.02070000022649765, -0.17839999496936798, 0.12800000607967377, 0.04569999873638153, 0.04479999840259552, -0.03189999982714653, 0.07500000298023224, 0.0027000000700354576, 0.06340000033378601, -0.11720000207424164, -0.14560000598430634, 0.07450000196695328, -0.015399999916553497, -0.045099999755620956, 0.004900000058114529, -0.010900000110268593, -0.12600000202655792, 0.1006999984383583, -0.07370000332593918, -0.027799999341368675, -0.09520000219345093, 0.08489999920129776, 0.0658000037074089, -0.03020000085234642, -0.08720000088214874, 0.00139999995008111, -0.014299999922513962, 0.03269999846816063, -0.04650000110268593, -0.2281000018119812, 0.015300000086426735, -0.03680000081658363, -0.050599999725818634, -0.010499999858438969, -0.11620000004768372, -0.05310000106692314, -0.013299999758601189, 0.2386000007390976, 0.06350000202655792, 0.024399999529123306, -0.08749999850988388, -0.07169999927282333, -0.021400000900030136, -0.11649999767541885, 0.006800000090152025, 0.07530000060796738, 0.1216999962925911, -0.20239999890327454, -0.0340999998152256, -0.012400000356137753, -0.09440000355243683, -0.01640000008046627, 0.004999999888241291, 0.11500000208616257, -0.09120000153779984, -0.06710000336170197, 0.12470000237226486, -0.1396999955177307, -0.0934000015258789, 0.20579999685287476, 0.04670000076293945, 0.27970001101493835, -0.20669999718666077, 0.10130000114440918, -0.1688999980688095, -0.11879999935626984, -0.09740000218153, 0.03779999911785126, 0.1444000005722046, -0.01759999990463257, -0.009200000204145908, -0.010400000028312206, -0.040800001472234726, 0.13819999992847443, -0.0835999995470047, 0.050700001418590546, 0.09629999846220016, -0.16680000722408295, 0.06069999933242798, -0.17949999868869781, 0.032499998807907104, -0.00800000037997961, -0.05009999871253967, -0.12939999997615814, -0.026100000366568565, -0.009100000374019146, -0.0982000008225441, 0.09440000355243683, -0.028599999845027924, 0.02410000003874302, 0.0714000016450882, 0.04439999908208847, 0.11479999870061874, 0.057500001043081284, 0.11429999768733978, -0.007400000002235174, 0.21879999339580536, -0.1573999971151352, -0.11299999803304672, -0.04769999906420708, 0.08839999884366989, 0.057100001722574234, -0.007400000002235174, 0.12300000339746475, -0.004100000020116568, 0.05689999833703041], [-0.006000000052154064, 0.14149999618530273, -0.06019999831914902, 0.0007999999797903001, -0.1006999984383583, 0.08020000159740448, -0.0052999998442828655, 0.08590000122785568, -0.0617000013589859, -0.07519999891519547, 0.10790000110864639, -0.058400001376867294, 0.19699999690055847, 0.002899999963119626, -0.08049999922513962, 0.0340999998152256, 0.04280000180006027, -0.06599999964237213, 9.999999747378752e-05, -0.03700000047683716, 0.07919999957084656, -0.07370000332593918, 0.007600000128149986, 0.01979999989271164, 0.03220000118017197, -0.0551999993622303, -0.009200000204145908, 0.12120000272989273, -0.08299999684095383, 0.14910000562667847, 0.11559999734163284, -0.18690000474452972, 0.003599999938160181, 0.002300000051036477, 0.04390000179409981, -0.03240000084042549, 0.16899999976158142, 0.05999999865889549, 0.16580000519752502, -0.023399999365210533, 0.033900000154972076, -0.10750000178813934, 0.009200000204145908, 0.11469999700784683, -0.06520000100135803, 0.003100000089034438, -0.09719999879598618, 0.062199998646974564, -0.004399999976158142, -0.12720000743865967, 0.027799999341368675, -0.02979999966919422, -0.08320000022649765, 0.06939999759197235, -0.1429000049829483, 0.1459999978542328, -0.033799998462200165, -0.024000000208616257, 0.12319999933242798, 0.06830000132322311, 0.08380000293254852, 0.09359999746084213, 0.05310000106692314, -0.03280000016093254, 0.12919999659061432, -0.05889999866485596, -0.012799999676644802, -0.04050000011920929, -0.06199999898672104, 0.12049999833106995, 0.15410000085830688, 0.14229999482631683, -0.07180000096559525, -0.1527000069618225, -0.11649999767541885, -0.25780001282691956, 0.014700000174343586, -0.1290999948978424, -0.11159999668598175, -0.053700000047683716, 0.12880000472068787, -0.0340999998152256, -0.07509999722242355, -0.07159999758005142, -0.018400000408291817, -0.006200000178068876, 0.06270000338554382, 0.0763000026345253, -0.022299999371170998, 0.0640999972820282, -0.0013000000035390258, 0.008700000122189522, 0.04100000113248825, -0.03660000115633011, -0.1972000002861023, -0.055399999022483826, -0.16210000216960907, 0.13860000669956207, 0.003599999938160181, -0.08320000022649765, -0.022199999541044235, -0.029200000688433647, -0.07680000364780426, -0.017799999564886093, -0.09019999951124191, 0.05660000070929527, 0.06210000067949295, 0.08489999920129776, 0.005100000184029341, 0.09459999948740005, 0.007499999832361937, 0.05490000173449516, 0.17149999737739563, 0.0071000000461936, 0.14839999377727509, 0.05990000069141388, -0.1307000070810318, -0.0575999990105629, 0.0820000022649765, 0.12349999696016312, -0.07779999822378159, 0.016699999570846558, 0.00039999998989515007, 0.17910000681877136, -0.10700000077486038, -0.024700000882148743, 0.1005999967455864, 0.09149999916553497], [-0.07029999792575836, 0.06509999930858612, -0.06509999930858612, -0.06970000267028809, 0.1266999989748001, -0.00989999994635582, -0.01679999940097332, 0.029899999499320984, 0.11829999834299088, -0.0066999997943639755, -0.022299999371170998, -0.07739999890327454, -0.1451999992132187, -0.0071000000461936, 0.06440000236034393, -0.03420000150799751, 0.027499999850988388, 0.017999999225139618, 0.2070000022649765, 0.09960000216960907, -0.012900000438094139, -0.04769999906420708, -0.1559000015258789, -0.07599999755620956, 0.1981000006198883, -0.22280000150203705, -0.04560000076889992, -0.04690000042319298, -0.12939999997615814, 0.01899999938905239, -0.030400000512599945, 0.12380000203847885, -0.002400000113993883, 0.14890000224113464, -0.08630000054836273, -0.053300000727176666, -0.17790000140666962, 0.05590000003576279, -0.2110999971628189, 0.04969999939203262, 0.03830000013113022, -0.08630000054836273, -0.007000000216066837, 0.07890000194311142, -0.04540000110864639, -0.14869999885559082, 0.1615999937057495, 0.0035000001080334187, 0.14990000426769257, 0.008700000122189522, 0.04479999840259552, 0.037700001150369644, -0.07349999994039536, -0.014299999922513962, -0.09380000084638596, -0.024900000542402267, 0.020899999886751175, 0.019099999219179153, 0.07590000331401825, -0.11630000174045563, 0.03189999982714653, -0.07750000059604645, 0.0071000000461936, -0.15199999511241913, 0.1054999977350235, 0.04170000180602074, 0.020800000056624413, 0.09730000048875809, -0.09099999815225601, 0.00139999995008111, -0.09830000251531601, 0.03319999948143959, -0.05420000106096268, -0.04729999974370003, 0.046799998730421066, -0.04360000044107437, 0.02800000086426735, 0.040800001472234726, -0.09560000151395798, -0.061500001698732376, 0.1005999967455864, -0.10750000178813934, -0.004800000227987766, -0.05290000140666962, -0.13130000233650208, 0.12309999763965607, 0.009200000204145908, 0.0026000000070780516, 0.01600000075995922, 0.007799999788403511, 0.06689999997615814, -0.20819999277591705, 0.006200000178068876, 0.004900000058114529, -0.1347000002861023, 0.08969999849796295, -0.050999999046325684, 0.021400000900030136, -0.07370000332593918, 0.004399999976158142, -0.2045000046491623, 0.005900000222027302, 0.05079999938607216, -0.03579999879002571, 0.040800001472234726, -0.0812000036239624, 0.15629999339580536, 0.1737000048160553, -9.999999747378752e-05, 0.07010000199079514, -0.021400000900030136, -0.07760000228881836, 0.14090000092983246, -0.1151999980211258, -0.039900001138448715, 0.023600000888109207, 0.09380000084638596, 0.10199999809265137, 0.02250000089406967, -0.000699999975040555, 0.015599999576807022, -0.02199999988079071, -0.12960000336170197, -0.1216999962925911, 0.13009999692440033, -0.13609999418258667, 0.07370000332593918, 0.03629999980330467], [0.014100000262260437, -0.08349999785423279, 0.0908999964594841, 0.09669999778270721, -0.1120000034570694, -0.06930000334978104, -0.12439999729394913, -0.1379999965429306, 0.07989999651908875, -0.0803999975323677, 0.02710000053048134, 0.017899999395012856, -0.07959999889135361, -0.05889999866485596, -0.08820000290870667, 0.09989999979734421, -0.05169999971985817, -0.04910000041127205, 0.08089999854564667, -0.04740000143647194, 0.04659999907016754, -0.0015999999595806003, -0.13169999420642853, 0.09160000085830688, 0.043699998408555984, 0.09300000220537186, 0.1469999998807907, 0.243599995970726, -0.08100000023841858, 0.015200000256299973, -0.05180000141263008, -0.1395999938249588, -0.001500000013038516, -0.003100000089034438, -0.06880000233650208, 0.05090000107884407, 0.11640000343322754, -0.11249999701976776, -0.12120000272989273, 0.11890000104904175, 0.06989999860525131, 0.15189999341964722, 0.024000000208616257, 0.07339999824762344, -0.03240000084042549, 0.05649999901652336, 0.1477999985218048, -0.10279999673366547, -0.008700000122189522, 0.0210999995470047, 0.06830000132322311, -0.05510000139474869, 0.03700000047683716, 0.19280000030994415, 0.009399999864399433, 0.06970000267028809, -0.10300000011920929, 0.0017999999690800905, 0.006599999964237213, -0.12559999525547028, -0.11580000072717667, 0.19089999794960022, -0.03060000017285347, -0.06360000371932983, 0.09449999779462814, -0.03460000082850456, -0.1500999927520752, 0.20640000700950623, 0.0820000022649765, 0.0019000000320374966, -0.010599999688565731, 0.09260000288486481, 0.1274999976158142, 0.1298999935388565, -0.011099999770522118, -0.12939999997615814, 0.06949999928474426, -0.1356000006198883, 0.1103999987244606, -0.0203000009059906, -0.0940999984741211, -0.15379999577999115, -0.03530000150203705, -0.0071000000461936, -0.05999999865889549, 0.1453000009059906, 0.02979999966919422, 0.11580000072717667, -0.002899999963119626, -0.1395999938249588, 0.04639999940991402, 0.08100000023841858, 0.07000000029802322, 0.1316000074148178, 0.07999999821186066, 0.023000000044703484, -0.14499999582767487, 0.09489999711513519, -0.08969999849796295, 0.032600000500679016, 0.025200000032782555, -0.16619999706745148, 0.31790000200271606, 0.14659999310970306, 0.13860000669956207, -0.03139999881386757, -0.18809999525547028, -0.053199999034404755, -0.11140000075101852, -0.02590000070631504, 0.18060000240802765, 0.13819999992847443, 0.03999999910593033, 0.022700000554323196, 0.13019999861717224, 0.11029999703168869, -0.093299999833107, -0.051100000739097595, 0.0746999979019165, 0.032099999487400055, -0.025699999183416367, -0.06360000371932983, 0.1306000053882599, 0.10379999876022339, -0.08219999819993973, 0.11599999666213989, -0.08489999920129776, -0.07209999859333038], [0.052299998700618744, 0.05640000104904175, -0.030300000682473183, -0.03720000013709068, -0.060600001364946365, 0.03739999979734421, -0.009700000286102295, -0.08470000326633453, -0.058400001376867294, -9.999999747378752e-05, 0.05849999934434891, -0.2386000007390976, 0.11620000004768372, 0.10920000076293945, 0.06440000236034393, 0.10090000182390213, 0.06440000236034393, 0.09870000183582306, -0.16349999606609344, 0.06080000102519989, 0.07339999824762344, 0.048700001090765, -0.05810000002384186, 0.10189999639987946, 0.025100000202655792, -0.020899999886751175, -0.10289999842643738, 0.04729999974370003, -0.009399999864399433, 0.0017999999690800905, -0.052000001072883606, -0.03319999948143959, 0.012500000186264515, 0.05640000104904175, -0.12929999828338623, -0.07609999924898148, -0.07859999686479568, -0.046300001442432404, -0.09109999984502792, -0.020899999886751175, 0.08449999988079071, 0.23549999296665192, -0.20200000703334808, -0.10419999808073044, 0.06159999966621399, 0.021400000900030136, 0.13930000364780426, 0.015300000086426735, 0.09080000221729279, 0.05260000005364418, -0.13050000369548798, 0.056299999356269836, 0.00800000037997961, 0.020800000056624413, 0.055799998342990875, 0.04230000078678131, -0.06319999694824219, -0.07500000298023224, -0.04439999908208847, 0.025800000876188278, -0.08609999716281891, 0.14190000295639038, 0.1316000074148178, 0.11990000307559967, 0.09220000356435776, -0.026399999856948853, -0.07769999653100967, 0.0357000008225441, 0.053199999034404755, 0.11129999905824661, 0.1348000019788742, -0.08410000056028366, 0.033399999141693115, 0.03819999843835831, 0.052299998700618744, 0.027699999511241913, 0.04749999940395355, 0.019899999722838402, -0.06880000233650208, 0.05770000070333481, 0.004399999976158142, -0.006899999920278788, 0.13030000030994415, 0.004100000020116568, -0.0031999999191612005, 0.14489999413490295, -0.09099999815225601, 0.014800000004470348, 0.022299999371170998, -0.06040000170469284, -0.10270000249147415, 0.1876000016927719, -0.02669999934732914, -0.13979999721050262, -0.08879999816417694, -0.12330000102519989, -0.22179999947547913, 0.2289000004529953, -0.09830000251531601, -0.05550000071525574, -0.06469999998807907, -0.03500000014901161, 0.006200000178068876, -0.08</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>[0.714610037299822]</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>[0.06514500455316456]</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>[0.6923231552848566]</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>[0.07024363004299519]</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>[-2.9579451670930474]</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>[1.2953550853068527]</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>[0.8489112669824683]</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>[0.03470796371393567]</t>
+        </is>
+      </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>[0.6041374130678876]</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>[0.09388317771771132]</t>
+        </is>
+      </c>
+      <c r="O29" t="inlineStr">
+        <is>
+          <t>[-0.9670039364394654]</t>
+        </is>
+      </c>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>[0.6466475156726956]</t>
+        </is>
+      </c>
+      <c r="Q29" t="inlineStr">
+        <is>
+          <t>[-0.17347188737557495]</t>
+        </is>
+      </c>
+      <c r="R29" t="inlineStr">
+        <is>
+          <t>[0.12653046172912566]</t>
+        </is>
+      </c>
+      <c r="S29" t="inlineStr">
+        <is>
+          <t>[-0.06881448196868956]</t>
+        </is>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>[0.09005867139036196]</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>[-1.0502938673961641]</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>[0.1960555182072824]</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>[-0.19784677669409856]</t>
+        </is>
+      </c>
+      <c r="X29" t="inlineStr">
+        <is>
+          <t>[0.12548717524897357]</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>[-0.15518079111330962]</t>
+        </is>
+      </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>[0.09506353508681635]</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>[-2.0881087070432236]</t>
+        </is>
+      </c>
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>[0.2841195095020772]</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>[-1.0165264874398132]</t>
+        </is>
+      </c>
+      <c r="AD29" t="inlineStr">
+        <is>
+          <t>[0.1689767958527664]</t>
+        </is>
+      </c>
+      <c r="AE29" t="inlineStr">
+        <is>
+          <t>[-1.0118629192685846]</t>
+        </is>
+      </c>
+      <c r="AF29" t="inlineStr">
+        <is>
+          <t>[0.21663352446897904]</t>
+        </is>
+      </c>
+      <c r="AG29" t="inlineStr">
+        <is>
+          <t>[-3.6189793144503497]</t>
+        </is>
+      </c>
+      <c r="AH29" t="inlineStr">
+        <is>
+          <t>[0.3438828180568527]</t>
+        </is>
+      </c>
+      <c r="AI29" t="inlineStr">
+        <is>
+          <t>[-1.467074631227483]</t>
+        </is>
+      </c>
+      <c r="AJ29" t="inlineStr">
+        <is>
+          <t>[0.20217401964691772]</t>
+        </is>
+      </c>
+      <c r="AK29" t="inlineStr">
+        <is>
+          <t>[-0.9453466210226371]</t>
+        </is>
+      </c>
+      <c r="AL29" t="inlineStr">
+        <is>
+          <t>[0.20648429097158652]</t>
+        </is>
+      </c>
+      <c r="AM29" t="inlineStr">
+        <is>
+          <t>[-3.6049112408569224]</t>
+        </is>
+      </c>
+      <c r="AN29" t="inlineStr">
+        <is>
+          <t>[0.3536905670804743]</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>model_128_64_3</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>[128, 64]</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>[[[0.025800000876188278, -0.06419999897480011, -0.005400000140070915, 0.029899999499320984, 0.02449999935925007, -0.04399999976158142, -0.07069999724626541, 0.009800000116229057, -0.008299999870359898, -0.02370000071823597, 0.05350000038743019, 0.012000000104308128, 0.05649999901652336, -0.08569999784231186, -0.01899999938905239, 0.1006999984383583, 0.043699998408555984, 0.05550000071525574, -0.012400000356137753, 0.024900000542402267, -0.02850000001490116, 0.019300000742077827, -0.030400000512599945, -0.006000000052154064, 0.017100000753998756, 0.026000000536441803, 0.024000000208616257, -0.00559999980032444, 0.03750000149011612, 0.023600000888109207, 0.04470000043511391, -0.11550000309944153, -0.05739999935030937, -0.038600001484155655, 0.09920000284910202, -0.01850000023841858, 0.06840000301599503, 0.01769999973475933, 0.0771000012755394, -9.999999747378752e-05, -0.06710000336170197, 0.0414000004529953, 0.03220000118017197, 0.006500000134110451, 9.999999747378752e-05, 0.05260000005364418, -0.08470000326633453, -0.0406000018119812, -0.024700000882148743, 0.05829999968409538, 0.020400000736117363, 0.018699999898672104, 0.021900000050663948, -0.09279999881982803, -0.046799998730421066, -0.05609999969601631, 0.025499999523162842, 0.016599999740719795, 0.04809999838471413, -0.06289999932050705, 0.06310000270605087, -0.032999999821186066, 0.0071000000461936, 0.06989999860525131, 0.03819999843835831, -0.040699999779462814, 0.04129999876022339, -0.031599998474121094, 0.039400000125169754, -0.06400000303983688, -0.03060000017285347, 0.08089999854564667, -0.13809999823570251, 0.01510000042617321, -0.051500000059604645, -0.1128000020980835, 0.018699999898672104, -0.013700000010430813, 0.04520000144839287, -0.012199999764561653, -0.02500000037252903, 0.019500000402331352, 0.045899998396635056, 0.03240000084042549, 0.011500000022351742, 0.0210999995470047, -0.015599999576807022, -0.021199999377131462, 0.041200000792741776, -0.023000000044703484, 0.0007999999797903001, -0.02669999934732914, 0.04479999840259552, -0.058400001376867294, -0.04749999940395355, 0.03579999879002571, 0.03180000185966492, 0.07940000295639038, -0.07440000027418137, -0.11640000343322754, 0.11949999630451202, 0.03220000118017197, 0.015200000256299973, 0.04619999974966049, -0.008299999870359898, -0.04989999905228615, 0.002899999963119626, 0.01940000057220459, 0.011099999770522118, 0.06419999897480011, -0.0649000033736229, -0.05299999937415123, -0.009700000286102295, -0.039400000125169754, 0.012799999676644802, 0.03830000013113022, -0.018300000578165054, -0.007300000172108412, -0.023900000378489494, -0.06970000267028809, 0.039799999445676804, 0.019999999552965164, 0.025699999183416367, 0.03280000016093254, -0.013299999758601189, -0.05979999899864197, 0.08389999717473984, -0.048700001090765], [0.0215000007301569, 0.0714000016450882, -0.023800000548362732, 0.11559999734163284, 0.05959999933838844, -0.016899999231100082, -0.015200000256299973, -0.050999999046325684, -0.02630000002682209, 0.05009999871253967, 0.008899999782443047, 0.006000000052154064, -0.01549999974668026, 0.05999999865889549, -0.055799998342990875, 0.05869999900460243, -0.013799999840557575, -0.020500000566244125, 0.042500000447034836, 0.008100000210106373, -0.06430000066757202, 0.00559999980032444, -0.0027000000700354576, -0.07729999721050262, -0.001500000013038516, 0.01679999940097332, 0.08209999650716782, 0.053300000727176666, 0.03139999881386757, 0.026599999517202377, 0.01730000041425228, 0.01119999960064888, -0.019500000402331352, -0.002199999988079071, -0.04170000180602074, -0.07919999957084656, 0.003800000064074993, 0.016200000420212746, -0.03350000083446503, -0.017500000074505806, 0.08669999986886978, -0.013700000010430813, -0.020099999383091927, 0.017500000074505806, -0.04659999907016754, 0.04100000113248825, -0.04569999873638153, 0.012400000356137753, 0.14239999651908875, -0.0272000003606081, 0.0003000000142492354, -0.027000000700354576, -0.0015999999595806003, 0.02930000051856041, -0.01209999993443489, -0.04610000178217888, -0.03189999982714653, -0.0203000009059906, 0.04839999973773956, 0.05180000141263008, -0.009399999864399433, -0.050999999046325684, -0.10329999774694443, 0.06289999932050705, 0.029999999329447746, -0.08190000057220459, -0.014299999922513962, 0.021800000220537186, 0.035999998450279236, 0.004999999888241291, 0.01759999990463257, 0.015300000086426735, -0.08780000358819962, 0.06729999929666519, 0.004399999976158142, -0.009700000286102295, -0.05640000104904175, 0.02199999988079071, 0.10300000011920929, -0.010300000198185444, 0.03709999844431877, 0.014700000174343586, 0.053300000727176666, 0.044199999421834946, -0.03009999915957451, -0.03319999948143959, 0.031700000166893005, -0.025299999862909317, -0.019300000742077827, -0.045099999755620956, 0.002400000113993883, 0.047200001776218414, -0.0658000037074089, -0.02710000053048134, -0.026499999687075615, 0.09220000356435776, 0.054999999701976776, -0.028699999675154686, 0.07129999995231628, -0.01759999990463257, 0.05429999902844429, 0.10840000212192535, 0.07039999961853027, -0.04899999871850014, 0.02239999920129776, 0.04479999840259552, -0.05180000141263008, 0.02019999921321869, 0.010700000450015068, 0.009800000116229057, 0.01860000006854534, -0.03420000150799751, -0.07530000060796738, 0.023399999365210533, 0.042100001126527786, 0.054099999368190765, -0.04600000008940697, -0.0658000037074089, -0.017100000753998756, -0.08380000293254852, 0.030500000342726707, -0.08150000125169754, 0.04179999977350235, 0.03660000115633011, 0.023600000888109207, -0.09610000252723694, 0.0357000008225441, 0.04580000042915344]], [[-0.01679999940097332, -0.06289999932050705, 0.021900000050663948, -0.14409999549388885, 0.006099999882280827, -0.08190000057220459, 0.010499999858438969, -0.07850000262260437, -0.0284000001847744, -0.1720000058412552, 0.033799998462200165, -0.11760000139474869, -0.05180000141263008, -0.1598999947309494, 0.03660000115633011, 0.09640000015497208, 0.019600000232458115, -0.14159999787807465, 0.00019999999494757503, 0.05460000038146973, 0.051500000059604645, 0.08739999681711197, -0.023499999195337296, -0.0551999993622303, -0.030500000342726707, 0.050999999046325684, 0.09440000355243683, 0.002099999925121665, -0.049800001084804535, 0.1273999959230423, -0.02239999920129776, -0.0340999998152256, -0.06830000132322311, 0.08889999985694885, -0.16660000383853912, 0.0005000000237487257, -0.1460999995470047, -0.17000000178813934, 0.026499999687075615, -0.11720000207424164, 0.12460000067949295, 0.17990000545978546, 0.050599999725818634, 0.09470000118017197, -0.05739999935030937, 0.05530000105500221, -0.10379999876022339, 0.16500000655651093, 0.04149999842047691, -0.049800001084804535, -0.1014999970793724, -0.11680000275373459, 0.15649999678134918, 0.07569999992847443, 0.04619999974966049, 0.04479999840259552, 0.025599999353289604, -0.11540000140666962, -0.04879999905824661, 0.031199999153614044, -0.05490000173449516, -0.08510000258684158, 0.00139999995008111, -0.09149999916553497, 0.05810000002384186, -0.06210000067949295, -0.035599999129772186, 0.024399999529123306, -0.15549999475479126, -0.003700000001117587, 0.1492999941110611, -0.012199999764561653, -0.011599999852478504, -0.19419999420642853, 0.08470000326633453, 0.05469999834895134, 0.03869999945163727, -0.06270000338554382, -0.008500000461935997, -0.07410000264644623, -0.053700000047683716, -0.0812000036239624, -0.013299999758601189, -0.15029999613761902, -0.04259999841451645, -0.15569999814033508, 0.00039999998989515007, 0.04619999974966049, 0.03889999911189079, 0.028599999845027924, -0.03539999946951866, 0.03220000118017197, 0.0674000009894371, -0.13840000331401825, 0.04039999842643738, -0.10339999943971634, 0.06080000102519989, 0.17679999768733978, -0.15230000019073486, 0.11940000206232071, -0.03319999948143959, 0.1647000014781952, -0.17170000076293945, -0.04100000113248825, -0.08009999990463257, 0.045899998396635056, 0.04179999977350235, 0.08020000159740448, -0.02630000002682209, -0.008999999612569809, -0.03700000047683716, -0.09619999676942825, 0.009499999694526196, -0.02239999920129776, 0.04839999973773956, 0.22280000150203705, -0.04529999941587448, 0.014999999664723873, 0.19040000438690186, 0.11919999867677689, -0.017400000244379044, 0.03739999979734421, -0.09920000284910202, 0.01730000041425228, -0.0006000000284984708, -0.020600000396370888, 0.0786999985575676, -0.021900000050663948], [0.035100001841783524, 0.006200000178068876, 0.05950000137090683, 0.004999999888241291, -0.021900000050663948, -0.07540000230073929, -0.034699998795986176, -0.014100000262260437, 0.0024999999441206455, -0.09399999678134918, 0.05429999902844429, 0.1543000042438507, -0.049300000071525574, 0.11079999804496765, -0.05220000073313713, 0.0738999992609024, 0.07169999927282333, 0.05920000001788139, -0.07840000092983246, -0.05640000104904175, 0.14239999651908875, -0.2888999879360199, 0.01759999990463257, -0.07119999825954437, 0.15139999985694885, 0.022199999541044235, 0.09239999949932098, -0.026000000536441803, -0.006399999838322401, -0.06769999861717224, -0.14190000295639038, -0.015599999576807022, 0.00570000009611249, -0.017899999395012856, -0.04390000179409981, -0.10890000313520432, -0.020400000736117363, -0.01489999983459711, 0.06030000001192093, 0.04089999943971634, -0.07739999890327454, -0.2273000031709671, -0.15369999408721924, 0.012400000356137753, 0.0851999968290329, -0.04560000076889992, -0.12030000239610672, 0.0723000019788742, -0.026799999177455902, -0.10450000315904617, -0.11389999836683273, -0.07259999960660934, 0.125, 0.1785999983549118, 0.05779999867081642, 0.027300000190734863, -0.008700000122189522, 0.08699999749660492, -0.07000000029802322, -0.0737999975681305, -0.018699999898672104, 0.04540000110864639, -0.10779999941587448, -0.03849999979138374, 0.18930000066757202, -0.09700000286102295, -0.0794999971985817, -0.15620000660419464, -0.13429999351501465, -0.06920000165700912, 0.027300000190734863, 0.061000000685453415, -0.03290000185370445, -0.08290000259876251, 0.11050000041723251, 0.08640000224113464, 0.038100000470876694, 0.07329999655485153, -0.04190000146627426, 0.0272000003606081, -0.008299999870359898, 0.052400000393390656, 0.13030000030994415, -0.013199999928474426, 0.05400000140070915, -0.2102999985218048, -0.0568000003695488, 0.029100000858306885, -0.07940000295639038, -0.1234000027179718, 0.0215000007301569, 0.04540000110864639, -0.09210000187158585, 0.08209999650716782, 0.11349999904632568, -0.00139999995008111, -0.04580000042915344, -0.11550000309944153, -0.002099999925121665, -0.033900000154972076, 0.07970000058412552, -0.16009999811649323, -0.008299999870359898, 0.15000000596046448, 0.15129999816417694, 0.1039000004529953, -0.12759999930858612, 0.041999999433755875, 0.003800000064074993, 0.006300000008195639, 0.008999999612569809, -0.09549999982118607, -0.05950000137090683, -0.033799998462200165, 0.09319999814033508, 0.03620000183582306, 0.07680000364780426, -0.051100000739097595, 0.06459999829530716, -0.2125999927520752, 0.0010999999940395355, -0.05689999833703041, -0.017100000753998756, -0.13349999487400055, 0.04270000010728836, 0.07940000295639038, 0.019999999552965164, -0.02710000053048134], [0.03240000084042549, -0.04490000009536743, 0.01759999990463257, 0.061500001698732376, -0.12150000035762787, 0.04340000078082085, -0.0658000037074089, 0.13819999992847443, 0.07519999891519547, -0.0934000015258789, -0.0560000017285347, 0.02160000056028366, 0.10809999704360962, -0.08510000258684158, -0.22849999368190765, -0.08460000157356262, -0.07010000199079514, -0.0, -0.012000000104308128, -0.050599999725818634, 0.031199999153614044, -0.06040000170469284, 0.08980000019073486, -0.14820000529289246, -0.0006000000284984708, 0.062199998646974564, -0.06669999659061432, 0.08489999920129776, -0.043699998408555984, -0.058400001376867294, 0.019300000742077827, 0.043699998408555984, 0.08449999988079071, -0.08500000089406967, -0.09529999643564224, 0.007899999618530273, -0.07159999758005142, 0.04580000042915344, 0.02759999968111515, -0.18440000712871552, 0.02370000071823597, 0.06459999829530716, -0.05609999969601631, 0.010999999940395355, 0.2313999980688095, -0.06939999759197235, -0.12150000035762787, 0.03189999982714653, -0.013799999840557575, 0.056299999356269836, -0.06639999896287918, 0.08799999952316284, -0.12479999661445618, -0.05730000138282776, -0.07209999859333038, 0.09669999778270721, 0.15530000627040863, -0.01889999955892563, -0.1264999955892563, -0.10790000110864639, 0.018200000748038292, 0.14970000088214874, 0.014499999582767487, 0.019500000402331352, -0.16019999980926514, 0.11840000003576279, 0.01119999960064888, 0.09179999679327011, -0.0681999996304512, -0.012299999594688416, 0.04360000044107437, 0.13359999656677246, 0.2687999904155731, -0.04989999905228615, 0.11410000175237656, -0.050700001418590546, 0.0917000025510788, 0.00930000003427267, -0.1103999987244606, 0.06319999694824219, 0.04089999943971634, 0.07779999822378159, -0.15029999613761902, 0.09679999947547913, 0.016699999570846558, 0.0032999999821186066, -0.06109999865293503, 0.07280000299215317, -0.042500000447034836, -0.061799999326467514, -0.0038999998942017555, 0.03500000014901161, 0.002199999988079071, -0.035100001841783524, -0.07180000096559525, -0.08259999752044678, 0.02850000001490116, -0.003599999938160181, 0.03139999881386757, 0.2565999925136566, 0.09179999679327011, 0.11339999735355377, 0.06880000233650208, 0.05979999899864197, -0.1316000074148178, 0.15389999747276306, -0.032099999487400055, -0.09380000084638596, 0.03709999844431877, 0.013199999928474426, -0.021299999207258224, -0.1665000021457672, -0.09969999641180038, -0.010700000450015068, 0.029200000688433647, -0.058400001376867294, -0.06430000066757202, -0.07029999792575836, -0.14110000431537628, 0.09629999846220016, 0.06610000133514404, 0.08510000258684158, -0.014700000174343586, -0.09239999949932098, 0.009200000204145908, 0.014100000262260437, -0.06499999761581421, -0.08269999921321869], [0.052400000393390656, 0.05849999934434891, -0.12860000133514404, 0.011300000362098217, -0.10040000081062317, 0.05900000035762787, 0.05590000003576279, -0.1088000014424324, 0.008100000210106373, -0.005400000140070915, -0.07000000029802322, -0.019200000911951065, -0.01769999973475933, -0.10639999806880951, -0.053599998354911804, -0.02669999934732914, -0.027899999171495438, -0.025800000876188278, 0.056299999356269836, -0.16130000352859497, -0.05310000106692314, -0.13809999823570251, -0.1469999998807907, -0.05920000001788139, 0.058800000697374344, -0.026000000536441803, 0.09960000216960907, -0.028599999845027924, -0.05920000001788139, 0.013500000350177288, -0.043699998408555984, -0.05779999867081642, 0.028300000354647636, 0.039799999445676804, 0.17180000245571136, -0.03819999843835831, 0.12240000069141388, -0.2468000054359436, 0.07689999788999557, -0.05609999969601631, 0.0794999971985817, 0.07159999758005142, 0.1534000039100647, -0.12359999865293503, -0.060600001364946365, 0.0746999979019165, -0.1265999972820282, 0.03150000050663948, -0.03370000049471855, 0.03959999978542328, 0.021800000220537186, 0.16539999842643738, -0.09269999712705612, -0.042100001126527786, 0.05290000140666962, 0.03280000016093254, 0.014000000432133675, -0.05640000104904175, 0.13289999961853027, 0.04899999871850014, 0.09200000017881393, 0.08389999717473984, -0.009499999694526196, 0.11209999769926071, 0.05380000174045563, -0.0478999987244606, -0.03009999915957451, -0.036400001496076584, -0.19200000166893005, 0.0828000009059906, 0.16920000314712524, 0.07540000230073929, 0.01510000042617321, 0.10949999839067459, -0.042399998754262924, 0.04410000145435333, -0.06639999896287918, -0.0038999998942017555, 0.08179999887943268, 0.01810000091791153, -0.0560000017285347, -0.027400000020861626, 0.08510000258684158, -0.08100000023841858, 0.07209999859333038, -0.0038999998942017555, -0.07670000195503235, 0.03449999913573265, -0.08630000054836273, 0.08860000222921371, 0.06419999897480011, -0.11079999804496765, -0.022099999710917473, -0.08259999752044678, 0.009399999864399433, -0.1096000000834465, 0.03550000116229057, -0.19259999692440033, -0.10109999775886536, -0.04769999906420708, -0.03200000151991844, -0.026499999687075615, 0.017000000923871994, -0.1356000006198883, -0.002400000113993883, -0.06480000168085098, -0.1136000007390976, -0.03460000082850456, -0.07989999651908875, 0.20839999616146088, 0.10029999911785126, -0.0568000003695488, 0.1193000003695488, 0.01679999940097332, 0.11330000311136246, -0.021199999377131462, 0.003700000001117587, -0.1306000053882599, -0.2660999894142151, 0.00800000037997961, 0.022199999541044235, -0.03009999915957451, -0.16189999878406525, -0.07980000227689743, -0.08370000123977661, -0.09000000357627869, 0.07530000060796738, 0.13519999384880066], [0.046300001442432404, 0.17960000038146973, -0.03240000084042549, 0.014700000174343586, 0.025100000202655792, 0.025800000876188278, 0.13120000064373016, -0.06210000067949295, 0.0885000005364418, 0.023600000888109207, 0.10170000046491623, 0.09560000151395798, -0.09070000052452087, 0.04619999974966049, -0.033799998462200165, -0.012299999594688416, -0.05119999870657921, 0.03929999843239784, -0.0210999995470047, -0.01940000057220459, 0.010499999858438969, 0.10849999636411667, 0.07649999856948853, 0.1177000030875206, -0.1273999959230423, 0.210099995136261, 0.025200000032782555, 0.07919999957084656, 0.06400000303983688, -0.11800000071525574, -0.08070000261068344, 0.006599999964237213, -0.06679999828338623, -0.11969999969005585, 0.07090000063180923, -0.026599999517202377, -0.10119999945163727, 0.014600000344216824, -0.06689999997615814, -0.10480000078678131, -0.09359999746084213, -0.01759999990463257, -0.10649999976158142, -0.10559999942779541, -0.06300000101327896, 0.015699999406933784, 0.04010000079870224, 0.12150000035762787, -0.2167000025510788, -0.08659999817609787, -0.06790000200271606, -0.0674000009894371, -0.007799999788403511, -0.07090000063180923, -0.008700000122189522, 0.03689999878406525, -0.0723000019788742, -0.0722000002861023, 0.21940000355243683, 0.01640000008046627, 0.023499999195337296, 0.18950000405311584, -0.05460000038146973, 0.03689999878406525, -0.08330000191926956, -0.16339999437332153, 0.05249999836087227, 0.11580000072717667, -0.04170000180602074, -0.21220000088214874, 0.033399999141693115, 0.041999999433755875, -0.010200000368058681, 0.06700000166893005, 0.13809999823570251, -0.009999999776482582, 0.04969999939203262, 0.07989999651908875, 0.15160000324249268, 0.050599999725818634, -0.10080000013113022, -0.014299999922513962, -0.13500000536441803, 0.03189999982714653, 0.0210999995470047, 0.12610000371932983, -0.10220000147819519, 0.04659999907016754, 0.08950000256299973, 0.03359999880194664, -0.09109999984502792, 0.0340999998152256, -0.11180000007152557, 0.15039999783039093, 0.09070000052452087, -0.0272000003606081, 0.08030000329017639, 0.10509999841451645, -0.014999999664723873, 0.04800000041723251, -0.013399999588727951, 0.03449999913573265, 0.02419999986886978, -0.12950000166893005, 0.14249999821186066, 0.07479999959468842, -0.0008999999845400453, 0.07900000363588333, 0.12680000066757202, 0.05550000071525574, -0.08829999715089798, -0.09950000047683716, 0.0421999990940094, 0.01940000057220459, -0.027300000190734863, 0.10320000350475311, 0.04600000008940697, 0.013500000350177288, -0.0010000000474974513, -0.03579999879002571, 0.06260000169277191, 0.012199999764561653, -0.0272000003606081, 0.12030000239610672, 0.15080000460147858, -0.18700000643730164, 0.14309999346733093, 0.020600000396370888], [0.1624000072479248, 0.13339999318122864, -0.014700000174343586, -0.13259999454021454, 0.08910000324249268, 0.07440000027418137, -0.020099999383091927, 0.013899999670684338, 0.1753000020980835, 0.06499999761581421, -0.16099999845027924, 0.020099999383091927, 0.21389999985694885, 0.0502999983727932, 0.0364999994635582, 0.03840000182390213, -0.08330000191926956, -0.04960000142455101, 0.10559999942779541, 0.014299999922513962, -0.06419999897480011, 0.05000000074505806, -0.08309999853372574, 0.10440000146627426, 0.02850000001490116, 0.14419999718666077, -0.053599998354911804, 0.08079999685287476, 0.10300000011920929, 0.021199999377131462, 0.03689999878406525, 0.11739999800920486, 0.01360000018030405, -0.05739999935030937, -0.001500000013038516, -0.07850000262260437, -0.06620000302791595, -0.06970000267028809, -0.04479999840259552, 0.11949999630451202, -0.1777999997138977, -0.0494999997317791, -0.00800000037997961, -0.034299999475479126, 0.043299999088048935, -0.0015999999595806003, -0.15489999949932098, 0.12630000710487366, 0.050700001418590546, 0.16940000653266907, -0.10679999738931656, 0.10130000114440918, 0.06260000169277191, -0.008500000461935997, -0.16009999811649323, 0.05609999969601631, -0.1378999948501587, 0.028300000354647636, 0.005400000140070915, -0.11860000342130661, -0.009399999864399433, -0.05820000171661377, -0.013100000098347664, -0.15039999783039093, -0.04569999873638153, 0.0471000000834465, -0.013199999928474426, 0.019200000911951065, 0.04600000008940697, 0.06780000030994415, -0.007400000002235174, -0.08179999887943268, 0.046300001442432404, 0.07819999754428864, 0.0778999999165535, -0.13359999656677246, 0.009499999694526196, 0.12790000438690186, -0.052000001072883606, 0.0012000000569969416, -0.02930000051856041, -0.0868000015616417, 0.10409999638795853, -0.049300000071525574, 0.03869999945163727, -0.012400000356137753, -0.026900000870227814, 0.20409999787807465, 0.08980000019073486, 0.14470000565052032, 0.10920000076293945, 0.09109999984502792, -0.06800000369548798, -0.1356000006198883, 0.13940000534057617, -0.08789999783039093, 0.02879999950528145, -0.10180000215768814, -0.1151999980211258, -0.09189999848604202, -0.002199999988079071, 0.04010000079870224, -0.05609999969601631, -0.04670000076293945, -0.008100000210106373, 0.034699998795986176, 0.03819999843835831, -0.05829999968409538, -0.13330000638961792, -0.09179999679327011, 0.1509000062942505, 0.06210000067949295, -0.01679999940097332, 0.0625, 0.02800000086426735, 0.0031999999191612005, -0.07760000228881836, 0.06360000371932983, 0.06350000202655792, -0.032999999821186066, -0.13359999656677246, -0.10029999911785126, -0.07069999724626541, -0.05429999902844429, 0.18299999833106995, 0.04659999907016754, -0.12269999831914902, -0.10360000282526016], [-0.1543000042438507, -0.038100000470876694, 0.062300000339746475, 0.05939999967813492, 0.03060000017285347, 0.1316000074148178, 0.0142000000923872, -0.039400000125169754, 0.10639999806880951, 0.04479999840259552, -0.014299999922513962, -0.028699999675154686, -0.1128000020980835, -0.1404000073671341, 0.08950000256299973, -0.06400000303983688, -0.013700000010430813, -0.07429999858140945, -0.1395999938249588, -0.0860000029206276, -0.09860000014305115, -0.08860000222921371, -0.06360000371932983, 0.03189999982714653, -0.007600000128149986, -0.12559999525547028, 0.04190000146627426, -0.23720000684261322, 0.03680000081658363, 0.1289999932050705, -0.04560000076889992, 0.001500000013038516, 0.048700001090765, -0.16050000488758087, -0.22529999911785126, -0.06199999898672104, -0.12099999934434891, -0.09830000251531601, 0.12530000507831573, 0.044199999421834946, -0.06970000267028809, 0.050700001418590546, -0.08990000188350677, -0.22419999539852142, 0.08659999817609787, 0.008999999612569809, -0.06599999964237213, 0.04170000180602074, -0.15330000221729279, -0.11490000039339066, -0.0210999995470047, 0.17239999771118164, 0.010300000198185444, -0.09049999713897705, -0.1290999948978424, -0.018799999728798866, -0.0044999998062849045, 0.11779999732971191, -0.02590000070631504, -0.03550000116229057, 0.01769999973475933, -0.17520000040531158, -0.025599999353289604, -0.050999999046325684, -0.09529999643564224, -0.11330000311136246, -0.10260000079870224, 0.0142000000923872, 0.07069999724626541, -0.0348999984562397, -0.049800001084804535, -0.021400000900030136, 0.03530000150203705, 0.05260000005364418, -0.1882999986410141, 0.11150000244379044, 0.03539999946951866, 0.05689999833703041, 0.12610000371932983, 9.999999747378752e-05, -0.043800000101327896, -0.06849999725818634, -0.043699998408555984, -0.037300001829862595, -0.05990000069141388, 0.009999999776482582, -0.04619999974966049, 0.04270000010728836, 0.13699999451637268, -0.01769999973475933, -0.026000000536441803, -0.0333000011742115, 0.1080000028014183, 0.18019999563694, 0.12080000340938568, -0.00559999980032444, -0.006399999838322401, -0.053300000727176666, 0.07479999959468842, 0.11869999766349792, -0.03539999946951866, 0.052400000393390656, 0.010999999940395355, 0.09529999643564224, 0.030400000512599945, 0.05420000106096268, 0.03590000048279762, 0.060100000351667404, -0.1632000058889389, 0.03060000017285347, -0.13130000233650208, 0.029600000008940697, -0.09279999881982803, 0.029600000008940697, -0.07500000298023224, -0.0763000026345253, -0.001500000013038516, 0.09120000153779984, 0.0032999999821186066, 0.02329999953508377, -0.14820000529289246, 0.1023000031709671, -0.052400000393390656, -0.10660000145435333, -0.11060000211000443, -0.0020000000949949026, 0.023900000378489494, 0.04619999974966049], [-0.017400000244379044, 0.12409999966621399, -0.10830000042915344, -0.006200000178068876, -0.1876000016927719, 0.09030000120401382, 0.008100000210106373, 0.07050000131130219, -0.008700000122189522, 0.006300000008195639, 0.006800000090152025, -0.16459999978542328, 0.007600000128149986, 0.08229999989271164, -0.04190000146627426, 0.12520000338554382, -0.03909999877214432, 0.15919999778270721, -0.08479999750852585, 0.057999998331069946, -0.030799999833106995, 0.181099995970726, 0.012799999676644802, 0.08399999886751175, -0.11800000071525574, 0.042500000447034836, -0.02759999968111515, -0.009399999864399433, 0.10159999877214432, 0.02630000002682209, 0.024399999529123306, -0.019200000911951065, 0.07900000363588333, -0.1216999962925911, -0.05810000002384186, 0.050700001418590546, 0.10559999942779541, -0.06440000236034393, -0.04529999941587448, 0.0357000008225441, -0.11389999836683273, 0.1404000073671341, -0.12630000710487366, -0.019300000742077827, 0.08320000022649765, 0.06430000066757202, -0.13979999721050262, -0.032099999487400055, 0.18279999494552612, 0.007600000128149986, -0.09269999712705612, -0.10109999775886536, 0.010900000110268593, 0.02669999934732914, 0.023399999365210533, 0.009600000455975533, -0.08320000022649765, 0.07129999995231628, -0.1306000053882599, -0.041099999099969864, 0.08640000224113464, 0.21209999918937683, 0.012199999764561653, 0.1347000002861023, 0.07109999656677246, -0.06989999860525131, -0.16680000722408295, 0.007300000172108412, -0.0044999998062849045, -0.08449999988079071, 0.05660000070929527, -0.09120000153779984, 0.02319999970495701, -0.09849999845027924, -0.01080000028014183, 0.17990000545978546, -0.19220000505447388, 0.008999999612569809, 0.013000000268220901, -0.08540000021457672, 0.0406000018119812, 0.09950000047683716, 0.042100001126527786, -0.08630000054836273, -0.14589999616146088, 0.10450000315904617, -0.041999999433755875, -0.06289999932050705, -0.053300000727176666, 0.00139999995008111, 0.2076999992132187, 0.10620000213384628, 0.08399999886751175, 0.013199999928474426, 0.11320000141859055, 0.023600000888109207, -0.06970000267028809, -0.07940000295639038, 0.021400000900030136, 0.05009999871253967, -0.050999999046325684, -0.03420000150799751, -0.006099999882280827, 0.1776999980211258, 0.015599999576807022, -0.09799999743700027, 0.06080000102519989, 0.06390000134706497, 0.040300000458955765, 0.09160000085830688, 0.07689999788999557, -0.0908999964594841, 0.09229999780654907, 0.12060000002384186, -0.09179999679327011, 0.06159999966621399, -0.18219999969005585, -0.045899998396635056, 0.024900000542402267, 0.0340999998152256, 0.04399999976158142, -0.06019999831914902, 0.10679999738931656, 0.007600000128149986, -0.13339999318122864, -0.051500000059604645, -0.02930000051856041, 0.044199999421834946], [-0.04360000044107437, -0.0674000009894371, 0.05339999869465828, 0.11349999904632568, 0.11240000277757645, -0.008299999870359898, 0.006899999920278788, 0.10260000079870224, 0.2639999985694885, 0.0012000000569969416, -0.020500000566244125, 0.0722000002861023, 0.1014999970793724, -0.11420000344514847, -0.19359999895095825, -0.07779999822378159, 0.15379999577999115, 0.04610000178217888, -0.10419999808073044, 0.156700000166893, 0.04960000142455101, 0.10589999705553055, 0.04960000142455101, 0.011300000362098217, -0.04740000143647194, -0.02329999953508377, 0.28139999508857727, -0.030700000002980232, 0.005499999970197678, 0.004100000020116568, 0.09279999881982803, -0.14489999413490295, 0.01679999940097332, 0.009100000374019146, -0.0210999995470047, -0.052299998700618744, 0.08309999853372574, -0.14499999582767487, -0.10649999976158142, -0.057500001043081284, -0.11100000143051147, 0.04619999974966049, 0.14650000631809235, 0.025699999183416367, -0.00430000014603138, -0.0044999998062849045, -0.1281999945640564, -0.0723000019788742, -0.030700000002980232, 0.03590000048279762, 0.09679999947547913, 0.07159999758005142, -0.014999999664723873, -0.05130000039935112, 0.10540000349283218, 0.04309999942779541, 0.029100000858306885, -0.061400000005960464, 0.09300000220537186, -0.011300000362098217, -0.13189999759197235, 0.07410000264644623, -0.06430000066757202, -0.10589999705553055, 0.03709999844431877, -0.04740000143647194, 0.11670000106096268, -0.06549999862909317, -0.013000000268220901, -0.032099999487400055, -0.12189999967813492, 0.04619999974966049, -0.052799999713897705, 0.10159999877214432, -0.07680000364780426, 0.02759999968111515, 0.03539999946951866, -0.06199999898672104, -0.01590000092983246, 0.016300000250339508, -0.07919999957084656, 0.026799999177455902, 0.08799999952316284, 0.08349999785423279, -0.1941000074148178, -0.1589999943971634, -0.0674000009894371, 0.13289999961853027, 0.15790000557899475, -0.09279999881982803, -0.055399999022483826, 0.03280000016093254, -0.05719999969005585, -0.08950000256299973, -0.09300000220537186, 0.02290000021457672, -0.0997999981045723, 0.025699999183416367, 0.17000000178813934, -0.006599999964237213, 0.004800000227987766, -0.07240000367164612, 0.018300000578165054, -0.024800000712275505, 0.00930000003427267, -0.09130000323057175, 0.03579999879002571, -0.09019999951124191, -0.12960000336170197, 0.0868000015616417, 0.018200000748038292, -0.10040000081062317, 0.14399999380111694, 0.06859999895095825, -0.024399999529123306, 0.07850000262260437, -0.08100000023841858, -0.058800000697374344, 0.12120000272989273, -0.10429999977350235, 0.004900000058114529, 0.004699999932199717, 0.15760000050067902, 0.030500000342726707, -0.0142000000923872, -0.050999999046325684, -0.03689999878406525, -0.08649999648332596], [0.1111999973654747, -0.1062999963760376, -0.028200000524520874, 0.09470000118017197, 0.1420000046491623, -0.016899999231100082, -0.00279999990016222, -0.004600000102072954, -0.014499999582767487, 0.04439999908208847, -0.007600000128149986, 0.009499999694526196, -0.0024999999441206455, 0.16779999434947968, 0.051899999380111694, -0.004999999888241291, 0.07900000363588333, -0.07900000363588333, 0.029999999329447746, 0.1768999993801117, -0.07460000365972519, 0.1281999945640564, -0.16529999673366547, 0.04390000179409981, 0.1753000020980835, 0.15449999272823334, 0.04430000111460686, -0.07620000094175339, -0.0803999975323677, -0.07880000025033951, -0.08389999717473984, 0.08380000293254852, 0.10100000351667404, 0.050999999046325684, -0.027400000020861626, 0.026200000196695328, 0.12639999389648438, 0.12129999697208405, 0.08649999648332596, -0.03849999979138374, -0.05290000140666962, -0.04820000007748604, 0.023099999874830246, 0.002199999988079071, -0.016499999910593033, 0.11110000312328339, -0.0357000008225441, 0.014999999664723873, 0.012799999676644802, -0.21690000593662262, -0.0, 0.0625, -0.03359999880194664, 0.10760000348091125, -0.015399999916553497, -0.00279999990016222, 0.0421999990940094, -0.032999999821186066, 0.06499999761581421, 0.13770000636577606, 0.02669999934732914, -0.017899999395012856, -0.02630000002682209, -0.07150000333786011, -0.14509999752044678, -0.07680000364780426, 0.02250000089406967, 0.05730000138282776, -0.10750000178813934, 0.027300000190734863, -0.0851999968290329, -0.09870000183582306, 0.1137000024318695, 0.023000000044703484, -0.10189999639987946, 0.034699998795986176, -0.11490000039339066, -0.0494999997317791, 0.07490000128746033, 0.06589999794960022, 0.014999999664723873, -0.12309999763965607, 0.042399998754262924, -0.2696000039577484, 0.06449999660253525, -0.08860000222921371, 0.06270000338554382, -0.13259999454021454, -0.030700000002980232, 0.052299998700618744, -0.0005000000237487257, 0.16009999811649323, -0.05260000005364418, 0.08869999647140503, 0.042500000447034836, -0.03460000082850456, -0.00839999970048666, 0.062199998646974564, 0.1396999955177307, 0.03500000014901161, 0.13500000536441803, 0.1031000018119812, 0.09260000288486481, -0.022</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>[[[0.05779999867081642, -0.11129999905824661, 0.017400000244379044, -0.028699999675154686, -0.015300000086426735, -0.014600000344216824, -0.031199999153614044, 0.06459999829530716, 0.08009999990463257, -0.08070000261068344, 0.03750000149011612, -0.008999999612569809, 0.0803999975323677, -0.10490000247955322, 0.030899999663233757, 0.08810000121593475, 0.025800000876188278, 0.06390000134706497, -0.021700000390410423, 0.002899999963119626, 0.035599999129772186, 0.03779999911785126, -0.028999999165534973, 0.05620000138878822, -0.006200000178068876, 0.020800000056624413, -0.05079999938607216, -0.044599998742341995, 0.009600000455975533, 0.003700000001117587, 0.0007999999797903001, -0.0746999979019165, -0.030899999663233757, 0.003599999938160181, 0.09740000218153, 0.04360000044107437, 0.042899999767541885, -0.04230000078678131, 0.06270000338554382, 0.009999999776482582, -0.10050000250339508, 0.05950000137090683, 0.06210000067949295, -0.029400000348687172, 0.05810000002384186, 0.014800000004470348, -0.05920000001788139, -0.07169999927282333, -0.0575999990105629, 0.08980000019073486, 0.009600000455975533, 0.08429999649524689, -0.00279999990016222, -0.08290000259876251, -0.03709999844431877, 0.01549999974668026, 0.0674000009894371, 0.03060000017285347, 0.0203000009059906, -0.1080000028014183, 0.04839999973773956, 0.030300000682473183, 0.0828000009059906, 0.020800000056624413, 0.0013000000035390258, 0.02630000002682209, 0.006599999964237213, -0.01679999940097332, 0.021299999207258224, -0.050999999046325684, -0.026799999177455902, 0.016499999910593033, -0.11029999703168869, -0.04390000179409981, -0.05559999868273735, -0.08760000020265579, -0.00279999990016222, -0.0551999993622303, -0.032600000500679016, 0.0203000009059906, -0.03999999910593033, 0.011300000362098217, 0.04390000179409981, -0.016699999570846558, 0.0729999989271164, 0.05530000105500221, -0.05480000004172325, 0.04039999842643738, 0.04129999876022339, 0.007499999832361937, -0.0017000000225380063, -0.04410000145435333, 0.07769999653100967, 0.017400000244379044, -0.012199999764561653, -0.016100000590085983, -0.03139999881386757, 0.08429999649524689, -0.09780000150203705, -0.12049999833106995, 0.0617000013589859, -0.028200000524520874, -0.04170000180602074, 0.08649999648332596, -0.04859999939799309, -0.0794999971985817, 0.016100000590085983, -0.005799999926239252, 0.002400000113993883, 0.03660000115633011, -0.05739999935030937, -0.010999999940395355, 0.03460000082850456, -0.058400001376867294, -0.025499999523162842, -0.0019000000320374966, 0.013100000098347664, 0.04259999841451645, 0.015200000256299973, 0.003100000089034438, 0.021800000220537186, 0.06199999898672104, -0.02329999953508377, -0.014000000432133675, -0.004999999888241291, -0.010300000198185444, 0.0007999999797903001, -0.051600001752376556], [-0.02979999966919422, 0.08020000159740448, -0.03720000013709068, 0.0877000018954277, 0.049800001084804535, 0.015599999576807022, 0.043299999088048935, -0.06270000338554382, -0.1290999948978424, 0.061500001698732376, -0.045499999076128006, 0.031300000846385956, -0.027499999850988388, 0.09809999912977219, -0.03750000149011612, 0.021199999377131462, -0.051100000739097595, -0.07620000094175339, 0.04670000076293945, -0.00019999999494757503, -0.030799999833106995, -0.021800000220537186, -0.018799999728798866, -0.044199999421834946, 0.003599999938160181, -0.03290000185370445, 0.04830000177025795, 0.058800000697374344, 0.007000000216066837, 0.016200000420212746, -0.027300000190734863, 0.07490000128746033, 0.01810000091791153, 0.052000001072883606, -0.09220000356435776, -0.04610000178217888, -0.08829999715089798, 0.0026000000070780516, -0.07169999927282333, -0.006399999838322401, 0.1274999976158142, -0.03400000184774399, -0.05999999865889549, 0.04320000112056732, -0.054099999368190765, -0.00860000029206276, -0.01850000023841858, 0.01730000041425228, 0.15600000321865082, -0.04580000042915344, 0.006300000008195639, -0.02459999918937683, -0.03290000185370445, 0.08649999648332596, 0.01600000075995922, -0.01489999983459711, -0.03790000081062317, -0.03519999980926514, -0.01860000006854534, 0.07180000096559525, -0.06840000301599503, -0.033900000154972076, -0.08659999817609787, -0.0026000000070780516, 0.028699999675154686, -0.05180000141263008, -0.026799999177455902, -0.0015999999595806003, 0.016699999570846558, 0.0674000009894371, 0.07090000063180923, -0.01889999955892563, -0.032600000500679016, 0.06430000066757202, 0.05380000174045563, 0.06289999932050705, -0.008700000122189522, 0.016300000250339508, 0.08489999920129776, 0.0008999999845400453, 0.07150000333786011, 0.0024999999441206455, -0.01899999938905239, 0.024900000542402267, -0.07850000262260437, -0.06509999930858612, 0.14069999754428864, -0.04309999942779541, -0.05689999833703041, -0.016100000590085983, -0.011500000022351742, 0.04859999939799309, -0.08889999985694885, -0.022600000724196434, -0.016899999231100082, 0.07689999788999557, 0.0340999998152256, -0.07079999893903732, 0.13199999928474426, 0.013399999588727951, -0.029500000178813934, 0.07199999690055847, 0.03200000151991844, -0.03869999945163727, 0.1151999980211258, 0.07100000232458115, -0.0010000000474974513, 9.999999747378752e-05, -0.010200000368058681, -0.020600000396370888, 0.09070000052452087, -0.014499999582767487, -0.08179999887943268, 0.03400000184774399, 0.02239999920129776, 0.03880000114440918, -0.08420000225305557, -0.066600002348423, -0.027899999171495438, -0.06750000268220901, -0.021700000390410423, -0.057100001722574234, 0.039000000804662704, 0.014100000262260437, -0.004000000189989805, -0.07760000228881836, -0.007699999958276749, 0.09870000183582306]], [[0.060100000351667404, -0.07699999958276749, -0.003100000089034438, -0.15360000729560852, -0.02199999988079071, -0.0786999985575676, 0.006500000134110451, -0.0771000012755394, -0.04179999977350235, -0.17839999496936798, 0.00039999998989515007, -0.1761000007390976, -0.012199999764561653, -0.1867000013589859, 0.05339999869465828, 0.09369999915361404, -0.010099999606609344, -0.13300000131130219, 0.030799999833106995, 0.1177000030875206, 0.03709999844431877, 0.07500000298023224, -0.11410000175237656, 0.038100000470876694, -0.08129999786615372, 0.05700000002980232, 0.06459999829530716, 0.0272000003606081, -0.0544000007212162, 0.08839999884366989, -0.10409999638795853, 0.007199999876320362, -0.11050000041723251, 0.03020000085234642, -0.18219999969005585, 0.09040000289678574, -0.17579999566078186, -0.17560000717639923, 0.0071000000461936, -0.10610000044107437, 0.1809999942779541, 0.23899999260902405, 0.022700000554323196, 0.12790000438690186, -0.0348999984562397, 0.004699999932199717, -0.23890000581741333, 0.11559999734163284, 0.03610000014305115, -0.0340999998152256, -0.08959999680519104, -0.03869999945163727, 0.14470000565052032, 0.08820000290870667, 0.02759999968111515, 0.1454000025987625, 0.04800000041723251, -0.12300000339746475, -0.07880000025033951, 0.04740000143647194, -0.10159999877214432, -0.08879999816417694, -0.053700000047683716, -0.16369999945163727, 0.06239999830722809, -0.016200000420212746, -0.05180000141263008, -0.011599999852478504, -0.10970000177621841, 0.06539999693632126, 0.18629999458789825, -0.066600002348423, -0.04039999842643738, -0.22210000455379486, 0.058800000697374344, 0.09380000084638596, 0.018200000748038292, -0.05790000036358833, -0.007300000172108412, -0.09700000286102295, 0.03750000149011612, -0.12880000472068787, -0.0272000003606081, -0.14659999310970306, -0.053700000047683716, -0.16869999468326569, 0.012500000186264515, 0.043299999088048935, -0.01730000041425228, 0.045099999755620956, -0.12049999833106995, 0.026499999687075615, 0.12610000371932983, -0.17739999294281006, 0.05900000035762787, -0.14839999377727509, 0.06369999796152115, 0.22390000522136688, -0.16689999401569366, 0.1216999962925911, -0.05400000140070915, 0.07620000094175339, -0.22040000557899475, 0.03929999843239784, -0.07159999758005142, 0.02419999986886978, 0.07639999687671661, 0.028699999675154686, -0.0674000009894371, -0.007799999788403511, 0.010700000450015068, -0.027699999511241913, 0.019200000911951065, -0.03180000185966492, 0.03020000085234642, 0.19329999387264252, -0.07020000368356705, 0.04390000179409981, 0.19059999287128448, 0.11209999769926071, -0.0010999999940395355, -0.01549999974668026, -0.13210000097751617, -0.017500000074505806, -0.06870000064373016, 0.051600001752376556, 0.09700000286102295, 0.005799999926239252], [-0.0722000002861023, -0.008999999612569809, 0.12460000067949295, -0.048700001090765, -0.014299999922513962, -0.03959999978542328, -0.01640000008046627, 0.017400000244379044, 0.1266999989748001, -0.0035000001080334187, 0.025599999353289604, 0.25040000677108765, -0.04410000145435333, 0.13910000026226044, -0.023900000378489494, -0.007000000216066837, -0.010499999858438969, 0.0406000018119812, -0.05810000002384186, -0.001500000013038516, 0.10779999941587448, -0.33480000495910645, 0.06710000336170197, -0.12849999964237213, 0.12849999964237213, -0.016200000420212746, 0.028200000524520874, -0.05889999866485596, -0.10499999672174454, -0.14959999918937683, -0.21699999272823334, 0.06759999692440033, 0.017899999395012856, -0.1071000024676323, -0.08060000091791153, -0.11659999936819077, -0.044199999421834946, 0.09549999982118607, 0.04899999871850014, 0.04340000078082085, -0.12319999933242798, -0.24120000004768372, -0.15780000388622284, -0.03370000049471855, 0.06449999660253525, -0.18039999902248383, -0.010300000198185444, 0.07959999889135361, -0.02710000053048134, -0.08540000021457672, -0.19300000369548798, -0.12330000102519989, 0.1956000030040741, 0.3124000132083893, 0.11869999766349792, -0.012000000104308128, -0.035999998450279236, 0.08659999817609787, -0.13189999759197235, -0.10999999940395355, -0.04820000007748604, 0.14669999480247498, -0.19629999995231628, -0.1704999953508377, 0.19830000400543213, 0.021199999377131462, -0.16539999842643738, -0.15379999577999115, -0.20090000331401825, -0.021400000900030136, 0.04749999940395355, 0.09319999814033508, 0.004399999976158142, -0.009399999864399433, 0.10270000249147415, 0.09080000221729279, 0.08470000326633453, 0.053199999034404755, 0.026200000196695328, 0.017000000923871994, 0.019300000742077827, 0.03530000150203705, 0.05790000036358833, -0.10719999670982361, 0.18649999797344208, -0.2827000021934509, -0.12530000507831573, 0.05490000173449516, -0.19220000505447388, -0.06939999759197235, -0.0035000001080334187, 0.1225999966263771, -0.16940000653266907, 0.13050000369548798, 0.14339999854564667, 0.002300000051036477, -0.094200000166893, -0.19189999997615814, 0.03999999910593033, 0.013199999928474426, 0.12430000305175781, -0.1949000060558319, -0.014399999752640724, 0.10750000178813934, 0.08100000023841858, 0.07829999923706055, -0.09650000184774399, -0.0026000000070780516, -0.05400000140070915, -0.003599999938160181, 0.01640000008046627, -0.00430000014603138, -0.007199999876320362, -0.09239999949932098, 0.004900000058114529, 0.009700000286102295, 0.17229999601840973, -0.014499999582767487, 0.14419999718666077, -0.13770000636577606, -0.03579999879002571, -0.07020000368356705, -0.08619999885559082, -0.19830000400543213, -0.03779999911785126, 0.07320000231266022, 0.010099999606609344, -0.04670000076293945], [0.04820000007748604, 0.013899999670684338, -0.02160000056028366, 0.11670000106096268, -0.08940000087022781, 0.019899999722838402, -0.08079999685287476, 0.10570000112056732, 0.01119999960064888, -0.09939999878406525, -0.04800000041723251, 0.019600000232458115, 0.06509999930858612, -0.053300000727176666, -0.251800000667572, -0.060600001364946365, -0.0340999998152256, 0.0015999999595806003, -0.057500001043081284, -0.0835999995470047, 0.05469999834895134, -0.039799999445676804, 0.06639999896287918, -0.19750000536441803, 0.04129999876022339, 0.08630000054836273, 0.0071000000461936, 0.11110000312328339, 0.026000000536441803, -0.00839999970048666, 0.07649999856948853, -0.006399999838322401, 0.12020000070333481, -0.02590000070631504, -0.0851999968290329, -0.08820000290870667, -0.047200001776218414, 0.010499999858438969, 0.018699999898672104, -0.19740000367164612, 0.02969999983906746, 0.005200000014156103, -0.07490000128746033, 0.051899999380111694, 0.19189999997615814, -0.001500000013038516, -0.09369999915361404, 0.09470000118017197, 0.010499999858438969, 0.013899999670684338, -0.02290000021457672, 0.02850000001490116, -0.12300000339746475, -0.11789999902248383, -0.0625, -0.01140000019222498, 0.13249999284744263, -0.010400000028312206, -0.05979999899864197, -0.09179999679327011, 0.049300000071525574, 0.0892999991774559, 0.05689999833703041, 0.12430000305175781, -0.16019999980926514, 0.02419999986886978, 0.062199998646974564, 0.11140000075101852, -0.05389999970793724, -0.06419999897480011, 0.03700000047683716, 0.1776999980211258, 0.2581000030040741, -0.04699999839067459, 0.1298000067472458, -0.07530000060796738, 0.09570000320672989, 0.05139999836683273, -0.10509999841451645, 0.06790000200271606, -0.009999999776482582, 0.09430000185966492, -0.09610000252723694, 0.1339000016450882, -0.06599999964237213, 0.01850000023841858, -0.03759999945759773, 0.03440000116825104, 0.018200000748038292, -0.08990000188350677, 0.051899999380111694, 0.05310000106692314, -0.039400000125169754, -0.057500001043081284, -0.10329999774694443, -0.04690000042319298, 0.08299999684095383, -0.04010000079870224, 0.03840000182390213, 0.22390000522136688, 0.06620000302791595, 0.20960000157356262, 0.11050000041723251, -0.002899999963119626, -0.08889999985694885, 0.19869999587535858, -0.05869999900460243, -0.025200000032782555, 0.07930000126361847, 0.023600000888109207, -0.03229999914765358, -0.24210000038146973, -0.1446000039577484, 0.02449999935925007, 0.0860000029206276, 0.0013000000035390258, -0.12860000133514404, -0.12770000100135803, -0.24079999327659607, 0.042399998754262924, 0.09950000047683716, 0.08370000123977661, 0.027899999171495438, -0.03620000183582306, 0.07840000092983246, -0.029400000348687172, -0.02280000038444996, -0.06310000270605087], [0.03709999844431877, 0.053700000047683716, -0.11840000003576279, -0.04230000078678131, -0.1088000014424324, 0.08630000054836273, 0.0851999968290329, -0.09080000221729279, 0.043800000101327896, 0.019899999722838402, -0.11230000108480453, -0.025800000876188278, -0.01640000008046627, -0.09359999746084213, -0.0044999998062849045, -0.04470000043511391, -0.03790000081062317, -0.03200000151991844, 0.058400001376867294, -0.1145000010728836, -0.07270000129938126, -0.1670999974012375, -0.16940000653266907, -0.030700000002980232, 0.042500000447034836, -0.021800000220537186, 0.05169999971985817, -0.05040000006556511, -0.0957999974489212, -0.032099999487400055, -0.08460000157356262, -0.02019999921321869, 0.01889999955892563, 0.00419999985024333, 0.15520000457763672, 0.001500000013038516, 0.09570000320672989, -0.21250000596046448, 0.06639999896287918, -0.04349999874830246, 0.0731000006198883, 0.07940000295639038, 0.13670000433921814, -0.14059999585151672, -0.043699998408555984, 0.02800000086426735, -0.11729999631643295, 0.04179999977350235, -0.04749999940395355, 0.04699999839067459, -0.0052999998442828655, 0.17219999432563782, -0.06689999997615814, -0.024399999529123306, 0.0617000013589859, 0.09480000287294388, 0.016100000590085983, -0.03590000048279762, 0.10180000215768814, 0.03750000149011612, 0.04650000110268593, 0.12080000340938568, 0.029400000348687172, 0.02459999918937683, 0.06679999828338623, 0.03739999979734421, -0.036400001496076584, -0.04580000042915344, -0.20110000669956207, 0.10700000077486038, 0.18770000338554382, 0.06440000236034393, 0.03020000085234642, 0.1264999955892563, -0.02370000071823597, 0.06729999929666519, -0.04580000042915344, -0.03519999980926514, 0.09449999779462814, 0.013500000350177288, -0.04430000111460686, -0.049300000071525574, 0.022299999371170998, -0.10809999704360962, 0.10100000351667404, -0.02800000086426735, -0.10849999636411667, 0.05000000074505806, -0.11309999972581863, 0.1412999927997589, 0.06400000303983688, -0.0877000018954277, -0.0203000009059906, -0.07169999927282333, 0.029400000348687172, -0.13600000739097595, 0.009100000374019146, -0.20360000431537628, -0.09839999675750732, -0.03189999982714653, -0.06379999965429306, -0.07079999893903732, 0.0003000000142492354, -0.12160000205039978, -0.011500000022351742, -0.0885000005364418, -0.08910000324249268, -0.06360000371932983, -0.12449999898672104, 0.2021999955177307, 0.120899997651577, -0.0015999999595806003, 0.14949999749660492, 0.008700000122189522, 0.07989999651908875, -0.05790000036358833, 0.011300000362098217, -0.1039000004529953, -0.23589999973773956, 0.022700000554323196, 0.021199999377131462, -0.05660000070929527, -0.19670000672340393, -0.10260000079870224, -0.14139999449253082, -0.04340000078082085, 0.05000000074505806, 0.1737000048160553], [0.02930000051856041, 0.15960000455379486, -0.020899999886751175, -0.040800001472234726, 0.010999999940395355, 0.05990000069141388, 0.1542000025510788, -0.01889999955892563, 0.14300000667572021, 0.053599998354911804, 0.05380000174045563, 0.11159999668598175, -0.0868000015616417, 0.04910000041127205, 0.016100000590085983, -0.025800000876188278, -0.07900000363588333, 0.029100000858306885, 0.0203000009059906, 0.02459999918937683, -0.014100000262260437, 0.08810000121593475, 0.10490000247955322, 0.12530000507831573, -0.1793999969959259, 0.23649999499320984, -0.043699998408555984, 0.0544000007212162, 0.03099999949336052, -0.15680000185966492, -0.11879999935626984, 0.03880000114440918, -0.07559999823570251, -0.1454000025987625, 0.06199999898672104, 0.01360000018030405, -0.12559999525547028, 0.03449999913573265, -0.08250000327825546, -0.093299999833107, -0.12349999696016312, -0.005499999970197678, -0.11590000241994858, -0.15790000557899475, -0.04190000146627426, -0.054499998688697815, 0.06530000269412994, 0.1185000017285347, -0.23109999299049377, -0.07190000265836716, -0.09390000253915787, -0.056699998676776886, 0.01510000042617321, -0.01140000019222498, 0.0017000000225380063, 0.10920000076293945, -0.0738999992609024, -0.06599999964237213, 0.16359999775886536, -0.011300000362098217, -0.014600000344216824, 0.2320999950170517, -0.00419999985024333, -0.06289999932050705, -0.056299999356269836, -0.0860000029206276, 0.03319999948143959, 0.10989999771118164, -0.05339999869465828, -0.17900000512599945, 0.05770000070333481, 0.029100000858306885, -0.002199999988079071, 0.09000000357627869, 0.1720999926328659, 0.014499999582767487, 0.039000000804662704, 0.06080000102519989, 0.17520000040531158, 0.06430000066757202, -0.10260000079870224, -0.019500000402331352, -0.16599999368190765, -0.006800000090152025, 0.053199999034404755, 0.10490000247955322, -0.12540000677108765, 0.06239999830722809, 0.06859999895095825, 0.050200000405311584, -0.09239999949932098, 0.06270000338554382, -0.11580000072717667, 0.16930000483989716, 0.11699999868869781, -0.0421999990940094, -0.00800000037997961, 0.0949999988079071, -0.019500000402331352, 0.06289999932050705, -0.0348999984562397, -0.012199999764561653, 0.0044999998062849045, -0.1054999977350235, 0.1225999966263771, 0.04839999973773956, 0.005799999926239252, 0.02280000038444996, 0.10740000009536743, 0.05640000104904175, -0.10090000182390213, -0.0568000003695488, 0.054999999701976776, 0.003100000089034438, -0.07370000332593918, 0.09809999912977219, 0.05889999866485596, 0.04830000177025795, 0.04800000041723251, 0.0003000000142492354, 0.014999999664723873, -0.011699999682605267, -0.04399999976158142, 0.09780000150203705, 0.12809999287128448, -0.16830000281333923, 0.09870000183582306, 0.0031999999191612005], [0.11230000108480453, 0.12330000102519989, -0.014800000004470348, -0.14550000429153442, 0.12139999866485596, 0.020999999716877937, -0.02419999986886978, -0.002400000113993883, 0.13809999823570251, 0.026499999687075615, -0.1168999969959259, 0.039400000125169754, 0.1808999925851822, 0.027300000190734863, 0.022700000554323196, 0.07850000262260437, -0.033799998462200165, -0.040699999779462814, 0.12080000340938568, -0.060600001364946365, -0.0020000000949949026, 0.08940000087022781, -0.12620000541210175, 0.07569999992847443, 0.0786999985575676, 0.17149999737739563, -0.027499999850988388, 0.08869999647140503, 0.09200000017881393, 0.06849999725818634, 0.023800000548362732, 0.11829999834299088, 0.0012000000569969416, -0.010300000198185444, 0.025800000876188278, -0.14880000054836273, -0.040699999779462814, -0.13359999656677246, 0.015699999406933784, 0.04989999905228615, -0.16830000281333923, -0.053599998354911804, 0.01730000041425228, -0.06390000134706497, -0.013399999588727951, 0.08370000123977661, -0.15279999375343323, 0.14190000295639038, 0.04100000113248825, 0.17249999940395355, -0.11620000004768372, 0.05530000105500221, 0.041200000792741776, -0.05530000105500221, -0.2143000066280365, -0.006000000052154064, -0.15160000324249268, 0.0421999990940094, 0.0575999990105629, -0.1005999967455864, 0.0544000007212162, -0.0722000002861023, -0.06719999760389328, -0.08889999985694885, -0.014999999664723873, -0.033399999141693115, -0.004600000102072954, 0.04149999842047691, 0.036400001496076584, 0.01769999973475933, -0.04100000113248825, -0.026900000870227814, 0.03779999911785126, 0.08470000326633453, 0.034699998795986176, -0.12139999866485596, 0.013500000350177288, 0.0502999983727932, -0.042100001126527786, 0.049300000071525574, -0.028300000354647636, -0.03150000050663948, 0.052799999713897705, -0.02070000022649765, 0.058800000697374344, 0.022199999541044235, 0.014700000174343586, 0.20430000126361847, 0.11500000208616257, 0.1120000034570694, 0.1720000058412552, 0.050599999725818634, -0.0640999972820282, -0.12729999423027039, 0.1331000030040741, -0.045899998396635056, 0.06360000371932983, -0.10949999839067459, -0.10970000177621841, -0.09390000253915787, 0.03790000081062317, 0.0917000025510788, -0.03739999979734421, -0.09929999709129333, 0.014100000262260437, 0.0917000025510788, -0.01720000058412552, -0.005499999970197678, -0.094200000166893, -0.08550000190734863, 0.16259999573230743, -0.03840000182390213, -0.061500001698732376, 0.09870000183582306, 0.06960000097751617, 0.03840000182390213, -0.057500001043081284, 0.0551999993622303, 0.09049999713897705, -0.03530000150203705, -0.12070000171661377, -0.038600001484155655, -0.03999999910593033, -0.028300000354647636, 0.225600004196167, -0.012000000104308128, -0.14190000295639038, -0.10369999706745148], [-0.1429000049829483, -0.018400000408291817, 0.0430000014603138, 0.1273999959230423, 0.059300001710653305, 0.08990000188350677, -0.017899999395012856, -0.04230000078678131, 0.05779999867081642, 0.024399999529123306, 9.999999747378752e-05, -0.0364999994635582, -0.12139999866485596, -0.1265999972820282, 0.07890000194311142, -0.01850000023841858, 0.004600000102072954, -0.0494999997317791, -0.22130000591278076, -0.09799999743700027, -0.06369999796152115, -0.09220000356435776, -0.12049999833106995, 0.008799999952316284, 0.016100000590085983, -0.12229999899864197, 0.0982000008225441, -0.20730000734329224, 0.05310000106692314, 0.12790000438690186, -0.025599999353289604, -0.01759999990463257, 0.05909999832510948, -0.14480000734329224, -0.1996999979019165, -0.11540000140666962, -0.10670000314712524, -0.125900000333786, 0.12439999729394913, 0.034699998795986176, -0.07360000163316727, 0.03280000016093254, -0.08489999920129776, -0.21299999952316284, 0.04839999973773956, 0.05249999836087227, -0.08229999989271164, 0.06120000034570694, -0.11829999834299088, -0.12520000338554382, 0.0013000000035390258, 0.1454000025987625, 0.013100000098347664, -0.13500000536441803, -0.1436000019311905, -0.08839999884366989, -0.00989999994635582, 0.13210000097751617, 0.01850000023841858, -0.028300000354647636, 0.03799999877810478, -0.21250000596046448, -0.08250000327825546, 0.022600000724196434, -0.06750000268220901, -0.19140000641345978, -0.09049999713897705, 0.0364999994635582, 0.07999999821186066, 0.019300000742077827, -0.0625, 0.023399999365210533, 0.021900000050663948, 0.05869999900460243, -0.18719999492168427, 0.06530000269412994, 0.1145000010728836, 0.0794999971985817, 0.15559999644756317, -0.00419999985024333, -0.041600000113248825, -0.0771000012755394, -0.03449999913573265, -0.00019999999494757503, -0.07890000194311142, 0.01590000092983246, -0.03779999911785126, 0.017999999225139618, 0.1468999981880188, -0.011099999770522118, -0.013299999758601189, -0.0357000008225441, 0.09070000052452087, 0.16050000488758087, 0.09510000050067902, 0.035999998450279236, 0.054999999701976776, -0.05920000001788139, 0.07050000131130219, 0.08169999718666077, -0.008799999952316284, 0.1046999990940094, 0.024700000882148743, 0.07400000095367432, 0.04179999977350235, 0.05480000004172325, 0.009200000204145908, 0.0908999964594841, -0.1543000042438507, 0.046300001442432404, -0.10970000177621841, 0.0015999999595806003, -0.10610000044107437, 0.049300000071525574, -0.06520000100135803, -0.07440000027418137, -0.02930000051856041, 0.043299999088048935, -0.05270000174641609, -0.014999999664723873, -0.1062999963760376, 0.10970000177621841, -0.03759999945759773, -0.07320000231266022, -0.09210000187158585, -0.04639999940991402, 0.08079999685287476, 0.07699999958276749], [-0.04410000145435333, 0.07280000299215317, -0.1264999955892563, -0.07450000196695328, -0.1876000016927719, 0.050999999046325684, -0.005499999970197678, 0.023399999365210533, -0.012600000016391277, -0.028200000524520874, 0.06199999898672104, -0.14489999413490295, 0.011099999770522118, -0.014100000262260437, 0.013799999840557575, 0.14720000326633453, -0.039400000125169754, 0.19670000672340393, 0.01590000092983246, -0.007799999788403511, -0.010200000368058681, 0.23510000109672546, -0.040800001472234726, 0.11249999701976776, -0.12240000069141388, 0.024900000542402267, -0.04019999876618385, 0.009800000116229057, 0.07940000295639038, 0.10939999669790268, -0.028300000354647636, -0.048900000751018524, 0.019500000402331352, -0.05590000003576279, -0.028999999165534973, -0.005499999970197678, 0.11559999734163284, -0.15080000460147858, 0.024700000882148743, -0.07660000026226044, -0.02759999968111515, 0.22290000319480896, -0.043699998408555984, 0.025100000202655792, 0.03590000048279762, 0.09780000150203705, -0.2199999988079071, -0.12919999659061432, 0.09430000185966492, 0.024399999529123306, -0.0835999995470047, -0.03350000083446503, -0.05939999967813492, 0.09399999678134918, -0.02449999935925007, 0.1062999963760376, -0.1265999972820282, 0.02879999950528145, -0.14990000426769257, 0.005799999926239252, 0.14149999618530273, 0.19990000128746033, -0.044599998742341995, 0.1273999959230423, 0.10100000351667404, -0.1695999950170517, -0.20090000331401825, -0.020500000566244125, 0.04129999876022339, -0.12439999729394913, 0.007199999876320362, -0.16120000183582306, -0.06239999830722809, -0.12049999833106995, -0.12330000102519989, 0.29760000109672546, -0.29739999771118164, -0.05299999937415123, -0.02500000037252903, -0.042500000447034836, 0.1014999970793724, 0.1754000037908554, 0.020600000396370888, -0.039799999445676804, -0.11500000208616257, 0.18979999423027039, 0.016200000420212746, -0.06589999794960022, -0.06030000001192093, -0.06109999865293503, 0.16019999980926514, 0.035999998450279236, 0.11400000005960464, 0.010599999688565731, 0.1550000011920929, 0.025299999862909317, -0.08940000087022781, -0.026000000536441803, -0.013899999670684338, 0.05249999836087227, -0.013899999670684338, -0.05640000104904175, -0.008299999870359898, 0.16089999675750732, 0.026900000870227814, -0.044599998742341995, 0.04259999841451645, 0.12530000507831573, 0.08410000056028366, 0.09549999982118607, 0.10029999911785126, -0.210099995136261, 0.03370000049471855, 0.13420000672340393, 0.024000000208616257, 0.13840000331401825, -0.1404000073671341, -0.0005000000237487257, 0.06719999760389328, 0.08560000360012054, 0.013399999588727951, -0.016599999740719795, 0.14329999685287476, -0.0494999997317791, -0.10189999639987946, -0.09520000219345093, -0.1145000010728836, 0.062300000339746475], [-0.0892999991774559, -0.0494999997317791, 0.035999998450279236, 0.11640000343322754, 0.1428000032901764, -0.049400001764297485, -0.03240000084042549, 0.09380000084638596, 0.24799999594688416, 0.0032999999821186066, 0.04540000110864639, 0.09640000015497208, 0.043699998408555984, -0.15629999339580536, -0.22120000422000885, -0.05209999904036522, 0.13850000500679016, 0.04989999905228615, -0.039799999445676804, 0.04490000009536743, 0.04690000042319298, 0.20059999823570251, 0.06390000134706497, -0.030400000512599945, -0.022299999371170998, 0.007799999788403511, 0.31700000166893005, -0.00139999995008111, 0.06880000233650208, 0.1111999973654747, 0.08889999985694885, -0.19789999723434448, 0.0421999990940094, 0.0763000026345253, 0.009600000455975533, -0.10679999738931656, 0.11259999871253967, -0.21220000088214874, -0.06939999759197235, -0.11140000075101852, -0.06920000165700912, 0.02930000051856041, 0.17980000376701355, 0.07329999655485153, -0.039500001817941666, 0.06790000200271606, -0.1080000028014183, -0.06710000336170197, -0.026200000196695328, -0.0007999999797903001, 0.1185000017285347, 0.03840000182390213, -0.13050000369548798, -0.060499999672174454, 0.0617000013589859, 0.005900000222027302, -0.03750000149011612, -0.08659999817609787, 0.11169999837875366, -0.010400000028312206, -0.058800000697374344, 0.056299999356269836, -0.10859999805688858, -0.03269999846816063, 0.06199999898672104, -0.14069999754428864, 0.12200000137090683, -0.049400001764297485, 0.00800000037997961, -0.07020000368356705, -0.1647000014781952, 0.04529999941587448, -0.0925000011920929, 0.14139999449253082, -0.08860000222921371, 0.0414000004529953, -0.060499999672174454, -0.06620000302791595, -0.03999999910593033, 0.04360000044107437, -0.07880000025033951, 0.1460999995470047, 0.13189999759197235, 0.11029999703168869, -0.18649999797344208, -0.0966000035405159, 0.0034000000450760126, 0.11429999768733978, 0.22380000352859497, -0.18639999628067017, -0.0215000007301569, -0.015799999237060547, -0.07729999721050262, -0.10029999911785126, -0.1014999970793724, 0.07800000160932541, -0.08900000154972076, -0.025800000876188278, 0.17440000176429749, -0.0038999998942017555, 0.026599999517202377, 0.010200000368058681, 0.05990000069141388, -0.07069999724626541, 0.027400000020861626, 0.017899999395012856, 0.015200000256299973, -0.08550000190734863, -0.08020000159740448, 0.1137000024318695, -0.019500000402331352, -0.19439999759197235, 0.04450000077486038, 0.09269999712705612, 0.008999999612569809, 0.1678999960422516, -0.09059999883174896, -0.06809999793767929, 0.1356000006198883, -0.10849999636411667, -0.014100000262260437, 0.07890000194311142, 0.24690000712871552, 0.07930000126361847, 0.0697999969124794, -0.1454000025987625, -0.03519999980926514, -0.1137000024318695], [-0.021199999377131462, -0.09799999743700027, 0.05730000138282776, 0.0215000007301569, 0.21729999780654907, 0.03999999910593033, 0.03880000114440918, 0.030799999833106995, 0.03200000151991844, 0.12370000034570694, -0.017899999395012856, 0.06400000303983688, -0.04089999943971634, 0.20990000665187836, 0.11569999903440475, -0.030300000682473183, 0.027400000020861626, -0.10260000079870224, -0.014299999922513962, 0.19979999959468842, -0.04690000042319298, 0.038600001484155655, -0.10429999977350235, -0.030899999663233757, 0.21449999511241913, 0.15520000457763672, 0.021800000220537186, -0.1412999927997589, -0.20730000734329224, -0.17030000686645508, -0.20319999754428864, 0.15489999949932098, 0.11219999939203262, -0.03229999914765358, -0.056699998676776886, -0.037700001150369644, 0.09669999778270721, 0.26080000400543213, 0.12700000405311584, -0.06449999660253525, -0.0957999974489212, -0.09600000083446503, 0.02290000021457672, -0.08619999885559082, -0.002300000051036477, 0.04600000008940697, 0.0794999971985817, 0.12600000202655792, -0.013500000350177288, -0.21789999306201935, -0.09929999709129333, -0.060100000351667404, 0.05299999937415123, 0.12860000133514404, -0.005499999970197678, -0.09969999641180038, 0.00989999994635582, -0.0031999999191612005, 0.04470000043511391, 0.04919999837875366, -0.04170000180602074, 0.06719999760389328, -0.05000000074505806, -0.1339000016450882, -0.15880000591278076, 0.10289999842643738, 0.00989999994635582, 0.12359999865293503, -0.21060000360012054, 0.049400001764297485, -0.043800000101327896, -0.007199999876320362, 0.21449999511241913, 0.09380000084638596, -0.11940000206232071, -0.0020000000949949026, 0.05270000174641609, -0.09109999984502792, 0.17440000176429749, 0.066600002348423, 0.039799999445676804, -0.13680000603199005, -0.04919999837875366, -0.30239999294281006, 0.2012999951839447, -0.17409999668598175, 0.017100000753998756, -0.08760000020265579, -0.09309999644756317, 0.15189999341964722, 0.133200004696846, 0.2110999971628189, -0.11209999769926071, 0.1680999994277954, 0.04740000143647194, -9.999999747378752e-05, 0.001500000013038516, -0.030500000342726707, 0.2272000014781952, 0.08160000294446945, 0.25189998745918274, 0.1641999930143356</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>[-12.136071370145906]</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>[2.9985267215507294]</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>[-17.479437371710638]</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>[4.218915997214308]</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>[0.06532884293451813]</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>[0.30589889078318017]</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>[-11.736975960843834]</t>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>[2.925926312605601]</t>
+        </is>
+      </c>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>[-18.940602774071543]</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>[4.729133835417226]</t>
+        </is>
+      </c>
+      <c r="O30" t="inlineStr">
+        <is>
+          <t>[-1.515646239348786]</t>
+        </is>
+      </c>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>[0.827012270209717]</t>
+        </is>
+      </c>
+      <c r="Q30" t="inlineStr">
+        <is>
+          <t>[-0.526378038472842]</t>
+        </is>
+      </c>
+      <c r="R30" t="inlineStr">
+        <is>
+          <t>[0.16458282474333588]</t>
+        </is>
+      </c>
+      <c r="S30" t="inlineStr">
+        <is>
+          <t>[-0.27994162106210996]</t>
+        </is>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>[0.1078483158627865]</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>[-2.1242424387091834]</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>[0.2987498426770443]</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>[-0.7625849436524414]</t>
+        </is>
+      </c>
+      <c r="X30" t="inlineStr">
+        <is>
+          <t>[0.18464949776443793]</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>[-0.3233972069048896]</t>
+        </is>
+      </c>
+      <c r="Z30" t="inlineStr">
+        <is>
+          <t>[0.10890660386687263]</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>[-2.266103804772871]</t>
+        </is>
+      </c>
+      <c r="AB30" t="inlineStr">
+        <is>
+          <t>[0.30049583710524086]</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>[-0.7739481747214421]</t>
+        </is>
+      </c>
+      <c r="AD30" t="inlineStr">
+        <is>
+          <t>[0.1486497104998922]</t>
+        </is>
+      </c>
+      <c r="AE30" t="inlineStr">
+        <is>
+          <t>[-0.718007158474274]</t>
+        </is>
+      </c>
+      <c r="AF30" t="inlineStr">
+        <is>
+          <t>[0.18499170208799492]</t>
+        </is>
+      </c>
+      <c r="AG30" t="inlineStr">
+        <is>
+          <t>[-2.589744439841989]</t>
+        </is>
+      </c>
+      <c r="AH30" t="inlineStr">
+        <is>
+          <t>[0.26725632440371283]</t>
+        </is>
+      </c>
+      <c r="AI30" t="inlineStr">
+        <is>
+          <t>[-1.1955556342131772]</t>
+        </is>
+      </c>
+      <c r="AJ30" t="inlineStr">
+        <is>
+          <t>[0.17992334010036126]</t>
+        </is>
+      </c>
+      <c r="AK30" t="inlineStr">
+        <is>
+          <t>[-0.6764236181764416]</t>
+        </is>
+      </c>
+      <c r="AL30" t="inlineStr">
+        <is>
+          <t>[0.17794008452088406]</t>
+        </is>
+      </c>
+      <c r="AM30" t="inlineStr">
+        <is>
+          <t>[-2.1965463685253175]</t>
+        </is>
+      </c>
+      <c r="AN30" t="inlineStr">
+        <is>
+          <t>[0.24551793479788347]</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>model_128_64_4</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>[128, 64]</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>[[[0.07999999821186066, 0.005799999926239252, -0.07419999688863754, 0.015799999237060547, 0.03500000014901161, -0.018699999898672104, -0.015799999237060547, -0.043299999088048935, 0.013000000268220901, 0.042500000447034836, -0.10080000013113022, 0.057500001043081284, -0.02810000069439411, 0.10559999942779541, -0.01590000092983246, -0.015799999237060547, 0.06909999996423721, 0.006899999920278788, 0.009600000455975533, -0.08489999920129776, -0.06239999830722809, -0.00860000029206276, -0.0658000037074089, 0.037300001829862595, -0.05820000171661377, -0.061500001698732376, 0.04960000142455101, 0.0917000025510788, -0.01510000042617321, -0.06719999760389328, -0.00279999990016222, 0.1103999987244606, 0.04879999905824661, 0.0210999995470047, 0.03229999914765358, 0.1177000030875206, -0.002199999988079071, -0.013399999588727951, 0.054999999701976776, 0.02410000003874302, -0.03189999982714653, -0.027000000700354576, -0.03830000013113022, 0.014999999664723873, -0.030500000342726707, 0.1274999976158142, 0.06849999725818634, -0.05130000039935112, 0.08389999717473984, -0.042500000447034836, 0.09709999710321426, 0.013399999588727951, -0.05310000106692314, -0.001500000013038516, 0.03840000182390213, 0.13680000603199005, -0.07649999856948853, 0.024900000542402267, 9.999999747378752e-05, -0.05130000039935112, -0.0007999999797903001, 0.02800000086426735, 0.0038999998942017555, -0.0908999964594841, -0.07919999957084656, 0.04610000178217888, 0.03669999912381172, 0.004800000227987766, 0.03620000183582306, 0.027799999341368675, 0.05209999904036522, -0.08340000361204147, -0.03959999978542328, -0.012900000438094139, -0.02850000001490116, -0.042100001126527786, 0.05820000171661377, -0.03319999948143959, -0.026900000870227814, 0.04500000178813934, 0.06790000200271606, -0.03180000185966492, -0.009200000204145908, 0.007699999958276749, -0.039500001817941666, -0.05990000069141388, -0.03359999880194664, -0.011699999682605267, -0.013500000350177288, 0.05959999933838844, -0.021900000050663948, -0.013000000268220901, 0.01140000019222498, 0.02800000086426735, 0.03150000050663948, 0.020999999716877937, 0.04569999873638153, -0.006399999838322401, -0.0071000000461936, 0.037300001829862595, 0.01590000092983246, 0.02329999953508377, -0.04969999939203262, -0.04019999876618385, 0.021400000900030136, 0.0689999982714653, -0.015399999916553497, 0.031599998474121094, -0.003599999938160181, -0.07039999961853027, -0.022099999710917473, -0.007899999618530273, 0.01860000006854534, 0.05869999900460243, 0.03709999844431877, -0.014700000174343586, -0.04170000180602074, 0.009999999776482582, 0.017899999395012856, -0.07649999856948853, 0.14429999887943268, -0.003599999938160181, -0.04270000010728836, 0.0284000001847744, -0.10570000112056732, 0.010300000198185444, 0.0272000003606081, -0.049300000071525574], [-0.06889999657869339, -0.03480000048875809, 0.006200000178068876, -0.008700000122189522, -0.026100000366568565, 0.1177000030875206, 0.006099999882280827, 0.03889999911189079, 0.07580000162124634, -0.04569999873638153, -0.02329999953508377, 0.040699999779462814, -0.009499999694526196, -0.11670000106096268, -0.015699999406933784, 0.027899999171495438, -0.022199999541044235, 0.05429999902844429, 0.0722000002861023, -0.10029999911785126, 0.09849999845027924, -0.020800000056624413, 0.043800000101327896, 0.006200000178068876, -0.03189999982714653, 0.08900000154972076, 0.022299999371170998, -0.02969999983906746, -0.04699999839067459, 0.011900000274181366, -0.00279999990016222, 0.04699999839067459, 0.0019000000320374966, 0.09210000187158585, 0.026499999687075615, 0.029400000348687172, -0.005400000140070915, -0.0034000000450760126, -0.025699999183416367, -0.0333000011742115, 0.08720000088214874, 0.0406000018119812, 0.01720000058412552, -0.015399999916553497, 0.05620000138878822, 0.013799999840557575, -0.0044999998062849045, 0.08190000057220459, 0.011800000444054604, -0.05869999900460243, 0.05950000137090683, -0.03229999914765358, -0.009600000455975533, 0.07249999791383743, -0.023900000378489494, 0.10589999705553055, -0.0026000000070780516, -0.047200001776218414, 0.05900000035762787, -0.01209999993443489, -0.04749999940395355, 0.029899999499320984, 0.010200000368058681, -0.013799999840557575, -0.002400000113993883, 0.031300000846385956, -0.010700000450015068, 0.02019999921321869, -0.10000000149011612, 0.05730000138282776, -0.054099999368190765, -0.05339999869465828, 0.016899999231100082, -0.03460000082850456, -0.00559999980032444, -0.004800000227987766, 0.03500000014901161, 0.020400000736117363, -0.00279999990016222, 0.15029999613761902, -0.05290000140666962, -0.019700000062584877, -0.029999999329447746, -0.07819999754428864, 0.029899999499320984, 0.0034000000450760126, 0.05869999900460243, 0.014399999752640724, -0.08079999685287476, -0.10639999806880951, 0.02889999933540821, -0.04729999974370003, 0.04820000007748604, -0.04270000010728836, 0.0027000000700354576, -0.0357000008225441, -0.06719999760389328, -0.06639999896287918, 0.04439999908208847, -0.0035000001080334187, 0.0035000001080334187, 0.002899999963119626, -0.028599999845027924, -0.0625, -0.0010000000474974513, 0.10010000318288803, 0.03629999980330467, -0.05090000107884407, 0.11919999867677689, -0.01759999990463257, -0.09849999845027924, 0.04010000079870224, -0.06159999966621399, 0.048900000751018524, 0.014600000344216824, -0.000699999975040555, 0.03480000048875809, 0.02669999934732914, 0.03009999915957451, 0.02590000070631504, -0.03150000050663948, 0.017799999564886093, 0.0, 0.01730000041425228, -0.024800000712275505, -0.028200000524520874, 0.0024999999441206455, 0.017999999225139618]], [[-0.05260000005364418, 0.032999999821186066, -0.02539999969303608, 0.017000000923871994, -0.030400000512599945, -0.07109999656677246, 0.021900000050663948, 0.08730000257492065, -0.05380000174045563, 0.0934000015258789, -0.07100000232458115, -0.020600000396370888, 0.11590000241994858, 0.0052999998442828655, -0.05350000038743019, 0.0738999992609024, -0.014100000262260437, 0.09430000185966492, -0.15569999814033508, 0.03519999980926514, 0.11349999904632568, -0.04809999838471413, 0.13989999890327454, 0.02879999950528145, 0.09939999878406525, -0.037300001829862595, -0.11379999667406082, -0.03799999877810478, 0.11640000343322754, 0.23999999463558197, -0.14249999821186066, -0.06279999762773514, -0.02449999935925007, -0.08089999854564667, -0.04740000143647194, 0.04410000145435333, -0.015300000086426735, 0.1014999970793724, 0.01850000023841858, 0.08389999717473984, -0.04659999907016754, -0.19609999656677246, -0.06800000369548798, -0.1526000052690506, -0.08590000122785568, 0.09880000352859497, 0.002400000113993883, -0.01850000023841858, -0.13619999587535858, -0.013399999588727951, 0.09520000219345093, 0.093299999833107, -0.09000000357627869, 0.053700000047683716, 0.0012000000569969416, 0.014399999752640724, -0.10859999805688858, 0.019600000232458115, 0.07750000059604645, 0.12080000340938568, 0.07639999687671661, 0.07689999788999557, 0.014399999752640724, 0.1517000049352646, -0.04600000008940697, -0.08129999786615372, -0.15489999949932098, 0.07069999724626541, -0.09730000048875809, 0.11999999731779099, -0.042100001126527786, 0.21770000457763672, 0.0020000000949949026, -0.021299999207258224, -0.016200000420212746, -0.2985000014305115, 0.11580000072717667, -0.10769999772310257, -0.00559999980032444, -0.12070000171661377, -0.06909999996423721, -0.0729999989271164, 0.03590000048279762, 0.2175000011920929, 0.024000000208616257, -0.06319999694824219, 0.1704999953508377, 0.016599999740719795, 0.07829999923706055, 0.05559999868273735, 0.03400000184774399, -0.008299999870359898, -0.007799999788403511, -0.035999998450279236, 0.10610000044107437, 0.002300000051036477, -0.028999999165534973, -0.05050000175833702, 0.13519999384880066, -0.05400000140070915, 0.008500000461935997, 0.09049999713897705, -0.009200000204145908, 0.016300000250339508, 0.057100001722574234, 0.0038999998942017555, -0.029400000348687172, 0.10440000146627426, -0.05260000005364418, -0.09799999743700027, -0.054099999368190765, -0.035999998450279236, -0.11599999666213989, 0.05810000002384186, -0.007400000002235174, -0.07490000128746033, 0.030799999833106995, 0.1071000024676323, -0.09950000047683716, 0.037300001829862595, -0.03370000049471855, -0.09390000253915787, -0.013299999758601189, -0.14190000295639038, -0.05260000005364418, 0.11940000206232071, 0.0731000006198883, 0.02630000002682209], [0.03480000048875809, 0.08780000358819962, -0.11879999935626984, 0.10980000346899033, 0.08240000158548355, -0.13449999690055847, 0.05249999836087227, 0.028599999845027924, 0.015699999406933784, -0.024000000208616257, 0.1559000015258789, 0.10130000114440918, -0.0203000009059906, -0.05350000038743019, 0.027799999341368675, -0.018799999728798866, -0.013899999670684338, -0.026900000870227814, -0.02539999969303608, -0.26109999418258667, -0.04639999940991402, 0.053700000047683716, -0.062300000339746475, -0.10050000250339508, -0.09390000253915787, 0.10980000346899033, 0.13989999890327454, 0.054099999368190765, 0.11289999634027481, 0.044199999421834946, 0.005400000140070915, -0.13109999895095825, -0.01979999989271164, -0.06260000169277191, 0.020600000396370888, -0.03280000016093254, -0.11400000005960464, -0.08299999684095383, 0.09679999947547913, 0.15620000660419464, 0.025100000202655792, 0.06319999694824219, -0.06759999692440033, 0.01940000057220459, -0.0032999999821186066, 0.01759999990463257, -0.07329999655485153, -0.08810000121593475, 0.12240000069141388, 0.15139999985694885, -0.013000000268220901, 0.15649999678134918, 0.04540000110864639, 0.024900000542402267, -0.07959999889135361, 0.16590000689029694, -0.2125999927520752, -0.014100000262260437, -0.03920000046491623, -0.10909999907016754, -0.01600000075995922, 0.011900000274181366, -0.14020000398159027, -0.05429999902844429, 0.029999999329447746, -0.14180000126361847, 0.021299999207258224, 0.016200000420212746, 0.023600000888109207, 0.03150000050663948, -0.13179999589920044, 0.14429999887943268, -0.0020000000949949026, -0.00800000037997961, -0.016899999231100082, -0.014100000262260437, 0.016899999231100082, -0.03660000115633011, -0.01080000028014183, -0.1177000030875206, 0.01209999993443489, -0.05090000107884407, -0.0544000007212162, 0.02199999988079071, 0.007699999958276749, 0.023800000548362732, 0.045099999755620956, -0.05040000006556511, 0.06769999861717224, 0.04320000112056732, -0.03720000013709068, -0.01720000058412552, 0.08869999647140503, 0.02759999968111515, -0.01899999938905239, 0.16030000150203705, 0.09669999778270721, -0.12269999831914902, -0.08590000122785568, 0.07249999791383743, 0.0949999988079071, -0.04859999939799309, 0.11240000277757645, 0.009600000455975533, -0.10180000215768814, 0.056699998676776886, -0.0006000000284984708, -0.14650000631809235, -0.09700000286102295, 0.025299999862909317, 0.005200000014156103, 0.03709999844431877, -0.09880000352859497, -0.12489999830722809, -0.14730000495910645, 0.1868000030517578, -0.08980000019073486, 0.011800000444054604, -0.0026000000070780516, -0.043800000101327896, 0.10440000146627426, -0.03269999846816063, 0.09480000287294388, -0.0778999999165535, 0.28610000014305115, 0.05770000070333481, 0.057500001043081284, -0.14880000054836273], [-0.0210999995470047, 0.0215000007301569, 0.10920000076293945, -0.04529999941587448, -0.0210999995470047, -0.05139999836683273, 0.07020000368356705, 0.11010000109672546, 0.08860000222921371, -0.055799998342990875, 0.03929999843239784, -0.00989999994635582, -0.05959999933838844, -0.06700000166893005, 0.07129999995231628, -0.0012000000569969416, 0.12479999661445618, -0.03999999910593033, 0.06480000168085098, 0.13369999825954437, -0.018699999898672104, 0.12770000100135803, 0.12229999899864197, 0.01119999960064888, 0.06679999828338623, -0.008299999870359898, -0.06360000371932983, 0.17260000109672546, 0.12540000677108765, 0.07880000025033951, -0.09719999879598618, -0.007300000172108412, -0.0625, -0.18279999494552612, 0.07540000230073929, -0.14030000567436218, 0.10700000077486038, -0.02590000070631504, -0.06920000165700912, -0.14560000598430634, -0.0568000003695488, 0.03530000150203705, -0.10360000282526016, -0.09489999711513519, 0.001500000013038516, -0.02669999934732914, -0.025599999353289604, 0.12449999898672104, 0.16369999945163727, -0.016100000590085983, -0.11829999834299088, 0.045499999076128006, 0.12700000405311584, -0.066600002348423, -0.11720000207424164, 0.07450000196695328, 0.006899999920278788, 0.07119999825954437, -0.032999999821186066, -0.09769999980926514, 0.02669999934732914, -0.0494999997317791, -0.06369999796152115, 0.017899999395012856, 0.07190000265836716, 0.030400000512599945, 0.05559999868273735, -0.014999999664723873, -0.03060000017285347, -0.1459999978542328, -0.12080000340938568, 0.16419999301433563, -0.09120000153779984, -0.07020000368356705, -0.06849999725818634, -0.15240000188350677, 0.021800000220537186, 0.10000000149011612, 0.08569999784231186, 0.09520000219345093, 0.07280000299215317, 0.011599999852478504, 0.01940000057220459, -0.03480000048875809, 0.18369999527931213, -0.04740000143647194, 0.14749999344348907, 0.19580000638961792, -0.09350000321865082, 0.020600000396370888, 0.08489999920129776, -0.12129999697208405, 0.04639999940991402, -0.05249999836087227, -0.07500000298023224, 0.054099999368190765, -0.008299999870359898, 0.2223999947309494, -0.06750000268220901, 0.0560000017285347, 0.011699999682605267, -0.0885000005364418, -0.08460000157356262, -0.005100000184029341, -0.034699998795986176, 0.05660000070929527, 0.0364999994635582, -0.047600001096725464, -0.18140000104904175, -0.007000000216066837, -0.04729999974370003, -0.09009999781847, 0.03680000081658363, 0.04809999838471413, -0.017000000923871994, -0.12200000137090683, 0.08619999885559082, -0.1688999980688095, -0.03999999910593033, -0.039000000804662704, -0.23999999463558197, -0.016499999910593033, 0.07779999822378159, 0.11389999836683273, 0.0210999995470047, -0.04050000011920929, 0.008799999952316284, -0.025499999523162842], [0.020400000736117363, -0.053300000727176666, -0.14869999885559082, 0.03139999881386757, 0.07259999960660934, 0.06930000334978104, -0.01730000041425228, -0.06319999694824219, 0.01590000092983246, -0.027499999850988388, 0.06599999964237213, -0.12399999797344208, -0.05249999836087227, 0.02419999986886978, -0.121799997985363, -0.0032999999821186066, -0.09650000184774399, -0.01979999989271164, -0.012000000104308128, 0.09740000218153, 0.05620000138878822, -0.02930000051856041, 0.1023000031709671, 0.14149999618530273, 0.07569999992847443, 0.041099999099969864, -0.1023000031709671, 0.07020000368356705, -0.2393999993801117, -0.06790000200271606, -0.02969999983906746, 0.028599999845027924, 0.047200001776218414, -0.16590000689029694, 0.061900001019239426, 0.0348999984562397, -0.08079999685287476, 0.07180000096559525, -0.11819999665021896, -0.0860000029206276, 0.06520000100135803, -0.010499999858438969, 0.06379999965429306, -0.05119999870657921, 0.13510000705718994, -0.0019000000320374966, -0.19059999287128448, 0.0364999994635582, 0.2150000035762787, 0.04690000042319298, -0.047600001096725464, 0.010499999858438969, 0.13670000433921814, 0.024000000208616257, -0.1704999953508377, 0.06549999862909317, 0.02810000069439411, 0.006300000008195639, 0.0035000001080334187, -0.049800001084804535, -0.022700000554323196, 0.10419999808073044, -0.053300000727176666, 0.013000000268220901, 0.05090000107884407, 0.05550000071525574, -0.03840000182390213, -0.12030000239610672, -0.10989999771118164, 0.0142000000923872, 0.042100001126527786, -0.10989999771118164, -0.005499999970197678, -0.003599999938160181, -0.006000000052154064, -0.045899998396635056, -0.07190000265836716, -0.1632000058889389, -0.20239999890327454, -0.065700002014637, -0.09860000014305115, -0.10679999738931656, 0.014499999582767487, -9.999999747378752e-05, -0.08309999853372574, 0.13120000064373016, 0.07020000368356705, -0.013899999670684338, 0.05640000104904175, -0.007499999832361937, 0.06620000302791595, -0.09160000085830688, -0.10369999706745148, -0.11999999731779099, -0.00139999995008111, -0.008700000122189522, -0.08290000259876251, 0.14190000295639038, -0.1386999934911728, 0.16210000216960907, 0.03889999911189079, 0.04039999842643738, -0.0617000013589859, 0.011599999852478504, -0.024000000208616257, -0.20489999651908875, -0.14069999754428864, 0.041099999099969864, 0.03319999948143959, 0.06530000269412994, 0.029200000688433647, 0.02250000089406967, -0.16449999809265137, -0.007899999618530273, 0.039000000804662704, 0.031599998474121094, 0.06729999929666519, 0.19769999384880066, -0.08540000021457672, 0.08060000091791153, 0.07509999722242355, -0.1388999968767166, -0.029200000688433647, -0.04010000079870224, 0.17000000178813934, 0.0012000000569969416, -0.10300000011920929, 0.02879999950528145], [-0.05739999935030937, -0.032600000500679016, -0.1290999948978424, -0.09350000321865082, -0.09910000115633011, 0.003100000089034438, -0.01140000019222498, 0.008100000210106373, -0.0934000015258789, 0.0026000000070780516, 0.050599999725818634, 0.03700000047683716, 0.020099999383091927, -0.04769999906420708, 0.04960000142455101, 0.07400000095367432, -0.03240000084042549, -0.05429999902844429, 0.028699999675154686, -0.022299999371170998, -0.11169999837875366, -0.2526000142097473, 0.0421999990940094, -0.04839999973773956, 0.006000000052154064, 0.034299999475479126, -0.10540000349283218, 0.11110000312328339, 0.03660000115633011, -0.258899986743927, -0.050700001418590546, -0.03680000081658363, -0.17080000042915344, -0.13339999318122864, 0.08630000054836273, -0.0027000000700354576, -0.06920000165700912, -0.03709999844431877, -0.0364999994635582, 0.05959999933838844, -0.007600000128149986, 0.030400000512599945, -0.20010000467300415, 0.07980000227689743, -0.061000000685453415, 0.14190000295639038, 0.03959999978542328, 0.038600001484155655, 0.09570000320672989, -0.05950000137090683, -0.012400000356137753, -0.059700001031160355, 0.028999999165534973, 0.009399999864399433, -0.09860000014305115, 0.02459999918937683, 0.08980000019073486, 0.09489999711513519, 0.0071000000461936, 0.06109999865293503, 0.1526000052690506, -0.13040000200271606, 0.15950000286102295, 0.09799999743700027, -0.10570000112056732, 0.039900001138448715, 0.09589999914169312, 0.004999999888241291, -0.023900000378489494, -0.04619999974966049, -0.0066999997943639755, -0.09589999914169312, 0.08990000188350677, 0.05469999834895134, -0.15690000355243683, 0.09619999676942825, -0.04399999976158142, -0.09319999814033508, -0.0551999993622303, -0.1770000010728836, -0.015300000086426735, 0.026499999687075615, -0.01979999989271164, -0.029100000858306885, -0.0017999999690800905, -0.01769999973475933, 0.09279999881982803, 0.16599999368190765, 0.03550000116229057, 0.065700002014637, 0.05920000001788139, 0.18719999492168427, -0.11079999804496765, 0.07329999655485153, 0.15070000290870667, 0.02979999966919422, 0.05490000173449516, -0.062300000339746475, -0.02410000003874302, -0.015300000086426735, -0.031199999153614044, -0.026200000196695328, 0.06449999660253525, 0.005900000222027302, 0.06530000269412994, 0.1728000044822693, 0.024700000882148743, -0.017500000074505806, -0.00930000003427267, 0.03680000081658363, 0.04280000180006027, 0.01600000075995922, 0.09449999779462814, -0.08540000021457672, 0.04019999876618385, 0.06030000001192093, 0.07580000162124634, -0.06019999831914902, -0.09809999912977219, 0.12129999697208405, 0.054499998688697815, -0.039799999445676804, 0.14880000054836273, 0.06639999896287918, -0.0272000003606081, 0.2152000069618225, 0.13570000231266022, 0.19679999351501465], [0.066600002348423, -0.005900000222027302, -0.13269999623298645, 0.0010000000474974513, 0.03970000147819519, 0.13580000400543213, -0.04019999876618385, -0.011599999852478504, 0.14470000565052032, 0.010400000028312206, -0.06610000133514404, 0.2556999921798706, 0.13410000503063202, -0.010999999940395355, -0.032600000500679016, 0.11469999700784683, -0.11050000041723251, 0.03530000150203705, 0.051600001752376556, -0.08760000020265579, -0.010400000028312206, -0.07810000330209732, 0.10350000113248825, 0.11900000274181366, -0.012600000016391277, -0.03350000083446503, -0.005499999970197678, 0.017799999564886093, -0.01489999983459711, 0.05939999967813492, 0.22290000319480896, 0.10419999808073044, -0.13809999823570251, -0.023000000044703484, -0.09640000015497208, -0.05260000005364418, -0.09619999676942825, -0.14069999754428864, 0.07079999893903732, -0.06780000030994415, -0.08959999680519104, 0.054499998688697815, -0.20250000059604645, 0.11270000040531158, -0.020600000396370888, 0.07750000059604645, 0.13079999387264252, 0.02329999953508377, 0.0494999997317791, -0.09809999912977219, 0.06639999896287918, 0.10819999873638153, 0.02590000070631504, -0.042899999767541885, -0.006099999882280827, -0.09560000151395798, 0.15279999375343323, 0.03669999912381172, 0.09319999814033508, 0.12200000137090683, -0.22529999911785126, 0.07400000095367432, -0.033399999141693115, -0.02019999921321869, 0.1256999969482422, 0.03739999979734421, -0.0544000007212162, -0.004399999976158142, -0.004000000189989805, 0.15189999341964722, 0.01769999973475933, -0.020800000056624413, 0.012000000104308128, -0.030400000512599945, -0.0803999975323677, -0.04340000078082085, -0.12449999898672104, -0.1160999983549118, 0.11110000312328339, 0.04989999905228615, -0.11999999731779099, -0.11349999904632568, 0.03280000016093254, 0.0471000000834465, -0.09260000288486481, -0.044599998742341995, -0.09769999980926514, 0.1265999972820282, -0.039000000804662704, -0.013199999928474426, -0.0019000000320374966, -0.017400000244379044, -0.03099999949336052, 0.03880000114440918, -0.15049999952316284, 0.12520000338554382, -0.03319999948143959, -0.0034000000450760126, 0.1023000031709671, 0.1371999979019165, 0.011900000274181366, -0.01600000075995922, -0.04039999842643738, 0.03240000084042549, 0.0052999998442828655, 0.08330000191926956, 0.1339000016450882, 0.04490000009536743, -0.14720000326633453, 0.015599999576807022, -0.024299999698996544, -0.061400000005960464, -0.17389999330043793, -0.054499998688697815, -0.008100000210106373, 0.03840000182390213, -0.026100000366568565, -0.040699999779462814, -0.022299999371170998, 0.09690000116825104, -0.03929999843239784, -0.05640000104904175, -0.06870000064373016, 0.07240000367164612, -0.053700000047683716, -0.17470000684261322, -0.008200000040233135, -0.13660000264644623], [-0.1289999932050705, -0.044599998742341995, 0.04100000113248825, 0.1469999998807907, -0.12099999934434891, -0.018799999728798866, -0.05559999868273735, 0.19290000200271606, 0.05939999967813492, -0.014600000344216824, -0.03920000046491623, -0.016100000590085983, 0.0215000007301569, 0.17520000040531158, -0.1678999960422516, 0.2362000048160553, 0.03280000016093254, 0.03020000085234642, 0.12210000306367874, -0.04670000076293945, 0.026100000366568565, 0.03889999911189079, 0.020400000736117363, 0.027499999850988388, 0.14339999854564667, 0.0035000001080334187, 0.07999999821186066, 0.04749999940395355, -0.06840000301599503, 0.148499995470047, -0.10010000318288803, 0.03460000082850456, 0.2637999951839447, -0.07859999686479568, -0.07270000129938126, -0.09520000219345093, 0.10719999670982361, -0.02979999966919422, -0.028699999675154686, 0.09690000116825104, -0.03739999979734421, -0.009399999864399433, 0.0908999964594841, 0.14890000224113464, -0.0658000037074089, 0.06129999831318855, -0.061000000685453415, 0.032999999821186066, 0.10769999772310257, -0.0020000000949949026, -0.07530000060796738, -0.07930000126361847, 0.10760000348091125, -0.066600002348423, 0.05270000174641609, 0.03720000013709068, 0.11969999969005585, 0.06400000303983688, 0.004800000227987766, -0.07039999961853027, -0.03480000048875809, 0.0803999975323677, 0.019300000742077827, -0.03720000013709068, 0.01720000058412552, -0.06620000302791595, -0.1152999997138977, 0.10689999908208847, -0.033799998462200165, -0.0575999990105629, -0.15389999747276306, -0.0032999999821186066, -0.09529999643564224, 0.07649999856948853, 0.04479999840259552, 0.12240000069141388, 0.09939999878406525, -0.08209999650716782, 0.038600001484155655, 0.05350000038743019, 0.0071000000461936, -0.15399999916553497, -0.11990000307559967, -0.013000000268220901, -0.08569999784231186, 0.028599999845027924, -0.11270000040531158, -0.006899999920278788, 0.025699999183416367, 0.014800000004470348, -0.05260000005364418, 0.0032999999821186066, 0.02449999935925007, 0.09399999678134918, 0.059700001031160355, 0.017799999564886093, 0.04600000008940697, 0.027899999171495438, 0.023800000548362732, -0.035999998450279236, -0.048700001090765, -0.010599999688565731, -0.046799998730421066, 0.08640000224113464, -0.20640000700950623, 0.09849999845027924, 0.10890000313520432, -0.032600000500679016, 0.02329999953508377, -0.03519999980926514, 0.07980000227689743, 0.22789999842643738, 0.03220000118017197, -0.014100000262260437, 0.0949999988079071, 0.15279999375343323, 0.14380000531673431, 0.0017000000225380063, -0.014399999752640724, -0.034299999475479126, 0.03620000183582306, -0.14659999310970306, 0.04919999837875366, -0.007699999958276749, -0.15279999375343323, 0.03310000151395798, 0.13779999315738678, 0.07159999758005142], [-0.10109999775886536, 0.10490000247955322, 0.02250000089406967, 0.0071000000461936, 0.035100001841783524, 0.021700000390410423, -0.002300000051036477, -0.05260000005364418, -0.0364999994635582, -0.09600000083446503, 0.10360000282526016, 0.17900000512599945, -0.020400000736117363, 0.10970000177621841, -0.02449999935925007, 0.2079000025987625, -0.09780000150203705, -0.12999999523162842, -0.008799999952316284, 0.05939999967813492, 0.040699999779462814, -0.06520000100135803, 0.025599999353289604, -0.04170000180602074, -0.05730000138282776, -0.1420000046491623, -0.07850000262260437, -0.0803999975323677, -0.014600000344216824, 0.014000000432133675, 0.2433999925851822, -0.16269999742507935, 0.06319999694824219, -0.04899999871850014, 0.08139999955892563, -0.04619999974966049, 0.04270000010728836, -0.09610000252723694, -0.14579999446868896, 0.020500000566244125, -0.039900001138448715, 0.0786999985575676, 0.020600000396370888, -0.05990000069141388, -0.08510000258684158, -0.1678999960422516, 0.07150000333786011, -0.06560000032186508, 0.015399999916553497, 0.016300000250339508, -0.00559999980032444, 0.03590000048279762, 0.0925000011920929, -0.04340000078082085, 0.10779999941587448, -0.04360000044107437, -0.10790000110864639, -0.1273999959230423, 0.11330000311136246, -0.15309999883174896, 0.07370000332593918, 0.10440000146627426, -0.053599998354911804, -0.07419999688863754, 0.032999999821186066, 0.0052999998442828655, 0.04600000008940697, -0.13910000026226044, -0.00430000014603138, 0.010300000198185444, 0.007499999832361937, 0.07400000095367432, -0.06539999693632126, 0.24199999868869781, -0.0737999975681305, 0.0640999972820282, -0.006800000090152025, -0.04580000042915344, -0.0723000019788742, 0.050599999725818634, 0.016300000250339508, 0.09969999641180038, -0.030700000002980232, -0.0430000014603138, 0.12880000472068787, -0.0406000018119812, 0.10970000177621841, -0.1468999981880188, 0.04479999840259552, -0.02459999918937683, 0.029400000348687172, -0.05559999868273735, 0.00570000009611249, 0.005499999970197678, 0.07609999924898148, -0.0008999999845400453, -0.08399999886751175, 0.009800000116229057, 0.18700000643730164, 0.16509999334812164, 0.032999999821186066, -0.006099999882280827, -0.07419999688863754, -0.026000000536441803, -0.018400000408291817, 0.007600000128149986, -0.040800001472234726, -0.038600001484155655, 0.07349999994039536, -0.09860000014305115, -0.0812000036239624, -0.11670000106096268, 0.09570000320672989, -0.18559999763965607, 0.1436000019311905, -0.10660000145435333, 0.05779999867081642, -0.014800000004470348, 0.04729999974370003, 0.1859000027179718, -0.03319999948143959, 0.008200000040233135, -0.09350000321865082, -0.09260000288486481, -0.0658000037074089, 0.17749999463558197, 0.0860000029206276, -0.05810000002384186], [-0.08649999648332596, 0.12939999997615814, -0.0034000000450760126, 0.18019999563694, 0.06539999693632126, 0.07609999924898148, 0.0917000025510788, -0.08940000087022781, -0.07460000365972519, 0.10999999940395355, 0.03269999846816063, 0.10249999910593033, 0.03480000048875809, -0.005499999970197678, -0.07150000333786011, 0.027300000190734863, 0.19769999384880066, -0.06689999997615814, -0.052000001072883606, 0.02969999983906746, -0.11219999939203262, 0.04580000042915344, 0.0006000000284984708, -0.020099999383091927, 0.22349999845027924, -0.08640000224113464, -0.07180000096559525, 0.11760000139474869, -0.20229999721050262, -0.016200000420212746, -0.01850000023841858, -0.18639999628067017, -0.04820000007748604, -0.14720000326633453, 0.018300000578165054, -0.0414000004529953, -0.10689999908208847, 0.1467999964952469, 0.08969999849796295, -0.013399999588727951, -0.12409999966621399, -0.000699999975040555, -0.12370000034570694, 0.0044999998062849045, -0.06109999865293503, 0.024700000882148743, -0.193900004029274, 0.004900000058114529, -0.09989999979734421, -0.04690000042319298, -0.06700000166893005, -0.03889999911189079, -0.16009999811649323, 0.13199999928474426, -0.03240000084042549, -0.07620000094175339, -0.17399999499320984, -0.007300000172108412, -0.04729999974370003, 0.004699999932199717, -0.10580000281333923, -0.045099999755620956, -0.04149999842047691, 0.06300000101327896, -0.06369999796152115, 0.1128000020980835, 0.07720000296831131, 0.05550000071525574, -0.05490000173449516, 0.10109999775886536, 0.04470000043511391, -0.006099999882280827, -0.031199999153614044, 0.0940999984741211, 0.0478999987244606, 0.06809999793767929, -0.008299999870359898, -0.023099999874830246, -0.04170000180602074, -0.09910000115633011, -0.052299998700618744, -0.07180000096559525, -0.07259999960660934, 0.016200000420212746, 0.08529999852180481, 0.012799999676644802, -0.10530000180006027, -0.06129999831318855, -0.10279999673366547, -0.00430000014603138, -0.07410000264644623, -0.08340000361204147, 0.03099999949336052, -0.10119999945163727, -0.12929999828338623, -0.08110000193119049, -0.025299999862909317, -0.07620000094175339, 0.06700000166893005, 0.06530000269412994, 0.07999999821186066, -0.09070000052452087, -0.06549999862909317, -0.07890000194311142, -0.14139999449253082, 0.10700000077486038, 0.1396999955177307, -0.02239999920129776, 0.03920000046491623, -0.11909999698400497, 0.026000000536441803, 0.05270000174641609, -0.01080000028014183, 0.04650000110268593, 0.08550000190734863, -0.031300000846385956, -0.06520000100135803, -0.09600000083446503, 0.01940000057220459, -0.04540000110864639, 0.04170000180602074, 0.18050000071525574, 0.004399999976158142, 0.14509999752044678, 0.028599999845027924, -0.05050000175833702, -0.12319999933242798, 0.17679999768733978], [0.043299999088048935, 0.17499999701976776, 0.1429000049829483, -0.016499999910593033, -0.01899999938905239, -0.02239999920129776, 0.02500000037252903, -0.02759999968111515, -0.18160000443458557, 0.23280000686645508, 0.1348000019788742, -0.038100000470876694, -0.1088000014424324, 0.07930000126361847, 0.07349999994039536, 0.0284000001847744, 0.03539999946951866, 0.07999999821186066, -0.13580000400543213, -0.038100000470876694, 0.18250000476837158, -0.13899999856948853, 0.007499999832361937, -0.0027000000700354576, -0.13339999318122864, 0.12210000306367874, 0.024700000882148743, -0.016300000250339508, -0.03290000185370445, 0.06260000169277191, 0.015699999406933784, 0.017100000753998756, -0.005900000222027302, 0.02449999935925007, -0.1517000049352646, -0.0917000025510788, -0.09049999713897705, 0.12210000306367874, -0.0333000011742115, 0.07339999824762344, -0.08070000261068344, 0.1046999990940094, -0.07450000196695328, 0.05050000175833702, 0.029100000858306885, -0.15129999816417694, 0.020899999886751175, 0.17389999330043793, 0.16120000183582306, 0.014499999582767487, -0.02370000071823597, -0.01889999955892563, -0.01119999960064888, -0.04439999908208847, -0.014800000004470348, 0.019099999219179153, -0.030799999833106995, -0.05959999933838844, -0.07419999688863754, 0.012400000356137753, -0.0625, 0.03579999879002571, 0.03720000013709068, -0.08399999886751175, -0.09019999951124191, 0.05730000138282776, 0.015799999237060547, -0.05420000106096268, 0.12229999899864197, 0.10040000081062317, 0.08370000123977661, -0.07079999893903732, -0.10010000318288803, -0.007499999832361937, 0.0794999971985817, 0.13920000195503235, -0.032999999821186066, -0.0272000003606081, 0.030899999663233757, 0.008999999612569809, -0.17270000278949738, 0.13169999420642853, -0.04170000180602074, 0.13840000331401825, 0.054499998688697815, -0.040300000458955765, 0.10220000147819519, 0.12120000272989273, 0.11289999634027481, 0.17790000140666962, 0.028599999845027924, 0.025299999862909317, -0.020800000056624413, -0.14900000393390656, -0.0215000007301569, 0.07800000160932541, -0.02449999935925007, 0.11010000109672546, 0.07249999791383743, -0.1356000006198883, -0.00700000021606683</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>[[[0.10639999806880951, 0.044199999421834946, -0.0608999989926815, -0.0284000001847744, 0.06769999861717224, -0.0738999992609024, -0.03350000083446503, -0.05299999937415123, -0.04360000044107437, 0.029500000178813934, -0.07280000299215317, -0.009499999694526196, -0.015599999576807022, 0.13830000162124634, -0.000699999975040555, -0.043800000101327896, 0.07419999688863754, -0.03909999877214432, -0.0625, 0.0005000000237487257, -0.12250000238418579, -0.010599999688565731, -0.07440000027418137, -0.03620000183582306, -0.021400000900030136, -0.10970000177621841, 0.011099999770522118, 0.09719999879598618, -0.004000000189989805, -0.061799999326467514, -0.014999999664723873, 0.08250000327825546, 0.016699999570846558, -0.0357000008225441, -0.011500000022351742, 0.07519999891519547, -0.035599999129772186, -0.0203000009059906, 0.06449999660253525, 0.052799999713897705, -0.08470000326633453, -0.03790000081062317, -0.05719999969005585, 0.033900000154972076, -0.06109999865293503, 0.09359999746084213, 0.0729999989271164, -0.0892999991774559, 0.04560000076889992, 0.03220000118017197, 0.05860000103712082, 0.043699998408555984, -0.0421999990940094, -0.09610000252723694, 0.06960000097751617, 0.12070000171661377, -0.07670000195503235, 0.06400000303983688, -0.04410000145435333, 0.03849999979138374, 0.039900001138448715, -0.0007999999797903001, 0.006200000178068876, -0.05869999900460243, -0.07199999690055847, -0.029200000688433647, 0.02879999950528145, -0.020600000396370888, 0.0860000029206276, -0.008700000122189522, 0.08340000361204147, -0.041999999433755875, -0.04100000113248825, 0.008500000461935997, -0.00570000009611249, -0.047200001776218414, 0.07090000063180923, -0.04270000010728836, 0.02019999921321869, -0.04639999940991402, 0.07580000162124634, -0.041099999099969864, 0.0333000011742115, 0.053300000727176666, -0.06480000168085098, -0.04729999974370003, -0.07620000094175339, -0.023499999195337296, 0.0608999989926815, 0.10409999638795853, -0.03830000013113022, 0.0357000008225441, -0.03830000013113022, 0.07429999858140945, 0.051600001752376556, 0.06400000303983688, 0.07000000029802322, 0.05559999868273735, -0.050999999046325684, 0.056699998676776886, 0.022299999371170998, 0.010200000368058681, -0.02199999988079071, 0.00419999985024333, -9.999999747378752e-05, 0.037700001150369644, -0.04259999841451645, 0.06390000134706497, -0.08009999990463257, -0.08089999854564667, 0.025599999353289604, -0.06469999998807907, 0.06369999796152115, 0.02410000003874302, 0.023099999874830246, -0.027000000700354576, -0.039400000125169754, -0.033900000154972076, -0.016300000250339508, -0.07199999690055847, 0.09629999846220016, 0.01549999974668026, -0.013700000010430813, 0.032999999821186066, -0.08309999853372574, 0.06030000001192093, 0.041600000113248825, -0.06530000269412994], [-0.09309999644756317, -0.021800000220537186, 0.053700000047683716, 0.028699999675154686, -0.03229999914765358, 0.08959999680519104, 0.010599999688565731, 0.0835999995470047, 0.07320000231266022, -0.09300000220537186, 0.05730000138282776, 0.0032999999821186066, 0.014800000004470348, -0.147599995136261, -0.00800000037997961, 0.03689999878406525, -0.09600000083446503, 0.011599999852478504, 0.09030000120401382, -0.04340000078082085, 0.1111999973654747, 0.006899999920278788, 0.10040000081062317, -0.001500000013038516, 0.014100000262260437, 0.09120000153779984, -0.05249999836087227, -0.11140000075101852, -0.025800000876188278, 0.059300001710653305, -0.035999998450279236, -0.03519999980926514, -0.038100000470876694, 0.04560000076889992, 0.007199999876320362, -0.04740000143647194, 0.06939999759197235, 0.043699998408555984, -0.065700002014637, -0.04879999905824661, 0.09489999711513519, 0.025200000032782555, 0.04809999838471413, -0.037700001150369644, 0.053599998354911804, -0.06210000067949295, -0.061900001019239426, 0.10180000215768814, -0.07440000027418137, 0.0007999999797903001, -0.002199999988079071, -0.026399999856948853, 0.016599999740719795, 0.14890000224113464, -0.08910000324249268, 0.07680000364780426, 0.00930000003427267, -0.06729999929666519, 0.059700001031160355, -0.01119999960064888, -0.02410000003874302, -0.004999999888241291, 0.01769999973475933, 0.08789999783039093, 0.05979999899864197, 0.006899999920278788, -0.06880000233650208, 0.04039999842643738, -0.10809999704360962, 0.01080000028014183, -0.08950000256299973, 0.0203000009059906, 0.01810000091791153, -0.04749999940395355, 0.028300000354647636, 0.030899999663233757, 0.014399999752640724, 0.030700000002980232, 0.04320000112056732, 0.07760000228881836, -0.10220000147819519, 0.02329999953508377, -0.013399999588727951, -0.07129999995231628, 0.08540000021457672, 0.07859999686479568, 0.04470000043511391, 0.025299999862909317, -0.09279999881982803, -0.10620000213384628, 0.08709999918937683, -0.05400000140070915, 0.028699999675154686, -0.06069999933242798, -0.005799999926239252, -0.08699999749660492, -0.09120000153779984, -0.06419999897480011, 0.0917000025510788, -0.09700000286102295, -0.057500001043081284, -0.05609999969601631, 0.019700000062584877, -0.019200000911951065, -0.009100000374019146, 0.056699998676776886, 0.026900000870227814, -0.052000001072883606, 0.10509999841451645, 0.0015999999595806003, -0.09790000319480896, 0.06769999861717224, -0.04360000044107437, 0.021299999207258224, -0.00279999990016222, 0.053700000047683716, 0.07259999960660934, 0.03200000151991844, 0.0714000016450882, 0.07280000299215317, -0.10899999737739563, 0.03750000149011612, 0.018699999898672104, -0.026599999517202377, 0.08269999921321869, -0.04349999874830246, -0.05909999832510948, 0.07559999823570251]], [[-0.03200000151991844, 0.12039999663829803, -0.022199999541044235, -0.032600000500679016, 0.045499999076128006, -0.1582999974489212, -0.035999998450279236, 0.1298000067472458, -0.01489999983459711, -0.0031999999191612005, -0.057999998331069946, -0.11980000138282776, 0.07029999792575836, 0.02979999966919422, -0.016499999910593033, 0.02979999966919422, -0.02800000086426735, 0.04270000010728836, -0.21289999783039093, -0.06310000270605087, 0.042399998754262924, -0.01140000019222498, 0.2337999939918518, -0.056299999356269836, 0.12300000339746475, -0.04809999838471413, -0.13230000436306, -0.11550000309944153, 0.12049999833106995, 0.2117999941110611, -0.2053000032901764, -0.08160000294446945, -0.10040000081062317, -0.13349999487400055, 0.0010999999940395355, 0.009200000204145908, -0.007899999618530273, 0.10289999842643738, 0.11509999632835388, 0.11190000176429749, -0.06989999860525131, -0.2822999954223633, -0.08389999717473984, -0.10450000315904617, -0.09120000153779984, 0.06549999862909317, 0.017000000923871994, -0.05090000107884407, -0.22579999268054962, 0.07109999656677246, 0.12319999933242798, 0.13830000162124634, -0.09889999777078629, 0.07989999651908875, -0.03519999980926514, 0.04149999842047691, -0.120899997651577, 0.031599998474121094, 0.010099999606609344, 0.12890000641345978, 0.09009999781847, -0.008200000040233135, 0.08489999920129776, 0.14509999752044678, 0.0027000000700354576, -0.19050000607967377, -0.25099998712539673, 0.10750000178813934, -0.006000000052154064, 0.23389999568462372, -0.09870000183582306, 0.2167000025510788, -0.0003000000142492354, -0.0568000003695488, 0.07169999927282333, -0.27619999647140503, 0.1881999969482422, -0.1454000025987625, -0.008500000461935997, -0.18930000066757202, -0.06199999898672104, -0.07569999992847443, 0.13089999556541443, 0.2888999879360199, 0.11739999800920486, -0.05820000171661377, 0.12890000641345978, -0.00570000009611249, 0.08609999716281891, 0.13019999861717224, 0.03500000014901161, -0.06210000067949295, -0.04659999907016754, -0.0013000000035390258, 0.14810000360012054, 0.019099999219179153, 0.03750000149011612, -0.0333000011742115, 0.14640000462532043, -0.1137000024318695, 0.016100000590085983, 0.010400000028312206, 0.021400000900030136, 0.10270000249147415, -0.05660000070929527, 0.007000000216066837, -0.10220000147819519, 0.15139999985694885, -0.11990000307559967, -0.1623000055551529, 0.01080000028014183, -0.03849999979138374, -0.0617000013589859, 0.030899999663233757, 0.02290000021457672, -0.11190000176429749, 0.03720000013709068, 0.044599998742341995, -0.04179999977350235, -0.005900000222027302, -0.12549999356269836, -0.05510000139474869, -0.04910000041127205, -0.08500000089406967, 0.010999999940395355, 0.16050000488758087, 0.18330000340938568, 0.058400001376867294], [0.054099999368190765, 0.1128000020980835, -0.12189999967813492, 0.17260000109672546, 0.07129999995231628, -0.12530000507831573, -0.00279999990016222, -0.006500000134110451, 0.04670000076293945, -0.013100000098347664, 0.1501999944448471, 0.1826999932527542, -0.008100000210106373, -0.059700001031160355, 0.028699999675154686, -0.03689999878406525, -0.023900000378489494, -0.02759999968111515, -0.046799998730421066, -0.29910001158714294, -0.053599998354911804, 0.03420000150799751, -0.08429999649524689, -0.07760000228881836, -0.09200000017881393, 0.07890000194311142, 0.15520000457763672, 0.08060000091791153, 0.09139999747276306, 0.07819999754428864, -0.009100000374019146, -0.1315000057220459, 0.015300000086426735, -0.04450000077486038, 0.02160000056028366, 0.022299999371170998, -0.1257999986410141, -0.05079999938607216, 0.039400000125169754, 0.1639000028371811, 0.0681999996304512, 0.09200000017881393, -0.0763000026345253, 0.057999998331069946, -0.01899999938905239, 0.03720000013709068, -0.05689999833703041, -0.08730000257492065, 0.1420000046491623, 0.133200004696846, 0.05260000005364418, 0.19850000739097595, 0.012000000104308128, 0.06939999759197235, -0.14169999957084656, 0.17820000648498535, -0.23070000112056732, 0.013899999670684338, -0.039000000804662704, -0.11389999836683273, -0.06289999932050705, 0.005900000222027302, -0.08129999786615372, -0.07810000330209732, 0.029100000858306885, -0.1565999984741211, 0.08290000259876251, 0.04569999873638153, 0.029400000348687172, 0.08179999887943268, -0.1347000002861023, 0.16220000386238098, -0.011500000022351742, -0.06849999725818634, -0.06499999761581421, -0.017100000753998756, 0.06289999932050705, -0.06639999896287918, -0.002199999988079071, -0.12020000070333481, 0.0005000000237487257, -0.03629999980330467, -0.042899999767541885, -0.015200000256299973, -0.01850000023841858, 0.04039999842643738, 0.018699999898672104, -0.03400000184774399, -0.031199999153614044, -0.01140000019222498, -0.012900000438094139, -0.014299999922513962, 0.11029999703168869, 0.01679999940097332, -0.013199999928474426, 0.14249999821186066, 0.1527000069618225, -0.15449999272823334, -0.09640000015497208, 0.08739999681711197, 0.08619999885559082, -0.01269999984651804, 0.07980000227689743, -0.017100000753998756, -0.1256999969482422, 0.06310000270605087, 0.02800000086426735, -0.13220000267028809, -0.0674000009894371, -0.012600000016391277, -0.024299999698996544, 0.045099999755620956, -0.07100000232458115, -0.09589999914169312, -0.12680000066757202, 0.20579999685287476, -0.10140000283718109, 0.04479999840259552, 0.011800000444054604, -0.04699999839067459, 0.13689999282360077, -0.00800000037997961, 0.10029999911785126, -0.07660000026226044, 0.2599000036716461, 0.1251000016927719, -0.013299999758601189, -0.19660000503063202], [-0.015799999237060547, -0.039900001138448715, 0.0908999964594841, 0.03669999912381172, -0.051600001752376556, 0.02979999966919422, 0.09189999848604202, 0.05460000038146973, 0.08640000224113464, -0.009399999864399433, -9.999999747378752e-05, 0.013299999758601189, -0.026399999856948853, -0.04050000011920929, 0.026900000870227814, -0.002099999925121665, 0.13750000298023224, 0.020600000396370888, 0.02370000071823597, 0.14229999482631683, 0.03180000185966492, 0.07670000195503235, 0.051899999380111694, 0.10350000113248825, -0.029400000348687172, -0.06040000170469284, -0.03359999880194664, 0.22859999537467957, 0.10809999704360962, 0.09459999948740005, -0.04520000144839287, 0.009499999694526196, 0.020500000566244125, -0.1501999944448471, 0.07810000330209732, -0.10090000182390213, 0.10000000149011612, 0.00930000003427267, -0.09130000323057175, -0.17910000681877136, -0.04410000145435333, 0.0714000016450882, -0.09009999781847, -0.09510000050067902, -0.008500000461935997, 0.019899999722838402, -0.007699999958276749, 0.15379999577999115, 0.24609999358654022, -0.06340000033378601, -0.09790000319480896, 0.048900000751018524, 0.10909999907016754, -0.07660000026226044, -0.14980000257492065, 0.08540000021457672, 0.011900000274181366, 0.10189999639987946, 0.04390000179409981, -0.08780000358819962, 0.02290000021457672, 0.002300000051036477, -0.08709999918937683, -0.02500000037252903, 0.008500000461935997, 0.08240000158548355, 0.14499999582767487, -0.030700000002980232, -0.025699999183416367, -0.13740000128746033, -0.10199999809265137, 0.17139999568462372, -0.09759999811649323, -0.04820000007748604, -0.12780000269412994, -0.15680000185966492, 0.00039999998989515007, 0.09549999982118607, 0.062300000339746475, 0.16099999845027924, 0.06669999659061432, 0.010999999940395355, -0.004999999888241291, -0.033799998462200165, 0.11400000005960464, -0.01979999989271164, 0.1542000025510788, 0.181099995970726, -0.10119999945163727, -0.004399999976158142, 0.050200000405311584, -0.12800000607967377, 0.0868000015616417, -0.08550000190734863, -0.1289999932050705, 0.027499999850988388, -0.05040000006556511, 0.20260000228881836, -0.10119999945163727, 0.0989999994635582, 0.03660000115633011, -0.012900000438094139, -0.09790000319480896, -0.04650000110268593, -0.002199999988079071, 0.07079999893903732, 0.08590000122785568, -0.04650000110268593, -0.10849999636411667, 0.016499999910593033, -0.11749999970197678, -0.13519999384880066, -0.013899999670684338, 0.07410000264644623, 0.0035000001080334187, -0.14090000092983246, 0.07859999686479568, -0.14579999446868896, -0.0689999982714653, -0.04520000144839287, -0.2240000069141388, -0.01720000058412552, 0.09120000153779984, 0.11089999973773956, 0.004800000227987766, -0.010400000028312206, -0.029899999499320984, -0.06199999898672104], [0.025100000202655792, -0.056299999356269836, -0.16419999301433563, -0.008700000122189522, 0.10909999907016754, 0.0544000007212162, -0.01899999938905239, -0.04500000178813934, -0.0012000000569969416, -0.03020000085234642, 0.02889999933540821, -0.22210000455379486, -0.048700001090765, 0.07970000058412552, -0.13300000131130219, -0.025699999183416367, -0.06509999930858612, -0.010900000110268593, -0.05420000106096268, 0.11389999836683273, 0.009200000204145908, -0.017100000753998756, 0.16609999537467957, 0.10740000009536743, 0.04039999842643738, 0.02710000053048134, -0.11550000309944153, 0.05290000140666962, -0.23899999260902405, -0.08420000225305557, -0.01940000057220459, 0.06040000170469284, 0.005799999926239252, -0.18240000307559967, 0.09839999675750732, -0.03840000182390213, -0.07500000298023224, 0.09640000015497208, 0.003599999938160181, -0.07519999891519547, 0.007899999618530273, -0.10249999910593033, 0.05900000035762787, -0.07410000264644623, 0.12759999930858612, 0.05050000175833702, -0.1868000030517578, 0.027699999511241913, 0.18440000712871552, 0.08229999989271164, -0.09149999916553497, 0.0032999999821186066, 0.14910000562667847, -0.023800000548362732, -0.13660000264644623, 0.09290000051259995, 0.043299999088048935, 0.017999999225139618, -0.01360000018030405, -0.022600000724196434, 0.0632999986410141, 0.09390000253915787, -0.07559999823570251, 0.03350000083446503, 0.03590000048279762, 0.005100000184029341, -0.09189999848604202, -0.1306000053882599, -0.05400000140070915, 0.1143999993801117, 0.042899999767541885, -0.10679999738931656, 0.009999999776482582, 0.04749999940395355, 0.05310000106692314, -0.00989999994635582, -0.09009999781847, -0.15240000188350677, -0.2272000014781952, -0.07270000129938126, -0.10360000282526016, -0.11699999868869781, 0.07490000128746033, 0.05490000173449516, -0.051500000059604645, 0.1386999934911728, 0.07419999688863754, -0.06379999965429306, 0.18330000340938568, 0.07090000063180923, 0.03200000151991844, -0.07509999722242355, -0.1216999962925911, -0.11469999700784683, -0.023000000044703484, -0.002899999963119626, -0.08510000258684158, 0.17589999735355377, -0.11990000307559967, 0.15150000154972076, 0.04580000042915344, -0.0052999998442828655, 0.021400000900030136, 0.04439999908208847, -0.04490000009536743, -0.18070000410079956, -0.19040000438690186, 0.059700001031160355, -0.0012000000569969416, 0.06210000067949295, 0.0551999993622303, -0.022700000554323196, -0.19629999995231628, -0.02590000070631504, 0.06019999831914902, -0.033399999141693115, 0.0689999982714653, 0.1525000035762787, -0.08780000358819962, 0.053599998354911804, 0.014100000262260437, -0.12020000070333481, -0.04450000077486038, 0.0013000000035390258, 0.22460000216960907, -0.012400000356137753, -0.02319999970495701, 0.06859999895095825], [-0.026499999687075615, 0.04639999940991402, -0.058800000697374344, -0.0746999979019165, -0.10249999910593033, -0.07429999858140945, -0.08380000293254852, 0.014999999664723873, -0.10830000042915344, -0.0502999983727932, 0.07559999823570251, 0.05380000174045563, -0.043800000101327896, -0.09839999675750732, 0.12229999899864197, 0.03229999914765358, -0.011300000362098217, -0.10520000010728836, -0.040699999779462814, -0.09019999951124191, -0.19689999520778656, -0.19089999794960022, 0.09989999979734421, -0.07769999653100967, 0.07970000058412552, -0.00019999999494757503, -0.09600000083446503, 0.005100000184029341, 0.005900000222027302, -0.29670000076293945, -0.07540000230073929, -0.07859999686479568, -0.20559999346733093, -0.21780000627040863, 0.08569999784231186, -0.05559999868273735, -0.021700000390410423, -0.022099999710917473, 0.027799999341368675, 0.08940000087022781, 0.04769999906420708, -0.0026000000070780516, -0.23160000145435333, 0.07530000060796738, -0.07800000160932541, 0.08749999850988388, -0.00039999998989515007, -0.03720000013709068, 0.019899999722838402, 0.020400000736117363, 0.008700000122189522, -0.0142000000923872, 0.041600000113248825, 0.05570000037550926, -0.13670000433921814, 0.012500000186264515, 0.08079999685287476, 0.11869999766349792, -0.06639999896287918, 0.0357000008225441, 0.23440000414848328, -0.20880000293254852, 0.22259999811649323, 0.08460000157356262, -0.052299998700618744, -0.0284000001847744, 0.06700000166893005, 0.08479999750852585, 0.05820000171661377, 0.04529999941587448, -0.05849999934434891, -0.1006999984383583, 0.035999998450279236, 0.007000000216066837, -0.1388999968767166, 0.15399999916553497, 0.019899999722838402, -0.12210000306367874, -0.0746999979019165, -0.2628999948501587, -0.07029999792575836, 0.07840000092983246, 0.059700001031160355, 0.025499999523162842, -0.03240000084042549, -0.025699999183416367, 0.024800000712275505, 0.09489999711513519, 0.08380000293254852, 0.07670000195503235, 0.10610000044107437, 0.1850000023841858, -0.12120000272989273, 0.07580000162124634, 0.1737000048160553, 0.0406000018119812, 0.12300000339746475, -0.07419999688863754, -0.04149999842047691, -0.07900000363588333, 0.010200000368058681, -0.07440000027418137, 0.07039999961853027, 0.04619999974966049, -0.01679999940097332, 0.12880000472068787, 0.013700000010430813, -0.02239999920129776, -0.09629999846220016, -0.016100000590085983, 0.08730000257492065, 0.06849999725818634, 0.15850000083446503, -0.13349999487400055, 0.08860000222921371, 0.049800001084804535, 0.10670000314712524, -0.10090000182390213, -0.041999999433755875, 0.05820000171661377, -0.018200000748038292, 0.03460000082850456, 0.09239999949932098, 0.08470000326633453, 0.049800001084804535, 0.25369998812675476, 0.13729999959468842, 0.24560000002384186], [0.04149999842047691, -0.03869999945163727, -0.10819999873638153, -0.02160000056028366, 0.013100000098347664, 0.13910000026226044, 0.027000000700354576, 0.025800000876188278, 0.07999999821186066, 0.024399999529123306, -0.04340000078082085, 0.2743000090122223, 0.1348000019788742, -0.05380000174045563, -0.014700000174343586, 0.17499999701976776, -0.13289999961853027, -0.058800000697374344, 0.15299999713897705, -0.03180000185966492, -0.01510000042617321, -0.014399999752640724, 0.06319999694824219, 0.0681999996304512, 0.08009999990463257, -0.00019999999494757503, -0.03999999910593033, -9.999999747378752e-05, 0.0010999999940395355, 0.0608999989926815, 0.21739999949932098, 0.07419999688863754, -0.12189999967813492, -0.06199999898672104, -0.12600000202655792, -0.10580000281333923, -0.06120000034570694, -0.19020000100135803, 0.05920000001788139, -0.05779999867081642, -0.09860000014305115, 0.08540000021457672, -0.22360000014305115, 0.06689999997615814, -0.009499999694526196, 0.035100001841783524, 0.06040000170469284, 0.0203000009059906, -0.006399999838322401, -0.13619999587535858, 0.017400000244379044, 0.009600000455975533, 0.07029999792575836, -0.09109999984502792, 0.0575999990105629, -0.12610000371932983, 0.17170000076293945, 0.006399999838322401, 0.0689999982714653, 0.07190000265836716, -0.19050000607967377, 0.11829999834299088, -0.10260000079870224, 0.0763000026345253, 0.1914999932050705, 0.09790000319480896, -0.10670000314712524, -0.019700000062584877, -0.06419999897480011, 0.043800000101327896, 0.04270000010728836, -0.0340999998152256, -0.007699999958276749, 0.03669999912381172, -0.07569999992847443, -0.029400000348687172, -0.1914999932050705, -0.10970000177621841, 0.15530000627040863, 0.06109999865293503, -0.13979999721050262, -0.08980000019073486, -0.010499999858438969, 0.021199999377131462, -0.13410000503063202, -0.07490000128746033, -0.05990000069141388, 0.1460999995470047, -0.006099999882280827, -0.027000000700354576, 0.041099999099969864, -0.010700000450015068, -0.07039999961853027, 0.05950000137090683, -0.14300000667572021, 0.16590000689029694, -0.06419999897480011, -0.014499999582767487, 0.16519999504089355, 0.09030000120401382, -0.05640000104904175, -0.03590000048279762, -0.04089999943971634, 0.015799999237060547, 0.0632999986410141, 0.02630000002682209, 0.1152999997138977, 0.008200000040233135, -0.19249999523162842, 0.07760000228881836, -0.020999999716877937, -0.04830000177025795, -0.20239999890327454, -0.09640000015497208, -0.04399999976158142, 0.120899997651577, -0.02630000002682209, -0.04830000177025795, -0.08020000159740448, 0.1404999941587448, -0.01679999940097332, -0.06019999831914902, -0.06599999964237213, 0.016499999910593033, -0.03799999877810478, -0.2467000037431717, -0.029500000178813934, -0.07209999859333038], [-0.15389999747276306, -0.08489999920129776, 0.049800001084804535, 0.1808999925851822, -0.1589999943971634, 0.03849999979138374, -0.029899999499320984, 0.11540000140666962, 0.15649999678134918, -0.008200000040233135, -0.1234000027179718, -0.013000000268220901, 0.05920000001788139, 0.1467999964952469, -0.17389999330043793, 0.2759000062942505, 0.1395999938249588, 0.04619999974966049, 0.1632000058889389, -0.13580000400543213, 0.10769999772310257, 0.018300000578165054, -0.018699999898672104, 0.1356000006198883, 0.1551000028848648, 0.0010999999940395355, 0.23029999434947968, -0.05400000140070915, -0.03009999915957451, 0.06650000065565109, -0.016899999231100082, 0.0430000014603138, 0.2883000075817108, -0.00019999999494757503, -0.23190000653266907, -0.0731000006198883, 0.02850000001490116, 0.04859999939799309, 0.04039999842643738, 0.037300001829862595, 0.03280000016093254, 0.013299999758601189, 0.13439999520778656, 0.13259999454021454, -0.03999999910593033, 0.049300000071525574, -0.056699998676776886, 0.01730000041425228, 0.21539999544620514, 0.007799999788403511, -0.06719999760389328, -0.1177000030875206, 0.13910000026226044, 0.005100000184029341, 0.1136000007390976, 0.04450000077486038, 0.10480000078678131, 0.020600000396370888, 0.05950000137090683, -0.037300001829862595, -0.04899999871850014, 0.029100000858306885, 0.03680000081658363, -0.06620000302791595, -0.014499999582767487, 0.004600000102072954, -0.10670000314712524, 0.18379999697208405, 0.002400000113993883, -0.12880000472068787, -0.18209999799728394, -0.017799999564886093, -0.053300000727176666, 0.08089999854564667, 0.06840000301599503, 0.17170000076293945, 0.059700001031160355, -0.023600000888109207, -0.08299999684095383, 0.11840000003576279, 0.004800000227987766, -0.059700001031160355, -0.10540000349283218, -0.015599999576807022, -0.16189999878406525, 0.008500000461935997, -0.06970000267028809, -0.07959999889135361, 0.009999999776482582, -0.019999999552965164, -0.0071000000461936, 0.07620000094175339, 0.09459999948740005, 0.01810000091791153, 0.031599998474121094, 0.01360000018030405, -0.029899999499320984, 0.027300000190734863, -0.032099999487400055, -0.05510000139474869, 0.05559999868273735, 0.045499999076128006, -0.033900000154972076, 0.015399999916553497, -0.20409999787807465, 0.10639999806880951, 0.1517000049352646, -0.0430000014603138, 0.08720000088214874, 0.023800000548362732, 0.060100000351667404, 0.22339999675750732, 0.039900001138448715, -0.03840000182390213, 0.07429999858140945, 0.061400000005960464, 0.21230000257492065, 0.16200000047683716, -0.031700000166893005, -0.08020000159740448, 0.10809999704360962, -0.11100000143051147, 0.06780000030994415, -0.019099999219179153, -0.21529999375343323, 0.0007999999797903001, 0.10409999638795853, 0.01510000042617321], [-0.10530000180006027, 0.07639999687671661, 0.026599999517202377, 0.059300001710653305, -0.008500000461935997, 0.04839999973773956, 0.015599999576807022, -0.08649999648332596, -0.026900000870227814, -0.06499999761581421, 0.07850000262260437, 0.23260000348091125, 0.034699998795986176, 0.06560000032186508, -0.02239999920129776, 0.23499999940395355, -0.03150000050663948, -0.13339999318122864, 0.014700000174343586, 0.053599998354911804, 0.07429999858140945, -0.06830000132322311, -0.06930000334978104, 0.0024999999441206455, -0.034699998795986176, -0.14219999313354492, -0.018699999898672104, -0.0771000012755394, -0.010700000450015068, 0.0010999999940395355, 0.2939999997615814, -0.20350000262260437, 0.11479999870061874, -0.027799999341368675, 0.03909999877214432, -0.040699999779462814, 0.05400000140070915, -0.09640000015497208, -0.1348000019788742, -0.012400000356137753, 0.010300000198185444, 0.15569999814033508, -0.007400000002235174, -0.08340000361204147, -0.0763000026345253, -0.20180000364780426, 0.05660000070929527, -0.09529999643564224, 0.07050000131130219, -0.04989999905228615, 0.008899999782443047, 0.005900000222027302, 0.11230000108480453, -0.007899999618530273, 0.13650000095367432, -0.07159999758005142, -0.11010000109672546, -0.125, 0.14920000731945038, -0.1632000058889389, 0.04639999940991402, 0.13009999692440033, -0.059300001710653305, -0.06949999928474426, 0.030500000342726707, 0.08009999990463257, 0.0560000017285347, -0.13169999420642853, -0.007899999618530273, -0.09989999979734421, 0.039000000804662704, 0.07039999961853027, -0.06509999930858612, 0.24940000474452972, -0.13750000298023224, 0.09489999711513519, -0.040800001472234726, -0.004399999976158142, -0.06530000269412994, 0.07999999821186066, 0.004399999976158142, 0.15279999375343323, -0.06880000233650208, -0.09809999912977219, 0.05400000140070915, -0.051899999380111694, 0.1216999962925911, -0.14669999480247498, 0.04969999939203262, -0.06509999930858612, 0.07280000299215317, -0.01140000019222498, 0.04450000077486038, -0.016300000250339508, 0.052400000393390656, -0.01360000018030405, -0.11159999668598175, -0.025800000876188278, 0.15790000557899475, 0.1673000007867813, 0.05079999938607216, 0.07129999995231628, -0.13670000433921814, -0.09679999947547913, 0.023499999195337296, -0.012500000186264515, 0.012299999594688416, -0.050599999725818634, 0.12039999663829803, -0.05700000002980232, -0.10989999771118164, -0.10209999978542328, 0.10509999841451645, -0.17890000343322754, 0.133200004696846, -0.055399999022483826, 0.05790000036358833, 0.05779999867081642, 0.012500000186264515, 0.17309999465942383, 0.03440000116825104, 0.02759999968111515, -0.08569999784231186, -0.12470000237226486, -0.1152999997138977, 0.17399999499320984, 0.029899999499320984, -0.07519999891519547], [-0.1137000024318695, 0.15960000455379486, 0.05180000141263008, 0.1728000044822693, 0.03229999914765358, -0.006099999882280827, 0.09000000357627869, -0.013100000098347664, -0.1703999936580658, 0.12300000339746475, 0.08569999784231186, 0.15449999272823334, 0.01489999983459711, -0.07850000262260437, -0.040800001472234726, 0.041999999433755875, 0.1404999941587448, -0.1688999980688095, 0.01889999955892563, 0.0722000002861023, -0.17399999499320984, 0.14499999582767487, 0.014800000004470348, -0.08399999886751175, 0.350600004196167, -0.044599998742341995, -0.13410000503063202, 0.07989999651908875, -0.20749999582767487, 0.033799998462200165, -0.0738999992609024, -0.21449999511241913, -0.08420000225305557, -0.2160000056028366, 0.025599999353289604, -0.13670000433921814, -0.04619999974966049, 0.121799997985363, 0.04410000145435333, 0.043699998408555984, -0.13300000131130219, 0.005499999970197678, -0.16269999742507935, -0.07900000363588333, -0.05620000138878822, -0.01759999990463257, -0.299699991941452, -0.009600000455975533, -0.19110000133514404, -0.01899999938905239, -0.11389999836683273, -0.09030000120401382, -0.1306000053882599, 0.09109999984502792, -0.010999999940395355, -0.08789999783039093, -0.16110000014305115, -0.0333000011742115, -0.13529999554157257, -0.030500000342726707, -0.060100000351667404, -0.08219999819993973, -0.040300000458955765, 0.17589999735355377, 0.031199999153614044, 0.12330000102519989, -0.05350000038743019, 0.06809999793767929, -0.121799997985363, 0.0052999998442828655, 0.04179999977350235, 0.01720000058412552, -0.06400000303983688, 0.14810000360012054, 0.05959999933838844, 0.10199999809265137, -0.015399999916553497, -0.052799999713897705, -0.032499998807907104, -0.1695999950170517, -0.12430000305175781, -0.05040000006556511, -0.12610000371932983, 0.002099999925121665, 0.08720000088214874, 0.007199999876320362, -0.12460000067949295, -0.10679999738931656, -0.07479999959468842, -0.052000001072883606, 0.010400000028312206, -0.09189999848604202, -0.024399999529123306, -0.0835999995470047, -0.08269999921321869, -0.04560000076889992, 0.011699999682605267, -0.1039000004529953, 0.16850000619888306, 0.008100000210106373, -0.023099999874830246, -0.16619999706745148, -0.07180000096559525, -0.05790000036358833, -0.14000000059604645, 0.0697999969124794, 0.11079999804496765, -0.06780000030994415, -0.08410000056028366, -0.11590000241994858, 0.020600000396370888, 0.1120000034570694, 0.008100000210106373, 0.027000000700354576, 0.05220000073313713, 0.07739999890327454, -0.04989999905228615, -0.14030000567436218, 0.0674000009894371, 0.007699999958276749, 0.03959999978542328, 0.17960000038146973, 0.00800000037997961, 0.11150000244379044, 0.05480000004172325, -0.09440000355243683, -0.16930000483989716, 0.2752000093460083], [0.019500000402331352, 0.19359999895095825, 0.10689999908208847, -0.1216999962925911, 0.026000000536441803, -0.0052999998442828655, 0.0778999999165535, 0.018300000578165054, -0.01850000023841858, 0.12290000170469284, 0.13619999587535858, -0.1362999975681305, -0.1437000036239624, 0.12470000237226486, 0.09049999713897705, 0.07699999958276749, -0.021199999377131462, 0.07590000331401825, -0.09809999912977219, -0.08290000259876251, 0.19840000569820404, -0.164900004863739, 0.10249999910593033, -0.07349999994039536, -0.09719999879598618, 0.11100000143051147, -0.04699999839067459, -0.02449999935925007, 0.04129999876022339, 0.010599999688565731, -0.009600000455975533, 0.0658000037074089, 0.0015999999595806003, 0.07419999688863754, -0.18209999799728394, 0.04600000008940697, -0.21699999272823334, 0.014000000432133675, 0.009499999694526196, 0.05829999968409538, -0.11349999904632568, 0.07159999758005142, -0.054499998688697815, 0.11389999836683273, 0.051500000059604645, -0.12359999865293503, 0.11500000208616257, 0.18889999389648438, 0.10369999706745148, 0.0210999995470047, -0.0658000037074089, -0.05689999833703041, -0.0003000000142492354, -0.0746999979019165, -0.010400000028312206, -0.04230000078678131, -0.003800000064074993, -0.09849999845027924, 0.01209999993443489, -0.014499999582767487, -0.17990000545978546, 0.0982000008225441, 0.012799999676644802, -0.17730000615119934, -0.06520000100135803, 0.017500000074505806, 0.03269999846816063, -0.12099999934434891, 0.1535000056028366, 0.1671999990940094, 0.0421999990940094, -0.13510000705718994, -0.11559999734163284, 0.005499999970197678, 0.12800000607967377, 0.05139999836683273, -0.043299999088048935, -0.011699999682605267, 0.17260000109672546, 0.06350000202655792, -0.08799999952316284, 0.037700001150369644, -0.03660000115633011, 0.10639999806880951, 0.1370999962091446, -0.094200000166893, 0.12860000133514404, 0.23499999940395355, 0.05559999868273735, 0.24199999868869781, -0.0632999986410141, 0.08910000324249268, -0.07190000265836716, -0.09139999747276306, 0.0142000000923872, 0.14229999482631683, -0.054999999701976776, 0.2012999951839447, 0.009399999864399433, -0.13760000467300415, 0.04170000180602074, -0.13439999520778656, -0.008600000292062</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>[0.8823174424189308]</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>[0.026863000635733342]</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>[0.5631142335498087]</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>[0.09974244951058936]</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>[-1.2382268581766476]</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>[0.7325262024635171]</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>[0.8927325485411692]</t>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>[0.024641379529520894]</t>
+        </is>
+      </c>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>[0.7094551336985818]</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>[0.06890591891833055]</t>
+        </is>
+      </c>
+      <c r="O31" t="inlineStr">
+        <is>
+          <t>[0.5642814409267511]</t>
+        </is>
+      </c>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>[0.14324136242819063]</t>
+        </is>
+      </c>
+      <c r="Q31" t="inlineStr">
+        <is>
+          <t>[-0.23409071576093132]</t>
+        </is>
+      </c>
+      <c r="R31" t="inlineStr">
+        <is>
+          <t>[0.13306673109151465]</t>
+        </is>
+      </c>
+      <c r="S31" t="inlineStr">
+        <is>
+          <t>[-0.11793754430395298]</t>
+        </is>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>[0.09419779731274944]</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>[-1.616987557099053]</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>[0.2502445428960194]</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>[-0.2838852154360909]</t>
+        </is>
+      </c>
+      <c r="X31" t="inlineStr">
+        <is>
+          <t>[0.13450061574122252]</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>[-0.21398670282027732]</t>
+        </is>
+      </c>
+      <c r="Z31" t="inlineStr">
+        <is>
+          <t>[0.09990286231063548]</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>[-2.330038291457175]</t>
+        </is>
+      </c>
+      <c r="AB31" t="inlineStr">
+        <is>
+          <t>[0.3063780895517242]</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>[-0.914349958998276]</t>
+        </is>
+      </c>
+      <c r="AD31" t="inlineStr">
+        <is>
+          <t>[0.16041481439854297]</t>
+        </is>
+      </c>
+      <c r="AE31" t="inlineStr">
+        <is>
+          <t>[-0.8545429712062429]</t>
+        </is>
+      </c>
+      <c r="AF31" t="inlineStr">
+        <is>
+          <t>[0.1996936154465433]</t>
+        </is>
+      </c>
+      <c r="AG31" t="inlineStr">
+        <is>
+          <t>[-2.579328945393767]</t>
+        </is>
+      </c>
+      <c r="AH31" t="inlineStr">
+        <is>
+          <t>[0.26648089127477353]</t>
+        </is>
+      </c>
+      <c r="AI31" t="inlineStr">
+        <is>
+          <t>[-1.330243892608192]</t>
+        </is>
+      </c>
+      <c r="AJ31" t="inlineStr">
+        <is>
+          <t>[0.19096089293896934]</t>
+        </is>
+      </c>
+      <c r="AK31" t="inlineStr">
+        <is>
+          <t>[-0.8123694125535643]</t>
+        </is>
+      </c>
+      <c r="AL31" t="inlineStr">
+        <is>
+          <t>[0.19236973456842826]</t>
+        </is>
+      </c>
+      <c r="AM31" t="inlineStr">
+        <is>
+          <t>[-2.7684638094854486]</t>
+        </is>
+      </c>
+      <c r="AN31" t="inlineStr">
+        <is>
+          <t>[0.2894453404385533]</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>model_264_128_0</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>[264, 128]</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>[[[0.03319999948143959, 0.0027000000700354576, -0.016699999570846558, -0.0017999999690800905, 0.12229999899864197, -0.014700000174343586, -0.04670000076293945, -0.05999999865889549, -0.0005000000237487257, -0.16120000183582306, -0.057500001043081284, -0.03150000050663948, 0.04129999876022339, 0.027000000700354576, -0.054999999701976776, 0.0066999997943639755, 0.0007999999797903001, 0.059300001710653305, 0.00139999995008111, -0.021199999377131462, 0.06199999898672104, 0.042500000447034836, 0.11349999904632568, 0.019600000232458115, 0.05620000138878822, -0.0026000000070780516, -0.029600000008940697, 0.05090000107884407, -0.008500000461935997, 0.039400000125169754, 0.014999999664723873, 0.01720000058412552, 0.03959999978542328, 0.014700000174343586, 0.010400000028312206, 0.060499999672174454, -0.015599999576807022, -0.013299999758601189, 0.07540000230073929, -0.02539999969303608, 0.0722000002861023, -0.014800000004470348, -0.05270000174641609, 0.08399999886751175, -0.05649999901652336, 0.015200000256299973, -0.012799999676644802, -0.015799999237060547, 0.018699999898672104, 0.006300000008195639, -0.03020000085234642, 0.09740000218153, 0.07370000332593918, 0.02070000022649765, 0.014800000004470348, -0.029400000348687172, -0.04830000177025795, 0.004000000189989805, -0.07289999723434448, -0.042399998754262924, 0.0008999999845400453, -0.04740000143647194, -0.061400000005960464, -0.007499999832361937, 0.02319999970495701, -0.028599999845027924, 0.02879999950528145, 0.014399999752640724, 0.1039000004529953, -0.06560000032186508, -0.04690000042319298, -0.0005000000237487257, 0.03680000081658363, 0.04340000078082085, -0.10540000349283218, -0.03840000182390213, 0.014999999664723873, 0.025499999523162842, 0.006800000090152025, -0.04230000078678131, 0.03500000014901161, 0.0035000001080334187, 0.019099999219179153, 0.00019999999494757503, 0.05869999900460243, -0.0035000001080334187, -0.053300000727176666, 0.043800000101327896, 0.01119999960064888, -0.0010000000474974513, -0.04439999908208847, -0.06549999862909317, -0.08110000193119049, 0.02759999968111515, 0.018699999898672104, -0.0010000000474974513, 0.026200000196695328, -0.006500000134110451, 0.04010000079870224, -0.0892999991774559, 0.002899999963119626, -0.04540000110864639, -0.14000000059604645, -0.05000000074505806, 0.06949999928474426, -0.03139999881386757, -0.013700000010430813, 0.04580000042915344, -0.007899999618530273, -0.011300000362098217, 0.08389999717473984, 0.03620000183582306, -0.05420000106096268, -0.022199999541044235, 0.049800001084804535, -0.024900000542402267, 0.020400000736117363, 0.026799999177455902, 0.014800000004470348, 0.08070000261068344, -0.02410000003874302, -0.044199999421834946, 0.03819999843835831, -0.003000000026077032, 0.043299999088048935, 0.05959999933838844, 0.021199999377131462, 0.024399999529123306, 0.0357000008225441, -0.05339999869465828, -0.034299999475479126, 0.01360000018030405, -0.08009999990463257, -0.0008999999845400453, 0.02239999920129776, 0.03480000048875809, -0.005799999926239252, -0.03189999982714653, 0.019099999219179153, -0.014800000004470348, -0.019500000402331352, -0.07180000096559525, -0.01759999990463257, -0.07119999825954437, -0.01979999989271164, -0.029600000008940697, -0.07909999787807465, -0.01360000018030405, 0.005400000140070915, -0.03790000081062317, 0.042899999767541885, -0.039799999445676804, -0.1054999977350235, -0.052000001072883606, 0.06800000369548798, -0.05739999935030937, 0.04529999941587448, -0.02500000037252903, 0.01940000057220459, -0.011699999682605267, -0.09629999846220016, -0.03460000082850456, 0.05469999834895134, 0.002400000113993883, 0.007600000128149986, -0.04659999907016754, 0.0038999998942017555, 0.01899999938905239, 0.052400000393390656, -0.0010000000474974513, 0.06689999997615814, -0.014499999582767487, -0.10840000212192535, -0.05849999934434891, 0.09889999777078629, -0.04019999876618385, 0.06459999829530716, -0.047200001776218414, -0.042100001126527786, 0.09960000216960907, -0.04879999905824661, 0.062199998646974564, -0.0142000000923872, -0.029100000858306885, 0.007499999832361937, -0.029999999329447746, 0.06840000301599503, 0.028300000354647636, 0.042500000447034836, -0.03099999949336052, 0.009100000374019146, 0.030899999663233757, 0.02329999953508377, 0.03020000085234642, 0.021199999377131462, 0.015599999576807022, 0.05490000173449516, -0.0215000007301569, 0.016899999231100082, -0.005799999926239252, -0.025299999862909317, 0.05999999865889549, -0.01979999989271164, -0.015300000086426735, -0.0494999997317791, -0.12300000339746475, -0.042500000447034836, 0.048900000751018524, 0.048700001090765, -0.04639999940991402, 0.010999999940395355, -0.08259999752044678, 0.03849999979138374, -0.04430000111460686, -0.007300000172108412, 0.056299999356269836, -0.057999998331069946, -0.07970000058412552, 0.005200000014156103, -0.01979999989271164, -0.049300000071525574, 0.04690000042319298, -0.10719999670982361, -0.04580000042915344, -0.0003000000142492354, -0.09889999777078629, -0.0333000011742115, -0.04740000143647194, 0.02019999921321869, 0.04360000044107437, -0.009200000204145908, -0.05260000005364418, -0.03550000116229057, -0.011099999770522118, 0.007499999832361937, -0.014100000262260437, 0.04490000009536743, 0.042399998754262924, -0.01510000042617321, -0.06759999692440033, -0.02370000071823597, -0.08839999884366989, 0.010200000368058681, -0.04010000079870224, 0.0008999999845400453, 0.04859999939799309, -0.057100001722574234, 0.005499999970197678, 0.03629999980330467, -0.09080000221729279, 0.032099999487400055, -0.02019999921321869, 0.002099999925121665, 0.0031999999191612005, -0.08340000361204147, -0.07880000025033951, -0.02500000037252903, 0.060100000351667404, 0.05620000138878822, 0.03590000048279762, 0.0024999999441206455, 0.0020000000949949026, 0.03680000081658363, 0.018400000408291817], [-0.04270000010728836, -0.04430000111460686, 0.013500000350177288, 0.0027000000700354576, -0.04439999908208847, 0.02290000021457672, 0.015200000256299973, 0.0674000009894371, -0.02459999918937683, 0.0649000033736229, -0.05400000140070915, -0.01549999974668026, -0.03180000185966492, -0.07940000295639038, -0.038600001484155655, 0.04230000078678131, -0.027799999341368675, -0.006800000090152025, 0.025499999523162842, 0.04360000044107437, -0.03880000114440918, 0.06210000067949295, 0.05869999900460243, 0.025100000202655792, -0.015300000086426735, -0.08150000125169754, -0.050599999725818634, -0.002899999963119626, 0.06210000067949295, 0.017899999395012856, -0.06780000030994415, 0.022700000554323196, 0.08009999990463257, 0.05139999836683273, 0.02500000037252903, 0.0, -0.042899999767541885, -0.08730000257492065, 0.021199999377131462, -0.10909999907016754, -0.07370000332593918, 0.009499999694526196, 0.04190000146627426, 0.054999999701976776, 0.013500000350177288, 0.04580000042915344, -0.02800000086426735, 0.007400000002235174, -0.003599999938160181, -0.019200000911951065, -0.02250000089406967, 0.002300000051036477, -0.010099999606609344, 0.026900000870227814, 0.03420000150799751, -0.030400000512599945, 0.03180000185966492, 0.039000000804662704, 0.00800000037997961, 0.0272000003606081, 0.0052999998442828655, -0.0632999986410141, -0.002400000113993883, -0.05460000038146973, -0.021900000050663948, 0.05810000002384186, 0.14980000257492065, 0.00419999985024333, 0.05270000174641609, 0.008899999782443047, 0.16339999437332153, -0.0005000000237487257, 0.0406000018119812, 0.011900000274181366, 0.0215000007301569, 0.12330000102519989, -0.01080000028014183, 0.004999999888241291, -0.06599999964237213, 0.002099999925121665, -0.050999999046325684, -0.022099999710917473, 0.007199999876320362, 0.009499999694526196, -0.03020000085234642, -0.005900000222027302, -0.07810000330209732, -0.018300000578165054, 0.061000000685453415, -0.026000000536441803, 0.008899999782443047, -0.09070000052452087, -0.019600000232458115, -0.0771000012755394, -0.04639999940991402, 0.07829999923706055, 0.01730000041425228, 0.08129999786615372, 0.0364999994635582, -0.03020000085234642, 0.07829999923706055, -0.023600000888109207, -0.026599999517202377, 0.01360000018030405, -0.10450000315904617, 0.06310000270605087, 0.013100000098347664, -0.07620000094175339, -0.09239999949932098, -0.10279999673366547, 0.020999999716877937, -0.05339999869465828, -0.10809999704360962, -0.10920000076293945, 0.09769999980926514, -0.05290000140666962, 0.02669999934732914, 0.0215000007301569, 0.07360000163316727, 0.0010999999940395355, 0.05040000006556511, 0.018200000748038292, 0.0017999999690800905, 0.09009999781847, 0.03020000085234642, -0.003700000001117587, -0.04699999839067459, -0.024800000712275505, -0.1745000034570694, -0.026799999177455902, -0.08560000360012054, 0.03319999948143959, -0.02019999921321869, -0.09099999815225601, -0.02759999968111515, -0.07999999821186066, 0.05310000106692314, 0.05869999900460243, -0.04699999839067459, 0.03970000147819519, 0.032499998807907104, -0.04780000075697899, 0.0843999981880188, 0.010499999858438969, -0.06599999964237213, -0.012799999676644802, 0.04780000075697899, -0.06769999861717224, -0.0003000000142492354, -0.04610000178217888, 0.0348999984562397, -0.04010000079870224, -0.1103999987244606, 0.06689999997615814, 0.09000000357627869, -0.0406000018119812, 0.04839999973773956, -0.09480000287294388, -0.08649999648332596, 0.054999999701976776, 0.06159999966621399, -0.013500000350177288, 0.025800000876188278, 0.03460000082850456, 0.05810000002384186, -0.0430000014603138, -0.06620000302791595, -0.11219999939203262, 0.0010000000474974513, 0.08460000157356262, 0.03480000048875809, -0.01549999974668026, 0.013500000350177288, 0.013799999840557575, -0.05820000171661377, 0.04809999838471413, 0.006500000134110451, 0.015300000086426735, 0.09640000015497208, 0.006899999920278788, 0.003599999938160181, 0.051100000739097595, -0.0812000036239624, -0.04500000178813934, -0.026599999517202377, 0.041600000113248825, -0.07159999758005142, 0.017899999395012856, -0.12439999729394913, -0.03629999980330467, 0.04729999974370003, 0.0044999998062849045, -0.05959999933838844, -0.033399999141693115, 0.008299999870359898, -0.07959999889135361, -0.05490000173449516, 0.005499999970197678, -0.01979999989271164, 0.006800000090152025, 0.11410000175237656, 0.007000000216066837, -0.04500000178813934, -0.032999999821186066, -0.02590000070631504, 0.06639999896287918, -0.050700001418590546, 0.024399999529123306, 0.05209999904036522, -0.07360000163316727, -0.020400000736117363, 0.019300000742077827, -0.0625, 0.024800000712275505, 0.016599999740719795, 0.0007999999797903001, -0.0210999995470047, -0.06120000034570694, -0.0478999987244606, 0.017400000244379044, 0.039799999445676804, 0.09040000289678574, 0.04650000110268593, -0.010099999606609344, -0.0010000000474974513, 0.03189999982714653, -0.10660000145435333, -0.007699999958276749, 0.10189999639987946, 0.044199999421834946, -0.00039999998989515007, -0.06589999794960022, 0.004900000058114529, 0.13230000436306, 0.06459999829530716, -0.05609999969601631, 0.021900000050663948, 0.02630000002682209, 0.07980000227689743, 0.061500001698732376, -0.04600000008940697, 0.08250000327825546, -0.05770000070333481, 0.019600000232458115, 0.038600001484155655, -0.041099999099969864, -0.013199999928474426, 0.066600002348423, -0.059700001031160355, 0.05460000038146973, -0.011099999770522118, 0.026000000536441803, -0.02280000038444996, 0.07900000363588333, 0.03610000014305115, 0.06319999694824219, 0.01679999940097332, -0.018400000408291817, -0.041099999099969864, 0.034299999475479126, -0.002300000051036477, -0.0568000003695488, 0.024900000542402267, 0.03579999879002571]], [[0.004399999976158142, 0.0027000000700354576, 0.07680000364780426, -0.010499999858438969, -0.004000000189989805, -0.07209999859333038, -0.018699999898672104, 0.10909999907016754, -0.018300000578165054, 0.07119999825954437, -0.0006000000284984708, -0.014100000262260437, -0.03550000116229057, 0.01759999990463257, -0.07500000298023224, -0.028599999845027924, 0.08810000121593475, -0.014999999664723873, -0.05900000035762787, -0.03060000017285347, -0.024900000542402267, -0.009700000286102295, 0.08290000259876251, 0.0414000004529953, 0.033399999141693115, -0.13259999454021454, 0.029600000008940697, -0.03840000182390213, 0.008200000040233135, 0.019099999219179153, 0.10119999945163727, -0.04830000177025795, -0.1143999993801117, -0.02239999920129776, 0.026799999177455902, -0.040699999779462814, 0.00570000009611249, 0.024900000542402267, 0.055799998342990875, 0.037700001150369644, -0.04800000041723251, 0.020400000736117363, 0.04439999908208847, 0.02879999950528145, -0.054099999368190765, 0.039000000804662704, 0.04470000043511391, 0.04809999838471413, -0.1324000060558319, 0.08399999886751175, 0.03669999912381172, -0.03709999844431877, -0.04340000078082085, -0.012299999594688416, 0.0706000030040741, 0.04610000178217888, 0.08100000023841858, 0.03060000017285347, 0.011699999682605267, -0.032499998807907104, 0.05339999869465828, 0.027899999171495438, 0.007600000128149986, 0.03929999843239784, -0.03970000147819519, -0.032999999821186066, -0.08560000360012054, 0.08990000188350677, 0.03869999945163727, 0.03220000118017197, 0.17910000681877136, -0.06790000200271606, 0.02419999986886978, -0.05350000038743019, -0.02290000021457672, 0.14079999923706055, -0.03280000016093254, -0.05559999868273735, 0.015799999237060547, -0.008899999782443047, 0.0778999999165535, 0.021400000900030136, 0.03909999877214432, 0.0044999998062849045, 0.09629999846220016, 0.037300001829862595, -0.01510000042617321, -0.022600000724196434, 0.012000000104308128, 0.04399999976158142, -0.06120000034570694, 0.01489999983459711, -0.015300000086426735, 0.03460000082850456, 0.028599999845027924, -0.051500000059604645, -0.16949999332427979, 0.018200000748038292, -0.09149999916553497, -0.07029999792575836, 0.07900000363588333, -0.08129999786615372, -0.0272000003606081, -0.014499999582767487, 0.025499999523162842, -0.031300000846385956, 0.022600000724196434, -0.005200000014156103, 0.08879999816417694, -0.08839999884366989, -0.045099999755620956, -0.039799999445676804, -0.019500000402331352, 0.09849999845027924, 0.002400000113993883, -0.06040000170469284, 0.026900000870227814, 0.14159999787807465, -0.01600000075995922, -0.052000001072883606, 0.04340000078082085, 0.05609999969601631, -0.07900000363588333, -0.031599998474121094, 0.11349999904632568, 0.07039999961853027, -0.04479999840259552, -0.12200000137090683, -0.04989999905228615, 0.06589999794960022, -0.007400000002235174, -0.011099999770522118, -0.0203000009059906, 0.04470000043511391, 0.09080000221729279, 0.06719999760389328, 0.002400000113993883, -0.02319999970495701, -0.027699999511241913, -0.04839999973773956, -0.06239999830722809, 0.05829999968409538, 0.039799999445676804, -0.016899999231100082, 0.11590000241994858, 0.13339999318122864, 0.07500000298023224, -0.003800000064074993, -0.02630000002682209, 0.042399998754262924, -0.15870000422000885, -0.12139999866485596, 0.07980000227689743, -0.04699999839067459, 0.0044999998062849045, -0.06289999932050705, 0.07649999856948853, 0.015799999237060547, 0.04340000078082085, -0.06840000301599503, 0.02329999953508377, 0.007400000002235174, -0.053199999034404755, 0.1688999980688095, -0.002099999925121665, -0.06689999997615814, -0.013199999928474426, 0.06159999966621399, 0.03060000017285347, 0.011900000274181366, 0.018300000578165054, -0.05510000139474869, 0.029600000008940697, -0.07460000365972519, 0.08299999684095383, 0.05959999933838844, 0.0010000000474974513, 0.03139999881386757, -0.05620000138878822, 0.01209999993443489, -0.015799999237060547, 0.0966000035405159, 0.07349999994039536, -0.01510000042617321, 0.002300000051036477, -0.034699998795986176, 0.04839999973773956, 0.01140000019222498, 0.05779999867081642, -0.08550000190734863, -0.12080000340938568, 0.08160000294446945, -0.008100000210106373, -0.06430000066757202, -0.039400000125169754, -0.10270000249147415, 0.07090000063180923, -0.026599999517202377, 0.04010000079870224, 0.016200000420212746, 0.03909999877214432, 0.0575999990105629, 0.05380000174045563, 0.08619999885559082, 0.07689999788999557, 0.0697999969124794, -0.04619999974966049, 0.08919999748468399, 0.05510000139474869, 0.04320000112056732, 0.01269999984651804, 0.05339999869465828, 0.08330000191926956, 0.012000000104308128, 0.040300000458955765, -0.11460000276565552, 0.15770000219345093, 0.058800000697374344, -0.023399999365210533, 0.07760000228881836, 0.13449999690055847, 0.02290000021457672, -0.14249999821186066, -0.021400000900030136, 0.04320000112056732, 0.06159999966621399, 0.023900000378489494, -0.03849999979138374, 0.13680000603199005, -0.0015999999595806003, -0.048700001090765, -0.010499999858438969, -0.07150000333786011, -0.0471000000834465, 0.011300000362098217, -0.0869000032544136, -0.041999999433755875, 0.04879999905824661, 0.038100000470876694, -0.04179999977350235, 0.021900000050663948, -0.017000000923871994, 0.004800000227987766, 0.0008999999845400453, -0.04360000044107437, 0.07079999893903732, -0.06639999896287918, -0.05260000005364418, 0.07509999722242355, -0.0778999999165535, -0.04650000110268593, -0.04340000078082085, 0.06069999933242798, 0.066600002348423, 0.002099999925121665, 0.07460000365972519, 0.03629999980330467, 0.009800000116229057, 0.09019999951124191, -0.07079999893903732, 0.0551999993622303, -0.06840000301599503, 0.054499998688697815, 0.04529999941587448], [0.09799999743700027, 0.03229999914765358, 0.06469999998807907, 0.06210000067949295, 0.029400000348687172, 0.05119999870657921, 0.11500000208616257, -0.07109999656677246, -0.0860000029206276, -0.07109999656677246, 0.034699998795986176, 0.020400000736117363, -0.14810000360012054, 0.03359999880194664, -0.0031999999191612005, -0.011500000022351742, -0.10679999738931656, 0.043800000101327896, 0.024399999529123306, -0.008700000122189522, 0.005100000184029341, -0.059300001710653305, 0.009800000116229057, -0.047600001096725464, 0.04179999977350235, -0.03579999879002571, -0.02630000002682209, -0.07729999721050262, -0.032499998807907104, -0.030700000002980232, 0.06310000270605087, 0.08560000360012054, 0.09910000115633011, 0.052299998700618744, -0.01360000018030405, 0.09309999644756317, -0.019700000062584877, -0.04309999942779541, -0.0031999999191612005, -0.044599998742341995, -0.0340999998152256, 0.10589999705553055, -0.03009999915957451, 0.07660000026226044, 0.03359999880194664, -0.028599999845027924, 0.04399999976158142, -0.06239999830722809, -0.06449999660253525, -0.0551999993622303, -0.06040000170469284, 0.022099999710917473, 0.07670000195503235, 0.025599999353289604, -0.04569999873638153, 0.11869999766349792, 0.04910000041127205, -0.03550000116229057, 0.010099999606609344, -0.02019999921321869, -0.09629999846220016, 0.03869999945163727, 0.03750000149011612, 0.03759999945759773, -0.07880000025033951, 0.0575999990105629, 0.0034000000450760126, -0.027400000020861626, -0.0008999999845400453, -0.08820000290870667, 0.02019999921321869, -0.0333000011742115, 0.05249999836087227, -0.0020000000949949026, 0.08399999886751175, -0.06960000097751617, 0.022700000554323196, -0.08879999816417694, 0.03370000049471855, -0.08579999953508377, -0.03750000149011612, -0.04430000111460686, 0.049300000071525574, 0.00800000037997961, -0.027000000700354576, -0.08529999852180481, 0.043299999088048935, -0.00559999980032444, 0.07150000333786011, -0.07699999958276749, -0.016599999740719795, -0.012799999676644802, -0.11729999631643295, -0.020999999716877937, 0.003100000089034438, 0.1550000011920929, -0.0430000014603138, 0.09309999644756317, -0.08229999989271164, 0.07429999858140945, 0.06719999760389328, 0.061400000005960464, 0.00430000014603138, -0.01810000091791153, 0.00419999985024333, -0.08299999684095383, 0.11349999904632568, -0.01810000091791153, 0.01730000041425228, 0.03819999843835831, 0.0674000009894371, 0.01489999983459711, 0.1014999970793724, 0.05950000137090683, 0.09650000184774399, -0.029999999329447746, -0.010200000368058681, 0.10209999978542328, -0.0066999997943639755, -0.04390000179409981, -0.04910000041127205, -0.07660000026226044, -0.1088000014424324, 0.05950000137090683, -0.08579999953508377, 0.031300000846385956, -0.03180000185966492, -0.18320000171661377, -0.09679999947547913, 0.20970000326633453, 0.0, -0.05050000175833702, 0.1331000030040741, 0.011300000362098217, -0.040300000458955765, -0.0019000000320374966, -0.058800000697374344, -0.03480000048875809, -0.04410000145435333, 0.05790000036358833, 0.10989999771118164, -0.08380000293254852, -0.05469999834895134, -0.019899999722838402, 0.164000004529953, -0.04230000078678131, -0.007300000172108412, 0.02410000003874302, 0.04399999976158142, 0.03720000013709068, 0.010300000198185444, 0.03739999979734421, -0.08550000190734863, -0.06629999727010727, 0.07259999960660934, 0.017500000074505806, -0.03620000183582306, 0.0658000037074089, 0.07129999995231628, 0.09769999980926514, -0.038600001484155655, -0.045899998396635056, 0.01510000042617321, -0.0284000001847744, 0.008799999952316284, 0.15449999272823334, 0.025100000202655792, 0.053199999034404755, -0.07320000231266022, 0.029500000178813934, -0.0142000000923872, 0.05959999933838844, -0.00139999995008111, -0.04690000042319298, 0.0869000032544136, -0.003800000064074993, 0.0364999994635582, -0.02319999970495701, -0.033900000154972076, 0.0012000000569969416, 0.02810000069439411, 0.08900000154972076, -0.003599999938160181, -0.025499999523162842, 0.026399999856948853, -0.034299999475479126, -0.049400001764297485, 0.0017000000225380063, 0.01769999973475933, 0.06069999933242798, -0.025800000876188278, 0.01080000028014183, 0.043699998408555984, 0.0032999999821186066, -0.01549999974668026, -0.06300000101327896, -0.00930000003427267, 0.08150000125169754, 0.03680000081658363, -0.01549999974668026, 0.023000000044703484, -0.09390000253915787, 0.01600000075995922, 0.051899999380111694, -0.03620000183582306, 0.056699998676776886, -0.04360000044107437, 0.05310000106692314, 0.032999999821186066, 0.010099999606609344, 0.04520000144839287, -0.022199999541044235, 0.1152999997138977, -0.06989999860525131, 0.046799998730421066, -0.05950000137090683, -0.018799999728798866, -0.053199999034404755, 0.07079999893903732, 0.058800000697374344, -0.05139999836683273, -0.12240000069141388, 0.01640000008046627, -0.015799999237060547, 0.0406000018119812, -0.03959999978542328, -0.061799999326467514, 0.048700001090765, -0.03700000047683716, -0.07729999721050262, 0.028999999165534973, -0.08780000358819962, -0.04659999907016754, 0.04619999974966049, -0.0026000000070780516, 0.08370000123977661, 0.14249999821186066, 0.028200000524520874, 0.01640000008046627, 0.045899998396635056, 0.020899999886751175, 0.06520000100135803, -0.0052999998442828655, -0.015699999406933784, -0.11810000240802765, 0.016300000250339508, -0.0013000000035390258, 0.013100000098347664, -0.07569999992847443, 0.004100000020116568, 0.054099999368190765, 0.054499998688697815, 0.021700000390410423, -0.057999998331069946, -0.012400000356137753, 0.13379999995231628, 0.047200001776218414, 0.012900000438094139, -0.038100000470876694, 0.09489999711513519, 0.01119999960064888, -0.11169999837875366, 0.10159999877214432, -0.04580000042915344], [-0.08129999786615372, -0.042899999767541885, -0.027799999341368675, -0.041600000113248825, 0.009200000204145908, -0.041999999433755875, 0.029400000348687172, -0.00800000037997961, 0.08240000158548355, -0.035999998450279236, 0.03700000047683716, 0.051899999380111694, -0.062199998646974564, -0.018699999898672104, -0.053700000047683716, -0.0843999981880188, 0.03629999980330467, -0.008200000040233135, -0.021700000390410423, 0.031599998474121094, -0.00989999994635582, -0.009100000374019146, -0.066600002348423, 0.0044999998062849045, -0.03970000147819519, -0.030700000002980232, 0.016200000420212746, 0.022600000724196434, 0.032600000500679016, -0.14180000126361847, -0.06459999829530716, -0.017799999564886093, 0.03660000115633011, -0.04179999977350235, 0.09019999951124191, -0.00839999970048666, -0.03579999879002571, -0.11999999731779099, 0.03590000048279762, -0.03849999979138374, -0.07779999822378159, 0.06530000269412994, 0.07270000129938126, -0.008899999782443047, -0.04569999873638153, -0.00559999980032444, -0.1185000017285347, -0.05079999938607216, 0.028200000524520874, 0.021199999377131462, 0.056299999356269836, 0.026100000366568565, -0.026599999517202377, 0.0003000000142492354, 0.09260000288486481, -0.04690000042319298, 0.019999999552965164, -0.006200000178068876, 0.05119999870657921, 0.04280000180006027, 0.15559999644756317, 0.09179999679327011, 0.039900001138448715, -0.11190000176429749, -0.027499999850988388, 0.0689999982714653, 0.08250000327825546, 0.013899999670684338, 0.005200000014156103, 0.06019999831914902, -0.01600000075995922, -0.004999999888241291, -0.04349999874830246, -0.08940000087022781, 0.013299999758601189, 0.07180000096559525, -0.05950000137090683, -0.039400000125169754, -0.03790000081062317, -0.1062999963760376, 0.08229999989271164, -0.14749999344348907, -0.11110000312328339, -0.01269999984651804, -0.08129999786615372, 0.014999999664723873, -0.05950000137090683, -0.045499999076128006, -0.01600000075995922, 0.0006000000284984708, 0.06930000334978104, 0.021800000220537186, -0.030300000682473183, -0.021400000900030136, -0.018200000748038292, -0.03290000185370445, -0.01979999989271164, -0.05469999834895134, -0.03500000014901161, 0.1670999974012375, -0.021199999377131462, 0.12939999997615814, -0.023900000378489494, 0.028699999675154686, -0.005499999970197678, -0.06430000066757202, 0.008100000210106373, -0.014700000174343586, 0.0035000001080334187, -0.12710000574588776, -0.021299999207258224, -0.1551000028848648, -0.05570000037550926, 0.0421999990940094, 0.03240000084042549, 0.09539999812841415, -0.060600001364946365, -0.06599999964237213, -0.10369999706745148, 0.033399999141693115, 0.013500000350177288, 0.07779999822378159, 0.18080000579357147, -0.05350000038743019, 0.042899999767541885, 0.0560000017285347, -0.16329999268054962, 0.02759999968111515, 0.07919999957084656, 0.10849999636411667, -0.13109999895095825, -0.05510000139474869, -0.004399999976158142, -0.031099999323487282, 0.037300001829862595, -0.03350000083446503, 0.05040000006556511, 0.05260000005364418, 0.08349999785423279, 0.026000000536441803, 0.004000000189989805, -0.006200000178068876, 0.03420000150799751, 0.014100000262260437, 0.09830000251531601, 0.002099999925121665, 0.02250000089406967, 0.04809999838471413, -0.1396999955177307, -0.06790000200271606, 0.11460000276565552, 0.020400000736117363, -0.0754999965429306, -0.05719999969005585, 0.08219999819993973, 0.07919999957084656, 0.07930000126361847, 0.07800000160932541, 0.0560000017285347, 0.06960000097751617, -0.048500001430511475, -0.04399999976158142, 0.07039999961853027, -0.04280000180006027, 0.0430000014603138, 0.03539999946951866, 0.04349999874830246, -0.03620000183582306, 0.048700001090765, 0.09520000219345093, 0.025299999862909317, -0.0674000009894371, 0.01640000008046627, -0.00989999994635582, 0.043800000101327896, -0.061000000685453415, 0.023099999874830246, 0.09440000355243683, 0.07850000262260437, -0.051600001752376556, -0.060600001364946365, -0.011500000022351742, -0.07670000195503235, -0.0348999984562397, 0.04170000180602074, 0.05530000105500221, 0.10689999908208847, 0.0203000009059906, 0.025599999353289604, 0.04500000178813934, -0.06289999932050705, 0.0006000000284984708, -0.048700001090765, -0.012900000438094139, 0.015200000256299973, 0.03370000049471855, 0.01269999984651804, -0.023800000548362732, -0.016499999910593033, 0.03920000046491623, -0.015300000086426735, -0.042100001126527786, -0.0406000018119812, 0.09309999644756317, -0.03830000013113022, 0.043800000101327896, -0.14650000631809235, 0.1565999984741211, -0.008500000461935997, -0.06939999759197235, 0.006300000008195639, -0.059700001031160355, -0.011599999852478504, 0.048500001430511475, 0.026499999687075615, 0.043699998408555984, 9.999999747378752e-05, -0.027300000190734863, 0.01720000058412552, 0.003599999938160181, 0.02710000053048134, -0.03240000084042549, 0.006300000008195639, -0.06970000267028809, 0.08139999955892563, 0.035100001841783524, -0.00419999985024333, 0.07909999787807465, -0.03680000081658363, 0.04800000041723251, 0.0044999998062849045, 0.002300000051036477, 0.007300000172108412, -0.015799999237060547, -0.12210000306367874, -0.00279999990016222, -0.11569999903440475, 0.08410000056028366, -0.028699999675154686, 0.050599999725818634, 0.012000000104308128, 0.08460000157356262, 0.11060000211000443, 0.010700000450015068, -0.01640000008046627, -0.0843999981880188, -0.0035000001080334187, 0.014800000004470348, -0.032600000500679016, -0.07580000162124634, 0.13099999725818634, -0.11550000309944153, -0.002400000113993883, 0.040699999779462814, -0.11029999703168869, -0.01759999990463257, 0.05480000004172325, 0.015799999237060547, -0.009700000286102295, -0.013899999670684338, -0.042399998754262924, 0.02500000037252903, 0.004699999932199717, 0.04740000143647194], [-0.015599999576807022, -0.034299999475479126, 0.025699999183416367, 0.038100000470876694, 0.030500000342726707, 0.02250000089406967, 0.01979999989271164, 0.11400000005960464, 0.05469999834895134, -0.004699999932199717, 0.043800000101327896, -0.022700000554323196, 0.03500000014901161, -0.050700001418590546, -0.01940000057220459, -0.18330000340938568, 0.07530000060796738, -0.08250000327825546, 0.07199999690055847, -0.07670000195503235, 0.04500000178813934, 0.017500000074505806, 0.05209999904036522, -0.04969999939203262, 0.027899999171495438, -0.014700000174343586, -0.04699999839067459, -0.09229999780654907, -0.043800000101327896, -0.05389999970793724, -0.029400000348687172, 0.0210999995470047, 0.039400000125169754, -0.011599999852478504, 0.09080000221729279, -0.017000000923871994, -0.06040000170469284, 0.039000000804662704, -0.094200000166893, -0.027899999171495438, 0.043299999088048935, 0.02329999953508377, 0.10559999942779541, -0.011699999682605267, 0.023600000888109207, -0.03880000114440918, 0.041999999433755875, -0.0006000000284984708, -0.10279999673366547, -0.0640999972820282, 0.16529999673366547, 0.04919999837875366, -0.0658000037074089, -0.06159999966621399, -0.11909999698400497, 0.053599998354911804, -0.01510000042617321, 0.044599998742341995, -0.0026000000070780516, -0.0215000007301569, 0.025200000032782555, 0.0544000007212162, -0.0575999990105629, 0.13899999856948853, -0.03660000115633011, -0.10100000351667404, 0.06279999762773514, -0.0406000018119812, 0.003700000001117587, 0.0027000000700354576, 0.05009999871253967, 0.08449999988079071, -0.14059999585151672, 0.041099999099969864, 0.013100000098347664, 0.01489999983459711, -0.033799998462200165, -0.10010000318288803, 0.00839999970048666, 0.031599998474121094, 0.03359999880194664, -0.010900000110268593, -0.019999999552965164, -0.03799999877810478, -0.020400000736117363, -0.008999999612569809, -0.0885000005364418, 0.03929999843239784, -0.014700000174343586, -0.1062999963760376, 0.07540000230073929, 0.025800000876188278, -0.10980000346899033, 0.04179999977350235, -0.05469999834895134, -0.021199999377131462, 0.09910000115633011, 0.0010999999940395355, 0.04650000110268593, 0.09399999678134918, -0.06759999692440033, -0.024299999698996544, -0.03579999879002571, -0.018200000748038292, -0.007699999958276749, -0.07810000330209732, 0.029500000178813934, 0.004000000189989805, -0.12319999933242798, 0.07259999960660934, -0.020600000396370888, 0.11389999836683273, 0.09269999712705612, -0.027799999341368675, -0.050200000405311584, -0.008799999952316284, 0.11969999969005585, -0.045499999076128006, 0.0348999984562397, 0.11500000208616257, -0.008100000210106373, -0.08579999953508377, -0.0681999996304512, -0.09099999815225601, -0.021299999207258224, 0.021900000050663948, -0.10409999638795853, -0.08060000091791153, -0.026200000196695328, -0.007300000172108412, -0.025699999183416367, 0.055799998342990875, -0.08460000157356262, -0.045099999755620956, -0.093299999833107, 0.14020000398159027, -0.0333000011742115, -0.0617000013589859, -0.03290000185370445, 0.017000000923871994, -0.14749999344348907, -0.0010000000474974513, 0.07199999690055847, 0.024700000882148743, 0.014700000174343586, -0.007799999788403511, 0.03880000114440918, 0.022299999371170998, 0.05570000037550926, 0.05249999836087227, -0.06840000301599503, -0.05939999967813492, 0.039799999445676804, -0.004800000227987766, 0.01940000057220459, -0.03440000116825104, -0.026399999856948853, -0.06880000233650208, 0.00570000009611249, 0.00860000029206276, 0.13199999928474426, 0.045499999076128006, -0.03830000013113022, -0.029200000688433647, 0.010200000368058681, 0.02759999968111515, -0.14190000295639038, -0.06310000270605087, -0.010700000450015068, 0.0502999983727932, -0.04619999974966049, 0.033799998462200165, -0.0803999975323677, 0.07479999959468842, 0.01720000058412552, 0.13079999387264252, 0.04010000079870224, 0.020999999716877937, -0.011300000362098217, 0.015799999237060547, -0.01600000</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>[[[0.07739999890327454, 0.035599999129772186, 0.02759999968111515, -0.025299999862909317, 0.08529999852180481, 0.002199999988079071, 0.006399999838322401, -0.055799998342990875, 0.056299999356269836, -0.13750000298023224, -0.0052999998442828655, 0.024800000712275505, 0.01889999955892563, 0.0706000030040741, 0.008100000210106373, -0.04690000042319298, 0.05220000073313713, 0.042399998754262924, -0.06809999793767929, -0.04280000180006027, 0.049300000071525574, -0.0364999994635582, 0.06270000338554382, -0.04580000042915344, -0.0024999999441206455, 0.065700002014637, 0.049300000071525574, -0.0026000000070780516, -0.07680000364780426, -0.030500000342726707, 0.04800000041723251, -0.04769999906420708, -0.018300000578165054, -0.060100000351667404, -0.06830000132322311, 0.02250000089406967, 0.011500000022351742, 0.06400000303983688, -0.019999999552965164, 0.03020000085234642, 0.08900000154972076, 0.06340000033378601, 0.008700000122189522, 0.03060000017285347, 0.016899999231100082, 0.015799999237060547, 0.04529999941587448, 0.014700000174343586, 0.006399999838322401, 0.042899999767541885, 0.046799998730421066, 0.06199999898672104, 0.04540000110864639, -0.03819999843835831, -0.04859999939799309, 0.02669999934732914, -0.009999999776482582, -0.055799998342990875, -0.024900000542402267, -0.03180000185966492, 0.020600000396370888, 0.007899999618530273, -0.0035000001080334187, 0.04800000041723251, 0.03830000013113022, -0.04170000180602074, -0.017999999225139618, -0.005799999926239252, 0.023099999874830246, 0.009800000116229057, -0.1054999977350235, 0.01549999974668026, -0.050700001418590546, -0.004600000102072954, -0.04190000146627426, -0.08619999885559082, -0.009499999694526196, -0.01850000023841858, 0.06889999657869339, 0.016699999570846558, 0.07090000063180923, 0.016300000250339508, -0.008100000210106373, -0.06939999759197235, 0.06469999998807907, -0.031199999153614044, 0.023900000378489494, -0.01080000028014183, -0.07010000199079514, 0.03370000049471855, 0.014800000004470348, -0.012900000438094139, -0.004800000227987766, 0.07119999825954437, 0.06909999996423721, -0.052400000393390656, 0.00430000014603138, -0.06560000032186508, -0.03970000147819519, -0.04500000178813934, -0.08389999717473984, 0.029500000178813934, -0.07050000131130219, -0.019999999552965164, 0.13500000536441803, -0.06279999762773514, -0.012000000104308128, 0.03460000082850456, 0.06560000032186508, 0.02850000001490116, 0.04820000007748604, 0.05640000104904175, 0.0284000001847744, 0.02969999983906746, -0.017100000753998756, 0.058800000697374344, -0.03060000017285347, -0.04560000076889992, -0.02590000070631504, 0.007400000002235174, -0.023499999195337296, -0.0010999999940395355, 0.01119999960064888, -0.07999999821186066, -0.036400001496076584, 0.021400000900030136, 0.0608999989926815, -0.0007999999797903001, 0.10119999945163727, 0.011900000274181366, 0.05570000037550926, -0.033399999141693115, -0.033399999141693115, 0.0820000022649765, 0.06159999966621399, 0.07240000367164612, -0.03959999978542328, -0.01810000091791153, 0.07349999994039536, -0.07779999822378159, -0.032499998807907104, -0.009499999694526196, -0.045899998396635056, -0.03319999948143959, 0.04500000178813934, 0.0044999998062849045, -0.05530000105500221, 0.053300000727176666, -0.011500000022351742, 0.03909999877214432, -0.0012000000569969416, 0.03779999911785126, -0.02800000086426735, -0.04540000110864639, -0.027000000700354576, 0.033799998462200165, -0.006800000090152025, 0.024900000542402267, 0.07649999856948853, -0.03319999948143959, -0.06199999898672104, 0.009600000455975533, 0.01119999960064888, -0.05310000106692314, -0.06960000097751617, -0.006099999882280827, 0.060499999672174454, 0.07559999823570251, 0.012299999594688416, -0.0478999987244606, 0.018400000408291817, 0.04010000079870224, -0.032600000500679016, -0.037700001150369644, 0.09929999709129333, -0.06469999998807907, -0.014800000004470348, -0.029999999329447746, -0.0737999975681305, 0.03750000149011612, -0.00039999998989515007, -0.023600000888109207, 0.03709999844431877, 0.008100000210106373, 0.051100000739097595, -0.03139999881386757, 0.06639999896287918, -0.03350000083446503, 0.09549999982118607, 0.03150000050663948, -0.06319999694824219, -0.023099999874830246, 0.0723000019788742, 0.00860000029206276, -0.009800000116229057, 0.0934000015258789, 0.061500001698732376, 0.019899999722838402, 0.05339999869465828, 0.029999999329447746, -0.0794999971985817, 0.016899999231100082, 0.049800001084804535, 0.04410000145435333, 0.0010999999940395355, -0.08829999715089798, 0.023499999195337296, -0.012500000186264515, -0.04529999941587448, 0.023499999195337296, -0.014700000174343586, 0.007000000216066837, 0.04230000078678131, 0.0024999999441206455, -0.03550000116229057, 0.0284000001847744, -0.006399999838322401, -0.015699999406933784, 0.031300000846385956, 0.04089999943971634, -0.016300000250339508, -0.01600000075995922, -0.07329999655485153, 0.003599999938160181, 0.065700002014637, -0.03590000048279762, 0.045899998396635056, -0.013399999588727951, -0.06920000165700912, -0.012900000438094139, 0.03220000118017197, 0.03779999911785126, -0.023099999874830246, -0.09539999812841415, -0.0494999997317791, 0.0820000022649765, -0.0019000000320374966, -0.01899999938905239, -0.08500000089406967, -0.03370000049471855, 0.028300000354647636, -0.12349999696016312, 0.050999999046325684, -0.013000000268220901, -0.03290000185370445, 0.03180000185966492, 0.017999999225139618, -0.09440000355243683, 0.07090000063180923, -0.046300001442432404, -0.0017999999690800905, -0.042399998754262924, 0.05999999865889549, -0.06700000166893005, -0.03739999979734421, -0.05779999867081642, -0.05420000106096268, -0.014000000432133675, 0.04910000041127205, -0.03880000114440918, -0.0203000009059906, 0.04360000044107437, -0.02199999988079071, -0.048900000751018524], [-0.006399999838322401, -0.0005000000237487257, 0.07919999957084656, -0.020400000736117363, -0.10329999774694443, 0.010599999688565731, 0.07660000026226044, 0.08649999648332596, 0.030500000342726707, 0.10209999978542328, 0.02290000021457672, 0.04050000011920929, -0.07010000199079514, -0.03500000014901161, 0.013500000350177288, -0.0203000009059906, 0.027499999850988388, -0.03440000116825104, -0.039400000125169754, 0.052400000393390656, -0.0697999969124794, -0.022199999541044235, -0.020600000396370888, -0.03460000082850456, -0.10119999945163727, 0.006000000052154064, 0.03350000083446503, -0.0640999972820282, 0.0010000000474974513, -0.049400001764297485, -0.04170000180602074, -0.044599998742341995, 0.026000000536441803, -0.016499999910593033, -0.035599999129772186, -0.054499998688697815, -0.04019999876618385, -0.009999999776482582, -0.06880000233650208, -0.0689999982714653, -0.0835999995470047, 0.08340000361204147, 0.1062999963760376, -0.002199999988079071, 0.06729999929666519, 0.019999999552965164, 0.019200000911951065, 0.042899999767541885, -0.028300000354647636, 0.01759999990463257, 0.06889999657869339, -0.0617000013589859, -0.07270000129938126, -0.04320000112056732, -0.030899999663233757, 0.021700000390410423, 0.07779999822378159, -0.02160000056028366, 0.07680000364780426, 0.052299998700618744, 0.03550000116229057, -0.007699999958276749, 0.05810000002384186, 0.01769999973475933, -0.004100000020116568, 0.06800000369548798, 0.1088000014424324, -0.009499999694526196, -0.023800000548362732, 0.08479999750852585, 0.15559999644756317, 0.009399999864399433, -0.04600000008940697, -0.028300000354647636, 0.09690000116825104, 0.0803999975323677, -0.020099999383091927, -0.03889999911189079, -0.018699999898672104, 0.061400000005960464, -0.007000000216066837, -0.020099999383091927, -0.024800000712275505, -0.05660000070929527, -0.02630000002682209, -0.03139999881386757, 0.002099999925121665, -0.03869999945163727, -0.021199999377131462, 0.003599999938160181, 0.04560000076889992, -0.04190000146627426, 0.054499998688697815, -0.07050000131130219, -0.001500000013038516, 0.03519999980926514, 0.0010000000474974513, 0.0020000000949949026, -0.019999999552965164, 0.018799999728798866, 0.002099999925121665, 0.04500000178813934, 0.050700001418590546, 0.03269999846816063, -0.06080000102519989, 0.030799999833106995, 0.03880000114440918, -0.10109999775886536, -0.03060000017285347, -0.06710000336170197, -0.02019999921321869, -0.03579999879002571, -0.03290000185370445, -0.052799999713897705, 0.028599999845027924, 0.0013000000035390258, -0.010700000450015068, -0.041600000113248825, 0.031700000166893005, -0.04989999905228615, 0.06729999929666519, 0.05090000107884407, -0.049400001764297485, -0.00989999994635582, -0.04569999873638153, -0.048500001430511475, -0.010900000110268593, -0.06549999862909317, -0.11890000104904175, 0.03020000085234642, 0.0012000000569969416, -0.026000000536441803, 0.03620000183582306, -0.01810000091791153, -0.016699999570846558, -0.058400001376867294, -0.008500000461935997, 0.08739999681711197, 0.009399999864399433, -0.00860000029206276, 0.03530000150203705, 0.019899999722838402, 0.060100000351667404, 0.058800000697374344, 0.012799999676644802, 0.022199999541044235, 0.09130000323057175, -0.000699999975040555, -0.016499999910593033, 0.03460000082850456, -0.009700000286102295, 0.061799999326467514, -0.049800001084804535, 0.05990000069141388, -0.011699999682605267, 0.04919999837875366, -0.0006000000284984708, -0.04690000042319298, -0.03220000118017197, 0.04820000007748604, 0.10719999670982361, 0.03709999844431877, -0.026799999177455902, -0.01810000091791153, -0.015699999406933784, -9.999999747378752e-05, -0.027400000020861626, -0.05920000001788139, -0.0771000012755394, 0.03680000081658363, -0.019700000062584877, 0.03689999878406525, 0.09870000183582306, 0.04410000145435333, -0.08410000056028366, 0.009600000455975533, -0.08380000293254852, 0.07419999688863754, 0.07819999754428864, -0.06520000100135803, 0.05810000002384186, -0.03500000014901161, -0.027499999850988388, 0.001500000013038516, 0.01600000075995922, 0.05550000071525574, -0.09049999713897705, -0.039900001138448715, -0.08269999921321869, 0.02810000069439411, -0.023499999195337296, -0.051100000739097595, -0.022199999541044235, -0.03689999878406525, -0.02410000003874302, -0.030500000342726707, -0.031099999323487282, 0.048700001090765, 0.009499999694526196, 0.027499999850988388, 0.06449999660253525, -0.044199999421834946, 0.048900000751018524, 0.02449999935925007, 0.03200000151991844, 0.11949999630451202, 0.024800000712275505, -0.04470000043511391, -0.02019999921321869, -0.004699999932199717, -0.023900000378489494, 0.11289999634027481, -0.07249999791383743, 0.0737999975681305, -0.03739999979734421, -0.03220000118017197, 0.03460000082850456, -0.01850000023841858, -0.0357000008225441, 0.07490000128746033, 0.08330000191926956, 0.021400000900030136, 0.08590000122785568, 0.04490000009536743, 0.06390000134706497, 0.10509999841451645, -0.031300000846385956, 0.04839999973773956, 0.016300000250339508, -0.01510000042617321, 0.04270000010728836, -0.017400000244379044, 0.01679999940097332, 0.06499999761581421, 0.00430000014603138, 0.029200000688433647, -0.03220000118017197, -0.03280000016093254, 0.04830000177025795, 0.1071000024676323, 0.006500000134110451, 0.07360000163316727, -0.03440000116825104, 0.060100000351667404, -0.019099999219179153, -0.06880000233650208, 0.06430000066757202, -0.026200000196695328, -0.04010000079870224, 0.11129999905824661, -0.0494999997317791, 0.01489999983459711, 0.0494999997317791, 0.021199999377131462, 0.09839999675750732, 0.10279999673366547, -0.010900000110268593, -0.09160000085830688, -0.0632999986410141, -0.04259999841451645, -0.035100001841783524, -0.020899999886751175, -0.028599999845027924, -0.02810000069439411]], [[-0.035999998450279236, -0.07119999825954437, 0.039799999445676804, 0.01510000042617321, -0.03620000183582306, -0.1136000007390976, 0.031199999153614044, 0.06199999898672104, -0.020600000396370888, 0.03880000114440918, 0.009600000455975533, -0.054099999368190765, 0.0008999999845400453, -0.056699998676776886, -0.04479999840259552, -0.06040000170469284, 0.05209999904036522, -0.06729999929666519, -0.016100000590085983, -0.09359999746084213, -0.08590000122785568, -0.0017999999690800905, 0.11599999666213989, 0.0925000011920929, 0.0794999971985817, -0.16740000247955322, 0.032999999821186066, -0.013000000268220901, 0.051600001752376556, 0.017799999564886093, 0.08739999681711197, 0.019600000232458115, -0.09459999948740005, 0.020800000056624413, 0.0625, -0.06970000267028809, 0.049300000071525574, -0.01769999973475933, 0.051100000739097595, 0.04390000179409981, -0.032099999487400055, 0.010300000198185444, 0.09759999811649323, 0.06449999660253525, -0.027799999341368675, 0.0551999993622303, 0.05290000140666962, 0.009100000374019146, -0.11869999766349792, 0.03909999877214432, 0.02850000001490116, -0.02329999953508377, -0.05050000175833702, -0.06469999998807907, 0.11299999803304672, 0.03790000081062317, 0.024399999529123306, 0.047200001776218414, 0.06560000032186508, -0.0649000033736229, 0.020800000056624413, 0.0203000009059906, -0.01979999989271164, 0.061900001019239426, -0.10279999673366547, 0.011900000274181366, -0.043299999088048935, 0.08349999785423279, 0.04470000043511391, -0.009499999694526196, 0.16850000619888306, -0.09309999644756317, 0.02879999950528145, -0.07270000129938126, -0.08370000123977661, 0.14749999344348907, -0.01590000092983246, -0.021900000050663948, -0.0027000000700354576, -0.013899999670684338, 0.05779999867081642, 0.0333000011742115, 0.0737999975681305, 0.03849999979138374, 0.06870000064373016, 0.06970000267028809, -0.052799999713897705, 0.016100000590085983, 0.04410000145435333, -0.012000000104308128, -0.08229999989271164, -0.03189999982714653, -0.011099999770522118, 0.009800000116229057, -0.014499999582767487, -0.01600000075995922, -0.20909999310970306, 0.05869999900460243, -0.1274999976158142, -0.10970000177621841, 0.10589999705553055, -0.10869999974966049, -0.07519999891519547, 0.06780000030994415, 0.05249999836087227, -0.061000000685453415, 9.999999747378752e-05, 0.04969999939203262, 0.07259999960660934, -0.10350000113248825, 0.01209999993443489, -0.018300000578165054, 0.01730000041425228, 0.04820000007748604, 0.008500000461935997, -0.0812000036239624, 0.0010999999940395355, 0.16449999809265137, 0.025499999523162842, -0.030500000342726707, 0.012900000438094139, 0.10220000147819519, -0.06639999896287918, -0.024700000882148743, 0.06310000270605087, 0.1071000024676323, -0.051500000059604645, -0.060600001364946365, -0.09120000153779984, 0.12530000507831573, -0.0478999987244606, 0.03189999982714653, -0.06669999659061432, -0.020600000396370888, 0.09220000356435776, 0.12020000070333481, -0.01119999960064888, -0.08340000361204147, 0.026100000366568565, -0.010400000028312206, -0.06159999966621399, 0.028200000524520874, 0.094200000166893, 0.014299999922513962, 0.1054999977350235, 0.09910000115633011, 0.05590000003576279, -0.08489999920129776, -0.0024999999441206455, -0.00430000014603138, -0.13279999792575836, -0.08919999748468399, 0.03150000050663948, -0.08959999680519104, -0.023900000378489494, -0.09529999643564224, 0.06400000303983688, -0.03240000084042549, -0.0066999997943639755, -0.09799999743700027, -0.014999999664723873, 0.02419999986886978, -0.07289999723434448, 0.1665000021457672, 0.05829999968409538, -0.10559999942779541, -0.06360000371932983, -0.021900000050663948, -0.0010000000474974513, 0.006000000052154064, 0.05249999836087227, -0.07109999656677246, 0.022700000554323196, -0.09030000120401382, 0.032999999821186066, 0.08990000188350677, 0.03700000047683716, 0.04010000079870224, -0.04830000177025795, 0.022099999710917473, 0.03819999843835831, 0.1200999990105629, 0.03280000016093254, -0.1264999955892563, -0.05510000139474869, -0.08980000019073486, 0.043800000101327896, 0.06830000132322311, 0.16099999845027924, -0.10769999772310257, -0.07569999992847443, 0.032099999487400055, -0.033900000154972076, -0.02979999966919422, -0.09279999881982803, -0.12210000306367874, 0.1054999977350235, -0.028599999845027924, 0.04820000007748604, -0.029500000178813934, 0.07689999788999557, 0.10379999876022339, 0.0560000017285347, 0.04690000042319298, 0.036400001496076584, 0.018799999728798866, -0.058400001376867294, 0.12680000066757202, 0.012400000356137753, 0.07649999856948853, 0.05570000037550926, 0.041099999099969864, 0.0778999999165535, 0.03819999843835831, 0.060499999672174454, -0.11389999836683273, 0.13130000233650208, 0.026599999517202377, 0.002300000051036477, 0.02500000037252903, 0.09019999951124191, 0.045099999755620956, -0.15790000557899475, -0.044599998742341995, -0.021400000900030136, 0.0430000014603138, -0.011599999852478504, -0.07020000368356705, 0.08309999853372574, 0.016899999231100082, -0.11569999903440475, -0.032099999487400055, -0.04839999973773956, -0.0877000018954277, 0.02850000001490116, -0.11190000176429749, -0.006599999964237213, 0.061799999326467514, 0.06360000371932983, -0.05310000106692314, 0.0778999999165535, 0.006000000052154064, 0.024399999529123306, -0.009700000286102295, -0.025699999183416367, 0.10869999974966049, -0.06239999830722809, -0.029500000178813934, 0.0885000005364418, -0.08590000122785568, -0.03759999945759773, -0.003700000001117587, 0.05209999904036522, 0.014399999752640724, -0.025200000032782555, 0.06729999929666519, 0.05009999871253967, 0.03500000014901161, 0.12370000034570694, -0.0414000004529953, 0.04230000078678131, -0.09139999747276306, 0.09830000251531601, 0.06889999657869339], [0.09730000048875809, 0.06800000369548798, 0.04919999837875366, 0.0697999969124794, -0.0071000000461936, 0.04569999873638153, 0.10279999673366547, -0.08429999649524689, -0.09539999812841415, -0.1014999970793724, 0.012400000356137753, -0.02199999988079071, -0.14480000734329224, 0.02459999918937683, 0.021199999377131462, -0.030899999663233757, -0.11429999768733978, 0.0013000000035390258, 0.06350000202655792, -0.041600000113248825, -0.03180000185966492, -0.05950000137090683, 0.037300001829862595, -0.04500000178813934, 0.06750000268220901, -0.032099999487400055, -0.0031999999191612005, -0.060600001364946365, -0.014499999582767487, -0.05559999868273735, 0.11010000109672546, 0.09210000187158585, 0.11129999905824661, 0.08389999717473984, 0.0020000000949949026, 0.044599998742341995, -0.0052999998442828655, -0.07180000096559525, -0.0007999999797903001, -0.04230000078678131, -0.03150000050663948, 0.09560000151395798, -0.02969999983906746, 0.0949999988079071, -0.002400000113993883, -0.05310000106692314, 0.02239999920129776, -0.07450000196695328, -0.050599999725818634, -0.05090000107884407, -0.03240000084042549, 0.01899999938905239, 0.06880000233650208, 0.025200000032782555, -0.0333000011742115, 0.1005999967455864, 0.0364999994635582, -0.04129999876022339, 0.041200000792741776, -0.024700000882148743, -0.1200999990105629, 0.00279999990016222, 0.0142000000923872, 0.002099999925121665, -0.1096000000834465, 0.07909999787807465, 0.02410000003874302, -0.048500001430511475, -0.008899999782443047, -0.11050000041723251, -0.0, -0.05420000106096268, 0.04879999905824661, -0.01720000058412552, 0.08309999853372574, -0.08619999885559082, 0.024900000542402267, -0.09160000085830688, 0.04170000180602074, -0.10869999974966049, -0.07639999687671661, -0.04619999974966049, 0.03999999910593033, 0.04270000010728836, -0.050999999046325684, -0.10459999740123749, 0.04740000143647194, 0.026399999856948853, 0.10599999874830246, -0.0843999981880188, -0.03849999979138374, -0.00559999980032444, -0.10369999706745148, -0.0430000014603138, -0.004600000102072954, 0.14139999449253082, -0.05860000103712082, 0.11180000007152557, -0.11590000241994858, 0.039799999445676804, 0.10729999840259552, 0.044199999421834946, -0.039500001817941666, -0.00019999999494757503, 0.05350000038743019, -0.11129999905824661, 0.08839999884366989, 0.009700000286102295, 0.00839999970048666, 0.019300000742077827, 0.05999999865889549, 0.038600001484155655, 0.11110000312328339, 0.04749999940395355, 0.11500000208616257, -0.057500001043081284, -0.01860000006854534, 0.15189999341964722, 0.014800000004470348, -0.004800000227987766, -0.06939999759197235, -0.07159999758005142, -0.11649999767541885, 0.06880000233650208, -0.10360000282526016, 0.03480000048875809, -0.027300000190734863, -0.15710000693798065, -0.10779999941587448, 0.27950000762939453, -0.026100000366568565, -0.050200000405311584, 0.12770000100135803, -0.01850000023841858, -0.02290000021457672, 0.03519999980926514, -0.06419999897480011, -0.05290000140666962, -0.024399999529123306, 0.07329999655485153, 0.1152999997138977, -0.12330000102519989, -0.06639999896287918, 0.009399999864399433, 0.17880000174045563, -0.07400000095367432, 0.014499999582767487, 0.011099999770522118, 0.051600001752376556, 0.030500000342726707, 0.04050000011920929, 0.045499999076128006, -0.10289999842643738, -0.09910000115633011, 0.06459999829530716, 0.0034000000450760126, -0.017100000753998756, 0.05299999937415123, 0.051600001752376556, 0.08590000122785568, -0.06480000168085098, -0.028300000354647636, 0.010400000028312206, -0.010999999940395355, 0.045499999076128006, 0.1289999932050705, 0.00039999998989515007, 0.04580000042915344, -0.08209999650716782, -0.022299999371170998, -0.011099999770522118, 0.013799999840557575, -0.02630000002682209, -0.014600000344216824, 0.06340000033378601, 0.015399999916553497, 0.05869999900460243, 0.006599999964237213, -0.03539999946951866, -0.008299999870359898, 0.07450000196695328, 0.1527000069618225, -0.01209999993443489, -0.04969999939203262, 0.005100000184029341, -0.09130000323057175, -0.04190000146627426, 0.03620000183582306, 0.07039999961853027, 0.04450000077486038, -0.00570000009611249, -0.019600000232458115, 0.012600000016391277, 0.03700000047683716, -0.03350000083446503, -0.08990000188350677, 0.00930000003427267, 0.0869000032544136, 0.058400001376867294, -0.03889999911189079, 0.04010000079870224, -0.08190000057220459, 0.023800000548362732, 0.03180000185966492, -0.05849999934434891, 0.03620000183582306, -0.04050000011920929, 0.06859999895095825, 0.037700001150369644, -0.004800000227987766, 0.07900000363588333, -0.04740000143647194, 0.12470000237226486, -0.061400000005960464, 0.08479999750852585, -0.09099999815225601, -0.004600000102072954, -0.06300000101327896, 0.11670000106096268, 0.009700000286102295, -0.057999998331069946, -0.11810000240802765, 0.014700000174343586, 0.05959999933838844, 0.011800000444054604, -0.07500000298023224, -0.09459999948740005, 0.039900001138448715, -0.041200000792741776, -0.07680000364780426, -0.008299999870359898, -0.1404000073671341, -0.03869999945163727, 0.066600002348423, 0.008100000210106373, 0.06759999692440033, 0.14190000295639038, 0.022099999710917473, 0.03310000151395798, 0.04470000043511391, 0.03790000081062317, 0.08969999849796295, 0.049300000071525574, -0.01269999984651804, -0.1306000053882599, 0.019899999722838402, -0.0003000000142492354, 0.04580000042915344, -0.06800000369548798, 0.00860000029206276, 0.054099999368190765, 0.05719999969005585, 0.04960000142455101, -0.09359999746084213, -0.047600001096725464, 0.13580000400543213, 0.07129999995231628, 0.005499999970197678, -0.03150000050663948, 0.1264999955892563, 0.009999999776482582, -0.10450000315904617, 0.12999999523162842, -0.023000000044703484], [-0.11490000039339066, -0.03830000013113022, -0.04690000042319298, 0.003599999938160181, -0.03280000016093254, -0.06069999933242798, 0.026499999687075615, -0.05139999836683273, 0.07289999723434448, -0.05040000006556511, 0.04639999940991402, 0.008999999612569809, -0.058800000697374344, -0.04190000146627426, -0.01269999984651804, -0.09000000357627869, 0.02370000071823597, -0.023499999195337296, -0.009399999864399433, 0.00139999995008111, -0.03550000116229057, -0.0066999997943639755, -0.03739999979734421, -0.027799999341368675, -0.0034000000450760126, -0.03819999843835831, -0.0010999999940395355, 0.03229999914765358, 0.06360000371932983, -0.18490000069141388, -0.07209999859333038, -0.026499999687075615, 0.07259999960660934, -0.005200000014156103, 0.10920000076293945, -0.049300000071525574, -0.013500000350177288, -0.131400004029274, 0.051100000739097595, -0.06599999964237213, -0.07970000058412552, 0.05999999865889549, 0.10610000044107437, -0.0044999998062849045, -0.06400000303983688, -0.030500000342726707, -0.12620000541210175, -0.0885000005364418, 0.040800001472234726, 0.0005000000237487257, 0.1062999963760376, 0.026900000870227814, -0.03590000048279762, -0.01590000092983246, 0.12970000505447388, -0.06989999860525131, -0.006899999920278788, -0.024700000882148743, 0.09600000083446503, 0.03779999911785126, 0.1362999975681305, 0.04749999940395355, 0.023499999195337296, -0.13840000331401825, -0.06849999725818634, 0.09059999883174896, 0.11800000071525574, -0.016699999570846558, -0.02319999970495701, 0.009200000204145908, -0.01810000091791153, -0.027699999511241913, -0.009499999694526196, -0.125, 0.01510000042617321, 0.0729999989271164, -0.0689999982714653, -0.01489999983459711, -0.046300001442432404, -0.16120000183582306, 0.05640000104904175, -0.1615000069141388, -0.08089999854564667, 0.01860000006854534, -0.1096000000834465, 0.006899999920278788, -0.06800000369548798, -0.011800000444054604, 0.02319999970495701, -0.022199999541044235, 0.047200001776218414, 0.022299999371170998, -0.051500000059604645, -0.04360000044107437, -0.0406000018119812, -0.032099999487400055, -0.049300000071525574, -0.019200000911951065, -0.05689999833703041, 0.14190000295639038, 0.024299999698996544, 0.08820000290870667, -0.061900001019239426, 0.051899999380111694, -0.01269999984651804, -0.11180000007152557, -0.0052999998442828655, 0.04190000146627426, 0.020600000396370888, -0.17239999771118164, -0.009200000204145908, -0.12120000272989273, -0.0697999969124794, 0.02070000022649765, 0.06469999998807907, 0.07079999893903732, -0.09730000048875809, -0.03610000014305115, -0.07370000332593918, 0.0625, -0.008700000122189522, 0.10429999977350235, 0.22509999573230743, -0.0020000000949949026, -0.002199999988079071, 0.08829999715089798, -0.19850000739097595, 0.04619999974966049, 0.048500001430511475, 0.16869999468326569, -0.1648000031709671, -0.045899998396635056, -0.02410000003874302, -0.07150000333786011, 0.06870000064373016, 0.010400000028312206, 0.026599999517202377, 0.029400000348687172, 0.10899999737739563, 0.05130000039935112, 0.10379999876022339, -0.04780000075697899, 0.04729999974370003, 0.05009999871253967, 0.08609999716281891, -0.03550000116229057, 0.052000001072883606, 0.04190000146627426, -0.11320000141859055, -0.062300000339746475, 0.13689999282360077, 0.03819999843835831, -0.10570000112056732, -0.12710000574588776, 0.06939999759197235, 0.05090000107884407, 0.11569999903440475, 0.05640000104904175, 0.03590000048279762, 0.07169999927282333, -0.09709999710321426, -0.008200000040233135, 0.06809999793767929, -0.011099999770522118, 0.08980000019073486, 0.020999999716877937, 0.025499999523162842, -0.09309999644756317, 0.0007999999797903001, 0.04879999905824661, 0.0026000000070780516, -0.08889999985694885, 0.052000001072883606, 0.019099999219179153, -0.00019999999494757503, -0.06849999725818634, 0.03480000048875809, 0.11089999973773956, 0.11249999701976776, -0.03310000151395798, -0.014999999664723873, -0.031199999153614044, -0.12020000070333481, -0.07010000199079514, 0.05510000139474869, 0.028300000354647636, 0.09350000321865082, 0.05040000006556511, 0.060499999672174454, 0.03350000083446503, -0.017899999395012856, -0.045099999755620956, -0.07639999687671661, -0.027300000190734863, -0.028300000354647636, 0.009100000374019146, 0.032600000500679016, 0.04879999905824661, 0.002199999988079071, -0.004000000189989805, 0.010499999858438969, -0.027699999511241913, -0.04740000143647194, 0.07069999724626541, -0.04690000042319298, 0.03359999880194664, -0.08550000190734863, 0.18930000066757202, -0.010900000110268593, -0.12950000166893005, 0.08349999785423279, -0.08060000091791153, -0.0284000001847744, 0.09849999845027924, 0.050999999046325684, 0.03920000046491623, 0.027799999341368675, -0.04740000143647194, 0.07180000096559525, -0.03920000046491623, 0.01119999960064888, -0.02889999933540821, 0.02250000089406967, -0.03750000149011612, 0.05640000104904175, 0.023499999195337296, -0.03720000013709068, 0.07819999754428864, -0.02669999934732914, 0.03009999915957451, 0.01549999974668026, -0.017999999225139618, 0.019999999552965164, -0.02419999986886978, -0.11749999970197678, -0.010999999940395355, -0.11400000005960464, 0.056299999356269836, 0.01679999940097332, 0.04879999905824661, 0.04969999939203262, 0.1307000070810318, 0.1193000003695488, 0.016599999740719795, -0.03920000046491623, -0.09839999675750732, -0.00930000003427267, 0.04490000009536743, 0.002899999963119626, -0.07970000058412552, 0.08560000360012054, -0.09520000219345093, -0.016200000420212746, 0.0012000000569969416, -0.1348000019788742, 0.0038999998942017555, 0.07400000095367432, 0.04089999943971634, -0.00989999994635582, -0.0019000000320374966, -0.0471000000834465, 0.006099999882280827, 0.023399999365210533, 0.07940000295639038], [0.016499999910593033, -0.005900000222027302, 0.008799999952316284, 0.010099999606609344, -0.017000000923871994, 0.028699999675154686, -0.022099999710917473, 0.13279999792575836, 0.05480000004172325, -0.0, -0.007199999876320362, -0.0731000006198883, 0.03310000151395798, -0.05820000171661377, -0.0272000003606081, -0.21439999341964722, 0.08720000088214874, -0.1216999962925911, 0.0949999988079071, -0.09929999709129333, 0.03550000116229057, 0.024399999529123306, 0.03830000013113022, -0.07029999792575836, 0.002300000051036477, -0.011599999852478504, -0.005900000222027302, -0.09679999947547913, -0.017500000074505806, -0.08699999749660492, -0.018699999898672104, 0.021800000220537186, 0.01080000028014183, 0.012600000016391277, 0.08489999920129776, -0.07519999891519547, -0.04780000075697899, 0.060499999672174454, -0.12319999933242798, -0.01889999955892563, 0.05990000069141388, 0.04569999873638153, 0.06260000169277191, -0.00419999985024333, 0.0003000000142492354, -0.07769999653100967, 0.0272000003606081, -0.0017999999690800905, -0.0934000015258789, -0.06549999862909317, 0.21699999272823334, 0.026100000366568565, -0.09019999951124191, -0.1023000031709671, -0.10050000250339508, 0.02070000022649765, -0.008799999952316284, 0.007799999788403511, 0.030500000342726707, -0.02239999920129776, 0.006500000134110451, 0.04740000143647194, -0.05550000071525574, 0.12060000002384186, -0.06530000269412994, -0.10040000081062317, 0.07039999961853027, -0.09629999846220016, -0.03449999913573265, 0.004900000058114529, 0.04690000042319298, 0.06620000302791595, -0.17249999940395355, 0.011900000274181366, 0.04390000179409981, 0.010700000450015068, -0.05609999969601631, -0.10760000348091125, 0.05090000107884407, 0.022099999710917473, 0.007699999958276749, -0.00860000029206276, -0.05380000174045563, 0.000699999975040555, -0.009100000374019146, 0.003100000089034438, -0.0729999989271164, 0.08330000191926956, -0.025800000876188278, -0.09430000185966492, 0.07460000365972519, 0.03929999843239784, -0.07880000025033951, 0.021199999377131462, -0.045499999076128006, -0.03590000048279762, 0.12060000002384186, 0.0032999999821186066, 0.026799999177455902, 0.09629999846220016, -0.06710000336170197, -0.00839999970048666, -0.032600000500679016, -0.05429999902844429, 0.033900000154972076, -0.07029999792575836, 0.02419999986886978, -0.01600000075995922, -0.09459999948740005, 0.12389999628067017, -0.04450000077486038, 0.11400000005960464, 0.09709999710321426, -0.024299999698996544, -0.020600000396370888, -0.02329999953508377, 0.11429999768733978, -0.004900000058114529, 0.04479999840259552, 0.18479999899864197, -0.030300000682473183, -0.0934000015258789, -0.060600001364946365, -0.07259999960660934, -0.04769999906420708, 0.03020000085234642, -0.06159999966621399, -0.09600000083446503, 0.006800000090152025, 0.029100000858306885, -0.011099999770522118, 0.02290000021457672, -0.07509999722242355, -0.0471000000834465, -0.06260000169277191, 0.17239999771118164, -0.05990000069141388, -0.05990000069141388, -0.05640000104904175, 0.04039999842643738, -0.12759999930858612, -0.012900000438094139, 0.0754999965429306, 0.06379999965429306, 0.06270000338554382, -0.02280000038444996, 0.08429999649524689, 0.0746999979019165, 0.08110000193119049, 0.0632999986410141, -0.028599999845027924, -0.04650000110268593, 0.050700001418590546, 0.00839999970048666, 0.0035000001080334187, -0.013500000350177288, -0.017400000244379044, -0.05169999971985817, 0.006800000090152025, 0.028200000524520874, 0.14730000495910645, 0.04089999943971634, -0.060499999672174454, -0.04479999840259552, -0.019700000062584877, 0.015799999237060547, -0.12759999930858612, -0.03970000147819519, -0.04780000075697899, 0.004699999932199717, -0.018400000408291817, -0.0015999999595806003, -0.05869999900460243, 0.11670000106096268, -0.011599999852478504, 0.1459999978542328, 0.042899999767541885, 0.0544000007212162, 0.016699999570846558, 0.029500000178813934, 0.03970000147819519, 0.12470000237226486, -0.02559999935328960</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>[0.5103931987132552]</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>[0.11176089375152168]</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>[0.7086262692688682]</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>[0.06652157579383013]</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>[-14.872584269919765]</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>[5.194774531478183]</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>[0.4062508902661437]</t>
+        </is>
+      </c>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>[0.13639549517853886]</t>
+        </is>
+      </c>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>[0.8641482271877967]</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>[0.03221874597707682]</t>
+        </is>
+      </c>
+      <c r="O32" t="inlineStr">
+        <is>
+          <t>[-20.56666988484104]</t>
+        </is>
+      </c>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>[7.089987591793918]</t>
+        </is>
+      </c>
+      <c r="Q32" t="inlineStr">
+        <is>
+          <t>[-0.2844462129765444]</t>
+        </is>
+      </c>
+      <c r="R32" t="inlineStr">
+        <is>
+          <t>[0.13849634928845406]</t>
+        </is>
+      </c>
+      <c r="S32" t="inlineStr">
+        <is>
+          <t>[-1.3120974859950567]</t>
+        </is>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>[0.19481811972661]</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>[-0.43556035884142674]</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>[0.1372727756474851]</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>[-0.2368789928361874]</t>
+        </is>
+      </c>
+      <c r="X32" t="inlineStr">
+        <is>
+          <t>[0.12957621455072474]</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>[-1.1722664215390992]</t>
+        </is>
+      </c>
+      <c r="Z32" t="inlineStr">
+        <is>
+          <t>[0.17876277615634248]</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>[-0.10592033156964953]</t>
+        </is>
+      </c>
+      <c r="AB32" t="inlineStr">
+        <is>
+          <t>[0.10174950818191696]</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>[-0.3276355157298745]</t>
+        </is>
+      </c>
+      <c r="AD32" t="inlineStr">
+        <is>
+          <t>[0.11125050769513636]</t>
+        </is>
+      </c>
+      <c r="AE32" t="inlineStr">
+        <is>
+          <t>[-0.8782022257276663]</t>
+        </is>
+      </c>
+      <c r="AF32" t="inlineStr">
+        <is>
+          <t>[0.20224119840768653]</t>
+        </is>
+      </c>
+      <c r="AG32" t="inlineStr">
+        <is>
+          <t>[-1.249035666454907]</t>
+        </is>
+      </c>
+      <c r="AH32" t="inlineStr">
+        <is>
+          <t>[0.167440611927252]</t>
+        </is>
+      </c>
+      <c r="AI32" t="inlineStr">
+        <is>
+          <t>[-0.48955753718651707]</t>
+        </is>
+      </c>
+      <c r="AJ32" t="inlineStr">
+        <is>
+          <t>[0.12206758197603669]</t>
+        </is>
+      </c>
+      <c r="AK32" t="inlineStr">
+        <is>
+          <t>[-0.9163855051771792]</t>
+        </is>
+      </c>
+      <c r="AL32" t="inlineStr">
+        <is>
+          <t>[0.20341028071219544]</t>
+        </is>
+      </c>
+      <c r="AM32" t="inlineStr">
+        <is>
+          <t>[-1.9879421239948605]</t>
+        </is>
+      </c>
+      <c r="AN32" t="inlineStr">
+        <is>
+          <t>[0.22949561651979186]</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>model_264_128_1</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>[264, 128]</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>[[[0.01979999989271164, -0.020899999886751175, 0.04690000042319298, 0.05649999901652336, 0.05119999870657921, -0.12319999933242798, 0.017400000244379044, 0.01510000042617321, -0.01759999990463257, 0.030300000682473183, -0.039000000804662704, -0.014499999582767487, 0.03610000014305115, 0.09679999947547913, -0.0632999986410141, 0.003100000089034438, -0.010999999940395355, -0.0006000000284984708, 0.009399999864399433, 0.00570000009611249, -0.03370000049471855, -0.07819999754428864, -0.08079999685287476, 0.07209999859333038, 0.03180000185966492, -0.039500001817941666, 0.04800000041723251, -0.0617000013589859, 0.14569999277591705, -0.03849999979138374, -0.019700000062584877, 0.003700000001117587, -0.012799999676644802, 0.02979999966919422, -0.010999999940395355, -0.023900000378489494, -0.02449999935925007, 0.014000000432133675, -0.05990000069141388, -0.028300000354647636, 0.032099999487400055, -0.0835999995470047, -0.06310000270605087, -0.0348999984562397, 0.05040000006556511, -0.029600000008940697, 0.026799999177455902, -0.005100000184029341, -0.12250000238418579, 0.03200000151991844, -0.028999999165534973, 0.0731000006198883, 0.017999999225139618, -0.03880000114440918, 0.07970000058412552, -0.007000000216066837, 0.031300000846385956, -0.03139999881386757, 0.050599999725818634, 0.06360000371932983, -0.04699999839067459, 0.028300000354647636, 0.056699998676776886, -0.07150000333786011, -0.09989999979734421, 0.006500000134110451, -0.049400001764297485, 0.02630000002682209, -0.010700000450015068, -0.07890000194311142, 0.10100000351667404, -0.03750000149011612, -0.08540000021457672, 0.07190000265836716, 0.05290000140666962, 0.017999999225139618, 0.026200000196695328, 0.04619999974966049, -0.05559999868273735, 0.0210999995470047, -0.01590000092983246, 0.07689999788999557, 0.05220000073313713, 0.025200000032782555, 0.10400000214576721, -0.0284000001847744, 0.0005000000237487257, -0.05040000006556511, -0.094200000166893, 0.009399999864399433, 0.0364999994635582, -0.06710000336170197, 0.00559999980032444, -0.10379999876022339, 0.07909999787807465, -0.015599999576807022, 0.09070000052452087, 0.008700000122189522, -0.023000000044703484, 0.031599998474121094, 0.04809999838471413, 0.0835999995470047, 0.01640000008046627, 0.043800000101327896, -0.02879999950528145, -0.014600000344216824, 0.023600000888109207, 0.002899999963119626, -0.05040000006556511, 0.05000000074505806, -0.03449999913573265, -0.019500000402331352, -0.01889999955892563, -0.009499999694526196, 0.03790000081062317, -0.004800000227987766, -0.06629999727010727, -0.05990000069141388, 0.019500000402331352, 0.0771000012755394, -0.051899999380111694, 0.08720000088214874, -0.03909999877214432, -0.049300000071525574, 0.008500000461935997, -0.0737999975681305, -0.01730000041425228, -0.04349999874830246, 0.08550000190734863, 0.06120000034570694, 0.04780000075697899, 0.006500000134110451, -0.028300000354647636, -0.08110000193119049, -0.052299998700618744, -0.0640999972820282, 0.020800000056624413, -0.007799999788403511, 0.02199999988079071, -0.0071000000461936, -0.0284000001847744, -0.08789999783039093, 0.0017999999690800905, -0.016699999570846558, -0.0284000001847744, -0.07460000365972519, -0.05310000106692314, -0.028699999675154686, 0.0544000007212162, 0.041600000113248825, 0.019600000232458115, 0.021800000220537186, -0.05310000106692314, 0.02810000069439411, -0.013899999670684338, -0.02070000022649765, 0.0031999999191612005, -0.06729999929666519, 0.03150000050663948, -0.0008999999845400453, -0.03610000014305115, -0.005100000184029341, 0.03750000149011612, -0.00430000014603138, -0.0689999982714653, -0.05299999937415123, 0.09290000051259995, 0.017799999564886093, -0.054499998688697815, 0.007899999618530273, 0.05350000038743019, 0.01889999955892563, 0.01269999984651804, 0.014399999752640724, -0.008999999612569809, 0.03590000048279762, -0.04910000041127205, -0.061900001019239426, -0.006200000178068876, -0.0284000001847744, -0.005799999926239252, -0.09480000287294388, -0.06880000233650208, -0.09839999675750732, 0.014700000174343586, 0.08150000125169754, 0.06889999657869339, -0.07959999889135361, 0.05299999937415123, -0.013299999758601189, 0.03750000149011612, 0.04399999976158142, 0.08150000125169754, 0.06270000338554382, -0.008299999870359898, 0.01549999974668026, 0.0017000000225380063, -0.02239999920129776, -0.04050000011920929, -0.027000000700354576, -0.08240000158548355, -0.05040000006556511, 0.03139999881386757, 0.05719999969005585, 0.04309999942779541, 0.04479999840259552, -0.01850000023841858, 0.0738999992609024, -0.04479999840259552, 0.03269999846816063, -0.03959999978542328, -0.07020000368356705, 0.04129999876022339, 0.10819999873638153, -0.0272000003606081, -0.06279999762773514, -0.03889999911189079, 0.0828000009059906, 0.05270000174641609, 0.024900000542402267, -0.05079999938607216, -0.07769999653100967, -0.07289999723434448, 0.017000000923871994, -0.08510000258684158, -0.04960000142455101, -0.011800000444054604, 0.08110000193119049, 0.027300000190734863, 0.030700000002980232, -0.011300000362098217, 0.01549999974668026, 0.007400000002235174, -0.044599998742341995, 0.07500000298023224, -0.01889999955892563, -0.05590000003576279, 0.03240000084042549, 0.05079999938607216, 0.08720000088214874, -0.07329999655485153, 0.030300000682473183, 0.03959999978542328, 0.0013000000035390258, 0.02810000069439411, -0.030899999663233757, -0.10530000180006027, -0.03350000083446503, 0.0421999990940094, -0.08380000293254852, -0.03229999914765358, -0.007899999618530273, -0.04320000112056732, 0.039400000125169754, 0.010900000110268593, -0.07999999821186066, 0.030899999663233757, 0.01889999955892563, 0.03099999949336052, -0.03920000046491623, 0.054499998688697815, -0.030700000002980232, -0.10980000346899033, 0.052299998700618744], [0.06289999932050705, -0.04699999839067459, 0.04859999939799309, -0.00559999980032444, -0.019099999219179153, 0.04349999874830246, 0.03629999980330467, -0.009200000204145908, 0.0632999986410141, 0.012900000438094139, -0.021900000050663948, -0.026799999177455902, -0.024700000882148743, -0.06729999929666519, -0.05249999836087227, 0.05350000038743019, 0.011500000022351742, -0.060499999672174454, 0.05920000001788139, 0.13079999387264252, -0.031300000846385956, 0.09000000357627869, -0.05660000070929527, -0.008999999612569809, 0.08829999715089798, -0.08240000158548355, -0.07339999824762344, 0.007199999876320362, 0.030300000682473183, -0.009800000116229057, 0.02449999935925007, -0.02669999934732914, -0.01730000041425228, 0.024800000712275505, -0.06289999932050705, 0.03519999980926514, -0.04340000078082085, 0.03269999846816063, 0.012600000016391277, 0.04639999940991402, 0.025599999353289604, 0.047200001776218414, 0.03590000048279762, 0.06880000233650208, 0.011699999682605267, -0.04800000041723251, 0.005200000014156103, 0.04769999906420708, 0.1088000014424324, 0.006800000090152025, -0.03319999948143959, 0.1023000031709671, -0.042500000447034836, -0.0010999999940395355, 0.06030000001192093, -0.08410000056028366, 0.0019000000320374966, -0.010599999688565731, -0.002400000113993883, 0.01860000006854534, -0.012799999676644802, 0.06129999831318855, 0.07119999825954437, 0.007499999832361937, 0.010200000368058681, 0.08169999718666077, -0.043299999088048935, 0.04650000110268593, -0.05169999971985817, -0.05400000140070915, 0.0019000000320374966, -0.065700002014637, -0.041099999099969864, -0.05000000074505806, -0.000699999975040555, 0.0006000000284984708, -0.011900000274181366, 0.006800000090152025, -0.030799999833106995, -0.013500000350177288, 0.013199999928474426, -0.004800000227987766, 0.044199999421834946, 0.04899999871850014, -0.03220000118017197, -0.05689999833703041, -0.023900000378489494, -0.016499999910593033, -0.04149999842047691, -0.07349999994039536, -0.08510000258684158, 0.03590000048279762, 0.06949999928474426, 0.05169999971985817, -0.027699999511241913, -0.06159999966621399, -0.05900000035762787, 0.06019999831914902, -0.13950000703334808, -0.12479999661445618, -0.017100000753998756, -0.004699999932199717, 0.0024999999441206455, 0.00930000003427267, 0.01730000041425228, 0.04670000076293945, 0.0471000000834465, -0.061400000005960464, 0.007300000172108412, 0.03920000046491623, -0.08110000193119049, -0.059700001031160355, 0.03909999877214432, -0.1467999964952469, -0.0005000000237487257, -0.03830000013113022, -0.08969999849796295, 0.06909999996423721, -0.031099999323487282, -0.09390000253915787, -0.012400000356137753, 0.03500000014901161, 0.046799998730421066, -0.023900000378489494, 0.03970000147819519, 0.09309999644756317, 0.09790000319480896, -0.0729999989271164, 0.04470000043511391, 0.028999999165534973, 0.03779999911785126, 0.05249999836087227, -0.014800000004470348, 0.03500000014901161, 0.002099999925121665, 0.08129999786615372, -0.0364999994635582, -0.019300000742077827, 0.0885000005364418, -0.002300000051036477, 0.006200000178068876, 0.023499999195337296, 0.02329999953508377, -0.013100000098347664, 0.017000000923871994, -0.02889999933540821, -0.04050000011920929, 0.09319999814033508, 0.11479999870061874, -0.09009999781847, 0.03830000013113022, -0.11339999735355377, 0.08429999649524689, 0.04309999942779541, 0.0035000001080334187, 0.05350000038743019, -0.07429999858140945, -0.0035000001080334187, 0.07320000231266022, 0.0843999981880188, 0.018400000408291817, 0.045099999755620956, -0.06260000169277191, -0.01679999940097332, 0.007699999958276749, -0.02590000070631504, 0.035599999129772186, -0.012799999676644802, 0.03579999879002571, 0.017999999225139618, -0.0471000000834465, -0.043699998408555984, 0.03999999910593033, 0.03009999915957451, 0.0925000011920929, 0.01759999990463257, 0.09239999949932098, 0.05420000106096268, 0.009399999864399433, 0.045899998396635056, -0.02539999969303608, 0.004999999888241291, 0.04410000145435333, -0.0272000003606081, 0.03680000081658363, -0.030500000342726707, -0.0013000000035390258, -0.054499998688697815, -0.05559999868273735, -0.01600000075995922, 0.00570000009611249, 0.04540000110864639, 0.07000000029802322, -0.03680000081658363, 0.05829999968409538, -0.019500000402331352, -0.0035000001080334187, 0.017999999225139618, 0.0038999998942017555, 0.06889999657869339, 0.0010999999940395355, -0.0568000003695488, -0.014600000344216824, 0.05169999971985817, 0.06870000064373016, -0.04989999905228615, 0.05380000174045563, -0.06889999657869339, 0.010700000450015068, -0.1023000031709671, 0.0017999999690800905, -0.05429999902844429, 0.010300000198185444, 0.06480000168085098, -0.042399998754262924, 0.00989999994635582, -0.011699999682605267, -0.11829999834299088, 0.059300001710653305, 0.03999999910593033, 0.021299999207258224, -0.012500000186264515, -0.028200000524520874, -0.04769999906420708, -0.04100000113248825, 0.016699999570846558, -0.0142000000923872, 0.06650000065565109, 0.05220000073313713, 0.0006000000284984708, 0.0812000036239624, -0.05420000106096268, -0.041099999099969864, -0.036400001496076584, 0.13210000097751617, -0.10429999977350235, 0.05950000137090683, -0.031099999323487282, -0.03750000149011612, -0.007199999876320362, -0.017000000923871994, -0.04170000180602074, -0.023099999874830246, 0.04050000011920929, -0.001500000013038516, -0.0348999984562397, 0.0697999969124794, 0.04170000180602074, -0.04050000011920929, 0.021700000390410423, -0.07079999893903732, -0.09229999780654907, 0.00930000003427267, -0.027499999850988388, 0.0031999999191612005, -0.014499999582767487, 0.028599999845027924, 0.07919999957084656, 0.061799999326467514, -0.050700001418590546, 0.01940000057220459, -0.029899999499320984, -0.007000000216066837, 0.024299999698996544]], [[0.008899999782443047, 0.010999999940395355, 0.03460000082850456, -0.01850000023841858, 0.0357000008225441, 0.04729999974370003, -0.019999999552965164, 0.012000000104308128, 0.01889999955892563, 0.023499999195337296, 0.03669999912381172, 0.06310000270605087, 0.09759999811649323, -0.04619999974966049, -0.061799999326467514, -0.013199999928474426, -0.01080000028014183, -0.05790000036358833, 0.016300000250339508, -0.06639999896287918, -0.013799999840557575, 0.006200000178068876, 0.06909999996423721, -0.06960000097751617, 0.06379999965429306, 0.1509000062942505, -0.035599999129772186, 0.025100000202655792, -0.02239999920129776, -0.00559999980032444, 0.053599998354911804, 0.09449999779462814, -0.031099999323487282, -0.014100000262260437, -0.07180000096559525, -0.03920000046491623, 0.0729999989271164, -0.03750000149011612, 0.11980000138282776, -0.010499999858438969, -0.014000000432133675, 0.06449999660253525, 0.0027000000700354576, 0.009800000116229057, 0.025699999183416367, 0.05429999902844429, -0.0568000003695488, 0.019300000742077827, -0.05719999969005585, -0.07429999858140945, -0.023900000378489494, -0.004399999976158142, -0.020500000566244125, -0.017000000923871994, 0.07349999994039536, -0.05900000035762787, -0.005900000222027302, 0.0502999983727932, 0.0406000018119812, -0.06040000170469284, -0.07829999923706055, 0.08669999986886978, -0.004900000058114529, -0.09430000185966492, -0.004699999932199717, 0.019899999722838402, 0.12409999966621399, 0.01720000058412552, -0.08460000157356262, -0.06880000233650208, -0.1136000007390976, 0.07109999656677246, -0.014999999664723873, -0.002300000051036477, 0.039799999445676804, 0.030700000002980232, -0.07900000363588333, 0.014000000432133675, -0.1274999976158142, -0.008799999952316284, 0.1242000013589859, 0.010099999606609344, 0.12839999794960022, 0.03579999879002571, 0.07100000232458115, 0.09099999815225601, 0.11050000041723251, 0.10610000044107437, -0.12950000166893005, -0.04820000007748604, -0.045499999076128006, 0.0013000000035390258, -0.009999999776482582, -0.07180000096559525, -0.040300000458955765, -0.07000000029802322, -0.09200000017881393, 0.07010000199079514, 0.022600000724196434, -0.04780000075697899, -0.05090000107884407, 0.06350000202655792, 0.032999999821186066, -0.06390000134706497, 0.11670000106096268, -0.003599999938160181, 0.019300000742077827, -0.1476999968290329, 0.14249999821186066, 0.04610000178217888, 0.01489999983459711, 0.03590000048279762, 0.027300000190734863, -0.15230000019073486, 0.028300000354647636, -0.10320000350475311, -0.12929999828338623, -0.06419999897480011, -0.030799999833106995, 0.02759999968111515, 0.05400000140070915, 0.035100001841783524, -0.013199999928474426, -0.046799998730421066, 0.01759999990463257, -0.025499999523162842, -0.08879999816417694, -0.00279999990016222, 0.03790000081062317, -0.028200000524520874, 0.052299998700618744, -0.019600000232458115, 0.0658000037074089, 0.0957999974489212, -0.0003000000142492354, 0.003000000026077032, -0.013399999588727951, 0.11060000211000443, 0.0471000000834465, -0.023499999195337296, -0.02459999918937683, 0.000699999975040555, -0.004800000227987766, 0.05050000175833702, 0.08320000022649765, 0.024700000882148743, -0.017100000753998756, 0.02370000071823597, 0.013199999928474426, -0.013000000268220901, -0.0142000000923872, 0.00019999999494757503, 0.013100000098347664, -0.021900000050663948, -0.0471000000834465, 0.03689999878406525, -0.01730000041425228, -0.02759999968111515, -0.030300000682473183, -0.021900000050663948, -0.022099999710917473, 0.032099999487400055, 0.04830000177025795, -0.001500000013038516, -0.06509999930858612, -0.013299999758601189, 0.014600000344216824, -0.02319999970495701, -0.1454000025987625, 0.10840000212192535, 0.10189999639987946, -0.039400000125169754, -0.020600000396370888, -0.008500000461935997, -0.0771000012755394, -0.044199999421834946, 0.10859999805688858, -0.05570000037550926, -0.053599998354911804, -0.023499999195337296, 0.028300000354647636, 0.08370000123977661, -0.015300000086426735, 0.004999999888241291, -0.03759999945759773, -0.08739999681711197, 0.0038999998942017555, -0.014600000344216824, -0.03500000014901161, 0.016300000250339508, -0.06469999998807907, -0.05810000002384186, 0.03020000085234642, 0.0008999999845400453, 0.04780000075697899, -0.08030000329017639, 0.1420000046491623, 0.08869999647140503, 0.020800000056624413, -0.022299999371170998, 0.11100000143051147, -0.06769999861717224, -0.1316000074148178, 0.03669999912381172, 0.04800000041723251, -0.1111999973654747, 0.00930000003427267, 0.046799998730421066, 0.05050000175833702, 0.07580000162124634, 0.00800000037997961, 0.07500000298023224, -0.09969999641180038, -0.039799999445676804, -0.004900000058114529, 0.022700000554323196, -0.07010000199079514, 0.02410000003874302, 0.007499999832361937, -0.17440000176429749, -0.02319999970495701, 0.025599999353289604, 0.010400000028312206, 0.04170000180602074, 0.1046999990940094, -0.11860000342130661, 0.02449999935925007, -0.07959999889135361, 0.025499999523162842, 0.009800000116229057, -0.13089999556541443, 0.041999999433755875, -0.030899999663233757, 0.010999999940395355, -0.11729999631643295, 0.024000000208616257, 0.015399999916553497, 0.07419999688863754, 0.006399999838322401, 0.053599998354911804, -0.04340000078082085, 0.013899999670684338, 0.009499999694526196, 0.09480000287294388, -0.07000000029802322, 0.009700000286102295, 0.08100000023841858, -0.05050000175833702, -0.05249999836087227, 0.06639999896287918, -0.04830000177025795, -0.0071000000461936, -0.07590000331401825, 0.037300001829862595, -0.009700000286102295, 0.06520000100135803, 0.038600001484155655, -0.0966000035405159, -0.00019999999494757503, 0.02590000070631504, -0.13109999895095825, -0.008700000122189522, -0.07989999651908875, -0.12020000070333481], [0.006200000178068876, 0.06790000200271606, -0.012900000438094139, -0.09960000216960907, -0.05000000074505806, -0.013700000010430813, 0.003000000026077032, -0.05270000174641609, 0.019600000232458115, 0.01940000057220459, 0.008700000122189522, -0.03750000149011612, 0.09070000052452087, -0.026200000196695328, 0.02710000053048134, 0.07100000232458115, 0.03189999982714653, -0.1039000004529953, 0.0746999979019165, -0.0625, 0.005799999926239252, 0.07850000262260437, 0.0575999990105629, 0.004900000058114529, 0.008200000040233135, 0.024399999529123306, 0.019999999552965164, -0.09560000151395798, 0.10249999910593033, -0.04650000110268593, -0.010599999688565731, 0.026799999177455902, -0.008700000122189522, 0.06120000034570694, 0.03750000149011612, -0.007799999788403511, 0.10289999842643738, 0.12929999828338623, -0.05339999869465828, 0.09520000219345093, 0.04309999942779541, 0.1136000007390976, 0.08129999786615372, -0.01640000008046627, 0.04650000110268593, 0.004900000058114529, -0.004600000102072954, -0.05609999969601631, -0.1046999990940094, -0.07479999959468842, -0.04309999942779541, 0.009399999864399433, -0.019899999722838402, -0.08699999749660492, 0.03840000182390213, -0.16519999504089355, -0.022700000554323196, -0.13899999856948853, 0.049300000071525574, -0.05119999870657921, 0.08990000188350677, 0.010300000198185444, -0.05169999971985817, 0.008999999612569809, 0.025200000032782555, -0.039799999445676804, -0.02459999918937683, -0.07050000131130219, 0.05939999967813492, 0.025800000876188278, 0.02850000001490116, 0.029200000688433647, 0.08619999885559082, -0.08309999853372574, 0.11630000174045563, -0.0917000025510788, 0.013000000268220901, 0.020500000566244125, 0.05820000171661377, 0.05900000035762787, 0.00559999980032444, 0.010300000198185444, -0.07090000063180923, 0.03519999980926514, 0.042100001126527786, -0.04729999974370003, 0.09889999777078629, 0.13979999721050262, -0.03519999980926514, -0.024800000712275505, 0.025100000202655792, -0.024800000712275505, -0.030700000002980232, 0.08229999989271164, -0.10530000180006027, -0.06920000165700912, -0.021700000390410423, 0.015300000086426735, 0.10840000212192535, -0.03060000017285347, 0.038100000470876694, -0.05829999968409538, -9.999999747378752e-05, 0.012500000186264515, 0.08320000022649765, 0.06400000303983688, -0.07209999859333038, 0.0019000000320374966, 0.018400000408291817, -0.05469999834895134, 0.04490000009536743, -0.07649999856948853, 0.1111999973654747, -0.09300000220537186, -0.06970000267028809, 0.04520000144839287, -0.004000000189989805, -0.01769999973475933, -0.09380000084638596, -0.07479999959468842, -0.037700001150369644, -0.0007999999797903001, -0.020899999886751175, 0.06109999865293503, 0.01850000023841858, 0.058800000697374344, 0.07909999787807465, 0.14020000398159027, 0.08219999819993973, 0.01489999983459711, 0.06419999897480011, 0.0020000000949949026, 0.015399999916553497, -0.021199999377131462, 0.03909999877214432, -0.0478999987244606, -0.02410000003874302, -0.0007999999797903001, 0.030500000342726707, -0.06750000268220901, -0.15940000116825104, 0.03539999946951866, 0.09059999883174896, 0.031300000846385956, 0.010900000110268593, -0.10840000212192535, -0.03290000185370445, 0.026900000870227814, 0.023099999874830246, 0.00839999970048666, -0.03229999914765358, 0.08640000224113464, 0.0738999992609024, 0.040699999779462814, -0.0284000001847744, 0.003599999938160181, -0.0035000001080334187, -0.015599999576807022, -0.006599999964237213, 0.0885000005364418, 0.07720000296831131, -0.02539999969303608, 0.0008999999845400453, -0.0044999998062849045, -0.05770000070333481, 0.02329999953508377, -0.0625, -0.05180000141263008, 0.006200000178068876, -0.019700000062584877, 0.019600000232458115, 0.06650000065565109, -0.0031999999191612005, -0.01360000018030405, 0.018400000408291817, 0.07660000026226044, 0.011699999682605267, -0.03669999912381172, -0.04560000076889992, 0.02500000037252903, 0.0706000030040741, -0.057500001043081284, -0.06270000338554382, -0.13609999418258667, 0.018300000578165054, 0.019899999722838402, -0.08980000019073486, 0.026900000870227814, 0.011099999770522118, -0.011599999852478504, 0.03400000184774399, 0.07800000160932541, -0.019899999722838402, 0.00279999990016222, -0.09000000357627869, -0.050200000405311584, -0.053599998354911804, -0.014499999582767487, 0.020400000736117363, 0.00559999980032444, 0.03909999877214432, -0.11110000312328339, 0.04039999842643738, 0.10090000182390213, -0.06340000033378601, -0.013799999840557575, -0.13349999487400055, 0.02290000021457672, -0.014700000174343586, -0.0008999999845400453, 0.04340000078082085, 0.042100001126527786, 0.04089999943971634, 0.07580000162124634, -0.07400000095367432, 0.03400000184774399, 0.10339999943971634, -0.01850000023841858, 0.02850000001490116, 0.0071000000461936, -0.12759999930858612, 0.05270000174641609, 0.0005000000237487257, -0.09470000118017197, -0.008200000040233135, -0.03830000013113022, 0.033399999141693115, 0.03970000147819519, -0.11230000108480453, -0.05000000074505806, 0.010499999858438969, 0.09830000251531601, -0.036400001496076584, 0.055799998342990875, 0.023600000888109207, 0.049800001084804535, -0.024700000882148743, -0.0026000000070780516, 0.07720000296831131, -0.1103999987244606, 0.08389999717473984, 0.006099999882280827, -0.005200000014156103, -0.04439999908208847, 0.20999999344348907, 0.02539999969303608, -0.09269999712705612, -0.020600000396370888, 0.0689999982714653, 0.023499999195337296, 0.1266999989748001, -0.01979999989271164, 0.09080000221729279, 0.05950000137090683, -0.050200000405311584, 0.11490000039339066, 0.07199999690055847, -0.0284000001847744, 0.14740000665187836, 0.0348999984562397, 0.033900000154972076, -0.05130000039935112, 0.012500000186264515, -0.007000000216066837], [-0.011300000362098217, -0.12160000205039978, 0.05130000039935112, 0.010300000198185444, 0.02500000037252903, -0.0066999997943639755, 0.0066999997943639755, -0.0681999996304512, -0.07320000231266022, -0.1306000053882599, 0.08669999986886978, -0.00800000037997961, -0.06710000336170197, -0.06030000001192093, -0.09539999812841415, -0.02329999953508377, 0.01899999938905239, 0.05889999866485596, 0.03720000013709068, -0.021400000900030136, -0.05730000138282776, -0.05420000106096268, 0.08529999852180481, 0.06970000267028809, 0.03519999980926514, -0.005900000222027302, 0.006599999964237213, -0.04410000145435333, -0.0031999999191612005, 0.011900000274181366, -0.05959999933838844, 0.020999999716877937, -0.022099999710917473, 0.01119999960064888, -0.01119999960064888, -0.05380000174045563, -0.015599999576807022, 0.07739999890327454, 0.01600000075995922, -0.053599998354911804, -0.060499999672174454, -0.06620000302791595, -0.02449999935925007, 0.10790000110864639, -0.0649000033736229, -0.03370000049471855, 0.009499999694526196, 0.03680000081658363, 0.010099999606609344, 0.06930000334978104, 0.020099999383091927, -0.02669999934732914, -0.04670000076293945, 0.007699999958276749, -0.12160000205039978, -0.02370000071823597, -0.0026000000070780516, -0.07819999754428864, 0.06669999659061432, 0.06539999693632126, -0.1023000031709671, 0.06560000032186508, -0.0340999998152256, -0.04800000041723251, -0.016599999740719795, 0.06350000202655792, 0.09749999642372131, 0.12300000339746475, -0.012799999676644802, -0.02810000069439411, -0.00430000014603138, 0.0885000005364418, 0.10580000281333923, 0.03680000081658363, -0.03269999846816063, -0.019999999552965164, 0.15940000116825104, 0.10790000110864639, 0.003599999938160181, -0.026599999517202377, -0.027300000190734863, -0.04830000177025795, 0.03700000047683716, 0.003100000089034438, -0.10589999705553055, 0.03840000182390213, 0.007799999788403511, 0.09629999846220016, 0.05270000174641609, 0.003700000001117587, 0.03590000048279762, -0.12800000607967377, -0.054099999368190765, -0.08910000324249268, -0.004000000189989805, -0.048900000751018524, 0.09669999778270721, -0.11289999634027481, -0.0989999994635582, -0.07959999889135361, 0.053199999034404755, -0.013299999758601189, 0.0010000000474974513, -0.041099999099969864, -0.0406000018119812, 0.01640000008046627, -0.027400000020861626, -0.001500000013038516, 0.04280000180006027, 0.07500000298023224, -0.047200001776218414, -0.01730000041425228, -0.06210000067949295, -0.05260000005364418, -0.039799999445676804, 0.034299999475479126, 0.07440000027418137, 0.02199999988079071, -0.09929999709129333, 0.05959999933838844, 0.012199999764561653, -0.0019000000320374966, -0.051600001752376556, -0.01140000019222498, -0.023600000888109207, -0.05000000074505806, -0.027000000700354576, -0.015599999576807022, 0.047600001096725464, -0.016599999740719795, -0.044199999421834946, 0.030700000002980232, 0.05209999904036522, -0.10729999840259552, 0.00279999990016222, -0.09300000220537186, -0.010499999858438969, 0.02930000051856041, 0.011800000444054604, -0.01720000058412552, 0.01489999983459711, 0.09719999879598618, -0.024000000208616257, 0.025299999862909317, 0.05040000006556511, 0.03959999978542328, 0.0035000001080334187, -0.012500000186264515, -0.04360000044107437, -0.05180000141263008, 0.002199999988079071, 0.05130000039935112, 0.08079999685287476, -0.10459999740123749, -0.01209999993443489, 0.006500000134110451, 0.003700000001117587, 0.06369999796152115, -0.016100000590085983, -0.08340000361204147, 0.012000000104308128, 0.01889999955892563, -0.0794999971985817, -0.11429999768733978, -0.08340000361204147, 0.12250000238418579, 0.028300000354647636, -0.0013000000035390258, 0.05810000002384186, 0.09319999814033508, -0.016599999740719795, -0.010200000368058681, -0.010300000198185444, 0.01720000058412552, 0.04749999940395355, -0.051500000059604645, -0.03590000048279762, 0.11900000274181366, -0.12849999964237213, -0.03830000013113022, 0.0885000005364418, 0.04490000009536743, -0.05959999933838844, -0.0551999993622303, 0.023800000548362732, -0.08139999955892563, 0.028200000524520874, -0.006599999964237213, 0.06239999830722809, 0.019099999219179153, -0.09920000284910202, -0.15760000050067902, -0.024399999529123306, 0.04479999840259552, 0.019500000402331352, -0.0568000003695488, -0.03959999978542328, 0.05649999901652336, -0.01489999983459711, -0.023099999874830246, 0.027799999341368675, 0.10970000177621841, 0.12559999525547028, -0.07769999653100967, -0.06620000302791595, 0.06360000371932983, 0.06620000302791595, 0.020999999716877937, 0.09309999644756317, 0.03150000050663948, -0.09160000085830688, -0.00860000029206276, 0.0017999999690800905, 0.042899999767541885, 0.0010000000474974513, 0.03669999912381172, 0.009399999864399433, -0.149399995803833, -0.10849999636411667, 0.10520000010728836, -0.08079999685287476, -0.05849999934434891, -0.0142000000923872, -0.028300000354647636, 0.026799999177455902, 0.11580000072717667, 0.017799999564886093, -0.07020000368356705, -0.15309999883174896, 0.027799999341368675, 0.08129999786615372, 0.10279999673366547, 0.03689999878406525, -0.03629999980330467, -0.01679999940097332, 0.021700000390410423, 0.05350000038743019, -0.12080000340938568, 0.0689999982714653, -0.008100000210106373, 0.014000000432133675, -0.061900001019239426, -0.010200000368058681, 0.0925000011920929, 0.09969999641180038, 0.0478999987244606, -0.03449999913573265, 0.02879999950528145, 0.06679999828338623, 0.049800001084804535, -0.08110000193119049, 0.036400001496076584, -0.013500000350177288, -0.05979999899864197, -0.04670000076293945, 0.030799999833106995, 0.04309999942779541, -0.011599999852478504, 0.10980000346899033, 0.09319999814033508, -0.13600000739097595, 0.006099999882280827, -0.0010000000474974513, -0.0892999991774559], [0.042500000447034836, 0.05389999970793724, -0.016300000250339508, 0.027499999850988388, -0.07079999893903732, 0.0982000008225441, -0.06480000168085098, -0.06069999933242798, -0.07259999960660934, -0.027899999171495438, 0.01080000028014183, 0.05130000039935112, 0.06639999896287918, -0.02669999934732914, 0.08229999989271164, -0.11050000041723251, 0.11479999870061874, -0.0917000025510788, -0.02850000001490116, 0.010900000110268593, 0.10050000250339508, -0.01640000008046627, 0.04230000078678131, -0.08940000087022781, 0.1014999970793724, 0.09549999982118607, -0.016599999740719795, -0.05990000069141388, -0.07599999755620956, -0.03790000081062317, 0.049400001764297485, -0.08070000261068344, -0.027499999850988388, -0.12389999628067017, -0.009200000204145908, 0.09549999982118607, -0.014700000174343586, 0.07000000029802322, 0.03849999979138374, -0.12700000405311584, -0.004800000227987766, -0.07540000230073929, -0.016200000420212746, 0.021700000390410423, 0.06989999860525131, -0.041600000113248825, -0.02199999988079071, -0.051600001752376556, 0.015699999406933784, 0.08070000261068344, 0.043800000101327896, -0.049300000071525574, 0.020500000566244125, -0.052000001072883606, -0.03420000150799751, 0.08969999849796295, -0.007000000216066837, 0.029899999499320984, -0.125, -0.04780000075697899, -0.023099999874830246, -0.021700000390410423, 0.03220000118017197, 0.1477999985218048, -0.06719999760389328, -0.03060000017285347, 0.027499999850988388, -0.03400000184774399, 0.05779999867081642, -0.02449999935925007, -0.010099999606609344, 0.03929999843239784, 0.09059999883174896, -0.01940000057220459, -0.0017999999690800905, 0.06019999831914902, -0.011800000444054604, -0.04280000180006027, -0.02290000021457672, -0.0551999993622303, 0.041999999433755875, -0.03790000081062317, -0.05730000138282776, 0.012900000438094139, 0.08550000190734863, -0.02199999988079071, -0.0026000000070780516, 0.03200000151991844, 0.07280000299215317, 0.018400000408291817, -0.035100001841783524, -0.03420000150799751, -0.07000000029802322, 0.008799999952316284, -0.03590000048279762, 0.03240000084042549, 0.006899999920278788, -0.0430000014603138, -0.0632999986410141, 0.021299999207258224, 0.03579999879002571, 0.031199999153614044, 0.04699999839067459, -0.009200000204145908, 0.06270000338554382, 0.13040000200271606, 0.03189999982714653, 0.11180000007152557, 0.025200000032782555, -0.024299999698996544, 0.038100000470876694, 0.060499999672174454, -0.04019999876618385, 0.07280000299215317, -0.050599999725818634, 0.06689999997615814, 0.010400000028312206, -0.03819999843835831, -0.017100000753998756, 0.12700000405311584, 0.036400001496076584, 0.10329999774694443, 0.04839999973773956, -0.04349999874830246, -0.012400000356137753, 0.11829999834299088, -0.08380000293254852, -0.026499999687075615, 0.1177000030875206, 0.014800000004470348, 0.0778999999165535, 0.0066999997943639755, 0.15620000660419464, -0.050700001418590546, 0.014100000262260437, 0.039400000125169754, 0.032600000500679016, -0.02590000070631504, 0.14249999821186066, 0.02319999970495701, 0.0210999995470047, -0.08460000157356262, -0.004100000020116568, 0.06430000066757202, 0.08299999684095383, -0.020999999716877937, -0.005799999926239252, -0.026499999687075615, 0.026900000870227814, -0.027799999341368675, 0.04650000110268593, -0.12039999663829803, 0.0632999986410141, -0.029200000688433647, -0.0560000017285347, 0.03929999843239784, -0.05739999935030937, 0.05090000107884407, -0.02810000069439411, 0.19269999861717224, -0.04050000011920929, 0.12080000340938568, -0.010300000198185444, -0.057500001043081284, 0.015399999916553497, 0.06539999693632126, 0.06530000269412994, 0.013700000010430813, -0.06260000169277191, -0.1858000010251999, 0.01889999955892563, 0.00989999994635582, -0.023000000044703484, -0.07580000162124634, -0.01679999940097332, 0.0142000000923872, 0.048700001090765, 0.026599999517202377, -0.004800000227987766, 0.018799999728798866, 0.05480000004172325, -0.0320000015</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>[[[-0.011500000022351742, 0.005900000222027302, 0.028999999165534973, 0.04899999871850014, 0.05130000039935112, -0.10289999842643738, -0.009800000116229057, 0.0003000000142492354, -0.04740000143647194, -0.0038999998942017555, -0.020099999383091927, 0.01360000018030405, 0.050700001418590546, 0.06650000065565109, -0.0471000000834465, -0.023099999874830246, -0.012799999676644802, 0.04969999939203262, -0.01679999940097332, -0.032999999821186066, -0.013500000350177288, -0.09189999848604202, -0.0544000007212162, 0.029999999329447746, -0.019200000911951065, -0.020099999383091927, 0.0746999979019165, -0.03189999982714653, 0.12269999831914902, -0.012500000186264515, -0.015599999576807022, 0.0333000011742115, 0.000699999975040555, 0.013899999670684338, 0.005200000014156103, -0.040300000458955765, 0.002899999963119626, -0.00800000037997961, -0.03519999980926514, -0.02160000056028366, 0.011500000022351742, -0.09189999848604202, -0.04149999842047691, -0.07590000331401825, 0.010400000028312206, -0.0035000001080334187, 0.007899999618530273, -0.0203000009059906, -0.12680000066757202, 0.005900000222027302, -0.007199999876320362, 0.018799999728798866, 0.03359999880194664, -0.01600000075995922, 0.032099999487400055, 0.01269999984651804, 0.04919999837875366, -0.039400000125169754, 0.029400000348687172, 0.016699999570846558, 0.006800000090152025, -0.015599999576807022, 0.03350000083446503, -0.07599999755620956, -0.06549999862909317, -0.023600000888109207, -0.01979999989271164, -0.006000000052154064, 0.019999999552965164, -0.027300000190734863, 0.08009999990463257, 0.0032999999821186066, -0.05790000036358833, 0.023099999874830246, 0.029200000688433647, 0.021700000390410423, 0.027400000020861626, 0.013199999928474426, -0.025699999183416367, 0.029400000348687172, 0.0357000008225441, 0.026000000536441803, 0.011900000274181366, -0.014999999664723873, 0.0949999988079071, -0.0020000000949949026, 0.01360000018030405, 0.0024999999441206455, -0.06610000133514404, 0.0478999987244606, 0.05620000138878822, -0.019700000062584877, -0.03840000182390213, -0.08100000023841858, 0.04270000010728836, 0.007199999876320362, 0.09160000085830688, -0.013299999758601189, 0.006200000178068876, 0.0608999989926815, 0.04010000079870224, 0.05950000137090683, 0.0024999999441206455, 0.020500000566244125, -0.005900000222027302, -0.024800000712275505, -0.00570000009611249, 0.02329999953508377, -0.04490000009536743, 0.025499999523162842, -0.005200000014156103, 0.008999999612569809, 9.999999747378752e-05, 0.03150000050663948, 0.021900000050663948, 0.024800000712275505, -0.027799999341368675, -0.061000000685453415, 0.05079999938607216, 0.09319999814033508, -0.006000000052154064, 0.051100000739097595, -0.033399999141693115, -0.025499999523162842, -0.04039999842643738, -0.09489999711513519, -0.032099999487400055, -0.018799999728798866, 0.056299999356269836, 0.004399999976158142, 0.024700000882148743, -0.025599999353289604, 0.00430000014603138, -0.0406000018119812, -0.029899999499320984, -0.0689999982714653, 0.05270000174641609, 0.02070000022649765, -0.010300000198185444, 0.005799999926239252, -0.024800000712275505, -0.09239999949932098, -0.0348999984562397, 0.035599999129772186, 0.0007999999797903001, -0.032600000500679016, -0.026100000366568565, -0.05310000106692314, 0.03579999879002571, 0.0729999989271164, 0.00019999999494757503, 0.04270000010728836, -0.05689999833703041, 0.007300000172108412, -0.032499998807907104, -0.0608999989926815, 0.03220000118017197, -0.024700000882148743, 0.009600000455975533, -0.04320000112056732, -0.02019999921321869, -0.04879999905824661, 0.057999998331069946, -0.011599999852478504, -0.023900000378489494, -0.006399999838322401, 0.07159999758005142, 0.014299999922513962, -0.03060000017285347, -0.0210999995470047, 0.017500000074505806, 0.04859999939799309, -0.04019999876618385, -0.006300000008195639, -0.03840000182390213, 0.03060000017285347, -0.08240000158548355, -0.09260000288486481, -0.017100000753998756, -0.03790000081062317, 0.016699999570846558, -0.056699998676776886, -0.06080000102519989, -0.07000000029802322, -0.024800000712275505, 0.03269999846816063, 0.022299999371170998, -0.05079999938607216, 0.03709999844431877, 0.031599998474121094, 0.009499999694526196, 0.027300000190734863, 0.02500000037252903, 0.03539999946951866, -0.06109999865293503, 0.026499999687075615, -0.003000000026077032, -0.03220000118017197, -0.01759999990463257, -0.04019999876618385, -0.05490000173449516, -0.020600000396370888, 0.01979999989271164, 0.013500000350177288, 0.01899999938905239, 0.05719999969005585, -0.009800000116229057, 0.060100000351667404, -0.012900000438094139, 0.03629999980330467, -0.023600000888109207, -0.04349999874830246, 0.015300000086426735, 0.052400000393390656, -0.0003000000142492354, -0.035999998450279236, -0.03180000185966492, 0.10090000182390213, 0.012500000186264515, -0.01140000019222498, -0.00430000014603138, -0.03759999945759773, -0.05180000141263008, 0.01899999938905239, -0.03790000081062317, -0.04280000180006027, -0.026599999517202377, 0.03840000182390213, -0.020500000566244125, 0.002400000113993883, -0.03280000016093254, 0.038600001484155655, 0.02710000053048134, -0.01810000091791153, 0.03460000082850456, 0.0357000008225441, -0.06340000033378601, 0.03999999910593033, 0.0658000037074089, 0.06669999659061432, -0.03290000185370445, 0.06210000067949295, 0.020800000056624413, -0.035100001841783524, 0.06480000168085098, -0.012600000016391277, -0.06719999760389328, -0.0617000013589859, 0.019300000742077827, -0.06030000001192093, 0.0010999999940395355, 0.04690000042319298, 0.0032999999821186066, 0.02710000053048134, 0.02199999988079071, -0.0333000011742115, 0.007300000172108412, -0.007799999788403511, 0.006599999964237213, -0.008100000210106373, 0.025599999353289604, -0.006300000008195639, -0.08160000294446945, -9.999999747378752e-05], [0.032999999821186066, -0.01860000006854534, 0.03220000118017197, -0.01600000075995922, -0.022099999710917473, 0.04410000145435333, 0.009600000455975533, -0.04859999939799309, 0.03370000049471855, -0.021700000390410423, 0.019700000062584877, 0.023099999874830246, -0.033399999141693115, -0.07649999856948853, -0.03240000084042549, 0.0272000003606081, -0.01600000075995922, -0.009600000455975533, 0.03280000016093254, 0.09510000050067902, 0.013500000350177288, 0.07829999923706055, -0.02930000051856041, -0.05050000175833702, 0.039799999445676804, -0.0632999986410141, -0.04740000143647194, 0.03539999946951866, 0.006800000090152025, 0.018400000408291817, 0.03519999980926514, 0.00279999990016222, -0.004100000020116568, 0.00559999980032444, -0.049400001764297485, 0.017799999564886093, -0.017400000244379044, 0.01269999984651804, 0.05999999865889549, 0.05290000140666962, 0.0008999999845400453, 0.03920000046491623, 0.07970000058412552, 0.03240000084042549, -0.03020000085234642, -0.02199999988079071, -0.015599999576807022, 0.03440000116825104, 0.1071000024676323, -0.019999999552965164, -0.013799999840557575, 0.045899998396635056, -0.0006000000284984708, 0.02250000089406967, 0.012400000356137753, -0.06599999964237213, 0.01600000075995922, -0.019999999552965164, -0.024900000542402267, -0.027000000700354576, 0.04019999876618385, 0.01860000006854534, 0.04879999905824661, 0.003800000064074993, 0.04089999943971634, 0.05290000140666962, -0.013500000350177288, 0.013700000010430813, -0.021800000220537186, -0.023000000044703484, -0.02239999920129776, -0.025299999862909317, -0.014000000432133675, -0.09740000218153, -0.024700000882148743, 0.0034000000450760126, -0.04859999939799309, -0.026499999687075615, 0.020099999383091927, -0.00559999980032444, 0.041200000792741776, -0.05590000003576279, 0.0032999999821186066, 0.009100000374019146, -0.04529999941587448, -0.029899999499320984, -0.03480000048875809, 0.03680000081658363, -0.016100000590085983, -0.014000000432133675, -0.07360000163316727, 0.08169999718666077, 0.025299999862909317, 0.07530000060796738, -0.06430000066757202, -0.01759999990463257, -0.05920000001788139, 0.03970000147819519, -0.11100000143051147, -0.09640000015497208, -0.024299999698996544, -0.029200000688433647, -0.012900000438094139, -0.014000000432133675, 0.04050000011920929, 0.03880000114440918, 0.020899999886751175, -0.04010000079870224, 0.012000000104308128, 0.01489999983459711, -0.05119999870657921, -0.030899999663233757, 0.05939999967813492, -0.10580000281333923, -0.01759999990463257, -0.005900000222027302, -0.051500000059604645, 0.07180000096559525, -0.0, -0.08020000159740448, 0.03400000184774399, -0.0013000000035390258, 0.056299999356269836, -0.0019000000320374966, -0.008500000461935997, 0.11249999701976776, 0.08380000293254852, -0.02669999934732914, 0.014800000004470348, -0.02630000002682209, 0.015200000256299973, 0.021199999377131462, 0.020800000056624413, 0.07620000094175339, 0.024800000712275505, 0.07980000227689743, -0.007799999788403511, 0.009200000204145908, 0.05739999935030937, 0.016200000420212746, -0.02019999921321869, 0.04619999974966049, -0.014000000432133675, 0.017899999395012856, 0.04800000041723251, 0.013299999758601189, -0.014499999582767487, 0.06800000369548798, 0.09619999676942825, -0.05990000069141388, 0.04399999976158142, -0.0940999984741211, 0.08250000327825546, 0.02239999920129776, -0.013399999588727951, 0.01360000018030405, -0.0674000009894371, 0.03799999877810478, 0.05079999938607216, 0.04360000044107437, 0.03739999979734421, 0.004999999888241291, -0.042100001126527786, -0.030700000002980232, 0.0560000017285347, 0.024000000208616257, -0.006399999838322401, -0.018300000578165054, 0.06120000034570694, -0.0071000000461936, -0.08370000123977661, -0.019099999219179153, -0.010099999606609344, 0.006200000178068876, 0.042399998754262924, 0.012199999764561653, 0.061900001019239426, 0.023099999874830246, -0.0005000000237487257, 0.03709999844431877, -0.025599999353289604, 0.04410000145435333, 0.05550000071525574, 0.002300000051036477, -0.02319999970495701, -0.05730000138282776, -0.04820000007748604, -0.025599999353289604, -0.07450000196695328, 0.006399999838322401, -0.021299999207258224, 0.028300000354647636, 0.01489999983459711, -0.06440000236034393, 0.006200000178068876, -0.008799999952316284, -0.002899999963119626, 0.009600000455975533, 0.03009999915957451, 0.05530000105500221, 0.029500000178813934, -0.026900000870227814, -0.028999999165534973, 0.00570000009611249, 0.046300001442432404, -0.041099999099969864, 0.06920000165700912, -0.08739999681711197, 0.042100001126527786, -0.10100000351667404, 0.04039999842643738, -0.006200000178068876, -0.016300000250339508, 0.02979999966919422, -0.01769999973475933, 0.03779999911785126, -0.002899999963119626, -0.07739999890327454, 0.020400000736117363, 0.000699999975040555, 0.06920000165700912, 0.02850000001490116, -0.008100000210106373, -0.05119999870657921, 0.006500000134110451, 0.04879999905824661, -0.0038999998942017555, 0.024800000712275505, 0.0032999999821186066, -0.03150000050663948, 0.08799999952316284, -0.02979999966919422, -0.021400000900030136, -0.008700000122189522, 0.09220000356435776, -0.05009999871253967, 0.05869999900460243, -0.02630000002682209, -0.0007999999797903001, -0.030899999663233757, 0.025699999183416367, -0.011800000444054604, -0.04390000179409981, 0.02889999933540821, 0.012600000016391277, -0.01730000041425228, 0.0885000005364418, 0.01489999983459711, -0.0632999986410141, 0.04529999941587448, -0.03799999877810478, -0.03739999979734421, 0.05469999834895134, -0.016599999740719795, 0.011500000022351742, 0.030700000002980232, 0.005499999970197678, 0.051500000059604645, 0.03819999843835831, -0.020099999383091927, -0.011699999682605267, -0.006300000008195639, 0.02160000056028366, -0.025100000202655792]], [[-0.00139999995008111, 0.027400000020861626, 0.027899999171495438, 0.004000000189989805, 0.031599998474121094, 0.06030000001192093, -0.03180000185966492, 0.014999999664723873, 0.012299999594688416, 0.03240000084042549, 0.05719999969005585, 0.06920000165700912, 0.11810000240802765, -0.032099999487400055, -0.06840000301599503, -0.00279999990016222, -0.02969999983906746, -0.07680000364780426, 0.0066999997943639755, -0.07649999856948853, -0.03020000085234642, 0.02979999966919422, 0.07729999721050262, -0.06120000034570694, 0.03999999910593033, 0.1624000072479248, -0.0364999994635582, 0.041099999099969864, -0.051100000739097595, -0.01489999983459711, 0.03970000147819519, 0.10509999841451645, -0.04800000041723251, -0.004999999888241291, -0.08829999715089798, -0.04410000145435333, 0.0877000018954277, -0.016499999910593033, 0.1265999972820282, 0.008500000461935997, -0.007899999618530273, 0.052799999713897705, 0.03420000150799751, -0.015599999576807022, -0.005799999926239252, 0.06199999898672104, -0.05420000106096268, 0.013100000098347664, -0.08630000054836273, -0.09019999951124191, -0.020099999383091927, 0.012500000186264515, -0.047200001776218414, -0.003800000064074993, 0.04179999977350235, -0.02410000003874302, 0.014399999752640724, 0.02879999950528145, 0.023099999874830246, -0.06759999692440033, -0.05909999832510948, 0.06599999964237213, -0.020999999716877937, -0.11729999631643295, -0.007300000172108412, 0.04740000143647194, 0.14329999685287476, 0.03370000049471855, -0.05420000106096268, -0.04569999873638153, -0.1193000003695488, 0.06360000371932983, 0.0010000000474974513, -0.020899999886751175, 0.024700000882148743, 0.03539999946951866, -0.06700000166893005, -0.017799999564886093, -0.11749999970197678, -0.020899999886751175, 0.15150000154972076, 0.021199999377131462, 0.10450000315904617, 0.01769999973475933, 0.07769999653100967, 0.08860000222921371, 0.09769999980926514, 0.10379999876022339, -0.12039999663829803, -0.042399998754262924, -0.06679999828338623, -0.021299999207258224, -0.024800000712275505, -0.053199999034404755, -0.017400000244379044, -0.053199999034404755, -0.08049999922513962, 0.04919999837875366, 0.05400000140070915, -0.018799999728798866, -0.0071000000461936, 0.045099999755620956, 0.03460000082850456, -0.07750000059604645, 0.09749999642372131, -0.01899999938905239, 0.00800000037997961, -0.1632000058889389, 0.15780000388622284, 0.03629999980330467, 0.014999999664723873, 0.020400000736117363, 0.05009999871253967, -0.14270000159740448, 0.02239999920129776, -0.07180000096559525, -0.12890000641345978, -0.07930000126361847, -0.012900000438094139, 0.007799999788403511, 0.06750000268220901, 0.0007999999797903001, 0.01140000019222498, 0.0026000000070780516, 0.030899999663233757, -0.03689999878406525, -0.09589999914169312, 0.0357000008225441, -0.0035000001080334187, -0.07100000232458115, 0.026000000536441803, -0.025800000876188278, 0.0632999986410141, 0.11230000108480453, 0.01769999973475933, 0.02160000056028366, 0.030899999663233757, 0.11760000139474869, 0.035100001841783524, -0.0006000000284984708, -0.03229999914765358, 0.013500000350177288, -0.015200000256299973, 0.043800000101327896, 0.08879999816417694, 0.0494999997317791, -0.008500000461935997, 0.029600000008940697, 0.007300000172108412, 0.0020000000949949026, -0.006300000008195639, 0.012900000438094139, 0.0044999998062849045, -0.023099999874830246, -0.05849999934434891, 0.02590000070631504, 0.0010000000474974513, -0.028999999165534973, -0.036400001496076584, -0.02290000021457672, -0.01850000023841858, 0.026499999687075615, 0.06210000067949295, -0.010900000110268593, -0.031199999153614044, -0.03020000085234642, 0.011099999770522118, -0.03739999979734421, -0.16840000450611115, 0.10090000182390213, 0.06419999897480011, -0.03319999948143959, -0.0560000017285347, -0.0006000000284984708, -0.06669999659061432, -0.022600000724196434, 0.10459999740123749, -0.06840000301599503, -0.07530000060796738, -0.018799999728798866, 0.03189999982714653, 0.09880000352859497, 0.0, 0.04340000078082085, -0.04019999876618385, -0.09989999979734421, -0.007799999788403511, -0.03139999881386757, -0.047600001096725464, 0.04639999940991402, -0.08160000294446945, -0.06830000132322311, 0.02070000022649765, -0.03880000114440918, 0.02319999970495701, -0.07450000196695328, 0.1428000032901764, 0.07649999856948853, 0.00279999990016222, 0.003100000089034438, 0.10029999911785126, -0.07419999688863754, -0.12070000171661377, 0.02500000037252903, 0.0471000000834465, -0.10239999741315842, 0.036400001496076584, 0.0017000000225380063, 0.0868000015616417, 0.03700000047683716, 0.010700000450015068, 0.07680000364780426, -0.11840000003576279, -0.07199999690055847, 0.025100000202655792, 0.032600000500679016, -0.08089999854564667, 0.03970000147819519, -0.009100000374019146, -0.19329999387264252, -0.011699999682605267, 0.007899999618530273, 0.0142000000923872, 0.01140000019222498, 0.1145000010728836, -0.13950000703334808, 0.011300000362098217, -0.08089999854564667, 0.01360000018030405, -0.0031999999191612005, -0.11429999768733978, 0.031300000846385956, -0.030300000682473183, 0.011900000274181366, -0.14890000224113464, 0.030899999663233757, 0.029600000008940697, 0.06830000132322311, 0.025499999523162842, 0.06830000132322311, -0.05009999871253967, 0.0340999998152256, -0.030799999833106995, 0.11140000075101852, -0.06019999831914902, 0.010700000450015068, 0.09030000120401382, -0.05790000036358833, -0.061400000005960464, 0.03849999979138374, -0.04039999842643738, -0.017999999225139618, -0.061799999326467514, 0.04639999940991402, -0.02459999918937683, 0.0731000006198883, 0.027400000020861626, -0.10909999907016754, -0.02979999966919422, 0.0071000000461936, -0.09589999914169312, -0.0026000000070780516, -0.06889999657869339, -0.11620000004768372], [0.016899999231100082, 0.050999999046325684, -0.005499999970197678, -0.12160000205039978, -0.052400000393390656, -0.03319999948143959, 0.01640000008046627, -0.037300001829862595, 0.031199999153614044, 0.009200000204145908, -0.011699999682605267, -0.04729999974370003, 0.06949999928474426, -0.043699998408555984, 0.03009999915957451, 0.05790000036358833, 0.05480000004172325, -0.07989999651908875, 0.08709999918937683, -0.031599998474121094, 0.02239999920129776, 0.06549999862909317, 0.04450000077486038, -0.00930000003427267, 0.029899999499320984, 0.01209999993443489, 0.022199999541044235, -0.11110000312328339, 0.13019999861717224, -0.032999999821186066, 0.009100000374019146, 0.011699999682605267, 0.004800000227987766, 0.050999999046325684, 0.05660000070929527, -0.0044999998062849045, 0.08799999952316284, 0.10429999977350235, -0.05950000137090683, 0.07479999959468842, 0.03530000150203705, 0.12700000405311584, 0.05130000039935112, 0.009100000374019146, 0.0778999999165535, -0.006200000178068876, -0.00800000037997961, -0.048500001430511475, -0.07660000026226044, -0.060600001364946365, -0.0494999997317791, 0.013500000350177288, 0.002899999963119626, -0.10239999741315842, 0.058800000697374344, -0.1941000074148178, -0.04569999873638153, -0.11550000309944153, 0.06610000133514404, -0.06469999998807907, 0.0723000019788742, 0.02969999983906746, -0.03460000082850456, 0.03060000017285347, 0.04820000007748604, -0.05009999871253967, -0.04479999840259552, -0.0957999974489212, 0.030500000342726707, 0.02810000069439411, 0.03290000185370445, 0.04809999838471413, 0.06949999928474426, -0.06629999727010727, 0.1340000033378601, -0.09309999644756317, 0.003599999938160181, 0.030500000342726707, 0.02419999986886978, 0.07670000195503235, -0.021900000050663948, -0.006399999838322401, -0.04740000143647194, 0.05820000171661377, 0.0340999998152256, -0.0551999993622303, 0.10729999840259552, 0.1476999968290329, -0.04529999941587448, -0.0551999993622303, 0.04410000145435333, -0.0008999999845400453, -0.02250000089406967, 0.06650000065565109, -0.1347000002861023, -0.08820000290870667, -0.035999998450279236, 0.040800001472234726, 0.0786999985575676, -0.03880000114440918, -0.009800000116229057, -0.03880000114440918, -0.0026000000070780516, 0.021900000050663948, 0.10180000215768814, 0.07880000025033951, -0.061500001698732376, 0.018699999898672104, 9.999999747378752e-05, -0.02410000003874302, 0.06960000097751617, -0.06030000001192093, 0.08889999985694885, -0.10350000113248825, -0.06279999762773514, 0.015599999576807022, -0.0031999999191612005, -0.02070000022649765, -0.11309999972581863, -0.05909999832510948, -0.04969999939203262, 0.033399999141693115, -0.04320000112056732, 0.014700000174343586, 0.007699999958276749, 0.07689999788999557, 0.08889999985694885, 0.10300000011920929, 0.11990000307559967, 0.03779999911785126, 0.06970000267028809, 0.02979999966919422, 0.021400000900030136, -0.0357000008225441, 0.019300000742077827, -0.06610000133514404, -0.06859999895095825, -0.02969999983906746, 0.04399999976158142, -0.09000000357627869, -0.14970000088214874, 0.01940000057220459, 0.11050000041723251, 0.058400001376867294, 0.003100000089034438, -0.13189999759197235, -0.041999999433755875, 0.029200000688433647, 0.029400000348687172, -0.0066999997943639755, -0.06109999865293503, 0.07289999723434448, 0.08309999853372574, 0.043299999088048935, -0.01549999974668026, 0.016200000420212746, -0.021299999207258224, -0.011500000022351742, 0.0007999999797903001, 0.08399999886751175, 0.07209999859333038, -0.014600000344216824, -0.013899999670684338, 0.007300000172108412, -0.08860000222921371, 0.045099999755620956, -0.03739999979734421, -0.03819999843835831, 0.025699999183416367, -0.010300000198185444, 0.03840000182390213, 0.07119999825954437, 0.01600000075995922, -0.02979999966919422, 0.00279999990016222, 0.05249999836087227, 0.036400001496076584, -0.023900000378489494, -0.027400000020861626, 0.04050000011920929, 0.065700002014637, -0.0731000006198883, -0.07980000227689743, -0.1543000042438507, 0.02669999934732914, 0.01209999993443489, -0.07559999823570251, 0.04259999841451645, 0.02419999986886978, -0.023099999874830246, 0.05139999836683273, 0.08820000290870667, -0.008899999782443047, 0.01860000006854534, -0.06870000064373016, -0.054099999368190765, -0.07460000365972519, -0.0027000000700354576, 0.01600000075995922, -0.021900000050663948, 0.04820000007748604, -0.11779999732971191, 0.03009999915957451, 0.10760000348091125, -0.06080000102519989, -0.03220000118017197, -0.1589999943971634, 0.04410000145435333, -0.04830000177025795, 0.017899999395012856, 0.020500000566244125, 0.041999999433755875, 0.059700001031160355, 0.10329999774694443, -0.08489999920129776, 0.02319999970495701, 0.11670000106096268, -0.019500000402331352, 0.04479999840259552, 0.024800000712275505, -0.13750000298023224, 0.07569999992847443, -0.007199999876320362, -0.06289999932050705, -0.023499999195337296, -0.017500000074505806, 0.04659999907016754, 0.03840000182390213, -0.09989999979734421, -0.031199999153614044, -0.007499999832361937, 0.10750000178813934, -0.03840000182390213, 0.04190000146627426, 0.05220000073313713, 0.049300000071525574, -0.042399998754262924, 0.0035000001080334187, 0.05609999969601631, -0.12319999933242798, 0.09470000118017197, -0.013100000098347664, 0.029600000008940697, -0.04800000041723251, 0.19789999723434448, 0.021400000900030136, -0.1225999966263771, -0.01080000028014183, 0.07930000126361847, 0.04800000041723251, 0.11739999800920486, -0.023000000044703484, 0.0738999992609024, 0.05040000006556511, -0.03460000082850456, 0.10490000247955322, 0.08240000158548355, -0.010300000198185444, 0.15610000491142273, 0.05079999938607216, 0.005900000222027302, -0.060499999672174454, -9.999999747378752e-05, -0.015699999406933784], [-0.02419999986886978, -0.10369999706745148, 0.04230000078678131, 0.031300000846385956, 0.025200000032782555, 0.006300000008195639, -0.007600000128149986, -0.09149999916553497, -0.08910000324249268, -0.12049999833106995, 0.10750000178813934, 0.0010000000474974513, -0.04800000041723251, -0.04089999943971634, -0.08980000019073486, -0.009800000116229057, -0.0032999999821186066, 0.03830000013113022, 0.023499999195337296, -0.05209999904036522, -0.07249999791383743, -0.043800000101327896, 0.10050000250339508, 0.08110000193119049, 0.013199999928474426, 0.00559999980032444, 0.011599999852478504, -0.027699999511241913, -0.03139999881386757, -0.006200000178068876, -0.0737999975681305, 0.03920000046491623, -0.03530000150203705, 0.023099999874830246, -0.029100000858306885, -0.05130000039935112, -9.999999747378752e-05, 0.1023000031709671, 0.026499999687075615, -0.03500000014901161, -0.052799999713897705, -0.08060000091791153, 0.006000000052154064, 0.08269999921321869, -0.09589999914169312, -0.02160000056028366, 0.011500000022351742, 0.027400000020861626, -0.013100000098347664, 0.05299999937415123, 0.03359999880194664, -0.0017000000225380063, -0.06599999964237213, 0.02319999970495701, -0.11949999630451202, -0.019099999219179153, 0.016200000420212746, -0.1005999967455864, 0.04780000075697899, 0.07999999821186066, -0.07909999787807465, 0.043699998408555984, -0.051500000059604645, -0.0689999982714653, -0.01979999989271164, 0.06040000170469284, 0.11760000139474869, 0.10740000009536743, 0.01489999983459711, -0.014299999922513962, -0.008100000210106373, 0.10180000215768814, 0.12290000170469284, 0.018200000748038292, -0.045499999076128006, -0.01140000019222498, 0.17000000178813934, 0.07850000262260437, 0.03590000048279762, -0.019500000402331352, 0.002199999988079071, -0.041099999099969864, 0.011300000362098217, -0.018400000408291817, -0.10050000250339508, 0.044599998742341995, -0.00039999998989515007, 0.12139999866485596, 0.06350000202655792, 0.0038999998942017555, 0.01600000075995922, -0.1477999985218048, -0.0649000033736229, -0.06499999761581421, 0.018300000578165054, -0.03229999914765358, 0.11240000277757645, -0.10859999805688858, -0.07150000333786011, -0.0689999982714653, 0.07410000264644623, -0.03269999846816063, -0.000699999975040555, -0.06109999865293503, -0.05869999900460243, 0.0066999997943639755, -0.03840000182390213, -0.019200000911951065, 0.05999999865889549, 0.04179999977350235, -0.02979999966919422, -0.037300001829862595, -0.03929999843239784, -0.041999999433755875, -0.048900000751018524, 0.06270000338554382, 0.08330000191926956, 0.02449999935925007, -0.07840000092983246, 0.042500000447034836, 0.02710000053048134, -0.03629999980330467, -0.032099999487400055, 0.032499998807907104, -0.00930000003427267, -0.06870000064373016, -0.035100001841783524, 0.021700000390410423, 0.012199999764561653, -0.059700001031160355, -0.0714000016450882, 0.01979999989271164, 0.04149999842047691, -0.09229999780654907, 0.021800000220537186, -0.07689999788999557, 0.02979999966919422, 0.05770000070333481, -0.0012000000569969416, 0.005400000140070915, 0.0010999999940395355, 0.11559999734163284, -0.038600001484155655, -0.0017000000225380063, 0.061799999326467514, 0.06599999964237213, 0.03280000016093254, -0.019500000402331352, -0.052400000393390656, -0.03519999980926514, 0.02879999950528145, 0.061400000005960464, 0.11620000004768372, -0.1096000000834465, -0.02590000070631504, -0.007300000172108412, 0.01759999990463257, 0.057100001722574234, -0.025800000876188278, -0.0860000029206276, 0.0272000003606081, 0.01209999993443489, -0.06419999897480011, -0.12600000202655792, -0.054099999368190765, 0.10019999742507935, -0.0017999999690800905, -0.013700000010430813, 0.04190000146627426, 0.08229999989271164, -0.05420000106096268, -0.0031999999191612005, -0.03099999949336052, 0.03480000048875809, 0.05609999969601631, -0.030500000342726707, -0.061500001698732376, 0.10480000078678131, -0.14569999277591705, -0.0544000007212162, 0.09570000320672989, 0.06599999964237213, -0.041099999099969864, -0.03720000013709068, 0.010499999858438969, -0.07989999651908875, 0.014399999752640724, -0.016300000250339508, 0.05000000074505806, 0.030899999663233757, -0.11800000071525574, -0.16699999570846558, -0.03779999911785126, 0.0284000001847744, -0.004600000102072954, -0.04910000041127205, -0.020999999716877937, 0.04190000146627426, -0.012299999594688416, -0.0017999999690800905, 0.021199999377131462, 0.0997999981045723, 0.13289999961853027, -0.09290000051259995, -0.0729999989271164, 0.06920000165700912, 0.0934000015258789, 0.0017999999690800905, 0.1298999935388565, 0.014700000174343586, -0.06880000233650208, -0.006099999882280827, -0.014700000174343586, 0.014999999664723873, 0.030700000002980232, 0.053300000727176666, -0.005200000014156103, -0.13379999995231628, -0.12530000507831573, 0.10429999977350235, -0.06430000066757202, -0.0714000016450882, -0.00419999985024333, -0.06109999865293503, 0.042500000447034836, 0.0949999988079071, 0.00279999990016222, -0.07540000230073929, -0.17720000445842743, 0.035599999129772186, 0.09539999812841415, 0.11159999668598175, 0.0414000004529953, -0.022700000554323196, -0.0502999983727932, 0.023099999874830246, 0.06629999727010727, -0.11819999665021896, 0.08980000019073486, 0.0019000000320374966, -0.00039999998989515007, -0.044599998742341995, -0.02319999970495701, 0.09870000183582306, 0.11320000141859055, 0.05469999834895134, -0.0015999999595806003, 0.01759999990463257, 0.056699998676776886, 0.031700000166893005, -0.0697999969124794, 0.04659999907016754, 0.003599999938160181, -0.04619999974966049, -0.04439999908208847, 0.0421999990940094, 0.03150000050663948, -0.03200000151991844, 0.10040000081062317, 0.08299999684095383, -0.1151999980211258, 0.01850000023841858, 0.013500000350177288, -0.07509999722242355], [0.024800000712275505, 0.04600000008940697, -0.02879999950528145, 0.028999999165534973, -0.05719999969005585, 0.10199999809265137, -0.05689999833703041, -0.03370000049471855, -0.07109999656677246, -0.045499999076128006, -0.009200000204145908, 0.06430000066757202, 0.0697999969124794, -0.033900000154972076, 0.07970000058412552, -0.13819999992847443, 0.08030000329017639, -0.08320000022649765, -0.024700000882148743, -0.005900000222027302, 0.09700000286102295, -0.03229999914765358, 0.039799999445676804, -0.10559999942779541, 0.13650000095367432, 0.0966000035405159, 0.0, -0.07109999656677246, -0.08250000327825546, -0.024900000542402267, 0.03880000114440918, -0.06369999796152115, -0.011099999770522118, -0.1315000057220459, 0.002199999988079071, 0.10000000149011612, -0.020099999383091927, 0.06199999898672104, 0.04540000110864639, -0.11490000039339066, 0.009800000116229057, -0.05590000003576279, -0.03009999915957451, 0.020400000736117363, 0.08739999681711197, -0.06440000236034393, -0.019300000742077827, -0.03739999979734421, -0.0032999999821186066, 0.08780000358819962, 0.04230000078678131, -0.023600000888109207, 0.04019999876618385, -0.054099999368190765, -0.013500000350177288, 0.09929999709129333, 0.007300000172108412, -0.0008999999845400453, -0.10140000283718109, -0.042500000447034836, -0.012299999594688416, -0.020600000396370888, 0.02250000089406967, 0.163100004196167, -0.05889999866485596, -0.03280000016093254, 0.06129999831318855, -0.018699999898672104, 0.046300001442432404, -0.01590000092983246, -0.021299999207258224, 0.032499998807907104, 0.09920000284910202, -0.0020000000949949026, 0.03020000085234642, 0.07620000094175339, -0.01080000028014183, -0.03620000183582306, -0.041099999099969864, -0.05480000004172325, 0.025499999523162842, -0.05169999971985817, -0.04309999942779541, 0.0038999998942017555, 0.0877000018954277, 0.016599999740719795, 0.02969999983906746, 0.03200000151991844, 0.06260000169277191, -0.003700000001117587, -0.04149999842047691, -0.03420000150799751, -0.04529999941587448, -0.010200000368058681, -0.010499999858438969, 0.0430000014603138, 0.005499999970197678, -0.03999999910593033, -0.04690000042319298, 0.013700000010430813, 0.05959999933838844, 0.0348999984562397, 0.04039999842643738, -0.006000000052154064, 0.05909999832510948, 0.14020000398159027, 0.03779999911785126, 0.08739999681711197, 0.03889999911189079, -0.021400000900030136, 0.041999999433755875, 0.05420000106096268, -0.0333000011742115, 0.06780000030994415, -0.03970000147819519, 0.050700001418590546, 0.020600000396370888, -0.04919999837875366, 0.025299999862909317, 0.13609999418258667, 0.03790000081062317, 0.09399999678134918, 0.01549999974668026, -0.03579999879002571, 0.000699999975040555, 0.11569999903440475, -0.08980000019073486, -0.02759999968111515, 0.11150000244379044, 0.013199999928474426, 0.09179999679327011, -0.0010999999940395355, 0.13429999351501465, -0.0729999989271164, 0.01940000057220459, 0.0364999994635582, 0.007300000172108412, -0.03550000116229057, 0.133200004696846, 0.003000000026077032, 0.03689999878406525, -0.09130000323057175, -0.006500000134110451, 0.05550000071525574, 0.07090000063180923, -0.014700000174343586, 0.00039999998989515007, -0.003700000001117587, 0.032499998807907104, -0.03280000016093254, 0.026100000366568565, -0.10350000113248825, 0.07999999821186066, -0.016699999570846558, -0.07590000331401825, 0.045099999755620956, -0.07490000128746033, 0.060600001364946365, -0.037700001150369644, 0.21439999341964722, -0.02160000056028366, 0.11320000141859055, -0.014000000432133675, -0.04659999907016754, 0.003000000026077032, 0.03970000147819519, 0.05620000138878822, 0.027300000190734863, -0.040300000458955765, -0.1923000067472458, 0.018799999728798866, 0.028699999675154686, -0.03680000081658363, -0.060600001364946365, 0.01510000042617321, -0.004800000227987766, 0.065700002014637, 0.03500000014901161, 0.013700000010430813, 0.</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>[-32.191869669982324]</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>[7.57659617850917]</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>[-35.4916720944625]</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>[8.331168101476413]</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>[-0.12339649208249903]</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>[0.36766486078020355]</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>[-29.265616790241246]</t>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>[6.952589437715945]</t>
+        </is>
+      </c>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>[-33.530321856352394]</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr">
+        <is>
+          <t>[8.189246598455767]</t>
+        </is>
+      </c>
+      <c r="O33" t="inlineStr">
+        <is>
+          <t>[-12.464418159979264]</t>
+        </is>
+      </c>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>[4.426393049771545]</t>
+        </is>
+      </c>
+      <c r="Q33" t="inlineStr">
+        <is>
+          <t>[-1.6020425406686836]</t>
+        </is>
+      </c>
+      <c r="R33" t="inlineStr">
+        <is>
+          <t>[0.28056713386288545]</t>
+        </is>
+      </c>
+      <c r="S33" t="inlineStr">
+        <is>
+          <t>[-2.0709802152608803]</t>
+        </is>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>[0.2587618363320274]</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>[-3.5391034679482445]</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>[0.4340432836270653]</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>[-1.832238307181656]</t>
+        </is>
+      </c>
+      <c r="X33" t="inlineStr">
+        <is>
+          <t>[0.29670705111470513]</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>[-2.440588686755394]</t>
+        </is>
+      </c>
+      <c r="Z33" t="inlineStr">
+        <is>
+          <t>[0.28313708629750983]</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>[-8.486551097984368]</t>
+        </is>
+      </c>
+      <c r="AB33" t="inlineStr">
+        <is>
+          <t>[0.8728041984656679]</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>[-12.206904907816206]</t>
+        </is>
+      </c>
+      <c r="AD33" t="inlineStr">
+        <is>
+          <t>[1.1066854258325558]</t>
+        </is>
+      </c>
+      <c r="AE33" t="inlineStr">
+        <is>
+          <t>[-11.406186366098435]</t>
+        </is>
+      </c>
+      <c r="AF33" t="inlineStr">
+        <is>
+          <t>[1.3358742546355884]</t>
+        </is>
+      </c>
+      <c r="AG33" t="inlineStr">
+        <is>
+          <t>[-17.801393106319058]</t>
+        </is>
+      </c>
+      <c r="AH33" t="inlineStr">
+        <is>
+          <t>[1.3997629356270591]</t>
+        </is>
+      </c>
+      <c r="AI33" t="inlineStr">
+        <is>
+          <t>[-12.807633432474372]</t>
+        </is>
+      </c>
+      <c r="AJ33" t="inlineStr">
+        <is>
+          <t>[1.1315201889395579]</t>
+        </is>
+      </c>
+      <c r="AK33" t="inlineStr">
+        <is>
+          <t>[-11.443369978532687]</t>
+        </is>
+      </c>
+      <c r="AL33" t="inlineStr">
+        <is>
+          <t>[1.3207725551571763]</t>
+        </is>
+      </c>
+      <c r="AM33" t="inlineStr">
+        <is>
+          <t>[-23.90167113596708]</t>
+        </is>
+      </c>
+      <c r="AN33" t="inlineStr">
+        <is>
+          <t>[1.9126288704953849]</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>model_264_128_2</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>[264, 128]</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>[[[-0.05169999971985817, 0.011599999852478504, 0.05860000103712082, 0.015599999576807022, -0.0568000003695488, 0.0071000000461936, -0.04830000177025795, 0.012000000104308128, 0.012199999764561653, 0.0006000000284984708, -0.012400000356137753, 0.032099999487400055, 0.012500000186264515, -0.06700000166893005, -9.999999747378752e-05, 0.053700000047683716, -0.13729999959468842, 0.050999999046325684, -0.026900000870227814, 0.04170000180602074, -0.0071000000461936, 0.04320000112056732, 0.0003000000142492354, 0.015699999406933784, -0.0632999986410141, 0.04490000009536743, -0.0071000000461936, 0.08869999647140503, 0.030500000342726707, -0.001500000013038516, 0.05389999970793724, -0.05169999971985817, -0.02070000022649765, 0.0020000000949949026, 0.01140000019222498, 0.009800000116229057, 0.01940000057220459, -0.03799999877810478, -0.01640000008046627, 0.01549999974668026, -0.024399999529123306, 0.09529999643564224, -0.006300000008195639, -0.015699999406933784, -0.07580000162124634, -0.03310000151395798, -0.020099999383091927, 0.032099999487400055, 0.10859999805688858, 0.09799999743700027, 0.048700001090765, -0.03189999982714653, 0.02250000089406967, -0.05260000005364418, -0.016499999910593033, 0.02250000089406967, -0.0203000009059906, -0.004600000102072954, 0.022700000554323196, -0.01769999973475933, -0.05779999867081642, 0.13570000231266022, -0.026399999856948853, -0.004699999932199717, 0.01940000057220459, -0.014499999582767487, -0.07180000096559525, 0.035599999129772186, 0.02669999934732914, 0.06109999865293503, -0.020500000566244125, 0.0340999998152256, 0.062199998646974564, 0.04610000178217888, 0.01489999983459711, -0.07909999787807465, 0.0786999985575676, 0.016200000420212746, -0.037300001829862595, 0.04659999907016754, -0.05420000106096268, 0.04479999840259552, -0.061400000005960464, -0.031300000846385956, 0.04540000110864639, 0.013299999758601189, -0.0006000000284984708, -0.011900000274181366, -0.09560000151395798, 0.02879999950528145, 0.07519999891519547, 0.05119999870657921, -0.01600000075995922, 0.012600000016391277, -0.00839999970048666, -0.05860000103712082, -0.08869999647140503, 0.04019999876618385, -0.0215000007301569, -0.013799999840557575, 0.053300000727176666, -0.08959999680519104, 0.052000001072883606, 0.007300000172108412, 0.026100000366568565, -0.016300000250339508, -0.020899999886751175, -0.03929999843239784, -0.11860000342130661, 0.030500000342726707, 0.029400000348687172, 0.039500001817941666, -0.031300000846385956, 0.027499999850988388, -0.030500000342726707, -0.05730000138282776, 0.013399999588727951, -0.0215000007301569, -0.061000000685453415, 0.016899999231100082, -0.026000000536441803, -0.03720000013709068, -0.05510000139474869, 0.015200000256299973, -0.015300000086426735, 0.0551999993622303, -0.017400000244379044, -0.033799998462200165, 0.0421999990940094, 0.009600000455975533, 0.024299999698996544, 0.07769999653100967, -0.030899999663233757, 0.01549999974668026, -0.0284000001847744, 0.08179999887943268, -0.07509999722242355, -0.07479999959468842, 0.051899999380111694, 0.04619999974966049, -0.0038999998942017555, 0.04190000146627426, -0.04690000042319298, 0.06920000165700912, -0.12280000001192093, 0.015599999576807022, 0.06719999760389328, 0.029999999329447746, 0.02850000001490116, 0.05979999899864197, -0.03370000049471855, 0.019099999219179153, 0.06639999896287918, -0.0421999990940094, -0.04450000077486038, -0.028999999165534973, -0.01119999960064888, 0.10209999978542328, 0.0414000004529953, -0.12240000069141388, -0.07519999891519547, 0.0706000030040741, 0.03319999948143959, 0.08320000022649765, 0.07699999958276749, 0.03290000185370445, -0.04969999939203262, -0.08209999650716782, 0.060499999672174454, -0.06599999964237213, 0.0010000000474974513, -0.05009999871253967, -0.028999999165534973, 0.07029999792575836, 0.0714000016450882, -0.02539999969303608, 0.05090000107884407, 0.07479999959468842, -0.035100001841783524, -0.023900000378489494, 0.007499999832361937, 0.05000000074505806, 0.09740000218153, 0.03500000014901161, 0.0017999999690800905, 0.010700000450015068, -0.039400000125169754, -0.010300000198185444, 0.04569999873638153, 0.010200000368058681, 0.027699999511241913, -0.024800000712275505, -0.03739999979734421, 0.031599998474121094, -0.04639999940991402, 0.04910000041127205, -0.07890000194311142, 0.08820000290870667, 0.01860000006854534, -0.06780000030994415, 0.01720000058412552, 0.04309999942779541, 0.008100000210106373, -0.01899999938905239, 0.0617000013589859, -0.06319999694824219, -0.040300000458955765, -0.09430000185966492, -0.030300000682473183, 0.07940000295639038, -0.017899999395012856, 0.006399999838322401, -0.016499999910593033, 0.02759999968111515, -0.014700000174343586, 0.09009999781847, 0.015300000086426735, -0.030899999663233757, 0.007799999788403511, 0.04129999876022339, -0.014000000432133675, 0.048500001430511475, 0.03669999912381172, 0.006200000178068876, 0.060600001364946365, 0.004399999976158142, 0.0625, -0.0357000008225441, 0.00860000029206276, 0.10670000314712524, -0.017799999564886093, 0.018300000578165054, -0.047600001096725464, -0.00019999999494757503, 0.02759999968111515, -0.09929999709129333, 0.09880000352859497, 0.05220000073313713, 0.005499999970197678, 0.03669999912381172, -0.031700000166893005, 0.022299999371170998, 0.04490000009536743, 0.0015999999595806003, 0.0608999989926815, 0.014399999752640724, 0.04910000041127205, 0.03579999879002571, 0.017799999564886093, -0.10750000178813934, 0.04540000110864639, 0.006800000090152025, -0.05220000073313713, -0.007600000128149986, 0.07999999821186066, 0.014399999752640724, 0.023399999365210533, -0.00139999995008111, 0.04170000180602074, -0.028699999675154686, -0.002899999963119626, 0.03139999881386757, 0.01899999938905239, -0.026000000536441803], [-0.0771000012755394, 0.08399999886751175, -0.006599999964237213, 0.018799999728798866, 0.013500000350177288, -0.05040000006556511, 0.04919999837875366, -0.10289999842643738, 0.024299999698996544, 0.07859999686479568, -0.019500000402331352, -0.012900000438094139, 0.0215000007301569, -0.07660000026226044, 0.026200000196695328, -0.007000000216066837, -0.007799999788403511, -0.08449999988079071, -0.0575999990105629, -0.01080000028014183, -0.09149999916553497, 0.013299999758601189, 0.03739999979734421, -0.04769999906420708, 0.047600001096725464, -0.017000000923871994, 0.006800000090152025, 0.027799999341368675, -0.06539999693632126, -0.07419999688863754, -0.0364999994635582, -0.03629999980330467, -0.12639999389648438, -0.033799998462200165, -0.03350000083446503, -0.0364999994635582, -0.07209999859333038, 0.020500000566244125, 0.0640999972820282, 0.04650000110268593, 0.06769999861717224, -0.13050000369548798, -0.04859999939799309, -0.04500000178813934, -0.00419999985024333, -0.10270000249147415, 0.033900000154972076, 0.026200000196695328, 0.025100000202655792, -0.05220000073313713, 0.0982000008225441, -0.006899999920278788, -0.022199999541044235, 0.012600000016391277, 0.01209999993443489, 0.05570000037550926, 0.06499999761581421, -0.007799999788403511, -0.0005000000237487257, -0.031300000846385956, -0.024000000208616257, 0.094200000166893, -0.020600000396370888, 0.03849999979138374, -0.014100000262260437, -0.05380000174045563, 0.1379999965429306, -0.005400000140070915, -0.008500000461935997, 0.02280000038444996, 0.013799999840557575, -0.0017999999690800905, -0.005900000222027302, -0.02070000022649765, -0.06889999657869339, -0.06360000371932983, 0.042899999767541885, -0.016200000420212746, -0.0215000007301569, 0.08919999748468399, 0.120899997651577, 0.027899999171495438, -0.06790000200271606, 0.004800000227987766, 0.013899999670684338, -0.008799999952316284, -0.08659999817609787, -0.05939999967813492, -0.024800000712275505, -0.045899998396635056, 0.041999999433755875, -0.013899999670684338, -0.04230000078678131, -0.025200000032782555, -0.04390000179409981, -0.04859999939799309, 0.011699999682605267, 0.06689999997615814, 0.023000000044703484, 0.003700000001117587, -0.030300000682473183, -0.05270000174641609, -0.0020000000949949026, -0.029600000008940697, -0.03709999844431877, -0.02370000071823597, 0.12370000034570694, 0.009600000455975533, -0.046799998730421066, -0.07150000333786011, 0.10029999911785126, -0.061500001698732376, 0.04650000110268593, 0.04610000178217888, -0.005400000140070915, -0.09139999747276306, 0.07169999927282333, 0.017799999564886093, 0.10869999974966049, 0.026599999517202377, 0.004600000102072954, -0.10939999669790268, 0.06289999932050705, -0.11580000072717667, 0.01269999984651804, 0.021800000220537186, 0.029600000008940697, 0.022199999541044235, 0.0430000014603138, -0.0877000018954277, 0.05339999869465828, 0.020899999886751175, 0.013700000010430813, 0.05649999901652336, 0.05649999901652336, 0.07000000029802322, 0.03009999915957451, -0.04390000179409981, 0.03370000049471855, -0.06840000301599503, -0.029999999329447746, -0.03460000082850456, -0.010999999940395355, 0.08009999990463257, -0.05559999868273735, 0.003599999938160181, 0.0860000029206276, 0.002300000051036477, 0.005200000014156103, -0.033799998462200165, -0.0649000033736229, -0.07349999994039536, 0.016899999231100082, -0.01489999983459711, -0.09749999642372131, 0.029500000178813934, 0.013899999670684338, 0.031199999153614044, 0.04340000078082085, -0.026200000196695328, -0.002300000051036477, -0.004399999976158142, -0.022700000554323196, -0.02630000002682209, 0.10459999740123749, -0.07760000228881836, -0.047600001096725464, -0.031599998474121094, 0.03620000183582306, 0.0017000000225380063, -0.008100000210106373, -0.07280000299215317, -0.006500000134110451, -0.023499999195337296, -0.03220000118017197, -0.042899999767541885, 0.048900000751018524, -0.00559999980032444, 0.016300000250339508, 0.010400000028312206, 0.028300000354647636, 0.034699998795986176, 0.003100000089034438, 0.026900000870227814, 0.0340999998152256, -0.026900000870227814, 0.024700000882148743, 0.008299999870359898, -0.09430000185966492, -0.02199999988079071, -0.025499999523162842, 0.005799999926239252, -0.026000000536441803, 0.042100001126527786, 0.028300000354647636, 0.05380000174045563, -0.06520000100135803, 0.06310000270605087, -0.002199999988079071, -0.03709999844431877, -0.016599999740719795, 0.05810000002384186, -0.006399999838322401, -0.04859999939799309, 0.01940000057220459, 0.033900000154972076, 0.007600000128149986, 0.026200000196695328, 0.02759999968111515, 0.061000000685453415, 0.07670000195503235, -0.10970000177621841, -0.025299999862909317, 0.021400000900030136, 0.03460000082850456, 0.031300000846385956, 0.04050000011920929, -0.03480000048875809, -0.1054999977350235, 0.0007999999797903001, 0.05530000105500221, 0.02280000038444996, -0.03009999915957451, 0.043800000101327896, 0.04190000146627426, 0.048500001430511475, 0.07370000332593918, -0.03200000151991844, 0.13449999690055847, 0.0210999995470047, 0.027799999341368675, -0.05119999870657921, -0.021800000220537186, 0.016899999231100082, -0.09459999948740005, 0.05119999870657921, 0.11559999734163284, -0.06679999828338623, -0.007000000216066837, 0.013899999670684338, 0.010200000368058681, 0.006599999964237213, -0.0828000009059906, -0.07079999893903732, 0.026900000870227814, -0.03739999979734421, -0.05609999969601631, 0.020800000056624413, 0.0421999990940094, -0.0982000008225441, 0.040300000458955765, 0.03020000085234642, -0.07689999788999557, -0.0551999993622303, -0.03550000116229057, -0.02419999986886978, -0.07370000332593918, -0.005799999926239252, -0.04569999873638153, -0.00989999994635582, -0.07810000330209732, 0.0052999998442828655, 0.013899999670684338, -0.041600000113248825]], [[0.10029999911785126, -0.05700000002980232, -0.006200000178068876, 0.030700000002980232, 0.04259999841451645, -0.10140000283718109, 0.026599999517202377, 0.08259999752044678, -0.02280000038444996, -0.16619999706745148, -0.0005000000237487257, -0.023499999195337296, 0.015599999576807022, 0.0333000011742115, 0.029600000008940697, 0.035999998450279236, 0.05180000141263008, -0.03909999877214432, -0.09139999747276306, 0.05920000001788139, 0.06400000303983688, -0.03920000046491623, 0.13770000636577606, 0.0333000011742115, 0.03889999911189079, 0.03189999982714653, -0.009200000204145908, -0.05350000038743019, 0.02329999953508377, 0.021700000390410423, -0.00559999980032444, -0.022099999710917473, 0.09780000150203705, -0.023900000378489494, -0.08340000361204147, -0.018400000408291817, -0.020600000396370888, 0.050999999046325684, -0.024800000712275505, -0.05660000070929527, 0.042500000447034836, 0.07720000296831131, 0.026000000536441803, 0.023099999874830246, -0.006300000008195639, -0.01759999990463257, 0.06159999966621399, 0.017899999395012856, -0.0010000000474974513, -0.012500000186264515, -0.10499999672174454, -0.03310000151395798, 0.051600001752376556, 0.04610000178217888, -0.061799999326467514, 0.08540000021457672, 0.03460000082850456, -0.13410000503063202, -0.04390000179409981, -0.0430000014603138, -0.03920000046491623, 0.016499999910593033, 0.009999999776482582, -0.007799999788403511, 0.028300000354647636, -0.04820000007748604, -0.07639999687671661, -0.012799999676644802, -0.025200000032782555, -0.02459999918937683, -0.02669999934732914, -0.07829999923706055, -0.009200000204145908, 0.02630000002682209, -0.13519999384880066, 0.06279999762773514, -0.03269999846816063, 0.13689999282360077, 0.05249999836087227, -0.0617000013589859, -0.0017999999690800905, 0.017899999395012856, 0.0017000000225380063, 0.05469999834895134, -0.04670000076293945, 0.030799999833106995, 0.12999999523162842, -0.09210000187158585, -0.08479999750852585, -0.09690000116825104, 0.07320000231266022, -0.1080000028014183, 0.0608999989926815, -0.00019999999494757503, -0.0044999998062849045, -0.039400000125169754, -0.017899999395012856, -0.048700001090765, 0.10459999740123749, -0.08129999786615372, -0.09600000083446503, 0.06710000336170197, 0.07639999687671661, -0.010599999688565731, -0.09359999746084213, 0.08730000257492065, -0.024700000882148743, 0.04439999908208847, -0.01360000018030405, -0.04439999908208847, 0.02759999968111515, -0.044599998742341995, -0.03269999846816063, -0.029500000178813934, 0.028699999675154686, 0.032099999487400055, -0.04639999940991402, -0.006500000134110451, -0.020899999886751175, -0.09019999951124191, 0.13249999284744263, 0.13779999315738678, 0.07199999690055847, -0.026900000870227814, -0.05820000171661377, -0.09700000286102295, 0.06239999830722809, -0.022600000724196434, -0.05460000038146973, -0.006099999882280827, 0.0003000000142492354, 0.05609999969601631, 0.12520000338554382, -0.009399999864399433, -0.04749999940395355, 0.0478999987244606, 0.03759999945759773, 0.0632999986410141, 0.03759999945759773, -0.005900000222027302, 0.09189999848604202, -0.047600001096725464, 0.07090000063180923, -0.025499999523162842, 0.0003000000142492354, -0.016599999740719795, -0.13189999759197235, 0.03350000083446503, -0.11779999732971191, -0.06599999964237213, -0.03269999846816063, -0.03830000013113022, -0.029200000688433647, 0.04780000075697899, 0.03150000050663948, 0.01360000018030405, -0.09390000253915787, 0.11789999902248383, 0.018799999728798866, -0.04800000041723251, 0.03920000046491623, 0.014700000174343586, -0.05700000002980232, 0.11289999634027481, 0.04740000143647194, -0.06920000165700912, 0.004100000020116568, 0.02810000069439411, -0.015799999237060547, -0.04179999977350235, 0.12639999389648438, 0.0071000000461936, -0.019099999219179153, 0.0031999999191612005, -0.014999999664723873, 0.08560000360012054, 0.04340000078082085, 0.09269999712705612, 0.07840000092983246, -0.06260000169277191, 0.039000000804662704, 0.01730000041425228, 0.004100000020116568, -0.09839999675750732, -0.07810000330209732, -0.009600000455975533, 0.16439999639987946, -0.06830000132322311, -0.01209999993443489, -0.09759999811649323, -0.04699999839067459, 0.10010000318288803, -0.08169999718666077, -0.023600000888109207, -0.06750000268220901, 0.01730000041425228, -0.003599999938160181, -0.025599999353289604, -0.022700000554323196, -0.04600000008940697, 0.02810000069439411, -0.03500000014901161, -0.020600000396370888, 0.019600000232458115, -0.16329999268054962, -0.065700002014637, -0.025800000876188278, 0.049400001764297485, 0.046300001442432404, 0.00800000037997961, -0.022099999710917473, 0.033900000154972076, 0.13840000331401825, 0.07209999859333038, -0.09520000219345093, 0.028999999165534973, 0.038600001484155655, 0.006200000178068876, -0.019999999552965164, 0.040699999779462814, -0.09589999914169312, 0.03840000182390213, 0.029400000348687172, -0.03750000149011612, -0.031700000166893005, -0.04780000075697899, 0.039900001138448715, 0.08649999648332596, 0.07240000367164612, 0.005900000222027302, -0.002199999988079071, 0.04989999905228615, -0.12549999356269836, -0.053599998354911804, -0.16619999706745148, 0.06319999694824219, 0.0071000000461936, 0.007799999788403511, -0.019700000062584877, 0.09279999881982803, 0.006500000134110451, -0.039400000125169754, 0.04529999941587448, -0.050999999046325684, 0.06920000165700912, -0.030700000002980232, -0.1460999995470047, 0.0738999992609024, -0.040699999779462814, -0.0658000037074089, 0.03530000150203705, -0.02969999983906746, 0.019700000062584877, 0.04740000143647194, 0.005100000184029341, 0.043800000101327896, -0.05000000074505806, -0.014000000432133675, -0.007600000128149986, 0.05040000006556511, 0.03779999911785126, -0.002099999925121665, -0.09910000115633011, -0.046300001442432404], [0.08860000222921371, 0.03590000048279762, -0.011900000274181366, 0.1462000012397766, 0.03240000084042549, -0.0035000001080334187, 0.09830000251531601, -0.08340000361204147, -0.11599999666213989, -0.007499999832361937, -0.004600000102072954, -0.026599999517202377, 0.12600000202655792, -0.02239999920129776, -0.030500000342726707, 0.044199999421834946, 0.04600000008940697, -0.01360000018030405, -0.05270000174641609, 0.004399999976158142, 0.010200000368058681, -0.05350000038743019, -0.1071000024676323, 0.03909999877214432, -0.011300000362098217, 0.019999999552965164, -0.04309999942779541, 0.0763000026345253, 0.017799999564886093, 0.007400000002235174, -0.030899999663233757, -0.01590000092983246, 0.01119999960064888, 0.013700000010430813, 0.04320000112056732, -0.1160999983549118, 0.09200000017881393, -0.09939999878406525, 0.049400001764297485, -0.015799999237060547, 0.05790000036358833, 0.0763000026345253, -0.06109999865293503, -0.07180000096559525, -0.044599998742341995, 0.08609999716281891, -0.1665000021457672, 0.035100001841783524, 0.008799999952316284, 0.06360000371932983, -0.00839999970048666, 0.057100001722574234, -0.04490000009536743, -0.0052999998442828655, -0.08020000159740448, 0.05849999934434891, -0.06120000034570694, -0.05270000174641609, -0.02329999953508377, 0.08169999718666077, 0.04650000110268593, -0.05700000002980232, 0.06809999793767929, -0.049800001084804535, 0.07029999792575836, 0.07109999656677246, 0.07890000194311142, 0.030899999663233757, 0.046799998730421066, 0.08100000023841858, 0.08669999986886978, -0.06030000001192093, -0.07150000333786011, -0.014299999922513962, -0.03400000184774399, -0.11240000277757645, 0.1404000073671341, 0.010200000368058681, 0.05220000073313713, 0.008299999870359898, 0.05389999970793724, -0.08820000290870667, 0.00279999990016222, 0.030899999663233757, -0.10760000348091125, -0.0722000002861023, 0.03180000185966492, 0.04659999907016754, 0.06040000170469284, 0.11330000311136246, -0.01119999960064888, 0.053199999034404755, 0.020500000566244125, 0.033399999141693115, 0.02969999983906746, -0.003000000026077032, -0.0142000000923872, 0.0625, 0.013500000350177288, -0.058800000697374344, -0.02250000089406967, 0.14190000295639038, -0.04619999974966049, 0.05050000175833702, 0.008700000122189522, -0.06310000270605087, 0.12449999898672104, 0.03099999949336052, 0.10000000149011612, -0.011900000274181366, -0.016499999910593033, 0.03550000116229057, 0.06610000133514404, -0.029500000178813934, 0.05640000104904175, -0.0763000026345253, -0.06369999796152115, 0.004699999932199717, 0.01549999974668026, 0.02199999988079071, -0.10360000282526016, -0.050599999725818634, -0.10830000042915344, -0.10040000081062317, -0.010499999858438969, -0.0010000000474974513, 0.1256999969482422, 0.008500000461935997, 0.051600001752376556, -9.999999747378752e-05, -0.002400000113993883, 0.05770000070333481, 0.04839999973773956, -0.01860000006854534, -0.043699998408555984, 0.05660000070929527, 0.08529999852180481, 0.04650000110268593, 0.11720000207424164, -0.02280000038444996, 0.17389999330043793, -0.01140000019222498, -0.023600000888109207, -0.0406000018119812, 0.012500000186264515, -0.04349999874830246, 0.032999999821186066, -0.019999999552965164, -0.013799999840557575, -0.08049999922513962, -0.057100001722574234, 0.019999999552965164, -0.07819999754428864, -0.021299999207258224, -0.04170000180602074, -0.08640000224113464, -0.06530000269412994, -0.02710000053048134, -0.050700001418590546, -0.0348999984562397, -0.038100000470876694, 0.00419999985024333, 0.05950000137090683, -0.09830000251531601, 0.05510000139474869, -0.09109999984502792, -0.04769999906420708, -0.06080000102519989, -0.0005000000237487257, 0.033399999141693115, 0.0925000011920929, 0.09880000352859497, 0.012900000438094139, -0.07129999995231628, 0.004000000189989805, 0.04280000180006027, -0.04170000180602074, 0.003000000026077032, 0.04560000076889992, 0.03909999877214432, -0.05820000171661377, -0.029200000688433647, -0.008700000122189522, 0.004999999888241291, 0.07959999889135361, 0.010900000110268593, 0.006500000134110451, -0.06909999996423721, 0.035100001841783524, 0.061400000005960464, -0.005100000184029341, 0.004699999932199717, -0.010599999688565731, -0.03229999914765358, 0.07670000195503235, 0.016100000590085983, -0.12680000066757202, -0.09260000288486481, -0.07840000092983246, 0.04560000076889992, -0.09149999916553497, -0.055399999022483826, 0.02459999918937683, -0.024800000712275505, -0.04639999940991402, -0.036400001496076584, -0.0478999987244606, -0.028999999165534973, -0.06750000268220901, -0.0746999979019165, -0.04050000011920929, -0.006399999838322401, -0.008999999612569809, -0.020500000566244125, 0.03370000049471855, 0.002199999988079071, 0.05950000137090683, 0.0034000000450760126, 0.05739999935030937, -0.006000000052154064, -0.08269999921321869, -0.014999999664723873, -0.1606999933719635, 0.0027000000700354576, 0.02810000069439411, 0.01549999974668026, -0.0812000036239624, 0.00860000029206276, -0.09910000115633011, 0.0026000000070780516, -0.027699999511241913, 0.021199999377131462, -0.027699999511241913, -0.0771000012755394, 0.026000000536441803, -0.03799999877810478, -0.006099999882280827, -0.014399999752640724, 0.094200000166893, -0.02160000056028366, -0.013000000268220901, -0.10909999907016754, 0.12710000574588776, -0.03480000048875809, 0.05480000004172325, 0.052000001072883606, 0.055399999022483826, -0.11819999665021896, -0.03359999880194664, 0.014499999582767487, 0.14970000088214874, 0.051100000739097595, -0.02290000021457672, -0.07090000063180923, 0.05640000104904175, 0.08340000361204147, -0.05119999870657921, -0.04659999907016754, 0.07490000128746033, 0.0917000025510788, -0.03669999912381172, -0.06400000303983688, -0.051500000059604645, -0.1298999935388565], [0.1316000074148178, -0.03929999843239784, -0.012799999676644802, -0.01209999993443489, 0.01720000058412552, -0.02019999921321869, -0.12389999628067017, 0.028200000524520874, -0.07660000026226044, -0.10520000010728836, -0.03739999979734421, -0.01640000008046627, 0.01640000008046627, -0.015799999237060547, -0.1770000010728836, 0.03310000151395798, 0.062199998646974564, -0.03970000147819519, 0.016300000250339508, 0.037300001829862595, 0.09139999747276306, -0.02800000086426735, -0.005200000014156103, 0.002300000051036477, -0.10050000250339508, 0.00019999999494757503, 0.042500000447034836, -0.04600000008940697, -0.011099999770522118, -0.003800000064074993, 0.07280000299215317, -0.06270000338554382, 0.065700002014637, 0.1251000016927719, 0.12280000001192093, 0.042100001126527786, -0.04039999842643738, -0.05730000138282776, 0.03539999946951866, -0.023099999874830246, -0.006000000052154064, -0.024399999529123306, 0.05510000139474869, -0.0568000003695488, 0.12139999866485596, 0.005900000222027302, 0.028699999675154686, -0.020500000566244125, 0.04019999876618385, 0.11230000108480453, -0.05860000103712082, -0.07460000365972519, 0.03460000082850456, 0.06069999933242798, 0.07289999723434448, -0.059300001710653305, 0.044599998742341995, 0.01269999984651804, -0.08500000089406967, -0.00430000014603138, 0.0026000000070780516, -0.07010000199079514, -0.07450000196695328, 0.10809999704360962, 0.06970000267028809, 0.03669999912381172, 0.019200000911951065, -0.03139999881386757, -0.007600000128149986, -0.032600000500679016, -0.005400000140070915, 0.03819999843835831, -0.003700000001117587, -0.010599999688565731, -0.017500000074505806, -0.00559999980032444, -0.018200000748038292, -0.014000000432133675, -0.10939999669790268, 0.0551999993622303, -0.03840000182390213, 0.032499998807907104, 0.0908999964594841, -0.025499999523162842, -0.07320000231266022, -0.02239999920129776, 0.08389999717473984, 0.01549999974668026, -0.02019999921321869, 0.01360000018030405, -0.08760000020265579, 0.018400000408291817, 0.04270000010728836, -0.0142000000923872, -0.026000000536441803, 0.04899999871850014, -0.07599999755620956, 0.05820000171661377, -0.002400000113993883, -0.043699998408555984, 0.01360000018030405, -0.07460000365972519, -0.1054999977350235, 0.014700000174343586, 0.05889999866485596, -0.06270000338554382, 0.01730000041425228, -0.02160000056028366, 0.04309999942779541, 0.023000000044703484, -0.08699999749660492, 0.08630000054836273, -0.11140000075101852, 0.11760000139474869, 0.010099999606609344, 0.07569999992847443, 0.07079999893903732, 0.16269999742507935, -0.01810000091791153, 0.002199999988079071, 0.09040000289678574, -0.028599999845027924, -0.06809999793767929, -0.10819999873638153, -0.028200000524520874, -0.007699999958276749, -0.09920000284910202, 0.04149999842047691, 0.03689999878406525, 0.007600000128149986, -0.07810000330209732, -0.07500000298023224, 0.012299999594688416, -0.06849999725818634, 0.00989999994635582, -0.03830000013113022, 0.07450000196695328, 0.07590000331401825, 0.004999999888241291, 0.04010000079870224, 0.031700000166893005, -0.051600001752376556, -0.027300000190734863, -0.03020000085234642, -0.010700000450015068, -0.07509999722242355, -0.07270000129938126, 0.016599999740719795, -0.011800000444054604, 0.04989999905228615, 0.027799999341368675, 0.00139999995008111, -0.11810000240802765, 0.09319999814033508, -0.008100000210106373, 0.03150000050663948, 0.020400000736117363, 0.043699998408555984, 0.01720000058412552, 0.011300000362098217, -0.120899997651577, -0.022700000554323196, 0.005799999926239252, -0.07079999893903732, -0.03420000150799751, -0.04969999939203262, -0.014600000344216824, 0.0406000018119812, -0.025100000202655792, 0.07450000196695328, -0.04170000180602074, 0.0778999999165535, -0.03830000013113022, -0.09939999878406525, -0.002199999988079071, -0.09309999644756317, 0.004399999976158142, -0.03240000084042549, -0.03180000185966492, -0.0007999999797903001, -0.03709999844431877, 0.06710000336170197, -0.04439999908208847, -0.054999999701976776, 0.12039999663829803, 0.021800000220537186, -0.053599998354911804, -0.005200000014156103, 0.10409999638795853, -0.06270000338554382, 0.017899999395012856, 0.04280000180006027, -0.09260000288486481, 0.012500000186264515, -0.14229999482631683, 0.15189999341964722, 0.051500000059604645, 0.09570000320672989, 0.014100000262260437, -0.041999999433755875, -0.054499998688697815, 0.09489999711513519, -0.04650000110268593, -0.003700000001117587, 0.03550000116229057, 0.08879999816417694, -0.04479999840259552, 0.02290000021457672, -0.05180000141263008, -0.006599999964237213, -0.04179999977350235, -0.037300001829862595, -0.028999999165534973, 0.09260000288486481, 0.008500000461935997, -0.03840000182390213, 0.060100000351667404, -0.05400000140070915, -0.029600000008940697, 0.0406000018119812, 0.019099999219179153, -0.02969999983906746, -0.05790000036358833, -0.007799999788403511, -0.08269999921321869, 0.01899999938905239, 0.18459999561309814, -0.07020000368356705, 0.08579999953508377, 0.03539999946951866, 0.009100000374019146, -0.01640000008046627, -0.12470000237226486, -0.01730000041425228, -0.010300000198185444, -0.025299999862909317, 0.023800000548362732, -0.08079999685287476, -0.0357000008225441, -0.16329999268054962, 0.028300000354647636, 0.11349999904632568, -0.06300000101327896, -0.055799998342990875, 0.016599999740719795, 0.011599999852478504, 0.031099999323487282, 0.014600000344216824, -0.06270000338554382, -0.004600000102072954, -0.0681999996304512, 0.007600000128149986, 0.015599999576807022, 0.03579999879002571, 0.045899998396635056, 0.07729999721050262, 0.022199999541044235, -0.03060000017285347, 0.18549999594688416, -0.016599999740719795, -0.061500001698732376, 0.11159999668598175, -0.04580000042915344, -0.08619999885559082], [-0.1251000016927719, 0.15160000324249268, -0.0414000004529953, 0.010700000450015068, -0.006599999964237213, -0.043299999088048935, 0.07519999891519547, -0.032099999487400055, 0.07450000196695328, -0.09759999811649323, -0.030899999663233757, 0.014800000004470348, 0.014800000004470348, -0.000699999975040555, -0.0892999991774559, -0.019300000742077827, 0.007499999832361937, -0.07209999859333038, -0.05009999871253967, 0.004399999976158142, -0.07440000027418137, 0.05090000107884407, -0.0044999998062849045, -0.03420000150799751, 0.04529999941587448, -0.023099999874830246, 0.09430000185966492, -0.012900000438094139, 0.01489999983459711, 0.007499999832361937, -0.15369999408721924, 0.015399999916553497, 0.010499999858438969, -0.010200000368058681, 0.06440000236034393, 0.018400000408291817, -0.04039999842643738, -0.08139999955892563, 0.04340000078082085, -0.05299999937415123, -0.06419999897480011, -0.04320000112056732, 0.0026000000070780516, -0.013899999670684338, 0.008299999870359898, 0.051899999380111694, 0.016699999570846558, 0.028300000354647636, -0.03849999979138374, 0.06030000001192093, 0.10239999741315842, -0.06109999865293503, -0.031700000166893005, 0.03680000081658363, -0.008100000210106373, -0.04439999908208847, 0.02199999988079071, 0.07029999792575836, 0.03180000185966492, 0.02930000051856041, 0.034699998795986176, 0.053199999034404755, -0.05979999899864197, -0.04349999874830246, -0.13490000367164612, -0.024900000542402267, 0.1143999993801117, -0.03449999913573265, -0.03889999911189079, -0.0003000000142492354, 0.03819999843835831, -0.11379999667406082, -0.061500001698732376, -0.10100000351667404, 0.04540000110864639, 0.15139999985694885, 0.09000000357627869, 0.010900000110268593, 0.05119999870657921, 0.029200000688433647, -0.014000000432133675, -0.06589999794960022, -0.016899999231100082, 0.013899999670684338, -0.05869999900460243, -0.03269999846816063, 0.003100000089034438, -0.07840000092983246, -0.0017000000225380063, 0.020600000396370888, 0.0997999981045723, 0.01679999940097332, 0.05260000005364418, 0.1031000018119812, -0.010700000450015068, -0.1014999970793724, -0.08799999952316284, 0.05460000038146973, 0.03779999911785126, -0.027499999850988388, 0.04430000111460686, -0.04820000007748604, -0.00279999990016222, 0.06650000065565109, 0.11620000004768372, -0.04969999939203262, 0.08420000225305557, -0.0681999996304512, 0.005900000222027302, -0.034299999475479126, 0.0008999999845400453, -0.017000000923871994, -0.10790000110864639, -0.00930000003427267, -0.007699999958276749, -0.04259999841451645, 0.12800000607967377, 0.09510000050067902, -0.0035000001080334187, 0.05689999833703041, 0.11339999735355377, 0.016300000250339508, 0.02969999983906746, 0.0052999998442828655, -0.012299999594688416, -0.11710000038146973, 0.04529999941587448, 0.0006000000284984708, 0.019300000742077827, -0.012400000356137753, -0.06400000303983688, 0.008100000210106373, -0.0071000000461936, -0.09279999881982803, -0.04780000075697899, -0.0210999995470047, -0.06319999694824219, 0.062300000339746475, 0.052400000393390656, -0.0908999964594841, 0.09939999878406525, 0.03700000047683716, 0.10270000249147415, -0.07829999923706055, -0.00800000037997961, 0.0031999999191612005, -0.04399999976158142, -0.0771000012755394, 0.03959999978542328, 0.03550000116229057, -0.15449999272823334, 0.18050000071525574, -0.004900000058114529, 0.01360000018030405, -0.08900000154972076, 0.1274999976158142, 0.015300000086426735, 0.027799999341368675, 0.1467999964952469, 0.009999999776482582, 0.07519999891519547, 0.06679999828338623, 0.00930000003427267, -0.007600000128149986, 0.05169999971985817, 0.06469999998807907, 0.02070000022649765, 0.0015999999595806003, -0.0024999999441206455, -0.051899999380111694, 0.06499999761581421, -0.1615000069141388, -0.08250000327825546, 0.038600001484155655, -0.12790000438690186, -0.002300000051036477, 0.06319999694824219, 0.015799999237060547, -0.05380000174045563, -0.</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>[[[-0.0017999999690800905, -0.04670000076293945, 0.008100000210106373, -0.027300000190734863, -0.049300000071525574, -0.0019000000320374966, -0.07069999724626541, 0.07819999754428864, -0.01940000057220459, -0.05909999832510948, 0.020999999716877937, 0.006599999964237213, -0.02500000037252903, -0.0006000000284984708, -0.027400000020861626, 0.04919999837875366, -0.09139999747276306, 0.06390000134706497, 0.017400000244379044, 0.015799999237060547, 0.030799999833106995, -0.0071000000461936, -0.039400000125169754, 0.06729999929666519, -0.08330000191926956, 0.02410000003874302, -0.022199999541044235, 0.023900000378489494, 0.08540000021457672, 0.04910000041127205, 0.05590000003576279, 0.0026000000070780516, 0.05909999832510948, 0.03720000013709068, 0.028300000354647636, 0.03269999846816063, 0.07419999688863754, -0.053599998354911804, -0.06350000202655792, -0.03139999881386757, -0.06859999895095825, 0.13109999895095825, 0.01730000041425228, 0.02500000037252903, -0.04749999940395355, 0.007499999832361937, -0.023499999195337296, -0.03350000083446503, 0.03880000114440918, 0.08380000293254852, -0.018699999898672104, -0.00860000029206276, 0.05050000175833702, -0.019300000742077827, -0.05770000070333481, -0.045099999755620956, -0.03400000184774399, -0.023499999195337296, -0.0020000000949949026, -0.008299999870359898, 0.0052999998442828655, 0.08320000022649765, 0.03819999843835831, -0.04960000142455101, 0.00989999994635582, 0.014700000174343586, -0.10859999805688858, 0.0052999998442828655, 0.021199999377131462, 0.004100000020116568, -0.06949999928474426, 0.020099999383091927, 0.032999999821186066, 0.04800000041723251, 0.07999999821186066, -0.0071000000461936, 0.007799999788403511, 0.03500000014901161, -0.017799999564886093, -0.02160000056028366, -0.10849999636411667, -0.011900000274181366, -0.023099999874830246, -0.007799999788403511, -0.0010000000474974513, -0.01850000023841858, 0.06430000066757202, 0.03799999877810478, -0.049300000071525574, 0.0828000009059906, 0.008899999782443047, 0.031300000846385956, 0.0421999990940094, 0.024900000542402267, 0.031300000846385956, 0.014600000344216824, -0.03920000046491623, -0.010499999858438969, -0.0575999990105629, -0.01600000075995922, 0.03400000184774399, -0.0010000000474974513, -0.005100000184029341, 0.04340000078082085, 0.019899999722838402, 0.01899999938905239, -0.06080000102519989, -0.0024999999441206455, -0.05660000070929527, 0.06880000233650208, -0.009800000116229057, 0.05640000104904175, -0.06560000032186508, -0.02459999918937683, -0.012000000104308128, -0.012000000104308128, -0.05169999971985817, -0.01850000023841858, -0.12630000710487366, -0.016300000250339508, 0.0013000000035390258, 0.005200000014156103, -0.08139999955892563, 0.06030000001192093, -0.06210000067949295, 0.006200000178068876, -0.017000000923871994, -0.05400000140070915, -0.00430000014603138, 0.060600001364946365, -0.016699999570846558, 0.03610000014305115, -0.023600000888109207, -0.01810000091791153, -0.07890000194311142, 0.013700000010430813, -0.06080000102519989, -0.014800000004470348, -0.002300000051036477, 0.0494999997317791, 0.01549999974668026, 0.05570000037550926, -0.00139999995008111, -0.0005000000237487257, -0.04859999939799309, 0.03840000182390213, -0.02539999969303608, 0.012299999594688416, 0.01269999984651804, 0.036400001496076584, 0.03240000084042549, 0.05999999865889549, 0.00419999985024333, 0.0034000000450760126, 0.015799999237060547, -0.017400000244379044, 0.007600000128149986, 0.06159999966621399, -0.0203000009059906, -0.03830000013113022, -0.025499999523162842, 0.037700001150369644, -0.0034000000450760126, 0.07729999721050262, -0.006800000090152025, 0.07699999958276749, 0.01759999990463257, -0.005499999970197678, -0.009200000204145908, -0.02239999920129776, -0.020400000736117363, 0.016100000590085983, 0.002300000051036477, 0.0625, 0.04780000075697899, 0.008500000461935997, 0.012500000186264515, 0.0142000000923872, -0.05979999899864197, 0.0071000000461936, -0.019700000062584877, 0.00430000014603138, 0.05290000140666962, -0.026100000366568565, -0.025499999523162842, 0.016499999910593033, -0.04190000146627426, -0.04600000008940697, 0.09780000150203705, 0.018300000578165054, 0.0026000000070780516, -0.019999999552965164, -0.0012000000569969416, -0.02250000089406967, -0.07609999924898148, 0.00139999995008111, -0.01119999960064888, 0.01640000008046627, -0.010599999688565731, -0.024299999698996544, 0.03009999915957451, -0.01489999983459711, 0.04360000044107437, 0.01510000042617321, 0.013799999840557575, -0.05810000002384186, -0.025299999862909317, -0.05990000069141388, -0.0681999996304512, 0.011099999770522118, -0.07500000298023224, 0.08089999854564667, 0.008200000040233135, 0.0008999999845400453, -0.040699999779462814, 0.021800000220537186, -0.03519999980926514, -0.004000000189989805, 0.07699999958276749, 0.028599999845027924, -0.04349999874830246, -0.004999999888241291, 0.02070000022649765, -0.0494999997317791, 0.003100000089034438, -0.025800000876188278, 0.033399999141693115, 0.004100000020116568, -0.03739999979734421, 0.0575999990105629, -0.031599998474121094, 0.056699998676776886, -0.017799999564886093, -0.017799999564886093, 0.09149999916553497, -0.04490000009536743, 0.01119999960064888, 0.09059999883174896, 0.018799999728798866, 0.0, -0.007400000002235174, -0.01510000042617321, 0.09749999642372131, 0.04610000178217888, 0.0272000003606081, 0.04580000042915344, 0.06440000236034393, -0.01810000091791153, -0.01640000008046627, -0.04919999837875366, 0.022299999371170998, -0.027899999171495438, 0.0272000003606081, 0.0203000009059906, 0.05310000106692314, 0.026399999856948853, 0.06629999727010727, 0.012600000016391277, 0.02850000001490116, -0.011300000362098217, 0.05739999935030937, 0.016699999570846558, -0.0012000000569969416, 0.013299999758601189], [-0.02800000086426735, 0.04699999839067459, -0.07159999758005142, 0.017100000753998756, 0.0471000000834465, -0.05420000106096268, 0.06369999796152115, -0.05220000073313713, -0.015300000086426735, 0.031199999153614044, 0.016200000420212746, -0.060499999672174454, -0.01860000006854534, -0.017999999225139618, -0.003700000001117587, -0.004800000227987766, 0.04969999939203262, -0.10100000351667404, -0.019700000062584877, -0.04270000010728836, -0.06289999932050705, -0.03359999880194664, -0.005200000014156103, 0.003100000089034438, 0.03189999982714653, -0.050599999725818634, -0.015200000256299973, -0.03869999945163727, -0.06849999725818634, -0.032999999821186066, -0.06340000033378601, 0.016300000250339508, -0.05609999969601631, 0.002199999988079071, -0.012199999764561653, -0.028599999845027924, -0.026000000536441803, 0.007600000128149986, 0.051100000739097595, 0.0071000000461936, 0.030400000512599945, -0.1216999962925911, -0.03830000013113022, -0.0024999999441206455, 0.0502999983727932, -0.07599999755620956, 0.0071000000461936, -0.028699999675154686, -0.05220000073313713, -0.0885000005364418, 0.038100000470876694, 0.028999999165534973, 0.00570000009611249, 0.06129999831318855, -0.004800000227987766, 0.0006000000284984708, 0.06340000033378601, -0.025800000876188278, -0.023399999365210533, -0.02250000089406967, 0.05209999904036522, 0.04320000112056732, 0.01979999989271164, -0.012799999676644802, -0.04050000011920929, -0.0348999984562397, 0.1256999969482422, -0.043299999088048935, -0.016200000420212746, -0.03970000147819519, -0.0007999999797903001, -0.024900000542402267, -0.05389999970793724, -0.03790000081062317, -0.017100000753998756, 0.0044999998062849045, -0.025800000876188278, -0.032600000500679016, 0.014700000174343586, 0.024000000208616257, 0.08330000191926956, -0.027400000020861626, -0.02319999970495701, 0.030500000342726707, -0.00430000014603138, -0.03849999979138374, -0.028300000354647636, -0.016899999231100082, 0.02459999918937683, -0.052400000393390656, -0.025299999862909317, -0.05290000140666962, 0.012500000186264515, -0.018799999728798866, -0.004800000227987766, 0.0210999995470047, 0.06210000067949295, 0.014700000174343586, 0.025100000202655792, 0.0032999999821186066, -0.061000000685453415, 0.05139999836683273, -0.05810000002384186, -0.0003000000142492354, -0.037700001150369644, 0.039000000804662704, 0.09220000356435776, 0.04769999906420708, 0.019700000062584877, -0.040300000458955765, 0.08219999819993973, -0.06759999692440033, 0.02419999986886978, -0.00570000009611249, 0.016499999910593033, -0.04619999974966049, 0.013799999840557575, 0.029400000348687172, 0.06639999896287918, -0.015699999406933784, 0.04729999974370003, -0.06780000030994415, 0.058400001376867294, -0.08749999850988388, 0.007199999876320362, -0.03290000185370445, 0.042899999767541885, 0.010700000450015068, -0.00430000014603138, -0.051600001752376556, -0.022600000724196434, -0.024800000712275505, 0.009800000116229057, -0.009100000374019146, 0.02199999988079071, 0.006000000052154064, 0.0478999987244606, 0.012600000016391277, -0.01269999984651804, -0.08330000191926956, 0.01759999990463257, -0.018300000578165054, 0.032999999821186066, 0.03319999948143959, 0.016499999910593033, 0.008899999782443047, -0.007899999618530273, -0.022099999710917473, -0.015200000256299973, -0.06939999759197235, 0.002300000051036477, -0.04540000110864639, -0.051500000059604645, 0.0364999994635582, -0.02019999921321869, 0.05640000104904175, 0.03240000084042549, -0.018799999728798866, -0.02070000022649765, 0.05719999969005585, 0.054099999368190765, -0.07289999723434448, -0.06859999895095825, -0.04610000178217888, 0.0272000003606081, -0.043800000101327896, 0.02160000056028366, 0.04659999907016754, -0.024900000542402267, 0.05530000105500221, -0.019200000911951065, -0.039400000125169754, 0.029200000688433647, -0.041600000113248825, -0.07270000129938126, -0.005100000184029341, 0.015699999406933784, -0.07079999893903732, 0.007000000216066837, 0.054999999701976776, 0.0027000000700354576, -0.01269999984651804, -0.04390000179409981, -0.03579999879002571, 0.024000000208616257, -0.019300000742077827, 0.03020000085234642, 0.008500000461935997, -0.06239999830722809, -0.01940000057220459, -0.04360000044107437, 0.008100000210106373, 0.010300000198185444, -0.003800000064074993, 0.006200000178068876, 0.011300000362098217, -0.007600000128149986, -0.010499999858438969, -0.025699999183416367, 0.03880000114440918, 0.0010999999940395355, 0.009100000374019146, 0.012600000016391277, 0.00559999980032444, -0.02160000056028366, 0.04650000110268593, 0.04560000076889992, 0.08070000261068344, 0.006599999964237213, -0.007699999958276749, 0.03150000050663948, -0.06729999929666519, -0.006599999964237213, 0.004699999932199717, 0.0333000011742115, -0.03720000013709068, -0.006200000178068876, -0.003599999938160181, -0.07339999824762344, -0.033799998462200165, 0.0333000011742115, -0.0357000008225441, -0.055399999022483826, 0.003100000089034438, -0.01209999993443489, 0.022700000554323196, 0.04439999908208847, 0.01119999960064888, 0.09539999812841415, -0.04039999842643738, 0.019500000402331352, 0.008700000122189522, 0.016499999910593033, -0.006399999838322401, -0.03970000147819519, 0.12380000203847885, 0.031300000846385956, -0.05299999937415123, 0.002300000051036477, -0.029899999499320984, 0.04639999940991402, -0.03319999948143959, -0.04659999907016754, -0.02850000001490116, -0.027300000190734863, -0.003700000001117587, -0.06960000097751617, -0.04749999940395355, 0.016200000420212746, -0.011900000274181366, 0.014000000432133675, 0.0015999999595806003, -0.027400000020861626, -0.013199999928474426, -0.06509999930858612, -0.009700000286102295, -0.03420000150799751, 0.016899999231100082, -0.08169999718666077, 0.01209999993443489, -0.013000000268220901, -0.009399999864399433, -0.043699998408555984, -0.009499999694526196]], [[0.08619999885559082, -0.06889999657869339, 0.04479999840259552, 0.050999999046325684, 0.04439999908208847, -0.06639999896287918, 0.07419999688863754, 0.11649999767541885, -0.02290000021457672, -0.15060000121593475, -0.04809999838471413, 0.020899999886751175, 0.013799999840557575, 0.0044999998062849045, 0.06319999694824219, 0.014100000262260437, 0.02669999934732914, -0.003599999938160181, -0.10419999808073044, 0.10679999738931656, 0.05889999866485596, -0.0032999999821186066, 0.16220000386238098, 0.011300000362098217, 0.08609999716281891, 0.03009999915957451, 0.03920000046491623, 0.007899999618530273, 0.06549999862909317, 0.0015999999595806003, -0.010499999858438969, -0.03750000149011612, 0.11810000240802765, -0.01679999940097332, -0.03909999877214432, -0.04309999942779541, -0.049800001084804535, 0.030700000002980232, -0.04540000110864639, -0.057999998331069946, 0.014600000344216824, 0.057999998331069946, 0.05389999970793724, 0.04320000112056732, 0.014600000344216824, -0.03669999912381172, 0.05660000070929527, 0.007000000216066837, 0.04740000143647194, -0.014499999582767487, -0.06689999997615814, -0.06629999727010727, 0.02669999934732914, 0.002199999988079071, -0.024700000882148743, 0.1274999976158142, -0.007300000172108412, -0.10830000042915344, -0.027499999850988388, -0.0560000017285347, -0.0892999991774559, 0.039900001138448715, -0.008299999870359898, 0.04839999973773956, 0.04010000079870224, -0.008899999782443047, -0.08510000258684158, 0.011599999852478504, -0.011599999852478504, 0.025100000202655792, 0.043800000101327896, -0.10480000078678131, 0.047200001776218414, 0.0044999998062849045, -0.1395999938249588, 0.030700000002980232, 0.013199999928474426, 0.13259999454021454, 0.05050000175833702, -0.11420000344514847, 0.05000000074505806, 0.042100001126527786, -0.03460000082850456, 0.0608999989926815, -0.03350000083446503, 0.03099999949336052, 0.13750000298023224, -0.10239999741315842, -0.09830000251531601, -0.07649999856948853, 0.09749999642372131, -0.09380000084638596, 0.01590000092983246, -0.024800000712275505, -0.045499999076128006, -0.11069999635219574, -0.06719999760389328, -0.03319999948143959, 0.12300000339746475, -0.038600001484155655, -0.06589999794960022, 0.00800000037997961, 0.07590000331401825, -0.039400000125169754, -0.0681999996304512, 0.10459999740123749, 0.002199999988079071, -0.006899999920278788, -0.01590000092983246, -0.07670000195503235, 0.0032999999821186066, -0.027400000020861626, -0.0006000000284984708, -0.00989999994635582, 0.0038999998942017555, 0.0026000000070780516, -0.004800000227987766, -0.00430000014603138, -0.010700000450015068, -0.06300000101327896, 0.1080000028014183, 0.1362999975681305, 0.09459999948740005, -0.06270000338554382, -0.04100000113248825, -0.056299999356269836, 0.05920000001788139, -0.004600000102072954, -0.005400000140070915, -0.06430000066757202, -0.032999999821186066, -0.016200000420212746, 0.11389999836683273, 0.0017999999690800905, 0.002400000113993883, 0.06440000236034393, 0.07329999655485153, 0.029600000008940697, 0.06210000067949295, -0.013899999670684338, 0.05139999836683273, -0.044199999421834946, 0.0210999995470047, 0.04100000113248825, -0.02969999983906746, -0.009800000116229057, -0.08479999750852585, 0.009499999694526196, -0.13830000162124634, -0.05700000002980232, -0.06840000301599503, -0.03750000149011612, 0.0013000000035390258, 0.00279999990016222, 0.0015999999595806003, -0.004000000189989805, -0.12790000438690186, 0.16509999334812164, 0.04349999874830246, -0.07760000228881836, -0.0032999999821186066, 0.061900001019239426, -0.051100000739097595, 0.13809999823570251, 0.10119999945163727, -0.0649000033736229, -0.053700000047683716, -0.028999999165534973, -0.06030000001192093, -0.0544000007212162, 0.17550000548362732, -0.027699999511241913, -0.052000001072883606, 0.039900001138448715, -0.03689999878406525, 0.11819999665021896, 0.05920000001788139, 0.045499999076128006, 0.0731000006198883, -0.09380000084638596, 0.06430000066757202, 0.05739999935030937, -0.04320000112056732, -0.13339999318122864, -0.09059999883174896, 0.03790000081062317, 0.13289999961853027, -0.13680000603199005, -0.05590000003576279, -0.13179999589920044, -0.016100000590085983, 0.1282999962568283, -0.10350000113248825, 0.02419999986886978, -0.026399999856948853, 0.04490000009536743, 0.014000000432133675, -0.024299999698996544, 0.025100000202655792, -0.08640000224113464, 0.08420000225305557, 0.006200000178068876, -0.056299999356269836, -0.010599999688565731, -0.14409999549388885, -0.04170000180602074, -0.043800000101327896, 0.021700000390410423, 0.0357000008225441, 0.06469999998807907, -0.08060000091791153, 0.021900000050663948, 0.12890000641345978, 0.09229999780654907, -0.04989999905228615, 0.08240000158548355, 0.04190000146627426, -0.03440000116825104, -0.0551999993622303, 0.031700000166893005, -0.059300001710653305, 0.07100000232458115, 0.05649999901652336, 0.02539999969303608, -0.03660000115633011, -0.05469999834895134, 0.03530000150203705, 0.08299999684095383, 0.08919999748468399, 0.05590000003576279, -0.0024999999441206455, 0.07540000230073929, -0.14380000531673431, -0.030700000002980232, -0.1712000072002411, 0.015399999916553497, -0.04039999842643738, -0.002899999963119626, -0.022099999710917473, 0.12999999523162842, 0.004699999932199717, -0.005100000184029341, 0.0024999999441206455, -0.059700001031160355, 0.07930000126361847, -0.053599998354911804, -0.14159999787807465, 0.055799998342990875, -0.04190000146627426, -0.1046999990940094, -0.039900001138448715, -0.023000000044703484, 0.04309999942779541, 0.011699999682605267, 0.0013000000035390258, 0.043699998408555984, -0.07639999687671661, -0.03319999948143959, 0.006300000008195639, 0.0364999994635582, -0.013000000268220901, -0.025299999862909317, -0.06859999895095825, -0.008899999782443047], [0.1039000004529953, 0.043699998408555984, -0.06719999760389328, 0.12070000171661377, 0.009399999864399433, -0.03519999980926514, 0.05290000140666962, -0.14429999887943268, -0.10930000245571136, -0.03310000151395798, 0.04639999940991402, -0.054499998688697815, 0.1477999985218048, 0.013000000268220901, -0.05889999866485596, 0.07039999961853027, 0.06769999861717224, -0.04910000041127205, -0.04309999942779541, -0.04410000145435333, 0.01940000057220459, -0.07989999651908875, -0.08100000023841858, 0.04690000042319298, -0.05559999868273735, 0.08150000125169754, -0.11580000072717667, 0.0142000000923872, -0.0421999990940094, 0.03269999846816063, -0.03020000085234642, -0.00019999999494757503, 0.006800000090152025, 0.008500000461935997, 0.010300000198185444, -0.09709999710321426, 0.1257999986410141, -0.08020000159740448, 0.06019999831914902, -0.005200000014156103, 0.08110000193119049, 0.0843999981880188, -0.06650000065565109, -0.06759999692440033, -0.08410000056028366, 0.10559999942779541, -0.1761000007390976, 0.05559999868273735, -0.06539999693632126, 0.0575999990105629, -0.045099999755620956, 0.07249999791383743, -0.012000000104308128, 0.0430000014603138, -0.121799997985363, 0.007199999876320362, -0.02329999953508377, -0.08330000191926956, -0.0203000009059906, 0.08720000088214874, 0.07370000332593918, -0.09030000120401382, 0.09369999915361404, -0.10559999942779541, 0.065700002014637, 0.030500000342726707, 0.07660000026226044, 0.00800000037997961, 0.061900001019239426, 0.032600000500679016, 0.03709999844431877, -0.061000000685453415, -0.131400004029274, 0.013399999588727951, -0.04410000145435333, -0.04740000143647194, 0.09109999984502792, 0.017100000753998756, 0.053199999034404755, 0.001500000013038516, -0.0010000000474974513, -0.10700000077486038, 0.039799999445676804, 0.0333000011742115, -0.147599995136261, -0.06830000132322311, 0.0348999984562397, 0.041600000113248825, 0.07509999722242355, 0.09109999984502792, -0.031099999323487282, 0.039799999445676804, 0.05249999836087227, 0.05689999833703041, 0.07100000232458115, 0.05050000175833702, 0.04399999976158142, 0.056699998676776886, -0.03680000081658363, -0.08449999988079071, -0.06120000034570694, 0.17520000040531158, -0.0406000018119812, 0.08820000290870667, -0.016300000250339508, -0.08309999853372574, 0.11100000143051147, 0.06920000165700912, 0.10119999945163727, 0.020899999886751175, 0.01269999984651804, 0.022299999371170998, 0.041200000792741776, -0.04639999940991402, 0.0737999975681305, -0.045099999755620956, -0.10760000348091125, 0.009800000116229057, -0.0027000000700354576, -0.009499999694526196, -0.07280000299215317, -0.04830000177025795, -0.15530000627040863, -0.07859999686479568, -0.0284000001847744, -0.03849999979138374, 0.1695999950170517, -0.008500000461935997, 0.023000000044703484, 0.038600001484155655, 0.028999999165534973, 0.09549999982118607, 0.059700001031160355, -0.04399999976158142, -0.07280000299215317, 0.03709999844431877, 0.043699998408555984, 0.07129999995231628, 0.08560000360012054, -0.02290000021457672, 0.1899999976158142, -0.01119999960064888, 0.005900000222027302, -0.10939999669790268, 0.04820000007748604, -0.05460000038146973, -0.033399999141693115, 0.007799999788403511, 0.0017999999690800905, -0.07850000262260437, -0.028999999165534973, 0.028999999165534973, -0.11289999634027481, 0.020999999716877937, -0.002199999988079071, -0.055799998342990875, -0.03620000183582306, -0.07880000025033951, -0.07540000230073929, -0.02250000089406967, 0.004600000102072954, -0.04740000143647194, 0.05779999867081642, -0.0949999988079071, 0.008100000210106373, -0.07699999958276749, 0.00839999970048666, -0.011800000444054604, 0.04100000113248825, 0.07670000195503235, 0.0560000017285347, 0.13809999823570251, 0.05040000006556511, -0.06080000102519989, 0.026499999687075615, 0.01640000008046627, -0.06840000301599503, 0.02250000089406967, 0.053599998354911804, 0.05389999970793724, -0.051500000059604645, -0.07649999856948853, 0.03920000046491623, 0.04349999874830246, 0.11580000072717667, -0.02979999966919422, 0.032999999821186066, -0.021299999207258224, 0.07850000262260437, 0.08569999784231186, -0.027400000020861626, -0.02250000089406967, 0.019600000232458115, -0.09950000047683716, 0.041200000792741776, -0.010200000368058681, -0.14079999923706055, -0.09440000355243683, -0.12520000338554382, 0.08429999649524689, -0.11379999667406082, -0.09870000183582306, 0.06790000200271606, 0.012900000438094139, -0.05730000138282776, -0.0551999993622303, -0.028300000354647636, -0.01940000057220459, -0.046300001442432404, -0.14380000531673431, 0.012900000438094139, 0.013500000350177288, 0.00279999990016222, -0.031099999323487282, 0.003599999938160181, -0.03460000082850456, 0.062199998646974564, 0.03660000115633011, 0.09510000050067902, 0.04839999973773956, -0.12890000641345978, -0.023800000548362732, -0.17870000004768372, -0.052000001072883606, -0.01209999993443489, 0.0034000000450760126, -0.08969999849796295, 0.008299999870359898, -0.125900000333786, -0.042500000447034836, -0.04129999876022339, 0.0017000000225380063, 0.0005000000237487257, -0.1088000014424324, 0.0066999997943639755, 0.0007999999797903001, 0.04010000079870224, -0.013899999670684338, 0.1379999965429306, -0.06549999862909317, -0.023499999195337296, -0.1444000005722046, 0.1688999980688095, -0.019300000742077827, 0.030899999663233757, 0.06920000165700912, 0.03449999913573265, -0.09830000251531601, 0.002300000051036477, 0.058800000697374344, 0.193900004029274, 0.022700000554323196, -0.05939999967813492, -0.025599999353289604, 0.05009999871253967, 0.09709999710321426, -0.04170000180602074, -0.02669999934732914, 0.04010000079870224, 0.09260000288486481, 0.008700000122189522, -0.03689999878406525, -0.08320000022649765, -0.16920000314712524], [0.16019999980926514, -0.061799999326467514, -0.065700002014637, -0.04520000144839287, -0.00930000003427267, -0.03200000151991844, -0.14650000631809235, 0.015799999237060547, -0.06159999966621399, -0.14749999344348907, 0.014999999664723873, -0.05810000002384186, 0.039799999445676804, 0.014499999582767487, -0.18930000066757202, 0.06949999928474426, 0.09059999883174896, -0.05990000069141388, 0.050700001418590546, 0.002199999988079071, 0.13009999692440033, -0.05469999834895134, -0.07190000265836716, 0.0027000000700354576, -0.11869999766349792, -0.023499999195337296, 0.024000000208616257, -0.0812000036239624, -0.05609999969601631, 0.007799999788403511, 0.10339999943971634, -0.08500000089406967, 0.04050000011920929, 0.14419999718666077, 0.04740000143647194, 0.06109999865293503, -0.011300000362098217, -0.010999999940395355, 0.04859999939799309, 0.015200000256299973, 0.030300000682473183, 0.00839999970048666, 0.020999999716877937, -0.09589999914169312, 0.06639999896287918, 0.05180000141263008, 0.03889999911189079, -0.01720000058412552, 0.04520000144839287, 0.11270000040531158, -0.11919999867677689, -0.03350000083446503, 0.06830000132322311, 0.06870000064373016, 0.04399999976158142, -0.08219999819993973, 0.03579999879002571, 0.005400000140070915, -0.09679999947547913, 0.02810000069439411, 0.0502999983727932, -0.10480000078678131, -0.0617000013589859, 0.07540000230073929, 0.04320000112056732, 0.023099999874830246, -0.009200000204145908, -0.08330000191926956, -0.010900000110268593, -0.0674000009894371, -0.05350000038743019, 0.08980000019073486, -0.05660000070929527, 0.013100000098347664, 0.019300000742077827, 0.018799999728798866, -0.04569999873638153, -0.00989999994635582, -0.12690000236034393, 0.06390000134706497, -0.07119999825954437, -0.002099999925121665, 0.1225999966263771, -0.05939999967813492, -0.045899998396635056, -0.012799999676644802, 0.0794999971985817, 0.06109999865293503, 0.02710000053048134, -0.01730000041425228, -0.13249999284744263, -0.014600000344216824, 0.06509999930858612, 0.0142000000923872, 0.0052999998442828655, 0.11540000140666962, -0.05290000140666962, -0.003800000064074993, 0.021700000390410423, -0.035999998450279236, -0.011300000362098217, -0.03739999979734421, -0.01590000092983246, 0.012600000016391277, 0.025100000202655792, -0.07959999889135361, -0.03280000016093254, 0.03750000149011612, 0.07450000196695328, 0.07670000195503235, -0.09969999641180038, 0.08259999752044678, -0.16380000114440918, 0.07419999688863754, 0.05130000039935112, 0.14640000462532043, 0.020500000566244125, 0.14270000159740448, -0.04280000180006027, -0.020800000056624413, 0.12129999697208405, 0.0015999999595806003, -0.05570000037550926, -0.025699999183416367, -0.07159999758005142, -0.04490000009536743, -0.14730000495910645, 0.008500000461935997, 0.054099999368190765, 0.053599998354911804, -0.01600000075995922, -0.06549999862909317, 0.028599999845027924, -0.05559999868273735, -0.01850000023841858, -0.0885000005364418, 0.12210000306367874, 0.10450000315904617, -0.02810000069439411, 0.06970000267028809, 0.07540000230073929, -0.09889999777078629, 0.032999999821186066, -0.03959999978542328, 0.0414000004529953, -0.09200000017881393, -0.14650000631809235, 0.05310000106692314, -0.006800000090152025, 0.0430000014603138, 0.0966000035405159, 0.00800000037997961, -0.14900000393390656, 0.13420000672340393, 0.004999999888241291, 0.05649999901652336, 0.0478999987244606, -0.012799999676644802, -0.00570000009611249, -9.999999747378752e-05, -0.0949999988079071, -0.051500000059604645, 0.031300000846385956, -0.07599999755620956, -0.10339999943971634, -0.04089999943971634, 0.020099999383091927, 0.0885000005364418, 0.020600000396370888, 0.08869999647140503, -0.10769999772310257, 0.1420000046491623, -0.016200000420212746, -0.13760000467300415, 0.039000000804662704, -0.1185000017285347, -0.005400000140070915, 0.04010000079870224, -0.008200000040233135, 0.04910000041127205, -0.09470000118017197, 0.050999999046325684, -0.026900000870227814, 0.004600000102072954, 0.156700000166893, -0.050700001418590546, -0.08510000258684158, -0.022299999371170998, 0.1370999962091446, -0.023499999195337296, -0.04309999942779541, 0.00419999985024333, -0.0771000012755394, 0.018699999898672104, -0.17149999737739563, 0.1031000018119812, 0.07100000232458115, 0.05590000003576279, -0.014800000004470348, -0.02500000037252903, -0.09510000050067902, 0.02199999988079071, -0.03350000083446503, 0.01940000057220459, -0.0019000000320374966, 0.05180000141263008, -0.025800000876188278, 0.0015999999595806003, -0.05299999937415123, -0.04149999842047691, -0.007699999958276749, -0.006099999882280827, 0.008200000040233135, 0.03629999980330467, -0.04780000075697899, -0.09049999713897705, 0.07829999923706055, -0.03500000014901161, -0.0340999998152256, -0.0027000000700354576, 0.0012000000569969416, -0.07169999927282333, -0.07249999791383743, -0.037300001829862595, -0.11069999635219574, 0.0015999999595806003, 0.21170000731945038, -0.05169999971985817, 0.06939999759197235, 0.002099999925121665, -0.033900000154972076, -0.08229999989271164, -0.1006999984383583, -0.03849999979138374, 0.0034000000450760126, 0.005200000014156103, 0.03869999945163727, -0.04619999974966049, -0.0689999982714653, -0.17329999804496765, 0.030799999833106995, 0.0908999964594841, -0.018699999898672104, -0.09860000014305115, -0.004600000102072954, 0.05510000139474869, 0.06700000166893005, 0.031099999323487282, -0.07150000333786011, 0.0026000000070780516, -0.03539999946951866, -0.008100000210106373, -0.013199999928474426, 0.05849999934434891, 0.07460000365972519, 0.031099999323487282, 0.06530000269412994, -0.01360000018030405, 0.18279999494552612, -0.02759999968111515, -0.016100000590085983, 0.12639999389648438, -0.0892999991774559, -0.0674000009894371], [-0.1031000018119812, 0.12700000405311584, -0.09019999951124191, -0.011699999682605267, -0.010400000028312206, -0.051899999380111694, 0.035100001841783524, -0.08129999786615372, 0.06790000200271606, -0.11559999734163284, 0.01600000075995922, -0.031300000846385956, 0.03610000014305115, 0.024299999698996544, -0.12919999659061432, 0.009700000286102295, 0.023800000548362732, -0.09719999879598618, -0.08309999853372574, -0.032099999487400055, -0.05009999871253967, 0.019300000742077827, -0.026900000870227814, 0.004399999976158142, 0.03449999913573265, -0.05249999836087227, 0.060100000351667404, -0.06960000097751617, -0.019899999722838402, -0.001500000013038516, -0.11959999799728394, 0.04450000077486038, -0.013399999588727951, 0.008999999612569809, 0.03539999946951866, 0.06459999829530716, -0.01510000042617321, -0.045499999076128006, 0.09440000355243683, -0.04740000143647194, -0.05559999868273735, -0.01600000075995922, -0.03500000014901161, -0.04520000144839287, -0.03539999946951866, 0.0860000029206276, 0.05820000171661377, 0.04639999940991402, -0.026499999687075615, 0.10589999705553055, 0.05009999871253967, -0.014999999664723873, -0.0026000000070780516, 0.07069999724626541, -0.03869999945163727, -0.09549999982118607, 0.016599999740719795, 0.04490000009536743, -0.004800000227987766, 0.06369999796152115, 0.0737999975681305, 0.03189999982714653, -0.03880000114440918, -0.0778999999165535, -0.14000000059604645, -0.05000000074505806, 0.10939999669790268, -0.04659999907016754, -0.04320000112056732, -0.03550000116229057, -0.011900000274181366, -0.07859999686479568, -0.09070000052452087, -0.0737999975681305, 0.06509999930858612, 0.1404000073671341, 0.0674000009894371, 0.0066999997943639755, 0.018200000748038292, 0.05490000173449516, -0.04729999974370003, -0.09600000083446503, 0.014800000004470348, 0.0005000000237487257, -0.003000000026077032, -0.05420000106096268, -0.025200000032782555, -0.061000000685453415, 0.04010000079870224, 0.006000000052154064, 0.06340000033378601, 0.00800000037997961, 0.09769999980926514, 0.13529999554157257, 0.019899999722838402, -0.03959999978542328, -0.11540000140666962, 0.02280000038444996, 0.05869999900460243, -0.0215000007301569, 0.01510000042617321, -0.019700000062584877, 0.05719999969005585, 0.08269999921321869, 0.09319999814033508, -0.03720000013709068, 0.05380000174045563, -0.019700000062584877, 0.023900000378489494, 9.999999747378752e-05, 0.0494999997317791, -0.05510000139474869, -0.1386999934911728, -0.02449999935925007, 0.01119999960064888, -0.013700000010430813, 0.08919999748468399, 0.07999999821186066, -0.024399999529123306, 0.02319999970495701, 0.13220000267028809, 0.027699999511241913, 0.039400000125169754, 0.06440000236034393, -0.03539999946951866, -0.1606999933719635, 0.02199999988079071, 0.012199999764561653, 0.06310000270605087, 0.0210999995470047, -0.03550000116229057, -0.008299999870359898, 0.004900000058114529, -0.11010000109672546, -0.09570000320672989, -0.07280000299215317, -0.020500000566244125, 0.08290000259876251, 0.03779999911785126, -0.08269999921321869, 0.12330000102519989, 0.03819999843835831, 0.14869999885559082, -0.04899999871850014, 0.04190000146627426, 0.04399999976158142, -0.08810000121593475, -0.043299999088048935, 0.08739999681711197, -0.0003000000142492354, -0.09380000084638596, 0.1459999978542328, -0.032499998807907104, 0.04340000078082085, -0.07450000196695328, 0.1517000049352646, 0.031599998474121094, -0.042399998754262924, 0.1315000057220459, -0.006099999882280827, 0.09690000116825104, 0.0017000000225380063, -0.020800000056624413, -0.033399999141693115, 0.01119999960064888, 0.05810000002384186, 0.02889999933540821, 0.0406000018119812, 0.050599999725818634, -0.07159999758005142, 0.040300000458955765, -0.1266999989748001, -0.055799998342990875, -0.011500000022351742, -0.09470000118017197, -0.026399999856948853, 0.04399999976158142, 0.05420000106096268, -0.04170000180602074, 0.0388</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>[-1.9563037111139807]</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>[0.6748254805421628]</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>[-1.071155195386282]</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>[0.4728515057447245]</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>[-2.7086680021313407]</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>[1.2137717309014704]</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>[-1.5144887840800023]</t>
+        </is>
+      </c>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>[0.5776260329538945]</t>
+        </is>
+      </c>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>[0.0125492757593062]</t>
+        </is>
+      </c>
+      <c r="N34" t="inlineStr">
+        <is>
+          <t>[0.23418482799757492]</t>
+        </is>
+      </c>
+      <c r="O34" t="inlineStr">
+        <is>
+          <t>[-23.881599860714264]</t>
+        </is>
+      </c>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>[8.179762347104042]</t>
+        </is>
+      </c>
+      <c r="Q34" t="inlineStr">
+        <is>
+          <t>[0.41095092911531783]</t>
+        </is>
+      </c>
+      <c r="R34" t="inlineStr">
+        <is>
+          <t>[0.06351464549086108]</t>
+        </is>
+      </c>
+      <c r="S34" t="inlineStr">
+        <is>
+          <t>[-0.004761582348723925]</t>
+        </is>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>[0.08466155230581411]</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>[-0.15218912838641008]</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>[0.11017593147536199]</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>[0.32033467595653264]</t>
+        </is>
+      </c>
+      <c r="X34" t="inlineStr">
+        <is>
+          <t>[0.07120216315502417]</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>[-0.011403755691519857]</t>
+        </is>
+      </c>
+      <c r="Z34" t="inlineStr">
+        <is>
+          <t>[0.08323166136051832]</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>[-0.4276780243416094]</t>
+        </is>
+      </c>
+      <c r="AB34" t="inlineStr">
+        <is>
+          <t>[0.1313526233962188]</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>[-0.7082212475693024]</t>
+        </is>
+      </c>
+      <c r="AD34" t="inlineStr">
+        <is>
+          <t>[0.1431420587925658]</t>
+        </is>
+      </c>
+      <c r="AE34" t="inlineStr">
+        <is>
+          <t>[-0.5465498362367853]</t>
+        </is>
+      </c>
+      <c r="AF34" t="inlineStr">
+        <is>
+          <t>[0.16652950784176657]</t>
+        </is>
+      </c>
+      <c r="AG34" t="inlineStr">
+        <is>
+          <t>[-2.4376131281996845]</t>
+        </is>
+      </c>
+      <c r="AH34" t="inlineStr">
+        <is>
+          <t>[0.2559301545725179]</t>
+        </is>
+      </c>
+      <c r="AI34" t="inlineStr">
+        <is>
+          <t>[-0.9691926330878384]</t>
+        </is>
+      </c>
+      <c r="AJ34" t="inlineStr">
+        <is>
+          <t>[0.161373144148616]</t>
+        </is>
+      </c>
+      <c r="AK34" t="inlineStr">
+        <is>
+          <t>[-0.5160092828631151]</t>
+        </is>
+      </c>
+      <c r="AL34" t="inlineStr">
+        <is>
+          <t>[0.1609132781250972]</t>
+        </is>
+      </c>
+      <c r="AM34" t="inlineStr">
+        <is>
+          <t>[-3.1823461360234315]</t>
+        </is>
+      </c>
+      <c r="AN34" t="inlineStr">
+        <is>
+          <t>[0.3212345035996145]</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>model_264_128_3</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>[264, 128]</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>[[[0.025800000876188278, -0.06419999897480011, -0.005400000140070915, 0.029899999499320984, 0.02449999935925007, -0.04399999976158142, -0.07069999724626541, 0.009800000116229057, -0.008299999870359898, -0.02370000071823597, 0.05350000038743019, 0.012000000104308128, 0.05649999901652336, -0.08569999784231186, -0.01899999938905239, 0.1006999984383583, 0.043699998408555984, 0.05550000071525574, -0.012400000356137753, 0.024900000542402267, -0.02850000001490116, 0.019300000742077827, -0.030400000512599945, -0.006000000052154064, 0.017100000753998756, 0.026000000536441803, 0.024000000208616257, -0.00559999980032444, 0.03750000149011612, 0.023600000888109207, 0.04470000043511391, -0.11550000309944153, -0.05739999935030937, -0.038600001484155655, 0.09920000284910202, -0.01850000023841858, 0.06840000301599503, 0.01769999973475933, 0.0771000012755394, -9.999999747378752e-05, -0.06710000336170197, 0.0414000004529953, 0.03220000118017197, 0.006500000134110451, 9.999999747378752e-05, 0.05260000005364418, -0.08470000326633453, -0.0406000018119812, -0.024700000882148743, 0.05829999968409538, 0.020400000736117363, 0.018699999898672104, 0.021900000050663948, -0.09279999881982803, -0.046799998730421066, -0.05609999969601631, 0.025499999523162842, 0.016599999740719795, 0.04809999838471413, -0.06289999932050705, 0.06310000270605087, -0.032999999821186066, 0.0071000000461936, 0.06989999860525131, 0.03819999843835831, -0.040699999779462814, 0.04129999876022339, -0.031599998474121094, 0.039400000125169754, -0.06400000303983688, -0.03060000017285347, 0.08089999854564667, -0.13809999823570251, 0.01510000042617321, -0.051500000059604645, -0.1128000020980835, 0.018699999898672104, -0.013700000010430813, 0.04520000144839287, -0.012199999764561653, -0.02500000037252903, 0.019500000402331352, 0.045899998396635056, 0.03240000084042549, 0.011500000022351742, 0.0210999995470047, -0.015599999576807022, -0.021199999377131462, 0.041200000792741776, -0.023000000044703484, 0.0007999999797903001, -0.02669999934732914, 0.04479999840259552, -0.058400001376867294, -0.04749999940395355, 0.03579999879002571, 0.03180000185966492, 0.07940000295639038, -0.07440000027418137, -0.11640000343322754, 0.11949999630451202, 0.03220000118017197, 0.015200000256299973, 0.04619999974966049, -0.008299999870359898, -0.04989999905228615, 0.002899999963119626, 0.01940000057220459, 0.011099999770522118, 0.06419999897480011, -0.0649000033736229, -0.05299999937415123, -0.009700000286102295, -0.039400000125169754, 0.012799999676644802, 0.03830000013113022, -0.018300000578165054, -0.007300000172108412, -0.023900000378489494, -0.06970000267028809, 0.039799999445676804, 0.019999999552965164, 0.025699999183416367, 0.03280000016093254, -0.013299999758601189, -0.05979999899864197, 0.08389999717473984, -0.048700001090765, 0.0215000007301569, 0.0714000016450882, -0.023800000548362732, 0.11559999734163284, 0.05959999933838844, -0.016899999231100082, -0.015200000256299973, -0.050999999046325684, -0.02630000002682209, 0.05009999871253967, 0.008899999782443047, 0.006000000052154064, -0.01549999974668026, 0.05999999865889549, -0.055799998342990875, 0.05869999900460243, -0.013799999840557575, -0.020500000566244125, 0.042500000447034836, 0.008100000210106373, -0.06430000066757202, 0.00559999980032444, -0.0027000000700354576, -0.07729999721050262, -0.001500000013038516, 0.01679999940097332, 0.08209999650716782, 0.053300000727176666, 0.03139999881386757, 0.026599999517202377, 0.01730000041425228, 0.01119999960064888, -0.019500000402331352, -0.002199999988079071, -0.04170000180602074, -0.07919999957084656, 0.003800000064074993, 0.016200000420212746, -0.03350000083446503, -0.017500000074505806, 0.08669999986886978, -0.013700000010430813, -0.020099999383091927, 0.017500000074505806, -0.04659999907016754, 0.04100000113248825, -0.04569999873638153, 0.012400000356137753, 0.14239999651908875, -0.0272000003606081, 0.0003000000142492354, -0.027000000700354576, -0.0015999999595806003, 0.02930000051856041, -0.01209999993443489, -0.04610000178217888, -0.03189999982714653, -0.0203000009059906, 0.04839999973773956, 0.05180000141263008, -0.009399999864399433, -0.050999999046325684, -0.10329999774694443, 0.06289999932050705, 0.029999999329447746, -0.08190000057220459, -0.014299999922513962, 0.021800000220537186, 0.035999998450279236, 0.004999999888241291, 0.01759999990463257, 0.015300000086426735, -0.08780000358819962, 0.06729999929666519, 0.004399999976158142, -0.009700000286102295, -0.05640000104904175, 0.02199999988079071, 0.10300000011920929, -0.010300000198185444, 0.03709999844431877, 0.014700000174343586, 0.053300000727176666, 0.044199999421834946, -0.03009999915957451, -0.03319999948143959, 0.031700000166893005, -0.025299999862909317, -0.019300000742077827, -0.045099999755620956, 0.002400000113993883, 0.047200001776218414, -0.0658000037074089, -0.02710000053048134, -0.026499999687075615, 0.09220000356435776, 0.054999999701976776, -0.028699999675154686, 0.07129999995231628, -0.01759999990463257, 0.05429999902844429, 0.10840000212192535, 0.07039999961853027, -0.04899999871850014, 0.02239999920129776, 0.04479999840259552, -0.05180000141263008, 0.02019999921321869, 0.010700000450015068, 0.009800000116229057, 0.01860000006854534, -0.03420000150799751, -0.07530000060796738, 0.023399999365210533, 0.042100001126527786, 0.054099999368190765, -0.04600000008940697, -0.0658000037074089, -0.017100000753998756, -0.08380000293254852, 0.030500000342726707, -0.08150000125169754, 0.04179999977350235, 0.03660000115633011, 0.023600000888109207, -0.09610000252723694, 0.0357000008225441, 0.04580000042915344, 0.013100000098347664, 0.015399999916553497, -0.03440000116825104, 0.022299999371170998, -0.05649999901652336, 0.06499999761581421, 0.02889999933540821, -0.010099999606609344], [0.11140000075101852, 0.017100000753998756, -0.024399999529123306, 0.06069999933242798, -0.05079999938607216, 0.04399999976158142, 0.030300000682473183, -0.052299998700618744, 0.03959999978542328, 0.02850000001490116, 0.024800000712275505, 0.031300000846385956, -0.03590000048279762, 0.007300000172108412, 0.03799999877810478, 0.061500001698732376, -0.03180000185966492, 0.0210999995470047, 0.05719999969005585, 0.0617000013589859, 0.07779999822378159, -0.08560000360012054, 0.011699999682605267, 0.047200001776218414, 0.0746999979019165, -0.027400000020861626, -0.07129999995231628, -0.09139999747276306, -0.018300000578165054, -0.0333000011742115, -0.027499999850988388, 0.06469999998807907, 0.04529999941587448, 0.023499999195337296, 0.029200000688433647, -0.02850000001490116, -0.024700000882148743, -0.03689999878406525, -0.026599999517202377, -0.03790000081062317, -0.052400000393390656, 0.003800000064074993, 0.002300000051036477, -0.05469999834895134, -0.008200000040233135, 0.05620000138878822, 0.02630000002682209, 0.00430000014603138, 0.03139999881386757, -0.04780000075697899, 0.054999999701976776, 0.08079999685287476, -0.043299999088048935, 0.08460000157356262, 0.000699999975040555, 0.020800000056624413, -0.04919999837875366, -0.027400000020861626, 0.06419999897480011, 0.059700001031160355, -0.06419999897480011, -0.02070000022649765, 0.008999999612569809, -0.002199999988079071, -0.03849999979138374, -0.020999999716877937, -0.04340000078082085, 0.04969999939203262, -0.010099999606609344, -0.03530000150203705, 0.08299999684095383, -0.03920000046491623, 0.07750000059604645, 0.042399998754262924, -0.00279999990016222, -0.04560000076889992, 0.06480000168085098, 0.03420000150799751, -0.05999999865889549, 0.1429000049829483, -0.02160000056028366, -0.03689999878406525, 0.004100000020116568, 0.005200000014156103, 0.010099999606609344, 0.0215000007301569, 0.04019999876618385, 0.12630000710487366, -0.04569999873638153, 0.0017000000225380063, -0.07479999959468842, 0.15240000188350677, 0.04969999939203262, -0.009399999864399433, 0.03420000150799751, -0.020800000056624413, -0.06689999997615814, 0.03550000116229057, -0.0020000000949949026, -0.06120000034570694, 0.10980000346899033, 0.009499999694526196, 0.010599999688565731, 0.07769999653100967, 0.06889999657869339, 0.017000000923871994, 0.040800001472234726, 0.08829999715089798, 0.04639999940991402, 0.02630000002682209, 0.019200000911951065, -0.006099999882280827, 0.059300001710653305, 0.010099999606609344, -0.03700000047683716, -0.03400000184774399, 0.01140000019222498, -0.04749999940395355, -0.03759999945759773, 0.002400000113993883, 0.03790000081062317, 0.0284000001847744, -0.0032999999821186066, 0.04270000010728836, 0.013899999670684338, 0.0406000018119812, 0.03240000084042549, 0.015599999576807022, -0.003000000026077032, 0.01600000075995922, 0.023399999365210533, 0.000699999975040555, 0.03139999881386757, 0.03620000183582306, 0.03139999881386757, 0.05260000005364418, -0.06970000267028809, 0.021299999207258224, 0.10859999805688858, -0.015300000086426735, 0.04010000079870224, 0.05420000106096268, 0.02329999953508377, 0.08760000020265579, 0.0340999998152256, -0.005400000140070915, 0.01590000092983246, 0.006000000052154064, -0.029400000348687172, -0.04600000008940697, -0.022700000554323196, -0.03929999843239784, 0.029200000688433647, 0.03229999914765358, 0.05889999866485596, 0.004399999976158142, 0.10199999809265137, -0.0502999983727932, -0.06780000030994415, -0.047200001776218414, -0.012799999676644802, 0.014399999752640724, 0.040300000458955765, -0.017500000074505806, -0.06289999932050705, 0.1005999967455864, -0.05119999870657921, 0.00019999999494757503, -0.027000000700354576, 0.10409999638795853, 0.04580000042915344, 0.006000000052154064, 0.06949999928474426, 0.02239999920129776, 0.02239999920129776, 0.030500000342726707, -0.007600000128149986, 0.00139999995008111, 0.08079999685287476, -0.017000000923871994, 0.08489999920129776, -0.11649999767541885, -0.0608999989926815, -0.03689999878406525, 0.05999999865889549, 0.039500001817941666, -0.04399999976158142, 0.024399999529123306, -0.004999999888241291, 0.07580000162124634, -0.025299999862909317, -0.005100000184029341, 0.08150000125169754, 0.033399999141693115, -0.002099999925121665, -0.007400000002235174, -0.009100000374019146, -0.03519999980926514, -0.021199999377131462, -0.050700001418590546, -0.04610000178217888, -0.050700001418590546, 0.07970000058412552, 0.022600000724196434, -0.03530000150203705, -0.026399999856948853, -0.11819999665021896, 0.023499999195337296, 0.018200000748038292, 0.06960000097751617, -0.022600000724196434, -0.07100000232458115, 0.02500000037252903, -0.051100000739097595, -0.010599999688565731, -0.023099999874830246, -0.03449999913573265, -0.07720000296831131, 0.07400000095367432, -0.026100000366568565, -0.013199999928474426, -0.09870000183582306, 0.044199999421834946, 0.14480000734329224, -0.04039999842643738, 0.009100000374019146, 0.004800000227987766, -0.02879999950528145, 0.045099999755620956, 0.025599999353289604, -0.020899999886751175, 0.01360000018030405, 0.011099999770522118, 0.03869999945163727, 0.025599999353289604, -0.015200000256299973, 0.033900000154972076, -0.0877000018954277, -0.00019999999494757503, -0.08320000022649765, -0.01769999973475933, -0.06809999793767929, 0.02669999934732914, 0.10649999976158142, 0.07129999995231628, 0.018300000578165054, -0.0203000009059906, 0.05860000103712082, 0.08980000019073486, 0.006300000008195639, 0.046300001442432404, 0.04749999940395355, 0.06800000369548798, 0.03970000147819519, 0.05480000004172325, -0.003000000026077032, -0.0722000002861023, -0.007199999876320362, 0.010999999940395355, 0.014800000004470348, 0.057100001722574234, 0.014600000344216824, 0.004000000189989805, -0.0706000030040741]], [[-0.03700000047683716, 0.014600000344216824, -0.03739999979734421, 0.017500000074505806, 0.0017999999690800905, 0.024399999529123306, -0.026900000870227814, -0.007499999832361937, 0.0649000033736229, -0.027699999511241913, -0.11620000004768372, -0.14730000495910645, 0.031599998474121094, -0.020999999716877937, 0.08619999885559082, 0.08179999887943268, 0.08449999988079071, 0.004800000227987766, -0.029600000008940697, 0.06809999793767929, 0.0560000017285347, -0.021400000900030136, -0.0013000000035390258, 0.048900000751018524, -0.10130000114440918, 0.024700000882148743, 0.0494999997317791, -0.01549999974668026, 0.053599998354911804, -0.09279999881982803, 0.03180000185966492, -0.0031999999191612005, 0.045899998396635056, -0.03759999945759773, 0.008100000210106373, -0.024900000542402267, -0.002199999988079071, 0.06400000303983688, -0.004100000020116568, -0.14790000021457672, -0.08179999887943268, 0.03550000116229057, -0.0820000022649765, -0.02199999988079071, 0.01759999990463257, 0.02800000086426735, -0.032600000500679016, 0.010400000028312206, 0.020800000056624413, 0.038100000470876694, 0.018699999898672104, 0.10540000349283218, 0.16859999299049377, 0.016499999910593033, 0.10260000079870224, -0.09939999878406525, 0.004000000189989805, 0.0020000000949949026, 0.014999999664723873, -0.0982000008225441, 0.03660000115633011, -0.06960000097751617, -0.04320000112056732, 0.039400000125169754, 0.005100000184029341, 0.09309999644756317, -0.07180000096559525, -0.006399999838322401, 0.05169999971985817, -0.11829999834299088, -0.045899998396635056, 0.08630000054836273, 0.08560000360012054, 0.00839999970048666, -0.07150000333786011, 0.058800000697374344, 0.0723000019788742, 0.1039000004529953, -0.007499999832361937, -0.01889999955892563, 0.02449999935925007, -0.06780000030994415, 0.02370000071823597, 0.13079999387264252, 0.02370000071823597, -0.008500000461935997, -0.12060000002384186, -0.054499998688697815, -0.00860000029206276, 0.0005000000237487257, 0.18970000743865967, 0.03739999979734421, 0.04089999943971634, 0.040699999779462814, -0.06300000101327896, -0.06210000067949295, 0.032999999821186066, -0.05530000105500221, 0.06109999865293503, 0.03480000048875809, 0.005799999926239252, 0.046799998730421066, -0.13529999554157257, -0.0017000000225380063, 0.10270000249147415, -0.02539999969303608, -0.19519999623298645, -0.052400000393390656, 0.12110000103712082, -0.016699999570846558, 0.008100000210106373, -0.01679999940097332, 0.050599999725818634, 0.04500000178813934, -0.11060000211000443, 0.09000000357627869, 0.11050000041723251, 0.024000000208616257, -0.05310000106692314, 0.02250000089406967, -0.1185000017285347, -0.007899999618530273, -0.023000000044703484, -0.09799999743700027, 0.03189999982714653, -0.013500000350177288, 0.04639999940991402, -0.120899997651577, -0.06920000165700912, -0.03629999980330467, 0.04809999838471413, -0.025499999523162842, 0.08299999684095383, -0.024800000712275505, -0.04650000110268593, -0.0035000001080334187, 0.0210999995470047, 0.03060000017285347, -0.03660000115633011, 0.0003000000142492354, -0.023499999195337296, -0.009999999776482582, 0.022099999710917473, 0.04320000112056732, 0.020899999886751175, 0.009200000204145908, 0.08179999887943268, 0.07400000095367432, 0.07490000128746033, -0.07010000199079514, -0.10450000315904617, -0.01209999993443489, -0.017100000753998756, 0.07850000262260437, 0.07900000363588333, 0.033799998462200165, -0.06109999865293503, 0.006300000008195639, -0.06840000301599503, 0.030300000682473183, -0.03440000116825104, -0.022600000724196434, 0.025599999353289604, -0.11010000109672546, -0.04050000011920929, 0.09759999811649323, -0.05290000140666962, 0.004000000189989805, -0.0007999999797903001, -0.017100000753998756, -0.00279999990016222, 0.09539999812841415, 0.009600000455975533, 0.0203000009059906, -0.06509999930858612, -0.0551999993622303, 0.04010000079870224, 0.031199999153614044, -0.1023000031709671, -0.054999999701976776, -0.04610000178217888, -0.016100000590085983, 0.0027000000700354576, -0.043299999088048935, 0.04320000112056732, -0.08529999852180481, -0.008100000210106373, 0.05730000138282776, 0.04390000179409981, -0.08030000329017639, -0.02800000086426735, 0.006000000052154064, -0.02370000071823597, -0.010599999688565731, -0.0414000004529953, -0.006399999838322401, 0.002400000113993883, 0.004100000020116568, -0.0031999999191612005, -0.06469999998807907, 0.002899999963119626, -0.014100000262260437, -0.0348999984562397, -0.040699999779462814, -0.004399999976158142, -0.052000001072883606, 0.028699999675154686, -0.0031999999191612005, -0.06289999932050705, -0.024299999698996544, -0.04960000142455101, -0.06379999965429306, 0.07329999655485153, 0.09709999710321426, 0.1890999972820282, -0.03480000048875809, 0.058400001376867294, 0.028599999845027924, -0.007000000216066837, -0.006300000008195639, -0.013000000268220901, -0.06390000134706497, -0.010300000198185444, 0.01679999940097332, 0.03290000185370445, -0.14409999549388885, -0.04410000145435333, 0.03669999912381172, -0.025499999523162842, 0.030300000682473183, 0.06710000336170197, 0.06430000066757202, 0.006500000134110451, 0.018699999898672104, -0.03610000014305115, -0.0003000000142492354, 0.013899999670684338, 0.05180000141263008, -0.07689999788999557, 0.057500001043081284, 0.03460000082850456, 0.061400000005960464, -0.03579999879002571, -0.14720000326633453, 0.13179999589920044, 0.015399999916553497, 0.051899999380111694, 0.03269999846816063, 0.06319999694824219, 0.06509999930858612, -0.03880000114440918, 0.05510000139474869, -0.0737999975681305, 0.00800000037997961, 0.061000000685453415, -0.10010000318288803, 0.006599999964237213, -0.061500001698732376, -0.03020000085234642, -0.09449999779462814, 0.11140000075101852, 0.08089999854564667, 0.04349999874830246, -0.05700000002980232], [-0.04010000079870224, 0.024800000712275505, -0.017999999225139618, -0.05050000175833702, 0.04740000143647194, 0.04879999905824661, -0.05429999902844429, -0.058400001376867294, 0.08590000122785568, 0.03420000150799751, -0.024900000542402267, 0.02630000002682209, 0.07850000262260437, -0.07090000063180923, 0.09769999980926514, -0.027400000020861626, -0.00279999990016222, -0.1111999973654747, -0.08789999783039093, 0.06260000169277191, 0.14640000462532043, -0.07810000330209732, 0.016599999740719795, 0.02669999934732914, 0.007899999618530273, 0.05559999868273735, 0.08070000261068344, 0.009999999776482582, 0.09070000052452087, 0.006500000134110451, 0.019500000402331352, -0.08060000091791153, 0.000699999975040555, 0.052000001072883606, 0.0738999992609024, -0.0017000000225380063, 0.006300000008195639, 0.07289999723434448, 0.09520000219345093, -0.04839999973773956, 0.04800000041723251, -0.0005000000237487257, 0.05920000001788139, 0.0414000004529953, -0.019500000402331352, -0.01769999973475933, 0.06019999831914902, -0.02319999970495701, -0.0071000000461936, -0.011500000022351742, -0.0632999986410141, 0.016599999740719795, 0.011099999770522118, -0.020500000566244125, -0.028699999675154686, 0.02019999921321869, -0.09070000052452087, 0.07739999890327454, 0.05559999868273735, -0.02590000070631504, 0.004900000058114529, -0.12790000438690186, 0.009499999694526196, 0.0142000000923872, 0.031199999153614044, 0.0471000000834465, 0.05079999938607216, 0.0035000001080334187, 0.018699999898672104, -0.021800000220537186, 0.06120000034570694, -0.013500000350177288, 0.08250000327825546, 0.06679999828338623, -0.016300000250339508, 0.013500000350177288, 0.033399999141693115, 0.06300000101327896, 0.0551999993622303, -0.007499999832361937, -0.03189999982714653, 0.12759999930858612, -0.0786999985575676, 0.010999999940395355, -0.06319999694824219, 0.014600000344216824, 0.018400000408291817, -0.029999999329447746, -0.0031999999191612005, 0.03280000016093254, 0.014800000004470348, -0.08070000261068344, -0.08060000091791153, -0.004600000102072954, -0.04259999841451645, 0.07729999721050262, -0.0706000030040741, -0.026100000366568565, -0.007300000172108412, 0.007499999832361937, 0.061900001019239426, 0.03680000081658363, 0.027899999171495438, 0.016699999570846558, -0.004900000058114529, -0.04800000041723251, -0.0210999995470047, -0.005100000184029341, -0.04179999977350235, 0.020800000056624413, 0.06319999694824219, 0.08129999786615372, 0.06520000100135803, -0.12639999389648438, 0.08399999886751175, -0.023399999365210533, 0.03440000116825104, -0.030899999663233757, -0.08429999649524689, 0.0017999999690800905, 0.01810000091791153, 0.10660000145435333, 0.04430000111460686, 0.1225999966263771, -0.06430000066757202, -0.005100000184029341, -0.07500000298023224, -0.04910000041127205, 0.01549999974668026, -0.02459999918937683, 0.035999998450279236, 0.11100000143051147, 0.027300000190734863, 0.020800000056624413, 0.12620000541210175, -0.057500001043081284, -0.06369999796152115, 0.018300000578165054, -0.06549999862909317, 0.06270000338554382, -0.06499999761581421, -0.0031999999191612005, -0.07509999722242355, -0.12479999661445618, -0.15049999952316284, 0.013700000010430813, -0.08749999850988388, 0.010599999688565731, -0.0031999999191612005, -0.10189999639987946, -0.04270000010728836, -0.04010000079870224, -0.041099999099969864, -0.0835999995470047, 0.0272000003606081, -0.006899999920278788, 0.012900000438094139, 0.004900000058114529, -0.006300000008195639, -0.0017999999690800905, -0.05860000103712082, -0.03449999913573265, 0.01679999940097332, -0.0729999989271164, -0.023099999874830246, 0.006300000008195639, 0.02630000002682209, 0.01549999974668026, -0.03220000118017197, -0.013899999670684338, -0.012400000356137753, -0.03610000014305115, -0.07540000230073929, -0.06350000202655792, 0.08720000088214874, -0.02969999983906746, -0.03869999945163727, -0.11460000276565552, 0.08389999717473984, 0.020500000566244125, 0.022700000554323196, -0.12720000743865967, -0.12359999865293503, -0.0617000013589859, 0.09319999814033508, -0.05559999868273735, 0.0284000001847744, 0.015699999406933784, 0.013899999670684338, -0.02449999935925007, 0.05590000003576279, -0.0031999999191612005, -0.020800000056624413, -0.026200000196695328, -0.05689999833703041, 0.013199999928474426, 0.15970000624656677, 0.11299999803304672, -0.016699999570846558, -0.009499999694526196, 0.07329999655485153, 0.09449999779462814, -0.032999999821186066, -0.08919999748468399, -0.07169999927282333, -0.10769999772310257, 0.04479999840259552, 0.07289999723434448, 0.009200000204145908, -0.02810000069439411, 0.011599999852478504, -0.017500000074505806, 0.08049999922513962, 0.05290000140666962, -0.004800000227987766, -0.09139999747276306, -0.02319999970495701, -0.08510000258684158, 0.14720000326633453, 0.13840000331401825, 0.021299999207258224, 0.0340999998152256, -0.01600000075995922, -0.10260000079870224, 0.008100000210106373, 0.01850000023841858, -0.0003000000142492354, 0.06459999829530716, -0.031099999323487282, -0.007400000002235174, -0.09520000219345093, -0.040800001472234726, 0.01769999973475933, -0.0035000001080334187, -0.11599999666213989, 0.04639999940991402, 0.10270000249147415, -0.08169999718666077, 0.018400000408291817, 0.09070000052452087, 0.07970000058412552, -0.09120000153779984, 0.12359999865293503, -0.010400000028312206, -0.044199999421834946, 0.05220000073313713, -0.07850000262260437, 0.01979999989271164, -0.08739999681711197, -0.1469999998807907, -0.024000000208616257, 0.11909999698400497, 0.10859999805688858, 0.023000000044703484, -0.003800000064074993, 0.08829999715089798, 0.014700000174343586, 0.014700000174343586, 0.14180000126361847, -0.028699999675154686, 0.0803999975323677, 0.005499999970197678, -0.10490000247955322, -0.04989999905228615], [0.07919999957084656, -0.047200001776218414, -0.052000001072883606, -0.03819999843835831, -0.014499999582767487, 0.023600000888109207, -0.011599999852478504, -0.028699999675154686, -0.08299999684095383, -0.032600000500679016, -0.023800000548362732, 0.042100001126527786, -0.08579999953508377, -0.07270000129938126, 0.0027000000700354576, 0.05559999868273735, 0.022199999541044235, -0.0284000001847744, 0.08510000258684158, 0.05869999900460243, -0.03350000083446503, 0.0203000009059906, 0.023800000548362732, -0.025800000876188278, -0.0502999983727932, 0.042399998754262924, -0.12269999831914902, -0.00989999994635582, 0.005200000014156103, 0.03519999980926514, 0.002899999963119626, -0.06469999998807907, 0.05290000140666962, -0.018300000578165054, 0.025800000876188278, 0.0421999990940094, -0.002199999988079071, -0.10499999672174454, 0.05180000141263008, 0.02979999966919422, -0.10209999978542328, -0.00800000037997961, -0.016699999570846558, -0.015399999916553497, -0.05040000006556511, 0.12710000574588776, 0.06469999998807907, -0.07670000195503235, 0.028599999845027924, -0.001500000013038516, 0.07599999755620956, -0.011300000362098217, -0.010700000450015068, -0.029200000688433647, -0.020899999886751175, -0.06989999860525131, -0.05480000004172325, -0.008200000040233135, 0.0142000000923872, 0.02889999933540821, 0.06350000202655792, -0.008899999782443047, 0.01140000019222498, -0.05490000173449516, 0.11720000207424164, -0.0284000001847744, 0.046300001442432404, 0.1273999959230423, 0.05249999836087227, 0.027799999341368675, -0.0364999994635582, 0.05139999836683273, -0.08320000022649765, 0.06390000134706497, 0.06289999932050705, 0.01899999938905239, -0.005799999926239252, -0.008799999952316284, -0.006200000178068876, -0.10490000247955322, -0.12430000305175781, -0.09849999845027924, -0.22619999945163727, 0.08139999955892563, 0.012199999764561653, -0.1462000012397766, -0.10580000281333923, 0.06719999760389328, -0.04010000079870224, -0.023399999365210533, -0.12240000069141388, 0.039900001138448715, 0.0035000001080334187, -0.0038999998942017555, 0.044599998742341995, -0.03539999946951866, 0.19519999623298645, -0.02889999933540821, 0.017500000074505806, -0.025100000202655792, 0.07699999958276749, 0.06310000270605087, -0.05050000175833702, -0.0017999999690800905, 0.01940000057220459, 0.04089999943971634, -0.009399999864399433, 0.11460000276565552, 0.01080000028014183, 0.10999999940395355, -0.09929999709129333, 0.07519999891519547, -0.04610000178217888, 0.045499999076128006, 0.026599999517202377, 0.029100000858306885, 0.14180000126361847, 0.05790000036358833, 0.039000000804662704, -0.020099999383091927, 0.024700000882148743, 0.028300000354647636, 0.003100000089034438, 0.01679999940097332, 0.0738999992609024, -0.03099999949336052, -0.06719999760389328, -0.10670000314712524, 0.03150000050663948, -0.03819999843835831, 0.01510000042617321, -0.03660000115633011, -0.11580000072717667, -0.024299999698996544, -0.03680000081658363, -0.03669999912381172, -0.0012000000569969416, 0.08470000326633453, 0.07829999923706055, -0.10890000313520432, -0.09099999815225601, 0.05420000106096268, -0.024000000208616257, 0.0015999999595806003, 0.038100000470876694, 0.05009999871253967, -0.05810000002384186, 0.025100000202655792, 0.04989999905228615, -0.0032999999821186066, 0.07769999653100967, -0.062199998646974564, 0.024800000712275505, -0.01940000057220459, 0.043699998408555984, -0.14149999618530273, -0.040300000458955765, -0.06539999693632126, -0.0771000012755394, 0.032999999821186066, 0.03669999912381172, 0.017799999564886093, 0.05469999834895134, -0.012199999764561653, 0.09769999980926514, -0.034699998795986176, 0.0013000000035390258, 0.07859999686479568, 0.04650000110268593, 0.020800000056624413, 0.027899999171495438, 0.05590000003576279, -0.1324000060558319, 0.039000000804662704, -0.00800000037997961, 0.09380000084638596, -0.04039999842643738, 0.05460000038146973, 0.03709999844431877, -0.03530000150203705, -0.018400000408291817, 0.010900000110268593, -0.027499999850988388, -0.12129999697208405, -0.016899999231100082, -0.09849999845027924, 0.010700000450015068, 0.06040000170469284, -0.10570000112056732, -0.08479999750852585, 0.042100001126527786, -0.017100000753998756, -0.020600000396370888, -0.15240000188350677, 0.0340999998152256, -0.015699999406933784, 0.011800000444054604, 0.04960000142455101, -0.05139999836683273, 0.1151999980211258, 0.011599999852478504, 0.029200000688433647, 0.05559999868273735, 0.06499999761581421, -0.01759999990463257, -0.004999999888241291, -0.11140000075101852, -0.007899999618530273, -0.052299998700618744, -0.0071000000461936, -0.04430000111460686, -0.07989999651908875, 0.056699998676776886, -0.002199999988079071, -0.06199999898672104, -0.0885000005364418, -0.060600001364946365, -0.03869999945163727, -0.06889999657869339, -0.06459999829530716, -0.0272000003606081, -0.017999999225139618, 0.038100000470876694, 0.04809999838471413, -0.08060000091791153, 0.0689999982714653, -0.07400000095367432, 0.1031000018119812, 0.0020000000949949026, -0.08030000329017639, -0.017400000244379044, 0.007699999958276749, 0.09189999848604202, -0.019700000062584877, -0.031599998474121094, -0.05310000106692314, 0.028300000354647636, 0.04670000076293945, 0.010700000450015068, -0.027000000700354576, -0.05829999968409538, 0.03530000150203705, 0.02850000001490116, -0.03180000185966492, 0.09099999815225601, -0.1054999977350235, -0.0272000003606081, -0.07989999651908875, -0.0502999983727932, -0.0625, 0.06639999896287918, 0.003700000001117587, -0.0010000000474974513, 0.02969999983906746, -0.07940000295639038, 0.016599999740719795, -0.010999999940395355, 0.009999999776482582, 0.09359999746084213, -0.031300000846385956, 0.12070000171661377, -0.020099999383091927, -0.07959999889135361, 0.07569999992847443], [0.0284000001847744, -0.02800000086426735, -0.03620000183582306, 0.03269999846816063, 0.039500001817941666, 0.02319999970495701, 0.09989999979734421, 0.13510000705718994, 0.05820000171661377, 0.032600000500679016, 0.0608999989926815, -0.026000000536441803, 0.026399999856948853, -0.023600000888109207, 0.06639999896287918, 0.06920000165700912, -0.07360000163316727, 0.07890000194311142, -0.03689999878406525, 0.04659999907016754, -0.07519999891519547, 0.07410000264644623, -0.05999999865889549, -0.025499999523162842, 0.05510000139474869, 0.04919999837875366, -0.05510000139474869, 0.051500000059604645, 0.05260000005364418, -0.0908999964594841, 0.03319999948143959, 0.006599999964237213, 0.0027000000700354576, 0.04839999973773956, 0.055799998342990875, -0.012600000016391277, -0.025599999353289604, 0.011300000362098217, -0.08959999680519104, 0.05990000069141388, 0.006500000134110451, -0.05999999865889549, 0.015799999237060547, 0.035599999129772186, 0.014499999582767487, -0.041600000113248825, 0.14270000159740448, -0.0722000002861023, 0.01489999983459711, -0.16439999639987946, 0.058400001376867294, 0.058800000697374344, 0.062300000339746475, 0.08640000224113464, 0.017500000074505806, 0.09600000083446503, 0.018799999728798866, 0.12129999697208405, 0.01759999990463257, -0.004699999932199717, -0.011699999682605267, 0.08579999953508377, 0.03180000185966492, -0.01720000058412552, -0.032499998807907104, 0.08399999886751175, 0.06469999998807907, -0.04490000009536743, -0.11890000104904175, -0.013100000098347664, 0.05649999901652336, 0.03370000049471855, 0.0010000000474974513, -0.04899999871850014, 0.0215000007301569, -0.10450000315904617, -0.04179999977350235, -0.06930000334978104, -0.04450000077486038, -0.010200000368058681, 0.04170000180602074, -0.03660000115633011, 0.006099999882280827, -0.10740000009536743, -0.025699999183416367, -0.022299999371170998, -0.009999999776482582, -0.04089999943971634, -0.12939999997615814, 0.01209999993443489, 0.006099999882280827, 0.15109999477863312, 0.014399999752640724, 0.0017000000225380063, -0.16699999570846558, 0.026399999856948853, 0.10899999737739563, 0.05979999899864197, -0.026399999856948853, -0.006099999882280827, 0.005200000014156103, 0.00570000009611249, 0.06679999828338623, 0.03370000049471855, 0.005799999926239252, 0.00570000009611249, -0.031700000166893005, 0.026799999177455902, -0.09759999811649323, 0.012400000356137753, -0.009700000286102295, 0.03999999910593033, -0.02280000038444996, -0.006899999920278788, -0.04340000078082085, -0.059700001031160355, -0.03009999915957451, 0.13199999928474426, -0.07500000298023224, 0.07000000029802322, 0.00279999990016222, -0.04919999837875366, 0.07349999994039536, 0.09870000183582306, -0.0640999972820282, -0.07859999686479568, -0.04179999977350235, -0.008100000210106373, -0.0038999998942017555, 0.030300000682473183, 0.056299999356269836, -0.05779999867081642, 0.06080000102519989, -0.06350000202655792, -0.05270000174641609, 0.019099999219179153, -0.12160000205039978, -0.006500000134110451, -0.1256999969482422, 0.08810000121593475, -0.09430000185966492, 0.026000000536441803, 0.05490000173449516, 0.07840000092983246, 0.10499999672174454, -0.020899999886751175, 0.0020000000949949026, 0.01860000006854534, 0.02070000022649765, 0.03590000048279762, 0.0032999999821186066, -0.03849999979138374, -0.06430000066757202, 0.07000000029802322, 0.01269999984651804, 0.01080000028014183, 0.02280000038444996, 0.04659999907016754, -0.1290999948978424, 0.061000000685453415, 0.03310000151395798, -0.07980000227689743, -0.020800000056624413, 0.1225999966263771, -0.004100000020116568, -0.0430000014603138, -0.1088000014424324, 0.050700001418590546, 0.015300000086426735, -0.00419999985024333, -0.058800000697374344, -0.07329999655485153, -0.022199999541044235, 0.08540000021457672, 0.025699999183416367, -0.010499999858438969, -0.02410000003874302, -0.07020000368356705, 0.03799999877810478, -0.1510</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>[[[-0.022299999371170998, -0.028300000354647636, -0.01860000006854534, -0.054499998688697815, 0.07450000196695328, -0.04100000113248825, -0.08609999716281891, 0.05900000035762787, -0.06499999761581421, -0.011599999852478504, -0.010999999940395355, -0.027400000020861626, 0.06560000032186508, -0.04039999842643738, -0.06679999828338623, 0.052799999713897705, 0.013899999670684338, 0.0017999999690800905, -0.025100000202655792, -0.04170000180602074, -0.06019999831914902, 0.07320000231266022, 0.02759999968111515, -0.04410000145435333, -0.037300001829862595, 0.0738999992609024, 0.07919999957084656, 0.060499999672174454, -0.01140000019222498, 0.05900000035762787, 0.08190000057220459, -0.07559999823570251, -0.08919999748468399, -0.0031999999191612005, 0.04600000008940697, 0.061500001698732376, 0.020600000396370888, -0.00860000029206276, 0.035599999129772186, 0.0203000009059906, 0.009200000204145908, -0.003599999938160181, -0.002300000051036477, 0.05620000138878822, 0.022600000724196434, -0.015200000256299973, -0.05169999971985817, 0.0026000000070780516, -0.03550000116229057, 0.05079999938607216, -0.06360000371932983, -0.0544000007212162, 0.05530000105500221, -0.09080000221729279, 0.009499999694526196, -0.03480000048875809, 0.05609999969601631, 0.027799999341368675, 0.004999999888241291, -0.04190000146627426, 0.10769999772310257, 0.03840000182390213, -0.009499999694526196, 0.041600000113248825, 0.05730000138282776, 0.009700000286102295, 0.08299999684095383, -0.03519999980926514, 0.0010999999940395355, 0.003800000064074993, -0.052400000393390656, 0.07959999889135361, -0.13079999387264252, -0.03519999980926514, -0.014700000174343586, -0.04010000079870224, -0.06610000133514404, -0.0568000003695488, 0.12210000306367874, -0.09629999846220016, -0.02239999920129776, 0.06549999862909317, -0.01850000023841858, 0.006099999882280827, -0.03590000048279762, -0.02070000022649765, -0.05939999967813492, -0.07500000298023224, 0.0348999984562397, 0.01269999984651804, 0.07349999994039536, -0.09809999912977219, -0.01360000018030405, 0.008899999782443047, -0.06319999694824219, 0.018699999898672104, 0.0142000000923872, -0.00419999985024333, -0.050599999725818634, -0.050999999046325684, 0.04390000179409981, -0.011500000022351742, -0.02019999921321869, 0.006899999920278788, -0.07029999792575836, -0.007499999832361937, -0.047600001096725464, -0.07959999889135361, -0.04560000076889992, 0.011300000362098217, 0.002300000051036477, -0.0038999998942017555, -0.06480000168085098, -0.05290000140666962, 0.07720000296831131, 0.07490000128746033, 0.004100000020116568, 0.048500001430511475, 0.04190000146627426, -0.019099999219179153, -0.039500001817941666, -0.026200000196695328, 0.029899999499320984, -0.04659999907016754, -0.013899999670684338, -0.0697999969124794, 0.03660000115633011, -0.009700000286102295, -0.026200000196695328, 0.03350000083446503, -0.01769999973475933, 0.06340000033378601, -0.011500000022351742, -0.03200000151991844, -0.03139999881386757, -0.09589999914169312, 0.0272000003606081, 9.999999747378752e-05, -0.08129999786615372, 0.008200000040233135, -0.06390000134706497, -0.0012000000569969416, -0.05689999833703041, -0.029400000348687172, -0.061400000005960464, 0.005900000222027302, -0.016899999231100082, -0.0215000007301569, -0.024700000882148743, 0.04899999871850014, 0.030400000512599945, 0.007699999958276749, -9.999999747378752e-05, -0.03150000050663948, 0.01940000057220459, 0.00139999995008111, -0.045499999076128006, 0.07159999758005142, 0.07909999787807465, -0.002199999988079071, 0.012400000356137753, -0.01720000058412552, -0.028699999675154686, -0.004900000058114529, 0.06080000102519989, -0.07859999686479568, 0.027000000700354576, -0.04670000076293945, 0.018300000578165054, -0.06610000133514404, -0.020400000736117363, -0.03660000115633011, -0.09570000320672989, -0.009800000116229057, -0.02410000003874302, -0.04919999837875366, 0.08089999854564667, 0.010900000110268593, -0.06689999997615814, 0.04749999940395355, -0.08299999684095383, 0.08789999783039093, 0.07050000131130219, 0.008100000210106373, -0.08500000089406967, -0.06610000133514404, 0.05849999934434891, 0.007899999618530273, 0.025800000876188278, -0.0949999988079071, -0.06129999831318855, -0.0031999999191612005, -0.04179999977350235, -0.03150000050663948, 0.0007999999797903001, 0.0066999997943639755, 0.022299999371170998, 0.024900000542402267, 0.04619999974966049, 0.06279999762773514, -0.049400001764297485, 0.06480000168085098, -0.08340000361204147, -0.002199999988079071, 0.004800000227987766, 0.0071000000461936, 0.12439999729394913, 0.020899999886751175, -0.013100000098347664, -0.041600000113248825, 0.020400000736117363, 0.0957999974489212, -0.000699999975040555, 0.03359999880194664, -0.007000000216066837, 0.03849999979138374, 0.029899999499320984, 0.024399999529123306, -0.08659999817609787, 0.026200000196695328, -0.016899999231100082, 0.057999998331069946, -0.08100000023841858, 0.018200000748038292, 0.025200000032782555, 0.010900000110268593, 0.032600000500679016, 0.05689999833703041, -0.03959999978542328, 0.028300000354647636, 0.03620000183582306, -0.0066999997943639755, 0.025100000202655792, 0.0031999999191612005, -0.028699999675154686, 0.034299999475479126, -0.051899999380111694, 0.08100000023841858, -0.011900000274181366, 0.017500000074505806, -0.03590000048279762, 0.0851999968290329, -0.019500000402331352, 0.007899999618530273, -0.09070000052452087, -0.016599999740719795, 0.021800000220537186, -0.07530000060796738, -0.013399999588727951, -0.03550000116229057, -0.012199999764561653, -0.045099999755620956, -0.02930000051856041, -0.06880000233650208, -0.03139999881386757, 0.010599999688565731, 0.07670000195503235, -0.025599999353289604, -0.04170000180602074, -0.016899999231100082, -0.0892999991774559, -0.01600000075995922, 0.003800000064074993, 0.06199999898672104], [0.06319999694824219, 0.05829999968409538, -0.017899999395012856, -0.019200000911951065, 0.00430000014603138, 0.053599998354911804, 0.05380000174045563, -0.0013000000035390258, -0.014399999752640724, 0.04490000009536743, -0.042500000447034836, -0.016300000250339508, -0.004100000020116568, 0.06109999865293503, -0.031099999323487282, 0.015599999576807022, -0.05820000171661377, -0.03530000150203705, 0.04839999973773956, -0.011699999682605267, 0.05299999937415123, -0.029600000008940697, 0.04830000177025795, 0.01360000018030405, 0.02590000070631504, 0.01080000028014183, -0.019300000742077827, -0.021900000050663948, -0.06109999865293503, -0.003100000089034438, 0.004800000227987766, 0.1111999973654747, 0.02449999935925007, 0.06430000066757202, -0.024800000712275505, 0.053700000047683716, -0.0763000026345253, -0.06419999897480011, -0.07859999686479568, -0.009399999864399433, 0.026599999517202377, -0.03909999877214432, -0.03550000116229057, -0.009600000455975533, 0.014000000432133675, -0.011699999682605267, 0.07880000025033951, 0.04600000008940697, 0.0215000007301569, -0.07400000095367432, -0.030799999833106995, 0.0038999998942017555, -0.015699999406933784, 0.10409999638795853, 0.044199999421834946, 0.050599999725818634, -0.02459999918937683, -0.01979999989271164, -0.010700000450015068, 0.0869000032544136, -0.03290000185370445, 0.00800000037997961, -0.00019999999494757503, -0.03610000014305115, -0.011599999852478504, 0.03370000049471855, -0.006800000090152025, 0.04100000113248825, -0.05490000173449516, 0.03689999878406525, 0.07249999791383743, -0.053599998354911804, 0.12030000239610672, -0.006099999882280827, 0.032499998807907104, 0.031099999323487282, -0.01940000057220459, -0.0031999999191612005, -0.026799999177455902, 0.05739999935030937, -0.031599998474121094, 0.007499999832361937, -0.0640999972820282, -0.05249999836087227, -0.045499999076128006, -0.019999999552965164, -0.009700000286102295, 0.0731000006198883, -0.07199999690055847, 0.04259999841451645, -0.005499999970197678, 0.08590000122785568, -0.011800000444054604, 0.06080000102519989, 0.0272000003606081, -0.03999999910593033, -0.08460000157356262, -0.05490000173449516, 0.035599999129772186, 0.014800000004470348, 0.031099999323487282, -0.04320000112056732, -0.016200000420212746, 0.03869999945163727, 0.01080000028014183, 0.05790000036358833, -0.010300000198185444, -0.00570000009611249, -0.009100000374019146, -0.022600000724196434, 0.0925000011920929, 0.0414000004529953, 0.00279999990016222, 0.017500000074505806, 0.01759999990463257, -0.004800000227987766, 0.04560000076889992, 0.0007999999797903001, 0.038100000470876694, 0.054999999701976776, -0.02280000038444996, -0.020899999886751175, 0.0026000000070780516, -0.032099999487400055, 0.010200000368058681, 0.03460000082850456, -0.01860000006854534, 0.05790000036358833, -0.04490000009536743, -0.0284000001847744, 0.03700000047683716, -0.07559999823570251, -0.04740000143647194, 0.022700000554323196, 0.023600000888109207, 0.032099999487400055, -0.019899999722838402, -0.05550000071525574, 0.017400000244379044, -0.01549999974668026, -0.008700000122189522, -0.013700000010430813, 0.03400000184774399, -0.007300000172108412, -0.020999999716877937, 0.026799999177455902, -0.03689999878406525, -0.02329999953508377, 0.03880000114440918, -0.00430000014603138, -0.0008999999845400453, 0.053599998354911804, 0.020400000736117363, -0.01510000042617321, -0.011099999770522118, -0.05339999869465828, 0.026100000366568565, -0.013299999758601189, -0.011900000274181366, -0.06620000302791595, 0.01759999990463257, 0.0003000000142492354, 0.02969999983906746, 0.05999999865889549, -0.007300000172108412, 0.0052999998442828655, 0.011599999852478504, -0.014000000432133675, -0.08139999955892563, 0.05490000173449516, 0.04780000075697899, -0.03999999910593033, 0.024700000882148743, -0.021299999207258224, 0.0754999965429306, -0.02810000069439411, -0.0754999965429306, 0.03849999979138374, 0.01679999940097332, 0.02930000051856041, 0.00559999980032444, -0.05820000171661377, 0.002099999925121665, 0.013399999588727951, 0.01209999993443489, -0.010200000368058681, -0.07689999788999557, -0.027899999171495438, 0.014700000174343586, 0.04360000044107437, 0.04439999908208847, -0.07500000298023224, 0.00930000003427267, 0.09610000252723694, 0.019700000062584877, -0.030300000682473183, -0.052799999713897705, 0.020999999716877937, 0.002400000113993883, -0.00419999985024333, -0.005799999926239252, -0.07660000026226044, -0.00430000014603138, 0.03460000082850456, 0.0284000001847744, -0.04619999974966049, -0.11729999631643295, 0.06260000169277191, -0.02710000053048134, 0.01510000042617321, -0.062199998646974564, -0.03440000116825104, 0.056299999356269836, 0.024000000208616257, -0.04989999905228615, 0.04650000110268593, 0.01850000023841858, -0.00559999980032444, -0.0026000000070780516, -0.055399999022483826, 0.04050000011920929, -0.012199999764561653, -0.008200000040233135, 0.07020000368356705, -0.0722000002861023, 0.059300001710653305, -0.040699999779462814, 0.05139999836683273, -0.05000000074505806, -0.03629999980330467, -0.0649000033736229, 0.0625, 0.006500000134110451, -0.003000000026077032, 0.07810000330209732, -0.0142000000923872, -0.02800000086426735, -0.019500000402331352, -0.0340999998152256, -0.007600000128149986, 0.023600000888109207, -0.014800000004470348, -0.029899999499320984, 0.03959999978542328, 0.029600000008940697, 0.06459999829530716, 0.02329999953508377, 0.10360000282526016, 0.0203000009059906, 0.062300000339746475, -0.031199999153614044, -0.03449999913573265, 0.004800000227987766, 0.07639999687671661, -0.014600000344216824, -0.049400001764297485, -0.014800000004470348, -0.048700001090765, 0.007000000216066837, -0.05270000174641609, 0.030799999833106995, -0.04919999837875366, -0.030300000682473183, 0.00139999995008111]], [[-0.06419999897480011, -0.0035000001080334187, -0.05249999836087227, -0.0020000000949949026, 0.013199999928474426, 0.03020000085234642, -0.05000000074505806, 0.010900000110268593, 0.02850000001490116, -0.012900000438094139, -0.13699999451637268, -0.16599999368190765, 0.06159999966621399, 0.012400000356137753, 0.061900001019239426, 0.053300000727176666, 0.0502999983727932, 0.030700000002980232, 0.00279999990016222, 0.04729999974370003, 0.08449999988079071, 0.020099999383091927, 0.03500000014901161, 0.040800001472234726, -0.10980000346899033, 0.044199999421834946, 0.08030000329017639, 0.010599999688565731, 0.02810000069439411, -0.065700002014637, 0.048500001430511475, 0.04439999908208847, 0.02759999968111515, -0.01269999984651804, -0.02250000089406967, 0.012000000104308128, -0.022299999371170998, 0.02539999969303608, -0.0019000000320374966, -0.13840000331401825, -0.05530000105500221, 0.010499999858438969, -0.10570000112056732, -0.006899999920278788, 0.03290000185370445, -0.003100000089034438, -0.029400000348687172, -0.01889999955892563, 0.0031999999191612005, 0.007400000002235174, -0.017799999564886093, 0.06719999760389328, 0.1784999966621399, 0.04479999840259552, 0.10159999877214432, -0.06449999660253525, -0.007400000002235174, -0.007799999788403511, -0.0052999998442828655, -0.06449999660253525, 0.022199999541044235, -0.031199999153614044, -0.06390000134706497, 0.029100000858306885, 0.027000000700354576, 0.11320000141859055, -0.026900000870227814, 0.020999999716877937, 0.01889999955892563, -0.08560000360012054, -0.014999999664723873, 0.08609999716281891, 0.055799998342990875, 0.013799999840557575, -0.10130000114440918, 0.08209999650716782, 0.09529999643564224, 0.09109999984502792, 0.012299999594688416, -0.05469999834895134, -0.016899999231100082, -0.04230000078678131, -0.0027000000700354576, 0.1088000014424324, -0.0066999997943639755, -0.033399999141693115, -0.14550000429153442, -0.08879999816417694, -0.04190000146627426, 0.016499999910593033, 0.22589999437332153, -0.00019999999494757503, 0.0071000000461936, 0.0706000030040741, -0.0860000029206276, -0.08470000326633453, -0.01860000006854534, -0.10119999945163727, 0.04740000143647194, 0.08229999989271164, -0.03709999844431877, 0.029600000008940697, -0.13169999420642853, -0.029400000348687172, 0.06109999865293503, 0.004699999932199717, -0.20350000262260437, -0.03759999945759773, 0.08720000088214874, -0.02759999968111515, 0.005100000184029341, -0.008100000210106373, 0.045099999755620956, -0.004399999976158142, -0.12680000066757202, 0.10740000009536743, 0.12610000371932983, 0.04749999940395355, -0.03139999881386757, 0.024800000712275505, -0.15629999339580536, -0.023499999195337296, -0.009600000455975533, -0.09510000050067902, 0.013199999928474426, -0.019999999552965164, 0.022099999710917473, -0.08969999849796295, -0.06620000302791595, -0.05909999832510948, 0.049400001764297485, -0.05079999938607216, 0.06030000001192093, -0.016899999231100082, -0.03229999914765358, -0.01549999974668026, 0.050700001418590546, 0.009800000116229057, -0.07010000199079514, -0.01899999938905239, -0.024399999529123306, -0.04280000180006027, 0.03519999980926514, 0.003000000026077032, -0.00839999970048666, -0.02199999988079071, 0.13130000233650208, 0.04450000077486038, 0.09309999644756317, -0.0364999994635582, -0.13920000195503235, -0.026799999177455902, 0.000699999975040555, 0.04690000042319298, 0.04129999876022339, -0.007000000216066837, -0.09200000017881393, 0.02630000002682209, -0.06880000233650208, -0.005400000140070915, -0.04560000076889992, -0.03620000183582306, 0.05090000107884407, -0.09369999915361404, -0.016100000590085983, 0.11150000244379044, -0.02810000069439411, -0.0026000000070780516, -0.026900000870227814, -0.04659999907016754, 0.03099999949336052, 0.09300000220537186, 0.017799999564886093, 0.010400000028312206, -0.02250000089406967, -0.07999999821186066, 0.035599999129772186, 0.030300000682473183, -0.09000000357627869, -0.03099999949336052, -0.07050000131130219, 0.004000000189989805, 0.03579999879002571, -0.07289999723434448, 0.02500000037252903, -0.11069999635219574, -0.025699999183416367, 0.023900000378489494, 0.05380000174045563, -0.093299999833107, 0.008500000461935997, -0.006800000090152025, -0.06920000165700912, 0.020600000396370888, -0.02800000086426735, 0.0015999999595806003, -0.01899999938905239, 0.027300000190734863, 0.024299999698996544, -0.04479999840259552, -0.009700000286102295, -0.014499999582767487, -0.0272000003606081, 0.007699999958276749, 0.023099999874830246, -0.07620000094175339, -0.005900000222027302, 0.030899999663233757, -0.06880000233650208, -0.04430000111460686, -0.08179999887943268, -0.04899999871850014, 0.10199999809265137, 0.12099999934434891, 0.16590000689029694, -0.014299999922513962, 0.09799999743700027, 0.015300000086426735, 0.01899999938905239, -0.020999999716877937, 0.026000000536441803, -0.02759999968111515, -0.04360000044107437, -0.006000000052154064, -0.008799999952316284, -0.11379999667406082, -0.039500001817941666, 0.06909999996423721, -0.04690000042319298, -0.01850000023841858, 0.06030000001192093, 0.08950000256299973, 0.040300000458955765, -0.014100000262260437, -0.010400000028312206, 0.0017000000225380063, -0.004100000020116568, 0.08250000327825546, -0.11309999972581863, 0.08479999750852585, 0.0714000016450882, 0.04639999940991402, -0.027699999511241913, -0.18729999661445618, 0.0917000025510788, 0.045499999076128006, 0.06650000065565109, 0.025599999353289604, 0.03739999979734421, 0.07750000059604645, -0.07039999961853027, 0.011900000274181366, -0.09539999812841415, 0.013399999588727951, 0.059700001031160355, -0.12229999899864197, 0.03869999945163727, -0.09279999881982803, -0.03440000116825104, -0.12600000202655792, 0.08839999884366989, 0.06469999998807907, 0.0364999994635582, -0.030700000002980232], [-0.027699999511241913, 0.02449999935925007, -0.0007999999797903001, -0.03500000014901161, 0.04800000041723251, 0.04390000179409981, -0.03220000118017197, -0.062300000339746475, 0.1054999977350235, -0.004800000227987766, -0.05620000138878822, 0.041200000792741776, 0.06560000032186508, -0.08129999786615372, 0.13099999725818634, -0.009499999694526196, 0.020500000566244125, -0.0851999968290329, -0.10790000110864639, 0.08309999853372574, 0.11990000307559967, -0.09399999678134918, -0.0215000007301569, 0.05220000073313713, 0.007799999788403511, 0.039000000804662704, 0.0494999997317791, 0.046300001442432404, 0.10429999977350235, -0.02070000022649765, -0.002099999925121665, -0.11749999970197678, 0.05079999938607216, 0.015699999406933784, 0.12700000405311584, -0.027400000020861626, 0.01489999983459711, 0.1290999948978424, 0.07079999893903732, -0.04749999940395355, 0.007600000128149986, 0.029400000348687172, 0.05739999935030937, -0.003599999938160181, -0.037300001829862595, -0.00570000009611249, 0.03240000084042549, -0.02889999933540821, -0.018699999898672104, -0.022099999710917473, -0.04899999871850014, 0.0348999984562397, -0.007499999832361937, -0.025599999353289604, -0.07119999825954437, -0.0024999999441206455, -0.11980000138282776, 0.07810000330209732, 0.028300000354647636, -0.07050000131130219, -0.02459999918937683, -0.14259999990463257, 0.028999999165534973, 0.0066999997943639755, 0.025200000032782555, 0.03519999980926514, 0.013299999758601189, -0.031199999153614044, 0.049800001084804535, -0.03660000115633011, 0.06639999896287918, 0.03689999878406525, 0.09529999643564224, 0.019099999219179153, 0.0013000000035390258, 0.002400000113993883, -0.0034000000450760126, 0.06790000200271606, 0.038100000470876694, 0.011900000274181366, -0.006000000052154064, 0.09849999845027924, -0.08619999885559082, 0.021700000390410423, -0.056699998676776886, 0.031099999323487282, 0.03060000017285347, 0.006000000052154064, 0.0008999999845400453, 0.0414000004529953, -0.017899999395012856, -0.07150000333786011, -0.05779999867081642, -0.03849999979138374, -0.006099999882280827, 0.1160999983549118, -0.04600000008940697, -0.007400000002235174, 0.006899999920278788, -0.012799999676644802, 0.06759999692440033, 0.03310000151395798, 0.0568000003695488, 0.03189999982714653, 0.006399999838322401, -0.07909999787807465, -0.021299999207258224, -0.018799999728798866, -0.017100000753998756, 0.030799999833106995, 0.015300000086426735, 0.07530000060796738, 0.06920000165700912, -0.10180000215768814, 0.1177000030875206, -0.042500000447034836, 0.020899999886751175, -0.04259999841451645, -0.07289999723434448, -0.011900000274181366, 0.029400000348687172, 0.15880000591278076, 0.02410000003874302, 0.10040000081062317, -0.07509999722242355, 0.0019000000320374966, -0.057100001722574234, -0.07800000160932541, 0.03610000014305115, -0.004900000058114529, 0.05220000073313713, 0.13120000064373016, 0.04879999905824661, 0.008999999612569809, 0.10599999874830246, -0.04320000112056732, -0.1014999970793724, 0.026499999687075615, -0.03970000147819519, 0.0649000033736229, -0.10040000081062317, 0.01730000041425228, -0.06729999929666519, -0.0786999985575676, -0.13510000705718994, 0.042399998754262924, -0.08579999953508377, 0.032499998807907104, 0.03189999982714653, -0.12210000306367874, -0.007699999958276749, 0.021299999207258224, -0.053300000727176666, -0.039000000804662704, 0.04610000178217888, 0.007600000128149986, 0.05040000006556511, -0.041099999099969864, -0.01590000092983246, 0.03680000081658363, -0.07639999687671661, -0.023900000378489494, -0.014600000344216824, -0.05559999868273735, -0.050999999046325684, 0.019999999552965164, 0.0027000000700354576, 0.05620000138878822, -0.013500000350177288, 0.010599999688565731, -0.013000000268220901, -0.02250000089406967, -0.08869999647140503, -0.06080000102519989, 0.09939999878406525, 0.0071000000461936, -0.07119999825954437, -0.11590000241994858, 0.10090000182390213, -0.017799999564886093, 0.027300000190734863, -0.1501999944448471, -0.15330000221729279, -0.053300000727176666, 0.1168999969959259, -0.04190000146627426, 0.06129999831318855, 0.03519999980926514, 0.0142000000923872, -0.029100000858306885, 0.045499999076128006, 0.027300000190734863, 0.016699999570846558, -0.039000000804662704, -0.05869999900460243, 0.0071000000461936, 0.13860000669956207, 0.10010000318288803, -0.030899999663233757, -0.007799999788403511, 0.06040000170469284, 0.09709999710321426, -0.02879999950528145, -0.0877000018954277, -0.08380000293254852, -0.08910000324249268, 0.040800001472234726, 0.055399999022483826, 0.02329999953508377, -0.0071000000461936, 0.06210000067949295, 0.0, 0.04580000042915344, 0.0674000009894371, 0.00139999995008111, -0.1216999962925911, -0.0364999994635582, -0.06069999933242798, 0.11620000004768372, 0.13259999454021454, -0.02669999934732914, -0.002199999988079071, 0.014000000432133675, -0.056699998676776886, 0.016699999570846558, 0.004600000102072954, 0.030899999663233757, 0.028599999845027924, -0.0210999995470047, 0.03739999979734421, -0.07530000060796738, -0.0640999972820282, 0.002300000051036477, 0.02290000021457672, -0.13230000436306, 0.00039999998989515007, 0.14259999990463257, -0.11699999868869781, 0.043699998408555984, 0.03660000115633011, 0.03669999912381172, -0.07500000298023224, 0.12300000339746475, 0.017999999225139618, -0.0003000000142492354, 0.015599999576807022, -0.1177000030875206, -0.0052999998442828655, -0.07689999788999557, -0.12370000034570694, -0.04569999873638153, 0.12849999964237213, 0.15060000121593475, 0.017000000923871994, 0.008100000210106373, 0.09640000015497208, 0.002400000113993883, 0.04540000110864639, 0.11379999667406082, -0.01640000008046627, 0.10369999706745148, 0.019099999219179153, -0.12449999898672104, -0.07090000063180923], [0.09099999815225601, -0.009600000455975533, -0.08269999921321869, -9.999999747378752e-05, -0.03449999913573265, 0.0494999997317791, -0.05640000104904175, -0.043800000101327896, -0.09700000286102295, -0.026200000196695328, 0.02160000056028366, 0.010099999606609344, -0.09040000289678574, -0.06790000200271606, -9.999999747378752e-05, 0.02410000003874302, -0.0024999999441206455, -0.01720000058412552, 0.1185000017285347, 0.0575999990105629, 0.006599999964237213, 0.03840000182390213, 0.002300000051036477, -0.04809999838471413, -0.07699999958276749, -0.0026000000070780516, -0.07010000199079514, -0.05130000039935112, -0.030799999833106995, 0.07980000227689743, 0.059300001710653305, -0.04479999840259552, 0.011800000444054604, -0.012500000186264515, -0.02319999970495701, 0.08129999786615372, 0.017999999225139618, -0.15379999577999115, 0.07209999859333038, 0.020099999383091927, -0.0868000015616417, -0.06279999762773514, 0.04270000010728836, 0.02160000056028366, -0.050700001418590546, 0.09969999641180038, 0.0843999981880188, -0.05249999836087227, 0.01209999993443489, 0.013500000350177288, 0.11479999870061874, 0.007499999832361937, -0.01730000041425228, -0.025299999862909317, 0.03530000150203705, -0.019600000232458115, -0.016499999910593033, 0.029100000858306885, 0.0560000017285347, 0.02800000086426735, 0.06520000100135803, -0.026499999687075615, -0.019899999722838402, -0.043699998408555984, 0.12049999833106995, -0.014999999664723873, 0.038100000470876694, 0.15379999577999115, -0.013199999928474426, -0.0015999999595806003, -0.03009999915957451, 0.021199999377131462, -0.06610000133514404, 0.09040000289678574, 0.019999999552965164, 0.008999999612569809, 0.0348999984562397, -0.012400000356137753, 0.00430000014603138, -0.04899999871850014, -0.15559999644756317, -0.09109999984502792, -0.23970000445842743, 0.07289999723434448, -0.00039999998989515007, -0.1242000013589859, -0.13079999387264252, 0.041099999099969864, -0.040300000458955765, -0.02979999966919422, -0.17319999635219574, 0.03700000047683716, -0.012799999676644802, 0.06040000170469284, 0.01269999984651804, -0.031700000166893005, 0.18700000643730164, 0.019500000402331352, 0.04470000043511391, -0.020899999886751175, 0.1234000027179718, 0.07859999686479568, -0.09910000115633011, -0.025299999862909317, 0.044199999421834946, 0.04470000043511391, -0.04149999842047691, 0.11860000342130661, -0.017400000244379044, 0.09269999712705612, -0.08649999648332596, 0.0989999994635582, -0.03290000185370445, 0.013799999840557575, 0.006899999920278788, 0.0284000001847744, 0.1445000022649765, 0.005200000014156103, 0.010400000028312206, -0.005499999970197678, 0.02979999966919422, 0.02850000001490116, 0.03420000150799751, 0.05079999938607216, 0.10660000145435333, -0.04659999907016754, -0.10540000349283218, -0.1071000024676323, 0.01549999974668026, -0.06790000200271606, 0.009999999776482582, -0.09080000221729279, -0.11789999902248383, -0.06469999998807907, -0.007400000002235174, -0.028300000354647636, 0.013799999840557575, 0.04149999842047691, 0.13850000500679016, -0.05380000174045563, -0.053300000727176666, 0.031300000846385956, -0.03889999911189079, 0.004800000227987766, 0.04360000044107437, 0.004000000189989805, -0.020800000056624413, 0.02319999970495701, -0.01140000019222498, -0.05400000140070915, 0.05460000038146973, -0.08309999853372574, -0.002899999963119626, -0.03400000184774399, 0.04780000075697899, -0.193900004029274, -0.039500001817941666, -0.03310000151395798, -0.05790000036358833, 0.0203000009059906, 0.0421999990940094, 0.0414000004529953, 0.04600000008940697, -0.032099999487400055, 0.09830000251531601, -0.021800000220537186, 0.03610000014305115, 0.06069999933242798, 0.0348999984562397, -0.02160000056028366, 0.011300000362098217, 0.05260000005364418, -0.1362999975681305, 0.03739999979734421, -0.000699999975040555, 0.058400001376867294, -0.019600000232458115, 0.05090000107884407, 0.027400000020861626, -0.010300000198185444, 0.012600000016391277, 0.04280000180006027, 0.026000000536441803, -0.1501999944448471, -0.059300001710653305, -0.07609999924898148, 0.010400000028312206, 0.028699999675154686, -0.15209999680519104, -0.11729999631643295, -0.002400000113993883, -0.006500000134110451, -0.01119999960064888, -0.21850000321865082, 0.007600000128149986, -0.0357000008225441, 0.056299999356269836, 0.025800000876188278, -0.09459999948740005, 0.05990000069141388, 0.00989999994635582, 0.007600000128149986, 0.07360000163316727, 0.08669999986886978, -0.027899999171495438, -0.027400000020861626, -0.08330000191926956, -0.06840000301599503, -0.1005999967455864, -0.0471000000834465, -0.04809999838471413, -0.09960000216960907, 0.1071000024676323, -0.010300000198185444, -0.07670000195503235, -0.12479999661445618, -0.07519999891519547, -0.0908999964594841, -0.054499998688697815, -0.06800000369548798, -0.017000000923871994, -0.0038999998942017555, 0.01549999974668026, 0.09160000085830688, -0.08590000122785568, 0.06960000097751617, -0.11590000241994858, 0.11909999698400497, 0.06270000338554382, -0.08370000123977661, -0.0038999998942017555, 0.031199999153614044, 0.09600000083446503, -0.04800000041723251, -0.004800000227987766, -0.05220000073313713, 0.00839999970048666, 0.05649999901652336, 0.004399999976158142, -0.002199999988079071, -0.05469999834895134, 0.06909999996423721, 0.019899999722838402, -0.0357000008225441, 0.07810000330209732, -0.08370000123977661, 0.010200000368058681, -0.0681999996304512, -0.05909999832510948, -0.07919999957084656, 0.10920000076293945, 0.006000000052154064, -0.017899999395012856, 0.016100000590085983, -0.05550000071525574, 0.006800000090152025, 0.002099999925121665, -0.005499999970197678, 0.07119999825954437, -0.06849999725818634, 0.17440000176429749, -0.025100000202655792, -0.05660000070929527, 0.08959999680519104], [-0.016100000590085983, -0.018400000408291817, -0.0706000030040741, 0.012199999764561653, 0.05460000038146973, 0.06080000102519989, 0.06650000065565109, 0.16060000658035278, 0.019500000402331352, 0.06629999727010727, 0.025699999183416367, -0.05810000002384186, 0.06769999861717224, 0.03530000150203705, 0.04989999905228615, 0.03620000183582306, -0.1145000010728836, 0.10679999738931656, 0.012199999764561653, 0.009700000286102295, -0.03539999946951866, 0.12710000574588776, -0.02889999933540821, -0.031599998474121094, 0.0272000003606081, 0.0608999989926815, -0.023099999874830246, 0.08299999684095383, 0.019200000911951065, -0.05849999934434891, 0.04899999871850014, 0.0697999969124794, -0.01759999990463257, 0.07890000194311142, 0.0035000001080334187, 0.02410000003874302, -0.050999999046325684, -0.026100000366568565, -0.06889999657869339, 0.10459999740123749, 0.03290000185370445, -0.08910000324249268, -0.018799999728798866, 0.07360000163316727, 0.02850000001490116, -0.06849999725818634, 0.15629999339580536, -0.0820000022649765, -0.014800000004470348, -0.21220000088214874, 0.027000000700354576, 0.007300000172108412, 0.07660000026226044, 0.1445000022649765, 0.011500000022351742, 0.1453000009059906, 0.031300000846385956, 0.11749999970197678, -0.019600000232458115, 0.04190000146627426, -0.04569999873638153, 0.13770000636577606, -0.0017000000225380063, -0.065700002014637, -0.00279999990016222, 0.10750000178813934, 0.1177000030875206, -0.02290000021457672, -0.15649999678134918, 0.041099999099969864, 0.10360000282526016, -0.011500000022351742, -0.02370000071823597, -0.06279999762773514, -0.027499999850988388, -0.06560000032186508, -0.01679999940097332, -0.05869999900460243, -0.02850000001490116, -0.05559999868273735, -0.0008999999845400453, 0.002899999963119626, -0.026200000196695328, -0.1501999944448471, -0.06520000100135803, -0.052299998700618744, -0.045499999076128006, -0.06809999793767929, -0.16609999537467957, -0.003100000089034438, 0.03999999910593033, 0.12759999930858612, -0.01850000023841858, 0.039400000125169754, -0.186599999666214, -0.009700000286102295, 0.06790000200271606, 0.011900000274181366, -0.039900001138448715, 0.03319999948143959, -0.053599998354911804, -0.0284000001847744, 0.06849999725818634, -0.0005000000237487257, -0.039500001817941666, 0.03920000046491623, -0.04800000041723251, 0.024000000208616257, -0.13689999282360077, -0.005400000140070915, -0.04650000110268593, 0.03460000082850456, -0.03500000014901161, -0.031099999323487282, -0.07580000162124634, -0.06440000236034393, -0.003000000026077032, 0.13930000364780426, -0.045499999076128006, 0.03830000013113022, -0.051100000739097595, -0.05640000104904175, 0.09880000352859497, 0.11649999767541885, -0.0803999975323677, -0.07039999961853027, -0.08879999816417694, 0.03229999914765358, -0.007000000216066837, -0.008799999952316284, 0.06080000102519989, -0.0934000015258789, 0.016699999570846558, -0.05460000038146973, -0.030700000002980232, 0.009200000204145908, -0.08919999748468399, -0.045899998396635056, -0.1527000069618225, 0.06889999657869339, -0.07769999653100967, -0.009100000374019146, 0.05169999971985817, 0.029999999329447746, 0.06589999794960022, -0.03819999843835831, 0.04439999908208847, -0.01119999960064888, 0.050200000405311584, 0.0674000009894371, -0.03060000017285347, -0.024299999698996544, -0.041600000113248825, 0.025200000032782555, -0.04179999977350235, -0.03620000183582306, -0.0006000000284984708, 0.07199999690055847, -0.08659999817609787, 0.01850000023841858, 0.014800000004470348, -0.09709999710321426, -0.035599999129772186, 0.1451999992132187, 0.01860000006854534, -0.02969999983906746, -0.08160000294446945, 0.0203000009059906, -0.04729999974370003, -0.0333000011742115, -0.018400000408291817, -0.0421999990940094, 0.0038999998942017555, 0.06080000102519989, 0.0925000011920929, -0.0544000007212162, -0.04490000009536743, -0.015200000256299973, 0</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>[0.11835401044516358]</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>[0.2012503574422075]</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>[-0.2664063159986032]</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>[0.2891247042899098]</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>[-2.792066953610636]</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>[1.2410665142668775]</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>[0.26865469857890445]</t>
+        </is>
+      </c>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>[0.16800396480348623]</t>
+        </is>
+      </c>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>[-0.7833797659722512]</t>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr">
+        <is>
+          <t>[0.42294817705431753]</t>
+        </is>
+      </c>
+      <c r="O35" t="inlineStr">
+        <is>
+          <t>[-12.010138744771947]</t>
+        </is>
+      </c>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>[4.277049853338091]</t>
+        </is>
+      </c>
+      <c r="Q35" t="inlineStr">
+        <is>
+          <t>[0.14034963158079294]</t>
+        </is>
+      </c>
+      <c r="R35" t="inlineStr">
+        <is>
+          <t>[0.09269242766859936]</t>
+        </is>
+      </c>
+      <c r="S35" t="inlineStr">
+        <is>
+          <t>[-0.28036857281618577]</t>
+        </is>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>[0.10788429096264575]</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>[0.10950691917162003]</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>[0.08515173614772042]</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>[0.10535908467341137]</t>
+        </is>
+      </c>
+      <c r="X35" t="inlineStr">
+        <is>
+          <t>[0.09372314014679675]</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>[-0.27102527847233193]</t>
+        </is>
+      </c>
+      <c r="Z35" t="inlineStr">
+        <is>
+          <t>[0.10459674977787373]</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>[-0.036766797348358526]</t>
+        </is>
+      </c>
+      <c r="AB35" t="inlineStr">
+        <is>
+          <t>[0.09538708053211423]</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>[-0.3524639228349038]</t>
+        </is>
+      </c>
+      <c r="AD35" t="inlineStr">
+        <is>
+          <t>[0.11333102818661896]</t>
+        </is>
+      </c>
+      <c r="AE35" t="inlineStr">
+        <is>
+          <t>[-0.24175465756716807]</t>
+        </is>
+      </c>
+      <c r="AF35" t="inlineStr">
+        <is>
+          <t>[0.13370975001236327]</t>
+        </is>
+      </c>
+      <c r="AG35" t="inlineStr">
+        <is>
+          <t>[-1.7065253836353644]</t>
+        </is>
+      </c>
+      <c r="AH35" t="inlineStr">
+        <is>
+          <t>[0.20150070236408682]</t>
+        </is>
+      </c>
+      <c r="AI35" t="inlineStr">
+        <is>
+          <t>[-0.555569038046293]</t>
+        </is>
+      </c>
+      <c r="AJ35" t="inlineStr">
+        <is>
+          <t>[0.12747715098656423]</t>
+        </is>
+      </c>
+      <c r="AK35" t="inlineStr">
+        <is>
+          <t>[-0.2491507563130264]</t>
+        </is>
+      </c>
+      <c r="AL35" t="inlineStr">
+        <is>
+          <t>[0.13258820070755653]</t>
+        </is>
+      </c>
+      <c r="AM35" t="inlineStr">
+        <is>
+          <t>[-1.3901607946140655]</t>
+        </is>
+      </c>
+      <c r="AN35" t="inlineStr">
+        <is>
+          <t>[0.1835816767454677]</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>model_264_128_4</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>[264, 128]</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>[[[0.07999999821186066, 0.005799999926239252, -0.07419999688863754, 0.015799999237060547, 0.03500000014901161, -0.018699999898672104, -0.015799999237060547, -0.043299999088048935, 0.013000000268220901, 0.042500000447034836, -0.10080000013113022, 0.057500001043081284, -0.02810000069439411, 0.10559999942779541, -0.01590000092983246, -0.015799999237060547, 0.06909999996423721, 0.006899999920278788, 0.009600000455975533, -0.08489999920129776, -0.06239999830722809, -0.00860000029206276, -0.0658000037074089, 0.037300001829862595, -0.05820000171661377, -0.061500001698732376, 0.04960000142455101, 0.0917000025510788, -0.01510000042617321, -0.06719999760389328, -0.00279999990016222, 0.1103999987244606, 0.04879999905824661, 0.0210999995470047, 0.03229999914765358, 0.1177000030875206, -0.002199999988079071, -0.013399999588727951, 0.054999999701976776, 0.02410000003874302, -0.03189999982714653, -0.027000000700354576, -0.03830000013113022, 0.014999999664723873, -0.030500000342726707, 0.1274999976158142, 0.06849999725818634, -0.05130000039935112, 0.08389999717473984, -0.042500000447034836, 0.09709999710321426, 0.013399999588727951, -0.05310000106692314, -0.001500000013038516, 0.03840000182390213, 0.13680000603199005, -0.07649999856948853, 0.024900000542402267, 9.999999747378752e-05, -0.05130000039935112, -0.0007999999797903001, 0.02800000086426735, 0.0038999998942017555, -0.0908999964594841, -0.07919999957084656, 0.04610000178217888, 0.03669999912381172, 0.004800000227987766, 0.03620000183582306, 0.027799999341368675, 0.05209999904036522, -0.08340000361204147, -0.03959999978542328, -0.012900000438094139, -0.02850000001490116, -0.042100001126527786, 0.05820000171661377, -0.03319999948143959, -0.026900000870227814, 0.04500000178813934, 0.06790000200271606, -0.03180000185966492, -0.009200000204145908, 0.007699999958276749, -0.039500001817941666, -0.05990000069141388, -0.03359999880194664, -0.011699999682605267, -0.013500000350177288, 0.05959999933838844, -0.021900000050663948, -0.013000000268220901, 0.01140000019222498, 0.02800000086426735, 0.03150000050663948, 0.020999999716877937, 0.04569999873638153, -0.006399999838322401, -0.0071000000461936, 0.037300001829862595, 0.01590000092983246, 0.02329999953508377, -0.04969999939203262, -0.04019999876618385, 0.021400000900030136, 0.0689999982714653, -0.015399999916553497, 0.031599998474121094, -0.003599999938160181, -0.07039999961853027, -0.022099999710917473, -0.007899999618530273, 0.01860000006854534, 0.05869999900460243, 0.03709999844431877, -0.014700000174343586, -0.04170000180602074, 0.009999999776482582, 0.017899999395012856, -0.07649999856948853, 0.14429999887943268, -0.003599999938160181, -0.04270000010728836, 0.0284000001847744, -0.10570000112056732, 0.010300000198185444, 0.0272000003606081, -0.049300000071525574, -0.06889999657869339, -0.03480000048875809, 0.006200000178068876, -0.008700000122189522, -0.026100000366568565, 0.1177000030875206, 0.006099999882280827, 0.03889999911189079, 0.07580000162124634, -0.04569999873638153, -0.02329999953508377, 0.040699999779462814, -0.009499999694526196, -0.11670000106096268, -0.015699999406933784, 0.027899999171495438, -0.022199999541044235, 0.05429999902844429, 0.0722000002861023, -0.10029999911785126, 0.09849999845027924, -0.020800000056624413, 0.043800000101327896, 0.006200000178068876, -0.03189999982714653, 0.08900000154972076, 0.022299999371170998, -0.02969999983906746, -0.04699999839067459, 0.011900000274181366, -0.00279999990016222, 0.04699999839067459, 0.0019000000320374966, 0.09210000187158585, 0.026499999687075615, 0.029400000348687172, -0.005400000140070915, -0.0034000000450760126, -0.025699999183416367, -0.0333000011742115, 0.08720000088214874, 0.0406000018119812, 0.01720000058412552, -0.015399999916553497, 0.05620000138878822, 0.013799999840557575, -0.0044999998062849045, 0.08190000057220459, 0.011800000444054604, -0.05869999900460243, 0.05950000137090683, -0.03229999914765358, -0.009600000455975533, 0.07249999791383743, -0.023900000378489494, 0.10589999705553055, -0.0026000000070780516, -0.047200001776218414, 0.05900000035762787, -0.01209999993443489, -0.04749999940395355, 0.029899999499320984, 0.010200000368058681, -0.013799999840557575, -0.002400000113993883, 0.031300000846385956, -0.010700000450015068, 0.02019999921321869, -0.10000000149011612, 0.05730000138282776, -0.054099999368190765, -0.05339999869465828, 0.016899999231100082, -0.03460000082850456, -0.00559999980032444, -0.004800000227987766, 0.03500000014901161, 0.020400000736117363, -0.00279999990016222, 0.15029999613761902, -0.05290000140666962, -0.019700000062584877, -0.029999999329447746, -0.07819999754428864, 0.029899999499320984, 0.0034000000450760126, 0.05869999900460243, 0.014399999752640724, -0.08079999685287476, -0.10639999806880951, 0.02889999933540821, -0.04729999974370003, 0.04820000007748604, -0.04270000010728836, 0.0027000000700354576, -0.0357000008225441, -0.06719999760389328, -0.06639999896287918, 0.04439999908208847, -0.0035000001080334187, 0.0035000001080334187, 0.002899999963119626, -0.028599999845027924, -0.0625, -0.0010000000474974513, 0.10010000318288803, 0.03629999980330467, -0.05090000107884407, 0.11919999867677689, -0.01759999990463257, -0.09849999845027924, 0.04010000079870224, -0.06159999966621399, 0.048900000751018524, 0.014600000344216824, -0.000699999975040555, 0.03480000048875809, 0.02669999934732914, 0.03009999915957451, 0.02590000070631504, -0.03150000050663948, 0.017799999564886093, 0.0, 0.01730000041425228, -0.024800000712275505, -0.028200000524520874, 0.0024999999441206455, 0.017999999225139618, 0.021700000390410423, -0.01860000006854534, -0.07999999821186066, -0.04659999907016754, -0.014999999664723873, -0.10260000079870224, 0.025699999183416367, 0.06729999929666519], [0.08720000088214874, 0.038100000470876694, 0.0357000008225441, -0.004699999932199717, -0.015799999237060547, -0.004100000020116568, -0.033799998462200165, -0.01850000023841858, -0.053300000727176666, 0.027000000700354576, -0.03139999881386757, -0.03680000081658363, -0.04969999939203262, 0.06109999865293503, 0.011099999770522118, -0.032099999487400055, 0.03550000116229057, -0.06889999657869339, -0.07999999821186066, 0.004399999976158142, -0.020600000396370888, 0.04639999940991402, -0.005799999926239252, -9.999999747378752e-05, -0.03150000050663948, -0.010400000028312206, -0.04699999839067459, -0.06239999830722809, -0.06689999997615814, -0.025100000202655792, 0.04259999841451645, -0.11240000277757645, -0.044599998742341995, -0.04149999842047691, -0.06729999929666519, -0.01769999973475933, 0.05810000002384186, -0.042399998754262924, 0.08569999784231186, -0.0478999987244606, 0.032999999821186066, 0.008700000122189522, 0.006500000134110451, -0.014800000004470348, 0.07800000160932541, -0.13220000267028809, 0.014700000174343586, -0.027899999171495438, 0.010099999606609344, 0.0019000000320374966, -0.002400000113993883, 0.026000000536441803, -0.00279999990016222, 0.07500000298023224, 0.06920000165700912, 0.008700000122189522, -0.003000000026077032, -0.02290000021457672, 0.014800000004470348, 0.04859999939799309, 0.052299998700618744, 0.04619999974966049, -0.012799999676644802, -0.01590000092983246, 0.04270000010728836, -0.020600000396370888, -0.027300000190734863, 0.11630000174045563, 0.0551999993622303, 0.003800000064074993, 0.0026000000070780516, 0.057100001722574234, -0.08950000256299973, 0.05530000105500221, 0.0632999986410141, 0.05480000004172325, -0.006500000134110451, 0.04149999842047691, 0.029200000688433647, -0.03759999945759773, -0.03880000114440918, -0.09459999948740005, -0.010499999858438969, 0.008899999782443047, 0.03590000048279762, 0.04179999977350235, 0.07410000264644623, -0.053700000047683716, 0.02199999988079071, -0.07800000160932541, 0.038100000470876694, -0.012000000104308128, 0.07670000195503235, 0.08799999952316284, 0.01810000091791153, 0.016899999231100082, -0.04179999977350235, -0.0044999998062849045, 0.09059999883174896, 0.06499999761581421, -0.0010000000474974513, 0.06620000302791595, 0.005400000140070915, -0.019099999219179153, 0.10029999911785126, 0.003100000089034438, 0.02250000089406967, -0.029500000178813934, 0.08609999716281891, 0.025599999353289604, -0.0835999995470047, -0.010300000198185444, -0.06159999966621399, -0.022700000554323196, -0.08730000257492065, -0.03790000081062317, -0.0617000013589859, -0.07769999653100967, -0.0007999999797903001, 0.017999999225139618, -0.0038999998942017555, -0.017100000753998756, 0.07180000096559525, 0.006399999838322401, 0.04580000042915344, -0.04650000110268593, 0.044599998742341995, -0.01810000091791153, 0.0071000000461936, -0.034299999475479126, -0.014299999922513962, 0.06610000133514404, -0.021800000220537186, -0.013000000268220901, -0.0934000015258789, -0.047200001776218414, -0.009100000374019146, -0.05490000173449516, -0.0681999996304512, 0.012900000438094139, 0.050999999046325684, -0.025699999183416367, -0.04490000009536743, -0.07859999686479568, -0.04439999908208847, 0.00570000009611249, 0.02969999983906746, -0.017400000244379044, -0.030400000512599945, -0.009100000374019146, -0.04500000178813934, -0.003100000089034438, 0.009800000116229057, -0.03449999913573265, 0.025200000032782555, -0.03350000083446503, 0.03290000185370445, 0.016899999231100082, -0.07199999690055847, -0.04010000079870224, -0.06260000169277191, 0.13169999420642853, -0.0034000000450760126, 0.08290000259876251, 0.03350000083446503, 0.06270000338554382, 0.11169999837875366, -0.020500000566244125, 0.007000000216066837, 0.1889999955892563, -0.029899999499320984, 0.05990000069141388, 0.08980000019073486, -0.02449999935925007, -0.04560000076889992, 0.08380000293254852, -0.013799999840557575, -0.013899999670684338, -0.08630000054836273, -0.014399999752640724, 0.00019999999494757503, -0.04360000044107437, 0.10830000042915344, -0.04170000180602074, 0.09369999915361404, -0.0949999988079071, 0.01730000041425228, 0.054999999701976776, -0.0032999999821186066, -0.01209999993443489, 0.042899999767541885, -0.01080000028014183, 0.00419999985024333, 0.00559999980032444, -0.04690000042319298, -0.011099999770522118, 0.07760000228881836, 0.0034000000450760126, -0.005900000222027302, 0.028999999165534973, -0.04149999842047691, -0.026599999517202377, 0.051100000739097595, 0.03739999979734421, -0.07670000195503235, -0.05290000140666962, 0.04410000145435333, -0.04450000077486038, -0.05389999970793724, 0.06750000268220901, -0.004000000189989805, -0.04670000076293945, 0.09049999713897705, -0.024299999698996544, -0.04410000145435333, 0.02850000001490116, 0.037700001150369644, 0.025800000876188278, -0.07689999788999557, -0.05640000104904175, -0.05260000005364418, -0.05389999970793724, -0.055399999022483826, -0.05649999901652336, 0.004000000189989805, -0.04360000044107437, -0.012500000186264515, 0.06780000030994415, -0.04839999973773956, -0.020800000056624413, 0.06499999761581421, -0.03669999912381172, -0.08070000261068344, 0.07029999792575836, 0.050999999046325684, -0.0812000036239624, 0.053300000727176666, 0.059300001710653305, -0.004100000020116568, 0.02070000022649765, 0.01860000006854534, -0.0005000000237487257, -0.05739999935030937, -0.0020000000949949026, -0.02449999935925007, -0.01269999984651804, -0.012400000356137753, -0.061400000005960464, -0.0012000000569969416, -0.024000000208616257, 0.02979999966919422, -0.08410000056028366, 0.018200000748038292, -0.07240000367164612, 0.01119999960064888, -0.0052999998442828655, -0.08649999648332596, 0.002099999925121665, -0.009800000116229057, 0.012500000186264515, -0.019999999552965164, 0.013100000098347664, 0.07010000199079514, -0.06469999998807907]], [[0.08969999849796295, -0.06499999761581421, 0.01510000042617321, 0.007199999876320362, -0.011300000362098217, 0.07259999960660934, 0.06210000067949295, 0.00019999999494757503, -0.05429999902844429, -0.021199999377131462, 0.028300000354647636, 0.0421999990940094, 0.08049999922513962, 0.021800000220537186, -0.008700000122189522, 0.013100000098347664, 0.009700000286102295, 0.015399999916553497, 0.01940000057220459, -0.008100000210106373, -0.08669999986886978, 0.011500000022351742, -0.015399999916553497, 0.06340000033378601, -0.00839999970048666, 0.045099999755620956, -0.03660000115633011, -0.03229999914765358, -0.05730000138282776, -0.042100001126527786, 0.058800000697374344, 0.05130000039935112, -0.04439999908208847, 0.012600000016391277, -0.0364999994635582, 0.10220000147819519, 0.03739999979734421, 0.04190000146627426, -0.07819999754428864, 0.08009999990463257, 0.02889999933540821, -0.10140000283718109, 0.05790000036358833, -0.1339000016450882, 0.004600000102072954, 0.011099999770522118, 0.07199999690055847, -0.03280000016093254, -0.050700001418590546, 0.0215000007301569, 0.1006999984383583, 0.03240000084042549, -0.06870000064373016, 0.015200000256299973, 0.027899999171495438, 0.07660000026226044, -0.13770000636577606, 0.02850000001490116, 0.02850000001490116, 0.07720000296831131, -0.0632999986410141, 0.01940000057220459, 0.0027000000700354576, -0.014600000344216824, 0.0478999987244606, 0.08669999986886978, -0.11900000274181366, 0.03669999912381172, -0.08429999649524689, 0.06040000170469284, 0.06449999660253525, 0.010499999858438969, -0.05009999871253967, -0.009499999694526196, 0.009800000116229057, -0.023900000378489494, -0.13670000433921814, 0.039900001138448715, -0.02280000038444996, -0.029200000688433647, -0.02979999966919422, 0.05900000035762787, 0.016699999570846558, -0.020500000566244125, 0.05009999871253967, 0.048700001090765, 0.0892999991774559, -0.04399999976158142, -0.03420000150799751, 0.05389999970793724, 0.029400000348687172, 0.1103999987244606, 0.010300000198185444, 0.025800000876188278, 0.09099999815225601, -0.043699998408555984, -0.03229999914765358, 0.08169999718666077, 0.12839999794960022, 0.017500000074505806, -0.10849999636411667, -0.023800000548362732, 0.019500000402331352, 0.0, -0.010900000110268593, -0.06629999727010727, 0.10840000212192535, -0.007899999618530273, 0.05079999938607216, 0.09510000050067902, 0.08229999989271164, 0.009499999694526196, 0.13779999315738678, 0.04610000178217888, -0.026499999687075615, 0.032099999487400055, -0.04989999905228615, 0.0560000017285347, 0.05510000139474869, 0.08129999786615372, 0.03460000082850456, -0.06599999964237213, -0.04540000110864639, 0.06440000236034393, 0.022700000554323196, -0.05290000140666962, 0.048700001090765, 0.00989999994635582, -0.16429999470710754, 0.05050000175833702, 0.14910000562667847, -0.10520000010728836, 0.042899999767541885, -0.0908999964594841, 0.02710000053048134, -0.14560000598430634, 0.009399999864399433, -0.04439999908208847, 0.01209999993443489, 0.022700000554323196, -0.0430000014603138, -0.031300000846385956, -0.052400000393390656, -0.030300000682473183, 0.04349999874830246, -0.005400000140070915, 0.019999999552965164, -0.06210000067949295, 0.12439999729394913, 0.0015999999595806003, 0.042399998754262924, -0.02539999969303608, 0.044199999421834946, 0.06639999896287918, -0.09200000017881393, -0.10360000282526016, 0.02800000086426735, -0.06530000269412994, -0.024399999529123306, 0.012600000016391277, -0.050200000405311584, 0.011800000444054604, -0.07859999686479568, 0.05260000005364418, 0.04050000011920929, 0.045899998396635056, 0.0568000003695488, -0.040699999779462814, -0.048700001090765, -0.07599999755620956, -0.09099999815225601, -0.01679999940097332, 0.06289999932050705, -0.0012000000569969416, -0.12530000507831573, -0.011500000022351742, 0.020500000566244125, 0.02630000002682209, -0.09189999848604202, 0.017500000074505806, 0.06700000166893005, -0.06069999933242798, 0.07769999653100967, 0.0024999999441206455, -0.0868000015616417, 0.065700002014637, -0.003000000026077032, 0.04450000077486038, 0.1289999932050705, 0.1868000030517578, -0.10249999910593033, 0.031300000846385956, -0.11500000208616257, -0.025100000202655792, 0.07329999655485153, -0.03880000114440918, 0.006200000178068876, -0.018799999728798866, -0.048500001430511475, 0.02879999950528145, 0.01940000057220459, -0.05649999901652336, 0.004399999976158142, -0.03220000118017197, -0.003700000001117587, -0.10419999808073044, -0.01489999983459711, -0.010499999858438969, 0.020899999886751175, -0.0203000009059906, 0.018799999728798866, 0.06390000134706497, -0.13230000436306, 0.0803999975323677, -0.006500000134110451, -0.02590000070631504, 0.05209999904036522, 0.11309999972581863, -0.04129999876022339, -0.06030000001192093, -0.03889999911189079, 0.06639999896287918, 0.02419999986886978, -0.036400001496076584, 0.09489999711513519, -0.039500001817941666, 0.00930000003427267, -0.048500001430511475, 0.052000001072883606, -0.014299999922513962, 0.01209999993443489, -0.03830000013113022, 0.07959999889135361, 0.006300000008195639, -0.033900000154972076, -0.06310000270605087, -0.008200000040233135, 0.002300000051036477, 0.05420000106096268, 0.07079999893903732, 0.015399999916553497, -0.037300001829862595, 0.05620000138878822, -0.057999998331069946, -0.027699999511241913, 0.05640000104904175, -0.03590000048279762, -0.021400000900030136, 0.1151999980211258, -0.06210000067949295, -0.2125999927520752, -0.09040000289678574, -0.0010000000474974513, 0.015300000086426735, -0.02539999969303608, 0.08410000056028366, -0.07460000365972519, -0.024900000542402267, 0.024900000542402267, 0.0877000018954277, -0.07410000264644623, -0.017500000074505806, 0.06780000030994415, -0.010200000368058681], [0.051600001752376556, -0.07670000195503235, 0.03139999881386757, -0.026599999517202377, 0.04690000042319298, -0.07419999688863754, -0.10080000013113022, -0.09700000286102295, -0.011500000022351742, 0.0723000019788742, -0.03700000047683716, 0.0949999988079071, -0.06040000170469284, -0.0024999999441206455, 0.012199999764561653, 0.026799999177455902, 0.01489999983459711, -0.056299999356269836, -0.014299999922513962, -0.01679999940097332, 0.019700000062584877, 0.010700000450015068, -0.09430000185966492, 0.10909999907016754, 0.010200000368058681, -0.03519999980926514, 0.03779999911785126, 0.05979999899864197, -0.030799999833106995, -0.00559999980032444, -0.0794999971985817, 0.058800000697374344, -0.034299999475479126, -0.0034000000450760126, 0.04360000044107437, -0.06599999964237213, -0.006099999882280827, 0.05810000002384186, -0.010499999858438969, -0.07419999688863754, -0.09210000187158585, 0.049800001084804535, -0.013799999840557575, -0.0019000000320374966, -0.061500001698732376, -0.010599999688565731, 0.052400000393390656, 0.08590000122785568, -0.13040000200271606, -0.10769999772310257, -0.031199999153614044, 0.0333000011742115, 0.13220000267028809, -0.002300000051036477, 0.053599998354911804, 0.00419999985024333, -0.04050000011920929, 0.00430000014603138, -0.028999999165534973, -0.025200000032782555, -0.0478999987244606, -0.03629999980330467, 0.04179999977350235, -0.11100000143051147, -0.03200000151991844, 0.03959999978542328, -0.09440000355243683, -0.06960000097751617, 0.002199999988079071, -0.03929999843239784, 0.03099999949336052, 0.04039999842643738, -0.0877000018954277, 0.13600000739097595, -0.02419999986886978, 0.026900000870227814, -0.05660000070929527, -0.0066999997943639755, 0.021800000220537186, -0.03020000085234642, -0.0284000001847744, 0.033799998462200165, 0.05689999833703041, 0.07360000163316727, 0.07259999960660934, -0.1485999971628189, 0.00930000003427267, 0.06710000336170197, 0.021900000050663948, -0.005499999970197678, 0.10670000314712524, -0.025800000876188278, 0.061400000005960464, -0.07649999856948853, 0.051100000739097595, -0.039799999445676804, 0.07980000227689743, -0.026399999856948853, 0.04780000075697899, 0.05209999904036522, -0.037700001150369644, 0.02850000001490116, 0.04529999941587448, -0.12809999287128448, -0.09189999848604202, 0.03519999980926514, 0.05820000171661377, -0.03290000185370445, -0.0502999983727932, -0.0017000000225380063, -0.019500000402331352, 0.03139999881386757, 0.06859999895095825, -0.10980000346899033, -0.0746999979019165, -0.17249999940395355, -0.0794999971985817, -0.07850000262260437, 0.010499999858438969, 0.020400000736117363, -0.011900000274181366, 0.050200000405311584, -0.02290000021457672, -0.05990000069141388, -0.033900000154972076, -0.09390000253915787, 0.061799999326467514, -0.040300000458955765, -0.09149999916553497, 0.08460000157356262, -0.00839999970048666, 0.023399999365210533, 0.0908999964594841, -0.008799999952316284, 0.11060000211000443, 0.03660000115633011, 0.0430000014603138, 0.03700000047683716, -0.039799999445676804, -0.00139999995008111, 0.0008999999845400453, -0.04390000179409981, 0.0044999998062849045, -0.08049999922513962, -0.04839999973773956, 0.0754999965429306, 0.05700000002980232, 0.11509999632835388, 0.009800000116229057, 0.10779999941587448, -0.08110000193119049, 0.05559999868273735, -0.026799999177455902, 0.05510000139474869, 0.04089999943971634, -0.10239999741315842, 0.03319999948143959, -0.022600000724196434, 0.011300000362098217, 0.0608999989926815, 0.004800000227987766, 0.016699999570846558, 0.04910000041127205, -0.011800000444054604, 0.05869999900460243, -0.1770000010728836, -0.13269999623298645, -0.11299999803304672, -0.003599999938160181, 0.013700000010430813, 0.06469999998807907, -0.04230000078678131, -0.07339999824762344, 0.1137000024318695, 0.07989999651908875, 0.008899999782443047, 0.12849999964237213, 0.10660000145435333, 0.1454000025987625, 0.025699999183416367, -0.014100000262260437, 0.014999999664723873, -0.04270000010728836, -0.022600000724196434, -0.0997999981045723, -0.049800001084804535, -0.031700000166893005, -0.13210000097751617, 0.016599999740719795, -0.04780000075697899, -0.06589999794960022, 0.0625, -0.08510000258684158, -0.0032999999821186066, 0.07850000262260437, 0.012500000186264515, -0.07739999890327454, -0.07760000228881836, 0.05779999867081642, 0.010999999940395355, 0.0006000000284984708, -0.0940999984741211, 0.04309999942779541, -0.07270000129938126, 0.019600000232458115, 0.011099999770522118, -0.06880000233650208, -0.012299999594688416, -0.08649999648332596, -0.008899999782443047, 0.07320000231266022, 0.0406000018119812, 0.06129999831318855, 0.011800000444054604, -0.018799999728798866, -0.00559999980032444, -0.0658000037074089, -0.05700000002980232, -0.039000000804662704, 0.004699999932199717, -0.004600000102072954, -0.09520000219345093, 0.020899999886751175, -0.10649999976158142, -0.009700000286102295, -0.009700000286102295, -0.019300000742077827, -0.02759999968111515, -0.09300000220537186, -0.015200000256299973, -0.013700000010430813, -0.022700000554323196, -0.06780000030994415, -0.008899999782443047, -0.10249999910593033, -0.04490000009536743, 0.0035000001080334187, -0.015599999576807022, 0.04360000044107437, 0.0940999984741211, -0.0012000000569969416, 0.08219999819993973, -0.05220000073313713, -0.006399999838322401, 0.07769999653100967, -0.08489999920129776, -0.0071000000461936, 0.05559999868273735, 0.11289999634027481, -0.08810000121593475, 0.01080000028014183, 0.05920000001788139, -0.019200000911951065, -0.060600001364946365, -0.05900000035762787, -0.008500000461935997, 0.02979999966919422, -0.03840000182390213, -0.07819999754428864, 0.033900000154972076, -0.02979999966919422, 0.008500000461935997, -0.00800000037997961, -0.09130000323057175], [-0.007000000216066837, 0.033900000154972076, -0.027899999171495438, -0.024900000542402267, 0.04390000179409981, -0.08560000360012054, 0.010900000110268593, 0.02070000022649765, 0.061500001698732376, 0.0020000000949949026, 0.0272000003606081, -0.06279999762773514, 0.09229999780654907, -0.06449999660253525, -0.01549999974668026, 0.07880000025033951, 0.052799999713897705, 0.008999999612569809, 0.03669999912381172, -0.05050000175833702, -0.09650000184774399, 0.06449999660253525, 0.033799998462200165, -0.02930000051856041, 0.02019999921321869, 0.013700000010430813, -0.02019999921321869, 0.07159999758005142, -0.021199999377131462, -0.015399999916553497, -0.02160000056028366, -0.0007999999797903001, -0.1324000060558319, 0.11590000241994858, -0.0038999998942017555, -0.0771000012755394, 0.05380000174045563, -0.007199999876320362, 0.10050000250339508, 0.1680999994277954, 0.004900000058114529, 0.05420000106096268, 0.03840000182390213, -0.034299999475479126, -0.1225999966263771, -0.0738999992609024, 0.13330000638961792, 0.0210999995470047, -0.11559999734163284, -0.03929999843239784, -0.05139999836683273, 0.06589999794960022, -0.01769999973475933, 0.08129999786615372, -0.060600001364946365, -0.02160000056028366, -0.01549999974668026, 0.005900000222027302, -0.07249999791383743, 0.13210000097751617, 0.14419999718666077, -0.009700000286102295, 0.008899999782443047, -0.06830000132322311, -0.030899999663233757, -0.08420000225305557, 0.04019999876618385, 0.020999999716877937, 0.02019999921321869, 0.09139999747276306, 0.08290000259876251, -0.009999999776482582, -0.02239999920129776, 0.014800000004470348, 0.12600000202655792, 0.06480000168085098, -0.08309999853372574, -0.025200000032782555, -0.054499998688697815, 0.06599999964237213, -0.03849999979138374, -0.02810000069439411, 0.11500000208616257, 0.01600000075995922, -0.048500001430511475, -0.024299999698996544, 0.06530000269412994, -0.0625, -0.022199999541044235, -0.07900000363588333, -0.0494999997317791, -0.04809999838471413, -0.07109999656677246, -0.016699999570846558, 0.0414000004529953, -0.017500000074505806, 0.017799999564886093, -0.03660000115633011, 0.010700000450015068, -0.08760000020265579, 0.01140000019222498, 0.06390000134706497, 0.0617000013589859, -0.01720000058412552, -0.0027000000700354576, -0.04270000010728836, 0.013100000098347664, -0.03290000185370445, 0.037300001829862595, -0.018200000748038292, -0.09969999641180038, -0.04349999874830246, -0.11100000143051147, 0.03269999846816063, -0.03620000183582306, 0.029400000348687172, -0.00430000014603138, 0.06260000169277191, 0.051500000059604645, -0.01489999983459711, 0.03739999979734421, 0.08879999816417694, 0.0007999999797903001, -0.0649000033736229, 0.05909999832510948, -0.006099999882280827, 0.0649000033736229, 0.023099999874830246, -0.06360000371932983, -0.08290000259876251, 0.01730000041425228, 0.026000000536441803, 0.08349999785423279, 0.13930000364780426, -0.018699999898672104, -0.15160000324249268, 0.00930000003427267, -0.004999999888241291, -0.06800000369548798, 0.008200000040233135, -0.028699999675154686, 0.004699999932199717, 0.019099999219179153, 0.026000000536441803, 0.05590000003576279, 0.02930000051856041, -0.03150000050663948, -0.06499999761581421, -0.03440000116825104, -0.07970000058412552, -0.03180000185966492, -0.015599999576807022, 0.04820000007748604, 0.10459999740123749, 0.11860000342130661, 0.046799998730421066, -0.07750000059604645, 0.0568000003695488, -0.10570000112056732, 0.031099999323487282, 0.010300000198185444, -0.021800000220537186, 0.05339999869465828, 0.0, 0.03009999915957451, 0.13130000233650208, 0.027799999341368675, -0.09629999846220016, 0.042899999767541885, -0.031099999323487282, 0.009399999864399433, 0.055399999022483826, 0.0706000030040741, -0.017999999225139618, -0.11479999870061874, -0.010400000028312206, -0.06030000001192093, 0.03620000183582306, -0.043299999088048935, -0.033799998462200165, -0.06909999996423721, -0.01360000018030405, -0.05909999832510948, 0.0142000000923872, -0.058400001376867294, -0.003599999938160181, 0.02070000022649765, 0.019300000742077827, -0.08129999786615372, 0.006599999964237213, -0.15479999780654907, -0.016599999740719795, 0.060100000351667404, -0.015599999576807022, -0.03819999843835831, -0.02669999934732914, -0.04839999973773956, -0.06589999794960022, 0.03460000082850456, -0.049400001764297485, -0.04619999974966049, 0.061000000685453415, 0.05909999832510948, 0.03680000081658363, -0.004399999976158142, -0.030899999663233757, -0.12790000438690186, -0.04100000113248825, -0.05559999868273735, -0.00139999995008111, -0.06930000334978104, -0.02280000038444996, -0.07360000163316727, -0.09300000220537186, -0.03709999844431877, -0.0012000000569969416, -0.042100001126527786, -0.032099999487400055, 0.12839999794960022, 0.028999999165534973, -0.0142000000923872, -0.0015999999595806003, -0.043299999088048935, -0.09390000253915787, -0.14990000426769257, 0.05869999900460243, 0.031700000166893005, 0.023900000378489494, 0.05040000006556511, 0.06300000101327896, -0.10790000110864639, 0.0681999996304512, -0.035100001841783524, -0.029200000688433647, -0.08139999955892563, 0.019099999219179153, -0.09849999845027924, -0.08470000326633453, -0.0052999998442828655, 0.11909999698400497, -0.029899999499320984, 0.06369999796152115, 0.039000000804662704, 0.033799998462200165, -0.013399999588727951, -0.03920000046491623, 0.008500000461935997, -0.09950000047683716, 0.029400000348687172, -0.1476999968290329, -0.011800000444054604, 0.025800000876188278, -0.0471000000834465, -0.029999999329447746, 0.07819999754428864, 0.0957999974489212, 0.057500001043081284, 0.10000000149011612, 0.01720000058412552, -0.11400000005960464, 0.10189999639987946, 0.02199999988079071, -0.057999998331069946, -0.04520000144839287], [-0.06549999862909317, -0.07339999824762344, -0.05889999866485596, -0.018300000578165054, -0.09880000352859497, 0.04470000043511391, -0.003100000089034438, -0.14059999585151672, 0.03889999911189079, 0.05090000107884407, 0.041200000792741776, 0.030899999663233757, -0.006899999920278788, 0.09600000083446503, -0.13619999587535858, -0.010900000110268593, -0.08720000088214874, -0.061500001698732376, -0.010900000110268593, 0.017799999564886093, 0.006099999882280827, -0.06109999865293503, 0.007199999876320362, -0.09520000219345093, -0.12880000472068787, 0.013100000098347664, 0.03689999878406525, 0.05790000036358833, -0.003000000026077032, -0.0272000003606081, -0.024399999529123306, -0.016699999570846558, -0.040699999779462814, 0.07769999653100967, -0.05420000106096268, 0.08619999885559082, -0.061500001698732376, 0.028599999845027924, -0.07069999724626541, -0.12319999933242798, -0.035100001841783524, 0.027499999850988388, -0.04430000111460686, 0.029999999329447746, -0.008200000040233135, -0.07090000063180923, 0.061799999326467514, 0.09589999914169312, 0.03150000050663948, -0.004100000020116568, -0.007799999788403511, 0.11879999935626984, -0.045099999755620956, -0.08470000326633453, -0.03720000013709068, -0.014600000344216824, 0.12099999934434891, -0.01899999938905239, -0.012299999594688416, -0.1266999989748001, 0.1111999973654747, -0.07429999858140945, -0.08619999885559082, -0.14339999854564667, -0.09679999947547913, 0.05130000039935112, 0.12540000677108765, 0.03689999878406525, -0.04360000044107437, -0.010700000450015068, 0.10140000283718109, -0.041099999099969864, 0.11100000143051147, -0.02160000056028366, -0.054499998688697815, -0.07450000196695328, -0.0625, 0.02669999934732914, 0.0966000035405159, 0.10790000110864639, 0.10649999976158142, -0.009100000374019146, 0.06710000336170197, 0.048700001090765, -0.0026000000070780516, -0.11739999800920486, -0.0035000001080334187, -0.07509999722242355, 0.03739999979734421, 0.07429999858140945, -0.003100000089034438, -0.019300000742077827, -0.08820000290870667, -0.006300000008195639, 0.0421999990940094, -0.03660000115633011, -0.043699998408555984, 0.14079999923706055, 0.05640000104904175, -0.12150000035762787, -0.05339999869465828, -0.026499999687075615, -0.005900000222027302, -0.061799999326467514, 0.018699999898672104, 0.00019999999494757503, 0.05079999938607216, -0.04659999907016754, -0.0027000000700354576, 0.02969999983906746, -0.12020000070333481, 0.01979999989271164, 0.01769999973475933, 0.031199999153614044, -0.09709999710321426, 0.09459999948740005, 0.021299999207258224, 0.05990000069141388, -0.09470000118017197, 0.010200000368058681, 0.07010000199079514, -0.010900000110268593, -0.055799998342990875, -0.04560000076889992, -0.0010999999940395355, 0.0017000000225380063, -0.08470000326633453, 0.06939999759197235, -0.009399999864399433, 0.012400000356137753, -0.014000000432133675, -0.09200000017881393, -0.05090000107884407, 0.015699999406933784, -0.01730000041425228, 0.029400000348687172, -0.012600000016391277, 0.09109999984502792, -0.08659999817609787, 0.11509999632835388, -0.02419999986886978, -0.025499999523162842, 0.003700000001117587, -0.07100000232458115, 0.03669999912381172, -0.0284000001847744, 0.055399999022483826, -0.023800000548362732, -0.05660000070929527, 0.01269999984651804, 0.07109999656677246, 0.007199999876320362, -0.014999999664723873, -0.014399999752640724, 0.06840000301599503, -0.02370000071823597, 0.06369999796152115, 0.054099999368190765, 0.09839999675750732, 0.007199999876320362, -0.04390000179409981, -0.03620000183582306, 0.0008999999845400453, -0.009600000455975533, -0.04399999976158142, -0.008999999612569809, 0.09790000319480896, 0.01600000075995922, 0.022099999710917473, -0.029600000008940697, -0.04039999842643738, 0.0674000009894371, -0.03189999982714653, 0.013500000350177288, 0.005499999970197678, 0.031199999153614044, 0.09399999678134918, 0.12309999763965607, -0.06889999657869339, -0.013500000350177288, 0.00719</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>[[[0.010599999688565731, -0.057100001722574234, -0.07039999961853027, -0.033799998462200165, 0.002199999988079071, 0.013299999758601189, 0.020400000736117363, 0.0052999998442828655, 0.0284000001847744, 0.004699999932199717, -0.07159999758005142, 0.03460000082850456, 0.026799999177455902, 0.06620000302791595, 0.01140000019222498, 0.0026000000070780516, 0.010200000368058681, 0.07720000296831131, 0.09719999879598618, -0.03579999879002571, -0.03579999879002571, -0.07109999656677246, -0.04749999940395355, 0.012500000186264515, -0.012199999764561653, -0.033399999141693115, 0.07840000092983246, 0.04360000044107437, 0.019600000232458115, -0.008700000122189522, -0.051100000739097595, 0.12039999663829803, 0.06210000067949295, 0.015200000256299973, 0.04490000009536743, 0.08489999920129776, -0.035100001841783524, 0.05310000106692314, 0.011900000274181366, 0.042399998754262924, -0.054499998688697815, -0.021700000390410423, -0.002899999963119626, 0.0006000000284984708, -0.11309999972581863, 0.12150000035762787, -0.00800000037997961, -0.023099999874830246, 0.055399999022483826, 0.009200000204145908, 0.04349999874830246, -0.010099999606609344, 0.010599999688565731, -0.06589999794960022, -0.01269999984651804, 0.07349999994039536, -0.04390000179409981, 0.05810000002384186, -0.032099999487400055, -0.08860000222921371, -0.061000000685453415, 0.005799999926239252, 0.020899999886751175, -0.03799999877810478, -0.045499999076128006, 0.00860000029206276, 0.02419999986886978, -0.07930000126361847, -0.04450000077486038, -0.005799999926239252, 0.01549999974668026, -0.041200000792741776, 0.017500000074505806, -0.03310000151395798, -0.0737999975681305, -0.0608999989926815, 0.02879999950528145, -0.07349999994039536, -0.015200000256299973, 0.039000000804662704, 0.050599999725818634, 0.012400000356137753, 0.005100000184029341, -0.022199999541044235, -0.07739999890327454, -0.08320000022649765, -0.10220000147819519, 0.06199999898672104, -0.0052999998442828655, 0.06930000334978104, -0.02250000089406967, 0.01940000057220459, -0.0364999994635582, -0.009999999776482582, -0.014800000004470348, -0.01600000075995922, 0.06310000270605087, -0.02879999950528145, -0.0617000013589859, -0.020400000736117363, -0.02410000003874302, -0.019200000911951065, -0.016200000420212746, 0.01590000092983246, -0.05249999836087227, 0.07159999758005142, -0.04540000110864639, 0.02669999934732914, -0.0812000036239624, -0.045099999755620956, 0.02590000070631504, -0.020099999383091927, 0.09749999642372131, 0.03240000084042549, 0.10220000147819519, 0.041999999433755875, -0.014100000262260437, 0.04129999876022339, 0.03840000182390213, -0.03460000082850456, 0.11640000343322754, 0.0071000000461936, -0.10620000213384628, 0.01730000041425228, -0.08150000125169754, 0.021900000050663948, -0.046799998730421066, 0.012199999764561653, -0.0020000000949949026, 0.026000000536441803, 0.050200000405311584, -0.07590000331401825, 0.02630000002682209, 0.08699999749660492, 0.034299999475479126, 0.06300000101327896, 0.03400000184774399, -0.02889999933540821, 0.024299999698996544, -0.007300000172108412, -0.032600000500679016, -0.05689999833703041, 0.04820000007748604, 0.02979999966919422, 0.05559999868273735, 0.0034000000450760126, 0.0017999999690800905, -0.011900000274181366, 0.07079999893903732, -0.008200000040233135, 0.05270000174641609, 0.009100000374019146, -0.017999999225139618, 0.05700000002980232, -0.03550000116229057, 0.008100000210106373, -0.07450000196695328, -0.030799999833106995, 0.03689999878406525, 0.02590000070631504, 0.0658000037074089, 0.061799999326467514, 0.027799999341368675, -0.019999999552965164, -0.04230000078678131, -0.06809999793767929, -0.0877000018954277, 0.01810000091791153, 0.0215000007301569, -0.03420000150799751, 0.04170000180602074, -0.07349999994039536, 0.016200000420212746, 0.014999999664723873, 0.054099999368190765, 0.04149999842047691, 0.010200000368058681, 0.0052999998442828655, 0.07410000264644623, 0.035599999129772186, -0.02290000021457672, 0.04729999974370003, -0.053300000727176666, 0.09179999679327011, -0.04259999841451645, 0.03720000013709068, -0.009600000455975533, -0.06459999829530716, 0.009600000455975533, 0.011900000274181366, -0.010599999688565731, 0.00570000009611249, -0.01590000092983246, -0.01140000019222498, 0.06840000301599503, 0.022700000554323196, -0.09019999951124191, 0.03400000184774399, -0.022199999541044235, -0.019099999219179153, 0.07800000160932541, 0.02410000003874302, -0.07940000295639038, -0.014000000432133675, 0.07289999723434448, 0.08950000256299973, -0.05339999869465828, 0.07660000026226044, -0.012400000356137753, -0.04960000142455101, 0.01899999938905239, -0.02710000053048134, -0.0066999997943639755, 0.03920000046491623, 0.05339999869465828, -0.049800001084804535, -0.039799999445676804, -0.06949999928474426, 0.04360000044107437, 0.003800000064074993, 0.03840000182390213, -0.00279999990016222, 0.02810000069439411, 0.04399999976158142, -0.04580000042915344, -0.03240000084042549, 0.03689999878406525, -0.09189999848604202, 0.062300000339746475, 0.0027000000700354576, -0.0794999971985817, -0.004399999976158142, 0.07270000129938126, 0.06759999692440033, -0.013799999840557575, 0.02160000056028366, 0.08340000361204147, -0.07739999890327454, -0.031099999323487282, 0.0012000000569969416, -0.029100000858306885, 0.014399999752640724, 0.061400000005960464, 0.008200000040233135, 0.01889999955892563, -0.025699999183416367, 0.003000000026077032, 0.07039999961853027, -0.0035000001080334187, 0.05730000138282776, -0.03849999979138374, 0.05900000035762787, 0.00039999998989515007, 0.05990000069141388, -0.011500000022351742, -0.01640000008046627, 0.07639999687671661, -0.01940000057220459, -0.020400000736117363, -0.01119999960064888, 0.01850000023841858, -0.04259999841451645, -0.03020000085234642, 0.10599999874830246], [0.02630000002682209, -0.001500000013038516, 0.07500000298023224, -0.05400000140070915, -0.07569999992847443, 0.03539999946951866, 0.011599999852478504, 0.043800000101327896, -0.053199999034404755, -0.0210999995470047, 0.008799999952316284, -0.0860000029206276, -0.00019999999494757503, 0.01360000018030405, 0.05790000036358833, 0.003599999938160181, -0.03460000082850456, -0.019899999722838402, -0.03709999844431877, 0.0551999993622303, 0.02539999969303608, 0.003100000089034438, 0.03180000185966492, -0.03319999948143959, 0.031300000846385956, 0.02930000051856041, -0.04050000011920929, -0.1273999959230423, -0.03579999879002571, 0.0502999983727932, 0.0005000000237487257, -0.14740000665187836, -0.06610000133514404, -0.04820000007748604, -0.08009999990463257, -0.08420000225305557, 0.03229999914765358, -0.0038999998942017555, 0.006500000134110451, -0.05990000069141388, 0.06949999928474426, 0.04349999874830246, 0.05920000001788139, -0.012400000356137753, 0.044599998742341995, -0.17710000276565552, -0.06939999759197235, 0.016899999231100082, -0.056299999356269836, 0.05389999970793724, -0.08269999921321869, -0.02979999966919422, 0.04540000110864639, 0.06920000165700912, 0.007699999958276749, -0.08429999649524689, 0.05849999934434891, -0.004100000020116568, -0.03099999949336052, 0.013899999670684338, -0.004999999888241291, -0.02590000070631504, 0.005499999970197678, 0.05590000003576279, 0.094200000166893, -0.06440000236034393, -0.04989999905228615, 0.04129999876022339, -0.008200000040233135, -0.0364999994635582, -0.07930000126361847, 0.11460000276565552, -0.04650000110268593, 0.05510000139474869, 0.06560000032186508, 0.0649000033736229, -0.0681999996304512, 0.048500001430511475, 0.06639999896287918, -0.08470000326633453, -0.07590000331401825, -0.044599998742341995, -0.02979999966919422, -0.03359999880194664, 0.06599999964237213, 0.05290000140666962, 0.04769999906420708, -0.01860000006854534, 0.03579999879002571, -0.11680000275373459, 0.02539999969303608, 0.03200000151991844, 0.051600001752376556, 0.054499998688697815, -0.03790000081062317, -0.0210999995470047, -0.04410000145435333, 0.016100000590085983, 0.07109999656677246, 0.025299999862909317, -0.04910000041127205, 0.04190000146627426, 0.051899999380111694, 0.014499999582767487, 0.04430000111460686, -0.015399999916553497, -0.011699999682605267, -0.02449999935925007, 0.039500001817941666, 0.0723000019788742, -0.03799999877810478, -0.028300000354647636, -0.003700000001117587, -0.0851999968290329, -0.05380000174045563, -0.004600000102072954, -0.025800000876188278, -0.045099999755620956, 0.00800000037997961, 0.09470000118017197, -0.057100001722574234, 0.009600000455975533, 0.10750000178813934, -0.019500000402331352, 0.10859999805688858, -0.07999999821186066, -0.002300000051036477, 0.03830000013113022, 0.07599999755620956, 0.000699999975040555, -0.026499999687075615, 0.04729999974370003, 0.017500000074505806, -0.08399999886751175, -0.062300000339746475, -0.05180000141263008, -0.07819999754428864, -0.02710000053048134, -0.01769999973475933, -0.034299999475479126, 0.07209999859333038, 0.045899998396635056, -0.002199999988079071, -0.08609999716281891, 0.021299999207258224, -0.05480000004172325, -0.04780000075697899, 0.06689999997615814, -0.09910000115633011, 0.008200000040233135, -0.0885000005364418, 0.024000000208616257, 0.059700001031160355, -0.12370000034570694, -0.003100000089034438, 0.001500000013038516, 0.03970000147819519, -0.024399999529123306, -0.04050000011920929, -0.08619999885559082, -0.0348999984562397, 0.08299999684095383, 0.011099999770522118, 0.02800000086426735, 0.026000000536441803, 0.012400000356137753, 0.08560000360012054, 0.027300000190734863, -0.05889999866485596, 0.1242000013589859, -0.010999999940395355, 0.03180000185966492, 0.04399999976158142, -0.03539999946951866, 0.008700000122189522, 0.03310000151395798, -0.024700000882148743, 0.08340000361204147, -0.1290999948978424, 0.051100000739097595, 0.0017999999690800905, -0.08550000190734863, 0.0794999971985817, -0.08699999749660492, 0.025599999353289604, -0.023099999874830246, -0.07029999792575836, 0.009499999694526196, 0.02329999953508377, -0.052000001072883606, 0.02930000051856041, -0.026799999177455902, 0.0494999997317791, -0.05220000073313713, 0.003599999938160181, -0.03720000013709068, 0.12540000677108765, -0.039799999445676804, 0.04780000075697899, 0.052000001072883606, -0.00279999990016222, 0.03799999877810478, 0.022199999541044235, 0.024299999698996544, -0.04309999942779541, -0.024800000712275505, 0.010300000198185444, -0.13459999859333038, -0.0071000000461936, 0.046300001442432404, 0.03319999948143959, 0.017899999395012856, 0.04340000078082085, 0.014800000004470348, -0.09520000219345093, 0.0044999998062849045, 0.10999999940395355, 0.11159999668598175, -0.10899999737739563, 0.012600000016391277, -0.09749999642372131, -0.012000000104308128, -0.038100000470876694, -0.01679999940097332, 0.06870000064373016, -0.0017999999690800905, -0.01360000018030405, 0.017899999395012856, -0.004900000058114529, -0.059300001710653305, 0.03880000114440918, 0.042500000447034836, -0.03460000082850456, 0.031700000166893005, 0.01720000058412552, -0.019700000062584877, 0.01489999983459711, 0.03229999914765358, 0.04309999942779541, -0.03869999945163727, 0.11089999973773956, -0.066600002348423, -0.008799999952316284, -0.0142000000923872, -0.06539999693632126, -0.053700000047683716, -0.04320000112056732, -0.03739999979734421, 0.013899999670684338, -0.001500000013038516, -0.0003000000142492354, -0.06369999796152115, 0.06800000369548798, -0.008100000210106373, 0.01080000028014183, -0.026799999177455902, -0.051500000059604645, 0.023399999365210533, 0.10419999808073044, 0.07240000367164612, 0.010400000028312206, 0.10849999636411667, 0.015599999576807022, -0.05510000139474869]], [[0.04910000041127205, -0.03790000081062317, -0.02800000086426735, -0.010999999940395355, -0.053700000047683716, 0.09880000352859497, 0.09520000219345093, 0.024399999529123306, -0.044599998742341995, -0.06809999793767929, 0.05649999901652336, 0.010499999858438969, 0.10209999978542328, -0.0020000000949949026, 0.03999999910593033, -0.002300000051036477, -0.03280000016093254, 0.06769999861717224, 0.05290000140666962, 0.025100000202655792, -0.06629999727010727, 0.004800000227987766, 0.026499999687075615, 0.02500000037252903, 0.02669999934732914, 0.01209999993443489, -0.048700001090765, -0.05469999834895134, -0.05209999904036522, 0.016899999231100082, 0.06449999660253525, 0.10080000013113022, -0.02250000089406967, -0.019600000232458115, 0.009499999694526196, 0.06310000270605087, 0.0210999995470047, -0.004399999976158142, -0.11949999630451202, 0.08560000360012054, 0.00430000014603138, -0.07490000128746033, 0.11990000307559967, -0.09319999814033508, -0.006300000008195639, -0.020999999716877937, 0.02500000037252903, 0.008100000210106373, -0.09350000321865082, 0.07419999688863754, 0.07280000299215317, -0.006800000090152025, -0.09160000085830688, 0.00559999980032444, -0.03099999949336052, 0.04089999943971634, -0.1014999970793724, 0.06440000236034393, -0.008999999612569809, 0.00800000037997961, -0.09149999916553497, -0.011900000274181366, 0.035599999129772186, 0.029600000008940697, 0.062300000339746475, 0.04529999941587448, -0.14429999887943268, -0.00930000003427267, -0.11999999731779099, 0.04740000143647194, 0.02250000089406967, -0.014800000004470348, -0.01269999984651804, -0.020600000396370888, 0.043699998408555984, -0.03200000151991844, -0.1835000067949295, 0.028300000354647636, 0.008700000122189522, -0.03440000116825104, -0.03240000084042549, 0.08829999715089798, 0.014999999664723873, 0.01140000019222498, 0.04830000177025795, 0.029999999329447746, 0.07970000058412552, -0.019999999552965164, 0.003800000064074993, 0.043800000101327896, 0.00800000037997961, 0.12770000100135803, -0.052799999713897705, -0.0012000000569969416, 0.0658000037074089, -0.0714000016450882, -0.04809999838471413, 0.07580000162124634, 0.1348000019788742, 0.032999999821186066, -0.13600000739097595, -0.0738999992609024, 0.062300000339746475, 0.05009999871253967, -0.048500001430511475, -0.10819999873638153, 0.10909999907016754, 0.023600000888109207, 0.057100001722574234, 0.07840000092983246, 0.10170000046491623, -0.01679999940097332, 0.18140000104904175, 0.01850000023841858, 0.02459999918937683, 0.09539999812841415, -0.023800000548362732, 0.10999999940395355, 0.06790000200271606, 0.11649999767541885, 0.005100000184029341, -0.025800000876188278, -0.044199999421834946, 0.003800000064074993, 0.06069999933242798, -0.07100000232458115, 0.012600000016391277, -0.004800000227987766, -0.11180000007152557, 0.04839999973773956, 0.1160999983549118, -0.07100000232458115, 0.09030000120401382, -0.10869999974966049, 0.06340000033378601, -0.12540000677108765, 0.006899999920278788, -0.013899999670684338, 0.041600000113248825, 0.03370000049471855, 0.005499999970197678, 0.03790000081062317, -0.07020000368356705, -0.04259999841451645, 0.10740000009536743, -0.00019999999494757503, -0.029500000178813934, -0.020500000566244125, 0.09780000150203705, 0.035599999129772186, 0.011300000362098217, -0.007400000002235174, 0.05790000036358833, 0.03139999881386757, -0.08169999718666077, -0.08110000193119049, -0.002400000113993883, -0.08669999986886978, 0.0010000000474974513, 0.05169999971985817, 0.00430000014603138, -0.0015999999595806003, -0.07320000231266022, 0.013100000098347664, 0.03530000150203705, 0.06499999761581421, 0.013799999840557575, -0.06279999762773514, -0.07400000095367432, -0.14159999787807465, -0.041999999433755875, -0.03790000081062317, 0.03590000048279762, -0.04690000042319298, -0.09449999779462814, -0.0544000007212162, -0.004100000020116568, 0.05400000140070915, -0.13429999351501465, 0.04769999906420708, 0.07169999927282333, -0.09529999643564224, 0.05260000005364418, -0.035599999129772186, -0.11710000038146973, 0.1339000016450882, -0.06279999762773514, -0.014399999752640724, 0.1720999926328659, 0.1784999966621399, -0.10939999669790268, -0.018200000748038292, -0.09619999676942825, -0.06599999964237213, 0.094200000166893, -0.08110000193119049, -0.021800000220537186, -0.04989999905228615, -0.06889999657869339, -0.007699999958276749, 0.035599999129772186, -0.0860000029206276, -0.06750000268220901, -0.021700000390410423, 0.02889999933540821, -0.05979999899864197, -0.07410000264644623, -0.06610000133514404, 0.055399999022483826, -0.04769999906420708, 0.04230000078678131, 0.11590000241994858, -0.15080000460147858, 0.1103999987244606, 0.035999998450279236, -0.034299999475479126, 0.05920000001788139, 0.14669999480247498, -0.06109999865293503, -0.02070000022649765, -0.09149999916553497, 0.08910000324249268, 0.04019999876618385, 0.0024999999441206455, 0.12770000100135803, 0.006200000178068876, 0.05299999937415123, -0.0868000015616417, 0.08240000158548355, -0.06260000169277191, -0.006000000052154064, -0.0608999989926815, 0.11680000275373459, -0.017500000074505806, -0.01899999938905239, -0.032999999821186066, -0.05790000036358833, 0.01489999983459711, 0.10689999908208847, 0.04010000079870224, 0.06610000133514404, -0.0625, 0.10819999873638153, -0.0640999972820282, -0.06629999727010727, 0.03739999979734421, -0.049300000071525574, 0.012500000186264515, 0.08139999955892563, -0.029600000008940697, -0.25380000472068787, -0.07109999656677246, 0.03099999949336052, 0.07620000094175339, -0.024800000712275505, 0.10189999639987946, -0.018400000408291817, 0.010200000368058681, 0.004600000102072954, 0.12790000438690186, -0.06239999830722809, 0.05310000106692314, 0.018799999728798866, 0.000699999975040555], [0.034699998795986176, -0.11249999701976776, 0.045099999755620956, -0.025800000876188278, -0.004699999932199717, -0.05939999967813492, -0.14509999752044678, -0.11949999630451202, -0.06129999831318855, 0.06800000369548798, 0.02979999966919422, 0.12600000202655792, -0.08089999854564667, 0.02419999986886978, 0.021400000900030136, 0.006899999920278788, 0.0017999999690800905, -0.05959999933838844, -0.00930000003427267, 0.024000000208616257, 0.03579999879002571, 0.00930000003427267, -0.09549999982118607, 0.07240000367164612, 0.04690000042319298, -0.002199999988079071, -0.006899999920278788, 0.043800000101327896, -0.05889999866485596, -0.01510000042617321, -0.08919999748468399, 0.02319999970495701, -0.04670000076293945, 0.029600000008940697, 0.01860000006854534, -0.04670000076293945, -0.012000000104308128, 0.062300000339746475, -0.020899999886751175, -0.08489999920129776, -0.13860000669956207, 0.052799999713897705, -0.029999999329447746, 0.03020000085234642, -0.08150000125169754, 0.036400001496076584, 0.04960000142455101, 0.07800000160932541, -0.17749999463558197, -0.09650000184774399, -0.0697999969124794, -0.03420000150799751, 0.08320000022649765, 0.03849999979138374, 0.05959999933838844, 0.04839999973773956, -0.03700000047683716, -0.0007999999797903001, 0.015699999406933784, -0.019700000062584877, -0.07580000162124634, -0.023000000044703484, 0.014800000004470348, -0.1468999981880188, -0.0215000007301569, 0.018300000578165054, -0.12129999697208405, -0.07370000332593918, -0.03790000081062317, -0.06019999831914902, 0.053700000047683716, 0.03539999946951866, -0.04050000011920929, 0.08020000159740448, 0.024900000542402267, -0.013500000350177288, -0.033900000154972076, -0.025699999183416367, 0.018400000408291817, 0.013899999670684338, 0.045899998396635056, -0.0, 0.07599999755620956, 0.13030000030994415, 0.00039999998989515007, -0.15449999272823334, 0.016899999231100082, 0.09960000216960907, 0.052000001072883606, 0.011099999770522118, 0.09459999948740005, -0.00989999994635582, 0.060100000351667404, -0.09070000052452087, -9.999999747378752e-05, -0.04010000079870224, 0.11779999732971191, -0.01759999990463257, 0.05490000173449516, 0.02419999986886978, -0.024000000208616257, 0.03310000151395798, 0.09679999947547913, -0.09849999845027924, -0.053599998354911804, 9.999999747378752e-05, 0.04360000044107437, -0.0364999994635582, -0.06759999692440033, -0.03229999914765358, -0.06210000067949295, 0.05480000004172325, 0.06989999860525131, -0.10660000145435333, -0.08669999986886978, -0.19760000705718994, -0.05180000141263008, -0.11339999735355377, 0.024299999698996544, 0.04010000079870224, -0.05689999833703041, 0.0203000009059906, 0.027699999511241913, -0.09679999947547913, -0.03060000017285347, -0.09049999713897705, 0.024800000712275505, -0.07649999856948853, -0.04800000041723251, 0.09529999643564224, 0.01889999955892563, 0.04699999839067459, 0.08940000087022781, -0.02370000071823597, 0.16920000314712524, 0.008500000461935997, 0.12269999831914902, 0.06920000165700912, -0.09200000017881393, 0.041999999433755875, -0.03550000116229057, 0.023600000888109207, -0.034699998795986176, -0.09669999778270721, -0.039900001138448715, 0.062199998646974564, 0.09430000185966492, 0.14880000054836273, 0.004399999976158142, 0.17659999430179596, -0.050599999725818634, 0.03200000151991844, -0.06210000067949295, 0.05939999967813492, 0.053199999034404755, -0.13179999589920044, 0.015399999916553497, -0.042500000447034836, 0.029600000008940697, 0.0746999979019165, 0.019500000402331352, 0.0406000018119812, 0.007499999832361937, -0.01140000019222498, 0.05119999870657921, -0.16040000319480896, -0.14319999516010284, -0.07419999688863754, 0.04529999941587448, -0.028999999165534973, 0.09130000323057175, -0.014600000344216824, -0.05180000141263008, 0.15479999780654907, 0.07989999651908875, -0.05350000038743019, 0.08129999786615372, 0.11069999635219574, 0.13379999995231628, 0.025499999523162842, -0.02850000001490116, 0.10289999842643738, -0.10509999841451645, -0.004800000227987766, -0.09759999811649323, -0.03500000014901161, -0.02199999988079071, -0.1005999967455864, 0.06469999998807907, -0.08569999784231186, -0.0731000006198883, 0.11729999631643295, -0.03920000046491623, -0.0203000009059906, 0.11230000108480453, -0.052299998700618744, -0.07129999995231628, -0.0714000016450882, 0.0625, -0.042399998754262924, -0.011099999770522118, -0.1517000049352646, 0.09109999984502792, -0.06830000132322311, -0.004900000058114529, 0.006899999920278788, -0.07370000332593918, -0.04740000143647194, -0.12759999930858612, -0.013000000268220901, 0.10819999873638153, 0.0272000003606081, 0.07190000265836716, -0.019600000232458115, 0.007600000128149986, 0.006599999964237213, -0.11789999902248383, -0.05209999904036522, -0.06270000338554382, 0.05490000173449516, 0.011900000274181366, -0.09109999984502792, 0.007400000002235174, -0.14149999618530273, -0.06080000102519989, -0.010499999858438969, -0.047200001776218414, -0.08510000258684158, -0.06769999861717224, 0.03370000049471855, 0.0010999999940395355, -0.05730000138282776, -0.058400001376867294, -0.014499999582767487, -0.1404000073671341, -0.020099999383091927, -0.00039999998989515007, 0.047200001776218414, 0.029400000348687172, 0.013100000098347664, 0.003000000026077032, 0.10320000350475311, -0.07490000128746033, -0.04529999941587448, 0.061500001698732376, -0.12110000103712082, 0.008100000210106373, 0.0284000001847744, 0.05090000107884407, -0.1103999987244606, -0.00989999994635582, 0.007199999876320362, -0.048900000751018524, -0.03959999978542328, -0.07360000163316727, 0.03269999846816063, 0.04100000113248825, -0.05739999935030937, -0.13439999520778656, 0.01769999973475933, -0.053300000727176666, -0.029200000688433647, 0.05719999969005585, -0.07289999723434448], [-0.08669999986886978, 0.0885000005364418, -0.09309999644756317, 0.010300000198185444, -0.03689999878406525, -0.1574999988079071, -0.06159999966621399, 0.06620000302791595, 0.011599999852478504, 0.029600000008940697, 0.03689999878406525, -0.11860000342130661, 0.12839999794960022, -0.10540000349283218, 0.04729999974370003, 0.093299999833107, 0.07810000330209732, 0.044599998742341995, 0.12559999525547028, -0.05959999933838844, -0.13339999318122864, -0.014499999582767487, 0.07320000231266022, 0.006000000052154064, 0.015300000086426735, -0.027300000190734863, -0.016899999231100082, -0.009200000204145908, -0.01979999989271164, 0.04479999840259552, -0.08579999953508377, -0.017400000244379044, -0.14980000257492065, 0.050599999725818634, 0.03709999844431877, -0.1216999962925911, 0.06780000030994415, -0.04270000010728836, 0.08449999988079071, 0.12470000237226486, -0.053599998354911804, 0.12800000607967377, 0.08060000091791153, -0.12250000238418579, -0.09019999951124191, -0.09359999746084213, 0.1662999987602234, 0.06210000067949295, -0.2085999995470047, -0.07100000232458115, -0.0737999975681305, 0.015399999916553497, -0.0348999984562397, 0.039000000804662704, -0.07729999721050262, -0.046300001442432404, -0.0034000000450760126, 0.02800000086426735, -0.020400000736117363, 0.07890000194311142, 0.18469999730587006, -0.029500000178813934, -0.02710000053048134, -0.0066999997943639755, 0.03180000185966492, 0.0044999998062849045, 0.04430000111460686, 0.02419999986886978, -0.014100000262260437, 0.08229999989271164, 0.048500001430511475, -0.037700001150369644, -0.06889999657869339, 0.059300001710653305, 0.15150000154972076, 0.07500000298023224, -0.05889999866485596, 0.015699999406933784, -0.002899999963119626, 0.03840000182390213, -0.016699999570846558, 0.01140000019222498, 0.1737000048160553, -0.01810000091791153, -0.03620000183582306, -0.030500000342726707, 0.03200000151991844, -0.06599999964237213, -0.05730000138282776, -0.07850000262260437, -0.045499999076128006, -0.09309999644756317, -0.09799999743700027, -0.08100000023841858, 0.08709999918937683, -0.10320000350475311, -0.018200000748038292, -0.020600000396370888, 0.027300000190734863, -0.0843999981880188, 0.065700002014637, 0.043299999088048935, 0.03139999881386757, 0.0032999999821186066, -0.01489999983459711, -0.03610000014305115, 0.040699999779462814, -0.11919999867677689, 0.08429999649524689, -0.025800000876188278, -0.16279999911785126, -0.13570000231266022, -0.1454000025987625, 0.01600000075995922, -0.05040000006556511, 0.07739999890327454, -0.00019999999494757503, 0.06509999930858612, 0.08030000329017639, -0.10890000313520432, 0.06889999657869339, 0.1517000049352646, -0.0035000001080334187, -0.047200001776218414, 0.010200000368058681, 0.012400000356137753, 0.061500001698732376, 0.04349999874830246, -0.038100000470876694, -0.04230000078678131, -0.04320000112056732, 0.06710000336170197, 0.17180000245571136, 0.17880000174045563, -0.09440000355243683, -0.10530000180006027, -0.01119999960064888, -0.04470000043511391, -0.08060000091791153, 0.04919999837875366, 0.06480000168085098, -0.07959999889135361, -0.0013000000035390258, -0.022299999371170998, 0.11810000240802765, 0.12489999830722809, -0.13819999992847443, -0.06419999897480011, -0.10769999772310257, -0.03720000013709068, -0.05609999969601631, -0.05350000038743019, 0.0035000001080334187, 0.15410000085830688, 0.08980000019073486, 0.02630000002682209, -0.09019999951124191, 0.041600000113248825, -0.13300000131130219, 0.06069999933242798, 0.02250000089406967, -0.0706000030040741, 0.03550000116229057, -0.09130000323057175, -0.012500000186264515, 0.08619999885559082, 0.038100000470876694, -0.11469999700784683, 0.006399999838322401, -0.016300000250339508, -0.03060000017285347, -0.031099999323487282, 0.0917000025510788, -0.06379999965429306, -0.08380000293254852, -0.016499999910593033, -0.1736000031232834, 0.04320000112056732, -0.011900000274181366, -0.07490000128746033, -0.0034000000450760126, -0.08240000158548355, 0.04149999842047691, 0.02019999921321869, -0.07930000126361847, -0.025499999523162842, 0.013100000098347664, -0.08049999922513962, -0.007199999876320362, -0.0843999981880188, -0.1745000034570694, -0.05640000104904175, 0.1054999977350235, -0.07819999754428864, -0.08529999852180481, 0.032999999821186066, -0.06040000170469284, -0.07450000196695328, -0.021800000220537186, -0.04430000111460686, 0.04619999974966049, 0.02930000051856041, 0.04230000078678131, 0.14790000021457672, 0.012600000016391277, -0.03909999877214432, -0.15230000019073486, -0.021299999207258224, -0.041099999099969864, 0.027699999511241913, -0.031300000846385956, 0.065700002014637, -0.06729999929666519, -0.06419999897480011, -0.05050000175833702, -0.052799999713897705, -0.08749999850988388, 0.000699999975040555, 0.10379999876022339, 0.04479999840259552, -0.022299999371170998, -0.009800000116229057, -0.0575999990105629, -0.02969999983906746, -0.10649999976158142, 0.09000000357627869, 0.06539999693632126, 0.03920000046491623, 0.09920000284910202, 0.004699999932199717, -0.10729999840259552, 0.0828000009059906, -0.04830000177025795, -0.07450000196695328, -0.08969999849796295, -0.023099999874830246, -0.1728000044822693, -0.08370000123977661, -0.018300000578165054, 0.15240000188350677, -0.06430000066757202, 0.0430000014603138, 0.1071000024676323, 0.10289999842643738, -0.020999999716877937, -0.0551999993622303, -0.0786999985575676, -0.06939999759197235, 0.041600000113248825, -0.09279999881982803, 0.030300000682473183, 0.06360000371932983, -0.026599999517202377, 0.019700000062584877, 0.11760000139474869, 0.07930000126361847, 0.05660000070929527, 0.16249999403953552, 0.04050000011920929, -0.06539999693632126, 0.10189999639987946, 0.07460000365972519, -0.07500000298023224, 0.02669999934732914], [-0.08410000056028366, -0.09120000153779984, -0.061799999326467514, 0.016499999910593033, -0.1387999951839447, 0.04839999973773956, 0.033900000154972076, -0.1395999938249588, 0.02630000002682209, 0.025299999862909317, 0.08659999817609787, -0.02319999970495701, 0.005400000140070915, 0.048900000751018524, -0.08579999953508377, -0.039500001817941666, -0.0820000022649765, -0.04780000075697899, -0.007499999832361937, 0.07000000029802322, 0.03579999879002571, -0.053700000047683716, 0.04659999907016754, -0.11739999800920486, -0.08900000154972076, 0.016100000590085983, 0.029200000688433647, 0.05990000069141388, 0.01140000019222498, -0.028699999675154686, -0.041200000792741776, -0.057500001043081284, -0.040699999779462814, 0.07490000128746033, -0.065700002014637, 0.03920000046491623, -0.11490000039339066, -0.00139999995008111, -0.08030000329017639, -0.13079999387264252, -0.06319999694824219, 0.05770000070333481, -0.023900000378489494, 0.0658000037074089, 0.0026000000070780516, -0.041200000792741776, 0.05570000037550926, 0.12860000133514404, -0.000699999975040555, 0.006500000134110451, -0.053300000727176666, 0.05420000106096268, -0.14110000431537628, -0.05779999867081642, -0.0142000000923872, -0.017000000923871994, 0.12720000743865967, 0.018699999898672104, -0.06379999965429306, -0.1542000025510788, 0.05270000174641609, -0.04349999874830246, -0.05490000173449516, -0.19920000433921814, -0.15479999780654907, 0.045099999755620956, 0.1412000060081482, 0.023499999195337296, -0.0494999997317791, -0.020899999886751175, 0.09070000052452087, -0.05790000036358833, 0.15690000355243683, -0.059300001710653305, -0.052000001072883606, -0.05849999934434891, -0.06769999861717224, 0.009999999776482582, 0.09220000356435776, 0.11509999632835388, 0.1664000004529953, 0.014299999922513962, 0.09239999949932098, 0.06769999861717224, -0.03779999911785126, -0.13300000131130219, -0.028599999845027924, -0.09650000184774399, 0.05990000069141388, 0.11029999703168869, 0.01080000028014183, -0.0210999995470047, -0.1006999984383583, -0.04580000042915344, -0.01209999993443489, -0.019099999219179153, -0.01679999940097332, 0.1527000069618225, 0.06710000336170197, -0.13249999284744263, -0.04650000110268593, -0.0421999990940094, 0.00989999994635582, -0.019999999552965164, -0.013799999840557575, -0.04610000178217888, 0.04170000180602074, -0.050999999046325684, -0.002300000051036477, -0.01810000091791153, -0.13019999861717224, -0.02710000053048134, 0.020800000056624413, 0.0272000003606081, -0.07989999651908875, 0.11110000312328339, 0.07270000129938126, 0.06300000101327896, -0.07039999961853027, 0.050599999725818634, 0.008799999952316284, 0.018699999898672104, 0.0015999999595806003, -0.08240000158548355, 0.039500001817941666, 0.027300000190734863, -0.08460000157356262, 0.015300000086426735, 0.0032999999821186066, -0.0035000001080334187, -0.02370000071823597, -0.051899999380111694, -0.04190000146627426, -0.027300000190734863, 0.04919999837875366, 0.026000000536441803, 0.01119999960064888, 0.13279999792575836, -0.10999999940395355, 0.14720000326633453, -0.03009999915957451, 0.029400000348687172, -0.03370000049471855, -0.12070000171661377, 0.03550000116229057, -0.006800000090152025, 0.057100001722574234, -0.04659999907016754, -0.07919999957084656, 0.05660000070929527, 0.05209999904036522, -0.027699999511241913, -0.06909999996423721, -0.04960000142455101, 0.09239999949932098, -0.06889999657869339, 0.03539999946951866, 0.06729999929666519, 0.15870000422000885, 0.031700000166893005, -0.03869999945163727, -0.0925000011920929, 0.0010000000474974513, -0.032499998807907104, -0.04659999907016754, -0.006200000178068876, 0.0658000037074089, 0.02889999933540821, 0.07819999754428864, -0.056699998676776886, 0.011599999852478504, 0.05959999933838844, -0.06509999930858612, 0.0020000000949949026, 0.04129999876022339, -0.004399999976158142, 0.06639999896287918, 0.10029999911785126, -0.0771000012755394, -0.02319999970495701, -0.0005000000237487257, 0.03880000114440918, -0.11159999668598175, -0.0</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>[-0.7955631687459035]</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>[0.40986715053582196]</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>[-2.2024723082695874]</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>[0.7311349030938428]</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>[-2.9386895626760254]</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>[1.289053116974996]</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>[-1.1031210573377366]</t>
+        </is>
+      </c>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>[0.4831270200381]</t>
+        </is>
+      </c>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>[-3.1081574616525973]</t>
+        </is>
+      </c>
+      <c r="N36" t="inlineStr">
+        <is>
+          <t>[0.974294843202283]</t>
+        </is>
+      </c>
+      <c r="O36" t="inlineStr">
+        <is>
+          <t>[-0.30011079378645333]</t>
+        </is>
+      </c>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>[0.4274080998653555]</t>
+        </is>
+      </c>
+      <c r="Q36" t="inlineStr">
+        <is>
+          <t>[-0.49555870339346164]</t>
+        </is>
+      </c>
+      <c r="R36" t="inlineStr">
+        <is>
+          <t>[0.16125970747079527]</t>
+        </is>
+      </c>
+      <c r="S36" t="inlineStr">
+        <is>
+          <t>[-0.5038782175445498]</t>
+        </is>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>[0.1267172895669423]</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>[-2.609084197410573]</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>[0.34511192947948416]</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>[-0.5719864899657072]</t>
+        </is>
+      </c>
+      <c r="X36" t="inlineStr">
+        <is>
+          <t>[0.16468228490773162]</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>[-0.5017319759414736]</t>
+        </is>
+      </c>
+      <c r="Z36" t="inlineStr">
+        <is>
+          <t>[0.12358234441235896]</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>[-3.7125118368035404]</t>
+        </is>
+      </c>
+      <c r="AB36" t="inlineStr">
+        <is>
+          <t>[0.433571703140376]</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>[-1.9485020814547527]</t>
+        </is>
+      </c>
+      <c r="AD36" t="inlineStr">
+        <is>
+          <t>[0.2470725960669074]</t>
+        </is>
+      </c>
+      <c r="AE36" t="inlineStr">
+        <is>
+          <t>[-1.5692275465878485]</t>
+        </is>
+      </c>
+      <c r="AF36" t="inlineStr">
+        <is>
+          <t>[0.27664947410157514]</t>
+        </is>
+      </c>
+      <c r="AG36" t="inlineStr">
+        <is>
+          <t>[-5.407234366638603]</t>
+        </is>
+      </c>
+      <c r="AH36" t="inlineStr">
+        <is>
+          <t>[0.47701833239592895]</t>
+        </is>
+      </c>
+      <c r="AI36" t="inlineStr">
+        <is>
+          <t>[-2.577997043722592]</t>
+        </is>
+      </c>
+      <c r="AJ36" t="inlineStr">
+        <is>
+          <t>[0.2932128746564392]</t>
+        </is>
+      </c>
+      <c r="AK36" t="inlineStr">
+        <is>
+          <t>[-1.6180057418561211]</t>
+        </is>
+      </c>
+      <c r="AL36" t="inlineStr">
+        <is>
+          <t>[0.27788212831836157]</t>
+        </is>
+      </c>
+      <c r="AM36" t="inlineStr">
+        <is>
+          <t>[-4.679293769622129]</t>
+        </is>
+      </c>
+      <c r="AN36" t="inlineStr">
+        <is>
+          <t>[0.43621093413745293]</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>model_62_32_16_0</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>[62, 32, 16]</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>[[[0.03319999948143959, 0.0027000000700354576, -0.016699999570846558, -0.0017999999690800905, 0.12229999899864197, -0.014700000174343586, -0.04670000076293945, -0.05999999865889549, -0.0005000000237487257, -0.16120000183582306, -0.057500001043081284, -0.03150000050663948, 0.04129999876022339, 0.027000000700354576, -0.054999999701976776, 0.0066999997943639755, 0.0007999999797903001, 0.059300001710653305, 0.00139999995008111, -0.021199999377131462, 0.06199999898672104, 0.042500000447034836, 0.11349999904632568, 0.019600000232458115, 0.05620000138878822, -0.0026000000070780516, -0.029600000008940697, 0.05090000107884407, -0.008500000461935997, 0.039400000125169754, 0.014999999664723873, 0.01720000058412552, 0.03959999978542328, 0.014700000174343586, 0.010400000028312206, 0.060499999672174454, -0.015599999576807022, -0.013299999758601189, 0.07540000230073929, -0.02539999969303608, 0.0722000002861023, -0.014800000004470348, -0.05270000174641609, 0.08399999886751175, -0.05649999901652336, 0.015200000256299973, -0.012799999676644802, -0.015799999237060547, 0.018699999898672104, 0.006300000008195639, -0.03020000085234642, 0.09740000218153, 0.07370000332593918, 0.02070000022649765, 0.014800000004470348, -0.029400000348687172, -0.04830000177025795, 0.004000000189989805, -0.07289999723434448, -0.042399998754262924, 0.0008999999845400453, -0.04740000143647194], [-0.061400000005960464, -0.007499999832361937, 0.02319999970495701, -0.028599999845027924, 0.02879999950528145, 0.014399999752640724, 0.1039000004529953, -0.06560000032186508, -0.04690000042319298, -0.0005000000237487257, 0.03680000081658363, 0.04340000078082085, -0.10540000349283218, -0.03840000182390213, 0.014999999664723873, 0.025499999523162842, 0.006800000090152025, -0.04230000078678131, 0.03500000014901161, 0.0035000001080334187, 0.019099999219179153, 0.00019999999494757503, 0.05869999900460243, -0.0035000001080334187, -0.053300000727176666, 0.043800000101327896, 0.01119999960064888, -0.0010000000474974513, -0.04439999908208847, -0.06549999862909317, -0.08110000193119049, 0.02759999968111515, 0.018699999898672104, -0.0010000000474974513, 0.026200000196695328, -0.006500000134110451, 0.04010000079870224, -0.0892999991774559, 0.002899999963119626, -0.04540000110864639, -0.14000000059604645, -0.05000000074505806, 0.06949999928474426, -0.03139999881386757, -0.013700000010430813, 0.04580000042915344, -0.007899999618530273, -0.011300000362098217, 0.08389999717473984, 0.03620000183582306, -0.05420000106096268, -0.022199999541044235, 0.049800001084804535, -0.024900000542402267, 0.020400000736117363, 0.026799999177455902, 0.014800000004470348, 0.08070000261068344, -0.02410000003874302, -0.044199999421834946, 0.03819999843835831, -0.003000000026077032]], [[0.08709999918937683, -0.028200000524520874, -0.2856000065803528, 0.2578999996185303, -0.15639999508857727, -0.18649999797344208, 0.0729999989271164, -0.006000000052154064, 0.04340000078082085, -0.07150000333786011, 0.17579999566078186, 0.03830000013113022, -0.12099999934434891, 0.043699998408555984, 0.004900000058114529, 0.0885000005364418, -0.16500000655651093, 0.08479999750852585, -0.006599999964237213, -0.045099999755620956, 0.05590000003576279, 0.06350000202655792, 0.24889999628067017, 0.017999999225139618, -0.13860000669956207, 0.0812000036239624, -0.15780000388622284, -0.029200000688433647, -0.1906999945640564, 0.06210000067949295, -0.04919999837875366, 0.1525000035762787, -0.07039999961853027, -0.035100001841783524, -0.16339999437332153, -0.04749999940395355, 0.11569999903440475, 0.08139999955892563, -0.04650000110268593, 0.0357000008225441, -0.05689999833703041, 0.0989999994635582, -0.017000000923871994, 0.243599995970726, -0.12080000340938568, 0.03220000118017197, 0.13670000433921814, -0.001500000013038516, 0.0015999999595806003, 0.2321999967098236, -0.05550000071525574, 0.30979999899864197, -0.08950000256299973, -0.1662999987602234, -0.052299998700618744, -0.019999999552965164, 0.01140000019222498, -0.03290000185370445, -0.031599998474121094, 0.32839998602867126, 0.14959999918937683, 0.04500000178813934], [-0.09799999743700027, -0.12449999898672104, -0.0885000005364418, -0.035599999129772186, 0.06589999794960022, -0.014100000262260437, -0.09950000047683716, -0.0997999981045723, -0.11410000175237656, -0.18359999358654022, 0.06430000066757202, 0.06710000336170197, -0.16210000216960907, 0.2547999918460846, 0.0966000035405159, 0.07890000194311142, -0.01730000041425228, -0.30230000615119934, -0.1257999986410141, 0.14470000565052032, -0.10859999805688858, -0.1835000067949295, 0.037300001829862595, 0.09880000352859497, 0.24770000576972961, -0.3531000018119812, -0.07150000333786011, 0.03999999910593033, -0.23970000445842743, -0.0803999975323677, 0.08389999717473984, 0.1103999987244606, 0.10849999636411667, 0.07289999723434448, -0.11299999803304672, -0.0044999998062849045, 0.10970000177621841, -0.12280000001192093, 0.01600000075995922, 0.21199999749660492, 0.07180000096559525, -0.07029999792575836, 0.13910000026226044, 0.10639999806880951, 0.04490000009536743, 0.0860000029206276, 0.23829999566078186, 0.09139999747276306, -0.060600001364946365, -0.16740000247955322, -0.043299999088048935, -0.07900000363588333, -0.05490000173449516, 0.04910000041127205, 0.05869999900460243, -0.08789999783039093, 0.02419999986886978, -0.12389999628067017, -0.02810000069439411, -0.028200000524520874, -0.12080000340938568, 0.11089999973773956], [0.06939999759197235, 0.034699998795986176, -0.06449999660253525, 0.04089999943971634, -0.1573999971151352, 0.09790000319480896, -0.05849999934434891, 0.10409999638795853, 0.03610000014305115, 0.08730000257492065, -0.013199999928474426, -0.057500001043081284, 0.19609999656677246, 0.1256999969482422, -0.11869999766349792, -0.0015999999595806003, 0.2660999894142151, -0.11469999700784683, -0.27649998664855957, 0.17919999361038208, -0.09539999812841415, -0.2143000066280365, 0.04479999840259552, -0.0754999965429306, 0.07450000196695328, 0.07500000298023224, 0.062300000339746475, -0.09210000187158585, -0.02449999935925007, -0.023900000378489494, -0.06080000102519989, -0.0649000033736229, 0.011099999770522118, -0.02539999969303608, -0.1005999967455864, -0.021800000220537186, 0.049400001764297485, 0.24819999933242798, 0.3330000042915344, -0.09359999746084213, 0.08500000089406967, 0.1088000014424324, -0.002199999988079071, -0.2313999980688095, -0.22040000557899475, -0.12080000340938568, 0.2126999944448471, 0.10589999705553055, 0.11010000109672546, 0.149399995803833, 0.1046999990940094, 0.06859999895095825, -0.056699998676776886, -0.23499999940395355, -0.15729999542236328, -0.006599999964237213, -0.10029999911785126, 0.045499999076128006, -0.053700000047683716, -0.12919999659061432, -0.08860000222921371, 0.10339999943971634], [0.00930000003427267, 0.01510000042617321, -0.09880000352859497, -0.08470000326633453, -0.14499999582767487, -0.03009999915957451, 0.28450000286102295, -0.024000000208616257, 0.05920000001788139, 0.28279998898506165, -0.010900000110268593, 0.040699999779462814, 0.04740000143647194, 0.01549999974668026, 0.1266999989748001, -0.04039999842643738, -0.12620000541210175, -0.061000000685453415, 0.0494999997317791, -0.060100000351667404, 0.14839999377727509, -0.31859999895095825, 0.01590000092983246, 0.12070000171661377, -0.011500000022351742, 0.012600000016391277, -0.08560000360012054, 0.13109999895095825, 0.14020000398159027, 0.08560000360012054, 0.16220000386238098, -0.0210999995470047, -0.0885000005364418, 0.4350999891757965, 0.10490000247955322, 0.08150000125169754, 0.08160000294446945, -0.02459999918937683, -0.042500000447034836, -0.05169999971985817, 0.20999999344348907, -0.19760000705718994, -0.23649999499320984, 0.026599999517202377, -0.054099999368190765, 0.1808999925851822, 0.005799999926239252, -0.08560000360012054, -0.051600001752376556, -0.0812000036239624, 0.07050000131130219, 0.006500000134110451, -0.00419999985024333, -0.2538999915122986, -0.022199999541044235, -0.15109999477863312, -0.065700002014637, 0.007600000128149986, -0.02590000070631504, 0.002099999925121665, -0.121799997985363, 0.004100000020116568], [0.12070000171661377, 0.008500000461935997, 0.09200000017881393, -0.11469999700784683, -0.04619999974966049, -0.1500999927520752, 0.17470000684261322, -0.07599999755620956, 0.08079999685287476, -0.09719999879598618, -0.013100000098347664, 0.09870000183582306, 0.010099999606609344, 0.12470000237226486, -0.07720000296831131, -0.12479999661445618, 0.004699999932199717, 0.07460000365972519, -0.22040000557899475, 0.23229999840259552, 0.029200000688433647, -0.07479999959468842, -0.04769999906420708, 0.14800000190734863, -0.07360000163316727, 0.1339000016450882, -0.04690000042319298, 0.09740000218153, 0.10320000350475311, -0.017100000753998756, -0.1315000057220459, -0.06889999657869339, 0.26499998569488525, -0.09920000284910202, 0.11739999800920486, 0.186599999666214, -0.011500000022351742, 0.11089999973773956, -0.04670000076293945, -0.09139999747276306, -0.1014999970793724, -0.22679999470710754, 0.15060000121593475, 0.10769999772310257, 0.21570000052452087, -0.24310000240802765, 0.016300000250339508, 0.061500001698732376, -0.11100000143051147, 0.07999999821186066, -0.12380000203847885, 0.061799999326467514, 0.23839999735355377, 0.03849999979138374, 0.040300000458955765, -0.10939999669790268, -0.23000000417232513, -0.1420000046491623, -0.035999998450279236, 0.2328999936580658, -0.19189999997615814, 0.02290000021457672], [-0.17550000548362732, 0.07029999792575836, -0.03689999878406525, 0.015599999576807022, 0.06270000338554382, 0.060499999672174454, 0.006000000052154064, 0.24650000035762787, -0.1404999941587448, 0.005200000014156103, -0.1688999980688095, 0.1062999963760376, -0.0649000033736229, -0.1525000035762787, 0.08900000154972076, 0.16249999403953552, 0.04360000044107437, 0.05790000036358833, 0.03099999949336052, 0.08129999786615372, -0.13009999692440033, -0.05380000174045563, 0.21150000393390656, -0.07119999825954437, 0.057100001722574234, -0.18549999594688416, 0.08340000361204147, 0.0357000008225441, 0.12319999933242798, -0.0763000026345253, -0.03359999880194664, -0.08540000021457672, 0.1518000066280365, -0.005499999970197678, -0.00139999995008111, 0.16279999911785126, 0.16609999537467957, 0.1331000030040741, -0.35499998927116394, -0.05959999933838844, -0.13860000669956207, 0.02160000056028366, 0.08640000224113464, -0.0640999972820282, 0.008100000210106373, 0.13420000672340393, -0.07880000025033951, 0.005799999926239252, 0.13359999656677246, 0.2802000045776367, 0.19339999556541443, -0.017400000244379044, -0.057100001722574234, 0.027000000700354576, 0.01119999960064888, -0.3091000020503998, 0.00559999980032444, 0.23499999940395355, 0.04170000180602074, 0.11389999836683273, -0.1225999966263771, 0.1281999945640564], [-0.01590000092983246, 0.2761000096797943, -0.2117999941110611, -0.0357000008225441, -0.03620000183582306, -0.07970000058412552, 0.14169999957084656, 0.06260000169277191, 0.06989999860525131, 0.11140000075101852, -0.2533000111579895, -0.07980000227689743, -0.06790000200271606, 0.012799999676644802, 0.20810000598430634, -0.0038999998942017555, -0.04830000177025795, -0.027000000700354576, 0.10679999738931656, 0.10369999706745148, -0.21879999339580536, -0.06689999997615814, -0.05339999869465828, -0.040699999779462814, 0.1881999969482422, 0.10199999809265137, 0.16539999842643738, -0.16169999539852142, -0.048500001430511475, 0.04919999837875366, 0.12070000171661377, 0.05950000137090683, 0.0010000000474974513, -0.0024999999441206455, -0.13590000569820404, 0.008200000040233135, -0.00930000003427267, 0.05959999933838844, 0.25859999656677246, 0.08659999817609787, -0.2976999878883362, -0.14630000293254852, -0.006000000052154064, -0.06199999898672104, 0.15489999949932098, 0.09109999984502792, 0.005200000014156103, 0.0357000008225441, -0.12610000371932983, 0.0348999984562397, 0.05299999937415123, 0.11069999635219574, -0.039400000125169754, 0.11739999800920486, -0.010499999858438969, 0.04390000179409981, 0.0272000003606081, -0.13840000331401825, 0.27390000224113464, 0.08659999817609787, 0.01810000091791153, -0.3305000066757202], [-0.13689999282360077, 0.04349999874830246, -0.07609999924898148, -0.12470000237226486, -0.00019999999494757503, 0.004800000227987766, 0.14329999685287476, 0.11640000343322754, -0.1525000035762787, -0.07819999754428864, -0.1873999983072281, -0.030700000002980232, 0.13330000638961792, -0.0771000012755394, -0.10639999806880951, 0.04170000180602074, 0.17239999771118164, 0.1639000028371811, 0.007699999958276749, -0.008299999870359898, 0.11860000342130661, -0.1177000030875206, -0.13210000097751617, 0.12780000269412994, -0.09120000153779984, 0.06270000338554382, -0.0019000000320374966, 0.14409999549388885, -0.29589998722076416, -0.09350000321865082, -0.23880000412464142, 0.09709999710321426, -0.04879999905824661, 0.00930000003427267, -0.23569999635219574, -0.04230000078678131, 0.07339999824762344, -0.1754000037908554, 0.09719999879598618, 0.004000000189989805, -0.09950000047683716, -0.10019999742507935, -0.10869999974966049, -0.08860000222921371, 0.030799999833106995, 0.05009999871253967, -0.2946999967098236, 0.23770000040531158, -0.13770000636577606, -0.014299999922513962, -0.11860000342130661, -0.05869999900460243, -0.2669999897480011, -0.06069999933242798, 0.11940000206232071, -0.03680000081658363, -0.015200000256299973, -0.020899999886751175, -0.2635999917984009, 0.06610000133514404, 0.03400000184774399, 0.11309999972581863], [0.13950000703334808, 0.05339999869465828, 0.1340000033378601, 0.1298000067472458, 0.21410000324249268, -0.002099999925121665, -0.133200004696846, 0.04019999876618385, 0.020099999383091927, 0.02319999970495701, -0.12759999930858612, -0.007600000128149986, -0.06310000270605087, -0.1451999992132187, 0.09390000253915787, 0.21279999613761902, 0.0007999999797903001, 0.21480000019073486, -0.007699999958276749, 0.09560000151395798, 0.028599999845027924, 0.019200000911951065, 0.07190000265836716, 0.11550000309944153, 0.0892999991774559, -0.02669999934732914, -0.02710000053048134, -0.06109999865293503, 0.15289999544620514, -0.18369999527931213, 0.2053000032901764, -0.04560000076889992, -0.11840000003576279, 0.04769999906420708, -0.2669000029563904, 0.10260000079870224, -0.0032999999821186066, 0.1421000063419342, 0.13410000503063202, 0.11230000108480453, 0.19760000705718994, -0.028300000354647636, 0.02710000053048134, 0.03350000083446503, -0.07689999788999557, 0.13740000128746033, -0.039799999445676804, 0.07400000095367432, 0.04100000113248825, -0.07959999889135361, -0.09730000048875809, -0.08550000190734863, 0.21119999885559082, -0.010099999606609344, -0.07270000129938126, 0.24160000681877136, -0.08259999752044678, -0.006399999838322401, -0.34310001134872437, 0.27379998564720154, -0.16220000386238098, -0.10109999775886536], [-0.04859999939799309, -0.11890000104904175, 0.1647000014781952, 0.18770000338554382, 0.019300000742077827, -0.21089999377727509, -0.1265999972820282, -0.10189999639987946, -0.23100000619888306, -0.07800000160932541, -0.35089999437332153, 0.2303999960422516, -0.03790000081062317, 0.009700000286102295, 0.07829999923706055, 0.0038999998942017555, 0.03579999879002571, -0.10249999910593033, 0.028699999675154686, 0.13950000703334808, 0.08259999752044678, 0.02810000069439411, -0.05689999833703041, -0.10000000149011612, 0.001500000013038516, 0.01640000008046627, 0.03579999879002571, 0.3188000023365021, 0.05939999967813492, -0.019700000062584877, -0.03420000150799751, 0.15129999816417694, 0.08150000125169754, 0.02070000022649765, 0.019600000232458115, 0.01979999989271164, 0.0771000012755394, -0.1987999975681305, 0.1096000000834465, -0.12219999730587006, 0.08110000193119049, 0.029999999329447746, 0.05640000104904175, -0.05869999900460243, -0.11349999904632568, 0.05009999871253967, -0.06830000132322311, -0.12200000137090683, -0.13369999825954437, 0.24629999697208405, -0.0803999975323677, 0.11890000104904175, 0.14499999582767487, -0.2773999869823456, -0.08320000022649765, 0.13089999556541443, 0.09120000153779984, -0.02630000002682209, 0.15150000154972076, -0.11069999635219574, 0.04690000042319298, -0.15970000624656677], [-0.03359999880194664, 0.06120000034570694, -0.2944999933242798, -0.08879999816417694, -0.14720000326633453, 0.08470000326633453, -0.014299999922513962, -0.06030000001192093, 0.031599998474121094, 0.11729999631643295, -0.13680000603199005, 0.1347000002861023, -0.2442999929189682, -0.09160000085830688, 0.2078000009059906, 0.13019999861717224, 0.08739999681711197, -0.10279999673366547, -0.10930000245571136, -0.06909999996423721, 0.05660000070929527, 0.04729999974370003, 0.07670000195503235, 0.03280000016093254, -0.011099999770522118, -0.14980000257492065, -0.20559999346733093, 0.049400001764297485, 0.13429999351501465, 0.26190000772476196, -0.017999999225139618, -0.13490000367164612, 0.07100000232458115, -0.048500001430511475, 0.11909999698400497, -0.003800000064074993, 0.0608999989926815, -0.0007999999797903001, 0.08370000123977661, -0.0038999998942017555, 0.032999999821186066, 0.16019999980926514, 0.03310000151395798, -0.04430000111460686, -0.00279999990016222, -0.2567000091075897, -0.2797999978065491, 0.11739999800920486, 0.21070000529289246, -0.02199999988079071, -0.22349999845027924, 0.15449999272823334, -0.03620000183582306, 0.11069999635219574, 0.00279999990016222, 0.060499999672174454, 0.10189999639987946, -0.1657000035047531, -0.20329999923706055, -0.13920000195503235, -0.08320000022649765, -0.08190000057220459], [-0.010099999606609344, -0.10769999772310257, -0.1379999965429306, -0.03449999913573265, -0.0066999997943639755, -0.09470000118017197, 0.016599999740719795, -0.06870000064373016, 0.07320000231266022, -0.055799998342990875, -0.0210999995470047, 0.02539999969303608, 0.19050000607967377, -0.04800000041723251, -0.14499999582767487, -0.07109999656677246, -0.16850000619888306, -0.0142000000923872, 0.13539999723434448, 0.09260000288486481, 0.1436000019311905, -0.0038999998942017555, 0.09189999848604202, 0.024000000208616257, 0.18019999563694, -0.05119999870657921, -0.14569999277591705, -0.1046999990940094, -0.2556000053882599, 0.007499999832361937, 0.06989999860525131, -0.16609999537467957, 0.12060000002384186, 0.1907999962568283, -0.061900001019239426, -0.01730000041425228, -0.06360000371932983, -0.0860000029206276, -0.1996999979019165, -0.12559999525547028, 0.041999999433755875, 0.17870000004768372, -0.04670000076293945, -0.3944000005722046, -0.09120000153779984, -0.15000000596046448, 0.0020000000949949026, 0.07460000365972519, -0.12939999997615814, 0.18930000066757202, 0.22470000386238098, -0.09539999812841415, 0.1889999955892563, 0.17820000648498535, -0.005200000014156103, 0.08510000258684158, 0.1151999980211258, -0.17499999701976776, -0.09390000253915787, 0.12189999967813492, -0.030899999663233757, -0.15469999611377716], [-0.02669999934732914, 0.0020000000949949026, 0.051899999380111694, -0.039799999445676804, -0.07509999722242355, 0.289000004529953, -0.022099999710917473, -0.13410000503063202, 0.1597999930381775, 0.004100000020116568, -0.018799999728798866, 0.10339999943971634, 0.03359999880194664, -0.09529999643564224, -0.18709999322891235, 0.03739999979734421, 0.10719999670982361, -0.3197999894618988, 0.027799999341368675, 0.12790000438690186, 0.14059999585151672, 0.16779999434947968, -0.05990000069141388, 0.00989999994635582, 0.08980000019073486, -0.05139999836683273, -0.057500001043081284, -0.16210000216960907, -0.07680000364780426, -0.035100001841783524, 0.10970000177621841, -0.1177000030875206, 0.013100000098347664, -0.11509999632835388, -0.06440000236034393, 0.2524999976158142, -0.10899999737739563, -0.053300000727176666, 0.06159999966621399, 0.2808000147342682, 0.06639999896287918, 0.024800000712275505, -0.08030000329017639, 0.027400000020861626, 0.15520000457763672, -0.023499999195337296, -0.25220000743865967, -0.24079999327659607, -0.10000000149011612, 0.05999999865889549, 0.07020000368356705, 0.1469999998807907, -0.09390000253915787, -0.28380000591278076, 0.08460000157356262, -0.06859999895095825, -0.008200000040233135, 0.09200000017881393, 0.06970000267028809, 0.23499999940395355, 0.026499999687075615, 0.020800000056624413], [-0.3790999948978424, 0.043299999088048935, 0.18199999630451202, 0.0007999999797903001, 0.014700000174343586, 0.2151000052690506, 0.03689999878406525, -0.1876000016927719, 0.017799999564886093, 0.05860000103712082, 0.1460999995470047, -0.19830000400543213, -0.0754999965429306, -0.18369999527931213, 0.08630000054836273, 0.06019999831914902, 0.0034000000450760126, 0.03920000046491623, -0.10540000349283218, -0.02539999969303608, 0.07810000330209732, 0.06449999660253525, -0.06159999966621399, 0.025299999862909317, -0.20739999413490295, -0.08340000361204147, -0.14110000431537628, 0.21539999544620514, -0.014999999664723873, -0.027799999341368675, -0.164000004529953, -0.10379999876022339, -0.0551999993622303, 0.04360000044107437, 0.05999999865889549, 0.125, 0.10610000044107437, -0.07000000029802322, 0.11509999632835388, 0.23589999973773956, -0.22509999573230743, -0.09589999914169312, -0.017400000244379044, -0.08269999921321869, -0.1995999962091446, -0.0031999999191612005, 0.28870001435279846, 0.11389999836683273, 0.0032999999821186066, 0.09730000048875809, 0.2076999992132187, 0.10050000250339508, 0.10859999805688858, 0.029999999329447746, -0.002899999963119626, 0.05909999832510948, -0.062199998646974564, -0.06759999692440033, 0.013100000098347664, 0.04659999907016754, -0.024299999698996544, -0.1940000057220459], [-0.06159999966621399, 0.10670000314712524, -0.11110000312328339, 0.15029999613761902, -0.022199999541044235, -0.2160000056028366, -0.1842000037431717, -0.22020000219345093, -0.007400000002235174, 0.08309999853372574, -0.1859000027179718, -0.06549999862909317, 0.3366999924182892, -0.09059999883174896, -0.0681999996304512, 0.007000000216066837, -0.03180000185966492, -0.07490000128746033, 0.04769999906420708, 0.1459999978542328, 0.2946000099182129, -0.14090000092983246, -0.0034000000450760126, -0.04540000110864639, -0.14390000700950623, -0.04699999839067459, -0.02889999933540821, -0.11029999703168869, 0.08590000122785568, -0.07750000059604645, -0.20160000026226044, -0.00839999970048666, 0.0032999999821186066, -0.005499999970197678, -0.11739999800920486, 0.003100000089034438, 0.02280000038444996, 0.0333000011742115, -0.13330000638961792, 0.07370000332593918, -0.05119999870657921, 0.12110000103712082, 0.029500000178813934, 0.2542000114917755, 0.14110000431537628, 0.06109999865293503, 0.04600000008940697, -0.06319999694824219, 0.30070000886917114, -0.11540000140666962, 0.09200000017881393, -0.0608999989926815, -0.1687999963760376, 0.05770000070333481, 0.05570000037550926, 0.0794999971985817, -0.13650000095367432, -0.15719999372959137, 0.10819999873638153, -0.11089999973773956, -0.1914999932050705, -0.08309999853372574], [-0.08799999952316284, 0.07919999957084656, -0.09019999951124191, -0.14589999616146088, -0.10819999873638153, 0.11779999732971191, -0.02759999968111515, -0.1289999932050705, 0.09139999747276306, -0.07989999651908875, -0.05310000106692314, -0.06719999760389328, 0.10499999672174454, 0.009999999776482582, 0.125, 0.10360000282526016, 0.05400000140070915, 0.08799999952316284, 0.1762000024318695, 0.06610000133514404, 0.07360000163316727, -0.07339999824762344, 0.1005999967455864, -0.1468999981880188, -0.1615000069141388, -0.10689999908208847, -0.18850000202655792, -0.17059999704360962, -0.05829999968409538, -0.05950000137090683, 0.07569999992847443, 0.1881999969482422, 0.006300000008195639, 0.08959999680519104, -0.029200000688433647, 0.32199999690055847, -0.26840001344680786, 0.05510000139474869, 0.007499999832361937, -0.18140000104904175, -0.14900000393390656, -0.06530000269412994, 0.20319999754428864, 0.026000000536441803, -0.07959999889135361, 0.12120000272989273, -0.031199999153614044, 0.09610000252723694, -0.11400000005960464, -0.03550000116229057, -0.14000000059604645, 0.06109999865293503, 0.24770000576972961, -0.03229999914765358, -0.10080000013113022, 0.11800000071525574, 0.03739999979734421, 0.03060000017285347, 0.0786999985575676, -0.19439999759197235, 0.11150000244379044, 0.33469998836517334], [-0.03550000116229057, 0.11169999837875366, -0.10130000114440918, -0.11400000005960464, -0.2168000042438507, -0.04729999974370003, -0.13590000569820404, -0.11420000344514847, -0.1031000018119812, -0.13580000400543213, 0.010599999688565731, 0.06530000269412994, -0.14429999887943268, 0.1160999983549118, -0.031599998474121094, -0.002899999963119626, 0.1785999983549118, -0.13570000231266022, 0.09229999780654907, -0.17339999973773956, 0.04309999942779541, -0.03909999877214432, 0.1793999969959259, -0.17599999904632568, 0.06639999896287918, 0.1200999990105629, 0.10400000214576721, -0.0885000005364418, 0.3343000113964081, -0.148499995470047, -0.2418999969959259, -0.12110000103712082, -0.07450000196695328, 0.07479999959468842, -0.13729999959468842, -0.07880000025033951, -0.17249999940395355, -0.2849999964237213, -0.05999999865889549, -0.08529999852180481, -0.06369999796152115, -0.18150000274181366, -0.015200000256299973, -0.09510000050067902, 0.06769999861717224, -0.05460000038146973, 0.19519999623298645, 0.0494999997317791, 0.04780000075697899, -0.14350000023841858, 0.04529999941587448, 0.020999999716877937, 0.07620000094175339, -0.09120000153779984, 0.008700000122189522, -0.00019999999494757503, 0.1316000074148178, 0.11640000343322754, -0.1574999988079071, 0.24500000476837158, 0.02280000038444996, -0.07320000231266022], [0.0066999997943639755, -0.09470000118017197, -0.04879999905824661, 0.2418999969959259, 0.050200000405311584, 0.10339999943971634, -0.0421999990940094, -0.03020000085234642, -0.11940000206232071, -0.015799999237060547, -0.06560000032186508, -0.034699998795986176, 0.03920000046491623, 0.21580000221729279, 0.07100000232458115, -0.36239999532699585, 0.014499999582767487, 0.2711000144481659, 0.02969999983906746, -0.08049999922513962, -0.0803999975323677, -0.07329999655485153, 0.11720000207424164, 0.12929999828338623, 0.08150000125169754, -0.14480000734329224, 0.010700000450015068, -0.10559999942779541, -0.03620000183582306, 0.00839999970048666, -0.14139999449253082, -0.01140000019222498, 0.3422999978065491, 0.07530000060796738, 0.11630000174045563, 0.12189999967813492, -0.05050000175833702, -0.051600001752376556, 0.04149999842047691, 0.2134000062942505, -0.07530000060796738, -0.1039000004529953, -0.24650000035762787, -0.0013000000035390258, -0.11309999972581863, -0.07959999889135361, -0.19529999792575836, 0.019300000742077827, 0.193900004029274, -0.14790000021457672, 0.052799999713897705, 0.08150000125169754, 0.007499999832361937, -0.06629999727010727, -0.14589999616146088, 0.22120000422000885, 0.0430000014603138, 0.1298000067472458, 0.10750000178813934, 0.10329999774694443, -0.0017999999690800905, 0.053599998354911804], [0.4327000081539154, 0.10580000281333923, 0.025499999523162842, -0.09769999980926514, -0.0731000006198883, 0.13030000030994415, 0.008799999952316284, -0.05590000003576279, -0.0406000018119812, 0.1648000031709671, -0.019899999722838402, 0.0706000030040741, 0.009399999864399433, 0.15569999814033508, -0.10090000182390213, -0.007199999876320362, -0.03610000014305115, -0.08760000020265579, -0.16359999775886536, -0.07270000129938126, 0.14010000228881836, 0.04050000011920929, -0.12380000203847885, 0.04520000144839287, -0.029899999499320984, -0.26260000467300415, -0.09870000183582306, -0.007000000216066837, 0.06509999930858612, 0.011900000274181366, 0.11949999630451202, 0.11620000004768372, -0.11089999973773956, -0.1476999968290329, -0.12939999997615814, -0.09629999846220016, 0.05900000035762787, -0.1875, -0.11580000072717667, -0.02930000051856041, -0.16019999980926514, -0.23970000445842743, -0.029200000688433647, 0.0697999969124794, -0.11900000274181366, 0.05700000002980232, -0.07819999754428864, 0.2531000077724457, 0.13420000672340393, 0.3174000084400177, 0.12200000137090683, -0.15950000286102295, 0.043800000101327896, 0.05860000103712082, -0.006599999964237213, 0.14409999549388885, -0.006399999838322401, 0.10840000212192535, 0.13519999384880066, 0.0010999999940395355, 0.013500000350177288, -0.027300000190734863], [0.0031999999191612005, -0.15029999613761902, 0.16050000488758087, -0.05299999937415123, -0.219200000166893, 0.16859999299049377, -0.01549999974668026, 0.11840000003576279, -0.24449999630451202, -0.002300000051036477, -0.08129999786615372, -0.020500000566244125, -0.1396999955177307, 0.093299999833107, -0.16869999468326569, 0.07280000299215317, -0.2870999872684479, -0.07519999891519547, 0.299699991941452, 0.13519999384880066, -0.1168999969959259, -0.0843999981880188, 0.07959999889135361, 0.09059999883174896, 0.0649000033736229, 0.15479999780654907, -0.1776999980211258, -0.022199999541044235, 0.020099999383091927, -0.1800999939441681, 0.07169999927282333, 0.010300000198185444, -0.10119999945163727, -0.10170000046491623, 0.11400000005960464, -0.006399999838322401, -0.06369999796152115, 0.1518000066280365, -0.08799999952316284, -0.02930000051856041, -0.26750001311302185, -0.0869000032544136, 0.04190000146627426, 0.008200000040233135, -0.22390000522136688, -0.1331000030040741, -0.0478999987244606, -0.05299999937415123, 0.1137000024318695, -0.08739999681711197, -0.025800000876188278, -0.03400000184774399, -0.1688999980688095, -0.16590000689029694, 0.10580000281333923, 0.08980000019073486, -0.09139999747276306, -0.18690000474452972, -0.0949999988079071, -0.08479999750852585, -0.07050000131130219, -0.11840000003576279], [0.10140000283718109, -0.18549999594688416, -0.1006999984383583, -0.16419999301433563, -0.029400000348687172, -0.014700000174343586, 0.05169999971985817, -0.21050000190734863, -0.0843999981880188, 0.0210999995470047, 0.018699999898672104, -0.15479999780654907, 0.10209999978542328, 0.13680000603199005, -0.03660000115633011, 0.1664000004529953, 0.10109999775886536, 0.1623000055551529, 0.03799999877810478, -0.08150000125169754, -0.010300000198185444, -0.04230000078678131, -0.08349999785423279, -0.015799999237060547, 0.2071000039577484, 0.009700000286102295, 0.1550000011920929, -0.07289999723434448, -0.10209999978542328, -0.022700000554323196, -0.1979999989271164, -0.011300000362098217, -0.1738000065088272, 0.12189999967813492, 0.10589999705553055, -0.11240000277757645, -0.053199999034404755, 0.047600001096725464, -0.01600000075995922, 0.2840999960899353, -0.06719999760389328, 0.031599998474121094, 0.1151999980211258, 0.017400000244379044, -0.1436000019311905, 0.1151999980211258, -0.121799997985363, -0.23309999704360962, 0.12139999866485596, 0.24860000610351562, -0.2442999929189682, 0.10689999908208847, 0.27399998903274536, 0.04610000178217888, 0.10419999808073044, -0.18629999458789825, -0.0006000000284984708, 0.08889999985694885, -0.031199999153614044, -0.06469999998807907, -0.17569999396800995, -0.11079999804496765], [-0.05429999902844429, -0.012600000016391277, -0.16859999299049377, 0.12030000239610672, -0.05570000037550926, -0.08609999716281891, -0.0828000009059906, -0.04699999839067459, -0.03200000151991844, 0.1899999976158142, -0.19200000166893005, -0.13590000569820404, 0.013500000350177288, -0.0003000000142492354, -0.24660000205039978, 0.10010000318288803, -0.257999986410141, 0.06350000202655792, -0.03830000013113022, -0.23639999330043793, -0.26010000705718994, -0.06480000168085098, -0.18880000710487366, 0.12800000607967377, -0.0471000000834465, -0.035100001841783524, -0.05079999938607216, -0.06469999998807907, -0.02500000037252903, -0.07169999927282333, 0.004000000189989805, 0.05400000140070915, -0.008500000461935997, -0.1981000006198883, 0.10170000046491623, 0.20479999482631683, 0.12150000035762787, -0.07500000298023224, 0.0729999989271164, -0.029100000858306885, 0.09399999678134918, 0.0421999990940094, 0.03849999979138374, -0.04230000078678131, 0.2759999930858612, -0.03200000151991844, 0.11159999668598175, 0.10580000281333923, 0.04129999876022339, -0.027499999850988388, 0.13510000705718994, 0.04190000146627426, 0.2766999900341034, -0.20100000500679016, 0.2199999988079071, -0.0340999998152256, 0.19869999587535858, 0.11029999703168869, -0.13459999859333038, -0.0729999989271164, 0.03680000081658363, 0.04349999874830246], [0.03420000150799751, -0.02239999920129776, 0.017000000923871994, 0.29409998655319214, -0.06419999897480011, 0.04430000111460686, -0.07769999653100967, -0.05310000106692314, 0.07100000232458115, -0.15230000019073486, 0.0008999999845400453, -0.002300000051036477, 0.1785999983549118, 0.09030000120401382, -0.012900000438094139, 0.13040000200271606, 0.17960000038146973, -0.07370000332593918, 0.2362000048160553, 0.1096000000834465, -0.11630000174045563, -0.09189999848604202, 0.004999999888241291, 0.25929999351501465, -0.04490000009536743, 0.20589999854564667, -0.008999999612569809, 0.11379999667406082, 0.04399999976158142, 0.156800001859</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>[[[0.05310000106692314, -0.025800000876188278, 0.03319999948143959, 0.05620000138878822, 0.1736000031232834, -0.06069999933242798, -0.0737999975681305, -0.07989999651908875, 0.039900001138448715, -0.17720000445842743, -0.11500000208616257, -0.0066999997943639755, 0.06360000371932983, 0.05889999866485596, -0.12530000507831573, -0.03680000081658363, -0.08470000326633453, 0.10029999911785126, -0.012500000186264515, -0.09619999676942825, 0.09149999916553497, 0.10570000112056732, 0.14390000700950623, 0.050999999046325684, 0.09589999914169312, -0.024700000882148743, -0.06840000301599503, 0.08789999783039093, 0.02810000069439411, 0.09080000221729279, 0.05180000141263008, -0.05090000107884407, 0.07259999960660934, 0.07810000330209732, 0.049300000071525574, 0.12349999696016312, 0.04729999974370003, 0.01850000023841858, 0.09030000120401382, -0.019600000232458115, 0.14069999754428864, 0.029200000688433647, -0.07660000026226044, 0.1054999977350235, -0.07150000333786011, -0.009800000116229057, -0.020500000566244125, -0.048900000751018524, 0.029200000688433647, -0.08479999750852585, -0.05770000070333481, 0.13079999387264252, 0.09570000320672989, 0.048900000751018524, -0.06859999895095825, -0.05590000003576279, -0.08340000361204147, -0.020800000056624413, -0.07129999995231628, 0.012199999764561653, -0.07989999651908875, -0.05829999968409538], [-0.11320000141859055, -0.013199999928474426, 0.02449999935925007, -0.07900000363588333, 0.027899999171495438, 0.08139999955892563, 0.17000000178813934, 0.00139999995008111, -0.10480000078678131, 0.04349999874830246, 0.04129999876022339, 0.051500000059604645, -0.1665000021457672, -0.10199999809265137, 0.011800000444054604, 0.04479999840259552, 0.08020000159740448, -0.029100000858306885, 0.09359999746084213, 0.005499999970197678, -0.03359999880194664, -0.018300000578165054, 0.029100000858306885, -0.07010000199079514, -0.12430000305175781, 0.09319999814033508, 0.08229999989271164, -0.00419999985024333, -0.06939999759197235, -0.093299999833107, -0.1428000032901764, 0.03269999846816063, -0.009999999776482582, -0.008500000461935997, -0.0015999999595806003, 0.003800000064074993, -0.04129999876022339, -0.13689999282360077, -0.03189999982714653, -0.09009999781847, -0.17339999973773956, -0.06800000369548798, 0.11309999972581863, -0.10400000214576721, 0.05249999836087227, 0.05530000105500221, -0.0015999999595806003, -0.0026000000070780516, 0.1006999984383583, 0.10760000348091125, -0.03819999843835831, -0.07750000059604645, 0.027000000700354576, -0.042500000447034836, 0.07159999758005142, 0.08139999955892563, 0.023499999195337296, 0.12540000677108765, 0.02410000003874302, -0.03539999946951866, 0.03590000048279762, 0.0731000006198883]], [[0.1785999983549118, -0.10459999740123749, -0.2667999863624573, 0.328000009059906, -0.1307000070810318, -0.2838999927043915, 0.05299999937415123, -0.01730000041425228, 0.16670000553131104, -0.13269999623298645, 0.23989999294281006, 0.0681999996304512, -0.10570000112056732, 0.05469999834895134, -0.11630000174045563, 0.15870000422000885, -0.02419999986886978, 0.10639999806880951, -0.15240000188350677, -0.131400004029274, 0.09470000118017197, 0.16290000081062317, 0.23360000550746918, -0.03550000116229057, -0.06030000001192093, 0.06769999861717224, -0.18170000612735748, -0.08349999785423279, -0.0471000000834465, 0.1647000014781952, -0.014000000432133675, 0.13860000669956207, 0.053199999034404755, 0.10649999976158142, -0.15449999272823334, -0.033799998462200165, 0.12330000102519989, 0.11630000174045563, -0.017500000074505806, 0.15790000557899475, 0.048700001090765, 0.1444000005722046, -0.028200000524520874, 0.34599998593330383, -0.18070000410079956, -0.041099999099969864, 0.21089999377727509, 0.029899999499320984, -0.1656000018119812, 0.23960000276565552, 0.03689999878406525, 0.4480000138282776, -0.15530000627040863, -0.08429999649524689, 0.019899999722838402, -0.03880000114440918, 0.0608999989926815, -0.08709999918937683, 0.015300000086426735, 0.3675000071525574, 0.07760000228881836, 0.011699999682605267], [-0.13940000534057617, -0.08380000293254852, 0.0012000000569969416, -0.01940000057220459, 0.11400000005960464, 0.041200000792741776, -0.15860000252723694, -0.22660000622272491, -0.149399995803833, -0.15760000050067902, -0.0714000016450882, 0.05420000106096268, -0.15770000219345093, 0.22840000689029694, 0.11620000004768372, 0.03319999948143959, -0.0908999964594841, -0.32339999079704285, -0.0625, 0.1784999966621399, -0.06949999928474426, -0.1776999980211258, 0.10740000009536743, 0.15610000491142273, 0.28459998965263367, -0.328000009059906, -0.11879999935626984, 0.16179999709129333, -0.266400009393692, -0.11810000240802765, 0.11010000109672546, 0.0885000005364418, 0.04360000044107437, 0.02800000086426735, -0.0868000015616417, -0.02280000038444996, 0.16359999775886536, -0.09049999713897705, 0.00430000014603138, 0.2160000056028366, 0.04309999942779541, -0.04749999940395355, 0.06669999659061432, 0.14569999277591705, 0.06340000033378601, 0.0982000008225441, 0.1907999962568283, 0.002300000051036477, 0.006200000178068876, -0.20839999616146088, -0.07320000231266022, -0.08429999649524689, -0.07720000296831131, 0.052299998700618744, 0.013399999588727951, -0.08320000022649765, -0.010200000368058681, -0.17170000076293945, -0.08449999988079071, 0.017000000923871994, -0.07720000296831131, 0.07190000265836716], [0.05979999899864197, 0.0032999999821186066, -0.08479999750852585, 0.06300000101327896, -0.13449999690055847, 0.12370000034570694, -0.029400000348687172, 0.19339999556541443, 0.0044999998062849045, 0.06620000302791595, 0.05959999933838844, -0.0003000000142492354, 0.1525000035762787, 0.1185000017285347, -0.11959999799728394, -0.148499995470047, 0.2651999890804291, -0.11840000003576279, -0.32499998807907104, 0.18860000371932983, -0.13030000030994415, -0.29350000619888306, 0.065700002014637, -0.11729999631643295, 0.05979999899864197, 0.09359999746084213, 0.0729999989271164, -0.10790000110864639, 0.007799999788403511, -0.05469999834895134, -0.052000001072883606, -0.025200000032782555, 0.005499999970197678, -0.007300000172108412, -0.1200999990105629, -0.007300000172108412, 0.013000000268220901, 0.23839999735355377, 0.3571999967098236, -0.07699999958276749, 0.04039999842643738, 0.10300000011920929, 0.05660000070929527, -0.29159998893737793, -0.18230000138282776, -0.15000000596046448, 0.2583000063896179, 0.1761000007390976, 0.14409999549388885, 0.1347000002861023, 0.06469999998807907, 0.09070000052452087, -0.04010000079870224, -0.22499999403953552, -0.15330000221729279, 0.04410000145435333, -0.05480000004172325, 0.057100001722574234, -0.032999999821186066, -0.1762000024318695, -0.04989999905228615, 0.1396999955177307], [0.00800000037997961, -0.052400000393390656, -0.11069999635219574, -0.010900000110268593, -0.043299999088048935, -0.03889999911189079, 0.23029999434947968, -0.10279999673366547, 0.10610000044107437, 0.21060000360012054, -0.023600000888109207, 0.1103999987244606, 0.06379999965429306, 0.04019999876618385, 0.038600001484155655, -0.05310000106692314, -0.08990000188350677, -0.04170000180602074, -0.03139999881386757, -0.07020000368356705, 0.16019999980926514, -0.31690001487731934, 0.10620000213384628, 0.0608999989926815, 0.05999999865889549, 0.12489999830722809, -0.13420000672340393, 0.23639999330043793, 0.18709999322891235, 0.10189999639987946, 0.24070000648498535, -0.022099999710917473, -0.16009999811649323, 0.46560001373291016, 0.11469999700784683, 0.11999999731779099, 0.01720000058412552, 0.05909999832510948, -0.012400000356137753, 0.025200000032782555, 0.2345999926328659, -0.17020000517368317, -0.26330000162124634, 0.07609999924898148, -0.09210000187158585, 0.1088000014424324, -0.026399999856948853, -0.13349999487400055, -0.058800000697374344, -0.13590000569820404, -0.0020000000949949026, 0.09290000051259995, 0.019999999552965164, -0.2231999933719635, 0.041099999099969864, -0.10750000178813934, -0.00019999999494757503, -0.030799999833106995, -0.07580000162124634, -0.003800000064074993, -0.12620000541210175, 0.06120000034570694], [0.18850000202655792, -0.01940000057220459, 0.12460000067949295, -0.1266999989748001, -0.0066999997943639755, -0.2125999927520752, 0.21549999713897705, -0.03920000046491623, 0.09440000355243683, -0.13899999856948853, 0.03869999945163727, 0.09920000284910202, 0.07440000027418137, 0.18799999356269836, -0.14229999482631683, -0.1573999971151352, 0.03830000013113022, 0.11969999969005585, -0.23909999430179596, 0.17010000348091125, 0.05700000002980232, -0.12939999997615814, -0.025800000876188278, 0.14640000462532043, -0.08900000154972076, 0.07970000058412552, -0.010400000028312206, 0.11919999867677689, 0.1703999936580658, -0.032499998807907104, -0.11739999800920486, -0.07039999961853027, 0.2393999993801117, -0.06679999828338623, 0.1574999988079071, 0.24449999630451202, -0.04769999906420708, 0.11150000244379044, -0.04800000041723251, -0.0989999994635582, -0.039900001138448715, -0.18359999358654022, 0.2037999927997589, 0.08470000326633453, 0.2513999938964844, -0.2433999925851822, 0.027499999850988388, 0.1720000058412552, -0.17479999363422394, 0.020999999716877937, -0.07360000163316727, 0.05139999836683273, 0.27880001068115234, 0.045899998396635056, 0.09539999812841415, -0.13670000433921814, -0.14380000531673431, -0.11940000206232071, -0.00019999999494757503, 0.24580000340938568, -0.23319999873638153, -0.033900000154972076], [-0.1678999960422516, 0.1145000010728836, -0.09929999709129333, -0.05770000070333481, -0.04309999942779541, 0.041600000113248825, 0.05950000137090683, 0.33169999718666077, -0.14710000157356262, 0.034299999475479126, -0.14470000565052032, 0.03280000016093254, -0.09430000185966492, -0.17409999668598175, 0.17870000004768372, 0.19709999859333038, 0.037300001829862595, 0.0348999984562397, 0.10939999669790268, 0.09880000352859497, -0.21199999749660492, -0.030500000342726707, 0.12439999729394913, -0.05510000139474869, -0.02019999921321869, -0.3122999966144562, 0.14339999854564667, -0.08649999648332596, 0.07919999957084656, -0.06620000302791595, -0.11550000309944153, -0.0778999999165535, 0.19470000267028809, -0.021900000050663948, -0.02759999968111515, 0.08470000326633453, 0.17419999837875366, 0.03999999910593033, -0.3571999967098236, -0.13359999656677246, -0.16009999811649323, -0.026399999856948853, 0.12809999287128448, -0.11379999667406082, -0.00930000003427267, 0.1972000002861023, -0.023499999195337296, 0.04190000146627426, 0.12759999930858612, 0.3698999881744385, 0.2484000027179718, -0.09629999846220016, -0.06859999895095825, -0.000699999975040555, 0.003000000026077032, -0.33719998598098755, -0.07440000027418137, 0.30250000953674316, 0.09799999743700027, 0.03739999979734421, -0.11159999668598175, 0.08250000327825546], [-0.010499999858438969, 0.30959999561309814, -0.22290000319480896, -0.09910000115633011, -0.13979999721050262, -0.06319999694824219, 0.20469999313354492, 0.17589999735355377, 0.018799999728798866, 0.1445000022649765, -0.20550000667572021, -0.12860000133514404, -0.10580000281333923, 0.0038999998942017555, 0.29589998722076416, 0.032999999821186066, -0.065700002014637, -0.03460000082850456, 0.17430000007152557, 0.10840000212192535, -0.25119999051094055, -0.08219999819993973, -0.12290000170469284, -0.015200000256299973, 0.11320000141859055, 0.0364999994635582, 0.22470000386238098, -0.29260000586509705, -0.08699999749660492, 0.030799999833106995, 0.0421999990940094, 0.06509999930858612, 0.07859999686479568, -0.0142000000923872, -0.15080000460147858, -0.012400000356137753, 0.016699999570846558, -0.01940000057220459, 0.243599995970726, 0.019300000742077827, -0.3296999931335449, -0.1907999962568283, 0.04430000111460686, -0.12610000371932983, 0.19179999828338623, 0.14309999346733093, 0.03779999911785126, 0.09589999914169312, -0.1282999962568283, 0.10239999741315842, 0.10809999704360962, 0.03189999982714653, -0.052000001072883606, 0.09149999916553497, -0.04149999842047691, 0.033399999141693115, -0.021199999377131462, -0.07530000060796738, 0.3280999958515167, 0.07519999891519547, 0.020500000566244125, -0.33000001311302185], [-0.21170000731945038, 0.06870000064373016, -0.09040000289678574, -0.0820000022649765, -0.0012000000569969416, 0.0406000018119812, 0.07479999959468842, 0.06469999998807907, -0.1371999979019165, -0.037700001150369644, -0.16680000722408295, 0.00860000029206276, 0.08810000121593475, -0.14630000293254852, -0.047600001096725464, 0.052000001072883606, 0.1453000009059906, 0.11410000175237656, -0.012600000016391277, 0.0471000000834465, 0.10570000112056732, -0.041099999099969864, -0.11829999834299088, 0.08389999717473984, -0.04410000145435333, 0.06340000033378601, -0.07240000367164612, 0.11320000141859055, -0.33820000290870667, -0.07699999958276749, -0.211899995803833, 0.10019999742507935, -0.022700000554323196, -0.012799999676644802, -0.28439998626708984, -0.10620000213384628, 0.15860000252723694, -0.14429999887943268, 0.10350000113248825, 0.04439999908208847, -0.14010000228881836, -0.10010000318288803, -0.18629999458789825, -0.04259999841451645, -0.023499999195337296, 0.05139999836683273, -0.29269999265670776, 0.12370000034570694, -0.08389999717473984, 0.021900000050663948, -0.16539999842643738, -0.02199999988079071, -0.3456000089645386, -0.05739999935030937, 0.07639999687671661, 0.002400000113993883, -0.030500000342726707, -0.09149999916553497, -0.3192000091075897, 0.0502999983727932, 0.061900001019239426, 0.1607999950647354], [0.17669999599456787, 0.01549999974668026, 0.12160000205039978, 0.14669999480247498, 0.2295999974012375, -0.07050000131130219, -0.1762000024318695, 0.008799999952316284, 0.09049999713897705, -0.009600000455975533, -0.10989999771118164, 0.0608999989926815, -0.05730000138282776, -0.1542000025510788, 0.026200000196695328, 0.32820001244544983, 0.12439999729394913, 0.2206999957561493, -0.09950000047683716, 0.08529999852180481, 0.029100000858306885, 0.1031000018119812, 0.06129999831318855, 0.053199999034404755, 0.1581999957561493, 0.017100000753998756, -0.04399999976158142, -0.07530000060796738, 0.18490000069141388, -0.11259999871253967, 0.2134000062942505, -0.06639999896287918, -0.002199999988079071, 0.09950000047683716, -0.26840001344680786, 0.10199999809265137, -0.03269999846816063, 0.17260000109672546, 0.15690000355243683, 0.1842000037431717, 0.2775999903678894, -0.01860000006854534, 0.010499999858438969, 0.11209999769926071, -0.13249999284744263, 0.06939999759197235, -0.019999999552965164, 0.024700000882148743, -0.042899999767541885, -0.0714000016450882, -0.054499998688697815, 0.007600000128149986, 0.21580000221729279, 0.03350000083446503, -0.026200000196695328, 0.2264000028371811, -0.07590000331401825, -0.04809999838471413, -0.33489999175071716, 0.2759000062942505, -0.20479999482631683, -0.08380000293254852], [-0.13529999554157257, -0.07280000299215317, 0.12049999833106995, 0.19030000269412994, -0.03460000082850456, -0.13259999454021454, -0.1581999957561493, -0.12780000269412994, -0.26660001277923584, -0.01940000057220459, -0.4223000109195709, 0.22419999539852142, -0.12389999628067017, -0.0763000026345253, 0.15760000050067902, 0.023000000044703484, -0.004699999932199717, -0.17080000042915344, 0.09920000284910202, 0.22190000116825104, 0.04399999976158142, 0.06040000170469284, -0.06069999933242798, -0.1071000024676323, 0.0003000000142492354, 0.09839999675750732, 0.008899999782443047, 0.2612000107765198, -0.024299999698996544, -0.01979999989271164, -0.06499999761581421, 0.16369999945163727, 0.09189999848604202, -0.01979999989271164, -0.04039999842643738, -0.05700000002980232, 0.12549999356269836, -0.21879999339580536, 0.11840000003576279, -0.12880000472068787, 0.0015999999595806003, -0.0340999998152256, 0.004999999888241291, -0.05249999836087227, -0.14480000734329224, 0.05700000002980232, -0.07090000063180923, -0.24040000140666962, -0.04309999942779541, 0.31929999589920044, -0.14020000398159027, 0.11569999903440475, 0.09059999883174896, -0.2962999939918518, -0.17020000517368317, 0.1738000065088272, 0.008700000122189522, -0.02800000086426735, 0.11909999698400497, -0.12189999967813492, 0.1031000018119812, -0.07850000262260437], [-0.09679999947547913, 0.07739999890327454, -0.34279999136924744, -0.07850000262260437, -0.16290000081062317, 0.15790000557899475, -0.03060000017285347, -0.022700000554323196, 0.004699999932199717, 0.09019999951124191, -0.2222999930381775, 0.17000000178813934, -0.3237000107765198, -0.16290000081062317, 0.274399995803833, 0.19699999690055847, 0.07280000299215317, -0.1137000024318695, -0.10840000212192535, -0.00839999970048666, -0.0005000000237487257, 0.06880000233650208, 0.10859999805688858, -0.011699999682605267, -0.014600000344216824, 0.05620000138878822, -0.22599999606609344, 0.021800000220537186, 0.07959999889135361, 0.2669000029563904, -0.07530000060796738, -0.11590000241994858, 0.09839999675750732, -0.05620000138878822, 0.0771000012755394, -0.06849999725818634, 0.0908999964594841, -0.018799999728798866, 0.11209999769926071, -0.002899999963119626, -0.03909999877214432, 0.11150000244379044, 0.004699999932199717, -0.0560000017285347, -0.026399999856948853, -0.25870001316070557, -0.30869999527931213, 0.03280000016093254, 0.2467000037431717, 0.023600000888109207, -0.28839999437332153, 0.15620000660419464, -0.062199998646974564, 0.1023000031709671, -0.062199998646974564, 0.11630000174045563, 0.01899999938905239, -0.15189999341964722, -0.2071000039577484, -0.19349999725818634, -0.04270000010728836, 0.01549999974668026], [-0.0560000017285347, -0.0851999968290329, -0.14959999918937683, -0.012000000104308128, -0.0026000000070780516, -0.028599999845027924, -0.023000000044703484, -0.026000000536441803, 0.016100000590085983, -0.09040000289678574, -0.15029999613761902, 0.05130000039935112, 0.15320000052452087, -0.08900000154972076, -0.08060000091791153, -0.08179999887943268, -0.19059999287128448, 0.0031999999191612005, 0.1793999969959259, 0.1509000062942505, 0.14339999854564667, -0.0348999984562397, 0.16410000622272491, 0.009999999776482582, 0.1696999967098236, 0.06859999895095825, -0.17229999601840973, -0.05270000174641609, -0.3116999864578247, -0.03889999911189079, 0.058800000697374344, -0.13600000739097595, 0.08950000256299973, 0.19609999656677246, -0.08139999955892563, -0.024800000712275505, -0.030700000002980232, -0.0771000012755394, -0.14880000054836273, -0.17640000581741333, -0.030700000002980232, 0.16750000417232513, -0.09300000220537186, -0.44929999113082886, -0.09099999815225601, -0.14309999346733093, -0.09730000048875809, 0.004800000227987766, -0.0697999969124794, 0.17419999837875366, 0.1128000020980835, -0.15049999952316284, 0.18230000138282776, 0.15449999272823334, -0.08789999783039093, 0.1518000066280365, 0.031199999153614044, -0.13249999284744263, -0.16179999709129333, 0.11420000344514847, -0.02590000070631504, -0.07810000330209732], [-0.0024999999441206455, -0.04190000146627426, 0.06469999998807907, 0.03869999945163727, 0.01080000028014183, 0.2150000035762787, -0.08889999985694885, -0.19550000131130219, 0.25119999051094055, -0.014100000262260437, 0.025299999862909317, 0.2125999927520752, 0.039000000804662704, -0.10109999775886536, -0.29649999737739563, 0.11180000007152557, 0.2574999928474426, -0.3158999979496002, -0.07670000195503235, 0.10530000180006027, 0.18050000071525574, 0.26420000195503235, -0.06360000371932983, -0.04830000177025795, 0.18289999663829803, -0.06210000067949295, -0.12970000505447388, -0.16660000383853912, -0.0017999999690800905, 0.04010000079870224, 0.20350000262260437, -0.121799997985363, 0.06319999694824219, -0.07500000298023224, -0.06120000034570694, 0.25760000944137573, -0.10350000113248825, 0.03709999844431877, 0.06880000233650208, 0.3734999895095825, 0.12330000102519989, 0.0803999975323677, -0.13930000364780426, 0.12280000001192093, 0.09799999743700027, -0.09459999948740005, -0.25, -0.29809999465942383, -0.16820000112056732, 0.017500000074505806, 0.09650000184774399, 0.25360000133514404, -0.12020000070333481, -0.23989999294281006, 0.13699999451637268, -0.065700002014637, 0.07119999825954437, -0.0010000000474974513, 0.023399999365210533, 0.2736000120639801, -0.007799999788403511, 0.019700000062584877], [-0.2793000042438507, -0.0203000009059906, 0.21439999341964722, 0.05700000002980232, 0.0560000017285347, 0.11840000003576279, 0.01510000042617321, -0.21209999918937683, 0.14710000157356262, -0.0035000001080334187, 0.20000000298023224, -0.16249999403953552, -0.06449999660253525, -0.1881999969482422, -0.026000000536441803, 0.10329999774694443, 0.0982000008225441, 0.06769999861717224, -0.21809999644756317, -0.10769999772310257, 0.13040000200271606, 0.14589999616146088, -0.0617000013589859, 0.006899999920278788, -0.11710000038146973, -0.1031000018119812, -0.18160000443458557, 0.17870000004768372, 0.12080000340938568, 0.06530000269412994, -0.1120000034570694, -0.1088000014424324, 0.05820000171661377, 0.10980000346899033, 0.08330000191926956, 0.14880000054836273, 0.12929999828338623, -0.023000000044703484, 0.1071000024676323, 0.3353999853134155, -0.11659999936819077, -0.03920000046491623, -0.028699999675154686, 0.02019999921321869, -0.23340000212192535, -0.0575999990105629, 0.3646000027656555, 0.1729000061750412, -0.13050000369548798, 0.09690000116825104, 0.29739999771118164, 0.2379000037908554, 0.05339999869465828, 0.11060000211000443, 0.0697999969124794, 0.05810000002384186, -0.0017999999690800905, -0.1696999967098236, 0.03629999980330467, 0.09880000352859497, -0.0917000025510788, -0.23880000412464142], [-0.13989999890327454, 0.17440000176429749, -0.12970000505447388, 0.1388999968767166, -0.0731000006198883, -0.13910000026226044, -0.2134999930858612, -0.26030001044273376, -0.054999999701976776, 0.14489999413490295, -0.2870999872684479, -0.1518000066280365, 0.2750999927520752, -0.15770000219345093, 0.00430000014603138, -0.03590000048279762, -0.12559999525547028, -0.12800000607967377, 0.1339000016450882, 0.21850000321865082, 0.3027999997138977, -0.1128000020980835, -0.0020000000949949026, 0.0012000000569969416, -0.14820000529289246, -0.019700000062584877, -0.05079999938607216, -0.10589999705553055, 0.0027000000700354576, -0.10670000314712524, -0.23649999499320984, -0.019099999219179153, 0.0015999999595806003, -0.06279999762773514, -0.1501999944448471, -0.06390000134706497, 0.09300000220537186, 0.010400000028312206, -0.15049999952316284, 0.04560000076889992, -0.12160000205039978, 0.06689999997615814, -0.023499999195337296, 0.2606000006198883, 0.12330000102519989, 0.10369999706745148, 0.022299999371170998, -0.17720000445842743, 0.3970000147819519, -0.05000000074505806, 0.06909999996423721, -0.08730000257492065, -0.21850000321865082, 0.03539999946951866, -0.017000000923871994, 0.07500000298023224, -0.24950000643730164, -0.15870000422000885, 0.07129999995231628, -0.09430000185966492, -0.12999999523162842, -0.05730000138282776], [-0.12319999933242798, 0.0738999992609024, -0.08089999854564667, -0.10480000078678131, -0.06379999965429306, 0.15029999613761902, 0.010099999606609344, -0.10350000113248825, 0.03550000116229057, -0.09629999846220016, -0.050599999725818634, -0.008500000461935997, 0.11620000004768372, 0.04170000180602074, 0.1039000004529953, 0.024800000712275505, 0.013899999670684338, 0.11490000039339066, 0.19259999692440033, 0.04769999906420708, 0.10670000314712524, -0.17949999868869781, 0.13670000433921814, -0.15279999375343323, -0.17319999635219574, -0.08370000123977661, -0.1914999932050705, -0.14270000159740448, -0.06279999762773514, -0.08869999647140503, 0.12070000171661377, 0.22100000083446503, -0.14409999549388885, 0.14219999313354492, -0.01489999983459711, 0.3734000027179718, -0.29030001163482666, 0.08990000188350677, -9.999999747378752e-05, -0.2076999992132187, -0.19750000536441803, -0.057999998331069946, 0.24449999630451202, -0.0414000004529953, -0.05040000006556511, 0.10930000245571136, -0.05040000006556511, 0.15520000457763672, -0.06530000269412994, -0.09570000320672989, -0.24169999361038208, 0.02019999921321869, 0.31779998540878296, -0.07760000228881836, -0.13819999992847443, 0.15469999611377716, 0.15330000221729279, 0.07829999923706055, 0.03610000014305115, -0.17790000140666962, 0.1023000031709671, 0.37540000677108765], [-0.0966000035405159, 0.14329999685287476, -0.16040000319480896, -0.12530000507831573, -0.23180000483989716, -0.049300000071525574, -0.11029999703168869, -0.07490000128746033, -0.1655000001192093, -0.09269999712705612, 0.09149999916553497, 0.08320000022649765, -0.17059999704360962, 0.08959999680519104, -0.00139999995008111, -0.02290000021457672, 0.15119999647140503, -0.13220000267028809, 0.1039000004529953, -0.17190000414848328, 0.07180000096559525, -0.10840000212192535, 0.18799999356269836, -0.2215999960899353, 0.05620000138878822, 0.21739999949932098, 0.12049999833106995, -0.17020000517368317, 0.2906000018119812, -0.09220000356435776, -0.2856000065803528, -0.05959999933838844, 0.008100000210106373, 0.13650000095367432, -0.20090000331401825, -0.07360000163316727, -0.09839999675750732, -0.3000999987125397, -0.08410000056028366, -0.11680000275373459, -0.0697999969124794, -0.22460000216960907, 0.013100000098347664, -0.15410000085830688, 0.040699999779462814, -0.06379999965429306, 0.17630000412464142, 0.046799998730421066, 0.016599999740719795, -0.13809999823570251, 0.00430000014603138, 0.0034000000450760126, 0.05730000138282776, -0.13169999420642853, -0.04399999976158142, 0.04490000009536743, 0.12489999830722809, 0.19339999556541443, -0.18539999425411224, 0.23180000483989716, -0.003000000026077032, 0.017999999225139618], [0.08510000258684158, -0.16169999539852142, -0.0746999979019165, 0.24500000476837158, 0.06350000202655792, 0.02590000070631504, -0.012299999594688416, -0.0010999999940395355, -0.047200001776218414, -0.06459999829530716, 0.07680000364780426, -0.021199999377131462, 0.09149999916553497, 0.29330000281333923, 0.00019999999494757503, -0.357699990272522, 0.08060000091791153, 0.3163999915122986, -0.048700001090765, -0.15639999508857727, -0.08380000293254852, -0.07119999825954437, 0.0649000033736229, 0.10559999942779541, 0.0843999981880188, -0.2635999917984009, 0.03290000185370445, -0.1746000051498413, 0.04100000113248825, 0.07159999758005142, -0.11699999868869781, -0.008200000040233135, 0.39750000834465027, 0.120899997651577, 0.13459999859333038, 0.19089999794960022, -0.12319999933242798, -0.03500000014901161, 0.03200000151991844, 0.24490000307559967, -0.0012000000569969416, -0.07419999688863754, -0.188400000333786, 0.017899999395012856, -0.13220000267028809, -0.1289999932050705, -0.14560000598430634, 0.14149999618530273, 0.10329999774694443, -0.14869999885559082, 0.10760000348091125, 0.11339999735355377, 0.059300001710653305, -0.041999999433755875, -0.06679999828338623, 0.19979999959468842, 0.12110000103712082, 0.1185000017285347, 0.14980000257492065, 0.10440000146627426, -0.0625, 0.0020000000949949026], [0.45989999175071716, 0.13369999825954437, 0.05860000103712082, -0.14980000257492065, -0.14390000700950623, 0.1386999934911728, 0.053199999034404755, -0.030899999663233757, -0.07980000227689743, 0.195700004696846, -0.029500000178813934, -0.009600000455975533, 0.04820000007748604, 0.18209999799728394, -0.03779999911785126, -0.1678999960422516, -0.10300000011920929, -0.07419999688863754, -0.09200000017881393, -0.08540000021457672, 0.15530000627040863, -0.02879999950528145, -0.1340000033378601, 0.12620000541210175, -0.07509999722242355, -0.37709999084472656, -0.053700000047683716, 0.01209999993443489, 0.04610000178217888, -0.027899999171495438, 0.07840000092983246, 0.09489999711513519, -0.09459999948740005, -0.17659999430179596, -0.10729999840259552, -0.08079999685287476, 0.07660000026226044, -0.23579999804496765, -0.13950000703334808, -0.08860000222921371, -0.1624000072479248, -0.24809999763965607, 0.00860000029206276, 0.024800000712275505, -0.07530000060796738, 0.11509999632835388, -0.05339999869465828, 0.3357999920845032, 0.16140000522136688, 0.32510000467300415, 0.19480000436306, -0.2337999939918518, 0.05290000140666962, 0.041600000113248825, -0.024000000208616257, 0.07069999724626541, -0.05510000139474869, 0.14380000531673431, 0.16779999434947968, 0.02019999921321869, 0.02590000070631504, -0.12770000100135803], [-0.050700001418590546, -0.08760000020265579, 0.1704999953508377, -0.08720000088214874, -0.251800000667572, 0.23649999499320984, -0.049300000071525574, 0.05270000174641609, -0.2711000144481659, 0.0414000004529953, -0.19110000133514404, -0.08780000358819962, -0.14429999887943268, 0.06270000338554382, -0.10499999672174454, 0.08919999748468399, -0.3492000102996826, -0.09520000219345093, 0.3758000135421753, 0.1906999945640564, -0.09920000284910202, -0.06390000134706497, 0.05559999868273735, 0.12349999696016312, 0.07209999859333038, 0.1623000055551529, -0.17720000445842743, -0.020600000396370888, -0.04619999974966049, -0.1770000010728836, 0.025599999353289604, -0.011900000274181366, -0.11590000241994858, -0.14990000426769257, 0.11299999803304672, -0.05950000137090683, 0.0010000000474974513, 0.13050000369548798, -0.09120000153779984, -0.0729999989271164, -0.32190001010894775, -0.12929999828338623, -0.0142000000923872, 0.020999999716877937, -0.2451999932527542, -0.07739999890327454, -0.08709999918937683, -0.15970000624656677, 0.15629999339580536, -0.061400000005960464, -0.018400000408291817, -0.059300001710653305, -0.20880000293254852, -0.17919999361038208, 0.035599999129772186, 0.0778999999165535, -0.1891999989748001, -0.1696999967098236, -0.11509999632835388, -0.05620000138878822, -0.0215000007301569, -0.1282999962568283], [0.20800000429153442, -0.26840001344680786, -0.07810000330209732, -0.11460000276565552, 0.040300000458955765, -0.07900000363588333, 0.10109999775886536, -0.18330000340938568, -0.059300001710653305, -0.06239999830722809, 0.035999998450279236, -0.02449999935925007, 0.16740000247955322, 0.23000000417232513, -0.13050000369548798, 0.08429999649524689, 0.17509999871253967, 0.24070000648498535, -0.06859999895095825, -0.1736000031232834, 0.030700000002980232, -0.1356000006198883, -0.04100000113248825, -0.030799999833106995, 0.22220000624656677, 0.034699998795986176, 0.1851000040769577, -0.024700000882148743, 0.014100000262260437, -0.038600001484155655, -0.11640000343322754, -0.0071000000461936, -0.30410000681877136, 0.186599999666214, 0.18129999935626984, -0.010200000368058681, -0.1817999929189682, 0.12070000171661377, -0.03099999949336052, 0.30660000443458557, 0.013199999928474426, 0.10000000149011612, 0.18619999289512634, -0.004399999976158142, -0.09830000251531601, 0.03779999911785126, -0.12630000710487366, -0.08739999681711197, 0.08820000290870667, 0.15860000252723694, -0.3336000144481659, 0.11980000138282776, 0.37790000438690186, 0.05920000001788139, 0.1754000037908554, -0.16580000519752502, 0.1785999983549118, 0.10100000351667404, -0.020899999886751175, -0.043299999088048935, -0.21330000460147858, -0.15219999849796295], [-0.04100000113248825, -0.025499999523162842, -0.14149999618530273, 0.16380000114440918, -0.019300000742077827, -0.0746999979019165, -0.05400000140070915, -0.051600001752376556, -0.04360000044107437, 0.16609999537467957, -0.14550000429153442, -0.08290000259876251, 0.040800001472234726, 0.03660000115633011, -0.2992999851703644, -0.00570000009611249, -0.31049999594688416, 0.07240000367164612, -0.09910000115633011, -0.2793999910354614, -0.21860000491142273, -0.15309999883174896, -0.1712999939918518, 0.1404999941587448, -0.026200000196695328, -0.07919999957084656, -0.05510000139474869, -0.03629999980330467, 0.03060000017285347, -0.10530000180006027, 0.07720000296831131, 0.062199998646974564, -0.1882999986410141, -0.17810000479221344, 0.13220000267028809, 0.25380000472068787, 0.0957999974489212, -0.0017999999690800905, 0.03790000081062317, -0.033900000154972076, 0.10819999873638153, 0.0794999971985817, 0.07829999923706055, -0.07850000262260437, 0.3172000050544739, -0.05959999933838844, 0.09619999676942825, 0.1956000030040741, 0.06800000369548798, -0.09399999678134918, 0.09650000184774399, 0.021199999377131462, 0.30410000681877136, -0.2272000014781952, 0.22179999947547913, -0.026499999687075615, 0.3601999878883362, 0.0917000025510788, -0.15870000422000885, -0.03590000048279762, 0.03920000046491623, 0.011300000362098217], [0.09369999915361404, -0.0357000008225441, 0.04659999907016754, 0.2676999866962433, -0.05700000002980232, -0.01140000019222498, -0.03319999948143959, -0.007499999832361937, 0.0706000030040741, -0.1808999925851822, 0.052400000393390656, -0.026499999687075615, 0.23729999363422394, 0.14589999616146088, -0.06809999793767929, 0.10199999809265137, 0.19009999930858612, -0.03610000014305115, 0.2433999925851822, 0.0568000003695488, -0.09459999948740005, -0.13940000534057617, -0.011800000444054604, 0.2768999934196472, -0.07240000367164612, 0.12120000272989273, 0.03319999948143959, 0.13609999418258667, 0.09600000083446503, 0.1404000073671341, 0.12189999967813492, -0.10559999942779541, -0.05240000039339</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>[0.9201849450109477]</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>[0.01821911349466547]</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>[0.8101134594826704]</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>[0.043351718308839694]</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>[-2.33040326633708]</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>[1.0899733637140785]</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>[0.7726773062603174]</t>
+        </is>
+      </c>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>[0.05222035851445986]</t>
+        </is>
+      </c>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>[0.8318649991735508]</t>
+        </is>
+      </c>
+      <c r="N37" t="inlineStr">
+        <is>
+          <t>[0.03987506949188933]</t>
+        </is>
+      </c>
+      <c r="O37" t="inlineStr">
+        <is>
+          <t>[-0.3023029598637694]</t>
+        </is>
+      </c>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>[0.42812876885923884]</t>
+        </is>
+      </c>
+      <c r="Q37" t="inlineStr">
+        <is>
+          <t>[-0.20060562606717935]</t>
+        </is>
+      </c>
+      <c r="R37" t="inlineStr">
+        <is>
+          <t>[0.12945617688431738]</t>
+        </is>
+      </c>
+      <c r="S37" t="inlineStr">
+        <is>
+          <t>[-0.14653627957822635]</t>
+        </is>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>[0.09660753646364653]</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>[-1.0827282572980659]</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>[0.19915699610812118]</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>[-0.3532454411853614]</t>
+        </is>
+      </c>
+      <c r="X37" t="inlineStr">
+        <is>
+          <t>[0.14176683624058262]</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>[-0.233992784472834]</t>
+        </is>
+      </c>
+      <c r="Z37" t="inlineStr">
+        <is>
+          <t>[0.10154922698338478]</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>[-0.9607743630696495]</t>
+        </is>
+      </c>
+      <c r="AB37" t="inlineStr">
+        <is>
+          <t>[0.1803998185067127]</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>[-0.932594928160287]</t>
+        </is>
+      </c>
+      <c r="AD37" t="inlineStr">
+        <is>
+          <t>[0.1619436693124912]</t>
+        </is>
+      </c>
+      <c r="AE37" t="inlineStr">
+        <is>
+          <t>[-0.9624597158298605]</t>
+        </is>
+      </c>
+      <c r="AF37" t="inlineStr">
+        <is>
+          <t>[0.21131388266908957]</t>
+        </is>
+      </c>
+      <c r="AG37" t="inlineStr">
+        <is>
+          <t>[-3.4761972120470706]</t>
+        </is>
+      </c>
+      <c r="AH37" t="inlineStr">
+        <is>
+          <t>[0.3332526964650732]</t>
+        </is>
+      </c>
+      <c r="AI37" t="inlineStr">
+        <is>
+          <t>[-1.374197495143426]</t>
+        </is>
+      </c>
+      <c r="AJ37" t="inlineStr">
+        <is>
+          <t>[0.19456284173696328]</t>
+        </is>
+      </c>
+      <c r="AK37" t="inlineStr">
+        <is>
+          <t>[-1.009295628858193]</t>
+        </is>
+      </c>
+      <c r="AL37" t="inlineStr">
+        <is>
+          <t>[0.21327200962211668]</t>
+        </is>
+      </c>
+      <c r="AM37" t="inlineStr">
+        <is>
+          <t>[-2.6950665205924933]</t>
+        </is>
+      </c>
+      <c r="AN37" t="inlineStr">
+        <is>
+          <t>[0.2838078965502998]</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>model_62_32_16_1</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>[62, 32, 16]</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>[[[0.01979999989271164, -0.020899999886751175, 0.04690000042319298, 0.05649999901652336, 0.05119999870657921, -0.12319999933242798, 0.017400000244379044, 0.01510000042617321, -0.01759999990463257, 0.030300000682473183, -0.039000000804662704, -0.014499999582767487, 0.03610000014305115, 0.09679999947547913, -0.0632999986410141, 0.003100000089034438, -0.010999999940395355, -0.0006000000284984708, 0.009399999864399433, 0.00570000009611249, -0.03370000049471855, -0.07819999754428864, -0.08079999685287476, 0.07209999859333038, 0.03180000185966492, -0.039500001817941666, 0.04800000041723251, -0.0617000013589859, 0.14569999277591705, -0.03849999979138374, -0.019700000062584877, 0.003700000001117587, -0.012799999676644802, 0.02979999966919422, -0.010999999940395355, -0.023900000378489494, -0.02449999935925007, 0.014000000432133675, -0.05990000069141388, -0.028300000354647636, 0.032099999487400055, -0.0835999995470047, -0.06310000270605087, -0.0348999984562397, 0.05040000006556511, -0.029600000008940697, 0.026799999177455902, -0.005100000184029341, -0.12250000238418579, 0.03200000151991844, -0.028999999165534973, 0.0731000006198883, 0.017999999225139618, -0.03880000114440918, 0.07970000058412552, -0.007000000216066837, 0.031300000846385956, -0.03139999881386757, 0.050599999725818634, 0.06360000371932983, -0.04699999839067459, 0.028300000354647636], [0.056699998676776886, -0.07150000333786011, -0.09989999979734421, 0.006500000134110451, -0.049400001764297485, 0.02630000002682209, -0.010700000450015068, -0.07890000194311142, 0.10100000351667404, -0.03750000149011612, -0.08540000021457672, 0.07190000265836716, 0.05290000140666962, 0.017999999225139618, 0.026200000196695328, 0.04619999974966049, -0.05559999868273735, 0.0210999995470047, -0.01590000092983246, 0.07689999788999557, 0.05220000073313713, 0.025200000032782555, 0.10400000214576721, -0.0284000001847744, 0.0005000000237487257, -0.05040000006556511, -0.094200000166893, 0.009399999864399433, 0.0364999994635582, -0.06710000336170197, 0.00559999980032444, -0.10379999876022339, 0.07909999787807465, -0.015599999576807022, 0.09070000052452087, 0.008700000122189522, -0.023000000044703484, 0.031599998474121094, 0.04809999838471413, 0.0835999995470047, 0.01640000008046627, 0.043800000101327896, -0.02879999950528145, -0.014600000344216824, 0.023600000888109207, 0.002899999963119626, -0.05040000006556511, 0.05000000074505806, -0.03449999913573265, -0.019500000402331352, -0.01889999955892563, -0.009499999694526196, 0.03790000081062317, -0.004800000227987766, -0.06629999727010727, -0.05990000069141388, 0.019500000402331352, 0.0771000012755394, -0.051899999380111694, 0.08720000088214874, -0.03909999877214432, -0.049300000071525574]], [[0.0031999999191612005, -0.219200000166893, 0.003000000026077032, 0.20440000295639038, 0.37229999899864197, 0.029500000178813934, -0.12210000306367874, 0.031099999323487282, -0.017500000074505806, 0.07940000295639038, -0.03720000013709068, 0.08150000125169754, -0.015599999576807022, 0.2563000023365021, 0.0142000000923872, 0.05180000141263008, 0.09589999914169312, 0.17190000414848328, -0.08410000056028366, -0.04610000178217888, -0.11990000307559967, -0.0949999988079071, -0.03929999843239784, -0.03720000013709068, -0.0989999994635582, 0.09390000253915787, -0.07989999651908875, 0.03889999911189079, 0.03739999979734421, -0.07050000131130219, -0.195700004696846, 0.12030000239610672, 0.13249999284744263, -0.06889999657869339, -0.15230000019073486, -0.15039999783039093, -0.09049999713897705, 0.16899999976158142, -0.049300000071525574, 0.03060000017285347, 0.07440000027418137, 0.020899999886751175, -0.06040000170469284, 0.021299999207258224, 0.15770000219345093, -0.047200001776218414, -0.06679999828338623, -0.017500000074505806, 0.1657000035047531, 0.09619999676942825, 0.1639000028371811, -0.2386000007390976, 0.011599999852478504, 0.058400001376867294, -0.05469999834895134, -0.12129999697208405, 0.15330000221729279, -0.09839999675750732, 0.15729999542236328, -0.05040000006556511, 0.335099995136261, 0.21610000729560852], [-0.16220000386238098, -0.0640999972820282, -0.06549999862909317, -0.16529999673366547, -0.18880000710487366, -0.10540000349283218, 0.2070000022649765, -0.01119999960064888, 0.13019999861717224, -0.026599999517202377, -0.08079999685287476, 0.06509999930858612, -0.05350000038743019, 0.1289999932050705, -0.07750000059604645, 0.1451999992132187, -0.20000000298023224, -0.05270000174641609, -0.022099999710917473, 0.04179999977350235, 0.11490000039339066, -0.1656000018119812, -0.005100000184029341, -0.04800000041723251, -0.3319000005722046, -0.051500000059604645, 0.1071000024676323, -0.011099999770522118, -0.13330000638961792, -0.008200000040233135, -0.17949999868869781, 0.0892999991774559, 0.120899997651577, 0.01510000042617321, 0.08869999647140503, 0.11819999665021896, 0.09000000357627869, 0.16369999945163727, -0.06729999929666519, 0.10509999841451645, -0.0215000007301569, 0.34299999475479126, 0.05999999865889549, 0.21089999377727509, 0.13410000503063202, 0.009399999864399433, 0.13040000200271606, 0.09130000323057175, 0.04500000178813934, 0.14069999754428864, -0.0851999968290329, -0.07460000365972519, 0.0414000004529953, -0.20980000495910645, -0.0044999998062849045, 0.006599999964237213, 0.1688999980688095, 0.2248000055551529, -0.05570000037550926, 0.053300000727176666, -0.0925000011920929, 0.17900000512599945], [-0.13650000095367432, 0.13680000603199005, 0.10409999638795853, 0.057999998331069946, -0.14419999718666077, 0.07209999859333038, 0.05079999938607216, -0.05299999937415123, -0.06689999997615814, 0.03319999948143959, -0.29789999127388, 0.026900000870227814, 0.05920000001788139, -0.1289999932050705, 0.07509999722242355, 0.14640000462532043, -0.002199999988079071, -0.1264999955892563, -0.0851999968290329, 0.001500000013038516, -0.01600000075995922, 0.17669999599456787, -0.06199999898672104, -0.1664000004529953, 0.0689999982714653, 0.02590000070631504, -0.14560000598430634, -0.17319999635219574, 0.016599999740719795, -0.08969999849796295, 0.18469999730587006, 0.10220000147819519, 0.1868000030517578, -0.010700000450015068, 0.1103999987244606, -0.1225999966263771, 0.14839999377727509, -0.027499999850988388, 0.12389999628067017, 0.19869999587535858, -0.07069999724626541, 0.17919999361038208, 0.06759999692440033, -0.06939999759197235, -0.2337000072002411, -0.2842000126838684, 0.03750000149011612, 0.04360000044107437, -0.07989999651908875, 0.053199999034404755, -0.033799998462200165, -0.32089999318122864, -0.03819999843835831, -0.002899999963119626, -0.07800000160932541, -0.1891999989748001, 0.1509000062942505, -0.2037999927997589, 0.07559999823570251, -0.0015999999595806003, 0.09690000116825104, -0.1340000033378601], [0.014299999922513962, 0.10689999908208847, -0.039400000125169754, -0.12409999966621399, -0.1818999946117401, 0.12970000505447388, -0.20409999787807465, 0.01850000023841858, -0.007199999876320362, 0.21040000021457672, 0.16060000658035278, 0.218299999833107, 0.10599999874830246, 0.10109999775886536, -0.05950000137090683, 0.01759999990463257, -0.21580000221729279, -0.15399999916553497, -0.026599999517202377, 0.06610000133514404, -0.07410000264644623, 0.014600000344216824, -0.031700000166893005, -0.16979999840259552, 0.06669999659061432, -0.07519999891519547, -0.03819999843835831, 0.2750999927520752, 0.05900000035762787, -0.11010000109672546, 0.1152999997138977, -0.014700000174343586, 0.04479999840259552, -0.01850000023841858, -0.14229999482631683, -0.09600000083446503, -0.02319999970495701, 0.06970000267028809, 0.07129999995231628, 0.008100000210106373, 0.03660000115633011, -0.22020000219345093, 0.14900000393390656, -0.0430000014603138, 0.043299999088048935, 0.06870000064373016, -0.0966000035405159, -0.018699999898672104, -0.27559998631477356, 0.3824000060558319, -0.04910000041127205, -0.06620000302791595, 0.09160000085830688, 0.15809999406337738, 0.08420000225305557, -0.024900000542402267, 0.0989999994635582, 0.22849999368190765, 0.17820000648498535, -0.03280000016093254, -0.061000000685453415, 0.08980000019073486], [0.06729999929666519, -0.06960000097751617, -0.11699999868869781, 0.18729999661445618, -0.11420000344514847, 0.11840000003576279, -0.08749999850988388, -0.14259999990463257, -0.04320000112056732, 0.14569999277591705, 0.09019999951124191, -0.08669999986886978, -0.06019999831914902, -0.2069000005722046, 0.28839999437332153, -0.1875, -0.038600001484155655, -0.16500000655651093, -0.21860000491142273, 0.0982000008225441, 0.15320000052452087, -0.006899999920278788, 0.22339999675750732, -0.1956000030040741, 0.04690000042319298, -0.044199999421834946, 0.07249999791383743, -0.0020000000949949026, -0.04699999839067459, 0.1290999948978424, -0.08420000225305557, 0.1446000039577484, -0.027400000020861626, -0.1046999990940094, 0.10679999738931656, -0.01489999983459711, -0.3571000099182129, 0.181099995970726, 0.14190000295639038, -0.013700000010430813, -0.15469999611377716, -0.047200001776218414, -0.048500001430511475, -0.010999999940395355, -0.040699999779462814, 0.062199998646974564, 0.00139999995008111, -0.008299999870359898, -0.012799999676644802, -0.0071000000461936, 0.0868000015616417, -0.029500000178813934, -0.09120000153779984, -0.3125999867916107, -0.12359999865293503, -0.020099999383091927, -0.020099999383091927, 0.03700000047683716, 0.01899999938905239, 0.20280000567436218, 0.05299999937415123, 0.12060000002384186], [-0.0348999984562397, 0.08780000358819962, 0.08179999887943268, 0.00559999980032444, 0.10109999775886536, 0.08489999920129776, -0.06319999694824219, -0.08429999649524689, -0.023600000888109207, -0.265500009059906, -0.06840000301599503, -0.06459999829530716, -0.09109999984502792, -0.08630000054836273, 0.10350000113248825, 0.00139999995008111, 0.11569999903440475, -0.1972000002861023, -0.12839999794960022, 0.056299999356269836, -0.004399999976158142, 0.1446000039577484, 0.13300000131130219, 0.07490000128746033, -0.11209999769926071, -0.0034000000450760126, 0.2847999930381775, -0.093299999833107, -0.16140000522136688, -0.21529999375343323, -0.031099999323487282, -0.09700000286102295, -0.08209999650716782, -0.20250000059604645, -0.09359999746084213, -0.07810000330209732, 0.05590000003576279, 0.1535000056028366, -0.18389999866485596, -0.07530000060796738, 0.18080000579357147, -0.03669999912381172, 0.08910000324249268, 0.1420000046491623, 0.0892999991774559, -0.018200000748038292, -0.20679999887943268, 0.03840000182390213, -0.028999999165534973, -0.046300001442432404, -0.10480000078678131, -0.06589999794960022, -0.08370000123977661, 0.009700000286102295, 0.23479999601840973, 0.15320000052452087, 0.14000000059604645, -0.08139999955892563, 0.3650999963283539, 0.09019999951124191, -0.16269999742507935, -0.08009999990463257], [0.05420000106096268, 0.10769999772310257, 0.12489999830722809, 0.016499999910593033, 0.03680000081658363, -0.0010000000474974513, 0.008299999870359898, -0.09109999984502792, -0.19099999964237213, -0.015399999916553497, 0.016899999231100082, -0.10540000349283218, 0.04309999942779541, 0.09459999948740005, 0.017899999395012856, -0.0005000000237487257, 0.22139999270439148, 0.07699999958276749, 0.04010000079870224, -0.05389999970793724, -0.05920000001788139, 0.03709999844431877, 0.017999999225139618, 0.05999999865889549, 0.05860000103712082, -0.32839998602867126, -0.08389999717473984, -0.042399998754262924, -0.2418999969959259, 0.3790999948978424, -0.05510000139474869, -0.2280000001192093, 0.006399999838322401, -0.02329999953508377, -0.05950000137090683, -0.1386999934911728, 0.06599999964237213, -0.030500000342726707, 0.07280000299215317, -0.006099999882280827, 0.15770000219345093, -0.050200000405311584, 0.005400000140070915, 0.24729999899864197, -0.1331000030040741, -0.23240000009536743, 0.30230000615119934, -0.04170000180602074, -0.1412000060081482, 0.061500001698732376, 0.04600000008940697, 0.02370000071823597, 0.08540000021457672, -0.030500000342726707, -0.13619999587535858, 0.05649999901652336, 0.06319999694824219, 0.21619999408721924, 0.14319999516010284, 0.0778999999165535, 0.026100000366568565, 0.18250000476837158], [-0.010400000028312206, 0.12280000001192093, 0.16979999840259552, 0.03889999911189079, -0.0949999988079071, 0.014600000344216824, -0.028200000524520874, -0.18170000612735748, 0.1632000058889389, -0.041099999099969864, -0.19539999961853027, 0.1120000034570694, -0.09719999879598618, 0.12439999729394913, 0.05130000039935112, -0.1151999980211258, 0.17059999704360962, -0.10499999672174454, 0.2831999957561493, 0.02329999953508377, -0.05810000002384186, 0.07779999822378159, -0.08479999750852585, -0.2842000126838684, 0.03150000050663948, -0.0005000000237487257, -0.024900000542402267, 0.0706000030040741, 0.14550000429153442, -0.12700000405311584, -0.10220000147819519, 0.03779999911785126, -0.13989999890327454, -0.00570000009611249, 0.0012000000569969416, 0.22509999573230743, 0.09160000085830688, 0.09610000252723694, 0.020999999716877937, -0.36570000648498535, 0.04399999976158142, -0.13420000672340393, -0.05530000105500221, 0.002899999963119626, -0.02710000053048134, 0.14180000126361847, 0.17149999737739563, -0.06440000236034393, 0.12120000272989273, -0.17170000076293945, -0.024299999698996544, -0.1526000052690506, -0.0843999981880188, 0.040800001472234726, -0.20170000195503235, 0.014299999922513962, 0.2282000035047531, 0.19519999623298645, -0.0478999987244606, 0.0406000018119812, 0.06270000338554382, -0.04729999974370003], [-0.23399999737739563, -0.1639000028371811, -0.04529999941587448, 0.030300000682473183, -0.007600000128149986, 0.2029999941587448, 0.01549999974668026, -0.14309999346733093, -0.04529999941587448, 0.1459999978542328, 0.009800000116229057, 0.0697999969124794, 0.36010000109672546, 0.1340000033378601, 0.26010000705718994, 0.07639999687671661, 0.12110000103712082, -0.17110000550746918, 0.09669999778270721, 0.11299999803304672, -0.1687999963760376, -0.09369999915361404, -0.15719999372959137, 0.23489999771118164, -0.15160000324249268, 0.22280000150203705, 0.07989999651908875, 0.022099999710917473, 0.043800000101327896, 0.007000000216066837, -0.03610000014305115, -0.14920000731945038, -0.02590000070631504, -0.026399999856948853, -0.04399999976158142, 0.0008999999845400453, -0.1281999945640564, -0.10450000315904617, 0.0723000019788742, 0.21070000529289246, 0.09570000320672989, -0.10239999741315842, -0.11209999769926071, -0.003700000001117587, -0.13899999856948853, -0.006399999838322401, 0.08780000358819962, 0.08829999715089798, 0.10209999978542328, 0.042100001126527786, -0.04179999977350235, 0.042399998754262924, -0.08560000360012054, -0.018699999898672104, 0.0729999989271164, 0.13519999384880066, 0.12470000237226486, 0.06840000301599503, -0.16820000112056732, 0.20329999923706055, -0.03700000047683716, -0.17339999973773956], [0.16599999368190765, -0.31029999256134033, 0.04960000142455101, 0.11190000176429749, 0.13230000436306, 0.11630000174045563, -0.18790000677108765, -0.05090000107884407, 0.03779999911785126, -0.050999999046325684, -0.17550000548362732, 0.15469999611377716, -0.055399999022483826, 0.00839999970048666, -0.007000000216066837, -0.01360000018030405, 0.06509999930858612, -0.08990000188350677, 0.09489999711513519, 0.01860000006854534, -0.1339000016450882, 0.25, -0.054999999701976776, -0.05490000173449516, 0.0012000000569969416, -0.17319999635219574, 0.035599999129772186, 0.00019999999494757503, -0.22439999878406525, 0.12540000677108765, 0.15950000286102295, 0.3287000060081482, 0.03750000149011612, 0.0989999994635582, 0.09059999883174896, 0.07519999891519547, -0.013000000268220901, 0.10130000114440918, 0.011800000444054604, 0.13580000400543213, -0.0012000000569969416, 0.05079999938607216, -0.012299999594688416, 0.021900000050663948, -0.014000000432133675, 0.05169999971985817, 0.08229999989271164, 0.1542000025510788, 0.09799999743700027, 0.066600002348423, -0.31700000166893005, 0.11429999768733978, -0.0892999991774559, 0.2410999983549118, 0.11879999935626984, -0.03310000151395798, -0.20880000293254852, 0.052299998700618744, -0.09870000183582306, 0.027000000700354576, -0.13369999825954437, 0.12970000505447388], [0.18330000340938568, 0.29840001463890076, -0.017999999225139618, 0.19020000100135803, 0.1054999977350235, 0.2401999980211258, 0.00930000003427267, -0.16840000450611115, -0.06830000132322311, -0.09149999916553497, 0.14910000562667847, -0.10750000178813934, -0.09390000253915787, -0.18790000677108765, 0.04039999842643738, -0.10769999772310257, -0.10660000145435333, 0.26759999990463257, 0.09059999883174896, -0.10589999705553055, -0.20000000298023224, 0.05270000174641609, -0.06199999898672104, 0.07530000060796738, -0.20800000429153442, 0.12770000100135803, 0.010700000450015068, 0.1467999964952469, 0.10289999842643738, 0.02800000086426735, 0.007699999958276749, 0.0731000006198883, 0.011300000362098217, -0.019600000232458115, -0.0071000000461936, -0.07029999792575836, 0.061400000005960464, 0.03240000084042549, -0.16949999332427979, 0.1720000058412552, -0.01489999983459711, 0.1477999985218048, 0.0908999964594841, -0.23770000040531158, 0.051500000059604645, 0.08789999783039093, 0.13130000233650208, 0.21289999783039093, -0.024399999529123306, -0.020800000056624413, -0.11760000139474869, 0.03020000085234642, 0.1590999960899353, -0.09290000051259995, -0.10140000283718109, -0.12809999287128448, 0.12370000034570694, 0.21150000393390656, 0.04580000042915344, 0.07020000368356705, -0.03869999945163727, -0.1152999997138977], [-0.08049999922513962, 0.0632999986410141, -0.060499999672174454, 0.3569999933242798, 0.05849999934434891, -0.008100000210106373, -0.10920000076293945, 0.14790000021457672, 0.03959999978542328, 0.10530000180006027, 0.0940999984741211, -0.14100000262260437, -0.2069000005722046, 0.16539999842643738, 0.03660000115633011, 0.21070000529289246, -0.16339999437332153, -0.05290000140666962, -0.24320000410079956, 0.10580000281333923, 0.021700000390410423, 0.049800001084804535, -0.15960000455379486, 0.09399999678134918, -0.10540000349283218, -0.17669999599456787, 0.09830000251531601, -0.1185000017285347, 0.20080000162124634, -0.0851999968290329, 0.030899999663233757, 0.14910000562667847, -0.17509999871253967, 0.014999999664723873, -0.13410000503063202, -0.04170000180602074, 0.22619999945163727, -0.0010999999940395355, 0.12610000371932983, 0.028699999675154686, 0.11249999701976776, -0.012799999676644802, -0.005100000184029341, 0.0430000014603138, -0.09849999845027924, 0.10180000215768814, 0.2223999947309494, -0.30329999327659607, -0.10840000212192535, -0.03500000014901161, -0.1281999945640564, 0.16210000216960907, -0.15360000729560852, -0.08479999750852585, -0.003599999938160181, -0.011099999770522118, 0.015599999576807022, 0.009200000204145908, -0.05460000038146973, -0.033900000154972076, 0.023600000888109207, -0.060499999672174454], [0.023600000888109207, 0.11400000005960464, 0.12359999865293503, -0.14970000088214874, 0.021800000220537186, 0.03720000013709068, 0.17419999837875366, 0.11299999803304672, -0.04259999841451645, 0.25949999690055847, -0.0027000000700354576, 0.1266999989748001, -0.25, -0.013500000350177288, -0.0737999975681305, 0.1899999976158142, 0.12970000505447388, -0.1103999987244606, 0.1273999959230423, -0.035999998450279236, -0.10090000182390213, -0.08380000293254852, 0.12890000641345978, 0.14429999887943268, 0.052400000393390656, -0.1023000031709671, -0.13249999284744263, -0.121799997985363, -0.23569999635219574, -0.16130000352859497, -0.17890000343322754, 0.12399999797344208, -0.008799999952316284, 0.1881999969482422, -0.0478999987244606, -0.0731000006198883, -0.13699999451637268, -0.08829999715089798, -0.18850000202655792, 0.08479999750852585, 9.999999747378752e-05, -0.18479999899864197, -0.0771000012755394, -0.29809999465942383, 0.04910000041127205, 0.030300000682473183, -0.013799999840557575, 0.03709999844431877, -0.08630000054836273, 0.023600000888109207, -0.17560000717639923, 0.08389999717473984, -0.2612999975681305, -0.2079000025987625, -0.13339999318122864, 0.017999999225139618, 0.06549999862909317, -0.027499999850988388, 0.07699999958276749, 0.05829999968409538, 0.04659999907016754, 0.017899999395012856], [0.020400000736117363, -0.04149999842047691, 0.029200000688433647, -0.042399998754262924, 0.19480000436306, -0.0771000012755394, 0.1704999953508377, -0.040800001472234726, -0.04170000180602074, -0.00839999970048666, -0.07150000333786011, -0.08460000157356262, 0.10130000114440918, -0.00039999998989515007, -0.1526000052690506, -0.1289999932050705, -0.021400000900030136, -0.439300000667572, -0.10400000214576721, -0.01209999993443489, 0.026200000196695328, 0.016100000590085983, -0.17100000381469727, -0.051100000739097595, -0.16200000047683716, 0.11410000175237656, -0.23149999976158142, 0.04129999876022339, 0.027799999341368675, 0.3257000148296356, -0.09570000320672989, -0.04309999942779541, 0.0027000000700354576, -0.12160000205039978, -0.04100000113248825, -0.2669999897480011, 0.15629999339580536, 0.015300000086426735, 0.1396999955177307, -0.13259999454021454, 0.007000000216066837, -0.012299999594688416, 0.017500000074505806, -0.05909999832510948, 0.18359999358654022, 0.23579999804496765, -0.125900000333786, 0.11400000005960464, -0.16519999504089355, -0.08089999854564667, -0.2549000084400177, 0.013799999840557575, 0.007699999958276749, -0.06679999828338623, -0.11219999939203262, -0.015799999237060547, -0.03189999982714653, -0.08250000327825546, -0.0568000003695488, -0.043800000101327896, 0.06880000233650208, -0.03060000017285347], [-0.06270000338554382, -0.00430000014603138, -0.015399999916553497, 0.14069999754428864, -0.02290000021457672, -0.12250000238418579, 0.04619999974966049, -0.09130000323057175, 0.11980000138282776, -0.1876000016927719, 0.05270000174641609, -0.10559999942779541, 0.1460999995470047, 0.16380000114440918, -0.04899999871850014, 0.21250000596046448, 0.22349999845027924, 0.12890000641345978, -0.11580000072717667, -0.07169999927282333, -0.16429999470710754, -0.13210000097751617, -0.07029999792575836, -0.15780000388622284, -0.031300000846385956, 0.2013999968767166, -0.11800000071525574, 0.027899999171495438, -0.20280000567436218, 0.011300000362098217, 0.0737999975681305, 0.0860000029206276, 0.17090000212192535, 0.05590000003576279, -0.21870000660419464, 0.1761000007390976, -0.09809999912977219, 0.18930000066757202, 0.13699999451637268, -0.06019999831914902, -0.18809999525547028, -0.05420000106096268, 0.19589999318122864, -0.1378999948501587, -0.2011999934911728, 0.006899999920278788, -0.09929999709129333, -0.07829999923706055, -0.11410000175237656, -0.08229999989271164, -0.0658000037074089, 0.06939999759197235, -0.04600000008940697, -0.18209999799728394, -0.025599999353289604, 0.09130000323057175, -0.15970000624656677, 0.10429999977350235, 0.17949999868869781, -0.09529999643564224, -0.1875, -0.061400000005960464], [-0.011900000274181366, -0.043800000101327896, -0.12430000305175781, -0.10949999839067459, 0.11230000108480453, 0.08209999650716782, -0.20520000159740448, -0.058800000697374344, 0.2215999960899353, -0.10930000245571136, 0.06679999828338623, 0.32760000228881836, -0.13089999556541443, -0.011599999852478504, -0.007899999618530273, -0.07209999859333038, -0.03370000049471855, -0.10480000078678131, 0.1712999939918518, 0.014999999664723873, 0.04960000142455101, 0.10830000042915344, -0.18790000677108765, 0.20069999992847443, -0.05460000038146973, 0.04960000142455101, -0.08309999853372574, -0.1720000058412552, -0.17509999871253967, 0.023099999874830246, -0.011099999770522118, -0.04170000180602074, -0.0966000035405159, -0.0674000009894371, 0.050200000405311584, -0.0015999999595806003, -0.014000000432133675, -0.1826000064611435, 0.12219999730587006, -0.002899999963119626, 0.007699999958276749, 0.07540000230073929, 0.3950999975204468, -0.06849999725818634, -0.13130000233650208, 0.019600000232458115, -0.0568000003695488, -0.13940000534057617, -0.055399999022483826, -0.1477999985218048, 0.2070000022649765, -9.999999747378752e-05, 0.05490000173449516, -0.24860000610351562, 0.12639999389648438, -0.1785999983549118, -0.020899999886751175, 0.09359999746084213, 0.04610000178217888, 0.04100000113248825, 0.17239999771118164, 0.09430000185966492], [0.05119999870657921, 0.10599999874830246, 0.0406000018119812, 0.1251000016927719, -0.14589999616146088, 0.2207999974489212, -0.10279999673366547, -0.00019999999494757503, 0.19480000436306, 0.08749999850988388, 0.125, -0.05310000106692314, -0.05350000038743019, 0.060600001364946365, -0.2409999966621399, -0.08399999886751175, 0.2070000022649765, -0.17409999668598175, -0.15690000355243683, 0.0034000000450760126, 0.13259999454021454, 0.04690000042319298, -0.1671999990940094, 0.2328999936580658, -0.13670000433921814, 0.15539999306201935, -0.1274999976158142, -0.15279999375343323, -0.12210000306367874, -0.061900001019239426, 0.19820000231266022, -0.16369999945163727, -0.042899999767541885, 0.01209999993443489, 0.0007999999797903001, 0.11879999935626984, -0.19269999861717224, 0.0608999989926815, -0.22370000183582306, -0.09040000289678574, -0.2858999967575073, 0.09239999949932098, -0.18490000069141388, 0.12330000102519989, 0.10140000283718109, -0.05130000039935112, 0.1264999955892563, -0.08860000222921371, -0.017000000923871994, 0.1371999979019165, -0.05829999968409538, -0.06520000100135803, 0.12639999389648438, 0.14730000495910645, -0.14589999616146088, -0.044199999421834946, -0.02449999935925007, -0.06459999829530716, 0.015599999576807022, -0.0019000000320374966, 0.019899999722838402, 0.02879999950528145], [0.21969999372959137, 0.03909999877214432, -0.20569999516010284, -0.041999999433755875, 0.12559999525547028, -0.19699999690055847, -0.012900000438094139, -0.19599999487400055, 0.15850000083446503, 0.1800999939441681, 0.11060000211000443, -0.17170000076293945, -0.16740000247955322, 0.09149999916553497, 0.2175000011920929, -0.07699999958276749, 0.21969999372959137, -0.0071000000461936, -0.020500000566244125, -0.04190000146627426, 0.04100000113248825, -0.06870000064373016, -0.025499999523162842, 0.0027000000700354576, -0.0008999999845400453, 0.049400001764297485, -0.002099999925121665, -0.22390000522136688, 0.05640000104904175, -0.08669999986886978, 0.051600001752376556, 0.08129999786615372, 0.10249999910593033, 0.08879999816417694, 0.10450000315904617, 0.02879999950528145, 0.18389999866485596, -0.22120000422000885, 0.1850000023841858, 0.065700002014637, -0.14569999277591705, -0.07090000063180923, 0.16529999673366547, 0.11959999799728394, 0.226500004529953, -0.03999999910593033, -0.00800000037997961, 0.2506999969482422, -0.10689999908208847, 0.15219999849796295, 0.09589999914169312, -0.08250000327825546, -0.1696999967098236, 0.14800000190734863, 0.01730000041425228, 0.18129999935626984, 0.07930000126361847, 0.10419999808073044, 0.004699999932199717, -0.022600000724196434, -0.03669999912381172, -0.07289999723434448], [0.07190000265836716, -0.05490000173449516, 0.06400000303983688, -0.09440000355243683, -0.017100000753998756, 0.013199999928474426, -0.05739999935030937, 0.188400000333786, -0.03150000050663948, 0.13109999895095825, 0.1273999959230423, -0.14429999887943268, 0.21850000321865082, -0.06679999828338623, 0.057100001722574234, -0.14920000731945038, -0.0908999964594841, -0.0714000016450882, 0.020400000736117363, 0.20550000667572021, -0.11429999768733978, 0.1200999990105629, 0.1459999978542328, -0.014100000262260437, -0.06629999727010727, 0.20520000159740448, 0.07349999994039536, -0.20469999313354492, 0.04619999974966049, -0.1606999933719635, -0.07259999960660934, -0.04129999876022339, 0.2371000051498413, 0.12620000541210175, -0.10459999740123749, 0.1873999983072281, 0.007799999788403511, -0.056699998676776886, 0.014800000004470348, -0.043699998408555984, 0.17659999430179596, -0.10920000076293945, 0.08110000193119049, 0.09640000015497208, 0.08209999650716782, -0.0982000008225441, 0.26499998569488525, 0.10249999910593033, -0.052299998700618744, -0.2741999924182892, -0.1873999983072281, -0.08550000190734863, 0.03200000151991844, -0.08389999717473984, -0.014700000174343586, -0.20479999482631683, -0.16940000653266907, 0.059700001031160355, 0.11159999668598175, -0.20960000157356262, 0.058800000697374344, 0.17470000684261322], [0.11339999735355377, -0.07800000160932541, 0.04360000044107437, -0.06289999932050705, -0.018300000578165054, -0.06800000369548798, -0.07199999690055847, 0.04280000180006027, -0.12160000205039978, -0.04780000075697899, -0.14669999480247498, -0.17100000381469727, -0.2222999930381775, -0.17350000143051147, -0.05299999937415123, 0.07159999758005142, -0.006399999838322401, -0.10570000112056732, -0.14010000228881836, 0.12129999697208405, 0.12030000239610672, -0.056699998676776886, -0.06239999830722809, -0.16910000145435333, -0.04690000042319298, 0.3206000030040741, 0.0210999995470047, 0.18790000677108765, -0.05429999902844429, 0.1551000028848648, -0.07779999822378159, -0.04410000145435333, -0.0632999986410141, 0.09030000120401382, -0.27390000224113464, -0.010599999688565731, -0.1039000004529953, -0.2858000099658966, -0.24140000343322754, 0.03720000013709068, 0.08320000022649765, 0.06809999793767929, 0.21230000257492065, -0.038100000470876694, -0.15219999849796295, -0.03449999913573265, 0.12020000070333481, -0.10570000112056732, 0.10869999974966049, 0.12080000340938568, 0.08250000327825546, -0.125, -0.24940000474452972, 0.18469999730587006, 0.01810000091791153, 0.0010000000474974513, -0.04430000111460686, 0.17790000140666962, -0.08049999922513962, 0.053300000727176666, 0.020800000056624413, 0.010599999688565731], [-0.241799995303154, 0.01510000042617321, -0.003000000026077032, -0.0714000016450882, -0.07970000058412552, 0.17139999568462372, -0.034699998795986176, 0.08070000261068344, 0.06289999932050705, 0.09709999710321426, -0.017500000074505806, -0.20880000293254852, -0.1868000030517578, 0.11959999799728394, 0.09780000150203705, 0.0066999997943639755, 0.13169999420642853, 0.004900000058114529, 0.14219999313354492, -0.2547999918460846, 0.11749999970197678, 0.2578999996185303, 0.10999999940395355, 0.16060000658035278, 0.17679999768733978, 0.1460999995470047, -0.01679999940097332, -0.08879999816417694, 0.14720000326633453, 0.17329999804496765, 0.033900000154972076, 0.11169999837875366, 0.19329999387264252, 0.08720000088214874, -0.11299999803304672, -0.1281999945640564, -0.056699998676776886, 0.14309999346733093, -0.004000000189989805, -0.19210000336170197, 0.26669999957084656, 0.10499999672174454, 0.04479999840259552, -0.004600000102072954, 0.002099999925121665, 0.10760000348091125, -0.07769999653100967, 0.013000000268220901, 0.07440000027418137, 0.23360000550746918, 0.003800000064074993, -0.11909999698400497, 0.08179999887943268, -0.17890000343322754, 0.10320000350475311, 0.020400000736117363, -0.12409999966621399, 0.10909999907016754, -0.14550000429153442, -0.08879999816417694, -0.08969999849796295, -0.0681999996304512], [0.1023000031709671, 0.027300000190734863, -0.0421999990940094, -0.026000000536441803, 0.10970000177621841, -0.04360000044107437, 0.08529999852180481, 0.059300001710653305, 0.009999999776482582, 0.15800000727176666, -0.11789999902248383, 0.02070000022649765, -0.020099999383091927, -0.00559999980032444, 0.0210999995470047, -0.1242000013589859, -0.2142000049352646, 0.0828000009059906, 0.0012000000569969416, 0.021700000390410423, -0.14270000159740448, -0.22939999401569366, -0.017400000244379044, 0.0013000000035390258, -0.03460000082850456, -0.09470000118017197, -0.20100000500679016, -0.3630000054836273, -0.027899999171495438, -0.061400000005960464, 0.11550000309944153, -0.03970000147819519, 0.059700001031160355, -0.2572000026702881, -0.24070000648498535, -0.017799999564886093, -0.08609999716281891, 0.1949000060558319, -0.10620000213384628, -0.2386000007390976, 0.08209999650716782, 0.024000000208616257, 0.03889999911189079, 0.033900000154972076, -0.18080000579357147, 0.025499999523162842, 0.009800000116229057, 0.13439999520778656, -0.07729999721050262, -0.005200000014156103, 0.13369999825954437, -0.005799999926239252, -0.08789999783039093, 0.14169999957084656, 0.061000000685453415, -0.19120000302791595, -0.016899999231100082, 0.012600000016391277, -0.2102999985218048, 0.258899986743927, -0.26109999418258667, -0.05139999836683273], [0.0722000002861023, 0.09989999979734421, -0.1712999939918518, 0.01360000018030405, 0.04170000180602074, 0.20880000293254852, 0.06639999896287918, 0.17139999568462372, 0.01899999938905239, -0.028300000354647636, -0.014600000344216824, 0.20000000298023224, -0.07569999992847443, 0.04569999873638153, 0.08399999886751175, 0.07209999859333038, 0.17440000176429749, -0.04960000142455101, -0.14339999854564667, 0.18219999969005585, 0.0017999999690800905, -0.18400000035762787, 0.16099999845027924, -0.08340000361204147, 0.06289999932050705, -0.05000000074505806, -0.052299998700618744, -0.017999999225139618, 0.10209999978542328, 0.2037000060081482, -0.032099999487400055, -0.0350000001490116</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>[[[0.014299999922513962, -0.03590000048279762, 0.06369999796152115, 0.09350000321865082, 0.08609999716281891, -0.13230000436306, 0.09179999679327011, 0.02019999921321869, -0.029500000178813934, -0.01730000041425228, -0.010499999858438969, -0.09019999951124191, -0.03180000185966492, 0.11100000143051147, -0.11029999703168869, -0.08030000329017639, 0.04580000042915344, 0.08060000091791153, 0.028599999845027924, -0.050700001418590546, -0.1137000024318695, -0.15469999611377716, -0.15399999916553497, 0.12290000170469284, 0.07509999722242355, -0.03009999915957451, 0.07810000330209732, -0.11289999634027481, 0.18889999389648438, -0.07850000262260437, -0.06109999865293503, 0.03550000116229057, -0.06400000303983688, 0.013700000010430813, -0.05829999968409538, 0.057999998331069946, -0.0017999999690800905, 0.017000000923871994, -0.09430000185966492, -0.11349999904632568, -0.006899999920278788, -0.14380000531673431, -0.07890000194311142, -0.012600000016391277, 0.024700000882148743, -0.0575999990105629, 0.08940000087022781, -0.014100000262260437, -0.13899999856948853, 0.057999998331069946, -0.12250000238418579, 0.09470000118017197, -0.06989999860525131, 0.00139999995008111, 0.08659999817609787, 0.01640000008046627, 0.06689999997615814, -0.03750000149011612, 0.08320000022649765, 0.010400000028312206, -0.038100000470876694, 0.0544000007212162], [0.0851999968290329, -0.08160000294446945, -0.15320000052452087, 0.0027000000700354576, -0.07569999992847443, 0.07729999721050262, -0.12030000239610672, -0.11919999867677689, 0.14069999754428864, -0.04769999906420708, -0.14139999449253082, 0.08980000019073486, 0.03849999979138374, 0.004800000227987766, 0.07050000131130219, 0.06960000097751617, -0.11010000109672546, -0.02329999953508377, -0.05959999933838844, 0.09449999779462814, 0.0892999991774559, 0.048700001090765, 0.1428000032901764, -0.0658000037074089, -0.02319999970495701, -0.051899999380111694, -0.15299999713897705, 0.04430000111460686, -0.004699999932199717, -0.07519999891519547, 0.0860000029206276, -0.1387999951839447, 0.15209999680519104, -0.05779999867081642, 0.12039999663829803, -0.04170000180602074, -0.060600001364946365, 0.0786999985575676, 0.07800000160932541, 0.10740000009536743, -0.0071000000461936, 0.06360000371932983, 0.04410000145435333, -0.014999999664723873, 0.06889999657869339, 0.027799999341368675, -0.1062999963760376, 0.045899998396635056, 0.03830000013113022, -0.06289999932050705, -0.00839999970048666, 0.01360000018030405, 0.04129999876022339, -0.057100001722574234, -0.14820000529289246, -0.07750000059604645, 0.007499999832361937, 0.12950000166893005, -0.08209999650716782, 0.09839999675750732, -0.06469999998807907, -0.1039000004529953]], [[-0.033900000154972076, -0.1671999990940094, 0.0012000000569969416, 0.24729999899864197, 0.3303000032901764, 0.01679999940097332, -0.08969999849796295, 0.07919999957084656, -0.026000000536441803, 0.14880000054836273, 0.11680000275373459, 0.09860000014305115, -0.0026000000070780516, 0.20430000126361847, 0.04809999838471413, 0.008700000122189522, 0.11140000075101852, 0.11460000276565552, -0.0908999964594841, -0.09640000015497208, -0.12530000507831573, -0.10999999940395355, -0.02969999983906746, -0.03620000183582306, -0.16940000653266907, 0.16899999976158142, -0.11840000003576279, 0.05620000138878822, 0.007499999832361937, -0.07100000232458115, -0.14419999718666077, 0.08309999853372574, 0.07530000060796738, -0.03909999877214432, -0.17669999599456787, -0.17839999496936798, -0.06769999861717224, 0.06300000101327896, -0.01850000023841858, 0.03909999877214432, 0.09290000051259995, 0.01269999984651804, -0.0697999969124794, 0.07760000228881836, 0.12370000034570694, -0.026799999177455902, -0.0997999981045723, -0.020500000566244125, 0.2320999950170517, 0.0714000016450882, 0.2890999913215637, -0.24619999527931213, 0.041600000113248825, 0.08699999749660492, -0.059700001031160355, -0.04500000178813934, 0.12380000203847885, -0.09229999780654907, 0.11900000274181366, -0.05920000001788139, 0.45329999923706055, 0.20440000295639038], [-0.15770000219345093, -0.06639999896287918, -0.04919999837875366, -0.20170000195503235, -0.16689999401569366, -0.11810000240802765, 0.18719999492168427, -0.0421999990940094, 0.1467999964952469, -0.05040000006556511, -0.22190000116825104, 0.06650000065565109, -0.08340000361204147, 0.1915999948978424, -0.09780000150203705, 0.1915999948978424, -0.19979999959468842, 0.0024999999441206455, -0.02019999921321869, 0.07840000092983246, 0.10999999940395355, -0.13840000331401825, 0.002099999925121665, -0.0284000001847744, -0.25870001316070557, -0.1264999955892563, 0.16140000522136688, -0.03610000014305115, -0.11860000342130661, -0.00800000037997961, -0.22949999570846558, 0.1273999959230423, 0.14980000257492065, -0.00279999990016222, 0.12280000001192093, 0.15940000116825104, 0.0640999972820282, 0.2685000002384186, -0.09189999848604202, 0.09160000085830688, -0.03680000081658363, 0.358599990606308, 0.0738999992609024, 0.1662999987602234, 0.16529999673366547, -0.006000000052154064, 0.1648000031709671, 0.08630000054836273, -0.017500000074505806, 0.18389999866485596, -0.19689999520778656, -0.04039999842643738, 0.015300000086426735, -0.22030000388622284, 0.004900000058114529, -0.06129999831318855, 0.19099999964237213, 0.2150000035762787, -0.01940000057220459, 0.04769999906420708, -0.25369998812675476, 0.19259999692440033], [-0.16509999334812164, 0.04859999939799309, 0.14149999618530273, 0.05649999901652336, -0.10350000113248825, 0.06949999928474426, -0.015200000256299973, -0.09730000048875809, -0.10599999874830246, -0.07039999961853027, -0.384799987077713, -0.04410000145435333, 0.024700000882148743, -0.07559999823570251, 0.020400000736117363, 0.12860000133514404, -0.025699999183416367, -0.10100000351667404, -0.035100001841783524, 0.025299999862909317, -0.06840000301599503, 0.15690000355243683, -0.07660000026226044, -0.13609999418258667, 0.11800000071525574, -0.04729999974370003, -0.08879999816417694, -0.15520000457763672, 0.08110000193119049, -0.16220000386238098, 0.11900000274181366, 0.1500999927520752, 0.26260000467300415, 0.010999999940395355, 0.20069999992847443, -0.04729999974370003, 0.15150000154972076, 0.03189999982714653, 0.0949999988079071, 0.14710000157356262, -0.1071000024676323, 0.14090000092983246, 0.03959999978542328, -0.09920000284910202, -0.26010000705718994, -0.3382999897003174, 0.10459999740123749, 0.09220000356435776, -0.17440000176429749, 0.10920000076293945, -0.1565999984741211, -0.3691999912261963, -0.12999999523162842, -0.01269999984651804, -0.021400000900030136, -0.16290000081062317, 0.2231999933719635, -0.2483000010251999, 0.11469999700784683, -0.03150000050663948, 0.08910000324249268, -0.08110000193119049], [-0.010400000028312206, 0.16920000314712524, -0.05920000001788139, -0.07069999724626541, -0.2020999938249588, 0.10279999673366547, -0.19660000503063202, 0.06469999998807907, -0.033399999141693115, 0.3183000087738037, 0.24789999425411224, 0.21130000054836273, 0.11919999867677689, 0.06449999660253525, -0.0737999975681305, -0.04259999841451645, -0.1979999989271164, -0.20080000162124634, -0.0010000000474974513, -0.000699999975040555, -0.15240000188350677, -0.014999999664723873, -0.03400000184774399, -0.1655000001192093, 0.03420000150799751, 0.002099999925121665, -0.06069999933242798, 0.3061999976634979, 0.0754999965429306, -0.1454000025987625, 0.15569999814033508, -0.03280000016093254, 0.008299999870359898, 0.010499999858438969, -0.14589999616146088, -0.11699999868869781, -0.008100000210106373, -0.03790000081062317, 0.07460000365972519, 0.002400000113993883, 0.05270000174641609, -0.249099999666214, 0.11100000143051147, 0.00559999980032444, 0.007000000216066837, 0.0746999979019165, -0.1023000031709671, -0.01119999960064888, -0.24199999868869781, 0.3427000045776367, 0.029999999329447746, -0.08540000021457672, 0.06700000166893005, 0.20309999585151672, 0.09640000015497208, -0.0010000000474974513, 0.11219999939203262, 0.2361000031232834, 0.16750000417232513, -0.07670000195503235, 0.019500000402331352, 0.08550000190734863], [-0.041999999433755875, -0.11320000141859055, -0.10740000009536743, 0.23929999768733978, -0.14959999918937683, 0.1526000052690506, -0.13779999315738678, -0.11379999667406082, -0.16979999840259552, 0.1762000024318695, 0.3296999931335449, -0.15539999306201935, -0.048700001090765, -0.2535000145435333, 0.27720001339912415, -0.2660999894142151, -0.0031999999191612005, -0.2094999998807907, -0.1315000057220459, 0.01209999993443489, 0.061000000685453415, -0.029500000178813934, 0.20550000667572021, -0.2020999938249588, -0.006099999882280827, 0.03139999881386757, 0.052000001072883606, 0.08730000257492065, -0.00039999998989515007, 0.06030000001192093, -0.060499999672174454, 0.14149999618530273, -0.019300000742077827, -0.06030000001192093, 0.14110000431537628, 0.03759999945759773, -0.26919999718666077, -0.02329999953508377, 0.15940000116825104, -0.05139999836683273, -0.14149999618530273, -0.11140000075101852, -0.09600000083446503, 0.0608999989926815, -0.1988999992609024, 0.03880000114440918, 0.051100000739097595, 0.03229999914765358, 0.00559999980032444, 0.01510000042617321, 0.09080000221729279, -0.15489999949932098, -0.18400000035762787, -0.10080000013113022, -0.05550000071525574, 0.15629999339580536, 0.03759999945759773, -0.017500000074505806, -0.0017999999690800905, 0.09560000151395798, 0.2565999925136566, 0.16419999301433563], [0.05570000037550926, 0.11050000041723251, 0.10620000213384628, -0.11479999870061874, 0.09239999949932098, 0.11969999969005585, 0.014600000344216824, -0.09319999814033508, 0.054099999368190765, -0.3212999999523163, -0.16660000383853912, 0.02329999953508377, -0.12680000066757202, -0.06319999694824219, 0.15440000593662262, 0.14730000495910645, 0.14839999377727509, -0.06319999694824219, -0.22460000216960907, 0.147599995136261, 0.12549999356269836, 0.22930000722408295, 0.15649999678134918, 0.010900000110268593, -0.06040000170469284, -0.05909999832510948, 0.32409998774528503, -0.1808999925851822, -0.24150000512599945, -0.10029999911785126, -0.03460000082850456, -0.04179999977350235, -0.1598999947309494, -0.3221000134944916, -0.17990000545978546, -0.11540000140666962, 0.014999999664723873, 0.3499999940395355, -0.17970000207424164, 0.0038999998942017555, 0.19550000131130219, 0.08669999986886978, 0.1882999986410141, 0.12489999830722809, 0.16740000247955322, 0.027799999341368675, -0.22910000383853912, -0.065700002014637, -0.028300000354647636, -0.06669999659061432, -0.20069999992847443, -0.023600000888109207, 0.02539999969303608, -0.05869999900460243, 0.13050000369548798, 0.01640000008046627, 0.04100000113248825, -0.041099999099969864, 0.36149999499320984, 0.17749999463558197, -0.3619000017642975, -0.13539999723434448], [-0.09640000015497208, 0.11289999634027481, 0.15060000121593475, 0.14800000190734863, 0.13449999690055847, -0.014499999582767487, 0.01899999938905239, -0.2460000067949295, -0.13099999725818634, -0.14730000495910645, 0.02590000070631504, -0.12800000607967377, -0.016200000420212746, 0.219200000166893, 0.02199999988079071, 0.036400001496076584, 0.18160000443458557, 0.10689999908208847, 0.07940000295639038, -0.12690000236034393, -0.13079999387264252, 0.03920000046491623, 0.019999999552965164, 0.13099999725818634, 0.07429999858140945, -0.5651000142097473, -0.06270000338554382, -0.10260000079870224, -0.1800999939441681, 0.351500004529953, -0.023800000548362732, -0.1965000033378601, 0.05860000103712082, -0.016599999740719795, 0.05920000001788139, -0.14920000731945038, 0.10729999840259552, 0.045899998396635056, 0.2223999947309494, 0.08799999952316284, 0.18029999732971191, -0.04019999876618385, -0.09769999980926514, 0.2809999883174896, -0.18299999833106995, -0.13740000128746033, 0.27900001406669617, -0.022099999710917473, -0.14429999887943268, 0.04839999973773956, 0.007799999788403511, -0.003000000026077032, 0.1379999965429306, 0.05689999833703041, -0.2526000142097473, 0.013899999670684338, 0.1800999939441681, 0.28290000557899475, 0.07940000295639038, 0.07180000096559525, 0.12349999696016312, 0.05139999836683273], [-0.02630000002682209, 0.10729999840259552, 0.2054000049829483, 0.0348999984562397, -0.05810000002384186, 0.0017999999690800905, -0.06729999929666519, -0.21279999613761902, 0.15719999372959137, -0.13740000128746033, -0.27950000762939453, 0.09080000221729279, -0.14419999718666077, 0.17569999396800995, 0.003800000064074993, -0.08370000123977661, 0.16519999504089355, -0.04910000041127205, 0.2903999984264374, 0.0551999993622303, -0.08810000121593475, 0.0851999968290329, -0.08089999854564667, -0.27720001339912415, 0.08309999853372574, -0.10249999910593033, 0.04089999943971634, 0.06440000236034393, 0.18960000574588776, -0.1525000035762787, -0.1492999941110611, 0.10819999873638153, -0.11550000309944153, -0.010599999688565731, 0.08079999685287476, 0.2736999988555908, 0.09109999984502792, 0.21879999339580536, 0.010300000198185444, -0.35600000619888306, 0.01640000008046627, -0.13410000503063202, -0.07180000096559525, -9.999999747378752e-05, -0.030400000512599945, 0.11069999635219574, 0.21439999341964722, -0.05860000103712082, 0.03530000150203705, -0.17000000178813934, -0.1421000063419342, -0.19040000438690186, -0.12770000100135803, 0.08290000259876251, -0.20569999516010284, -0.032999999821186066, 0.2791000008583069, 0.17919999361038208, -0.019099999219179153, 0.02539999969303608, 0.03790000081062317, -0.031300000846385956], [-0.2500999867916107, -0.0681999996304512, -0.057100001722574234, 0.032999999821186066, -0.030799999833106995, 0.22910000383853912, 0.11270000040531158, -0.13019999861717224, -0.018799999728798866, 0.20550000667572021, 0.1347000002861023, 0.0989999994635582, 0.3788999915122986, 0.08910000324249268, 0.3407000005245209, 0.07829999923706055, 0.20029999315738678, -0.1964000016450882, 0.07750000059604645, 0.06620000302791595, -0.11869999766349792, -0.07540000230073929, -0.15870000422000885, 0.2386000007390976, -0.21969999372959137, 0.3140999972820282, 0.029100000858306885, -0.006000000052154064, -0.022099999710917473, 0.06859999895095825, 0.027499999850988388, -0.2102999985218048, -0.08340000361204147, -0.03869999945163727, -0.1500999927520752, -0.051500000059604645, -0.1177000030875206, -0.23929999768733978, 0.11569999903440475, 0.21719999611377716, 0.1444000005722046, -0.08169999718666077, -0.08060000091791153, 0.033799998462200165, -0.1509000062942505, 0.0658000037074089, 0.03700000047683716, 0.04580000042915344, 0.2070000022649765, 0.05139999836683273, 0.07660000026226044, 0.0892999991774559, -0.003100000089034438, 0.019200000911951065, 0.04659999907016754, 0.18950000405311584, 0.05079999938607216, 0.09459999948740005, -0.21610000729560852, 0.2305999994277954, 0.0210999995470047, -0.20999999344348907], [0.13189999759197235, -0.3061000108718872, 0.011900000274181366, 0.1899999976158142, 0.13940000534057617, 0.04800000041723251, -0.14720000326633453, -0.015200000256299973, 0.08269999921321869, -0.10909999907016754, -0.273499995470047, 0.1688999980688095, -0.026100000366568565, 0.027699999511241913, -0.05640000104904175, 0.005200000014156103, 0.027899999171495438, -0.004000000189989805, 0.07000000029802322, -0.06360000371932983, -0.22660000622272491, 0.16990000009536743, -0.04600000008940697, -0.030500000342726707, 0.04969999939203262, -0.2669000029563904, 0.0471000000834465, -0.08290000259876251, -0.21369999647140503, 0.06080000102519989, 0.1777999997138977, 0.398499995470047, -0.016699999570846558, 0.1356000006198883, 0.14429999887943268, 0.0820000022649765, -0.05920000001788139, 0.2802000045776367, 0.03449999913573265, 0.17219999432563782, 0.032999999821186066, 0.06719999760389328, -0.09229999780654907, 0.053199999034404755, 0.014600000344216824, 0.01140000019222498, 0.06679999828338623, 0.14499999582767487, 0.08609999716281891, -0.0038999998942017555, -0.36230000853538513, 0.1665000021457672, -0.07559999823570251, 0.271699994802475, 0.07119999825954437, -0.11069999635219574, -0.1688999980688095, 0.10559999942779541, -0.1103999987244606, -0.04149999842047691, -0.21050000190734863, 0.0812000036239624], [0.22110000252723694, 0.24120000004768372, -0.011300000362098217, 0.1688999980688095, 0.13300000131130219, 0.21299999952316284, -0.023499999195337296, -0.186599999666214, -0.05119999870657921, -0.11670000106096268, -0.0215000007301569, -0.08789999783039093, -0.1054999977350235, -0.120899997651577, -0.008700000122189522, -0.05469999834895134, -0.12399999797344208, 0.3183000087738037, 0.07090000063180923, -0.0625, -0.23010000586509705, 0.062199998646974564, -0.04360000044107437, 0.06459999829530716, -0.12770000100135803, 0.02449999935925007, 0.060499999672174454, 0.13009999692440033, 0.12549999356269836, 0.027499999850988388, -0.04019999876618385, 0.13449999690055847, 0.020800000056624413, -0.03970000147819519, 0.04600000008940697, -0.04619999974966049, 0.03240000084042549, 0.19249999523162842, -0.1964000016450882, 0.20579999685287476, -0.034699998795986176, 0.17599999904632568, 0.0892999991774559, -0.2712000012397766, 0.08730000257492065, 0.06300000101327896, 0.15960000455379486, 0.20800000429153442, -0.10289999842643738, -0.050599999725818634, -0.2498999983072281, 0.030500000342726707, 0.1395999938249588, -0.1168999969959259, -0.14079999923706055, -0.2313999980688095, 0.13740000128746033, 0.22200000286102295, 0.08990000188350677, 0.05829999968409538, -0.16609999537467957, -0.12349999696016312], [-0.02800000086426735, 0.1671999990940094, -0.0658000037074089, 0.36970001459121704, 0.01489999983459711, 0.0017999999690800905, 0.04280000180006027, 0.22169999778270721, 0.21330000460147858, 0.05860000103712082, 0.1597999930381775, 0.020400000736117363, -0.24580000340938568, 0.15299999713897705, 0.16349999606609344, 0.37369999289512634, -0.11159999668598175, 0.04859999939799309, -0.43709999322891235, 0.06400000303983688, 0.11909999698400497, 0.06729999929666519, -0.11190000176429749, 0.08529999852180481, -0.20839999616146088, -0.18719999492168427, 0.07079999893903732, -0.2939999997615814, 0.05689999833703041, -9.999999747378752e-05, 0.14030000567436218, 0.16869999468326569, -0.3628999888896942, -0.10080000013113022, -0.23919999599456787, -0.1225999966263771, 0.1761000007390976, 0.08190000057220459, 0.19499999284744263, 0.10019999742507935, 0.22460000216960907, 0.1331000030040741, 0.06459999829530716, 0.1551000028848648, -0.00139999995008111, 0.23000000417232513, 0.0949999988079071, -0.3691999912261963, -0.0008999999845400453, -0.09529999643564224, -0.08829999715089798, 0.26969999074935913, 0.03310000151395798, -0.029899999499320984, -0.1761000007390976, -0.11330000311136246, -0.14579999446868896, 0.15379999577999115, -0.13510000705718994, 0.059700001031160355, -0.03189999982714653, -0.19220000505447388], [-0.05550000071525574, 0.2214999943971634, 0.1307000070810318, -0.0714000016450882, -0.005200000014156103, 0.00800000037997961, 0.1808999925851822, 0.1688999980688095, -0.0406000018119812, 0.2547000050544739, 0.05249999836087227, 0.12960000336170197, -0.321399986743927, -0.07930000126361847, -0.09120000153779984, 0.1476999968290329, 0.1266999989748001, -0.15330000221729279, 0.15839999914169312, -0.14149999618530273, -0.1607999950647354, -0.10080000013113022, 0.11389999836683273, 0.13930000364780426, -0.005200000014156103, -0.08060000091791153, -0.1273999959230423, -0.09189999848604202, -0.23109999299049377, -0.1923999935388565, -0.10620000213384628, 0.133200004696846, -0.038600001484155655, 0.21389999985694885, -0.050700001418590546, -0.08060000091791153, -0.09369999915361404, -0.05400000140070915, -0.17489999532699585, 0.1062999963760376, -0.02759999968111515, -0.18549999594688416, -0.13009999692440033, -0.2273000031709671, 0.0340999998152256, 0.02879999950528145, -0.04149999842047691, 0.057500001043081284, -0.05169999971985817, -0.048700001090765, -0.11599999666213989, 0.0851999968290329, -0.23399999737739563, -0.1615999937057495, -0.1898999959230423, 0.019999999552965164, 0.07850000262260437, -0.012199999764561653, 0.07580000162124634, 0.012299999594688416, 0.06769999861717224, -0.003000000026077032], [-0.022099999710917473, -0.038600001484155655, 0.006200000178068876, 0.011300000362098217, 0.15680000185966492, -0.09319999814033508, 0.1850000023841858, -0.010099999606609344, -0.06800000369548798, 0.07159999758005142, 0.06599999964237213, -0.08449999988079071, 0.13529999554157257, -0.05510000139474869, -0.14419999718666077, -0.210099995136261, -0.004999999888241291, -0.5080000162124634, -0.08950000256299973, -0.06689999997615814, -0.02319999970495701, -0.01510000042617321, -0.16689999401569366, -0.03620000183582306, -0.23149999976158142, 0.1973000019788742, -0.2849999964237213, 0.06859999895095825, 0.029600000008940697, 0.28459998965263367, -0.058800000697374344, -0.10090000182390213, -0.024000000208616257, -0.07729999721050262, -0.030400000512599945, -0.2791999876499176, 0.17630000412464142, -0.12540000677108765, 0.1720000058412552, -0.1370999962091446, 0.03310000151395798, -0.05649999901652336, -0.01899999938905239, -0.01940000057220459, 0.1370999962091446, 0.24490000307559967, -0.1451999992132187, 0.1459999978542328, -0.11010000109672546, -0.09549999982118607, -0.14030000567436218, -0.002099999925121665, -0.007799999788403511, -0.02070000022649765, -0.09049999713897705, 0.07509999722242355, -0.015300000086426735, -0.08269999921321869, -0.09529999643564224, -0.07649999856948853, 0.19249999523162842, -0.030400000512599945], [0.11230000108480453, -0.007699999958276749, -0.011699999682605267, 0.04039999842643738, -0.065700002014637, -0.11400000005960464, 0.1582999974489212, -0.09290000051259995, 0.2468000054359436, -0.1565999984741211, 0.08250000327825546, 0.06120000034570694, 0.1476999968290329, 0.210999995470047, -0.013399999588727951, 0.38769999146461487, 0.22990000247955322, 0.3596000075340271, -0.2919999957084656, 0.017100000753998756, -0.047200001776218414, -0.06480000168085098, -0.05220000073313713, -0.2459000051021576, 0.02459999918937683, 0.1193000003695488, -0.1136000007390976, -0.17509999871253967, -0.30640000104904175, 0.12780000269412994, 0.08990000188350677, 0.15049999952316284, 0.04450000077486038, -0.14399999380111694, -0.34389999508857727, 0.06729999929666519, -0.13519999384880066, 0.383899986743927, 0.1404999941587448, 0.06069999933242798, -0.07519999891519547, 0.10509999841451645, 0.28679999709129333, -0.11140000075101852, -0.13259999454021454, 0.10750000178813934, -0.14740000665187836, -0.15700000524520874, -0.0843999981880188, -0.15449999272823334, -0.1444000005722046, 0.14669999480247498, 0.09989999979734421, -0.18539999425411224, -0.19120000302791595, -0.08129999786615372, -0.2980000078678131, 0.2199999988079071, 0.13369999825954437, 0.014299999922513962, -0.2750000059604645, -0.1949000060558319], [-0.01810000091791153, -0.06620000302791595, -0.15780000388622284, -0.15129999816417694, 0.11490000039339066, 0.16979999840259552, -0.0885000005364418, -0.13279999792575836, 0.325300008058548, -0.31310001015663147, 0.07190000265836716, 0.3497999906539917, -0.10010000318288803, -0.06069999933242798, 0.11860000342130661, -0.04149999842047691, -0.03720000013709068, -0.018799999728798866, 0.08560000360012054, -0.0010000000474974513, 0.17520000040531158, 0.11259999871253967, -0.17550000548362732, 0.23749999701976776, -0.16580000519752502, 0.05959999933838844, -0.181099995970726, -0.3359000086784363, -0.2800000011920929, 0.05590000003576279, 0.03020000085234642, -0.15549999475479126, -0.12430000305175781, -0.17270000278949738, -0.03440000116825104, -0.06549999862909317, -0.0071000000461936, -0.17820000648498535, 0.23199999332427979, 0.06360000371932983, 0.10939999669790268, 0.09149999916553497, 0.4268999993801117, -0.07689999788999557, -0.013199999928474426, 0.11959999799728394, -0.15729999542236328, -0.12559999525547028, 0.05649999901652336, -0.12559999525547028, 0.2409999966621399, 0.13609999418258667, 0.1648000031709671, -0.2858000099658966, 0.06260000169277191, -0.03819999843835831, -0.09929999709129333, 0.17110000550746918, -0.06840000301599503, 0.19169999659061432, 0.20170000195503235, 0.01510000042617321], [0.052799999713897705, 0.0430000014603138, 0.0560000017285347, 0.10769999772310257, -0.1137000024318695, 0.23929999768733978, -0.1386999934911728, -0.0778999999165535, 0.20720000565052032, 0.026599999517202377, 0.0010999999940395355, -0.06530000269412994, -0.065700002014637, 0.11879999935626984, -0.2599000036716461, -0.03290000185370445, 0.17599999904632568, -0.1331000030040741, -0.14640000462532043, 0.052000001072883606, 0.14869999885559082, 0.07490000128746033, -0.1712000072002411, 0.22859999537467957, -0.08349999785423279, 0.03920000046491623, -0.09369999915361404, -0.15369999408721924, -0.09989999979734421, -0.05490000173449516, 0.15199999511241913, -0.1331000030040741, 0.028300000354647636, -0.003800000064074993, 0.06499999761581421, 0.1429000049829483, -0.19419999420642853, 0.15189999341964722, -0.22169999778270721, -0.0632999986410141, -0.3147999942302704, 0.10440000146627426, -0.18400000035762787, 0.06419999897480011, 0.10970000177621841, -0.06360000371932983, 0.14949999749660492, -0.07479999959468842, -0.07209999859333038, 0.16949999332427979, -0.15889999270439148, -0.07429999858140945, 0.12430000305175781, 0.13130000233650208, -0.1655000001192093, -0.11879999935626984, 0.00039999998989515007, -0.06610000133514404, 0.029200000688433647, 0.0007999999797903001, -0.0617000013589859, 0.024800000712275505], [0.06700000166893005, 0.05180000141263008, -0.08219999819993973, -0.08349999785423279, 0.16369999945163727, -0.11100000143051147, -0.027000000700354576, -0.2134000062942505, 0.06289999932050705, 0.16009999811649323, 0.28189998865127563, -0.22949999570846558, -0.22429999709129333, 0.05299999937415123, 0.32030001282691956, -0.10189999639987946, 0.3569999933242798, -0.023600000888109207, 0.029500000178813934, -0.08009999990463257, 0.1265999972820282, -0.026799999177455902, -0.07859999686479568, 0.022600000724196434, -0.07479999959468842, 0.09700000286102295, 0.0071000000461936, -0.17919999361038208, 0.05290000140666962, -0.008200000040233135, 0.013799999840557575, 0.048900000751018524, 0.12970000505447388, 0.0706000030040741, 0.06700000166893005, -0.016200000420212746, 0.3073999881744385, -0.46860000491142273, 0.20520000159740448, 0.012500000186264515, -0.1615000069141388, -0.10480000078678131, 0.19750000536441803, 0.11739999800920486, 0.094200000166893, 0.05040000006556511, 0.028999999165534973, 0.28049999475479126, -0.0430000014603138, 0.2824999988079071, 0.1445000022649765, -0.12970000505447388, -0.163100004196167, 0.18569999933242798, 0.05849999934434891, 0.35899999737739563, 0.04699999839067459, 0.008700000122189522, -0.06650000065565109, 0.014299999922513962, 0.1574999988079071, -0.01489999983459711], [0.09290000051259995, -0.16670000553131104, 0.0478999987244606, -0.1509000062942505, 0.01730000041425228, 0.038100000470876694, -0.12309999763965607, 0.10999999940395355, -0.03959999978542328, 0.035599999129772186, -0.025599999353289604, -0.20010000467300415, 0.24379999935626984, -0.03370000049471855, 0.031199999153614044, -0.20499999821186066, -0.12020000070333481, -0.08259999752044678, 0.060600001364946365, 0.27549999952316284, -0.09929999709129333, 0.11320000141859055, 0.1468999981880188, 0.014600000344216824, -0.040699999779462814, 0.19910000264644623, 0.07429999858140945, -0.1923999935388565, 0.08630000054836273, -0.21969999372959137, -0.1307000070810318, -0.12060000002384186, 0.3425000011920929, 0.13819999992847443, -0.0689999982714653, 0.23389999568462372, -0.02800000086426735, -0.036400001496076584, -0.017000000923871994, -0.08030000329017639, 0.13600000739097595, -0.19020000100135803, 0.08420000225305557, 0.011599999852478504, 0.15150000154972076, -0.13860000669956207, 0.29030001163482666, 0.181099995970726, -0.12240000069141388, -0.23340000212192535, -0.2558000087738037, -0.09489999711513519, -0.03680000081658363, -0.18490000069141388, 0.06769999861717224, -0.10719999670982361, -0.10930000245571136, 0.026799999177455902, 0.14229999482631683, -0.14300000667572021, 0.02930000051856041, 0.22200000286102295], [0.1168999969959259, -0.05420000106096268, 0.010700000450015068, -0.06030000001192093, -0.11990000307559967, -0.026200000196695328, 0.03909999877214432, 0.10989999771118164, -0.07680000364780426, -0.02969999983906746, -0.1386999934911728, -0.10360000282526016, -0.1632000058889389, -0.2240000069141388, 0.13910000026226044, 0.04470000043511391, -0.014299999922513962, -0.13850000500679016, -0.22689999639987946, 0.08640000224113464, 0.2502000033855438, -0.04839999973773956, -0.023399999365210533, -0.12200000137090683, -0.24220000207424164, 0.4065000116825104, -0.0835999995470047, 0.09080000221729279, -0.21529999375343323, 0.1551000028848648, -0.008799999952316284, -0.1582999974489212, -0.1371999979019165, 0.11590000241994858, -0.3637000024318695, -0.08399999886751175, -0.12380000203847885, -0.3490000069141388, -0.14820000529289246, 0.05469999834895134, 0.16910000145435333, 0.042899999767541885, 0.28780001401901245, -0.017899999395012856, -0.11670000106096268, 0.04820000007748604, 0.027300000190734863, -0.07119999825954437, 0.275299996137619, 0.19179999828338623, 0.28130000829696655, -0.034699998795986176, -0.1899999976158142, 0.1428000032901764, 0.05900000035762787, 0.21690000593662262, -0.17229999601840973, 0.1889999955892563, -0.21860000491142273, 0.13050000369548798, 0.0007999999797903001, 0.0012000000569969416], [-0.1632000058889389, 0.07720000296831131, 0.018400000408291817, -0.14820000529289246, -0.13920000195503235, 0.2021999955177307, 0.14820000529289246, 0.11949999630451202, 0.20280000567436218, -0.07460000365972519, 0.08219999819993973, -0.07289999723434448, -0.20280000567436218, 0.06440000236034393, 0.23010000586509705, 0.1599999964237213, 0.20110000669956207, 0.1914999932050705, -0.027799999341368675, -0.26660001277923584, 0.2303999960422516, 0.28630000352859497, 0.09690000116825104, 0.1428000032901764, 0.05649999901652336, 0.11630000174045563, -0.0731000006198883, -0.3529999852180481, 0.0026000000070780516, 0.3181000053882599, 0.062199998646974564, 0.12370000034570694, 0.020099999383091927, -0.0851999968290329, -0.26589998602867126, -0.23729999363422394, -0.0471000000834465, 0.359499990940094, 0.08720000088214874, -0.11509999632835388, 0.4226999878883362, 0.21789999306201935, 0.10109999775886536, 0.093299999833107, 0.10559999942779541, 0.25920000672340393, -0.18569999933242798, -0.07540000230073929, 0.18790000677108765, 0.18070000410079956, 0.031700000166893005, 0.07259999960660934, 0.2409999966621399, -0.16339999437332153, -0.03480000048875809, -0.04129999876022339, -0.29280000925064087, 0.23999999463558197, -0.2492000013589859, 0.07689999788999557, -0.14650000631809235, -0.20309999585151672], [0.17440000176429749, -0.03350000083446503, -0.0544000007212162, -0.10580000281333923, 0.0771000012755394, -0.032099999487400055, 0.10419999808073044, 0.04529999941587448, 0.06960000097751617, 0.08760000020265579, -0.2720000147819519, 0.06849999725818634, -0.026100000366568565, 0.012900000438094139, 0.04410000145435333, -0.035999998450279236, -0.25189998745918274, 0.12049999833106995, -0.05660000070929527, 0.11649999767541885, -0.04740000143647194, -0.19050000607967377, 0.013100000098347664, -0.03229999914765358, 9.999999747378752e-05, -0.15950000286102295, -0.19820000231266022, -0.42329999804496765, -0.09489999711513519, -0.006399999838322401, 0.0940999984741211, -0.02710000053048134, 0.021400000900030136, -0.3034999966621399, -0.2563999891281128, -0.025800000876188278, -0.13930000364780426, 0.4041000008583069, -0.09809999912977219, -0.18850000202655792, 0.07919999957084656, 0.08810000121593475, 0.09830000251531601, -0.015599999576807022, -0.08839999884366989, 0.027499999850988388, -0.014700000174343586, 0.10490000247955322, -0.093299999833107, -0.03280000016093254, 0.07169999927282333, 0.04100000113248825, -0.022700000554323196, 0.065700002014637, 0.005400000140070915, -0.26269999146461487, -0.05290000140666962, 0.03790000081062317, -0.2069000005722046, 0.31929999589920044, -0.48089998960494995, -0.07819999754428864], [0.3098999857902527, 0.12030000239610672, -0.24979999661445618, -0.11180000007152557, -0.1306000053882599, 0.2721000015735626, 0.24310000240802765, 0.2913999855518341, 0.17419999837875366, -0.06939999759197235, 0.02199999988079071, 0.36579999327659607, -0.008299999870359898, -0.07209999859333038, 0.2117999941110611, 0.22429999709129333, 0.2062000036239624, 0.08649999648332596, -0.3384000062942505, 0.23109999299049377, 0.1460999995470047, -0.1388999968767166, 0.20029999315738678, -0.17949999868869781, -0.04769999906420708, 0.020099999383091927, -0.1712000072002411, -0.2743000090122223, -0.06369999796152115, 0.3528999984264374, 0.03629999980330467, -0.07750000059604645, -0.32260000705718994, -0.13650000095367432, -0.32249999046325684, 0.04749999940395355, 0.04410000145435333, 0.2657999992370605</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>[-3.160692057357383]</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>[0.9497471475744135]</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>[-2.860954058786909]</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>[0.8814684405955877]</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>[-4.529113340716731]</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>[1.8095665252471655]</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>[-3.017403633144702]</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>[0.9228742391217223]</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>[-1.8706646887196023]</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>[0.6808097861120666]</t>
+        </is>
+      </c>
+      <c r="O38" t="inlineStr">
+        <is>
+          <t>[-9.956468327527404]</t>
+        </is>
+      </c>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>[3.601910953654165]</t>
+        </is>
+      </c>
+      <c r="Q38" t="inlineStr">
+        <is>
+          <t>[0.349996706926328]</t>
+        </is>
+      </c>
+      <c r="R38" t="inlineStr">
+        <is>
+          <t>[0.07008707893463234]</t>
+        </is>
+      </c>
+      <c r="S38" t="inlineStr">
+        <is>
+          <t>[0.031452203614829366]</t>
+        </is>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>[0.08161016639655387]</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>[-0.40176395310065494]</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>[0.13404105752823547]</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>[0.2892406494218015]</t>
+        </is>
+      </c>
+      <c r="X38" t="inlineStr">
+        <is>
+          <t>[0.07445959276361633]</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>[0.049148955815850326]</t>
+        </is>
+      </c>
+      <c r="Z38" t="inlineStr">
+        <is>
+          <t>[0.07824858437441727]</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>[-0.42009952561804664]</t>
+        </is>
+      </c>
+      <c r="AB38" t="inlineStr">
+        <is>
+          <t>[0.13065536836268005]</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>[-0.5900284603079868]</t>
+        </is>
+      </c>
+      <c r="AD38" t="inlineStr">
+        <is>
+          <t>[0.13323797937247298]</t>
+        </is>
+      </c>
+      <c r="AE38" t="inlineStr">
+        <is>
+          <t>[-0.395100153868432]</t>
+        </is>
+      </c>
+      <c r="AF38" t="inlineStr">
+        <is>
+          <t>[0.15022169772362415]</t>
+        </is>
+      </c>
+      <c r="AG38" t="inlineStr">
+        <is>
+          <t>[-1.7697031536491985]</t>
+        </is>
+      </c>
+      <c r="AH38" t="inlineStr">
+        <is>
+          <t>[0.20620428471678034]</t>
+        </is>
+      </c>
+      <c r="AI38" t="inlineStr">
+        <is>
+          <t>[-1.1895595321656112]</t>
+        </is>
+      </c>
+      <c r="AJ38" t="inlineStr">
+        <is>
+          <t>[0.17943196621250834]</t>
+        </is>
+      </c>
+      <c r="AK38" t="inlineStr">
+        <is>
+          <t>[-0.41824245837646257]</t>
+        </is>
+      </c>
+      <c r="AL38" t="inlineStr">
+        <is>
+          <t>[0.15053604600794482]</t>
+        </is>
+      </c>
+      <c r="AM38" t="inlineStr">
+        <is>
+          <t>[-1.0061248543900967]</t>
+        </is>
+      </c>
+      <c r="AN38" t="inlineStr">
+        <is>
+          <t>[0.15408493242780258]</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>model_62_32_16_2</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>[62, 32, 16]</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>[[[-0.05169999971985817, 0.011599999852478504, 0.05860000103712082, 0.015599999576807022, -0.0568000003695488, 0.0071000000461936, -0.04830000177025795, 0.012000000104308128, 0.012199999764561653, 0.0006000000284984708, -0.012400000356137753, 0.032099999487400055, 0.012500000186264515, -0.06700000166893005, -9.999999747378752e-05, 0.053700000047683716, -0.13729999959468842, 0.050999999046325684, -0.026900000870227814, 0.04170000180602074, -0.0071000000461936, 0.04320000112056732, 0.0003000000142492354, 0.015699999406933784, -0.0632999986410141, 0.04490000009536743, -0.0071000000461936, 0.08869999647140503, 0.030500000342726707, -0.001500000013038516, 0.05389999970793724, -0.05169999971985817, -0.02070000022649765, 0.0020000000949949026, 0.01140000019222498, 0.009800000116229057, 0.01940000057220459, -0.03799999877810478, -0.01640000008046627, 0.01549999974668026, -0.024399999529123306, 0.09529999643564224, -0.006300000008195639, -0.015699999406933784, -0.07580000162124634, -0.03310000151395798, -0.020099999383091927, 0.032099999487400055, 0.10859999805688858, 0.09799999743700027, 0.048700001090765, -0.03189999982714653, 0.02250000089406967, -0.05260000005364418, -0.016499999910593033, 0.02250000089406967, -0.0203000009059906, -0.004600000102072954, 0.022700000554323196, -0.01769999973475933, -0.05779999867081642, 0.13570000231266022], [-0.026399999856948853, -0.004699999932199717, 0.01940000057220459, -0.014499999582767487, -0.07180000096559525, 0.035599999129772186, 0.02669999934732914, 0.06109999865293503, -0.020500000566244125, 0.0340999998152256, 0.062199998646974564, 0.04610000178217888, 0.01489999983459711, -0.07909999787807465, 0.0786999985575676, 0.016200000420212746, -0.037300001829862595, 0.04659999907016754, -0.05420000106096268, 0.04479999840259552, -0.061400000005960464, -0.031300000846385956, 0.04540000110864639, 0.013299999758601189, -0.0006000000284984708, -0.011900000274181366, -0.09560000151395798, 0.02879999950528145, 0.07519999891519547, 0.05119999870657921, -0.01600000075995922, 0.012600000016391277, -0.00839999970048666, -0.05860000103712082, -0.08869999647140503, 0.04019999876618385, -0.0215000007301569, -0.013799999840557575, 0.053300000727176666, -0.08959999680519104, 0.052000001072883606, 0.007300000172108412, 0.026100000366568565, -0.016300000250339508, -0.020899999886751175, -0.03929999843239784, -0.11860000342130661, 0.030500000342726707, 0.029400000348687172, 0.039500001817941666, -0.031300000846385956, 0.027499999850988388, -0.030500000342726707, -0.05730000138282776, 0.013399999588727951, -0.0215000007301569, -0.061000000685453415, 0.016899999231100082, -0.026000000536441803, -0.03720000013709068, -0.05510000139474869, 0.015200000256299973]], [[-0.06159999966621399, -0.05979999899864197, 0.06759999692440033, 0.003100000089034438, -0.08370000123977661, 0.06639999896287918, -0.3873000144958496, 0.07000000029802322, 0.09539999812841415, -0.09040000289678574, 0.1111999973654747, 0.07590000331401825, 0.08160000294446945, -0.2184000015258789, 0.11100000143051147, 0.032099999487400055, 0.12610000371932983, 0.09049999713897705, 0.04270000010728836, -0.18529999256134033, 0.15209999680519104, -0.22429999709129333, -0.21969999372959137, -0.04540000110864639, -0.19120000302791595, 0.16210000216960907, -0.027300000190734863, 0.14890000224113464, -0.08190000057220459, -0.2345999926328659, 0.05900000035762787, 0.0828000009059906, -0.010499999858438969, 0.17219999432563782, 0.0940999984741211, -0.08560000360012054, 0.006200000178068876, -0.08110000193119049, -0.11270000040531158, 0.004800000227987766, 0.08380000293254852, -0.12160000205039978, -0.0869000032544136, -0.10379999876022339, -0.019999999552965164, -0.13529999554157257, 0.13099999725818634, -0.09120000153779984, -0.07360000163316727, 0.3716000020503998, -0.06120000034570694, -0.12999999523162842, -0.060499999672174454, -0.013299999758601189, 0.09390000253915787, -0.020800000056624413, -0.015399999916553497, -0.05130000039935112, -0.00139999995008111, -0.031199999153614044, 0.2029999941587448, -0.06970000267028809], [0.031099999323487282, 0.0017000000225380063, -0.21459999680519104, -0.02630000002682209, -0.2134000062942505, 0.03759999945759773, 0.027000000700354576, 0.1379999965429306, 0.04619999974966049, 0.0843999981880188, 0.27649998664855957, 0.03009999915957451, 0.13979999721050262, -0.007899999618530273, 0.026200000196695328, -0.23180000483989716, -0.1251000016927719, 0.10779999941587448, 0.012900000438094139, 0.12800000607967377, -0.04039999842643738, 0.12219999730587006, -0.06650000065565109, 0.21140000224113464, -0.008799999952316284, 0.012799999676644802, 0.028300000354647636, -0.16439999639987946, 0.07909999787807465, -0.0020000000949949026, -0.09740000218153, -0.09769999980926514, -0.15029999613761902, -0.10339999943971634, 0.0478999987244606, -0.13539999723434448, -0.14390000700950623, -0.1428000032901764, -0.01810000091791153, -0.2872999906539917, 0.06199999898672104, -0.06750000268220901, 0.002300000051036477, -0.02879999950528145, -0.024399999529123306, 0.024700000882148743, -0.048700001090765, -0.22859999537467957, -0.007400000002235174, -0.12229999899864197, -0.1754000037908554, -0.003100000089034438, -0.09099999815225601, -0.21389999985694885, -0.09529999643564224, 0.18930000066757202, -0.2621000111103058, -0.16940000653266907, 0.15870000422000885, 0.016300000250339508, 0.1696999967098236, -0.15109999477863312], [-0.013299999758601189, -0.13210000097751617, 0.065700002014637, 0.0026000000070780516, -0.042399998754262924, -0.3578000068664551, 0.1185000017285347, -0.051600001752376556, 0.14339999854564667, 0.13330000638961792, -0.15870000422000885, -0.0013000000035390258, -0.027699999511241913, 0.006500000134110451, -0.1290999948978424, -9.999999747378752e-05, -0.13619999587535858, -0.10140000283718109, 0.265500009059906, -0.014999999664723873, -0.14880000054836273, -0.0142000000923872, -0.06080000102519989, -0.03669999912381172, -0.16179999709129333, 0.018799999728798866, 0.10999999940395355, -0.04809999838471413, 0.042399998754262924, -0.20340000092983246, 0.10419999808073044, -0.2603999972343445, -0.19939999282360077, 0.0989999994635582, 0.061000000685453415, 0.10450000315904617, -0.12720000743865967, -0.007899999618530273, 0.19990000128746033, 0.12359999865293503, 0.06719999760389328, 0.2287999987602234, 0.226500004529953, 0.1746000051498413, -0.09830000251531601, -0.031099999323487282, 0.10369999706745148, -0.0917000025510788, 0.009700000286102295, 0.12549999356269836, -0.12449999898672104, 0.11640000343322754, -0.12960000336170197, 0.03310000151395798, 0.03869999945163727, -0.2134000062942505, -0.06610000133514404, 0.014100000262260437, -0.012199999764561653, 0.04520000144839287, 0.15119999647140503, -0.13169999420642853], [-0.266400009393692, -0.09049999713897705, -0.11959999799728394, 0.1023000031709671, 0.23729999363422394, 0.1923000067472458, -0.20280000567436218, 0.021299999207258224, -0.020899999886751175, 0.13809999823570251, -0.1979999989271164, -0.09369999915361404, 0.04800000041723251, 0.1509999930858612, 0.1647000014781952, -0.016699999570846558, 0.060499999672174454, -0.028200000524520874, 0.0737999975681305, -0.06849999725818634, 0.019300000742077827, -0.20649999380111694, 0.005499999970197678, 0.10180000215768814, 0.13650000095367432, 0.03830000013113022, 0.13259999454021454, 0.14030000567436218, 0.06069999933242798, -0.08489999920129776, 0.11180000007152557, -0.094200000166893, -0.2676999866962433, 0.1386999934911728, 0.015699999406933784, -0.1168999969959259, 0.08479999750852585, 0.08550000190734863, 0.06780000030994415, -0.05469999834895134, 0.1307000070810318, -0.04619999974966049, 0.2768999934196472, 0.004600000102072954, 0.06759999692440033, 0.09679999947547913, -0.06889999657869339, -0.06199999898672104, 0.19009999930858612, -0.12999999523162842, 0.15360000729560852, 0.006500000134110451, -0.07590000331401825, -0.04859999939799309, 0.046300001442432404, 0.2401999980211258, -0.05900000035762787, 0.17100000381469727, 0.18389999866485596, 0.08479999750852585, -0.13940000534057617, -0.01860000006854534], [-0.0778999999165535, 0.11320000141859055, 0.09440000355243683, -0.17059999704360962, -0.10930000245571136, 0.09679999947547913, -0.003800000064074993, -0.13120000064373016, 0.008500000461935997, -0.11649999767541885, -0.1340000033378601, 0.1177000030875206, -0.24220000207424164, 0.009999999776482582, 0.00930000003427267, -0.31709998846054077, 0.16099999845027924, -0.05939999967813492, -0.09260000288486481, 0.21719999611377716, 0.030400000512599945, 0.07580000162124634, -0.11469999700784683, -0.16930000483989716, -0.02329999953508377, 0.1655000001192093, 0.05180000141263008, -0.1914999932050705, 0.2206999957561493, 0.1770000010728836, 0.03750000149011612, -0.06129999831318855, -0.025800000876188278, 0.14180000126361847, 0.18029999732971191, 0.03269999846816063, 0.1858000010251999, -0.10719999670982361, 0.03150000050663948, 0.2272000014781952, -0.1446000039577484, 0.07649999856948853, 0.011599999852478504, 0.010900000110268593, -0.009800000116229057, -0.16859999299049377, -0.09149999916553497, -0.1324000060558319, 0.09000000357627869, 0.018200000748038292, -0.03240000084042549, -0.10440000146627426, -0.17810000479221344, 0.024700000882148743, 0.09880000352859497, 0.2272000014781952, -0.10199999809265137, 0.12349999696016312, -0.005100000184029341, -0.0843999981880188, 0.09839999675750732, 0.1500999927520752], [-0.2085999995470047, 0.0835999995470047, 0.14300000667572021, 0.013299999758601189, -0.263700008392334, 0.06790000200271606, 0.10670000314712524, -0.12189999967813492, 0.03449999913573265, 0.015399999916553497, -0.11829999834299088, -0.0005000000237487257, 0.24979999661445618, 0.10189999639987946, 0.12960000336170197, -0.22200000286102295, 0.0333000011742115, 0.07620000094175339, -0.16380000114440918, -0.06279999762773514, -0.09790000319480896, -0.04259999841451645, 0.019999999552965164, -0.1316000074148178, -0.051100000739097595, -0.04650000110268593, -0.39899998903274536, -0.005400000140070915, 0.13210000097751617, -0.07959999889135361, -0.04960000142455101, -0.16369999945163727, -0.12240000069141388, 0.14839999377727509, 0.02070000022649765, -0.03709999844431877, -0.1988999992609024, -0.0568000003695488, 0.04390000179409981, 0.02590000070631504, 0.016499999910593033, -0.024299999698996544, -0.04010000079870224, -0.09099999815225601, 0.10400000214576721, -0.20440000295639038, 0.09030000120401382, 0.09560000151395798, 0.05570000037550926, -0.034699998795986176, 0.0284000001847744, 0.0640999972820282, 0.21389999985694885, 0.06549999862909317, -0.03830000013113022, -0.0013000000035390258, 0.10899999737739563, -0.10189999639987946, -0.06629999727010727, 0.09040000289678574, -0.2655999958515167, -0.24400000274181366], [-0.05290000140666962, 0.11169999837875366, -0.03629999980330467, -0.31279999017715454, -0.03739999979734421, -0.07859999686479568, -0.017000000923871994, 0.10970000177621841, 0.2313999980688095, 0.15299999713897705, 0.10790000110864639, 0.05090000107884407, -0.24279999732971191, 0.1444000005722046, 0.03319999948143959, -0.04800000041723251, 0.008100000210106373, 0.03720000013709068, -0.16990000009536743, -0.328900009393692, -0.1137000024318695, -0.12240000069141388, 0.37860000133514404, 0.11389999836683273, -0.2565999925136566, 0.15440000593662262, -0.06069999933242798, -0.03700000047683716, -0.03660000115633011, 0.07890000194311142, 0.08669999986886978, 0.20260000228881836, 0.06920000165700912, 0.12549999356269836, 0.04479999840259552, -0.015799999237060547, -0.04619999974966049, 0.11680000275373459, 0.11330000311136246, -0.0027000000700354576, 0.027699999511241913, -0.06809999793767929, 0.06379999965429306, -0.041200000792741776, 0.03799999877810478, -0.021800000220537186, -0.06109999865293503, -0.2184000015258789, -0.13339999318122864, -0.17309999465942383, 0.058400001376867294, 0.0706000030040741, 0.07010000199079514, -0.00430000014603138, -0.0364999994635582, -0.09179999679327011, 0.0034000000450760126, 0.15330000221729279, 0.008700000122189522, -0.043800000101327896, 0.07069999724626541, -0.016200000420212746], [-0.0494999997317791, -0.2754000127315521, 0.00019999999494757503, -0.27639999985694885, -0.20739999413490295, 0.004399999976158142, -0.04540000110864639, 0.0737999975681305, 0.08250000327825546, 0.05559999868273735, -0.06790000200271606, -0.19789999723434448, 0.08009999990463257, -0.012000000104308128, 0.11079999804496765, 0.14259999990463257, -0.16349999606609344, 0.13300000131130219, 0.06279999762773514, 0.1599999964237213, 0.08879999816417694, -0.0835999995470047, 0.18479999899864197, 0.15309999883174896, 0.07119999825954437, -0.09529999643564224, 0.042500000447034836, 0.04650000110268593, 0.13369999825954437, 0.17080000042915344, -0.08139999955892563, -0.06459999829530716, 0.011800000444054604, 0.12960000336170197, -0.012500000186264515, 0.21899999678134918, 0.3203999996185303, -0.09570000320672989, 0.18150000274181366, -0.09350000321865082, 0.07739999890327454, 0.09449999779462814, -0.14110000431537628, 0.1023000031709671, 0.0284000001847744, -0.008700000122189522, 0.15809999406337738, -0.029899999499320984, 0.00430000014603138, 0.10119999945163727, 0.10869999974966049, -0.20069999992847443, 0.10819999873638153, -0.11900000274181366, 0.08609999716281891, 0.01730000041425228, 0.0003000000142492354, -0.06530000269412994, -0.14419999718666077, -0.24120000004768372, -0.08070000261068344, -0.0568000003695488], [0.24289999902248383, 0.09290000051259995, 0.12770000100135803, 0.014100000262260437, -0.04230000078678131, -0.022099999710917473, 0.0, -0.19760000705718994, 0.039500001817941666, 0.21320000290870667, -0.0877000018954277, 0.20659999549388885, 0.0763000026345253, -0.021199999377131462, 0.05000000074505806, 0.0027000000700354576, 0.024000000208616257, 0.0794999971985817, 0.061900001019239426, 0.1509999930858612, 0.009800000116229057, 0.050599999725818634, 0.30000001192092896, 0.016300000250339508, 0.0957999974489212, 0.24040000140666962, -0.05719999969005585, 0.0421999990940094, -0.13120000064373016, -0.12349999696016312, 0.08780000358819962, -0.048700001090765, -0.022600000724196434, 0.035999998450279236, -0.03530000150203705, 0.11190000176429749, 0.09120000153779984, 0.14560000598430634, -0.21629999577999115, -0.041600000113248825, -0.09700000286102295, -0.1761000007390976, 0.11739999800920486, -0.03280000016093254, -0.1835000067949295, 0.19529999792575836, 0.1678999960422516, 0.051600001752376556, 0.04650000110268593, 0.0071000000461936, -0.08919999748468399, -0.04670000076293945, -0.08460000157356262, 0.16619999706745148, -0.1137000024318695, 0.28690001368522644, 0.04769999906420708, 0.019099999219179153, -0.07580000162124634, -0.22280000150203705, 0.05079999938607216, -0.26980000734329224], [-0.125, -0.2651999890804291, -0.03530000150203705, -0.2370000034570694, 0.03660000115633011, -0.1859000027179718, -0.22920000553131104, -0.13860000669956207, -0.0820000022649765, -0.03669999912381172, -0.08810000121593475, 0.26100000739097595, 0.1704999953508377, 0.1354999989271164, -0.04450000077486038, -0.13210000097751617, 0.08609999716281891, -0.0142000000923872, 0.10840000212192535, -0.0026000000070780516, -0.07959999889135361, -0.09229999780654907, -0.07320000231266022, 0.0649000033736229, -0.08479999750852585, 0.06390000134706497, -0.08030000329017639, -0.2387000024318695, -0.17739999294281006, 0.04839999973773956, -0.14710000157356262, 0.06549999862909317, 0.038600001484155655, -0.18799999356269836, 0.17100000381469727, -0.1412000060081482, 0.10180000215768814, -0.1160999983549118, -0.02459999918937683, -0.026399999856948853, -0.07440000027418137, 0.01360000018030405, -0.011099999770522118, 0.0348999984562397, 0.24860000610351562, 0.32350000739097595, 0.013500000350177288, 0.08179999887943268, 0.11829999834299088, -0.034699998795986176, 0.12129999697208405, 0.09600000083446503, -0.057100001722574234, -0.007300000172108412, -0.10559999942779541, -0.049400001764297485, 0.11890000104904175, -0.060600001364946365, -0.21379999816417694, 0.07620000094175339, 0.05380000174045563, 0.010300000198185444], [-0.1080000028014183, 0.22789999842643738, 0.06509999930858612, 0.015200000256299973, 0.11420000344514847, 0.012900000438094139, -0.02239999920129776, -0.05389999970793724, 0.21140000224113464, -0.1940000057220459, -0.1080000028014183, -0.08209999650716782, -0.08869999647140503, -0.008899999782443047, 0.1581999957561493, 0.11999999731779099, -0.2069000005722046, 0.04360000044107437, 0.1128000020980835, -0.10610000044107437, -0.024000000208616257, 0.03779999911785126, 0.01730000041425228, 0.012500000186264515, -0.1712000072002411, -0.0957999974489212, -0.1088000014424324, 0.012799999676644802, -0.1282999962568283, 0.05339999869465828, -0.2222999930381775, -0.04809999838471413, -0.17499999701976776, -0.16030000150203705, 0.16099999845027924, 0.17710000276565552, 0.14630000293254852, 0.04399999976158142, -0.2842999994754791, 0.08980000019073486, -0.2282000035047531, 0.06520000100135803, 0.03840000182390213, -0.04639999940991402, 0.003599999938160181, 0.001500000013038516, -0.14560000598430634, 0.04410000145435333, -0.07639999687671661, -0.09529999643564224, 0.07240000367164612, -0.17800000309944153, -0.19820000231266022, -0.2720000147819519, 0.06960000097751617, -0.062300000339746475, -0.030799999833106995, -0.08290000259876251, 0.08219999819993973, 0.0697999969124794, -0.032499998807907104, -0.2671000063419342], [-0.14740000665187836, 0.17710000276565552, -0.09860000014305115, -0.023499999195337296, -0.11729999631643295, -0.03359999880194664, 0.24079999327659607, 0.07800000160932541, -0.29089999198913574, 0.12700000405311584, -0.14149999618530273, -0.23549999296665192, 0.02290000021457672, 0.08139999955892563, -0.0812000036239624, 0.14710000157356262, -0.020500000566244125, -0.17090000212192535, 0.07599999755620956, 0.05620000138878822, -0.1177000030875206, -0.06650000065565109, 0.020800000056624413, -0.10360000282526016, -0.13830000162124634, 0.21850000321865082, -0.007499999832361937, -0.030300000682473183, -0.08139999955892563, 0.14149999618530273, -0.006200000178068876, 0.06270000338554382, 0.06949999928474426, 0.09480000287294388, -0.14489999413490295, -0.15690000355243683, -0.009200000204145908, -0.08860000222921371, -0.2076999992132187, -0.16619999706745148, 0.09929999709129333, 0.02539999969303608, 0.1306000053882599, -0.1720999926328659, 0.0731000006198883, -0.11150000244379044, 0.013299999758601189, 0.13089999556541443, -0.0215000007301569, 0.23999999463558197, 0.13089999556541443, -0.013399999588727951, -0.12839999794960022, -0.24250000715255737, -0.08959999680519104, 0.08489999920129776, -0.05460000038146973, 0.09809999912977219, -0.22059999406337738, -0.01810000091791153, 0.1436000019311905, -0.03269999846816063], [0.09440000355243683, -0.15489999949932098, 0.003800000064074993, 0.12549999356269836, -0.18790000677108765, -0.06350000202655792, 0.004900000058114529, 0.06700000166893005, -0.08540000021457672, -0.11710000038146973, -0.018300000578165054, 0.15919999778270721, -0.033799998462200165, 0.2989000082015991, -0.031700000166893005, 0.22679999470710754, 0.054099999368190765, 0.19599999487400055, -0.16220000386238098, 0.025699999183416367, -0.03750000149011612, -0.0835999995470047, -0.049400001764297485, -0.06520000100135803, -0.0803999975323677, 0.06390000134706497, -0.08070000261068344, 0.19040000438690186, 0.07989999651908875, 0.14489999413490295, 0.0560000017285347, 0.03150000050663948, -0.048700001090765, 0.022199999541044235, -0.009600000455975533, 0.03449999913573265, -0.007499999832361937, 0.040300000458955765, 0.164900004863739, 0.30660000443458557, 0.2759999930858612, 0.054099999368190765, -0.1128000020980835, -0.09139999747276306, -0.06560000032186508, 0.18379999697208405, -0.005100000184029341, 0.21930000185966492, -0.1316000074148178, -0.1678999960422516, -0.09120000153779984, -0.15479999780654907, -0.2062000036239624, -0.09130000323057175, -0.11389999836683273, 0.13600000739097595, -0.11940000206232071, -0.03539999946951866, 0.0340999998152256, 0.19760000705718994, 0.11919999867677689, -0.07859999686479568], [-0.0860000029206276, 0.16699999570846558, 0.17159999907016754, 0.07020000368356705, 0.07079999893903732, 0.0066999997943639755, 0.18160000443458557, -0.04399999976158142, 0.05959999933838844, -0.14560000598430634, 0.19820000231266022, 0.10890000313520432, 0.046799998730421066, 0.22139999270439148, 0.06469999998807907, 0.010400000028312206, 0.11190000176429749, -0.0835999995470047, 0.11630000174045563, 0.07370000332593918, -0.05510000139474869, 0.0738999992609024, 0.012199999764561653, -0.16859999299049377, -0.08590000122785568, -0.04529999941587448, -0.02850000001490116, 0.1526000052690506, -0.02370000071823597, -0.08219999819993973, -0.08789999783039093, 0.10849999636411667, -0.06549999862909317, 0.017500000074505806, 0.017000000923871994, 0.07109999656677246, 0.12449999898672104, -0.05620000138878822, 0.04800000041723251, -0.26989999413490295, 0.26260000467300415, 0.2078000009059906, 0.12049999833106995, 0.032600000500679016, 0.17790000140666962, 0.07959999889135361, 0.026499999687075615, -0.1965000033378601, 0.08799999952316284, -0.00430000014603138, 0.060100000351667404, -0.33250001072883606, 0.05420000106096268, 0.1931000053882599, -0.19859999418258667, -0.04439999908208847, 0.14980000257492065, -0.11159999668598175, 0.1500999927520752, -0.13099999725818634, 0.1460999995470047, 0.1216999962925911], [0.08349999785423279, 0.04340000078082085, 0.01119999960064888, 0.05009999871253967, -0.05050000175833702, 0.10899999737739563, -0.07590000331401825, -0.09220000356435776, 0.09600000083446503, -0.1607999950647354, -0.2215999960899353, 0.007199999876320362, -0.06069999933242798, -0.07050000131130219, -0.1923999935388565, -0.14059999585151672, -0.24969999492168427, -0.12200000137090683, -0.313400000333786, -0.11010000109672546, 0.1168999969959259, 0.11990000307559967, 0.07959999889135361, 0.03700000047683716, 0.030799999833106995, -0.09239999949932098, 0.17309999465942383, 0.04919999837875366, 0.13979999721050262, 0.008500000461935997, -0.09640000015497208, -0.061799999326467514, 0.05849999934434891, 0.00800000037997961, 0.11569999903440475, 0.007400000002235174, 0.029899999499320984, 0.09359999746084213, 0.0471000000834465, -0.131400004029274, 0.2387000024318695, -0.2037999927997589, 0.13030000030994415, -0.07400000095367432, 0.059300001710653305, -0.033900000154972076, 0.24089999496936798, 0.12020000070333481, 0.09950000047683716, -0.026499999687075615, 0.24140000343322754, 0.11640000343322754, -0.15299999713897705, -0.028300000354647636, -0.021900000050663948, -0.0689999982714653, 0.15680000185966492, -0.17880000174045563, -0.006399999838322401, 0.04859999939799309, 0.3111000061035156, -0.019999999552965164], [0.026399999856948853, -0.05050000175833702, -0.012500000186264515, 0.04010000079870224, -0.005900000222027302, -0.3073999881744385, -0.043299999088048935, -0.05249999836087227, 0.13459999859333038, 0.1657000035047531, -0.009800000116229057, -0.030300000682473183, -0.19140000641345978, -0.1535000056028366, 0.025499999523162842, 0.0006000000284984708, 0.2378000020980835, 0.03460000082850456, -0.03150000050663948, -0.09560000151395798, 0.08569999784231186, 0.006800000090152025, -0.03550000116229057, -0.2287999987602234, 0.20069999992847443, 0.16120000183582306, 0.08619999885559082, 0.07639999687671661, 0.06499999761581421, 0.22290000319480896, -0.15209999680519104, 0.21490000188350677, -0.3865000009536743, -0.025699999183416367, 0.028999999165534973, 0.09290000051259995, 0.003800000064074993, -0.16670000553131104, -0.07680000364780426, -0.22509999573230743, 0.12110000103712082, 0.10809999704360962, -0.14339999854564667, -0.18649999797344208, -0.0722000002861023, -0.03610000014305115, 0.009399999864399433, 0.10520000010728836, 0.06610000133514404, -0.07980000227689743, -0.00430000014603138, 0.24469999969005585, -0.04529999941587448, -0.03150000050663948, -0.014499999582767487, -0.06239999830722809, 0.05999999865889549, -0.08449999988079071, 0.06589999794960022, -0.07649999856948853, -0.11680000275373459, -0.03480000048875809], [-0.16169999539852142, -0.07750000059604645, 0.1451999992132187, -0.20630000531673431, 0.08420000225305557, 0.052400000393390656, 0.25369998812675476, 0.06360000371932983, 0.026599999517202377, -0.2768000066280365, 0.06449999660253525, -0.07410000264644623, 0.004000000189989805, -0.07050000131130219, -0.10599999874830246, -0.014299999922513962, -0.08100000023841858, 0.21639999747276306, -0.017000000923871994, -0.006899999920278788, 0.2442999929189682, -0.14020000398159027, -0.005100000184029341, 0.186599999666214, 0.07530000060796738, 0.1891999989748001, -0.08619999885559082, 0.09719999879598618, -0.21819999814033508, 0.10379999876022339, 0.17219999432563782, -0.06639999896287918, -0.00039999998989515007, -0.07100000232458115, 0.17270000278949738, 0.03350000083446503, -0.17810000479221344, 0.14869999885559082, 0.04089999943971634, -0.034299999475479126, 0.055399999022483826, 0.16439999639987946, 0.1274999976158142, -0.0502999983727932, -0.09189999848604202, -0.061400000005960464, -0.14190000295639038, 0.06340000033378601, 0.2240000069141388, 0.08649999648332596, -0.18410000205039978, 0.15809999406337738, -0.08349999785423279, -0.05220000073313713, -0.10920000076293945, 0.1306000053882599, 0.1720999926328659, -0.13940000534057617, -0.024299999698996544, -0.09009999781847, -0.041099999099969864, 0.10639999806880951], [0.03849999979138374, -0.18289999663829803, 0.19220000505447388, -0.12520000338554382, 0.11289999634027481, 0.1800999939441681, 0.05820000171661377, 0.07129999995231628, 0.06700000166893005, 0.05950000137090683, -0.09099999815225601, 0.3562999963760376, -0.23180000483989716, 0.1234000027179718, 0.04470000043511391, -0.004699999932199717, -0.20810000598430634, -0.0010000000474974513, -0.06930000334978104, 0.2152000069618225, -0.17509999871253967, 0.08990000188350677, -0.20800000429153442, 0.16179999709129333, 0.10849999636411667, 0.031700000166893005, 0.09889999777078629, 0.11559999734163284, -0.14720000326633453, 0.017999999225139618, -0.10719999670982361, 0.1679999977350235, 0.04580000042915344, 0.15160000324249268, -0.021800000220537186, -0.10639999806880951, -0.20559999346733093, -0.05429999902844429, -0.025699999183416367, -0.2249000072479248, -0.022700000554323196, 0.12110000103712082, -0.027799999341368675, -0.01080000028014183, 0.017100000753998756, -0.15389999747276306, 0.08869999647140503, 0.05490000173449516, -0.14790000021457672, 0.08489999920129776, 0.04190000146627426, -0.0568000003695488, -0.10010000318288803, 0.018300000578165054, 0.10530000180006027, -0.04399999976158142, 0.06480000168085098, 0.1518000066280365, 0.043699998408555984, 0.09120000153779984, -0.1785999983549118, -0.18219999969005585], [-0.17730000615119934, -0.007600000128149986, -0.25699999928474426, 0.14309999346733093, 0.033399999141693115, -0.2004999965429306, 0.1103999987244606, 0.2329999953508377, 0.06589999794960022, -0.22630000114440918, 0.04280000180006027, 0.16189999878406525, -0.023900000378489494, 0.06629999727010727, 0.047600001096725464, -0.07980000227689743, 0.06610000133514404, 0.02410000003874302, 0.14659999310970306, -0.0010000000474974513, 0.034299999475479126, -0.03500000014901161, 0.15049999952316284, 0.008100000210106373, 0.08349999785423279, 0.14880000054836273, 0.07069999724626541, -0.05420000106096268, -0.030300000682473183, 0.20810000598430634, -0.07649999856948853, -0.2759999930858612, 0.12520000338554382, -0.006399999838322401, 0.042899999767541885, -0.09000000357627869, 0.03959999978542328, 0.04600000008940697, -0.009100000374019146, -0.04619999974966049, 0.046799998730421066, -0.25690001249313354, 0.06830000132322311, -0.11980000138282776, 0.002099999925121665, -0.1031000018119812, 0.10840000212192535, 0.10440000146627426, -0.07829999923706055, 0.03280000016093254, -0.006800000090152025, -0.15700000524520874, -0.15150000154972076, 0.3370000123977661, 0.1665000021457672, -0.19930000603199005, -0.13979999721050262, -0.07109999656677246, -0.0034000000450760126, -0.06319999694824219, -0.2117999941110611, -0.028999999165534973], [-0.052000001072883606, -0.02969999983906746, -0.06759999692440033, -0.09309999644756317, -0.012000000104308128, -0.01940000057220459, -0.27619999647140503, 0.06340000033378601, 0.11050000041723251, -0.1696999967098236, 0.1103999987244606, -0.1387999951839447, -0.07400000095367432, 0.2687000036239624, 0.049800001084804535, 0.06360000371932983, -0.006099999882280827, 0.06080000102519989, -0.03440000116825104, 0.06030000001192093, -0.17829999327659607, 0.17980000376701355, -0.14020000398159027, -0.14640000462532043, -0.16179999709129333, 0.31869998574256897, 0.09570000320672989, 0.15309999883174896, 0.15770000219345093, -0.02199999988079071, 0.020800000056624413, -0.23389999568462372, 0.03539999946951866, -0.1607999950647354, -0.21140000224113464, -0.09880000352859497, -0.031099999323487282, 0.17170000076293945, -0.10249999910593033, -0.14219999313354492, -0.16899999976158142, 0.08730000257492065, -0.05510000139474869, 0.1429000049829483, -0.26190000772476196, -0.04780000075697899, 0.1363999992609024, 0.026599999517202377, 0.12770000100135803, -0.09929999709129333, 0.09929999709129333, 0.07069999724626541, 0.14190000295639038, -0.02850000001490116, -0.00139999995008111, 0.031199999153614044, 0.15549999475479126, -0.04919999837875366, -0.08609999716281891, -0.009999999776482582, 0.011900000274181366, 0.03840000182390213], [-0.2054000049829483, 0.09319999814033508, 0.10729999840259552, 0.25130000710487366, -0.09809999912977219, -0.04470000043511391, -0.24950000643730164, -0.24650000035762787, -0.15610000491142273, -0.02449999935925007, 0.0020000000949949026, -0.04450000077486038, -0.1420000046491623, -0.05959999933838844, -0.11330000311136246, -0.014999999664723873, 0.09009999781847, -0.03700000047683716, -0.09520000219345093, 0.013000000268220901, -0.05480000004172325, -0.16200000047683716, 0.013500000350177288, 0.24400000274181366, -0.04019999876618385, -0.05000000074505806, -0.0024999999441206455, 0.07240000367164612, 0.06239999830722809, 0.08209999650716782, -0.14640000462532043, 0.03720000013709068, -0.02669999934732914, -0.14959999918937683, 0.121799997985363, 0.07699999958276749, -0.08259999752044678, 0.17350000143051147, 0.22579999268054962, -0.272599995136261, -0.13570000231266022, 0.021299999207258224, 0.039500001817941666, 0.15129999816417694, -0.11020000278949738, -0.09929999709129333, 0.012900000438094139, 0.057999998331069946, -0.1331000030040741, 0.07169999927282333, -0.11259999871253967, -0.12319999933242798, -0.04010000079870224, 0.04619999974966049, -0.3082999885082245, -0.031700000166893005, -0.20280000567436218, 0.13289999961853027, -0.17090000212192535, -0.07530000060796738, -0.07980000227689743, 0.01209999993443489], [-0.020800000056624413, 0.15610000491142273, -0.11259999871253967, -0.12060000002384186, 0.0877000018954277, 0.006500000134110451, -0.08720000088214874, -0.0674000009894371, -0.07010000199079514, -0.11900000274181366, -0.0020000000949949026, -0.01640000008046627, 0.028999999165534973, -0.24940000474452972, 0.06909999996423721, -0.0860000029206276, -0.009200000204145908, 0.08129999786615372, 0.030400000512599945, -0.017000000923871994, -0.031700000166893005, 0.14839999377727509, 0.03420000150799751, 0.3172000050544739, -0.2281000018119812, 0.09430000185966492, 0.04580000042915344, 0.029999999329447746, -0.007899999618530273, -0.06689999997615814, -0.35499998927116394, 0.04170000180602074, -0.05570000037550926, 0.14100000262260437, -0.28940001130104065, 0.05979999899864197, -0.02850000001490116, -0.27399998903274536, 0.041999999433755875, 0.17630000412464142, 0.19539999961853027, 0.13189999759197235, 0.2092999964952469, -0.08049999922513962, -0.13279999792575836, 0.05040000006556511, 0.06769999861717224, 0.21529999375343323, 0.021199999377131462, -0.1348000019788742, -0.14419999718666077, -0.03759999945759773, 0.06620000302791595, 0.13519999384880066, 0.032600000500679016, 0.06840000301599503, 0.0658000037074089, 0.09359999746084213, -0.06390000134706497, 0.05040000006556511, -0.04749999940395355, 0.13189999759197235], [-0.04600000008940697, -0.155799999833107, 0.14480000734329224, 0.1996999979019165, -0.2459000051021576, -0.066600002348423, -0.002300000051036477, 0.2526000142097473, -0.14489999413490295, -0.18310000002384186, 0.05999999865889549, -0.12020000070333481, -0.059300001710653305, 0.07079999893903732, -0.030400000512599945, -0.013500000350177288, 0.0649000033736229, -0.26350000500679016, 0.004999999888241291, -0.03790000081062317, 0.10849999636411667, 0.1501999944448471, -0.08640000224113464, 0.23849999904632568, 0.06639999896287918, 0.12330000102519989, -0.09300000220537186, 0.03460000082850456, -0.008299999870359898, -0.03290000185370445, 0.0186999998986</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>[[[0.017999999225139618, -0.10209999978542328, 0.14259999990463257, -0.03929999843239784, -0.0003000000142492354, -0.0860000029206276, -0.1096000000834465, 0.013700000010430813, 0.06310000270605087, -0.04800000041723251, -0.04179999977350235, -0.061500001698732376, 0.0812000036239624, -0.007400000002235174, -0.042899999767541885, 0.04830000177025795, -0.2312999963760376, 0.047200001776218414, -0.03539999946951866, 0.049300000071525574, -0.0778999999165535, 0.09730000048875809, -0.017899999395012856, 0.11869999766349792, -0.08259999752044678, 0.1264999955892563, 0.012799999676644802, 0.1257999986410141, -0.06120000034570694, -0.05779999867081642, 0.11140000075101852, -0.05119999870657921, -0.008299999870359898, 0.01119999960064888, 0.10180000215768814, -0.033799998462200165, 0.09350000321865082, -0.06729999929666519, -0.13179999589920044, 0.0640999972820282, -0.1459999978542328, 0.1306000053882599, 0.0012000000569969416, 0.017500000074505806, -0.08910000324249268, -0.012199999764561653, 0.014499999582767487, 0.07010000199079514, 0.14100000262260437, 0.10279999673366547, 0.1371999979019165, -0.13940000534057617, 0.03280000016093254, -0.04340000078082085, -0.05920000001788139, 0.04969999939203262, 0.11230000108480453, -0.0032999999821186066, 0.10279999673366547, 0.08749999850988388, -0.030899999663233757, 0.14890000224113464], [-0.08869999647140503, 0.07180000096559525, -0.019099999219179153, 0.05050000175833702, -0.02759999968111515, -0.006399999838322401, 0.06379999965429306, 0.09730000048875809, -0.10750000178813934, 0.1071000024676323, 0.1363999992609024, 0.08760000020265579, 0.0038999998942017555, -0.04960000142455101, 0.1551000028848648, -0.02850000001490116, 0.010499999858438969, 0.08590000122785568, 0.05590000003576279, -0.05460000038146973, -0.04390000179409981, -0.04529999941587448, 0.0215000007301569, -0.11500000208616257, -0.015699999406933784, -0.027300000190734863, -0.1712000072002411, -0.017100000753998756, 0.1256999969482422, 0.1395999938249588, -0.02810000069439411, 0.08060000091791153, -0.014700000174343586, -0.11230000108480453, -0.11670000106096268, 0.07509999722242355, -0.030899999663233757, 0.041099999099969864, 0.03359999880194664, -0.13750000298023224, 0.08640000224113464, -0.03139999881386757, 0.1046999990940094, -0.06530000269412994, 0.031199999153614044, -0.10260000079870224, -0.1809999942779541, 0.022099999710917473, -0.0066999997943639755, -0.016100000590085983, -0.14139999449253082, 0.04919999837875366, -0.0551999993622303, -0.10490000247955322, 0.10949999839067459, -0.10080000013113022, -0.17569999396800995, 0.06319999694824219, -0.03269999846816063, -0.06199999898672104, -0.10080000013113022, -0.042100001126527786]], [[0.0005000000237487257, -0.0989999994635582, 0.015399999916553497, -0.050599999725818634, -0.0860000029206276, -0.0008999999845400453, -0.38280001282691956, 0.06260000169277191, 0.1145000010728836, -0.03689999878406525, 0.13359999656677246, 0.11649999767541885, 0.12710000574588776, -0.2646999955177307, 0.07890000194311142, -0.01549999974668026, 0.13680000603199005, 0.16099999845027924, -0.010499999858438969, -0.18359999358654022, 0.20990000665187836, -0.19619999825954437, -0.2522999942302704, -0.07639999687671661, -0.26260000467300415, 0.20509999990463257, -0.0997999981045723, 0.22599999606609344, 0.0024999999441206455, -0.15320000052452087, 0.0706000030040741, 0.041200000792741776, -0.007400000002235174, 0.10100000351667404, 0.0658000037074089, -0.13740000128746033, 0.05310000106692314, -0.065700002014637, -0.14820000529289246, -0.04089999943971634, 0.12439999729394913, -0.18529999256134033, -0.12460000067949295, -0.1785999983549118, 0.01899999938905239, -0.2249000072479248, 0.14229999482631683, -0.13940000534057617, 0.0272000003606081, 0.3411000072956085, -0.07190000265836716, -0.06830000132322311, 0.01640000008046627, -0.09560000151395798, 0.15320000052452087, -0.002099999925121665, 0.05000000074505806, -0.026499999687075615, 0.1281999945640564, -0.04919999837875366, 0.11379999667406082, 0.02459999918937683], [0.1096000000834465, 0.07320000231266022, -0.4083999991416931, 0.13920000195503235, -0.06340000033378601, 0.07209999859333038, 0.19789999723434448, 0.18559999763965607, 0.22910000383853912, 0.15080000460147858, 0.3935999870300293, -0.052400000393390656, 0.05649999901652336, 0.08609999716281891, 0.02930000051856041, -0.26820001006126404, 0.07660000026226044, 0.32030001282691956, 0.19059999287128448, 0.2919999957084656, 0.09359999746084213, 0.05480000004172325, -0.17319999635219574, 0.33079999685287476, 0.0786999985575676, -0.03929999843239784, -0.20479999482631683, -0.23029999434947968, 0.26019999384880066, 0.18000000715255737, -0.25270000100135803, 0.014700000174343586, -0.25429999828338623, -0.07509999722242355, 0.025699999183416367, -0.34779998660087585, -0.10970000177621841, -0.015300000086426735, 0.06719999760389328, -0.39079999923706055, 0.2451999932527542, -0.23430000245571136, -0.18289999663829803, 0.10859999805688858, 0.010200000368058681, -0.24570000171661377, -0.06260000169277191, -0.4020000100135803, -0.13269999623298645, -0.32829999923706055, -0.303600013256073, 0.13830000162124634, 0.05050000175833702, -0.2883000075817108, -0.05079999938607216, 0.033799998462200165, -0.4146000146865845, -0.06480000168085098, 0.18310000002384186, 0.048700001090765, 0.21619999408721924, -0.1467999964952469], [-0.08510000258684158, -0.13989999890327454, 0.05990000069141388, 0.022700000554323196, -0.14630000293254852, -0.4099999964237213, 0.07940000295639038, -0.04410000145435333, 0.12080000340938568, 0.1817999929189682, -0.16609999537467957, 0.07209999859333038, 0.054499998688697815, 0.003599999938160181, -0.07259999960660934, 0.004600000102072954, -0.09040000289678574, -0.23729999363422394, 0.24809999763965607, -0.02070000022649765, -0.27889999747276306, 0.016200000420212746, -0.07810000330209732, -0.02290000021457672, -0.14749999344348907, 0.04019999876618385, 0.22439999878406525, -0.05999999865889549, 0.04259999841451645, -0.32919999957084656, 0.18610000610351562, -0.2303999960422516, -0.17419999837875366, 0.1859000027179718, 0.07329999655485153, 0.1559000015258789, -0.045499999076128006, -0.08820000290870667, 0.2094999998807907, 0.250900000333786, -0.02449999935925007, 0.2257000058889389, 0.39879998564720154, 0.1703999936580658, -0.15929999947547913, 0.07100000232458115, 0.04399999976158142, -0.007899999618530273, -0.12309999763965607, 0.17249999940395355, -0.10350000113248825, 0.055399999022483826, -0.22949999570846558, 0.07199999690055847, 0.02419999986886978, -0.17270000278949738, 0.019999999552965164, -0.011099999770522118, -0.03180000185966492, 0.04639999940991402, 0.06939999759197235, -0.11339999735355377], [-0.2824999988079071, -0.04769999906420708, -0.09709999710321426, 0.06610000133514404, 0.2921999990940094, 0.28929999470710754, -0.1776999980211258, 0.018200000748038292, -0.037700001150369644, 0.02930000051856041, -0.2614000141620636, -0.1428000032901764, -0.023900000378489494, 0.2476000040769577, 0.12620000541210175, -0.01860000006854534, 0.08579999953508377, -0.014299999922513962, 0.06750000268220901, -0.11259999871253967, -0.017899999395012856, -0.2939000129699707, 0.03189999982714653, 0.07090000063180923, 0.20029999315738678, -0.025800000876188278, 0.13779999315738678, 0.04259999841451645, -0.019200000911951065, -0.12720000743865967, 0.022600000724196434, -0.08869999647140503, -0.20829999446868896, 0.16830000281333923, 0.025599999353289604, -0.08569999784231186, 0.0027000000700354576, 0.181099995970726, 0.08560000360012054, -0.14509999752044678, 0.1500999927520752, -0.02590000070631504, 0.2272000014781952, 0.10019999742507935, 0.11389999836683273, 0.12790000438690186, -0.0031999999191612005, -0.05169999971985817, 0.1307000070810318, -0.13099999725818634, 0.15850000083446503, -0.01510000042617321, -0.11429999768733978, 0.030500000342726707, -0.033900000154972076, 0.20479999482631683, -0.16439999639987946, 0.17389999330043793, 0.051899999380111694, 0.09269999712705612, -0.06369999796152115, -0.09109999984502792], [-0.029999999329447746, 0.04439999908208847, 0.1404000073671341, -0.11729999631643295, -0.07349999994039536, 0.09719999879598618, -0.030500000342726707, -0.20239999890327454, 0.022199999541044235, 0.022099999710917473, -0.07569999992847443, 0.1525000035762787, -0.23010000586509705, -0.0035000001080334187, -0.02969999983906746, -0.32010000944137573, 0.1517000049352646, 0.02319999970495701, -0.13079999387264252, 0.28439998626708984, 0.10899999737739563, 0.09480000287294388, -0.05119999870657921, -0.21119999885559082, -0.049400001764297485, 0.2874000072479248, -0.047600001096725464, -0.1673000007867813, 0.2093999981880188, 0.272599995136261, 0.013299999758601189, -0.025100000202655792, -0.014100000262260437, 0.18240000307559967, 0.21299999952316284, 0.01600000075995922, 0.15770000219345093, -0.08320000022649765, -0.004999999888241291, 0.13420000672340393, -0.09839999675750732, 0.09989999979734421, -0.03660000115633011, 0.039900001138448715, -0.024000000208616257, -0.23019999265670776, -0.10540000349283218, -0.18160000443458557, 0.1289999932050705, 0.040699999779462814, -0.07699999958276749, -0.07519999891519547, -0.20389999449253082, 0.05820000171661377, 0.14149999618530273, 0.18520000576972961, -0.1145000010728836, 0.26010000705718994, 0.08780000358819962, -0.14920000731945038, 0.09629999846220016, 0.12870000302791595], [-0.211899995803833, 0.17739999294281006, 0.11479999870061874, 0.07150000333786011, -0.24400000274181366, 0.09019999951124191, 0.1274999976158142, -0.06129999831318855, 0.11100000143051147, -0.012900000438094139, -0.25360000133514404, -0.04360000044107437, 0.20430000126361847, 0.036400001496076584, 0.20829999446868896, -0.13179999589920044, -0.0414000004529953, 0.032099999487400055, -0.07119999825954437, 0.08070000261068344, -0.16259999573230743, -0.1404999941587448, 0.027300000190734863, -0.02329999953508377, 0.004000000189989805, -0.06729999929666519, -0.37220001220703125, -0.05730000138282776, 0.19750000536441803, -0.09650000184774399, -0.04430000111460686, -0.08720000088214874, -0.2240000069141388, 0.09799999743700027, -0.011099999770522118, 0.03779999911785126, -0.15060000121593475, -0.15360000729560852, 0.14110000431537628, -0.06870000064373016, -0.04529999941587448, -0.018200000748038292, 0.03750000149011612, -0.08959999680519104, 0.007400000002235174, -0.22339999675750732, -0.04230000078678131, 0.16840000450611115, 0.13920000195503235, 0.020600000396370888, 0.1712999939918518, 0.045099999755620956, 0.19509999454021454, 0.07119999825954437, -0.048500001430511475, -0.09589999914169312, 0.09969999641180038, -0.053199999034404755, -0.04650000110268593, 0.23680000007152557, -0.23880000412464142, -0.1704999953508377], [0.029100000858306885, 0.21639999747276306, -0.09650000184774399, -0.21459999680519104, 0.13650000095367432, -0.009499999694526196, 0.05389999970793724, 0.07620000094175339, 0.3057999908924103, 0.0575999990105629, 0.03500000014901161, -0.08320000022649765, -0.4016999900341034, 0.12999999523162842, -0.02850000001490116, 0.039799999445676804, 0.043800000101327896, 0.10849999636411667, -0.012500000186264515, -0.15459999442100525, 0.09000000357627869, -0.21729999780654907, 0.3887999951839447, 0.20999999344348907, -0.12870000302791595, 0.04659999907016754, -0.13609999418258667, -0.16979999840259552, 0.11420000344514847, 0.17000000178813934, -0.03400000184774399, 0.27309998869895935, -0.07739999890327454, 0.14900000393390656, -0.0674000009894371, -0.0406000018119812, -0.10930000245571136, 0.2517000138759613, 0.21400000154972076, -0.15960000455379486, 0.16279999911785126, -0.1062999963760376, -0.09799999743700027, 0.04650000110268593, 0.006000000052154064, -0.181099995970726, -0.12549999356269836, -0.35269999504089355, -0.050200000405311584, -0.2476000040769577, 0.15800000727176666, 0.13120000064373016, 0.1251000016927719, -0.007300000172108412, -0.014399999752640724, -0.22609999775886536, -0.1234000027179718, 0.34630000591278076, -0.024000000208616257, 0.07909999787807465, 0.2160000056028366, -0.05689999833703041], [-0.0625, -0.19519999623298645, -0.08190000057220459, -0.2567000091075897, -0.19339999556541443, -0.002400000113993883, 0.0017999999690800905, 0.09669999778270721, 0.09510000050067902, -0.0032999999821186066, -0.061400000005960464, -0.23639999330043793, 0.0544000007212162, -0.004699999932199717, 0.10440000146627426, 0.13449999690055847, -0.1177000030875206, 0.0746999979019165, 0.149399995803833, 0.10040000081062317, 0.0421999990940094, -0.11110000312328339, 0.12129999697208405, 0.18809999525547028, 0.08560000360012054, -0.18359999358654022, 0.07190000265836716, 0.052299998700618744, 0.15919999778270721, 0.19539999961853027, -0.10050000250339508, -0.08669999986886978, -0.00139999995008111, 0.13169999420642853, -0.05090000107884407, 0.17949999868869781, 0.34929999709129333, -0.10159999877214432, 0.227400004863739, -0.01860000006854534, 0.06289999932050705, 0.0406000018119812, -0.10520000010728836, 0.09070000052452087, 0.049800001084804535, -0.019999999552965164, 0.19990000128746033, -0.020600000396370888, -0.08720000088214874, 0.04910000041127205, 0.10040000081062317, -0.16590000689029694, 0.1565999984741211, -0.1412000060081482, 0.04769999906420708, 0.044599998742341995, 0.02370000071823597, -0.1573999971151352, -0.18199999630451202, -0.2648000121116638, -0.0722000002861023, -0.04450000077486038], [0.21040000021457672, -0.02969999983906746, 0.17219999432563782, 0.05640000104904175, -0.1324000060558319, -0.07959999889135361, -0.13019999861717224, -0.21480000019073486, 0.03880000114440918, 0.3328000009059906, 0.06480000168085098, 0.33709999918937683, 0.19380000233650208, -0.09480000287294388, 0.11259999871253967, 0.007899999618530273, -0.028999999165534973, 0.05730000138282776, -0.01759999990463257, 0.3167000114917755, -0.0026000000070780516, 0.17100000381469727, 0.32179999351501465, 0.0012000000569969416, 0.011800000444054604, 0.3472000062465668, -0.04749999940395355, 0.12729999423027039, -0.09160000085830688, -0.149399995803833, 0.17640000581741333, 0.05689999833703041, -0.02370000071823597, 0.07970000058412552, 0.00930000003427267, 0.06960000097751617, 0.14579999446868896, 0.004000000189989805, -0.30219998955726624, 0.04879999905824661, -0.2190999984741211, -0.14100000262260437, 0.16990000009536743, -0.06719999760389328, -0.3052999973297119, 0.147599995136261, 0.07329999655485153, 0.10080000013113022, -0.059700001031160355, 0.10329999774694443, -0.18400000035762787, -0.06270000338554382, -0.09300000220537186, 0.15440000593662262, -0.06689999997615814, 0.25679999589920044, 0.11159999668598175, 0.16419999301433563, -0.020899999886751175, -0.2870999872684479, -0.06629999727010727, -0.2508000135421753], [-0.12269999831914902, -0.1657000035047531, -0.11330000311136246, -0.2549999952316284, 0.056699998676776886, -0.17479999363422394, -0.18299999833106995, -0.09430000185966492, -0.1088000014424324, -0.13339999318122864, -0.19840000569820404, 0.18490000069141388, 0.10119999945163727, 0.1535000056028366, -0.05050000175833702, -0.07329999655485153, 0.07509999722242355, -0.05869999900460243, 0.20960000157356262, -0.07720000296831131, -0.1395999938249588, -0.17659999430179596, -0.11659999936819077, 0.1216999962925911, 0.002400000113993883, -0.04560000076889992, -0.03999999910593033, -0.3499999940395355, -0.17659999430179596, 0.0035000001080334187, -0.18619999289512634, 0.05310000106692314, 0.005799999926239252, -0.23499999940395355, 0.11779999732971191, -0.10899999737739563, 0.1088000014424324, -0.09910000115633011, 0.02669999934732914, -0.017100000753998756, -0.07429999858140945, 0.00570000009611249, 0.04899999871850014, 0.03229999914765358, 0.2547999918460846, 0.3249000012874603, 0.01769999973475933, 0.10620000213384628, 0.14890000224113464, -0.055399999022483826, 0.18379999697208405, 0.093299999833107, -0.04769999906420708, 0.0024999999441206455, -0.1565999984741211, -0.07720000296831131, 0.05820000171661377, -0.15000000596046448, -0.3118000030517578, 0.12479999661445618, 0.13349999487400055, -0.014800000004470348], [-0.08799999952316284, 0.32749998569488525, -0.015300000086426735, 0.02850000001490116, 0.2249000072479248, 0.056299999356269836, 0.03739999979734421, -0.044599998742341995, 0.18359999358654022, -0.2712000012397766, -0.21629999577999115, -0.19580000638961792, -0.2070000022649765, -0.003700000001117587, 0.16689999401569366, 0.17829999327659607, -0.21289999783039093, -0.008999999612569809, 0.22859999537467957, -0.155799999833107, -0.0885000005364418, -0.06340000033378601, 0.007499999832361937, 0.08429999649524689, -0.08540000021457672, -0.17829999327659607, -0.08139999955892563, -0.08990000188350677, -0.15219999849796295, 0.02539999969303608, -0.29589998722076416, -0.05770000070333481, -0.22220000624656677, -0.17970000207424164, 0.08569999784231186, 0.2207999974489212, 0.10320000350475311, 0.06840000301599503, -0.21559999883174896, -0.0071000000461936, -0.225600004196167, 0.06040000170469284, 0.12399999797344208, 0.010200000368058681, -0.006899999920278788, 0.026900000870227814, -0.16769999265670776, 0.07450000196695328, -0.020500000566244125, -0.11410000175237656, 0.14429999887943268, -0.16869999468326569, -0.21770000457763672, -0.2037000060081482, -0.009100000374019146, -0.11509999632835388, -0.13490000367164612, -0.1421000063419342, 0.019700000062584877, 0.12720000743865967, 0.08479999750852585, -0.30559998750686646], [-0.20149999856948853, 0.2854999899864197, -0.11749999970197678, -0.11169999837875366, -0.1501999944448471, -0.01549999974668026, 0.27129998803138733, 0.18359999358654022, -0.3244999945163727, 0.011300000362098217, -0.26179999113082886, -0.3151000142097473, -0.02539999969303608, 0.10360000282526016, -0.03530000150203705, 0.17880000174045563, -0.04699999839067459, -0.24889999628067017, 0.0868000015616417, -0.03539999946951866, -0.20149999856948853, -0.11079999804496765, -0.04800000041723251, -0.04560000076889992, -0.07190000265836716, 0.04089999943971634, 0.08749999850988388, -0.12430000305175781, -0.10300000011920929, 0.05730000138282776, 0.0210999995470047, 0.009800000116229057, 0.04839999973773956, 0.016499999910593033, -0.19030000269412994, -0.09719999879598618, -0.018699999898672104, -0.1006999984383583, -0.17599999904632568, -0.0722000002861023, 0.05900000035762787, 0.034699998795986176, 0.16740000247955322, -0.17419999837875366, 0.10300000011920929, -0.023399999365210533, 0.017899999395012856, 0.18960000574588776, 0.01119999960064888, 0.2345999926328659, 0.22470000386238098, -0.08749999850988388, -0.17170000076293945, -0.25060001015663147, -0.14429999887943268, 0.11990000307559967, -0.060100000351667404, -0.05380000174045563, -0.3314000070095062, 0.07609999924898148, 0.19619999825954437, -0.03009999915957451], [0.05770000070333481, -0.10859999805688858, -0.02290000021457672, 0.058800000697374344, -0.23510000109672546, -0.09229999780654907, 0.016100000590085983, 0.13120000064373016, -0.12359999865293503, -0.20409999787807465, -0.05990000069141388, 0.1624000072479248, -0.011099999770522118, 0.2964000105857849, -0.026000000536441803, 0.22450000047683716, 0.05860000103712082, 0.12729999423027039, -0.19609999656677246, -0.08150000125169754, -0.13670000433921814, -0.06800000369548798, -0.11240000277757645, -0.051899999380111694, -0.12939999997615814, -0.027400000020861626, -0.028699999675154686, 0.21580000221729279, 0.07530000060796738, 0.1088000014424324, 0.08799999952316284, -0.01810000091791153, -0.019300000742077827, -0.019200000911951065, -0.05959999933838844, 0.03310000151395798, 0.016699999570846558, 0.020600000396370888, 0.17579999566078186, 0.4108000099658966, 0.24379999935626984, 0.04479999840259552, -0.046799998730421066, -0.1282999962568283, -0.030300000682473183, 0.26179999113082886, 0.0908999964594841, 0.2621000111103058, -0.1590999960899353, -0.17730000615119934, -0.09839999675750732, -0.15489999949932098, -0.1915999948978424, -0.12380000203847885, -0.15060000121593475, 0.19930000603199005, -0.09709999710321426, -0.23489999771118164, -0.013199999928474426, 0.20309999585151672, 0.10890000313520432, -0.06939999759197235], [-0.0357000008225441, 0.11060000211000443, 0.22869999706745148, 0.056299999356269836, 0.09730000048875809, -0.02239999920129776, 0.15289999544620514, -0.06710000336170197, 0.05649999901652336, -0.11919999867677689, 0.22630000114440918, 0.13809999823570251, 0.07419999688863754, 0.1915999948978424, 0.051100000739097595, 0.031599998474121094, 0.08299999684095383, -0.00989999994635582, 0.05889999866485596, 0.10649999976158142, 0.012799999676644802, 0.10729999840259552, 0.040800001472234726, -0.2053000032901764, -0.15950000286102295, 0.037700001150369644, -0.10599999874830246, 0.23149999976158142, -0.03150000050663948, 0.010900000110268593, -0.08720000088214874, 0.12690000236034393, -0.056699998676776886, 0.02930000051856041, 0.01730000041425228, 0.03550000116229057, 0.08669999986886978, -0.03750000149011612, 0.0038999998942017555, -0.35589998960494995, 0.29919999837875366, 0.23070000112056732, 0.0706000030040741, 0.013799999840557575, 0.19329999387264252, 0.03220000118017197, 0.013799999840557575, -0.23499999940395355, 0.17800000309944153, 0.020999999716877937, 0.06499999761581421, -0.2799000144004822, 0.08089999854564667, 0.17550000548362732, -0.1379999965429306, -0.0658000037074089, 0.1362999975681305, -0.0007999999797903001, 0.22579999268054962, -0.1429000049829483, 0.14509999752044678, 0.10450000315904617], [0.0917000025510788, 0.1581999957561493, -0.08449999988079071, 0.09910000115633011, -0.01979999989271164, 0.11990000307559967, -0.011500000022351742, -0.04270000010728836, 0.10930000245571136, -0.2896000146865845, -0.3197999894618988, -0.06379999965429306, -0.11990000307559967, -0.05979999899864197, -0.2013999968767166, -0.1185000017285347, -0.21070000529289246, -0.15780000388622284, -0.2071000039577484, -0.1768999993801117, 0.07689999788999557, 0.03720000013709068, -0.005400000140070915, 0.09830000251531601, 0.09570000320672989, -0.2134000062942505, 0.21119999885559082, -0.007899999618530273, 0.16820000112056732, 0.005400000140070915, -0.13279999792575836, -0.08839999884366989, 0.02410000003874302, -0.02459999918937683, 0.05950000137090683, 0.011900000274181366, 0.04500000178813934, 0.10760000348091125, 0.11469999700784683, -0.09300000220537186, 0.24120000004768372, -0.2761000096797943, 0.16220000386238098, -0.08150000125169754, 0.093299999833107, -0.04639999940991402, 0.2757999897003174, 0.12639999389648438, 0.05920000001788139, -0.08150000125169754, 0.2563000023365021, 0.13840000331401825, -0.10339999943971634, -0.0575999990105629, -0.06599999964237213, -0.07029999792575836, 0.1599999964237213, -0.3174999952316284, -0.09239999949932098, 0.0997999981045723, 0.3504999876022339, -0.02160000056028366], [-0.010300000198185444, -0.0729999989271164, -0.07069999724626541, -0.00019999999494757503, -0.05130000039935112, -0.3580999970436096, -0.01640000008046627, 0.03240000084042549, 0.15299999713897705, 0.2143000066280365, 0.02160000056028366, 0.027899999171495438, -0.13459999859333038, -0.1500999927520752, 0.06319999694824219, -0.04610000178217888, 0.26919999718666077, -0.005400000140070915, -0.11190000176429749, -0.1460999995470047, -0.0052999998442828655, 0.025499999523162842, -0.1128000020980835, -0.19189999997615814, 0.13809999823570251, 0.14409999549388885, 0.08959999680519104, 0.14190000295639038, 0.10480000078678131, 0.24560000002384186, -0.10260000079870224, 0.1891999989748001, -0.3752000033855438, -0.057100001722574234, 0.0031999999191612005, 0.031300000846385956, 0.07590000331401825, -0.22390000522136688, -0.05990000069141388, -0.1298999935388565, 0.057999998331069946, 0.06279999762773514, -0.09120000153779984, -0.2092999964952469, -0.0340999998152256, 0.0044999998062849045, 0.06440000236034393, 0.1453000009059906, -0.009999999776482582, -0.12409999966621399, -0.02889999933540821, 0.26330000162124634, -0.013000000268220901, -0.10400000214576721, -0.03449999913573265, -0.0071000000461936, 0.11680000275373459, -0.155799999833107, 0.11209999769926071, -0.08669999986886978, -0.1768999993801117, 0.010400000028312206], [-0.10289999842643738, -0.05700000002980232, 0.1720000058412552, -0.1485999971628189, 0.15299999713897705, 0.07930000126361847, 0.27000001072883606, 0.04129999876022339, 0.044199999421834946, -0.361299991607666, 0.000699999975040555, -0.15860000252723694, -0.0754999965429306, -0.08240000158548355, -0.1289999932050705, 0.006300000008195639, -0.10199999809265137, 0.3192000091075897, 0.04569999873638153, 0.04399999976158142, 0.3319999873638153, -0.17910000681877136, 0.03060000017285347, 0.17520000040531158, 0.15880000591278076, 0.1808999925851822, -0.19470000267028809, 0.017000000923871994, -0.2280000001192093, 0.22609999775886536, 0.0940999984741211, -0.054499998688697815, -0.040699999779462814, -0.09889999777078629, 0.17730000615119934, 0.03189999982714653, -0.2434999942779541, 0.19949999451637268, 0.028300000354647636, -0.15189999341964722, 0.13130000233650208, 0.1745000034570694, 0.04780000075697899, -0.0210999995470047, -0.08169999718666077, -0.13609999418258667, -0.1889999955892563, 0.00019999999494757503, 0.3714999854564667, 0.08340000361204147, -0.15569999814033508, 0.1881999969482422, -0.08169999718666077, -0.03830000013113022, -0.0729999989271164, 0.07109999656677246, 0.10920000076293945, -0.022700000554323196, -0.016899999231100082, -0.05510000139474869, 0.023600000888109207, 0.08590000122785568], [0.011599999852478504, -0.1477999985218048, 0.10520000010728836, -0.05869999900460243, 0.11789999902248383, 0.14180000126361847, 0.07159999758005142, 0.06109999865293503, 0.09480000287294388, 0.07850000262260437, -0.11079999804496765, 0.3476000130176544, -0.24459999799728394, 0.14000000059604645, 0.065700002014637, 0.012199999764561653, -0.16030000150203705, -0.10890000313520432, 0.009100000374019146, 0.24860000610351562, -0.28220000863075256, 0.05829999968409538, -0.22660000622272491, 0.20180000364780426, 0.17829999327659607, 0.0066999997943639755, 0.14810000360012054, 0.04989999905228615, -0.11710000038146973, -0.07169999927282333, -0.14429999887943268, 0.1972000002861023, 0.02879999950528145, 0.24490000307559967, -0.02319999970495701, -0.0934000015258789, -0.1289999932050705, -0.0949999988079071, 0.0215000007301569, -0.15129999816417694, -0.0820000022649765, 0.023399999365210533, 0.11999999731779099, 0.016899999231100082, -0.03099999949336052, -0.16609999537467957, 0.05290000140666962, 0.10130000114440918, -0.2976999878883362, 0.0568000003695488, 0.07020000368356705, -0.05550000071525574, -0.12269999831914902, 0.05810000002384186, 0.046799998730421066, -0.061500001698732376, 0.07989999651908875, 0.1712999939918518, 0.011599999852478504, 0.10970000177621841, -0.163100004196167, -0.16519999504089355], [-0.13300000131130219, -0.07689999788999557, -0.23170000314712524, 0.17949999868869781, 0.15520000457763672, -0.164900004863739, 0.12240000069141388, 0.13580000400543213, 0.06629999727010727, -0.17100000381469727, 0.1606999933719635, 0.12520000338554382, -0.05689999833703041, 0.16449999809265137, -0.02710000053048134, -0.11840000003576279, 0.133200004696846, 0.11680000275373459, 0.12060000002384186, -0.04259999841451645, 0.13689999282360077, -0.009399999864399433, 0.19300000369548798, -0.06379999965429306, 0.0706000030040741, 0.2224999964237213, -0.029100000858306885, -0.04170000180602074, -0.08240000158548355, 0.29499998688697815, -0.15649999678134918, -0.24300000071525574, 0.17489999532699585, 0.10740000009536743, 0.11180000007152557, -0.19030000269412994, -0.04919999837875366, 0.15240000188350677, -0.05460000038146973, -0.12700000405311584, 0.1388999968767166, -0.23090000450611115, -0.03759999945759773, 0.020500000566244125, 0.0560000017285347, -0.16699999570846558, 0.19660000503063202, -0.005499999970197678, -0.20080000162124634, -0.009499999694526196, -0.12399999797344208, -0.12229999899864197, -0.18950000405311584, 0.4171000123023987, 0.2011999934911728, -0.22380000352859497, -0.22930000722408295, 0.02539999969303608, -0.07620000094175339, -0.17669999599456787, -0.1251000016927719, -0.0957999974489212], [-0.09260000288486481, 0.002400000113993883, -0.14100000262260437, -0.12790000438690186, -0.05420000106096268, -0.007300000172108412, -0.23160000145435333, 0.05649999901652336, 0.11959999799728394, -0.13220000267028809, 0.12189999967813492, -0.10809999704360962, -0.06629999727010727, 0.28790000081062317, 0.08489999920129776, 0.024800000712275505, 0.03020000085234642, -0.020899999886751175, -0.03700000047683716, 0.003700000001117587, -0.2281000018119812, 0.16599999368190765, -0.14110000431537628, -0.11760000139474869, -0.19550000131130219, 0.24410000443458557, 0.11270000040531158, 0.1965000033378601, 0.1964000016450882, -0.009100000374019146, 0.031099999323487282, -0.25119999051094055, 0.04470000043511391, -0.18629999458789825, -0.22779999673366547, -0.14270000159740448, -0.019999999552965164, 0.14270000159740448, -0.04899999871850014, -0.07129999995231628, -0.20679999887943268, 0.04149999842047691, -0.010499999858438969, 0.10580000281333923, -0.2222999930381775, -0.025499999523162842, 0.2004999965429306, 0.0551999993622303, 0.06549999862909317, -0.14630000293254852, 0.09989999979734421, 0.10199999809265137, 0.15029999613761902, -0.0681999996304512, -0.02669999934732914, 0.07159999758005142, 0.188400000333786, -0.12309999763965607, -0.04430000111460686, -0.006099999882280827, -0.014600000344216824, 0.02500000037252903], [-0.19339999556541443, -0.003800000064074993, 0.17249999940395355, 0.30970001220703125, -0.07769999653100967, -0.01979999989271164, -0.29319998621940613, -0.311599999666214, -0.14470000565052032, 0.013100000098347664, 0.051899999380111694, -0.022700000554323196, -0.12559999525547028, -0.058800000697374344, -0.1256999969482422, -0.0015999999595806003, 0.06849999725818634, 0.048700001090765, -0.11840000003576279, 0.1145000010728836, 0.0003000000142492354, -0.1460999995470047, 0.0803999975323677, 0.2151000052690506, -0.005100000184029341, 0.1500999927520752, -0.03319999948143959, 0.05660000070929527, 0.041099999099969864, 0.0575999990105629, -0.14949999749660492, 0.07410000264644623, -0.03880000114440918, -0.10989999771118164, 0.1988999992609024, 0.10859999805688858, -0.051899999380111694, 0.17839999496936798, 0.1875, -0.35679998993873596, -0.13519999384880066, 0.058400001376867294, 0.0003000000142492354, 0.17970000207424164, -0.15889999270439148, -0.14079999923706055, -0.07739999890327454, 0.035599999129772186, -0.08730000257492065, 0.10989999771118164, -0.13840000331401825, -0.15000000596046448, -0.0625, 0.08560000360012054, -0.27810001373291016, -0.0778999999165535, -0.23029999434947968, 0.2433999925851822, -0.16269999742507935, -0.11029999703168869, -0.10140000283718109, 0.013500000350177288], [-0.11069999635219574, 0.07900000363588333, 0.02930000051856041, -0.267300009727478, 0.00139999995008111, 0.010499999858438969, -0.23070000112056732, -0.10119999945163727, -0.18080000579357147, -0.11710000038146973, -0.05460000038146973, 0.059300001710653305, 0.10570000112056732, -0.24120000004768372, 0.1307000070810318, -0.043800000101327896, -0.13279999792575836, -0.12110000103712082, -0.11590000241994858, -0.120899997651577, -0.14110000431537628, 0.19920000433921814, 0.09589999914169312, 0.2257000058889389, -0.23360000550746918, 0.1582999974489212, 0.20720000565052032, 0.019700000062584877, -0.17339999973773956, -0.21160000562667847, -0.24709999561309814, 0.010900000110268593, 0.05420000106096268, 0.1817999929189682, -0.22529999911785126, 0.2102999985218048, -0.051899999380111694, -0.34049999713897705, -0.0868000015616417, 0.2500999867916107, 0.022099999710917473, 0.2563999891281128, 0.35010001063346863, -0.08799999952316284, -0.18150000274181366, 0.2662000060081482, -0.0003000000142492354, 0.3643999993801117, 0.05570000037550926, 0.005400000140070915, -0.05310000106692314, -0.1370999962091446, -0.04479999840259552, 0.21729999780654907, 0.017400000244379044, 0.13979999721050262, 0.10419999808073044, 0.08209999650716782, -0.11710000038146973, 0.04100000113248825, -0.06310000270605087, 0.0746999979019165], [-0.045099999755620956, -0.07190000265836716, 0.08640000224113464, 0.16120000183582306, -0.3107999861240387, -0.11479999870061874, 0.04340000078082085, 0.3531999886035919, -0.1137000024318695, -0.18889999389648438, -0.0340999998152256, -0.1388999968767166, -0.11829999834299088, -0.026000000536441803, 0.04529999941587448, -0.03590000048279762, 0.045899998396635056, -0.3003000020980835, 0.08399999886751175, -0.014800000004470348, 0.010499999858438969, 0.08489999920129776, -0.14499999582767487, 0.3057999908924103, 0.03350000083446503, 0.0714000016450882, -0.09669999778270721, 0.0754999965429306, 0.07989999651908875, 0.05730000138282776, 0.02019999921321869, 0.22789999842643738, 0.01810000091791153, 0.02710000053048134, 0.0364999994635582, 0.12729999423027</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>[0.0020323961545176683]</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>[0.2278027001416477]</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>[-0.2736686110418145]</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>[0.2907827100028541]</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>[-0.9531709526051979]</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>[0.6392331927602204]</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>[0.004079120777384815]</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>[0.22878202131722486]</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>[-0.9094384957341151]</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>[0.45284439488288336]</t>
+        </is>
+      </c>
+      <c r="O39" t="inlineStr">
+        <is>
+          <t>[0.20206734160911444]</t>
+        </is>
+      </c>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>[0.2623183216178862]</t>
+        </is>
+      </c>
+      <c r="Q39" t="inlineStr">
+        <is>
+          <t>[-0.06000641104306648]</t>
+        </is>
+      </c>
+      <c r="R39" t="inlineStr">
+        <is>
+          <t>[0.11429596402609506]</t>
+        </is>
+      </c>
+      <c r="S39" t="inlineStr">
+        <is>
+          <t>[-0.034976997214194894]</t>
+        </is>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>[0.08720751342834747]</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>[-1.29103602977967]</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>[0.2190760374367437]</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>[-0.22020773484878475]</t>
+        </is>
+      </c>
+      <c r="X39" t="inlineStr">
+        <is>
+          <t>[0.12782972316852995]</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>[-0.11462460190366675]</t>
+        </is>
+      </c>
+      <c r="Z39" t="inlineStr">
+        <is>
+          <t>[0.091726036103473]</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>[-0.8560511205213768]</t>
+        </is>
+      </c>
+      <c r="AB39" t="inlineStr">
+        <is>
+          <t>[0.17076482209663785]</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>[-0.7472161516526157]</t>
+        </is>
+      </c>
+      <c r="AD39" t="inlineStr">
+        <is>
+          <t>[0.14640967465956586]</t>
+        </is>
+      </c>
+      <c r="AE39" t="inlineStr">
+        <is>
+          <t>[-0.718463786918395]</t>
+        </is>
+      </c>
+      <c r="AF39" t="inlineStr">
+        <is>
+          <t>[0.1850408709594301]</t>
+        </is>
+      </c>
+      <c r="AG39" t="inlineStr">
+        <is>
+          <t>[-3.024784507391468]</t>
+        </is>
+      </c>
+      <c r="AH39" t="inlineStr">
+        <is>
+          <t>[0.29964503935823317]</t>
+        </is>
+      </c>
+      <c r="AI39" t="inlineStr">
+        <is>
+          <t>[-1.2604101000414087]</t>
+        </is>
+      </c>
+      <c r="AJ39" t="inlineStr">
+        <is>
+          <t>[0.18523809137808142]</t>
+        </is>
+      </c>
+      <c r="AK39" t="inlineStr">
+        <is>
+          <t>[-0.7526641814862685]</t>
+        </is>
+      </c>
+      <c r="AL39" t="inlineStr">
+        <is>
+          <t>[0.18603246172923388]</t>
+        </is>
+      </c>
+      <c r="AM39" t="inlineStr">
+        <is>
+          <t>[-2.044207697115051]</t>
+        </is>
+      </c>
+      <c r="AN39" t="inlineStr">
+        <is>
+          <t>[0.23381722043854294]</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>model_62_32_16_3</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>[62, 32, 16]</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>[[[0.025800000876188278, -0.06419999897480011, -0.005400000140070915, 0.029899999499320984, 0.02449999935925007, -0.04399999976158142, -0.07069999724626541, 0.009800000116229057, -0.008299999870359898, -0.02370000071823597, 0.05350000038743019, 0.012000000104308128, 0.05649999901652336, -0.08569999784231186, -0.01899999938905239, 0.1006999984383583, 0.043699998408555984, 0.05550000071525574, -0.012400000356137753, 0.024900000542402267, -0.02850000001490116, 0.019300000742077827, -0.030400000512599945, -0.006000000052154064, 0.017100000753998756, 0.026000000536441803, 0.024000000208616257, -0.00559999980032444, 0.03750000149011612, 0.023600000888109207, 0.04470000043511391, -0.11550000309944153, -0.05739999935030937, -0.038600001484155655, 0.09920000284910202, -0.01850000023841858, 0.06840000301599503, 0.01769999973475933, 0.0771000012755394, -9.999999747378752e-05, -0.06710000336170197, 0.0414000004529953, 0.03220000118017197, 0.006500000134110451, 9.999999747378752e-05, 0.05260000005364418, -0.08470000326633453, -0.0406000018119812, -0.024700000882148743, 0.05829999968409538, 0.020400000736117363, 0.018699999898672104, 0.021900000050663948, -0.09279999881982803, -0.046799998730421066, -0.05609999969601631, 0.025499999523162842, 0.016599999740719795, 0.04809999838471413, -0.06289999932050705, 0.06310000270605087, -0.032999999821186066], [0.0071000000461936, 0.06989999860525131, 0.03819999843835831, -0.040699999779462814, 0.04129999876022339, -0.031599998474121094, 0.039400000125169754, -0.06400000303983688, -0.03060000017285347, 0.08089999854564667, -0.13809999823570251, 0.01510000042617321, -0.051500000059604645, -0.1128000020980835, 0.018699999898672104, -0.013700000010430813, 0.04520000144839287, -0.012199999764561653, -0.02500000037252903, 0.019500000402331352, 0.045899998396635056, 0.03240000084042549, 0.011500000022351742, 0.0210999995470047, -0.015599999576807022, -0.021199999377131462, 0.041200000792741776, -0.023000000044703484, 0.0007999999797903001, -0.02669999934732914, 0.04479999840259552, -0.058400001376867294, -0.04749999940395355, 0.03579999879002571, 0.03180000185966492, 0.07940000295639038, -0.07440000027418137, -0.11640000343322754, 0.11949999630451202, 0.03220000118017197, 0.015200000256299973, 0.04619999974966049, -0.008299999870359898, -0.04989999905228615, 0.002899999963119626, 0.01940000057220459, 0.011099999770522118, 0.06419999897480011, -0.0649000033736229, -0.05299999937415123, -0.009700000286102295, -0.039400000125169754, 0.012799999676644802, 0.03830000013113022, -0.018300000578165054, -0.007300000172108412, -0.023900000378489494, -0.06970000267028809, 0.039799999445676804, 0.019999999552965164, 0.025699999183416367, 0.03280000016093254]], [[0.17739999294281006, 0.01899999938905239, 0.01640000008046627, 0.10279999673366547, -0.08789999783039093, -0.05209999904036522, -0.057100001722574234, 0.1354999989271164, -0.014499999582767487, 0.18860000371932983, 0.024299999698996544, -0.21320000290870667, 0.040699999779462814, -0.03869999945163727, 0.040800001472234726, 0.03970000147819519, 0.005499999970197678, 0.002400000113993883, 0.08299999684095383, -0.10040000081062317, 0.2955999970436096, -0.17399999499320984, 0.06780000030994415, -0.09939999878406525, -0.07540000230073929, 0.14480000734329224, 0.00839999970048666, 0.2371000051498413, -0.06469999998807907, 0.14480000734329224, -0.20160000026226044, -0.1454000025987625, -0.054999999701976776, 0.02250000089406967, 0.10279999673366547, -0.03310000151395798, 0.04039999842643738, 0.36970001459121704, -0.017000000923871994, -0.04340000078082085, -0.04610000178217888, 0.08540000021457672, -0.09969999641180038, 0.014399999752640724, 0.030400000512599945, 0.027699999511241913, -0.16410000622272491, -0.0071000000461936, -0.15320000052452087, -0.1509000062942505, -0.13050000369548798, 0.1932000070810318, 0.12549999356269836, 0.20909999310970306, -0.09019999951124191, -0.10859999805688858, -0.08560000360012054, 0.1128000020980835, -0.12610000371932983, -0.12200000137090683, 0.07649999856948853, -0.2784999907016754], [0.14820000529289246, 0.05950000137090683, -0.06040000170469284, 0.0044999998062849045, 0.11180000007152557, 0.07280000299215317, 0.04190000146627426, 0.04639999940991402, 0.09269999712705612, 0.17090000212192535, 0.17589999735355377, 0.10130000114440918, 0.11289999634027481, -0.04410000145435333, -0.06809999793767929, -0.265500009059906, -0.0015999999595806003, 0.005900000222027302, -0.010999999940395355, 0.05220000073313713, 0.014000000432133675, -0.10639999806880951, 0.0010000000474974513, 0.19200000166893005, 0.08980000019073486, -0.04520000144839287, 0.17659999430179596, -0.055799998342990875, -0.2540000081062317, 0.09489999711513519, 0.29589998722076416, -0.2662999927997589, -0.0471000000834465, -0.04430000111460686, -0.0052999998442828655, 0.011599999852478504, -0.02160000056028366, 0.05270000174641609, 0.0786999985575676, -0.2012999951839447, -0.015399999916553497, 0.14730000495910645, 0.07069999724626541, 0.0502999983727932, -0.30090001225471497, -0.008899999782443047, 0.21610000729560852, 0.07620000094175339, 0.0649000033736229, 0.005499999970197678, -0.19769999384880066, -0.055399999022483826, 0.0010999999940395355, -0.1340000033378601, -0.19850000739097595, -0.1257999986410141, -0.16979999840259552, 0.07530000060796738, 0.22859999537467957, 0.038100000470876694, -0.1177000030875206, -0.06419999897480011], [-0.07940000295639038, 0.18790000677108765, -0.15569999814033508, 0.18299999833106995, -0.3102000057697296, -0.18029999732971191, -0.028999999165534973, -0.08640000224113464, 0.013399999588727951, -0.31150001287460327, 0.1835000067949295, -0.01590000092983246, 0.055799998342990875, 0.17440000176429749, 0.05090000107884407, -0.03680000081658363, -0.05510000139474869, 0.2126999944448471, -0.06599999964237213, 0.007000000216066837, 0.09350000321865082, -0.05169999971985817, 0.0778999999165535, -0.07050000131130219, 0.2718999981880188, -0.02329999953508377, -0.024399999529123306, -0.08460000157356262, 0.12370000034570694, -0.01510000042617321, 0.03799999877810478, 0.07180000096559525, 0.1257999986410141, -0.07190000265836716, 0.23270000517368317, 0.1281999945640564, 0.03709999844431877, -0.05950000137090683, 0.01600000075995922, 0.039900001138448715, 0.16990000009536743, -0.05290000140666962, -0.016899999231100082, 0.04170000180602074, -0.24469999969005585, 0.08460000157356262, 0.07900000363588333, -0.014999999664723873, -0.15880000591278076, -0.181099995970726, 0.1298999935388565, 0.05959999933838844, -0.1776999980211258, 0.07840000092983246, -0.18060000240802765, -0.0722000002861023, -0.07259999960660934, 0.19609999656677246, -0.07660000026226044, 0.051600001752376556, -0.061500001698732376, 9.999999747378752e-05], [0.03440000116825104, 0.2190999984741211, -0.053599998354911804, 0.013399999588727951, 0.05220000073313713, 0.039799999445676804, -0.06300000101327896, 0.2371000051498413, -0.10329999774694443, -0.06809999793767929, -0.05719999969005585, 0.10239999741315842, -0.025499999523162842, -0.03700000047683716, 0.010400000028312206, -0.06019999831914902, 0.06340000033378601, -0.18170000612735748, -0.05220000073313713, -0.06970000267028809, -0.023900000378489494, 0.03610000014305115, 0.08550000190734863, -0.05510000139474869, -0.08540000021457672, -0.08370000123977661, -0.029899999499320984, 0.03020000085234642, 0.10080000013113022, -0.3059000074863434, -0.2531000077724457, -0.12919999659061432, -0.24809999763965607, -0.2606000006198883, -0.04520000144839287, 0.1339000016450882, -0.0333000011742115, 0.3100999891757965, 0.20419999957084656, 0.019500000402331352, -0.05180000141263008, -0.06459999829530716, 0.11840000003576279, -0.09780000150203705, 0.03220000118017197, -0.039900001138448715, 0.21889999508857727, 0.09510000050067902, 0.0010999999940395355, 0.003100000089034438, 0.21899999678134918, -0.012000000104308128, -0.23010000586509705, 0.03150000050663948, -0.10239999741315842, -0.2094999998807907, 0.016499999910593033, -0.07069999724626541, 0.11819999665021896, 0.07970000058412552, 0.12729999423027039, 0.11829999834299088], [0.07559999823570251, -0.17890000343322754, -0.05939999967813492, 0.04089999943971634, -0.14259999990463257, 0.19200000166893005, -0.16359999775886536, -0.17249999940395355, -0.19210000336170197, 0.08420000225305557, -0.14959999918937683, 0.030500000342726707, -0.15279999375343323, -0.03959999978542328, -0.008299999870359898, -0.04129999876022339, -0.15489999949932098, 0.1404000073671341, 0.12200000137090683, -0.05849999934434891, -0.23119999468326569, -0.16349999606609344, 0.04100000113248825, 0.1193000003695488, 9.999999747378752e-05, 0.35350000858306885, 0.009999999776482582, 0.025800000876188278, -0.06419999897480011, -0.21140000224113464, 0.257099986076355, 0.1784999966621399, -0.14790000021457672, -0.13220000267028809, 0.02329999953508377, 0.0649000033736229, -0.027899999171495438, 0.12229999899864197, 0.10809999704360962, 0.07090000063180923, -0.08429999649524689, -0.11990000307559967, -0.1324000060558319, 0.008999999612569809, -0.08460000157356262, 0.12150000035762787, -0.03869999945163727, -0.08860000222921371, 0.21130000054836273, -0.2409999966621399, 0.07989999651908875, -0.0026000000070780516, 0.02160000056028366, 0.04340000078082085, 0.12290000170469284, -0.14149999618530273, 0.07109999656677246, 0.1080000028014183, 0.05939999967813492, -0.0284000001847744, -0.05290000140666962, -0.03669999912381172], [-0.01510000042617321, -0.25189998745918274, 0.01730000041425228, -0.030799999833106995, 0.12540000677108765, 0.0010999999940395355, -0.16040000319480896, 0.03150000050663948, 0.03620000183582306, 0.20579999685287476, 0.01850000023841858, 0.20550000667572021, 0.07129999995231628, 0.09390000253915787, 0.01590000092983246, 0.04740000143647194, -0.020099999383091927, -0.05849999934434891, 0.13580000400543213, -0.014399999752640724, 0.1234000027179718, 0.17640000581741333, 0.020099999383091927, 0.051899999380111694, 0.1923000067472458, -0.30820000171661377, 0.1704999953508377, 0.020899999886751175, -0.0828000009059906, -0.15970000624656677, -0.02370000071823597, 0.15600000321865082, -0.00419999985024333, 0.15850000083446503, 0.004699999932199717, 0.1777999997138977, -0.04190000146627426, -0.04149999842047691, -0.00839999970048666, 0.05139999836683273, -0.24469999969005585, -0.21549999713897705, -0.1386999934911728, -0.17080000042915344, -0.06310000270605087, -0.03099999949336052, -0.10599999874830246, 0.11159999668598175, -0.1193000003695488, -0.1607999950647354, 0.048900000751018524, 0.020999999716877937, -0.03880000114440918, 0.1039000004529953, -0.20900000631809235, 0.1987999975681305, 0.06620000302791595, 0.19789999723434448, 0.11129999905824661, 0.13600000739097595, 0.1535000056028366, -0.12870000302791595], [0.053199999034404755, -0.029600000008940697, 0.17659999430179596, 0.03530000150203705, 0.3248000144958496, 0.012400000356137753, 0.16590000689029694, 0.004999999888241291, -0.11980000138282776, -0.10260000079870224, -0.05469999834895134, 0.05700000002980232, -0.12549999356269836, 0.07769999653100967, -0.04520000144839287, -0.019600000232458115, -0.09220000356435776, -0.13910000026226044, 0.011800000444054604, 0.004399999976158142, 0.2321999967098236, -0.043699998408555984, 0.14669999480247498, 0.043299999088048935, 0.31869998574256897, 0.21619999408721924, 0.16859999299049377, -0.012299999594688416, -0.04190000146627426, 0.08049999922513962, -9.999999747378752e-05, -0.040800001472234726, -0.01140000019222498, -0.030799999833106995, 0.12080000340938568, 0.12970000505447388, -0.08240000158548355, 0.08160000294446945, 0.05510000139474869, 0.024800000712275505, 0.040699999779462814, 0.019999999552965164, -0.2152000069618225, 0.1932000070810318, 0.043800000101327896, 0.3111000061035156, 0.028300000354647636, 0.20280000567436218, -0.15449999272823334, 0.0414000004529953, -0.06129999831318855, -0.042399998754262924, -0.17479999363422394, -0.12720000743865967, 0.17000000178813934, 0.07739999890327454, 0.18320000171661377, -0.1387999951839447, -0.15809999406337738, 0.05649999901652336, -0.011099999770522118, 0.10729999840259552], [-0.09719999879598618, 0.03750000149011612, 0.11100000143051147, 0.05400000140070915, -0.10409999638795853, -0.09350000321865082, 0.10809999704360962, -0.24809999763965607, -0.010099999606609344, -0.093299999833107, -0.04190000146627426, 0.14480000734329224, -0.12349999696016312, -0.08340000361204147, 0.22190000116825104, -0.2159000039100647, -0.07479999959468842, -0.06889999657869339, 0.005900000222027302, -0.04399999976158142, 0.05820000171661377, -0.024000000208616257, 0.05480000004172325, -0.0674000009894371, -0.07289999723434448, -0.05979999899864197, 0.020500000566244125, 0.1378999948501587, 0.11710000038146973, 0.12929999828338623, -0.09189999848604202, 0.10090000182390213, -0.030300000682473183, -0.15680000185966492, -0.28679999709129333, -0.22699999809265137, -0.15489999949932098, -0.05119999870657921, 0.08550000190734863, -0.033799998462200165, -0.10260000079870224, -0.1031000018119812, -0.016599999740719795, -0.18880000710487366, -0.040800001472234726, 0.21809999644756317, 0.03629999980330467, 0.07159999758005142, -0.053300000727176666, 0.03750000149011612, -0.21770000457763672, -0.02449999935925007, -0.07129999995231628, 0.11320000141859055, -0.21789999306201935, 0.046799998730421066, 0.20559999346733093, -0.030400000512599945, 0.16680000722408295, -0.2345999926328659, -0.24390000104904175, -0.13339999318122864], [0.04340000078082085, 0.1014999970793724, 0.05090000107884407, 0.04340000078082085, -0.11379999667406082, 0.054499998688697815, 0.0013000000035390258, -0.07819999754428864, -0.04100000113248825, 0.045099999755620956, -0.1306000053882599, 0.06849999725818634, 0.19930000603199005, -0.2451999932527542, 0.029899999499320984, -0.018699999898672104, -0.021800000220537186, -0.15240000188350677, -0.24050000309944153, -0.04349999874830246, -0.006500000134110451, -0.14560000598430634, 0.0494999997317791, -0.0, 0.15929999947547913, -0.12300000339746475, 0.02539999969303608, -0.09629999846220016, -0.0478999987244606, 0.20020000636577606, 0.043299999088048935, -0.05889999866485596, -0.2451999932527542, -0.24729999899864197, 0.19689999520778656, -0.179299995303154, 0.0820000022649765, -0.11140000075101852, -0.19259999692440033, -0.16060000658035278, 0.003100000089034438, -0.032499998807907104, -0.051899999380111694, -0.3165000081062317, -0.008899999782443047, 0.07349999994039536, -0.02199999988079071, -0.007199999876320362, 0.09910000115633011, -0.17839999496936798, 0.19099999964237213, -0.02969999983906746, -0.00279999990016222, -0.01940000057220459, 0.15600000321865082, 0.24650000035762787, -0.05909999832510948, -0.10329999774694443, -0.1145000010728836, 0.0723000019788742, 0.19200000166893005, -0.10719999670982361], [0.03229999914765358, -0.05829999968409538, -0.022299999371170998, 0.12449999898672104, 0.0333000011742115, -0.021800000220537186, -0.15219999849796295, 0.24729999899864197, 0.11420000344514847, -0.07760000228881836, -0.14069999754428864, -0.03920000046491623, 0.03689999878406525, 0.15729999542236328, 0.04600000008940697, -0.36390000581741333, -0.1454000025987625, -0.021299999207258224, -0.23579999804496765, -0.01889999955892563, 0.033799998462200165, 0.12319999933242798, -0.19910000264644623, -0.3107999861240387, -0.07850000262260437, -0.07649999856948853, 0.18539999425411224, 0.02290000021457672, -0.042899999767541885, -0.02329999953508377, 0.07349999994039536, -0.046300001442432404, 0.060600001364946365, -0.02329999953508377, -0.09539999812841415, 0.03819999843835831, -0.0820000022649765, -0.03539999946951866, -0.3330000042915344, 0.1428000032901764, 0.01889999955892563, -0.06840000301599503, -0.042399998754262924, 0.029500000178813934, -0.13040000200271606, 0.11249999701976776, -0.11330000311136246, 0.02199999988079071, 0.2167000025510788, -0.0003000000142492354, -0.030500000342726707, 0.04899999871850014, 0.05570000037550926, 0.009600000455975533, 0.11010000109672546, -0.2727000117301941, 0.1657000035047531, -0.06939999759197235, -0.09049999713897705, 0.11890000104904175, 0.012199999764561653, -0.0786999985575676], [0.21789999306201935, -0.06030000001192093, -0.07649999856948853, -0.04610000178217888, -0.0010999999940395355, 0.00930000003427267, -0.14319999516010284, -0.18610000610351562, -0.12630000710487366, -0.13449999690055847, -0.01810000091791153, 0.06870000064373016, -0.010400000028312206, -0.07410000264644623, 0.15549999475479126, 0.030400000512599945, 0.16339999437332153, 0.19609999656677246, -0.09350000321865082, 0.2809000015258789, 0.16449999809265137, -0.08129999786615372, -0.1673000007867813, -0.20890000462532043, -0.048500001430511475, 0.11330000311136246, 0.148499995470047, -0.27959999442100525, 0.09099999815225601, -0.1671999990940094, 0.01640000008046627, 0.009999999776482582, 0.022199999541044235, -0.002099999925121665, 0.06840000301599503, 0.11429999768733978, -0.02370000071823597, 0.1080000028014183, 0.18140000104904175, -0.03180000185966492, 0.07729999721050262, 0.02319999970495701, 0.09769999980926514, -0.20010000467300415, -0.005900000222027302, -0.00419999985024333, 0.032099999487400055, 0.011500000022351742, 0.028599999845027924, 0.15839999914169312, -0.3490999937057495, 0.04780000075697899, 0.12890000641345978, 0.008299999870359898, -0.03460000082850456, 0.15489999949932098, 0.06270000338554382, -0.10809999704360962, -0.01889999955892563, 0.10080000013113022, 0.25110000371932983, -0.053599998354911804], [0.032600000500679016, -0.11159999668598175, 0.11969999969005585, 0.1462000012397766, -0.18459999561309814, 0.043699998408555984, 0.009800000116229057, -0.19419999420642853, 0.06069999933242798, -0.03550000116229057, -0.029899999499320984, 0.2045000046491623, 0.0034000000450760126, 0.14659999310970306, -0.23250000178813934, 0.12639999389648438, 0.025499999523162842, -0.1039000004529953, -0.04780000075697899, 0.09600000083446503, 0.03530000150203705, -0.13349999487400055, -0.18780000507831573, 0.05900000035762787, -0.19169999659061432, -0.06859999895095825, -0.06520000100135803, -0.07840000092983246, 0.07819999754428864, -0.1396999955177307, -0.05920000001788139, -0.065700002014637, -0.06549999862909317, -0.2937000095844269, -0.08190000057220459, 0.0284000001847744, -0.1316000074148178, -0.04969999939203262, -0.22499999403953552, -0.01269999984651804, -0.07329999655485153, 0.0494999997317791, -0.3116999864578247, 0.15649999678134918, 0.06419999897480011, -0.13809999823570251, 0.09759999811649323, 0.313400000333786, -0.16859999299049377, -0.014299999922513962, -0.12720000743865967, -0.025200000032782555, 0.13369999825954437, 0.028699999675154686, 0.013899999670684338, -0.07519999891519547, -0.21559999883174896, 0.09380000084638596, -0.09239999949932098, 0.04879999905824661, -0.04410000145435333, 0.06719999760389328], [-0.029999999329447746, -0.09099999815225601, -0.13120000064373016, 0.22630000114440918, 0.1371999979019165, -0.09279999881982803, 0.03620000183582306, -0.007300000172108412, 0.2639999985694885, 0.025100000202655792, 0.14090000092983246, 0.04309999942779541, 0.12370000034570694, -0.23510000109672546, -0.013899999670684338, 0.15600000321865082, 0.08240000158548355, 0.0917000025510788, -0.05000000074505806, -0.034699998795986176, -0.2222999930381775, 0.0786999985575676, -0.09260000288486481, -0.21320000290870667, -0.10050000250339508, 0.2134999930858612, -0.06239999830722809, -0.06449999660253525, -0.054999999701976776, 0.025699999183416367, -0.010700000450015068, -0.22050000727176666, 0.13420000672340393, 0.10920000076293945, -0.010599999688565731, -0.16269999742507935, -0.22360000014305115, 0.02449999935925007, 0.17180000245571136, 0.13279999792575836, -0.011500000022351742, -0.06970000267028809, -0.2574999928474426, -0.1662999987602234, 0.10450000315904617, 0.26989999413490295, -0.042899999767541885, 0.04089999943971634, -0.08529999852180481, -0.11029999703168869, 0.08100000023841858, -0.14959999918937683, -0.12780000269412994, -0.08020000159740448, -0.029899999499320984, -0.06040000170469284, -0.13609999418258667, 0.012799999676644802, 0.09099999815225601, 0.12600000202655792, 0.051600001752376556, 0.00430000014603138], [-0.04340000078082085, -0.11330000311136246, 0.10480000078678131, 0.1444000005722046, 0.31839999556541443, 0.03350000083446503, 0.13750000298023224, -0.15119999647140503, -0.04470000043511391, 0.21660000085830688, -0.03620000183582306, -0.0020000000949949026, 0.17489999532699585, -0.0333000011742115, 0.0502999983727932, 0.12630000710487366, -0.0746999979019165, 0.0940999984741211, 0.010200000368058681, 0.04659999907016754, 0.11969999969005585, 0.13680000603199005, 0.13539999723434448, -0.018200000748038292, 0.12620000541210175, 0.025499999523162842, -0.16300000250339508, -0.11599999666213989, 0.07970000058412552, 0.036400001496076584, 0.05829999968409538, 0.02669999934732914, 0.03449999913573265, -0.2574999928474426, 0.10949999839067459, -0.052400000393390656, -0.05339999869465828, -0.029500000178813934, -0.09229999780654907, 0.210099995136261, -0.007199999876320362, -0.28940001130104065, 0.26100000739097595, 0.06729999929666519, 0.021800000220537186, -0.07460000365972519, 0.10909999907016754, -0.1168999969959259, 0.07429999858140945, -0.024700000882148743, -0.09239999949932098, 0.020099999383091927, 0.09529999643564224, 0.19189999997615814, -0.1899999976158142, -0.26989999413490295, -0.14720000326633453, -0.2004999965429306, -0.1111999973654747, 0.013700000010430813, -0.02800000086426735, -0.009700000286102295], [0.016599999740719795, 0.03229999914765358, 0.20759999752044678, -0.01810000091791153, -0.12729999423027039, 0.04800000041723251, -0.07909999787807465, -0.06949999928474426, -0.00800000037997961, -0.05590000003576279, -0.04129999876022339, 0.09669999778270721, -0.1535000056028366, -0.08709999918937683, 0.03310000151395798, 0.07320000231266022, -0.035999998450279236, -0.07580000162124634, -0.0877000018954277, 0.027699999511241913, -0.07649999856948853, 0.04010000079870224, -0.02850000001490116, 0.08659999817609787, 0.18709999322891235, -0.06849999725818634, 0.1598999947309494, 0.10080000013113022, -0.38029998540878296, 0.037300001829862595, -0.2705000042915344, 0.10840000212192535, 0.03009999915957451, -0.02319999970495701, -0.041600000113248825, -0.10199999809265137, -0.14419999718666077, -0.007300000172108412, 0.17919999361038208, 0.14350000023841858, 0.22220000624656677, 0.013100000098347664, -0.18219999969005585, 0.020899999886751175, -0.120899997651577, -0.08810000121593475, -0.010900000110268593, -0.31709998846054077, 0.010400000028312206, 0.30320000648498535, 0.015699999406933784, 0.04969999939203262, 0.018300000578165054, 0.12250000238418579, -0.0032999999821186066, -0.1388999968767166, -0.21220000088214874, -0.027899999171495438, -0.03849999979138374, 0.24449999630451202, 0.0026000000070780516, -0.07980000227689743], [0.05909999832510948, -0.14550000429153442, 0.040300000458955765, -0.0949999988079071, -0.004000000189989805, -0.06279999762773514, -0.07989999651908875, -0.15880000591278076, 0.04399999976158142, 0.012799999676644802, -0.03739999979734421, -0.09880000352859497, 0.06289999932050705, 0.11949999630451202, 0.2468000054359436, 0.06560000032186508, -0.2151000052690506, -0.06239999830722809, 0.2644999921321869, 0.23389999568462372, 0.10180000215768814, -0.1956000030040741, 0.07540000230073929, -0.22280000150203705, -0.19779999554157257, -0.15569999814033508, -0.12229999899864197, -0.08179999887943268, -0.032600000500679016, 0.05460000038146973, 0.04349999874830246, -0.03889999911189079, -0.12600000202655792, 0.07639999687671661, 0.10689999908208847, 0.017100000753998756, 0.08250000327825546, 0.05429999902844429, -0.12870000302791595, 0.02290000021457672, -0.12210000306367874, 0.19059999287128448, -0.12470000237226486, 0.034299999475479126, -0.012000000104308128, 0.008999999612569809, 0.05730000138282776, -0.16750000417232513, 0.014299999922513962, 0.06390000134706497, 0.10220000147819519, -0.03970000147819519, -0.36559998989105225, -0.003100000089034438, 0.02800000086426735, -0.028300000354647636, -0.07519999891519547, -0.18790000677108765, 0.17649999260902405, 0.22010000050067902, -0.17110000550746918, -0.0015999999595806003], [0.05730000138282776, 0.027400000020861626, -0.1054999977350235, -0.029500000178813934, -0.10999999940395355, -0.218299999833107, 0.11969999969005585, 0.0949999988079071, 0.15700000524520874, -0.0044999998062849045, -0.18780000507831573, -0.07970000058412552, 0.00839999970048666, -0.1412999927997589, -0.04769999906420708, -0.1282999962568283, -0.0357000008225441, 0.10670000314712524, -0.10209999978542328, -0.05480000004172325, 0.1753000020980835, 0.1662999987602234, 0.23549999296665192, 0.14970000088214874, -0.0364999994635582, 0.23409999907016754, -0.17630000412464142, 0.05460000038146973, 0.04450000077486038, -0.16680000722408295, -0.10570000112056732, 0.08659999817609787, 0.04230000078678131, 0.08950000256299973, 0.11810000240802765, -0.09610000252723694, 0.1120000034570694, -0.031599998474121094, -0.02930000051856041, -0.11270000040531158, -0.17419999837875366, -0.179299995303154, -0.17219999432563782, 0.0008999999845400453, -0.07429999858140945, -0.11010000109672546, 0.18170000612735748, 0.1436000019311905, 0.15060000121593475, 0.15109999477863312, -0.1437000036239624, 0.028200000524520874, 0.03880000114440918, 0.06030000001192093, 0.11720000207424164, 0.12129999697208405, -0.037300001829862595, -0.01510000042617321, 0.11289999634027481, 0.3659999966621399, -0.13650000095367432, -0.06069999933242798], [-0.011099999770522118, -0.10779999941587448, -0.006800000090152025, 0.17069999873638153, 0.262800008058548, 0.04320000112056732, 0.05530000105500221, 0.03229999914765358, -0.11569999903440475, -0.21199999749660492, 0.03669999912381172, 0.0917000025510788, 0.19619999825954437, -0.019099999219179153, 0.03020000085234642, -0.00930000003427267, 0.15600000321865082, 0.147599995136261, -0.08320000022649765, 0.09059999883174896, 0.07680000364780426, -0.18979999423027039, 0.09740000218153, -0.0027000000700354576, -0.02199999988079071, -0.10199999809265137, 0.19589999318122864, 0.3102000057697296, 0.21490000188350677, -0.07890000194311142, -0.20520000159740448, 0.044599998742341995, -0.01679999940097332, -0.006599999964237213, -0.05950000137090683, 0.019200000911951065, -0.029500000178813934, 0.07769999653100967, -0.0340999998152256, -0.021700000390410423, -0.021199999377131462, 0.05040000006556511, -0.020899999886751175, 0.08760000020265579, 0.009200000204145908, 0.008799999952316284, -0.0738999992609024, -0.2273000031709671, 0.3203999996185303, -0.11299999803304672, 0.01209999993443489, -0.1818999946117401, 0.08070000261068344, -0.08869999647140503, 0.03739999979734421, 0.19200000166893005, -0.2134000062942505, 0.18060000240802765, 0.004600000102072954, 0.04800000041723251, -0.23019999265670776, 0.07349999994039536], [-0.0006000000284984708, 0.09189999848604202, 0.04430000111460686, 0.14710000157356262, 0.08799999952316284, 0.023800000548362732, 0.019899999722838402, 0.06499999761581421, -0.18000000715255737, 0.0210999995470047, 0.06880000233650208, 0.0544000007212162, 0.06360000371932983, -0.2078000009059906, -0.13359999656677246, -0.019200000911951065, -0.04089999943971634, 0.062199998646974564, 0.3019999861717224, -0.05900000035762787, 0.0632999986410141, -0.1527000069618225, 0.0272000003606081, -0.049800001084804535, -0.05660000070929527, -0.020600000396370888, -0.21289999783039093, -0.04989999905228615, -0.2295999974012375, -0.24779999256134033, -0.2295999974012375, -0.05640000104904175, -0.015599999576807022, 0.13689999282360077, -0.11299999803304672, 0.0658000037074089, 0.11789999902248383, -0.3127000033855438, -0.07039999961853027, 0.04529999941587448, 0.22499999403953552, 0.1257999986410141, -0.02280000038444996, -0.19599999487400055, -0.26910001039505005, 0.0066999997943639755, -0.0778999999165535, 0.13030000030994415, 0.08919999748468399, -0.1274999976158142, -0.14569999277591705, -0.09300000220537186, -0.02879999950528145, 0.12919999659061432, -0.0024999999441206455, -0.03779999911785126, 0.13459999859333038, -0.10209999978542328, -0.15440000593662262, -0.0038999998942017555, -0.06469999998807907, 0.10760000348091125], [-0.18230000138282776, 0.18979999423027039, -0.0868000015616417, 0.04170000180602074, -0.09369999915361404, 0.05310000106692314, -0.049400001764297485, -0.022099999710917473, -0.007799999788403511, -0.03869999945163727, -0.15520000457763672, 0.014600000344216824, 0.13459999859333038, 0.023000000044703484, -0.23149999976158142, 0.09260000288486481, 0.1525000035762787, -0.05700000002980232, 0.24040000140666962, 0.27070000767707825, 0.023399999365210533, 0.21199999749660492, 0.13570000231266022, -0.1088000014424324, 0.02239999920129776, -0.02759999968111515, 0.15000000596046448, -0.06859999895095825, -0.08139999955892563, 0.05480000004172325, 0.08749999850988388, 0.016200000420212746, -0.010700000450015068, 0.03849999979138374, -0.29120001196861267, -0.17589999735355377, 0.019700000062584877, 0.2515000104904175, -0.03229999914765358, 0.11890000104904175, -0.08730000257492065, -0.023000000044703484, 0.15119999647140503, 0.0013000000035390258, -0.19210000336170197, 0.13950000703334808, 0.15360000729560852, -0.05299999937415123, -0.14579999446868896, -0.15649999678134918, -0.0803999975323677, 0.0868000015616417, 0.04149999842047691, 0.09570000320672989, 0.33739998936653137, 0.09860000014305115, -0.06710000336170197, 0.01489999983459711, -0.04919999837875366, 0.06549999862909317, -0.07150000333786011, 0.015699999406933784], [0.056699998676776886, 0.018200000748038292, -0.20829999446868896, -0.01769999973475933, 0.11299999803304672, 0.13220000267028809, -0.12399999797344208, 0.14659999310970306, -0.18619999289512634, -0.11100000143051147, -0.16279999911785126, -0.006899999920278788, -0.05640000104904175, 0.019099999219179153, 0.026599999517202377, -0.0989999994635582, 0.09870000183582306, 0.09880000352859497, 0.021800000220537186, -0.12160000205039978, 0.22339999675750732, 0.12960000336170197, -0.30469998717308044, 0.03240000084042549, -0.07069999724626541, 0.017100000753998756, -0.17339999973773956, 0.04839999973773956, -0.20489999651908875, 0.08020000159740448, 0.15649999678134918, 0.031300000846385956, 0.02070000022649765, -0.040300000458955765, -0.12269999831914902, 0.05079999938607216, -0.09160000085830688, -0.11479999870061874, -0.00039999998989515007, -0.22349999845027924, 0.027300000190734863, -0.08349999785423279, -0.14730000495910645, 0.002099999925121665, 0.22930000722408295, 0.04010000079870224, 0.2615000009536743, -0.24210000038146973, -0.1412000060081482, -0.13840000331401825, 0.031599998474121094, 0.021700000390410423, -0.1143999993801117, 0.1388999968767166, -0.13050000369548798, 0.16140000522136688, -0.14380000531673431, -0.09880000352859497, -0.14740000665187836, 0.010200000368058681, -0.14069999754428864, 0.033799998462200165], [0.1266999989748001, 0.11069999635219574, 0.0771000012755394, 0.0066999997943639755, 0.15240000188350677, -0.10890000313520432, -0.2433999925851822, -0.04740000143647194, 0.03689999878406525, -0.04729999974370003, -0.17870000004768372, 0.009600000455975533, -0.007000000216066837, 0.18140000104904175, -0.31949999928474426, 0.22550000250339508, 0.01850000023841858, -0.08020000159740448, -0.0917000025510788, -0.17949999868869781, 0.09080000221729279, -0.031599998474121094, 0.08139999955892563, -0.01720000058412552, 0.014000000432133675, -0.032999999821186066, -0.056299999356269836, 0.05770000070333481, 0.10930000245571136, -0.03400000184774399, 0.1860000044107437, 0.03660000115633011, 0.2143000066280365, -0.17949999868869781, -0.020400000736117363, -0.11760000139474869, 0.03020000085234642, -0.01860000006854534, 0.17679999768733978, -0.09730000048875809, 0.0794999971985817, 0.21140000224113464, 0.05999999865889549, -0.17640000581741333, 0.02019999921321869, -0.08959999680519104, -0.23119999468326569, -0.09799999743700027, -0.08060000091791153, -0.13510000705718994, -0.04650000110268593, -0.08299999684095383, 0.043299999088048935, -0.07460000365972519, -0.0608999989926815, -0.0957999974489212, 0.18469999730587006, -0.0949999988079071, 0.14399999380111694, 0.251800000667572, -0.19370000064373016, -0.12950000166893005], [0.07530000060796738, 0.010999999940395355, 0.03790000081062317, 0.10199999809265137, -0.01889999955892563, -0.22089999914169312, -0.19760000705718994, -0.1005999967455864, -0.09929999709129333, 0.15600000321865082, 0.06920000165700912, -0.1404999941587448, 0.002099999925121665, -0.05719999969005585, -0.05990000069141388, -0.13300000131130219, -0.1331000030040741, 0.05779999867081642, -0.025100000202655792, 0.052799999713897705, -0.188400000333786, -0.02280000038444996, -0.17000000178813934, 0.21780000627040863, 0.18719999492168427, -0.24169999361038208, -0.08309999853372574, -0.086300000548</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>[[[0.04639999940991402, -0.0851999968290329, -0.052400000393390656, -0.004100000020116568, 0.006399999838322401, -0.05550000071525574, -0.14390000700950623, 0.013100000098347664, 0.019899999722838402, -0.09549999982118607, 0.08529999852180481, -0.10029999911785126, 0.1062999963760376, -0.043299999088048935, -0.09740000218153, 0.15530000627040863, 0.010599999688565731, 0.13369999825954437, -0.023600000888109207, 0.019200000911951065, -0.12219999730587006, -0.002400000113993883, -0.000699999975040555, 0.05640000104904175, -0.016499999910593033, 0.08820000290870667, -0.021700000390410423, -0.039500001817941666, 0.1143999993801117, 0.09749999642372131, 0.015200000256299973, -0.08579999953508377, -0.08079999685287476, -0.07999999821186066, 0.10830000042915344, -0.03139999881386757, 0.16140000522136688, 0.09560000151395798, 0.07100000232458115, -0.025200000032782555, -0.08789999783039093, 0.062300000339746475, 0.0877000018954277, 0.06520000100135803, 0.06340000033378601, 0.07649999856948853, -0.09749999642372131, -0.05609999969601631, -0.014499999582767487, 0.09009999781847, 0.049400001764297485, 0.09570000320672989, 0.052299998700618744, -0.16740000247955322, -0.03830000013113022, -0.06199999898672104, 0.03480000048875809, 0.06689999997615814, 0.01269999984651804, -0.1242000013589859, 0.026499999687075615, -0.11190000176429749], [-0.003000000026077032, 0.11890000104904175, 0.05649999901652336, 0.061000000685453415, 0.08959999680519104, 0.09839999675750732, 0.07419999688863754, -0.24310000240802765, -0.04500000178813934, 0.0723000019788742, -0.133200004696846, 0.17389999330043793, -0.1096000000834465, -0.03400000184774399, 0.07100000232458115, -0.027400000020861626, 0.09809999912977219, -0.040300000458955765, -0.06289999932050705, 0.02969999983906746, 0.0868000015616417, 0.032499998807907104, -0.05660000070929527, -0.03620000183582306, 0.02590000070631504, -0.07440000027418137, 0.009399999864399433, -0.006800000090152025, -0.0071000000461936, -0.016499999910593033, 0.07259999960660934, -0.06239999830722809, 0.0038999998942017555, 0.09300000220537186, 0.016200000420212746, 0.07649999856948853, -0.10670000314712524, -0.15080000460147858, 0.10130000114440918, 0.07360000163316727, 0.057999998331069946, -0.019099999219179153, 0.014299999922513962, -0.06080000102519989, 0.0019000000320374966, 0.008799999952316284, 0.10029999911785126, 0.08649999648332596, -0.09030000120401382, -0.09929999709129333, -0.09279999881982803, -0.004800000227987766, -0.04500000178813934, 0.06369999796152115, -0.04479999840259552, 0.028200000524520874, -0.05530000105500221, -0.12960000336170197, 0.006200000178068876, 0.08389999717473984, 0.11110000312328339, 0.045099999755620956]], [[0.12349999696016312, 0.026200000196695328, 0.0203000009059906, 0.10000000149011612, -0.07109999656677246, 0.003599999938160181, -0.018699999898672104, 0.1931000053882599, 0.021400000900030136, 0.18400000035762787, 0.04690000042319298, -0.17339999973773956, 0.037700001150369644, 0.04360000044107437, 0.03539999946951866, 0.047200001776218414, -0.05860000103712082, 0.01360000018030405, 0.1339000016450882, -0.11550000309944153, 0.266400009393692, -0.16990000009536743, 0.07479999959468842, -0.08320000022649765, -0.056699998676776886, 0.18230000138282776, 0.024900000542402267, 0.2282000035047531, -0.03680000081658363, 0.1080000028014183, -0.19509999454021454, -0.10010000318288803, 0.02800000086426735, -0.02969999983906746, 0.05829999968409538, -0.0697999969124794, 0.06469999998807907, 0.3707999885082245, -0.04259999841451645, -0.007199999876320362, -0.0640999972820282, -0.01979999989271164, -0.15539999306201935, 0.05260000005364418, 0.009999999776482582, 0.006000000052154064, -0.1679999977350235, -0.06599999964237213, -0.1152999997138977, -0.1599999964237213, -0.16210000216960907, 0.23389999568462372, 0.16619999706745148, 0.22220000624656677, -0.011900000274181366, -0.041200000792741776, -0.07429999858140945, 0.10989999771118164, -0.1467999964952469, -0.12939999997615814, 0.061400000005960464, -0.29429998993873596], [0.12269999831914902, 0.16009999811649323, 0.03220000118017197, 0.052799999713897705, 0.21709999442100525, 0.0035000001080334187, 0.11879999935626984, 0.05119999870657921, 0.006300000008195639, 0.19990000128746033, 0.10480000078678131, 0.03150000050663948, 0.015200000256299973, -0.07850000262260437, -0.051500000059604645, -0.2930000126361847, 0.041200000792741776, -0.04659999907016754, 0.02329999953508377, 0.15139999985694885, 0.11389999836683273, -0.039900001138448715, -0.027499999850988388, 0.18889999389648438, 0.13729999959468842, -0.020500000566244125, 0.2624000012874603, 0.006599999964237213, -0.3334999978542328, 0.0608999989926815, 0.3781999945640564, -0.3393000066280365, -0.021800000220537186, -0.10490000247955322, 0.08749999850988388, 0.09120000153779984, -0.11060000211000443, -0.0551999993622303, 0.1696999967098236, -0.2554999887943268, -0.08030000329017639, 0.11420000344514847, -0.020099999383091927, 0.011099999770522118, -0.3806999921798706, -0.018200000748038292, 0.2467000037431717, 0.11400000005960464, 0.0006000000284984708, -0.08399999886751175, -0.25619998574256897, 0.04650000110268593, -0.06279999762773514, -0.08259999752044678, -0.23909999430179596, -0.1453000009059906, -0.2549999952316284, 0.033399999141693115, 0.33239999413490295, 0.14880000054836273, -0.02969999983906746, -0.022700000554323196], [-0.09040000289678574, 0.28850001096725464, -0.06759999692440033, 0.1981000006198883, -0.19380000233650208, -0.23999999463558197, 0.043299999088048935, -0.12240000069141388, -0.07159999758005142, -0.3084999918937683, 0.10450000315904617, -0.06350000202655792, -0.030899999663233757, 0.20679999887943268, 0.03579999879002571, -0.02370000071823597, -0.027400000020861626, 0.1754000037908554, -0.05270000174641609, -0.0020000000949949026, 0.17329999804496765, 0.013000000268220901, 0.10729999840259552, -0.10639999806880951, 0.3125999867916107, 0.03269999846816063, 0.05829999968409538, -0.04560000076889992, 0.05649999901652336, -0.04820000007748604, 0.11710000038146973, -0.006500000134110451, 0.1340000033378601, -0.11249999701976776, 0.3190000057220459, 0.20520000159740448, -0.003599999938160181, -0.1670999974012375, 0.11860000342130661, -0.027300000190734863, 0.09769999980926514, -0.020800000056624413, -0.0868000015616417, 0.0005000000237487257, -0.3222000002861023, 0.14010000228881836, 0.09910000115633011, 0.027000000700354576, -0.21619999408721924, -0.2700999975204468, 0.18930000066757202, 0.18719999492168427, -0.2402999997138977, 0.0763000026345253, -0.20430000126361847, -0.07460000365972519, -0.16619999706745148, 0.18569999933242798, 0.04259999841451645, 0.15119999647140503, -0.042500000447034836, 0.027799999341368675], [0.07880000025033951, 0.18029999732971191, -0.0868000015616417, -0.0024999999441206455, -0.0674000009894371, -0.008999999612569809, -0.12780000269412994, 0.35899999737739563, -0.10949999839067459, -0.06970000267028809, -0.07530000060796738, 0.042399998754262924, 0.0674000009894371, 0.01850000023841858, -0.00279999990016222, -0.07999999821186066, 0.06379999965429306, -0.18129999935626984, 0.012500000186264515, -0.12460000067949295, -0.09269999712705612, -0.002099999925121665, 0.07370000332593918, -0.06419999897480011, -0.23180000483989716, -0.07180000096559525, -0.07010000199079514, 0.07360000163316727, 0.03660000115633011, -0.32280001044273376, -0.2808000147342682, 0.04769999906420708, -0.21119999885559082, -0.30630001425743103, -0.11959999799728394, 0.1014999970793724, 0.03909999877214432, 0.4065000116825104, 0.17710000276565552, -0.08129999786615372, -0.07249999791383743, -0.11029999703168869, 0.09520000219345093, -0.08269999921321869, 0.0729999989271164, -0.14350000023841858, 0.20960000157356262, 0.12269999831914902, -0.011300000362098217, 0.07410000264644623, 0.2370000034570694, -0.10320000350475311, -0.24459999799728394, 0.0031999999191612005, -0.13289999961853027, -0.1720999926328659, 0.0786999985575676, 0.004999999888241291, 0.01810000091791153, -0.01269999984651804, 0.11289999634027481, 0.08810000121593475], [0.007699999958276749, -0.1589999943971634, -0.040699999779462814, 0.00839999970048666, -0.10199999809265137, 0.17810000479221344, -0.16609999537467957, -0.12049999833106995, -0.20669999718666077, 0.1143999993801117, -0.1680999994277954, 0.006399999838322401, -0.1565999984741211, 0.04899999871850014, -0.029500000178813934, -0.0551999993622303, -0.12710000574588776, 0.1396999955177307, 0.17329999804496765, -0.12020000070333481, -0.21899999678134918, -0.20909999310970306, 0.07569999992847443, 0.053199999034404755, -0.04100000113248825, 0.3725999891757965, -0.003000000026077032, 0.07890000194311142, -0.10599999874830246, -0.2328999936580658, 0.2784999907016754, 0.2029000073671341, -0.025800000876188278, -0.15870000422000885, -0.03550000116229057, 0.09520000219345093, -0.003800000064074993, 0.17190000414848328, 0.12060000002384186, -0.018799999728798866, -0.08349999785423279, -0.3043000102043152, -0.13030000030994415, 0.05820000171661377, -0.04809999838471413, 0.021700000390410423, 0.0215000007301569, -0.10540000349283218, 0.17090000212192535, -0.22759999334812164, 0.02979999966919422, 0.02449999935925007, 0.011599999852478504, 0.06239999830722809, 0.10350000113248825, -0.08529999852180481, 0.04619999974966049, 0.15410000085830688, 0.05559999868273735, 0.007499999832361937, 0.025200000032782555, -0.05950000137090683], [0.06610000133514404, -0.2768999934196472, 0.008200000040233135, -0.039500001817941666, 0.07919999957084656, -0.05689999833703041, -0.18799999356269836, 0.08869999647140503, 0.040699999779462814, 0.22179999947547913, 0.016699999570846558, 0.17319999635219574, 0.08579999953508377, -0.02979999966919422, -0.032999999821186066, 0.0625, 0.033799998462200165, -0.058400001376867294, 0.1454000025987625, 0.12250000238418579, 0.1348000019788742, 0.1655000001192093, -0.06109999865293503, 0.1518000066280365, 0.15629999339580536, -0.295199990272522, 0.1543000042438507, 0.05820000171661377, -0.11339999735355377, -0.1656000018119812, -0.023099999874830246, 0.12409999966621399, -0.03799999877810478, 0.13729999959468842, 0.04430000111460686, 0.20190000534057617, -0.06270000338554382, -0.03530000150203705, -0.01850000023841858, 0.1388999968767166, -0.27079999446868896, -0.22390000522136688, -0.12950000166893005, -0.15770000219345093, -0.031099999323487282, -0.09870000183582306, -0.09640000015497208, 0.13519999384880066, -0.17350000143051147, -0.13420000672340393, -0.07240000367164612, -0.10849999636411667, -0.04780000075697899, 0.07859999686479568, -0.2768000066280365, 0.11429999768733978, 0.09269999712705612, 0.1858000010251999, 0.1404000073671341, 0.12120000272989273, 0.24199999868869781, -0.10830000042915344], [0.09759999811649323, 0.06480000168085098, 0.2671999931335449, 0.19460000097751617, 0.4115000069141388, -0.09080000221729279, 0.2273000031709671, 0.04390000179409981, -0.20309999585151672, -0.0697999969124794, -0.125, -0.024399999529123306, -0.25459998846054077, -0.08049999922513962, 0.018300000578165054, -0.04830000177025795, 0.047600001096725464, -0.21080000698566437, 0.027899999171495438, 0.13189999759197235, 0.362199991941452, 0.02669999934732914, 0.042500000447034836, 0.0957999974489212, 0.36649999022483826, 0.23399999737739563, 0.20749999582767487, 0.08659999817609787, -0.1467999964952469, 0.026499999687075615, 0.07609999924898148, -0.13109999895095825, -0.10170000046491623, -0.0949999988079071, 0.23810000717639923, 0.20000000298023224, -0.21119999885559082, -0.05130000039935112, 0.12639999389648438, 0.10830000042915344, -0.03480000048875809, 0.08919999748468399, -0.2702000141143799, 0.14300000667572021, 0.0071000000461936, 0.32260000705718994, 0.11270000040531158, 0.2720000147819519, -0.2531999945640564, -0.031199999153614044, -0.18140000104904175, -0.053199999034404755, -0.26980000734329224, -0.0723000019788742, 0.041099999099969864, -0.001500000013038516, 0.13269999623298645, -0.21979999542236328, -0.07129999995231628, 0.17710000276565552, 0.11580000072717667, 0.22509999573230743], [0.015799999237060547, 0.027899999171495438, 0.08969999849796295, 0.08330000191926956, -0.17110000550746918, -0.10610000044107437, 0.08560000360012054, -0.3411000072956085, -0.01720000058412552, -0.16750000417232513, -0.01269999984651804, 0.10530000180006027, -0.09399999678134918, -0.12219999730587006, 0.21719999611377716, -0.21529999375343323, -0.09049999713897705, -0.05700000002980232, -0.05649999901652336, -0.07259999960660934, 0.04410000145435333, 0.020400000736117363, 0.1265999972820282, -0.1281999945640564, -0.015200000256299973, -0.08060000091791153, 0.04520000144839287, 0.04179999977350235, 0.15299999713897705, 0.22769999504089355, -0.13459999859333038, 0.13289999961853027, -0.1378999948501587, -0.1265999972820282, -0.22599999606609344, -0.2648000121116638, -0.17000000178813934, -0.10849999636411667, 0.0940999984741211, -0.15960000455379486, -0.09049999713897705, 0.18799999356269836, 0.03310000151395798, -0.2685999870300293, -0.09860000014305115, 0.40389999747276306, -0.06440000236034393, 0.15639999508857727, 0.024900000542402267, 0.03400000184774399, -0.010400000028312206, 0.046300001442432404, -0.10480000078678131, 0.04859999939799309, -0.2240000069141388, -0.027699999511241913, 0.23389999568462372, -0.020999999716877937, 0.14229999482631683, -0.31520000100135803, -0.41519999504089355, -0.10989999771118164], [0.0746999979019165, 0.03370000049471855, 0.00019999999494757503, 0.041200000792741776, -0.19629999995231628, 0.09229999780654907, -0.03440000116825104, -0.07150000333786011, 0.009800000116229057, 0.057999998331069946, -0.06279999762773514, 0.09589999914169312, 0.24150000512599945, -0.3068999946117401, 0.04820000007748604, -0.02239999920129776, -0.023600000888109207, -0.148499995470047, -0.2565000057220459, -0.002300000051036477, -0.04569999873638153, -0.1762000024318695, 0.0210999995470047, 0.04910000041127205, 0.16449999809265137, -0.1704999953508377, -0.023000000044703484, -0.11959999799728394, 0.019099999219179153, 0.219200000166893, -0.014800000004470348, -0.040699999779462814, -0.2872999906539917, -0.2102999985218048, 0.1695999950170517, -0.225600004196167, 0.08070000261068344, -0.08349999785423279, -0.2587999999523163, -0.012400000356137753, 0.044599998742341995, 0.020099999383091927, -0.022600000724196434, -0.3093999922275543, 0.03880000114440918, 0.05429999902844429, -0.04610000178217888, -0.017999999225139618, 0.12970000505447388, -0.13189999759197235, 0.13510000705718994, -0.14830000698566437, 0.0340999998152256, -0.01360000018030405, 0.14970000088214874, 0.2134000062942505, -0.006500000134110451, -0.1264999955892563, -0.15489999949932098, 0.01730000041425228, 0.19670000672340393, -0.10610000044107437], [0.08330000191926956, 0.0786999985575676, 0.1111999973654747, 0.2590000033378601, 0.15199999511241913, -0.14399999380111694, -0.10209999978542328, 0.3528999984264374, -0.019300000742077827, -0.016100000590085983, -0.289900004863739, -0.13699999451637268, -0.10409999638795853, -0.02410000003874302, -0.006000000052154064, -0.2678999900817871, -0.0013000000035390258, -0.03970000147819519, -0.12770000100135803, 0.12870000302791595, 0.17669999599456787, 0.20329999923706055, -0.27129998803138733, -0.19769999384880066, -0.08829999715089798, -0.027799999341368675, 0.2720000147819519, 0.16220000386238098, -0.1712999939918518, -0.0892999991774559, 0.2184000015258789, -0.16419999301433563, -0.04259999841451645, -0.1362999975681305, 0.023499999195337296, 0.1615000069141388, -0.16689999401569366, -0.09969999641180038, -0.18389999866485596, 0.3377000093460083, -0.13349999487400055, -0.029500000178813934, -0.11079999804496765, -0.02590000070631504, -0.17219999432563782, 0.009999999776482582, 0.011500000022351742, 0.10109999775886536, 0.07530000060796738, -0.10840000212192535, -0.22499999403953552, 0.027499999850988388, -0.033399999141693115, -0.05380000174045563, -0.029100000858306885, -0.305400013923645, 0.03280000016093254, -0.13289999961853027, 0.07919999957084656, 0.25699999928474426, 0.1768999993801117, -0.02199999988079071], [0.2567000091075897, -0.1565999984741211, -0.16349999606609344, -0.07069999724626541, -0.11180000007152557, 0.06390000134706497, -0.21369999647140503, -0.17059999704360962, -0.04580000042915344, -0.15139999985694885, 0.0551999993622303, 0.1071000024676323, 0.08079999685287476, -0.060100000351667404, 0.15000000596046448, 0.03669999912381172, 0.13809999823570251, 0.22660000622272491, -0.11890000104904175, 0.18970000743865967, 0.07739999890327454, -0.14640000462532043, -0.16050000488758087, -0.2281000018119812, -0.08900000154972076, 0.093299999833107, 0.06629999727010727, -0.33059999346733093, 0.17919999361038208, -0.12639999389648438, -0.07689999788999557, 0.07729999721050262, 0.005400000140070915, 0.04430000111460686, -0.014100000262260437, 0.044199999421834946, 0.015799999237060547, 0.1860000044107437, 0.08709999918937683, -0.026000000536441803, 0.13249999284744263, 0.05469999834895134, 0.17890000343322754, -0.1736000031232834, 0.0729999989271164, -0.025800000876188278, 0.007199999876320362, -0.00930000003427267, 0.08510000258684158, 0.24789999425411224, -0.29429998993873596, -0.05779999867081642, 0.17839999496936798, -0.03020000085234642, -0.008100000210106373, 0.15850000083446503, 0.14650000631809235, -0.07760000228881836, -0.11339999735355377, -0.002300000051036477, 0.18389999866485596, -0.07909999787807465], [-0.08839999884366989, -0.15459999442100525, 0.1404000073671341, 0.1485999971628189, -0.1420000046491623, 0.04619999974966049, 0.007899999618530273, -0.09830000251531601, 0.0860000029206276, 0.07190000265836716, -0.07620000094175339, 0.18440000712871552, -0.004000000189989805, 0.0731000006198883, -0.22040000557899475, 0.054099999368190765, 0.03660000115633011, -0.17520000040531158, 0.040300000458955765, 0.16680000722408295, 0.03240000084042549, -0.21539999544620514, -0.3375999927520752, 0.2102999985218048, -0.20739999413490295, -0.023499999195337296, -0.08730000257492065, 0.0478999987244606, 0.04349999874830246, -0.2590999901294708, -0.009200000204145908, -0.11760000139474869, 0.14579999446868896, -0.3434999883174896, -0.1429000049829483, 0.08609999716281891, -0.1256999969482422, 0.0027000000700354576, -0.22439999878406525, 0.024000000208616257, -0.09200000017881393, -0.2639000117778778, -0.3528999984264374, 0.3068999946117401, 0.11779999732971191, -0.3675999939441681, 0.1996999979019165, 0.2858000099658966, -0.25589999556541443, 0.05000000074505806, -0.3043000102043152, -0.12380000203847885, 0.14390000700950623, 0.11680000275373459, 0.004100000020116568, -0.1347000002861023, -0.22750000655651093, 0.0877000018954277, -0.07930000126361847, 0.11020000278949738, 0.12189999967813492, 0.06120000034570694], [-0.1306000053882599, -0.2353000044822693, -0.2842000126838684, 0.0925000011920929, -0.007600000128149986, 0.04729999974370003, -0.049400001764297485, -0.17350000143051147, 0.40549999475479126, -0.009999999776482582, 0.30889999866485596, 0.16439999639987946, 0.2962999939918518, -0.07079999893903732, 0.04430000111460686, 0.10869999974966049, -0.07370000332593918, 0.10639999806880951, -0.1785999983549118, -0.14569999277591705, -0.38690000772476196, -0.01269999984651804, 0.05889999866485596, -0.3377000093460083, -0.05779999867081642, 0.10369999706745148, -0.15790000557899475, -0.2522999942302704, 0.09960000216960907, 0.11720000207424164, -0.1745000034570694, -0.08429999649524689, 0.2079000025987625, 0.26190000772476196, -0.1371999979019165, -0.31459999084472656, -0.07569999992847443, 0.12099999934434891, 0.025800000876188278, 0.048900000751018524, 0.17720000445842743, -0.058400001376867294, -0.11990000307559967, -0.1136000007390976, 0.16599999368190765, 0.40059998631477356, -0.20640000700950623, -0.07609999924898148, 0.11699999868869781, -0.012900000438094139, 0.19110000133514404, -0.12460000067949295, -0.0026000000070780516, -0.040300000458955765, 0.12219999730587006, 0.01730000041425228, -0.0017000000225380063, 0.029500000178813934, -0.09799999743700027, -0.05730000138282776, -0.09749999642372131, -0.08900000154972076], [-0.02329999953508377, -0.15489999949932098, 0.07739999890327454, 0.19009999930858612, 0.3287000060081482, 0.06440000236034393, 0.13689999282360077, -0.28139999508857727, -0.008899999782443047, 0.24250000715255737, -0.009700000286102295, 0.001500000013038516, 0.1550000011920929, -0.1543000042438507, 0.10440000146627426, 0.07209999859333038, 0.0478999987244606, 0.03629999980330467, -0.13529999554157257, 0.05209999904036522, 0.14560000598430634, 0.13770000636577606, 0.08760000020265579, -0.028999999165534973, 0.21709999442100525, -0.037300001829862595, -0.17640000581741333, -0.15929999947547913, 0.17810000479221344, 0.05979999899864197, 0.023600000888109207, -0.06729999929666519, -0.0019000000320374966, -0.1467999964952469, 0.19040000438690186, -0.026599999517202377, -0.11469999700784683, -0.12219999730587006, -0.08020000159740448, 0.17730000615119934, 0.06920000165700912, -0.17030000686645508, 0.3215999901294708, 0.009499999694526196, 0.022299999371170998, -0.029200000688433647, 0.06650000065565109, -0.05119999870657921, 0.07569999992847443, -0.013100000098347664, -0.05620000138878822, 0.01979999989271164, 0.07159999758005142, 0.23430000245571136, -0.2678000032901764, -0.37950000166893005, -0.1477999985218048, -0.2667999863624573, -0.10429999977350235, -0.008100000210106373, 0.006500000134110451, 0.0544000007212162], [0.04809999838471413, 0.062199998646974564, 0.2851000130176544, 0.08630000054836273, -0.0689999982714653, -0.03750000149011612, -0.06719999760389328, 0.012600000016391277, -0.0689999982714653, 0.02449999935925007, -0.15880000591278076, 0.05180000141263008, -0.2257000058889389, -0.2492000013589859, 0.08100000023841858, 0.06750000268220901, 0.05310000106692314, -0.14020000398159027, -0.0333000011742115, 0.1656000018119812, -0.0032999999821186066, 0.058400001376867294, -0.13410000503063202, 0.21780000627040863, 0.15780000388622284, -0.0746999979019165, 0.1754000037908554, 0.20090000331401825, -0.46399998664855957, -0.01209999993443489, -0.16040000319480896, 0.03620000183582306, -0.0272000003606081, -0.12460000067949295, 0.032600000500679016, -0.008999999612569809, -0.21930000185966492, -0.03200000151991844, 0.28619998693466187, 0.3452000021934509, 0.11599999666213989, 0.02630000002682209, -0.20890000462532043, 0.009100000374019146, -0.11659999936819077, -0.19300000369548798, 0.055799998342990875, -0.24199999868869781, -0.0869000032544136, 0.2818000018596649, -0.17440000176429749, -0.0697999969124794, -0.03889999911189079, 0.1453000009059906, -0.10040000081062317, -0.188400000333786, -0.23999999463558197, -0.08259999752044678, 0.06679999828338623, 0.3440000116825104, 0.13169999420642853, -0.03610000014305115], [-0.017400000244379044, -0.17479999363422394, -0.003100000089034438, -0.17870000004768372, -0.008999999612569809, 0.009800000116229057, -0.09700000286102295, -0.19850000739097595, 0.07729999721050262, 0.003100000089034438, -0.007899999618530273, -0.049300000071525574, 0.1324000060558319, 0.24639999866485596, 0.21739999949932098, 0.06210000067949295, -0.3116999864578247, -0.029600000008940697, 0.2599000036716461, 0.1467999964952469, 0.030500000342726707, -0.21389999985694885, 0.14990000426769257, -0.25920000672340393, -0.22750000655651093, -0.14270000159740448, -0.1315000057220459, -0.12460000067949295, 0.03680000081658363, 0.06300000101327896, 0.010499999858438969, 0.0017999999690800905, -0.05739999935030937, 0.094200000166893, 0.019899999722838402, -0.028999999165534973, 0.155799999833107, 0.1500999927520752, -0.15860000252723694, -0.05920000001788139, -0.08659999817609787, 0.06440000236034393, -0.10170000046491623, 0.08730000257492065, -0.0052999998442828655, -0.006200000178068876, 0.0364999994635582, -0.24539999663829803, 0.0544000007212162, 0.07980000227689743, 0.1428000032901764, 0.03610000014305115, -0.30869999527931213, 0.002400000113993883, 0.1289999932050705, 0.025699999183416367, -0.07069999724626541, -0.12970000505447388, 0.13750000298023224, 0.17190000414848328, -0.243599995970726, -0.06340000033378601], [0.02800000086426735, 0.044599998742341995, -0.08730000257492065, -0.06390000134706497, -0.09350000321865082, -0.2012999951839447, 0.13099999725818634, 0.1462000012397766, 0.14350000023841858, -0.014999999664723873, -0.20180000364780426, -0.08380000293254852, 0.01269999984651804, -0.048900000751018524, -0.09139999747276306, -0.10890000313520432, -0.11079999804496765, 0.13230000436306, -0.029200000688433647, -0.06390000134706497, 0.14990000426769257, 0.17350000143051147, 0.2754000127315521, 0.1527000069618225, -0.07819999754428864, 0.2858999967575073, -0.15960000455379486, 0.07680000364780426, 0.004699999932199717, -0.18979999423027039, -0.08590000122785568, 0.12449999898672104, 0.13449999690055847, 0.010099999606609344, 0.06689999997615814, -0.10700000077486038, 0.1444000005722046, 0.03009999915957451, -0.02459999918937683, -0.12929999828338623, -0.20389999449253082, -0.311599999666214, -0.1979999989271164, 0.05079999938607216, -0.09399999678134918, -0.1509000062942505, 0.20739999413490295, 0.09470000118017197, 0.15209999680519104, 0.13580000400543213, -0.1858000010251999, -0.002899999963119626, 0.051899999380111694, 0.04500000178813934, 0.17499999701976776, 0.163100004196167, -0.06270000338554382, 0.029500000178813934, 0.10849999636411667, 0.3815999925136566, -0.1527000069618225, -0.09430000185966492], [-0.09690000116825104, -0.1362999975681305, -0.05429999902844429, 0.09740000218153, 0.2485000044107437, 0.13609999418258667, 0.06379999965429306, -0.0406000018119812, -0.0544000007212162, -0.2459000051021576, 0.08259999752044678, 0.15559999644756317, 0.2578999996185303, 0.09099999815225601, 0.026000000536441803, -0.025200000032782555, 0.06880000233650208, 0.17080000042915344, -0.10480000078678131, 0.051899999380111694, 0.007300000172108412, -0.1973000019788742, 0.1655000001192093, -0.02410000003874302, -0.006000000052154064, -0.11330000311136246, 0.188400000333786, 0.24240000545978546, 0.29660001397132874, -0.06440000236034393, -0.2467000037431717, 0.07680000364780426, 0.03579999879002571, 0.048700001090765, -0.1200999990105629, -0.03759999945759773, 0.03620000183582306, 0.11079999804496765, -0.07540000230073929, -0.06750000268220901, 0.022299999371170998, 9.999999747378752e-05, -0.017999999225139618, 0.11699999868869781, 0.007300000172108412, 0.05260000005364418, -0.12280000001192093, -0.3116999864578247, 0.3995000123977661, -0.10559999942779541, 0.06650000065565109, -0.11029999703168869, 0.14489999413490295, -0.0551999993622303, 0.13910000026226044, 0.21480000019073486, -0.20679999887943268, 0.19419999420642853, -0.03610000014305115, -0.017799999564886093, -0.2858000099658966, 0.019600000232458115], [0.07280000299215317, 0.07739999890327454, 0.01860000006854534, 0.18129999935626984, 0.05779999867081642, 0.025200000032782555, -0.0007999999797903001, -0.05730000138282776, -0.16869999468326569, -0.019300000742077827, 0.08940000087022781, 0.06480000168085098, 0.07530000060796738, -0.30559998750686646, -0.11890000104904175, -0.025299999862909317, 0.03359999880194664, 0.051500000059604645, 0.20100000500679016, -0.025800000876188278, 0.055799998342990875, -0.10450000315904617, 0.028200000524520874, -0.07760000228881836, -0.009999999776482582, -0.0723000019788742, -0.20759999752044678, -0.13760000467300415, -0.1785999983549118, -0.19840000569820404, -0.2635999917984009, -0.07190000265836716, -0.17649999260902405, 0.19920000433921814, -0.03680000081658363, 0.03959999978542328, 0.093299999833107, -0.37610000371932983, -0.05400000140070915, 0.03689999878406525, 0.24289999902248383, 0.33329999446868896, 0.029200000688433647, -0.2953999936580658, -0.2847000062465668, 0.1307000070810318, -0.1467999964952469, 0.1956000030040741, 0.1290999948978424, -0.12200000137090683, -0.04859999939799309, -0.10480000078678131, -0.03779999911785126, 0.10140000283718109, -0.01899999938905239, -0.0820000022649765, 0.16429999470710754, -0.12929999828338623, -0.1307000070810318, -0.055399999022483826, -0.1469999998807907, 0.133200004696846], [-0.2222999930381775, 0.20069999992847443, -0.07649999856948853, 0.04190000146627426, -0.06539999693632126, 0.10480000078678131, -0.03189999982714653, -0.006800000090152025, -0.00039999998989515007, -0.04969999939203262, -0.15700000524520874, 0.02979999966919422, 0.12929999828338623, 0.11089999973773956, -0.23980000615119934, 0.09950000047683716, 0.09440000355243683, -0.04410000145435333, 0.2736000120639801, 0.20010000467300415, 0.005200000014156103, 0.21060000360012054, 0.16089999675750732, -0.12099999934434891, 0.04089999943971634, 0.026399999856948853, 0.15970000624656677, -0.0608999989926815, -0.065700002014637, 0.03920000046491623, 0.09790000319480896, 0.03620000183582306, 0.06319999694824219, 0.02370000071823597, -0.3325999975204468, -0.19359999895095825, 0.043800000101327896, 0.288100004196167, -0.03750000149011612, 0.0560000017285347, -0.08410000056028366, -0.12530000507831573, 0.11819999665021896, 0.0502999983727932, -0.21369999647140503, 0.12240000069141388, 0.1467999964952469, -0.0949999988079071, -0.12219999730587006, -0.1655000001192093, -0.0828000009059906, 0.1761000007390976, 0.05810000002384186, 0.0957999974489212, 0.40799999237060547, 0.1386999934911728, -0.07919999957084656, 0.03709999844431877, -0.07680000364780426, 0.0731000006198883, -0.10050000250339508, -0.0034000000450760126], [0.17820000648498535, 0.16030000150203705, -0.065700002014637, 0.14300000667572021, 0.24629999697208405, -0.009800000116229057, -0.062300000339746475, 0.29980000853538513, -0.32829999923706055, -0.039400000125169754, -0.3246000111103058, -0.12680000066757202, -0.20730000734329224, -0.1680999994277954, -0.06340000033378601, -0.0066999997943639755, 0.25600001215934753, 0.08100000023841858, 0.1437000036239624, -0.005100000184029341, 0.37630000710487366, 0.21850000321865082, -0.4187999963760376, 0.09309999644756317, -0.0957999974489212, 0.10320000350475311, -0.08250000327825546, 0.2012999951839447, -0.3479999899864197, 0.008299999870359898, 0.3086000084877014, -0.09019999951124191, -0.08780000358819962, -0.19030000269412994, 0.006000000052154064, 0.1890999972820282, -0.19750000536441803, -0.2045000046491623, 0.1565999984741211, -0.12359999865293503, -0.1565999984741211, -0.031099999323487282, -0.23669999837875366, -0.07249999791383743, 0.16920000314712524, -0.14139999449253082, 0.3952000141143799, -0.12330000102519989, -0.3066999912261963, -0.23000000417232513, -0.09860000014305115, 0.003800000064074993, -0.23899999260902405, 0.03799999877810478, -0.28290000557899475, 0.10660000145435333, -0.2809000015258789, -0.14720000326633453, 0.03480000048875809, 0.1589999943971634, 0.014999999664723873, 0.11739999800920486], [0.06639999896287918, 0.13850000500679016, 0.09309999644756317, -0.012199999764561653, 0.19300000369548798, -0.07729999721050262, -0.22589999437332153, -0.046799998730421066, 0.02710000053048134, -0.07100000232458115, -0.1809999942779541, 0.017000000923871994, -0.01899999938905239, 0.2842999994754791, -0.3343000113964081, 0.2393999993801117, -0.03539999946951866, -0.05920000001788139, -0.07670000195503235, -0.2304999977350235, 0.09459999948740005, -0.027499999850988388, 0.121799997985363, -0.04039999842643738, 0.014399999752640724, 0.013899999670684338, -0.03830000013113022, 0.052000001072883606, 0.11339999735355377, -0.04039999842643738, 0.1867000013589859, 0.0608999989926815, 0.28929999470710754, -0.1988999992609024, -0.05119999870657921, -0.11840000003576279, 0.05959999933838844, -0.03660000115633011, 0.18479999899864197, -0.18080000579357147, 0.07460000365972519, 0.11429999768733978, 0.02449999935925007, -0.14589999616146088, -0.008299999870359898, -0.08529999852180481, -0.24539999663829803, -0.13099999725818634, -0.06379999965429306, -0.1542000025510788, -0.0032999999821186066, 0.00839999970048666, 0.04659999907016754, -0.0746999979019165, 0.004800000227987766, -0.04280000180006027, 0.16009999811649323, -0.06239999830722809, 0.13449999690055847, 0.27469998598098755, -0.2305999994277954, -0.15549999475479126], [0.04969999939203262, -0.031199999153614044, 0.028699999675154686, 0.17260000109672546, 0.02879999950528145, -0.16439999639987946, -0.186599999666214, -0.18690000474452972, -0.03229999914765358, 0.149399995803833, 0.07980000227689743, -0.0026000000070780516, -0.042399998754262924, -0.17419999837875366, 0.018699999898672104, -0.17010000348091125, -0.04439999908208847, 0.0066999997943639755, -0.13590000569820404, 0.12160000205039978, -0.1809999942779541, -0.02710000053048134, -0.2515000104904175, 0.28380000591278076, 0.22789999842643738, -0.31209999322891235, -0.10760000348091125, -0.08940000087022781, 0.21699999272823334, -0.08049999922513962, -0.11110000312328339, -0.2328999936580658, -0.1460999995470047, 0.2709999978542328, 0.024000000208616257, -0.134399995207</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>[0.8009152664614392]</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>[0.0454444008826629]</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>[0.6369134841851238]</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>[0.08289383919713925]</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>[-2.325858758142937]</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>[1.088486038460448]</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>[0.743516953606764]</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>[0.05891904769909721]</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>[0.27709113826188203]</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>[0.17144580816854804]</t>
+        </is>
+      </c>
+      <c r="O40" t="inlineStr">
+        <is>
+          <t>[0.03440652428990465]</t>
+        </is>
+      </c>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>[0.3174363867049193]</t>
+        </is>
+      </c>
+      <c r="Q40" t="inlineStr">
+        <is>
+          <t>[-0.05311210846647452]</t>
+        </is>
+      </c>
+      <c r="R40" t="inlineStr">
+        <is>
+          <t>[0.11355258082475783]</t>
+        </is>
+      </c>
+      <c r="S40" t="inlineStr">
+        <is>
+          <t>[-0.08123644019150134]</t>
+        </is>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>[0.09110534981069213]</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>[-1.210271593111902]</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>[0.21135308916312487]</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>[-0.15478032454157953]</t>
+        </is>
+      </c>
+      <c r="X40" t="inlineStr">
+        <is>
+          <t>[0.12097550686720457]</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>[-0.1558208597240891]</t>
+        </is>
+      </c>
+      <c r="Z40" t="inlineStr">
+        <is>
+          <t>[0.09511620838722691]</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>[-2.162342847309676]</t>
+        </is>
+      </c>
+      <c r="AB40" t="inlineStr">
+        <is>
+          <t>[0.29094937513236047]</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>[-0.7809898642264717]</t>
+        </is>
+      </c>
+      <c r="AD40" t="inlineStr">
+        <is>
+          <t>[0.14923977571220717]</t>
+        </is>
+      </c>
+      <c r="AE40" t="inlineStr">
+        <is>
+          <t>[-0.6202276126653088]</t>
+        </is>
+      </c>
+      <c r="AF40" t="inlineStr">
+        <is>
+          <t>[0.17446298891042267]</t>
+        </is>
+      </c>
+      <c r="AG40" t="inlineStr">
+        <is>
+          <t>[-2.822939753573392]</t>
+        </is>
+      </c>
+      <c r="AH40" t="inlineStr">
+        <is>
+          <t>[0.2846177058224883]</t>
+        </is>
+      </c>
+      <c r="AI40" t="inlineStr">
+        <is>
+          <t>[-1.2047290729325164]</t>
+        </is>
+      </c>
+      <c r="AJ40" t="inlineStr">
+        <is>
+          <t>[0.18067509319141012]</t>
+        </is>
+      </c>
+      <c r="AK40" t="inlineStr">
+        <is>
+          <t>[-0.6370527154321908]</t>
+        </is>
+      </c>
+      <c r="AL40" t="inlineStr">
+        <is>
+          <t>[0.17376115165092365]</t>
+        </is>
+      </c>
+      <c r="AM40" t="inlineStr">
+        <is>
+          <t>[-2.7466354005565297]</t>
+        </is>
+      </c>
+      <c r="AN40" t="inlineStr">
+        <is>
+          <t>[0.28776876038549304]</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>model_62_32_16_4</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>[62, 32, 16]</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>[[[0.07999999821186066, 0.005799999926239252, -0.07419999688863754, 0.015799999237060547, 0.03500000014901161, -0.018699999898672104, -0.015799999237060547, -0.043299999088048935, 0.013000000268220901, 0.042500000447034836, -0.10080000013113022, 0.057500001043081284, -0.02810000069439411, 0.10559999942779541, -0.01590000092983246, -0.015799999237060547, 0.06909999996423721, 0.006899999920278788, 0.009600000455975533, -0.08489999920129776, -0.06239999830722809, -0.00860000029206276, -0.0658000037074089, 0.037300001829862595, -0.05820000171661377, -0.061500001698732376, 0.04960000142455101, 0.0917000025510788, -0.01510000042617321, -0.06719999760389328, -0.00279999990016222, 0.1103999987244606, 0.04879999905824661, 0.0210999995470047, 0.03229999914765358, 0.1177000030875206, -0.002199999988079071, -0.013399999588727951, 0.054999999701976776, 0.02410000003874302, -0.03189999982714653, -0.027000000700354576, -0.03830000013113022, 0.014999999664723873, -0.030500000342726707, 0.1274999976158142, 0.06849999725818634, -0.05130000039935112, 0.08389999717473984, -0.042500000447034836, 0.09709999710321426, 0.013399999588727951, -0.05310000106692314, -0.001500000013038516, 0.03840000182390213, 0.13680000603199005, -0.07649999856948853, 0.024900000542402267, 9.999999747378752e-05, -0.05130000039935112, -0.0007999999797903001, 0.02800000086426735], [0.0038999998942017555, -0.0908999964594841, -0.07919999957084656, 0.04610000178217888, 0.03669999912381172, 0.004800000227987766, 0.03620000183582306, 0.027799999341368675, 0.05209999904036522, -0.08340000361204147, -0.03959999978542328, -0.012900000438094139, -0.02850000001490116, -0.042100001126527786, 0.05820000171661377, -0.03319999948143959, -0.026900000870227814, 0.04500000178813934, 0.06790000200271606, -0.03180000185966492, -0.009200000204145908, 0.007699999958276749, -0.039500001817941666, -0.05990000069141388, -0.03359999880194664, -0.011699999682605267, -0.013500000350177288, 0.05959999933838844, -0.021900000050663948, -0.013000000268220901, 0.01140000019222498, 0.02800000086426735, 0.03150000050663948, 0.020999999716877937, 0.04569999873638153, -0.006399999838322401, -0.0071000000461936, 0.037300001829862595, 0.01590000092983246, 0.02329999953508377, -0.04969999939203262, -0.04019999876618385, 0.021400000900030136, 0.0689999982714653, -0.015399999916553497, 0.031599998474121094, -0.003599999938160181, -0.07039999961853027, -0.022099999710917473, -0.007899999618530273, 0.01860000006854534, 0.05869999900460243, 0.03709999844431877, -0.014700000174343586, -0.04170000180602074, 0.009999999776482582, 0.017899999395012856, -0.07649999856948853, 0.14429999887943268, -0.003599999938160181, -0.04270000010728836, 0.0284000001847744]], [[0.10570000112056732, -0.20900000631809235, 0.023800000548362732, 0.1678999960422516, -0.10080000013113022, -0.10750000178813934, 0.04520000144839287, -0.02979999966919422, 0.1387999951839447, -0.07580000162124634, 0.08240000158548355, -0.1014999970793724, -0.08470000326633453, 0.11259999871253967, -0.06440000236034393, -0.08879999816417694, -0.048700001090765, 0.1445000022649765, -0.13189999759197235, 0.15139999985694885, -0.012299999594688416, 0.011099999770522118, -0.35019999742507935, 0.009700000286102295, 0.010900000110268593, 0.008100000210106373, -0.1526000052690506, 0.051899999380111694, 0.3052000105381012, 0.024299999698996544, -0.1160999983549118, -0.0071000000461936, 0.11739999800920486, -0.002099999925121665, -0.05299999937415123, -0.23720000684261322, 0.012299999594688416, -0.060100000351667404, -0.22429999709129333, -0.0737999975681305, -0.015599999576807022, -0.061000000685453415, 0.010900000110268593, -0.2644999921321869, -0.07720000296831131, -0.10909999907016754, 0.08969999849796295, -0.10689999908208847, 0.2102999985218048, -0.14059999585151672, 0.18870000541210175, -0.08829999715089798, 0.07989999651908875, -0.03689999878406525, -0.11620000004768372, -0.10440000146627426, 0.08429999649524689, 0.07750000059604645, -0.03790000081062317, -0.17319999635219574, -0.2549000084400177, -0.07050000131130219], [0.1151999980211258, 0.14869999885559082, -0.13330000638961792, 0.020600000396370888, -0.33090001344680786, 0.24660000205039978, -0.030400000512599945, 0.10599999874830246, -0.02419999986886978, 0.0982000008225441, 0.04839999973773956, 0.0908999964594841, 0.14190000295639038, -0.025699999183416367, 0.12139999866485596, 0.02239999920129776, 0.03909999877214432, 0.05590000003576279, -0.03480000048875809, -0.03929999843239784, 0.04650000110268593, 0.1143999993801117, -0.18950000405311584, 0.06809999793767929, 0.06480000168085098, -0.024299999698996544, 0.02410000003874302, 0.13580000400543213, 0.0031999999191612005, 0.0203000009059906, 0.03420000150799751, -0.06729999929666519, 0.007300000172108412, -0.11940000206232071, 0.08190000057220459, 0.2282000035047531, 0.1777999997138977, 0.20100000500679016, -0.03539999946951866, -0.05779999867081642, 0.21899999678134918, 0.2295999974012375, 0.1306000053882599, -0.03790000081062317, 0.010700000450015068, -0.20419999957084656, 0.22100000083446503, 0.17669999599456787, 0.20649999380111694, 0.11249999701976776, 0.02449999935925007, -0.06870000064373016, -0.05950000137090683, -0.06970000267028809, 0.1395999938249588, -0.027699999511241913, 0.016200000420212746, 0.016100000590085983, 0.05909999832510948, 0.3012000024318695, -0.16820000112056732, -0.10480000078678131], [0.0031999999191612005, -0.028999999165534973, -0.14810000360012054, -0.18310000002384186, 0.13300000131130219, -0.14229999482631683, 0.16249999403953552, 0.05849999934434891, -0.2924000024795532, -0.10670000314712524, -0.08699999749660492, 0.12839999794960022, -0.21070000529289246, 0.0737999975681305, 0.0820000022649765, -0.02630000002682209, -0.15459999442100525, 0.13699999451637268, -0.1574999988079071, 0.07500000298023224, 0.20810000598430634, 0.121799997985363, -0.14550000429153442, 0.02710000053048134, 0.029899999499320984, 0.1371999979019165, -0.03840000182390213, 0.14749999344348907, -0.0640999972820282, 0.03590000048279762, 0.22550000250339508, 0.02419999986886978, -0.07559999823570251, 0.024399999529123306, -0.10000000149011612, 0.06279999762773514, 0.0568000003695488, -0.07880000025033951, 0.07530000060796738, 0.02630000002682209, 0.21230000257492065, -0.00019999999494757503, -0.08810000121593475, -0.04500000178813934, -0.2370000034570694, 0.03460000082850456, 0.23729999363422394, 0.003800000064074993, 0.028999999165534973, 0.10949999839067459, 0.02630000002682209, 0.10490000247955322, -0.15070000290870667, -0.12919999659061432, -0.04610000178217888, -0.012400000356137753, -0.10970000177621841, 0.1550000011920929, -0.26510000228881836, -0.10740000009536743, 0.1868000030517578, 0.1454000025987625], [0.017400000244379044, -0.03350000083446503, -0.00419999985024333, -0.06750000268220901, -0.07169999927282333, -0.06639999896287918, 0.04349999874830246, -0.11980000138282776, 0.07190000265836716, 0.027799999341368675, -0.031700000166893005, -0.1785999983549118, -0.09769999980926514, -0.10279999673366547, -0.18469999730587006, 0.1386999934911728, 0.13030000030994415, -0.12060000002384186, -0.2800000011920929, -0.036400001496076584, 0.08460000157356262, 0.10679999738931656, -0.1168999969959259, -0.18199999630451202, 0.10180000215768814, -0.14489999413490295, 0.0560000017285347, 0.13120000064373016, -0.04019999876618385, -0.17489999532699585, 0.10010000318288803, -0.09449999779462814, -0.011099999770522118, -0.06340000033378601, -0.12020000070333481, -0.09589999914169312, 0.06400000303983688, 0.17520000040531158, 0.10530000180006027, -0.09059999883174896, -0.3569999933242798, 0.10700000077486038, -9.999999747378752e-05, 0.1509999930858612, -0.02889999933540821, 0.04430000111460686, 0.12729999423027039, -0.2524999976158142, 0.08640000224113464, 0.04019999876618385, -0.09040000289678574, -0.07360000163316727, 0.06920000165700912, 0.00860000029206276, 0.4058000147342682, 0.11640000343322754, 0.06469999998807907, 0.1712000072002411, -0.03060000017285347, -0.03449999913573265, 0.09189999848604202, 0.01640000008046627], [-0.004999999888241291, 0.14319999516010284, 0.2240999937057495, 0.1476999968290329, 0.0012000000569969416, -0.1111999973654747, -0.016599999740719795, 0.24639999866485596, -0.07999999821186066, -0.2175000011920929, 0.05290000140666962, -0.21559999883174896, -0.18709999322891235, -0.04450000077486038, -0.03460000082850456, 0.15760000050067902, 0.04439999908208847, 0.09160000085830688, 0.08330000191926956, -0.15970000624656677, 0.010499999858438969, -0.18449999392032623, 0.01979999989271164, -0.053599998354911804, -0.120899997651577, -0.07079999893903732, 0.25920000672340393, -0.02319999970495701, -0.23569999635219574, 0.014000000432133675, -0.03579999879002571, 0.09179999679327011, 0.19480000436306, -0.18490000069141388, -0.09960000216960907, -0.13330000638961792, -0.007899999618530273, 0.09210000187158585, -0.2637999951839447, 0.049400001764297485, 0.016699999570846558, -0.0778999999165535, 0.04569999873638153, -0.26330000162124634, 0.031300000846385956, 0.013700000010430813, 0.08969999849796295, 0.1031000018119812, 0.03669999912381172, -0.0421999990940094, -0.13289999961853027, 0.052000001072883606, -0.19439999759197235, -0.05209999904036522, 0.017899999395012856, 0.14640000462532043, -0.08460000157356262, 0.17710000276565552, -0.0812000036239624, 0.15320000052452087, 0.026499999687075615, -0.045099999755620956], [-0.08420000225305557, -0.09780000150203705, -0.0348999984562397, 0.16169999539852142, -0.11020000278949738, 0.23100000619888306, -0.007499999832361937, 0.11969999969005585, -0.006800000090152025, 0.11209999769926071, 0.044599998742341995, -0.10320000350475311, -0.027799999341368675, -0.1940000057220459, 0.03099999949336052, -0.12020000070333481, -0.2578999996185303, -0.11739999800920486, -0.15289999544620514, -0.0640999972820282, -0.027499999850988388, 0.3125999867916107, 0.147599995136261, 0.2542000114917755, 0.04809999838471413, 0.14180000126361847, 0.16040000319480896, -0.017000000923871994, -0.06419999897480011, -0.2833000123500824, 0.022600000724196434, 0.026799999177455902, 0.0835999995470047, 0.1678999960422516, -0.15469999611377716, -0.08250000327825546, 0.055399999022483826, 0.04390000179409981, 0.049400001764297485, -0.09950000047683716, -0.02850000001490116, -0.06769999861717224, -0.13650000095367432, -0.13529999554157257, 0.12559999525547028, -0.025200000032782555, 0.0568000003695488, 0.11140000075101852, -0.04610000178217888, -0.18729999661445618, 0.15690000355243683, 0.12210000306367874, -0.07769999653100967, 0.18649999797344208, -0.04410000145435333, 0.10819999873638153, 0.061500001698732376, 0.09049999713897705, 0.04010000079870224, -0.03620000183582306, -0.02539999969303608, 0.25690001249313354], [-0.034299999475479126, 0.16519999504089355, 0.06889999657869339, -0.2363000065088272, -0.2838999927043915, -0.06459999829530716, 0.11230000108480453, -0.06369999796152115, -0.25040000677108765, 0.10589999705553055, -0.10840000212192535, -0.01889999955892563, 0.00139999995008111, -0.053300000727176666, -0.044599998742341995, 0.07429999858140945, 0.08150000125169754, 0.06310000270605087, -0.04129999876022339, 0.18970000743865967, -0.08950000256299973, 0.004000000189989805, 0.16369999945163727, 0.10660000145435333, -0.0010000000474974513, 0.10930000245571136, 0.21379999816417694, -0.17110000550746918, 0.0860000029206276, -0.05649999901652336, -0.13609999418258667, -0.03229999914765358, -0.08919999748468399, 0.03200000151991844, 0.07180000096559525, -0.3671000003814697, -0.08860000222921371, 0.01889999955892563, -0.03579999879002571, -0.007899999618530273, 0.08320000022649765, 0.07639999687671661, 0.15289999544620514, 0.12370000034570694, -0.1404999941587448, -0.259799987077713, 0.09149999916553497, 0.03290000185370445, 0.04179999977350235, -0.0658000037074089, -0.28630000352859497, -0.09099999815225601, 0.02879999950528145, 0.17759999632835388, -0.11389999836683273, -0.17249999940395355, 0.05040000006556511, 0.06700000166893005, -0.0430000014603138, -0.11550000309944153, 0.01979999989271164, 0.03139999881386757], [-0.11569999903440475, -0.09830000251531601, 0.029899999499320984, 0.1965000033378601, 0.06419999897480011, -0.05460000038146973, 0.14339999854564667, 0.11159999668598175, 0.2460000067949295, 0.3086000084877014, 0.07890000194311142, -0.018799999728798866, -0.10339999943971634, 0.032999999821186066, -0.061000000685453415, 0.04569999873638153, 0.06700000166893005, 0.21899999678134918, 0.04569999873638153, -0.046300001442432404, -0.03519999980926514, 0.04619999974966049, 0.15800000727176666, 0.005499999970197678, 0.09179999679327011, 0.156700000166893, 0.019500000402331352, -0.15649999678134918, 0.14380000531673431, 0.15209999680519104, 0.029200000688433647, -0.05909999832510948, 0.012600000016391277, -0.1005999967455864, -0.14499999582767487, 0.14100000262260437, 0.0017999999690800905, 0.20819999277591705, -0.05790000036358833, 0.008200000040233135, 0.01080000028014183, 0.2750000059604645, 0.13490000367164612, -0.06930000334978104, -0.28949999809265137, -0.08529999852180481, -0.12240000069141388, 0.06920000165700912, -0.2249000072479248, 0.03999999910593033, 0.07720000296831131, -0.17229999601840973, -0.07400000095367432, -0.11410000175237656, 0.07289999723434448, -0.024700000882148743, -0.06270000338554382, 0.10999999940395355, 0.10909999907016754, -0.14980000257492065, 0.1941000074148178, 0.13609999418258667], [-0.13269999623298645, 0.027499999850988388, -0.12449999898672104, 0.013199999928474426, -0.11420000344514847, 0.1834000051021576, -0.10119999945163727, -0.14429999887943268, -0.04430000111460686, -0.09679999947547913, 0.02329999953508377, 0.0406000018119812, -0.1445000022649765, 0.3260999917984009, -0.04749999940395355, 0.11190000176429749, -0.2126999944448471, -0.04179999977350235, -0.17790000140666962, 0.03799999877810478, 0.056299999356269836, -0.014700000174343586, 0.03150000050663948, -0.22540000081062317, -0.1817999929189682, 0.12430000305175781, 0.08479999750852585, 0.03189999982714653, -0.17180000245571136, -0.19840000569820404, -0.05290000140666962, -0.2635999917984009, 0.1704999953508377, 0.09260000288486481, 0.2572000026702881, 0.131400004029274, -0.12189999967813492, 0.07599999755620956, -0.14030000567436218, 0.18729999661445618, -0.04919999837875366, 0.0689999982714653, 0.0640999972820282, -0.016200000420212746, -0.04670000076293945, -0.1412999927997589, -0.10670000314712524, -0.17239999771118164, -0.1655000001192093, -0.1014999970793724, -0.013500000350177288, -0.0272000003606081, -0.04050000011920929, -0.21060000360012054, -0.06210000067949295, -0.010700000450015068, -0.07289999723434448, -0.027899999171495438, 0.050599999725818634, -0.03680000081658363, -0.13120000064373016, 0.11169999837875366], [-0.027899999171495438, 0.019500000402331352, -0.09939999878406525, -0.007400000002235174, 0.0940999984741211, 0.06369999796152115, -0.10040000081062317, -0.0026000000070780516, -0.12720000743865967, -0.17749999463558197, 0.13940000534057617, 0.2542000114917755, -0.1379999965429306, -0.15970000624656677, 0.06610000133514404, -0.07509999722242355, 0.22599999606609344, 0.011099999770522118, -0.08730000257492065, -0.04740000143647194, -0.2037999927997589, 0.07249999791383743, -0.15469999611377716, 0.25999999046325684, 0.0024999999441206455, 0.04699999839067459, 0.30640000104904175, 0.0024999999441206455, -0.016699999570846558, 0.025499999523162842, 0.17509999871253967, -0.0013000000035390258, 0.2206999957561493, -0.09019999951124191, -0.0203000009059906, 0.026499999687075615, -0.13359999656677246, 0.01590000092983246, -0.0934000015258789, -0.04749999940395355, -0.1964000016450882, -0.03440000116825104, -0.03779999911785126, 0.056299999356269836, -0.20749999582767487, 0.07460000365972519, -0.008899999782443047, -0.028599999845027924, 0.07880000025033951, -0.07460000365972519, 0.02199999988079071, 0.0860000029206276, 0.06270000338554382, -0.10750000178813934, 0.03840000182390213, -0.2612999975681305, -0.013700000010430813, -0.20430000126361847, 0.3018999993801117, -0.09650000184774399, 0.09860000014305115, -0.12080000340938568], [-0.11670000106096268, -0.040800001472234726, -0.23240000009536743, 0.1589999943971634, -0.19910000264644623, -0.031599998474121094, -0.17900000512599945, -0.04859999939799309, -0.06270000338554382, 0.15060000121593475, 0.06840000301599503, 0.21719999611377716, -0.07180000096559525, -0.043800000101327896, -0.08839999884366989, -0.15129999816417694, -0.009600000455975533, 0.0031999999191612005, -0.12240000069141388, 0.16439999639987946, 0.04439999908208847, -0.3441999852657318, -0.004100000020116568, 0.17470000684261322, 0.12139999866485596, 0.03959999978542328, -0.195700004696846, -0.12939999997615814, 0.09910000115633011, -0.13689999282360077, -0.08309999853372574, -0.038600001484155655, 0.14419999718666077, -0.16459999978542328, -0.06350000202655792, 0.019300000742077827, 0.07970000058412552, -0.06949999928474426, 0.06549999862909317, 0.11169999837875366, 0.033900000154972076, -0.047600001096725464, -0.035100001841783524, -0.050200000405311584, 0.09300000220537186, 0.09189999848604202, -0.17589999735355377, -0.010999999940395355, 0.08980000019073486, -0.003599999938160181, -0.28130000829696655, 0.17149999737739563, -0.04270000010728836, 0.02889999933540821, 0.13040000200271606, 0.08500000089406967, -0.24279999732971191, 0.23090000450611115, -0.013100000098347664, 0.009100000374019146, 0.10920000076293945, -0.0957999974489212], [-0.05719999969005585, 0.14630000293254852, -0.0364999994635582, 0.010900000110268593, 0.09080000221729279, -0.0746999979019165, -0.15690000355243683, -0.07720000296831131, -0.00570000009611249, -0.03799999877810478, -0.11219999939203262, -0.006000000052154064, -0.20589999854564667, 0.000699999975040555, -0.11299999803304672, 0.03819999843835831, -0.09300000220537186, 0.18490000069141388, -0.060499999672174454, 0.02979999966919422, -0.0017000000225380063, 0.04170000180602074, 0.0934000015258789, 0.06109999865293503, 0.07689999788999557, 0.08330000191926956, 0.2305999994277954, -0.03799999877810478, 0.10339999943971634, 0.05380000174045563, -0.17990000545978546, 0.06260000169277191, -0.05490000173449516, 0.008700000122189522, 0.018699999898672104, 0.09619999676942825, -0.02319999970495701, 0.12349999696016312, 0.20080000162124634, -0.12680000066757202, 0.017999999225139618, 0.11140000075101852, -0.08460000157356262, 0.0786999985575676, 0.11339999735355377, 0.18469999730587006, -0.12080000340938568, 0.23649999499320984, 0.1647000014781952, -0.16040000319480896, 0.026799999177455902, -0.019200000911951065, 0.3440999984741211, -0.38530001044273376, -0.05979999899864197, 0.09369999915361404, 0.20630000531673431, 0.1137000024318695, -0.19509999454021454, 0.056699998676776886, -0.12960000336170197, -0.06809999793767929], [0.10679999738931656, -0.05249999836087227, 0.11569999903440475, -0.006399999838322401, 0.03720000013709068, 0.13770000636577606, -0.2574999928474426, 0.0746999979019165, -0.00279999990016222, -0.02459999918937683, -0.11259999871253967, -0.03200000151991844, 0.006500000134110451, -0.06539999693632126, 0.008200000040233135, 0.43050000071525574, -0.09929999709129333, -0.12809999287128448, -0.07069999724626541, 0.0820000022649765, -0.002300000051036477, -0.12690000236034393, 0.10159999877214432, -0.06920000165700912, 0.05350000038743019, 0.10220000147819519, -0.13420000672340393, -0.14910000562667847, 0.17820000648498535, -0.004399999976158142, 0.08420000225305557, -0.03550000116229057, -0.12439999729394913, -0.08799999952316284, -0.13210000097751617, 0.0940999984741211, 0.03920000046491623, 0.05820000171661377, 0.006899999920278788, -0.1331000030040741, 0.07769999653100967, -0.07039999961853027, -0.2962999939918518, -0.20489999651908875, 0.015200000256299973, -0.1657000035047531, 0.10840000212192535, -0.10249999910593033, 0.13199999928474426, -0.1768999993801117, -0.12839999794960022, -0.05510000139474869, 0.00139999995008111, -0.13099999725818634, 0.01640000008046627, -0.1647000014781952, -0.0284000001847744, -0.28700000047683716, 0.015699999406933784, 0.02370000071823597, 0.21770000457763672, 0.07769999653100967], [-0.00800000037997961, -0.027300000190734863, -0.01510000042617321, 0.032099999487400055, 0.024299999698996544, -0.1793999969959259, -0.11980000138282776, 0.20029999315738678, -0.06549999862909317, -0.3077999949455261, -0.1289999932050705, -0.07760000228881836, -0.0471000000834465, 0.19290000200271606, -0.022099999710917473, -0.05979999899864197, -0.07119999825954437, -0.048700001090765, 0.10679999738931656, 0.0010000000474974513, -0.019099999219179153, 0.15459999442100525, -0.04500000178813934, 0.25949999690055847, 0.21119999885559082, -0.24570000171661377, -0.12770000100135803, 0.10050000250339508, 0.1054999977350235, -0.06030000001192093, -0.15000000596046448, 0.15379999577999115, -0.05950000137090683, -0.000699999975040555, 0.2808000147342682, 0.04619999974966049, -0.07670000195503235, 0.11670000106096268, 0.1979999989271164, -0.02280000038444996, -0.07569999992847443, 0.04960000142455101, -0.041999999433755875, -0.0044999998062849045, 0.002199999988079071, -0.21040000021457672, -0.1023000031709671, 0.06769999861717224, -0.10840000212192535, -0.10170000046491623, -0.1420000046491623, -0.11110000312328339, -0.3131999969482422, -0.04259999841451645, 0.16500000655651093, -0.021299999207258224, 0.03959999978542328, 0.039799999445676804, 0.15950000286102295, -0.12120000272989273, 0.03620000183582306, 0.02969999983906746], [0.04259999841451645, -0.18359999358654022, -0.20919999480247498, -0.16269999742507935, 0.07660000026226044, 0.12219999730587006, 0.012500000186264515, 0.16500000655651093, 0.010599999688565731, -0.027899999171495438, 0.07249999791383743, -0.18719999492168427, -0.0632999986410141, 0.0729999989271164, 0.0012000000569969416, 0.08810000121593475, 0.3249000012874603, 0.18459999561309814, 0.002300000051036477, -0.06989999860525131, 0.08179999887943268, -0.27730000019073486, -0.05310000106692314, 0.1266999989748001, -0.09009999781847, 0.09359999746084213, 0.01899999938905239, -0.1200999990105629, -0.09279999881982803, -0.25870001316070557, -0.010099999606609344, -0.11150000244379044, -0.23000000417232513, -0.09139999747276306, 0.12389999628067017, 0.08739999681711197, 0.0722000002861023, -0.09989999979734421, 0.15549999475479126, 0.019200000911951065, -0.1120000034570694, 0.1459999978542328, 0.11209999769926071, -0.14239999651908875, 0.0925000011920929, 0.07370000332593918, 0.147599995136261, 0.1720999926328659, -0.05590000003576279, -0.1396999955177307, 0.07890000194311142, 0.05860000103712082, -0.004399999976158142, 0.12449999898672104, 0.03400000184774399, 0.015799999237060547, 0.04839999973773956, -0.15389999747276306, -0.10040000081062317, -0.25540000200271606, -0.11949999630451202, -0.014700000174343586], [0.00839999970048666, -0.2084999978542328, 0.10409999638795853, -0.005499999970197678, -0.05310000106692314, -0.010900000110268593, 0.1143999993801117, 0.025599999353289604, -0.1444000005722046, -0.07540000230073929, 0.17419999837875366, -0.1671999990940094, -0.0027000000700354576, 0.29679998755455017, 0.25519999861717224, 0.035599999129772186, 0.03290000185370445, 0.03889999911189079, -0.01759999990463257, -0.1356000006198883, -0.1907999962568283, 0.1387999951839447, 0.19349999725818634, -0.04149999842047691, 0.22349999845027924, 0.31049999594688416, -0.05180000141263008, 0.035100001841783524, 0.08009999990463257, -0.1046999990940094, 0.23669999837875366, 0.05420000106096268, 0.18729999661445618, -0.12800000607967377, -0.04830000177025795, -0.06159999966621399, -0.049300000071525574, -0.147599995136261, 0.11429999768733978, -0.02889999933540821, 0.043800000101327896, 0.0714000016450882, 0.12030000239610672, 0.04470000043511391, 0.1421000063419342, 0.06539999693632126, -0.20559999346733093, -0.09019999951124191, 0.22380000352859497, 0.1242000013589859, -0.18320000171661377, -0.08160000294446945, -0.021800000220537186, -0.04809999838471413, 0.035100001841783524, 0.08129999786615372, 0.052799999713897705, -0.12060000002384186, -0.07249999791383743, 0.0658000037074089, -0.0771000012755394, -0.059300001710653305], [-0.14560000598430634, 0.21690000593662262, 0.02879999950528145, 0.06780000030994415, -0.16740000247955322, -0.03790000081062317, 0.10869999974966049, -0.10520000010728836, -0.14499999582767487, 0.022600000724196434, 0.052400000393390656, -0.15279999375343323, -0.05530000105500221, -0.16820000112056732, 0.07410000264644623, -0.19470000267028809, 0.07329999655485153, -0.01979999989271164, -0.06859999895095825, -0.002300000051036477, 0.15469999611377716, 0.0421999990940094, -0.03629999980330467, -0.04540000110864639, 0.07599999755620956, 0.016499999910593033, -0.08399999886751175, -0.2727000117301941, 0.17990000545978546, -0.03819999843835831, 0.055799998342990875, 0.22769999504089355, 0.033399999141693115, 0.13830000162124634, -0.0, 0.2304999977350235, -0.11800000071525574, -0.050200000405311584, -0.02850000001490116, 0.050700001418590546, -0.2865999937057495, 0.03819999843835831, -0.022099999710917473, -0.06679999828338623, 0.026200000196695328, -0.15389999747276306, 0.1720000058412552, -0.04450000077486038, -0.14409999549388885, -0.006899999920278788, 0.03290000185370445, -0.0706000030040741, -0.09619999676942825, -0.1518000066280365, -0.13349999487400055, 0.21699999272823334, -0.05700000002980232, -0.26440000534057617, -0.17550000548362732, 0.02329999953508377, 0.048900000751018524, -0.2590999901294708], [0.15039999783039093, 0.2547000050544739, 0.16920000314712524, -0.026900000870227814, -0.17350000143051147, -0.0746999979019165, 0.005499999970197678, 0.12060000002384186, -0.029400000348687172, -0.15219999849796295, -0.16130000352859497, 0.012299999594688416, 0.11919999867677689, 0.013700000010430813, 0.024800000712275505, 0.13349999487400055, 0.16140000522136688, -0.21070000529289246, -0.2037000060081482, 0.17249999940395355, -0.02800000086426735, -0.036400001496076584, -0.020899999886751175, 0.026200000196695328, -0.019200000911951065, 0.26269999146461487, -0.20880000293254852, 0.016499999910593033, 0.03689999878406525, -0.039900001138448715, -0.006099999882280827, -0.017000000923871994, 0.164000004529953, -0.0771000012755394, -0.10729999840259552, -0.00419999985024333, 0.12380000203847885, -0.25, 0.0052999998442828655, 0.022299999371170998, -0.07450000196695328, 0.07000000029802322, 0.046300001442432404, 0.08079999685287476, -0.013000000268220901, 0.20499999821186066, -0.053700000047683716, 0.19920000433921814, -0.32989999651908875, -0.0714000016450882, 0.2345000058412552, -0.03370000049471855, -0.07209999859333038, -0.1282999962568283, 0.037700001150369644, -0.08900000154972076, 0.1467999964952469, 0.1639000028371811, 0.09709999710321426, 0.039000000804662704, -0.016899999231100082, 0.03319999948143959], [0.07100000232458115, 0.08630000054836273, -0.15459999442100525, -0.002400000113993883, 0.24250000715255737, -0.07980000227689743, -0.024700000882148743, 0.003700000001117587, 0.13770000636577606, 0.02930000051856041, 0.26510000228881836, -0.17880000174045563, 0.17980000376701355, -0.1526000052690506, -0.06549999862909317, 0.10270000249147415, 0.043299999088048935, -0.006500000134110451, 0.010999999940395355, 0.022700000554323196, -0.16009999811649323, 0.2904999852180481, -0.020099999383091927, 0.07750000059604645, -0.0071000000461936, -0.0035000001080334187, -0.13689999282360077, -0.1648000031709671, -0.14399999380111694, -0.18400000035762787, -0.061500001698732376, -0.0982000008225441, 0.02669999934732914, -0.131400004029274, 0.14890000224113464, -0.02419999986886978, 0.09359999746084213, -0.15559999644756317, 0.08950000256299973, 0.02449999935925007, 0.012299999594688416, -0.24400000274181366, 0.1754000037908554, 0.1177000030875206, -0.027400000020861626, -0.1867000013589859, 0.07440000027418137, -0.016300000250339508, 0.0608999989926815, -0.07909999787807465, 0.0020000000949949026, -0.05469999834895134, 0.03959999978542328, -0.2939999997615814, -0.1518000066280365, -0.06589999794960022, -0.22499999403953552, 0.18289999663829803, -0.09920000284910202, 0.08900000154972076, 0.11779999732971191, -0.015200000256299973], [-0.02889999933540821, 0.11620000004768372, 0.11100000143051147, -0.21580000221729279, -0.06599999964237213, 0.16830000281333923, -0.14309999346733093, 0.06800000369548798, 0.19609999656677246, 0.0421999990940094, -0.06620000302791595, 0.09679999947547913, -0.4223000109195709, 0.04149999842047691, -0.14419999718666077, -0.11749999970197678, 0.2680000066757202, 0.006500000134110451, -0.03970000147819519, -0.13529999554157257, -0.07930000126361847, 0.15109999477863312, -0.16220000386238098, -0.1589999943971634, 0.2768999934196472, 0.013199999928474426, -0.01600000075995922, -0.08259999752044678, -0.0019000000320374966, 0.03840000182390213, 0.08730000257492065, 0.12330000102519989, -0.06499999761581421, -0.04100000113248825, 0.09539999812841415, 0.0658000037074089, 0.03480000048875809, -0.149399995803833, -0.0625, 0.2013999968767166, 0.19580000638961792, -0.12269999831914902, 0.04969999939203262, -0.04540000110864639, 0.19050000607967377, -0.12370000034570694, -0.08100000023841858, -0.10840000212192535, -0.01269999984651804, -0.09809999912977219, 0.05310000106692314, 0.015699999406933784, 0.04690000042319298, 0.1387999951839447, -0.08129999786615372, 0.002400000113993883, 0.12349999696016312, 0.09629999846220016, 0.0005000000237487257, 0.05820000171661377, 0.1421000063419342, 0.12430000305175781], [-0.04780000075697899, 0.05420000106096268, 0.030400000512599945, 0.07100000232458115, -0.07090000063180923, 0.05119999870657921, 0.05570000037550926, -0.20180000364780426, 0.0019000000320374966, 0.1738000065088272, -0.004100000020116568, -0.03319999948143959, -0.18330000340938568, 0.03480000048875809, 0.14640000462532043, 0.018699999898672104, 0.0754999965429306, 0.0357000008225441, -0.006099999882280827, -0.09430000185966492, 0.02759999968111515, -0.045499999076128006, 0.1736000031232834, 0.13650000095367432, -0.20440000295639038, 0.03929999843239784, -0.21879999339580536, 0.20839999616146088, -0.01590000092983246, 0.014499999582767487, 0.2700999975204468, -0.07150000333786011, -0.2858000099658966, -0.15520000457763672, 0.09849999845027924, -0.11509999632835388, -0.3003999888896942, 0.09000000357627869, 0.05979999899864197, -0.12770000100135803, -0.05620000138878822, -0.22290000319480896, -0.05990000069141388, -0.10090000182390213, 0.050599999725818634, -0.12960000336170197, -0.020500000566244125, 0.023800000548362732, -0.07720000296831131, -0.05469999834895134, 0.10189999639987946, 0.12219999730587006, -0.0746999979019165, -0.10170000046491623, 0.002099999925121665, -0.09780000150203705, 0.16269999742507935, 0.26249998807907104, 0.07980000227689743, 0.08980000019073486, 0.011099999770522118, -0.25540000200271606], [0.08709999918937683, -0.02319999970495701, 0.28349998593330383, 0.022600000724196434, 0.04560000076889992, 0.19930000603199005, -0.02879999950528145, 0.18039999902248383, -0.034699998795986176, -0.09629999846220016, 0.2563000023365021, 0.05480000004172325, -0.04749999940395355, -0.04230000078678131, -0.08560000360012054, -0.04270000010728836, -0.031099999323487282, -0.03200000151991844, -0.1996999979019165, 0.15889999270439148, -0.07689999788999557, -0.0934000015258789, 0.025499999523162842, 0.15719999372959137, -0.16259999573230743, -0.1185000017285347, -0.11240000277757645, -0.13009999692440033, 0.02759999968111515, 0.05209999904036522, 0.032499998807907104, 0.0019000000320374966, -0.1882999986410141, 0.014000000432133675, -0.016899999231100082, 0.05040000006556511, -0.1776999980211258, -0.010700000450015068, 0.1420000046491623, 0.07460000365972519, 0.16910000145435333, 0.05169999971985817, 0.12489999830722809, 0.16050000488758087, -0.26440000534057617, 0.07829999923706055, 0.08889999985694885, -0.20170000195503235, 0.09319999814033508, -0.031199999153614044, -0.03869999945163727, 0.008700000122189522, -0.01769999973475933, -0.058400001376867294, -0.05510000139474869, 0.43140000104904175, 0.1396999955177307, 0.03739999979734421, 0.15680000185966492, 0.03099999949336052, -0.11479999870061874, 0.06930000334978104], [-0.164000004529953, 0.2046000063419342, -0.1542000025510788, -0.049800001084804535, -0.06350000202655792, -0.09139999747276306, -0.04800000041723251, -0.08980000019073486, 0.1793999969959259, -0.17759999632835388, 0.23469999432563782, -0.044599998742341995, -0.06129999831318855, -0.0348999984562397, 0.20720000565052032, 0.16949999332427979, -0.2599000036716461, -0.12139999866485596, 0.16269999742507935, -0.1687999963760376, 0.08259999752044678, -0.08489999920129776, -0.0812000036239624, 0.06840000301599503, -0.06509999930858612, -0.04170000180602074, -0.014800000004470348, 0.053300000727176666, 0.3003999888896942, -0.13040000200271606, 0.060600001364946365, 0.1146999970078</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t xml:space="preserve">[[[0.09070000052452087, 0.04749999940395355, -0.06310000270605087, 0.03400000184774399, 0.0038999998942017555, -0.02800000086426735, -0.033399999141693115, -0.08560000360012054, -0.00419999985024333, 0.039000000804662704, -0.09440000355243683, 0.09430000185966492, 0.020800000056624413, 0.13079999387264252, -0.08940000087022781, -0.045899998396635056, 0.14219999313354492, -0.01889999955892563, -0.08569999784231186, -0.1307000070810318, 0.0007999999797903001, 0.006399999838322401, -0.06509999930858612, 0.11980000138282776, -0.0430000014603138, -0.07039999961853027, 0.06700000166893005, 0.04740000143647194, -0.0052999998442828655, -0.07190000265836716, -0.0714000016450882, 0.15790000557899475, 0.08969999849796295, 0.0729999989271164, 0.023499999195337296, 0.17749999463558197, 0.020899999886751175, -0.08529999852180481, 0.09279999881982803, 0.008100000210106373, -0.001500000013038516, -0.03290000185370445, -0.12240000069141388, 0.0024999999441206455, 0.05460000038146973, 0.05950000137090683, 0.0689999982714653, -0.035599999129772186, 0.08839999884366989, -0.030899999663233757, 0.12549999356269836, -0.07880000025033951, -0.022199999541044235, -0.06350000202655792, 0.044599998742341995, 0.14509999752044678, -0.08669999986886978, 0.04659999907016754, -0.0142000000923872, -0.0034000000450760126, -0.0210999995470047, 0.041099999099969864], [-0.019999999552965164, -0.13359999656677246, -0.1014999970793724, 0.005100000184029341, 0.025200000032782555, 0.0868000015616417, 0.050700001418590546, 0.06270000338554382, 0.09220000356435776, -0.133200004696846, -0.033799998462200165, -0.02459999918937683, 0.007899999618530273, -0.10589999705553055, 0.07519999891519547, -0.028999999165534973, -0.06310000270605087, 0.041999999433755875, 0.10530000180006027, 0.026399999856948853, -0.08079999685287476, -0.05389999970793724, -0.013700000010430813, -0.11079999804496765, 0.014499999582767487, 0.04280000180006027, -0.054999999701976776, -0.009600000455975533, -0.043299999088048935, 0.062199998646974564, 0.10589999705553055, -0.010999999940395355, -0.014000000432133675, -0.0763000026345253, -0.0203000009059906, -0.07199999690055847, 0.008299999870359898, 0.0812000036239624, 0.004600000102072954, 0.0868000015616417, 0.012199999764561653, -0.044199999421834946, 0.07090000063180923, 0.04809999838471413, -0.04569999873638153, -0.034699998795986176, 0.04960000142455101, -0.05719999969005585, -0.07999999821186066, 0.051899999380111694, -0.06279999762773514, 0.06769999861717224, 0.08169999718666077, 0.04439999908208847, -0.11029999703168869, -0.07850000262260437, 0.010900000110268593, -0.1316000074148178, 0.19670000672340393, 0.02419999986886978, 0.021199999377131462, -0.002400000113993883]], [[0.11320000141859055, -0.1446000039577484, 0.04899999871850014, 0.10170000046491623, -0.12399999797344208, -0.07240000367164612, 0.02239999920129776, -0.02669999934732914, 0.10209999978542328, -0.08860000222921371, 0.09369999915361404, -0.1453000009059906, -0.11100000143051147, 0.12610000371932983, -0.051600001752376556, -0.05920000001788139, -0.11069999635219574, 0.10790000110864639, -0.15240000188350677, 0.15449999272823334, 0.05959999933838844, 0.027000000700354576, -0.28870001435279846, 0.04910000041127205, 0.120899997651577, 0.04149999842047691, -0.14270000159740448, -0.03720000013709068, 0.3553999960422516, -0.014600000344216824, -0.1306000053882599, -0.07100000232458115, 0.051600001752376556, -0.021199999377131462, -0.16459999978542328, -0.21889999508857727, -0.10939999669790268, -9.999999747378752e-05, -0.2653999924659729, -0.06610000133514404, -0.008999999612569809, 0.005499999970197678, -0.024399999529123306, -0.2531000077724457, -0.025100000202655792, -0.16329999268054962, 0.037300001829862595, -0.07559999823570251, 0.1843000054359436, -0.12290000170469284, 0.19339999556541443, -0.12189999967813492, 0.0989999994635582, 0.005799999926239252, -0.14720000326633453, -0.15800000727176666, 0.2694999873638153, 0.05909999832510948, -0.03799999877810478, -0.186599999666214, -0.2045000046491623, -0.12600000202655792], [-0.05550000071525574, 0.22769999504089355, -0.0013000000035390258, -0.049300000071525574, -0.43220001459121704, 0.15929999947547913, 0.0032999999821186066, 0.12489999830722809, -0.1500999927520752, 0.15219999849796295, 0.16349999606609344, 0.18479999899864197, 0.23499999940395355, 0.03480000048875809, 0.1168999969959259, -0.11479999870061874, -0.04010000079870224, -0.031300000846385956, -0.11320000141859055, -0.0778999999165535, 0.16580000519752502, 0.14259999990463257, -0.28999999165534973, 0.1459999978542328, 0.12110000103712082, 0.07429999858140945, -0.12210000306367874, 0.1745000034570694, 0.012799999676644802, 0.008799999952316284, -0.00930000003427267, -0.19910000264644623, -0.014999999664723873, -0.044199999421834946, 0.033799998462200165, 0.35740000009536743, 0.1534000039100647, 0.18770000338554382, 0.11710000038146973, -0.14900000393390656, 0.17350000143051147, 0.34220001101493835, 0.10080000013113022, -0.15219999849796295, 0.02879999950528145, -0.30630001425743103, 0.25060001015663147, 0.2190999984741211, 0.30730000138282776, 0.13410000503063202, 0.07829999923706055, -0.12839999794960022, -0.03999999910593033, -0.18000000715255737, 0.26989999413490295, 0.05389999970793724, 0.012199999764561653, 0.12970000505447388, 0.025800000876188278, 0.41359999775886536, -0.09860000014305115, -0.23000000417232513], [-0.014499999582767487, -0.06669999659061432, -0.1265999972820282, -0.15209999680519104, 0.14159999787807465, -0.17520000040531158, 0.19290000200271606, 0.07249999791383743, -0.328900009393692, -0.13740000128746033, -0.06019999831914902, 0.1738000065088272, -0.18799999356269836, 0.06440000236034393, 0.09290000051259995, -0.06289999932050705, -0.15029999613761902, 0.13500000536441803, -0.15289999544620514, 0.07940000295639038, 0.16940000653266907, 0.10909999907016754, -0.219200000166893, 0.024399999529123306, -0.030700000002980232, 0.14149999618530273, -0.06019999831914902, 0.20739999413490295, -0.09679999947547913, 0.05979999899864197, 0.24050000309944153, 0.05480000004172325, -0.04610000178217888, 0.04500000178813934, -0.038100000470876694, 0.0786999985575676, 0.1462000012397766, -0.09989999979734421, 0.11779999732971191, 0.0032999999821186066, 0.17990000545978546, -0.009200000204145908, -0.0544000007212162, -0.06340000033378601, -0.2777999937534332, 0.05779999867081642, 0.2854999899864197, -0.003100000089034438, 0.06809999793767929, 0.09600000083446503, 0.01899999938905239, 0.09690000116825104, -0.16099999845027924, -0.17990000545978546, -0.0010999999940395355, 0.03500000014901161, -0.17960000038146973, 0.17299999296665192, -0.2791000008583069, -0.06970000267028809, 0.15549999475479126, 0.15880000591278076], [0.0364999994635582, -0.00039999998989515007, 0.00019999999494757503, -0.14489999413490295, -0.09769999980926514, -0.013199999928474426, 0.03830000013113022, -0.06930000334978104, 0.04749999940395355, 0.014800000004470348, -0.05079999938607216, -0.21469999849796295, -0.12110000103712082, -0.09179999679327011, -0.13750000298023224, 0.13369999825954437, 0.10490000247955322, -0.1462000012397766, -0.2937999963760376, -0.030799999833106995, 0.09640000015497208, 0.11140000075101852, -0.03240000084042549, -0.15000000596046448, 0.2092999964952469, -0.14990000426769257, 0.08370000123977661, 0.052299998700618744, -0.03200000151991844, -0.19519999623298645, 0.12359999865293503, -0.13019999861717224, -0.1274999976158142, -0.11379999667406082, -0.210999995470047, -0.07999999821186066, 0.0035000001080334187, 0.1639000028371811, 0.10109999775886536, -0.060600001364946365, -0.3028999865055084, 0.14650000631809235, -0.01269999984651804, 0.16599999368190765, -0.0003000000142492354, 0.02539999969303608, 0.12250000238418579, -0.23109999299049377, 0.05900000035762787, 0.10639999806880951, -0.08100000023841858, -0.08070000261068344, 0.1362999975681305, 0.0032999999821186066, 0.35989999771118164, 0.06480000168085098, 0.06629999727010727, 0.1542000025510788, 0.007799999788403511, -0.08150000125169754, 0.12690000236034393, -0.02800000086426735], [0.08240000158548355, 0.20309999585151672, 0.18080000579357147, 0.1598999947309494, -0.04230000078678131, -0.0706000030040741, -0.08720000088214874, 0.19059999287128448, -0.04039999842643738, -0.2531000077724457, 0.015699999406933784, -0.2678999900817871, -0.22609999775886536, -0.0012000000569969416, -0.0681999996304512, 0.1574999988079071, 0.09319999814033508, 0.05009999871253967, 0.06369999796152115, -0.19840000569820404, 0.04969999939203262, -0.10419999808073044, 0.0575999990105629, -0.021199999377131462, -0.09019999951124191, -0.08479999750852585, 0.3154999911785126, -0.0851999968290329, -0.19130000472068787, -0.058800000697374344, -0.06319999694824219, 0.18979999423027039, 0.2425999939441681, -0.20309999585151672, -0.13570000231266022, -0.10779999941587448, -0.15839999914169312, 0.17679999768733978, -0.2612999975681305, 0.0869000032544136, 0.019899999722838402, -0.03400000184774399, 0.0015999999595806003, -0.18880000710487366, 0.0982000008225441, -0.032499998807907104, 0.014700000174343586, 0.05950000137090683, -0.002300000051036477, -0.025200000032782555, -0.09529999643564224, 0.015799999237060547, -0.1737000048160553, -0.03970000147819519, -0.05009999871253967, 0.09120000153779984, 0.03620000183582306, 0.12080000340938568, -0.0272000003606081, 0.10559999942779541, -0.014000000432133675, -0.07209999859333038], [-0.06549999862909317, -0.18700000643730164, -0.13760000467300415, 0.21469999849796295, 0.00279999990016222, 0.24040000140666962, 0.04879999905824661, 0.10999999940395355, 0.09290000051259995, 0.027799999341368675, 0.04659999907016754, -0.1257999986410141, -0.024800000712275505, -0.2815000116825104, 0.023900000378489494, -0.009499999694526196, -0.20909999310970306, -0.044199999421834946, -0.057999998331069946, 0.005799999926239252, -0.12449999898672104, 0.20090000331401825, 0.18770000338554382, 0.17350000143051147, -0.011300000362098217, 0.1712999939918518, 0.1858000010251999, 0.0032999999821186066, -0.01600000075995922, -0.26840001344680786, 0.08070000261068344, 0.017000000923871994, 0.1670999974012375, 0.15240000188350677, -0.08709999918937683, -0.17630000412464142, 0.01720000058412552, 0.04879999905824661, -0.05950000137090683, -0.09529999643564224, -0.0786999985575676, -0.14830000698566437, -0.0502999983727932, -0.13850000500679016, 0.06340000033378601, 0.07739999890327454, 0.1054999977350235, 0.20810000598430634, -0.06430000066757202, -0.26759999990463257, 0.09700000286102295, 0.17020000517368317, -0.13840000331401825, 0.2851000130176544, -0.11429999768733978, 0.09780000150203705, 0.1396999955177307, 0.0763000026345253, 0.011099999770522118, -0.12530000507831573, 0.08240000158548355, 0.36169999837875366], [-0.0035000001080334187, 0.07769999653100967, -0.014299999922513962, -0.1298000067472458, -0.22259999811649323, -0.1080000028014183, 0.017100000753998756, -0.179299995303154, -0.16329999268054962, 0.15520000457763672, -0.25609999895095825, 0.006399999838322401, 0.012299999594688416, -0.05290000140666962, -0.1062999963760376, 0.10180000215768814, 0.26429998874664307, 0.09749999642372131, -0.02500000037252903, 0.15049999952316284, -0.18050000071525574, 0.027000000700354576, 0.20829999446868896, 0.04089999943971634, -0.1412000060081482, 0.007400000002235174, 0.24390000104904175, -0.09679999947547913, 0.007000000216066837, -0.03759999945759773, -0.1737000048160553, 0.07639999687671661, -0.015300000086426735, 0.05779999867081642, 0.1932000070810318, -0.39419999718666077, -0.007600000128149986, -0.0010000000474974513, -0.004900000058114529, 0.00430000014603138, 0.10480000078678131, -0.016300000250339508, 0.11760000139474869, 0.15880000591278076, -0.18140000104904175, -0.15479999780654907, 0.10159999877214432, -0.032099999487400055, 0.050599999725818634, -0.09000000357627869, -0.249099999666214, -0.05609999969601631, -0.04910000041127205, 0.21359999477863312, -0.19169999659061432, -0.15489999949932098, -0.001500000013038516, 0.05950000137090683, -0.019500000402331352, -0.19259999692440033, -0.06019999831914902, 0.09989999979734421], [-0.0406000018119812, -0.20489999651908875, -0.05040000006556511, 0.25780001282691956, 0.11649999767541885, -0.05000000074505806, 0.1597999930381775, 0.11909999698400497, 0.30640000104904175, 0.2930999994277954, -0.0034000000450760126, -0.008700000122189522, -0.10580000281333923, 0.025599999353289604, -0.03150000050663948, 0.009200000204145908, 0.18119999766349792, 0.26820001006126404, 0.09210000187158585, -0.0674000009894371, -0.1436000019311905, 0.019700000062584877, 0.16120000183582306, -0.028300000354647636, -0.07419999688863754, 0.014700000174343586, 0.09279999881982803, -0.05990000069141388, 0.023600000888109207, 0.17190000414848328, 0.0632999986410141, 0.10440000146627426, 0.08579999953508377, -0.1469999998807907, 0.014000000432133675, 0.12269999831914902, 0.12860000133514404, 0.05869999900460243, 0.012799999676644802, 0.04349999874830246, 0.054499998688697815, 0.2045000046491623, 0.1996999979019165, -0.03370000049471855, -0.364300012588501, 0.026399999856948853, -0.049400001764297485, 0.011599999852478504, -0.2160000056028366, 0.0869000032544136, 0.09749999642372131, -0.1468999981880188, -0.03310000151395798, -0.1543000042438507, 0.033399999141693115, 0.01489999983459711, -0.29989999532699585, 0.09549999982118607, 0.1949000060558319, -0.1858000010251999, 0.10599999874830246, 0.2249000072479248], [-0.06459999829530716, 0.018300000578165054, -0.18970000743865967, 0.019200000911951065, -0.07970000058412552, 0.22660000622272491, -0.1265999972820282, -0.15060000121593475, 0.0348999984562397, -0.1362999975681305, -0.0203000009059906, -0.039400000125169754, -0.1809999942779541, 0.3070000112056732, -0.0502999983727932, 0.1973000019788742, -0.1987999975681305, 0.029100000858306885, -0.15139999985694885, 0.0697999969124794, -0.025299999862909317, -0.02759999968111515, 0.11949999630451202, -0.27309998869895935, -0.1534000039100647, 0.11649999767541885, 0.14139999449253082, -0.038600001484155655, -0.12430000305175781, -0.2207999974489212, -0.04670000076293945, -0.25119999051094055, 0.1607999950647354, 0.0560000017285347, 0.21410000324249268, 0.07580000162124634, -0.20499999821186066, 0.11900000274181366, -0.24979999661445618, 0.22579999268054962, -0.03220000118017197, 0.02280000038444996, 0.060100000351667404, 0.028300000354647636, -0.021400000900030136, -0.1265999972820282, -0.13269999623298645, -0.17000000178813934, -0.2110999971628189, -0.1404999941587448, -0.0494999997317791, -0.009399999864399433, -0.07100000232458115, -0.14820000529289246, -0.13950000703334808, -0.07000000029802322, 0.03480000048875809, -0.07580000162124634, 0.05119999870657921, -0.10029999911785126, -0.09319999814033508, 0.18940000236034393], [-0.059700001031160355, 0.08659999817609787, -0.026499999687075615, 0.047600001096725464, 0.08980000019073486, -0.00419999985024333, -0.10100000351667404, -0.056299999356269836, -0.1882999986410141, -0.31459999084472656, 0.23109999299049377, 0.23520000278949738, -0.19699999690055847, -0.16140000522136688, 0.012400000356137753, -0.04960000142455101, 0.15880000591278076, -0.026900000870227814, -0.1136000007390976, -0.043299999088048935, -0.10029999911785126, 0.10300000011920929, -0.26249998807907104, 0.27000001072883606, -0.004000000189989805, 0.14720000326633453, 0.2321999967098236, 0.0357000008225441, 0.05979999899864197, -0.003599999938160181, 0.10279999673366547, -0.08169999718666077, 0.26409998536109924, -0.021199999377131462, -0.032999999821186066, 0.03849999979138374, -0.25290000438690186, 0.07739999890327454, -0.17880000174045563, -0.10649999976158142, -0.3003999888896942, 0.00279999990016222, -0.054499998688697815, 0.0430000014603138, -0.1720000058412552, -0.017400000244379044, -0.06710000336170197, -9.999999747378752e-05, 0.12710000574588776, -0.15489999949932098, -0.00559999980032444, 0.02930000051856041, -0.017500000074505806, -0.10409999638795853, 0.10909999907016754, -0.23720000684261322, 0.10459999740123749, -0.21060000360012054, 0.21449999511241913, -0.01119999960064888, 0.12610000371932983, -0.1664000004529953], [-0.11949999630451202, -0.10530000180006027, -0.23180000483989716, 0.18870000541210175, -0.1808999925851822, -0.0502999983727932, -0.14640000462532043, -0.026499999687075615, -0.07890000194311142, 0.12380000203847885, 0.06889999657869339, 0.25519999861717224, -0.05209999904036522, -0.05490000173449516, -0.061400000005960464, -0.1923999935388565, 0.011500000022351742, -0.016699999570846558, -0.10450000315904617, 0.16580000519752502, -0.03009999915957451, -0.3653999865055084, -0.06610000133514404, 0.16869999468326569, 0.033399999141693115, 0.0035000001080334187, -0.19300000369548798, -0.06350000202655792, 0.03530000150203705, -0.10989999771118164, -0.05550000071525574, 0.0430000014603138, 0.17820000648498535, -0.1597999930381775, 0.03240000084042549, 0.031300000846385956, 0.23520000278949738, -0.11599999666213989, 0.12759999930858612, 0.1062999963760376, 0.02280000038444996, -0.0722000002861023, 0.010300000198185444, -0.06019999831914902, 0.03550000116229057, 0.14339999854564667, -0.10620000213384628, -0.029200000688433647, 0.12280000001192093, 0.022199999541044235, -0.2806999981403351, 0.17870000004768372, -0.012299999594688416, -0.02500000037252903, 0.1599999964237213, 0.13169999420642853, -0.3921999931335449, 0.243599995970726, 0.012600000016391277, 0.02669999934732914, 0.05310000106692314, -0.06689999997615814], [-0.21199999749660492, 0.20469999313354492, 0.031700000166893005, 0.01759999990463257, 0.07649999856948853, -0.1565999984741211, -0.19259999692440033, -0.13650000095367432, -0.022600000724196434, 0.07159999758005142, -0.10679999738931656, -0.007199999876320362, -0.1340000033378601, -0.02070000022649765, -0.1809999942779541, 0.07190000265836716, -0.16009999811649323, 0.20909999310970306, -0.07360000163316727, 0.00800000037997961, 0.09749999642372131, 0.06769999861717224, 0.11670000106096268, 0.048700001090765, 0.11890000104904175, 0.11869999766349792, 0.11540000140666962, -0.02969999983906746, 0.13249999284744263, 0.12770000100135803, -0.24220000207424164, -0.08060000091791153, -0.03709999844431877, 0.06379999965429306, -0.03180000185966492, 0.07829999923706055, 0.000699999975040555, 0.14249999821186066, 0.12060000002384186, -0.1574999988079071, 0.015399999916553497, 0.09860000014305115, -0.16110000014305115, 0.032099999487400055, 0.1728000044822693, 0.10930000245571136, -0.1746000051498413, 0.21369999647140503, 0.14159999787807465, -0.18129999935626984, -0.023800000548362732, -0.020899999886751175, 0.2985999882221222, -0.28360000252723694, -0.038600001484155655, 0.1023000031709671, 0.27549999952316284, 0.17020000517368317, -0.29190000891685486, 0.06019999831914902, -0.07190000265836716, -0.12349999696016312], [0.10419999808073044, -0.10849999636411667, 0.11620000004768372, 0.017999999225139618, 0.10530000180006027, 0.09640000015497208, -0.2354000061750412, 0.07959999889135361, -0.018400000408291817, -0.03819999843835831, -0.0786999985575676, -0.030899999663233757, -0.024299999698996544, -0.07620000094175339, 0.018699999898672104, 0.4422000050544739, -0.09780000150203705, -0.16369999945163727, -0.027799999341368675, 0.08089999854564667, -0.05130000039935112, -0.16779999434947968, 0.041999999433755875, -0.10090000182390213, -0.03660000115633011, 0.09120000153779984, -0.13230000436306, -0.07739999890327454, 0.148499995470047, -0.025200000032782555, 0.07509999722242355, -0.054999999701976776, -0.0364999994635582, -0.05689999833703041, -0.10899999737739563, 0.10350000113248825, 0.03669999912381172, 0.04529999941587448, -0.014499999582767487, -0.15469999611377716, -0.026799999177455902, -0.07919999957084656, -0.24289999902248383, -0.2378000020980835, -0.04520000144839287, -0.1185000017285347, 0.10220000147819519, -0.10849999636411667, 0.16519999504089355, -0.21780000627040863, -0.1200999990105629, -0.07840000092983246, -0.03999999910593033, -0.13040000200271606, 0.04919999837875366, -0.11270000040531158, -0.012500000186264515, -0.2883000075817108, -0.013799999840557575, 0.062300000339746475, 0.23520000278949738, 0.14499999582767487], [-0.12970000505447388, 0.12630000710487366, 0.14259999990463257, -0.06790000200271606, -0.1014999970793724, -0.23749999701976776, -0.18960000574588776, 0.13410000503063202, -0.1809999942779541, -0.2337000072002411, -0.04280000180006027, -0.062199998646974564, -0.0340999998152256, 0.26089999079704285, -0.1216999962925911, -0.08139999955892563, -0.19850000739097595, -0.1704999953508377, 0.009499999694526196, -0.011699999682605267, 0.13899999856948853, 0.2705000042915344, -0.09560000151395798, 0.36410000920295715, 0.3806000053882599, -0.10199999809265137, -0.24369999766349792, 0.03519999980926514, 0.20360000431537628, -0.08940000087022781, -0.24490000307559967, 0.002199999988079071, -0.08489999920129776, 0.0989999994635582, 0.1597999930381775, 0.12729999423027039, -0.2303999960422516, 0.24869999289512634, 0.04349999874830246, -0.09430000185966492, -0.11819999665021896, 0.17810000479221344, -0.15870000422000885, -0.059700001031160355, 0.12380000203847885, -0.387800008058548, -0.24369999766349792, 0.1103999987244606, -0.09130000323057175, -0.13699999451637268, -0.14499999582767487, -0.18240000307559967, -0.3702000081539154, 0.0640999972820282, 0.24699999392032623, -0.06960000097751617, 0.23589999973773956, 0.0803999975323677, 0.05660000070929527, -0.04050000011920929, 0.09269999712705612, -0.11860000342130661], [0.14429999887943268, -0.299699991941452, -0.3312000036239624, -0.032600000500679016, 0.1736000031232834, 0.13099999725818634, -0.05180000141263008, 0.09700000286102295, 0.12630000710487366, -0.016100000590085983, -0.0934000015258789, -0.19619999825954437, -0.07599999755620956, 0.030899999663233757, -0.0272000003606081, 0.1535000056028366, 0.4487999975681305, 0.2745000123977661, 0.060600001364946365, -0.07900000363588333, -0.032999999821186066, -0.2818000018596649, 0.03759999945759773, 0.026900000870227814, -0.250900000333786, -0.025699999183416367, 0.0934000015258789, -0.11710000038146973, -0.18559999763965607, -0.2298000007867813, 0.019200000911951065, 0.05220000073313713, -0.12489999830722809, -0.11940000206232071, 0.2793000042438507, 0.027699999511241913, 0.16089999675750732, -0.16979999840259552, 0.17419999837875366, 0.0729999989271164, -0.05920000001788139, 0.0364999994635582, 0.11540000140666962, -0.021900000050663948, 0.06539999693632126, 0.19760000705718994, 0.13050000369548798, 0.09009999781847, -0.10209999978542328, -0.14589999616146088, 0.07209999859333038, 0.11550000309944153, -0.037300001829862595, 0.17149999737739563, -0.07599999755620956, -0.004900000058114529, -0.0333000011742115, -0.2475000023841858, -0.050700001418590546, -0.35850000381469727, -0.23639999330043793, 0.08619999885559082], [0.15289999544620514, -0.1834000051021576, 0.0997999981045723, -0.00279999990016222, -0.042100001126527786, -0.0010000000474974513, 0.13079999387264252, 0.04010000079870224, -0.16609999537467957, -0.1923999935388565, 0.21130000054836273, -0.15199999511241913, -0.055399999022483826, 0.32690000534057617, 0.26579999923706055, -0.02239999920129776, 0.024800000712275505, -0.010499999858438969, -0.010400000028312206, -0.15569999814033508, -0.19280000030994415, 0.1388999968767166, 0.11590000241994858, -0.004999999888241291, 0.17309999465942383, 0.3393999934196472, -0.0010999999940395355, 0.07159999758005142, 0.0877000018954277, -0.1559000015258789, 0.2459000051021576, 0.16500000655651093, 0.21070000529289246, -0.133200004696846, -0.007699999958276749, -0.017799999564886093, -0.1062999963760376, -0.1257999986410141, 0.15410000085830688, -0.04170000180602074, -0.017500000074505806, 0.1251000016927719, 0.16300000250339508, 0.06210000067949295, 0.12479999661445618, 0.07720000296831131, -0.19099999964237213, -0.07100000232458115, 0.2847000062465668, 0.11100000143051147, -0.1467999964952469, -0.12359999865293503, -0.021700000390410423, -0.13169999420642853, 0.060100000351667404, 0.10249999910593033, 0.03889999911189079, -0.1404999941587448, -0.0210999995470047, 0.10939999669790268, -0.07119999825954437, -0.03620000183582306], [-0.1753000020980835, 0.3176000118255615, 0.1080000028014183, 0.0012000000569969416, -0.21379999816417694, -0.03460000082850456, 0.06780000030994415, -0.1265999972820282, -0.23109999299049377, 0.04320000112056732, 0.08940000087022781, -0.18379999697208405, -0.10080000013113022, -0.1371999979019165, 0.05810000002384186, -0.16349999606609344, -0.02160000056028366, -0.08959999680519104, -0.11100000143051147, -0.009499999694526196, 0.259799987077713, 0.08829999715089798, -0.01730000041425228, 0.020099999383091927, 0.19030000269412994, 0.08209999650716782, -0.11270000040531158, -0.34950000047683716, 0.23149999976158142, -0.07720000296831131, 0.00839999970048666, 0.11800000071525574, 0.0003000000142492354, 0.15539999306201935, -0.10970000177621841, 0.2678999900817871, -0.3043999969959259, 0.02239999920129776, -0.14470000565052032, 0.03009999915957451, -0.3100000023841858, 0.13830000162124634, -0.08460000157356262, -0.07440000027418137, 0.10050000250339508, -0.25589999556541443, 0.053199999034404755, -0.019200000911951065, -0.16359999775886536, -0.0015999999595806003, 0.04190000146627426, -0.1281999945640564, -0.09799999743700027, -0.06970000267028809, -0.120899997651577, 0.17010000348091125, 0.07339999824762344, -0.26759999990463257, -0.2071000039577484, 0.052000001072883606, 0.09650000184774399, -0.3488999903202057], [0.1436000019311905, 0.1678999960422516, 0.08259999752044678, 0.04780000075697899, -0.07320000231266022, -0.09759999811649323, -0.05260000005364418, 0.06040000170469284, 0.053199999034404755, -0.07779999822378159, -0.2619999945163727, 0.012299999594688416, 0.10790000110864639, -0.025699999183416367, -0.029999999329447746, 0.2029000073671341, 0.2418999969959259, -0.15129999816417694, -0.15569999814033508, 0.17100000381469727, -0.11580000072717667, -0.04309999942779541, 0.051899999380111694, -0.04320000112056732, -0.11349999904632568, 0.19740000367164612, -0.18860000371932983, 0.019899999722838402, 0.013299999758601189, -0.008500000461935997, -0.06710000336170197, 0.023800000548362732, 0.2223999947309494, -0.042500000447034836, -0.07569999992847443, -0.052799999713897705, 0.2329999953508377, -0.21610000729560852, 0.015399999916553497, 0.07760000228881836, -0.04520000144839287, -0.00430000014603138, 0.006000000052154064, 0.14390000700950623, -0.016499999910593033, 0.26249998807907104, -0.043699998408555984, 0.06909999996423721, -0.3693999946117401, -0.1339000016450882, 0.218299999833107, 0.0052999998442828655, -0.13259999454021454, -0.046799998730421066, -0.04019999876618385, -0.09189999848604202, 0.13850000500679016, 0.09319999814033508, 0.06949999928474426, -0.031199999153614044, -0.08290000259876251, 0.11389999836683273], [0.19689999520778656, 0.010400000028312206, -0.3001999855041504, -0.0013000000035390258, 0.2874999940395355, 0.051600001752376556, -0.03750000149011612, 0.05590000003576279, 0.2653000056743622, 0.0568000003695488, 0.10819999873638153, -0.2757999897003174, 0.1378999948501587, -0.16779999434947968, 0.02319999970495701, 0.12960000336170197, 0.14000000059604645, 0.05079999938607216, 0.05689999833703041, 0.016599999740719795, -0.289900004863739, 0.2540000081062317, 0.14630000293254852, 0.033900000154972076, -0.05869999900460243, -0.15530000627040863, 0.0066999997943639755, -0.26159998774528503, -0.2515000104904175, -0.2150000035762787, 0.007300000172108412, 0.05009999871253967, 0.010599999688565731, -0.26899999380111694, 0.2572999894618988, -0.06340000033378601, 0.30649998784065247, -0.2531000077724457, 0.19920000433921814, 0.16200000047683716, 0.15539999306201935, -0.32269999384880066, 0.20589999854564667, 0.20819999277591705, -0.06480000168085098, -0.07890000194311142, 0.14980000257492065, -0.09390000253915787, -0.0333000011742115, 0.066600002348423, 0.050599999725818634, 0.02810000069439411, 0.18860000371932983, -0.3296000063419342, -0.2865999937057495, -0.12359999865293503, -0.40709999203681946, 0.11240000277757645, 0.06539999693632126, -0.07909999787807465, 0.0649000033736229, 0.05739999935030937], [-0.00139999995008111, 0.026599999517202377, 0.08049999922513962, -0.17339999973773956, -0.019899999722838402, 0.16449999809265137, -0.10249999910593033, 0.09709999710321426, 0.21070000529289246, -0.0203000009059906, -0.07490000128746033, 0.1151999980211258, -0.4131999909877777, 0.01810000091791153, -0.10329999774694443, -0.1379999965429306, 0.30320000648498535, 0.0044999998062849045, -0.0012000000569969416, -0.1340000033378601, -0.17640000581741333, 0.11169999837875366, -0.210999995470047, -0.18979999423027039, 0.16699999570846558, -0.03060000017285347, 0.01269999984651804, -0.02160000056028366, -0.06520000100135803, 0.05460000038146973, 0.12549999356269836, 0.2386000007390976, -0.0203000009059906, -0.04809999838471413, 0.1923000067472458, 0.06419999897480011, 0.12240000069141388, -0.1923000067472458, 0.02239999920129776, 0.21199999749660492, 0.1785999983549118, -0.17080000042915344, 0.11270000040531158, -0.04259999841451645, 0.12460000067949295, -0.04280000180006027, 0.008100000210106373, -0.11940000206232071, 0.014700000174343586, -0.08460000157356262, 0.05460000038146973, 0.028200000524520874, 0.07159999758005142, 0.0746999979019165, -0.07509999722242355, 0.04879999905824661, 0.0019000000320374966, 0.09679999947547913, 0.04729999974370003, 0.06040000170469284, 0.1005999967455864, 0.1923999935388565], [-0.17260000109672546, 0.03180000185966492, 0.09229999780654907, 0.027899999171495438, -0.12610000371932983, 0.017799999564886093, 0.10090000182390213, -0.15770000219345093, -0.07169999927282333, 0.179299995303154, 0.04520000144839287, 0.07199999690055847, -0.09679999947547913, 0.05040000006556511, 0.17890000343322754, -0.08330000191926956, 0.10649999976158142, -0.00839999970048666, -0.05530000105500221, -0.07280000299215317, -0.01209999993443489, -0.060100000351667404, 0.11129999905824661, 0.17669999599456787, -0.18080000579357147, 0.05310000106692314, -0.2897999882698059, 0.24639999866485596, -0.05000000074505806, 0.06300000101327896, 0.30959999561309814, -0.12439999729394913, -0.319599986076355, -0.16859999299049377, 0.1128000020980835, -0.021400000900030136, -0.26350000500679016, 0.041200000792741776, 0.20499999821186066, -0.16910000145435333, -0.04149999842047691, -0.18770000338554382, -0.048500001430511475, -0.17949999868869781, 0.01119999960064888, -0.11749999970197678, 0.05040000006556511, 0.054999999701976776, 0.002300000051036477, -0.015599999576807022, 0.09889999777078629, 0.12200000137090683, -0.029999999329447746, -0.22190000116825104, 0.08799999952316284, -0.030400000512599945, 0.0746999979019165, 0.3391000032424927, 0.13590000569820404, 0.14110000431537628, 0.01140000019222498, -0.2978000044822693], [0.06159999966621399, 0.017500000074505806, 0.31630000472068787, -0.06199999898672104, 0.0017999999690800905, 0.2386000007390976, 0.05400000140070915, 0.26420000195503235, -0.10080000013113022, -0.11020000278949738, 0.28369998931884766, 0.05270000174641609, -0.03739999979734421, -0.03929999843239784, -0.025800000876188278, -0.07940000295639038, -0.09610000252723694, -0.03370000049471855, -0.21040000021457672, 0.17980000376701355, -0.061799999326467514, -0.1145000010728836, 0.09889999777078629, 0.21040000021457672, -0.04580000042915344, -0.1054999977350235, -0.12759999930858612, -0.20309999585151672, 0.03830000013113022, 0.08269999921321869, 0.1111999973654747, -0.09049999713897705, -0.34380000829696655, -0.03060000017285347, -0.1265999972820282, 0.07270000129938126, -0.19460000097751617, -0.08540000021457672, 0.1527000069618225, 0.07320000231266022, 0.23729999363422394, 0.09790000319480896, 0.16519999504089355, 0.13169999420642853, -0.25839999318122864, 0.06700000166893005, 0.13989999890327454, -0.15060000121593475, 0.08940000087022781, 0.05889999866485596, -0.04800000041723251, 0.013500000350177288, 0.0778999999165535, -0.1160999983549118, -0.053300000727176666, 0.4115999937057495, 0.058400001376867294, 0.06080000102519989, 0.17550000548362732, 0.04659999907016754, -0.05979999899864197, 0.01360000018030405], [-0.13410000503063202, 0.1421000063419342, -0.20100000500679016, 0.014000000432133675, -0.00800000037997961, -0.11429999768733978, -0.020899999886751175, -0.08179999887943268, 0.22290000319480896, -0.28060001134872437, 0.2621999979019165, -0.0284000001847744, -0.07370000332593918, -0.06560000032186508, 0.1949000060558319, 0.1899999976158142, -0.21649999916553497, -0.08940000087022781, 0.19660000503063202, -0.15790000557899475, 0.010099999606609344, -0.11389999836683273, -0.15240000188350677, 0.022299999371170998, -0.1412999927997589, -0.024000000208616257, -0.003599999938160181, 0.10869999974966049, 0.31779998540878296, -0.1251000016927719, 0.07609999924898148, 0.1712000072002411, </t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>[0.7584569348445777]</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>[0.05513622108660621]</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>[0.6948476159480901]</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>[0.06966728741620294]</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>[-5.542669764851375]</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>[2.141282962140738]</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>[0.5602018681861396]</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>[0.10103001921844783]</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>[0.9024409909690096]</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>[0.0231371947872179]</t>
+        </is>
+      </c>
+      <c r="O41" t="inlineStr">
+        <is>
+          <t>[-1.4670388817204238]</t>
+        </is>
+      </c>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>[0.8110327256488199]</t>
+        </is>
+      </c>
+      <c r="Q41" t="inlineStr">
+        <is>
+          <t>[-0.2571285807015531]</t>
+        </is>
+      </c>
+      <c r="R41" t="inlineStr">
+        <is>
+          <t>[0.13555080567357336]</t>
+        </is>
+      </c>
+      <c r="S41" t="inlineStr">
+        <is>
+          <t>[-0.28309499447837694]</t>
+        </is>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>[0.10811402017822914]</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>[-1.349902124684283]</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>[0.2247049977164815]</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>[-0.3851315780629354]</t>
+        </is>
+      </c>
+      <c r="X41" t="inlineStr">
+        <is>
+          <t>[0.1451072478226148]</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>[-0.3853904685938194]</t>
+        </is>
+      </c>
+      <c r="Z41" t="inlineStr">
+        <is>
+          <t>[0.11400822835115104]</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>[-1.6232670006470502]</t>
+        </is>
+      </c>
+      <c r="AB41" t="inlineStr">
+        <is>
+          <t>[0.2413520391354517]</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>[-1.0995411013512912]</t>
+        </is>
+      </c>
+      <c r="AD41" t="inlineStr">
+        <is>
+          <t>[0.1759330860652126]</t>
+        </is>
+      </c>
+      <c r="AE41" t="inlineStr">
+        <is>
+          <t>[-0.9530926868969205]</t>
+        </is>
+      </c>
+      <c r="AF41" t="inlineStr">
+        <is>
+          <t>[0.21030525903369626]</t>
+        </is>
+      </c>
+      <c r="AG41" t="inlineStr">
+        <is>
+          <t>[-3.3450463905266057]</t>
+        </is>
+      </c>
+      <c r="AH41" t="inlineStr">
+        <is>
+          <t>[0.3234885232517763]</t>
+        </is>
+      </c>
+      <c r="AI41" t="inlineStr">
+        <is>
+          <t>[-1.543505969372632]</t>
+        </is>
+      </c>
+      <c r="AJ41" t="inlineStr">
+        <is>
+          <t>[0.20843748272347218]</t>
+        </is>
+      </c>
+      <c r="AK41" t="inlineStr">
+        <is>
+          <t>[-0.9722971805103775]</t>
+        </is>
+      </c>
+      <c r="AL41" t="inlineStr">
+        <is>
+          <t>[0.20934489540422396]</t>
+        </is>
+      </c>
+      <c r="AM41" t="inlineStr">
+        <is>
+          <t>[-3.355523034496806]</t>
+        </is>
+      </c>
+      <c r="AN41" t="inlineStr">
+        <is>
+          <t>[0.33453574486629467]</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>model_128_64_32_0</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>[128, 64, 32]</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>[[[0.03319999948143959, 0.0027000000700354576, -0.016699999570846558, -0.0017999999690800905, 0.12229999899864197, -0.014700000174343586, -0.04670000076293945, -0.05999999865889549, -0.0005000000237487257, -0.16120000183582306, -0.057500001043081284, -0.03150000050663948, 0.04129999876022339, 0.027000000700354576, -0.054999999701976776, 0.0066999997943639755, 0.0007999999797903001, 0.059300001710653305, 0.00139999995008111, -0.021199999377131462, 0.06199999898672104, 0.042500000447034836, 0.11349999904632568, 0.019600000232458115, 0.05620000138878822, -0.0026000000070780516, -0.029600000008940697, 0.05090000107884407, -0.008500000461935997, 0.039400000125169754, 0.014999999664723873, 0.01720000058412552, 0.03959999978542328, 0.014700000174343586, 0.010400000028312206, 0.060499999672174454, -0.015599999576807022, -0.013299999758601189, 0.07540000230073929, -0.02539999969303608, 0.0722000002861023, -0.014800000004470348, -0.05270000174641609, 0.08399999886751175, -0.05649999901652336, 0.015200000256299973, -0.012799999676644802, -0.015799999237060547, 0.018699999898672104, 0.006300000008195639, -0.03020000085234642, 0.09740000218153, 0.07370000332593918, 0.02070000022649765, 0.014800000004470348, -0.029400000348687172, -0.04830000177025795, 0.004000000189989805, -0.07289999723434448, -0.042399998754262924, 0.0008999999845400453, -0.04740000143647194, -0.061400000005960464, -0.007499999832361937, 0.02319999970495701, -0.028599999845027924, 0.02879999950528145, 0.014399999752640724, 0.1039000004529953, -0.06560000032186508, -0.04690000042319298, -0.0005000000237487257, 0.03680000081658363, 0.04340000078082085, -0.10540000349283218, -0.03840000182390213, 0.014999999664723873, 0.025499999523162842, 0.006800000090152025, -0.04230000078678131, 0.03500000014901161, 0.0035000001080334187, 0.019099999219179153, 0.00019999999494757503, 0.05869999900460243, -0.0035000001080334187, -0.053300000727176666, 0.043800000101327896, 0.01119999960064888, -0.0010000000474974513, -0.04439999908208847, -0.06549999862909317, -0.08110000193119049, 0.02759999968111515, 0.018699999898672104, -0.0010000000474974513, 0.026200000196695328, -0.006500000134110451, 0.04010000079870224, -0.0892999991774559, 0.002899999963119626, -0.04540000110864639, -0.14000000059604645, -0.05000000074505806, 0.06949999928474426, -0.03139999881386757, -0.013700000010430813, 0.04580000042915344, -0.007899999618530273, -0.011300000362098217, 0.08389999717473984, 0.03620000183582306, -0.05420000106096268, -0.022199999541044235, 0.049800001084804535, -0.024900000542402267, 0.020400000736117363, 0.026799999177455902, 0.014800000004470348, 0.08070000261068344, -0.02410000003874302, -0.044199999421834946, 0.03819999843835831, -0.003000000026077032, 0.043299999088048935, 0.05959999933838844, 0.021199999377131462, 0.024399999529123306], [0.0357000008225441, -0.05339999869465828, -0.034299999475479126, 0.01360000018030405, -0.08009999990463257, -0.0008999999845400453, 0.02239999920129776, 0.03480000048875809, -0.005799999926239252, -0.03189999982714653, 0.019099999219179153, -0.014800000004470348, -0.019500000402331352, -0.07180000096559525, -0.01759999990463257, -0.07119999825954437, -0.01979999989271164, -0.029600000008940697, -0.07909999787807465, -0.01360000018030405, 0.005400000140070915, -0.03790000081062317, 0.042899999767541885, -0.039799999445676804, -0.1054999977350235, -0.052000001072883606, 0.06800000369548798, -0.05739999935030937, 0.04529999941587448, -0.02500000037252903, 0.01940000057220459, -0.011699999682605267, -0.09629999846220016, -0.03460000082850456, 0.05469999834895134, 0.002400000113993883, 0.007600000128149986, -0.04659999907016754, 0.0038999998942017555, 0.01899999938905239, 0.052400000393390656, -0.0010000000474974513, 0.06689999997615814, -0.014499999582767487, -0.10840000212192535, -0.05849999934434891, 0.09889999777078629, -0.04019999876618385, 0.06459999829530716, -0.047200001776218414, -0.042100001126527786, 0.09960000216960907, -0.04879999905824661, 0.062199998646974564, -0.0142000000923872, -0.029100000858306885, 0.007499999832361937, -0.029999999329447746, 0.06840000301599503, 0.028300000354647636, 0.042500000447034836, -0.03099999949336052, 0.009100000374019146, 0.030899999663233757, 0.02329999953508377, 0.03020000085234642, 0.021199999377131462, 0.015599999576807022, 0.05490000173449516, -0.0215000007301569, 0.016899999231100082, -0.005799999926239252, -0.025299999862909317, 0.05999999865889549, -0.01979999989271164, -0.015300000086426735, -0.0494999997317791, -0.12300000339746475, -0.042500000447034836, 0.048900000751018524, 0.048700001090765, -0.04639999940991402, 0.010999999940395355, -0.08259999752044678, 0.03849999979138374, -0.04430000111460686, -0.007300000172108412, 0.056299999356269836, -0.057999998331069946, -0.07970000058412552, 0.005200000014156103, -0.01979999989271164, -0.049300000071525574, 0.04690000042319298, -0.10719999670982361, -0.04580000042915344, -0.0003000000142492354, -0.09889999777078629, -0.0333000011742115, -0.04740000143647194, 0.02019999921321869, 0.04360000044107437, -0.009200000204145908, -0.05260000005364418, -0.03550000116229057, -0.011099999770522118, 0.007499999832361937, -0.014100000262260437, 0.04490000009536743, 0.042399998754262924, -0.01510000042617321, -0.06759999692440033, -0.02370000071823597, -0.08839999884366989, 0.010200000368058681, -0.04010000079870224, 0.0008999999845400453, 0.04859999939799309, -0.057100001722574234, 0.005499999970197678, 0.03629999980330467, -0.09080000221729279, 0.032099999487400055, -0.02019999921321869, 0.002099999925121665, 0.0031999999191612005, -0.08340000361204147, -0.07880000025033951]], [[0.05609999969601631, -0.02930000051856041, -0.0027000000700354576, -0.029899999499320984, -0.21469999849796295, -0.0738999992609024, 0.08550000190734863, 0.05510000139474869, -0.06159999966621399, -0.04010000079870224, -0.027899999171495438, 0.00839999970048666, 0.0414000004529953, 0.10440000146627426, 0.07500000298023224, 0.0737999975681305, -0.02459999918937683, -0.15070000290870667, -0.01489999983459711, -0.045099999755620956, 0.03759999945759773, -0.12110000103712082, 0.12399999797344208, -0.05460000038146973, -0.019200000911951065, -0.02500000037252903, -0.016300000250339508, 0.10379999876022339, -0.05350000038743019, 0.029600000008940697, 0.06539999693632126, -0.05000000074505806, 0.005400000140070915, 0.009399999864399433, 0.059700001031160355, 0.17720000445842743, -0.06669999659061432, 0.00139999995008111, 0.04659999907016754, 0.19920000433921814, -0.07850000262260437, 0.00139999995008111, -0.16060000658035278, 0.08640000224113464, -0.07859999686479568, -0.14650000631809235, 0.0478999987244606, -0.05350000038743019, 0.02449999935925007, -0.04439999908208847, -0.05260000005364418, 0.05909999832510948, 0.03280000016093254, 0.08169999718666077, 0.12200000137090683, 0.0869000032544136, 0.033799998462200165, 0.052000001072883606, 0.027499999850988388, -0.015200000256299973, 0.022700000554323196, -0.05570000037550926, -0.054499998688697815, 0.13439999520778656, -0.011599999852478504, -0.10360000282526016, -0.010700000450015068, -0.011800000444054604, 0.037300001829862595, -0.023399999365210533, 0.13850000500679016, -0.030500000342726707, 0.17149999737739563, -0.25189998745918274, 0.08020000159740448, -0.04690000042319298, 0.06019999831914902, 0.16740000247955322, -0.045499999076128006, -0.01730000041425228, -0.02329999953508377, -0.05999999865889549, -0.02370000071823597, 0.03359999880194664, -0.15690000355243683, -0.020800000056624413, 0.10830000042915344, 0.12049999833106995, 0.15219999849796295, -0.04729999974370003, -0.02160000056028366, 0.18870000541210175, 0.1080000028014183, -0.1898999959230423, 0.051500000059604645, -0.10999999940395355, 0.15039999783039093, 0.0071000000461936, 0.05849999934434891, 0.01269999984651804, 0.054099999368190765, -0.01899999938905239, -0.031599998474121094, 0.12370000034570694, 0.12770000100135803, 0.035599999129772186, -0.01209999993443489, -0.0982000008225441, 0.04650000110268593, -0.01810000091791153, -0.1315000057220459, -0.14399999380111694, -0.11389999836683273, 0.02239999920129776, 0.08070000261068344, 0.15369999408721924, -0.09510000050067902, -0.010700000450015068, 0.08959999680519104, -0.009100000374019146, -0.06239999830722809, 0.051899999380111694, -0.14839999377727509, -0.0723000019788742, -0.03819999843835831, 0.1396999955177307, -0.10970000177621841, 0.08609999716281891], [0.01889999955892563, -0.02800000086426735, 0.10790000110864639, -0.13830000162124634, 0.14730000495910645, 0.19760000705718994, 0.09759999811649323, 0.03799999877810478, 0.04039999842643738, -0.08940000087022781, 0.002899999963119626, -0.03700000047683716, -0.1492999941110611, -0.00039999998989515007, -0.0778999999165535, -0.03680000081658363, -0.006000000052154064, 0.02410000003874302, 0.029400000348687172, -0.07240000367164612, 0.12849999964237213, 0.07289999723434448, 0.0869000032544136, 0.13210000097751617, 0.11670000106096268, 0.08569999784231186, -0.025699999183416367, 0.020500000566244125, -0.09870000183582306, -0.01769999973475933, 0.012000000104308128, 0.07100000232458115, -0.09510000050067902, -0.023000000044703484, -0.031099999323487282, 0.12060000002384186, 0.10109999775886536, -0.03220000118017197, 0.01889999955892563, 0.2222999930381775, 0.01979999989271164, 0.014999999664723873, -0.09989999979734421, 0.08009999990463257, -0.0674000009894371, -0.13519999384880066, 0.15800000727176666, 0.05820000171661377, 0.04969999939203262, 0.055399999022483826, 0.08070000261068344, -0.156700000166893, 0.056299999356269836, 0.06759999692440033, -0.07109999656677246, -0.1257999986410141, 0.08529999852180481, 0.023000000044703484, 0.035100001841783524, -0.08179999887943268, 0.15000000596046448, 0.04809999838471413, 0.09380000084638596, 0.06319999694824219, 0.0024999999441206455, 0.02290000021457672, -0.16429999470710754, 0.061000000685453415, 0.018400000408291817, 0.008299999870359898, 0.008200000040233135, -0.18289999663829803, 0.09309999644756317, -0.06859999895095825, 0.012400000356137753, -0.002300000051036477, 0.13490000367164612, -0.1657000035047531, 0.10260000079870224, 0.05299999937415123, -0.11869999766349792, 0.10620000213384628, -0.09359999746084213, 0.058800000697374344, 0.22190000116825104, 0.028599999845027924, 0.05649999901652336, -0.03310000151395798, -0.03660000115633011, -0.1324000060558319, -0.0357000008225441, -0.07410000264644623, -0.17309999465942383, 0.019600000232458115, -0.01979999989271164, -0.13750000298023224, -0.00839999970048666, -0.12080000340938568, 0.009200000204145908, -0.003700000001117587, 0.03189999982714653, 0.029400000348687172, 0.13609999418258667, -0.10429999977350235, 0.000699999975040555, 0.018699999898672104, 0.04650000110268593, -0.036400001496076584, -0.059300001710653305, -0.11720000207424164, -0.12680000066757202, 0.04740000143647194, -0.10339999943971634, -0.09520000219345093, -0.13339999318122864, 0.041099999099969864, -0.06019999831914902, -0.09860000014305115, 0.10599999874830246, -0.014600000344216824, 0.019500000402331352, -0.02419999986886978, 0.06729999929666519, 0.05909999832510948, 0.15690000355243683, 0.007799999788403511, 0.05420000106096268, 0.030799999833106995], [0.056699998676776886, 0.015300000086426735, -0.004399999976158142, -0.07400000095367432, -0.1655000001192093, 0.24269999563694, 0.001500000013038516, -0.0640999972820282, -0.05570000037550926, 0.06270000338554382, -0.043699998408555984, 0.09099999815225601, 0.09189999848604202, -0.09369999915361404, 0.08540000021457672, -0.020500000566244125, 0.12080000340938568, 0.14480000734329224, 0.09960000216960907, 0.03999999910593033, 0.1671999990940094, 0.05460000038146973, 0.0364999994635582, 0.025200000032782555, -0.1509999930858612, -0.0697999969124794, -0.08950000256299973, 0.1256999969482422, -0.11680000275373459, 0.04740000143647194, 0.19760000705718994, -0.09480000287294388, -0.12290000170469284, 0.13120000064373016, 0.11760000139474869, -0.1348000019788742, -0.17919999361038208, 0.08340000361204147, -0.0035000001080334187, -0.006599999964237213, -0.0019000000320374966, 0.013100000098347664, -0.14900000393390656, -0.023399999365210533, 0.051899999380111694, 0.07069999724626541, 0.10899999737739563, 0.04410000145435333, 0.13989999890327454, -0.13249999284744263, -0.03370000049471855, -0.026799999177455902, -0.04859999939799309, -0.0142000000923872, 0.04309999942779541, 0.06400000303983688, -0.05860000103712082, 0.03240000084042549, 0.009100000374019146, 0.04170000180602074, -0.03620000183582306, -0.08709999918937683, -0.008899999782443047, -0.1526000052690506, 0.04100000113248825, 0.050200000405311584, 0.003100000089034438, -0.0348999984562397, -0.1655000001192093, -0.16760000586509705, 0.04740000143647194, -0.039799999445676804, 0.029100000858306885, 0.10809999704360962, -0.07329999655485153, -0.06129999831318855, 0.0357000008225441, -0.07180000096559525, 0.10970000177621841, 0.08799999952316284, -0.07199999690055847, 0.005400000140070915, -0.024399999529123306, 0.09149999916553497, -0.04969999939203262, 0.021199999377131462, -0.008500000461935997, 0.03889999911189079, -0.016699999570846558, -0.11349999904632568, -0.1264999955892563, -0.1639000028371811, 0.125900000333786, 0.181099995970726, 0.006599999964237213, -0.1023000031709671, -0.04039999842643738, -0.015599999576807022, -0.03519999980926514, -0.03610000014305115, -0.11339999735355377, -0.12139999866485596, -0.012799999676644802, -0.13249999284744263, -0.018300000578165054, -0.19339999556541443, -0.026000000536441803, -0.05490000173449516, 0.06599999964237213, 0.05139999836683273, -0.048700001090765, -0.17560000717639923, -0.04580000042915344, 0.017500000074505806, -0.004000000189989805, 0.11909999698400497, 0.09730000048875809, 0.015799999237060547, -0.033900000154972076, -0.023000000044703484, -0.0019000000320374966, -0.06260000169277191, 0.023099999874830246, 0.0035000001080334187, -0.12309999763965607, 0.004000000189989805, -0.04910000041127205, -0.03460000082850456], [0.042399998754262924, 0.06880000233650208, -0.02969999983906746, -0.027000000700354576, 0.10620000213384628, -0.009499999694526196, 0.010300000198185444, -0.0071000000461936, -0.011699999682605267, 0.0031999999191612005, -0.1347000002861023, -0.013199999928474426, -0.022299999371170998, -0.013799999840557575, -0.07000000029802322, -0.07079999893903732, 0.15610000491142273, 0.007899999618530273, -0.15129999816417694, -0.04349999874830246, 0.07429999858140945, -0.09679999947547913, -0.07159999758005142, 0.01979999989271164, 0.06520000100135803, 0.09960000216960907, -0.015300000086426735, 0.001500000013038516, 0.16500000655651093, 0.0697999969124794, -0.028200000524520874, -0.15729999542236328, -0.04270000010728836, 0.016899999231100082, -0.045499999076128006, 0.11469999700784683, 0.0215000007301569, 0.07199999690055847, -0.1429000049829483, 0.025299999862909317, 0.016899999231100082, 0.018799999728798866, -0.08410000056028366, -0.13379999995231628, -0.07109999656677246, 0.21469999849796295, 0.039799999445676804, -0.019899999722838402, -0.02199999988079071, 0.12039999663829803, -0.09109999984502792, -0.0575999990105629, 0.04639999940991402, 0.22849999368190765, -0.003800000064074993, 0.14499999582767487, -0.06880000233650208, 0.026499999687075615, 0.06809999793767929, -0.08030000329017639, 0.10570000112056732, 0.05209999904036522, 0.17470000684261322, 0.0812000036239624, 0.018200000748038292, -0.0471000000834465, -0.05260000005364418, -0.02370000071823597, -0.13040000200271606, 0.02969999983906746, 0.07840000092983246, 0.026200000196695328, 0.07779999822378159, 0.06930000334978104, -0.18639999628067017, 0.010599999688565731, -0.034699998795986176, -0.14499999582767487, -0.09920000284910202, 0.0551999993622303, 0.10490000247955322, -0.0868000015616417, 0.009800000116229057, -0.009100000374019146, 0.00930000003427267, 0.10499999672174454, 0.13259999454021454, 0.062300000339746475, 0.13410000503063202, 0.026900000870227814, -0.013899999670684338, -0.04050000011920929, 0.0012000000569969416, -0.0020000000949949026, 0.08070000261068344, -0.039000000804662704, -0.032099999487400055, 0.09470000118017197, 0.07769999653100967, -0.08209999650716782, -0.04010000079870224, 0.10580000281333923, -0.09860000014305115, 0.15219999849796295, -0.13660000264644623, -0.09279999881982803, -0.1396999955177307, -0.13279999792575836, -0.13899999856948853, -0.12120000272989273, 0.09269999712705612, 0.042100001126527786, 0.11349999904632568, 0.13779999315738678, 0.11100000143051147, 0.18029999732971191, -0.0738999992609024, -0.07680000364780426, -0.11410000175237656, -0.10180000215768814, 0.04639999940991402, 0.023399999365210533, -0.03849999979138374, 0.07500000298023224, -0.041099999099969864, 0.03530000150203705, 0.13089999556541443, -0.08659999817609787], [0.08869999647140503, 0.14259999990463257, -0.10450000315904617, 0.049300000071525574, 0.08590000122785568, 0.01590000092983246, -0.16210000216960907, -0.08449999988079071, -0.07020000368356705, -0.057100001722574234, 0.031300000846385956, -0.004399999976158142, -0.03530000150203705, 0.10999999940395355, -0.06729999929666519, -0.04129999876022339, 0.0026000000070780516, -0.1607999950647354, -0.07970000058412552, 0.09510000050067902, -0.02889999933540821, -0.15360000729560852, -0.0006000000284984708, 0.30070000886917114, -0.04910000041127205, -0.019300000742077827, 0.024399999529123306, -0.06780000030994415, -0.08429999649524689, -0.004100000020116568, -0.03420000150799751, -0.0414000004529953, -0.04830000177025795, 0.04039999842643738, -0.04600000008940697, -0.02410000003874302, 0.033900000154972076, -0.019700000062584877, -0.11829999834299088, 0.09099999815225601, -0.10260000079870224, -0.018699999898672104, -0.048700001090765, -0.10409999638795853, 0.02759999968111515, -0.03189999982714653, -0.008500000461935997, -0.1242000013589859, -0.013399999588727951, 0.19140000641345978, 0.13269999623298645, -0.04399999976158142, 0.03480000048875809, -0.06750000268220901, 0.13940000534057617, -0.1356000006198883, 0.14429999887943268, -0.094200000166893, -0.06469999998807907, 0.018699999898672104, 0.05999999865889549, 0.07370000332593918, -0.07079999893903732, -0.08089999854564667, -0.011800000444054604, -0.020600000396370888, -0.19030000269412994, -0.02410000003874302, 0.16990000009536743, -0.025200000032782555, -0.09080000221729279, 0.04280000180006027, 0.02879999950528145, -0.11550000309944153, 0.0723000019788742, -0.0544000007212162, -0.05609999969601631, 0.0771000012755394, 0.03799999877810478, 0.012500000186264515, 0.09799999743700027, -0.03550000116229057, -0.0908999964594841, -0.016899999231100082, -0.040699999779462814, -0.007499999832361937, -0.14239999651908875, -0.05700000002980232, -0.029600000008940697, -0.0632999986410141, 0.01889999955892563, -0.08020000159740448, -0.010499999858438969, 0.09610000252723694, 0.05420000106096268, -0.07370000332593918, -0.11980000138282776, 0.023399999365210533, 0.07729999721050262, 0.20100000500679016, 0.006200000178068876, -0.027699999511241913, -0.11029999703168869, -0.03849999979138374, 0.02759999968111515, -0.2354000061750412, 0.014399999752640724, -0.07050000131130219, -0.034699998795986176, 0.0729999989271164, 0.07339999824762344, -0.1784999966621399, -0.017899999395012856, 0.08540000021457672, 0.04179999977350235, -0.002300000051036477, -0.02710000053048134, -0.07829999923706055, -0.13920000195503235, -0.03400000184774399, 0.06080000102519989, 0.09399999678134918, 0.06469999998807907, 0.029500000178813934, -0.12319999933242798, -0.08749999850988388, -0.14079999923706055, 0.1615000069141388], [-0.01899999938905239, 0.12219999730587006, -0.05620000138878822, -0.1882999986410141, -0.11219999939203262, -0.10580000281333923, 0.010099999606609344, 0.06040000170469284, -0.16300000250339508, -0.006399999838322401, -0.05820000171661377, -0.006099999882280827, -0.06210000067949295, 0.07339999824762344, -0.03970000147819519, 0.18250000476837158, -0.05979999899864197, 0.027699999511241913, -0.1370999962091446, 0.02500000037252903, -0.09399999678134918, -0.18060000240802765, -0.033900000154972076, 0.05530000105500221, 0.016100000590085983, -0.13179999589920044, 0.12999999523162842, 0.06700000166893005, -0.0737999975681305, -0.12219999730587006, 0.030899999663233757, -0.11259999871253967, -0.024399999529123306, 0.059300001710653305, -0.13650000095367432, 0.0008999999845400453, 0.06340000033378601, 0.010900000110268593, 0.01080000028014183, 0.039000000804662704, -0.0794999971985817, -0.057500001043081284, 0.061000000685453415, -0.06880000233650208, 0.030500000342726707, -0.03739999979734421, -0.013799999840557575, -0.05900000035762787, 0.062300000339746475, -0.1444000005722046, -0.04600000008940697, -0.20980000495910645, 0.012900000438094139, -0.14489999413490295, 0.06560000032186508, -0.06199999898672104, 0.05860000103712082, 0.27709999680519104, 0.05920000001788139, 0.015699999406933784, -0.00839999970048666, 0.15060000121593475, -0.065700002014637, 0.009499999694526196, 0.08839999884366989, -0.04500000178813934, 0.10790000110864639, -0.01489999983459711, -0.09749999642372131, -0.164900004863739, 0.02239999920129776, -0.024000000208616257, 0.007600000128149986, -0.04129999876022339, 0.14110000431537628, 0.06679999828338623, -0.0003000000142492354, -0.1273999959230423, 0.1467999964952469, 0.04659999907016754, -0.08799999952316284, 0.1876000016927719, -0.002199999988079071, 0.11429999768733978, -0.0203000009059906, -0.049800001084804535, -0.09019999951124191, 0.13089999556541443, -0.009800000116229057, 0.0828000009059906, 0.00989999994635582, -0.10679999738931656, -0.008100000210106373, -0.00570000009611249, -0.014399999752640724, 0.04809999838471413, -0.05009999871253967, 0.1006999984383583, -0.09690000116825104, -0.0560000017285347, 0.09640000015497208, -0.06300000101327896, -0.0010999999940395355, 0.10639999806880951, -0.06880000233650208, 0.03519999980926514, -0.014399999752640724, -0.09960000216960907, 0.03539999946951866, 0.01269999984651804, -0.03920000046491623, 0.23080000281333923, 0.05649999901652336, 0.035999998450279236, 0.01489999983459711, -0.06069999933242798, -0.09390000253915787, 0.04520000144839287, -0.08640000224113464, 0.04309999942779541, 0.0026000000070780516, 0.03139999881386757, 0.11400000005960464, 0.07530000060796738, -0.04969999939203262, 0.10639999806880951, 0.12389999628067017, -0.0885000005364418], [-0.15970000624656677, -0.07100000232458115, 0.06539999693632126, 0.060100000351667404, -0.05429999902844429, 0.09109999984502792, -0.0017000000225380063, -0.04809999838471413, -0.011699999682605267, 0.06419999897480011, -0.13940000534057617, 0.03669999912381172, -0.04050000011920929, -0.00559999980032444, -0.05090000107884407, 0.12229999899864197, -0.02070000022649765, -0.04780000075697899, 0.0044999998062849045, -0.02969999983906746, -0.07850000262260437, 0.09719999879598618, -0.031700000166893005, 0.030500000342726707, 0.15700000524520874, -0.021900000050663948, 0.044599998742341995, 0.0066999997943639755, -0.07850000262260437, 0.0754999965429306, -0.18780000507831573, 0.0010999999940395355, 0.05169999971985817, -0.1673000007867813, 0.0746999979019165, -0.026100000366568565, -0.01759999990463257, 0.08290000259876251, -0.023399999365210533, 0.12099999934434891, -0.09149999916553497, -0.20250000059604645, -0.16930000483989716, -0.03799999877810478, 0.025800000876188278, -0.027499999850988388, 0.09539999812841415, -0.1793999969959259, 0.09709999710321426, -0.09109999984502792, -0.18289999663829803, -0.12639999389648438, -0.002899999963119626, -0.0019000000320374966, -0.04149999842047691, -0.10480000078678131, 0.004699999932199717, 0.01769999973475933, -0.0689999982714653, -0.03519999980926514, -0.02329999953508377, -0.0502999983727932, 0.04619999974966049, 0.08910000324249268, -0.06750000268220901, -0.057100001722574234, 0.00570000009611249, -0.08240000158548355, 0.04230000078678131, 0.07819999754428864, -0.00559999980032444, 0.10949999839067459, 0.1817999929189682, 0.010999999940395355, -0.023499999195337296, -0.10409999638795853, 0.0013000000035390258, -0.008700000122189522, 0.003800000064074993, -0.05609999969601631, 0.17080000042915344, -0.04089999943971634, -0.0203000009059906, 0.11230000108480453, 0.03020000085234642, -0.1785999983549118, 0.12319999933242798, -0.07280000299215317, -0.20020000636577606, 0.03290000185370445, -0.04179999977350235, -0.055399999022483826, 0.09650000184774399, 0.0763000026345253, -0.047200001776218414, 0.07720000296831131, 0.15620000660419464, 0.01209999993443489, 0.09030000120401382, 0.011500000022351742, -0.07190000265836716, -0.03790000081062317, -0.22290000319480896, -0.013799999840557575, -0.023499999195337296, -0.012900000438094139, -0.02930000051856041, 0.12129999697208405, 0.11010000109672546, -0.10939999669790268, 0.009399999864399433, 0.04490000009536743, 0.13439999520778656, 0.05999999865889549, -0.10320000350475311, -0.05990000069141388, 0.20749999582767487, 0.05820000171661377, 0.13840000331401825, -0.04859999939799309, 0.07440000027418137, 0.0851999968290329, 0.08259999752044678, 0.016899999231100082, -0.10100000351667404, -0.006500000134110451, 0.08919999748468399, 0.06960000097751617], [-0.03319999948143959, 0.10769999772310257, 0.10930000245571136, 0.10480000078678131, 0.04780000075697899, 0.09449999779462814, 0.07360000163316727, 0.02810000069439411, -0.054499998688697815, -0.1606999933719635, 0.03840000182390213, 0.11429999768733978, -0.30550000071525574, -0.19850000739097595, -0.1476999968290329, -0.1354999989271164, 0.028699999675154686, 0.04309999942779541, 0.14339999854564667, -0.0348999984562397, 0.07370000332593918, -0.18019999563694, -0.1234000027179718, 0.020899999886751175, 0.05480000004172325, -0.03660000115633011, 0.09220000356435776, 0.04019999876618385, -0.11270000040531158, -0.12189999967813492, -0.01590000092983246, -0.10040000081062317, -0.1307000070810318, 0.07989999651908875, -0.09109999984502792, 0.057500001043081284, -0.11879999935626984, 0.006300000008195639, -0.03220000118017197, -0.01080000028014183, -0.003700000001117587, -0.11490000039339066, 0.11289999634027481, -0.04960000142455101, -0.09790000319480896, -0.027000000700354576, -0.020099999383091927, 0.041999999433755875, 0.03480000048875809, 0.10890000313520432, -0.08079999685287476, 0.17919999361038208, -0.07479999959468842, 0.031099999323487282, 0.061500001698732376, -0.10199999809265137, -0.13120000064373016, 0.15569999814033508, -0.1265999972820282, -0.016899999231100082, 0.10939999669790268, -0.07699999958276749, -0.008700000122189522, -0.07760000228881836, 0.11110000312328339, -0.14010000228881836, 0.1915999948978424, -0.025200000032782555, 0.006800000090152025, 0.08100000023841858, 0.030700000002980232, -0.022700000554323196, -0.059700001031160355, -0.07639999687671661, -0.006800000090152025, 0.003800000064074993, 0.04830000177025795, 0.12800000607967377, -0.07090000063180923, 0.004399999976158142, -0.011500000022351742, -0.1914999932050705, -0.0008999999845400453, -0.12160000205039978, 0.1071000024676323, 0.03909999877214432, -0.05990000069141388, 0.13189999759197235, -0.04600000008940697, -0.07769999653100967, 0.08540000021457672, -0.026900000870227814, 0.16509999334812164, -0.04969999939203262, -0.1281999945640564, -0.02539999969303608, 0.04129999876022339, -0.021199999377131462, -0.03880000114440918, -0.00139999995008111, -0.025499999523162842, -0.011800000444054604, -0.021199999377131462, 0.029899999499320984, 0.020999999716877937, -0.006099999882280827, -0.023000000044703484, 0.09989999979734421, -0.004600000102072954, 0.029899999499320984, -0.014600000344216824, -0.09059999883174896, 0.06129999831318855, -0.021199999377131462, -0.0017999999690800905, -0.04699999839067459, -0.035100001841783524, -0.011099999770522118, 0.11900000274181366, 0.07689999788999557, 0.033799998462200165, 0.05979999899864197, 0.14990000426769257, -0.006800000090152025, 0.005499999970197678, 0.04170000180602074, -0.0007999999797903001, -0.11230000108480453], [-0.03970000147819519, -0.0066999997943639755, 0.019500000402331352, 0.07000000029802322, -0.0203000009059906, -0.02370000071823597, 0.06800000369548798, -0.05730000138282776, -0.07729999721050262, 0.05889999866485596, 0.07000000029802322, 0.23579999804496765, 0.03359999880194664, 0.11990000307559967, 0.02979999966919422, 0.21809999644756317, -0.10949999839067459, -0.11410000175237656, 0.0851999968290329, 0.07580000162124634, -0.004100000020116568, 0.12070000171661377, -0.016100000590085983, -0.11599999666213989, 0.021400000900030136, -0.06620000302791595, 0.13439999520778656, -0.22589999437332153, 0.06340000033378601, -0.10000000149011612, 0.03500000014901161, -0.14069999754428864, -0.08139999955892563, -0.07769999653100967, 0.05689999833703041, 0.00430000014603138, -0.05180000141263008, 0.06930000334978104, 0.059300001710653305, -0.024700000882148743, 0.04839999973773956, 0.06870000064373016, -0.000699999975040555, -0.00559999980032444, 0.10029999911785126, -0.008100000210106373, 0.15279999375343323, -0.10400000214576721, -0.02800000086426735, 0.15129999816417694, 0.041600000113248825, -0.08579999953508377, -0.00860000029206276, 0.08209999650716782, -0.10329999774694443, -0.07989999651908875, -0.04690000042319298, -0.01889999955892563, 0.15000000596046448, -0.11829999834299088, 0.057500001043081284, 0.09889999777078629, -0.15199999511241913, -0.007899999618530273, 0.02019999921321869, -0.03020000085234642, 0.08649999648332596, -0.1639000028371811, -0.11490000039339066, 0.148499995470047, 0.14579999446868896, 0.08659999817609787, -0.012000000104308128, 0.08590000122785568, 0.0828000009059906, -0.13439999520778656, -0.02070000022649765, -0.04490000009536743, 0.01549999974668026, -0.02710000053048134, -0.010300000198185444, -0.04650000110268593, -0.147599995136261, 0.012299999594688416, 0.028300000354647636, 0.11599999666213989, -0.04050000011920929, -0.0575999990105629, 0.11649999767541885, 0.009399999864399433, -0.03020000085234642, 0.05490000173449516, 0.03750000149011612, 0.1151999980211258, 0.042899999767541885, -0.18199999630451202, -0.0340999998152256, 0.02419999986886978, -0.007400000002235174, -0.0035000001080334187, 0.08980000019073486, 0.13230000436306, 0.04830000177025795, 0.08169999718666077, 0.03150000050663948, -0.14350000023841858, -0.004100000020116568, -0.007699999958276749, -0.14730000495910645, 0.21130000054836273, 0.061799999326467514, -0.04100000113248825, -0.05990000069141388, -0.038600001484155655, -0.16329999268054962, -0.03449999913573265, 0.07460000365972519, -0.0003000000142492354, 0.07569999992847443, 0.09390000253915787, 0.019999999552965164, 0.016899999231100082, 9.999999747378752e-05, 0.035100001841783524, 0.12710000574588776, 0.09809999912977219, 0.003100000089034438, -0.08579999953508377], [0.018200000748038292, 0.07010000199079514, 0.11110000312328339, -0.041099999099969864, -0.01140000019222498, 0.12470000237226486, -0.10740000009536743, -0.06560000032186508, 0.009100000374019146, 0.15070000290870667, -0.014299999922513962, -0.0658000037074089, -0.023099999874830246, 0.04809999838471413, -0.03849999979138374, 0.040699999779462814, 0.002199999988079071, -0.05640000104904175, -0.011699999682605267, 0.21289999783039093, 0.1648000031709671, -0.023600000888109207, -0.10119999945163727, -0.07199999690055847, 0.05609999969601631, 0.0357000008225441, 0.04170000180602074, -0.0674000009894371, -0.14169999957084656, -0.02449999935925007, -0.06909999996423721, -0.18170000612735748, 0.12880000472068787, 0.04600000008940697, -0.062199998646974564, 0.03370000049471855, -0.007199999876320362, 0.05939999967813492, 0.08839999884366989, -0.10180000215768814, -0.003100000089034438, -0.1315000057220459, -0.09759999811649323, -0.029999999329447746, 0.08489999920129776, -0.11659999936819077, -0.07609999924898148, 0.07109999656677246, -0.022600000724196434, -0.011500000022351742, -0.002300000051036477, 0.022099999710917473, -0.1362999975681305, 0.09520000219345093, -0.13269999623298645, -0.008500000461935997, 0.06840000301599503, -0.17579999566078186, 0.012799999676644802, -0.059300001710653305, -0.05900000035762787, 0.013100000098347664, -0.07909999787807465, 0.06639999896287918, -0.013700000010430813, 0.034699998795986176, -0.03440000116825104, -0.1273999959230423, 0.11389999836683273, -0.14329999685287476, -0.14169999957084656, -0.005400000140070915, -0.13339999318122864, 0.1662999987602234, 0.007400000002235174, -0.08879999816417694, -0.11900000274181366, 0.04780000075697899, -0.053300000727176666, -0.00430000014603138, -0.016300000250339508, 0.05990000069141388, -0.023000000044703484, 0.007899999618530273, -0.07199999690055847, 0.1120000034570694, 0.040699999779462814, 0.08579999953508377, -0.04439999908208847, 0.02850000001490116, 0.0982000008225441, -0.0038999998942017555, 0.07329999655485153, -0.06809999793767929, -0.16220000386238098, -0.1331000030040741, 0.09600</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>[[[0.009200000204145908, 0.04390000179409981, 0.02930000051856041, 0.01860000006854534, 0.1543000042438507, -0.04919999837875366, -0.04050000011920929, -0.09849999845027924, 0.02410000003874302, -0.1867000013589859, -0.06859999895095825, -0.04100000113248825, 0.06930000334978104, 0.07660000026226044, -0.05700000002980232, 0.05999999865889549, 0.046300001442432404, 0.057999998331069946, 0.055799998342990875, -0.023600000888109207, 0.09629999846220016, 0.07750000059604645, 0.10920000076293945, 0.07199999690055847, 0.0706000030040741, 0.05209999904036522, -0.046300001442432404, 0.09449999779462814, -0.06599999964237213, 0.06430000066757202, -0.007300000172108412, 0.014700000174343586, 0.08380000293254852, 0.0494999997317791, -0.012799999676644802, 0.07980000227689743, -0.014600000344216824, 0.02250000089406967, 0.0794999971985817, -0.05050000175833702, 0.039400000125169754, -0.0203000009059906, -0.08150000125169754, 0.07819999754428864, 0.006500000134110451, 0.06449999660253525, -0.03200000151991844, -0.004699999932199717, -0.032499998807907104, 0.07349999994039536, -0.0015999999595806003, 0.03460000082850456, 0.12200000137090683, -0.0706000030040741, 0.04820000007748604, 0.01640000008046627, -0.06669999659061432, -0.041600000113248825, -0.10130000114440918, -0.05490000173449516, -0.06080000102519989, -0.06419999897480011, -0.06989999860525131, -0.04050000011920929, 0.06849999725818634, -0.05000000074505806, 0.03840000182390213, -0.001500000013038516, 0.12160000205039978, -0.048700001090765, -0.07240000367164612, -0.02290000021457672, 0.05119999870657921, 0.009600000455975533, -0.04390000179409981, -0.03660000115633011, 0.04490000009536743, 0.041200000792741776, 0.0502999983727932, -0.09049999713897705, -0.009700000286102295, 0.031599998474121094, 0.004100000020116568, 0.06270000338554382, 0.04919999837875366, 0.05869999900460243, -0.03530000150203705, 0.0024999999441206455, 0.05889999866485596, 0.061500001698732376, 0.0017999999690800905, -0.031099999323487282, -0.0551999993622303, -0.03959999978542328, 0.07699999958276749, 0.05220000073313713, 0.0478999987244606, 0.05920000001788139, 0.06870000064373016, -0.12630000710487366, 0.00570000009611249, -0.0746999979019165, -0.1517000049352646, 0.010400000028312206, 0.09960000216960907, -0.03970000147819519, -0.021700000390410423, 0.048700001090765, -0.0681999996304512, -0.05779999867081642, 0.08240000158548355, 0.08839999884366989, -0.02879999950528145, 0.028999999165534973, 0.06610000133514404, 0.02410000003874302, 0.06689999997615814, 0.00419999985024333, 0.03370000049471855, 0.09220000356435776, -0.052000001072883606, -0.013399999588727951, -0.007199999876320362, 0.03009999915957451, -0.00570000009611249, 0.0640999972820282, 0.03830000013113022, 0.08299999684095383], [0.027000000700354576, -0.04410000145435333, -0.049400001764297485, -0.010300000198185444, -0.149399995803833, 0.03590000048279762, 0.05119999870657921, 0.045899998396635056, -0.06319999694824219, -0.022700000554323196, 0.08370000123977661, 0.020899999886751175, -0.03750000149011612, -0.06679999828338623, 0.040300000458955765, -0.06960000097751617, -0.048700001090765, -0.06949999928474426, -0.0722000002861023, 0.02669999934732914, -0.016300000250339508, -0.05889999866485596, -0.02710000053048134, -0.04619999974966049, -0.14190000295639038, -0.04919999837875366, 0.0843999981880188, -0.08820000290870667, 0.06350000202655792, -0.05400000140070915, 0.003000000026077032, 0.002300000051036477, -0.09920000284910202, -0.051100000739097595, 0.04769999906420708, -0.04969999939203262, 0.013199999928474426, -0.01889999955892563, -0.05660000070929527, 0.06599999964237213, 0.024399999529123306, 0.028300000354647636, 0.10530000180006027, -0.08020000159740448, -0.10400000214576721, -0.09210000187158585, 0.12610000371932983, -0.06069999933242798, 0.08720000088214874, -0.06769999861717224, -0.0038999998942017555, 0.021400000900030136, -0.0885000005364418, 0.09399999678134918, -0.030700000002980232, 0.0142000000923872, 0.04479999840259552, 0.037300001829862595, 0.12280000001192093, 0.08179999887943268, 0.08479999750852585, -0.008200000040233135, 0.05990000069141388, 0.03200000151991844, -0.05180000141263008, 0.06260000169277191, -0.021900000050663948, -0.006399999838322401, 0.0012000000569969416, 0.049300000071525574, 0.06610000133514404, 0.0005000000237487257, -0.07119999825954437, 0.030799999833106995, 0.0421999990940094, 0.025599999353289604, -0.09179999679327011, -0.1542000025510788, -0.049300000071525574, 0.0868000015616417, -0.003100000089034438, -0.041600000113248825, -0.025299999862909317, -0.07580000162124634, -0.0005000000237487257, -0.10159999877214432, 0.05810000002384186, 0.0026000000070780516, -0.0835999995470047, -0.07569999992847443, -0.009399999864399433, 0.03610000014305115, 0.01720000058412552, 0.027499999850988388, -0.1120000034570694, -0.057100001722574234, -0.02419999986886978, -0.07999999821186066, -0.05810000002384186, -0.0007999999797903001, 0.013799999840557575, 0.1062999963760376, 0.03290000185370445, -0.04529999941587448, -0.0560000017285347, 0.018699999898672104, 0.032499998807907104, -0.06769999861717224, 0.04529999941587448, 0.06459999829530716, -0.06880000233650208, -0.08209999650716782, 0.030799999833106995, -0.0869000032544136, -0.048500001430511475, -0.013799999840557575, -0.049300000071525574, 0.029400000348687172, -0.09589999914169312, -0.05009999871253967, 0.06350000202655792, -0.09399999678134918, 0.019200000911951065, -0.003100000089034438, 0.011699999682605267, -0.06589999794960022, -0.12330000102519989, -0.07249999791383743]], [[-0.016499999910593033, -0.06719999760389328, -0.008100000210106373, -0.017000000923871994, -0.23849999904632568, -0.012799999676644802, 0.08500000089406967, 0.041200000792741776, -0.07680000364780426, -0.041600000113248825, -0.0017999999690800905, 0.007300000172108412, 0.04989999905228615, 0.11169999837875366, 0.07639999687671661, 0.1023000031709671, -0.015799999237060547, -0.15919999778270721, 0.021400000900030136, -0.04529999941587448, 0.058400001376867294, -0.09989999979734421, 0.08630000054836273, -0.025800000876188278, -0.0348999984562397, 0.01720000058412552, -0.021199999377131462, 0.07720000296831131, -0.08089999854564667, 0.03020000085234642, 0.06750000268220901, -0.03799999877810478, 0.030899999663233757, -0.007899999618530273, 0.04410000145435333, 0.18160000443458557, -0.053199999034404755, -0.002099999925121665, 0.04129999876022339, 0.1988999992609024, -0.06469999998807907, 0.02290000021457672, -0.193900004029274, 0.02800000086426735, -0.03480000048875809, -0.125, 0.04699999839067459, -0.03009999915957451, 0.014700000174343586, -0.024399999529123306, -0.011900000274181366, 0.024700000882148743, -0.009700000286102295, 0.07660000026226044, 0.11659999936819077, 0.07810000330209732, 0.02199999988079071, 0.053599998354911804, 0.004600000102072954, -0.014700000174343586, 0.002400000113993883, -0.010499999858438969, -0.07090000063180923, 0.11720000207424164, 0.00930000003427267, -0.09860000014305115, -0.06800000369548798, -0.039000000804662704, 0.03280000016093254, -0.03200000151991844, 0.12860000133514404, -0.019999999552965164, 0.16290000081062317, -0.2696000039577484, 0.10589999705553055, -0.024900000542402267, 0.05829999968409538, 0.14970000088214874, -0.02889999933540821, -0.02930000051856041, -0.07760000228881836, -0.0689999982714653, -0.04830000177025795, 0.061900001019239426, -0.2011999934911728, -0.03629999980330467, 0.13339999318122864, 0.156700000166893, 0.1476999968290329, -0.030500000342726707, -0.01510000042617321, 0.2021999955177307, 0.13500000536441803, -0.20389999449253082, 0.0284000001847744, -0.0908999964594841, 0.156700000166893, 0.019600000232458115, 0.07129999995231628, -0.012199999764561653, 0.07670000195503235, -0.016200000420212746, -0.002899999963119626, 0.16300000250339508, 0.14409999549388885, 0.05220000073313713, -0.0006000000284984708, -0.1306000053882599, 0.062199998646974564, -0.04039999842643738, -0.14569999277591705, -0.14000000059604645, -0.1388999968767166, 0.06769999861717224, 0.029999999329447746, 0.17270000278949738, -0.09109999984502792, -0.02539999969303608, 0.16580000519752502, -0.03189999982714653, -0.08780000358819962, 0.030899999663233757, -0.18700000643730164, -0.11900000274181366, -0.05420000106096268, 0.12430000305175781, -0.12139999866485596, 0.11379999667406082], [0.03530000150203705, -0.14069999754428864, 0.08410000056028366, -0.08060000091791153, 0.17489999532699585, 0.16169999539852142, 0.1647000014781952, 0.09780000150203705, 0.10649999976158142, -0.05480000004172325, -0.003800000064074993, 0.049800001084804535, -0.16060000658035278, -0.013399999588727951, -0.10740000009536743, -0.020899999886751175, -0.09520000219345093, -0.006899999920278788, -0.008100000210106373, -0.1088000014424324, 0.07970000058412552, -0.029400000348687172, 0.11540000140666962, 0.11209999769926071, 0.14910000562667847, 0.07320000231266022, -0.031700000166893005, -0.0340999998152256, -0.04989999905228615, -0.06930000334978104, -0.005400000140070915, 0.07900000363588333, -0.15800000727176666, -0.09870000183582306, -0.10220000147819519, 0.05849999934434891, 0.06069999933242798, -0.07900000363588333, -0.012500000186264515, 0.19679999351501465, 0.012900000438094139, -0.09650000184774399, -0.12120000272989273, 0.11919999867677689, -0.10509999841451645, -0.15960000455379486, 0.09650000184774399, 0.09640000015497208, 0.1225999966263771, 0.10499999672174454, 0.09600000083446503, -0.10689999908208847, 0.029100000858306885, 0.09390000253915787, -0.05429999902844429, -0.1446000039577484, 0.026599999517202377, 0.006899999920278788, 0.024900000542402267, -0.1136000007390976, 0.18880000710487366, 0.012900000438094139, 0.08340000361204147, 0.08470000326633453, -0.035999998450279236, -0.002300000051036477, -0.1501999944448471, 0.0925000011920929, 0.053599998354911804, -0.03180000185966492, 0.03579999879002571, -0.17010000348091125, 0.06300000101327896, -0.06040000170469284, -0.012900000438094139, -0.0284000001847744, 0.0828000009059906, -0.1518000066280365, 0.13429999351501465, 0.13779999315738678, -0.09549999982118607, 0.041200000792741776, -0.06719999760389328, 0.014800000004470348, 0.18490000069141388, 0.003100000089034438, 0.052299998700618744, 0.003700000001117587, -0.057999998331069946, -0.1826000064611435, -0.13729999959468842, -0.10589999705553055, -0.19760000705718994, 0.013899999670684338, 0.030899999663233757, -0.17219999432563782, -0.03819999843835831, -0.08240000158548355, 0.010300000198185444, -0.06920000165700912, 0.07649999856948853, 0.04479999840259552, 0.13230000436306, -0.11630000174045563, -0.0026000000070780516, 0.04360000044107437, 0.021900000050663948, -0.009399999864399433, -0.08009999990463257, -0.06310000270605087, -0.10849999636411667, -0.06279999762773514, -0.09210000187158585, -0.06030000001192093, -0.10890000313520432, 0.042500000447034836, -0.07450000196695328, -0.11919999867677689, 0.15569999814033508, -0.046799998730421066, 0.03959999978542328, 0.04540000110864639, 0.019899999722838402, 0.07360000163316727, 0.2160000056028366, 0.01489999983459711, 0.07530000060796738, 0.0010000000474974513], [0.09120000153779984, 0.03550000116229057, -0.1062999963760376, -0.0949999988079071, -0.0414000004529953, 0.2639000117778778, 0.10119999945163727, -0.009700000286102295, -0.008700000122189522, 0.09440000355243683, -0.10939999669790268, 0.05959999933838844, 0.05829999968409538, -0.006000000052154064, -0.07259999960660934, 0.09910000115633011, 0.13950000703334808, 0.1445000022649765, 0.10859999805688858, -0.013299999758601189, 0.18289999663829803, 0.0421999990940094, 0.08959999680519104, -0.0210999995470047, -0.18250000476837158, -0.0731000006198883, -0.06769999861717224, 0.11410000175237656, -0.07890000194311142, 0.02449999935925007, 0.22380000352859497, -0.10289999842643738, -0.1665000021457672, 0.19110000133514404, 0.1331000030040741, -0.15870000422000885, -0.25119999051094055, 0.010499999858438969, 0.019700000062584877, -0.1459999978542328, 0.0575999990105629, 0.09570000320672989, -0.13199999928474426, -0.014399999752640724, 0.028300000354647636, 0.11299999803304672, 0.10419999808073044, 0.12680000066757202, 0.18449999392032623, -0.09149999916553497, -0.05550000071525574, 0.06750000268220901, -0.04270000010728836, -0.0364999994635582, 0.08299999684095383, 0.03009999915957451, -0.18289999663829803, 0.005100000184029341, -0.07450000196695328, -0.03660000115633011, -0.024900000542402267, -0.15620000660419464, -0.0038999998942017555, -0.12269999831914902, 0.0869000032544136, 0.01600000075995922, -0.00559999980032444, -0.029899999499320984, -0.13349999487400055, -0.24160000681877136, 0.026599999517202377, -0.06859999895095825, 0.06719999760389328, 0.16290000081062317, -0.10989999771118164, 0.013299999758601189, 0.07010000199079514, -0.025299999862909317, 0.193900004029274, 0.17339999973773956, -0.1469999998807907, 0.04690000042319298, -0.0284000001847744, 0.0357000008225441, -0.05999999865889549, 0.03099999949336052, -0.039900001138448715, 0.09570000320672989, -0.055399999022483826, -0.1808999925851822, -0.2603999972343445, -0.17569999396800995, 0.08789999783039093, 0.15549999475479126, 0.04769999906420708, -0.13979999721050262, -0.1046999990940094, -0.026000000536441803, -0.020899999886751175, -0.11810000240802765, -0.12319999933242798, -0.1565999984741211, -0.13670000433921814, -0.19280000030994415, 0.008799999952316284, -0.2451000064611435, -0.025699999183416367, -0.11940000206232071, 0.03220000118017197, -0.01899999938905239, -0.05180000141263008, -0.14550000429153442, -0.16169999539852142, 0.06700000166893005, 0.006899999920278788, 0.08869999647140503, 0.11079999804496765, -0.001500000013038516, 0.04910000041127205, -0.05389999970793724, -0.05719999969005585, -0.04830000177025795, -0.013799999840557575, 0.01720000058412552, -0.00839999970048666, 0.06080000102519989, -0.01590000092983246, -0.08309999853372574], [0.10580000281333923, 0.06790000200271606, 0.02370000071823597, -0.14380000531673431, 0.09880000352859497, -0.07930000126361847, -0.0502999983727932, -0.03750000149011612, -0.00839999970048666, -0.026000000536441803, -0.0722000002861023, -0.21930000185966492, -0.016300000250339508, -0.023499999195337296, -0.07580000162124634, -0.10329999774694443, 0.15870000422000885, 0.0008999999845400453, -0.14800000190734863, 0.01510000042617321, 0.11129999905824661, 0.02800000086426735, -0.09489999711513519, 0.025100000202655792, 0.0406000018119812, 0.11150000244379044, -0.002400000113993883, 0.04149999842047691, 0.15569999814033508, 0.1225999966263771, 0.00419999985024333, -0.15060000121593475, -0.004000000189989805, 0.02879999950528145, 0.01899999938905239, 0.16619999706745148, 0.061500001698732376, 0.10119999945163727, -0.09130000323057175, 0.05429999902844429, 0.035599999129772186, 0.04540000110864639, -0.047600001096725464, -0.10499999672174454, -0.06629999727010727, 0.2249000072479248, 0.0803999975323677, -0.07609999924898148, -0.06279999762773514, 0.09690000116825104, -0.11550000309944153, -0.05510000139474869, 0.07280000299215317, 0.18790000677108765, -0.023099999874830246, 0.17180000245571136, -0.08179999887943268, 0.050999999046325684, 0.05389999970793724, -0.0340999998152256, 0.07880000025033951, 0.009100000374019146, 0.16290000081062317, 0.06350000202655792, 0.05480000004172325, -0.01489999983459711, 0.00559999980032444, -0.04569999873638153, -0.16380000114440918, 0.042899999767541885, 0.06480000168085098, 0.05389999970793724, 0.054099999368190765, 0.03370000049471855, -0.20149999856948853, -0.09920000284910202, -0.045899998396635056, -0.19099999964237213, -0.1136000007390976, 0.030400000512599945, 0.1476999968290329, -0.07150000333786011, -0.02879999950528145, -0.0066999997943639755, 0.03579999879002571, 0.12439999729394913, 0.1525000035762787, 0.022299999371170998, 0.125, 0.051100000739097595, -0.016499999910593033, -0.006300000008195639, 0.04439999908208847, 0.0024999999441206455, 0.10300000011920929, -0.01810000091791153, -0.021299999207258224, 0.044599998742341995, 0.08420000225305557, -0.05900000035762787, -0.08100000023841858, 0.14640000462532043, -0.11749999970197678, 0.14059999585151672, -0.1274999976158142, -0.11940000206232071, -0.11349999904632568, -0.14569999277591705, -0.12070000171661377, -0.15489999949932098, 0.05739999935030937, 0.014399999752640724, 0.0868000015616417, 0.09470000118017197, 0.08810000121593475, 0.20000000298023224, -0.057100001722574234, -0.11169999837875366, -0.18639999628067017, -0.05420000106096268, 0.011500000022351742, -0.025499999523162842, -0.05180000141263008, 0.07670000195503235, -0.029999999329447746, 0.024000000208616257, 0.06300000101327896, -0.06129999831318855], [0.07410000264644623, 0.21850000321865082, -0.3172000050544739, -0.06809999793767929, 0.23639999330043793, 0.13459999859333038, -0.023499999195337296, -0.27720001339912415, 0.1071000024676323, -0.21410000324249268, 0.07810000330209732, -0.20350000262260437, 0.15860000252723694, 0.11699999868869781, -0.2037999927997589, 0.0032999999821186066, 0.0786999985575676, -0.27630001306533813, 0.051100000739097595, 0.1679999977350235, 0.1298000067472458, -0.08139999955892563, 0.08060000091791153, 0.5192000269889832, 0.08730000257492065, 0.12150000035762787, 0.16200000047683716, 0.10970000177621841, -0.19429999589920044, 0.13500000536441803, -0.225600004196167, 0.013899999670684338, -0.02590000070631504, 0.06069999933242798, -0.03189999982714653, 0.1331000030040741, 0.008799999952316284, -9.999999747378752e-05, -0.28929999470710754, -0.03620000183582306, -0.20430000126361847, 0.19030000269412994, -0.1940000057220459, -0.271699994802475, 0.06440000236034393, 0.13779999315738678, -0.11940000206232071, -0.23579999804496765, 0.10520000010728836, 0.374099999666214, 0.2906999886035919, 0.1525000035762787, 0.2240999937057495, -0.0027000000700354576, 0.27810001373291016, -0.06310000270605087, -0.008999999612569809, -0.14630000293254852, -0.22779999673366547, 0.15080000460147858, 0.20419999957084656, 0.0471000000834465, -0.2442999929189682, -0.13429999351501465, -0.10689999908208847, -0.1606999933719635, -0.1956000030040741, -0.0746999979019165, 0.3718000054359436, -0.07329999655485153, -0.01679999940097332, -0.10090000182390213, -0.08269999921321869, -0.019600000232458115, 0.24250000715255737, 0.0430000014603138, -0.1745000034570694, 0.012299999594688416, 0.13089999556541443, 0.06270000338554382, -0.07620000094175339, 0.13109999895095825, -0.2061000019311905, 0.07180000096559525, -0.12250000238418579, -0.15469999611377716, -0.056699998676776886, 0.1096000000834465, 0.08330000191926956, -0.04769999906420708, 0.05689999833703041, -0.003700000001117587, -0.11110000312328339, -0.04479999840259552, -0.04410000145435333, 0.05480000004172325, 0.05550000071525574, 0.15800000727176666, 0.10350000113248825, 0.04390000179409981, 0.16539999842643738, -0.060600001364946365, -0.3131999969482422, -0.10480000078678131, 0.18569999933242798, -0.4343999922275543, -0.08980000019073486, -0.06019999831914902, -0.22110000252723694, -0.011300000362098217, 0.1793999969959259, -0.29739999771118164, -0.11699999868869781, 0.14100000262260437, 0.15850000083446503, 0.05959999933838844, 0.1632000058889389, 0.08540000021457672, -0.23430000245571136, -0.1776999980211258, -0.0722000002861023, 0.11810000240802765, 0.025800000876188278, 0.019500000402331352, -0.06340000033378601, -0.19869999587535858, -0.2485000044107437, 0.34610000252723694], [0.06279999762773514, 0.1054999977350235, -0.013799999840557575, -0.18160000443458557, -0.07760000228881836, -0.2093999981880188, -0.000699999975040555, 0.06840000301599503, -0.16169999539852142, -0.02459999918937683, -0.11249999701976776, 0.019500000402331352, -0.03359999880194664, 0.04659999907016754, -0.05050000175833702, 0.1469999998807907, -0.04910000041127205, 0.0364999994635582, -0.16779999434947968, 0.01679999940097332, -0.10559999942779541, -0.1834000051021576, 0.013199999928474426, 0.03220000118017197, 0.04569999873638153, -0.1607999950647354, 0.14229999482631683, 0.10989999771118164, -0.05400000140070915, -0.07919999957084656, 0.03689999878406525, -0.09099999815225601, -0.0019000000320374966, 0.06199999898672104, -0.15070000290870667, 0.001500000013038516, 0.041999999433755875, 0.052299998700618744, 0.016599999740719795, 0.04390000179409981, -0.1005999967455864, -0.11949999630451202, 0.09030000120401382, 0.04540000110864639, 0.002099999925121665, -0.05920000001788139, 0.010400000028312206, -0.09120000153779984, 0.07829999923706055, -0.16089999675750732, -0.08060000091791153, -0.1671999990940094, 0.0568000003695488, -0.13940000534057617, 0.07100000232458115, 0.0024999999441206455, 0.07900000363588333, 0.29910001158714294, 0.0502999983727932, -0.0012000000569969416, 0.007400000002235174, 0.11219999939203262, -0.06120000034570694, 0.018200000748038292, 0.10459999740123749, -0.050599999725818634, 0.19760000705718994, 0.026399999856948853, -0.11869999766349792, -0.17170000076293945, -0.047600001096725464, -0.026100000366568565, 0.0272000003606081, -0.031199999153614044, 0.10639999806880951, -0.04230000078678131, 0.0640999972820282, -0.08389999717473984, 0.13410000503063202, 0.02590000070631504, -0.0071000000461936, 0.19179999828338623, 0.004900000058114529, 0.09889999777078629, 0.03530000150203705, -0.01889999955892563, -0.1128000020980835, 0.06880000233650208, 0.007799999788403511, 0.11349999904632568, -0.004900000058114529, -0.14249999821186066, -0.03139999881386757, -0.005799999926239252, 0.05950000137090683, 0.03269999846816063, -0.05939999967813492, 0.07150000333786011, -0.05779999867081642, -0.024800000712275505, 0.05730000138282776, -0.08020000159740448, -0.01860000006854534, 0.05739999935030937, -0.07810000330209732, 0.04179999977350235, -0.02800000086426735, -0.0284000001847744, 0.024000000208616257, 0.036400001496076584, -0.003000000026077032, 0.2168000042438507, 0.10840000212192535, -0.0071000000461936, 0.08540000021457672, -0.062199998646974564, -0.10109999775886536, 0.0544000007212162, -0.1987999975681305, 0.07079999893903732, 0.05730000138282776, 0.07559999823570251, 0.13259999454021454, 0.14970000088214874, -0.013799999840557575, 0.11129999905824661, 0.15379999577999115, -0.10279999673366547], [-0.15029999613761902, -0.12559999525547028, 0.09780000150203705, 0.0738999992609024, -0.12039999663829803, 0.045099999755620956, -0.09139999747276306, -0.021299999207258224, -0.10599999874830246, 0.07400000095367432, -0.06700000166893005, 0.016499999910593033, -0.05640000104904175, -0.004100000020116568, -0.01979999989271164, 0.06949999928474426, -0.08089999854564667, -0.03959999978542328, 0.026100000366568565, 0.010700000450015068, -0.06930000334978104, 0.14110000431537628, -0.04960000142455101, -0.007899999618530273, 0.12929999828338623, 0.003700000001117587, 0.042899999767541885, -0.049800001084804535, -0.05719999969005585, 0.06310000270605087, -0.15880000591278076, -0.008500000461935997, 0.06369999796152115, -0.22470000386238098, 0.13449999690055847, -0.04129999876022339, 0.05900000035762787, 0.0966000035405159, 0.004399999976158142, 0.15700000524520874, -0.07410000264644623, -0.1875, -0.16619999706745148, -0.025200000032782555, -0.05920000001788139, -0.06920000165700912, 0.08879999816417694, -0.2363000065088272, 0.06620000302791595, -0.09200000017881393, -0.23090000450611115, -0.1559000015258789, -0.04479999840259552, -0.018799999728798866, -0.06260000169277191, -0.11010000109672546, -0.012799999676644802, 0.014999999664723873, -0.07270000129938126, 0.019300000742077827, -0.021700000390410423, -0.06459999829530716, 0.07000000029802322, 0.024399999529123306, 0.015200000256299973, -0.020099999383091927, -0.01510000042617321, -0.10360000282526016, 0.041999999433755875, 0.15809999406337738, 0.033399999141693115, 0.1324000060558319, 0.11240000277757645, 0.0044999998062849045, -0.004399999976158142, -0.16920000314712524, -0.03180000185966492, -0.07259999960660934, 0.02630000002682209, -0.06120000034570694, 0.21310000121593475, -0.1014999970793724, -0.08150000125169754, 0.08139999955892563, 0.03920000046491623, -0.2395000010728836, 0.1745000034570694, -0.0430000014603138, -0.2556000053882599, 0.018799999728798866, -0.029600000008940697, -0.07919999957084656, 0.10270000249147415, 0.1151999980211258, -0.0908999964594841, 0.1062999963760376, 0.2160000056028366, 0.012299999594688416, 0.05770000070333481, -0.010999999940395355, -0.061900001019239426, -0.014499999582767487, -0.18700000643730164, -0.029500000178813934, 0.00800000037997961, 0.0348999984562397, -0.010200000368058681, 0.06620000302791595, 0.1678999960422516, -0.05119999870657921, -0.008299999870359898, 0.11150000244379044, 0.11339999735355377, 0.05829999968409538, -0.13689999282360077, -0.08429999649524689, 0.17329999804496765, 0.04399999976158142, 0.08590000122785568, 0.06809999793767929, 0.09650000184774399, 0.019899999722838402, 0.11159999668598175, -0.0681999996304512, -0.11490000039339066, -0.01510000042617321, 0.040699999779462814, 0.03830000013113022], [-0.06239999830722809, 0.0989999994635582, 0.1768999993801117, 0.12549999356269836, -0.008700000122189522, 0.07880000025033951, -0.014700000174343586, 0.0608999989926815, -0.1379999965429306, -0.11729999631643295, 0.024800000712275505, 0.10379999876022339, -0.36559998989105225, -0.17810000479221344, -0.12309999763965607, -0.15860000252723694, 0.005900000222027302, 0.12389999628067017, 0.14429999887943268, -0.01119999960064888, 0.050200000405311584, -0.12020000070333481, -0.1543000042438507, -0.041099999099969864, 0.014700000174343586, -0.04780000075697899, 0.04129999876022339, 0.0013000000035390258, -0.07980000227689743, -0.1597999930381775, 0.03290000185370445, -0.1445000022649765, -0.11599999666213989, 0.06509999930858612, -0.05009999871253967, 0.043299999088048935, -0.04399999976158142, -0.002400000113993883, 0.03790000081062317, 0.00019999999494757503, 0.020099999383091927, -0.08860000222921371, 0.14079999923706055, -0.052400000393390656, -0.13220000267028809, -0.07209999859333038, -0.006000000052154064, 0.03700000047683716, -0.034299999475479126, 0.061400000005960464, -0.1581999957561493, 0.12540000677108765, -0.13300000131130219, -0.006099999882280827, 0.010700000450015068, -0.14249999821186066, -0.13660000264644623, 0.15729999542236328, -0.10760000348091125, -0.0478999987244606, 0.06400000303983688, -0.06300000101327896, 0.05090000107884407, -0.09830000251531601, 0.18490000069141388, -0.10520000010728836, 0.15139999985694885, -0.03929999843239784, -0.05209999904036522, 0.15279999375343323, 0.013500000350177288, 0.02759999968111515, -0.05849999934434891, -0.10459999740123749, -0.010099999606609344, -0.018699999898672104, 0.0649000033736229, 0.13750000298023224, -0.08669999986886978, -0.022299999371170998, 0.026399999856948853, -0.23070000112056732, -0.03060000017285347, -0.1565999984741211, 0.120899997651577, 0.05260000005364418, -0.13689999282360077, 0.12489999830722809, -0.10750000178813934, -0.09459999948740005, 0.11739999800920486, -0.03519999980926514, 0.19359999895095825, 0.03060000017285347, -0.10360000282526016, -0.02419999986886978, 0.01940000057220459, -0.05260000005364418, -0.08669999986886978, 0.0026000000070780516, -0.06210000067949295, -0.02800000086426735, -0.0, 0.04859999939799309, 0.014600000344216824, 0.03180000185966492, -0.004800000227987766, 0.04670000076293945, 0.04100000113248825, 0.0608999989926815, -0.0575999990105629, -0.00800000037997961, 0.015300000086426735, -0.027899999171495438, -0.06109999865293503, -0.12359999865293503, -0.08879999816417694, -0.061900001019239426, 0.13120000064373016, 0.15119999647140503, 0.057500001043081284, -0.01889999955892563, 0.1923999935388565, -0.08470000326633453, 0.007899999618530273, 0.09130000323057175, 0.01489999983459711, -0.16990000009536743], [-0.06620000302791595, -0.017100000753998756, 0.04309999942779541, 0.019899999722838402, -0.0502999983727932, -0.05739999935030937, -0.03579999879002571, -0.07620000094175339, -0.13529999554157257, 0.09759999811649323, 0.09309999644756317, 0.19179999828338623, -0.006099999882280827, 0.1534000039100647, 0.06840000301599503, 0.179299995303154, -0.10920000076293945, -0.050700001418590546, 0.14920000731945038, 0.13989999890327454, 0.02250000089406967, 0.20200000703334808, -0.03590000048279762, -0.08789999783039093, 0.02419999986886978, -0.002300000051036477, 0.07900000363588333, -0.23829999566078186, 0.011800000444054604, -0.09210000187158585, 0.06639999896287918, -0.21459999680519104, 0.006000000052154064, -0.08229999989271164, 0.11230000108480453, -0.00989999994635582, 0.02290000021457672, 0.11620000004768372, 0.10320000350475311, 0.016200000420212746, 0.07240000367164612, 0.09780000150203705, -0.03830000013113022, -0.00989999994635582, 0.15330000221729279, -0.01810000091791153, 0.08940000087022781, -0.08919999748468399, -0.10989999771118164, 0.1671999990940094, 0.032099999487400055, -0.11569999903440475, -0.030700000002980232, 0.02199999988079071, -0.12839999794960022, -0.14339999854564667, -0.0917000025510788, -0.04129999876022339, 0.10930000245571136, -0.13429999351501465, 0.04170000180602074, 0.11800000071525574, -0.17520000040531158, -0.0551999993622303, 0.14880000054836273, -0.013000000268220901, 0.05719999969005585, -0.1720000058412552, -0.07050000131130219, 0.1396999955177307, 0.1598999947309494, 0.09489999711513519, -0.02979999966919422, 0.053599998354911804, 0.0738999992609024, -0.2313999980688095, -0.0544000007212162, -0.07010000199079514, 0.05849999934434891, -0.057100001722574234, 0.016499999910593033, -0.09950000047683716, -0.16619999706745148, 0.05979999899864197, 0.0044999998062849045, 0.08510000258684158, -0.02239999920129776, -0.015200000256299973, 0.09019999951124191, 0.11840000003576279, -9.999999747378752e-05, 0.10769999772310257, 0.06030000001192093, 0.1615999937057495, 0.02879999950528145, -0.14990000426769257, 0.03440000116825104, 0.036400001496076584, -0.03999999910593033, -0.06199999898672104, 0.10220000147819519, 0.1096000000834465, 0.07739999890327454, 0.1340000033378601, 0.08389999717473984, -0.11569999903440475, -0.005400000140070915, -0.04170000180602074, -0.11029999703168869, 0.16339999437332153, 0.04969999939203262, 0.042899999767541885, -0.09019999951124191, -0.007600000128149986, -0.20759999752044678, 0.01549999974668026, 0.10890000313520432, -0.021400000900030136, 0.1046999990940094, 0.20759999752044678, -0.024800000712275505, -0.05040000006556511, -0.003700000001117587, -0.0729999989271164, 0.0868000015616417, 0.17020000517368317, -0.04540000110864639, -0.04050000011920929], [0.024299999698996544, 0.06449999660253525, 0.12290000170469284, -0.001500000013038516, -0.006200000178068876, 0.09700000286102295, -0.1264999955892563, -0.04540000110864639, -0.019099999219179153, 0.18320000171661377, -0.02879999950528145, -0.022600000724196434, -0.061500001698732376, 0.05909999832510948, -0.02070000022649765, 0.008999999612569809, -0.019899999722838402, -0.0052999998442828655, -0.050700001418590546, 0.20960000157356262, 0.1331000030040741, -0.0430000014603138, -0.0771000012755394, -0.11670000106096268, 0.06379999965429306, -0.012600000016391277, 0.01489999983459711, -0.0860000029206276, -0.11209999769926071, -0.0502999983727932, -0.049800001084804535, -0.21279999613761902, 0.11509999632835388, 0.03359999880194664, -0.0729999989271164, 0.019200000911951065, -0.012900000438094139, 0.04769999906420708, 0.10209999978542328, -0.09730000048875809, -0.020500000566244125, -0.14149999618530273, -0.0625, -0.002400000113993883, 0.028200000524520874, -0.1526000052690506, -0.08410000056028366, 0.07810000330209732, -0.027300000190734863, -0.04699999839067459, -0.05920000001788139, 0.02019999921321869, -0.1785999983549118, 0.11999999731779099, -0.14790000021457672, -0.03189999982714653, 0.06520000100135803, -0.18379999697208405, 0.05869999900460243, -0.07199999690055847, -0.053300000727176666, 0.008999999612569809, -0.039799999445676804, 0.08879999816417694, -0.0414000004529953, 0.029400000348687172, -0.03550000116229057, -0.1031000018119812, 0.0940999984741211, -0.10440000146627426, -0.1421000063419342, -0.007699999958276749, -0.10339999943971634, 0.1808999925851822, -0.02280000038444996, -0.09239999949932098, -0.12530000507831573, 0.06859999895095825, -0.08760000020265579, -0.00039999998989515007, 0.055399999022483826, 0.028999999165534973, 0.002099999925121665, -0.02070000022649765, -0.029500000178813934, 0.12630000710487366, -0.007699999958276749, 0.06589999794960022, -0.06030000001192093, 0.008700000122189522, 0.12099999934434891, -0.01860000006854534, 0.048500001430511475, -0.012199999764561653, -0.16349999606609344, -0.1599999964237213, 0.0786999985575676, -0.21410000324249268, 0.03799999877810478, -0.0010000000474974513, -0.04320000112056732, -0.11050000041723251, -0.06650000065565109, 0.017999999225139618, -0.0560000017285347, 0.025100000202655792, -0.021700000390410423, -0.09610000252723694, 0.00</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>[-0.334384819361621]</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>[0.3045955236495507]</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>[-1.5828950599347391]</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>[0.5896833906949054]</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>[-4.014377355594913]</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>[1.641103889265856]</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>[-0.45605619178708134]</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>[0.3344838788484201]</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>[-0.3082805326790461]</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>[0.3102731548995626]</t>
+        </is>
+      </c>
+      <c r="O42" t="inlineStr">
+        <is>
+          <t>[-1.927238723580952]</t>
+        </is>
+      </c>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>[0.9623222472095898]</t>
+        </is>
+      </c>
+      <c r="Q42" t="inlineStr">
+        <is>
+          <t>[0.009179213570972844]</t>
+        </is>
+      </c>
+      <c r="R42" t="inlineStr">
+        <is>
+          <t>[0.10683597361506736]</t>
+        </is>
+      </c>
+      <c r="S42" t="inlineStr">
+        <is>
+          <t>[-0.01618439537225247]</t>
+        </is>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>[0.0856240424121838]</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>[-0.9224239660550808]</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>[0.18382819793422414]</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>[-0.08495874926853508]</t>
+        </is>
+      </c>
+      <c r="X42" t="inlineStr">
+        <is>
+          <t>[0.11366095510405744]</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>[-0.07601594339693363]</t>
+        </is>
+      </c>
+      <c r="Z42" t="inlineStr">
+        <is>
+          <t>[0.08854880567266529]</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>[-1.3921686406149978]</t>
+        </is>
+      </c>
+      <c r="AB42" t="inlineStr">
+        <is>
+          <t>[0.22008997910845596]</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>[-0.9883105197805506]</t>
+        </is>
+      </c>
+      <c r="AD42" t="inlineStr">
+        <is>
+          <t>[0.16661241143399255]</t>
+        </is>
+      </c>
+      <c r="AE42" t="inlineStr">
+        <is>
+          <t>[-0.9313018770968762]</t>
+        </is>
+      </c>
+      <c r="AF42" t="inlineStr">
+        <is>
+          <t>[0.20795886660168456]</t>
+        </is>
+      </c>
+      <c r="AG42" t="inlineStr">
+        <is>
+          <t>[-3.320966428455904]</t>
+        </is>
+      </c>
+      <c r="AH42" t="inlineStr">
+        <is>
+          <t>[0.3216957710760588]</t>
+        </is>
+      </c>
+      <c r="AI42" t="inlineStr">
+        <is>
+          <t>[-1.5540931176336255]</t>
+        </is>
+      </c>
+      <c r="AJ42" t="inlineStr">
+        <is>
+          <t>[0.20930508773769826]</t>
+        </is>
+      </c>
+      <c r="AK42" t="inlineStr">
+        <is>
+          <t>[-0.8852475696602577]</t>
+        </is>
+      </c>
+      <c r="AL42" t="inlineStr">
+        <is>
+          <t>[0.20010521699344766]</t>
+        </is>
+      </c>
+      <c r="AM42" t="inlineStr">
+        <is>
+          <t>[-2.9194530746403418]</t>
+        </is>
+      </c>
+      <c r="AN42" t="inlineStr">
+        <is>
+          <t>[0.3010424106148203]</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>model_128_64_32_1</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>[128, 64, 32]</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>[[[0.01979999989271164, -0.020899999886751175, 0.04690000042319298, 0.05649999901652336, 0.05119999870657921, -0.12319999933242798, 0.017400000244379044, 0.01510000042617321, -0.01759999990463257, 0.030300000682473183, -0.039000000804662704, -0.014499999582767487, 0.03610000014305115, 0.09679999947547913, -0.0632999986410141, 0.003100000089034438, -0.010999999940395355, -0.0006000000284984708, 0.009399999864399433, 0.00570000009611249, -0.03370000049471855, -0.07819999754428864, -0.08079999685287476, 0.07209999859333038, 0.03180000185966492, -0.039500001817941666, 0.04800000041723251, -0.0617000013589859, 0.14569999277591705, -0.03849999979138374, -0.019700000062584877, 0.003700000001117587, -0.012799999676644802, 0.02979999966919422, -0.010999999940395355, -0.023900000378489494, -0.02449999935925007, 0.014000000432133675, -0.05990000069141388, -0.028300000354647636, 0.032099999487400055, -0.0835999995470047, -0.06310000270605087, -0.0348999984562397, 0.05040000006556511, -0.029600000008940697, 0.026799999177455902, -0.005100000184029341, -0.12250000238418579, 0.03200000151991844, -0.028999999165534973, 0.0731000006198883, 0.017999999225139618, -0.03880000114440918, 0.07970000058412552, -0.007000000216066837, 0.031300000846385956, -0.03139999881386757, 0.050599999725818634, 0.06360000371932983, -0.04699999839067459, 0.028300000354647636, 0.056699998676776886, -0.07150000333786011, -0.09989999979734421, 0.006500000134110451, -0.049400001764297485, 0.02630000002682209, -0.010700000450015068, -0.07890000194311142, 0.10100000351667404, -0.03750000149011612, -0.08540000021457672, 0.07190000265836716, 0.05290000140666962, 0.017999999225139618, 0.026200000196695328, 0.04619999974966049, -0.05559999868273735, 0.0210999995470047, -0.01590000092983246, 0.07689999788999557, 0.05220000073313713, 0.025200000032782555, 0.10400000214576721, -0.0284000001847744, 0.0005000000237487257, -0.05040000006556511, -0.094200000166893, 0.009399999864399433, 0.0364999994635582, -0.06710000336170197, 0.00559999980032444, -0.10379999876022339, 0.07909999787807465, -0.015599999576807022, 0.09070000052452087, 0.008700000122189522, -0.023000000044703484, 0.031599998474121094, 0.04809999838471413, 0.0835999995470047, 0.01640000008046627, 0.043800000101327896, -0.02879999950528145, -0.014600000344216824, 0.023600000888109207, 0.002899999963119626, -0.05040000006556511, 0.05000000074505806, -0.03449999913573265, -0.019500000402331352, -0.01889999955892563, -0.009499999694526196, 0.03790000081062317, -0.004800000227987766, -0.06629999727010727, -0.05990000069141388, 0.019500000402331352, 0.0771000012755394, -0.051899999380111694, 0.08720000088214874, -0.03909999877214432, -0.049300000071525574, 0.008500000461935997, -0.0737999975681305, -0.01730000041425228, -0.04349999874830246], [0.08550000190734863, 0.06120000034570694, 0.04780000075697899, 0.006500000134110451, -0.028300000354647636, -0.08110000193119049, -0.052299998700618744, -0.0640999972820282, 0.020800000056624413, -0.007799999788403511, 0.02199999988079071, -0.0071000000461936, -0.0284000001847744, -0.08789999783039093, 0.0017999999690800905, -0.016699999570846558, -0.0284000001847744, -0.07460000365972519, -0.05310000106692314, -0.028699999675154686, 0.0544000007212162, 0.041600000113248825, 0.019600000232458115, 0.021800000220537186, -0.05310000106692314, 0.02810000069439411, -0.013899999670684338, -0.02070000022649765, 0.0031999999191612005, -0.06729999929666519, 0.03150000050663948, -0.0008999999845400453, -0.03610000014305115, -0.005100000184029341, 0.03750000149011612, -0.00430000014603138, -0.0689999982714653, -0.05299999937415123, 0.09290000051259995, 0.017799999564886093, -0.054499998688697815, 0.007899999618530273, 0.05350000038743019, 0.01889999955892563, 0.01269999984651804, 0.014399999752640724, -0.008999999612569809, 0.03590000048279762, -0.04910000041127205, -0.061900001019239426, -0.006200000178068876, -0.0284000001847744, -0.005799999926239252, -0.09480000287294388, -0.06880000233650208, -0.09839999675750732, 0.014700000174343586, 0.08150000125169754, 0.06889999657869339, -0.07959999889135361, 0.05299999937415123, -0.013299999758601189, 0.03750000149011612, 0.04399999976158142, 0.08150000125169754, 0.06270000338554382, -0.008299999870359898, 0.01549999974668026, 0.0017000000225380063, -0.02239999920129776, -0.04050000011920929, -0.027000000700354576, -0.08240000158548355, -0.05040000006556511, 0.03139999881386757, 0.05719999969005585, 0.04309999942779541, 0.04479999840259552, -0.01850000023841858, 0.0738999992609024, -0.04479999840259552, 0.03269999846816063, -0.03959999978542328, -0.07020000368356705, 0.04129999876022339, 0.10819999873638153, -0.0272000003606081, -0.06279999762773514, -0.03889999911189079, 0.0828000009059906, 0.05270000174641609, 0.024900000542402267, -0.05079999938607216, -0.07769999653100967, -0.07289999723434448, 0.017000000923871994, -0.08510000258684158, -0.04960000142455101, -0.011800000444054604, 0.08110000193119049, 0.027300000190734863, 0.030700000002980232, -0.011300000362098217, 0.01549999974668026, 0.007400000002235174, -0.044599998742341995, 0.07500000298023224, -0.01889999955892563, -0.05590000003576279, 0.03240000084042549, 0.05079999938607216, 0.08720000088214874, -0.07329999655485153, 0.030300000682473183, 0.03959999978542328, 0.0013000000035390258, 0.02810000069439411, -0.030899999663233757, -0.10530000180006027, -0.03350000083446503, 0.0421999990940094, -0.08380000293254852, -0.03229999914765358, -0.007899999618530273, -0.04320000112056732, 0.039400000125169754, 0.010900000110268593, -0.07999999821186066]], [[0.1736000031232834, 0.07769999653100967, -0.03539999946951866, 0.08649999648332596, -0.032099999487400055, -0.04320000112056732, 0.16920000314712524, 0.11079999804496765, -0.05009999871253967, 0.051500000059604645, -0.07370000332593918, -0.09109999984502792, -0.06459999829530716, -0.0044999998062849045, -0.010300000198185444, -0.15559999644756317, 0.023800000548362732, -0.06530000269412994, 0.02630000002682209, -0.0357000008225441, -0.1404000073671341, 0.1599999964237213, -0.03480000048875809, -0.014600000344216824, -0.04430000111460686, -0.03840000182390213, -0.14499999582767487, -0.032999999821186066, -0.03869999945163727, -0.0203000009059906, 0.18310000002384186, -0.06830000132322311, -0.09719999879598618, 0.15129999816417694, 0.05249999836087227, 0.06629999727010727, 0.15219999849796295, 0.2125999927520752, 0.07370000332593918, -0.06800000369548798, 0.042399998754262924, -0.05290000140666962, -0.005499999970197678, 0.10339999943971634, -0.11680000275373459, -0.009700000286102295, -0.13109999895095825, -0.06769999861717224, 0.09510000050067902, -0.07000000029802322, 0.03550000116229057, -0.053599998354911804, -0.06589999794960022, -0.04619999974966049, -0.035100001841783524, 0.07289999723434448, -0.028200000524520874, -0.00039999998989515007, 0.002899999963119626, -0.21950000524520874, -0.03220000118017197, 0.007499999832361937, 0.012900000438094139, 0.09290000051259995, 0.03739999979734421, 0.16329999268054962, 0.18770000338554382, 0.16329999268054962, 0.03920000046491623, -0.0551999993622303, -0.04650000110268593, 0.019300000742077827, -0.10260000079870224, 0.17960000038146973, -0.00989999994635582, -0.028200000524520874, 0.08250000327825546, 0.01720000058412552, -0.17589999735355377, 0.14499999582767487, 0.14480000734329224, 0.03889999911189079, -0.01720000058412552, -0.08229999989271164, -0.07509999722242355, -0.026499999687075615, 0.022199999541044235, -0.0568000003695488, -0.16899999976158142, -0.012000000104308128, -0.09619999676942825, 0.062199998646974564, 0.029100000858306885, 0.16019999980926514, -0.09380000084638596, 0.0689999982714653, 0.014000000432133675, 0.04259999841451645, 0.12839999794960022, 0.06019999831914902, 0.026200000196695328, 0.025800000876188278, -0.05270000174641609, 0.08429999649524689, 0.054999999701976776, 0.07460000365972519, -0.0729999989271164, 0.06989999860525131, 0.09619999676942825, 0.056299999356269836, -0.14509999752044678, 0.04010000079870224, 0.016100000590085983, -0.09520000219345093, -0.0406000018119812, -0.03530000150203705, -0.06369999796152115, -0.05249999836087227, 0.06129999831318855, -0.04410000145435333, -0.00930000003427267, 0.027899999171495438, 0.09889999777078629, -0.17100000381469727, -0.06449999660253525, 0.09279999881982803, 0.006000000052154064, -0.008899999782443047], [0.11270000040531158, -0.041200000792741776, 0.07180000096559525, -0.021800000220537186, 0.1145000010728836, -0.010999999940395355, 0.013899999670684338, -0.13079999387264252, -0.016100000590085983, -0.05000000074505806, 0.056699998676776886, 0.02459999918937683, 0.027499999850988388, 0.062300000339746475, -0.01730000041425228, 0.02879999950528145, 0.13169999420642853, -0.0007999999797903001, -0.010200000368058681, 0.06340000033378601, 0.0966000035405159, -0.05510000139474869, -0.10580000281333923, -0.04729999974370003, -0.041600000113248825, -0.08869999647140503, 0.01979999989271164, 0.08269999921321869, 0.25839999318122864, 0.05649999901652336, -0.009700000286102295, -0.061799999326467514, 0.023900000378489494, -0.052400000393390656, -0.1200999990105629, 0.04619999974966049, 0.013100000098347664, 0.09000000357627869, 0.17100000381469727, 0.026799999177455902, -0.16339999437332153, 0.0649000033736229, -0.021400000900030136, -0.07829999923706055, -0.0478999987244606, 0.024900000542402267, -0.08190000057220459, 0.05689999833703041, 0.12520000338554382, -0.1468999981880188, -0.07320000231266022, 0.07999999821186066, 0.09189999848604202, -0.0414000004529953, -0.07490000128746033, -0.1103999987244606, -0.1421000063419342, 0.03700000047683716, -0.11420000344514847, 0.049300000071525574, -0.0723000019788742, -0.051899999380111694, -0.11029999703168869, 0.0778999999165535, 0.09849999845027924, 0.06689999997615814, 0.1088000014424324, -0.08030000329017639, 0.12489999830722809, -0.014700000174343586, 0.07769999653100967, 0.15790000557899475, -0.07509999722242355, 0.03880000114440918, 0.09690000116825104, -0.11940000206232071, -0.06310000270605087, 0.09799999743700027, -0.07890000194311142, 0.038100000470876694, -0.061400000005960464, -0.021299999207258224, 0.1517000049352646, 0.0007999999797903001, 0.013299999758601189, 0.019300000742077827, -0.04619999974966049, -0.046300001442432404, 0.2126999944448471, -0.1331000030040741, -0.11659999936819077, -0.13899999856948853, 0.04989999905228615, 0.009600000455975533, -0.03229999914765358, 0.15649999678134918, 0.16920000314712524, 0.033900000154972076, -0.01549999974668026, -0.07670000195503235, -0.10000000149011612, 0.18019999563694, -0.12430000305175781, -0.1454000025987625, -0.014999999664723873, -0.023099999874830246, -0.18050000071525574, -0.20970000326633453, 0.053599998354911804, -0.020400000736117363, 0.065700002014637, 0.011699999682605267, -0.022700000554323196, -0.006000000052154064, 0.07050000131130219, 0.03920000046491623, 0.0934000015258789, -0.1356000006198883, 0.003100000089034438, -0.007499999832361937, 0.009100000374019146, 0.05959999933838844, 0.05920000001788139, -0.014600000344216824, 0.08470000326633453, 0.07829999923706055, -0.07859999686479568, 0.04349999874830246], [0.19529999792575836, -0.15199999511241913, -0.07940000295639038, 0.0272000003606081, -0.19439999759197235, -0.06260000169277191, -0.01590000092983246, -0.022299999371170998, 0.06539999693632126, 0.01549999974668026, 0.04540000110864639, -0.08820000290870667, -0.10840000212192535, 0.06449999660253525, 0.12269999831914902, 0.004600000102072954, 0.009999999776482582, 0.010499999858438969, -0.022700000554323196, 0.0044999998062849045, -0.03689999878406525, 0.002400000113993883, -0.04960000142455101, 0.07280000299215317, 0.08219999819993973, 0.0934000015258789, 0.04820000007748604, -0.05990000069141388, 0.04309999942779541, -0.07180000096559525, -0.14149999618530273, 0.010499999858438969, 0.07270000129938126, -0.0706000030040741, 0.08299999684095383, 0.15760000050067902, 0.1453000009059906, -0.13779999315738678, 0.09390000253915787, 0.05860000103712082, 0.026599999517202377, 0.03189999982714653, -0.15970000624656677, 0.2003999948501587, -0.07479999959468842, -0.15809999406337738, -0.028599999845027924, -0.16169999539852142, -0.09319999814033508, -0.09189999848604202, 0.08669999986886978, 0.16910000145435333, -0.03660000115633011, 0.03779999911785126, 0.03660000115633011, 0.055799998342990875, 0.043299999088048935, -0.017899999395012856, -0.0284000001847744, -0.005200000014156103, -0.0860000029206276, 0.1737000048160553, 0.06949999928474426, -0.14800000190734863, -0.10899999737739563, 0.023600000888109207, -0.040800001472234726, -0.0803999975323677, 0.11259999871253967, 0.07980000227689743, -0.14100000262260437, 0.002899999963119626, -0.047600001096725464, 0.038100000470876694, 0.1396999955177307, -0.15839999914169312, -0.019899999722838402, -0.1307000070810318, -0.1088000014424324, 0.03350000083446503, 0.0430000014603138, 0.005200000014156103, 0.009499999694526196, 0.07039999961853027, -0.004900000058114529, 0.005400000140070915, 0.10419999808073044, 0.008899999782443047, 0.13619999587535858, 0.1006999984383583, -0.006300000008195639, -0.12540000677108765, -0.19179999828338623, -0.1665000021457672, 0.0005000000237487257, -0.0066999997943639755, -0.0006000000284984708, 0.09769999980926514, 0.10450000315904617, -0.06509999930858612, 0.0044999998062849045, -0.03539999946951866, -0.08950000256299973, 0.1315000057220459, 0.07159999758005142, 0.010200000368058681, -0.04859999939799309, 0.1023000031709671, 0.0019000000320374966, -0.05270000174641609, 0.13050000369548798, 0.012600000016391277, 0.031199999153614044, -0.0729999989271164, -0.025299999862909317, 0.06790000200271606, 0.06129999831318855, -0.005900000222027302, 0.08330000191926956, -0.08410000056028366, 0.0406000018119812, -0.1264999955892563, 0.03819999843835831, 0.09319999814033508, 0.08699999749660492, 0.011599999852478504, 0.0007999999797903001, 0.1378999948501587], [-0.14190000295639038, -0.09489999711513519, 0.11289999634027481, -0.009100000374019146, -0.0746999979019165, -0.02199999988079071, 0.08990000188350677, -0.021800000220537186, 0.012199999764561653, 0.15379999577999115, -0.10419999808073044, -0.04039999842643738, 0.06669999659061432, 0.15719999372959137, 0.03590000048279762, 0.026100000366568565, -0.16990000009536743, -0.09510000050067902, -0.09989999979734421, 0.07069999724626541, 0.10499999672174454, -0.031599998474121094, -0.155799999833107, 0.048500001430511475, -0.04019999876618385, -0.06840000301599503, 0.056299999356269836, -0.031099999323487282, -0.17080000042915344, -0.14869999885559082, 0.18790000677108765, 0.30570000410079956, 0.08739999681711197, -0.1340000033378601, -0.07959999889135361, 0.005200000014156103, 0.05180000141263008, 0.0771000012755394, 0.05220000073313713, -0.10220000147819519, 0.021700000390410423, -0.060600001364946365, -0.005400000140070915, -0.13650000095367432, -0.10520000010728836, -0.010400000028312206, 0.0333000011742115, -0.03709999844431877, -0.133200004696846, 0.0333000011742115, 0.02019999921321869, -0.04309999942779541, -0.14259999990463257, -0.055399999022483826, 0.004699999932199717, 0.11649999767541885, -0.10000000149011612, 0.12039999663829803, -0.11150000244379044, 0.061400000005960464, 0.11739999800920486, 0.1526000052690506, -0.05180000141263008, -0.10279999673366547, -0.10660000145435333, 0.004600000102072954, -0.09210000187158585, 0.05180000141263008, 0.0723000019788742, -0.12880000472068787, 0.0706000030040741, -0.06289999932050705, -0.05550000071525574, -0.00559999980032444, 0.06030000001192093, 0.06459999829530716, -0.1387999951839447, 0.011099999770522118, -0.02160000056028366, 0.02850000001490116, 0.03539999946951866, -0.021199999377131462, -0.016200000420212746, -0.05829999968409538, -0.02630000002682209, -0.047200001776218414, 0.1071000024676323, -0.028999999165534973, 0.06949999928474426, -0.11479999870061874, 0.03669999912381172, 0.04960000142455101, 0.1720999926328659, -0.06340000033378601, -0.07370000332593918, 0.07209999859333038, -0.10819999873638153, 0.06719999760389328, 0.018799999728798866, 0.008100000210106373, 9.999999747378752e-05, -0.04859999939799309, -0.13860000669956207, -0.09719999879598618, -0.06949999928474426, 0.09239999949932098, -0.013799999840557575, -0.008700000122189522, -0.05689999833703041, -0.13089999556541443, 0.0731000006198883, 0.041099999099969864, -0.08470000326633453, -0.01590000092983246, 0.1459999978542328, -0.06989999860525131, -0.12880000472068787, -0.06970000267028809, -0.04780000075697899, -0.02759999968111515, 0.05719999969005585, 0.06419999897480011, 0.13369999825954437, -0.020899999886751175, -0.04729999974370003, 0.061500001698732376, -0.03280000016093254, 0.05779999867081642], [-0.050999999046325684, 0.034299999475479126, 0.007699999958276749, 0.10830000042915344, -0.09880000352859497, 0.061000000685453415, 0.01889999955892563, 0.184000000357627